--- a/SINGLE HADITH CONTENT/BOOK WISE FINAL UPDATED CONTENT/BN/BN_UPODESH.xlsx
+++ b/SINGLE HADITH CONTENT/BOOK WISE FINAL UPDATED CONTENT/BN/BN_UPODESH.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দ্বীন হচ্ছে উপদেশ ও কল্যাণ কামনা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীন হলো কল্যাণ কামনা—আল্লাহ, তাঁর কিতাব, রাসূল, মুসলিম নেতা ও সাধারণ মুসলমানের জন্য।"},"heading":{"title":"দ্বীন হচ্ছে উপদেশ: কল্যাণ কামনার সহজ শিক্ষা","description":"এই হাদিসের মূল বিষয় হলো কল্যাণ কামনা। নবী করীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, দ্বীন হচ্ছে উপদেশ। তিনি কথাটি তিনবার বলেছেন, যা বিষয়টির গুরুত্ব বোঝায়। সাহাবীরা জানতে চেয়েছেন, কার জন্য এই উপদেশ বা নসীহত? উত্তরে তিনি বলেছেন, আল্লাহর জন্য, তাঁর কিতাবের জন্য, তাঁর রাসূলের জন্য, মুসলিম নেতাদের জন্য এবং সাধারণ মুসলমানের জন্য। এখানে উপদেশ মানে শুধু কথা বলা নয়; বরং সত্য, ভালোবাসা ও কল্যাণের মন রাখা। আল্লাহর প্রতি সঠিক বিশ্বাস, কিতাবের মর্যাদা, রাসূলের আনুগত্য, নেতার ভালো চাওয়া এবং মুসলমানদের জন্য ভালো চাওয়া—এসবই দ্বীনের অংশ। তাই দ্বীন হচ্ছে উপদেশ হাদিসটি মুসলিম জীবনে আন্তরিকতার বড় শিক্ষা দেয়।"},"teachings":["দ্বীনের একটি বড় অংশ হলো সবার জন্য সত্যিকারের কল্যাণ কামনা করা।","আল্লাহ, কিতাব ও রাসূলের প্রতি দায়িত্বশীল মন রাখা জরুরি।","মুসলিম নেতা ও সাধারণ মুসলমানদের জন্য ভালো চাওয়া ঈমানি আচরণ।","উপদেশ দিতে হলে আন্তরিকতা ও কল্যাণের মন থাকা দরকার।"],"related_hadiths":[{"id":"55","book_id":"2","label":"Sahih Muslim"},{"id":"4200","book_id":"3","label":"Sunan an-Nasai"},{"id":"4৯66","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দ্বীন হচ্ছে উপদেশ ও কল্যাণ কামনা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীন হলো কল্যাণ কামনা—আল্লাহ, তাঁর কিতাব, রাসূল, মুসলিম নেতা ও সাধারণ মুসলমানের জন্য।"},"heading":{"title":"দ্বীন হচ্ছে উপদেশ: কল্যাণ কামনার সহজ শিক্ষা","description":"এই হাদিসের মূল বিষয় হলো কল্যাণ কামনা। নবী করীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, দ্বীন হচ্ছে উপদেশ। তিনি কথাটি তিনবার বলেছেন, যা বিষয়টির গুরুত্ব বোঝায়। সাহাবীরা জানতে চেয়েছেন, কার জন্য এই উপদেশ বা নসীহত? উত্তরে তিনি বলেছেন, আল্লাহর জন্য, তাঁর কিতাবের জন্য, তাঁর রাসূলের জন্য, মুসলিম নেতাদের জন্য এবং সাধারণ মুসলমানের জন্য। এখানে উপদেশ মানে শুধু কথা বলা নয়; বরং সত্য, ভালোবাসা ও কল্যাণের মন রাখা। আল্লাহর প্রতি সঠিক বিশ্বাস, কিতাবের মর্যাদা, রাসূলের আনুগত্য, নেতার ভালো চাওয়া এবং মুসলমানদের জন্য ভালো চাওয়া—এসবই দ্বীনের অংশ। তাই দ্বীন হচ্ছে উপদেশ হাদিসটি মুসলিম জীবনে আন্তরিকতার বড় শিক্ষা দেয়।"},"teachings":["দ্বীনের একটি বড় অংশ হলো সবার জন্য সত্যিকারের কল্যাণ কামনা করা।","আল্লাহ, কিতাব ও রাসূলের প্রতি দায়িত্বশীল মন রাখা জরুরি।","মুসলিম নেতা ও সাধারণ মুসলমানদের জন্য ভালো চাওয়া ঈমানি আচরণ।","উপদেশ দিতে হলে আন্তরিকতা ও কল্যাণের মন থাকা দরকার।"],"related_hadiths":[{"id":"55","book_id":"2","label":"Sahih Muslim"},{"id":"4200","book_id":"3","label":"Sunan an-Nasai"},{"id":"4966","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কালিমার ওজন ও আল্লাহর নামের মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. নিরানব্বই দফতরের বিপরীতে কালিমার ছোট কাগজ ভারী হবে; আল্লাহর নামের মর্যাদা বোঝায়।"},"heading":{"title":"কালিমার ওজন: নিরানব্বই দফতর ও ছোট কাগজের হাদিস","description":"এই হাদিসে কিয়ামতের দিন এক ব্যক্তির হিসাবের কথা এসেছে। তার আমলনামা নিরানব্বইটি বড় দফতরে খোলা হবে, প্রতিটি দফতর দৃষ্টিসীমা পর্যন্ত বিস্তৃত। আল্লাহ তাকে জিজ্ঞেস করবেন, সে কি এগুলোর কিছু অস্বীকার করতে পারে বা ফেরেশতারা কি তার প্রতি যুলুম করেছে। সে বলবে, না। এরপর আল্লাহ বলবেন, তার একটি নেকী আছে এবং আজ তার প্রতি যুলুম করা হবে না। তারপর একটি ছোট কাগজ বের হবে, যাতে কালিমার সাক্ষ্য লেখা থাকবে। দফতর এক পাল্লায় আর কালিমার কাগজ অন্য পাল্লায় রাখা হলে কালিমার পাল্লা ভারী হবে। এই হাদিস কালিমার মর্যাদা, আল্লাহর ন্যায়বিচার এবং তাওহীদের গুরুত্ব শেখায়।"},"teachings":["কিয়ামতের হিসাব আল্লাহর ন্যায়বিচারের সঙ্গে হবে।","কালিমার সাক্ষ্য তাওহীদের বড় মর্যাদা বোঝায়।","ফেরেশতাদের লেখা আমলনামা অস্বীকার করা যাবে না।","আল্লাহর নামের মর্যাদা মানুষের হিসাবের চেয়ে বড়।"],"related_hadiths":[{"id":"263৯","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"4300","book_id":"6","label":"Sunan Ibn Majah"},{"id":"555৯","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কালিমার ওজন ও আল্লাহর নামের মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. নিরানব্বই দফতরের বিপরীতে কালিমার ছোট কাগজ ভারী হবে; আল্লাহর নামের মর্যাদা বোঝায়।"},"heading":{"title":"কালিমার ওজন: নিরানব্বই দফতর ও ছোট কাগজের হাদিস","description":"এই হাদিসে কিয়ামতের দিন এক ব্যক্তির হিসাবের কথা এসেছে। তার আমলনামা নিরানব্বইটি বড় দফতরে খোলা হবে, প্রতিটি দফতর দৃষ্টিসীমা পর্যন্ত বিস্তৃত। আল্লাহ তাকে জিজ্ঞেস করবেন, সে কি এগুলোর কিছু অস্বীকার করতে পারে বা ফেরেশতারা কি তার প্রতি যুলুম করেছে। সে বলবে, না। এরপর আল্লাহ বলবেন, তার একটি নেকী আছে এবং আজ তার প্রতি যুলুম করা হবে না। তারপর একটি ছোট কাগজ বের হবে, যাতে কালিমার সাক্ষ্য লেখা থাকবে। দফতর এক পাল্লায় আর কালিমার কাগজ অন্য পাল্লায় রাখা হলে কালিমার পাল্লা ভারী হবে। এই হাদিস কালিমার মর্যাদা, আল্লাহর ন্যায়বিচার এবং তাওহীদের গুরুত্ব শেখায়।"},"teachings":["কিয়ামতের হিসাব আল্লাহর ন্যায়বিচারের সঙ্গে হবে।","কালিমার সাক্ষ্য তাওহীদের বড় মর্যাদা বোঝায়।","ফেরেশতাদের লেখা আমলনামা অস্বীকার করা যাবে না।","আল্লাহর নামের মর্যাদা মানুষের হিসাবের চেয়ে বড়।"],"related_hadiths":[{"id":"2639","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"4300","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5559","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রাতের ভোগ-বিলাস ও হারাম বিনোদনের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য-পানীয় ও আনন্দ-প্রমোদের মধ্যে ডুবে থাকা কিছু লোকের ভয়াবহ রূপান্তর নিয়ে সতর্কতা।"},"heading":{"title":"ভোগ-বিলাস, মদ ও বিনোদনের ভয়াবহ পরিণতি সম্পর্কে হাদিস","description":"এই হাদিসে বলা হয়েছে, উম্মতের কিছু লোক নানা খাদ্য-পানীয় ও আনন্দ-প্রমোদের মধ্যে রাত কাটাবে। এরপর তাদের সকাল হবে শূকর ও বানরের আকৃতিতে রূপান্তরিত হয়ে। দেওয়া ব্যাখ্যায় বলা হয়েছে, এক শ্রেণীর অর্থশালী মানুষ নানা ধরনের মদ ও পানীয়ের ব্যবস্থা করে ভোগ-বিলাসে ডুবে থাকবে এবং নায়িকা, মদ ও বাদ্যযন্ত্রের মাধ্যমে রাত কাটাবে। হাদিসের মূল শিক্ষা হলো, সম্পদ ও বিনোদন যেন মানুষকে হালাল-হারামের সীমা ভুলিয়ে না দেয়। দুনিয়ার আরাম যদি আল্লাহর অবাধ্যতা, নেশা ও অশ্লীলতার পথে নেয়, তবে তা মুমিনের জন্য বিপদের কারণ। তাই আনন্দেও সংযম, লজ্জা ও আল্লাহভীতি থাকা দরকার। তাই দুনিয়ার আরামকে নিয়ন্ত্রণে রাখা এবং আখিরাতের জবাবদিহি মনে রাখা এই হাদিসের বড় শিক্ষা।"},"teachings":["ভোগ-বিলাসে ডুবে হারামকে স্বাভাবিক করা বিপজ্জনক।","মদ, নায়িকা ও বাদ্যযন্ত্রের পরিবেশ থেকে সতর্ক থাকা দরকার।","সম্পদ মানুষকে আল্লাহভীতি ভুলিয়ে দিলে তা ক্ষতির কারণ হতে পারে।","আনন্দ ও বিনোদনেও হালাল-হারামের সীমা মানতে হবে।"],"related_hadiths":[{"id":"55৯0","book_id":"1","label":"Sahih Bukhari"},{"id":"4৯24","book_id":"4","label":"Sunan Abu Dawud"},{"id":"৮0","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রাতের ভোগ-বিলাস ও হারাম বিনোদনের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য-পানীয় ও আনন্দ-প্রমোদের মধ্যে ডুবে থাকা কিছু লোকের ভয়াবহ রূপান্তর নিয়ে সতর্কতা।"},"heading":{"title":"ভোগ-বিলাস, মদ ও বিনোদনের ভয়াবহ পরিণতি সম্পর্কে হাদিস","description":"এই হাদিসে বলা হয়েছে, উম্মতের কিছু লোক নানা খাদ্য-পানীয় ও আনন্দ-প্রমোদের মধ্যে রাত কাটাবে। এরপর তাদের সকাল হবে শূকর ও বানরের আকৃতিতে রূপান্তরিত হয়ে। দেওয়া ব্যাখ্যায় বলা হয়েছে, এক শ্রেণীর অর্থশালী মানুষ নানা ধরনের মদ ও পানীয়ের ব্যবস্থা করে ভোগ-বিলাসে ডুবে থাকবে এবং নায়িকা, মদ ও বাদ্যযন্ত্রের মাধ্যমে রাত কাটাবে। হাদিসের মূল শিক্ষা হলো, সম্পদ ও বিনোদন যেন মানুষকে হালাল-হারামের সীমা ভুলিয়ে না দেয়। দুনিয়ার আরাম যদি আল্লাহর অবাধ্যতা, নেশা ও অশ্লীলতার পথে নেয়, তবে তা মুমিনের জন্য বিপদের কারণ। তাই আনন্দেও সংযম, লজ্জা ও আল্লাহভীতি থাকা দরকার। তাই দুনিয়ার আরামকে নিয়ন্ত্রণে রাখা এবং আখিরাতের জবাবদিহি মনে রাখা এই হাদিসের বড় শিক্ষা।"},"teachings":["ভোগ-বিলাসে ডুবে হারামকে স্বাভাবিক করা বিপজ্জনক।","মদ, নায়িকা ও বাদ্যযন্ত্রের পরিবেশ থেকে সতর্ক থাকা দরকার।","সম্পদ মানুষকে আল্লাহভীতি ভুলিয়ে দিলে তা ক্ষতির কারণ হতে পারে।","আনন্দ ও বিনোদনেও হালাল-হারামের সীমা মানতে হবে।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"4924","book_id":"4","label":"Sunan Abu Dawud"},{"id":"80","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ ও বাদ্যযন্ত্রের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. মদের নাম বদলে পান করা, গায়িকা ও বাদ্যযন্ত্রকে সম্মান করা—এসব কাজের ভয়াবহ পরিণতি এই হাদিসে সতর্ক করা হয়েছে।"},"heading":{"title":"মদ ও বাদ্যযন্ত্র সম্পর্কে হাদিস: নাম বদলালেও পাপ বদলায় না","description":"এই হাদিসের মূল শিক্ষা হলো, হারাম জিনিসের নাম বদলালে তা হালাল হয়ে যায় না। নবী করীম সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তাঁর উম্মতের কিছু মানুষ মদ পান করবে, কিন্তু সেটির অন্য নাম রাখবে। অর্থাৎ বাহ্যিক নাম পাল্টালেও কাজের আসল রূপ পাল্টাবে না। হাদিসে আরও এসেছে, কিছু নেতাকে গায়িকা ও বাদ্যযন্ত্র দিয়ে সম্মান করা হবে। এতে বোঝা যায়, নেতৃত্ব ও সমাজ যখন পাপকে বিনোদন বা মর্যাদার বিষয় বানায়, তখন তা বড় বিপদের কারণ হয়। মদ, গান-বাজনা, অশ্লীলতা ও খারাপ সংস্কৃতির দিকে ঝুঁকে পড়া এখানে কঠোরভাবে সতর্ক করা হয়েছে। তাই একজন মুসলিমের জন্য প্রয়োজন হলো, কাজের নাম নয়, কাজের আসল হুকুম ও ফল নিয়ে ভাবা।"},"teachings":["মদের নাম বদলালেও মদ্যপানের পাপ বদলায় না।","নেতা ও দায়িত্বশীলদের পাপাচার সমাজে বড় ক্ষতির কারণ হতে পারে।","গায়িকা ও বাদ্যযন্ত্রকে সম্মানের মাধ্যম বানানো থেকে সতর্ক থাকা উচিত।","হারামকে সুন্দর নামে চালু করার প্রবণতা ঈমানের জন্য ক্ষতিকর।"],"related_hadiths":[{"id":"2475","book_id":"1","label":"Sahih Bukhari"},{"id":"6772","book_id":"1","label":"Sahih Bukhari"},{"id":"1৮৯৮","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ ও বাদ্যযন্ত্রের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. মদের নাম বদলে পান করা, গায়িকা ও বাদ্যযন্ত্রকে সম্মান করা—এসব কাজের ভয়াবহ পরিণতি এই হাদিসে সতর্ক করা হয়েছে।"},"heading":{"title":"মদ ও বাদ্যযন্ত্র সম্পর্কে হাদিস: নাম বদলালেও পাপ বদলায় না","description":"এই হাদিসের মূল শিক্ষা হলো, হারাম জিনিসের নাম বদলালে তা হালাল হয়ে যায় না। নবী করীম সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তাঁর উম্মতের কিছু মানুষ মদ পান করবে, কিন্তু সেটির অন্য নাম রাখবে। অর্থাৎ বাহ্যিক নাম পাল্টালেও কাজের আসল রূপ পাল্টাবে না। হাদিসে আরও এসেছে, কিছু নেতাকে গায়িকা ও বাদ্যযন্ত্র দিয়ে সম্মান করা হবে। এতে বোঝা যায়, নেতৃত্ব ও সমাজ যখন পাপকে বিনোদন বা মর্যাদার বিষয় বানায়, তখন তা বড় বিপদের কারণ হয়। মদ, গান-বাজনা, অশ্লীলতা ও খারাপ সংস্কৃতির দিকে ঝুঁকে পড়া এখানে কঠোরভাবে সতর্ক করা হয়েছে। তাই একজন মুসলিমের জন্য প্রয়োজন হলো, কাজের নাম নয়, কাজের আসল হুকুম ও ফল নিয়ে ভাবা।"},"teachings":["মদের নাম বদলালেও মদ্যপানের পাপ বদলায় না।","নেতা ও দায়িত্বশীলদের পাপাচার সমাজে বড় ক্ষতির কারণ হতে পারে।","গায়িকা ও বাদ্যযন্ত্রকে সম্মানের মাধ্যম বানানো থেকে সতর্ক থাকা উচিত।","হারামকে সুন্দর নামে চালু করার প্রবণতা ঈমানের জন্য ক্ষতিকর।"],"related_hadiths":[{"id":"2475","book_id":"1","label":"Sahih Bukhari"},{"id":"6772","book_id":"1","label":"Sahih Bukhari"},{"id":"1898","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পথভ্রষ্ট নেতা ও ঈমানের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ভ্রান্ত নেতা, ভুল আলেম, মূর্তিপূজা ও বিজাতিদের সাথে মিশে যাওয়ার ফিতনা থেকে উম্মতকে সতর্ক করা হয়েছে।"},"heading":{"title":"পথভ্রষ্ট নেতা ও আলেম সম্পর্কে হাদিস: ঈমান রক্ষার সতর্কতা","description":"এই হাদিসে নবী করীম সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম উম্মতের জন্য এক বড় ভয় প্রকাশ করেছেন। তিনি বলেছেন, তিনি বেশি ভয় করেন নেতা ও এক শ্রেণীর আলেম সমাজকে। কারণ মানুষ সাধারণত নেতা ও আলেমদের কথা দেখে ও শুনে পথ নেয়। তারা যদি ভুল পথে ডাকে, তাহলে অনেক মানুষ ক্ষতিগ্রস্ত হতে পারে। হাদিসে আরও বলা হয়েছে, উম্মতের কিছু লোক মূর্তিপূজা করবে এবং কিছু লোক মুশরিকদের সাথে মিশে যাবে। এখানে মূল শিক্ষা হলো, ঈমান, তাওহীদ ও ইসলামী পরিচয়কে হালকা করে দেখা যাবে না। কারও পদ, নাম বা বাহ্যিক সম্মান দেখে অন্ধভাবে অনুসরণ না করে সত্য-ভিত্তিক দীন মানতে হবে।"},"teachings":["ভ্রান্ত নেতা ও ভুল আলেম মানুষের দীনী জীবনে বড় ক্ষতির কারণ হতে পারে।","তাওহীদ রক্ষা করা একজন মুসলিমের মূল দায়িত্ব।","অন্ধ অনুসরণ নয়, সত্য ও সঠিক দীন বুঝে চলা দরকার।","মূর্তিপূজা ও শিরকের পথ থেকে দূরে থাকা জরুরি।"],"related_hadiths":[{"id":"5406","book_id":"14","label":"Mishkat al-Masabih"},{"id":"70৮4","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পথভ্রষ্ট নেতা ও ঈমানের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ভ্রান্ত নেতা, ভুল আলেম, মূর্তিপূজা ও বিজাতিদের সাথে মিশে যাওয়ার ফিতনা থেকে উম্মতকে সতর্ক করা হয়েছে।"},"heading":{"title":"পথভ্রষ্ট নেতা ও আলেম সম্পর্কে হাদিস: ঈমান রক্ষার সতর্কতা","description":"এই হাদিসে নবী করীম সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম উম্মতের জন্য এক বড় ভয় প্রকাশ করেছেন। তিনি বলেছেন, তিনি বেশি ভয় করেন নেতা ও এক শ্রেণীর আলেম সমাজকে। কারণ মানুষ সাধারণত নেতা ও আলেমদের কথা দেখে ও শুনে পথ নেয়। তারা যদি ভুল পথে ডাকে, তাহলে অনেক মানুষ ক্ষতিগ্রস্ত হতে পারে। হাদিসে আরও বলা হয়েছে, উম্মতের কিছু লোক মূর্তিপূজা করবে এবং কিছু লোক মুশরিকদের সাথে মিশে যাবে। এখানে মূল শিক্ষা হলো, ঈমান, তাওহীদ ও ইসলামী পরিচয়কে হালকা করে দেখা যাবে না। কারও পদ, নাম বা বাহ্যিক সম্মান দেখে অন্ধভাবে অনুসরণ না করে সত্য-ভিত্তিক দীন মানতে হবে।"},"teachings":["ভ্রান্ত নেতা ও ভুল আলেম মানুষের দীনী জীবনে বড় ক্ষতির কারণ হতে পারে।","তাওহীদ রক্ষা করা একজন মুসলিমের মূল দায়িত্ব।","অন্ধ অনুসরণ নয়, সত্য ও সঠিক দীন বুঝে চলা দরকার।","মূর্তিপূজা ও শিরকের পথ থেকে দূরে থাকা জরুরি।"],"related_hadiths":[{"id":"5406","book_id":"14","label":"Mishkat al-Masabih"},{"id":"7084","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর মানুষের কঠিন সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. বৃদ্ধ যিনাকারী, মিথ্যাবাদী শাসক ও অহঙ্কারী দরিদ্র ব্যক্তির জন্য কিয়ামতের কঠিন সতর্কতা এসেছে।"},"heading":{"title":"তিন শ্রেণীর মানুষের ব্যাপারে হাদিস: যিনা, মিথ্যা ও অহঙ্কারের ভয়াবহতা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তিন ধরনের মানুষের ব্যাপারে কঠিন সতর্কতা দিয়েছেন। তারা হলো বৃদ্ধ যিনাকারী, মিথ্যাবাদী শাসক এবং অহঙ্কারী দরিদ্র ব্যক্তি। হাদিসে বলা হয়েছে, কিয়ামতের দিন আল্লাহ তাদের সাথে কথা বলবেন না, তাদের পবিত্র করবেন না; অন্য বর্ণনায় আছে, তাদের দিকে তাকাবেন না এবং তাদের জন্য যন্ত্রণাদায়ক শাস্তি রয়েছে। এখানে তিনটি পাপ খুব স্পষ্ট: যিনা, মিথ্যা এবং অহঙ্কার। বয়স, পদ বা অবস্থা কোনো মানুষকে গুনাহ থেকে নিরাপদ করে না। বিশেষ করে শাসকের মিথ্যা মানুষের উপর বড় প্রভাব ফেলে। আবার দরিদ্র হয়েও অহঙ্কার করা দেখায় যে অহঙ্কার শুধু সম্পদের কারণে নয়, মনের রোগ হিসেবেও থাকতে পারে।"},"teachings":["যিনা, মিথ্যা ও অহঙ্কার—তিনটি কাজই গুরুতর পাপ।","ক্ষমতাবান ব্যক্তির মিথ্যা সমাজে বড় ক্ষতি আনতে পারে।","দারিদ্র্য অহঙ্কার থেকে নিরাপত্তা দেয় না; মনকে বিনয়ী রাখতে হয়।","কিয়ামতের জবাবদিহির কথা মনে রাখা গুনাহ থেকে বাঁচতে সাহায্য করে।"],"related_hadiths":[{"id":"1৯4","book_id":"2","label":"Sahih Muslim"},{"id":"2515","book_id":"1","label":"Sahih Bukhari"},{"id":"6772","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর মানুষের কঠিন সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. বৃদ্ধ যিনাকারী, মিথ্যাবাদী শাসক ও অহঙ্কারী দরিদ্র ব্যক্তির জন্য কিয়ামতের কঠিন সতর্কতা এসেছে।"},"heading":{"title":"তিন শ্রেণীর মানুষের ব্যাপারে হাদিস: যিনা, মিথ্যা ও অহঙ্কারের ভয়াবহতা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তিন ধরনের মানুষের ব্যাপারে কঠিন সতর্কতা দিয়েছেন। তারা হলো বৃদ্ধ যিনাকারী, মিথ্যাবাদী শাসক এবং অহঙ্কারী দরিদ্র ব্যক্তি। হাদিসে বলা হয়েছে, কিয়ামতের দিন আল্লাহ তাদের সাথে কথা বলবেন না, তাদের পবিত্র করবেন না; অন্য বর্ণনায় আছে, তাদের দিকে তাকাবেন না এবং তাদের জন্য যন্ত্রণাদায়ক শাস্তি রয়েছে। এখানে তিনটি পাপ খুব স্পষ্ট: যিনা, মিথ্যা এবং অহঙ্কার। বয়স, পদ বা অবস্থা কোনো মানুষকে গুনাহ থেকে নিরাপদ করে না। বিশেষ করে শাসকের মিথ্যা মানুষের উপর বড় প্রভাব ফেলে। আবার দরিদ্র হয়েও অহঙ্কার করা দেখায় যে অহঙ্কার শুধু সম্পদের কারণে নয়, মনের রোগ হিসেবেও থাকতে পারে।"},"teachings":["যিনা, মিথ্যা ও অহঙ্কার—তিনটি কাজই গুরুতর পাপ।","ক্ষমতাবান ব্যক্তির মিথ্যা সমাজে বড় ক্ষতি আনতে পারে।","দারিদ্র্য অহঙ্কার থেকে নিরাপত্তা দেয় না; মনকে বিনয়ী রাখতে হয়।","কিয়ামতের জবাবদিহির কথা মনে রাখা গুনাহ থেকে বাঁচতে সাহায্য করে।"],"related_hadiths":[{"id":"194","book_id":"2","label":"Sahih Muslim"},{"id":"2515","book_id":"1","label":"Sahih Bukhari"},{"id":"6772","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুসলিমের রক্ত ও তিন ব্যতিক্রম","description":"$book_name$ $hadith_number$ - $chapter_name$. মুসলিমের রক্তের মর্যাদা এবং তিন ধরনের অপরাধে শরয়ী দণ্ডের বিষয় এই হাদিসে উল্লেখ করা হয়েছে।"},"heading":{"title":"মুসলিমের রক্তের মর্যাদা: তিন ব্যতিক্রম সম্পর্কে হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম মুসলিমের রক্তের মর্যাদা স্পষ্ট করেছেন। যে ব্যক্তি আল্লাহ ছাড়া কোনো মাবুদ নেই এবং মুহাম্মাদ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম আল্লাহর রাসূল—এই সাক্ষ্য দেয়, তার রক্ত হালাল নয়। তবে তিনটি অপরাধের কথা হাদিসে এসেছে: বিবাহের পর যিনা, আল্লাহ ও তাঁর রাসূলের বিরুদ্ধে যুদ্ধের অবস্থান, এবং কাউকে হত্যা করা। হাদিসে এদের জন্য শরয়ী দণ্ডের কথা বলা হয়েছে। ইসলামী স্কলারদের মতে, এসব দণ্ড ব্যক্তি বা দল নিজের ইচ্ছায় প্রয়োগ করতে পারে না; বিচার, প্রমাণ ও বৈধ কর্তৃপক্ষের মাধ্যমে হয়। এই হাদিস মানুষের জীবনকে সম্মান করতে শেখায় এবং একই সাথে গুরুতর অপরাধের ভয়াবহতা বুঝায়।"},"teachings":["একজন মুসলিমের জীবন ও রক্তের মর্যাদা অনেক বড়।","হত্যা, যিনা ও আল্লাহ-রাসূলের বিরুদ্ধে যুদ্ধ গুরুতর অপরাধ।","শরয়ী দণ্ড ব্যক্তিগত প্রতিশোধের বিষয় নয়; বিচারব্যবস্থার বিষয়।","জীবনের নিরাপত্তা ও ন্যায়বিচার ইসলামের গুরুত্বপূর্ণ শিক্ষা।"],"related_hadiths":[{"id":"6৮7৮","book_id":"1","label":"Sahih Bukhari"},{"id":"6৮7৯","book_id":"1","label":"Sahih Bukhari"},{"id":"3562","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুসলিমের রক্ত ও তিন ব্যতিক্রম","description":"$book_name$ $hadith_number$ - $chapter_name$. মুসলিমের রক্তের মর্যাদা এবং তিন ধরনের অপরাধে শরয়ী দণ্ডের বিষয় এই হাদিসে উল্লেখ করা হয়েছে।"},"heading":{"title":"মুসলিমের রক্তের মর্যাদা: তিন ব্যতিক্রম সম্পর্কে হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম মুসলিমের রক্তের মর্যাদা স্পষ্ট করেছেন। যে ব্যক্তি আল্লাহ ছাড়া কোনো মাবুদ নেই এবং মুহাম্মাদ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম আল্লাহর রাসূল—এই সাক্ষ্য দেয়, তার রক্ত হালাল নয়। তবে তিনটি অপরাধের কথা হাদিসে এসেছে: বিবাহের পর যিনা, আল্লাহ ও তাঁর রাসূলের বিরুদ্ধে যুদ্ধের অবস্থান, এবং কাউকে হত্যা করা। হাদিসে এদের জন্য শরয়ী দণ্ডের কথা বলা হয়েছে। ইসলামী স্কলারদের মতে, এসব দণ্ড ব্যক্তি বা দল নিজের ইচ্ছায় প্রয়োগ করতে পারে না; বিচার, প্রমাণ ও বৈধ কর্তৃপক্ষের মাধ্যমে হয়। এই হাদিস মানুষের জীবনকে সম্মান করতে শেখায় এবং একই সাথে গুরুতর অপরাধের ভয়াবহতা বুঝায়।"},"teachings":["একজন মুসলিমের জীবন ও রক্তের মর্যাদা অনেক বড়।","হত্যা, যিনা ও আল্লাহ-রাসূলের বিরুদ্ধে যুদ্ধ গুরুতর অপরাধ।","শরয়ী দণ্ড ব্যক্তিগত প্রতিশোধের বিষয় নয়; বিচারব্যবস্থার বিষয়।","জীবনের নিরাপত্তা ও ন্যায়বিচার ইসলামের গুরুত্বপূর্ণ শিক্ষা।"],"related_hadiths":[{"id":"6878","book_id":"1","label":"Sahih Bukhari"},{"id":"6879","book_id":"1","label":"Sahih Bukhari"},{"id":"3562","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অর্ধরাতের দোয়া ও ক্ষমার সুযোগ","description":"$book_name$ $hadith_number$ - $chapter_name$. অর্ধরাতে দোয়া, সাহায্য ও সংকটমুক্তির আহ্বান আসে; তবে অশ্লীলতায় লিপ্তদের জন্য কঠিন সতর্কতা আছে।"},"heading":{"title":"অর্ধরাতের দোয়া সম্পর্কে হাদিস: আল্লাহর কাছে ফিরে আসার সময়","description":"এই হাদিসে অর্ধরাতের দোয়া ও ক্ষমা চাওয়ার বড় সুযোগের কথা এসেছে। রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, অর্ধরাতে আকাশের দরজা খোলা হয়। তখন আহ্বান করা হয়—কেউ দোয়া করবে কি, তার দোয়া কবুল করা হবে? কেউ সাহায্য চাইবে কি, তাকে সাহায্য করা হবে? কেউ সংকটে আছে কি, তার সংকট দূর করা হবে? হাদিসে বলা হয়েছে, এ সময় কোনো মুসলমান দোয়া করলে আল্লাহ তার দোয়া কবুল করেন। তবে অশ্লীল কাজে লিপ্ত নারীর ব্যাপারে ব্যতিক্রমের কথা এসেছে। অন্য বর্ণনায় ক্ষমা চাওয়ার কথাও আছে। এই হাদিস আমাদের শেখায়, রাতের নীরব সময়ে আল্লাহর কাছে দোয়া, ইস্তেগফার ও নিজের ভুল থেকে ফিরে আসা খুব গুরুত্বপূর্ণ।"},"teachings":["অর্ধরাত দোয়া ও ইস্তেগফারের গুরুত্বপূর্ণ সময় হিসেবে বর্ণিত হয়েছে।","সংকটে পড়লে আল্লাহর কাছে সাহায্য চাইতে হবে।","অশ্লীল কাজে লিপ্ত থাকা দোয়া ও ক্ষমার পথে বাধা হতে পারে।","নিজের ভুল বুঝে আল্লাহর কাছে ফিরে আসা দরকার।"],"related_hadiths":[{"id":"1145","book_id":"1","label":"Sahih Bukhari"},{"id":"1656","book_id":"2","label":"Sahih Muslim"},{"id":"6৮45","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অর্ধরাতের দোয়া ও ক্ষমার সুযোগ","description":"$book_name$ $hadith_number$ - $chapter_name$. অর্ধরাতে দোয়া, সাহায্য ও সংকটমুক্তির আহ্বান আসে; তবে অশ্লীলতায় লিপ্তদের জন্য কঠিন সতর্কতা আছে।"},"heading":{"title":"অর্ধরাতের দোয়া সম্পর্কে হাদিস: আল্লাহর কাছে ফিরে আসার সময়","description":"এই হাদিসে অর্ধরাতের দোয়া ও ক্ষমা চাওয়ার বড় সুযোগের কথা এসেছে। রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, অর্ধরাতে আকাশের দরজা খোলা হয়। তখন আহ্বান করা হয়—কেউ দোয়া করবে কি, তার দোয়া কবুল করা হবে? কেউ সাহায্য চাইবে কি, তাকে সাহায্য করা হবে? কেউ সংকটে আছে কি, তার সংকট দূর করা হবে? হাদিসে বলা হয়েছে, এ সময় কোনো মুসলমান দোয়া করলে আল্লাহ তার দোয়া কবুল করেন। তবে অশ্লীল কাজে লিপ্ত নারীর ব্যাপারে ব্যতিক্রমের কথা এসেছে। অন্য বর্ণনায় ক্ষমা চাওয়ার কথাও আছে। এই হাদিস আমাদের শেখায়, রাতের নীরব সময়ে আল্লাহর কাছে দোয়া, ইস্তেগফার ও নিজের ভুল থেকে ফিরে আসা খুব গুরুত্বপূর্ণ।"},"teachings":["অর্ধরাত দোয়া ও ইস্তেগফারের গুরুত্বপূর্ণ সময় হিসেবে বর্ণিত হয়েছে।","সংকটে পড়লে আল্লাহর কাছে সাহায্য চাইতে হবে।","অশ্লীল কাজে লিপ্ত থাকা দোয়া ও ক্ষমার পথে বাধা হতে পারে।","নিজের ভুল বুঝে আল্লাহর কাছে ফিরে আসা দরকার।"],"related_hadiths":[{"id":"1145","book_id":"1","label":"Sahih Bukhari"},{"id":"1656","book_id":"2","label":"Sahih Muslim"},{"id":"6845","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যিনা ও গোপন প্রবৃত্তির ভয়","description":"$book_name$ $hadith_number$ - $chapter_name$. যিনা ও গোপন প্রবৃত্তিকে উম্মতের জন্য ভয়ংকর ফিতনা হিসেবে সতর্ক করা হয়েছে।"},"heading":{"title":"যিনা ও গোপন প্রবৃত্তি সম্পর্কে হাদিস: অন্তরের পবিত্রতার শিক্ষা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তিনি উম্মতের জন্য যে বিষয়ে বেশি ভয় করেন তা হলো যিনা ও গোপন প্রবৃত্তি। এখানে যিনা শুধু প্রকাশ্য পাপ নয়, বরং তার পেছনের মনের টান, লুকানো কামনা ও গোপন ইচ্ছার দিকেও ইশারা আছে। মানুষ বাইরে ভালো দেখালেও অন্তরে খারাপ আকাঙ্ক্ষা লালন করতে পারে। তাই শুধু বাহ্যিক আচরণ নয়, অন্তরও ঠিক রাখা দরকার। এই হাদিস আমাদের শেখায়, পাপের আগের ধাপগুলোকে হালকা করে দেখা যাবে না। চোখ, কথা, একাকী আচরণ ও গোপন ইচ্ছার জায়গায় আল্লাহভীতি থাকা জরুরি। যিনা থেকে বাঁচতে হলে গোপন প্রবৃত্তিকেও নিয়ন্ত্রণ করতে হবে।"},"teachings":["যিনা উম্মতের জন্য বড় ফিতনা হিসেবে সতর্ক করা হয়েছে।","গোপন কামনা ও লুকানো প্রবৃত্তি পাপের দিকে নিয়ে যেতে পারে।","বাহ্যিক আচরণের সাথে অন্তরের পবিত্রতাও দরকার।","একাকী অবস্থাতেও আল্লাহভীতি বজায় রাখা জরুরি।"],"related_hadiths":[{"id":"6772","book_id":"1","label":"Sahih Bukhari"},{"id":"6243","book_id":"1","label":"Sahih Bukhari"},{"id":"৮6","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যিনা ও গোপন প্রবৃত্তির ভয়","description":"$book_name$ $hadith_number$ - $chapter_name$. যিনা ও গোপন প্রবৃত্তিকে উম্মতের জন্য ভয়ংকর ফিতনা হিসেবে সতর্ক করা হয়েছে।"},"heading":{"title":"যিনা ও গোপন প্রবৃত্তি সম্পর্কে হাদিস: অন্তরের পবিত্রতার শিক্ষা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তিনি উম্মতের জন্য যে বিষয়ে বেশি ভয় করেন তা হলো যিনা ও গোপন প্রবৃত্তি। এখানে যিনা শুধু প্রকাশ্য পাপ নয়, বরং তার পেছনের মনের টান, লুকানো কামনা ও গোপন ইচ্ছার দিকেও ইশারা আছে। মানুষ বাইরে ভালো দেখালেও অন্তরে খারাপ আকাঙ্ক্ষা লালন করতে পারে। তাই শুধু বাহ্যিক আচরণ নয়, অন্তরও ঠিক রাখা দরকার। এই হাদিস আমাদের শেখায়, পাপের আগের ধাপগুলোকে হালকা করে দেখা যাবে না। চোখ, কথা, একাকী আচরণ ও গোপন ইচ্ছার জায়গায় আল্লাহভীতি থাকা জরুরি। যিনা থেকে বাঁচতে হলে গোপন প্রবৃত্তিকেও নিয়ন্ত্রণ করতে হবে।"},"teachings":["যিনা উম্মতের জন্য বড় ফিতনা হিসেবে সতর্ক করা হয়েছে।","গোপন কামনা ও লুকানো প্রবৃত্তি পাপের দিকে নিয়ে যেতে পারে।","বাহ্যিক আচরণের সাথে অন্তরের পবিত্রতাও দরকার।","একাকী অবস্থাতেও আল্লাহভীতি বজায় রাখা জরুরি।"],"related_hadiths":[{"id":"6772","book_id":"1","label":"Sahih Bukhari"},{"id":"6243","book_id":"1","label":"Sahih Bukhari"},{"id":"86","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দোভাষী ছাড়া রবের সাথে কথা","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে প্রত্যেকে দোভাষী ছাড়া রবের সঙ্গে কথা বলবে; সামনে জাহান্নাম দেখে দান দ্বারা বাঁচতে বলা হয়েছে।"},"heading":{"title":"দোভাষী ছাড়া রবের সাথে কথা ও জাহান্নাম থেকে বাঁচার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তোমাদের প্রত্যেকের সঙ্গে তার রব কথা বলবেন। তার ও রবের মাঝে কোনো দোভাষী থাকবে না এবং এমন কোনো পর্দাও থাকবে না যা তাকে আড়াল করে। সে ডানে তাকিয়ে নিজের আগে পাঠানো আমল ছাড়া কিছু দেখবে না, বামে তাকিয়েও নিজের আমল দেখবে। সামনে তাকালে জাহান্নাম দেখবে। এরপর নবীজি বলেছেন, খেজুরের অর্ধেক অংশ দিয়েও জাহান্নাম থেকে বাঁচার চেষ্টা করো। এই হাদিস কিয়ামতের জবাবদিহি, আমলের গুরুত্ব এবং ছোট দানের মূল্য শেখায়। সামান্য ভালো কাজকেও ছোট মনে করা ঠিক নয়, কারণ আখেরাতে মানুষ নিজের পাঠানো কাজই সামনে পাবে।"},"teachings":["কিয়ামতে প্রত্যেকে নিজের রবের সামনে জবাবদিহি করবে।","মানুষ নিজের পাঠানো আমলই সামনে দেখতে পাবে।","সামান্য দানও জাহান্নাম থেকে বাঁচার চেষ্টা হতে পারে।","আখেরাতের জন্য ভালো কাজ আগে পাঠানো দরকার।"],"related_hadiths":[{"id":"653৯","book_id":"1","label":"Sahih Bukhari"},{"id":"1016","book_id":"2","label":"Sahih Muslim"},{"id":"5550","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দোভাষী ছাড়া রবের সাথে কথা","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে প্রত্যেকে দোভাষী ছাড়া রবের সঙ্গে কথা বলবে; সামনে জাহান্নাম দেখে দান দ্বারা বাঁচতে বলা হয়েছে।"},"heading":{"title":"দোভাষী ছাড়া রবের সাথে কথা ও জাহান্নাম থেকে বাঁচার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তোমাদের প্রত্যেকের সঙ্গে তার রব কথা বলবেন। তার ও রবের মাঝে কোনো দোভাষী থাকবে না এবং এমন কোনো পর্দাও থাকবে না যা তাকে আড়াল করে। সে ডানে তাকিয়ে নিজের আগে পাঠানো আমল ছাড়া কিছু দেখবে না, বামে তাকিয়েও নিজের আমল দেখবে। সামনে তাকালে জাহান্নাম দেখবে। এরপর নবীজি বলেছেন, খেজুরের অর্ধেক অংশ দিয়েও জাহান্নাম থেকে বাঁচার চেষ্টা করো। এই হাদিস কিয়ামতের জবাবদিহি, আমলের গুরুত্ব এবং ছোট দানের মূল্য শেখায়। সামান্য ভালো কাজকেও ছোট মনে করা ঠিক নয়, কারণ আখেরাতে মানুষ নিজের পাঠানো কাজই সামনে পাবে।"},"teachings":["কিয়ামতে প্রত্যেকে নিজের রবের সামনে জবাবদিহি করবে।","মানুষ নিজের পাঠানো আমলই সামনে দেখতে পাবে।","সামান্য দানও জাহান্নাম থেকে বাঁচার চেষ্টা হতে পারে।","আখেরাতের জন্য ভালো কাজ আগে পাঠানো দরকার।"],"related_hadiths":[{"id":"6539","book_id":"1","label":"Sahih Bukhari"},{"id":"1016","book_id":"2","label":"Sahih Muslim"},{"id":"5550","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মায়েয ও গামেদী নারীর খাঁটি তওবা","description":"$book_name$ $hadith_number$ - $chapter_name$. মায়েয ও গামেদী নারীর ঘটনায় পাপের স্বীকারোক্তি, তওবা, বিচার ও শিশুর হকের শিক্ষা এসেছে।"},"heading":{"title":"মায়েয ও গামেদী নারীর তওবা: যিনা, বিচার ও আল্লাহর ক্ষমার শিক্ষা","description":"এই দীর্ঘ হাদিসে মায়েয ইবনে মালেক রাদিয়াল্লাহু আনহু এবং গামেদী গোত্রের এক নারীর ঘটনা এসেছে। মায়েয বারবার রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর কাছে এসে নিজেকে পবিত্র করার কথা বলেন। নবীজি প্রথমে তাকে ফিরে গিয়ে আল্লাহর কাছে ক্ষমা চাইতে ও তওবা করতে বলেন। পরে বিষয়টি যাচাই করা হয়—তিনি পাগল কি না, মদ পান করেছেন কি না, সত্যিই যিনা করেছেন কি না। এরপর রজমের নির্দেশ দেওয়া হয়। গামেদী নারীও তওবার জন্য আসেন। তিনি গর্ভবতী ছিলেন, তাই সন্তান জন্ম ও দুধপানের বিষয় বিবেচনা করা হয়। হাদিসে তওবার মর্যাদা, বিচারপূর্ব যাচাই, শিশুর হক এবং পাপীকে গালি না দেওয়ার শিক্ষা আছে। ইসলামী স্কলারদের মতে, এসব দণ্ড ব্যক্তিগতভাবে প্রয়োগের বিষয় নয়; বৈধ বিচারব্যবস্থার বিষয়।"},"teachings":["খাঁটি তওবা আল্লাহর কাছে বড় মর্যাদার বিষয়।","গুরুতর অভিযোগে যাচাই ছাড়া সিদ্ধান্ত নেওয়া যায় না।","শিশুর হক ও দুধপানের দায়িত্ব বিবেচনা করা হয়েছে।","তওবাকারী মানুষকে গালি দেওয়া উচিত নয়।"],"related_hadiths":[{"id":"355৮","book_id":"14","label":"Mishkat al-Masabih"},{"id":"4353","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6৮24","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মায়েয ও গামেদী নারীর খাঁটি তওবা","description":"$book_name$ $hadith_number$ - $chapter_name$. মায়েয ও গামেদী নারীর ঘটনায় পাপের স্বীকারোক্তি, তওবা, বিচার ও শিশুর হকের শিক্ষা এসেছে।"},"heading":{"title":"মায়েয ও গামেদী নারীর তওবা: যিনা, বিচার ও আল্লাহর ক্ষমার শিক্ষা","description":"এই দীর্ঘ হাদিসে মায়েয ইবনে মালেক রাদিয়াল্লাহু আনহু এবং গামেদী গোত্রের এক নারীর ঘটনা এসেছে। মায়েয বারবার রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর কাছে এসে নিজেকে পবিত্র করার কথা বলেন। নবীজি প্রথমে তাকে ফিরে গিয়ে আল্লাহর কাছে ক্ষমা চাইতে ও তওবা করতে বলেন। পরে বিষয়টি যাচাই করা হয়—তিনি পাগল কি না, মদ পান করেছেন কি না, সত্যিই যিনা করেছেন কি না। এরপর রজমের নির্দেশ দেওয়া হয়। গামেদী নারীও তওবার জন্য আসেন। তিনি গর্ভবতী ছিলেন, তাই সন্তান জন্ম ও দুধপানের বিষয় বিবেচনা করা হয়। হাদিসে তওবার মর্যাদা, বিচারপূর্ব যাচাই, শিশুর হক এবং পাপীকে গালি না দেওয়ার শিক্ষা আছে। ইসলামী স্কলারদের মতে, এসব দণ্ড ব্যক্তিগতভাবে প্রয়োগের বিষয় নয়; বৈধ বিচারব্যবস্থার বিষয়।"},"teachings":["খাঁটি তওবা আল্লাহর কাছে বড় মর্যাদার বিষয়।","গুরুতর অভিযোগে যাচাই ছাড়া সিদ্ধান্ত নেওয়া যায় না।","শিশুর হক ও দুধপানের দায়িত্ব বিবেচনা করা হয়েছে।","তওবাকারী মানুষকে গালি দেওয়া উচিত নয়।"],"related_hadiths":[{"id":"3558","book_id":"14","label":"Mishkat al-Masabih"},{"id":"4353","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6824","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | স্বপ্নে পাপের পরিণতি ও জান্নাতের দৃশ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. মিথ্যা, কুরআন অবহেলা, যিনা ও সুদের পরিণতি এবং মুমিন-শহীদের মর্যাদা স্বপ্নে দেখানো হয়েছে।"},"heading":{"title":"নবীজির স্বপ্নের হাদিস: মিথ্যা, যিনা, সুদ ও কুরআন অবহেলার পরিণতি","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর এক দীর্ঘ স্বপ্নের বর্ণনা আছে। তিনি ফজরের পর সাহাবিদের কাছে স্বপ্ন জানতে চাইতেন এবং আল্লাহর ইচ্ছায় তার ব্যাখ্যা করতেন। এক রাতে তিনি দুইজন ফেরেশতার সাথে বিভিন্ন দৃশ্য দেখেন। এক ব্যক্তির গাল চেরা হচ্ছিল, কারণ সে মিথ্যা বলত এবং তা ছড়িয়ে পড়ত। আরেকজনের মাথা পাথর দিয়ে ভাঙা হচ্ছিল, কারণ সে কুরআন শিখেও রাতে তা থেকে গাফেল ছিল এবং দিনে আমল করত না। তন্দুরের মতো স্থানে উলঙ্গ নারী-পুরুষ ছিল; তারা যিনাকারী। রক্তের নদীতে থাকা ব্যক্তি সুদখোর। পরে তিনি ইবরাহীম আলাইহিস সালাম, শিশুদের, জান্নাতের ঘর এবং শহীদদের ঘর দেখেন। হাদিসটি পাপের পরিণতি ও সৎ জীবনের আশা—দুই দিকই শেখায়।"},"teachings":["মিথ্যা ছড়ানো বড় পাপ এবং এর পরিণতি ভয়াবহ হতে পারে।","কুরআন শিখে অবহেলা করা ও আমল না করা বিপদের কারণ।","যিনা ও সুদ থেকে দূরে থাকার শক্ত সতর্কতা এসেছে।","মুমিন ও শহীদদের জন্য সম্মানের দৃশ্য বর্ণিত হয়েছে।"],"related_hadiths":[{"id":"60৯6","book_id":"1","label":"Sahih Bukhari"},{"id":"6772","book_id":"1","label":"Sahih Bukhari"},{"id":"20৮6","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | স্বপ্নে পাপের পরিণতি ও জান্নাতের দৃশ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. মিথ্যা, কুরআন অবহেলা, যিনা ও সুদের পরিণতি এবং মুমিন-শহীদের মর্যাদা স্বপ্নে দেখানো হয়েছে।"},"heading":{"title":"নবীজির স্বপ্নের হাদিস: মিথ্যা, যিনা, সুদ ও কুরআন অবহেলার পরিণতি","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর এক দীর্ঘ স্বপ্নের বর্ণনা আছে। তিনি ফজরের পর সাহাবিদের কাছে স্বপ্ন জানতে চাইতেন এবং আল্লাহর ইচ্ছায় তার ব্যাখ্যা করতেন। এক রাতে তিনি দুইজন ফেরেশতার সাথে বিভিন্ন দৃশ্য দেখেন। এক ব্যক্তির গাল চেরা হচ্ছিল, কারণ সে মিথ্যা বলত এবং তা ছড়িয়ে পড়ত। আরেকজনের মাথা পাথর দিয়ে ভাঙা হচ্ছিল, কারণ সে কুরআন শিখেও রাতে তা থেকে গাফেল ছিল এবং দিনে আমল করত না। তন্দুরের মতো স্থানে উলঙ্গ নারী-পুরুষ ছিল; তারা যিনাকারী। রক্তের নদীতে থাকা ব্যক্তি সুদখোর। পরে তিনি ইবরাহীম আলাইহিস সালাম, শিশুদের, জান্নাতের ঘর এবং শহীদদের ঘর দেখেন। হাদিসটি পাপের পরিণতি ও সৎ জীবনের আশা—দুই দিকই শেখায়।"},"teachings":["মিথ্যা ছড়ানো বড় পাপ এবং এর পরিণতি ভয়াবহ হতে পারে।","কুরআন শিখে অবহেলা করা ও আমল না করা বিপদের কারণ।","যিনা ও সুদ থেকে দূরে থাকার শক্ত সতর্কতা এসেছে।","মুমিন ও শহীদদের জন্য সম্মানের দৃশ্য বর্ণিত হয়েছে।"],"related_hadiths":[{"id":"6096","book_id":"1","label":"Sahih Bukhari"},{"id":"6772","book_id":"1","label":"Sahih Bukhari"},{"id":"2086","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে কুকুর ও ছবি রাখার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. যে ঘরে কুকুর ও ছবি থাকে, সে ঘরে রহমতের ফেরেশতা প্রবেশ না করার সতর্কতা এসেছে।"},"heading":{"title":"ঘরে কুকুর ও ছবি সম্পর্কে হাদিস: ফেরেশতা প্রবেশ না করার সতর্কতা","description":"এই হাদিসে নবী সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যে ঘরে কুকুর ও ছবি থাকে, সে ঘরে ফেরেশতা প্রবেশ করে না। এখানে মূল শিক্ষা হলো ঘরের পরিবেশকে এমন রাখা, যা আল্লাহর রহমত ও বরকতের সাথে মানানসই। হাদিসের ভাষায় কুকুর ও ছবি—দুটি বিষয় আলাদা করে উল্লেখ হয়েছে। তাই ঘরের সাজসজ্জা, দেয়াল, পর্দা বা ব্যবহারের জিনিসে ছবি রাখার বিষয়টি মুসলিম জীবনে সতর্কতার দাবি রাখে। তবে হাদিসের বাইরে গিয়ে সব ধরনের প্রয়োজনীয় ব্যবহার নিয়ে বড় দাবি করা ঠিক নয়। ইসলামী স্কলারদের মতে, প্রাণীর ছবি ও অপ্রয়োজনীয় ছবি রাখার বিষয়ে বিশেষ সতর্কতা আছে। এই হাদিস পরিবারকে ঘরের দীনী পরিবেশ নিয়ে ভাবতে শেখায়।"},"teachings":["ঘরের পরিবেশকে রহমত ও বরকতের উপযোগী রাখা উচিত।","কুকুর ও ছবি রাখার বিষয়ে হাদিসে সতর্কতা এসেছে।","অপ্রয়োজনীয় ছবি দিয়ে ঘর সাজানো থেকে বাঁচা উচিত।","পরিবারে দীনী সচেতনতা গড়ে তোলা দরকার।"],"related_hadiths":[{"id":"5৯61","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯5৯","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯52","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে কুকুর ও ছবি রাখার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. যে ঘরে কুকুর ও ছবি থাকে, সে ঘরে রহমতের ফেরেশতা প্রবেশ না করার সতর্কতা এসেছে।"},"heading":{"title":"ঘরে কুকুর ও ছবি সম্পর্কে হাদিস: ফেরেশতা প্রবেশ না করার সতর্কতা","description":"এই হাদিসে নবী সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যে ঘরে কুকুর ও ছবি থাকে, সে ঘরে ফেরেশতা প্রবেশ করে না। এখানে মূল শিক্ষা হলো ঘরের পরিবেশকে এমন রাখা, যা আল্লাহর রহমত ও বরকতের সাথে মানানসই। হাদিসের ভাষায় কুকুর ও ছবি—দুটি বিষয় আলাদা করে উল্লেখ হয়েছে। তাই ঘরের সাজসজ্জা, দেয়াল, পর্দা বা ব্যবহারের জিনিসে ছবি রাখার বিষয়টি মুসলিম জীবনে সতর্কতার দাবি রাখে। তবে হাদিসের বাইরে গিয়ে সব ধরনের প্রয়োজনীয় ব্যবহার নিয়ে বড় দাবি করা ঠিক নয়। ইসলামী স্কলারদের মতে, প্রাণীর ছবি ও অপ্রয়োজনীয় ছবি রাখার বিষয়ে বিশেষ সতর্কতা আছে। এই হাদিস পরিবারকে ঘরের দীনী পরিবেশ নিয়ে ভাবতে শেখায়।"},"teachings":["ঘরের পরিবেশকে রহমত ও বরকতের উপযোগী রাখা উচিত।","কুকুর ও ছবি রাখার বিষয়ে হাদিসে সতর্কতা এসেছে।","অপ্রয়োজনীয় ছবি দিয়ে ঘর সাজানো থেকে বাঁচা উচিত।","পরিবারে দীনী সচেতনতা গড়ে তোলা দরকার।"],"related_hadiths":[{"id":"5961","book_id":"1","label":"Sahih Bukhari"},{"id":"5959","book_id":"1","label":"Sahih Bukhari"},{"id":"5952","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবি অঙ্কনকারীর কঠিন শাস্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবি-মূর্তি অঙ্কনকারীদের জন্য কিয়ামতের কঠিন শাস্তির সতর্কতা এই হাদিসে এসেছে।"},"heading":{"title":"ছবি অঙ্কনকারীর শাস্তি সম্পর্কে হাদিস: ছবি-মূর্তি থেকে সতর্কতা","description":"এই হাদিসে আবদুল্লাহ ইবনে মাসউদ রাদিয়াল্লাহু আনহু বলেন, তিনি নবী সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-কে বলতে শুনেছেন যে, আল্লাহর কাছে ছবি-মূর্তি অঙ্কনকারীদের কঠিন শাস্তি হবে। হাদিসের মূল কথা খুব স্পষ্ট: ছবি-মূর্তি তৈরি বা অঙ্কনের বিষয়টি হালকা করে দেখার সুযোগ নেই। এখানে বিশেষ করে প্রাণীর ছবি ও মূর্তি তৈরির ব্যাপারে সতর্কতা বোঝা যায়, কারণ অন্য হাদিসগুলোতেও ছবির ঘর, ছবিযুক্ত পর্দা এবং ছবি নির্মাতাদের শাস্তির কথা এসেছে। একজন মুসলিমের জন্য উচিত হলো ঘর, পোশাক, সাজসজ্জা ও কাজকর্মে এমন বিষয় এড়িয়ে চলা, যা এই সতর্কতার মধ্যে পড়ে।"},"teachings":["ছবি-মূর্তি অঙ্কনকারীদের জন্য কঠিন সতর্কতা এসেছে।","ধর্মীয় বিষয়ে হালকা মনোভাব রাখা ঠিক নয়।","ঘর ও ব্যবহারের জিনিসে ছবি নিয়ে সতর্ক হওয়া দরকার।","যে কাজ আল্লাহর অসন্তুষ্টির কারণ হতে পারে, তা থেকে দূরে থাকা উচিত।"],"related_hadiths":[{"id":"5৯51","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯54","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯61","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবি অঙ্কনকারীর কঠিন শাস্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবি-মূর্তি অঙ্কনকারীদের জন্য কিয়ামতের কঠিন শাস্তির সতর্কতা এই হাদিসে এসেছে।"},"heading":{"title":"ছবি অঙ্কনকারীর শাস্তি সম্পর্কে হাদিস: ছবি-মূর্তি থেকে সতর্কতা","description":"এই হাদিসে আবদুল্লাহ ইবনে মাসউদ রাদিয়াল্লাহু আনহু বলেন, তিনি নবী সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-কে বলতে শুনেছেন যে, আল্লাহর কাছে ছবি-মূর্তি অঙ্কনকারীদের কঠিন শাস্তি হবে। হাদিসের মূল কথা খুব স্পষ্ট: ছবি-মূর্তি তৈরি বা অঙ্কনের বিষয়টি হালকা করে দেখার সুযোগ নেই। এখানে বিশেষ করে প্রাণীর ছবি ও মূর্তি তৈরির ব্যাপারে সতর্কতা বোঝা যায়, কারণ অন্য হাদিসগুলোতেও ছবির ঘর, ছবিযুক্ত পর্দা এবং ছবি নির্মাতাদের শাস্তির কথা এসেছে। একজন মুসলিমের জন্য উচিত হলো ঘর, পোশাক, সাজসজ্জা ও কাজকর্মে এমন বিষয় এড়িয়ে চলা, যা এই সতর্কতার মধ্যে পড়ে।"},"teachings":["ছবি-মূর্তি অঙ্কনকারীদের জন্য কঠিন সতর্কতা এসেছে।","ধর্মীয় বিষয়ে হালকা মনোভাব রাখা ঠিক নয়।","ঘর ও ব্যবহারের জিনিসে ছবি নিয়ে সতর্ক হওয়া দরকার।","যে কাজ আল্লাহর অসন্তুষ্টির কারণ হতে পারে, তা থেকে দূরে থাকা উচিত।"],"related_hadiths":[{"id":"5951","book_id":"1","label":"Sahih Bukhari"},{"id":"5954","book_id":"1","label":"Sahih Bukhari"},{"id":"5961","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবি-মূর্তি নির্মাতাদের জবাবদিহি","description":"$book_name$ $hadith_number$ - $chapter_name$. যারা ছবি-মূর্তি তৈরি করে, কিয়ামতে তাদের বলা হবে—যা বানিয়েছ তাতে প্রাণ দাও।"},"heading":{"title":"ছবি-মূর্তি তৈরি সম্পর্কে হাদিস: যা বানানো হয় তাতে প্রাণ দিতে বলা হবে","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যারা এসব ছবি-মূর্তি তৈরি করে, কিয়ামতের দিন তাদের শাস্তি দেওয়া হবে। তাদের বলা হবে, তোমরা যা বানিয়েছ তাতে প্রাণ দাও। এই কথাটি মানুষের সীমাবদ্ধতা মনে করিয়ে দেয়। মানুষ আঁকতে বা বানাতে পারে, কিন্তু প্রাণ দিতে পারে না। তাই প্রাণীর ছবি-মূর্তি বানানোকে হাদিসে কঠিনভাবে সতর্ক করা হয়েছে। এখানে মূল শিক্ষা হলো সৃষ্টির মালিক আল্লাহ, আর মানুষ যেন এমন কাজকে খেলা বা গর্বের বিষয় না বানায় যা আল্লাহর অসন্তুষ্টির কারণ হতে পারে। মুসলিম জীবনে সাজসজ্জা, শিল্পকর্ম ও ঘরের জিনিস বেছে নেওয়ার সময় এই হাদিসের শিক্ষা মনে রাখা দরকার।"},"teachings":["সৃষ্টির ক্ষমতা একমাত্র আল্লাহর; মানুষ প্রাণ দিতে পারে না।","ছবি-মূর্তি তৈরি সম্পর্কে কিয়ামতের জবাবদিহি আছে।","শিল্প বা সাজসজ্জা বাছাইয়ে দীনী সতর্কতা দরকার।","আল্লাহর অসন্তুষ্টির আশঙ্কা আছে এমন কাজ থেকে দূরে থাকা উচিত।"],"related_hadiths":[{"id":"5৯50","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯54","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯61","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবি-মূর্তি নির্মাতাদের জবাবদিহি","description":"$book_name$ $hadith_number$ - $chapter_name$. যারা ছবি-মূর্তি তৈরি করে, কিয়ামতে তাদের বলা হবে—যা বানিয়েছ তাতে প্রাণ দাও।"},"heading":{"title":"ছবি-মূর্তি তৈরি সম্পর্কে হাদিস: যা বানানো হয় তাতে প্রাণ দিতে বলা হবে","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যারা এসব ছবি-মূর্তি তৈরি করে, কিয়ামতের দিন তাদের শাস্তি দেওয়া হবে। তাদের বলা হবে, তোমরা যা বানিয়েছ তাতে প্রাণ দাও। এই কথাটি মানুষের সীমাবদ্ধতা মনে করিয়ে দেয়। মানুষ আঁকতে বা বানাতে পারে, কিন্তু প্রাণ দিতে পারে না। তাই প্রাণীর ছবি-মূর্তি বানানোকে হাদিসে কঠিনভাবে সতর্ক করা হয়েছে। এখানে মূল শিক্ষা হলো সৃষ্টির মালিক আল্লাহ, আর মানুষ যেন এমন কাজকে খেলা বা গর্বের বিষয় না বানায় যা আল্লাহর অসন্তুষ্টির কারণ হতে পারে। মুসলিম জীবনে সাজসজ্জা, শিল্পকর্ম ও ঘরের জিনিস বেছে নেওয়ার সময় এই হাদিসের শিক্ষা মনে রাখা দরকার।"},"teachings":["সৃষ্টির ক্ষমতা একমাত্র আল্লাহর; মানুষ প্রাণ দিতে পারে না।","ছবি-মূর্তি তৈরি সম্পর্কে কিয়ামতের জবাবদিহি আছে।","শিল্প বা সাজসজ্জা বাছাইয়ে দীনী সতর্কতা দরকার।","আল্লাহর অসন্তুষ্টির আশঙ্কা আছে এমন কাজ থেকে দূরে থাকা উচিত।"],"related_hadiths":[{"id":"5950","book_id":"1","label":"Sahih Bukhari"},{"id":"5954","book_id":"1","label":"Sahih Bukhari"},{"id":"5961","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | একটি ছবি তৈরিরও কঠিন জবাবদিহি","description":"$book_name$ $hadith_number$ - $chapter_name$. একটি ছবি-মূর্তি তৈরি করলেও কিয়ামতে শাস্তি ও প্রাণ দেওয়ার অক্ষমতার সতর্কতা এসেছে।"},"heading":{"title":"একটি ছবি-মূর্তি তৈরির শাস্তি: প্রাণ দিতে বলা হবে কিন্তু পারবে না","description":"এই হাদিসে বলা হয়েছে, যে ব্যক্তি একটি ছবি-মূর্তিও তৈরি করবে, তাকে শাস্তি দেওয়া হবে এবং তাতে প্রাণ দিতে বলা হবে; কিন্তু সে তা করতে পারবে না। হাদিসের ভাষা দেখায়, বিষয়টি সংখ্যার কারণে ছোট হয়ে যায় না। একটি ছবিও যদি নিষিদ্ধ ছবির মধ্যে পড়ে, তবে তা নিয়ে সতর্কতা আছে। এখানে মূল শিক্ষা হলো, মানুষ যেন সৃষ্টির কাজকে নিজের ক্ষমতার বিষয় মনে না করে। ছবি-মূর্তি তৈরি, ঘরে রাখা বা সাজসজ্জায় ব্যবহার করার আগে একজন মুসলিমকে ভাবতে হবে—এটি কি হাদিসের সতর্কতার মধ্যে পড়ে কি না। এই হাদিস অপ্রয়োজনীয় প্রাণীর ছবি ও মূর্তি থেকে দূরে থাকার শক্ত শিক্ষা দেয়।"},"teachings":["একটি ছবিও হাদিসের সতর্কতার বিষয় হতে পারে।","মানুষ ছবি বানাতে পারে, কিন্তু প্রাণ দিতে পারে না।","অপ্রয়োজনীয় প্রাণীর ছবি-মূর্তি থেকে দূরে থাকা উচিত।","ছোট মনে হওয়া কাজও কিয়ামতে জবাবদিহির কারণ হতে পারে।"],"related_hadiths":[{"id":"5৯50","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯51","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯61","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | একটি ছবি তৈরিরও কঠিন জবাবদিহি","description":"$book_name$ $hadith_number$ - $chapter_name$. একটি ছবি-মূর্তি তৈরি করলেও কিয়ামতে শাস্তি ও প্রাণ দেওয়ার অক্ষমতার সতর্কতা এসেছে।"},"heading":{"title":"একটি ছবি-মূর্তি তৈরির শাস্তি: প্রাণ দিতে বলা হবে কিন্তু পারবে না","description":"এই হাদিসে বলা হয়েছে, যে ব্যক্তি একটি ছবি-মূর্তিও তৈরি করবে, তাকে শাস্তি দেওয়া হবে এবং তাতে প্রাণ দিতে বলা হবে; কিন্তু সে তা করতে পারবে না। হাদিসের ভাষা দেখায়, বিষয়টি সংখ্যার কারণে ছোট হয়ে যায় না। একটি ছবিও যদি নিষিদ্ধ ছবির মধ্যে পড়ে, তবে তা নিয়ে সতর্কতা আছে। এখানে মূল শিক্ষা হলো, মানুষ যেন সৃষ্টির কাজকে নিজের ক্ষমতার বিষয় মনে না করে। ছবি-মূর্তি তৈরি, ঘরে রাখা বা সাজসজ্জায় ব্যবহার করার আগে একজন মুসলিমকে ভাবতে হবে—এটি কি হাদিসের সতর্কতার মধ্যে পড়ে কি না। এই হাদিস অপ্রয়োজনীয় প্রাণীর ছবি ও মূর্তি থেকে দূরে থাকার শক্ত শিক্ষা দেয়।"},"teachings":["একটি ছবিও হাদিসের সতর্কতার বিষয় হতে পারে।","মানুষ ছবি বানাতে পারে, কিন্তু প্রাণ দিতে পারে না।","অপ্রয়োজনীয় প্রাণীর ছবি-মূর্তি থেকে দূরে থাকা উচিত।","ছোট মনে হওয়া কাজও কিয়ামতে জবাবদিহির কারণ হতে পারে।"],"related_hadiths":[{"id":"5950","book_id":"1","label":"Sahih Bukhari"},{"id":"5951","book_id":"1","label":"Sahih Bukhari"},{"id":"5961","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে ছবিযুক্ত বস্তু রাখার বিধান","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি ঘরে ছবিযুক্ত কিছু দেখলে তা ভেঙে বা সরিয়ে দিতেন—এতে ঘর পবিত্র রাখার শিক্ষা আছে।"},"heading":{"title":"ঘরে ছবিযুক্ত বস্তু সম্পর্কে হাদিস: নবীজির আমলের শিক্ষা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা থেকে এসেছে, রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তাঁর ঘরে ছবিযুক্ত কোনো কিছু দেখলে তা ছিঁড়ে বা ভেঙে ফেলতেন। এটি শুধু কথা নয়, নবীজির বাস্তব আমল। এর মাধ্যমে বোঝা যায়, ঘরের ভেতর ছবিযুক্ত বস্তু রাখা নিয়ে তিনি খুব সতর্ক ছিলেন। ঘর একজন মুসলিমের শান্তি, ইবাদত ও পরিবারের জায়গা। তাই সেখানে এমন জিনিস রাখা ঠিক নয়, যা দীনী পরিবেশকে নষ্ট করে বা হাদিসের সতর্কতার মধ্যে পড়ে। এই হাদিস আমাদের শেখায়, ঘরের সাজসজ্জা শুধু সৌন্দর্যের জন্য নয়; তা ঈমান, সালাত ও আল্লাহর স্মরণের অনুকূল হওয়া দরকার।"},"teachings":["নবীজি ছবিযুক্ত বস্তু ঘরে রেখে দিতেন না।","ঘরের পরিবেশকে দীনীভাবে পরিষ্কার রাখা দরকার।","সাজসজ্জার জিনিস বাছাইয়ে সতর্ক হতে হবে।","কথার সাথে আমলের মিল রাখা নবীজির শিক্ষা।"],"related_hadiths":[{"id":"5৯55","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯5৯","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯61","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে ছবিযুক্ত বস্তু রাখার বিধান","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি ঘরে ছবিযুক্ত কিছু দেখলে তা ভেঙে বা সরিয়ে দিতেন—এতে ঘর পবিত্র রাখার শিক্ষা আছে।"},"heading":{"title":"ঘরে ছবিযুক্ত বস্তু সম্পর্কে হাদিস: নবীজির আমলের শিক্ষা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা থেকে এসেছে, রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তাঁর ঘরে ছবিযুক্ত কোনো কিছু দেখলে তা ছিঁড়ে বা ভেঙে ফেলতেন। এটি শুধু কথা নয়, নবীজির বাস্তব আমল। এর মাধ্যমে বোঝা যায়, ঘরের ভেতর ছবিযুক্ত বস্তু রাখা নিয়ে তিনি খুব সতর্ক ছিলেন। ঘর একজন মুসলিমের শান্তি, ইবাদত ও পরিবারের জায়গা। তাই সেখানে এমন জিনিস রাখা ঠিক নয়, যা দীনী পরিবেশকে নষ্ট করে বা হাদিসের সতর্কতার মধ্যে পড়ে। এই হাদিস আমাদের শেখায়, ঘরের সাজসজ্জা শুধু সৌন্দর্যের জন্য নয়; তা ঈমান, সালাত ও আল্লাহর স্মরণের অনুকূল হওয়া দরকার।"},"teachings":["নবীজি ছবিযুক্ত বস্তু ঘরে রেখে দিতেন না।","ঘরের পরিবেশকে দীনীভাবে পরিষ্কার রাখা দরকার।","সাজসজ্জার জিনিস বাছাইয়ে সতর্ক হতে হবে।","কথার সাথে আমলের মিল রাখা নবীজির শিক্ষা।"],"related_hadiths":[{"id":"5955","book_id":"1","label":"Sahih Bukhari"},{"id":"5959","book_id":"1","label":"Sahih Bukhari"},{"id":"5961","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত পর্দা ও কঠিন সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত পর্দা ছিঁড়ে ফেলা এবং ছবি-মূর্তি অঙ্কনকারীদের শাস্তির কথা এই হাদিসে এসেছে।"},"heading":{"title":"ছবিযুক্ত পর্দা সম্পর্কে হাদিস: ঘরের সাজসজ্জায় দীনী সতর্কতা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা বলেন, রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম সফর থেকে এসে ছবিযুক্ত পর্দা দেখেন। তিনি তা ছিঁড়ে টুকরা করে দেন এবং বলেন, যারা ছবি-মূর্তি অঙ্কন করে, কিয়ামতের দিন তাদের কঠিন শাস্তি হবে। হাদিসটি দেখায়, ছবিযুক্ত পর্দা বা ঘরের সাজসজ্জা শুধু সাধারণ বস্তু নয়; তা ইবাদত, ঘরের পরিবেশ ও দীনী সতর্কতার সাথে জড়িত হতে পারে। এখানে ছবি-মূর্তি অঙ্কনের শাস্তির কথাও যুক্ত হয়েছে। তাই মুসলিম পরিবারে দেয়াল, পর্দা, কাপড় বা সাজসজ্জায় প্রাণীর ছবি ব্যবহারে সতর্ক থাকা উচিত। এই হাদিস আমাদের শেখায়, ঘরের সৌন্দর্যের চেয়ে আল্লাহর সন্তুষ্টি বেশি গুরুত্বপূর্ণ।"},"teachings":["ছবিযুক্ত পর্দা ঘরে রাখার বিষয়ে হাদিসে সতর্কতা আছে।","নবীজি অপছন্দনীয় বস্তু সরিয়ে দিতেন।","ছবি-মূর্তি অঙ্কনকারীদের জন্য কিয়ামতের শাস্তির সতর্কতা এসেছে।","ঘরের সাজসজ্জায় আল্লাহর সন্তুষ্টিকে অগ্রাধিকার দিতে হবে।"],"related_hadiths":[{"id":"5৯52","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯55","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯5৯","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত পর্দা ও কঠিন সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত পর্দা ছিঁড়ে ফেলা এবং ছবি-মূর্তি অঙ্কনকারীদের শাস্তির কথা এই হাদিসে এসেছে।"},"heading":{"title":"ছবিযুক্ত পর্দা সম্পর্কে হাদিস: ঘরের সাজসজ্জায় দীনী সতর্কতা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা বলেন, রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম সফর থেকে এসে ছবিযুক্ত পর্দা দেখেন। তিনি তা ছিঁড়ে টুকরা করে দেন এবং বলেন, যারা ছবি-মূর্তি অঙ্কন করে, কিয়ামতের দিন তাদের কঠিন শাস্তি হবে। হাদিসটি দেখায়, ছবিযুক্ত পর্দা বা ঘরের সাজসজ্জা শুধু সাধারণ বস্তু নয়; তা ইবাদত, ঘরের পরিবেশ ও দীনী সতর্কতার সাথে জড়িত হতে পারে। এখানে ছবি-মূর্তি অঙ্কনের শাস্তির কথাও যুক্ত হয়েছে। তাই মুসলিম পরিবারে দেয়াল, পর্দা, কাপড় বা সাজসজ্জায় প্রাণীর ছবি ব্যবহারে সতর্ক থাকা উচিত। এই হাদিস আমাদের শেখায়, ঘরের সৌন্দর্যের চেয়ে আল্লাহর সন্তুষ্টি বেশি গুরুত্বপূর্ণ।"},"teachings":["ছবিযুক্ত পর্দা ঘরে রাখার বিষয়ে হাদিসে সতর্কতা আছে।","নবীজি অপছন্দনীয় বস্তু সরিয়ে দিতেন।","ছবি-মূর্তি অঙ্কনকারীদের জন্য কিয়ামতের শাস্তির সতর্কতা এসেছে।","ঘরের সাজসজ্জায় আল্লাহর সন্তুষ্টিকে অগ্রাধিকার দিতে হবে।"],"related_hadiths":[{"id":"5952","book_id":"1","label":"Sahih Bukhari"},{"id":"5955","book_id":"1","label":"Sahih Bukhari"},{"id":"5959","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত পর্দা সরানোর নির্দেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. সফর থেকে ফিরে নবীজি ছবিযুক্ত পর্দা সরাতে বললেন; ঘরকে ছবি থেকে পরিষ্কার রাখার শিক্ষা আছে।"},"heading":{"title":"ছবিযুক্ত পর্দা সরানো সম্পর্কে হাদিস: ঘরকে দীনীভাবে সাজানোর শিক্ষা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা বলেন, রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম এক সফর থেকে ফিরে দেখলেন, তিনি ছবিযুক্ত একটি পর্দা ঝুলিয়েছেন। তখন নবীজি তাকে সেটি সরিয়ে ফেলতে বললেন, আর তিনি তা সরিয়ে দিলেন। এই হাদিসের শিক্ষা খুব সরল: ঘরের ভেতরে ছবিযুক্ত পর্দা বা এমন সাজসজ্জা রাখা থেকে সতর্ক থাকতে হবে। নবীজি বিষয়টি দেখেই নির্দেশ দিয়েছেন, আর আয়েশা রাদিয়াল্লাহু আনহা তা মেনে নিয়েছেন। এতে আনুগত্যের সুন্দর শিক্ষা আছে। মুসলিম ঘর শুধু থাকার জায়গা নয়; সেখানে সালাত, দোয়া ও আল্লাহর স্মরণ হয়। তাই ঘরের জিনিস বাছাইয়ে দীনী সচেতনতা থাকা দরকার।"},"teachings":["নবীজির নির্দেশ শুনে দ্রুত মানা সাহাবাদের সুন্দর গুণ।","ছবিযুক্ত পর্দা সরানোর শিক্ষা এই হাদিসে এসেছে।","ঘরের সাজসজ্জায় দীনী সতর্কতা রাখা উচিত।","মুসলিম ঘরকে ইবাদতের উপযোগী রাখা দরকার।"],"related_hadiths":[{"id":"5৯52","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯54","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯5৯","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত পর্দা সরানোর নির্দেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. সফর থেকে ফিরে নবীজি ছবিযুক্ত পর্দা সরাতে বললেন; ঘরকে ছবি থেকে পরিষ্কার রাখার শিক্ষা আছে।"},"heading":{"title":"ছবিযুক্ত পর্দা সরানো সম্পর্কে হাদিস: ঘরকে দীনীভাবে সাজানোর শিক্ষা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা বলেন, রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম এক সফর থেকে ফিরে দেখলেন, তিনি ছবিযুক্ত একটি পর্দা ঝুলিয়েছেন। তখন নবীজি তাকে সেটি সরিয়ে ফেলতে বললেন, আর তিনি তা সরিয়ে দিলেন। এই হাদিসের শিক্ষা খুব সরল: ঘরের ভেতরে ছবিযুক্ত পর্দা বা এমন সাজসজ্জা রাখা থেকে সতর্ক থাকতে হবে। নবীজি বিষয়টি দেখেই নির্দেশ দিয়েছেন, আর আয়েশা রাদিয়াল্লাহু আনহা তা মেনে নিয়েছেন। এতে আনুগত্যের সুন্দর শিক্ষা আছে। মুসলিম ঘর শুধু থাকার জায়গা নয়; সেখানে সালাত, দোয়া ও আল্লাহর স্মরণ হয়। তাই ঘরের জিনিস বাছাইয়ে দীনী সচেতনতা থাকা দরকার।"},"teachings":["নবীজির নির্দেশ শুনে দ্রুত মানা সাহাবাদের সুন্দর গুণ।","ছবিযুক্ত পর্দা সরানোর শিক্ষা এই হাদিসে এসেছে।","ঘরের সাজসজ্জায় দীনী সতর্কতা রাখা উচিত।","মুসলিম ঘরকে ইবাদতের উপযোগী রাখা দরকার।"],"related_hadiths":[{"id":"5952","book_id":"1","label":"Sahih Bukhari"},{"id":"5954","book_id":"1","label":"Sahih Bukhari"},{"id":"5959","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সালাতে মনোযোগ নষ্ট করে ছবিযুক্ত চাদর","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত চাদর সালাতে সামনে আসায় নবীজি তা সরাতে বলেন; সালাতে মনোযোগ রক্ষার শিক্ষা আছে।"},"heading":{"title":"সালাতে ছবিযুক্ত চাদর সম্পর্কে হাদিস: মনোযোগ রক্ষার সহজ শিক্ষা","description":"এই হাদিসে আনাস ইবনে মালেক রাদিয়াল্লাহু আনহু বলেন, আয়েশা রাদিয়াল্লাহু আনহার একটি চাদর ছিল, যা দিয়ে ঘরের এক পাশে পর্দা করা হয়েছিল। রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বললেন, এটি আমার সামনে থেকে সরাও; এর ছবিগুলো আমার সালাতে সামনে আসে। এখানে ছবির বিষয়ে সতর্কতার সাথে সালাতের মনোযোগের কথাও এসেছে। সালাত হলো আল্লাহর সামনে দাঁড়ানো। সেখানে এমন কিছু সামনে রাখা উচিত নয়, যা চোখে পড়ে মনকে ব্যস্ত করে। এই হাদিস আমাদের ঘর ও সালাতের জায়গা সাজানোর সময় ভাবতে শেখায়। দেয়াল, পর্দা, কাপড় বা সামনে থাকা জিনিস যেন ইবাদতে বাধা না হয়।"},"teachings":["সালাতে মনোযোগ নষ্ট করে এমন জিনিস সামনে রাখা উচিত নয়।","ছবিযুক্ত কাপড় বা পর্দা ইবাদতে বাধা হতে পারে।","নবীজি সালাতের একাগ্রতাকে গুরুত্ব দিয়েছেন।","ঘরের সালাতের জায়গা সরল ও মনোযোগবান্ধব হওয়া ভালো।"],"related_hadiths":[{"id":"374","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯55","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯61","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সালাতে মনোযোগ নষ্ট করে ছবিযুক্ত চাদর","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত চাদর সালাতে সামনে আসায় নবীজি তা সরাতে বলেন; সালাতে মনোযোগ রক্ষার শিক্ষা আছে।"},"heading":{"title":"সালাতে ছবিযুক্ত চাদর সম্পর্কে হাদিস: মনোযোগ রক্ষার সহজ শিক্ষা","description":"এই হাদিসে আনাস ইবনে মালেক রাদিয়াল্লাহু আনহু বলেন, আয়েশা রাদিয়াল্লাহু আনহার একটি চাদর ছিল, যা দিয়ে ঘরের এক পাশে পর্দা করা হয়েছিল। রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বললেন, এটি আমার সামনে থেকে সরাও; এর ছবিগুলো আমার সালাতে সামনে আসে। এখানে ছবির বিষয়ে সতর্কতার সাথে সালাতের মনোযোগের কথাও এসেছে। সালাত হলো আল্লাহর সামনে দাঁড়ানো। সেখানে এমন কিছু সামনে রাখা উচিত নয়, যা চোখে পড়ে মনকে ব্যস্ত করে। এই হাদিস আমাদের ঘর ও সালাতের জায়গা সাজানোর সময় ভাবতে শেখায়। দেয়াল, পর্দা, কাপড় বা সামনে থাকা জিনিস যেন ইবাদতে বাধা না হয়।"},"teachings":["সালাতে মনোযোগ নষ্ট করে এমন জিনিস সামনে রাখা উচিত নয়।","ছবিযুক্ত কাপড় বা পর্দা ইবাদতে বাধা হতে পারে।","নবীজি সালাতের একাগ্রতাকে গুরুত্ব দিয়েছেন।","ঘরের সালাতের জায়গা সরল ও মনোযোগবান্ধব হওয়া ভালো।"],"related_hadiths":[{"id":"374","book_id":"1","label":"Sahih Bukhari"},{"id":"5955","book_id":"1","label":"Sahih Bukhari"},{"id":"5961","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতের আলামত ও বস্তু কথা বলা","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতের আগে হিংস্র পশু, চাবুক, জুতার ফিতা ও উরুর কথা বলার আলামত হাদিসে এসেছে।"},"heading":{"title":"কিয়ামতের আলামত: পশু ও জিনিসপত্র কথা বলার হাদিস","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) শপথ করে বলেছেন, কিয়ামত কায়েম হবে না যতক্ষণ না কিছু বিস্ময়কর আলামত দেখা যায়। হিংস্র পশু মানুষের সঙ্গে কথা বলবে, মানুষের চাবুকের মাথা তার সঙ্গে কথা বলবে, জুতার ফিতা কথা বলবে এবং তার উরু তাকে জানাবে, তার অনুপস্থিতিতে তার স্ত্রী কী করেছে। হাদিসের ভাষা যেমন আছে, তেমনভাবেই গ্রহণ করা উচিত। এখানে কিয়ামতের আলামত, আল্লাহর ক্ষমতা এবং মানুষের অজানা বিষয় প্রকাশের কথা এসেছে। ব্যাখ্যায় নিজের থেকে সময়, পদ্ধতি বা আধুনিক কোনো জিনিসের সঙ্গে নিশ্চিত মিলিয়ে দেওয়া ঠিক নয়। মূল শিক্ষা হলো, কিয়ামত সত্য এবং আল্লাহ যেভাবে চান সেভাবে অদ্ভুত ঘটনাও ঘটতে পারে।"},"teachings":["কিয়ামতের আগে কিছু আশ্চর্য আলামত ঘটবে।","আল্লাহ চাইলে পশু ও জিনিসপত্রকেও কথা বলাতে পারেন।","হাদিসের আলামত নিজের ধারণা দিয়ে নির্দিষ্ট করা ঠিক নয়।","কিয়ামতের বিশ্বাস মানুষকে সতর্ক জীবন শেখায়।"],"related_hadiths":[{"id":"21৮1","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"5225","book_id":"14","label":"Mishkat al-Masabih"},{"id":"2৯6৯","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতের আলামত ও বস্তু কথা বলা","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতের আগে হিংস্র পশু, চাবুক, জুতার ফিতা ও উরুর কথা বলার আলামত হাদিসে এসেছে।"},"heading":{"title":"কিয়ামতের আলামত: পশু ও জিনিসপত্র কথা বলার হাদিস","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) শপথ করে বলেছেন, কিয়ামত কায়েম হবে না যতক্ষণ না কিছু বিস্ময়কর আলামত দেখা যায়। হিংস্র পশু মানুষের সঙ্গে কথা বলবে, মানুষের চাবুকের মাথা তার সঙ্গে কথা বলবে, জুতার ফিতা কথা বলবে এবং তার উরু তাকে জানাবে, তার অনুপস্থিতিতে তার স্ত্রী কী করেছে। হাদিসের ভাষা যেমন আছে, তেমনভাবেই গ্রহণ করা উচিত। এখানে কিয়ামতের আলামত, আল্লাহর ক্ষমতা এবং মানুষের অজানা বিষয় প্রকাশের কথা এসেছে। ব্যাখ্যায় নিজের থেকে সময়, পদ্ধতি বা আধুনিক কোনো জিনিসের সঙ্গে নিশ্চিত মিলিয়ে দেওয়া ঠিক নয়। মূল শিক্ষা হলো, কিয়ামত সত্য এবং আল্লাহ যেভাবে চান সেভাবে অদ্ভুত ঘটনাও ঘটতে পারে।"},"teachings":["কিয়ামতের আগে কিছু আশ্চর্য আলামত ঘটবে।","আল্লাহ চাইলে পশু ও জিনিসপত্রকেও কথা বলাতে পারেন।","হাদিসের আলামত নিজের ধারণা দিয়ে নির্দিষ্ট করা ঠিক নয়।","কিয়ামতের বিশ্বাস মানুষকে সতর্ক জীবন শেখায়।"],"related_hadiths":[{"id":"2181","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"5225","book_id":"14","label":"Mishkat al-Masabih"},{"id":"2969","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত বালিশ ও ফেরেশতার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত বালিশ দেখে নবীজি ঘরে প্রবেশ করলেন না; ছবি নির্মাতা ও ঘরে ছবির বিষয়ে সতর্কতা দিলেন।"},"heading":{"title":"ছবিযুক্ত বালিশ সম্পর্কে হাদিস: ঘরে ছবি থাকলে ফেরেশতা প্রবেশ না করার সতর্কতা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা একটি ছোট বালিশ কিনেছিলেন, তাতে ছবি ছিল। রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তা দেখে ঘরে প্রবেশ না করে দরজায় দাঁড়িয়ে থাকেন। আয়েশা রাদিয়াল্লাহু আনহা তাঁর মুখে অপছন্দের চিহ্ন দেখে তওবা করেন এবং নিজের ভুল জানতে চান। নবীজি বলেন, যারা এসব ছবি তৈরি করে, কিয়ামতের দিন তাদের শাস্তি দেওয়া হবে এবং বলা হবে, যাদের তৈরি করেছ তাদের জীবিত কর। এরপর তিনি বলেন, যে ঘরে ছবি থাকে, সে ঘরে ফেরেশতা প্রবেশ করে না। হাদিসটি ঘরের ছবি, ছবি নির্মাতা এবং দীনী পরিবেশ—তিনটি বিষয় একসাথে শেখায়। মুসলিম পরিবারের জন্য এটি ঘরকে অপ্রয়োজনীয় ছবি থেকে পরিষ্কার রাখার শক্ত শিক্ষা।"},"teachings":["ছবিযুক্ত বালিশ দেখেও নবীজি অপছন্দ প্রকাশ করেছেন।","ছবি নির্মাতাদের জন্য কিয়ামতের জবাবদিহির কথা এসেছে।","যে ঘরে ছবি থাকে, সেখানে ফেরেশতা প্রবেশ না করার সতর্কতা আছে।","ভুল বুঝতে পারলে দ্রুত তওবা করা মুমিনের গুণ।"],"related_hadiths":[{"id":"5৯4৯","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯50","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯5৯","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত বালিশ ও ফেরেশতার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত বালিশ দেখে নবীজি ঘরে প্রবেশ করলেন না; ছবি নির্মাতা ও ঘরে ছবির বিষয়ে সতর্কতা দিলেন।"},"heading":{"title":"ছবিযুক্ত বালিশ সম্পর্কে হাদিস: ঘরে ছবি থাকলে ফেরেশতা প্রবেশ না করার সতর্কতা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা একটি ছোট বালিশ কিনেছিলেন, তাতে ছবি ছিল। রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তা দেখে ঘরে প্রবেশ না করে দরজায় দাঁড়িয়ে থাকেন। আয়েশা রাদিয়াল্লাহু আনহা তাঁর মুখে অপছন্দের চিহ্ন দেখে তওবা করেন এবং নিজের ভুল জানতে চান। নবীজি বলেন, যারা এসব ছবি তৈরি করে, কিয়ামতের দিন তাদের শাস্তি দেওয়া হবে এবং বলা হবে, যাদের তৈরি করেছ তাদের জীবিত কর। এরপর তিনি বলেন, যে ঘরে ছবি থাকে, সে ঘরে ফেরেশতা প্রবেশ করে না। হাদিসটি ঘরের ছবি, ছবি নির্মাতা এবং দীনী পরিবেশ—তিনটি বিষয় একসাথে শেখায়। মুসলিম পরিবারের জন্য এটি ঘরকে অপ্রয়োজনীয় ছবি থেকে পরিষ্কার রাখার শক্ত শিক্ষা।"},"teachings":["ছবিযুক্ত বালিশ দেখেও নবীজি অপছন্দ প্রকাশ করেছেন।","ছবি নির্মাতাদের জন্য কিয়ামতের জবাবদিহির কথা এসেছে।","যে ঘরে ছবি থাকে, সেখানে ফেরেশতা প্রবেশ না করার সতর্কতা আছে।","ভুল বুঝতে পারলে দ্রুত তওবা করা মুমিনের গুণ।"],"related_hadiths":[{"id":"5949","book_id":"1","label":"Sahih Bukhari"},{"id":"5950","book_id":"1","label":"Sahih Bukhari"},{"id":"5959","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে ছবি টাঙ্গানোর সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত পর্দা, সৃষ্টির সাদৃশ্য বানানো ও ঘরে ফেরেশতা প্রবেশ না করার বিষয়ে স্পষ্ট সতর্কতা।"},"heading":{"title":"ঘরে ছবি টাঙ্গানো: সৃষ্টির সাদৃশ্য বানানো নিয়ে হাদিসের শিক্ষা","description":"এই হাদিসে মূল বিষয় হলো ঘরে ছবি টাঙ্গানো এবং প্রাণীর ছবি ব্যবহার। আয়েশা (রাঃ) ঘরের সামনে একটি পাতলা ছবিযুক্ত কাপড় ঝুলিয়েছিলেন। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তা দেখে অসন্তুষ্ট হন, কাপড়টি ছিঁড়ে ফেলেন এবং বলেন, যারা আল্লাহর সৃষ্টির সাদৃশ্য তৈরি করে, কিয়ামতের দিন তাদের কঠিন শাস্তির কথা বলা হয়েছে। হাদিসে আরও এসেছে, ছবির মালিকদের বলা হবে, যা তৈরি করেছ তা জীবিত কর। এখানে ঘরে ছবি থাকলে ফেরেশতা প্রবেশ না করার কথাও এসেছে। তবে আয়েশা (রাঃ) কাপড়টি কেটে বালিশ বানিয়েছিলেন, আর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে সেটিতে হেলান দিতে দেখা গেছে। তাই ছবিওয়ালা পর্দা টাঙ্গানো ও সম্মানের স্থানে রাখা থেকে সতর্ক থাকা এই হাদিসের মূল শিক্ষা।"},"teachings":["ঘরে প্রাণীর ছবি টাঙ্গানো থেকে সতর্ক থাকা উচিত।","আল্লাহর সৃষ্টির সাদৃশ্য বানানো গুরুতর সতর্কতার বিষয়।","ছবিযুক্ত জিনিস সম্মানের জায়গায় না রেখে ব্যবহার বদলানো হাদিসে এসেছে।","ঘরের পরিবেশ এমন রাখা দরকার, যাতে রহমতের ফেরেশতা আসার বাধা না থাকে।"],"related_hadiths":[{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯5৮","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে ছবি টাঙ্গানোর সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত পর্দা, সৃষ্টির সাদৃশ্য বানানো ও ঘরে ফেরেশতা প্রবেশ না করার বিষয়ে স্পষ্ট সতর্কতা।"},"heading":{"title":"ঘরে ছবি টাঙ্গানো: সৃষ্টির সাদৃশ্য বানানো নিয়ে হাদিসের শিক্ষা","description":"এই হাদিসে মূল বিষয় হলো ঘরে ছবি টাঙ্গানো এবং প্রাণীর ছবি ব্যবহার। আয়েশা (রাঃ) ঘরের সামনে একটি পাতলা ছবিযুক্ত কাপড় ঝুলিয়েছিলেন। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তা দেখে অসন্তুষ্ট হন, কাপড়টি ছিঁড়ে ফেলেন এবং বলেন, যারা আল্লাহর সৃষ্টির সাদৃশ্য তৈরি করে, কিয়ামতের দিন তাদের কঠিন শাস্তির কথা বলা হয়েছে। হাদিসে আরও এসেছে, ছবির মালিকদের বলা হবে, যা তৈরি করেছ তা জীবিত কর। এখানে ঘরে ছবি থাকলে ফেরেশতা প্রবেশ না করার কথাও এসেছে। তবে আয়েশা (রাঃ) কাপড়টি কেটে বালিশ বানিয়েছিলেন, আর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে সেটিতে হেলান দিতে দেখা গেছে। তাই ছবিওয়ালা পর্দা টাঙ্গানো ও সম্মানের স্থানে রাখা থেকে সতর্ক থাকা এই হাদিসের মূল শিক্ষা।"},"teachings":["ঘরে প্রাণীর ছবি টাঙ্গানো থেকে সতর্ক থাকা উচিত।","আল্লাহর সৃষ্টির সাদৃশ্য বানানো গুরুতর সতর্কতার বিষয়।","ছবিযুক্ত জিনিস সম্মানের জায়গায় না রেখে ব্যবহার বদলানো হাদিসে এসেছে।","ঘরের পরিবেশ এমন রাখা দরকার, যাতে রহমতের ফেরেশতা আসার বাধা না থাকে।"],"related_hadiths":[{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"5958","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুকুর ও ছবি থাকা ঘরের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ঘরে কুকুর বা ছবি থাকলে ফেরেশতা প্রবেশ করেন না—এ শিক্ষা ঘরকে পবিত্র রাখার কথা স্মরণ করায়।"},"heading":{"title":"কুকুর বা ছবি থাকা ঘরে ফেরেশতা প্রবেশ না করার শিক্ষা","description":"এই হাদিসে ঘরের ভেতরে কুকুর ও ছবি থাকার বিষয়ে স্পষ্ট সতর্কতা এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) চিন্তিত ছিলেন, কারণ জিব্রীল (আঃ) সাক্ষাতের ওয়াদা করেও আসেননি। পরে জানা গেল, তাঁর খাটের নিচে একটি কুকুর ছানা ছিল। সেটি বের করা হলো এবং জায়গায় পানি ছিটানো হলো। পরে জিব্রীল (আঃ) এসে বললেন, আমরা এমন ঘরে প্রবেশ করি না, যেখানে কুকুর বা ছবি থাকে। এরপর কুকুর বিষয়ে নির্দেশের কথাও এসেছে, তবে ছোট বাগানের হেফাযতে রাখা কুকুর ছেড়ে দেওয়া হয়েছে বলে বর্ণনায় আছে। তাই এই হাদিসে ঘরের ভেতরের পরিবেশ, অপ্রয়োজনীয় কুকুর রাখা এবং ছবি রাখার বিষয়ে সতর্কতা প্রধান শিক্ষা। এতে অযথা কঠোরতা নয়, বরং হাদিসে যে সীমা এসেছে, সেটি বোঝা জরুরি।"},"teachings":["ঘরের ভেতরে অপ্রয়োজনীয় কুকুর রাখা থেকে সতর্ক থাকতে হবে।","ঘরে ছবি থাকলে ফেরেশতা প্রবেশ না করার কথা হাদিসে এসেছে।","সমস্যার কারণ জানা গেলে তা সরিয়ে ঘর পরিষ্কার রাখা উচিত।","হাদিসে বাগান হেফাযতের কুকুরের আলাদা উল্লেখ আছে—এক বিষয়কে অন্য বিষয়ের সঙ্গে মেলানো ঠিক নয়।"],"related_hadiths":[{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯5৮","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুকুর ও ছবি থাকা ঘরের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ঘরে কুকুর বা ছবি থাকলে ফেরেশতা প্রবেশ করেন না—এ শিক্ষা ঘরকে পবিত্র রাখার কথা স্মরণ করায়।"},"heading":{"title":"কুকুর বা ছবি থাকা ঘরে ফেরেশতা প্রবেশ না করার শিক্ষা","description":"এই হাদিসে ঘরের ভেতরে কুকুর ও ছবি থাকার বিষয়ে স্পষ্ট সতর্কতা এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) চিন্তিত ছিলেন, কারণ জিব্রীল (আঃ) সাক্ষাতের ওয়াদা করেও আসেননি। পরে জানা গেল, তাঁর খাটের নিচে একটি কুকুর ছানা ছিল। সেটি বের করা হলো এবং জায়গায় পানি ছিটানো হলো। পরে জিব্রীল (আঃ) এসে বললেন, আমরা এমন ঘরে প্রবেশ করি না, যেখানে কুকুর বা ছবি থাকে। এরপর কুকুর বিষয়ে নির্দেশের কথাও এসেছে, তবে ছোট বাগানের হেফাযতে রাখা কুকুর ছেড়ে দেওয়া হয়েছে বলে বর্ণনায় আছে। তাই এই হাদিসে ঘরের ভেতরের পরিবেশ, অপ্রয়োজনীয় কুকুর রাখা এবং ছবি রাখার বিষয়ে সতর্কতা প্রধান শিক্ষা। এতে অযথা কঠোরতা নয়, বরং হাদিসে যে সীমা এসেছে, সেটি বোঝা জরুরি।"},"teachings":["ঘরের ভেতরে অপ্রয়োজনীয় কুকুর রাখা থেকে সতর্ক থাকতে হবে।","ঘরে ছবি থাকলে ফেরেশতা প্রবেশ না করার কথা হাদিসে এসেছে।","সমস্যার কারণ জানা গেলে তা সরিয়ে ঘর পরিষ্কার রাখা উচিত।","হাদিসে বাগান হেফাযতের কুকুরের আলাদা উল্লেখ আছে—এক বিষয়কে অন্য বিষয়ের সঙ্গে মেলানো ঠিক নয়।"],"related_hadiths":[{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"},{"id":"5958","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দেওয়ালে পর্দা লাগানো নিয়ে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. বিয়ের ঘর সাজাতে দেওয়াল ঢেকে পর্দা লাগানো দেখে আবু আইয়ুবের অপছন্দের শিক্ষা।"},"heading":{"title":"দেওয়ালে পর্দা লাগানো: বিয়ের ঘর সাজানোর সীমা নিয়ে শিক্ষা","description":"এই বর্ণনার মূল বিষয় হলো বিয়ের ঘর সাজাতে বাড়াবাড়ি এবং দেওয়ালে পর্দা লাগানো। বর্ণনাকারী বলেন, তাঁর বিয়ের সময় লোকজনকে দাওয়াত দেওয়া হয়েছিল। একজন ঘরটি সবুজ কাপড়, বিছানা ও বালিশ দিয়ে সাজান। আবু আইয়ুব (রাঃ) এসে দেখেন ঘরের দেওয়াল সবুজ কাপড় দিয়ে ঢাকা। তিনি প্রশ্ন করেন, তোমরা কি দেওয়ালে পর্দা লাগাও? এতে তাঁর অপছন্দ স্পষ্ট হয়। বর্ণনায় দেখা যায়, তিনি খাবার খেতে ও ঘরে প্রবেশ করতে অস্বীকার করে বেরিয়ে যান। এখানে ছবির প্রসঙ্গ নেই, বরং দেওয়াল ঢেকে সাজানোর বিষয় আছে। তাই ব্যাখ্যায় এই ঘটনার সীমার মধ্যেই থাকা দরকার। শিক্ষা হলো, বিয়ে বা ওয়ালীমার আয়োজনেও সরলতা রাখা, অপচয় ও বাড়তি সাজসজ্জা থেকে বেঁচে থাকা এবং সাহাবীদের সংবেদনশীলতা বোঝা।"},"teachings":["বিয়ের ঘর সাজাতে বাড়াবাড়ি করা থেকে সতর্ক থাকা উচিত।","দেওয়াল ঢেকে পর্দা লাগানো সাহাবীর কাছে অপছন্দনীয় ছিল।","দাওয়াতের আয়োজনেও সরলতা ও সংযম রাখা ভালো।","কোনো কাজ অপছন্দনীয় মনে হলে নম্রভাবে সতর্ক করা একটি শিক্ষা।"],"related_hadiths":[{"id":"5৯5৮","book_id":"1","label":"Sahih Bukhari"},{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দেওয়ালে পর্দা লাগানো নিয়ে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. বিয়ের ঘর সাজাতে দেওয়াল ঢেকে পর্দা লাগানো দেখে আবু আইয়ুবের অপছন্দের শিক্ষা।"},"heading":{"title":"দেওয়ালে পর্দা লাগানো: বিয়ের ঘর সাজানোর সীমা নিয়ে শিক্ষা","description":"এই বর্ণনার মূল বিষয় হলো বিয়ের ঘর সাজাতে বাড়াবাড়ি এবং দেওয়ালে পর্দা লাগানো। বর্ণনাকারী বলেন, তাঁর বিয়ের সময় লোকজনকে দাওয়াত দেওয়া হয়েছিল। একজন ঘরটি সবুজ কাপড়, বিছানা ও বালিশ দিয়ে সাজান। আবু আইয়ুব (রাঃ) এসে দেখেন ঘরের দেওয়াল সবুজ কাপড় দিয়ে ঢাকা। তিনি প্রশ্ন করেন, তোমরা কি দেওয়ালে পর্দা লাগাও? এতে তাঁর অপছন্দ স্পষ্ট হয়। বর্ণনায় দেখা যায়, তিনি খাবার খেতে ও ঘরে প্রবেশ করতে অস্বীকার করে বেরিয়ে যান। এখানে ছবির প্রসঙ্গ নেই, বরং দেওয়াল ঢেকে সাজানোর বিষয় আছে। তাই ব্যাখ্যায় এই ঘটনার সীমার মধ্যেই থাকা দরকার। শিক্ষা হলো, বিয়ে বা ওয়ালীমার আয়োজনেও সরলতা রাখা, অপচয় ও বাড়তি সাজসজ্জা থেকে বেঁচে থাকা এবং সাহাবীদের সংবেদনশীলতা বোঝা।"},"teachings":["বিয়ের ঘর সাজাতে বাড়াবাড়ি করা থেকে সতর্ক থাকা উচিত।","দেওয়াল ঢেকে পর্দা লাগানো সাহাবীর কাছে অপছন্দনীয় ছিল।","দাওয়াতের আয়োজনেও সরলতা ও সংযম রাখা ভালো।","কোনো কাজ অপছন্দনীয় মনে হলে নম্রভাবে সতর্ক করা একটি শিক্ষা।"],"related_hadiths":[{"id":"5958","book_id":"1","label":"Sahih Bukhari"},{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত স্থানে প্রবেশ নিয়ে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ওমর (রাঃ) গীর্জায় ছবি থাকার কারণে সেখানে প্রবেশ না করার কথা জানান।"},"heading":{"title":"ছবিযুক্ত স্থানে প্রবেশ: ওমর (রাঃ)-এর সতর্ক অবস্থান","description":"এই বর্ণনায় ছবিযুক্ত স্থানে প্রবেশের বিষয়ে ওমর (রাঃ)-এর অবস্থান এসেছে। সিরিয়ায় এক সম্মানিত খ্রিস্টান ব্যক্তি তাঁর জন্য খাবার তৈরি করেন এবং ওমর (রাঃ) ও তাঁর সাথীদের বাড়িতে এসে তাকে সম্মানিত করতে অনুরোধ করেন। ওমর (রাঃ) তাকে বলেন, তোমাদের গীর্জায় ছবি থাকার কারণে আমরা সেখানে প্রবেশ করি না। এখানে বর্ণনাটি গীর্জা, দাওয়াত এবং ছবি—এই তিনটি বিষয়ের সঙ্গে যুক্ত। হাদিসের আলোচনায় মূল কথা হলো, সম্মানিত দাওয়াত হলেও ছবিযুক্ত স্থানের বিষয়ে সতর্কতা রাখা। তবে এই বর্ণনা থেকে বাড়তি কোনো ঘটনা বা আলাদা বিধান বানিয়ে বলা ঠিক নয়। সহজ শিক্ষা হলো, যেখানে দ্বীনের দিক থেকে আপত্তির বিষয় থাকে, সেখানে সামাজিক সম্মান বা দাওয়াতের চাপেও একজন মুমিন সতর্ক থাকতে পারে।"},"teachings":["ছবিযুক্ত স্থানে প্রবেশের বিষয়ে সতর্কতা রাখা সাহাবীদের আমলে দেখা যায়।","সম্মানিত দাওয়াত হলেও দ্বীনের সীমা মনে রাখা দরকার।","ওমর (রাঃ) স্পষ্টভাবে কারণ জানিয়ে নিজের অবস্থান বলেছেন।","সামাজিক সম্পর্ক রাখতে গিয়ে শরিয়তের সতর্কতা ভুলে যাওয়া উচিত নয়।"],"related_hadiths":[{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯5৮","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত স্থানে প্রবেশ নিয়ে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ওমর (রাঃ) গীর্জায় ছবি থাকার কারণে সেখানে প্রবেশ না করার কথা জানান।"},"heading":{"title":"ছবিযুক্ত স্থানে প্রবেশ: ওমর (রাঃ)-এর সতর্ক অবস্থান","description":"এই বর্ণনায় ছবিযুক্ত স্থানে প্রবেশের বিষয়ে ওমর (রাঃ)-এর অবস্থান এসেছে। সিরিয়ায় এক সম্মানিত খ্রিস্টান ব্যক্তি তাঁর জন্য খাবার তৈরি করেন এবং ওমর (রাঃ) ও তাঁর সাথীদের বাড়িতে এসে তাকে সম্মানিত করতে অনুরোধ করেন। ওমর (রাঃ) তাকে বলেন, তোমাদের গীর্জায় ছবি থাকার কারণে আমরা সেখানে প্রবেশ করি না। এখানে বর্ণনাটি গীর্জা, দাওয়াত এবং ছবি—এই তিনটি বিষয়ের সঙ্গে যুক্ত। হাদিসের আলোচনায় মূল কথা হলো, সম্মানিত দাওয়াত হলেও ছবিযুক্ত স্থানের বিষয়ে সতর্কতা রাখা। তবে এই বর্ণনা থেকে বাড়তি কোনো ঘটনা বা আলাদা বিধান বানিয়ে বলা ঠিক নয়। সহজ শিক্ষা হলো, যেখানে দ্বীনের দিক থেকে আপত্তির বিষয় থাকে, সেখানে সামাজিক সম্মান বা দাওয়াতের চাপেও একজন মুমিন সতর্ক থাকতে পারে।"},"teachings":["ছবিযুক্ত স্থানে প্রবেশের বিষয়ে সতর্কতা রাখা সাহাবীদের আমলে দেখা যায়।","সম্মানিত দাওয়াত হলেও দ্বীনের সীমা মনে রাখা দরকার।","ওমর (রাঃ) স্পষ্টভাবে কারণ জানিয়ে নিজের অবস্থান বলেছেন।","সামাজিক সম্পর্ক রাখতে গিয়ে শরিয়তের সতর্কতা ভুলে যাওয়া উচিত নয়।"],"related_hadiths":[{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"5958","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে ছবি থাকলে প্রবেশ না করা","description":"$book_name$ $hadith_number$ - $chapter_name$. ঘরে ছবি থাকায় প্রবেশে অস্বীকৃতি এবং ছবি ভেঙে ফেলার পর প্রবেশ করার শিক্ষা।"},"heading":{"title":"ঘরে ছবি থাকলে প্রবেশ না করা: সাহাবীর আমলের শিক্ষা","description":"এই বর্ণনার মূল শিক্ষা হলো ঘরে ছবি থাকার বিষয়ে সতর্কতা। এক ব্যক্তি খাবার তৈরি করে দাওয়াত দিলেন। দাওয়াত গ্রহণের আগে জিজ্ঞেস করা হলো, ঘরে কি ছবি আছে? যখন বলা হলো, হ্যাঁ, তখন তিনি ঘরে প্রবেশ করতে অস্বীকার করলেন। পরে ছবি ভেঙে ফেলা হলে তিনি প্রবেশ করলেন। এখানে বিষয়টি খুব সরাসরি: দাওয়াত, ঘরের ছবি এবং ছবির কারণে প্রবেশ না করা। তাই ব্যাখ্যায় এটিকে অন্য ঘটনার সঙ্গে মিশিয়ে ফেলা ঠিক নয়। এই বর্ণনা আমাদের মনে করায়, খাবার বা দাওয়াতের আকর্ষণ থাকলেও ঘরের পরিবেশ ও দ্বীনি সতর্কতা গুরুত্বপূর্ণ। ছবি সরানো হলে প্রবেশ করার বিষয়টি দেখায়, আপত্তির কারণ দূর হলে সম্পর্ক বা দাওয়াত গ্রহণে বাধা থাকে না।"},"teachings":["দাওয়াতের ঘরে ছবি থাকলে সতর্কতা রাখা উচিত।","আপত্তির কারণ দূর হলে দাওয়াত গ্রহণ করা যায়—বর্ণনায় এমন আমল এসেছে।","ছবি সম্পর্কে সাহাবীদের সংবেদনশীলতা ছিল।","দ্বীনি সতর্কতা সামাজিক সৌজন্যের সঙ্গে মিলিয়ে রাখা দরকার।"],"related_hadiths":[{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯5৮","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে ছবি থাকলে প্রবেশ না করা","description":"$book_name$ $hadith_number$ - $chapter_name$. ঘরে ছবি থাকায় প্রবেশে অস্বীকৃতি এবং ছবি ভেঙে ফেলার পর প্রবেশ করার শিক্ষা।"},"heading":{"title":"ঘরে ছবি থাকলে প্রবেশ না করা: সাহাবীর আমলের শিক্ষা","description":"এই বর্ণনার মূল শিক্ষা হলো ঘরে ছবি থাকার বিষয়ে সতর্কতা। এক ব্যক্তি খাবার তৈরি করে দাওয়াত দিলেন। দাওয়াত গ্রহণের আগে জিজ্ঞেস করা হলো, ঘরে কি ছবি আছে? যখন বলা হলো, হ্যাঁ, তখন তিনি ঘরে প্রবেশ করতে অস্বীকার করলেন। পরে ছবি ভেঙে ফেলা হলে তিনি প্রবেশ করলেন। এখানে বিষয়টি খুব সরাসরি: দাওয়াত, ঘরের ছবি এবং ছবির কারণে প্রবেশ না করা। তাই ব্যাখ্যায় এটিকে অন্য ঘটনার সঙ্গে মিশিয়ে ফেলা ঠিক নয়। এই বর্ণনা আমাদের মনে করায়, খাবার বা দাওয়াতের আকর্ষণ থাকলেও ঘরের পরিবেশ ও দ্বীনি সতর্কতা গুরুত্বপূর্ণ। ছবি সরানো হলে প্রবেশ করার বিষয়টি দেখায়, আপত্তির কারণ দূর হলে সম্পর্ক বা দাওয়াত গ্রহণে বাধা থাকে না।"},"teachings":["দাওয়াতের ঘরে ছবি থাকলে সতর্কতা রাখা উচিত।","আপত্তির কারণ দূর হলে দাওয়াত গ্রহণ করা যায়—বর্ণনায় এমন আমল এসেছে।","ছবি সম্পর্কে সাহাবীদের সংবেদনশীলতা ছিল।","দ্বীনি সতর্কতা সামাজিক সৌজন্যের সঙ্গে মিলিয়ে রাখা দরকার।"],"related_hadiths":[{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"5958","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ওয়ালীমায় বাদ্যযন্ত্র থেকে বাঁচা","description":"$book_name$ $hadith_number$ - $chapter_name$. তবলা ও বাদ্যযন্ত্র থাকা ওয়ালীমাতে না যাওয়ার সংক্ষিপ্ত কিন্তু স্পষ্ট সতর্কতা।"},"heading":{"title":"ওয়ালীমায় বাদ্যযন্ত্র: দাওয়াত গ্রহণে সতর্কতার শিক্ষা","description":"এই বর্ণনার মূল বিষয় হলো ওয়ালীমা বা বিয়ের দাওয়াতে তবলা ও বাদ্যযন্ত্র থাকা। ইমাম আওযাঈ (রহ.) বলেন, আমরা এমন ওয়ালীমাতে যাই না, যেখানে তবলা ও বাদ্যযন্ত্র থাকে। বর্ণনাটি খুব সংক্ষিপ্ত, তাই এর ব্যাখ্যাও সীমিত রাখা দরকার। এখানে খাবার, বিয়ে বা দাওয়াতকে খারাপ বলা হয়নি; বরং নির্দিষ্টভাবে তবলা ও বাদ্যযন্ত্র থাকা ওয়ালীমার কথা বলা হয়েছে। তাই শিক্ষা হলো, আনন্দের আয়োজন হলেও এমন উপাদান থেকে দূরে থাকা, যা দ্বীনি দৃষ্টিতে আপত্তিকর হতে পারে। ওয়ালীমা ইসলামী জীবনের একটি সামাজিক আয়োজন, কিন্তু সেই আয়োজন যেন সীমার বাইরে না যায়। এই হাদিসভিত্তিক সার্চে মানুষ সাধারণত “ওয়ালিমায় গান বাজনা”, “বাদ্যযন্ত্র হাদিস” এবং “বিয়েতে তবলা” জাতীয় শব্দ খোঁজে।"},"teachings":["ওয়ালীমার দাওয়াতে বাদ্যযন্ত্র থাকলে সতর্ক থাকা দরকার।","বিয়ের আনন্দও শরিয়তের সীমার ভেতরে রাখা উচিত।","দাওয়াত গ্রহণের আগে পরিবেশ সম্পর্কে জানা উপকারী হতে পারে।","সংক্ষিপ্ত বর্ণনা থেকে অতিরিক্ত দাবি করা ঠিক নয়।"],"related_hadiths":[{"id":"55৯0","book_id":"1","label":"Sahih Bukhari"},{"id":"৯4৯","book_id":"1","label":"Sahih Bukhari"},{"id":"৯52","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ওয়ালীমায় বাদ্যযন্ত্র থেকে বাঁচা","description":"$book_name$ $hadith_number$ - $chapter_name$. তবলা ও বাদ্যযন্ত্র থাকা ওয়ালীমাতে না যাওয়ার সংক্ষিপ্ত কিন্তু স্পষ্ট সতর্কতা।"},"heading":{"title":"ওয়ালীমায় বাদ্যযন্ত্র: দাওয়াত গ্রহণে সতর্কতার শিক্ষা","description":"এই বর্ণনার মূল বিষয় হলো ওয়ালীমা বা বিয়ের দাওয়াতে তবলা ও বাদ্যযন্ত্র থাকা। ইমাম আওযাঈ (রহ.) বলেন, আমরা এমন ওয়ালীমাতে যাই না, যেখানে তবলা ও বাদ্যযন্ত্র থাকে। বর্ণনাটি খুব সংক্ষিপ্ত, তাই এর ব্যাখ্যাও সীমিত রাখা দরকার। এখানে খাবার, বিয়ে বা দাওয়াতকে খারাপ বলা হয়নি; বরং নির্দিষ্টভাবে তবলা ও বাদ্যযন্ত্র থাকা ওয়ালীমার কথা বলা হয়েছে। তাই শিক্ষা হলো, আনন্দের আয়োজন হলেও এমন উপাদান থেকে দূরে থাকা, যা দ্বীনি দৃষ্টিতে আপত্তিকর হতে পারে। ওয়ালীমা ইসলামী জীবনের একটি সামাজিক আয়োজন, কিন্তু সেই আয়োজন যেন সীমার বাইরে না যায়। এই হাদিসভিত্তিক সার্চে মানুষ সাধারণত “ওয়ালিমায় গান বাজনা”, “বাদ্যযন্ত্র হাদিস” এবং “বিয়েতে তবলা” জাতীয় শব্দ খোঁজে।"},"teachings":["ওয়ালীমার দাওয়াতে বাদ্যযন্ত্র থাকলে সতর্ক থাকা দরকার।","বিয়ের আনন্দও শরিয়তের সীমার ভেতরে রাখা উচিত।","দাওয়াত গ্রহণের আগে পরিবেশ সম্পর্কে জানা উপকারী হতে পারে।","সংক্ষিপ্ত বর্ণনা থেকে অতিরিক্ত দাবি করা ঠিক নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"949","book_id":"1","label":"Sahih Bukhari"},{"id":"952","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুদ নেওয়া-দেওয়ার ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সুদ গ্রহণকারী, প্রদানকারী, লেখক ও সাক্ষীদের একই সতর্কতার আওতায় আনার শিক্ষা।"},"heading":{"title":"সুদ নেওয়া ও দেওয়া: রিবা থেকে বাঁচার কঠোর সতর্কতা","description":"এই হাদিসের মূল বিষয় হলো সুদ বা রিবা। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সুদ গ্রহণকারী, সুদ প্রদানকারী, সুদের লেখক এবং সুদের দুই সাক্ষীর প্রতি অভিশাপ করেছেন। এরপর বলেছেন, অভিশাপে তারা সবাই সমান। এখানে শুধু সুদ খাওয়ার কথাই নেই; বরং যারা লেনদেনটি চালাতে সাহায্য করে, লেখে বা সাক্ষী থাকে, তাদের কথাও এসেছে। তাই ইসলামে সুদ থেকে বাঁচা মানে শুধু নিজের লাভের সুদ না নেওয়া নয়, বরং সুদের কাজে অংশ না নেওয়ার সতর্কতাও আছে। তবে হাদিসে যে চারটি ভূমিকা এসেছে, ব্যাখ্যায় সেটিতেই থাকা দরকার। বর্তমান জীবনে এই শিক্ষা আর্থিক লেনদেনের সময় সতর্কতা, হালাল উপার্জন এবং সন্দেহজনক চুক্তি এড়িয়ে চলার কথা মনে করায়।"},"teachings":["সুদ গ্রহণ ও প্রদান—দুটিই গুরুতর সতর্কতার বিষয়।","সুদের লেখক ও সাক্ষীর ভূমিকাও হাদিসে উল্লেখ হয়েছে।","আর্থিক চুক্তিতে হালাল-হারামের দিক দেখা জরুরি।","সুদের কাজে সহায়তা করা থেকেও সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"20৮5","book_id":"1","label":"Sahih Bukhari"},{"id":"20৮6","book_id":"1","label":"Sahih Bukhari"},{"id":"20৮7","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুদ নেওয়া-দেওয়ার ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সুদ গ্রহণকারী, প্রদানকারী, লেখক ও সাক্ষীদের একই সতর্কতার আওতায় আনার শিক্ষা।"},"heading":{"title":"সুদ নেওয়া ও দেওয়া: রিবা থেকে বাঁচার কঠোর সতর্কতা","description":"এই হাদিসের মূল বিষয় হলো সুদ বা রিবা। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সুদ গ্রহণকারী, সুদ প্রদানকারী, সুদের লেখক এবং সুদের দুই সাক্ষীর প্রতি অভিশাপ করেছেন। এরপর বলেছেন, অভিশাপে তারা সবাই সমান। এখানে শুধু সুদ খাওয়ার কথাই নেই; বরং যারা লেনদেনটি চালাতে সাহায্য করে, লেখে বা সাক্ষী থাকে, তাদের কথাও এসেছে। তাই ইসলামে সুদ থেকে বাঁচা মানে শুধু নিজের লাভের সুদ না নেওয়া নয়, বরং সুদের কাজে অংশ না নেওয়ার সতর্কতাও আছে। তবে হাদিসে যে চারটি ভূমিকা এসেছে, ব্যাখ্যায় সেটিতেই থাকা দরকার। বর্তমান জীবনে এই শিক্ষা আর্থিক লেনদেনের সময় সতর্কতা, হালাল উপার্জন এবং সন্দেহজনক চুক্তি এড়িয়ে চলার কথা মনে করায়।"},"teachings":["সুদ গ্রহণ ও প্রদান—দুটিই গুরুতর সতর্কতার বিষয়।","সুদের লেখক ও সাক্ষীর ভূমিকাও হাদিসে উল্লেখ হয়েছে।","আর্থিক চুক্তিতে হালাল-হারামের দিক দেখা জরুরি।","সুদের কাজে সহায়তা করা থেকেও সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"2085","book_id":"1","label":"Sahih Bukhari"},{"id":"2086","book_id":"1","label":"Sahih Bukhari"},{"id":"2087","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জেনে সুদ গ্রহণের ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. জেনে শুনে সামান্য সুদ গ্রহণকেও ভয়ংকর পাপ হিসেবে সতর্ক করা হয়েছে।"},"heading":{"title":"জেনে শুনে সুদ গ্রহণ: এক দিরহাম রিবার কঠিন সতর্কতা","description":"এই হাদিসে জেনে শুনে সুদ গ্রহণের ভয়াবহতা বলা হয়েছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কোনো ব্যক্তি জেনে শুনে এক দিরহাম বা একটি মুদ্রা সুদ গ্রহণ করলে তা ছত্রিশবার যেনা করার চেয়ে কঠিন হবে। এখানে মূল শব্দ হলো “জেনে শুনে”। অর্থাৎ মানুষ যখন বুঝে যে এটি সুদ, তবু গ্রহণ করে, তখন বিষয়টি খুব কঠিন সতর্কতার মধ্যে পড়ে। এই হাদিসের ব্যাখ্যায় অতিরিক্ত আর্থিক তত্ত্ব যোগ করার দরকার নেই; মূল শিক্ষা হলো, ছোট অঙ্কের সুদকেও হালকা মনে না করা। অনেক সময় মানুষ বলে “এ তো সামান্য”, কিন্তু হাদিসে সামান্য এক দিরহামের কথাই এসেছে। তাই রিবা, ব্যাংক সুদ বা ব্যক্তিগত ঋণের বাড়তি সুবিধা—যাই হোক, আগে যাচাই করা এবং আল্লাহকে ভয় করা জরুরি।"},"teachings":["জেনে শুনে সামান্য সুদ গ্রহণও হালকা বিষয় নয়।","হারাম লেনদেনে অঙ্ক ছোট হলেও সতর্কতা কমে না।","সুদকে সাধারণ লাভ মনে করে নেওয়া বিপজ্জনক হতে পারে।","লেনদেনের আগে তা সুদ কিনা বোঝার চেষ্টা করা দরকার।"],"related_hadiths":[{"id":"20৮5","book_id":"1","label":"Sahih Bukhari"},{"id":"20৮6","book_id":"1","label":"Sahih Bukhari"},{"id":"20৮7","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জেনে সুদ গ্রহণের ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. জেনে শুনে সামান্য সুদ গ্রহণকেও ভয়ংকর পাপ হিসেবে সতর্ক করা হয়েছে।"},"heading":{"title":"জেনে শুনে সুদ গ্রহণ: এক দিরহাম রিবার কঠিন সতর্কতা","description":"এই হাদিসে জেনে শুনে সুদ গ্রহণের ভয়াবহতা বলা হয়েছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কোনো ব্যক্তি জেনে শুনে এক দিরহাম বা একটি মুদ্রা সুদ গ্রহণ করলে তা ছত্রিশবার যেনা করার চেয়ে কঠিন হবে। এখানে মূল শব্দ হলো “জেনে শুনে”। অর্থাৎ মানুষ যখন বুঝে যে এটি সুদ, তবু গ্রহণ করে, তখন বিষয়টি খুব কঠিন সতর্কতার মধ্যে পড়ে। এই হাদিসের ব্যাখ্যায় অতিরিক্ত আর্থিক তত্ত্ব যোগ করার দরকার নেই; মূল শিক্ষা হলো, ছোট অঙ্কের সুদকেও হালকা মনে না করা। অনেক সময় মানুষ বলে “এ তো সামান্য”, কিন্তু হাদিসে সামান্য এক দিরহামের কথাই এসেছে। তাই রিবা, ব্যাংক সুদ বা ব্যক্তিগত ঋণের বাড়তি সুবিধা—যাই হোক, আগে যাচাই করা এবং আল্লাহকে ভয় করা জরুরি।"},"teachings":["জেনে শুনে সামান্য সুদ গ্রহণও হালকা বিষয় নয়।","হারাম লেনদেনে অঙ্ক ছোট হলেও সতর্কতা কমে না।","সুদকে সাধারণ লাভ মনে করে নেওয়া বিপজ্জনক হতে পারে।","লেনদেনের আগে তা সুদ কিনা বোঝার চেষ্টা করা দরকার।"],"related_hadiths":[{"id":"2085","book_id":"1","label":"Sahih Bukhari"},{"id":"2086","book_id":"1","label":"Sahih Bukhari"},{"id":"2087","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুখ বন্ধ ও শরীরের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে মুখ বন্ধ রাখা হবে এবং উরু ও কাঁধকে প্রথমে জিজ্ঞেস করা হবে—হাদিসটি জবাবদিহি শেখায়।"},"heading":{"title":"মুখ বন্ধ হলে উরু ও কাঁধের সাক্ষ্য: কিয়ামতের শিক্ষা","description":"এই হাদিসে নবী কারীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কিয়ামতের দিন মানুষকে এমন অবস্থায় ডাকা হবে, যখন তাদের মুখ বন্ধ থাকবে। তখন সর্বপ্রথম মানুষের উরু এবং কাঁধকে জিজ্ঞেস করা হবে। হাদিসের বক্তব্য সংক্ষিপ্ত, কিন্তু এর শিক্ষা স্পষ্ট। মানুষ দুনিয়ায় অনেক কিছু মুখে অস্বীকার করতে পারে, কিন্তু আখেরাতে আল্লাহর সামনে সত্য প্রকাশ পাবে। শরীরের অঙ্গ-প্রত্যঙ্গও সাক্ষ্য দিতে পারে—এটা কিয়ামতের জবাবদিহির বড় সতর্কতা। এই হাদিস আমাদের শেখায়, কাজ করার আগে ভাবতে হবে, একদিন সেই কাজের হিসাব দিতে হবে। মুখ বন্ধ থাকলেও আমল লুকিয়ে থাকবে না।"},"teachings":["কিয়ামতে মুখ বন্ধ থাকলেও সত্য প্রকাশ পাবে।","উরু ও কাঁধের সাক্ষ্যের কথা হাদিসে এসেছে।","মানুষের কাজ আল্লাহর কাছে লুকানো নয়।","দুনিয়ার আমল নিয়ে আখেরাতে জবাবদিহি আছে।"],"related_hadiths":[{"id":"2৯6৯","book_id":"2","label":"Sahih Muslim"},{"id":"5554","book_id":"14","label":"Mishkat al-Masabih"},{"id":"21৮1","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুখ বন্ধ ও শরীরের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে মুখ বন্ধ রাখা হবে এবং উরু ও কাঁধকে প্রথমে জিজ্ঞেস করা হবে—হাদিসটি জবাবদিহি শেখায়।"},"heading":{"title":"মুখ বন্ধ হলে উরু ও কাঁধের সাক্ষ্য: কিয়ামতের শিক্ষা","description":"এই হাদিসে নবী কারীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কিয়ামতের দিন মানুষকে এমন অবস্থায় ডাকা হবে, যখন তাদের মুখ বন্ধ থাকবে। তখন সর্বপ্রথম মানুষের উরু এবং কাঁধকে জিজ্ঞেস করা হবে। হাদিসের বক্তব্য সংক্ষিপ্ত, কিন্তু এর শিক্ষা স্পষ্ট। মানুষ দুনিয়ায় অনেক কিছু মুখে অস্বীকার করতে পারে, কিন্তু আখেরাতে আল্লাহর সামনে সত্য প্রকাশ পাবে। শরীরের অঙ্গ-প্রত্যঙ্গও সাক্ষ্য দিতে পারে—এটা কিয়ামতের জবাবদিহির বড় সতর্কতা। এই হাদিস আমাদের শেখায়, কাজ করার আগে ভাবতে হবে, একদিন সেই কাজের হিসাব দিতে হবে। মুখ বন্ধ থাকলেও আমল লুকিয়ে থাকবে না।"},"teachings":["কিয়ামতে মুখ বন্ধ থাকলেও সত্য প্রকাশ পাবে।","উরু ও কাঁধের সাক্ষ্যের কথা হাদিসে এসেছে।","মানুষের কাজ আল্লাহর কাছে লুকানো নয়।","দুনিয়ার আমল নিয়ে আখেরাতে জবাবদিহি আছে।"],"related_hadiths":[{"id":"2969","book_id":"2","label":"Sahih Muslim"},{"id":"5554","book_id":"14","label":"Mishkat al-Masabih"},{"id":"2181","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুদের পাপের স্তর","description":"$book_name$ $hadith_number$ - $chapter_name$. সুদের পাপের বহু স্তর আছে—এই হাদিস রিবা থেকে দূরে থাকার শক্ত সতর্কতা দেয়।"},"heading":{"title":"সুদের পাপের স্তর: রিবা থেকে দূরে থাকার শিক্ষা","description":"এই হাদিসে সুদের পাপকে খুব কঠিন ভাষায় সতর্ক করা হয়েছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, সুদের পাপের ৭০টি স্তর রয়েছে; তার মধ্যে সবচেয়ে সাধারণ স্তরও নিজের মাতাকে বিবাহ করার মতো ভয়াবহ উদাহরণ দিয়ে বোঝানো হয়েছে। এই ভাষা আমাদের জানায়, রিবা শুধু অর্থনৈতিক ভুল নয়; এটি বড় নৈতিক ও দ্বীনি বিপদের বিষয়। তবে ব্যাখ্যায় হাদিসের শব্দের বাইরে গিয়ে নির্দিষ্ট লোকের ব্যাপারে রায় দেওয়া উচিত নয়। মূল শিক্ষা হলো, সুদকে ছোট, আধুনিক বা সাধারণ সুবিধা মনে না করা। মুসলিমের আয়, ঋণ, ব্যবসা ও চুক্তি যতটা সম্ভব পরিষ্কার ও হালাল পথে রাখা প্রয়োজন। এই হাদিস “সুদের পাপ”, “রিবার স্তর” এবং “সুদ হারাম” বিষয়ে মানুষের খোঁজার সঙ্গে সরাসরি যুক্ত।"},"teachings":["সুদকে সাধারণ আর্থিক লাভ মনে করা ঠিক নয়।","রিবার পাপের স্তর সম্পর্কে হাদিসে কঠিন সতর্কতা এসেছে।","লেনদেনে সন্দেহ হলে জ্ঞানীদের কাছে জেনে নেওয়া ভালো।","হালাল উপার্জন রক্ষায় সুদ থেকে দূরে থাকা জরুরি।"],"related_hadiths":[{"id":"20৮5","book_id":"1","label":"Sahih Bukhari"},{"id":"20৮6","book_id":"1","label":"Sahih Bukhari"},{"id":"20৮7","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুদের পাপের স্তর","description":"$book_name$ $hadith_number$ - $chapter_name$. সুদের পাপের বহু স্তর আছে—এই হাদিস রিবা থেকে দূরে থাকার শক্ত সতর্কতা দেয়।"},"heading":{"title":"সুদের পাপের স্তর: রিবা থেকে দূরে থাকার শিক্ষা","description":"এই হাদিসে সুদের পাপকে খুব কঠিন ভাষায় সতর্ক করা হয়েছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, সুদের পাপের ৭০টি স্তর রয়েছে; তার মধ্যে সবচেয়ে সাধারণ স্তরও নিজের মাতাকে বিবাহ করার মতো ভয়াবহ উদাহরণ দিয়ে বোঝানো হয়েছে। এই ভাষা আমাদের জানায়, রিবা শুধু অর্থনৈতিক ভুল নয়; এটি বড় নৈতিক ও দ্বীনি বিপদের বিষয়। তবে ব্যাখ্যায় হাদিসের শব্দের বাইরে গিয়ে নির্দিষ্ট লোকের ব্যাপারে রায় দেওয়া উচিত নয়। মূল শিক্ষা হলো, সুদকে ছোট, আধুনিক বা সাধারণ সুবিধা মনে না করা। মুসলিমের আয়, ঋণ, ব্যবসা ও চুক্তি যতটা সম্ভব পরিষ্কার ও হালাল পথে রাখা প্রয়োজন। এই হাদিস “সুদের পাপ”, “রিবার স্তর” এবং “সুদ হারাম” বিষয়ে মানুষের খোঁজার সঙ্গে সরাসরি যুক্ত।"},"teachings":["সুদকে সাধারণ আর্থিক লাভ মনে করা ঠিক নয়।","রিবার পাপের স্তর সম্পর্কে হাদিসে কঠিন সতর্কতা এসেছে।","লেনদেনে সন্দেহ হলে জ্ঞানীদের কাছে জেনে নেওয়া ভালো।","হালাল উপার্জন রক্ষায় সুদ থেকে দূরে থাকা জরুরি।"],"related_hadiths":[{"id":"2085","book_id":"1","label":"Sahih Bukhari"},{"id":"2086","book_id":"1","label":"Sahih Bukhari"},{"id":"2087","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুদের শেষ পরিণাম কমে যাওয়া","description":"$book_name$ $hadith_number$ - $chapter_name$. সুদ বাহ্যিকভাবে বাড়তি মনে হলেও এর পরিণাম সংকোচন—এ শিক্ষা রিবা থেকে সতর্ক করে।"},"heading":{"title":"সুদ বাড়তি মনে হলেও পরিণাম কমে যায়: রিবার শিক্ষা","description":"এই হাদিসে সুদের পরিণাম নিয়ে সংক্ষিপ্ত কিন্তু গভীর সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, সুদ এমন বস্তু যার পরিণাম সংকুচিত হওয়া, যদিও তা বৃদ্ধি মনে হয়। অর্থাৎ বাহ্যিকভাবে সুদে টাকা বাড়ছে বলে দেখা যেতে পারে, কিন্তু হাদিসে তার শেষ ফল কমে যাওয়া বলা হয়েছে। এখানে “তাৎক্ষণিক লাভ” আর “শেষ পরিণাম”—এই দুইটি দিক বোঝা জরুরি। অনেক মানুষ সুদকে সহজ আয় বা নিশ্চিন্ত লাভ মনে করে। কিন্তু হাদিস শেখায়, মুমিন শুধু চোখের সামনে থাকা বাড়তি অঙ্ক দেখে সিদ্ধান্ত নেয় না; বরং আল্লাহর নির্দেশ ও শেষ ফলের কথাও ভাবে। তাই আয়-রোজগার, ঋণ, বিনিয়োগ ও চুক্তিতে রিবার সন্দেহ থাকলে সতর্ক হওয়া দরকার।"},"teachings":["সুদ বাহ্যিকভাবে বাড়তি মনে হলেও হাদিসে তার পরিণাম ভালো বলা হয়নি।","তাৎক্ষণিক লাভ দেখে হারাম লেনদেনে জড়ানো উচিত নয়।","আর্থিক সিদ্ধান্তে আখিরাতের চিন্তা রাখা দরকার।","হালাল পথে কম আয়ও বরকতের কারণ হতে পারে—এমন আশা করা যায়।"],"related_hadiths":[{"id":"20৮5","book_id":"1","label":"Sahih Bukhari"},{"id":"20৮6","book_id":"1","label":"Sahih Bukhari"},{"id":"20৮7","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুদের শেষ পরিণাম কমে যাওয়া","description":"$book_name$ $hadith_number$ - $chapter_name$. সুদ বাহ্যিকভাবে বাড়তি মনে হলেও এর পরিণাম সংকোচন—এ শিক্ষা রিবা থেকে সতর্ক করে।"},"heading":{"title":"সুদ বাড়তি মনে হলেও পরিণাম কমে যায়: রিবার শিক্ষা","description":"এই হাদিসে সুদের পরিণাম নিয়ে সংক্ষিপ্ত কিন্তু গভীর সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, সুদ এমন বস্তু যার পরিণাম সংকুচিত হওয়া, যদিও তা বৃদ্ধি মনে হয়। অর্থাৎ বাহ্যিকভাবে সুদে টাকা বাড়ছে বলে দেখা যেতে পারে, কিন্তু হাদিসে তার শেষ ফল কমে যাওয়া বলা হয়েছে। এখানে “তাৎক্ষণিক লাভ” আর “শেষ পরিণাম”—এই দুইটি দিক বোঝা জরুরি। অনেক মানুষ সুদকে সহজ আয় বা নিশ্চিন্ত লাভ মনে করে। কিন্তু হাদিস শেখায়, মুমিন শুধু চোখের সামনে থাকা বাড়তি অঙ্ক দেখে সিদ্ধান্ত নেয় না; বরং আল্লাহর নির্দেশ ও শেষ ফলের কথাও ভাবে। তাই আয়-রোজগার, ঋণ, বিনিয়োগ ও চুক্তিতে রিবার সন্দেহ থাকলে সতর্ক হওয়া দরকার।"},"teachings":["সুদ বাহ্যিকভাবে বাড়তি মনে হলেও হাদিসে তার পরিণাম ভালো বলা হয়নি।","তাৎক্ষণিক লাভ দেখে হারাম লেনদেনে জড়ানো উচিত নয়।","আর্থিক সিদ্ধান্তে আখিরাতের চিন্তা রাখা দরকার।","হালাল পথে কম আয়ও বরকতের কারণ হতে পারে—এমন আশা করা যায়।"],"related_hadiths":[{"id":"2085","book_id":"1","label":"Sahih Bukhari"},{"id":"2086","book_id":"1","label":"Sahih Bukhari"},{"id":"2087","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘুষ দেওয়া-নেওয়ার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ঘুষ গ্রহণকারী ও প্রদানকারীর ওপর অভিশাপের হাদিস ন্যায় ও সততার শিক্ষা দেয়।"},"heading":{"title":"ঘুষ দেওয়া ও নেওয়া: ন্যায়বিচার নষ্ট করার বড় সতর্কতা","description":"এই হাদিসের মূল বিষয় হলো ঘুষ। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ঘুষ গ্রহণকারী ও ঘুষ প্রদানকারীর উপর অভিশাপ করেছেন। বর্ণনাটি ছোট হলেও শিক্ষা খুব স্পষ্ট। ঘুষ শুধু টাকা নেওয়ার বিষয় নয়; এটি সাধারণত কোনো কাজকে অন্যায় পথে এগিয়ে নেওয়া, কারও অধিকার নষ্ট করা বা দায়িত্বশীল ব্যক্তিকে প্রভাবিত করার সঙ্গে জড়িত। তবে এই হাদিসে বিশেষভাবে দুই পক্ষের কথা এসেছে—যে দেয় এবং যে নেয়। তাই ব্যাখ্যায় এই সীমাই ধরে রাখা ভালো। বাস্তব জীবনে চাকরি, অফিস, বিচার, সেবা বা অনুমতির কাজে ঘুষের চাপ দেখা যেতে পারে। একজন মুমিনের দায়িত্ব হলো নিজের সামর্থ্য অনুযায়ী ঘুষ থেকে বাঁচা, ন্যায় পথে কাজ করা এবং হারাম উপার্জনকে হালকা মনে না করা।"},"teachings":["ঘুষ দেওয়া ও নেওয়া—দুই পক্ষই হাদিসে কঠোর সতর্কতার মধ্যে এসেছে।","অন্যায় সুবিধার জন্য অর্থ দেওয়া থেকে দূরে থাকা দরকার।","দায়িত্বশীল পদে থাকলে অবৈধ সুবিধা নেওয়া আরও বিপজ্জনক।","সততা ও ন্যায়ের পথে কাজ করা মুমিনের দায়িত্ব।"],"related_hadiths":[{"id":"35৮0","book_id":"4","label":"Sunan Abu Dawud"},{"id":"311৮","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘুষ দেওয়া-নেওয়ার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ঘুষ গ্রহণকারী ও প্রদানকারীর ওপর অভিশাপের হাদিস ন্যায় ও সততার শিক্ষা দেয়।"},"heading":{"title":"ঘুষ দেওয়া ও নেওয়া: ন্যায়বিচার নষ্ট করার বড় সতর্কতা","description":"এই হাদিসের মূল বিষয় হলো ঘুষ। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ঘুষ গ্রহণকারী ও ঘুষ প্রদানকারীর উপর অভিশাপ করেছেন। বর্ণনাটি ছোট হলেও শিক্ষা খুব স্পষ্ট। ঘুষ শুধু টাকা নেওয়ার বিষয় নয়; এটি সাধারণত কোনো কাজকে অন্যায় পথে এগিয়ে নেওয়া, কারও অধিকার নষ্ট করা বা দায়িত্বশীল ব্যক্তিকে প্রভাবিত করার সঙ্গে জড়িত। তবে এই হাদিসে বিশেষভাবে দুই পক্ষের কথা এসেছে—যে দেয় এবং যে নেয়। তাই ব্যাখ্যায় এই সীমাই ধরে রাখা ভালো। বাস্তব জীবনে চাকরি, অফিস, বিচার, সেবা বা অনুমতির কাজে ঘুষের চাপ দেখা যেতে পারে। একজন মুমিনের দায়িত্ব হলো নিজের সামর্থ্য অনুযায়ী ঘুষ থেকে বাঁচা, ন্যায় পথে কাজ করা এবং হারাম উপার্জনকে হালকা মনে না করা।"},"teachings":["ঘুষ দেওয়া ও নেওয়া—দুই পক্ষই হাদিসে কঠোর সতর্কতার মধ্যে এসেছে।","অন্যায় সুবিধার জন্য অর্থ দেওয়া থেকে দূরে থাকা দরকার।","দায়িত্বশীল পদে থাকলে অবৈধ সুবিধা নেওয়া আরও বিপজ্জনক।","সততা ও ন্যায়ের পথে কাজ করা মুমিনের দায়িত্ব।"],"related_hadiths":[{"id":"3580","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3118","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুপারিশের বিনিময়ে উপহার","description":"$book_name$ $hadith_number$ - $chapter_name$. সুপারিশের প্রতিদানে উপহার গ্রহণকে রিবার বড় দরজার সঙ্গে তুলনা করা হয়েছে।"},"heading":{"title":"সুপারিশের বিনিময়ে উপহার: হাদিসের সতর্ক শিক্ষা","description":"এই হাদিসে সুপারিশের বিনিময়ে উপহার গ্রহণের বিষয়ে সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কেউ যদি কারো জন্য সুপারিশ করে, তারপর সেই সুপারিশের প্রতিদান হিসেবে তাকে উপহার দেওয়া হয় এবং সে তা গ্রহণ করে, তাহলে সে সূদের দরজাসমূহের একটি বড় দরজায় উপস্থিত হলো। এখানে সাধারণ উপহার নয়, বরং সুপারিশের বদলে পাওয়া উপহারের কথা বলা হয়েছে। তাই ব্যাখ্যায় সব উপহারকে একভাবে বলা ঠিক নয়। বিষয়টি মূলত স্বার্থের বিনিময়ে প্রভাব ব্যবহার করা। কেউ চাকরি, কাজ, সুবিধা বা সিদ্ধান্তে সাহায্য করল, এরপর তার বিনিময়ে উপহার নিল—এমন অবস্থায় এই হাদিস সতর্ক করে। শিক্ষা হলো, ভালো কাজ বা ন্যায়সঙ্গত সুপারিশকে অর্থ বা উপহার নেওয়ার মাধ্যম বানানো ঠিক নয়।"},"teachings":["সুপারিশের বদলে উপহার গ্রহণ করা থেকে সতর্ক থাকতে হবে।","সাধারণ হাদিয়া ও স্বার্থের বিনিময়ের উপহার এক নয়।","প্রভাব বা পরিচয় ব্যবহার করে সুবিধা নেওয়া বিপজ্জনক হতে পারে।","মানুষের সাহায্য করলে তা আল্লাহর সন্তুষ্টির জন্য করা উচিত।"],"related_hadiths":[{"id":"3541","book_id":"4","label":"Sunan Abu Dawud"},{"id":"35৮0","book_id":"4","label":"Sunan Abu Dawud"},{"id":"4632","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুপারিশের বিনিময়ে উপহার","description":"$book_name$ $hadith_number$ - $chapter_name$. সুপারিশের প্রতিদানে উপহার গ্রহণকে রিবার বড় দরজার সঙ্গে তুলনা করা হয়েছে।"},"heading":{"title":"সুপারিশের বিনিময়ে উপহার: হাদিসের সতর্ক শিক্ষা","description":"এই হাদিসে সুপারিশের বিনিময়ে উপহার গ্রহণের বিষয়ে সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কেউ যদি কারো জন্য সুপারিশ করে, তারপর সেই সুপারিশের প্রতিদান হিসেবে তাকে উপহার দেওয়া হয় এবং সে তা গ্রহণ করে, তাহলে সে সূদের দরজাসমূহের একটি বড় দরজায় উপস্থিত হলো। এখানে সাধারণ উপহার নয়, বরং সুপারিশের বদলে পাওয়া উপহারের কথা বলা হয়েছে। তাই ব্যাখ্যায় সব উপহারকে একভাবে বলা ঠিক নয়। বিষয়টি মূলত স্বার্থের বিনিময়ে প্রভাব ব্যবহার করা। কেউ চাকরি, কাজ, সুবিধা বা সিদ্ধান্তে সাহায্য করল, এরপর তার বিনিময়ে উপহার নিল—এমন অবস্থায় এই হাদিস সতর্ক করে। শিক্ষা হলো, ভালো কাজ বা ন্যায়সঙ্গত সুপারিশকে অর্থ বা উপহার নেওয়ার মাধ্যম বানানো ঠিক নয়।"},"teachings":["সুপারিশের বদলে উপহার গ্রহণ করা থেকে সতর্ক থাকতে হবে।","সাধারণ হাদিয়া ও স্বার্থের বিনিময়ের উপহার এক নয়।","প্রভাব বা পরিচয় ব্যবহার করে সুবিধা নেওয়া বিপজ্জনক হতে পারে।","মানুষের সাহায্য করলে তা আল্লাহর সন্তুষ্টির জন্য করা উচিত।"],"related_hadiths":[{"id":"3541","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3580","book_id":"4","label":"Sunan Abu Dawud"},{"id":"4632","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দায়িত্বে অতিরিক্ত গ্রহণ খিয়ানাত","description":"$book_name$ $hadith_number$ - $chapter_name$. ভাতা নির্ধারিত কাজের দায়িত্বে অতিরিক্ত কিছু গ্রহণকে খিয়ানাত বলা হয়েছে।"},"heading":{"title":"দায়িত্বে অতিরিক্ত গ্রহণ: খিয়ানাত থেকে বাঁচার শিক্ষা","description":"এই হাদিসে সরকারি বা দায়িত্বপ্রাপ্ত কাজের সততা নিয়ে শিক্ষা আছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যাকে ভাতা দিয়ে কোনো কাজের দায়িত্ব দেওয়া হয়েছে, সে যদি সেই ভাতা ছাড়া অন্য কিছু গ্রহণ করে, তাহলে তা খিয়ানাত। এখানে মূল বিষয় হলো দায়িত্ব, নির্ধারিত ভাতা এবং অতিরিক্ত গ্রহণ। অর্থাৎ কেউ কোনো কাজের জন্য নিয়োগ পেয়েছে এবং তার পাওনা ঠিক করা আছে; এরপর কাজের কারণে বাড়তি কিছু নেওয়া আমানতের বিপরীত। এই হাদিসকে ঘুষ, অফিসের অবৈধ সুবিধা, কমিশন বা দায়িত্বের নামে উপহার নেওয়ার সঙ্গে মানুষ খোঁজে। তবে ব্যাখ্যায় মনে রাখতে হবে, হাদিসে নির্দিষ্টভাবে ভাতা দেওয়া দায়িত্বের অতিরিক্ত গ্রহণের কথা বলা হয়েছে। তাই মুসলিম কর্মী, কর্মকর্তা বা দায়িত্বশীল ব্যক্তি নিজের পাওনা ও অন্যের সম্পদের সীমা পরিষ্কার রাখবে।"},"teachings":["নির্ধারিত ভাতা পেলে দায়িত্বের কারণে বাড়তি কিছু নেওয়া থেকে বাঁচতে হবে।","কাজের আমানত রক্ষা করা একজন দায়িত্বশীল ব্যক্তির কর্তব্য।","অবৈধ সুবিধা খিয়ানাতের পথে নিয়ে যেতে পারে।","পাওনা ও উপহার—দুইয়ের সীমা পরিষ্কার রাখা দরকার।"],"related_hadiths":[{"id":"4632","book_id":"2","label":"Sahih Muslim"},{"id":"3541","book_id":"4","label":"Sunan Abu Dawud"},{"id":"311৮","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দায়িত্বে অতিরিক্ত গ্রহণ খিয়ানাত","description":"$book_name$ $hadith_number$ - $chapter_name$. ভাতা নির্ধারিত কাজের দায়িত্বে অতিরিক্ত কিছু গ্রহণকে খিয়ানাত বলা হয়েছে।"},"heading":{"title":"দায়িত্বে অতিরিক্ত গ্রহণ: খিয়ানাত থেকে বাঁচার শিক্ষা","description":"এই হাদিসে সরকারি বা দায়িত্বপ্রাপ্ত কাজের সততা নিয়ে শিক্ষা আছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যাকে ভাতা দিয়ে কোনো কাজের দায়িত্ব দেওয়া হয়েছে, সে যদি সেই ভাতা ছাড়া অন্য কিছু গ্রহণ করে, তাহলে তা খিয়ানাত। এখানে মূল বিষয় হলো দায়িত্ব, নির্ধারিত ভাতা এবং অতিরিক্ত গ্রহণ। অর্থাৎ কেউ কোনো কাজের জন্য নিয়োগ পেয়েছে এবং তার পাওনা ঠিক করা আছে; এরপর কাজের কারণে বাড়তি কিছু নেওয়া আমানতের বিপরীত। এই হাদিসকে ঘুষ, অফিসের অবৈধ সুবিধা, কমিশন বা দায়িত্বের নামে উপহার নেওয়ার সঙ্গে মানুষ খোঁজে। তবে ব্যাখ্যায় মনে রাখতে হবে, হাদিসে নির্দিষ্টভাবে ভাতা দেওয়া দায়িত্বের অতিরিক্ত গ্রহণের কথা বলা হয়েছে। তাই মুসলিম কর্মী, কর্মকর্তা বা দায়িত্বশীল ব্যক্তি নিজের পাওনা ও অন্যের সম্পদের সীমা পরিষ্কার রাখবে।"},"teachings":["নির্ধারিত ভাতা পেলে দায়িত্বের কারণে বাড়তি কিছু নেওয়া থেকে বাঁচতে হবে।","কাজের আমানত রক্ষা করা একজন দায়িত্বশীল ব্যক্তির কর্তব্য।","অবৈধ সুবিধা খিয়ানাতের পথে নিয়ে যেতে পারে।","পাওনা ও উপহার—দুইয়ের সীমা পরিষ্কার রাখা দরকার।"],"related_hadiths":[{"id":"4632","book_id":"2","label":"Sahih Muslim"},{"id":"3541","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3118","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অন্যায়ভাবে সম্পদ ভক্ষণ","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর সম্পদ অন্যায়ভাবে ভক্ষণকারীদের জন্য কিয়ামতের দিনের কঠিন সতর্কতা।"},"heading":{"title":"অন্যায়ভাবে সম্পদ ভক্ষণ: হারাম আয় থেকে বাঁচার শিক্ষা","description":"এই হাদিসে অন্যায়ভাবে সম্পদ ভক্ষণ করার ভয়াবহতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কিছু লোক আল্লাহর সম্পদ অন্যায়ভাবে ভক্ষণ করে; কিয়ামতের দিন তাদের জন্য জাহান্নাম রয়েছে। এখানে “আল্লাহর সম্পদ” এবং “অন্যায়ভাবে ভক্ষণ”—এই দুইটি কথা খুব গুরুত্বপূর্ণ। এটি ব্যক্তিগত লোভ, দায়িত্বের অপব্যবহার, আমানতের খিয়ানাত বা জনসম্পদ নষ্ট করার বিষয়ে সতর্কতা হিসেবে বোঝা যায়। তবে হাদিসে যেটুকু বলা হয়েছে, তার বাইরে নির্দিষ্ট কোনো ব্যক্তি বা প্রতিষ্ঠানের ওপর রায় দেওয়া ঠিক নয়। মূল শিক্ষা হলো, যে সম্পদ নিজের অধিকার নয়, তা গ্রহণ করা বা ব্যবহার করা ভয়ংকর পরিণামের কারণ হতে পারে। মুসলিমের জন্য হালাল আয়, আমানত রক্ষা এবং অন্যের অধিকার থেকে দূরে থাকা বড় দায়িত্ব।"},"teachings":["অন্যায়ভাবে সম্পদ নেওয়া আখিরাতের জন্য বিপজ্জনক।","আমানত ও জনসম্পদের বিষয়ে খুব সতর্ক থাকা দরকার।","নিজের অধিকার নয় এমন সম্পদ থেকে দূরে থাকতে হবে।","হারাম আয় সাময়িক লাভ মনে হলেও পরিণাম কঠিন হতে পারে।"],"related_hadiths":[{"id":"311৮","book_id":"1","label":"Sahih Bukhari"},{"id":"4632","book_id":"2","label":"Sahih Muslim"},{"id":"35৮0","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অন্যায়ভাবে সম্পদ ভক্ষণ","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর সম্পদ অন্যায়ভাবে ভক্ষণকারীদের জন্য কিয়ামতের দিনের কঠিন সতর্কতা।"},"heading":{"title":"অন্যায়ভাবে সম্পদ ভক্ষণ: হারাম আয় থেকে বাঁচার শিক্ষা","description":"এই হাদিসে অন্যায়ভাবে সম্পদ ভক্ষণ করার ভয়াবহতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কিছু লোক আল্লাহর সম্পদ অন্যায়ভাবে ভক্ষণ করে; কিয়ামতের দিন তাদের জন্য জাহান্নাম রয়েছে। এখানে “আল্লাহর সম্পদ” এবং “অন্যায়ভাবে ভক্ষণ”—এই দুইটি কথা খুব গুরুত্বপূর্ণ। এটি ব্যক্তিগত লোভ, দায়িত্বের অপব্যবহার, আমানতের খিয়ানাত বা জনসম্পদ নষ্ট করার বিষয়ে সতর্কতা হিসেবে বোঝা যায়। তবে হাদিসে যেটুকু বলা হয়েছে, তার বাইরে নির্দিষ্ট কোনো ব্যক্তি বা প্রতিষ্ঠানের ওপর রায় দেওয়া ঠিক নয়। মূল শিক্ষা হলো, যে সম্পদ নিজের অধিকার নয়, তা গ্রহণ করা বা ব্যবহার করা ভয়ংকর পরিণামের কারণ হতে পারে। মুসলিমের জন্য হালাল আয়, আমানত রক্ষা এবং অন্যের অধিকার থেকে দূরে থাকা বড় দায়িত্ব।"},"teachings":["অন্যায়ভাবে সম্পদ নেওয়া আখিরাতের জন্য বিপজ্জনক।","আমানত ও জনসম্পদের বিষয়ে খুব সতর্ক থাকা দরকার।","নিজের অধিকার নয় এমন সম্পদ থেকে দূরে থাকতে হবে।","হারাম আয় সাময়িক লাভ মনে হলেও পরিণাম কঠিন হতে পারে।"],"related_hadiths":[{"id":"3118","book_id":"1","label":"Sahih Bukhari"},{"id":"4632","book_id":"2","label":"Sahih Muslim"},{"id":"3580","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বড় গোনাহের সতর্ক তালিকা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, দারিদ্র্যের ভয়ে সন্তান হত্যা ও প্রতিবেশীর স্ত্রীর সঙ্গে ব্যভিচারের ভয়াবহতা।"},"heading":{"title":"আল্লাহর কাছে বড় গোনাহ: শিরক, সন্তান হত্যা ও প্রতিবেশীর অধিকার","description":"এই হাদিসে আল্লাহর কাছে বড় গোনাহ সম্পর্কে প্রশ্ন করা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) প্রথমে বলেন, আল্লাহর সমকক্ষ সাব্যস্ত করা, অথচ তিনি মানুষকে সৃষ্টি করেছেন। এরপর বলা হয়, নিজের সন্তানকে এ ভয়ে হত্যা করা যে সে তোমার সঙ্গে খাবে। তারপর বলা হয়, প্রতিবেশীর স্ত্রীর সঙ্গে ব্যভিচারে লিপ্ত হওয়া। শেষে কুরআনের আয়াত নাযিলের কথা এসেছে, যেখানে আল্লাহর সঙ্গে অন্য উপাস্যকে না ডাকা, অন্যায়ভাবে হত্যা না করা এবং ব্যভিচার না করার গুণ বলা হয়েছে। এই হাদিসে তিনটি বিষয় আলাদা: শিরক, দারিদ্র্যের ভয়ে সন্তান হত্যা এবং প্রতিবেশীর স্ত্রীর সঙ্গে ব্যভিচার। তাই ব্যাখ্যায় এগুলোকে মিশিয়ে ফেলা ঠিক নয়। শিক্ষা হলো, ঈমান, জীবন ও প্রতিবেশীর সম্মান—এই তিনটি বিষয়কে অত্যন্ত গুরুত্ব দেওয়া।"},"teachings":["আল্লাহর সঙ্গে কাউকে সমকক্ষ করা সবচেয়ে বড় সতর্কতার বিষয়।","দারিদ্র্যের ভয়ে সন্তান হত্যা বড় গোনাহ হিসেবে উল্লেখ হয়েছে।","প্রতিবেশীর অধিকার ও সম্মান রক্ষা করা জরুরি।","ব্যভিচার ও অন্যায় হত্যা থেকে দূরে থাকা মুমিনের গুণ।"],"related_hadiths":[{"id":"5৯76","book_id":"1","label":"Sahih Bukhari"},{"id":"2766","book_id":"1","label":"Sahih Bukhari"},{"id":"6৮57","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বড় গোনাহের সতর্ক তালিকা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, দারিদ্র্যের ভয়ে সন্তান হত্যা ও প্রতিবেশীর স্ত্রীর সঙ্গে ব্যভিচারের ভয়াবহতা।"},"heading":{"title":"আল্লাহর কাছে বড় গোনাহ: শিরক, সন্তান হত্যা ও প্রতিবেশীর অধিকার","description":"এই হাদিসে আল্লাহর কাছে বড় গোনাহ সম্পর্কে প্রশ্ন করা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) প্রথমে বলেন, আল্লাহর সমকক্ষ সাব্যস্ত করা, অথচ তিনি মানুষকে সৃষ্টি করেছেন। এরপর বলা হয়, নিজের সন্তানকে এ ভয়ে হত্যা করা যে সে তোমার সঙ্গে খাবে। তারপর বলা হয়, প্রতিবেশীর স্ত্রীর সঙ্গে ব্যভিচারে লিপ্ত হওয়া। শেষে কুরআনের আয়াত নাযিলের কথা এসেছে, যেখানে আল্লাহর সঙ্গে অন্য উপাস্যকে না ডাকা, অন্যায়ভাবে হত্যা না করা এবং ব্যভিচার না করার গুণ বলা হয়েছে। এই হাদিসে তিনটি বিষয় আলাদা: শিরক, দারিদ্র্যের ভয়ে সন্তান হত্যা এবং প্রতিবেশীর স্ত্রীর সঙ্গে ব্যভিচার। তাই ব্যাখ্যায় এগুলোকে মিশিয়ে ফেলা ঠিক নয়। শিক্ষা হলো, ঈমান, জীবন ও প্রতিবেশীর সম্মান—এই তিনটি বিষয়কে অত্যন্ত গুরুত্ব দেওয়া।"},"teachings":["আল্লাহর সঙ্গে কাউকে সমকক্ষ করা সবচেয়ে বড় সতর্কতার বিষয়।","দারিদ্র্যের ভয়ে সন্তান হত্যা বড় গোনাহ হিসেবে উল্লেখ হয়েছে।","প্রতিবেশীর অধিকার ও সম্মান রক্ষা করা জরুরি।","ব্যভিচার ও অন্যায় হত্যা থেকে দূরে থাকা মুমিনের গুণ।"],"related_hadiths":[{"id":"5976","book_id":"1","label":"Sahih Bukhari"},{"id":"2766","book_id":"1","label":"Sahih Bukhari"},{"id":"6857","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবীরা গোনাহের পরিচয়","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, মানুষ হত্যা ও মিথ্যা শপথ বা সাক্ষ্যের সতর্কতা।"},"heading":{"title":"কবীরা গোনাহ: শিরক, পিতা-মাতার অবাধ্যতা ও মিথ্যার ভয়াবহতা","description":"এই হাদিসে কবীরা গোনাহের কয়েকটি বড় দিক বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কবীরা গোনাহ হলো আল্লাহর সঙ্গে শরীক করা, পিতা-মাতার অবাধ্য হওয়া, মানুষ হত্যা করা এবং মিথ্যা শপথ করা। বর্ণনায় আরও এসেছে, আনাস (রাঃ)-এর বর্ণনায় মিথ্যা শপথের বদলে মিথ্যা সাক্ষ্য শব্দ এসেছে। এখানে দুটি বর্ণনার শব্দ আলাদা হওয়ায় ব্যাখ্যায় সতর্ক থাকা দরকার। শিরক ঈমানের মূলকে নষ্ট করে। পিতা-মাতার অবাধ্যতা পারিবারিক দায়িত্ব নষ্ট করে। মানুষ হত্যা জীবনের নিরাপত্তা ভাঙে। আর মিথ্যা শপথ বা মিথ্যা সাক্ষ্য মানুষের অধিকার ও বিচারকে ক্ষতিগ্রস্ত করে। তাই এই হাদিস ব্যক্তিগত ইবাদত, পরিবার, সমাজ ও ন্যায়বিচার—সব ক্ষেত্রেই সতর্কতার ডাক দেয়।"},"teachings":["শিরক কবীরা গোনাহের মধ্যে প্রথমে উল্লেখ হয়েছে।","পিতা-মাতার অবাধ্যতা বড় পাপ হিসেবে এসেছে।","অন্যায়ভাবে মানুষ হত্যা গুরুতর গোনাহ।","মিথ্যা শপথ ও মিথ্যা সাক্ষ্য অধিকার নষ্ট করতে পারে।"],"related_hadiths":[{"id":"5৯76","book_id":"1","label":"Sahih Bukhari"},{"id":"6৮71","book_id":"1","label":"Sahih Bukhari"},{"id":"2766","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবীরা গোনাহের পরিচয়","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, মানুষ হত্যা ও মিথ্যা শপথ বা সাক্ষ্যের সতর্কতা।"},"heading":{"title":"কবীরা গোনাহ: শিরক, পিতা-মাতার অবাধ্যতা ও মিথ্যার ভয়াবহতা","description":"এই হাদিসে কবীরা গোনাহের কয়েকটি বড় দিক বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কবীরা গোনাহ হলো আল্লাহর সঙ্গে শরীক করা, পিতা-মাতার অবাধ্য হওয়া, মানুষ হত্যা করা এবং মিথ্যা শপথ করা। বর্ণনায় আরও এসেছে, আনাস (রাঃ)-এর বর্ণনায় মিথ্যা শপথের বদলে মিথ্যা সাক্ষ্য শব্দ এসেছে। এখানে দুটি বর্ণনার শব্দ আলাদা হওয়ায় ব্যাখ্যায় সতর্ক থাকা দরকার। শিরক ঈমানের মূলকে নষ্ট করে। পিতা-মাতার অবাধ্যতা পারিবারিক দায়িত্ব নষ্ট করে। মানুষ হত্যা জীবনের নিরাপত্তা ভাঙে। আর মিথ্যা শপথ বা মিথ্যা সাক্ষ্য মানুষের অধিকার ও বিচারকে ক্ষতিগ্রস্ত করে। তাই এই হাদিস ব্যক্তিগত ইবাদত, পরিবার, সমাজ ও ন্যায়বিচার—সব ক্ষেত্রেই সতর্কতার ডাক দেয়।"},"teachings":["শিরক কবীরা গোনাহের মধ্যে প্রথমে উল্লেখ হয়েছে।","পিতা-মাতার অবাধ্যতা বড় পাপ হিসেবে এসেছে।","অন্যায়ভাবে মানুষ হত্যা গুরুতর গোনাহ।","মিথ্যা শপথ ও মিথ্যা সাক্ষ্য অধিকার নষ্ট করতে পারে।"],"related_hadiths":[{"id":"5976","book_id":"1","label":"Sahih Bukhari"},{"id":"6871","book_id":"1","label":"Sahih Bukhari"},{"id":"2766","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সাত ধ্বংসকারী গোনাহ","description":"$book_name$ $hadith_number$ - $chapter_name$. সাতটি ধ্বংসকারী গোনাহ থেকে দূরে থাকার নববী নির্দেশ।"},"heading":{"title":"সাতটি ধ্বংসকারী গোনাহ: মুমিনের জন্য সতর্ক তালিকা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সাতটি ধ্বংসকারী বিষয় থেকে দূরে থাকতে বলেছেন। সাহাবীগণ জিজ্ঞেস করলে তিনি একে একে বলেন: আল্লাহর সঙ্গে শরীক করা, জাদু করা, অন্যায়ভাবে মানুষ হত্যা করা, সুদ খাওয়া, ইয়াতীমের মাল অন্যায়ভাবে খাওয়া, জিহাদের ময়দান থেকে পালিয়ে যাওয়া এবং সরল নির্দোষ মুমিন নারীদের নামে ব্যভিচারের অপবাদ দেওয়া। এই হাদিসের শক্তি হলো এর স্পষ্ট তালিকা। প্রতিটি গোনাহ আলাদা আলাদা ক্ষতি করে—ঈমান, জীবন, সম্পদ, সমাজ, দুর্বল মানুষের অধিকার এবং মানুষের সম্মান নষ্ট করে। ব্যাখ্যায় তালিকার বাইরে নতুন গোনাহ যোগ না করাই ভালো। মূল শিক্ষা হলো, মুমিন নিজের ঈমান, আচরণ, লেনদেন, কথা এবং দায়িত্বের জায়গায় সতর্ক থাকবে।"},"teachings":["শিরক সাত ধ্বংসকারী গোনাহের প্রথমে এসেছে।","সুদ ও ইয়াতীমের মাল খাওয়া অর্থনৈতিক পাপের বড় সতর্কতা।","মানুষ হত্যা ও অপবাদ মানুষের জীবন ও সম্মান নষ্ট করে।","জিহাদের ময়দান থেকে পালানোর বিষয়টি নির্দিষ্ট অবস্থার সঙ্গে যুক্ত—এটি সাধারণ ভয়ের সঙ্গে মেলানো ঠিক নয়।"],"related_hadiths":[{"id":"2766","book_id":"1","label":"Sahih Bukhari"},{"id":"6৮57","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯76","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সাত ধ্বংসকারী গোনাহ","description":"$book_name$ $hadith_number$ - $chapter_name$. সাতটি ধ্বংসকারী গোনাহ থেকে দূরে থাকার নববী নির্দেশ।"},"heading":{"title":"সাতটি ধ্বংসকারী গোনাহ: মুমিনের জন্য সতর্ক তালিকা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সাতটি ধ্বংসকারী বিষয় থেকে দূরে থাকতে বলেছেন। সাহাবীগণ জিজ্ঞেস করলে তিনি একে একে বলেন: আল্লাহর সঙ্গে শরীক করা, জাদু করা, অন্যায়ভাবে মানুষ হত্যা করা, সুদ খাওয়া, ইয়াতীমের মাল অন্যায়ভাবে খাওয়া, জিহাদের ময়দান থেকে পালিয়ে যাওয়া এবং সরল নির্দোষ মুমিন নারীদের নামে ব্যভিচারের অপবাদ দেওয়া। এই হাদিসের শক্তি হলো এর স্পষ্ট তালিকা। প্রতিটি গোনাহ আলাদা আলাদা ক্ষতি করে—ঈমান, জীবন, সম্পদ, সমাজ, দুর্বল মানুষের অধিকার এবং মানুষের সম্মান নষ্ট করে। ব্যাখ্যায় তালিকার বাইরে নতুন গোনাহ যোগ না করাই ভালো। মূল শিক্ষা হলো, মুমিন নিজের ঈমান, আচরণ, লেনদেন, কথা এবং দায়িত্বের জায়গায় সতর্ক থাকবে।"},"teachings":["শিরক সাত ধ্বংসকারী গোনাহের প্রথমে এসেছে।","সুদ ও ইয়াতীমের মাল খাওয়া অর্থনৈতিক পাপের বড় সতর্কতা।","মানুষ হত্যা ও অপবাদ মানুষের জীবন ও সম্মান নষ্ট করে।","জিহাদের ময়দান থেকে পালানোর বিষয়টি নির্দিষ্ট অবস্থার সঙ্গে যুক্ত—এটি সাধারণ ভয়ের সঙ্গে মেলানো ঠিক নয়।"],"related_hadiths":[{"id":"2766","book_id":"1","label":"Sahih Bukhari"},{"id":"6857","book_id":"1","label":"Sahih Bukhari"},{"id":"5976","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দশটি নববী উপদেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতা, সালাত, মাদক, গোনাহ ও পরিবারের দায়িত্ব নিয়ে দশটি উপদেশ।"},"heading":{"title":"দশটি নববী উপদেশ: ঈমান, সালাত ও পরিবারের দায়িত্ব","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মু‘আয (রাঃ)-কে দশটি বিষয়ে উপদেশ দিয়েছেন। প্রথমে এসেছে, আল্লাহর সঙ্গে কাউকে শরীক না করা, যদিও হত্যা বা আগুনে জ্বালানোর ভয় থাকে। এরপর পিতা-মাতার অবাধ্য না হওয়া, ইচ্ছাকৃত ফরয সালাত ত্যাগ না করা, মাদক না পান করা, গোনাহ থেকে দূরে থাকা, জিহাদের ময়দান থেকে না পালানো, মহামারী এলাকায় থাকলে পালিয়ে না যাওয়া, সামর্থ্য অনুযায়ী পরিবারে ব্যয় করা, পরিবারের শাসন-শিক্ষা পুরো তুলে না নেওয়া এবং তাদেরকে আল্লাহর ভয় শেখানো। এই হাদিসে ব্যক্তিগত ঈমান, ইবাদত, চরিত্র, সামাজিক দায়িত্ব ও পরিবার—সব একসঙ্গে এসেছে। তাই ব্যাখ্যায় একটি দিককে পুরো হাদিস বানিয়ে ফেলা ঠিক নয়। এটি মুসলিম জীবনের ভারসাম্যপূর্ণ উপদেশ।"},"teachings":["শিরক থেকে দূরে থাকা সব অবস্থায় বড় দায়িত্ব।","ফরয সালাত ইচ্ছাকৃতভাবে ত্যাগ করা নিয়ে কঠিন সতর্কতা এসেছে।","মাদককে অশ্লীলতার মূল বলা হয়েছে।","পরিবারের খরচ, শিক্ষা ও আল্লাহভীতি শেখানো দায়িত্বের অংশ।"],"related_hadiths":[{"id":"5৯76","book_id":"1","label":"Sahih Bukhari"},{"id":"2766","book_id":"1","label":"Sahih Bukhari"},{"id":"6৮57","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দশটি নববী উপদেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতা, সালাত, মাদক, গোনাহ ও পরিবারের দায়িত্ব নিয়ে দশটি উপদেশ।"},"heading":{"title":"দশটি নববী উপদেশ: ঈমান, সালাত ও পরিবারের দায়িত্ব","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মু‘আয (রাঃ)-কে দশটি বিষয়ে উপদেশ দিয়েছেন। প্রথমে এসেছে, আল্লাহর সঙ্গে কাউকে শরীক না করা, যদিও হত্যা বা আগুনে জ্বালানোর ভয় থাকে। এরপর পিতা-মাতার অবাধ্য না হওয়া, ইচ্ছাকৃত ফরয সালাত ত্যাগ না করা, মাদক না পান করা, গোনাহ থেকে দূরে থাকা, জিহাদের ময়দান থেকে না পালানো, মহামারী এলাকায় থাকলে পালিয়ে না যাওয়া, সামর্থ্য অনুযায়ী পরিবারে ব্যয় করা, পরিবারের শাসন-শিক্ষা পুরো তুলে না নেওয়া এবং তাদেরকে আল্লাহর ভয় শেখানো। এই হাদিসে ব্যক্তিগত ঈমান, ইবাদত, চরিত্র, সামাজিক দায়িত্ব ও পরিবার—সব একসঙ্গে এসেছে। তাই ব্যাখ্যায় একটি দিককে পুরো হাদিস বানিয়ে ফেলা ঠিক নয়। এটি মুসলিম জীবনের ভারসাম্যপূর্ণ উপদেশ।"},"teachings":["শিরক থেকে দূরে থাকা সব অবস্থায় বড় দায়িত্ব।","ফরয সালাত ইচ্ছাকৃতভাবে ত্যাগ করা নিয়ে কঠিন সতর্কতা এসেছে।","মাদককে অশ্লীলতার মূল বলা হয়েছে।","পরিবারের খরচ, শিক্ষা ও আল্লাহভীতি শেখানো দায়িত্বের অংশ।"],"related_hadiths":[{"id":"5976","book_id":"1","label":"Sahih Bukhari"},{"id":"2766","book_id":"1","label":"Sahih Bukhari"},{"id":"6857","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বাম উরুর হাড় কথা বলবে","description":"$book_name$ $hadith_number$ - $chapter_name$. মুখ বন্ধ থাকার দিনে মানুষের বাম উরুর হাড় প্রথম কথা বলবে—এতে আমলের জবাবদিহির শিক্ষা আছে।"},"heading":{"title":"কিয়ামতে বাম উরুর হাড় কথা বলবে—হাদিসের সতর্কতা","description":"এই হাদিসে বলা হয়েছে, কিয়ামতের দিন মানুষের মুখ বন্ধ থাকবে। তখন মানুষের বাম উরুর হাড় সর্বপ্রথম কথা বলবে। হাদিসটি ছোট, কিন্তু কিয়ামতের সাক্ষ্য সম্পর্কে খুব গুরুত্বপূর্ণ শিক্ষা দেয়। দুনিয়ায় মানুষ মুখ দিয়ে কথা বলে, যুক্তি দেয়, অস্বীকার করে বা নিজেকে বাঁচাতে চায়। কিন্তু আখেরাতে আল্লাহ চাইলে শরীরের অংশও কথা বলবে। তখন কাজের সত্যতা প্রকাশ হবে। এই হাদিস আমাদের মনে করায়, গোপনে করা কাজও আল্লাহর জ্ঞানের বাইরে নয়। তাই আমল ঠিক রাখা, অন্যায় থেকে বাঁচা এবং কিয়ামতের হিসাব মনে রাখা একজন মুসলিমের জন্য প্রয়োজনীয়।"},"teachings":["কিয়ামতে মুখ বন্ধ থাকলেও অঙ্গ কথা বলবে।","বাম উরুর হাড়ের সাক্ষ্যের কথা হাদিসে এসেছে।","গোপন কাজও আল্লাহর কাছে প্রকাশ্য।","কিয়ামতের হিসাব মনে রেখে জীবন চালানো দরকার।"],"related_hadiths":[{"id":"2৯6৯","book_id":"2","label":"Sahih Muslim"},{"id":"5554","book_id":"14","label":"Mishkat al-Masabih"},{"id":"5555","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বাম উরুর হাড় কথা বলবে","description":"$book_name$ $hadith_number$ - $chapter_name$. মুখ বন্ধ থাকার দিনে মানুষের বাম উরুর হাড় প্রথম কথা বলবে—এতে আমলের জবাবদিহির শিক্ষা আছে।"},"heading":{"title":"কিয়ামতে বাম উরুর হাড় কথা বলবে—হাদিসের সতর্কতা","description":"এই হাদিসে বলা হয়েছে, কিয়ামতের দিন মানুষের মুখ বন্ধ থাকবে। তখন মানুষের বাম উরুর হাড় সর্বপ্রথম কথা বলবে। হাদিসটি ছোট, কিন্তু কিয়ামতের সাক্ষ্য সম্পর্কে খুব গুরুত্বপূর্ণ শিক্ষা দেয়। দুনিয়ায় মানুষ মুখ দিয়ে কথা বলে, যুক্তি দেয়, অস্বীকার করে বা নিজেকে বাঁচাতে চায়। কিন্তু আখেরাতে আল্লাহ চাইলে শরীরের অংশও কথা বলবে। তখন কাজের সত্যতা প্রকাশ হবে। এই হাদিস আমাদের মনে করায়, গোপনে করা কাজও আল্লাহর জ্ঞানের বাইরে নয়। তাই আমল ঠিক রাখা, অন্যায় থেকে বাঁচা এবং কিয়ামতের হিসাব মনে রাখা একজন মুসলিমের জন্য প্রয়োজনীয়।"},"teachings":["কিয়ামতে মুখ বন্ধ থাকলেও অঙ্গ কথা বলবে।","বাম উরুর হাড়ের সাক্ষ্যের কথা হাদিসে এসেছে।","গোপন কাজও আল্লাহর কাছে প্রকাশ্য।","কিয়ামতের হিসাব মনে রেখে জীবন চালানো দরকার।"],"related_hadiths":[{"id":"2969","book_id":"2","label":"Sahih Muslim"},{"id":"5554","book_id":"14","label":"Mishkat al-Masabih"},{"id":"5555","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিরক থেকে বাঁচার গুরুত্ব","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরকসহ মৃত্যু ও শিরকমুক্ত ঈমানের পরিণাম নিয়ে সংক্ষিপ্ত কিন্তু গভীর শিক্ষা।"},"heading":{"title":"শিরক থেকে বাঁচা: জান্নাত ও জাহান্নাম বিষয়ে হাদিসের শিক্ষা","description":"এই হাদিসের মূল বিষয় হলো শিরক ও তাওহীদ। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি আল্লাহর সঙ্গে বিন্দুমাত্র শরীক করে মারা যাবে, সে জাহান্নামে যাবে। আর যে ব্যক্তি আল্লাহর সঙ্গে বিন্দুমাত্র শরীক না করে মারা যাবে, সে জান্নাতে যাবে। হাদিসটি খুব সংক্ষিপ্ত, কিন্তু ঈমানের মূল কথা স্পষ্ট করে। এখানে “মারা যাবে” কথাটি গুরুত্বপূর্ণ; অর্থাৎ মানুষের শেষ অবস্থা ও ঈমানের অবস্থা বড় বিষয়। তাই ব্যাখ্যায় কারও নির্দিষ্ট পরিণাম নিয়ে কথা বলা উচিত নয়; বরং নিজের শিরকমুক্ত ঈমান রক্ষা করার শিক্ষা নেওয়া উচিত। তাওহীদ মানে আল্লাহকে একমাত্র রব, ইলাহ ও উপাস্য হিসেবে মানা। মুমিনের দোয়া হওয়া উচিত, আল্লাহ যেন তাকে শিরক থেকে বাঁচিয়ে রাখেন এবং শুদ্ধ ঈমানের ওপর মৃত্যু দেন।"},"teachings":["শিরক ঈমানের সবচেয়ে বড় বিপদ।","তাওহীদের ওপর মৃত্যু জান্নাত লাভের কারণ হিসেবে হাদিসে এসেছে।","নিজের ঈমান শিরকমুক্ত রাখার চেষ্টা করা জরুরি।","অন্যের পরিণাম নিয়ে রায় না দিয়ে নিজের সংশোধনে মন দেওয়া উচিত।"],"related_hadiths":[{"id":"5৯76","book_id":"1","label":"Sahih Bukhari"},{"id":"2766","book_id":"1","label":"Sahih Bukhari"},{"id":"6৮57","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিরক থেকে বাঁচার গুরুত্ব","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরকসহ মৃত্যু ও শিরকমুক্ত ঈমানের পরিণাম নিয়ে সংক্ষিপ্ত কিন্তু গভীর শিক্ষা।"},"heading":{"title":"শিরক থেকে বাঁচা: জান্নাত ও জাহান্নাম বিষয়ে হাদিসের শিক্ষা","description":"এই হাদিসের মূল বিষয় হলো শিরক ও তাওহীদ। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি আল্লাহর সঙ্গে বিন্দুমাত্র শরীক করে মারা যাবে, সে জাহান্নামে যাবে। আর যে ব্যক্তি আল্লাহর সঙ্গে বিন্দুমাত্র শরীক না করে মারা যাবে, সে জান্নাতে যাবে। হাদিসটি খুব সংক্ষিপ্ত, কিন্তু ঈমানের মূল কথা স্পষ্ট করে। এখানে “মারা যাবে” কথাটি গুরুত্বপূর্ণ; অর্থাৎ মানুষের শেষ অবস্থা ও ঈমানের অবস্থা বড় বিষয়। তাই ব্যাখ্যায় কারও নির্দিষ্ট পরিণাম নিয়ে কথা বলা উচিত নয়; বরং নিজের শিরকমুক্ত ঈমান রক্ষা করার শিক্ষা নেওয়া উচিত। তাওহীদ মানে আল্লাহকে একমাত্র রব, ইলাহ ও উপাস্য হিসেবে মানা। মুমিনের দোয়া হওয়া উচিত, আল্লাহ যেন তাকে শিরক থেকে বাঁচিয়ে রাখেন এবং শুদ্ধ ঈমানের ওপর মৃত্যু দেন।"},"teachings":["শিরক ঈমানের সবচেয়ে বড় বিপদ।","তাওহীদের ওপর মৃত্যু জান্নাত লাভের কারণ হিসেবে হাদিসে এসেছে।","নিজের ঈমান শিরকমুক্ত রাখার চেষ্টা করা জরুরি।","অন্যের পরিণাম নিয়ে রায় না দিয়ে নিজের সংশোধনে মন দেওয়া উচিত।"],"related_hadiths":[{"id":"5976","book_id":"1","label":"Sahih Bukhari"},{"id":"2766","book_id":"1","label":"Sahih Bukhari"},{"id":"6857","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গণকের কাছে যাওয়ার ভয়াবহ ক্ষতি","description":"$book_name$ $hadith_number$ - $chapter_name$. গণক বা জ্যোতিষীর কাছে গিয়ে প্রশ্ন করলে চল্লিশ দিন সালাত কবুল না হওয়ার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"গণকের কাছে যাওয়ার হাদিস: সালাত কবুল না হওয়ার সতর্কতা","description":"এই হাদিসে গণক বা জ্যোতিষীর কাছে যাওয়ার বিষয়ে কঠোর সতর্কতা দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি কোনো গণক বা জ্যোতির্বিদের কাছে যায় এবং তাকে কোনো কথা জিজ্ঞেস করে, চল্লিশ দিন তার সালাত কবুল করা হবে না। এখানে শুধু বিশ্বাস করার কথা নয়; জিজ্ঞেস করার কথাও এসেছে। কারণ ভবিষ্যৎ, ভাগ্য বা গায়েব জানার চেষ্টা মানুষকে ভুল নির্ভরতার দিকে নিয়ে যায়। একজন মুমিন জানে, গায়েবের জ্ঞান আল্লাহর। তাই বিপদ, হারানো জিনিস, ভবিষ্যৎ বা ভাগ্য জানার জন্য গণকের কাছে যাওয়া ঈমানের জন্য ক্ষতিকর। এই হাদিস মানুষকে আল্লাহর উপর ভরসা করতে শেখায়।"},"teachings":["গণক বা জ্যোতিষীর কাছে প্রশ্ন করা থেকে বাঁচতে হবে।","গায়েব জানার দাবিদারদের কাছে যাওয়া ঈমানের জন্য ক্ষতিকর।","সালাতের মর্যাদা রক্ষায় বিশ্বাসের ভুল দরজা বন্ধ করতে হবে।","ভাগ্য ও অদৃশ্য বিষয়ের ব্যাপারে আল্লাহর উপর ভরসা করতে হবে।"],"related_hadiths":[{"id":"45৯4","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গণকের কাছে যাওয়ার ভয়াবহ ক্ষতি","description":"$book_name$ $hadith_number$ - $chapter_name$. গণক বা জ্যোতিষীর কাছে গিয়ে প্রশ্ন করলে চল্লিশ দিন সালাত কবুল না হওয়ার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"গণকের কাছে যাওয়ার হাদিস: সালাত কবুল না হওয়ার সতর্কতা","description":"এই হাদিসে গণক বা জ্যোতিষীর কাছে যাওয়ার বিষয়ে কঠোর সতর্কতা দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি কোনো গণক বা জ্যোতির্বিদের কাছে যায় এবং তাকে কোনো কথা জিজ্ঞেস করে, চল্লিশ দিন তার সালাত কবুল করা হবে না। এখানে শুধু বিশ্বাস করার কথা নয়; জিজ্ঞেস করার কথাও এসেছে। কারণ ভবিষ্যৎ, ভাগ্য বা গায়েব জানার চেষ্টা মানুষকে ভুল নির্ভরতার দিকে নিয়ে যায়। একজন মুমিন জানে, গায়েবের জ্ঞান আল্লাহর। তাই বিপদ, হারানো জিনিস, ভবিষ্যৎ বা ভাগ্য জানার জন্য গণকের কাছে যাওয়া ঈমানের জন্য ক্ষতিকর। এই হাদিস মানুষকে আল্লাহর উপর ভরসা করতে শেখায়।"},"teachings":["গণক বা জ্যোতিষীর কাছে প্রশ্ন করা থেকে বাঁচতে হবে।","গায়েব জানার দাবিদারদের কাছে যাওয়া ঈমানের জন্য ক্ষতিকর।","সালাতের মর্যাদা রক্ষায় বিশ্বাসের ভুল দরজা বন্ধ করতে হবে।","ভাগ্য ও অদৃশ্য বিষয়ের ব্যাপারে আল্লাহর উপর ভরসা করতে হবে।"],"related_hadiths":[{"id":"4594","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যাতুল আনওয়াত ও শির্ক থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মুশরিকদের মতো বরকতের জন্য বিশেষ গাছ চাওয়াকে নবীজি পূর্ববর্তীদের ভুল রীতির সাথে তুলনা করেছেন।"},"heading":{"title":"যাতুল আনওয়াত হাদিস: বরকত লাভে ভুল পথ থেকে সাবধান","description":"এই হাদিসে হুনাইনের পথে একটি ঘটনার কথা এসেছে। কিছু নতুন মুসলিম মুশরিকদের একটি গাছ দেখে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম-কে বললেন, তাদের যেমন নির্দিষ্ট গাছ আছে, আমাদের জন্যও তেমন একটি গাছ নির্ধারণ করে দিন। নবীজি এ কথাকে খুব গুরুতরভাবে নিলেন এবং বললেন, এটি পূর্ববর্তী লোকদের রীতির মতো। তিনি বনী ইসরাঈলের সেই কথাও স্মরণ করালেন, যখন তারা মূসা আলাইহিস সালামকে মুশরিকদের মতো মা‘বূদ বানিয়ে দিতে বলেছিল। এখানে মূল শিক্ষা হলো—বরকত, সাহায্য ও কল্যাণের আশা আল্লাহর বিধান ছাড়া কোনো বস্তু বা স্থানের সাথে জুড়ে দেওয়া বিপজ্জনক। মুসলিমকে অন্যদের ভুল রীতি নকল করা থেকে বাঁচতে হবে।"},"teachings":["বরকত পাওয়ার নামে মুশরিকদের রীতি অনুসরণ করা যাবে না।","নতুন মুসলিম হলেও তাওহীদের বিষয়ে সতর্ক থাকা জরুরি।","কল্যাণের আশা আল্লাহর অনুমোদিত পথেই রাখতে হবে।","পূর্ববর্তী জাতির ভুল থেকে শিক্ষা নেওয়া দরকার।"],"related_hadiths":[{"id":"3456","book_id":"1","label":"Sahih Bukhari"},{"id":"266৯","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যাতুল আনওয়াত ও শির্ক থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মুশরিকদের মতো বরকতের জন্য বিশেষ গাছ চাওয়াকে নবীজি পূর্ববর্তীদের ভুল রীতির সাথে তুলনা করেছেন।"},"heading":{"title":"যাতুল আনওয়াত হাদিস: বরকত লাভে ভুল পথ থেকে সাবধান","description":"এই হাদিসে হুনাইনের পথে একটি ঘটনার কথা এসেছে। কিছু নতুন মুসলিম মুশরিকদের একটি গাছ দেখে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম-কে বললেন, তাদের যেমন নির্দিষ্ট গাছ আছে, আমাদের জন্যও তেমন একটি গাছ নির্ধারণ করে দিন। নবীজি এ কথাকে খুব গুরুতরভাবে নিলেন এবং বললেন, এটি পূর্ববর্তী লোকদের রীতির মতো। তিনি বনী ইসরাঈলের সেই কথাও স্মরণ করালেন, যখন তারা মূসা আলাইহিস সালামকে মুশরিকদের মতো মা‘বূদ বানিয়ে দিতে বলেছিল। এখানে মূল শিক্ষা হলো—বরকত, সাহায্য ও কল্যাণের আশা আল্লাহর বিধান ছাড়া কোনো বস্তু বা স্থানের সাথে জুড়ে দেওয়া বিপজ্জনক। মুসলিমকে অন্যদের ভুল রীতি নকল করা থেকে বাঁচতে হবে।"},"teachings":["বরকত পাওয়ার নামে মুশরিকদের রীতি অনুসরণ করা যাবে না।","নতুন মুসলিম হলেও তাওহীদের বিষয়ে সতর্ক থাকা জরুরি।","কল্যাণের আশা আল্লাহর অনুমোদিত পথেই রাখতে হবে।","পূর্ববর্তী জাতির ভুল থেকে শিক্ষা নেওয়া দরকার।"],"related_hadiths":[{"id":"3456","book_id":"1","label":"Sahih Bukhari"},{"id":"2669","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মানত পূরণ ও নাফরমানী থেকে বাঁচা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর আনুগত্যের মানত পূরণ করতে হবে, আর নাফরমানীর মানত পূরণ করা যাবে না—এটাই মূল শিক্ষা।"},"heading":{"title":"মানত সম্পর্কে হাদিস: আনুগত্যের মানত পূরণ, পাপের মানত নয়","description":"এই হাদিসে মানত সম্পর্কে সহজ ও পরিষ্কার নীতি দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি আল্লাহর আনুগত্যের কাজে মানত করে, সে যেন তা পূরণ করে। আর যে ব্যক্তি আল্লাহর নাফরমানীমূলক কাজে মানত করে, সে যেন আল্লাহর নাফরমানী না করে। অর্থাৎ মানত হলেই সব পূরণ করতে হবে—এমন নয়। যদি মানতটি ভালো কাজ, ইবাদত বা আল্লাহর আনুগত্যের মধ্যে পড়ে, তবে তা পূরণ করতে হবে। কিন্তু যদি তা পাপ, অন্যায় বা আল্লাহর অবাধ্যতার দিকে নিয়ে যায়, তাহলে তা করা যাবে না। এই হাদিস মানতের বিষয়ে আবেগ নয়, শরীয়তের সীমা মানতে শেখায়।"},"teachings":["আল্লাহর আনুগত্যের মানত পূরণ করতে হবে।","পাপ বা নাফরমানীর মানত পূরণ করা যাবে না।","মানতের আগে কাজটি বৈধ কি না তা বুঝে নেওয়া দরকার।","ইবাদতের ক্ষেত্রেও আল্লাহর সীমা মানা জরুরি।"],"related_hadiths":[{"id":"660৮","book_id":"1","label":"Sahih Bukhari"},{"id":"3426","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মানত পূরণ ও নাফরমানী থেকে বাঁচা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর আনুগত্যের মানত পূরণ করতে হবে, আর নাফরমানীর মানত পূরণ করা যাবে না—এটাই মূল শিক্ষা।"},"heading":{"title":"মানত সম্পর্কে হাদিস: আনুগত্যের মানত পূরণ, পাপের মানত নয়","description":"এই হাদিসে মানত সম্পর্কে সহজ ও পরিষ্কার নীতি দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি আল্লাহর আনুগত্যের কাজে মানত করে, সে যেন তা পূরণ করে। আর যে ব্যক্তি আল্লাহর নাফরমানীমূলক কাজে মানত করে, সে যেন আল্লাহর নাফরমানী না করে। অর্থাৎ মানত হলেই সব পূরণ করতে হবে—এমন নয়। যদি মানতটি ভালো কাজ, ইবাদত বা আল্লাহর আনুগত্যের মধ্যে পড়ে, তবে তা পূরণ করতে হবে। কিন্তু যদি তা পাপ, অন্যায় বা আল্লাহর অবাধ্যতার দিকে নিয়ে যায়, তাহলে তা করা যাবে না। এই হাদিস মানতের বিষয়ে আবেগ নয়, শরীয়তের সীমা মানতে শেখায়।"},"teachings":["আল্লাহর আনুগত্যের মানত পূরণ করতে হবে।","পাপ বা নাফরমানীর মানত পূরণ করা যাবে না।","মানতের আগে কাজটি বৈধ কি না তা বুঝে নেওয়া দরকার।","ইবাদতের ক্ষেত্রেও আল্লাহর সীমা মানা জরুরি।"],"related_hadiths":[{"id":"6608","book_id":"1","label":"Sahih Bukhari"},{"id":"3426","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নতুন স্থানে পড়ার নিরাপদ দোয়া","description":"$book_name$ $hadith_number$ - $chapter_name$. কোনো স্থানে নামলে আল্লাহর পূর্ণ কালামের আশ্রয় চাওয়ার দোয়া শেখানো হয়েছে।"},"heading":{"title":"নতুন স্থানে নামার দোয়া: আল্লাহর কালামের আশ্রয়","description":"এই হাদিসে সফর, বাড়ি, পথ বা কোনো নতুন স্থানে নামার সময় একটি দোয়া শেখানো হয়েছে। দোয়াটি হলো: أَعُوْذُ بِكَلِمَاتِ اللهِ التَّامَّاتِ مِنْ شَرِّ مَا خَلَقَ — অর্থাৎ, আমি আল্লাহর পূর্ণ কালামের নিকট তাঁর সৃষ্টির সব অনিষ্ট থেকে আশ্রয় চাই। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি কোনো বাড়ি বা স্থানে নেমে এই দোয়া পড়বে, সে ঐ স্থান ত্যাগ না করা পর্যন্ত কোনো কিছু তার ক্ষতি করতে পারবে না। এখানে মূল শিক্ষা হলো নিরাপত্তার জন্য তাবিজ বা কুসংস্কার নয়, আল্লাহর কাছে আশ্রয় চাওয়া। মুসলিমের ভরসা হবে আল্লাহর কালাম, দোয়া ও তাওয়াক্কুলের উপর।"},"teachings":["নতুন স্থানে নামলে আল্লাহর কাছে আশ্রয় চাইতে হবে।","সৃষ্টির অনিষ্ট থেকে বাঁচার জন্য দোয়া বড় উপায়।","নিরাপত্তার ভরসা তাবিজ নয়, আল্লাহর উপর রাখতে হবে।","দোয়া মুখস্থ করে জীবনে ব্যবহার করা দরকার।"],"related_hadiths":[{"id":"270৮","book_id":"2","label":"Sahih Muslim"},{"id":"2310","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নতুন স্থানে পড়ার নিরাপদ দোয়া","description":"$book_name$ $hadith_number$ - $chapter_name$. কোনো স্থানে নামলে আল্লাহর পূর্ণ কালামের আশ্রয় চাওয়ার দোয়া শেখানো হয়েছে।"},"heading":{"title":"নতুন স্থানে নামার দোয়া: আল্লাহর কালামের আশ্রয়","description":"এই হাদিসে সফর, বাড়ি, পথ বা কোনো নতুন স্থানে নামার সময় একটি দোয়া শেখানো হয়েছে। দোয়াটি হলো: أَعُوْذُ بِكَلِمَاتِ اللهِ التَّامَّاتِ مِنْ شَرِّ مَا خَلَقَ — অর্থাৎ, আমি আল্লাহর পূর্ণ কালামের নিকট তাঁর সৃষ্টির সব অনিষ্ট থেকে আশ্রয় চাই। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি কোনো বাড়ি বা স্থানে নেমে এই দোয়া পড়বে, সে ঐ স্থান ত্যাগ না করা পর্যন্ত কোনো কিছু তার ক্ষতি করতে পারবে না। এখানে মূল শিক্ষা হলো নিরাপত্তার জন্য তাবিজ বা কুসংস্কার নয়, আল্লাহর কাছে আশ্রয় চাওয়া। মুসলিমের ভরসা হবে আল্লাহর কালাম, দোয়া ও তাওয়াক্কুলের উপর।"},"teachings":["নতুন স্থানে নামলে আল্লাহর কাছে আশ্রয় চাইতে হবে।","সৃষ্টির অনিষ্ট থেকে বাঁচার জন্য দোয়া বড় উপায়।","নিরাপত্তার ভরসা তাবিজ নয়, আল্লাহর উপর রাখতে হবে।","দোয়া মুখস্থ করে জীবনে ব্যবহার করা দরকার।"],"related_hadiths":[{"id":"2708","book_id":"2","label":"Sahih Muslim"},{"id":"2310","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মূর্তিপূজার সূচনা থেকে শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. নেককারদের স্মৃতিতে মূর্তি স্থাপন পরে ইবাদতের পথে নিয়ে যায়—এ বর্ণনায় সেই বিপদের শুরু দেখানো হয়েছে।"},"heading":{"title":"মূর্তিপূজার সূচনা: নেককারদের নামে মূর্তি স্থাপনের বিপদ","description":"এই বর্ণনায় নূহ আলাইহিস সালাম-এর সম্প্রদায়ের কিছু নেককার মানুষের নাম নিয়ে বলা হয়েছে। তারা মারা গেলে শয়তান তাদের সম্প্রদায়কে কুমন্ত্রণা দিল—যেখানে তারা বসতেন, সেখানে তাদের মূর্তি স্থাপন করো এবং তাদের নামেই মূর্তির নাম রাখো। শুরুতে এগুলোর পূজা হয়নি। কিন্তু যারা এগুলো স্থাপন করেছিল তারা মারা গেল, এরপর মূল ঘটনা ও জ্ঞান হারিয়ে গেল। তখন সেই মূর্তিগুলোর ইবাদত শুরু হলো। এই বর্ণনার শিক্ষা খুব গভীর: নেককার মানুষকে ভালোবাসা এক বিষয়, আর তাদের নামে এমন স্মৃতিচিহ্ন বানানো আরেক বিষয়, যা পরে ইবাদতের রূপ নিতে পারে। শির্কের পথ অনেক সময় ধীরে ধীরে খুলে যায়।"},"teachings":["নেককারদের ভালোবাসা যেন ইবাদতের সীমা না ছাড়ায়।","মূর্তি বা প্রতিমা স্থাপন পরে বড় ফিতনার কারণ হতে পারে।","শয়তান ধীরে ধীরে মানুষকে শির্কের দিকে টানে।","ইতিহাস ভুলে গেলে ভুল কাজকে ধর্ম মনে করার ঝুঁকি থাকে।"],"related_hadiths":[{"id":"4৯20","book_id":"1","label":"Sahih Bukhari"},{"id":"4৯21","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মূর্তিপূজার সূচনা থেকে শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. নেককারদের স্মৃতিতে মূর্তি স্থাপন পরে ইবাদতের পথে নিয়ে যায়—এ বর্ণনায় সেই বিপদের শুরু দেখানো হয়েছে।"},"heading":{"title":"মূর্তিপূজার সূচনা: নেককারদের নামে মূর্তি স্থাপনের বিপদ","description":"এই বর্ণনায় নূহ আলাইহিস সালাম-এর সম্প্রদায়ের কিছু নেককার মানুষের নাম নিয়ে বলা হয়েছে। তারা মারা গেলে শয়তান তাদের সম্প্রদায়কে কুমন্ত্রণা দিল—যেখানে তারা বসতেন, সেখানে তাদের মূর্তি স্থাপন করো এবং তাদের নামেই মূর্তির নাম রাখো। শুরুতে এগুলোর পূজা হয়নি। কিন্তু যারা এগুলো স্থাপন করেছিল তারা মারা গেল, এরপর মূল ঘটনা ও জ্ঞান হারিয়ে গেল। তখন সেই মূর্তিগুলোর ইবাদত শুরু হলো। এই বর্ণনার শিক্ষা খুব গভীর: নেককার মানুষকে ভালোবাসা এক বিষয়, আর তাদের নামে এমন স্মৃতিচিহ্ন বানানো আরেক বিষয়, যা পরে ইবাদতের রূপ নিতে পারে। শির্কের পথ অনেক সময় ধীরে ধীরে খুলে যায়।"},"teachings":["নেককারদের ভালোবাসা যেন ইবাদতের সীমা না ছাড়ায়।","মূর্তি বা প্রতিমা স্থাপন পরে বড় ফিতনার কারণ হতে পারে।","শয়তান ধীরে ধীরে মানুষকে শির্কের দিকে টানে।","ইতিহাস ভুলে গেলে ভুল কাজকে ধর্ম মনে করার ঝুঁকি থাকে।"],"related_hadiths":[{"id":"4920","book_id":"1","label":"Sahih Bukhari"},{"id":"4921","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মক্কা বিজয়ে মূর্তি অপসারণের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. কা‘বার চারপাশের মূর্তি সরিয়ে সত্যের আগমন ও মিথ্যার বিলুপ্তির ঘোষণা দেওয়া হয়েছিল।"},"heading":{"title":"মক্কা বিজয়ের হাদিস: সত্য এসেছে, মিথ্যা বিলুপ্ত হয়েছে","description":"এই হাদিসে মক্কা বিজয়ের দিনের একটি দৃশ্য এসেছে। রাসূলুল্লাহ সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম যখন মক্কায় প্রবেশ করলেন, তখন কা‘বা ঘরের চারপাশে তিনশ ষাটটি মূর্তি ছিল। তিনি হাতে থাকা ছড়ি দিয়ে সেগুলোকে ঠোকা দিচ্ছিলেন এবং বলছিলেন, সত্য এসেছে আর মিথ্যা বিলুপ্ত হয়েছে; মিথ্যা তো বিলুপ্ত হওয়ারই। এই ঘটনা তাওহীদের বিজয় ও শির্কের অপসারণের বড় শিক্ষা দেয়। কা‘বা আল্লাহর ঘর, সেখানে মূর্তি থাকার কোনো স্থান নেই। হাদিসের মূল বার্তা হলো—সত্য প্রতিষ্ঠিত হলে মিথ্যা টেকে না। মুসলিমের হৃদয়েও তাওহীদের জায়গায় কোনো মূর্তি, শির্ক বা ভুল ভরসা রাখা যায় না।"},"teachings":["আল্লাহর ঘর থেকে মূর্তি অপসারণ তাওহীদের দাবি।","সত্য প্রতিষ্ঠার সাথে মিথ্যা দূর হয়।","শির্কের চিহ্নকে সম্মান নয়, বর্জন করতে হবে।","ইবাদতের স্থানকে শুদ্ধ রাখা জরুরি।"],"related_hadiths":[{"id":"4৯20","book_id":"1","label":"Sahih Bukhari"},{"id":"712","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মক্কা বিজয়ে মূর্তি অপসারণের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. কা‘বার চারপাশের মূর্তি সরিয়ে সত্যের আগমন ও মিথ্যার বিলুপ্তির ঘোষণা দেওয়া হয়েছিল।"},"heading":{"title":"মক্কা বিজয়ের হাদিস: সত্য এসেছে, মিথ্যা বিলুপ্ত হয়েছে","description":"এই হাদিসে মক্কা বিজয়ের দিনের একটি দৃশ্য এসেছে। রাসূলুল্লাহ সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম যখন মক্কায় প্রবেশ করলেন, তখন কা‘বা ঘরের চারপাশে তিনশ ষাটটি মূর্তি ছিল। তিনি হাতে থাকা ছড়ি দিয়ে সেগুলোকে ঠোকা দিচ্ছিলেন এবং বলছিলেন, সত্য এসেছে আর মিথ্যা বিলুপ্ত হয়েছে; মিথ্যা তো বিলুপ্ত হওয়ারই। এই ঘটনা তাওহীদের বিজয় ও শির্কের অপসারণের বড় শিক্ষা দেয়। কা‘বা আল্লাহর ঘর, সেখানে মূর্তি থাকার কোনো স্থান নেই। হাদিসের মূল বার্তা হলো—সত্য প্রতিষ্ঠিত হলে মিথ্যা টেকে না। মুসলিমের হৃদয়েও তাওহীদের জায়গায় কোনো মূর্তি, শির্ক বা ভুল ভরসা রাখা যায় না।"},"teachings":["আল্লাহর ঘর থেকে মূর্তি অপসারণ তাওহীদের দাবি।","সত্য প্রতিষ্ঠার সাথে মিথ্যা দূর হয়।","শির্কের চিহ্নকে সম্মান নয়, বর্জন করতে হবে।","ইবাদতের স্থানকে শুদ্ধ রাখা জরুরি।"],"related_hadiths":[{"id":"4920","book_id":"1","label":"Sahih Bukhari"},{"id":"712","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অশুভ লক্ষণ গ্রহণ শির্কী কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. কুলক্ষণ বা অশুভ ধারণাকে কাজের ভিত্তি বানানো শির্কী কাজ—এ কথা তিনবার বলা হয়েছে।"},"heading":{"title":"অশুভ লক্ষণ শির্ক: কুলক্ষণ বিশ্বাসের বিরুদ্ধে হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, অশুভ বা কুলক্ষণ ফল গ্রহণ করা শির্কী কাজ। তিনি কথাটি তিনবার বলেছেন। কোনো কথা তিনবার বলা হলে তার গুরুত্ব আরও পরিষ্কার হয়। কুলক্ষণ মানে কোনো পাখি, শব্দ, দিন, দিক, ব্যক্তি বা ঘটনার কারণে নিজের কাজে অশুভ ফল হবে—এমন বিশ্বাস করা। এই ধরনের ধারণা মানুষের সিদ্ধান্তকে আল্লাহর উপর ভরসা থেকে সরিয়ে দেয়। মুমিন কাজ করবে বৈধ কারণ, পরামর্শ ও দোয়ার মাধ্যমে; অশুভ ধারণার কারণে কাজ ছেড়ে দেবে না। এই হাদিস তাওহীদকে পরিষ্কার রাখার শিক্ষা দেয়। ভয়, অনুমান ও কুসংস্কার নয়—আল্লাহর উপর ভরসাই মুমিনের ভিত্তি।"},"teachings":["অশুভ লক্ষণকে সত্য ধরে নেওয়া শির্কী কাজ।","কুলক্ষণে বিশ্বাস মানুষের তাওয়াক্কুল দুর্বল করে।","নবীজি বিষয়টি তিনবার বলে গুরুত্ব বুঝিয়েছেন।","কাজের সিদ্ধান্ত কুসংস্কার নয়, আল্লাহর ভরসায় নিতে হবে।"],"related_hadiths":[{"id":"457৮","book_id":"14","label":"Mishkat al-Masabih"},{"id":"43৮2","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অশুভ লক্ষণ গ্রহণ শির্কী কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. কুলক্ষণ বা অশুভ ধারণাকে কাজের ভিত্তি বানানো শির্কী কাজ—এ কথা তিনবার বলা হয়েছে।"},"heading":{"title":"অশুভ লক্ষণ শির্ক: কুলক্ষণ বিশ্বাসের বিরুদ্ধে হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, অশুভ বা কুলক্ষণ ফল গ্রহণ করা শির্কী কাজ। তিনি কথাটি তিনবার বলেছেন। কোনো কথা তিনবার বলা হলে তার গুরুত্ব আরও পরিষ্কার হয়। কুলক্ষণ মানে কোনো পাখি, শব্দ, দিন, দিক, ব্যক্তি বা ঘটনার কারণে নিজের কাজে অশুভ ফল হবে—এমন বিশ্বাস করা। এই ধরনের ধারণা মানুষের সিদ্ধান্তকে আল্লাহর উপর ভরসা থেকে সরিয়ে দেয়। মুমিন কাজ করবে বৈধ কারণ, পরামর্শ ও দোয়ার মাধ্যমে; অশুভ ধারণার কারণে কাজ ছেড়ে দেবে না। এই হাদিস তাওহীদকে পরিষ্কার রাখার শিক্ষা দেয়। ভয়, অনুমান ও কুসংস্কার নয়—আল্লাহর উপর ভরসাই মুমিনের ভিত্তি।"},"teachings":["অশুভ লক্ষণকে সত্য ধরে নেওয়া শির্কী কাজ।","কুলক্ষণে বিশ্বাস মানুষের তাওয়াক্কুল দুর্বল করে।","নবীজি বিষয়টি তিনবার বলে গুরুত্ব বুঝিয়েছেন।","কাজের সিদ্ধান্ত কুসংস্কার নয়, আল্লাহর ভরসায় নিতে হবে।"],"related_hadiths":[{"id":"4578","book_id":"14","label":"Mishkat al-Masabih"},{"id":"4382","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিকের তিন আলামত","description":"$book_name$ $hadith_number$ - $chapter_name$. কথা বললে মিথ্যা, ওয়াদা করলে ভঙ্গ এবং আমানত রাখলে খিয়ানত—মুনাফিকের তিন আলামত এখানে এসেছে।"},"heading":{"title":"মুনাফিকের তিন আলামত: মিথ্যা, ওয়াদা ভঙ্গ ও খিয়ানত","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মুনাফিকের তিনটি আলামত বলেছেন। প্রথমত, সে কথা বললে মিথ্যা বলে। দ্বিতীয়ত, ওয়াদা করলে তা ভঙ্গ করে। তৃতীয়ত, তার কাছে আমানত রাখা হলে সে খিয়ানত করে। এই হাদিস খুব পরিচিত, কিন্তু এর শিক্ষা প্রতিদিনের জীবনে দরকার। মুনাফিকের আলামত হাদিস আমাদের কথা, প্রতিশ্রুতি ও আমানতের ব্যাপারে সতর্ক করে। মানুষকে বিশ্বাসযোগ্য হতে হলে সত্য বলা, ওয়াদা রাখা এবং আমানত রক্ষা করা জরুরি। এখানে শুধু বড় লেনদেন নয়; কথা, দায়িত্ব, গোপন তথ্য বা মানুষের হক—সব ক্ষেত্রেই সততা দরকার।"},"teachings":["মিথ্যা বলা মুনাফিকের আলামতের মধ্যে এসেছে।","ওয়াদা করে তা ভেঙে ফেলা খারাপ আচরণ।","আমানত রাখলে খিয়ানত করা মুনাফিকী স্বভাবের লক্ষণ।","সত্যবাদিতা ও আমানতদারি মুসলিম চরিত্রের জরুরি অংশ।"],"related_hadiths":[{"id":"33","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯","book_id":"2","label":"Sahih Muslim"},{"id":"2631","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিকের তিন আলামত","description":"$book_name$ $hadith_number$ - $chapter_name$. কথা বললে মিথ্যা, ওয়াদা করলে ভঙ্গ এবং আমানত রাখলে খিয়ানত—মুনাফিকের তিন আলামত এখানে এসেছে।"},"heading":{"title":"মুনাফিকের তিন আলামত: মিথ্যা, ওয়াদা ভঙ্গ ও খিয়ানত","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মুনাফিকের তিনটি আলামত বলেছেন। প্রথমত, সে কথা বললে মিথ্যা বলে। দ্বিতীয়ত, ওয়াদা করলে তা ভঙ্গ করে। তৃতীয়ত, তার কাছে আমানত রাখা হলে সে খিয়ানত করে। এই হাদিস খুব পরিচিত, কিন্তু এর শিক্ষা প্রতিদিনের জীবনে দরকার। মুনাফিকের আলামত হাদিস আমাদের কথা, প্রতিশ্রুতি ও আমানতের ব্যাপারে সতর্ক করে। মানুষকে বিশ্বাসযোগ্য হতে হলে সত্য বলা, ওয়াদা রাখা এবং আমানত রক্ষা করা জরুরি। এখানে শুধু বড় লেনদেন নয়; কথা, দায়িত্ব, গোপন তথ্য বা মানুষের হক—সব ক্ষেত্রেই সততা দরকার।"},"teachings":["মিথ্যা বলা মুনাফিকের আলামতের মধ্যে এসেছে।","ওয়াদা করে তা ভেঙে ফেলা খারাপ আচরণ।","আমানত রাখলে খিয়ানত করা মুনাফিকী স্বভাবের লক্ষণ।","সত্যবাদিতা ও আমানতদারি মুসলিম চরিত্রের জরুরি অংশ।"],"related_hadiths":[{"id":"33","book_id":"1","label":"Sahih Bukhari"},{"id":"59","book_id":"2","label":"Sahih Muslim"},{"id":"2631","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুলক্ষণ দূর করার দোয়া ও তাওহীদ","description":"$book_name$ $hadith_number$ - $chapter_name$. অশুভ ধারণা কাজ থেকে ফিরিয়ে দিলে তা শির্ক; এর কাফ্ফারা হিসেবে তাওহীদের দোয়া শেখানো হয়েছে।"},"heading":{"title":"কুলক্ষণ দূর করার দোয়া: অশুভ ধারণা থেকে তাওহীদের পথে","description":"এই হাদিসে কুলক্ষণ বা অশুভ ধারণার বাস্তব ক্ষতি বোঝানো হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, কুলক্ষণ যে ব্যক্তিকে তার প্রয়োজন, দায়িত্ব বা কর্তব্য থেকে ফিরিয়ে রাখে, সে শির্ক করল। অর্থাৎ মনে অশুভ ধারণা আসা এক বিষয়, কিন্তু সেই ধারণার কারণে বৈধ কাজ ছেড়ে দেওয়া বড় ভুল। সাহাবীগণ এর কাফ্ফারা জানতে চাইলে নবীজি একটি দোয়া শিখিয়েছেন: اللَّهُمَّ لاَ خَيْرَ إِلاَّ خَيْرُكَ وَلاَ طَيْرَ إِلاَّ طَيْرُكَ وَلاَ إِلَهَ غَيْرُكَ। অর্থ হলো, হে আল্লাহ! তোমার মঙ্গল ছাড়া কোনো মঙ্গল নেই। তোমার অশুভ ছাড়া কোনো অশুভ নেই এবং তুমি ছাড়া কোনো মা‘বূদ নেই। এই দোয়া কুসংস্কার ভেঙে তাওহীদ মজবুত করে।"},"teachings":["অশুভ ধারণার কারণে দায়িত্ব ছেড়ে দেওয়া শির্কের পথে নিয়ে যায়।","কুলক্ষণ দূর করতে নবীজি তাওহীদের দোয়া শিখিয়েছেন।","মঙ্গল ও অমঙ্গলের নিয়ন্ত্রণ আল্লাহর হাতে।","মন দুর্বল হলে দোয়ার মাধ্যমে আল্লাহর দিকে ফিরতে হবে।"],"related_hadiths":[{"id":"45৮4","book_id":"14","label":"Mishkat al-Masabih"},{"id":"457৮","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুলক্ষণ দূর করার দোয়া ও তাওহীদ","description":"$book_name$ $hadith_number$ - $chapter_name$. অশুভ ধারণা কাজ থেকে ফিরিয়ে দিলে তা শির্ক; এর কাফ্ফারা হিসেবে তাওহীদের দোয়া শেখানো হয়েছে।"},"heading":{"title":"কুলক্ষণ দূর করার দোয়া: অশুভ ধারণা থেকে তাওহীদের পথে","description":"এই হাদিসে কুলক্ষণ বা অশুভ ধারণার বাস্তব ক্ষতি বোঝানো হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, কুলক্ষণ যে ব্যক্তিকে তার প্রয়োজন, দায়িত্ব বা কর্তব্য থেকে ফিরিয়ে রাখে, সে শির্ক করল। অর্থাৎ মনে অশুভ ধারণা আসা এক বিষয়, কিন্তু সেই ধারণার কারণে বৈধ কাজ ছেড়ে দেওয়া বড় ভুল। সাহাবীগণ এর কাফ্ফারা জানতে চাইলে নবীজি একটি দোয়া শিখিয়েছেন: اللَّهُمَّ لاَ خَيْرَ إِلاَّ خَيْرُكَ وَلاَ طَيْرَ إِلاَّ طَيْرُكَ وَلاَ إِلَهَ غَيْرُكَ। অর্থ হলো, হে আল্লাহ! তোমার মঙ্গল ছাড়া কোনো মঙ্গল নেই। তোমার অশুভ ছাড়া কোনো অশুভ নেই এবং তুমি ছাড়া কোনো মা‘বূদ নেই। এই দোয়া কুসংস্কার ভেঙে তাওহীদ মজবুত করে।"},"teachings":["অশুভ ধারণার কারণে দায়িত্ব ছেড়ে দেওয়া শির্কের পথে নিয়ে যায়।","কুলক্ষণ দূর করতে নবীজি তাওহীদের দোয়া শিখিয়েছেন।","মঙ্গল ও অমঙ্গলের নিয়ন্ত্রণ আল্লাহর হাতে।","মন দুর্বল হলে দোয়ার মাধ্যমে আল্লাহর দিকে ফিরতে হবে।"],"related_hadiths":[{"id":"4584","book_id":"14","label":"Mishkat al-Masabih"},{"id":"4578","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিরক থেকে আমল রক্ষার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর সন্তুষ্টির জন্য আমল করা জরুরি; আমলে শিরক থাকলে তা প্রত্যাখ্যাত হওয়ার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"শিরক থেকে আমল রক্ষা: আল্লাহর জন্য খাঁটি ইবাদত","description":"এই হাদিসের মূল শিক্ষা হলো, ইবাদত ও সৎকাজ শুধু আল্লাহর জন্য হতে হবে। এখানে আল্লাহ তা‘আলা নিজেই বলেছেন, তিনি অংশীদারদের অংশীদারিত্ব থেকে সম্পূর্ণ মুক্ত। অর্থাৎ কেউ যদি কোনো আমল করে, কিন্তু সেই আমলে আল্লাহর সাথে অন্য কাউকে শরীক করে, তাহলে সেই আমল আল্লাহর কাছে গ্রহণযোগ্য থাকে না। শিরক শুধু প্রকাশ্য মূর্তি বা বস্তু পূজার মধ্যেই সীমাবদ্ধ নয়; আমলের উদ্দেশ্যে অন্য কারও সন্তুষ্টি, মর্যাদা বা প্রশংসা ঢুকে গেলে সেটিও ভয়ংকর বিষয়। এই হাদিস আমাদের নিয়ত ঠিক করার কথা স্মরণ করায়। তাই নামাজ, দান, শিক্ষা, দাওয়াত বা যে কোনো ভালো কাজের আগে নিজের অন্তরকে জিজ্ঞেস করা দরকার—আমি এটা কার জন্য করছি?"},"teachings":["আমল আল্লাহর জন্য খাঁটি না হলে তা গ্রহণযোগ্যতার ঝুঁকিতে পড়ে।","ইবাদতে আল্লাহর সাথে কাউকে শরীক করা বড় সতর্কতার বিষয়।","প্রতিটি ভালো কাজের আগে নিয়ত যাচাই করা দরকার।","মানুষের প্রশংসা নয়, আল্লাহর সন্তুষ্টিই আমলের মূল লক্ষ্য হওয়া উচিত।"],"related_hadiths":[{"id":"15৮","book_id":"2","label":"Sahih Muslim"},{"id":"1","book_id":"1","label":"Sahih Bukhari"},{"id":"7365","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিরক থেকে আমল রক্ষার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর সন্তুষ্টির জন্য আমল করা জরুরি; আমলে শিরক থাকলে তা প্রত্যাখ্যাত হওয়ার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"শিরক থেকে আমল রক্ষা: আল্লাহর জন্য খাঁটি ইবাদত","description":"এই হাদিসের মূল শিক্ষা হলো, ইবাদত ও সৎকাজ শুধু আল্লাহর জন্য হতে হবে। এখানে আল্লাহ তা‘আলা নিজেই বলেছেন, তিনি অংশীদারদের অংশীদারিত্ব থেকে সম্পূর্ণ মুক্ত। অর্থাৎ কেউ যদি কোনো আমল করে, কিন্তু সেই আমলে আল্লাহর সাথে অন্য কাউকে শরীক করে, তাহলে সেই আমল আল্লাহর কাছে গ্রহণযোগ্য থাকে না। শিরক শুধু প্রকাশ্য মূর্তি বা বস্তু পূজার মধ্যেই সীমাবদ্ধ নয়; আমলের উদ্দেশ্যে অন্য কারও সন্তুষ্টি, মর্যাদা বা প্রশংসা ঢুকে গেলে সেটিও ভয়ংকর বিষয়। এই হাদিস আমাদের নিয়ত ঠিক করার কথা স্মরণ করায়। তাই নামাজ, দান, শিক্ষা, দাওয়াত বা যে কোনো ভালো কাজের আগে নিজের অন্তরকে জিজ্ঞেস করা দরকার—আমি এটা কার জন্য করছি?"},"teachings":["আমল আল্লাহর জন্য খাঁটি না হলে তা গ্রহণযোগ্যতার ঝুঁকিতে পড়ে।","ইবাদতে আল্লাহর সাথে কাউকে শরীক করা বড় সতর্কতার বিষয়।","প্রতিটি ভালো কাজের আগে নিয়ত যাচাই করা দরকার।","মানুষের প্রশংসা নয়, আল্লাহর সন্তুষ্টিই আমলের মূল লক্ষ্য হওয়া উচিত।"],"related_hadiths":[{"id":"158","book_id":"2","label":"Sahih Muslim"},{"id":"1","book_id":"1","label":"Sahih Bukhari"},{"id":"7365","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গোপন শিরক ও লোক দেখানো নামাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. লোক দেখানোর উদ্দেশ্যে ইবাদত করা গোপন শিরকের অন্তর্ভুক্ত; নামাজেও নিয়ত খাঁটি রাখা জরুরি।"},"heading":{"title":"গোপন শিরক: লোক দেখানো ইবাদত থেকে সতর্কতা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) দাজ্জাল নিয়ে আলোচনার সময় আরও ভয়ঙ্কর একটি বিষয়ের কথা বলেছেন—গোপন শিরক। হাদিসে এর উদাহরণ দেওয়া হয়েছে, একজন মানুষ নামাজে দাঁড়ায় এবং মনে মনে ভাবে, কেউ তাকে দেখছে; তাই সে নামাজকে মানুষের চোখে সুন্দর করে তুলতে চায়। এখানে মূল বিষয় হলো রিয়া বা লোক দেখানো আমল। নামাজের বাহ্যিক রূপ সুন্দর হলেও যদি উদ্দেশ্য মানুষের প্রশংসা হয়, তাহলে তা অন্তরের জন্য ক্ষতিকর। এই হাদিস আমাদের শেখায়, ইবাদতের সময় মানুষের চোখ নয়, আল্লাহর সন্তুষ্টিকে সামনে রাখতে হবে। নিজের আমল নিয়ে অহংকার বা সুনাম পাওয়ার আশা থেকে সতর্ক থাকা মুমিনের দরকারি কাজ।"},"teachings":["লোক দেখানোর জন্য নামাজ পড়া গোপন শিরকের একটি উদাহরণ।","ইবাদতের সৌন্দর্য মানুষের প্রশংসার জন্য নয়, আল্লাহর সন্তুষ্টির জন্য হওয়া উচিত।","নামাজে দাঁড়ানোর সময় অন্তরের নিয়ত ঠিক রাখা দরকার।","সুনাম, নেতৃত্ব বা দুনিয়ার স্বার্থ ইবাদতের উদ্দেশ্য হওয়া উচিত নয়।"],"related_hadiths":[{"id":"7365","book_id":"2","label":"Sahih Muslim"},{"id":"1","book_id":"1","label":"Sahih Bukhari"},{"id":"15৮","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গোপন শিরক ও লোক দেখানো নামাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. লোক দেখানোর উদ্দেশ্যে ইবাদত করা গোপন শিরকের অন্তর্ভুক্ত; নামাজেও নিয়ত খাঁটি রাখা জরুরি।"},"heading":{"title":"গোপন শিরক: লোক দেখানো ইবাদত থেকে সতর্কতা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) দাজ্জাল নিয়ে আলোচনার সময় আরও ভয়ঙ্কর একটি বিষয়ের কথা বলেছেন—গোপন শিরক। হাদিসে এর উদাহরণ দেওয়া হয়েছে, একজন মানুষ নামাজে দাঁড়ায় এবং মনে মনে ভাবে, কেউ তাকে দেখছে; তাই সে নামাজকে মানুষের চোখে সুন্দর করে তুলতে চায়। এখানে মূল বিষয় হলো রিয়া বা লোক দেখানো আমল। নামাজের বাহ্যিক রূপ সুন্দর হলেও যদি উদ্দেশ্য মানুষের প্রশংসা হয়, তাহলে তা অন্তরের জন্য ক্ষতিকর। এই হাদিস আমাদের শেখায়, ইবাদতের সময় মানুষের চোখ নয়, আল্লাহর সন্তুষ্টিকে সামনে রাখতে হবে। নিজের আমল নিয়ে অহংকার বা সুনাম পাওয়ার আশা থেকে সতর্ক থাকা মুমিনের দরকারি কাজ।"},"teachings":["লোক দেখানোর জন্য নামাজ পড়া গোপন শিরকের একটি উদাহরণ।","ইবাদতের সৌন্দর্য মানুষের প্রশংসার জন্য নয়, আল্লাহর সন্তুষ্টির জন্য হওয়া উচিত।","নামাজে দাঁড়ানোর সময় অন্তরের নিয়ত ঠিক রাখা দরকার।","সুনাম, নেতৃত্ব বা দুনিয়ার স্বার্থ ইবাদতের উদ্দেশ্য হওয়া উচিত নয়।"],"related_hadiths":[{"id":"7365","book_id":"2","label":"Sahih Muslim"},{"id":"1","book_id":"1","label":"Sahih Bukhari"},{"id":"158","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দ্বীনে নতুন কাজের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীনের অংশ নয় এমন নতুন বিষয় ইবাদত হিসেবে চালু করলে তা প্রত্যাখ্যাত—হাদিসটি সুন্নাহ মেনে চলার শিক্ষা দেয়।"},"heading":{"title":"বিদআত থেকে বাঁচার হাদিস: দ্বীনে নতুন কিছু যোগ করার সতর্কতা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব স্পষ্টভাবে বলেছেন, যে ব্যক্তি দ্বীনের মধ্যে এমন কিছু নতুনভাবে চালু করে, যা দ্বীনের অংশ নয়, তা প্রত্যাখ্যাত। এখানে মূল শিক্ষা হলো, ইবাদতের ক্ষেত্রে নিজের পছন্দ, আবেগ বা প্রচলনকে দলিল বানানো যাবে না। ইসলাম আল্লাহর দেওয়া দ্বীন, আর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তা মানুষের কাছে পৌঁছে দিয়েছেন। তাই যে কাজকে ইবাদত বলা হবে, সেটির ভিত্তি কুরআন ও সুন্নাহতে থাকতে হবে। এই হাদিস মানুষকে বাড়াবাড়ি থেকে ফিরিয়ে আনে। দ্বীনের নামে নতুন আমল তৈরি করা দেখতে ভালো লাগলেও, হাদিসের ভাষায় তা গ্রহণযোগ্য নয়। তাই আমলের আগে জানা দরকার—এটি রাসূলের শেখানো পথে আছে কি না।"},"teachings":["দ্বীনের অংশ নয় এমন নতুন কাজ ইবাদত হিসেবে চালু করা গ্রহণযোগ্য নয়।","ইবাদতের মানদণ্ড ব্যক্তিগত পছন্দ নয়, কুরআন ও সুন্নাহ।","সুন্নাহ অনুসরণ করলে দ্বীনের সঠিক পথ পরিষ্কার থাকে।","ভালো মনে হলেই কোনো কাজ দ্বীনের আমল হয়ে যায় না।"],"related_hadiths":[{"id":"43৮5","book_id":"2","label":"Sahih Muslim"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দ্বীনে নতুন কাজের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীনের অংশ নয় এমন নতুন বিষয় ইবাদত হিসেবে চালু করলে তা প্রত্যাখ্যাত—হাদিসটি সুন্নাহ মেনে চলার শিক্ষা দেয়।"},"heading":{"title":"বিদআত থেকে বাঁচার হাদিস: দ্বীনে নতুন কিছু যোগ করার সতর্কতা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব স্পষ্টভাবে বলেছেন, যে ব্যক্তি দ্বীনের মধ্যে এমন কিছু নতুনভাবে চালু করে, যা দ্বীনের অংশ নয়, তা প্রত্যাখ্যাত। এখানে মূল শিক্ষা হলো, ইবাদতের ক্ষেত্রে নিজের পছন্দ, আবেগ বা প্রচলনকে দলিল বানানো যাবে না। ইসলাম আল্লাহর দেওয়া দ্বীন, আর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তা মানুষের কাছে পৌঁছে দিয়েছেন। তাই যে কাজকে ইবাদত বলা হবে, সেটির ভিত্তি কুরআন ও সুন্নাহতে থাকতে হবে। এই হাদিস মানুষকে বাড়াবাড়ি থেকে ফিরিয়ে আনে। দ্বীনের নামে নতুন আমল তৈরি করা দেখতে ভালো লাগলেও, হাদিসের ভাষায় তা গ্রহণযোগ্য নয়। তাই আমলের আগে জানা দরকার—এটি রাসূলের শেখানো পথে আছে কি না।"},"teachings":["দ্বীনের অংশ নয় এমন নতুন কাজ ইবাদত হিসেবে চালু করা গ্রহণযোগ্য নয়।","ইবাদতের মানদণ্ড ব্যক্তিগত পছন্দ নয়, কুরআন ও সুন্নাহ।","সুন্নাহ অনুসরণ করলে দ্বীনের সঠিক পথ পরিষ্কার থাকে।","ভালো মনে হলেই কোনো কাজ দ্বীনের আমল হয়ে যায় না।"],"related_hadiths":[{"id":"4385","book_id":"2","label":"Sahih Muslim"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নির্দেশনাহীন আমলের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের নির্দেশনা ছাড়া ইবাদত করলে তা পরিত্যাজ্য; তাই আমলকে সুন্নাহর সাথে মিলিয়ে করা জরুরি।"},"heading":{"title":"সুন্নাহ ছাড়া আমল নয়: নির্দেশনাহীন কাজের সতর্কতা","description":"এই হাদিসে বলা হয়েছে, যে ব্যক্তি এমন আমল করে যার ওপর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কোনো নির্দেশনা নেই, তা পরিত্যাজ্য। এখানে আমলের শুদ্ধতার গুরুত্বপূর্ণ নিয়ম বোঝানো হয়েছে। শুধু ভালো উদ্দেশ্য থাকলেই ইবাদত সঠিক হয়ে যায় না; ইবাদতের পদ্ধতিও রাসূলের শেখানো মতো হতে হবে। কেউ যদি নামাজ, রোজা, দোয়া, যিকির বা অন্য কোনো ইবাদতে নিজের মতো নিয়ম বানায়, তাহলে তা হাদিসের সতর্কতার মধ্যে পড়ে। এই শিক্ষা মানুষকে সুন্নাহর দিকে ফিরিয়ে নেয়। দ্বীনের কাজে নিরাপদ পথ হলো—যা প্রমাণিত, তা করা; যা প্রমাণিত নয়, তা ইবাদত হিসেবে না ধরা। এতে আমল পরিষ্কার থাকে এবং দ্বীনের নামে বাড়তি চাপ তৈরি হয় না।"},"teachings":["রাসূলের নির্দেশনা ছাড়া কোনো কাজ ইবাদত হিসেবে গ্রহণযোগ্য নয়।","ভালো নিয়তের পাশাপাশি সঠিক পদ্ধতিও জরুরি।","সুন্নাহর সাথে মিলিয়ে আমল করা নিরাপদ পথ।","নিজের বানানো নিয়মকে দ্বীনের অংশ বলা ঠিক নয়।"],"related_hadiths":[{"id":"26৯7","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নির্দেশনাহীন আমলের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের নির্দেশনা ছাড়া ইবাদত করলে তা পরিত্যাজ্য; তাই আমলকে সুন্নাহর সাথে মিলিয়ে করা জরুরি।"},"heading":{"title":"সুন্নাহ ছাড়া আমল নয়: নির্দেশনাহীন কাজের সতর্কতা","description":"এই হাদিসে বলা হয়েছে, যে ব্যক্তি এমন আমল করে যার ওপর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কোনো নির্দেশনা নেই, তা পরিত্যাজ্য। এখানে আমলের শুদ্ধতার গুরুত্বপূর্ণ নিয়ম বোঝানো হয়েছে। শুধু ভালো উদ্দেশ্য থাকলেই ইবাদত সঠিক হয়ে যায় না; ইবাদতের পদ্ধতিও রাসূলের শেখানো মতো হতে হবে। কেউ যদি নামাজ, রোজা, দোয়া, যিকির বা অন্য কোনো ইবাদতে নিজের মতো নিয়ম বানায়, তাহলে তা হাদিসের সতর্কতার মধ্যে পড়ে। এই শিক্ষা মানুষকে সুন্নাহর দিকে ফিরিয়ে নেয়। দ্বীনের কাজে নিরাপদ পথ হলো—যা প্রমাণিত, তা করা; যা প্রমাণিত নয়, তা ইবাদত হিসেবে না ধরা। এতে আমল পরিষ্কার থাকে এবং দ্বীনের নামে বাড়তি চাপ তৈরি হয় না।"},"teachings":["রাসূলের নির্দেশনা ছাড়া কোনো কাজ ইবাদত হিসেবে গ্রহণযোগ্য নয়।","ভালো নিয়তের পাশাপাশি সঠিক পদ্ধতিও জরুরি।","সুন্নাহর সাথে মিলিয়ে আমল করা নিরাপদ পথ।","নিজের বানানো নিয়মকে দ্বীনের অংশ বলা ঠিক নয়।"],"related_hadiths":[{"id":"2697","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিতাবুল্লাহ ও নবীর হেদায়াত","description":"$book_name$ $hadith_number$ - $chapter_name$. শ্রেষ্ঠ বাণী আল্লাহর কিতাব, শ্রেষ্ঠ হেদায়াত রাসূলের হেদায়াত; বিদআত থেকে সতর্ক থাকার শিক্ষা।"},"heading":{"title":"শ্রেষ্ঠ হেদায়াত: আল্লাহর কিতাব ও রাসূলের সুন্নাহ","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) হামদ ও ছালাতের পর কয়েকটি বড় মূলনীতি বলেছেন। শ্রেষ্ঠ বাণী হলো আল্লাহর কিতাব, আর শ্রেষ্ঠ হেদায়াত হলো মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর হেদায়াত। এর মানে, মুসলিমের পথচলার প্রধান আলো কুরআন ও সুন্নাহ। এরপর তিনি বলেছেন, দ্বীনের মধ্যে নতুন সৃষ্টি নিকৃষ্ট কাজ এবং প্রত্যেক নতুন সৃষ্টি ভ্রষ্টতা। এই হাদিস আমাদের শেখায়, দ্বীনকে সুন্দর করার নামে নতুন নিয়ম বানানো নয়; বরং আল্লাহর কিতাব ও নবীর পথ আঁকড়ে ধরা দরকার। ইবাদত, বিশ্বাস ও জীবনযাপনে সুন্নাহকে গুরুত্ব দিলে মানুষ বিভ্রান্তি থেকে দূরে থাকার সুযোগ পায়।"},"teachings":["আল্লাহর কিতাব মুসলিমের জন্য শ্রেষ্ঠ বাণী।","রাসূলুল্লাহর হেদায়াতই অনুসরণের জন্য শ্রেষ্ঠ পথ।","দ্বীনের মধ্যে নতুন সৃষ্টি থেকে সতর্ক থাকা দরকার।","কুরআন ও সুন্নাহকে জীবনের মূল দিশা বানানো উচিত।"],"related_hadiths":[{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"},{"id":"26৯7","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিতাবুল্লাহ ও নবীর হেদায়াত","description":"$book_name$ $hadith_number$ - $chapter_name$. শ্রেষ্ঠ বাণী আল্লাহর কিতাব, শ্রেষ্ঠ হেদায়াত রাসূলের হেদায়াত; বিদআত থেকে সতর্ক থাকার শিক্ষা।"},"heading":{"title":"শ্রেষ্ঠ হেদায়াত: আল্লাহর কিতাব ও রাসূলের সুন্নাহ","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) হামদ ও ছালাতের পর কয়েকটি বড় মূলনীতি বলেছেন। শ্রেষ্ঠ বাণী হলো আল্লাহর কিতাব, আর শ্রেষ্ঠ হেদায়াত হলো মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর হেদায়াত। এর মানে, মুসলিমের পথচলার প্রধান আলো কুরআন ও সুন্নাহ। এরপর তিনি বলেছেন, দ্বীনের মধ্যে নতুন সৃষ্টি নিকৃষ্ট কাজ এবং প্রত্যেক নতুন সৃষ্টি ভ্রষ্টতা। এই হাদিস আমাদের শেখায়, দ্বীনকে সুন্দর করার নামে নতুন নিয়ম বানানো নয়; বরং আল্লাহর কিতাব ও নবীর পথ আঁকড়ে ধরা দরকার। ইবাদত, বিশ্বাস ও জীবনযাপনে সুন্নাহকে গুরুত্ব দিলে মানুষ বিভ্রান্তি থেকে দূরে থাকার সুযোগ পায়।"},"teachings":["আল্লাহর কিতাব মুসলিমের জন্য শ্রেষ্ঠ বাণী।","রাসূলুল্লাহর হেদায়াতই অনুসরণের জন্য শ্রেষ্ঠ পথ।","দ্বীনের মধ্যে নতুন সৃষ্টি থেকে সতর্ক থাকা দরকার।","কুরআন ও সুন্নাহকে জীবনের মূল দিশা বানানো উচিত।"],"related_hadiths":[{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"},{"id":"2697","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জাহেলী রীতি ও অন্যায় রক্তপাত","description":"$book_name$ $hadith_number$ - $chapter_name$. হারামে অন্যায়, ইসলামে জাহেলী রীতি চাওয়া ও অন্যায় রক্তপাত—এসব থেকে কঠোরভাবে সতর্ক করা হয়েছে।"},"heading":{"title":"জাহেলী রীতি থেকে দূরে থাকা: ইসলামের পরিষ্কার সতর্কতা","description":"এই হাদিসে তিন ধরনের মানুষকে আল্লাহর কাছে সবচেয়ে বেশি ঘৃণিত বলা হয়েছে। প্রথমত, যে হারাম এলাকায় নিষিদ্ধ কাজ করে। দ্বিতীয়ত, যে ইসলামের মধ্যে জাহেলী যুগের রীতি চালু করতে চায়। তৃতীয়ত, যে অন্যায়ভাবে কারো রক্ত চাইতে থাকে শুধু রক্তপাতের উদ্দেশ্যে। এখানে মূল শিক্ষা হলো, ইসলাম মানুষকে পবিত্রতা, ন্যায় ও সুস্থ রীতি শেখায়। জাহেলিয়াত মানে এমন রীতি, যা ইসলামি নীতির বিপরীত। তাই মুসলিম সমাজে অন্যায় রসম, হিংসা, রক্তপাত বা পুরনো অন্ধ অভ্যাসকে ফিরিয়ে আনার চেষ্টা বিপজ্জনক। এই হাদিস আমাদের মনে করিয়ে দেয়, দ্বীনের নামে বা সমাজের নামে কোনো কাজ করা হলেও তা যদি ইসলামের ন্যায়নীতির বিরুদ্ধে যায়, তবে তা বর্জনীয়।"},"teachings":["হারাম এলাকায় নিষিদ্ধ কাজ করা কঠোর সতর্কতার বিষয়।","ইসলামের মধ্যে জাহেলী রীতি ফিরিয়ে আনার চেষ্টা নিন্দনীয়।","অন্যায়ভাবে কারো রক্তপাত চাওয়া বড় অন্যায়।","মুসলিমের কাজ হলো ন্যায়, পবিত্রতা ও ইসলামী রীতি মেনে চলা।"],"related_hadiths":[{"id":"6৮৮2","book_id":"1","label":"Sahih Bukhari"},{"id":"26৯7","book_id":"1","label":"Sahih Bukhari"},{"id":"43৮5","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জাহেলী রীতি ও অন্যায় রক্তপাত","description":"$book_name$ $hadith_number$ - $chapter_name$. হারামে অন্যায়, ইসলামে জাহেলী রীতি চাওয়া ও অন্যায় রক্তপাত—এসব থেকে কঠোরভাবে সতর্ক করা হয়েছে।"},"heading":{"title":"জাহেলী রীতি থেকে দূরে থাকা: ইসলামের পরিষ্কার সতর্কতা","description":"এই হাদিসে তিন ধরনের মানুষকে আল্লাহর কাছে সবচেয়ে বেশি ঘৃণিত বলা হয়েছে। প্রথমত, যে হারাম এলাকায় নিষিদ্ধ কাজ করে। দ্বিতীয়ত, যে ইসলামের মধ্যে জাহেলী যুগের রীতি চালু করতে চায়। তৃতীয়ত, যে অন্যায়ভাবে কারো রক্ত চাইতে থাকে শুধু রক্তপাতের উদ্দেশ্যে। এখানে মূল শিক্ষা হলো, ইসলাম মানুষকে পবিত্রতা, ন্যায় ও সুস্থ রীতি শেখায়। জাহেলিয়াত মানে এমন রীতি, যা ইসলামি নীতির বিপরীত। তাই মুসলিম সমাজে অন্যায় রসম, হিংসা, রক্তপাত বা পুরনো অন্ধ অভ্যাসকে ফিরিয়ে আনার চেষ্টা বিপজ্জনক। এই হাদিস আমাদের মনে করিয়ে দেয়, দ্বীনের নামে বা সমাজের নামে কোনো কাজ করা হলেও তা যদি ইসলামের ন্যায়নীতির বিরুদ্ধে যায়, তবে তা বর্জনীয়।"},"teachings":["হারাম এলাকায় নিষিদ্ধ কাজ করা কঠোর সতর্কতার বিষয়।","ইসলামের মধ্যে জাহেলী রীতি ফিরিয়ে আনার চেষ্টা নিন্দনীয়।","অন্যায়ভাবে কারো রক্তপাত চাওয়া বড় অন্যায়।","মুসলিমের কাজ হলো ন্যায়, পবিত্রতা ও ইসলামী রীতি মেনে চলা।"],"related_hadiths":[{"id":"6882","book_id":"1","label":"Sahih Bukhari"},{"id":"2697","book_id":"1","label":"Sahih Bukhari"},{"id":"4385","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রাসূলের আনুগত্য ও জান্নাতের পথ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের আনুগত্য জান্নাতের পথে নিয়ে যায়; অবাধ্যতা মানুষকে নিজের জন্য ক্ষতির দিকে ঠেলে দেয়।"},"heading":{"title":"রাসূলের আনুগত্য: জান্নাতের পথে চলার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের সবাই জান্নাতে প্রবেশ করবে, কেবল যে অসম্মত সে ছাড়া। সাহাবীগণ জানতে চাইলেন, কে অসম্মত? তিনি বললেন, যে তাঁর আনুগত্য করবে, সে জান্নাতে প্রবেশ করবে; আর যে তাঁর অবাধ্যতা করবে, সে যেন নিজেই অসম্মত হলো। এই কথায় রাসূলের আনুগত্যের গুরুত্ব পরিষ্কার। মুসলিম পরিচয় শুধু মুখের দাবি নয়; জীবনে নবীর নির্দেশ মানার চেষ্টা থাকতে হবে। সুন্নাহ মেনে চলা, তাঁর নিষেধ থেকে দূরে থাকা এবং তাঁর দেখানো পথে ইবাদত করা—এসবই আনুগত্যের অংশ। হাদিসটি কাউকে হতাশ করার জন্য নয়, বরং মানুষকে রাসূলের পথে ফিরিয়ে আনার জন্য শক্তিশালী স্মরণিকা।"},"teachings":["রাসূলের আনুগত্য জান্নাতের পথ অনুসরণের কারণ।","অবাধ্যতা মানুষকে নিজেই ক্ষতির পথে নিতে পারে।","মুসলিম জীবনে সুন্নাহ মানার চেষ্টা জরুরি।","নবীর নির্দেশকে ভালোবাসা ও মান্য করা ঈমানের দাবি।"],"related_hadiths":[{"id":"72৮1","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রাসূলের আনুগত্য ও জান্নাতের পথ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের আনুগত্য জান্নাতের পথে নিয়ে যায়; অবাধ্যতা মানুষকে নিজের জন্য ক্ষতির দিকে ঠেলে দেয়।"},"heading":{"title":"রাসূলের আনুগত্য: জান্নাতের পথে চলার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের সবাই জান্নাতে প্রবেশ করবে, কেবল যে অসম্মত সে ছাড়া। সাহাবীগণ জানতে চাইলেন, কে অসম্মত? তিনি বললেন, যে তাঁর আনুগত্য করবে, সে জান্নাতে প্রবেশ করবে; আর যে তাঁর অবাধ্যতা করবে, সে যেন নিজেই অসম্মত হলো। এই কথায় রাসূলের আনুগত্যের গুরুত্ব পরিষ্কার। মুসলিম পরিচয় শুধু মুখের দাবি নয়; জীবনে নবীর নির্দেশ মানার চেষ্টা থাকতে হবে। সুন্নাহ মেনে চলা, তাঁর নিষেধ থেকে দূরে থাকা এবং তাঁর দেখানো পথে ইবাদত করা—এসবই আনুগত্যের অংশ। হাদিসটি কাউকে হতাশ করার জন্য নয়, বরং মানুষকে রাসূলের পথে ফিরিয়ে আনার জন্য শক্তিশালী স্মরণিকা।"},"teachings":["রাসূলের আনুগত্য জান্নাতের পথ অনুসরণের কারণ।","অবাধ্যতা মানুষকে নিজেই ক্ষতির পথে নিতে পারে।","মুসলিম জীবনে সুন্নাহ মানার চেষ্টা জরুরি।","নবীর নির্দেশকে ভালোবাসা ও মান্য করা ঈমানের দাবি।"],"related_hadiths":[{"id":"7281","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জান্নাতের আহ্বান ও নবীর অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. জান্নাতের দাওয়াতে সাড়া দেওয়া মানে মুহাম্মাদকে মানা; তাঁর আনুগত্য আল্লাহর আনুগত্যের সাথে যুক্ত।"},"heading":{"title":"জান্নাতের আহ্বান: মুহাম্মাদের আনুগত্যই আল্লাহর আনুগত্য","description":"এই হাদিসে ফেরেশতাদের কথার মাধ্যমে একটি সুন্দর উদাহরণ এসেছে। এক ব্যক্তি ঘর বানালেন, ভোজের আয়োজন করলেন এবং একজন আহ্বায়ক পাঠালেন। যে আহ্বানে সাড়া দিল, সে ঘরে ঢুকল এবং খাবার পেল; যে সাড়া দিল না, সে ঢুকতেও পারল না, খেতেও পারল না। এরপর ব্যাখ্যা করা হলো—ঘরটি জান্নাত, আহ্বায়ক হলেন মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)। তাই যে মুহাম্মাদের আনুগত্য করল, সে আল্লাহর আনুগত্য করল; আর যে তাঁর অবাধ্য হলো, সে আল্লাহর অবাধ্য হলো। এই হাদিস আমাদের শেখায়, জান্নাতের পথ কল্পনা বা নিজের বানানো নিয়মে নয়; নবীর আহ্বানে সাড়া দেওয়ার মধ্যেই সঠিক পথ।"},"teachings":["মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর আহ্বানে সাড়া দেওয়া আল্লাহর আনুগত্যের অংশ।","জান্নাতের পথে নবীর নির্দেশনা অপরিহার্য।","নবীর অবাধ্যতা আল্লাহর অবাধ্যতার সাথে যুক্ত।","সঠিক পথ বুঝতে রাসূলের দাওয়াতকে গ্রহণ করা দরকার।"],"related_hadiths":[{"id":"72৮0","book_id":"1","label":"Sahih Bukhari"},{"id":"1৯৮৮","book_id":"2","label":"Sahih Muslim"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জান্নাতের আহ্বান ও নবীর অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. জান্নাতের দাওয়াতে সাড়া দেওয়া মানে মুহাম্মাদকে মানা; তাঁর আনুগত্য আল্লাহর আনুগত্যের সাথে যুক্ত।"},"heading":{"title":"জান্নাতের আহ্বান: মুহাম্মাদের আনুগত্যই আল্লাহর আনুগত্য","description":"এই হাদিসে ফেরেশতাদের কথার মাধ্যমে একটি সুন্দর উদাহরণ এসেছে। এক ব্যক্তি ঘর বানালেন, ভোজের আয়োজন করলেন এবং একজন আহ্বায়ক পাঠালেন। যে আহ্বানে সাড়া দিল, সে ঘরে ঢুকল এবং খাবার পেল; যে সাড়া দিল না, সে ঢুকতেও পারল না, খেতেও পারল না। এরপর ব্যাখ্যা করা হলো—ঘরটি জান্নাত, আহ্বায়ক হলেন মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)। তাই যে মুহাম্মাদের আনুগত্য করল, সে আল্লাহর আনুগত্য করল; আর যে তাঁর অবাধ্য হলো, সে আল্লাহর অবাধ্য হলো। এই হাদিস আমাদের শেখায়, জান্নাতের পথ কল্পনা বা নিজের বানানো নিয়মে নয়; নবীর আহ্বানে সাড়া দেওয়ার মধ্যেই সঠিক পথ।"},"teachings":["মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর আহ্বানে সাড়া দেওয়া আল্লাহর আনুগত্যের অংশ।","জান্নাতের পথে নবীর নির্দেশনা অপরিহার্য।","নবীর অবাধ্যতা আল্লাহর অবাধ্যতার সাথে যুক্ত।","সঠিক পথ বুঝতে রাসূলের দাওয়াতকে গ্রহণ করা দরকার।"],"related_hadiths":[{"id":"7280","book_id":"1","label":"Sahih Bukhari"},{"id":"1988","book_id":"2","label":"Sahih Muslim"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইবাদতে মধ্যপন্থা ও সুন্নাহ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের সুন্নাহ হলো ইবাদত, বিশ্রাম, সিয়াম ও বিবাহে ভারসাম্যপূর্ণ পথ; বাড়াবাড়ি নয়।"},"heading":{"title":"ইবাদতে মধ্যপন্থা: রাসূলের সুন্নাহ থেকে মুখ ফিরানো নয়","description":"এই হাদিসে তিনজন ব্যক্তি রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর ইবাদত সম্পর্কে জানতে এসে নিজেদের জন্য কঠোর সিদ্ধান্ত নেয়। একজন বলল, সে সারারাত নামাজ পড়বে; আরেকজন বলল, সবসময় রোজা রাখবে; তৃতীয়জন বলল, কখনো বিয়ে করবে না। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাদের ভুল ঠিক করে দিলেন। তিনি বললেন, তিনি আল্লাহকে বেশি ভয় করেন এবং বেশি পরহেযগার, তবু তিনি রোজা রাখেন আবার ছাড়েন, নামাজ পড়েন আবার ঘুমান, এবং বিবাহ করেছেন। তাই সুন্নাহ মানে অস্বাভাবিক কঠোরতা নয়; বরং আল্লাহর ইবাদত ও মানুষের স্বাভাবিক জীবনের মধ্যে সঠিক ভারসাম্য। এই হাদিস ইবাদতে বাড়াবাড়ি থেকে বাঁচতে শেখায়।"},"teachings":["ইবাদতে অতিরিক্ত বাড়াবাড়ি রাসূলের সুন্নাহ নয়।","রোজা, নামাজ, ঘুম ও বিবাহ—সবকিছুর মধ্যে ভারসাম্য দরকার।","রাসূলুল্লাহর জীবনই আল্লাহভীতির সঠিক নমুনা।","সুন্নাহ থেকে মুখ ফিরিয়ে নিজের বানানো পথ নেওয়া বিপজ্জনক।"],"related_hadiths":[{"id":"32৯4","book_id":"2","label":"Sahih Muslim"},{"id":"1৯61","book_id":"1","label":"Sahih Bukhari"},{"id":"1৯৮1","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইবাদতে মধ্যপন্থা ও সুন্নাহ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের সুন্নাহ হলো ইবাদত, বিশ্রাম, সিয়াম ও বিবাহে ভারসাম্যপূর্ণ পথ; বাড়াবাড়ি নয়।"},"heading":{"title":"ইবাদতে মধ্যপন্থা: রাসূলের সুন্নাহ থেকে মুখ ফিরানো নয়","description":"এই হাদিসে তিনজন ব্যক্তি রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর ইবাদত সম্পর্কে জানতে এসে নিজেদের জন্য কঠোর সিদ্ধান্ত নেয়। একজন বলল, সে সারারাত নামাজ পড়বে; আরেকজন বলল, সবসময় রোজা রাখবে; তৃতীয়জন বলল, কখনো বিয়ে করবে না। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাদের ভুল ঠিক করে দিলেন। তিনি বললেন, তিনি আল্লাহকে বেশি ভয় করেন এবং বেশি পরহেযগার, তবু তিনি রোজা রাখেন আবার ছাড়েন, নামাজ পড়েন আবার ঘুমান, এবং বিবাহ করেছেন। তাই সুন্নাহ মানে অস্বাভাবিক কঠোরতা নয়; বরং আল্লাহর ইবাদত ও মানুষের স্বাভাবিক জীবনের মধ্যে সঠিক ভারসাম্য। এই হাদিস ইবাদতে বাড়াবাড়ি থেকে বাঁচতে শেখায়।"},"teachings":["ইবাদতে অতিরিক্ত বাড়াবাড়ি রাসূলের সুন্নাহ নয়।","রোজা, নামাজ, ঘুম ও বিবাহ—সবকিছুর মধ্যে ভারসাম্য দরকার।","রাসূলুল্লাহর জীবনই আল্লাহভীতির সঠিক নমুনা।","সুন্নাহ থেকে মুখ ফিরিয়ে নিজের বানানো পথ নেওয়া বিপজ্জনক।"],"related_hadiths":[{"id":"3294","book_id":"2","label":"Sahih Muslim"},{"id":"1961","book_id":"1","label":"Sahih Bukhari"},{"id":"1981","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সৎপথে আহ্বান ও গোনাহের দায়","description":"$book_name$ $hadith_number$ - $chapter_name$. সৎপথে ডাকার সওয়াব আছে, আর পথভ্রষ্টতার দিকে ডাকলে অনুসারীদের মতো গোনাহের দায় আসে।"},"heading":{"title":"সৎপথে আহ্বান: দাওয়াতের সওয়াব ও দায়িত্ব","description":"এই হাদিসে দাওয়াতের বড় দায়িত্ব বোঝানো হয়েছে। যে ব্যক্তি কাউকে সৎ পথের দিকে আহ্বান করে, তার জন্য অনুসারীদের মতো সওয়াব থাকে; অথচ অনুসারীদের সওয়াব কমে না। আবার যে পথভ্রষ্টতার দিকে আহ্বান করে, তার ওপর অনুসারীদের মতো গোনাহ থাকে; অথচ তাদের গোনাহও কমে না। তাই কথা, লেখা, শিক্ষা, পোস্ট, পরামর্শ—সবকিছুতেই সতর্ক থাকা দরকার। মানুষকে ভালো কাজে ডাকা শুধু সুন্দর কাজ নয়, এটি দায়িত্বও। একইভাবে ভুল পথ, বিদআত, পাপ বা বিভ্রান্তি ছড়ানো হালকা বিষয় নয়। এই হাদিস আমাদের শেখায়, প্রভাবশালী কথা বলার আগে ভাবতে হবে—এটি মানুষকে আল্লাহর পথে ডাকছে, নাকি ভুল পথে ঠেলে দিচ্ছে?"},"teachings":["সৎপথে আহ্বান করলে অনুসারীদের মতো সওয়াবের অংশ পাওয়া যায়।","ভুল পথে ডাকলে অনুসারীদের মতো গোনাহের দায় আসতে পারে।","দাওয়াত, লেখা ও পরামর্শে সতর্ক থাকা জরুরি।","সওয়াব বা গোনাহ কারও থেকে কমে না; প্রত্যেকের নিজ নিজ হিসাব থাকে।"],"related_hadiths":[{"id":"26৯7","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সৎপথে আহ্বান ও গোনাহের দায়","description":"$book_name$ $hadith_number$ - $chapter_name$. সৎপথে ডাকার সওয়াব আছে, আর পথভ্রষ্টতার দিকে ডাকলে অনুসারীদের মতো গোনাহের দায় আসে।"},"heading":{"title":"সৎপথে আহ্বান: দাওয়াতের সওয়াব ও দায়িত্ব","description":"এই হাদিসে দাওয়াতের বড় দায়িত্ব বোঝানো হয়েছে। যে ব্যক্তি কাউকে সৎ পথের দিকে আহ্বান করে, তার জন্য অনুসারীদের মতো সওয়াব থাকে; অথচ অনুসারীদের সওয়াব কমে না। আবার যে পথভ্রষ্টতার দিকে আহ্বান করে, তার ওপর অনুসারীদের মতো গোনাহ থাকে; অথচ তাদের গোনাহও কমে না। তাই কথা, লেখা, শিক্ষা, পোস্ট, পরামর্শ—সবকিছুতেই সতর্ক থাকা দরকার। মানুষকে ভালো কাজে ডাকা শুধু সুন্দর কাজ নয়, এটি দায়িত্বও। একইভাবে ভুল পথ, বিদআত, পাপ বা বিভ্রান্তি ছড়ানো হালকা বিষয় নয়। এই হাদিস আমাদের শেখায়, প্রভাবশালী কথা বলার আগে ভাবতে হবে—এটি মানুষকে আল্লাহর পথে ডাকছে, নাকি ভুল পথে ঠেলে দিচ্ছে?"},"teachings":["সৎপথে আহ্বান করলে অনুসারীদের মতো সওয়াবের অংশ পাওয়া যায়।","ভুল পথে ডাকলে অনুসারীদের মতো গোনাহের দায় আসতে পারে।","দাওয়াত, লেখা ও পরামর্শে সতর্ক থাকা জরুরি।","সওয়াব বা গোনাহ কারও থেকে কমে না; প্রত্যেকের নিজ নিজ হিসাব থাকে।"],"related_hadiths":[{"id":"2697","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অপরিচিতদের জন্য সুসংবাদ","description":"$book_name$ $hadith_number$ - $chapter_name$. ইসলাম অপরিচিতভাবে শুরু হয়েছে এবং আবার অপরিচিত হবে; সুন্নাহ ঠিক রাখাদের জন্য সুসংবাদ।"},"heading":{"title":"ইসলাম অপরিচিত হবে: সুন্নাহ আঁকড়ে থাকা মানুষের মর্যাদা","description":"এই হাদিসে বলা হয়েছে, ইসলাম মুষ্টিমেয় লোকদের মাধ্যমে শুরু হয়েছে এবং একসময় আবার সেইরকম অপরিচিত অবস্থায় ফিরে আসবে। এরপর সুসংবাদ দেওয়া হয়েছে ‘গুরাবা’ বা সেই মুষ্টিমেয় লোকদের জন্য। তিরমিযীর বর্ণনায় এসেছে, তারা হলো এমন মানুষ, যারা রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর পরে মানুষ সুন্নাহর যে বিষয়গুলো নষ্ট করেছে, সেগুলো সংশোধনের চেষ্টা করে। এখানে শিক্ষা হলো, সত্য পথ অনেক সময় সংখ্যায় কম মানুষের কাছে থাকে। মানুষের ভিড়, প্রচলন বা জনপ্রিয়তা সবসময় সঠিকতার প্রমাণ নয়। মুসলিমের কাজ হলো কুরআন ও সুন্নাহর আলোকে নিজেকে ঠিক রাখা এবং ভদ্রভাবে মানুষকে সঠিক পথে ডাকতে থাকা।"},"teachings":["ইসলাম শুরুতে অপরিচিত ছিল এবং আবার অপরিচিত অবস্থায় ফিরবে।","সুন্নাহ ঠিক রাখার চেষ্টা করা প্রশংসনীয় কাজ।","সংখ্যা বেশি হলেই কোনো পথ সঠিক হয়ে যায় না।","সত্যের পথে থাকলে ধৈর্য ও বিনয় দরকার।"],"related_hadiths":[{"id":"267","book_id":"2","label":"Sahih Muslim"},{"id":"26৮","book_id":"2","label":"Sahih Muslim"},{"id":"2630","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অপরিচিতদের জন্য সুসংবাদ","description":"$book_name$ $hadith_number$ - $chapter_name$. ইসলাম অপরিচিতভাবে শুরু হয়েছে এবং আবার অপরিচিত হবে; সুন্নাহ ঠিক রাখাদের জন্য সুসংবাদ।"},"heading":{"title":"ইসলাম অপরিচিত হবে: সুন্নাহ আঁকড়ে থাকা মানুষের মর্যাদা","description":"এই হাদিসে বলা হয়েছে, ইসলাম মুষ্টিমেয় লোকদের মাধ্যমে শুরু হয়েছে এবং একসময় আবার সেইরকম অপরিচিত অবস্থায় ফিরে আসবে। এরপর সুসংবাদ দেওয়া হয়েছে ‘গুরাবা’ বা সেই মুষ্টিমেয় লোকদের জন্য। তিরমিযীর বর্ণনায় এসেছে, তারা হলো এমন মানুষ, যারা রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর পরে মানুষ সুন্নাহর যে বিষয়গুলো নষ্ট করেছে, সেগুলো সংশোধনের চেষ্টা করে। এখানে শিক্ষা হলো, সত্য পথ অনেক সময় সংখ্যায় কম মানুষের কাছে থাকে। মানুষের ভিড়, প্রচলন বা জনপ্রিয়তা সবসময় সঠিকতার প্রমাণ নয়। মুসলিমের কাজ হলো কুরআন ও সুন্নাহর আলোকে নিজেকে ঠিক রাখা এবং ভদ্রভাবে মানুষকে সঠিক পথে ডাকতে থাকা।"},"teachings":["ইসলাম শুরুতে অপরিচিত ছিল এবং আবার অপরিচিত অবস্থায় ফিরবে।","সুন্নাহ ঠিক রাখার চেষ্টা করা প্রশংসনীয় কাজ।","সংখ্যা বেশি হলেই কোনো পথ সঠিক হয়ে যায় না।","সত্যের পথে থাকলে ধৈর্য ও বিনয় দরকার।"],"related_hadiths":[{"id":"267","book_id":"2","label":"Sahih Muslim"},{"id":"268","book_id":"2","label":"Sahih Muslim"},{"id":"2630","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মতভেদে সুন্নাহ আঁকড়ে ধরা","description":"$book_name$ $hadith_number$ - $chapter_name$. মতভেদ দেখা দিলে রাসূলের সুন্নাহ ও খুলাফায়ে রাশেদীনের পথ শক্তভাবে ধরার উপদেশ দেওয়া হয়েছে।"},"heading":{"title":"মতভেদের সময়ে করণীয়: সুন্নাহকে মাড়ির দাঁত দিয়ে আঁকড়ে ধরা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর একটি গভীর উপদেশ এসেছে। তিনি তাকওয়া অবলম্বন, আমীরের কথা শোনা ও মানার কথা বলেছেন, যদিও তিনি হাবশী গোলাম হন। এরপর জানিয়েছেন, তাঁর পরে যারা বেঁচে থাকবে তারা অনেক মতভেদ দেখবে। সেই সময়ে করণীয় হলো রাসূলের সুন্নাহ এবং সুপথপ্রাপ্ত খুলাফায়ে রাশেদীনের সুন্নাহ শক্তভাবে ধরে রাখা। তিনি আরও সতর্ক করেছেন, দ্বীনের নতুন সৃষ্টি থেকে দূরে থাকতে; কারণ প্রত্যেক নতুন সৃষ্টি বিদআত, আর প্রত্যেক বিদআত পথভ্রষ্টতা। এই হাদিস মুসলিমকে আবেগ নয়, প্রমাণিত সুন্নাহর দিকে ফিরিয়ে দেয়। মতভেদে বিভ্রান্ত না হয়ে তাকওয়া, আনুগত্য ও সুন্নাহ—এই তিনটি বিষয় ধরে রাখা দরকার।"},"teachings":["মতভেদের সময় রাসূলের সুন্নাহ শক্তভাবে আঁকড়ে ধরতে হবে।","খুলাফায়ে রাশেদীনের পথও অনুসরণের গুরুত্বপূর্ণ দিশা।","দ্বীনের নতুন সৃষ্টি থেকে সতর্ক থাকা দরকার।","তাকওয়া ও বৈধ নেতৃত্বের আনুগত্য মুসলিম জীবনে গুরুত্বপূর্ণ।"],"related_hadiths":[{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"},{"id":"26৯7","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মতভেদে সুন্নাহ আঁকড়ে ধরা","description":"$book_name$ $hadith_number$ - $chapter_name$. মতভেদ দেখা দিলে রাসূলের সুন্নাহ ও খুলাফায়ে রাশেদীনের পথ শক্তভাবে ধরার উপদেশ দেওয়া হয়েছে।"},"heading":{"title":"মতভেদের সময়ে করণীয়: সুন্নাহকে মাড়ির দাঁত দিয়ে আঁকড়ে ধরা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর একটি গভীর উপদেশ এসেছে। তিনি তাকওয়া অবলম্বন, আমীরের কথা শোনা ও মানার কথা বলেছেন, যদিও তিনি হাবশী গোলাম হন। এরপর জানিয়েছেন, তাঁর পরে যারা বেঁচে থাকবে তারা অনেক মতভেদ দেখবে। সেই সময়ে করণীয় হলো রাসূলের সুন্নাহ এবং সুপথপ্রাপ্ত খুলাফায়ে রাশেদীনের সুন্নাহ শক্তভাবে ধরে রাখা। তিনি আরও সতর্ক করেছেন, দ্বীনের নতুন সৃষ্টি থেকে দূরে থাকতে; কারণ প্রত্যেক নতুন সৃষ্টি বিদআত, আর প্রত্যেক বিদআত পথভ্রষ্টতা। এই হাদিস মুসলিমকে আবেগ নয়, প্রমাণিত সুন্নাহর দিকে ফিরিয়ে দেয়। মতভেদে বিভ্রান্ত না হয়ে তাকওয়া, আনুগত্য ও সুন্নাহ—এই তিনটি বিষয় ধরে রাখা দরকার।"},"teachings":["মতভেদের সময় রাসূলের সুন্নাহ শক্তভাবে আঁকড়ে ধরতে হবে।","খুলাফায়ে রাশেদীনের পথও অনুসরণের গুরুত্বপূর্ণ দিশা।","দ্বীনের নতুন সৃষ্টি থেকে সতর্ক থাকা দরকার।","তাকওয়া ও বৈধ নেতৃত্বের আনুগত্য মুসলিম জীবনে গুরুত্বপূর্ণ।"],"related_hadiths":[{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"},{"id":"2697","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পরিচ্ছন্ন দ্বীন ও নবীর অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের আনা উজ্জ্বল দ্বীন যথেষ্ট; মূসা জীবিত থাকলেও তাঁকে মুহাম্মাদের অনুসরণ করতে হতো।"},"heading":{"title":"পরিচ্ছন্ন দ্বীন: রাসূলের অনুসরণই মুসলিমের নিরাপদ পথ","description":"এই হাদিসে ওমর (রাঃ) ইহুদীদের কিছু পুরনো ধর্মীয় কাহিনী লিখে রাখার অনুমতি চাইলে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাঁকে সতর্ক করেন। তিনি বলেন, তোমরা কি দিকভ্রান্ত হয়েছ, যেমন ইহুদী-নাছারারা দিকভ্রান্ত হয়েছে? এরপর তিনি জানান, তিনি উজ্জ্বল ও পরিচ্ছন্ন দ্বীন নিয়ে এসেছেন। এমনকি মূসা (আলাইহিস সালাম) যদি তখন জীবিত থাকতেন, তাঁর পক্ষেও মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ ছাড়া পথ থাকত না। এখানে শিক্ষা হলো, মুসলিমের জন্য রাসূলের আনা দ্বীন পূর্ণ ও পরিষ্কার। তাই দ্বীনের দিশা নেওয়ার ক্ষেত্রে অপ্রয়োজনীয়ভাবে অন্য ধর্মীয় কাহিনীর প্রতি আকর্ষণ রাখা ঠিক নয়। মুসলিমের মূল ভরসা কুরআন ও সুন্নাহ।"},"teachings":["রাসূলুল্লাহর আনা দ্বীন উজ্জ্বল ও পরিচ্ছন্ন।","দ্বীনের দিশা নিতে কুরআন ও সুন্নাহ যথেষ্ট পথনির্দেশ।","আগের জাতির দিকভ্রান্ত পথ অনুসরণ থেকে সতর্ক থাকতে হবে।","মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ সব মুসলিমের জন্য মূল পথ।"],"related_hadiths":[{"id":"72৮0","book_id":"1","label":"Sahih Bukhari"},{"id":"72৮1","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পরিচ্ছন্ন দ্বীন ও নবীর অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের আনা উজ্জ্বল দ্বীন যথেষ্ট; মূসা জীবিত থাকলেও তাঁকে মুহাম্মাদের অনুসরণ করতে হতো।"},"heading":{"title":"পরিচ্ছন্ন দ্বীন: রাসূলের অনুসরণই মুসলিমের নিরাপদ পথ","description":"এই হাদিসে ওমর (রাঃ) ইহুদীদের কিছু পুরনো ধর্মীয় কাহিনী লিখে রাখার অনুমতি চাইলে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাঁকে সতর্ক করেন। তিনি বলেন, তোমরা কি দিকভ্রান্ত হয়েছ, যেমন ইহুদী-নাছারারা দিকভ্রান্ত হয়েছে? এরপর তিনি জানান, তিনি উজ্জ্বল ও পরিচ্ছন্ন দ্বীন নিয়ে এসেছেন। এমনকি মূসা (আলাইহিস সালাম) যদি তখন জীবিত থাকতেন, তাঁর পক্ষেও মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ ছাড়া পথ থাকত না। এখানে শিক্ষা হলো, মুসলিমের জন্য রাসূলের আনা দ্বীন পূর্ণ ও পরিষ্কার। তাই দ্বীনের দিশা নেওয়ার ক্ষেত্রে অপ্রয়োজনীয়ভাবে অন্য ধর্মীয় কাহিনীর প্রতি আকর্ষণ রাখা ঠিক নয়। মুসলিমের মূল ভরসা কুরআন ও সুন্নাহ।"},"teachings":["রাসূলুল্লাহর আনা দ্বীন উজ্জ্বল ও পরিচ্ছন্ন।","দ্বীনের দিশা নিতে কুরআন ও সুন্নাহ যথেষ্ট পথনির্দেশ।","আগের জাতির দিকভ্রান্ত পথ অনুসরণ থেকে সতর্ক থাকতে হবে।","মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ সব মুসলিমের জন্য মূল পথ।"],"related_hadiths":[{"id":"7280","book_id":"1","label":"Sahih Bukhari"},{"id":"7281","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুরআন ও সুন্নাহ আঁকড়ে ধরা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর কিতাব ও রাসূলের সুন্নাহ শক্তভাবে ধরলে সঠিক পথে থাকার দিশা পাওয়া যায়।"},"heading":{"title":"কুরআন ও সুন্নাহ: পথভ্রষ্টতা থেকে বাঁচার মূল দিশা","description":"এই বর্ণনায় রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) দুইটি বিষয় আঁকড়ে ধরার কথা বলেছেন—আল্লাহর কিতাব এবং তাঁর রাসূলের সুন্নাত। যতদিন মুসলিমরা এই দুইটি শক্তভাবে ধরে রাখবে, তারা পথভ্রষ্ট হবে না—এটাই হাদিসের মূল শিক্ষা। কুরআন মুসলিমের বিশ্বাস, ইবাদত ও জীবনযাপনের মূল আলো। আর সুন্নাহ দেখায়, কুরআনের নির্দেশ বাস্তবে কীভাবে পালন করতে হয়। তাই শুধু কুরআনের নাম নেওয়া যথেষ্ট নয়, আবার সুন্নাহকে অবহেলা করাও ঠিক নয়। দুইটিকে একসাথে সম্মান ও অনুসরণ করতে হবে। এই হাদিস আমাদের আমলের মানদণ্ড পরিষ্কার করে—যে কথা, কাজ বা রীতি কুরআন ও সুন্নাহর সাথে মেলে, সেটিই নিরাপদ।"},"teachings":["আল্লাহর কিতাব মুসলিমের প্রধান পথনির্দেশ।","রাসূলের সুন্নাহ কুরআন অনুযায়ী চলার বাস্তব পথ দেখায়।","কুরআন ও সুন্নাহ একসাথে আঁকড়ে ধরা দরকার।","দ্বীনের কাজে সঠিক মানদণ্ড হলো কিতাব ও সুন্নাহ।"],"related_hadiths":[{"id":"72৮0","book_id":"1","label":"Sahih Bukhari"},{"id":"72৮1","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুরআন ও সুন্নাহ আঁকড়ে ধরা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর কিতাব ও রাসূলের সুন্নাহ শক্তভাবে ধরলে সঠিক পথে থাকার দিশা পাওয়া যায়।"},"heading":{"title":"কুরআন ও সুন্নাহ: পথভ্রষ্টতা থেকে বাঁচার মূল দিশা","description":"এই বর্ণনায় রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) দুইটি বিষয় আঁকড়ে ধরার কথা বলেছেন—আল্লাহর কিতাব এবং তাঁর রাসূলের সুন্নাত। যতদিন মুসলিমরা এই দুইটি শক্তভাবে ধরে রাখবে, তারা পথভ্রষ্ট হবে না—এটাই হাদিসের মূল শিক্ষা। কুরআন মুসলিমের বিশ্বাস, ইবাদত ও জীবনযাপনের মূল আলো। আর সুন্নাহ দেখায়, কুরআনের নির্দেশ বাস্তবে কীভাবে পালন করতে হয়। তাই শুধু কুরআনের নাম নেওয়া যথেষ্ট নয়, আবার সুন্নাহকে অবহেলা করাও ঠিক নয়। দুইটিকে একসাথে সম্মান ও অনুসরণ করতে হবে। এই হাদিস আমাদের আমলের মানদণ্ড পরিষ্কার করে—যে কথা, কাজ বা রীতি কুরআন ও সুন্নাহর সাথে মেলে, সেটিই নিরাপদ।"},"teachings":["আল্লাহর কিতাব মুসলিমের প্রধান পথনির্দেশ।","রাসূলের সুন্নাহ কুরআন অনুযায়ী চলার বাস্তব পথ দেখায়।","কুরআন ও সুন্নাহ একসাথে আঁকড়ে ধরা দরকার।","দ্বীনের কাজে সঠিক মানদণ্ড হলো কিতাব ও সুন্নাহ।"],"related_hadiths":[{"id":"7280","book_id":"1","label":"Sahih Bukhari"},{"id":"7281","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিদআত করলে সুন্নাহ হারানোর আশঙ্কা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীনে বিদআত চালু হলে সুন্নাহ হারানোর ভয় আছে; তাই প্রমাণিত আমলকে গুরুত্ব দেওয়া জরুরি।"},"heading":{"title":"বিদআত ও সুন্নাহ: নতুন আমলে পুরনো সুন্নাহ হারানোর ভয়","description":"এই বর্ণনায় বলা হয়েছে, কোনো সম্প্রদায় যখন তাদের দ্বীনের মধ্যে বিদআত সৃষ্টি করে, তখন আল্লাহ তাদের মধ্য থেকে সেই পরিমাণ সুন্নাত উঠিয়ে নেন; এরপর তা কিয়ামত পর্যন্ত আর ফিরে আসে না। এই কথার মূল শিক্ষা হলো, বিদআত শুধু একটি বাড়তি কাজ নয়; এটি সুন্নাহর জায়গা দখল করে নিতে পারে। মানুষ যখন নতুন বানানো আমলে ব্যস্ত হয়ে যায়, তখন রাসূলের শেখানো সহজ ও প্রমাণিত আমল অবহেলিত হয়। তাই দ্বীনের নামে নতুন রীতি যোগ করাকে হালকা করে দেখা ঠিক নয়। মুসলিমের জন্য নিরাপদ পথ হলো, প্রমাণিত সুন্নাহ শিখে সেটির ওপর আমল করা। যত বেশি সুন্নাহ জীবিত থাকবে, তত বেশি দ্বীনের আসল সৌন্দর্য মানুষের জীবনে থাকবে।"},"teachings":["বিদআত চালু হলে সুন্নাহ অবহেলিত হওয়ার ভয় থাকে।","দ্বীনের নতুন রীতি সুন্নাহর জায়গা দখল করতে পারে।","প্রমাণিত আমলকে অগ্রাধিকার দেওয়া জরুরি।","সুন্নাহ জীবিত রাখা মুসলিম সমাজের বড় দায়িত্ব।"],"related_hadiths":[{"id":"26৯7","book_id":"1","label":"Sahih Bukhari"},{"id":"43৮5","book_id":"2","label":"Sahih Muslim"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিদআত করলে সুন্নাহ হারানোর আশঙ্কা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীনে বিদআত চালু হলে সুন্নাহ হারানোর ভয় আছে; তাই প্রমাণিত আমলকে গুরুত্ব দেওয়া জরুরি।"},"heading":{"title":"বিদআত ও সুন্নাহ: নতুন আমলে পুরনো সুন্নাহ হারানোর ভয়","description":"এই বর্ণনায় বলা হয়েছে, কোনো সম্প্রদায় যখন তাদের দ্বীনের মধ্যে বিদআত সৃষ্টি করে, তখন আল্লাহ তাদের মধ্য থেকে সেই পরিমাণ সুন্নাত উঠিয়ে নেন; এরপর তা কিয়ামত পর্যন্ত আর ফিরে আসে না। এই কথার মূল শিক্ষা হলো, বিদআত শুধু একটি বাড়তি কাজ নয়; এটি সুন্নাহর জায়গা দখল করে নিতে পারে। মানুষ যখন নতুন বানানো আমলে ব্যস্ত হয়ে যায়, তখন রাসূলের শেখানো সহজ ও প্রমাণিত আমল অবহেলিত হয়। তাই দ্বীনের নামে নতুন রীতি যোগ করাকে হালকা করে দেখা ঠিক নয়। মুসলিমের জন্য নিরাপদ পথ হলো, প্রমাণিত সুন্নাহ শিখে সেটির ওপর আমল করা। যত বেশি সুন্নাহ জীবিত থাকবে, তত বেশি দ্বীনের আসল সৌন্দর্য মানুষের জীবনে থাকবে।"},"teachings":["বিদআত চালু হলে সুন্নাহ অবহেলিত হওয়ার ভয় থাকে।","দ্বীনের নতুন রীতি সুন্নাহর জায়গা দখল করতে পারে।","প্রমাণিত আমলকে অগ্রাধিকার দেওয়া জরুরি।","সুন্নাহ জীবিত রাখা মুসলিম সমাজের বড় দায়িত্ব।"],"related_hadiths":[{"id":"2697","book_id":"1","label":"Sahih Bukhari"},{"id":"4385","book_id":"2","label":"Sahih Muslim"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মূসার অনুসরণ নয়, মুহাম্মাদের অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. নবুঅতের পর মুহাম্মাদকে ছেড়ে অন্য পথ অনুসরণ করলে সরল পথ থেকে বিচ্যুতির সতর্কতা এসেছে।"},"heading":{"title":"মুহাম্মাদের অনুসরণ: সরল পথে থাকার মূল শর্ত","description":"এই বর্ণনায় রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কসম করে বলেছেন, যদি মূসা (আলাইহিস সালাম) মানুষের সামনে উপস্থিত হতেন এবং মানুষ তাঁকে অনুসরণ করে মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে ছেড়ে দিত, তাহলে তারা সরল পথ থেকে বিচ্যুত হতো। তিনি আরও বলেন, মূসা যদি জীবিত থাকতেন এবং তাঁর নবুঅতকাল পেতেন, তাহলে তিনিও তাঁকে অনুসরণ করতেন। এখানে মূল শিক্ষা হলো, শেষ নবী হিসেবে মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ মুসলিমের জন্য অপরিহার্য। অন্য নবীদের প্রতি ঈমান রাখা জরুরি, কিন্তু শরীআতের অনুসরণ হবে শেষ রাসূলের পথে। তাই দ্বীনের বিষয়ে নিরাপদ পথ হলো তাঁর সুন্নাহকে মানা এবং তাঁর নির্দেশকে অগ্রাধিকার দেওয়া।"},"teachings":["শেষ নবীর শরীআত অনুসরণ করা মুসলিমের দায়িত্ব।","মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে ছেড়ে অন্য পথ নেওয়া বিচ্যুতির কারণ।","আগের নবীদের প্রতি ঈমান থাকবে, কিন্তু অনুসরণ হবে শেষ রাসূলের শরীআতের।","সরল পথে থাকতে নবীর সুন্নাহকে অগ্রাধিকার দিতে হবে।"],"related_hadiths":[{"id":"72৮0","book_id":"1","label":"Sahih Bukhari"},{"id":"72৮1","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মূসার অনুসরণ নয়, মুহাম্মাদের অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. নবুঅতের পর মুহাম্মাদকে ছেড়ে অন্য পথ অনুসরণ করলে সরল পথ থেকে বিচ্যুতির সতর্কতা এসেছে।"},"heading":{"title":"মুহাম্মাদের অনুসরণ: সরল পথে থাকার মূল শর্ত","description":"এই বর্ণনায় রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কসম করে বলেছেন, যদি মূসা (আলাইহিস সালাম) মানুষের সামনে উপস্থিত হতেন এবং মানুষ তাঁকে অনুসরণ করে মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে ছেড়ে দিত, তাহলে তারা সরল পথ থেকে বিচ্যুত হতো। তিনি আরও বলেন, মূসা যদি জীবিত থাকতেন এবং তাঁর নবুঅতকাল পেতেন, তাহলে তিনিও তাঁকে অনুসরণ করতেন। এখানে মূল শিক্ষা হলো, শেষ নবী হিসেবে মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ মুসলিমের জন্য অপরিহার্য। অন্য নবীদের প্রতি ঈমান রাখা জরুরি, কিন্তু শরীআতের অনুসরণ হবে শেষ রাসূলের পথে। তাই দ্বীনের বিষয়ে নিরাপদ পথ হলো তাঁর সুন্নাহকে মানা এবং তাঁর নির্দেশকে অগ্রাধিকার দেওয়া।"},"teachings":["শেষ নবীর শরীআত অনুসরণ করা মুসলিমের দায়িত্ব।","মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে ছেড়ে অন্য পথ নেওয়া বিচ্যুতির কারণ।","আগের নবীদের প্রতি ঈমান থাকবে, কিন্তু অনুসরণ হবে শেষ রাসূলের শরীআতের।","সরল পথে থাকতে নবীর সুন্নাহকে অগ্রাধিকার দিতে হবে।"],"related_hadiths":[{"id":"7280","book_id":"1","label":"Sahih Bukhari"},{"id":"7281","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদীনার সম্মান ও প্রতিশ্রুতি রক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদীনার সম্মান, বিদআত থেকে বিরত থাকা ও মুসলমানের প্রতিশ্রুতি রক্ষার কঠোর শিক্ষা এসেছে।"},"heading":{"title":"মদীনার মর্যাদা: বিদআত, আশ্রয় ও প্রতিশ্রুতি ভঙ্গের সতর্কতা","description":"এই দীর্ঘ হাদিসে আলী (রাঃ) একটি লিখিত কাগজের কথা বলেন, যাতে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কয়েকটি গুরুত্বপূর্ণ নির্দেশ ছিল। এর মধ্যে আছে, মদীনা আইর থেকে সওর পর্যন্ত সম্মানার্হ এলাকা। সেখানে কেউ বিদআত সৃষ্টি করলে বা বিদআত সৃষ্টিকারীকে আশ্রয় দিলে তার ওপর কঠোর লা‘নতের কথা এসেছে। আরও বলা হয়েছে, মুসলমানদের প্রতিশ্রুতি এক; তাদের ক্ষুদ্র ব্যক্তিও সেই প্রতিশ্রুতির চেষ্টা করতে পারে। যে মুসলমানের প্রতিশ্রুতি ভঙ্গ করে, তার ব্যাপারেও কঠোর সতর্কতা এসেছে। এই হাদিস মদীনার মর্যাদা, দ্বীনে নতুন কাজের ভয়াবহতা এবং সামাজিক অঙ্গীকার রক্ষার গুরুত্ব একসাথে শেখায়। মুসলিমের কথা, আশ্রয় ও প্রতিশ্রুতি হালকা বিষয় নয়।"},"teachings":["মদীনা সম্মানার্হ এলাকা; সেখানে অন্যায় ও বিদআত থেকে সতর্ক থাকা দরকার।","বিদআতকারীকে আশ্রয় দেওয়া কঠোর সতর্কতার বিষয়।","মুসলমানের প্রতিশ্রুতি রক্ষা করা গুরুত্বপূর্ণ দায়িত্ব।","অন্যায়ভাবে সম্পর্ক বা আনুগত্য বদল করাও নিন্দনীয়।"],"related_hadiths":[{"id":"26৯7","book_id":"1","label":"Sahih Bukhari"},{"id":"43৮5","book_id":"2","label":"Sahih Muslim"},{"id":"6৮৮2","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদীনার সম্মান ও প্রতিশ্রুতি রক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদীনার সম্মান, বিদআত থেকে বিরত থাকা ও মুসলমানের প্রতিশ্রুতি রক্ষার কঠোর শিক্ষা এসেছে।"},"heading":{"title":"মদীনার মর্যাদা: বিদআত, আশ্রয় ও প্রতিশ্রুতি ভঙ্গের সতর্কতা","description":"এই দীর্ঘ হাদিসে আলী (রাঃ) একটি লিখিত কাগজের কথা বলেন, যাতে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কয়েকটি গুরুত্বপূর্ণ নির্দেশ ছিল। এর মধ্যে আছে, মদীনা আইর থেকে সওর পর্যন্ত সম্মানার্হ এলাকা। সেখানে কেউ বিদআত সৃষ্টি করলে বা বিদআত সৃষ্টিকারীকে আশ্রয় দিলে তার ওপর কঠোর লা‘নতের কথা এসেছে। আরও বলা হয়েছে, মুসলমানদের প্রতিশ্রুতি এক; তাদের ক্ষুদ্র ব্যক্তিও সেই প্রতিশ্রুতির চেষ্টা করতে পারে। যে মুসলমানের প্রতিশ্রুতি ভঙ্গ করে, তার ব্যাপারেও কঠোর সতর্কতা এসেছে। এই হাদিস মদীনার মর্যাদা, দ্বীনে নতুন কাজের ভয়াবহতা এবং সামাজিক অঙ্গীকার রক্ষার গুরুত্ব একসাথে শেখায়। মুসলিমের কথা, আশ্রয় ও প্রতিশ্রুতি হালকা বিষয় নয়।"},"teachings":["মদীনা সম্মানার্হ এলাকা; সেখানে অন্যায় ও বিদআত থেকে সতর্ক থাকা দরকার।","বিদআতকারীকে আশ্রয় দেওয়া কঠোর সতর্কতার বিষয়।","মুসলমানের প্রতিশ্রুতি রক্ষা করা গুরুত্বপূর্ণ দায়িত্ব।","অন্যায়ভাবে সম্পর্ক বা আনুগত্য বদল করাও নিন্দনীয়।"],"related_hadiths":[{"id":"2697","book_id":"1","label":"Sahih Bukhari"},{"id":"4385","book_id":"2","label":"Sahih Muslim"},{"id":"6882","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিতাব ও নবীর সুন্নাহর দিশা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর কিতাব ও নবীর সুন্নাহ শক্তভাবে ধরলে পথভ্রষ্টতা থেকে বাঁচার দিশা পাওয়া যায়।"},"heading":{"title":"কিতাব ও নবীর সুন্নাহ: পথভ্রষ্টতা থেকে বাঁচার দিশা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তিনি উম্মতের মাঝে এমন জিনিস রেখে যাচ্ছেন, যা শক্তভাবে ধরলে তারা পথভ্রষ্ট হবে না—আল্লাহর কিতাব এবং তাঁর নবীর সুন্নাত। এখানে মুসলিম জীবনের মূল ভিত্তি স্পষ্ট করা হয়েছে। কুরআন নির্দেশ দেয়, আর সুন্নাহ সেই নির্দেশের বাস্তব রূপ শেখায়। কেউ যদি শুধু নিজের মত, সমাজের প্রচলন বা আবেগকে ধর্মের মানদণ্ড বানায়, তাহলে ভুলের আশঙ্কা থাকে। কিন্তু কিতাব ও সুন্নাহকে মানদণ্ড বানালে পথ পরিষ্কার হয়। এই হাদিস আমাদের শেখায়, মতভেদ, সন্দেহ বা নতুন রীতির ভিড়ে নিরাপদ আশ্রয় হলো আল্লাহর কিতাব ও নবীর প্রমাণিত সুন্নাহ।"},"teachings":["আল্লাহর কিতাব ও নবীর সুন্নাহ মুসলিমের মূল পথনির্দেশ।","পথভ্রষ্টতা থেকে বাঁচতে কিতাব ও সুন্নাহ আঁকড়ে ধরতে হবে।","দ্বীনের মানদণ্ড সমাজের প্রচলন নয়, প্রমাণিত দলিল।","সুন্নাহ ছাড়া কুরআনের বাস্তব আমল বোঝা অসম্পূর্ণ হয়ে যায়।"],"related_hadiths":[{"id":"72৮0","book_id":"1","label":"Sahih Bukhari"},{"id":"72৮1","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিতাব ও নবীর সুন্নাহর দিশা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর কিতাব ও নবীর সুন্নাহ শক্তভাবে ধরলে পথভ্রষ্টতা থেকে বাঁচার দিশা পাওয়া যায়।"},"heading":{"title":"কিতাব ও নবীর সুন্নাহ: পথভ্রষ্টতা থেকে বাঁচার দিশা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তিনি উম্মতের মাঝে এমন জিনিস রেখে যাচ্ছেন, যা শক্তভাবে ধরলে তারা পথভ্রষ্ট হবে না—আল্লাহর কিতাব এবং তাঁর নবীর সুন্নাত। এখানে মুসলিম জীবনের মূল ভিত্তি স্পষ্ট করা হয়েছে। কুরআন নির্দেশ দেয়, আর সুন্নাহ সেই নির্দেশের বাস্তব রূপ শেখায়। কেউ যদি শুধু নিজের মত, সমাজের প্রচলন বা আবেগকে ধর্মের মানদণ্ড বানায়, তাহলে ভুলের আশঙ্কা থাকে। কিন্তু কিতাব ও সুন্নাহকে মানদণ্ড বানালে পথ পরিষ্কার হয়। এই হাদিস আমাদের শেখায়, মতভেদ, সন্দেহ বা নতুন রীতির ভিড়ে নিরাপদ আশ্রয় হলো আল্লাহর কিতাব ও নবীর প্রমাণিত সুন্নাহ।"},"teachings":["আল্লাহর কিতাব ও নবীর সুন্নাহ মুসলিমের মূল পথনির্দেশ।","পথভ্রষ্টতা থেকে বাঁচতে কিতাব ও সুন্নাহ আঁকড়ে ধরতে হবে।","দ্বীনের মানদণ্ড সমাজের প্রচলন নয়, প্রমাণিত দলিল।","সুন্নাহ ছাড়া কুরআনের বাস্তব আমল বোঝা অসম্পূর্ণ হয়ে যায়।"],"related_hadiths":[{"id":"7280","book_id":"1","label":"Sahih Bukhari"},{"id":"7281","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মধ্যম পথে সুন্নাহর আমল","description":"$book_name$ $hadith_number$ - $chapter_name$. বিদআতে বেশি চেষ্টা করার চেয়ে সুন্নাহর ওপর মধ্যমভাবে আমল করাই উত্তম—এটি বড় শিক্ষা।"},"heading":{"title":"সুন্নাহর ওপর মধ্যম আমল: বিদআতে পরিশ্রমের চেয়ে উত্তম","description":"এই বর্ণনায় বলা হয়েছে, শরীআতে নতুন কাজ নিয়ে বেশি পরিশ্রম করার চেয়ে মধ্যম পন্থায় সুন্নাহর ওপর আমল করা অনেক উত্তম। এখানে খুব দরকারি ভারসাম্যের শিক্ষা আছে। অনেক সময় মানুষ নতুন নতুন আমল, বিশেষ নিয়ম বা নিজের বানানো পদ্ধতিতে বেশি উৎসাহী হয়। কিন্তু যদি তা সুন্নাহভিত্তিক না হয়, তাহলে সেই পরিশ্রম নিরাপদ নয়। অন্যদিকে, সুন্নাহর প্রমাণিত আমল ছোট মনে হলেও সেটিই উত্তম পথ। দ্বীনে সফলতা বেশি জটিলতা বানানোর মধ্যে নয়; বরং রাসূলের শেখানো পথে স্থির থাকার মধ্যে। তাই কম হলেও নিয়মিত, খাঁটি এবং সুন্নাহসম্মত আমল করা উচিত। এই শিক্ষা মানুষকে সহজ, পরিষ্কার ও প্রমাণিত দ্বীনের পথে ফিরিয়ে আনে।"},"teachings":["বিদআতে বেশি পরিশ্রম করার চেয়ে সুন্নাহর ওপর কম আমলও উত্তম।","দ্বীনের কাজে প্রমাণিত পথকে অগ্রাধিকার দিতে হবে।","ইবাদতে জটিলতা নয়, সুন্নাহভিত্তিক সরলতা দরকার।","মধ্যম পন্থা মুসলিমকে বাড়াবাড়ি থেকে বাঁচায়।"],"related_hadiths":[{"id":"26৯7","book_id":"1","label":"Sahih Bukhari"},{"id":"43৮5","book_id":"2","label":"Sahih Muslim"},{"id":"5063","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মধ্যম পথে সুন্নাহর আমল","description":"$book_name$ $hadith_number$ - $chapter_name$. বিদআতে বেশি চেষ্টা করার চেয়ে সুন্নাহর ওপর মধ্যমভাবে আমল করাই উত্তম—এটি বড় শিক্ষা।"},"heading":{"title":"সুন্নাহর ওপর মধ্যম আমল: বিদআতে পরিশ্রমের চেয়ে উত্তম","description":"এই বর্ণনায় বলা হয়েছে, শরীআতে নতুন কাজ নিয়ে বেশি পরিশ্রম করার চেয়ে মধ্যম পন্থায় সুন্নাহর ওপর আমল করা অনেক উত্তম। এখানে খুব দরকারি ভারসাম্যের শিক্ষা আছে। অনেক সময় মানুষ নতুন নতুন আমল, বিশেষ নিয়ম বা নিজের বানানো পদ্ধতিতে বেশি উৎসাহী হয়। কিন্তু যদি তা সুন্নাহভিত্তিক না হয়, তাহলে সেই পরিশ্রম নিরাপদ নয়। অন্যদিকে, সুন্নাহর প্রমাণিত আমল ছোট মনে হলেও সেটিই উত্তম পথ। দ্বীনে সফলতা বেশি জটিলতা বানানোর মধ্যে নয়; বরং রাসূলের শেখানো পথে স্থির থাকার মধ্যে। তাই কম হলেও নিয়মিত, খাঁটি এবং সুন্নাহসম্মত আমল করা উচিত। এই শিক্ষা মানুষকে সহজ, পরিষ্কার ও প্রমাণিত দ্বীনের পথে ফিরিয়ে আনে।"},"teachings":["বিদআতে বেশি পরিশ্রম করার চেয়ে সুন্নাহর ওপর কম আমলও উত্তম।","দ্বীনের কাজে প্রমাণিত পথকে অগ্রাধিকার দিতে হবে।","ইবাদতে জটিলতা নয়, সুন্নাহভিত্তিক সরলতা দরকার।","মধ্যম পন্থা মুসলিমকে বাড়াবাড়ি থেকে বাঁচায়।"],"related_hadiths":[{"id":"2697","book_id":"1","label":"Sahih Bukhari"},{"id":"4385","book_id":"2","label":"Sahih Muslim"},{"id":"5063","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত ফেরত ও খিয়ানত না করা","description":"$book_name$ $hadith_number$ - $chapter_name$. যে আমানত রেখেছে তাকে তা বুঝিয়ে দাও, আর কেউ খিয়ানত করলেও তার সঙ্গে খিয়ানত করো না।"},"heading":{"title":"আমানত ফেরত দাও, খিয়ানতের জবাবে খিয়ানত করো না","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব সহজ কিন্তু গভীর একটি নিয়ম শিখিয়েছেন। যে ব্যক্তি তোমার কাছে আমানত রেখেছে, তাকে সময়মতো আমানত বুঝিয়ে দাও। আর যে তোমার সঙ্গে খিয়ানত করে, তার সঙ্গে তুমি খিয়ানত করো না। এখানে আমানতদারি ও নৈতিকতার বড় শিক্ষা আছে। কেউ অন্যায় করলেই তার মতো অন্যায় করা মুসলিমের আচরণ নয়। আমানত ফেরত দেওয়া মানুষের হক। আর খিয়ানতের জবাবে খিয়ানত না করা চরিত্রের শক্তি দেখায়। এই হাদিস ব্যবসা, সম্পর্ক, দায়িত্ব, টাকা-পয়সা, কথা বা কোনো জিনিসের হেফাজত—সব জায়গায় কাজে লাগে। মুসলিমের পরিচয় হলো সে নিজের দায়িত্ব ঠিক রাখে।"},"teachings":["যে আমানত রাখে, তাকে আমানত ফেরত দেওয়া জরুরি।","অন্য কেউ খিয়ানত করলেও নিজে খিয়ানত করা ঠিক নয়।","আমানতদারি মানুষের হক রক্ষার শিক্ষা দেয়।","ভালো চরিত্র অন্যের খারাপ আচরণের ওপর নির্ভর করে না।"],"related_hadiths":[{"id":"3535","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1264","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"2৯34","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত ফেরত ও খিয়ানত না করা","description":"$book_name$ $hadith_number$ - $chapter_name$. যে আমানত রেখেছে তাকে তা বুঝিয়ে দাও, আর কেউ খিয়ানত করলেও তার সঙ্গে খিয়ানত করো না।"},"heading":{"title":"আমানত ফেরত দাও, খিয়ানতের জবাবে খিয়ানত করো না","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব সহজ কিন্তু গভীর একটি নিয়ম শিখিয়েছেন। যে ব্যক্তি তোমার কাছে আমানত রেখেছে, তাকে সময়মতো আমানত বুঝিয়ে দাও। আর যে তোমার সঙ্গে খিয়ানত করে, তার সঙ্গে তুমি খিয়ানত করো না। এখানে আমানতদারি ও নৈতিকতার বড় শিক্ষা আছে। কেউ অন্যায় করলেই তার মতো অন্যায় করা মুসলিমের আচরণ নয়। আমানত ফেরত দেওয়া মানুষের হক। আর খিয়ানতের জবাবে খিয়ানত না করা চরিত্রের শক্তি দেখায়। এই হাদিস ব্যবসা, সম্পর্ক, দায়িত্ব, টাকা-পয়সা, কথা বা কোনো জিনিসের হেফাজত—সব জায়গায় কাজে লাগে। মুসলিমের পরিচয় হলো সে নিজের দায়িত্ব ঠিক রাখে।"},"teachings":["যে আমানত রাখে, তাকে আমানত ফেরত দেওয়া জরুরি।","অন্য কেউ খিয়ানত করলেও নিজে খিয়ানত করা ঠিক নয়।","আমানতদারি মানুষের হক রক্ষার শিক্ষা দেয়।","ভালো চরিত্র অন্যের খারাপ আচরণের ওপর নির্ভর করে না।"],"related_hadiths":[{"id":"3535","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1264","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"2934","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হাজরে আসওয়াদ ও সুন্নাহ অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. হাজরে আসওয়াদ নিজে উপকার-অপকার করতে পারে না; নবীকে করতে দেখে উমর তা চুম্বন করেন।"},"heading":{"title":"হাজরে আসওয়াদ চুম্বন: বিশ্বাস নয়, সুন্নাহ অনুসরণের শিক্ষা","description":"এই হাদিসে ওমর (রাঃ) হাজরে আসওয়াদের কাছে এসে তা চুম্বন করেন এবং বলেন, তিনি জানেন এটি একটি পাথর মাত্র; এটি কারও কল্যাণ বা অকল্যাণ করতে পারে না। এরপর তিনি বলেন, নবী (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে এটি চুম্বন করতে না দেখলে তিনি চুম্বন করতেন না। এই কথায় তাওহীদ ও সুন্নাহ অনুসরণের সুন্দর শিক্ষা আছে। হাজরে আসওয়াদকে সম্মান করা হয় রাসূলের আমল অনুসরণ করে, পাথরকে উপকার-অপকারের মালিক মনে করে নয়। তাই মুসলিমের বিশ্বাস পরিষ্কার হওয়া দরকার—উপকার ও ক্ষতির ক্ষমতা আল্লাহর হাতে। আর ইবাদতের কাজ করা হবে নবীর দেখানো পদ্ধতিতে। আবেগ, কুসংস্কার বা অতিরিক্ত বিশ্বাস এখানে গ্রহণযোগ্য নয়।"},"teachings":["হাজরে আসওয়াদ নিজে উপকার বা অপকার করার ক্ষমতা রাখে না।","উমর (রাঃ) এটি চুম্বন করেছেন নবীর অনুসরণে।","তাওহীদ হলো কল্যাণ-অকল্যাণের মালিক আল্লাহকে মানা।","ইবাদতের কাজে আবেগ নয়, রাসূলের সুন্নাহ অনুসরণ করা দরকার।"],"related_hadiths":[{"id":"2৯57","book_id":"2","label":"Sahih Muslim"},{"id":"2৯5৮","book_id":"2","label":"Sahih Muslim"},{"id":"2৯5৯","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হাজরে আসওয়াদ ও সুন্নাহ অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. হাজরে আসওয়াদ নিজে উপকার-অপকার করতে পারে না; নবীকে করতে দেখে উমর তা চুম্বন করেন।"},"heading":{"title":"হাজরে আসওয়াদ চুম্বন: বিশ্বাস নয়, সুন্নাহ অনুসরণের শিক্ষা","description":"এই হাদিসে ওমর (রাঃ) হাজরে আসওয়াদের কাছে এসে তা চুম্বন করেন এবং বলেন, তিনি জানেন এটি একটি পাথর মাত্র; এটি কারও কল্যাণ বা অকল্যাণ করতে পারে না। এরপর তিনি বলেন, নবী (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে এটি চুম্বন করতে না দেখলে তিনি চুম্বন করতেন না। এই কথায় তাওহীদ ও সুন্নাহ অনুসরণের সুন্দর শিক্ষা আছে। হাজরে আসওয়াদকে সম্মান করা হয় রাসূলের আমল অনুসরণ করে, পাথরকে উপকার-অপকারের মালিক মনে করে নয়। তাই মুসলিমের বিশ্বাস পরিষ্কার হওয়া দরকার—উপকার ও ক্ষতির ক্ষমতা আল্লাহর হাতে। আর ইবাদতের কাজ করা হবে নবীর দেখানো পদ্ধতিতে। আবেগ, কুসংস্কার বা অতিরিক্ত বিশ্বাস এখানে গ্রহণযোগ্য নয়।"},"teachings":["হাজরে আসওয়াদ নিজে উপকার বা অপকার করার ক্ষমতা রাখে না।","উমর (রাঃ) এটি চুম্বন করেছেন নবীর অনুসরণে।","তাওহীদ হলো কল্যাণ-অকল্যাণের মালিক আল্লাহকে মানা।","ইবাদতের কাজে আবেগ নয়, রাসূলের সুন্নাহ অনুসরণ করা দরকার।"],"related_hadiths":[{"id":"2957","book_id":"2","label":"Sahih Muslim"},{"id":"2958","book_id":"2","label":"Sahih Muslim"},{"id":"2959","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অন্যায়ভাবে জমি দখলের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. অর্ধহাত জমি অন্যায়ভাবে দখল করলে কিয়ামতে সাত জমিনের বোঝা তার কাঁধে দেওয়া হবে।"},"heading":{"title":"অন্যায়ভাবে জমি দখল: সাত জমিনের কঠিন সতর্কতা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি অত্যাচার করে অর্ধহাত জমি দখল করে, কিয়ামতের দিন অনুরূপ সাতটি জমিন তার কাঁধে ঝুলিয়ে দেওয়া হবে। এখানে জমি দখল সম্পর্কে খুব কঠোর সতর্কতা এসেছে। অল্প জমি হলেও অন্যায়ভাবে নেওয়া হালকা বিষয় নয়। মানুষের সম্পদ, জমি ও অধিকার রক্ষা করা ইসলামী ন্যায়ের অংশ। এই হাদিস জমির সীমানা, মালিকানা এবং অন্যের হক নিয়ে ভয় দেখায়। অর্ধহাত জমির কথাও এসেছে, তাই ছোট অন্যায়কে ছোট ভেবে নেওয়া ঠিক নয়। কিয়ামতের জবাবদিহি মনে রাখলে অন্যের সম্পদ দখল থেকে মানুষ বাঁচতে পারে।"},"teachings":["অন্যায়ভাবে অল্প জমি দখল করাও ভয়ংকর অপরাধ।","মানুষের জমি ও সম্পদের হক রক্ষা করা দরকার।","কিয়ামতে জমি দখলের কঠিন জবাবদিহি হবে।","ছোট অন্যায়কে হালকা মনে করা উচিত নয়।"],"related_hadiths":[{"id":"2452","book_id":"1","label":"Sahih Bukhari"},{"id":"1610","book_id":"2","label":"Sahih Muslim"},{"id":"2৯3৮","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অন্যায়ভাবে জমি দখলের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. অর্ধহাত জমি অন্যায়ভাবে দখল করলে কিয়ামতে সাত জমিনের বোঝা তার কাঁধে দেওয়া হবে।"},"heading":{"title":"অন্যায়ভাবে জমি দখল: সাত জমিনের কঠিন সতর্কতা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি অত্যাচার করে অর্ধহাত জমি দখল করে, কিয়ামতের দিন অনুরূপ সাতটি জমিন তার কাঁধে ঝুলিয়ে দেওয়া হবে। এখানে জমি দখল সম্পর্কে খুব কঠোর সতর্কতা এসেছে। অল্প জমি হলেও অন্যায়ভাবে নেওয়া হালকা বিষয় নয়। মানুষের সম্পদ, জমি ও অধিকার রক্ষা করা ইসলামী ন্যায়ের অংশ। এই হাদিস জমির সীমানা, মালিকানা এবং অন্যের হক নিয়ে ভয় দেখায়। অর্ধহাত জমির কথাও এসেছে, তাই ছোট অন্যায়কে ছোট ভেবে নেওয়া ঠিক নয়। কিয়ামতের জবাবদিহি মনে রাখলে অন্যের সম্পদ দখল থেকে মানুষ বাঁচতে পারে।"},"teachings":["অন্যায়ভাবে অল্প জমি দখল করাও ভয়ংকর অপরাধ।","মানুষের জমি ও সম্পদের হক রক্ষা করা দরকার।","কিয়ামতে জমি দখলের কঠিন জবাবদিহি হবে।","ছোট অন্যায়কে হালকা মনে করা উচিত নয়।"],"related_hadiths":[{"id":"2452","book_id":"1","label":"Sahih Bukhari"},{"id":"1610","book_id":"2","label":"Sahih Muslim"},{"id":"2938","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সালাত যাকাত ও মুসলমানের কল্যাণ","description":"$book_name$ $hadith_number$ - $chapter_name$. সালাত কায়েম, যাকাত আদায় ও সকল মুসলমানের কল্যাণ কামনার উপর বায়আতের শিক্ষা এই হাদিসে এসেছে।"},"heading":{"title":"সালাত যাকাত ও সকল মুসলমানের কল্যাণ কামনার বায়আত","description":"এই হাদিসে জারীর ইবনু আবদুল্লাহ (রাঃ) বলেন, তিনি রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর সাথে বায়আত করেছেন তিনটি বিষয়ের উপর: সালাত প্রতিষ্ঠা করা, যাকাত প্রদান করা এবং সকল মুসলমানের কল্যাণ কামনা করা। এখানে সালাত, যাকাত ও নসীহত একসঙ্গে এসেছে। এতে বোঝা যায়, ইবাদত শুধু ব্যক্তিগত কাজ নয়; মুসলমানদের জন্য ভালো চাওয়াও দ্বীনের অংশ। সালাত মানুষকে আল্লাহর সঙ্গে যুক্ত করে, যাকাত সম্পদের দায়িত্ব শেখায়, আর মুসলমানের কল্যাণ কামনা সমাজকে সুন্দর করে। এই বায়আত হাদিস আমাদের শেখায়, একজন মুসলিম নিজের ইবাদত ঠিক রাখার পাশাপাশি অন্য মুসলমানের ক্ষতি নয়, বরং কল্যাণ চায়।"},"teachings":["সালাত প্রতিষ্ঠা করা মুসলিম জীবনের গুরুত্বপূর্ণ দায়িত্ব।","যাকাত আদায় সম্পদের হক বুঝে দেওয়ার শিক্ষা দেয়।","সকল মুসলমানের কল্যাণ কামনা দ্বীনের সুন্দর আচরণ।","বায়আত মানে দায়িত্ব মেনে চলার অঙ্গীকার।"],"related_hadiths":[{"id":"57","book_id":"1","label":"Sahih Bukhari"},{"id":"56","book_id":"2","label":"Sahih Muslim"},{"id":"4৯67","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সালাত যাকাত ও মুসলমানের কল্যাণ","description":"$book_name$ $hadith_number$ - $chapter_name$. সালাত কায়েম, যাকাত আদায় ও সকল মুসলমানের কল্যাণ কামনার উপর বায়আতের শিক্ষা এই হাদিসে এসেছে।"},"heading":{"title":"সালাত যাকাত ও সকল মুসলমানের কল্যাণ কামনার বায়আত","description":"এই হাদিসে জারীর ইবনু আবদুল্লাহ (রাঃ) বলেন, তিনি রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর সাথে বায়আত করেছেন তিনটি বিষয়ের উপর: সালাত প্রতিষ্ঠা করা, যাকাত প্রদান করা এবং সকল মুসলমানের কল্যাণ কামনা করা। এখানে সালাত, যাকাত ও নসীহত একসঙ্গে এসেছে। এতে বোঝা যায়, ইবাদত শুধু ব্যক্তিগত কাজ নয়; মুসলমানদের জন্য ভালো চাওয়াও দ্বীনের অংশ। সালাত মানুষকে আল্লাহর সঙ্গে যুক্ত করে, যাকাত সম্পদের দায়িত্ব শেখায়, আর মুসলমানের কল্যাণ কামনা সমাজকে সুন্দর করে। এই বায়আত হাদিস আমাদের শেখায়, একজন মুসলিম নিজের ইবাদত ঠিক রাখার পাশাপাশি অন্য মুসলমানের ক্ষতি নয়, বরং কল্যাণ চায়।"},"teachings":["সালাত প্রতিষ্ঠা করা মুসলিম জীবনের গুরুত্বপূর্ণ দায়িত্ব।","যাকাত আদায় সম্পদের হক বুঝে দেওয়ার শিক্ষা দেয়।","সকল মুসলমানের কল্যাণ কামনা দ্বীনের সুন্দর আচরণ।","বায়আত মানে দায়িত্ব মেনে চলার অঙ্গীকার।"],"related_hadiths":[{"id":"57","book_id":"1","label":"Sahih Bukhari"},{"id":"56","book_id":"2","label":"Sahih Muslim"},{"id":"4967","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অনধিকার জমি নেওয়ার শাস্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. অনধিকারে কারও জমি নিলে কিয়ামতের দিন তাকে সাত তবক জমিন পর্যন্ত ধসিয়ে দেওয়ার সতর্কতা এসেছে।"},"heading":{"title":"অনধিকার জমি নেওয়ার পরিণতি ও হক রক্ষার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি অনধিকারে কারও কিছু জমি নেয়, কিয়ামতের দিন তাকে সাত তবক জমিন পর্যন্ত ধসিয়ে দেওয়া হবে। এই হাদিস জমি দখল, অন্যের হক নেওয়া এবং যুলুমের বিরুদ্ধে কঠোর সতর্কতা দেয়। জমি ছোট হোক বা বড়—অধিকার ছাড়া নেওয়া বৈধ নয়। মানুষের সম্পদে হাত দেওয়ার আগে মনে রাখতে হবে, আখেরাতে এর হিসাব আছে। এই হাদিস আমাদের জমির সীমানা, দলিল, মালিকানা ও ন্যায্য অধিকার বিষয়ে সতর্ক করে। অন্যের হক বাঁচিয়ে চলা শুধু সামাজিক নিয়ম নয়; এটি আখেরাতের জবাবদিহির সঙ্গেও জড়িত।"},"teachings":["অনধিকারে জমি নেওয়া যুলুমের মধ্যে পড়ে।","কিয়ামতে জমি দখলের কঠিন পরিণতির কথা এসেছে।","অন্যের সম্পদ ও জমির অধিকার মানা জরুরি।","ন্যায্য হক ছাড়া কিছু নেওয়া থেকে বিরত থাকা দরকার।"],"related_hadiths":[{"id":"2454","book_id":"1","label":"Sahih Bukhari"},{"id":"2৯5৮","book_id":"14","label":"Mishkat al-Masabih"},{"id":"1610","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অনধিকার জমি নেওয়ার শাস্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. অনধিকারে কারও জমি নিলে কিয়ামতের দিন তাকে সাত তবক জমিন পর্যন্ত ধসিয়ে দেওয়ার সতর্কতা এসেছে।"},"heading":{"title":"অনধিকার জমি নেওয়ার পরিণতি ও হক রক্ষার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি অনধিকারে কারও কিছু জমি নেয়, কিয়ামতের দিন তাকে সাত তবক জমিন পর্যন্ত ধসিয়ে দেওয়া হবে। এই হাদিস জমি দখল, অন্যের হক নেওয়া এবং যুলুমের বিরুদ্ধে কঠোর সতর্কতা দেয়। জমি ছোট হোক বা বড়—অধিকার ছাড়া নেওয়া বৈধ নয়। মানুষের সম্পদে হাত দেওয়ার আগে মনে রাখতে হবে, আখেরাতে এর হিসাব আছে। এই হাদিস আমাদের জমির সীমানা, দলিল, মালিকানা ও ন্যায্য অধিকার বিষয়ে সতর্ক করে। অন্যের হক বাঁচিয়ে চলা শুধু সামাজিক নিয়ম নয়; এটি আখেরাতের জবাবদিহির সঙ্গেও জড়িত।"},"teachings":["অনধিকারে জমি নেওয়া যুলুমের মধ্যে পড়ে।","কিয়ামতে জমি দখলের কঠিন পরিণতির কথা এসেছে।","অন্যের সম্পদ ও জমির অধিকার মানা জরুরি।","ন্যায্য হক ছাড়া কিছু নেওয়া থেকে বিরত থাকা দরকার।"],"related_hadiths":[{"id":"2454","book_id":"1","label":"Sahih Bukhari"},{"id":"2958","book_id":"14","label":"Mishkat al-Masabih"},{"id":"1610","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নম্রতা ও কোমলতার কল্যাণ","description":"$book_name$ $hadith_number$ - $chapter_name$. কোমলতা থেকে বঞ্চিত হলে মানুষ অনেক কল্যাণ হারায়; এই হাদিসে সুন্দর আচরণ ও নরম ব্যবহারের গুরুত্ব বোঝানো হয়েছে।"},"heading":{"title":"নম্রতা ও কোমলতা: কল্যাণ পাওয়ার বড় শিক্ষা","description":"এই হাদিসের মূল কথা খুব সরল: কোমলতা ও নম্রতা মানুষের জীবনে কল্যাণের দরজা খুলে দেয়। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যাকে কোমলতা থেকে বঞ্চিত করা হয়, তাকে কল্যাণ থেকেও বঞ্চিত করা হয়। এখানে নম্রতা মানে দুর্বলতা নয়; বরং কথা, আচরণ ও ব্যবহারকে নরম রাখা। পরিবারে, কাজে বা মানুষের সঙ্গে মেলামেশায় রুক্ষ কথা অনেক সময় সম্পর্ক নষ্ট করে। আর কোমল ব্যবহার মানুষকে কাছে আনে। তাই এই হাদিস আমাদের শেখায়, ভালো মুসলিম চরিত্র গড়তে নরম ভাষা, ধৈর্য আর সুন্দর আচরণ জরুরি। হাদিসে কল্যাণের কথা এসেছে, তাই আমরা বলতে পারি—নম্রতা মানুষকে ভালো গুণের দিকে নিয়ে যায়। তাই নিজের ভাষা ও আচরণে কোমলতা আছে কি না, তা নিয়মিত খেয়াল করা এই হাদিসের খুব বাস্তব প্রয়োগ।"},"teachings":["কথা ও আচরণে কোমলতা রাখা কল্যাণের কারণ।","রুক্ষ স্বভাব মানুষকে ভালো দিক থেকে দূরে নিতে পারে।","নম্র ব্যবহার পরিবার ও সমাজে সম্পর্ক সুন্দর করে।","কোমলতা দুর্বলতা নয়; এটি ভালো চরিত্রের অংশ।"],"related_hadiths":[{"id":"506৮","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নম্রতা ও কোমলতার কল্যাণ","description":"$book_name$ $hadith_number$ - $chapter_name$. কোমলতা থেকে বঞ্চিত হলে মানুষ অনেক কল্যাণ হারায়; এই হাদিসে সুন্দর আচরণ ও নরম ব্যবহারের গুরুত্ব বোঝানো হয়েছে।"},"heading":{"title":"নম্রতা ও কোমলতা: কল্যাণ পাওয়ার বড় শিক্ষা","description":"এই হাদিসের মূল কথা খুব সরল: কোমলতা ও নম্রতা মানুষের জীবনে কল্যাণের দরজা খুলে দেয়। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যাকে কোমলতা থেকে বঞ্চিত করা হয়, তাকে কল্যাণ থেকেও বঞ্চিত করা হয়। এখানে নম্রতা মানে দুর্বলতা নয়; বরং কথা, আচরণ ও ব্যবহারকে নরম রাখা। পরিবারে, কাজে বা মানুষের সঙ্গে মেলামেশায় রুক্ষ কথা অনেক সময় সম্পর্ক নষ্ট করে। আর কোমল ব্যবহার মানুষকে কাছে আনে। তাই এই হাদিস আমাদের শেখায়, ভালো মুসলিম চরিত্র গড়তে নরম ভাষা, ধৈর্য আর সুন্দর আচরণ জরুরি। হাদিসে কল্যাণের কথা এসেছে, তাই আমরা বলতে পারি—নম্রতা মানুষকে ভালো গুণের দিকে নিয়ে যায়। তাই নিজের ভাষা ও আচরণে কোমলতা আছে কি না, তা নিয়মিত খেয়াল করা এই হাদিসের খুব বাস্তব প্রয়োগ।"},"teachings":["কথা ও আচরণে কোমলতা রাখা কল্যাণের কারণ।","রুক্ষ স্বভাব মানুষকে ভালো দিক থেকে দূরে নিতে পারে।","নম্র ব্যবহার পরিবার ও সমাজে সম্পর্ক সুন্দর করে।","কোমলতা দুর্বলতা নয়; এটি ভালো চরিত্রের অংশ।"],"related_hadiths":[{"id":"5068","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জমি দখল হারাম ও কিয়ামতের দায়","description":"$book_name$ $hadith_number$ - $chapter_name$. অন্যায়ভাবে সামান্য জমি দখলও কিয়ামতে কঠিন দায়ের কারণ হবে; তাই জমি ও হকের ব্যাপারে সতর্ক থাকার শিক্ষা।"},"heading":{"title":"জমি দখল হারাম: অন্যের হক নিলে কিয়ামতে দায় আছে","description":"এই হাদিসের মূল শিক্ষা হলো, অন্যের জমি দখল করা শুধু সামাজিক অন্যায় নয়, আখিরাতের বড় দায়ও। এখানে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কেউ অন্যায়ভাবে কারো এক বিগত জমি দখল করলে তাকে কিয়ামতের দিন সেই জমির কারণে কঠিন অবস্থার মুখোমুখি হতে হবে। তাই জমি দখল হারাম—এই বিষয়টি খুব পরিষ্কারভাবে বোঝা যায়। অনেক সময় মানুষ জমির সীমানা, দলিল, উত্তরাধিকার বা ক্ষমতার জোরে সামান্য অংশকে ছোট ব্যাপার মনে করে। কিন্তু হাদিসটি শেখায়, অন্যের হক সামান্য হলেও তা হালকা নয়। মুসলিমের জন্য জরুরি হলো জমি, সম্পদ ও অধিকার নিয়ে ইনসাফ করা এবং কাউকে যুলুম না করা।"},"teachings":["অন্যের জমির সামান্য অংশও অন্যায়ভাবে নেওয়া বড় দায়ের কারণ।","জমি ও সম্পদের ব্যাপারে যুলুম থেকে বেঁচে থাকা জরুরি।","মানুষের হক নষ্ট করলে কিয়ামতের দিন জবাবদিহি করতে হবে।","সীমানা, দলিল ও মালিকানার বিষয়ে সততা রাখা ঈমানি আচরণের অংশ।"],"related_hadiths":[{"id":"2453","book_id":"1","label":"Sahih Bukhari"},{"id":"402৮","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জমি দখল হারাম ও কিয়ামতের দায়","description":"$book_name$ $hadith_number$ - $chapter_name$. অন্যায়ভাবে সামান্য জমি দখলও কিয়ামতে কঠিন দায়ের কারণ হবে; তাই জমি ও হকের ব্যাপারে সতর্ক থাকার শিক্ষা।"},"heading":{"title":"জমি দখল হারাম: অন্যের হক নিলে কিয়ামতে দায় আছে","description":"এই হাদিসের মূল শিক্ষা হলো, অন্যের জমি দখল করা শুধু সামাজিক অন্যায় নয়, আখিরাতের বড় দায়ও। এখানে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কেউ অন্যায়ভাবে কারো এক বিগত জমি দখল করলে তাকে কিয়ামতের দিন সেই জমির কারণে কঠিন অবস্থার মুখোমুখি হতে হবে। তাই জমি দখল হারাম—এই বিষয়টি খুব পরিষ্কারভাবে বোঝা যায়। অনেক সময় মানুষ জমির সীমানা, দলিল, উত্তরাধিকার বা ক্ষমতার জোরে সামান্য অংশকে ছোট ব্যাপার মনে করে। কিন্তু হাদিসটি শেখায়, অন্যের হক সামান্য হলেও তা হালকা নয়। মুসলিমের জন্য জরুরি হলো জমি, সম্পদ ও অধিকার নিয়ে ইনসাফ করা এবং কাউকে যুলুম না করা।"},"teachings":["অন্যের জমির সামান্য অংশও অন্যায়ভাবে নেওয়া বড় দায়ের কারণ।","জমি ও সম্পদের ব্যাপারে যুলুম থেকে বেঁচে থাকা জরুরি।","মানুষের হক নষ্ট করলে কিয়ামতের দিন জবাবদিহি করতে হবে।","সীমানা, দলিল ও মালিকানার বিষয়ে সততা রাখা ঈমানি আচরণের অংশ।"],"related_hadiths":[{"id":"2453","book_id":"1","label":"Sahih Bukhari"},{"id":"4028","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পবিত্র অন্তর ও সত্যভাষীর মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. উত্তম মানুষের পরিচয় হলো সত্য কথা বলা ও অন্তরকে পাপ, যুলুম, খিয়ানত ও হিংসা থেকে পরিষ্কার রাখা।"},"heading":{"title":"পবিত্র অন্তর ও সত্যভাষী: উত্তম মানুষের সহজ পরিচয়","description":"এই হাদিসে মানুষের উত্তম হওয়ার একটি সহজ কিন্তু গভীর মানদণ্ড বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে জিজ্ঞেস করা হলে তিনি বলেন, নিষ্কলুষ অন্তঃকরণ ও সত্যভাষী মানুষ উত্তম। এখানে পবিত্র অন্তর বলতে শুধু নরম মন বোঝানো হয়নি। হাদিসের ভাষায় এমন অন্তর, যেখানে পাপ নেই, যুলুম নেই, খিয়ানত নেই এবং হিংসা-বিদ্বেষ নেই। তাই পবিত্র অন্তর হাদিস আমাদের নিজের ভেতর দেখার শিক্ষা দেয়। আমরা মুখে সত্য বলি কি না, মানুষের প্রতি হিংসা রাখি কি না, কারো হক নষ্ট করি কি না—এসব বিষয় নিজের জীবনেই যাচাই করতে হবে। সত্যভাষী হওয়া এবং অন্তর পরিষ্কার রাখা একসঙ্গে চলা উচিত।"},"teachings":["উত্তম মানুষের বড় গুণ হলো সত্য কথা বলা।","অন্তরকে পাপ, যুলুম ও খিয়ানত থেকে পরিষ্কার রাখা দরকার।","হিংসা-বিদ্বেষ থেকে মুক্ত থাকা পবিত্র অন্তরের লক্ষণ।","বাহ্যিক ভালো আচরণের সঙ্গে ভেতরের সততাও জরুরি।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯3","book_id":"8","label":"Riyadus Salihin"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পবিত্র অন্তর ও সত্যভাষীর মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. উত্তম মানুষের পরিচয় হলো সত্য কথা বলা ও অন্তরকে পাপ, যুলুম, খিয়ানত ও হিংসা থেকে পরিষ্কার রাখা।"},"heading":{"title":"পবিত্র অন্তর ও সত্যভাষী: উত্তম মানুষের সহজ পরিচয়","description":"এই হাদিসে মানুষের উত্তম হওয়ার একটি সহজ কিন্তু গভীর মানদণ্ড বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে জিজ্ঞেস করা হলে তিনি বলেন, নিষ্কলুষ অন্তঃকরণ ও সত্যভাষী মানুষ উত্তম। এখানে পবিত্র অন্তর বলতে শুধু নরম মন বোঝানো হয়নি। হাদিসের ভাষায় এমন অন্তর, যেখানে পাপ নেই, যুলুম নেই, খিয়ানত নেই এবং হিংসা-বিদ্বেষ নেই। তাই পবিত্র অন্তর হাদিস আমাদের নিজের ভেতর দেখার শিক্ষা দেয়। আমরা মুখে সত্য বলি কি না, মানুষের প্রতি হিংসা রাখি কি না, কারো হক নষ্ট করি কি না—এসব বিষয় নিজের জীবনেই যাচাই করতে হবে। সত্যভাষী হওয়া এবং অন্তর পরিষ্কার রাখা একসঙ্গে চলা উচিত।"},"teachings":["উত্তম মানুষের বড় গুণ হলো সত্য কথা বলা।","অন্তরকে পাপ, যুলুম ও খিয়ানত থেকে পরিষ্কার রাখা দরকার।","হিংসা-বিদ্বেষ থেকে মুক্ত থাকা পবিত্র অন্তরের লক্ষণ।","বাহ্যিক ভালো আচরণের সঙ্গে ভেতরের সততাও জরুরি।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"593","book_id":"8","label":"Riyadus Salihin"}]}</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিশুদের প্রতি স্নেহ-মমতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুদের চুম্বন ও আদর নিয়ে এই হাদিস দেখায়, অন্তরে স্নেহ-মমতা থাকা আল্লাহর বড় দান।"},"heading":{"title":"শিশুদের প্রতি স্নেহ-মমতা: আদর, দয়া ও কোমল হৃদয়ের হাদিস","description":"এই হাদিসের মূল বিষয় শিশুদের প্রতি স্নেহ-মমতা। এক বেদুঈন সাহাবীদের শিশুদের চুমু দিতে দেখে বলল, তারা শিশুদের চুম্বন করে না। তখন রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বললেন, আল্লাহ যদি তার অন্তর থেকে রহমত তুলে নেন, তবে তিনি তা বাধা দিতে পারবেন কি? এই কথায় বোঝা যায়, শিশুকে আদর করা দুর্বলতা নয়; বরং অন্তরের দয়া ও কোমলতার লক্ষণ। শিশুদের প্রতি স্নেহ, চুম্বন ও ভালোবাসা দেখানো ইসলামী আদবের সঙ্গে মিলে যায়। প্রধান কীওয়ার্ড হলো শিশুদের প্রতি স্নেহ-মমতা, আর সম্পর্কিত কীওয়ার্ড হলো শিশুকে আদর করা, সন্তানকে চুমু দেওয়া, দয়ার হাদিস, কোমল হৃদয়। হাদিসটি আমাদের শেখায়, ঘরের ছোটদের সঙ্গে রুক্ষ আচরণ নয়, ভালোবাসা ও মমতা থাকা উচিত।"},"teachings":["শিশুকে আদর করা ও ভালোবাসা দেখানো সুন্দর আচরণ।","অন্তরে রহমত থাকা আল্লাহর দান—এটি হারিয়ে যাওয়া ভয়ংকর ক্ষতি।","শিশুদের সঙ্গে কঠোরতার বদলে কোমল আচরণ করা উচিত।"],"related_hadiths":[{"id":"5৯৯7","book_id":"1","label":"Sahih Bukhari"},{"id":"6013","book_id":"1","label":"Sahih Bukhari"},{"id":"600৮","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিশুদের প্রতি স্নেহ-মমতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুদের চুম্বন ও আদর নিয়ে এই হাদিস দেখায়, অন্তরে স্নেহ-মমতা থাকা আল্লাহর বড় দান।"},"heading":{"title":"শিশুদের প্রতি স্নেহ-মমতা: আদর, দয়া ও কোমল হৃদয়ের হাদিস","description":"এই হাদিসের মূল বিষয় শিশুদের প্রতি স্নেহ-মমতা। এক বেদুঈন সাহাবীদের শিশুদের চুমু দিতে দেখে বলল, তারা শিশুদের চুম্বন করে না। তখন রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বললেন, আল্লাহ যদি তার অন্তর থেকে রহমত তুলে নেন, তবে তিনি তা বাধা দিতে পারবেন কি? এই কথায় বোঝা যায়, শিশুকে আদর করা দুর্বলতা নয়; বরং অন্তরের দয়া ও কোমলতার লক্ষণ। শিশুদের প্রতি স্নেহ, চুম্বন ও ভালোবাসা দেখানো ইসলামী আদবের সঙ্গে মিলে যায়। প্রধান কীওয়ার্ড হলো শিশুদের প্রতি স্নেহ-মমতা, আর সম্পর্কিত কীওয়ার্ড হলো শিশুকে আদর করা, সন্তানকে চুমু দেওয়া, দয়ার হাদিস, কোমল হৃদয়। হাদিসটি আমাদের শেখায়, ঘরের ছোটদের সঙ্গে রুক্ষ আচরণ নয়, ভালোবাসা ও মমতা থাকা উচিত।"},"teachings":["শিশুকে আদর করা ও ভালোবাসা দেখানো সুন্দর আচরণ।","অন্তরে রহমত থাকা আল্লাহর দান—এটি হারিয়ে যাওয়া ভয়ংকর ক্ষতি।","শিশুদের সঙ্গে কঠোরতার বদলে কোমল আচরণ করা উচিত।"],"related_hadiths":[{"id":"5997","book_id":"1","label":"Sahih Bukhari"},{"id":"6013","book_id":"1","label":"Sahih Bukhari"},{"id":"6008","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দুই কন্যা লালন-পালনের ফজিলত","description":"$book_name$ $hadith_number$ - $chapter_name$. দুই কন্যাকে পূর্ণ বয়স্কা হওয়া পর্যন্ত লালন করলে কিয়ামতে নবীর নৈকট্যের আশা জাগে।"},"heading":{"title":"দুই কন্যার লালন-পালন: নবীর নৈকট্য লাভের আশাব্যঞ্জক হাদিস","description":"এই হাদিসের মূল বিষয় দুই কন্যার লালন-পালন। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি দুই কন্যাকে পূর্ণ বয়স্কা হওয়া পর্যন্ত লালন-পালন করবে, কিয়ামতের দিন সে তাঁর সঙ্গে এভাবে আসবে। এরপর তিনি নিজের আঙ্গুল একত্র করে দেখিয়েছেন। হাদিসটি কন্যা সন্তানের মর্যাদা ও তাদের দায়িত্বশীলভাবে বড় করার গুরুত্ব তুলে ধরে। এখানে প্রধান কীওয়ার্ড হলো দুই কন্যা লালন-পালনের হাদিস। সম্পর্কিত কীওয়ার্ড: কন্যা সন্তানের ফজিলত, মেয়েদের লালন-পালন, কন্যার মর্যাদা, ইসলামে সন্তান প্রতিপালন। হাদিসের শিক্ষা হলো, কন্যাদের যত্ন, নিরাপত্তা, খাবার, শিক্ষা ও বড় হওয়া পর্যন্ত অভিভাবকত্ব একটি মূল্যবান দায়িত্ব। তবে ব্যাখ্যায় আমরা শুধু হাদিসে থাকা কথাটুকুই ধরে বলি—এই কাজ কিয়ামতের দিনে রাসূলের নৈকট্যের কারণ হতে পারে।"},"teachings":["দুই কন্যাকে বড় হওয়া পর্যন্ত দায়িত্ব নিয়ে লালন-পালন করা প্রশংসনীয়।","কন্যা সন্তানকে অবহেলা নয়, যত্ন ও ভালো আচরণ দেওয়া দরকার।","কন্যাদের দায়িত্ব পালন কিয়ামতের দিনে নবীর নৈকট্যের কারণ হতে পারে।"],"related_hadiths":[{"id":"5৯৯5","book_id":"1","label":"Sahih Bukhari"},{"id":"5304","book_id":"1","label":"Sahih Bukhari"},{"id":"6005","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দুই কন্যা লালন-পালনের ফজিলত","description":"$book_name$ $hadith_number$ - $chapter_name$. দুই কন্যাকে পূর্ণ বয়স্কা হওয়া পর্যন্ত লালন করলে কিয়ামতে নবীর নৈকট্যের আশা জাগে।"},"heading":{"title":"দুই কন্যার লালন-পালন: নবীর নৈকট্য লাভের আশাব্যঞ্জক হাদিস","description":"এই হাদিসের মূল বিষয় দুই কন্যার লালন-পালন। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি দুই কন্যাকে পূর্ণ বয়স্কা হওয়া পর্যন্ত লালন-পালন করবে, কিয়ামতের দিন সে তাঁর সঙ্গে এভাবে আসবে। এরপর তিনি নিজের আঙ্গুল একত্র করে দেখিয়েছেন। হাদিসটি কন্যা সন্তানের মর্যাদা ও তাদের দায়িত্বশীলভাবে বড় করার গুরুত্ব তুলে ধরে। এখানে প্রধান কীওয়ার্ড হলো দুই কন্যা লালন-পালনের হাদিস। সম্পর্কিত কীওয়ার্ড: কন্যা সন্তানের ফজিলত, মেয়েদের লালন-পালন, কন্যার মর্যাদা, ইসলামে সন্তান প্রতিপালন। হাদিসের শিক্ষা হলো, কন্যাদের যত্ন, নিরাপত্তা, খাবার, শিক্ষা ও বড় হওয়া পর্যন্ত অভিভাবকত্ব একটি মূল্যবান দায়িত্ব। তবে ব্যাখ্যায় আমরা শুধু হাদিসে থাকা কথাটুকুই ধরে বলি—এই কাজ কিয়ামতের দিনে রাসূলের নৈকট্যের কারণ হতে পারে।"},"teachings":["দুই কন্যাকে বড় হওয়া পর্যন্ত দায়িত্ব নিয়ে লালন-পালন করা প্রশংসনীয়।","কন্যা সন্তানকে অবহেলা নয়, যত্ন ও ভালো আচরণ দেওয়া দরকার।","কন্যাদের দায়িত্ব পালন কিয়ামতের দিনে নবীর নৈকট্যের কারণ হতে পারে।"],"related_hadiths":[{"id":"5995","book_id":"1","label":"Sahih Bukhari"},{"id":"5304","book_id":"1","label":"Sahih Bukhari"},{"id":"6005","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইয়াতীম পালনকারীর মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইয়াতীম পালনকারীর জান্নাতে নবীর নৈকট্যের কথা এসেছে; এটি অসহায় শিশুর যত্নের বড় শিক্ষা।"},"heading":{"title":"ইয়াতীম পালনকারীর মর্যাদা: জান্নাতে নবীর নৈকট্যের হাদিস","description":"এই হাদিসের মূল বিষয় ইয়াতীম পালন। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তিনি ও ইয়াতীম পালনকারী জান্নাতে এভাবে থাকবেন। তারপর তিনি তর্জনী ও মধ্যমা আঙ্গুলের মাঝে সামান্য ফাঁক রেখে ইশারা করেছেন। হাদিসটি ইয়াতীম শিশুর প্রতি দায়িত্ব, দয়া ও যত্নের বড় মর্যাদা বুঝায়। এখানে প্রধান কীওয়ার্ড হলো ইয়াতীম পালনকারীর মর্যাদা। সম্পর্কিত কীওয়ার্ড: ইয়াতীমের হক, এতিমের যত্ন, ইয়াতীমকে সাহায্য, জান্নাতে নবীর সান্নিধ্য, অসহায় শিশুর লালন-পালন। হাদিসটি আমাদের মনে করায়, যে শিশুর সহায় দরকার, তাকে আশ্রয় ও যত্ন দেওয়া শুধু সামাজিক কাজ নয়; এটি বড় নেকির দরজা। তবে ইয়াতীমের সম্পদ বা অধিকার নিয়ে অতিরিক্ত আলোচনা এই হাদিসে নেই, তাই এখানে মূল শিক্ষা শুধু পালন ও যত্নের মর্যাদায় সীমিত রাখা হয়েছে।"},"teachings":["ইয়াতীম শিশুর দায়িত্ব নেওয়া জান্নাতে নবীর নৈকট্যের কারণ হতে পারে।","অসহায় শিশুর প্রতি দয়া, যত্ন ও নিরাপত্তা দেওয়া গুরুত্বপূর্ণ।","ইয়াতীম পালন শুধু দান নয়; এটি দীর্ঘমেয়াদি দায়িত্ব ও মমতার কাজ।"],"related_hadiths":[{"id":"6006","book_id":"1","label":"Sahih Bukhari"},{"id":"1432","book_id":"1","label":"Sahih Bukhari"},{"id":"600৮","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইয়াতীম পালনকারীর মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইয়াতীম পালনকারীর জান্নাতে নবীর নৈকট্যের কথা এসেছে; এটি অসহায় শিশুর যত্নের বড় শিক্ষা।"},"heading":{"title":"ইয়াতীম পালনকারীর মর্যাদা: জান্নাতে নবীর নৈকট্যের হাদিস","description":"এই হাদিসের মূল বিষয় ইয়াতীম পালন। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তিনি ও ইয়াতীম পালনকারী জান্নাতে এভাবে থাকবেন। তারপর তিনি তর্জনী ও মধ্যমা আঙ্গুলের মাঝে সামান্য ফাঁক রেখে ইশারা করেছেন। হাদিসটি ইয়াতীম শিশুর প্রতি দায়িত্ব, দয়া ও যত্নের বড় মর্যাদা বুঝায়। এখানে প্রধান কীওয়ার্ড হলো ইয়াতীম পালনকারীর মর্যাদা। সম্পর্কিত কীওয়ার্ড: ইয়াতীমের হক, এতিমের যত্ন, ইয়াতীমকে সাহায্য, জান্নাতে নবীর সান্নিধ্য, অসহায় শিশুর লালন-পালন। হাদিসটি আমাদের মনে করায়, যে শিশুর সহায় দরকার, তাকে আশ্রয় ও যত্ন দেওয়া শুধু সামাজিক কাজ নয়; এটি বড় নেকির দরজা। তবে ইয়াতীমের সম্পদ বা অধিকার নিয়ে অতিরিক্ত আলোচনা এই হাদিসে নেই, তাই এখানে মূল শিক্ষা শুধু পালন ও যত্নের মর্যাদায় সীমিত রাখা হয়েছে।"},"teachings":["ইয়াতীম শিশুর দায়িত্ব নেওয়া জান্নাতে নবীর নৈকট্যের কারণ হতে পারে।","অসহায় শিশুর প্রতি দয়া, যত্ন ও নিরাপত্তা দেওয়া গুরুত্বপূর্ণ।","ইয়াতীম পালন শুধু দান নয়; এটি দীর্ঘমেয়াদি দায়িত্ব ও মমতার কাজ।"],"related_hadiths":[{"id":"6006","book_id":"1","label":"Sahih Bukhari"},{"id":"1432","book_id":"1","label":"Sahih Bukhari"},{"id":"6008","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত, সত্যবাদিতা ও ভালো চরিত্র","description":"$book_name$ $hadith_number$ - $chapter_name$. আমানত রক্ষা, সত্য কথা, ভালো চরিত্র ও খাদ্যে সতর্কতা—এই চার গুণ মানুষের জীবনকে সঠিক পথে রাখে।"},"heading":{"title":"আমানত রক্ষা ও সত্য কথা: জীবনের চারটি মূল্যবান গুণ","description":"এই হাদিসে চারটি গুণের কথা এসেছে, যা একজন মুমিনের জীবনকে সুন্দর করে। আমানত রক্ষা করা, সত্য কথা বলা, উত্তম চরিত্র রাখা এবং খানা-পিনাতে সতর্ক থাকা—এসব বিষয় শুধু ইবাদতের বাইরে আলাদা কিছু নয়; বরং দৈনন্দিন জীবনের বড় পরীক্ষা। আমানত রক্ষা মানে কারো দেওয়া দায়িত্ব, সম্পদ বা বিশ্বাস নষ্ট না করা। সত্য কথা বলা মানে সুবিধা-অসুবিধা দেখে কথা বদলে না ফেলা। উত্তম চরিত্র মানে মানুষের সঙ্গে সুন্দর আচরণ করা। আর খানা-পিনাতে সতর্কতা মানে খাবার ও উপার্জনের উৎস নিয়ে সাবধান থাকা। হাদিসটি দুনিয়ার ক্ষতি নিয়ে হতাশ না হয়ে চরিত্র ও সততার দিকে মন দিতে শেখায়।"},"teachings":["আমানত রক্ষা করা মুমিনের গুরুত্বপূর্ণ গুণ।","সত্য কথা বলা চরিত্রের ভিত্তি মজবুত করে।","খানা-পিনার বিষয়ে সতর্কতা জীবনকে হালাল পথে রাখে।","ভালো চরিত্র মানুষের সঙ্গে আচরণে প্রকাশ পায়।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"205৯","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত, সত্যবাদিতা ও ভালো চরিত্র","description":"$book_name$ $hadith_number$ - $chapter_name$. আমানত রক্ষা, সত্য কথা, ভালো চরিত্র ও খাদ্যে সতর্কতা—এই চার গুণ মানুষের জীবনকে সঠিক পথে রাখে।"},"heading":{"title":"আমানত রক্ষা ও সত্য কথা: জীবনের চারটি মূল্যবান গুণ","description":"এই হাদিসে চারটি গুণের কথা এসেছে, যা একজন মুমিনের জীবনকে সুন্দর করে। আমানত রক্ষা করা, সত্য কথা বলা, উত্তম চরিত্র রাখা এবং খানা-পিনাতে সতর্ক থাকা—এসব বিষয় শুধু ইবাদতের বাইরে আলাদা কিছু নয়; বরং দৈনন্দিন জীবনের বড় পরীক্ষা। আমানত রক্ষা মানে কারো দেওয়া দায়িত্ব, সম্পদ বা বিশ্বাস নষ্ট না করা। সত্য কথা বলা মানে সুবিধা-অসুবিধা দেখে কথা বদলে না ফেলা। উত্তম চরিত্র মানে মানুষের সঙ্গে সুন্দর আচরণ করা। আর খানা-পিনাতে সতর্কতা মানে খাবার ও উপার্জনের উৎস নিয়ে সাবধান থাকা। হাদিসটি দুনিয়ার ক্ষতি নিয়ে হতাশ না হয়ে চরিত্র ও সততার দিকে মন দিতে শেখায়।"},"teachings":["আমানত রক্ষা করা মুমিনের গুরুত্বপূর্ণ গুণ।","সত্য কথা বলা চরিত্রের ভিত্তি মজবুত করে।","খানা-পিনার বিষয়ে সতর্কতা জীবনকে হালাল পথে রাখে।","ভালো চরিত্র মানুষের সঙ্গে আচরণে প্রকাশ পায়।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"2059","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অভাবীর জন্য সুপারিশ","description":"$book_name$ $hadith_number$ - $chapter_name$. অভাবী বা প্রয়োজনমন্দের জন্য সুপারিশ করলে নেকি হতে পারে; চূড়ান্ত ফায়সালা আল্লাহর ইচ্ছায় হয়।"},"heading":{"title":"অভাবীর জন্য সুপারিশ: সাহায্যের দরজা খুলে দেওয়ার হাদিস","description":"এই হাদিসের মূল বিষয় অভাবীর জন্য সুপারিশ। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর কাছে কোনো ভিক্ষুক বা প্রয়োজনমন্দ এলে তিনি সাহাবীদের বলতেন, তোমরা সুপারিশ কর, এতে তোমাদের নেকি দেওয়া হবে। আর আল্লাহ তাঁর রাসূলের মুখ দিয়ে যে ফয়সালা চান তা জারি করবেন। হাদিসটি দেখায়, সরাসরি সাহায্য করতে না পারলেও ভালো সুপারিশ, পরিচয় করিয়ে দেওয়া বা প্রয়োজনের কথা পৌঁছে দেওয়া নেকির কাজ হতে পারে। প্রধান কীওয়ার্ড হলো অভাবীর জন্য সুপারিশ। সম্পর্কিত কীওয়ার্ড: দরিদ্রকে সাহায্য, নেক সুপারিশ, প্রয়োজনমন্দের সহায়তা, ইসলামে সুপারিশ। হাদিসে একই সঙ্গে ভারসাম্যও আছে—সুপারিশ করা মানুষের কাজ, কিন্তু ফল আল্লাহর ইচ্ছা অনুযায়ী হয়। তাই সাহায্যের চেষ্টা করতে হবে, তবে ফল নিয়ে অহংকার বা চাপ সৃষ্টি করা ঠিক নয়।"},"teachings":["অভাবী মানুষের প্রয়োজনে ভালো সুপারিশ করা নেকির কারণ হতে পারে।","সরাসরি দিতে না পারলেও সাহায্যের দরজা খুলে দেওয়া যায়।","মানুষ চেষ্টা করবে, আর চূড়ান্ত ফল আল্লাহর ইচ্ছার উপর ছেড়ে দেবে।"],"related_hadiths":[{"id":"6006","book_id":"1","label":"Sahih Bukhari"},{"id":"6005","book_id":"1","label":"Sahih Bukhari"},{"id":"601৯","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অভাবীর জন্য সুপারিশ","description":"$book_name$ $hadith_number$ - $chapter_name$. অভাবী বা প্রয়োজনমন্দের জন্য সুপারিশ করলে নেকি হতে পারে; চূড়ান্ত ফায়সালা আল্লাহর ইচ্ছায় হয়।"},"heading":{"title":"অভাবীর জন্য সুপারিশ: সাহায্যের দরজা খুলে দেওয়ার হাদিস","description":"এই হাদিসের মূল বিষয় অভাবীর জন্য সুপারিশ। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর কাছে কোনো ভিক্ষুক বা প্রয়োজনমন্দ এলে তিনি সাহাবীদের বলতেন, তোমরা সুপারিশ কর, এতে তোমাদের নেকি দেওয়া হবে। আর আল্লাহ তাঁর রাসূলের মুখ দিয়ে যে ফয়সালা চান তা জারি করবেন। হাদিসটি দেখায়, সরাসরি সাহায্য করতে না পারলেও ভালো সুপারিশ, পরিচয় করিয়ে দেওয়া বা প্রয়োজনের কথা পৌঁছে দেওয়া নেকির কাজ হতে পারে। প্রধান কীওয়ার্ড হলো অভাবীর জন্য সুপারিশ। সম্পর্কিত কীওয়ার্ড: দরিদ্রকে সাহায্য, নেক সুপারিশ, প্রয়োজনমন্দের সহায়তা, ইসলামে সুপারিশ। হাদিসে একই সঙ্গে ভারসাম্যও আছে—সুপারিশ করা মানুষের কাজ, কিন্তু ফল আল্লাহর ইচ্ছা অনুযায়ী হয়। তাই সাহায্যের চেষ্টা করতে হবে, তবে ফল নিয়ে অহংকার বা চাপ সৃষ্টি করা ঠিক নয়।"},"teachings":["অভাবী মানুষের প্রয়োজনে ভালো সুপারিশ করা নেকির কারণ হতে পারে।","সরাসরি দিতে না পারলেও সাহায্যের দরজা খুলে দেওয়া যায়।","মানুষ চেষ্টা করবে, আর চূড়ান্ত ফল আল্লাহর ইচ্ছার উপর ছেড়ে দেবে।"],"related_hadiths":[{"id":"6006","book_id":"1","label":"Sahih Bukhari"},{"id":"6005","book_id":"1","label":"Sahih Bukhari"},{"id":"6019","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সম্পদে সততা ও বরকতের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. সম্পদ আকর্ষণীয় হলেও ন্যায্যভাবে অর্জন করলে তাতে বরকত হয়; অন্যায় তসরূপ আখিরাতের ক্ষতির কারণ।"},"heading":{"title":"হালাল সম্পদে বরকত: আল্লাহর সম্পদে অন্যায় তসরূপ নয়","description":"এই হাদিসে সম্পদের আকর্ষণ ও তার পরীক্ষার কথা বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, পার্থিব সম্পদ শ্যামল ও সুমিষ্ট, অর্থাৎ মানুষকে টানে। কিন্তু সম্পদ তখনই কল্যাণের কারণ হয়, যখন তা ন্যায়ভাবে পাওয়া যায়। হালাল সম্পদে বরকত—এই শিক্ষা এখানেই স্পষ্ট। আবার যারা আল্লাহ ও তাঁর রাসূলের সম্পদে নিজের ইচ্ছামতো তসরূপ করে, তাদের জন্য কিয়ামতের দিন কঠিন পরিণামের কথা এসেছে। তাই সম্পদ বেশি হওয়াই মূল কথা নয়; বরং তা কীভাবে পাওয়া হলো এবং কীভাবে ব্যবহার করা হলো, সেটাই বড় বিষয়। বিশেষ করে দায়িত্বে থাকা মাল, গনীমত বা জনস্বার্থের সম্পদে সততা রাখা খুব জরুরি।"},"teachings":["সম্পদ আকর্ষণীয় হলেও তা পরীক্ষা হতে পারে।","ন্যায়ভাবে পাওয়া সম্পদে বরকতের কথা এসেছে।","আল্লাহ ও রাসূলের সম্পদে অন্যায় তসরূপ গুরুতর অপরাধ।","সম্পদের উৎস ও ব্যবহার—দুই দিকেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"311৮","book_id":"1","label":"Sahih Bukhari"},{"id":"3073","book_id":"1","label":"Sahih Bukhari"},{"id":"210","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সম্পদে সততা ও বরকতের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. সম্পদ আকর্ষণীয় হলেও ন্যায্যভাবে অর্জন করলে তাতে বরকত হয়; অন্যায় তসরূপ আখিরাতের ক্ষতির কারণ।"},"heading":{"title":"হালাল সম্পদে বরকত: আল্লাহর সম্পদে অন্যায় তসরূপ নয়","description":"এই হাদিসে সম্পদের আকর্ষণ ও তার পরীক্ষার কথা বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, পার্থিব সম্পদ শ্যামল ও সুমিষ্ট, অর্থাৎ মানুষকে টানে। কিন্তু সম্পদ তখনই কল্যাণের কারণ হয়, যখন তা ন্যায়ভাবে পাওয়া যায়। হালাল সম্পদে বরকত—এই শিক্ষা এখানেই স্পষ্ট। আবার যারা আল্লাহ ও তাঁর রাসূলের সম্পদে নিজের ইচ্ছামতো তসরূপ করে, তাদের জন্য কিয়ামতের দিন কঠিন পরিণামের কথা এসেছে। তাই সম্পদ বেশি হওয়াই মূল কথা নয়; বরং তা কীভাবে পাওয়া হলো এবং কীভাবে ব্যবহার করা হলো, সেটাই বড় বিষয়। বিশেষ করে দায়িত্বে থাকা মাল, গনীমত বা জনস্বার্থের সম্পদে সততা রাখা খুব জরুরি।"},"teachings":["সম্পদ আকর্ষণীয় হলেও তা পরীক্ষা হতে পারে।","ন্যায়ভাবে পাওয়া সম্পদে বরকতের কথা এসেছে।","আল্লাহ ও রাসূলের সম্পদে অন্যায় তসরূপ গুরুতর অপরাধ।","সম্পদের উৎস ও ব্যবহার—দুই দিকেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"3118","book_id":"1","label":"Sahih Bukhari"},{"id":"3073","book_id":"1","label":"Sahih Bukhari"},{"id":"210","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সামান্য আত্মসাতের বড় পরিণাম","description":"$book_name$ $hadith_number$ - $chapter_name$. গনীমত বণ্টনের আগে নেওয়া ছোট চাদরও আগুনের কারণ বলা হয়েছে; আত্মসাৎ ছোট মনে করা উচিত নয়।"},"heading":{"title":"সামান্য আত্মসাৎও ভয়াবহ: গনীমতের মাল নিয়ে সতর্ক হোন","description":"এই হাদিসে মিদআম নামে এক ব্যক্তির ঘটনা এসেছে। তিনি মারা গেলে সাহাবীগণ তার জন্য জান্নাতের কথা বলেছিলেন। কিন্তু রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) জানালেন, খায়বারের গনীমত বণ্টনের আগে নেওয়া একটি চাদর তার জন্য আগুনের কারণ হচ্ছে। এটি শুনে একজন লোক জুতার ফিতা বা দু’টি ফিতা নিয়ে এলো। তখনও রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সেটির ব্যাপারে আগুনের কথা বললেন। এই হাদিসের মূল শিক্ষা হলো, আত্মসাৎ ছোট মনে করা যাবে না। গনীমতের মাল হোক বা অন্য কোনো আমানত—বণ্টন বা অনুমতি ছাড়া নেওয়া বড় দায়। বাহ্যিকভাবে ভালো অবস্থায় মৃত্যু হলেও মানুষের গোপন কাজের হিসাব আল্লাহর কাছে থাকবে।"},"teachings":["গনীমত বণ্টনের আগে কিছু নেওয়া আত্মসাতের মধ্যে পড়ে।","সামান্য বস্তু হলেও আত্মসাৎকে ছোট মনে করা ঠিক নয়।","মানুষের বাহ্যিক ধারণা সব সময় আসল অবস্থা জানায় না।","অমানত ও গনীমতের মাল ফেরত দিতে দেরি করা বিপজ্জনক।"],"related_hadiths":[{"id":"3073","book_id":"1","label":"Sahih Bukhari"},{"id":"3074","book_id":"1","label":"Sahih Bukhari"},{"id":"311৮","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সামান্য আত্মসাতের বড় পরিণাম","description":"$book_name$ $hadith_number$ - $chapter_name$. গনীমত বণ্টনের আগে নেওয়া ছোট চাদরও আগুনের কারণ বলা হয়েছে; আত্মসাৎ ছোট মনে করা উচিত নয়।"},"heading":{"title":"সামান্য আত্মসাৎও ভয়াবহ: গনীমতের মাল নিয়ে সতর্ক হোন","description":"এই হাদিসে মিদআম নামে এক ব্যক্তির ঘটনা এসেছে। তিনি মারা গেলে সাহাবীগণ তার জন্য জান্নাতের কথা বলেছিলেন। কিন্তু রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) জানালেন, খায়বারের গনীমত বণ্টনের আগে নেওয়া একটি চাদর তার জন্য আগুনের কারণ হচ্ছে। এটি শুনে একজন লোক জুতার ফিতা বা দু’টি ফিতা নিয়ে এলো। তখনও রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সেটির ব্যাপারে আগুনের কথা বললেন। এই হাদিসের মূল শিক্ষা হলো, আত্মসাৎ ছোট মনে করা যাবে না। গনীমতের মাল হোক বা অন্য কোনো আমানত—বণ্টন বা অনুমতি ছাড়া নেওয়া বড় দায়। বাহ্যিকভাবে ভালো অবস্থায় মৃত্যু হলেও মানুষের গোপন কাজের হিসাব আল্লাহর কাছে থাকবে।"},"teachings":["গনীমত বণ্টনের আগে কিছু নেওয়া আত্মসাতের মধ্যে পড়ে।","সামান্য বস্তু হলেও আত্মসাৎকে ছোট মনে করা ঠিক নয়।","মানুষের বাহ্যিক ধারণা সব সময় আসল অবস্থা জানায় না।","অমানত ও গনীমতের মাল ফেরত দিতে দেরি করা বিপজ্জনক।"],"related_hadiths":[{"id":"3073","book_id":"1","label":"Sahih Bukhari"},{"id":"3074","book_id":"1","label":"Sahih Bukhari"},{"id":"3118","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দায়িত্বের মাল আত্মসাৎ থেকে ভয়","description":"$book_name$ $hadith_number$ - $chapter_name$. দায়িত্বে থাকা ব্যক্তির চাদর আত্মসাৎ তার পরিণামকে ভয়াবহ করেছে; আমানতের মাল গোপন করা বড় অপরাধ।"},"heading":{"title":"দায়িত্বের মাল আত্মসাৎ: কারকারার ঘটনা থেকে সতর্ক শিক্ষা","description":"এই হাদিসে এমন এক ব্যক্তির কথা এসেছে, যে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর গনীমতের মালের দায়িত্বে ছিল। তার নাম ছিল কারকারা। সে মারা গেলে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাকে জাহান্নামী বলে জানান। পরে সাহাবীগণ গিয়ে দেখলেন, সে একটি চাদর আত্মসাৎ করেছিল। হাদিসটি দায়িত্বের মাল আত্মসাৎ সম্পর্কে কঠিন সতর্কতা দেয়। কেউ যদি কোনো সম্পদের পাহারাদার, দায়িত্বশীল বা ব্যবস্থাপক হয়, তাহলে তার দায়িত্ব আরও বড়। কারণ সে নিজের জন্য নয়, আমানতের জন্য কাজ করছে। একটি চাদরকে ছোট মনে করা হলেও হাদিসে তার পরিণাম কঠিনভাবে এসেছে। তাই সরকারি, সামাজিক, পারিবারিক বা যে কোনো দায়িত্বের মাল নিজের করে নেওয়া থেকে বেঁচে থাকা দরকার।"},"teachings":["দায়িত্বে থাকা মাল নিজের জন্য নেওয়া খিয়ানত।","আত্মসাৎ করা বস্তু ছোট হলেও এর দায় বড় হতে পারে।","দায়িত্বশীল ব্যক্তির আমানতদারি আরও বেশি জরুরি।","গোপনভাবে নেওয়া জিনিস আল্লাহর কাছে গোপন থাকে না।"],"related_hadiths":[{"id":"210","book_id":"2","label":"Sahih Muslim"},{"id":"3073","book_id":"1","label":"Sahih Bukhari"},{"id":"311৮","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দায়িত্বের মাল আত্মসাৎ থেকে ভয়","description":"$book_name$ $hadith_number$ - $chapter_name$. দায়িত্বে থাকা ব্যক্তির চাদর আত্মসাৎ তার পরিণামকে ভয়াবহ করেছে; আমানতের মাল গোপন করা বড় অপরাধ।"},"heading":{"title":"দায়িত্বের মাল আত্মসাৎ: কারকারার ঘটনা থেকে সতর্ক শিক্ষা","description":"এই হাদিসে এমন এক ব্যক্তির কথা এসেছে, যে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর গনীমতের মালের দায়িত্বে ছিল। তার নাম ছিল কারকারা। সে মারা গেলে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাকে জাহান্নামী বলে জানান। পরে সাহাবীগণ গিয়ে দেখলেন, সে একটি চাদর আত্মসাৎ করেছিল। হাদিসটি দায়িত্বের মাল আত্মসাৎ সম্পর্কে কঠিন সতর্কতা দেয়। কেউ যদি কোনো সম্পদের পাহারাদার, দায়িত্বশীল বা ব্যবস্থাপক হয়, তাহলে তার দায়িত্ব আরও বড়। কারণ সে নিজের জন্য নয়, আমানতের জন্য কাজ করছে। একটি চাদরকে ছোট মনে করা হলেও হাদিসে তার পরিণাম কঠিনভাবে এসেছে। তাই সরকারি, সামাজিক, পারিবারিক বা যে কোনো দায়িত্বের মাল নিজের করে নেওয়া থেকে বেঁচে থাকা দরকার।"},"teachings":["দায়িত্বে থাকা মাল নিজের জন্য নেওয়া খিয়ানত।","আত্মসাৎ করা বস্তু ছোট হলেও এর দায় বড় হতে পারে।","দায়িত্বশীল ব্যক্তির আমানতদারি আরও বেশি জরুরি।","গোপনভাবে নেওয়া জিনিস আল্লাহর কাছে গোপন থাকে না।"],"related_hadiths":[{"id":"210","book_id":"2","label":"Sahih Muslim"},{"id":"3073","book_id":"1","label":"Sahih Bukhari"},{"id":"3118","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল রিজিক ও দোয়া কবুলের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য, পানীয়, পোশাক ও জীবিকা হারাম হলে দোয়া কবুলের পথে বাধা তৈরি হয়; পবিত্র রিজিক জরুরি।"},"heading":{"title":"হালাল রিজিক ও দোয়া কবুল: খাদ্য-পোশাকে পবিত্রতা কেন জরুরি","description":"এই হাদিসে হালাল রিজিকের গুরুত্ব খুব সুন্দরভাবে বোঝানো হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ পবিত্র এবং তিনি পবিত্র ছাড়া গ্রহণ করেন না। এরপর এমন এক ব্যক্তির কথা এসেছে, যে সফরে ক্লান্ত, ধুলামলিন, দু’হাত তুলে কাতরভাবে দোয়া করছে। বাহ্যিকভাবে দোয়ার অনেক কারণ আছে। কিন্তু তার খাদ্য হারাম, পানীয় হারাম, পোশাক হারাম এবং জীবিকা হারাম। তাই বলা হয়েছে, তার দোয়া কীভাবে কবুল হবে? হালাল রিজিক হাদিস আমাদের শেখায়, দোয়া শুধু মুখের শব্দ নয়; জীবনের উপার্জন, খাবার ও পোশাকের সঙ্গেও এর সম্পর্ক আছে। তাই ইবাদতের সঙ্গে হালাল উপার্জনকে গুরুত্ব দেওয়া দরকার।"},"teachings":["আল্লাহ পবিত্র, তাই পবিত্র বস্তু গ্রহণ করেন।","হারাম খাদ্য, পানীয় ও পোশাক দোয়া কবুলের পথে বাধা হতে পারে।","দোয়ার সঙ্গে জীবিকার পবিত্রতার সম্পর্ক আছে।","হালাল উপার্জন ইবাদতের জীবনে গুরুত্বপূর্ণ অংশ।"],"related_hadiths":[{"id":"205৯","book_id":"1","label":"Sahih Bukhari"},{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"1205","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল রিজিক ও দোয়া কবুলের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য, পানীয়, পোশাক ও জীবিকা হারাম হলে দোয়া কবুলের পথে বাধা তৈরি হয়; পবিত্র রিজিক জরুরি।"},"heading":{"title":"হালাল রিজিক ও দোয়া কবুল: খাদ্য-পোশাকে পবিত্রতা কেন জরুরি","description":"এই হাদিসে হালাল রিজিকের গুরুত্ব খুব সুন্দরভাবে বোঝানো হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ পবিত্র এবং তিনি পবিত্র ছাড়া গ্রহণ করেন না। এরপর এমন এক ব্যক্তির কথা এসেছে, যে সফরে ক্লান্ত, ধুলামলিন, দু’হাত তুলে কাতরভাবে দোয়া করছে। বাহ্যিকভাবে দোয়ার অনেক কারণ আছে। কিন্তু তার খাদ্য হারাম, পানীয় হারাম, পোশাক হারাম এবং জীবিকা হারাম। তাই বলা হয়েছে, তার দোয়া কীভাবে কবুল হবে? হালাল রিজিক হাদিস আমাদের শেখায়, দোয়া শুধু মুখের শব্দ নয়; জীবনের উপার্জন, খাবার ও পোশাকের সঙ্গেও এর সম্পর্ক আছে। তাই ইবাদতের সঙ্গে হালাল উপার্জনকে গুরুত্ব দেওয়া দরকার।"},"teachings":["আল্লাহ পবিত্র, তাই পবিত্র বস্তু গ্রহণ করেন।","হারাম খাদ্য, পানীয় ও পোশাক দোয়া কবুলের পথে বাধা হতে পারে।","দোয়ার সঙ্গে জীবিকার পবিত্রতার সম্পর্ক আছে।","হালাল উপার্জন ইবাদতের জীবনে গুরুত্বপূর্ণ অংশ।"],"related_hadiths":[{"id":"2059","book_id":"1","label":"Sahih Bukhari"},{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"1205","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম খাদ্যের ভয়াবহ পরিণাম","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম খাদ্যে লালিত শরীরের পরিণাম কঠিন বলা হয়েছে; তাই খাবার ও উপার্জনে হালাল পথ জরুরি।"},"heading":{"title":"হারাম খাদ্য থেকে বাঁচুন: শরীর ও রিজিকের পবিত্রতা","description":"এই হাদিসে খুব সংক্ষিপ্ত ভাষায় বড় একটি সতর্কতা এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, হারাম খাদ্য দ্বারা পরিপুষ্ট শরীর জান্নাতে যাবে না। তাই হারাম খাদ্য হাদিস আমাদের শুধু খাবারের নাম নয়, খাবারের উৎস নিয়েও ভাবতে শেখায়। যে খাবার আমরা খাই, সেটি কীভাবে কেনা হলো, আয়টি বৈধ ছিল কি না, অন্যের হক মিশে আছে কি না—এসব বিষয় গুরুত্বপূর্ণ। শরীর খাবার দিয়ে গড়ে ওঠে, আর মুমিনের জীবন ইবাদত ও আনুগত্যের জন্য। তাই হারাম খাদ্যকে হালকা মনে করা ঠিক নয়। এই হাদিসের শিক্ষা হলো, নিজের ও পরিবারের খাবারের ব্যাপারে সতর্ক থাকা এবং হালাল রিজিকের চেষ্টা করা।"},"teachings":["হারাম খাদ্যে শরীর গড়ে ওঠা ভয়াবহ সতর্কতার বিষয়।","খাবারের সঙ্গে উপার্জনের উৎসও দেখা দরকার।","পরিবারের খাবার হালাল কি না তা অভিভাবকের দায়িত্বের অংশ।","হালাল রিজিকের চেষ্টা করা ঈমানি জীবনের গুরুত্বপূর্ণ কাজ।"],"related_hadiths":[{"id":"2236","book_id":"2","label":"Sahih Muslim"},{"id":"205৯","book_id":"1","label":"Sahih Bukhari"},{"id":"52","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম খাদ্যের ভয়াবহ পরিণাম","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম খাদ্যে লালিত শরীরের পরিণাম কঠিন বলা হয়েছে; তাই খাবার ও উপার্জনে হালাল পথ জরুরি।"},"heading":{"title":"হারাম খাদ্য থেকে বাঁচুন: শরীর ও রিজিকের পবিত্রতা","description":"এই হাদিসে খুব সংক্ষিপ্ত ভাষায় বড় একটি সতর্কতা এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, হারাম খাদ্য দ্বারা পরিপুষ্ট শরীর জান্নাতে যাবে না। তাই হারাম খাদ্য হাদিস আমাদের শুধু খাবারের নাম নয়, খাবারের উৎস নিয়েও ভাবতে শেখায়। যে খাবার আমরা খাই, সেটি কীভাবে কেনা হলো, আয়টি বৈধ ছিল কি না, অন্যের হক মিশে আছে কি না—এসব বিষয় গুরুত্বপূর্ণ। শরীর খাবার দিয়ে গড়ে ওঠে, আর মুমিনের জীবন ইবাদত ও আনুগত্যের জন্য। তাই হারাম খাদ্যকে হালকা মনে করা ঠিক নয়। এই হাদিসের শিক্ষা হলো, নিজের ও পরিবারের খাবারের ব্যাপারে সতর্ক থাকা এবং হালাল রিজিকের চেষ্টা করা।"},"teachings":["হারাম খাদ্যে শরীর গড়ে ওঠা ভয়াবহ সতর্কতার বিষয়।","খাবারের সঙ্গে উপার্জনের উৎসও দেখা দরকার।","পরিবারের খাবার হালাল কি না তা অভিভাবকের দায়িত্বের অংশ।","হালাল রিজিকের চেষ্টা করা ঈমানি জীবনের গুরুত্বপূর্ণ কাজ।"],"related_hadiths":[{"id":"2236","book_id":"2","label":"Sahih Muslim"},{"id":"2059","book_id":"1","label":"Sahih Bukhari"},{"id":"52","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল-হারাম ও সন্দেহজনক বিষয়","description":"$book_name$ $hadith_number$ - $chapter_name$. হালাল-হারাম স্পষ্ট; সন্দেহজনক বিষয় থেকে বাঁচলে দ্বীন ও মর্যাদা রক্ষা হয়, আর অন্তর ঠিক থাকলে শরীর ঠিক থাকে।"},"heading":{"title":"হালাল হারাম স্পষ্ট: সন্দেহজনক বিষয় থেকে বাঁচার শিক্ষা","description":"এই হাদিস ইসলামী জীবনের একটি মৌলিক নীতি শেখায়। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, হালাল স্পষ্ট এবং হারামও স্পষ্ট। মাঝখানে কিছু সন্দেহজনক বিষয় আছে, যা অনেক মানুষ জানে না। যে ব্যক্তি সন্দেহজনক বিষয় থেকে বেঁচে থাকে, সে তার দ্বীন ও মর্যাদা রক্ষা করে। আর যে সন্দেহজনক বিষয়ে পড়ে, সে হারামের কাছাকাছি চলে যায়। রাখালের উদাহরণ দিয়ে বোঝানো হয়েছে, নিষিদ্ধ সীমার ধারে থাকলে ভিতরে ঢুকে পড়ার ভয় থাকে। শেষে অন্তরের কথা বলা হয়েছে: অন্তর ঠিক থাকলে শরীর ঠিক থাকে, নষ্ট হলে শরীরও নষ্ট হয়। তাই সন্দেহজনক বিষয় হাদিস আমাদের সতর্ক, পরিষ্কার ও অন্তর-সচেতন জীবন শেখায়।"},"teachings":["হালাল ও হারামের স্পষ্ট সীমা মানা জরুরি।","সন্দেহজনক বিষয় থেকে দূরে থাকলে দ্বীন ও মর্যাদা রক্ষা হয়।","হারামের কাছাকাছি ঘোরাফেরা করা ঝুঁকিপূর্ণ।","অন্তর ভালো থাকলে আচরণও ভালো হওয়ার পথ তৈরি হয়।"],"related_hadiths":[{"id":"2236","book_id":"2","label":"Sahih Muslim"},{"id":"205৯","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯3","book_id":"8","label":"Riyadus Salihin"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল-হারাম ও সন্দেহজনক বিষয়","description":"$book_name$ $hadith_number$ - $chapter_name$. হালাল-হারাম স্পষ্ট; সন্দেহজনক বিষয় থেকে বাঁচলে দ্বীন ও মর্যাদা রক্ষা হয়, আর অন্তর ঠিক থাকলে শরীর ঠিক থাকে।"},"heading":{"title":"হালাল হারাম স্পষ্ট: সন্দেহজনক বিষয় থেকে বাঁচার শিক্ষা","description":"এই হাদিস ইসলামী জীবনের একটি মৌলিক নীতি শেখায়। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, হালাল স্পষ্ট এবং হারামও স্পষ্ট। মাঝখানে কিছু সন্দেহজনক বিষয় আছে, যা অনেক মানুষ জানে না। যে ব্যক্তি সন্দেহজনক বিষয় থেকে বেঁচে থাকে, সে তার দ্বীন ও মর্যাদা রক্ষা করে। আর যে সন্দেহজনক বিষয়ে পড়ে, সে হারামের কাছাকাছি চলে যায়। রাখালের উদাহরণ দিয়ে বোঝানো হয়েছে, নিষিদ্ধ সীমার ধারে থাকলে ভিতরে ঢুকে পড়ার ভয় থাকে। শেষে অন্তরের কথা বলা হয়েছে: অন্তর ঠিক থাকলে শরীর ঠিক থাকে, নষ্ট হলে শরীরও নষ্ট হয়। তাই সন্দেহজনক বিষয় হাদিস আমাদের সতর্ক, পরিষ্কার ও অন্তর-সচেতন জীবন শেখায়।"},"teachings":["হালাল ও হারামের স্পষ্ট সীমা মানা জরুরি।","সন্দেহজনক বিষয় থেকে দূরে থাকলে দ্বীন ও মর্যাদা রক্ষা হয়।","হারামের কাছাকাছি ঘোরাফেরা করা ঝুঁকিপূর্ণ।","অন্তর ভালো থাকলে আচরণও ভালো হওয়ার পথ তৈরি হয়।"],"related_hadiths":[{"id":"2236","book_id":"2","label":"Sahih Muslim"},{"id":"2059","book_id":"1","label":"Sahih Bukhari"},{"id":"593","book_id":"8","label":"Riyadus Salihin"}]}</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম রিজিক দোয়ার পথে বাধা","description":"$book_name$ $hadith_number$ - $chapter_name$. সফরে ক্লান্ত অবস্থায় দোয়া করলেও খাদ্য, পানীয়, পোশাক ও জীবিকা হারাম হলে দোয়া কবুলের প্রশ্ন ওঠে।"},"heading":{"title":"হারাম রিজিক দোয়ার পথে বাধা: হালাল জীবিকা কেন দরকার","description":"এই হাদিসে দোয়ার একটি গুরুত্বপূর্ণ দিক তুলে ধরা হয়েছে। একজন মানুষ দূর-দূরান্তে সফর করছে, চুল এলোমেলো, শরীরে ধুলা-বালি, দুই হাত আসমানের দিকে তুলে কাতরভাবে বলছে, হে প্রভু! হে প্রভু! বাহ্যিকভাবে এটি দোয়ার বিনয়ী অবস্থা। কিন্তু হাদিসে বলা হলো, তার খাদ্য হারাম, পানীয় হারাম, পোশাক হারাম এবং জীবিকা হারাম; তাহলে তার দোয়া কীভাবে কবুল হবে? তাই হারাম রিজিক দোয়ার পথে বড় বাধা হতে পারে। এই শিক্ষা আমাদের দৈনন্দিন জীবনে খুব দরকার। আমরা শুধু দোয়া বাড়াব না, বরং খাবার, পোশাক ও আয়ের উৎসও পবিত্র রাখার চেষ্টা করব। হালাল জীবিকা ইবাদতের সৌন্দর্য বাড়ায়।"},"teachings":["দোয়ার সঙ্গে হালাল জীবিকার সম্পর্ক আছে।","বাহ্যিক বিনয় থাকলেও হারাম রিজিক বড় বাধা হতে পারে।","খাদ্য, পানীয়, পোশাক ও আয়—সব ক্ষেত্রেই সতর্কতা দরকার।","আল্লাহ পবিত্র, তাই পবিত্র উপায় পছন্দনীয়।"],"related_hadiths":[{"id":"205৯","book_id":"1","label":"Sahih Bukhari"},{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"1205","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম রিজিক দোয়ার পথে বাধা","description":"$book_name$ $hadith_number$ - $chapter_name$. সফরে ক্লান্ত অবস্থায় দোয়া করলেও খাদ্য, পানীয়, পোশাক ও জীবিকা হারাম হলে দোয়া কবুলের প্রশ্ন ওঠে।"},"heading":{"title":"হারাম রিজিক দোয়ার পথে বাধা: হালাল জীবিকা কেন দরকার","description":"এই হাদিসে দোয়ার একটি গুরুত্বপূর্ণ দিক তুলে ধরা হয়েছে। একজন মানুষ দূর-দূরান্তে সফর করছে, চুল এলোমেলো, শরীরে ধুলা-বালি, দুই হাত আসমানের দিকে তুলে কাতরভাবে বলছে, হে প্রভু! হে প্রভু! বাহ্যিকভাবে এটি দোয়ার বিনয়ী অবস্থা। কিন্তু হাদিসে বলা হলো, তার খাদ্য হারাম, পানীয় হারাম, পোশাক হারাম এবং জীবিকা হারাম; তাহলে তার দোয়া কীভাবে কবুল হবে? তাই হারাম রিজিক দোয়ার পথে বড় বাধা হতে পারে। এই শিক্ষা আমাদের দৈনন্দিন জীবনে খুব দরকার। আমরা শুধু দোয়া বাড়াব না, বরং খাবার, পোশাক ও আয়ের উৎসও পবিত্র রাখার চেষ্টা করব। হালাল জীবিকা ইবাদতের সৌন্দর্য বাড়ায়।"},"teachings":["দোয়ার সঙ্গে হালাল জীবিকার সম্পর্ক আছে।","বাহ্যিক বিনয় থাকলেও হারাম রিজিক বড় বাধা হতে পারে।","খাদ্য, পানীয়, পোশাক ও আয়—সব ক্ষেত্রেই সতর্কতা দরকার।","আল্লাহ পবিত্র, তাই পবিত্র উপায় পছন্দনীয়।"],"related_hadiths":[{"id":"2059","book_id":"1","label":"Sahih Bukhari"},{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"1205","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক বিষয় ও অন্তরের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহজনক বিষয় ছাড়লে দ্বীন ও সম্মান নিরাপদ থাকে; অন্তর ভালো থাকলে জীবনও সঠিক পথে থাকে।"},"heading":{"title":"সন্দেহজনক বিষয় থেকে বাঁচুন: হালাল-হারামের নিরাপদ পথ","description":"এই হাদিসে হালাল, হারাম এবং সন্দেহজনক বিষয়ের সম্পর্ক পরিষ্কার করা হয়েছে। হালাল সুস্পষ্ট, হারামও সুস্পষ্ট। কিন্তু কিছু বিষয় আছে, যেগুলো সম্পর্কে অনেকেই সিদ্ধান্ত নিতে পারে না। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি সন্দেহের বস্তুকে পরিহার করে, তার দ্বীন ও সম্মান পরিষ্কার থাকে। আর যে সন্দেহজনক কাজে জড়ায়, সে হারামে পড়ে যেতে পারে। রাখালের উদাহরণটি খুব সহজ: নিষিদ্ধ এলাকার ধারে পশু চরালে ভেতরে ঢুকে পড়ার ভয় থাকে। তাই নিরাপদ পথ হলো হারামের কাছাকাছি না যাওয়া। হাদিসের শেষে অন্তরের গুরুত্ব এসেছে। অন্তর ভালো থাকলে জীবন ভালো দিকে যায়, আর অন্তর নষ্ট হলে কাজও নষ্ট হতে থাকে।"},"teachings":["সন্দেহজনক বিষয় এড়িয়ে চলা নিরাপদ পথ।","হারামের সীমানার কাছাকাছি গেলে পড়ে যাওয়ার ভয় থাকে।","দ্বীন ও সম্মান রক্ষায় সতর্কতা দরকার।","অন্তর ঠিক রাখা আচরণ ঠিক রাখার বড় মাধ্যম।"],"related_hadiths":[{"id":"2236","book_id":"2","label":"Sahih Muslim"},{"id":"205৯","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯3","book_id":"8","label":"Riyadus Salihin"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক বিষয় ও অন্তরের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহজনক বিষয় ছাড়লে দ্বীন ও সম্মান নিরাপদ থাকে; অন্তর ভালো থাকলে জীবনও সঠিক পথে থাকে।"},"heading":{"title":"সন্দেহজনক বিষয় থেকে বাঁচুন: হালাল-হারামের নিরাপদ পথ","description":"এই হাদিসে হালাল, হারাম এবং সন্দেহজনক বিষয়ের সম্পর্ক পরিষ্কার করা হয়েছে। হালাল সুস্পষ্ট, হারামও সুস্পষ্ট। কিন্তু কিছু বিষয় আছে, যেগুলো সম্পর্কে অনেকেই সিদ্ধান্ত নিতে পারে না। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি সন্দেহের বস্তুকে পরিহার করে, তার দ্বীন ও সম্মান পরিষ্কার থাকে। আর যে সন্দেহজনক কাজে জড়ায়, সে হারামে পড়ে যেতে পারে। রাখালের উদাহরণটি খুব সহজ: নিষিদ্ধ এলাকার ধারে পশু চরালে ভেতরে ঢুকে পড়ার ভয় থাকে। তাই নিরাপদ পথ হলো হারামের কাছাকাছি না যাওয়া। হাদিসের শেষে অন্তরের গুরুত্ব এসেছে। অন্তর ভালো থাকলে জীবন ভালো দিকে যায়, আর অন্তর নষ্ট হলে কাজও নষ্ট হতে থাকে।"},"teachings":["সন্দেহজনক বিষয় এড়িয়ে চলা নিরাপদ পথ।","হারামের সীমানার কাছাকাছি গেলে পড়ে যাওয়ার ভয় থাকে।","দ্বীন ও সম্মান রক্ষায় সতর্কতা দরকার।","অন্তর ঠিক রাখা আচরণ ঠিক রাখার বড় মাধ্যম।"],"related_hadiths":[{"id":"2236","book_id":"2","label":"Sahih Muslim"},{"id":"2059","book_id":"1","label":"Sahih Bukhari"},{"id":"593","book_id":"8","label":"Riyadus Salihin"}]}</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘৃণিত উপার্জন থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. কুকুর বিক্রয়, ব্যভিচারের বিনিময় ও সিঙ্গা লাগানোর মূল্যকে ঘৃণিত বলা হয়েছে; উপার্জনে সতর্কতা দরকার।"},"heading":{"title":"ঘৃণিত উপার্জন: কুকুর বিক্রয় ও অনৈতিক আয়ের সতর্কতা","description":"এই হাদিসে কয়েক ধরনের উপার্জনকে ঘৃণিত বলা হয়েছে। কুকুর বিক্রয়ের মূল্য, ব্যভিচারের বিনিময় এবং সিঙ্গা লাগানোর মূল্য—এই তিনটি বিষয় হাদিসে এসেছে। এখানে মূল শিক্ষা হলো, উপার্জনের সব পথ সমান নয়। টাকা পাওয়া গেলেই তা ভালো উপার্জন হয়ে যায় না। ঘৃণিত উপার্জন হাদিস আমাদের আয়ের উৎস নিয়ে সতর্ক করে। বিশেষ করে ব্যভিচারের বিনিময়ের মতো অনৈতিক আয়ের কথা স্পষ্টভাবে এসেছে। কুকুর বিক্রয়ের মূল্য ও সিঙ্গা লাগানোর মূল্য সম্পর্কেও হাদিসে সতর্ক ভাষা ব্যবহৃত হয়েছে। তাই মুসলিমের জন্য উপার্জনের ক্ষেত্রে শুধু লাভ নয়, শরিয়তের দৃষ্টিতে তা পরিষ্কার কি না—এটাও দেখা দরকার।"},"teachings":["সব ধরনের আয় গ্রহণযোগ্য নয়।","অনৈতিক কাজের বিনিময় ঘৃণিত উপার্জনের মধ্যে পড়ে।","উপার্জনের উৎস নিয়ে সতর্ক থাকা দরকার।","লাভের আগে হালাল-হারাম বিচার করা জরুরি।"],"related_hadiths":[{"id":"2237","book_id":"1","label":"Sahih Bukhari"},{"id":"22৮2","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯62","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘৃণিত উপার্জন থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. কুকুর বিক্রয়, ব্যভিচারের বিনিময় ও সিঙ্গা লাগানোর মূল্যকে ঘৃণিত বলা হয়েছে; উপার্জনে সতর্কতা দরকার।"},"heading":{"title":"ঘৃণিত উপার্জন: কুকুর বিক্রয় ও অনৈতিক আয়ের সতর্কতা","description":"এই হাদিসে কয়েক ধরনের উপার্জনকে ঘৃণিত বলা হয়েছে। কুকুর বিক্রয়ের মূল্য, ব্যভিচারের বিনিময় এবং সিঙ্গা লাগানোর মূল্য—এই তিনটি বিষয় হাদিসে এসেছে। এখানে মূল শিক্ষা হলো, উপার্জনের সব পথ সমান নয়। টাকা পাওয়া গেলেই তা ভালো উপার্জন হয়ে যায় না। ঘৃণিত উপার্জন হাদিস আমাদের আয়ের উৎস নিয়ে সতর্ক করে। বিশেষ করে ব্যভিচারের বিনিময়ের মতো অনৈতিক আয়ের কথা স্পষ্টভাবে এসেছে। কুকুর বিক্রয়ের মূল্য ও সিঙ্গা লাগানোর মূল্য সম্পর্কেও হাদিসে সতর্ক ভাষা ব্যবহৃত হয়েছে। তাই মুসলিমের জন্য উপার্জনের ক্ষেত্রে শুধু লাভ নয়, শরিয়তের দৃষ্টিতে তা পরিষ্কার কি না—এটাও দেখা দরকার।"},"teachings":["সব ধরনের আয় গ্রহণযোগ্য নয়।","অনৈতিক কাজের বিনিময় ঘৃণিত উপার্জনের মধ্যে পড়ে।","উপার্জনের উৎস নিয়ে সতর্ক থাকা দরকার।","লাভের আগে হালাল-হারাম বিচার করা জরুরি।"],"related_hadiths":[{"id":"2237","book_id":"1","label":"Sahih Bukhari"},{"id":"2282","book_id":"1","label":"Sahih Bukhari"},{"id":"5962","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নিষিদ্ধ আয়ের তিনটি পথ","description":"$book_name$ $hadith_number$ - $chapter_name$. কুকুরের মূল্য, যিনাকারীনীর উপার্জন ও গণকের উপার্জন খেতে নিষেধ করা হয়েছে; রিজিকে পবিত্রতা জরুরি।"},"heading":{"title":"নিষিদ্ধ আয় থেকে বাঁচুন: কুকুরের মূল্য, যিনা ও গণকের উপার্জন","description":"এই হাদিসে তিনটি উপার্জন খেতে নিষেধ করা হয়েছে: কুকুরের মূল্য, যিনাকারীনীর উপার্জন এবং গণকের উপার্জন। হাদিসটি খুব পরিষ্কারভাবে শেখায়, আয়ের উৎস ভালো না হলে সেই আয় গ্রহণ করা উচিত নয়। নিষিদ্ধ আয় শুধু ব্যক্তির পকেটে আসে না; তা খাবার, পরিবার ও জীবনের ওপরও প্রভাব ফেলে। বিশেষ করে যিনা-ভিত্তিক উপার্জন ও গণকের উপার্জন মানুষের নৈতিকতা ও বিশ্বাসের সঙ্গে জড়িত। কুকুরের মূল্য সম্পর্কেও স্পষ্ট নিষেধ এসেছে। তাই মুসলিমের জন্য উপার্জনের ক্ষেত্রে সতর্ক থাকা জরুরি। কোন কাজ থেকে আয় হচ্ছে, তা আল্লাহর নাফরমানির সঙ্গে যুক্ত কি না—এই প্রশ্ন নিজের কাছে রাখা দরকার।"},"teachings":["কুকুরের মূল্য খেতে নিষেধ করা হয়েছে।","যিনাকারীনীর উপার্জন গ্রহণযোগ্য নয়।","গণকের উপার্জন থেকে বাঁচতে বলা হয়েছে।","রিজিক পবিত্র রাখতে আয়ের উৎস যাচাই করা দরকার।"],"related_hadiths":[{"id":"5৯62","book_id":"1","label":"Sahih Bukhari"},{"id":"5761","book_id":"1","label":"Sahih Bukhari"},{"id":"2236","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নিষিদ্ধ আয়ের তিনটি পথ","description":"$book_name$ $hadith_number$ - $chapter_name$. কুকুরের মূল্য, যিনাকারীনীর উপার্জন ও গণকের উপার্জন খেতে নিষেধ করা হয়েছে; রিজিকে পবিত্রতা জরুরি।"},"heading":{"title":"নিষিদ্ধ আয় থেকে বাঁচুন: কুকুরের মূল্য, যিনা ও গণকের উপার্জন","description":"এই হাদিসে তিনটি উপার্জন খেতে নিষেধ করা হয়েছে: কুকুরের মূল্য, যিনাকারীনীর উপার্জন এবং গণকের উপার্জন। হাদিসটি খুব পরিষ্কারভাবে শেখায়, আয়ের উৎস ভালো না হলে সেই আয় গ্রহণ করা উচিত নয়। নিষিদ্ধ আয় শুধু ব্যক্তির পকেটে আসে না; তা খাবার, পরিবার ও জীবনের ওপরও প্রভাব ফেলে। বিশেষ করে যিনা-ভিত্তিক উপার্জন ও গণকের উপার্জন মানুষের নৈতিকতা ও বিশ্বাসের সঙ্গে জড়িত। কুকুরের মূল্য সম্পর্কেও স্পষ্ট নিষেধ এসেছে। তাই মুসলিমের জন্য উপার্জনের ক্ষেত্রে সতর্ক থাকা জরুরি। কোন কাজ থেকে আয় হচ্ছে, তা আল্লাহর নাফরমানির সঙ্গে যুক্ত কি না—এই প্রশ্ন নিজের কাছে রাখা দরকার।"},"teachings":["কুকুরের মূল্য খেতে নিষেধ করা হয়েছে।","যিনাকারীনীর উপার্জন গ্রহণযোগ্য নয়।","গণকের উপার্জন থেকে বাঁচতে বলা হয়েছে।","রিজিক পবিত্র রাখতে আয়ের উৎস যাচাই করা দরকার।"],"related_hadiths":[{"id":"5962","book_id":"1","label":"Sahih Bukhari"},{"id":"5761","book_id":"1","label":"Sahih Bukhari"},{"id":"2236","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম উপার্জন ও অভিশপ্ত কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. রক্ত, কুকুর ও ব্যভিচারের আয় নিষিদ্ধ; সুদ, উল্কি ও ছবি অঙ্কনের ব্যাপারেও কঠিন সতর্কতা এসেছে।"},"heading":{"title":"হারাম উপার্জন ও নিষিদ্ধ কাজ: রক্ত, সুদ, উল্কি ও ছবি নিয়ে সতর্কতা","description":"এই হাদিসে কয়েকটি বিষয় একসঙ্গে এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) রক্ত বিক্রয়ের মূল্য, কুকুর বিক্রয়ের মূল্য এবং ব্যভিচারের বিনিময় থেকে নিষেধ করেছেন। এরপর সুদ গ্রহীতা ও সুদদাতার প্রতি লা’নতের কথা এসেছে। আরও বলা হয়েছে, যে উল্কি করে এবং যে উল্কি করায়, তাদের ওপরও লা’নত করা হয়েছে। ছবি অঙ্কনকারীর প্রতিও লা’নতের কথা এসেছে। তাই হারাম উপার্জন হাদিস আমাদের আয়ের উৎস এবং কিছু কাজের ব্যাপারে গভীর সতর্ক করে। এখানে অযথা বাড়তি ব্যাখ্যা না করে মূল বার্তাই স্পষ্ট: মুসলিমকে এমন আয় ও কাজ থেকে দূরে থাকতে হবে, যেগুলোর ব্যাপারে নবী (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কঠিন নিষেধ দিয়েছেন।"},"teachings":["রক্ত, কুকুর ও ব্যভিচারের বিনিময় থেকে নিষেধ করা হয়েছে।","সুদ গ্রহণ ও সুদ দেওয়া—দুটির ব্যাপারেই কঠিন সতর্কতা এসেছে।","উল্কি করা ও করানো থেকে বাঁচতে বলা হয়েছে।","নিষিদ্ধ আয়ের সঙ্গে নিষিদ্ধ কাজ থেকেও দূরে থাকা দরকার।"],"related_hadiths":[{"id":"2237","book_id":"1","label":"Sahih Bukhari"},{"id":"22৮2","book_id":"1","label":"Sahih Bukhari"},{"id":"2236","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম উপার্জন ও অভিশপ্ত কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. রক্ত, কুকুর ও ব্যভিচারের আয় নিষিদ্ধ; সুদ, উল্কি ও ছবি অঙ্কনের ব্যাপারেও কঠিন সতর্কতা এসেছে।"},"heading":{"title":"হারাম উপার্জন ও নিষিদ্ধ কাজ: রক্ত, সুদ, উল্কি ও ছবি নিয়ে সতর্কতা","description":"এই হাদিসে কয়েকটি বিষয় একসঙ্গে এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) রক্ত বিক্রয়ের মূল্য, কুকুর বিক্রয়ের মূল্য এবং ব্যভিচারের বিনিময় থেকে নিষেধ করেছেন। এরপর সুদ গ্রহীতা ও সুদদাতার প্রতি লা’নতের কথা এসেছে। আরও বলা হয়েছে, যে উল্কি করে এবং যে উল্কি করায়, তাদের ওপরও লা’নত করা হয়েছে। ছবি অঙ্কনকারীর প্রতিও লা’নতের কথা এসেছে। তাই হারাম উপার্জন হাদিস আমাদের আয়ের উৎস এবং কিছু কাজের ব্যাপারে গভীর সতর্ক করে। এখানে অযথা বাড়তি ব্যাখ্যা না করে মূল বার্তাই স্পষ্ট: মুসলিমকে এমন আয় ও কাজ থেকে দূরে থাকতে হবে, যেগুলোর ব্যাপারে নবী (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কঠিন নিষেধ দিয়েছেন।"},"teachings":["রক্ত, কুকুর ও ব্যভিচারের বিনিময় থেকে নিষেধ করা হয়েছে।","সুদ গ্রহণ ও সুদ দেওয়া—দুটির ব্যাপারেই কঠিন সতর্কতা এসেছে।","উল্কি করা ও করানো থেকে বাঁচতে বলা হয়েছে।","নিষিদ্ধ আয়ের সঙ্গে নিষিদ্ধ কাজ থেকেও দূরে থাকা দরকার।"],"related_hadiths":[{"id":"2237","book_id":"1","label":"Sahih Bukhari"},{"id":"2282","book_id":"1","label":"Sahih Bukhari"},{"id":"2236","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম উপার্জনের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম মালে গড়া দেহের ভয়াবহ পরিণতি জানুন এবং হালাল রুজির পথে চলার শিক্ষা নিন।"},"heading":{"title":"হালাল রুজি ও হারাম উপার্জন: মুমিনের জীবনে সতর্কতার শিক্ষা","description":"এই হাদিসে হারাম উপার্জন সম্পর্কে খুব স্পষ্ট সতর্কতা এসেছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে দেহের গোশত হারাম মালে গঠিত, তা জান্নাতে প্রবেশ করতে পারবে না। কথাটি আমাদের খাবার, আয়, ব্যবসা ও লেনদেন নিয়ে ভাবতে শেখায়। শুধু টাকা হাতে এলেই তা ভালো হয়ে যায় না; টাকা কোথা থেকে এল, সেটাও বড় বিষয়। হালাল রুজি মুমিনের জীবনকে নিরাপদ পথে রাখে। আর হারাম মাল শরীরকে পুষ্ট করলেও তা আখিরাতের জন্য ভয়ংকর ক্ষতির কারণ হতে পারে। তাই এই হাদিসের মূল শিক্ষা হলো, আয়-রোজগারে সাবধান থাকা, সন্দেহজনক পথ এড়িয়ে চলা এবং নিজের পরিবারকে হালাল খাবার খাওয়ানোর চেষ্টা করা।"},"teachings":["হারাম উপার্জনে গড়া দেহের জন্য হাদিসে কঠিন সতর্কতা এসেছে।","খাবার ও আয় হালাল কি না, তা মুমিনের জন্য গুরুত্বপূর্ণ বিষয়।","পরিবারকে হালাল রুজি খাওয়ানো ঈমানি দায়িত্বের অংশ।","মাল বেশি হওয়া নয়, মাল হালাল হওয়াই আসল নিরাপত্তার পথ।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"15৯৯","book_id":"2","label":"Sahih Muslim"},{"id":"2760","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম উপার্জনের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম মালে গড়া দেহের ভয়াবহ পরিণতি জানুন এবং হালাল রুজির পথে চলার শিক্ষা নিন।"},"heading":{"title":"হালাল রুজি ও হারাম উপার্জন: মুমিনের জীবনে সতর্কতার শিক্ষা","description":"এই হাদিসে হারাম উপার্জন সম্পর্কে খুব স্পষ্ট সতর্কতা এসেছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে দেহের গোশত হারাম মালে গঠিত, তা জান্নাতে প্রবেশ করতে পারবে না। কথাটি আমাদের খাবার, আয়, ব্যবসা ও লেনদেন নিয়ে ভাবতে শেখায়। শুধু টাকা হাতে এলেই তা ভালো হয়ে যায় না; টাকা কোথা থেকে এল, সেটাও বড় বিষয়। হালাল রুজি মুমিনের জীবনকে নিরাপদ পথে রাখে। আর হারাম মাল শরীরকে পুষ্ট করলেও তা আখিরাতের জন্য ভয়ংকর ক্ষতির কারণ হতে পারে। তাই এই হাদিসের মূল শিক্ষা হলো, আয়-রোজগারে সাবধান থাকা, সন্দেহজনক পথ এড়িয়ে চলা এবং নিজের পরিবারকে হালাল খাবার খাওয়ানোর চেষ্টা করা।"},"teachings":["হারাম উপার্জনে গড়া দেহের জন্য হাদিসে কঠিন সতর্কতা এসেছে।","খাবার ও আয় হালাল কি না, তা মুমিনের জন্য গুরুত্বপূর্ণ বিষয়।","পরিবারকে হালাল রুজি খাওয়ানো ঈমানি দায়িত্বের অংশ।","মাল বেশি হওয়া নয়, মাল হালাল হওয়াই আসল নিরাপত্তার পথ।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"1599","book_id":"2","label":"Sahih Muslim"},{"id":"2760","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক কাজ ছেড়ে নিশ্চিত পথে চলা","description":"$book_name$ $hadith_number$ - $chapter_name$. মনে খটকা লাগা কাজ ছেড়ে পরিষ্কার ও শান্তির পথে চলার সুন্দর নববী শিক্ষা জানুন।"},"heading":{"title":"সন্দেহজনক কাজ থেকে বাঁচার হাদিস: সত্যে শান্তি, মিথ্যায় খটকা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম একটি সহজ কিন্তু গভীর নিয়ম শিখিয়েছেন। যে কাজে মনে খটকা লাগে, সে কাজ ছেড়ে এমন কাজ বেছে নিতে বলা হয়েছে যাতে খটকা নেই। মানুষের অন্তর অনেক সময় ভুল ও ঠিকের মাঝে অস্বস্তি টের পায়। হাদিসটি বলে, সত্য ও শুদ্ধ জিনিস সাধারণত অন্তরে প্রশান্তি আনে, আর মিথ্যা ও অশুদ্ধ জিনিস দ্বিধা তৈরি করে। তাই সন্দেহজনক কাজ এড়িয়ে চলা শুধু ইবাদতের বিষয় নয়; এটি চরিত্র, কথা, ব্যবসা ও সম্পর্কের ক্ষেত্রেও দরকারি। এই শিক্ষা মানুষকে নিরাপদ, পরিষ্কার এবং সৎ পথে চলতে সাহায্য করে।"},"teachings":["যে কাজে মনে খটকা লাগে, তা ছেড়ে দেওয়া ভালো।","সত্য অন্তরে প্রশান্তি আনে, মিথ্যা দ্বিধা সৃষ্টি করে।","সন্দেহজনক কাজ থেকে দূরে থাকা দ্বীন রক্ষার পথ।","কথা ও কাজে পরিষ্কার অবস্থান নেওয়া মুমিনের গুণ।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"15৯৯","book_id":"2","label":"Sahih Muslim"},{"id":"2553","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক কাজ ছেড়ে নিশ্চিত পথে চলা","description":"$book_name$ $hadith_number$ - $chapter_name$. মনে খটকা লাগা কাজ ছেড়ে পরিষ্কার ও শান্তির পথে চলার সুন্দর নববী শিক্ষা জানুন।"},"heading":{"title":"সন্দেহজনক কাজ থেকে বাঁচার হাদিস: সত্যে শান্তি, মিথ্যায় খটকা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম একটি সহজ কিন্তু গভীর নিয়ম শিখিয়েছেন। যে কাজে মনে খটকা লাগে, সে কাজ ছেড়ে এমন কাজ বেছে নিতে বলা হয়েছে যাতে খটকা নেই। মানুষের অন্তর অনেক সময় ভুল ও ঠিকের মাঝে অস্বস্তি টের পায়। হাদিসটি বলে, সত্য ও শুদ্ধ জিনিস সাধারণত অন্তরে প্রশান্তি আনে, আর মিথ্যা ও অশুদ্ধ জিনিস দ্বিধা তৈরি করে। তাই সন্দেহজনক কাজ এড়িয়ে চলা শুধু ইবাদতের বিষয় নয়; এটি চরিত্র, কথা, ব্যবসা ও সম্পর্কের ক্ষেত্রেও দরকারি। এই শিক্ষা মানুষকে নিরাপদ, পরিষ্কার এবং সৎ পথে চলতে সাহায্য করে।"},"teachings":["যে কাজে মনে খটকা লাগে, তা ছেড়ে দেওয়া ভালো।","সত্য অন্তরে প্রশান্তি আনে, মিথ্যা দ্বিধা সৃষ্টি করে।","সন্দেহজনক কাজ থেকে দূরে থাকা দ্বীন রক্ষার পথ।","কথা ও কাজে পরিষ্কার অবস্থান নেওয়া মুমিনের গুণ।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"1599","book_id":"2","label":"Sahih Muslim"},{"id":"2553","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গায়িকা কেনাবেচা ও হারাম মূল্য","description":"$book_name$ $hadith_number$ - $chapter_name$. গায়িকা ক্রয়-বিক্রয়, গান শেখানো ও তার মূল্য সম্পর্কে হাদিসের সতর্ক বার্তা জানুন।"},"heading":{"title":"গায়িকা ক্রয়-বিক্রয় ও হারাম উপার্জন নিয়ে হাদিসের শিক্ষা","description":"এই হাদিসে গায়িকা ক্রয়-বিক্রয়, তাদের গান শেখানো এবং এ ধরনের কাজে পাওয়া মূল্য সম্পর্কে কঠোরভাবে নিষেধ এসেছে। হাদিসের ভাষায় তাদের মূল্য হারাম বলা হয়েছে। এখানে মূল শিক্ষা হলো, বিনোদনের নামে এমন কাজে জড়ানো থেকে বাঁচা যা মানুষকে আল্লাহর পথ থেকে দূরে নিতে পারে। অনুবাদে কুরআনের একটি আয়াতের কথাও এসেছে, যেখানে রং-তামাশার গাথা কেনার কথা বলা হয়েছে। তাই এই হাদিস শুধু গান-বাজনা নিয়ে নয়; বরং এমন আয়ের পথ নিয়েও সতর্ক করে, যা দ্বীন ও চরিত্রের ক্ষতি করতে পারে। একজন মুমিনের উচিত নিজের আয় ও বিনোদন—দুটো ক্ষেত্রেই আল্লাহভীতি রাখা।"},"teachings":["গায়িকা ক্রয়-বিক্রয় ও গান শেখানোর বিষয়ে হাদিসে নিষেধ এসেছে।","এ ধরনের কাজের মূল্যকে হাদিসে হারাম বলা হয়েছে।","বিনোদন যেন দ্বীন থেকে দূরে নেওয়ার কারণ না হয়।","আয়ের উৎস হালাল কি না, তা যাচাই করা জরুরি।"],"related_hadiths":[{"id":"55৯0","book_id":"1","label":"Sahih Bukhari"},{"id":"4020","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গায়িকা কেনাবেচা ও হারাম মূল্য","description":"$book_name$ $hadith_number$ - $chapter_name$. গায়িকা ক্রয়-বিক্রয়, গান শেখানো ও তার মূল্য সম্পর্কে হাদিসের সতর্ক বার্তা জানুন।"},"heading":{"title":"গায়িকা ক্রয়-বিক্রয় ও হারাম উপার্জন নিয়ে হাদিসের শিক্ষা","description":"এই হাদিসে গায়িকা ক্রয়-বিক্রয়, তাদের গান শেখানো এবং এ ধরনের কাজে পাওয়া মূল্য সম্পর্কে কঠোরভাবে নিষেধ এসেছে। হাদিসের ভাষায় তাদের মূল্য হারাম বলা হয়েছে। এখানে মূল শিক্ষা হলো, বিনোদনের নামে এমন কাজে জড়ানো থেকে বাঁচা যা মানুষকে আল্লাহর পথ থেকে দূরে নিতে পারে। অনুবাদে কুরআনের একটি আয়াতের কথাও এসেছে, যেখানে রং-তামাশার গাথা কেনার কথা বলা হয়েছে। তাই এই হাদিস শুধু গান-বাজনা নিয়ে নয়; বরং এমন আয়ের পথ নিয়েও সতর্ক করে, যা দ্বীন ও চরিত্রের ক্ষতি করতে পারে। একজন মুমিনের উচিত নিজের আয় ও বিনোদন—দুটো ক্ষেত্রেই আল্লাহভীতি রাখা।"},"teachings":["গায়িকা ক্রয়-বিক্রয় ও গান শেখানোর বিষয়ে হাদিসে নিষেধ এসেছে।","এ ধরনের কাজের মূল্যকে হাদিসে হারাম বলা হয়েছে।","বিনোদন যেন দ্বীন থেকে দূরে নেওয়ার কারণ না হয়।","আয়ের উৎস হালাল কি না, তা যাচাই করা জরুরি।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"4020","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম দ্বারা প্রতিপালিত দেহের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম দ্বারা প্রতিপালিত দেহ সম্পর্কে নবীজির সতর্ক বাণী ও হালাল জীবনের শিক্ষা পড়ুন।"},"heading":{"title":"হারাম রুজি থেকে বাঁচার হাদিস: দেহ, খাদ্য ও আখিরাতের ভাবনা","description":"এই হাদিসে খুব সংক্ষিপ্ত ভাষায় বড় সতর্কতা দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে দেহ হারাম দ্বারা প্রতিপালিত, তা জান্নাতে প্রবেশ করবে না। এর মানে, মানুষের শরীর কী দিয়ে বড় হচ্ছে—এটি দ্বীনের দৃষ্টিতে গুরুত্বপূর্ণ। হারাম আয়, হারাম খাবার এবং অন্যায় পথে পাওয়া সম্পদ শুধু দুনিয়ার বিষয় নয়; এর আখিরাতের দিকও আছে। হালাল রুজি কম হলেও তা নিরাপদ। আর হারাম রুজি বেশি হলেও তা ক্ষতির কারণ হতে পারে। তাই এই হাদিস মুমিনকে নিজের উপার্জন, খাওয়া-দাওয়া ও পরিবারের খরচের উৎস নিয়ে সচেতন করে।"},"teachings":["হারাম দ্বারা প্রতিপালিত দেহ সম্পর্কে হাদিসে কঠিন সতর্কতা এসেছে।","রুজির উৎস হালাল হওয়া মুমিনের জীবনে বড় বিষয়।","কম হালাল আয়ও হারাম বেশি আয়ের চেয়ে নিরাপদ।","নিজের ও পরিবারের খাবারের উৎস যাচাই করা দরকার।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"15৯৯","book_id":"2","label":"Sahih Muslim"},{"id":"2760","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম দ্বারা প্রতিপালিত দেহের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম দ্বারা প্রতিপালিত দেহ সম্পর্কে নবীজির সতর্ক বাণী ও হালাল জীবনের শিক্ষা পড়ুন।"},"heading":{"title":"হারাম রুজি থেকে বাঁচার হাদিস: দেহ, খাদ্য ও আখিরাতের ভাবনা","description":"এই হাদিসে খুব সংক্ষিপ্ত ভাষায় বড় সতর্কতা দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে দেহ হারাম দ্বারা প্রতিপালিত, তা জান্নাতে প্রবেশ করবে না। এর মানে, মানুষের শরীর কী দিয়ে বড় হচ্ছে—এটি দ্বীনের দৃষ্টিতে গুরুত্বপূর্ণ। হারাম আয়, হারাম খাবার এবং অন্যায় পথে পাওয়া সম্পদ শুধু দুনিয়ার বিষয় নয়; এর আখিরাতের দিকও আছে। হালাল রুজি কম হলেও তা নিরাপদ। আর হারাম রুজি বেশি হলেও তা ক্ষতির কারণ হতে পারে। তাই এই হাদিস মুমিনকে নিজের উপার্জন, খাওয়া-দাওয়া ও পরিবারের খরচের উৎস নিয়ে সচেতন করে।"},"teachings":["হারাম দ্বারা প্রতিপালিত দেহ সম্পর্কে হাদিসে কঠিন সতর্কতা এসেছে।","রুজির উৎস হালাল হওয়া মুমিনের জীবনে বড় বিষয়।","কম হালাল আয়ও হারাম বেশি আয়ের চেয়ে নিরাপদ।","নিজের ও পরিবারের খাবারের উৎস যাচাই করা দরকার।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"1599","book_id":"2","label":"Sahih Muslim"},{"id":"2760","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিককে নেতা বলা থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মুনাফিক বা মিথ্যুক ব্যক্তিকে নেতা হিসেবে সম্মান করার বিষয়ে নবীজির সতর্ক বাণী জানুন।"},"heading":{"title":"মুনাফিককে নেতা বলা: সত্য, নেতৃত্ব ও ঈমানি সতর্কতার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম মুনাফিক ব্যক্তিকে নেতা বা সাইয়িদ বলতে নিষেধ করেছেন। অনুবাদে এসেছে, যদি নেতা মুনাফিক হয়, তাহলে এতে প্রতিপালককে অসন্তুষ্ট করার কথা বলা হয়েছে। অন্য বর্ণনায় মিথ্যুক মুনাফিককে নেতা বলা নিয়েও কঠিন সতর্কতা এসেছে। হাদিসটি নেতৃত্বের ভাষা ও সম্মান দেওয়ার বিষয়ে আমাদের সতর্ক করে। সম্মান এমন কাউকে দেওয়া উচিত নয়, যার ভেতরে মুনাফিকি, মিথ্যা বা দ্বীনের বিরুদ্ধে আচরণ আছে। এর মানে সাধারণ আচরণে অশোভন হওয়া নয়; বরং নৈতিক সম্মান ও নেতৃত্বের আসন কাকে দেওয়া হচ্ছে, সে বিষয়ে সতর্ক থাকা।"},"teachings":["মুনাফিক ব্যক্তিকে নেতৃত্বের সম্মান দেওয়ার বিষয়ে সতর্কতা এসেছে।","মিথ্যুক ও দ্বিমুখী চরিত্রের মানুষকে অকারণে বড় করা উচিত নয়।","নেতৃত্বের সম্মান নৈতিকতার সাথে জড়িত।","কথার মাধ্যমে কাকে মর্যাদা দিচ্ছি, তা ভাবা দরকার।"],"related_hadiths":[{"id":"33","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯","book_id":"2","label":"Sahih Muslim"},{"id":"4৮73","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিককে নেতা বলা থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মুনাফিক বা মিথ্যুক ব্যক্তিকে নেতা হিসেবে সম্মান করার বিষয়ে নবীজির সতর্ক বাণী জানুন।"},"heading":{"title":"মুনাফিককে নেতা বলা: সত্য, নেতৃত্ব ও ঈমানি সতর্কতার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম মুনাফিক ব্যক্তিকে নেতা বা সাইয়িদ বলতে নিষেধ করেছেন। অনুবাদে এসেছে, যদি নেতা মুনাফিক হয়, তাহলে এতে প্রতিপালককে অসন্তুষ্ট করার কথা বলা হয়েছে। অন্য বর্ণনায় মিথ্যুক মুনাফিককে নেতা বলা নিয়েও কঠিন সতর্কতা এসেছে। হাদিসটি নেতৃত্বের ভাষা ও সম্মান দেওয়ার বিষয়ে আমাদের সতর্ক করে। সম্মান এমন কাউকে দেওয়া উচিত নয়, যার ভেতরে মুনাফিকি, মিথ্যা বা দ্বীনের বিরুদ্ধে আচরণ আছে। এর মানে সাধারণ আচরণে অশোভন হওয়া নয়; বরং নৈতিক সম্মান ও নেতৃত্বের আসন কাকে দেওয়া হচ্ছে, সে বিষয়ে সতর্ক থাকা।"},"teachings":["মুনাফিক ব্যক্তিকে নেতৃত্বের সম্মান দেওয়ার বিষয়ে সতর্কতা এসেছে।","মিথ্যুক ও দ্বিমুখী চরিত্রের মানুষকে অকারণে বড় করা উচিত নয়।","নেতৃত্বের সম্মান নৈতিকতার সাথে জড়িত।","কথার মাধ্যমে কাকে মর্যাদা দিচ্ছি, তা ভাবা দরকার।"],"related_hadiths":[{"id":"33","book_id":"1","label":"Sahih Bukhari"},{"id":"59","book_id":"2","label":"Sahih Muslim"},{"id":"4873","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তর্ক, মিথ্যা ও সুন্দর চরিত্রের ফজিলত","description":"$book_name$ $hadith_number$ - $chapter_name$. হক হলেও তর্ক ছাড়া, মজা করেও মিথ্যা না বলা এবং চরিত্র সুন্দর করার বড় শিক্ষা জানুন।"},"heading":{"title":"সুন্দর চরিত্রের হাদিস: তর্ক ছাড়া, মিথ্যা ছাড়া, ভালো আচরণ","description":"এই হাদিসে তিনটি বড় আচরণ শেখানো হয়েছে। প্রথমত, কেউ হক হলেও তর্ক পরিহার করলে তার জন্য জান্নাতে ঘরের কথা এসেছে। দ্বিতীয়ত, মজা করেও মিথ্যা ছেড়ে দেওয়ার কথা বলা হয়েছে। তৃতীয়ত, চরিত্র সুন্দর করার ফজিলত এসেছে। হাদিসটি আমাদের দৈনন্দিন কথা ও আচরণকে ঠিক করার সহজ পথ দেখায়। অনেক সময় মানুষ সত্য কথা বলেও তর্কে জড়িয়ে পড়ে, আবার হাসানোর জন্য মিথ্যা বলে ফেলে। এই হাদিস শেখায়, সত্যের সাথে নম্রতা, কথার সাথে সততা এবং মানুষের সাথে ভালো ব্যবহার—সবই মুমিনের চরিত্রের অংশ। সুন্দর চরিত্র শুধু বাহ্যিক ভদ্রতা নয়; এটি কথা, রাগ, তর্ক ও আচরণে প্রকাশ পায়।"},"teachings":["হক হলেও অপ্রয়োজনীয় তর্ক ছেড়ে দেওয়া উত্তম কাজ।","মজা করেও মিথ্যা বলা থেকে বাঁচতে হবে।","সুন্দর চরিত্র জান্নাতের বড় ফজিলতের কারণ।","সত্য কথা বলার সঙ্গে নম্র আচরণও দরকার।"],"related_hadiths":[{"id":"4৮00","book_id":"4","label":"Sunan Abu Dawud"},{"id":"60৯4","book_id":"1","label":"Sahih Bukhari"},{"id":"2004","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তর্ক, মিথ্যা ও সুন্দর চরিত্রের ফজিলত","description":"$book_name$ $hadith_number$ - $chapter_name$. হক হলেও তর্ক ছাড়া, মজা করেও মিথ্যা না বলা এবং চরিত্র সুন্দর করার বড় শিক্ষা জানুন।"},"heading":{"title":"সুন্দর চরিত্রের হাদিস: তর্ক ছাড়া, মিথ্যা ছাড়া, ভালো আচরণ","description":"এই হাদিসে তিনটি বড় আচরণ শেখানো হয়েছে। প্রথমত, কেউ হক হলেও তর্ক পরিহার করলে তার জন্য জান্নাতে ঘরের কথা এসেছে। দ্বিতীয়ত, মজা করেও মিথ্যা ছেড়ে দেওয়ার কথা বলা হয়েছে। তৃতীয়ত, চরিত্র সুন্দর করার ফজিলত এসেছে। হাদিসটি আমাদের দৈনন্দিন কথা ও আচরণকে ঠিক করার সহজ পথ দেখায়। অনেক সময় মানুষ সত্য কথা বলেও তর্কে জড়িয়ে পড়ে, আবার হাসানোর জন্য মিথ্যা বলে ফেলে। এই হাদিস শেখায়, সত্যের সাথে নম্রতা, কথার সাথে সততা এবং মানুষের সাথে ভালো ব্যবহার—সবই মুমিনের চরিত্রের অংশ। সুন্দর চরিত্র শুধু বাহ্যিক ভদ্রতা নয়; এটি কথা, রাগ, তর্ক ও আচরণে প্রকাশ পায়।"},"teachings":["হক হলেও অপ্রয়োজনীয় তর্ক ছেড়ে দেওয়া উত্তম কাজ।","মজা করেও মিথ্যা বলা থেকে বাঁচতে হবে।","সুন্দর চরিত্র জান্নাতের বড় ফজিলতের কারণ।","সত্য কথা বলার সঙ্গে নম্র আচরণও দরকার।"],"related_hadiths":[{"id":"4800","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"2004","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বায়আত ও বড় গুনাহ থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, চুরি, যেনা, সন্তান হত্যা, অপবাদ ও অবাধ্যতা থেকে দূরে থাকার বায়আতের শিক্ষা এসেছে।"},"heading":{"title":"বায়আতের শর্ত ও বড় গুনাহ থেকে বাঁচার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সাহাবীদের কাছ থেকে বায়আত নেন। তিনি বলেন, তারা যেন আল্লাহর সঙ্গে কাউকে শরীক না করে, চুরি না করে, যেনা না করে, সন্তান হত্যা না করে, কারও প্রতি অপবাদ না দেয় এবং শরীআতসম্মত বিষয়ে অবাধ্যতা না করে। এরপর তিনি জানান, যে এসব অঙ্গীকার পূর্ণ করবে, তার পুরস্কার আল্লাহর কাছে। কেউ যদি কোনো অপরাধ করে এবং দুনিয়াতে শাস্তি পায়, তা তার জন্য কাফফারা হতে পারে। আর আল্লাহ যদি তা ঢেকে রাখেন, তাহলে বিষয়টি আল্লাহর ইচ্ছার উপর। এই হাদিসে বায়আত, তাওহীদ, নৈতিকতা, অপরাধ থেকে বাঁচা এবং আল্লাহর বিচার—সব মিলিয়ে দায়িত্বশীল জীবনের শিক্ষা আছে।"},"teachings":["শিরক, চুরি, যেনা, অপবাদ ও অন্যায় থেকে দূরে থাকা জরুরি।","শরীআতসম্মত বিষয়ে অবাধ্যতা করা ঠিক নয়।","অঙ্গীকার পূরণ করলে প্রতিদান আল্লাহর কাছে।","গুনাহের বিচার আল্লাহর ইচ্ছা ও ন্যায়ের সঙ্গে জড়িত।"],"related_hadiths":[{"id":"1৮","book_id":"1","label":"Sahih Bukhari"},{"id":"170৯","book_id":"2","label":"Sahih Muslim"},{"id":"1৮","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বায়আত ও বড় গুনাহ থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, চুরি, যেনা, সন্তান হত্যা, অপবাদ ও অবাধ্যতা থেকে দূরে থাকার বায়আতের শিক্ষা এসেছে।"},"heading":{"title":"বায়আতের শর্ত ও বড় গুনাহ থেকে বাঁচার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সাহাবীদের কাছ থেকে বায়আত নেন। তিনি বলেন, তারা যেন আল্লাহর সঙ্গে কাউকে শরীক না করে, চুরি না করে, যেনা না করে, সন্তান হত্যা না করে, কারও প্রতি অপবাদ না দেয় এবং শরীআতসম্মত বিষয়ে অবাধ্যতা না করে। এরপর তিনি জানান, যে এসব অঙ্গীকার পূর্ণ করবে, তার পুরস্কার আল্লাহর কাছে। কেউ যদি কোনো অপরাধ করে এবং দুনিয়াতে শাস্তি পায়, তা তার জন্য কাফফারা হতে পারে। আর আল্লাহ যদি তা ঢেকে রাখেন, তাহলে বিষয়টি আল্লাহর ইচ্ছার উপর। এই হাদিসে বায়আত, তাওহীদ, নৈতিকতা, অপরাধ থেকে বাঁচা এবং আল্লাহর বিচার—সব মিলিয়ে দায়িত্বশীল জীবনের শিক্ষা আছে।"},"teachings":["শিরক, চুরি, যেনা, অপবাদ ও অন্যায় থেকে দূরে থাকা জরুরি।","শরীআতসম্মত বিষয়ে অবাধ্যতা করা ঠিক নয়।","অঙ্গীকার পূরণ করলে প্রতিদান আল্লাহর কাছে।","গুনাহের বিচার আল্লাহর ইচ্ছা ও ন্যায়ের সঙ্গে জড়িত।"],"related_hadiths":[{"id":"18","book_id":"1","label":"Sahih Bukhari"},{"id":"1709","book_id":"2","label":"Sahih Muslim"},{"id":"18","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত, সত্য, চরিত্র ও বৈধ রুজি","description":"$book_name$ $hadith_number$ - $chapter_name$. চারটি গুণ—আমানত, সত্য কথা, সুন্দর চরিত্র ও বৈধ রুজি—নিয়ে নবীজির গভীর শিক্ষা জানুন।"},"heading":{"title":"চারটি গুণের হাদিস: আমানত, সত্যবাদিতা, সুন্দর চরিত্র ও বৈধ রুজি","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম চারটি জিনিসের কথা বলেছেন। এগুলো মানুষের জীবনে থাকলে দুনিয়ার অনেক কিছু হারালেও তার বড় ক্ষতি নেই—এমন শিক্ষা এসেছে। চারটি গুণ হলো আমানত রক্ষা করা, সত্য কথা বলা, সুন্দর চরিত্র রাখা এবং বৈধ রুজি গ্রহণ করা। এই চারটি বিষয় ব্যক্তিগত জীবন, পরিবার, ব্যবসা ও সমাজ—সব জায়গায় দরকার। আমানত মানুষকে বিশ্বাসযোগ্য করে, সত্য কথা তাকে পরিষ্কার রাখে, সুন্দর চরিত্র তাকে প্রিয় করে, আর বৈধ রুজি তার জীবনকে পবিত্র পথে রাখে। হাদিসটি খুব সহজ ভাষায় সফল মুসলিম জীবনের একটি নীতিমালা দেয়।"},"teachings":["আমানত রক্ষা মানুষকে বিশ্বাসযোগ্য করে।","সত্য কথা বলা মুমিনের বড় গুণ।","সুন্দর চরিত্র মানুষের সাথে সম্পর্ক ভালো রাখে।","বৈধ রুজি গ্রহণ করা জীবনের নিরাপদ পথ।"],"related_hadiths":[{"id":"60৯4","book_id":"1","label":"Sahih Bukhari"},{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"2004","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত, সত্য, চরিত্র ও বৈধ রুজি","description":"$book_name$ $hadith_number$ - $chapter_name$. চারটি গুণ—আমানত, সত্য কথা, সুন্দর চরিত্র ও বৈধ রুজি—নিয়ে নবীজির গভীর শিক্ষা জানুন।"},"heading":{"title":"চারটি গুণের হাদিস: আমানত, সত্যবাদিতা, সুন্দর চরিত্র ও বৈধ রুজি","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম চারটি জিনিসের কথা বলেছেন। এগুলো মানুষের জীবনে থাকলে দুনিয়ার অনেক কিছু হারালেও তার বড় ক্ষতি নেই—এমন শিক্ষা এসেছে। চারটি গুণ হলো আমানত রক্ষা করা, সত্য কথা বলা, সুন্দর চরিত্র রাখা এবং বৈধ রুজি গ্রহণ করা। এই চারটি বিষয় ব্যক্তিগত জীবন, পরিবার, ব্যবসা ও সমাজ—সব জায়গায় দরকার। আমানত মানুষকে বিশ্বাসযোগ্য করে, সত্য কথা তাকে পরিষ্কার রাখে, সুন্দর চরিত্র তাকে প্রিয় করে, আর বৈধ রুজি তার জীবনকে পবিত্র পথে রাখে। হাদিসটি খুব সহজ ভাষায় সফল মুসলিম জীবনের একটি নীতিমালা দেয়।"},"teachings":["আমানত রক্ষা মানুষকে বিশ্বাসযোগ্য করে।","সত্য কথা বলা মুমিনের বড় গুণ।","সুন্দর চরিত্র মানুষের সাথে সম্পর্ক ভালো রাখে।","বৈধ রুজি গ্রহণ করা জীবনের নিরাপদ পথ।"],"related_hadiths":[{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"2004","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহ ছাড়ুন, সত্যে শান্তি খুঁজুন","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহযুক্ত কথা ও কাজ ছেড়ে সত্যের শান্তি এবং মিথ্যার অশান্তি বুঝে চলার শিক্ষা নিন।"},"heading":{"title":"সত্যে প্রশান্তি, মিথ্যায় অশান্তি: সন্দেহ ছাড়ার হাদিস","description":"এই হাদিসে বলা হয়েছে, সন্দেহযুক্ত কথা ও কাজ ছেড়ে এমন দিকে ফিরে যেতে, যেখানে সন্দেহ নেই। এরপর বলা হয়েছে, সত্য প্রশান্তির নাম এবং মিথ্যা সন্দেহ ও অশান্তির নাম। এখানে সত্যবাদিতা শুধু মুখের কথা নয়; কাজের ক্ষেত্রেও সত্যের পথ বেছে নেওয়ার কথা আছে। যখন কোনো কথা, লেনদেন বা কাজ অন্তরে অস্বস্তি আনে, তখন তা নিয়ে থেমে ভাবা দরকার। মুমিনের জীবন এমন হওয়া উচিত, যেখানে কথা ও কাজে স্বচ্ছতা থাকে। মিথ্যা কিছু সময় সুবিধা দিলেও অন্তরে অস্থিরতা আনে। তাই এই হাদিস মানুষকে সহজ, সৎ ও শান্ত পথের দিকে ডাকছে।"},"teachings":["সন্দেহযুক্ত কথা ও কাজ ছেড়ে দেওয়া উচিত।","সত্য অন্তরে প্রশান্তি আনে।","মিথ্যা সন্দেহ ও অশান্তির কারণ হয়।","কথা ও কাজ—দুটোতেই সততা দরকার।"],"related_hadiths":[{"id":"60৯4","book_id":"1","label":"Sahih Bukhari"},{"id":"2607","book_id":"2","label":"Sahih Muslim"},{"id":"52","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহ ছাড়ুন, সত্যে শান্তি খুঁজুন","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহযুক্ত কথা ও কাজ ছেড়ে সত্যের শান্তি এবং মিথ্যার অশান্তি বুঝে চলার শিক্ষা নিন।"},"heading":{"title":"সত্যে প্রশান্তি, মিথ্যায় অশান্তি: সন্দেহ ছাড়ার হাদিস","description":"এই হাদিসে বলা হয়েছে, সন্দেহযুক্ত কথা ও কাজ ছেড়ে এমন দিকে ফিরে যেতে, যেখানে সন্দেহ নেই। এরপর বলা হয়েছে, সত্য প্রশান্তির নাম এবং মিথ্যা সন্দেহ ও অশান্তির নাম। এখানে সত্যবাদিতা শুধু মুখের কথা নয়; কাজের ক্ষেত্রেও সত্যের পথ বেছে নেওয়ার কথা আছে। যখন কোনো কথা, লেনদেন বা কাজ অন্তরে অস্বস্তি আনে, তখন তা নিয়ে থেমে ভাবা দরকার। মুমিনের জীবন এমন হওয়া উচিত, যেখানে কথা ও কাজে স্বচ্ছতা থাকে। মিথ্যা কিছু সময় সুবিধা দিলেও অন্তরে অস্থিরতা আনে। তাই এই হাদিস মানুষকে সহজ, সৎ ও শান্ত পথের দিকে ডাকছে।"},"teachings":["সন্দেহযুক্ত কথা ও কাজ ছেড়ে দেওয়া উচিত।","সত্য অন্তরে প্রশান্তি আনে।","মিথ্যা সন্দেহ ও অশান্তির কারণ হয়।","কথা ও কাজ—দুটোতেই সততা দরকার।"],"related_hadiths":[{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"2607","book_id":"2","label":"Sahih Muslim"},{"id":"52","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হিংসামুক্ত অন্তর ও সত্য ভাষার মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. উত্তম মানুষের পরিচয়ে সত্য ভাষা, পরহেযগার অন্তর ও হিংসা থেকে মুক্ত থাকার শিক্ষা জানুন।"},"heading":{"title":"হিংসামুক্ত অন্তর ও সত্য ভাষা: উত্তম মানুষের পরিচয়","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লামকে জিজ্ঞেস করা হলো, সবচেয়ে ভাল মানুষ কে? উত্তরে তিনি বললেন, যে ব্যক্তি হিংসা-বিদ্বেষ মুক্ত অন্তরের অধিকারী এবং সত্য কথার অধিকারী। সাহাবীগণ সত্য ভাষা বুঝলেন, কিন্তু হিংসা-বিদ্বেষ মুক্ত অন্তরের ব্যাখ্যা জানতে চাইলেন। তখন তিনি বললেন, সে ব্যক্তি স্বচ্ছ ও পরহেযগার; যার মধ্যে পাপ, সীমালংঘন, খিয়ানত ও হিংসা নেই। এই হাদিস আমাদের বাহ্যিক ভালো কাজের পাশাপাশি অন্তরের পরিচ্ছন্নতার দিকে ডাকে। শুধু মুখে সত্য বললেই শেষ নয়; অন্তর থেকেও হিংসা, খিয়ানত ও অন্যায় দূর করার চেষ্টা করতে হয়।"},"teachings":["সত্য ভাষা উত্তম মানুষের গুণ।","হিংসা-বিদ্বেষ মুক্ত অন্তর মুমিনের বড় সৌন্দর্য।","খিয়ানত ও সীমালংঘন থেকে দূরে থাকা দরকার।","ভালো মানুষ হতে অন্তর ও ভাষা—দুটোই ঠিক রাখা জরুরি।"],"related_hadiths":[{"id":"4216","book_id":"6","label":"Sunan Ibn Majah"},{"id":"৯1","book_id":"2","label":"Sahih Muslim"},{"id":"60৯4","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হিংসামুক্ত অন্তর ও সত্য ভাষার মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. উত্তম মানুষের পরিচয়ে সত্য ভাষা, পরহেযগার অন্তর ও হিংসা থেকে মুক্ত থাকার শিক্ষা জানুন।"},"heading":{"title":"হিংসামুক্ত অন্তর ও সত্য ভাষা: উত্তম মানুষের পরিচয়","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লামকে জিজ্ঞেস করা হলো, সবচেয়ে ভাল মানুষ কে? উত্তরে তিনি বললেন, যে ব্যক্তি হিংসা-বিদ্বেষ মুক্ত অন্তরের অধিকারী এবং সত্য কথার অধিকারী। সাহাবীগণ সত্য ভাষা বুঝলেন, কিন্তু হিংসা-বিদ্বেষ মুক্ত অন্তরের ব্যাখ্যা জানতে চাইলেন। তখন তিনি বললেন, সে ব্যক্তি স্বচ্ছ ও পরহেযগার; যার মধ্যে পাপ, সীমালংঘন, খিয়ানত ও হিংসা নেই। এই হাদিস আমাদের বাহ্যিক ভালো কাজের পাশাপাশি অন্তরের পরিচ্ছন্নতার দিকে ডাকে। শুধু মুখে সত্য বললেই শেষ নয়; অন্তর থেকেও হিংসা, খিয়ানত ও অন্যায় দূর করার চেষ্টা করতে হয়।"},"teachings":["সত্য ভাষা উত্তম মানুষের গুণ।","হিংসা-বিদ্বেষ মুক্ত অন্তর মুমিনের বড় সৌন্দর্য।","খিয়ানত ও সীমালংঘন থেকে দূরে থাকা দরকার।","ভালো মানুষ হতে অন্তর ও ভাষা—দুটোই ঠিক রাখা জরুরি।"],"related_hadiths":[{"id":"4216","book_id":"6","label":"Sunan Ibn Majah"},{"id":"91","book_id":"2","label":"Sahih Muslim"},{"id":"6094","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সত্য নেকীর পথে, মিথ্যা পাপের পথে","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য গ্রহণ ও মিথ্যা থেকে বাঁচার মাধ্যমে নেকী ও পাপের পথ বুঝে চলার শিক্ষা জানুন।"},"heading":{"title":"সত্য নেকীর সাথে, মিথ্যা পাপের সাথে: নবীজির সরল শিক্ষা","description":"এই হাদিসে সত্য ও মিথ্যার পথ খুব পরিষ্কার করে বলা হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, সত্য গ্রহণ কর; কারণ সত্য নেকীর সাথে রয়েছে। আর মিথ্যা থেকে বেঁচে থাক; কারণ মিথ্যা পাপের সাথে রয়েছে। এখানে সত্যকে শুধু ভালো অভ্যাস বলা হয়নি; বরং তা নেকীর পথে নিয়ে যায় বলা হয়েছে। আবার মিথ্যাকে ছোট ভুল হিসেবে দেখা হয়নি; তা পাপের সাথে যুক্ত বলা হয়েছে। তাই একজন মুমিনের কথা, প্রতিশ্রুতি, লেনদেন ও সম্পর্ক—সব জায়গায় সত্য দরকার। মিথ্যা সাময়িক সুবিধা দিলেও মানুষকে খারাপ পথে টেনে নিতে পারে।"},"teachings":["সত্য নেকীর পথে নিয়ে যায়।","মিথ্যা পাপের সাথে যুক্ত।","কথা ও লেনদেনে সত্যবাদিতা রাখা জরুরি।","মিথ্যাকে ছোট ভুল ভেবে অবহেলা করা উচিত নয়।"],"related_hadiths":[{"id":"60৯4","book_id":"1","label":"Sahih Bukhari"},{"id":"2607","book_id":"2","label":"Sahih Muslim"},{"id":"251৮","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সত্য নেকীর পথে, মিথ্যা পাপের পথে","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য গ্রহণ ও মিথ্যা থেকে বাঁচার মাধ্যমে নেকী ও পাপের পথ বুঝে চলার শিক্ষা জানুন।"},"heading":{"title":"সত্য নেকীর সাথে, মিথ্যা পাপের সাথে: নবীজির সরল শিক্ষা","description":"এই হাদিসে সত্য ও মিথ্যার পথ খুব পরিষ্কার করে বলা হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, সত্য গ্রহণ কর; কারণ সত্য নেকীর সাথে রয়েছে। আর মিথ্যা থেকে বেঁচে থাক; কারণ মিথ্যা পাপের সাথে রয়েছে। এখানে সত্যকে শুধু ভালো অভ্যাস বলা হয়নি; বরং তা নেকীর পথে নিয়ে যায় বলা হয়েছে। আবার মিথ্যাকে ছোট ভুল হিসেবে দেখা হয়নি; তা পাপের সাথে যুক্ত বলা হয়েছে। তাই একজন মুমিনের কথা, প্রতিশ্রুতি, লেনদেন ও সম্পর্ক—সব জায়গায় সত্য দরকার। মিথ্যা সাময়িক সুবিধা দিলেও মানুষকে খারাপ পথে টেনে নিতে পারে।"},"teachings":["সত্য নেকীর পথে নিয়ে যায়।","মিথ্যা পাপের সাথে যুক্ত।","কথা ও লেনদেনে সত্যবাদিতা রাখা জরুরি।","মিথ্যাকে ছোট ভুল ভেবে অবহেলা করা উচিত নয়।"],"related_hadiths":[{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"2607","book_id":"2","label":"Sahih Muslim"},{"id":"2518","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মিথ্যা ঈমানকে ক্ষতিগ্রস্ত করে","description":"$book_name$ $hadith_number$ - $chapter_name$. মিথ্যা থেকে বেঁচে থাকার গুরুত্ব এবং ঈমানের সাথে সত্যবাদিতার সম্পর্ক বুঝে নিন।"},"heading":{"title":"মিথ্যা থেকে বাঁচার হাদিস: ঈমানের জন্য সততার প্রয়োজন","description":"এই বর্ণনায় মিথ্যা থেকে বেঁচে থাকার কঠিন সতর্কতা এসেছে। বলা হয়েছে, মিথ্যা ঈমানকে ক্ষতিগ্রস্ত করে। কথাটি ছোট হলেও খুব গভীর। অনেক সময় মানুষ মিথ্যাকে হালকা ভাবে নেয়—মজা করে, সুবিধার জন্য, লজ্জা ঢাকতে বা সম্পর্ক বাঁচাতে। কিন্তু হাদিসের শিক্ষা হলো, মিথ্যা মানুষের ভেতরের ঈমানি শক্তিকে দুর্বল করে। সত্য বলা সব সময় সহজ না-ও হতে পারে, কিন্তু মিথ্যার পথে অভ্যাস তৈরি হলে তা চরিত্রকে নষ্ট করে। তাই মুমিনের জন্য সত্যবাদিতা শুধু সামাজিক ভালো গুণ নয়; এটি ঈমান রক্ষার সাথে জড়িত একটি বড় বিষয়।"},"teachings":["মিথ্যা ঈমানের ক্ষতির কারণ হতে পারে।","মিথ্যাকে ছোট বা হালকা বিষয় ভাবা উচিত নয়।","সত্যবাদিতা ঈমানি চরিত্রের অংশ।","সুবিধার জন্য মিথ্যা বলা থেকে বাঁচতে হবে।"],"related_hadiths":[{"id":"60৯4","book_id":"1","label":"Sahih Bukhari"},{"id":"2607","book_id":"2","label":"Sahih Muslim"},{"id":"4৯৯0","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মিথ্যা ঈমানকে ক্ষতিগ্রস্ত করে","description":"$book_name$ $hadith_number$ - $chapter_name$. মিথ্যা থেকে বেঁচে থাকার গুরুত্ব এবং ঈমানের সাথে সত্যবাদিতার সম্পর্ক বুঝে নিন।"},"heading":{"title":"মিথ্যা থেকে বাঁচার হাদিস: ঈমানের জন্য সততার প্রয়োজন","description":"এই বর্ণনায় মিথ্যা থেকে বেঁচে থাকার কঠিন সতর্কতা এসেছে। বলা হয়েছে, মিথ্যা ঈমানকে ক্ষতিগ্রস্ত করে। কথাটি ছোট হলেও খুব গভীর। অনেক সময় মানুষ মিথ্যাকে হালকা ভাবে নেয়—মজা করে, সুবিধার জন্য, লজ্জা ঢাকতে বা সম্পর্ক বাঁচাতে। কিন্তু হাদিসের শিক্ষা হলো, মিথ্যা মানুষের ভেতরের ঈমানি শক্তিকে দুর্বল করে। সত্য বলা সব সময় সহজ না-ও হতে পারে, কিন্তু মিথ্যার পথে অভ্যাস তৈরি হলে তা চরিত্রকে নষ্ট করে। তাই মুমিনের জন্য সত্যবাদিতা শুধু সামাজিক ভালো গুণ নয়; এটি ঈমান রক্ষার সাথে জড়িত একটি বড় বিষয়।"},"teachings":["মিথ্যা ঈমানের ক্ষতির কারণ হতে পারে।","মিথ্যাকে ছোট বা হালকা বিষয় ভাবা উচিত নয়।","সত্যবাদিতা ঈমানি চরিত্রের অংশ।","সুবিধার জন্য মিথ্যা বলা থেকে বাঁচতে হবে।"],"related_hadiths":[{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"2607","book_id":"2","label":"Sahih Muslim"},{"id":"4990","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিশুকে মিথ্যা প্রতিশ্রুতি না দেওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুকে “আসো নাও” বলে কিছু না দিলে সেটিও মিথ্যা—এই নববী শিক্ষা জানুন।"},"heading":{"title":"শিশুকে মিথ্যা কথা নয়: ছোট প্রতিশ্রুতিতেও সত্যের শিক্ষা","description":"এই হাদিসে শিশুদের সাথে সত্যবাদিতার শিক্ষা এসেছে। কেউ যদি বাচ্চাকে বলে, “আসো নাও”, কিন্তু পরে তাকে কিছু না দেয়, তাহলে সেটিকে মিথ্যা বলা হয়েছে। এতে বোঝা যায়, শিশুর সাথে কথাবার্তাও দ্বীনের বাইরে নয়। অনেক সময় বড়রা শিশুকে শান্ত করার জন্য বা কাছে ডাকার জন্য এমন কথা বলে যা পরে রাখে না। হাদিসটি শেখায়, শিশুকে ছোট মনে করে তার সাথে মিথ্যা বলা ঠিক নয়। কারণ শিশু বড়দের কথায় বিশ্বাস করতে শেখে। যদি বড়রা কথা না রাখে, তাহলে শিশুর মনেও মিথ্যার স্বাভাবিক ধারণা তৈরি হতে পারে। তাই সন্তানের সামনে সত্য কথা ও কথা রাখার অভ্যাস জরুরি।"},"teachings":["শিশুকে মিথ্যা প্রতিশ্রুতি দেওয়া থেকে বাঁচতে হবে।","ছোট কথাতেও সত্যবাদিতা দরকার।","বড়দের আচরণ শিশুদের শেখার মাধ্যম।","কথা দিলে তা রাখার চেষ্টা করা উচিত।"],"related_hadiths":[{"id":"4৯৯1","book_id":"4","label":"Sunan Abu Dawud"},{"id":"60৯4","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিশুকে মিথ্যা প্রতিশ্রুতি না দেওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুকে “আসো নাও” বলে কিছু না দিলে সেটিও মিথ্যা—এই নববী শিক্ষা জানুন।"},"heading":{"title":"শিশুকে মিথ্যা কথা নয়: ছোট প্রতিশ্রুতিতেও সত্যের শিক্ষা","description":"এই হাদিসে শিশুদের সাথে সত্যবাদিতার শিক্ষা এসেছে। কেউ যদি বাচ্চাকে বলে, “আসো নাও”, কিন্তু পরে তাকে কিছু না দেয়, তাহলে সেটিকে মিথ্যা বলা হয়েছে। এতে বোঝা যায়, শিশুর সাথে কথাবার্তাও দ্বীনের বাইরে নয়। অনেক সময় বড়রা শিশুকে শান্ত করার জন্য বা কাছে ডাকার জন্য এমন কথা বলে যা পরে রাখে না। হাদিসটি শেখায়, শিশুকে ছোট মনে করে তার সাথে মিথ্যা বলা ঠিক নয়। কারণ শিশু বড়দের কথায় বিশ্বাস করতে শেখে। যদি বড়রা কথা না রাখে, তাহলে শিশুর মনেও মিথ্যার স্বাভাবিক ধারণা তৈরি হতে পারে। তাই সন্তানের সামনে সত্য কথা ও কথা রাখার অভ্যাস জরুরি।"},"teachings":["শিশুকে মিথ্যা প্রতিশ্রুতি দেওয়া থেকে বাঁচতে হবে।","ছোট কথাতেও সত্যবাদিতা দরকার।","বড়দের আচরণ শিশুদের শেখার মাধ্যম।","কথা দিলে তা রাখার চেষ্টা করা উচিত।"],"related_hadiths":[{"id":"4991","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6094","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্তানকে দেওয়া কথাও রাখতে হবে","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুকে কিছু দেওয়ার কথা বলে না দিলে মিথ্যা লেখা হয়—এই শিক্ষামূলক হাদিস পড়ুন।"},"heading":{"title":"সন্তানকে দেওয়া প্রতিশ্রুতি: খেজুরের ঘটনায় সত্যবাদিতার শিক্ষা","description":"এই হাদিসে একটি ঘরোয়া ঘটনা এসেছে। আবদুল্লাহ ইবনে আমির রাদিয়াল্লাহু আনহুকে তাঁর মা ডাকলেন এবং বললেন, আসো, তোমাকে কিছু দেব। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম তখন তাঁদের ঘরে ছিলেন। তিনি জিজ্ঞেস করলেন, তুমি তাকে কী দিতে চাও? মা বললেন, খেজুর দেব। তখন নবীজি জানালেন, যদি কিছু না দাও, তবে তা মিথ্যা হিসেবে লেখা হবে। এই হাদিস আমাদের শেখায়, সন্তানকে দেওয়া ছোট প্রতিশ্রুতিও হালকা নয়। মা-বাবা যদি কথা রাখে, শিশু সত্য ও আস্থার পরিবেশে বড় হয়। আর কথা না রাখলে শিশুর মনেও মিথ্যা সহজ হয়ে যেতে পারে।"},"teachings":["সন্তানকে দেওয়া কথাও গুরুত্বের সাথে রাখা দরকার।","শিশুকে ডাকার জন্য মিথ্যা বলা উচিত নয়।","ছোট প্রতিশ্রুতিও মিথ্যা বা সত্যের অংশ হতে পারে।","মা-বাবার সত্যবাদিতা সন্তানের চরিত্র গঠনে সাহায্য করে।"],"related_hadiths":[{"id":"4৯৯1","book_id":"4","label":"Sunan Abu Dawud"},{"id":"60৯4","book_id":"1","label":"Sahih Bukhari"},{"id":"4৯৯0","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্তানকে দেওয়া কথাও রাখতে হবে","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুকে কিছু দেওয়ার কথা বলে না দিলে মিথ্যা লেখা হয়—এই শিক্ষামূলক হাদিস পড়ুন।"},"heading":{"title":"সন্তানকে দেওয়া প্রতিশ্রুতি: খেজুরের ঘটনায় সত্যবাদিতার শিক্ষা","description":"এই হাদিসে একটি ঘরোয়া ঘটনা এসেছে। আবদুল্লাহ ইবনে আমির রাদিয়াল্লাহু আনহুকে তাঁর মা ডাকলেন এবং বললেন, আসো, তোমাকে কিছু দেব। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম তখন তাঁদের ঘরে ছিলেন। তিনি জিজ্ঞেস করলেন, তুমি তাকে কী দিতে চাও? মা বললেন, খেজুর দেব। তখন নবীজি জানালেন, যদি কিছু না দাও, তবে তা মিথ্যা হিসেবে লেখা হবে। এই হাদিস আমাদের শেখায়, সন্তানকে দেওয়া ছোট প্রতিশ্রুতিও হালকা নয়। মা-বাবা যদি কথা রাখে, শিশু সত্য ও আস্থার পরিবেশে বড় হয়। আর কথা না রাখলে শিশুর মনেও মিথ্যা সহজ হয়ে যেতে পারে।"},"teachings":["সন্তানকে দেওয়া কথাও গুরুত্বের সাথে রাখা দরকার।","শিশুকে ডাকার জন্য মিথ্যা বলা উচিত নয়।","ছোট প্রতিশ্রুতিও মিথ্যা বা সত্যের অংশ হতে পারে।","মা-বাবার সত্যবাদিতা সন্তানের চরিত্র গঠনে সাহায্য করে।"],"related_hadiths":[{"id":"4991","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"4990","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হাসানোর জন্য মিথ্যা বলার ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মানুষকে হাসানোর জন্য মিথ্যা বলা নিয়ে নবীজির কঠিন সতর্ক বাণী জানুন।"},"heading":{"title":"হাসানোর জন্য মিথ্যা বলা: মজার কথাতেও সত্যের গুরুত্ব","description":"এই হাদিসে সেই ব্যক্তির জন্য কঠিন সতর্কতা এসেছে, যে মানুষকে হাসানোর জন্য মিথ্যা কথা বলে। নবীজি বলেছেন, তার জন্য ধ্বংস, তার জন্য ধ্বংস। কথাটি আমাদের দৈনন্দিন জীবনের একটি সাধারণ ভুল ধরিয়ে দেয়। অনেক সময় আড্ডা, গল্প, বক্তৃতা বা অনলাইনে মানুষ হাসানোর জন্য বানানো কথা বলে। কেউ ভাবতে পারে, এটি তো শুধু মজা। কিন্তু হাদিস দেখাচ্ছে, মজার নামেও মিথ্যা হালকা নয়। সত্যবাদিতা শুধু গুরুতর আলোচনায় দরকার নয়; হাসি-ঠাট্টাতেও দরকার। মুমিনের কথা এমন হওয়া উচিত, যাতে মানুষ আনন্দ পেলেও মিথ্যা বা ধোঁকার ওপর দাঁড়িয়ে না থাকে।"},"teachings":["মানুষকে হাসানোর জন্য মিথ্যা বলা থেকে বাঁচতে হবে।","মজা করেও মিথ্যা বলা হালকা বিষয় নয়।","আড্ডা ও গল্পেও সত্যবাদিতা দরকার।","কথার মাধ্যমে মানুষকে আনন্দ দিতে হলে মিথ্যা ছাড়াই দেওয়া উচিত।"],"related_hadiths":[{"id":"4৯৯0","book_id":"4","label":"Sunan Abu Dawud"},{"id":"60৯4","book_id":"1","label":"Sahih Bukhari"},{"id":"4৮00","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হাসানোর জন্য মিথ্যা বলার ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মানুষকে হাসানোর জন্য মিথ্যা বলা নিয়ে নবীজির কঠিন সতর্ক বাণী জানুন।"},"heading":{"title":"হাসানোর জন্য মিথ্যা বলা: মজার কথাতেও সত্যের গুরুত্ব","description":"এই হাদিসে সেই ব্যক্তির জন্য কঠিন সতর্কতা এসেছে, যে মানুষকে হাসানোর জন্য মিথ্যা কথা বলে। নবীজি বলেছেন, তার জন্য ধ্বংস, তার জন্য ধ্বংস। কথাটি আমাদের দৈনন্দিন জীবনের একটি সাধারণ ভুল ধরিয়ে দেয়। অনেক সময় আড্ডা, গল্প, বক্তৃতা বা অনলাইনে মানুষ হাসানোর জন্য বানানো কথা বলে। কেউ ভাবতে পারে, এটি তো শুধু মজা। কিন্তু হাদিস দেখাচ্ছে, মজার নামেও মিথ্যা হালকা নয়। সত্যবাদিতা শুধু গুরুতর আলোচনায় দরকার নয়; হাসি-ঠাট্টাতেও দরকার। মুমিনের কথা এমন হওয়া উচিত, যাতে মানুষ আনন্দ পেলেও মিথ্যা বা ধোঁকার ওপর দাঁড়িয়ে না থাকে।"},"teachings":["মানুষকে হাসানোর জন্য মিথ্যা বলা থেকে বাঁচতে হবে।","মজা করেও মিথ্যা বলা হালকা বিষয় নয়।","আড্ডা ও গল্পেও সত্যবাদিতা দরকার।","কথার মাধ্যমে মানুষকে আনন্দ দিতে হলে মিথ্যা ছাড়াই দেওয়া উচিত।"],"related_hadiths":[{"id":"4990","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"4800","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর কঠিন পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. বৃদ্ধ ব্যভিচারী, মিথ্যুক শাসক ও অহংকারী গরীব সম্পর্কে কিয়ামতের কঠিন সতর্কতা জানুন।"},"heading":{"title":"মিথ্যুক শাসকসহ তিন শ্রেণীর মানুষের কঠিন সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের কথা এসেছে, যাদের ব্যাপারে কিয়ামতের দিন কঠিন সতর্কতা দেওয়া হয়েছে। তারা হলো বৃদ্ধ ব্যভিচারকারী, মিথ্যুক শাসক এবং অহংকারী গরীব। হাদিসে বলা হয়েছে, আল্লাহ তাদের সাথে কথা বলবেন না, তাদের পবিত্র করবেন না, দয়ার দৃষ্টিতে তাকাবেন না এবং তাদের জন্য কষ্টদায়ক শাস্তি রয়েছে। এখানে বিশেষভাবে মিথ্যুক শাসকের কথা আমাদের দায়িত্ব ও ক্ষমতার জায়গায় সত্যের গুরুত্ব বুঝায়। যার হাতে নেতৃত্ব বা ক্ষমতা আছে, তার মিথ্যা শুধু নিজের ক্ষতি করে না; অন্যদেরও ক্ষতিগ্রস্ত করতে পারে। আর অহংকার ও পাপ যেকোন অবস্থায় ভয়ংকর বিষয়।"},"teachings":["মিথ্যুক শাসকের বিষয়ে হাদিসে কঠিন সতর্কতা এসেছে।","ক্ষমতা থাকলে সত্যবাদিতা আরও বেশি জরুরি।","অহংকার ও পাপ মানুষকে কঠিন পরিণতির দিকে নিতে পারে।","বয়স, পদ বা দারিদ্র্য কোনো পাপকে হালকা করে না।"],"related_hadiths":[{"id":"107","book_id":"2","label":"Sahih Muslim"},{"id":"60৯4","book_id":"1","label":"Sahih Bukhari"},{"id":"৯1","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর কঠিন পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. বৃদ্ধ ব্যভিচারী, মিথ্যুক শাসক ও অহংকারী গরীব সম্পর্কে কিয়ামতের কঠিন সতর্কতা জানুন।"},"heading":{"title":"মিথ্যুক শাসকসহ তিন শ্রেণীর মানুষের কঠিন সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের কথা এসেছে, যাদের ব্যাপারে কিয়ামতের দিন কঠিন সতর্কতা দেওয়া হয়েছে। তারা হলো বৃদ্ধ ব্যভিচারকারী, মিথ্যুক শাসক এবং অহংকারী গরীব। হাদিসে বলা হয়েছে, আল্লাহ তাদের সাথে কথা বলবেন না, তাদের পবিত্র করবেন না, দয়ার দৃষ্টিতে তাকাবেন না এবং তাদের জন্য কষ্টদায়ক শাস্তি রয়েছে। এখানে বিশেষভাবে মিথ্যুক শাসকের কথা আমাদের দায়িত্ব ও ক্ষমতার জায়গায় সত্যের গুরুত্ব বুঝায়। যার হাতে নেতৃত্ব বা ক্ষমতা আছে, তার মিথ্যা শুধু নিজের ক্ষতি করে না; অন্যদেরও ক্ষতিগ্রস্ত করতে পারে। আর অহংকার ও পাপ যেকোন অবস্থায় ভয়ংকর বিষয়।"},"teachings":["মিথ্যুক শাসকের বিষয়ে হাদিসে কঠিন সতর্কতা এসেছে।","ক্ষমতা থাকলে সত্যবাদিতা আরও বেশি জরুরি।","অহংকার ও পাপ মানুষকে কঠিন পরিণতির দিকে নিতে পারে।","বয়স, পদ বা দারিদ্র্য কোনো পাপকে হালকা করে না।"],"related_hadiths":[{"id":"107","book_id":"2","label":"Sahih Muslim"},{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"91","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দুই মুখের মানুষের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. দুনিয়ায় দ্বিমুখী আচরণকারীর কিয়ামতের ভয়াবহ পরিণতি সম্পর্কে হাদিসের শিক্ষা জানুন।"},"heading":{"title":"দ্বিমুখী চরিত্রের হাদিস: এক মুখে এক কথা, আরেক মুখে আরেক কথা নয়","description":"এই হাদিসে বলা হয়েছে, যার দুনিয়াতে দু’টি মুখ হবে, কিয়ামতের মাঠে তার মুখে আগুনের দু’টি জিহ্বা হবে। অর্থাৎ যে মানুষ একদলের সামনে এক কথা বলে, অন্য দলের সামনে উল্টো কথা বলে এবং মিথ্যা, চোগলখুরী বা পরনিন্দার মাধ্যমে সম্পর্ক নষ্ট করে—তার বিষয়ে কঠিন সতর্কতা এসেছে। দ্বিমুখী চরিত্র মানুষের আস্থা নষ্ট করে। এতে বন্ধু, পরিবার ও সমাজে ঝগড়া বাড়ে। মুমিনের কথা সোজা হওয়া উচিত। সে কারও সামনে এমন কথা বলবে না, যা অন্যের সামনে গিয়ে বদলে ফেলে। এই হাদিস আমাদের সত্যবাদী, পরিষ্কার এবং ভরসাযোগ্য হতে শেখায়।"},"teachings":["দ্বিমুখী আচরণের বিষয়ে হাদিসে কঠিন সতর্কতা এসেছে।","একজনের সামনে এক কথা, অন্যজনের সামনে আরেক কথা বলা ক্ষতিকর।","চোগলখুরী ও পরনিন্দা সম্পর্ক নষ্ট করে।","মুমিনের কথা পরিষ্কার ও বিশ্বাসযোগ্য হওয়া দরকার।"],"related_hadiths":[{"id":"4৮73","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6056","book_id":"1","label":"Sahih Bukhari"},{"id":"2606","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দুই মুখের মানুষের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. দুনিয়ায় দ্বিমুখী আচরণকারীর কিয়ামতের ভয়াবহ পরিণতি সম্পর্কে হাদিসের শিক্ষা জানুন।"},"heading":{"title":"দ্বিমুখী চরিত্রের হাদিস: এক মুখে এক কথা, আরেক মুখে আরেক কথা নয়","description":"এই হাদিসে বলা হয়েছে, যার দুনিয়াতে দু’টি মুখ হবে, কিয়ামতের মাঠে তার মুখে আগুনের দু’টি জিহ্বা হবে। অর্থাৎ যে মানুষ একদলের সামনে এক কথা বলে, অন্য দলের সামনে উল্টো কথা বলে এবং মিথ্যা, চোগলখুরী বা পরনিন্দার মাধ্যমে সম্পর্ক নষ্ট করে—তার বিষয়ে কঠিন সতর্কতা এসেছে। দ্বিমুখী চরিত্র মানুষের আস্থা নষ্ট করে। এতে বন্ধু, পরিবার ও সমাজে ঝগড়া বাড়ে। মুমিনের কথা সোজা হওয়া উচিত। সে কারও সামনে এমন কথা বলবে না, যা অন্যের সামনে গিয়ে বদলে ফেলে। এই হাদিস আমাদের সত্যবাদী, পরিষ্কার এবং ভরসাযোগ্য হতে শেখায়।"},"teachings":["দ্বিমুখী আচরণের বিষয়ে হাদিসে কঠিন সতর্কতা এসেছে।","একজনের সামনে এক কথা, অন্যজনের সামনে আরেক কথা বলা ক্ষতিকর।","চোগলখুরী ও পরনিন্দা সম্পর্ক নষ্ট করে।","মুমিনের কথা পরিষ্কার ও বিশ্বাসযোগ্য হওয়া দরকার।"],"related_hadiths":[{"id":"4873","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6056","book_id":"1","label":"Sahih Bukhari"},{"id":"2606","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবীরা গুনাহ থেকে বাঁচার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, হত্যা ও মিথ্যা কসম বা সাক্ষ্যের ভয়াবহতা বুঝুন।"},"heading":{"title":"কবীরা গুনাহ: শিরক, অবাধ্যতা, হত্যা ও মিথ্যার ভয়াবহ শিক্ষা","description":"এই হাদিসে বড় বড় কবীরা গুনাহের কয়েকটি স্পষ্ট উদাহরণ বলা হয়েছে। মূল বিষয় হলো, মানুষের ঈমান, পরিবার, জীবন ও কথার সততা—সবকিছু আল্লাহর কাছে গুরুত্বপূর্ণ। আল্লাহর সাথে কাউকে শরীক করা সবচেয়ে বড় অন্যায় হিসেবে এসেছে। এরপর পিতা-মাতার অবাধ্যতা বলা হয়েছে, যা পরিবার ও দায়িত্ববোধের সাথে জড়িত। কাউকে হত্যা করা মানুষের জীবনের অধিকার নষ্ট করে। আর মিথ্যা কসম বা মিথ্যা সাক্ষ্য মানুষের বিশ্বাস, বিচার ও সম্পর্ককে ক্ষতিগ্রস্ত করে। তাই এই হাদিস আমাদের শেখায়, বড় গুনাহ থেকে দূরে থাকতে হলে ঈমানকে শুদ্ধ রাখা, বাবা-মায়ের হক মানা, মানুষের জীবনকে সম্মান করা এবং কথায় সত্যবাদী থাকা জরুরি।"},"teachings":["আল্লাহর সাথে কাউকে শরীক করা বড় কবীরা গুনাহের অন্তর্ভুক্ত।","পিতা-মাতার অবাধ্যতা থেকে সতর্ক থাকা দরকার।","অন্যায়ভাবে কাউকে হত্যা করা ভয়াবহ গুনাহ।","মিথ্যা কসম ও মিথ্যা সাক্ষ্য মানুষের হক নষ্ট করতে পারে।"],"related_hadiths":[{"id":"161","book_id":"2","label":"Sahih Muslim"},{"id":"162","book_id":"2","label":"Sahih Muslim"},{"id":"6৮71","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবীরা গুনাহ থেকে বাঁচার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, হত্যা ও মিথ্যা কসম বা সাক্ষ্যের ভয়াবহতা বুঝুন।"},"heading":{"title":"কবীরা গুনাহ: শিরক, অবাধ্যতা, হত্যা ও মিথ্যার ভয়াবহ শিক্ষা","description":"এই হাদিসে বড় বড় কবীরা গুনাহের কয়েকটি স্পষ্ট উদাহরণ বলা হয়েছে। মূল বিষয় হলো, মানুষের ঈমান, পরিবার, জীবন ও কথার সততা—সবকিছু আল্লাহর কাছে গুরুত্বপূর্ণ। আল্লাহর সাথে কাউকে শরীক করা সবচেয়ে বড় অন্যায় হিসেবে এসেছে। এরপর পিতা-মাতার অবাধ্যতা বলা হয়েছে, যা পরিবার ও দায়িত্ববোধের সাথে জড়িত। কাউকে হত্যা করা মানুষের জীবনের অধিকার নষ্ট করে। আর মিথ্যা কসম বা মিথ্যা সাক্ষ্য মানুষের বিশ্বাস, বিচার ও সম্পর্ককে ক্ষতিগ্রস্ত করে। তাই এই হাদিস আমাদের শেখায়, বড় গুনাহ থেকে দূরে থাকতে হলে ঈমানকে শুদ্ধ রাখা, বাবা-মায়ের হক মানা, মানুষের জীবনকে সম্মান করা এবং কথায় সত্যবাদী থাকা জরুরি।"},"teachings":["আল্লাহর সাথে কাউকে শরীক করা বড় কবীরা গুনাহের অন্তর্ভুক্ত।","পিতা-মাতার অবাধ্যতা থেকে সতর্ক থাকা দরকার।","অন্যায়ভাবে কাউকে হত্যা করা ভয়াবহ গুনাহ।","মিথ্যা কসম ও মিথ্যা সাক্ষ্য মানুষের হক নষ্ট করতে পারে।"],"related_hadiths":[{"id":"161","book_id":"2","label":"Sahih Muslim"},{"id":"162","book_id":"2","label":"Sahih Muslim"},{"id":"6871","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জিহ্বা সংযমের গুরুত্ব","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূল صلى الله عليه وسلم জিহ্বার দিকে ইঙ্গিত করে কথার বিপদ থেকে সতর্ক করেছেন—এ হাদিসের সহজ শিক্ষা।"},"heading":{"title":"জিহ্বা সংযম: কথার কারণে বিপদে পড়া থেকে বাঁচার শিক্ষা","description":"এই হাদিসে একজন সাহাবী রাসূলুল্লাহ صلى الله عليه وسلم-কে জিজ্ঞেস করেন, তাঁর জন্য সবচেয়ে বেশি ভয়ের বিষয় কী। রাসূল صلى الله عليه وسلم নিজের জিহ্বা ধরলেন এবং বললেন, এটি। হাদিসটি খুব ছোট, কিন্তু শিক্ষা গভীর। মানুষ অনেক সময় হাতে বা কাজে যত ভুল করে, কথার মাধ্যমেও তত বড় ক্ষতি করে বসে। মিথ্যা, কষ্টদায়ক কথা, অশ্লীল ভাষা, গীবত বা অন্যের ক্ষতি করা কথা—এসবের দরজা খুলে যায় জিহ্বা নিয়ন্ত্রণ না করলে। তবে এই হাদিসে শুধু জিহ্বার ভয় বলা হয়েছে; অতিরিক্ত বিস্তারিত বিধান এখানে নেই। মূল বার্তা হলো, কথা বলার আগে ভাবা, অপ্রয়োজনীয় কথা কমানো এবং নিজের ভাষাকে আল্লাহর ভয় দিয়ে নিয়ন্ত্রণ করা।"},"teachings":["জিহ্বা মানুষের জন্য বড় পরীক্ষার কারণ হতে পারে।","কথা বলার আগে চিন্তা করা নিরাপদ অভ্যাস।","ভাষা নিয়ন্ত্রণ করা মুসলিম চরিত্রের গুরুত্বপূর্ণ অংশ।","অপ্রয়োজনীয় ও ক্ষতিকর কথা থেকে দূরে থাকা দরকার।"],"related_hadiths":[{"id":"2410","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3৯72","book_id":"6","label":"Sunan Ibn Majah"},{"id":"6474","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জিহ্বা সংযমের গুরুত্ব","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূল صلى الله عليه وسلم জিহ্বার দিকে ইঙ্গিত করে কথার বিপদ থেকে সতর্ক করেছেন—এ হাদিসের সহজ শিক্ষা।"},"heading":{"title":"জিহ্বা সংযম: কথার কারণে বিপদে পড়া থেকে বাঁচার শিক্ষা","description":"এই হাদিসে একজন সাহাবী রাসূলুল্লাহ صلى الله عليه وسلم-কে জিজ্ঞেস করেন, তাঁর জন্য সবচেয়ে বেশি ভয়ের বিষয় কী। রাসূল صلى الله عليه وسلم নিজের জিহ্বা ধরলেন এবং বললেন, এটি। হাদিসটি খুব ছোট, কিন্তু শিক্ষা গভীর। মানুষ অনেক সময় হাতে বা কাজে যত ভুল করে, কথার মাধ্যমেও তত বড় ক্ষতি করে বসে। মিথ্যা, কষ্টদায়ক কথা, অশ্লীল ভাষা, গীবত বা অন্যের ক্ষতি করা কথা—এসবের দরজা খুলে যায় জিহ্বা নিয়ন্ত্রণ না করলে। তবে এই হাদিসে শুধু জিহ্বার ভয় বলা হয়েছে; অতিরিক্ত বিস্তারিত বিধান এখানে নেই। মূল বার্তা হলো, কথা বলার আগে ভাবা, অপ্রয়োজনীয় কথা কমানো এবং নিজের ভাষাকে আল্লাহর ভয় দিয়ে নিয়ন্ত্রণ করা।"},"teachings":["জিহ্বা মানুষের জন্য বড় পরীক্ষার কারণ হতে পারে।","কথা বলার আগে চিন্তা করা নিরাপদ অভ্যাস।","ভাষা নিয়ন্ত্রণ করা মুসলিম চরিত্রের গুরুত্বপূর্ণ অংশ।","অপ্রয়োজনীয় ও ক্ষতিকর কথা থেকে দূরে থাকা দরকার।"],"related_hadiths":[{"id":"2410","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3972","book_id":"6","label":"Sunan Ibn Majah"},{"id":"6474","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সত্যবাদিতার পথ ও মিথ্যার ক্ষতি","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য মানুষকে পুণ্যের পথে নেয়, আর মিথ্যা পাপের দিকে ঠেলে দেয়—এ হাদিসের শিক্ষা।"},"heading":{"title":"সত্যবাদিতা: জান্নাতের পথে চলার সুন্দর শিক্ষা","description":"এই হাদিসে সত্য ও মিথ্যার ফল খুব পরিষ্কারভাবে বলা হয়েছে। সত্য পুণ্যময় কাজ, আর পুণ্য জান্নাতের পথ দেখায়। যে ব্যক্তি সত্যের উপর দৃঢ় থাকে, তাকে আল্লাহর কাছে সত্যনিষ্ঠ হিসেবে লেখা হয়। অন্যদিকে মিথ্যা পাপকাজ, আর পাপ জাহান্নামের পথ দেখায়। যে মিথ্যায় অভ্যস্ত হয়ে পড়ে, তাকে আল্লাহর কাছে মিথ্যুক হিসেবে লেখা হয়। এখানে মূল শিক্ষা হলো অভ্যাসের প্রভাব। একবার সত্য বলা ভালো, কিন্তু নিয়মিত সত্য বলা মানুষকে সত্যনিষ্ঠ করে। একইভাবে মিথ্যাকে ছোট মনে করলে তা অভ্যাসে পরিণত হতে পারে। তাই দৈনন্দিন কথা, লেনদেন, পরিবার ও সমাজে সত্যবাদিতা ধরে রাখা ঈমানী চরিত্রের বড় অংশ।"},"teachings":["সত্য কথা পুণ্যের পথে নিয়ে যায়।","নিয়মিত সত্য বলার অভ্যাস মানুষকে সত্যনিষ্ঠ করে।","মিথ্যা পাপের দিকে নিয়ে যেতে পারে।","মিথ্যায় অভ্যস্ত হওয়া থেকে শুরুতেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"60৯4","book_id":"1","label":"Sahih Bukhari"},{"id":"2607","book_id":"2","label":"Sahih Muslim"},{"id":"1৯71","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সত্যবাদিতার পথ ও মিথ্যার ক্ষতি","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য মানুষকে পুণ্যের পথে নেয়, আর মিথ্যা পাপের দিকে ঠেলে দেয়—এ হাদিসের শিক্ষা।"},"heading":{"title":"সত্যবাদিতা: জান্নাতের পথে চলার সুন্দর শিক্ষা","description":"এই হাদিসে সত্য ও মিথ্যার ফল খুব পরিষ্কারভাবে বলা হয়েছে। সত্য পুণ্যময় কাজ, আর পুণ্য জান্নাতের পথ দেখায়। যে ব্যক্তি সত্যের উপর দৃঢ় থাকে, তাকে আল্লাহর কাছে সত্যনিষ্ঠ হিসেবে লেখা হয়। অন্যদিকে মিথ্যা পাপকাজ, আর পাপ জাহান্নামের পথ দেখায়। যে মিথ্যায় অভ্যস্ত হয়ে পড়ে, তাকে আল্লাহর কাছে মিথ্যুক হিসেবে লেখা হয়। এখানে মূল শিক্ষা হলো অভ্যাসের প্রভাব। একবার সত্য বলা ভালো, কিন্তু নিয়মিত সত্য বলা মানুষকে সত্যনিষ্ঠ করে। একইভাবে মিথ্যাকে ছোট মনে করলে তা অভ্যাসে পরিণত হতে পারে। তাই দৈনন্দিন কথা, লেনদেন, পরিবার ও সমাজে সত্যবাদিতা ধরে রাখা ঈমানী চরিত্রের বড় অংশ।"},"teachings":["সত্য কথা পুণ্যের পথে নিয়ে যায়।","নিয়মিত সত্য বলার অভ্যাস মানুষকে সত্যনিষ্ঠ করে।","মিথ্যা পাপের দিকে নিয়ে যেতে পারে।","মিথ্যায় অভ্যস্ত হওয়া থেকে শুরুতেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"2607","book_id":"2","label":"Sahih Muslim"},{"id":"1971","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুখ ও লজ্জাস্থান হেফাজত","description":"$book_name$ $hadith_number$ - $chapter_name$. জিহ্বা ও লজ্জাস্থান হেফাজতের অঙ্গীকার জান্নাতের আশার বড় কারণ—হাদিসের শিক্ষা।"},"heading":{"title":"মুখ ও লজ্জাস্থান হেফাজত: জান্নাতের আশার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم দুইটি গুরুত্বপূর্ণ অঙ্গের দায়িত্ব নেওয়ার কথা বলেছেন। এক হলো দুই চোয়ালের মাঝের বস্তু, অর্থাৎ জিহ্বা; আর অন্যটি দুই পায়ের মাঝের বস্তু, অর্থাৎ লজ্জাস্থান। যে এগুলোর যিম্মাদার হবে, রাসূল صلى الله عليه وسلم তার জন্য জান্নাতের যিম্মাদার হওয়ার কথা বলেছেন। এখানে মানুষের চরিত্রের দুই বড় দরজা বোঝানো হয়েছে—কথা ও কামনা। জিহ্বা দিয়ে মিথ্যা, গালি, কষ্টদায়ক কথা বা অন্যায় কথা হতে পারে। লজ্জাস্থান নিয়ন্ত্রণ না করলে অবৈধ সম্পর্কের দিকে মানুষ ঝুঁকে যেতে পারে। তাই এই হাদিস মুসলিমকে নিজের ভাষা ও শালীনতা নিয়ে সতর্ক থাকতে শেখায়।"},"teachings":["জিহ্বা হেফাজত করা জান্নাতের আশার একটি বড় কারণ।","লজ্জাস্থান হেফাজত করা চরিত্র রক্ষার অংশ।","কথা ও কামনা—দুই ক্ষেত্রেই আত্মনিয়ন্ত্রণ দরকার।","নিজের অঙ্গের দায়িত্ব নেওয়া ঈমানী শৃঙ্খলার অংশ।"],"related_hadiths":[{"id":"6474","book_id":"1","label":"Sahih Bukhari"},{"id":"2410","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3৯72","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুখ ও লজ্জাস্থান হেফাজত","description":"$book_name$ $hadith_number$ - $chapter_name$. জিহ্বা ও লজ্জাস্থান হেফাজতের অঙ্গীকার জান্নাতের আশার বড় কারণ—হাদিসের শিক্ষা।"},"heading":{"title":"মুখ ও লজ্জাস্থান হেফাজত: জান্নাতের আশার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم দুইটি গুরুত্বপূর্ণ অঙ্গের দায়িত্ব নেওয়ার কথা বলেছেন। এক হলো দুই চোয়ালের মাঝের বস্তু, অর্থাৎ জিহ্বা; আর অন্যটি দুই পায়ের মাঝের বস্তু, অর্থাৎ লজ্জাস্থান। যে এগুলোর যিম্মাদার হবে, রাসূল صلى الله عليه وسلم তার জন্য জান্নাতের যিম্মাদার হওয়ার কথা বলেছেন। এখানে মানুষের চরিত্রের দুই বড় দরজা বোঝানো হয়েছে—কথা ও কামনা। জিহ্বা দিয়ে মিথ্যা, গালি, কষ্টদায়ক কথা বা অন্যায় কথা হতে পারে। লজ্জাস্থান নিয়ন্ত্রণ না করলে অবৈধ সম্পর্কের দিকে মানুষ ঝুঁকে যেতে পারে। তাই এই হাদিস মুসলিমকে নিজের ভাষা ও শালীনতা নিয়ে সতর্ক থাকতে শেখায়।"},"teachings":["জিহ্বা হেফাজত করা জান্নাতের আশার একটি বড় কারণ।","লজ্জাস্থান হেফাজত করা চরিত্র রক্ষার অংশ।","কথা ও কামনা—দুই ক্ষেত্রেই আত্মনিয়ন্ত্রণ দরকার।","নিজের অঙ্গের দায়িত্ব নেওয়া ঈমানী শৃঙ্খলার অংশ।"],"related_hadiths":[{"id":"6474","book_id":"1","label":"Sahih Bukhari"},{"id":"2410","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3972","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রক্ষাকারী ও ধ্বংসকারী কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. তাকওয়া, হক কথা ও মধ্যম পথ রক্ষা করে; প্রবৃত্তি, কৃপণতা ও অহংকার ধ্বংসের কারণ।"},"heading":{"title":"রক্ষাকারী তিন কাজ ও ধ্বংসকারী তিন কাজ: তাকওয়ার হাদিস","description":"এই হাদিসে মানুষের জন্য তিনটি রক্ষাকারী কাজ এবং তিনটি ধ্বংসকারী কাজ বলা হয়েছে। রক্ষাকারী কাজ হলো প্রকাশ্যে ও গোপনে আল্লাহকে ভয় করা, সন্তুষ্টি ও অসন্তুষ্টি—উভয় অবস্থায় হক কথা বলা এবং সচ্ছলতা ও অসচ্ছলতায় মধ্যম পথ রাখা। অর্থাৎ ভালো চরিত্র শুধু মানুষের সামনে নয়, একান্ত অবস্থাতেও দরকার। আবার সত্য কথা শুধু সুবিধার সময়ে নয়, রাগ বা অসন্তুষ্টির সময়েও জরুরি। ধ্বংসকারী কাজ হলো প্রবৃত্তির অনুসরণ, কৃপণতাকে মেনে নেওয়া এবং নিজের প্রতি অহংকার করা। হাদিসে আত্ম-অহংকারকে সবচেয়ে কঠিন বলা হয়েছে। তাই এই শিক্ষা আমাদের ভারসাম্য, সত্য এবং বিনয়ী জীবনের দিকে ডাকে।"},"teachings":["প্রকাশ্যে ও গোপনে আল্লাহকে ভয় করা রক্ষাকারী কাজ।","সন্তুষ্টি ও অসন্তুষ্টি—দুই অবস্থাতেই হক কথা বলা দরকার।","সচ্ছলতা ও অসচ্ছলতায় মধ্যম পথ রাখা ভালো অভ্যাস।","প্রবৃত্তি, কৃপণতা ও অহংকার ধ্বংসের কারণ হতে পারে।"],"related_hadiths":[{"id":"16৮","book_id":"2","label":"Sahih Muslim"},{"id":"1৯৮7","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"7200","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রক্ষাকারী ও ধ্বংসকারী কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. তাকওয়া, হক কথা ও মধ্যম পথ রক্ষা করে; প্রবৃত্তি, কৃপণতা ও অহংকার ধ্বংসের কারণ।"},"heading":{"title":"রক্ষাকারী তিন কাজ ও ধ্বংসকারী তিন কাজ: তাকওয়ার হাদিস","description":"এই হাদিসে মানুষের জন্য তিনটি রক্ষাকারী কাজ এবং তিনটি ধ্বংসকারী কাজ বলা হয়েছে। রক্ষাকারী কাজ হলো প্রকাশ্যে ও গোপনে আল্লাহকে ভয় করা, সন্তুষ্টি ও অসন্তুষ্টি—উভয় অবস্থায় হক কথা বলা এবং সচ্ছলতা ও অসচ্ছলতায় মধ্যম পথ রাখা। অর্থাৎ ভালো চরিত্র শুধু মানুষের সামনে নয়, একান্ত অবস্থাতেও দরকার। আবার সত্য কথা শুধু সুবিধার সময়ে নয়, রাগ বা অসন্তুষ্টির সময়েও জরুরি। ধ্বংসকারী কাজ হলো প্রবৃত্তির অনুসরণ, কৃপণতাকে মেনে নেওয়া এবং নিজের প্রতি অহংকার করা। হাদিসে আত্ম-অহংকারকে সবচেয়ে কঠিন বলা হয়েছে। তাই এই শিক্ষা আমাদের ভারসাম্য, সত্য এবং বিনয়ী জীবনের দিকে ডাকে।"},"teachings":["প্রকাশ্যে ও গোপনে আল্লাহকে ভয় করা রক্ষাকারী কাজ।","সন্তুষ্টি ও অসন্তুষ্টি—দুই অবস্থাতেই হক কথা বলা দরকার।","সচ্ছলতা ও অসচ্ছলতায় মধ্যম পথ রাখা ভালো অভ্যাস।","প্রবৃত্তি, কৃপণতা ও অহংকার ধ্বংসের কারণ হতে পারে।"],"related_hadiths":[{"id":"168","book_id":"2","label":"Sahih Muslim"},{"id":"1987","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"7200","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে মুমিনের গুনাহ ঢেকে মাফ","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতের দিন মুমিনের গুনাহ স্বীকারের পর আল্লাহ দুনিয়ায় ঢেকে রাখা গুনাহ মাফ করে দেবেন।"},"heading":{"title":"কিয়ামতের দিন মুমিনের গুনাহ ঢেকে মাফ করার হাদিস","description":"এই হাদিসে কিয়ামতের দিনের একটি গভীর দৃশ্য এসেছে। আল্লাহ মুমিন বান্দাকে নিজের নিকটবর্তী করবেন, তাকে ঢেকে রাখবেন এবং একে একে তার গুনাহ সম্পর্কে জিজ্ঞেস করবেন। বান্দা স্বীকার করবে যে সে গুনাহগুলো জানে। তখন সে মনে করবে, এসব কারণে সে ধ্বংস হয়ে যাবে। কিন্তু আল্লাহ বলবেন, দুনিয়াতে আমি তোমার এই গুনাহগুলো ঢেকে রেখেছিলাম, আজ আমি তা মাফ করে দিচ্ছি। তারপর তাকে নেকীর আমলনামা দেওয়া হবে। আর কাফের ও মুনাফিকদের ব্যাপারে সবার সামনে ঘোষণা হবে যে তারা রবের বিরুদ্ধে মিথ্যা বলত। এই হাদিস আল্লাহর ক্ষমা, গুনাহ ঢেকে রাখা এবং কিয়ামতের হিসাবের কথা মনে করায়।"},"teachings":["মুমিন বান্দা কিয়ামতে নিজের গুনাহ স্বীকার করবে।","আল্লাহ দুনিয়ায় গুনাহ ঢেকে রেখেছেন—এটি বড় দয়া।","ক্ষমা আল্লাহর পক্ষ থেকে আসে, তাই তাঁর দিকে ফিরতে হয়।","মিথ্যাচার ও মুনাফিকী কিয়ামতে প্রকাশ পাবে।"],"related_hadiths":[{"id":"2441","book_id":"1","label":"Sahih Bukhari"},{"id":"276৮","book_id":"2","label":"Sahih Muslim"},{"id":"5551","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে মুমিনের গুনাহ ঢেকে মাফ","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতের দিন মুমিনের গুনাহ স্বীকারের পর আল্লাহ দুনিয়ায় ঢেকে রাখা গুনাহ মাফ করে দেবেন।"},"heading":{"title":"কিয়ামতের দিন মুমিনের গুনাহ ঢেকে মাফ করার হাদিস","description":"এই হাদিসে কিয়ামতের দিনের একটি গভীর দৃশ্য এসেছে। আল্লাহ মুমিন বান্দাকে নিজের নিকটবর্তী করবেন, তাকে ঢেকে রাখবেন এবং একে একে তার গুনাহ সম্পর্কে জিজ্ঞেস করবেন। বান্দা স্বীকার করবে যে সে গুনাহগুলো জানে। তখন সে মনে করবে, এসব কারণে সে ধ্বংস হয়ে যাবে। কিন্তু আল্লাহ বলবেন, দুনিয়াতে আমি তোমার এই গুনাহগুলো ঢেকে রেখেছিলাম, আজ আমি তা মাফ করে দিচ্ছি। তারপর তাকে নেকীর আমলনামা দেওয়া হবে। আর কাফের ও মুনাফিকদের ব্যাপারে সবার সামনে ঘোষণা হবে যে তারা রবের বিরুদ্ধে মিথ্যা বলত। এই হাদিস আল্লাহর ক্ষমা, গুনাহ ঢেকে রাখা এবং কিয়ামতের হিসাবের কথা মনে করায়।"},"teachings":["মুমিন বান্দা কিয়ামতে নিজের গুনাহ স্বীকার করবে।","আল্লাহ দুনিয়ায় গুনাহ ঢেকে রেখেছেন—এটি বড় দয়া।","ক্ষমা আল্লাহর পক্ষ থেকে আসে, তাই তাঁর দিকে ফিরতে হয়।","মিথ্যাচার ও মুনাফিকী কিয়ামতে প্রকাশ পাবে।"],"related_hadiths":[{"id":"2441","book_id":"1","label":"Sahih Bukhari"},{"id":"2768","book_id":"2","label":"Sahih Muslim"},{"id":"5551","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সব নেশাদার দ্রব্য মদ","description":"$book_name$ $hadith_number$ - $chapter_name$. সব নেশাদার দ্রব্য মদ এবং সব মদ হারাম—তওবা ছাড়া আসক্তির ভয়াবহ সতর্কতা।"},"heading":{"title":"সব নেশাদার দ্রব্য মদ: খামর হারামের স্পষ্ট হাদিস","description":"এই হাদিসে খুব স্পষ্টভাবে বলা হয়েছে, সব নেশাদার দ্রব্য মদ এবং সব ধরনের মদ হারাম। অর্থাৎ শুধু নির্দিষ্ট কোনো পানীয় নয়, যে বস্তু নেশা তৈরি করে তা এই সতর্কতার মধ্যে পড়ে। হাদিসে আরও বলা হয়েছে, যে ব্যক্তি দুনিয়ায় মদ পান করে এবং তওবা ছাড়া আসক্ত অবস্থায় মারা যায়, সে পরকালে সুস্বাদু পানীয় পান করতে পাবে না। এখানে মূল শিক্ষা হলো নেশা থেকে দূরে থাকা এবং ভুল হলে তওবার দিকে ফিরে আসা। হাদিসে আসক্তির কথা এসেছে, তাই নিয়মিত নেশাকে সাধারণ অভ্যাস মনে করা বিপজ্জনক। একজন মুসলিমের জন্য বিবেক, ইবাদত ও চরিত্র রক্ষায় নেশাদার দ্রব্য থেকে বাঁচা প্রয়োজন।"},"teachings":["সব নেশাদার দ্রব্যকে মদের অন্তর্ভুক্ত বলা হয়েছে।","সব ধরনের মদ হারাম—এ শিক্ষা স্পষ্ট।","আসক্ত অবস্থায় তওবা ছাড়া মৃত্যু ভয়াবহ সতর্কতার বিষয়।","ভুল হলে তওবার দিকে দ্রুত ফিরে আসা দরকার।"],"related_hadiths":[{"id":"5112","book_id":"2","label":"Sahih Muslim"},{"id":"1৮62","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3450","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সব নেশাদার দ্রব্য মদ","description":"$book_name$ $hadith_number$ - $chapter_name$. সব নেশাদার দ্রব্য মদ এবং সব মদ হারাম—তওবা ছাড়া আসক্তির ভয়াবহ সতর্কতা।"},"heading":{"title":"সব নেশাদার দ্রব্য মদ: খামর হারামের স্পষ্ট হাদিস","description":"এই হাদিসে খুব স্পষ্টভাবে বলা হয়েছে, সব নেশাদার দ্রব্য মদ এবং সব ধরনের মদ হারাম। অর্থাৎ শুধু নির্দিষ্ট কোনো পানীয় নয়, যে বস্তু নেশা তৈরি করে তা এই সতর্কতার মধ্যে পড়ে। হাদিসে আরও বলা হয়েছে, যে ব্যক্তি দুনিয়ায় মদ পান করে এবং তওবা ছাড়া আসক্ত অবস্থায় মারা যায়, সে পরকালে সুস্বাদু পানীয় পান করতে পাবে না। এখানে মূল শিক্ষা হলো নেশা থেকে দূরে থাকা এবং ভুল হলে তওবার দিকে ফিরে আসা। হাদিসে আসক্তির কথা এসেছে, তাই নিয়মিত নেশাকে সাধারণ অভ্যাস মনে করা বিপজ্জনক। একজন মুসলিমের জন্য বিবেক, ইবাদত ও চরিত্র রক্ষায় নেশাদার দ্রব্য থেকে বাঁচা প্রয়োজন।"},"teachings":["সব নেশাদার দ্রব্যকে মদের অন্তর্ভুক্ত বলা হয়েছে।","সব ধরনের মদ হারাম—এ শিক্ষা স্পষ্ট।","আসক্ত অবস্থায় তওবা ছাড়া মৃত্যু ভয়াবহ সতর্কতার বিষয়।","ভুল হলে তওবার দিকে দ্রুত ফিরে আসা দরকার।"],"related_hadiths":[{"id":"5112","book_id":"2","label":"Sahih Muslim"},{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3450","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ত্বিনাতে খাবালের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নেশাদার দ্রব্য পানকারীর জন্য ত্বিনাতে খাবাল—জাহান্নামীদের রক্ত-পুঁজের কঠিন সতর্কতা।"},"heading":{"title":"ত্বিনাতে খাবাল: নেশাদার দ্রব্য পানকারীর কঠিন সতর্কতা","description":"এই হাদিসে নেশাদার দ্রব্য পানকারীদের জন্য খুব কঠিন সতর্কতা এসেছে। রাসূলুল্লাহ صلى الله عليه وسلم বলেছেন, আল্লাহর ওয়াদা রয়েছে যে নেশাদার দ্রব্য পানকারীকে তিনি ত্বিনাতে খাবাল পান করাবেন। সাহাবীগণ জিজ্ঞেস করলে রাসূল صلى الله عليه وسلم ব্যাখ্যা করেন, এটি জাহান্নামীদের শরীর থেকে গলে পড়া রক্ত-পুঁজ মিশ্রিত অত্যন্ত গরম তরল পদার্থ। হাদিসের ভাষা ভয় জাগায়, কারণ নেশা মানুষের বিবেক, ইবাদত ও চরিত্রকে ক্ষতি করতে পারে। এখানে অতিরিক্ত কোনো গল্প যোগ করার দরকার নেই; মূল শিক্ষা যথেষ্ট পরিষ্কার। মদ ও মাদক থেকে দূরে থাকা, আসক্তি হলে তওবা করা এবং সাহায্য নিয়ে ফিরে আসা—এটাই একজন মুসলিমের নিরাপদ পথ।"},"teachings":["নেশাদার দ্রব্য পানকারীর জন্য কঠিন সতর্কতা এসেছে।","ত্বিনাতে খাবালকে জাহান্নামীদের রক্ত-পুঁজের তরল বলা হয়েছে।","নেশাকে সাধারণ ভুল মনে করে হালকা করা উচিত নয়।","ভুল হলে তওবা ও নেশা ছাড়ার চেষ্টা জরুরি।"],"related_hadiths":[{"id":"5112","book_id":"2","label":"Sahih Muslim"},{"id":"1৮62","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3377","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ত্বিনাতে খাবালের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নেশাদার দ্রব্য পানকারীর জন্য ত্বিনাতে খাবাল—জাহান্নামীদের রক্ত-পুঁজের কঠিন সতর্কতা।"},"heading":{"title":"ত্বিনাতে খাবাল: নেশাদার দ্রব্য পানকারীর কঠিন সতর্কতা","description":"এই হাদিসে নেশাদার দ্রব্য পানকারীদের জন্য খুব কঠিন সতর্কতা এসেছে। রাসূলুল্লাহ صلى الله عليه وسلم বলেছেন, আল্লাহর ওয়াদা রয়েছে যে নেশাদার দ্রব্য পানকারীকে তিনি ত্বিনাতে খাবাল পান করাবেন। সাহাবীগণ জিজ্ঞেস করলে রাসূল صلى الله عليه وسلم ব্যাখ্যা করেন, এটি জাহান্নামীদের শরীর থেকে গলে পড়া রক্ত-পুঁজ মিশ্রিত অত্যন্ত গরম তরল পদার্থ। হাদিসের ভাষা ভয় জাগায়, কারণ নেশা মানুষের বিবেক, ইবাদত ও চরিত্রকে ক্ষতি করতে পারে। এখানে অতিরিক্ত কোনো গল্প যোগ করার দরকার নেই; মূল শিক্ষা যথেষ্ট পরিষ্কার। মদ ও মাদক থেকে দূরে থাকা, আসক্তি হলে তওবা করা এবং সাহায্য নিয়ে ফিরে আসা—এটাই একজন মুসলিমের নিরাপদ পথ।"},"teachings":["নেশাদার দ্রব্য পানকারীর জন্য কঠিন সতর্কতা এসেছে।","ত্বিনাতে খাবালকে জাহান্নামীদের রক্ত-পুঁজের তরল বলা হয়েছে।","নেশাকে সাধারণ ভুল মনে করে হালকা করা উচিত নয়।","ভুল হলে তওবা ও নেশা ছাড়ার চেষ্টা জরুরি।"],"related_hadiths":[{"id":"5112","book_id":"2","label":"Sahih Muslim"},{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3377","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদাসক্তির ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নিয়মিত নেশাদার দ্রব্য পানকারীকে মূর্তিপূজকের মতো গুরুতর অপরাধী বলা হয়েছে।"},"heading":{"title":"মদাসক্তি: নিয়মিত নেশা করার ভয়াবহ সতর্কতা","description":"এই হাদিসে নিয়মিত নেশাদার দ্রব্য পানকারীকে মূর্তিপূজকের ন্যায় অপরাধী বলা হয়েছে। এখানে মূল শিক্ষা হলো মদাসক্তি বা নেশার অভ্যাসকে খুব গুরুতরভাবে দেখা। হাদিসে একবার ভুল করা ও নিয়মিত আসক্তির মধ্যে ভাষাগতভাবে পার্থক্য আছে, কারণ ‘সর্বদা পানকারী’ শব্দটি অভ্যাস ও আসক্তির দিকে ইঙ্গিত করে। তবে কোনো মানুষকে ব্যক্তিগতভাবে বিচার করার চেয়ে নিজের অবস্থার দিকে তাকানো বেশি দরকার। মদ বা নেশা মানুষকে আল্লাহর আনুগত্য থেকে দূরে নিতে পারে এবং চরিত্র নষ্ট করতে পারে। তাই যে কেউ এই অভ্যাসে জড়িয়ে পড়লে তাকে তওবা, দোয়া ও বাস্তব পদক্ষেপের মাধ্যমে ফিরে আসার চেষ্টা করা উচিত।"},"teachings":["নিয়মিত নেশা করা গুরুতর অপরাধ হিসেবে এসেছে।","নেশার অভ্যাসকে হালকা করে দেখা ঠিক নয়।","মদাসক্তি আল্লাহর আনুগত্য থেকে দূরে নিতে পারে।","তওবা ও নেশা ছাড়ার চেষ্টা জরুরি।"],"related_hadiths":[{"id":"1৮62","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3377","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5112","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদাসক্তির ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নিয়মিত নেশাদার দ্রব্য পানকারীকে মূর্তিপূজকের মতো গুরুতর অপরাধী বলা হয়েছে।"},"heading":{"title":"মদাসক্তি: নিয়মিত নেশা করার ভয়াবহ সতর্কতা","description":"এই হাদিসে নিয়মিত নেশাদার দ্রব্য পানকারীকে মূর্তিপূজকের ন্যায় অপরাধী বলা হয়েছে। এখানে মূল শিক্ষা হলো মদাসক্তি বা নেশার অভ্যাসকে খুব গুরুতরভাবে দেখা। হাদিসে একবার ভুল করা ও নিয়মিত আসক্তির মধ্যে ভাষাগতভাবে পার্থক্য আছে, কারণ ‘সর্বদা পানকারী’ শব্দটি অভ্যাস ও আসক্তির দিকে ইঙ্গিত করে। তবে কোনো মানুষকে ব্যক্তিগতভাবে বিচার করার চেয়ে নিজের অবস্থার দিকে তাকানো বেশি দরকার। মদ বা নেশা মানুষকে আল্লাহর আনুগত্য থেকে দূরে নিতে পারে এবং চরিত্র নষ্ট করতে পারে। তাই যে কেউ এই অভ্যাসে জড়িয়ে পড়লে তাকে তওবা, দোয়া ও বাস্তব পদক্ষেপের মাধ্যমে ফিরে আসার চেষ্টা করা উচিত।"},"teachings":["নিয়মিত নেশা করা গুরুতর অপরাধ হিসেবে এসেছে।","নেশার অভ্যাসকে হালকা করে দেখা ঠিক নয়।","মদাসক্তি আল্লাহর আনুগত্য থেকে দূরে নিতে পারে।","তওবা ও নেশা ছাড়ার চেষ্টা জরুরি।"],"related_hadiths":[{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3377","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5112","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপানকারীর জান্নাত সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সর্বদা নেশাদার দ্রব্য পানকারীর জন্য জান্নাত বিষয়ে কঠিন সতর্কতা—নিজেকে সংশোধনের ডাক।"},"heading":{"title":"সর্বদা নেশাদার দ্রব্য পানকারী: জান্নাত বিষয়ে কঠিন সতর্কতা","description":"এই হাদিসে বলা হয়েছে, সর্বদা নেশাদার দ্রব্য পানকারী জান্নাতে যাবে না। হাদিসের ভাষা খুব কঠিন, তাই একে হালকা করে দেখা উচিত নয়। এখানে মূল বিষয় হলো মদাসক্তি ও নিয়মিত নেশা। নেশা মানুষের বিবেক ঢেকে দেয়, আমল দুর্বল করে এবং অনেক অন্যায়ের দরজা খুলে দিতে পারে। তবে হাদিস থেকে অতিরিক্ত সিদ্ধান্ত বানানো ঠিক নয়; যে কথা এসেছে, সেটুকুই মানতে হবে। মুসলিমের কাজ হলো ভয় পাওয়া, নিজেকে ফিরিয়ে আনা এবং তওবার পথ ধরা। যদি কারও জীবনে এই অভ্যাস থাকে, তাহলে গোপনে বা প্রকাশ্যে আল্লাহর কাছে ক্ষমা চেয়ে নেশা ছাড়ার বাস্তব চেষ্টা করা জরুরি।"},"teachings":["নিয়মিত নেশাদার দ্রব্য পানকারীর জন্য কঠিন সতর্কতা এসেছে।","নেশাকে সাধারণ সামাজিক অভ্যাস মনে করা ভুল।","নেশা ছাড়ার জন্য তওবা ও চেষ্টা দরকার।","হাদিসের ভাষা যতটুকু, ব্যাখ্যাও ততটুকুতে রাখা উচিত।"],"related_hadiths":[{"id":"1৮62","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"5112","book_id":"2","label":"Sahih Muslim"},{"id":"3377","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপানকারীর জান্নাত সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সর্বদা নেশাদার দ্রব্য পানকারীর জন্য জান্নাত বিষয়ে কঠিন সতর্কতা—নিজেকে সংশোধনের ডাক।"},"heading":{"title":"সর্বদা নেশাদার দ্রব্য পানকারী: জান্নাত বিষয়ে কঠিন সতর্কতা","description":"এই হাদিসে বলা হয়েছে, সর্বদা নেশাদার দ্রব্য পানকারী জান্নাতে যাবে না। হাদিসের ভাষা খুব কঠিন, তাই একে হালকা করে দেখা উচিত নয়। এখানে মূল বিষয় হলো মদাসক্তি ও নিয়মিত নেশা। নেশা মানুষের বিবেক ঢেকে দেয়, আমল দুর্বল করে এবং অনেক অন্যায়ের দরজা খুলে দিতে পারে। তবে হাদিস থেকে অতিরিক্ত সিদ্ধান্ত বানানো ঠিক নয়; যে কথা এসেছে, সেটুকুই মানতে হবে। মুসলিমের কাজ হলো ভয় পাওয়া, নিজেকে ফিরিয়ে আনা এবং তওবার পথ ধরা। যদি কারও জীবনে এই অভ্যাস থাকে, তাহলে গোপনে বা প্রকাশ্যে আল্লাহর কাছে ক্ষমা চেয়ে নেশা ছাড়ার বাস্তব চেষ্টা করা জরুরি।"},"teachings":["নিয়মিত নেশাদার দ্রব্য পানকারীর জন্য কঠিন সতর্কতা এসেছে।","নেশাকে সাধারণ সামাজিক অভ্যাস মনে করা ভুল।","নেশা ছাড়ার জন্য তওবা ও চেষ্টা দরকার।","হাদিসের ভাষা যতটুকু, ব্যাখ্যাও ততটুকুতে রাখা উচিত।"],"related_hadiths":[{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"5112","book_id":"2","label":"Sahih Muslim"},{"id":"3377","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অবাধ্যতা, জুয়া, খোঁটা ও মদাসক্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. পিতা-মাতার অবাধ্যতা, জুয়া-লটারী, খোঁটা দেওয়া ও মদাসক্তির কঠিন সতর্কতা।"},"heading":{"title":"অবাধ্য সন্তান, জুয়া, খোঁটা ও মদপান: চারটি গুরুতর সতর্কতা","description":"এই হাদিসে চার শ্রেণীর মানুষের ব্যাপারে জান্নাত বিষয়ে কঠিন সতর্কতা এসেছে। তারা হলো পিতা-মাতার অবাধ্য সন্তান, জুয়া ও লটারীতে অংশগ্রহণকারী, খোঁটাদানকারী এবং সর্বদা মদপানকারী। এখানে একসাথে কয়েকটি সামাজিক ও ব্যক্তিগত অপরাধ এসেছে। পিতা-মাতার অবাধ্যতা পরিবারকে আঘাত করে। জুয়া ও লটারী মানুষের সম্পদ ও মনকে অন্য পথে নেয়। খোঁটা দেওয়া দান বা উপকারের সৌন্দর্য নষ্ট করে। আর মদাসক্তি বিবেক ও চরিত্রকে ক্ষতি করে। হাদিসটি আমাদের শেখায়, শুধু ব্যক্তিগত ইবাদত নয়; পারিবারিক দায়িত্ব, অর্থনৈতিক সততা, মানুষের সম্মান এবং নেশা থেকে দূরে থাকা—সবই মুসলিম জীবনের অংশ।"},"teachings":["পিতা-মাতার অবাধ্যতা গুরুতর সতর্কতার বিষয়।","জুয়া ও লটারী থেকে দূরে থাকা দরকার।","উপকার করে খোঁটা দেওয়া খারাপ অভ্যাস।","সর্বদা মদপান করা ভয়াবহ পরিণতির কারণ হতে পারে।"],"related_hadiths":[{"id":"161","book_id":"2","label":"Sahih Muslim"},{"id":"6৮71","book_id":"1","label":"Sahih Bukhari"},{"id":"1৮62","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অবাধ্যতা, জুয়া, খোঁটা ও মদাসক্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. পিতা-মাতার অবাধ্যতা, জুয়া-লটারী, খোঁটা দেওয়া ও মদাসক্তির কঠিন সতর্কতা।"},"heading":{"title":"অবাধ্য সন্তান, জুয়া, খোঁটা ও মদপান: চারটি গুরুতর সতর্কতা","description":"এই হাদিসে চার শ্রেণীর মানুষের ব্যাপারে জান্নাত বিষয়ে কঠিন সতর্কতা এসেছে। তারা হলো পিতা-মাতার অবাধ্য সন্তান, জুয়া ও লটারীতে অংশগ্রহণকারী, খোঁটাদানকারী এবং সর্বদা মদপানকারী। এখানে একসাথে কয়েকটি সামাজিক ও ব্যক্তিগত অপরাধ এসেছে। পিতা-মাতার অবাধ্যতা পরিবারকে আঘাত করে। জুয়া ও লটারী মানুষের সম্পদ ও মনকে অন্য পথে নেয়। খোঁটা দেওয়া দান বা উপকারের সৌন্দর্য নষ্ট করে। আর মদাসক্তি বিবেক ও চরিত্রকে ক্ষতি করে। হাদিসটি আমাদের শেখায়, শুধু ব্যক্তিগত ইবাদত নয়; পারিবারিক দায়িত্ব, অর্থনৈতিক সততা, মানুষের সম্মান এবং নেশা থেকে দূরে থাকা—সবই মুসলিম জীবনের অংশ।"},"teachings":["পিতা-মাতার অবাধ্যতা গুরুতর সতর্কতার বিষয়।","জুয়া ও লটারী থেকে দূরে থাকা দরকার।","উপকার করে খোঁটা দেওয়া খারাপ অভ্যাস।","সর্বদা মদপান করা ভয়াবহ পরিণতির কারণ হতে পারে।"],"related_hadiths":[{"id":"161","book_id":"2","label":"Sahih Muslim"},{"id":"6871","book_id":"1","label":"Sahih Bukhari"},{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর কঠিন সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. পরিবারে বেহায়াপনা, পুরুষের বেশধারী নারী ও নিয়মিত নেশাকারীর ব্যাপারে সতর্কতা।"},"heading":{"title":"তিন শ্রেণীর মানুষ: পরিবার, পোশাক-আচরণ ও নেশা বিষয়ে সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের ব্যাপারে কঠিন সতর্কতা এসেছে। প্রথমত, যে ব্যক্তি তার পরিবারে বেহায়াপনার সুযোগ দেয়। দ্বিতীয়ত, পুরুষের বেশধারী নারী। তৃতীয়ত, নিয়মিত নেশাদার দ্রব্য পানকারী। এখানে পরিবার, পরিচয় ও নেশার বিষয় একসাথে এসেছে। পরিবারে অশালীনতার সুযোগ দেওয়া মানে নিজের দায়িত্বকে অবহেলা করা। পোশাক ও আচরণে সীমা রক্ষা করাও ইসলামী শালীনতার অংশ। আর নিয়মিত নেশা মানুষের বিবেক ও আমলকে ক্ষতি করে। হাদিসের ভাষা কঠোর, তাই এটি নিজের সংশোধনের জন্য নেওয়া উচিত। অন্যকে অপমান করার জন্য নয়; বরং নিজের পরিবার, চরিত্র ও অভ্যাস ঠিক করার জন্য।"},"teachings":["পরিবারে বেহায়াপনার সুযোগ দেওয়া গুরুতর সতর্কতার বিষয়।","পোশাক ও আচরণে শালীনতা রক্ষা করা দরকার।","নিয়মিত নেশাদার দ্রব্য পান করা ভয়াবহ অভ্যাস।","হাদিসের শিক্ষা নিজের সংশোধনের জন্য গ্রহণ করা উচিত।"],"related_hadiths":[{"id":"16৮","book_id":"2","label":"Sahih Muslim"},{"id":"1৮62","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"6136","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর কঠিন সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. পরিবারে বেহায়াপনা, পুরুষের বেশধারী নারী ও নিয়মিত নেশাকারীর ব্যাপারে সতর্কতা।"},"heading":{"title":"তিন শ্রেণীর মানুষ: পরিবার, পোশাক-আচরণ ও নেশা বিষয়ে সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের ব্যাপারে কঠিন সতর্কতা এসেছে। প্রথমত, যে ব্যক্তি তার পরিবারে বেহায়াপনার সুযোগ দেয়। দ্বিতীয়ত, পুরুষের বেশধারী নারী। তৃতীয়ত, নিয়মিত নেশাদার দ্রব্য পানকারী। এখানে পরিবার, পরিচয় ও নেশার বিষয় একসাথে এসেছে। পরিবারে অশালীনতার সুযোগ দেওয়া মানে নিজের দায়িত্বকে অবহেলা করা। পোশাক ও আচরণে সীমা রক্ষা করাও ইসলামী শালীনতার অংশ। আর নিয়মিত নেশা মানুষের বিবেক ও আমলকে ক্ষতি করে। হাদিসের ভাষা কঠোর, তাই এটি নিজের সংশোধনের জন্য নেওয়া উচিত। অন্যকে অপমান করার জন্য নয়; বরং নিজের পরিবার, চরিত্র ও অভ্যাস ঠিক করার জন্য।"},"teachings":["পরিবারে বেহায়াপনার সুযোগ দেওয়া গুরুতর সতর্কতার বিষয়।","পোশাক ও আচরণে শালীনতা রক্ষা করা দরকার।","নিয়মিত নেশাদার দ্রব্য পান করা ভয়াবহ অভ্যাস।","হাদিসের শিক্ষা নিজের সংশোধনের জন্য গ্রহণ করা উচিত।"],"related_hadiths":[{"id":"168","book_id":"2","label":"Sahih Muslim"},{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"6136","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপান, অবাধ্যতা ও দায়ূস","description":"$book_name$ $hadith_number$ - $chapter_name$. মদাসক্ত, পিতা-মাতার অবাধ্য সন্তান ও পরিবারে বেপর্দার সুযোগদাতার সতর্কতা।"},"heading":{"title":"মদাসক্ত, অবাধ্য সন্তান ও দায়ূস: তিন শ্রেণীর কঠিন সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর লোকের প্রতি আল্লাহ জান্নাত হারাম করেছেন বলে সতর্ক করা হয়েছে। তারা হলো সর্বদা মদপানকারী, পিতা-মাতার অবাধ্য সন্তান এবং পরিবারে বেপর্দা বা খারাপ কাজের সুযোগ দানকারী দায়ূস। এখানে তিনটি বিষয়ে জোর আছে—নিজের নেশার অভ্যাস, পিতা-মাতার হক এবং পরিবারের নৈতিক দায়িত্ব। মদাসক্তি ব্যক্তিকে ভেতর থেকে দুর্বল করে। পিতা-মাতার অবাধ্যতা কৃতজ্ঞতা ও দায়িত্বের বিপরীত। আর পরিবারে খারাপ কাজকে মেনে নেওয়া দায়িত্বহীনতা। হাদিসটি মানুষকে ভয় দেখিয়ে ভেঙে দিতে নয়; বরং জাগিয়ে দিতে এসেছে, যেন সে তওবা করে, সম্পর্ক ঠিক করে এবং পরিবারকে সঠিক পথে রাখতে চেষ্টা করে।"},"teachings":["সর্বদা মদপানকারী সম্পর্কে কঠিন সতর্কতা এসেছে।","পিতা-মাতার অবাধ্যতা বড় অপরাধের মধ্যে পড়ে।","পরিবারে খারাপ কাজ মেনে নেওয়া দায়িত্বহীনতা।","তওবা ও সংশোধনের পথে ফিরে আসা দরকার।"],"related_hadiths":[{"id":"161","book_id":"2","label":"Sahih Muslim"},{"id":"6৮71","book_id":"1","label":"Sahih Bukhari"},{"id":"1৮62","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপান, অবাধ্যতা ও দায়ূস","description":"$book_name$ $hadith_number$ - $chapter_name$. মদাসক্ত, পিতা-মাতার অবাধ্য সন্তান ও পরিবারে বেপর্দার সুযোগদাতার সতর্কতা।"},"heading":{"title":"মদাসক্ত, অবাধ্য সন্তান ও দায়ূস: তিন শ্রেণীর কঠিন সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর লোকের প্রতি আল্লাহ জান্নাত হারাম করেছেন বলে সতর্ক করা হয়েছে। তারা হলো সর্বদা মদপানকারী, পিতা-মাতার অবাধ্য সন্তান এবং পরিবারে বেপর্দা বা খারাপ কাজের সুযোগ দানকারী দায়ূস। এখানে তিনটি বিষয়ে জোর আছে—নিজের নেশার অভ্যাস, পিতা-মাতার হক এবং পরিবারের নৈতিক দায়িত্ব। মদাসক্তি ব্যক্তিকে ভেতর থেকে দুর্বল করে। পিতা-মাতার অবাধ্যতা কৃতজ্ঞতা ও দায়িত্বের বিপরীত। আর পরিবারে খারাপ কাজকে মেনে নেওয়া দায়িত্বহীনতা। হাদিসটি মানুষকে ভয় দেখিয়ে ভেঙে দিতে নয়; বরং জাগিয়ে দিতে এসেছে, যেন সে তওবা করে, সম্পর্ক ঠিক করে এবং পরিবারকে সঠিক পথে রাখতে চেষ্টা করে।"},"teachings":["সর্বদা মদপানকারী সম্পর্কে কঠিন সতর্কতা এসেছে।","পিতা-মাতার অবাধ্যতা বড় অপরাধের মধ্যে পড়ে।","পরিবারে খারাপ কাজ মেনে নেওয়া দায়িত্বহীনতা।","তওবা ও সংশোধনের পথে ফিরে আসা দরকার।"],"related_hadiths":[{"id":"161","book_id":"2","label":"Sahih Muslim"},{"id":"6871","book_id":"1","label":"Sahih Bukhari"},{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, সম্পর্কচ্ছেদ ও যাদু","description":"$book_name$ $hadith_number$ - $chapter_name$. মদাসক্তি, আত্মীয়তার সম্পর্ক ছিন্ন করা ও যাদু বিশ্বাসের ব্যাপারে কঠিন সতর্কতা।"},"heading":{"title":"মদাসক্তি, আত্মীয়তা ছিন্ন ও যাদু বিশ্বাস: তিনটি বড় সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর লোকের ব্যাপারে বলা হয়েছে, তারা জান্নাতে যাবে না। প্রথম শ্রেণী হলো সর্বদা নেশাদার দ্রব্য পানকারী। দ্বিতীয় হলো আত্মীয়তার সম্পর্ক বিচ্ছিন্নকারী। তৃতীয় হলো যাদুকে বিশ্বাসকারী। এখানে তিনটি ভিন্ন ক্ষতির দিক দেখা যায়। নেশা নিজের বিবেক ও আমলকে ক্ষতি করে। আত্মীয়তার সম্পর্ক ছিন্ন করা পরিবার ও সমাজের বন্ধন নষ্ট করে। আর যাদুকে বিশ্বাস করা ঈমানী চিন্তা ও আল্লাহর ওপর ভরসাকে দুর্বল করতে পারে। হাদিসটি আমাদের নিজের জীবনকে তিন দিক থেকে দেখতে শেখায়—অভ্যাস, সম্পর্ক এবং বিশ্বাস। ভুল থাকলে তা স্বীকার করে ফিরে আসাই নিরাপদ পথ।"},"teachings":["সর্বদা নেশাদার দ্রব্য পান করা ভয়াবহ সতর্কতার বিষয়।","আত্মীয়তার সম্পর্ক ছিন্ন করা থেকে দূরে থাকতে হবে।","যাদুকে বিশ্বাস করা ঈমানের জন্য বিপজ্জনক।","অভ্যাস, সম্পর্ক ও বিশ্বাস—তিন দিকেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"1৮62","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"5112","book_id":"2","label":"Sahih Muslim"},{"id":"6136","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, সম্পর্কচ্ছেদ ও যাদু","description":"$book_name$ $hadith_number$ - $chapter_name$. মদাসক্তি, আত্মীয়তার সম্পর্ক ছিন্ন করা ও যাদু বিশ্বাসের ব্যাপারে কঠিন সতর্কতা।"},"heading":{"title":"মদাসক্তি, আত্মীয়তা ছিন্ন ও যাদু বিশ্বাস: তিনটি বড় সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর লোকের ব্যাপারে বলা হয়েছে, তারা জান্নাতে যাবে না। প্রথম শ্রেণী হলো সর্বদা নেশাদার দ্রব্য পানকারী। দ্বিতীয় হলো আত্মীয়তার সম্পর্ক বিচ্ছিন্নকারী। তৃতীয় হলো যাদুকে বিশ্বাসকারী। এখানে তিনটি ভিন্ন ক্ষতির দিক দেখা যায়। নেশা নিজের বিবেক ও আমলকে ক্ষতি করে। আত্মীয়তার সম্পর্ক ছিন্ন করা পরিবার ও সমাজের বন্ধন নষ্ট করে। আর যাদুকে বিশ্বাস করা ঈমানী চিন্তা ও আল্লাহর ওপর ভরসাকে দুর্বল করতে পারে। হাদিসটি আমাদের নিজের জীবনকে তিন দিক থেকে দেখতে শেখায়—অভ্যাস, সম্পর্ক এবং বিশ্বাস। ভুল থাকলে তা স্বীকার করে ফিরে আসাই নিরাপদ পথ।"},"teachings":["সর্বদা নেশাদার দ্রব্য পান করা ভয়াবহ সতর্কতার বিষয়।","আত্মীয়তার সম্পর্ক ছিন্ন করা থেকে দূরে থাকতে হবে।","যাদুকে বিশ্বাস করা ঈমানের জন্য বিপজ্জনক।","অভ্যাস, সম্পর্ক ও বিশ্বাস—তিন দিকেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"5112","book_id":"2","label":"Sahih Muslim"},{"id":"6136","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে অঙ্গ-প্রত্যঙ্গের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে মুখ বন্ধ করে অঙ্গ-প্রত্যঙ্গকে কথা বলানো হবে; মানুষ নিজের কাজের সাক্ষ্য নিজ থেকেই পাবে।"},"heading":{"title":"কিয়ামতের দিন অঙ্গ-প্রত্যঙ্গের সাক্ষ্য দেওয়ার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কিয়ামতের দিনের এক কথোপকথনের কথা বলেছেন। বান্দা বলবে, সে নিজের বিরুদ্ধে শুধু নিজের পক্ষ থেকে সাক্ষ্য গ্রহণ করবে। তখন আল্লাহ বলবেন, আজ তুমি নিজেই তোমার সাক্ষী হিসেবে যথেষ্ট, আর কিরামান-কাতিবীনও সাক্ষী। এরপর তার মুখে মোহর লাগিয়ে দেওয়া হবে এবং অঙ্গ-প্রত্যঙ্গকে বলা হবে, তারা যেন তার কাজের কথা বলে। তখন অঙ্গ-প্রত্যঙ্গ তার কাজ প্রকাশ করবে। পরে মুখ খুলে দেওয়া হলে সে নিজের অঙ্গগুলোকে দোষ দেবে, অথচ তাদের জন্যই সে আগে নিজের রবের সঙ্গে বিতর্ক করছিল। এই হাদিস আমাদের মনে করায়, কিয়ামতের সাক্ষ্য খুব স্পষ্ট হবে এবং মানুষের কাজ লুকানো থাকবে না।"},"teachings":["কিয়ামতে মানুষের নিজের অঙ্গ-প্রত্যঙ্গ তার কাজের সাক্ষ্য দেবে।","কিরামান-কাতিবীন মানুষের কাজ লিখে রাখেন।","মুখের কথা দিয়ে সবকিছু অস্বীকার করা সম্ভব হবে না।","দুনিয়ার কাজের জন্য আখেরাতে জবাবদিহি আছে।"],"related_hadiths":[{"id":"2৯6৯","book_id":"2","label":"Sahih Muslim"},{"id":"5554","book_id":"14","label":"Mishkat al-Masabih"},{"id":"242৯","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে অঙ্গ-প্রত্যঙ্গের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে মুখ বন্ধ করে অঙ্গ-প্রত্যঙ্গকে কথা বলানো হবে; মানুষ নিজের কাজের সাক্ষ্য নিজ থেকেই পাবে।"},"heading":{"title":"কিয়ামতের দিন অঙ্গ-প্রত্যঙ্গের সাক্ষ্য দেওয়ার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কিয়ামতের দিনের এক কথোপকথনের কথা বলেছেন। বান্দা বলবে, সে নিজের বিরুদ্ধে শুধু নিজের পক্ষ থেকে সাক্ষ্য গ্রহণ করবে। তখন আল্লাহ বলবেন, আজ তুমি নিজেই তোমার সাক্ষী হিসেবে যথেষ্ট, আর কিরামান-কাতিবীনও সাক্ষী। এরপর তার মুখে মোহর লাগিয়ে দেওয়া হবে এবং অঙ্গ-প্রত্যঙ্গকে বলা হবে, তারা যেন তার কাজের কথা বলে। তখন অঙ্গ-প্রত্যঙ্গ তার কাজ প্রকাশ করবে। পরে মুখ খুলে দেওয়া হলে সে নিজের অঙ্গগুলোকে দোষ দেবে, অথচ তাদের জন্যই সে আগে নিজের রবের সঙ্গে বিতর্ক করছিল। এই হাদিস আমাদের মনে করায়, কিয়ামতের সাক্ষ্য খুব স্পষ্ট হবে এবং মানুষের কাজ লুকানো থাকবে না।"},"teachings":["কিয়ামতে মানুষের নিজের অঙ্গ-প্রত্যঙ্গ তার কাজের সাক্ষ্য দেবে।","কিরামান-কাতিবীন মানুষের কাজ লিখে রাখেন।","মুখের কথা দিয়ে সবকিছু অস্বীকার করা সম্ভব হবে না।","দুনিয়ার কাজের জন্য আখেরাতে জবাবদিহি আছে।"],"related_hadiths":[{"id":"2969","book_id":"2","label":"Sahih Muslim"},{"id":"5554","book_id":"14","label":"Mishkat al-Masabih"},{"id":"2429","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শাসকদের যুগ ও পাপকে হালাল মনে করার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইসলামের শুরু, খেলাফত, কঠোর শাসন এবং পাপকে হালাল মনে করার ভয়াবহ পরিণতি সম্পর্কে সতর্ক শিক্ষা।"},"heading":{"title":"অত্যাচারী শাসক ও পাপকে হালাল মনে করার হাদিস","description":"এই হাদিসের মূল বিষয় শাসনব্যবস্থা, ফিতনা এবং পাপকে হালাল মনে করার ভয়াবহতা। এখানে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ইসলামের শুরুতে নবুয়ত ও রহমতের কথা বলেছেন। এরপর খেলাফত ও রহমতের যুগের কথা এসেছে। তারপর এমন রাজত্ব ও কঠোর শাসনের কথা বলা হয়েছে, যেখানে যুলুম, উচ্ছৃঙ্খলতা এবং জমিনে বিপর্যয় দেখা দেবে। হাদিসে বিশেষভাবে বলা হয়েছে, কিছু অত্যাচারী শাসক রেশম, অবৈধ সম্পর্ক ও মদকে হালাল মনে করবে। তাদের দুনিয়াবী রিযিক ও সাহায্য পাওয়া যেতে পারে, কিন্তু সেটি তাদের কাজের সঠিকতা প্রমাণ করে না। তাই মুমিনের জন্য শিক্ষা হলো—ক্ষমতা, ধন বা বাহ্যিক সফলতা দেখে পাপকে ছোট মনে করা যাবে না। তাই নেতৃত্বের অবস্থানে থাকা মানুষদের জন্য এটি আরও বড় সতর্কতা, আর সাধারণ মানুষের জন্যও সত্য ও পাপের পার্থক্য বুঝে চলার শিক্ষা।"},"teachings":["ক্ষমতা ও দুনিয়াবী সাফল্য পাপকে বৈধ করে না।","রহমতপূর্ণ নেতৃত্ব মানুষের জন্য কল্যাণের পথ খুলে দেয়।","যুলুম, মদ ও অশ্লীলতাকে হালাল মনে করা বড় সতর্কতার বিষয়।","দুনিয়ার সাহায্য পেলেও আল্লাহর সামনে জবাবদিহি থেকে কেউ মুক্ত নয়।"],"related_hadiths":[{"id":"55৯0","book_id":"1","label":"Sahih Bukhari"},{"id":"৮0","book_id":"1","label":"Sahih Bukhari"},{"id":"৮1","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শাসকদের যুগ ও পাপকে হালাল মনে করার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইসলামের শুরু, খেলাফত, কঠোর শাসন এবং পাপকে হালাল মনে করার ভয়াবহ পরিণতি সম্পর্কে সতর্ক শিক্ষা।"},"heading":{"title":"অত্যাচারী শাসক ও পাপকে হালাল মনে করার হাদিস","description":"এই হাদিসের মূল বিষয় শাসনব্যবস্থা, ফিতনা এবং পাপকে হালাল মনে করার ভয়াবহতা। এখানে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ইসলামের শুরুতে নবুয়ত ও রহমতের কথা বলেছেন। এরপর খেলাফত ও রহমতের যুগের কথা এসেছে। তারপর এমন রাজত্ব ও কঠোর শাসনের কথা বলা হয়েছে, যেখানে যুলুম, উচ্ছৃঙ্খলতা এবং জমিনে বিপর্যয় দেখা দেবে। হাদিসে বিশেষভাবে বলা হয়েছে, কিছু অত্যাচারী শাসক রেশম, অবৈধ সম্পর্ক ও মদকে হালাল মনে করবে। তাদের দুনিয়াবী রিযিক ও সাহায্য পাওয়া যেতে পারে, কিন্তু সেটি তাদের কাজের সঠিকতা প্রমাণ করে না। তাই মুমিনের জন্য শিক্ষা হলো—ক্ষমতা, ধন বা বাহ্যিক সফলতা দেখে পাপকে ছোট মনে করা যাবে না। তাই নেতৃত্বের অবস্থানে থাকা মানুষদের জন্য এটি আরও বড় সতর্কতা, আর সাধারণ মানুষের জন্যও সত্য ও পাপের পার্থক্য বুঝে চলার শিক্ষা।"},"teachings":["ক্ষমতা ও দুনিয়াবী সাফল্য পাপকে বৈধ করে না।","রহমতপূর্ণ নেতৃত্ব মানুষের জন্য কল্যাণের পথ খুলে দেয়।","যুলুম, মদ ও অশ্লীলতাকে হালাল মনে করা বড় সতর্কতার বিষয়।","দুনিয়ার সাহায্য পেলেও আল্লাহর সামনে জবাবদিহি থেকে কেউ মুক্ত নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"80","book_id":"1","label":"Sahih Bukhari"},{"id":"81","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতের আলামত ও ইলম কমে যাওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইলম কমে যাওয়া, মূর্খতা, ব্যভিচার, মদপান ও নারী-পুরুষের সংখ্যার পরিবর্তন—কিয়ামতের কিছু আলামত।"},"heading":{"title":"কিয়ামতের আলামত: ইলম কমে যাওয়া ও মদপান বৃদ্ধি","description":"এই হাদিসে কিয়ামতের আলামত নিয়ে কয়েকটি স্পষ্ট সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, বিদ্যা উঠে যাবে বা কমে যাবে, মূর্খতা বেড়ে যাবে, ব্যভিচার বেশি হবে এবং মদপান বৃদ্ধি পাবে। আরও বলা হয়েছে, পুরুষের সংখ্যা কমে যাবে এবং নারীর সংখ্যা বেশি হবে, এমনকি একজন পুরুষ বহু নারীর দায়িত্বে থাকবে। হাদিসটি আমাদের বোঝায় যে সমাজে দ্বীনি জ্ঞান কমে গেলে ভুল কাজ সহজে ছড়িয়ে পড়ে। তাই কিয়ামতের আলামত হাদিস পড়ার উদ্দেশ্য শুধু ভবিষ্যৎ জানা নয়; বরং নিজের জীবনে ইলম, লজ্জাশীলতা, সংযম এবং হারাম থেকে বাঁচার চেষ্টা বাড়ানো। এই বার্তাটি সরল কিন্তু গভীর। তাই পাঠকের উচিত হাদিসটি পড়ে ভয় পাওয়ার পাশাপাশি নিজের ঘর, শিক্ষা ও চরিত্রের দিকে বাস্তবভাবে নজর দেওয়া।"},"teachings":["দ্বীনি ইলম কমে যাওয়া সমাজের জন্য বড় সতর্কতা।","মূর্খতা বাড়লে হারাম কাজের পথ সহজ হয়।","মদপান ও ব্যভিচার বৃদ্ধি কিয়ামতের আলামতের মধ্যে এসেছে।","হাদিসটি জ্ঞান ও নৈতিকতার গুরুত্ব মনে করিয়ে দেয়।"],"related_hadiths":[{"id":"৮0","book_id":"1","label":"Sahih Bukhari"},{"id":"৮1","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতের আলামত ও ইলম কমে যাওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইলম কমে যাওয়া, মূর্খতা, ব্যভিচার, মদপান ও নারী-পুরুষের সংখ্যার পরিবর্তন—কিয়ামতের কিছু আলামত।"},"heading":{"title":"কিয়ামতের আলামত: ইলম কমে যাওয়া ও মদপান বৃদ্ধি","description":"এই হাদিসে কিয়ামতের আলামত নিয়ে কয়েকটি স্পষ্ট সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, বিদ্যা উঠে যাবে বা কমে যাবে, মূর্খতা বেড়ে যাবে, ব্যভিচার বেশি হবে এবং মদপান বৃদ্ধি পাবে। আরও বলা হয়েছে, পুরুষের সংখ্যা কমে যাবে এবং নারীর সংখ্যা বেশি হবে, এমনকি একজন পুরুষ বহু নারীর দায়িত্বে থাকবে। হাদিসটি আমাদের বোঝায় যে সমাজে দ্বীনি জ্ঞান কমে গেলে ভুল কাজ সহজে ছড়িয়ে পড়ে। তাই কিয়ামতের আলামত হাদিস পড়ার উদ্দেশ্য শুধু ভবিষ্যৎ জানা নয়; বরং নিজের জীবনে ইলম, লজ্জাশীলতা, সংযম এবং হারাম থেকে বাঁচার চেষ্টা বাড়ানো। এই বার্তাটি সরল কিন্তু গভীর। তাই পাঠকের উচিত হাদিসটি পড়ে ভয় পাওয়ার পাশাপাশি নিজের ঘর, শিক্ষা ও চরিত্রের দিকে বাস্তবভাবে নজর দেওয়া।"},"teachings":["দ্বীনি ইলম কমে যাওয়া সমাজের জন্য বড় সতর্কতা।","মূর্খতা বাড়লে হারাম কাজের পথ সহজ হয়।","মদপান ও ব্যভিচার বৃদ্ধি কিয়ামতের আলামতের মধ্যে এসেছে।","হাদিসটি জ্ঞান ও নৈতিকতার গুরুত্ব মনে করিয়ে দেয়।"],"related_hadiths":[{"id":"80","book_id":"1","label":"Sahih Bukhari"},{"id":"81","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, গায়িকা ও বাদ্যযন্ত্রের ভয়াবহ সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপান, গায়িকা নিয়ে নাচ-গান ও বাদ্যযন্ত্রে মত্ততার কারণে বড় বিপদের বিষয়ে হাদিসের সতর্কতা।"},"heading":{"title":"মদ ও বাদ্যযন্ত্র সম্পর্কে ভয়াবহ সতর্কবার্তার হাদিস","description":"এই হাদিসের মূল বিষয় মদ, গায়িকা নিয়ে নাচ-গান এবং বাদ্যযন্ত্রে ব্যস্ত থাকা। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের মধ্যে এমন সময় আসবে যখন মানুষ নেশাদার দ্রব্য পান করবে, গায়িকাদের নিয়ে নাচ-গানে মত্ত হবে এবং বাদ্যযন্ত্র নিয়ে ব্যস্ত হবে। তখন তিন ধরনের ভয়াবহ বিপদের কথা বলা হয়েছে: ভূমি ধসে যাওয়া, উপর থেকে বা কোনো জাতির পক্ষ থেকে যুলুম চাপিয়ে দেওয়া, এবং অনেকের আকার-আকৃতি বিকৃত হওয়া। এখানে শিক্ষা হলো, আনন্দের নামে হারামকে সাধারণ বানানো নিরাপদ পথ নয়। হাদিসটি মানুষকে মদ, নাচ-গান এবং বাদ্যযন্ত্রের ফিতনা থেকে সাবধান হতে বলছে। তাই সতর্কতা শুরু হতে পারে নিজের পছন্দ, বন্ধু-বান্ধব এবং অবসর কাটানোর ধরন ঠিক করার মাধ্যমে।"},"teachings":["মদপানকে হাদিসে বড় বিপদের কারণ হিসেবে উল্লেখ করা হয়েছে।","গায়িকা ও নাচ-গানে মত্ত হওয়া থেকে সতর্ক করা হয়েছে।","বাদ্যযন্ত্রের প্রতি আসক্তি হাদিসে নিন্দিতভাবে এসেছে।","সমাজে হারাম কাজ ছড়ালে বিপদের আশঙ্কা বাড়ে।"],"related_hadiths":[{"id":"55৯0","book_id":"1","label":"Sahih Bukhari"},{"id":"4৯24","book_id":"4","label":"Sunan Abu Dawud"},{"id":"33৮৮","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, গায়িকা ও বাদ্যযন্ত্রের ভয়াবহ সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপান, গায়িকা নিয়ে নাচ-গান ও বাদ্যযন্ত্রে মত্ততার কারণে বড় বিপদের বিষয়ে হাদিসের সতর্কতা।"},"heading":{"title":"মদ ও বাদ্যযন্ত্র সম্পর্কে ভয়াবহ সতর্কবার্তার হাদিস","description":"এই হাদিসের মূল বিষয় মদ, গায়িকা নিয়ে নাচ-গান এবং বাদ্যযন্ত্রে ব্যস্ত থাকা। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের মধ্যে এমন সময় আসবে যখন মানুষ নেশাদার দ্রব্য পান করবে, গায়িকাদের নিয়ে নাচ-গানে মত্ত হবে এবং বাদ্যযন্ত্র নিয়ে ব্যস্ত হবে। তখন তিন ধরনের ভয়াবহ বিপদের কথা বলা হয়েছে: ভূমি ধসে যাওয়া, উপর থেকে বা কোনো জাতির পক্ষ থেকে যুলুম চাপিয়ে দেওয়া, এবং অনেকের আকার-আকৃতি বিকৃত হওয়া। এখানে শিক্ষা হলো, আনন্দের নামে হারামকে সাধারণ বানানো নিরাপদ পথ নয়। হাদিসটি মানুষকে মদ, নাচ-গান এবং বাদ্যযন্ত্রের ফিতনা থেকে সাবধান হতে বলছে। তাই সতর্কতা শুরু হতে পারে নিজের পছন্দ, বন্ধু-বান্ধব এবং অবসর কাটানোর ধরন ঠিক করার মাধ্যমে।"},"teachings":["মদপানকে হাদিসে বড় বিপদের কারণ হিসেবে উল্লেখ করা হয়েছে।","গায়িকা ও নাচ-গানে মত্ত হওয়া থেকে সতর্ক করা হয়েছে।","বাদ্যযন্ত্রের প্রতি আসক্তি হাদিসে নিন্দিতভাবে এসেছে।","সমাজে হারাম কাজ ছড়ালে বিপদের আশঙ্কা বাড়ে।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"4924","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | খাদ্য-পানীয় ও আমোদ-প্রমোদের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য-পানীয় ও বিনোদনে ডুবে থাকা কিছু লোকের ভয়াবহ রূপান্তর সম্পর্কে সতর্ক করা হয়েছে।"},"heading":{"title":"ভোগ-বিলাস ও আমোদ-প্রমোদের পরিণতি নিয়ে হাদিস","description":"এই হাদিসে ভোগ-বিলাস, খাদ্য-পানীয় এবং আমোদ-প্রমোদের বিষয়ে কঠোর সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের কিছু লোক রাত কাটাবে নানা ধরনের খাবার, পানীয় ও বিনোদনে ডুবে থেকে। এরপর তাদের সকাল হবে বানর ও শূকরের আকৃতিতে রূপান্তরিত হয়ে। হাদিসটি আনন্দ বা খাবারকে আলাদা করে নিষিদ্ধ বলছে না; বরং এমন জীবনধারার দিকে সতর্ক করছে যেখানে মানুষ আল্লাহভীতি ভুলে ভোগ, নেশা এবং অসংযত বিনোদনে ডুবে যায়। মূল শিক্ষা হলো, আনন্দ যেন ঈমান, লজ্জা ও হারাম-হালালের সীমা নষ্ট না করে। দুনিয়ার মজা সাময়িক, কিন্তু জবাবদিহি খুব বাস্তব। পরিবার ও সমাজে এমন পরিবেশ তৈরি করা দরকার, যেখানে আনন্দ থাকবে কিন্তু হারামের সীমা অতিক্রম করা হবে না।"},"teachings":["ভোগ-বিলাসে ডুবে আল্লাহভীতি ভুলে যাওয়া বিপজ্জনক।","বিনোদন যদি হারামের পথে নেয়, তা থেকে সতর্ক থাকা দরকার।","হাদিসে কিছু লোকের ভয়াবহ পরিণতির কথা এসেছে।","খাবার-পানীয় ও আনন্দের ক্ষেত্রেও সীমা মানা জরুরি।"],"related_hadiths":[{"id":"55৯0","book_id":"1","label":"Sahih Bukhari"},{"id":"4৯24","book_id":"4","label":"Sunan Abu Dawud"},{"id":"৮0","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | খাদ্য-পানীয় ও আমোদ-প্রমোদের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য-পানীয় ও বিনোদনে ডুবে থাকা কিছু লোকের ভয়াবহ রূপান্তর সম্পর্কে সতর্ক করা হয়েছে।"},"heading":{"title":"ভোগ-বিলাস ও আমোদ-প্রমোদের পরিণতি নিয়ে হাদিস","description":"এই হাদিসে ভোগ-বিলাস, খাদ্য-পানীয় এবং আমোদ-প্রমোদের বিষয়ে কঠোর সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের কিছু লোক রাত কাটাবে নানা ধরনের খাবার, পানীয় ও বিনোদনে ডুবে থেকে। এরপর তাদের সকাল হবে বানর ও শূকরের আকৃতিতে রূপান্তরিত হয়ে। হাদিসটি আনন্দ বা খাবারকে আলাদা করে নিষিদ্ধ বলছে না; বরং এমন জীবনধারার দিকে সতর্ক করছে যেখানে মানুষ আল্লাহভীতি ভুলে ভোগ, নেশা এবং অসংযত বিনোদনে ডুবে যায়। মূল শিক্ষা হলো, আনন্দ যেন ঈমান, লজ্জা ও হারাম-হালালের সীমা নষ্ট না করে। দুনিয়ার মজা সাময়িক, কিন্তু জবাবদিহি খুব বাস্তব। পরিবার ও সমাজে এমন পরিবেশ তৈরি করা দরকার, যেখানে আনন্দ থাকবে কিন্তু হারামের সীমা অতিক্রম করা হবে না।"},"teachings":["ভোগ-বিলাসে ডুবে আল্লাহভীতি ভুলে যাওয়া বিপজ্জনক।","বিনোদন যদি হারামের পথে নেয়, তা থেকে সতর্ক থাকা দরকার।","হাদিসে কিছু লোকের ভয়াবহ পরিণতির কথা এসেছে।","খাবার-পানীয় ও আনন্দের ক্ষেত্রেও সীমা মানা জরুরি।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"4924","book_id":"4","label":"Sunan Abu Dawud"},{"id":"80","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঈমান, সালাত, পরিবার ও গোনাহ থেকে বাঁচার দশ শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, ফরয সালাত ত্যাগ, মদপান, গোনাহ ও পরিবার বিষয়ে দশটি গুরুত্বপূর্ণ উপদেশ।"},"heading":{"title":"রাসূলের দশ উপদেশ: ঈমান, সালাত ও পরিবার জীবনের শিক্ষা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মু‘আয (রাঃ)-কে দশটি বিষয়ে উপদেশ দিয়েছেন। প্রথমে এসেছে আল্লাহর সাথে কাউকে শরীক না করা। এরপর পিতা-মাতার অবাধ্য না হওয়া, ইচ্ছা করে ফরয সালাত না ছাড়া, মদ পান না করা এবং গোনাহ থেকে বেঁচে থাকার কথা এসেছে। আরও আছে জিহাদ থেকে পলায়ন না করা, মহামারী দেখা দিলে যেখানে আছে সেখানে স্থির থাকা, সামর্থ্য অনুযায়ী পরিবারের জন্য ব্যয় করা, পরিবারকে আদব শেখানো এবং আল্লাহর ভয় মনে করিয়ে দেওয়া। হাদিসটি ব্যক্তিগত ঈমান, ইবাদত, পরিবার, শৃঙ্খলা ও দায়িত্ব—সব দিককে একসাথে মনে করিয়ে দেয়। এটি জীবনের জন্য সংক্ষিপ্ত কিন্তু শক্তিশালী দিকনির্দেশনা। ফলে এই দশ উপদেশ একজন মুসলিমকে ঘর, সমাজ ও ব্যক্তিগত ইবাদতে ভারসাম্য রাখতে সাহায্য করে।"},"teachings":["তাওহীদ হলো জীবনের সবচেয়ে মূল দায়িত্ব।","ইচ্ছা করে ফরয সালাত ত্যাগ করা বড় সতর্কতার বিষয়।","মদকে অশ্লীলতার মূল হিসেবে উল্লেখ করা হয়েছে।","পরিবারের ব্যয়, আদব ও আল্লাহভীতি শেখানো দায়িত্বের অংশ।"],"related_hadiths":[{"id":"527","book_id":"1","label":"Sahih Bukhari"},{"id":"5৯75","book_id":"1","label":"Sahih Bukhari"},{"id":"3371","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঈমান, সালাত, পরিবার ও গোনাহ থেকে বাঁচার দশ শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, ফরয সালাত ত্যাগ, মদপান, গোনাহ ও পরিবার বিষয়ে দশটি গুরুত্বপূর্ণ উপদেশ।"},"heading":{"title":"রাসূলের দশ উপদেশ: ঈমান, সালাত ও পরিবার জীবনের শিক্ষা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মু‘আয (রাঃ)-কে দশটি বিষয়ে উপদেশ দিয়েছেন। প্রথমে এসেছে আল্লাহর সাথে কাউকে শরীক না করা। এরপর পিতা-মাতার অবাধ্য না হওয়া, ইচ্ছা করে ফরয সালাত না ছাড়া, মদ পান না করা এবং গোনাহ থেকে বেঁচে থাকার কথা এসেছে। আরও আছে জিহাদ থেকে পলায়ন না করা, মহামারী দেখা দিলে যেখানে আছে সেখানে স্থির থাকা, সামর্থ্য অনুযায়ী পরিবারের জন্য ব্যয় করা, পরিবারকে আদব শেখানো এবং আল্লাহর ভয় মনে করিয়ে দেওয়া। হাদিসটি ব্যক্তিগত ঈমান, ইবাদত, পরিবার, শৃঙ্খলা ও দায়িত্ব—সব দিককে একসাথে মনে করিয়ে দেয়। এটি জীবনের জন্য সংক্ষিপ্ত কিন্তু শক্তিশালী দিকনির্দেশনা। ফলে এই দশ উপদেশ একজন মুসলিমকে ঘর, সমাজ ও ব্যক্তিগত ইবাদতে ভারসাম্য রাখতে সাহায্য করে।"},"teachings":["তাওহীদ হলো জীবনের সবচেয়ে মূল দায়িত্ব।","ইচ্ছা করে ফরয সালাত ত্যাগ করা বড় সতর্কতার বিষয়।","মদকে অশ্লীলতার মূল হিসেবে উল্লেখ করা হয়েছে।","পরিবারের ব্যয়, আদব ও আল্লাহভীতি শেখানো দায়িত্বের অংশ।"],"related_hadiths":[{"id":"527","book_id":"1","label":"Sahih Bukhari"},{"id":"5975","book_id":"1","label":"Sahih Bukhari"},{"id":"3371","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নেশাদার দ্রব্য সব অন্যায়ের চাবী","description":"$book_name$ $hadith_number$ - $chapter_name$. নেশাদার দ্রব্য থেকে দূরে থাকার উপদেশ এসেছে, কারণ তা বহু অন্যায়ের দরজা খুলে দিতে পারে।"},"heading":{"title":"নেশাদার দ্রব্য: সব অন্যায়ের চাবী সম্পর্কে হাদিস","description":"এই ছোট হাদিসটি খুব সহজ ভাষায় বড় শিক্ষা দেয়। আবূ দারদা (রাঃ) বলেন, তাঁর দোস্ত রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাঁকে অছিয়ত করেছেন—নেশাদার দ্রব্য পান করো না; নিশ্চয়ই তা সব ধরনের অন্যায়ের চাবী। এখানে মূল কথা হলো মদ বা নেশা মানুষকে শুধু একটি গোনাহে আটকে রাখে না; বরং তা বিবেক, লজ্জা এবং সংযম দুর্বল করে আরও অনেক ভুলের দিকে ঠেলে দিতে পারে। তাই ইসলাম শুধু শেষ ক্ষতি নয়, ক্ষতির দরজাও বন্ধ করতে শেখায়। এই হাদিস মাদক থেকে দূরে থাকা, সঙ্গ বাছাই করা এবং নিজের বিবেককে সুরক্ষিত রাখার পরিষ্কার বার্তা দেয়। বিশেষ করে তরুণদের জন্য এটি শক্ত বার্তা—নেশার শুরু ছোট মনে হলেও শেষটা খুব ক্ষতিকর হতে পারে।"},"teachings":["নেশাদার দ্রব্য থেকে দূরে থাকা নিরাপদ পথ।","মদকে বহু অন্যায়ের দরজা হিসেবে সতর্ক করা হয়েছে।","বিবেক নষ্ট হলে অন্য গোনাহে পড়ার ঝুঁকি বাড়ে।","ভালো উপদেশ মানা ঈমানি জীবনের অংশ।"],"related_hadiths":[{"id":"33৮৮","book_id":"6","label":"Sunan Ibn Majah"},{"id":"33৯0","book_id":"6","label":"Sunan Ibn Majah"},{"id":"36৮1","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নেশাদার দ্রব্য সব অন্যায়ের চাবী","description":"$book_name$ $hadith_number$ - $chapter_name$. নেশাদার দ্রব্য থেকে দূরে থাকার উপদেশ এসেছে, কারণ তা বহু অন্যায়ের দরজা খুলে দিতে পারে।"},"heading":{"title":"নেশাদার দ্রব্য: সব অন্যায়ের চাবী সম্পর্কে হাদিস","description":"এই ছোট হাদিসটি খুব সহজ ভাষায় বড় শিক্ষা দেয়। আবূ দারদা (রাঃ) বলেন, তাঁর দোস্ত রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাঁকে অছিয়ত করেছেন—নেশাদার দ্রব্য পান করো না; নিশ্চয়ই তা সব ধরনের অন্যায়ের চাবী। এখানে মূল কথা হলো মদ বা নেশা মানুষকে শুধু একটি গোনাহে আটকে রাখে না; বরং তা বিবেক, লজ্জা এবং সংযম দুর্বল করে আরও অনেক ভুলের দিকে ঠেলে দিতে পারে। তাই ইসলাম শুধু শেষ ক্ষতি নয়, ক্ষতির দরজাও বন্ধ করতে শেখায়। এই হাদিস মাদক থেকে দূরে থাকা, সঙ্গ বাছাই করা এবং নিজের বিবেককে সুরক্ষিত রাখার পরিষ্কার বার্তা দেয়। বিশেষ করে তরুণদের জন্য এটি শক্ত বার্তা—নেশার শুরু ছোট মনে হলেও শেষটা খুব ক্ষতিকর হতে পারে।"},"teachings":["নেশাদার দ্রব্য থেকে দূরে থাকা নিরাপদ পথ।","মদকে বহু অন্যায়ের দরজা হিসেবে সতর্ক করা হয়েছে।","বিবেক নষ্ট হলে অন্য গোনাহে পড়ার ঝুঁকি বাড়ে।","ভালো উপদেশ মানা ঈমানি জীবনের অংশ।"],"related_hadiths":[{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3390","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3681","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সব নেশাদার দ্রব্য হারাম হওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. হাদিসে স্পষ্ট বলা হয়েছে, যে কোনো নেশা উদ্রেককারী বস্তু হারাম; তাই মাদক থেকে দূরে থাকা জরুরি।"},"heading":{"title":"সব নেশাদার দ্রব্য হারাম: স্পষ্ট হাদিসের শিক্ষা","description":"এই হাদিসের মূল শিক্ষা খুব সরল: সব ধরনের নেশাদার দ্রব্য হারাম। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, “কুল্লু মুসকিরিন হারাম”—প্রতিটি নেশা উদ্রেককারী জিনিস হারাম। তাই বিষয়টি শুধু নির্দিষ্ট কোনো পানীয়ের মধ্যে সীমাবদ্ধ নয়। যে জিনিস মানুষের বিবেক ঢেকে দেয়, সিদ্ধান্ত নেওয়ার ক্ষমতা দুর্বল করে এবং তাকে ভুল কাজে ঠেলে দেয়, সেটি এই সতর্কতার মধ্যে পড়ে। হাদিসটি মুসলিমকে নাম বা ধরন নিয়ে চালাকি না করতে শেখায়। মদ, মাদক বা যে কোনো নেশা—মূল বিচার হলো তা নেশা সৃষ্টি করে কি না। ঈমানদার জীবনে বিবেক রক্ষা করা বড় দায়িত্ব। এ কারণে নেশা নিয়ে মজা, পরীক্ষা বা কৌতূহল দেখানোও মুমিনের জন্য ঝুঁকিপূর্ণ আচরণ হতে পারে।"},"teachings":["নেশা সৃষ্টি করে এমন জিনিস থেকে বাঁচতে হবে।","হারামকে নাম বদলে বৈধ ভাবা ঠিক নয়।","বিবেক ও সংযম রক্ষা করা ঈমানি জীবনের অংশ।","হাদিসটি মাদক বিষয়ে সংক্ষিপ্ত কিন্তু স্পষ্ট নির্দেশ দেয়।"],"related_hadiths":[{"id":"33৯0","book_id":"6","label":"Sunan Ibn Majah"},{"id":"33৯3","book_id":"6","label":"Sunan Ibn Majah"},{"id":"36৮1","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সব নেশাদার দ্রব্য হারাম হওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. হাদিসে স্পষ্ট বলা হয়েছে, যে কোনো নেশা উদ্রেককারী বস্তু হারাম; তাই মাদক থেকে দূরে থাকা জরুরি।"},"heading":{"title":"সব নেশাদার দ্রব্য হারাম: স্পষ্ট হাদিসের শিক্ষা","description":"এই হাদিসের মূল শিক্ষা খুব সরল: সব ধরনের নেশাদার দ্রব্য হারাম। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, “কুল্লু মুসকিরিন হারাম”—প্রতিটি নেশা উদ্রেককারী জিনিস হারাম। তাই বিষয়টি শুধু নির্দিষ্ট কোনো পানীয়ের মধ্যে সীমাবদ্ধ নয়। যে জিনিস মানুষের বিবেক ঢেকে দেয়, সিদ্ধান্ত নেওয়ার ক্ষমতা দুর্বল করে এবং তাকে ভুল কাজে ঠেলে দেয়, সেটি এই সতর্কতার মধ্যে পড়ে। হাদিসটি মুসলিমকে নাম বা ধরন নিয়ে চালাকি না করতে শেখায়। মদ, মাদক বা যে কোনো নেশা—মূল বিচার হলো তা নেশা সৃষ্টি করে কি না। ঈমানদার জীবনে বিবেক রক্ষা করা বড় দায়িত্ব। এ কারণে নেশা নিয়ে মজা, পরীক্ষা বা কৌতূহল দেখানোও মুমিনের জন্য ঝুঁকিপূর্ণ আচরণ হতে পারে।"},"teachings":["নেশা সৃষ্টি করে এমন জিনিস থেকে বাঁচতে হবে।","হারামকে নাম বদলে বৈধ ভাবা ঠিক নয়।","বিবেক ও সংযম রক্ষা করা ঈমানি জীবনের অংশ।","হাদিসটি মাদক বিষয়ে সংক্ষিপ্ত কিন্তু স্পষ্ট নির্দেশ দেয়।"],"related_hadiths":[{"id":"3390","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3393","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3681","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিবেক নষ্টকারী বস্তুই মদ—হারামের স্পষ্ট মানদণ্ড","description":"$book_name$ $hadith_number$ - $chapter_name$. যা বিবেকের ক্ষতি করে তা মদের অন্তর্ভুক্ত, আর সব ধরনের মদ হারাম—হাদিসের সরল শিক্ষা।"},"heading":{"title":"মদ কাকে বলে: বিবেক নষ্টকারী সব নেশার হুকুম","description":"এই হাদিসে মদের পরিচয় খুব সহজভাবে এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, প্রত্যেক নেশাদার বস্তুই মদ, আর প্রত্যেক মদই হারাম। অর্থাৎ মদ শুধু আঙুর, খেজুর বা নির্দিষ্ট কোনো নামে সীমাবদ্ধ নয়। যে জিনিস পান, খাওয়া বা গ্রহণ করলে মানুষের বিবেক ও বোঝার ক্ষমতা নষ্ট হয়, সেটি খামর বা মদের হুকুমের মধ্যে পড়ে। এই হাদিস নামের চেয়ে প্রভাবকে গুরুত্ব দেয়। তাই কোনো বস্তু আধুনিক নাম, নতুন প্যাকেট বা ভিন্ন রূপে এলেও যদি তা নেশা সৃষ্টি করে, তাহলে মুমিনের জন্য সতর্কতা একই থাকে। মূল কথা: বিবেক আল্লাহর বড় নেয়ামত, একে নেশার হাতে তুলে দেওয়া যাবে না। তাই পরিবারে ও সমাজে মাদককে সাধারণ বিষয় বানানো নয়, বরং পরিষ্কারভাবে ভুল বলা দরকার।"},"teachings":["নেশা সৃষ্টি করলে নাম বদলালেও হুকুম বদলায় না।","বিবেক নষ্টকারী বস্তু থেকে দূরে থাকা জরুরি।","সব ধরনের মদ হারাম—হাদিসে স্পষ্ট বলা হয়েছে।","মুমিনের জন্য হালাল-হারামের মানদণ্ড প্রভাবের ওপরও নির্ভর করে।"],"related_hadiths":[{"id":"33৮৮","book_id":"6","label":"Sunan Ibn Majah"},{"id":"33৯3","book_id":"6","label":"Sunan Ibn Majah"},{"id":"36৮1","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিবেক নষ্টকারী বস্তুই মদ—হারামের স্পষ্ট মানদণ্ড","description":"$book_name$ $hadith_number$ - $chapter_name$. যা বিবেকের ক্ষতি করে তা মদের অন্তর্ভুক্ত, আর সব ধরনের মদ হারাম—হাদিসের সরল শিক্ষা।"},"heading":{"title":"মদ কাকে বলে: বিবেক নষ্টকারী সব নেশার হুকুম","description":"এই হাদিসে মদের পরিচয় খুব সহজভাবে এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, প্রত্যেক নেশাদার বস্তুই মদ, আর প্রত্যেক মদই হারাম। অর্থাৎ মদ শুধু আঙুর, খেজুর বা নির্দিষ্ট কোনো নামে সীমাবদ্ধ নয়। যে জিনিস পান, খাওয়া বা গ্রহণ করলে মানুষের বিবেক ও বোঝার ক্ষমতা নষ্ট হয়, সেটি খামর বা মদের হুকুমের মধ্যে পড়ে। এই হাদিস নামের চেয়ে প্রভাবকে গুরুত্ব দেয়। তাই কোনো বস্তু আধুনিক নাম, নতুন প্যাকেট বা ভিন্ন রূপে এলেও যদি তা নেশা সৃষ্টি করে, তাহলে মুমিনের জন্য সতর্কতা একই থাকে। মূল কথা: বিবেক আল্লাহর বড় নেয়ামত, একে নেশার হাতে তুলে দেওয়া যাবে না। তাই পরিবারে ও সমাজে মাদককে সাধারণ বিষয় বানানো নয়, বরং পরিষ্কারভাবে ভুল বলা দরকার।"},"teachings":["নেশা সৃষ্টি করলে নাম বদলালেও হুকুম বদলায় না।","বিবেক নষ্টকারী বস্তু থেকে দূরে থাকা জরুরি।","সব ধরনের মদ হারাম—হাদিসে স্পষ্ট বলা হয়েছে।","মুমিনের জন্য হালাল-হারামের মানদণ্ড প্রভাবের ওপরও নির্ভর করে।"],"related_hadiths":[{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3393","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3681","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বেশি নেশা হলে কমও হারাম—সতর্কতার হাদিস","description":"$book_name$ $hadith_number$ - $chapter_name$. যে বস্তু বেশি খেলে নেশা হয়, তার অল্প পরিমাণও হারাম—হারাম থেকে দূরে থাকার পরিষ্কার শিক্ষা।"},"heading":{"title":"যার বেশি নেশা আনে, তার কমও হারাম: মাদক বিষয়ে হাদিস","description":"এই হাদিসে নেশাদার বস্তু সম্পর্কে একটি গুরুত্বপূর্ণ নীতি এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে বস্তু বেশি পরিমাণে গ্রহণ করলে বিবেকের ক্ষতি হয় বা নেশা আসে, তার কম পরিমাণও হারাম। এর মানে হলো, “অল্প খেলে ক্ষতি নেই”—এমন অজুহাত দিয়ে নেশার দরজা খোলা যাবে না। ইসলাম মানুষের বিবেক, আত্মসম্মান ও ইবাদতকে সুরক্ষিত রাখতে চায়। তাই যে জিনিস বেশি হলে মানুষকে মাতাল করে, সেটির সামান্য অংশও নিরাপদ খেলার বিষয় নয়। এই হাদিস মাদক, অ্যালকোহল ও নেশা নিয়ে আপস না করার শিক্ষা দেয়। ছোট ছাড় অনেক সময় বড় বিপদের শুরু হতে পারে। এই নীতি মানুষকে সন্দেহজনক নেশাদার জিনিস থেকেও দূরে থাকতে সাহায্য করে।"},"teachings":["অল্প নেশাদার দ্রব্যকেও হালকা মনে করা ঠিক নয়।","যার বেশি নেশা আনে, তার কমও হারাম।","হারামের দরজা শুরুতেই বন্ধ করা নিরাপদ।","বিবেক রক্ষা করা মুমিনের গুরুত্বপূর্ণ দায়িত্ব।"],"related_hadiths":[{"id":"33৮৮","book_id":"6","label":"Sunan Ibn Majah"},{"id":"33৯0","book_id":"6","label":"Sunan Ibn Majah"},{"id":"36৮1","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বেশি নেশা হলে কমও হারাম—সতর্কতার হাদিস","description":"$book_name$ $hadith_number$ - $chapter_name$. যে বস্তু বেশি খেলে নেশা হয়, তার অল্প পরিমাণও হারাম—হারাম থেকে দূরে থাকার পরিষ্কার শিক্ষা।"},"heading":{"title":"যার বেশি নেশা আনে, তার কমও হারাম: মাদক বিষয়ে হাদিস","description":"এই হাদিসে নেশাদার বস্তু সম্পর্কে একটি গুরুত্বপূর্ণ নীতি এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে বস্তু বেশি পরিমাণে গ্রহণ করলে বিবেকের ক্ষতি হয় বা নেশা আসে, তার কম পরিমাণও হারাম। এর মানে হলো, “অল্প খেলে ক্ষতি নেই”—এমন অজুহাত দিয়ে নেশার দরজা খোলা যাবে না। ইসলাম মানুষের বিবেক, আত্মসম্মান ও ইবাদতকে সুরক্ষিত রাখতে চায়। তাই যে জিনিস বেশি হলে মানুষকে মাতাল করে, সেটির সামান্য অংশও নিরাপদ খেলার বিষয় নয়। এই হাদিস মাদক, অ্যালকোহল ও নেশা নিয়ে আপস না করার শিক্ষা দেয়। ছোট ছাড় অনেক সময় বড় বিপদের শুরু হতে পারে। এই নীতি মানুষকে সন্দেহজনক নেশাদার জিনিস থেকেও দূরে থাকতে সাহায্য করে।"},"teachings":["অল্প নেশাদার দ্রব্যকেও হালকা মনে করা ঠিক নয়।","যার বেশি নেশা আনে, তার কমও হারাম।","হারামের দরজা শুরুতেই বন্ধ করা নিরাপদ।","বিবেক রক্ষা করা মুমিনের গুরুত্বপূর্ণ দায়িত্ব।"],"related_hadiths":[{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3390","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3681","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে রবকে দেখা ও আমলের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে রবকে দেখা, নেয়ামতের জবাবদিহি ও অঙ্গ-প্রত্যঙ্গের সাক্ষ্য—এই হাদিসে সতর্কতা এসেছে।"},"heading":{"title":"কিয়ামতের দিন রবকে দেখা ও অঙ্গের সাক্ষ্যের শিক্ষা","description":"এই হাদিসে সাহাবীরা জিজ্ঞেস করেছেন, কিয়ামতের দিন তারা কি তাদের রবকে দেখতে পাবে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সূর্য ও পূর্ণিমার চাঁদ দেখার উদাহরণ দিয়ে বলেছেন, রবকে দেখতে অসুবিধা হবে না। এরপর তিনি বান্দাদের জবাবদিহির কথা বলেন। আল্লাহ বান্দাকে নিজের দেওয়া মর্যাদা, নেতৃত্ব, পরিবার ও নিয়ামতের কথা স্মরণ করাবেন। কেউ আল্লাহর সাক্ষাতের কথা অস্বীকার করেছিল বলে তাকে কঠিন পরিণতির কথা বলা হবে। আর এক ব্যক্তি নিজের ভালো কাজের কথা বললেও তার মুখে মোহর লাগিয়ে অঙ্গ-প্রত্যঙ্গকে সাক্ষ্য দিতে বলা হবে। হাদিসে তাকে মুনাফিক বলা হয়েছে। এই হাদিস নেয়ামত, হিসাব, মুনাফিকী এবং সত্য সাক্ষ্যের কথা মনে করায়।"},"teachings":["কিয়ামতের দিন রবকে দেখার বিষয়টি হাদিসে এসেছে।","আল্লাহর দেওয়া নিয়ামতের জন্য জবাবদিহি থাকবে।","মুখে দাবি করলেই যথেষ্ট নয়, কাজের সাক্ষ্যও আসবে।","মুনাফিকী আচরণ আল্লাহর ক্রোধের কারণ হতে পারে।"],"related_hadiths":[{"id":"2৯6৮","book_id":"2","label":"Sahih Muslim"},{"id":"7440","book_id":"1","label":"Sahih Bukhari"},{"id":"5555","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে রবকে দেখা ও আমলের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে রবকে দেখা, নেয়ামতের জবাবদিহি ও অঙ্গ-প্রত্যঙ্গের সাক্ষ্য—এই হাদিসে সতর্কতা এসেছে।"},"heading":{"title":"কিয়ামতের দিন রবকে দেখা ও অঙ্গের সাক্ষ্যের শিক্ষা","description":"এই হাদিসে সাহাবীরা জিজ্ঞেস করেছেন, কিয়ামতের দিন তারা কি তাদের রবকে দেখতে পাবে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সূর্য ও পূর্ণিমার চাঁদ দেখার উদাহরণ দিয়ে বলেছেন, রবকে দেখতে অসুবিধা হবে না। এরপর তিনি বান্দাদের জবাবদিহির কথা বলেন। আল্লাহ বান্দাকে নিজের দেওয়া মর্যাদা, নেতৃত্ব, পরিবার ও নিয়ামতের কথা স্মরণ করাবেন। কেউ আল্লাহর সাক্ষাতের কথা অস্বীকার করেছিল বলে তাকে কঠিন পরিণতির কথা বলা হবে। আর এক ব্যক্তি নিজের ভালো কাজের কথা বললেও তার মুখে মোহর লাগিয়ে অঙ্গ-প্রত্যঙ্গকে সাক্ষ্য দিতে বলা হবে। হাদিসে তাকে মুনাফিক বলা হয়েছে। এই হাদিস নেয়ামত, হিসাব, মুনাফিকী এবং সত্য সাক্ষ্যের কথা মনে করায়।"},"teachings":["কিয়ামতের দিন রবকে দেখার বিষয়টি হাদিসে এসেছে।","আল্লাহর দেওয়া নিয়ামতের জন্য জবাবদিহি থাকবে।","মুখে দাবি করলেই যথেষ্ট নয়, কাজের সাক্ষ্যও আসবে।","মুনাফিকী আচরণ আল্লাহর ক্রোধের কারণ হতে পারে।"],"related_hadiths":[{"id":"2968","book_id":"2","label":"Sahih Muslim"},{"id":"7440","book_id":"1","label":"Sahih Bukhari"},{"id":"5555","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, মৃতপ্রাণী ও শূকরের মূল্য হারাম","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ মদ, মৃতপ্রাণী ও শূকর এবং এগুলোর মূল্য হারাম করেছেন—হারাম আয় থেকে বাঁচার শিক্ষা।"},"heading":{"title":"হারাম আয়: মদ ও নিষিদ্ধ বস্তুর মূল্য সম্পর্কে হাদিস","description":"এই হাদিসে শুধু মদ পান নয়, মদের মূল্য বা এর অর্থনৈতিক লেনদেনের দিকেও সতর্ক করা হয়েছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ নেশাদার দ্রব্য এবং তার মূল্য হারাম করেছেন। একইভাবে মৃতপ্রাণী ও তার মূল্য, শূকর ও তার মূল্যও হারাম করা হয়েছে। এখানে গুরুত্বপূর্ণ শিক্ষা হলো—কোনো বস্তু হারাম হলে তার ব্যবসা, মূল্য এবং লাভও সতর্কতার বিষয় হয়। মানুষ অনেক সময় নিজে না খেয়ে বিক্রি করে লাভ নেওয়াকে হালকা মনে করতে পারে। কিন্তু এই হাদিস জানায়, হারাম জিনিস থেকে অর্থ উপার্জনও নিরাপদ নয়। রিযিক পবিত্র রাখা ঈমানি জীবনের বড় অংশ। তাই আয়ের উৎস যাচাই করা এবং সন্দেহজনক লাভ থেকে বাঁচা একজন মুসলিমের নিত্যদিনের দায়িত্ব।"},"teachings":["মদ শুধু পান নয়, তার মূল্যও হারাম বলা হয়েছে।","হারাম বস্তু থেকে আয় নেওয়া থেকে বাঁচতে হবে।","রিযিক পবিত্র রাখা মুসলিম জীবনের গুরুত্বপূর্ণ কাজ।","মৃতপ্রাণী ও শূকরের মূল্য সম্পর্কেও হাদিসে সতর্কতা এসেছে।"],"related_hadiths":[{"id":"33৮৮","book_id":"6","label":"Sunan Ibn Majah"},{"id":"55৯0","book_id":"1","label":"Sahih Bukhari"},{"id":"36৮1","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, মৃতপ্রাণী ও শূকরের মূল্য হারাম","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ মদ, মৃতপ্রাণী ও শূকর এবং এগুলোর মূল্য হারাম করেছেন—হারাম আয় থেকে বাঁচার শিক্ষা।"},"heading":{"title":"হারাম আয়: মদ ও নিষিদ্ধ বস্তুর মূল্য সম্পর্কে হাদিস","description":"এই হাদিসে শুধু মদ পান নয়, মদের মূল্য বা এর অর্থনৈতিক লেনদেনের দিকেও সতর্ক করা হয়েছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ নেশাদার দ্রব্য এবং তার মূল্য হারাম করেছেন। একইভাবে মৃতপ্রাণী ও তার মূল্য, শূকর ও তার মূল্যও হারাম করা হয়েছে। এখানে গুরুত্বপূর্ণ শিক্ষা হলো—কোনো বস্তু হারাম হলে তার ব্যবসা, মূল্য এবং লাভও সতর্কতার বিষয় হয়। মানুষ অনেক সময় নিজে না খেয়ে বিক্রি করে লাভ নেওয়াকে হালকা মনে করতে পারে। কিন্তু এই হাদিস জানায়, হারাম জিনিস থেকে অর্থ উপার্জনও নিরাপদ নয়। রিযিক পবিত্র রাখা ঈমানি জীবনের বড় অংশ। তাই আয়ের উৎস যাচাই করা এবং সন্দেহজনক লাভ থেকে বাঁচা একজন মুসলিমের নিত্যদিনের দায়িত্ব।"},"teachings":["মদ শুধু পান নয়, তার মূল্যও হারাম বলা হয়েছে।","হারাম বস্তু থেকে আয় নেওয়া থেকে বাঁচতে হবে।","রিযিক পবিত্র রাখা মুসলিম জীবনের গুরুত্বপূর্ণ কাজ।","মৃতপ্রাণী ও শূকরের মূল্য সম্পর্কেও হাদিসে সতর্কতা এসেছে।"],"related_hadiths":[{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"3681","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, মৃতপ্রাণী, শূকর ও মূর্তি বিক্রি হারাম","description":"$book_name$ $hadith_number$ - $chapter_name$. মক্কা বিজয়ের বছরে নবীজি মদ, মৃতপ্রাণী, শূকর ও মূর্তির ক্রয়-বিক্রয় হারাম হওয়ার কথা বলেছেন।"},"heading":{"title":"হারাম ব্যবসা: মদ ও মূর্তি ক্রয়-বিক্রয় সম্পর্কে হাদিস","description":"এই হাদিসে মক্কা বিজয়ের বছরে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর একটি ঘোষণা এসেছে। তিনি বলেছেন, আল্লাহ মদ, মৃতপ্রাণী, শূকর এবং মূর্তির ক্রয়-বিক্রয় হারাম করেছেন। এখানে শিক্ষা শুধু কিছু জিনিস খাওয়া বা ব্যবহার না করার মধ্যে সীমাবদ্ধ নয়; বরং সেগুলোকে ব্যবসার পণ্য বানানো থেকেও বারণ করা হয়েছে। ইসলামে রিযিকের পবিত্রতা খুব গুরুত্বপূর্ণ। লাভ বেশি হলেই কোনো ব্যবসা ভালো হয়ে যায় না। হালাল-হারামের সীমা মানতে হয়। এই হাদিস ব্যবসায়ী, ক্রেতা ও সমাজ—সবার জন্য সতর্কতা: এমন পণ্য থেকে দূরে থাকা দরকার, যাকে আল্লাহ হারাম করেছেন। তাই ব্যবসায় সততা মানে শুধু ওজন ঠিক রাখা নয়, পণ্যটিও হালাল হওয়া। বিশেষ করে যে পণ্য মানুষের ঈমান, বিবেক বা তাওহীদের ক্ষতি করে, তা থেকে আয় করা মুমিনের জন্য নিরাপদ পথ নয়।"},"teachings":["হারাম জিনিস ব্যবসার পণ্য বানানো যায় না।","মদ, মৃতপ্রাণী, শূকর ও মূর্তির ক্রয়-বিক্রয় নিষিদ্ধ বলা হয়েছে।","লাভের চেয়ে হালাল রিযিক বেশি গুরুত্বপূর্ণ।","ব্যবসায়ও আল্লাহর সীমা মানা জরুরি।"],"related_hadiths":[{"id":"34৮5","book_id":"4","label":"Sunan Abu Dawud"},{"id":"33৮৮","book_id":"6","label":"Sunan Ibn Majah"},{"id":"55৯0","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, মৃতপ্রাণী, শূকর ও মূর্তি বিক্রি হারাম","description":"$book_name$ $hadith_number$ - $chapter_name$. মক্কা বিজয়ের বছরে নবীজি মদ, মৃতপ্রাণী, শূকর ও মূর্তির ক্রয়-বিক্রয় হারাম হওয়ার কথা বলেছেন।"},"heading":{"title":"হারাম ব্যবসা: মদ ও মূর্তি ক্রয়-বিক্রয় সম্পর্কে হাদিস","description":"এই হাদিসে মক্কা বিজয়ের বছরে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর একটি ঘোষণা এসেছে। তিনি বলেছেন, আল্লাহ মদ, মৃতপ্রাণী, শূকর এবং মূর্তির ক্রয়-বিক্রয় হারাম করেছেন। এখানে শিক্ষা শুধু কিছু জিনিস খাওয়া বা ব্যবহার না করার মধ্যে সীমাবদ্ধ নয়; বরং সেগুলোকে ব্যবসার পণ্য বানানো থেকেও বারণ করা হয়েছে। ইসলামে রিযিকের পবিত্রতা খুব গুরুত্বপূর্ণ। লাভ বেশি হলেই কোনো ব্যবসা ভালো হয়ে যায় না। হালাল-হারামের সীমা মানতে হয়। এই হাদিস ব্যবসায়ী, ক্রেতা ও সমাজ—সবার জন্য সতর্কতা: এমন পণ্য থেকে দূরে থাকা দরকার, যাকে আল্লাহ হারাম করেছেন। তাই ব্যবসায় সততা মানে শুধু ওজন ঠিক রাখা নয়, পণ্যটিও হালাল হওয়া। বিশেষ করে যে পণ্য মানুষের ঈমান, বিবেক বা তাওহীদের ক্ষতি করে, তা থেকে আয় করা মুমিনের জন্য নিরাপদ পথ নয়।"},"teachings":["হারাম জিনিস ব্যবসার পণ্য বানানো যায় না।","মদ, মৃতপ্রাণী, শূকর ও মূর্তির ক্রয়-বিক্রয় নিষিদ্ধ বলা হয়েছে।","লাভের চেয়ে হালাল রিযিক বেশি গুরুত্বপূর্ণ।","ব্যবসায়ও আল্লাহর সীমা মানা জরুরি।"],"related_hadiths":[{"id":"3485","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5590","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপান, পিতামাতার অবাধ্যতা ও খোটা দানের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদে আসক্তি, পিতা-মাতার অবাধ্যতা ও দান করে খোটা দেওয়ার ভয়াবহ পরিণতি সম্পর্কে সতর্কতা।"},"heading":{"title":"মদপানকারী, অবাধ্য সন্তান ও খোটা দানকারী সম্পর্কে হাদিস","description":"এই হাদিসে তিনটি কাজের বিষয়ে কঠোর সতর্কতা এসেছে: নেশাদার দ্রব্য পান করা, পিতা-মাতার অবাধ্য হওয়া এবং দান করে খোটা দেওয়া। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, এ ধরনের লোক জান্নাতে যাবে না—হাদিসের ভাষা অত্যন্ত সতর্কতামূলক। এর অর্থ বুঝতে আল্লাহর রহমত, তাওবা এবং অন্যান্য শরঈ বিষয় আলাদা আলোচনার বিষয়; তবে এই হাদিসের সরাসরি শিক্ষা হলো, এসব কাজ খুব ভয়াবহ। মদ মানুষের বিবেক নষ্ট করে, পিতা-মাতার অবাধ্যতা সম্পর্ক ভেঙে দেয়, আর খোটা দান সদকার সৌন্দর্য নষ্ট করে। তাই মুমিনের উচিত এসব কাজ থেকে দূরে থাকা এবং ভুল হলে দ্রুত তাওবার পথে ফেরা। তাই এই তিনটি বিষয়ে পরিবারে নিয়মিত নসিহত, আত্মসমালোচনা এবং সংশোধনের পরিবেশ থাকা দরকার।"},"teachings":["মদে আসক্তি ভয়াবহ গোনাহের দিকে নিয়ে যেতে পারে।","পিতা-মাতার অবাধ্যতা থেকে সতর্ক থাকতে হবে।","দান করে খোটা দেওয়া দানের সৌন্দর্য নষ্ট করে।","হাদিসটি তিনটি গুরুতর আচরণ থেকে বাঁচার শিক্ষা দেয়।"],"related_hadiths":[{"id":"5৯75","book_id":"1","label":"Sahih Bukhari"},{"id":"3371","book_id":"6","label":"Sunan Ibn Majah"},{"id":"33৮৮","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপান, পিতামাতার অবাধ্যতা ও খোটা দানের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদে আসক্তি, পিতা-মাতার অবাধ্যতা ও দান করে খোটা দেওয়ার ভয়াবহ পরিণতি সম্পর্কে সতর্কতা।"},"heading":{"title":"মদপানকারী, অবাধ্য সন্তান ও খোটা দানকারী সম্পর্কে হাদিস","description":"এই হাদিসে তিনটি কাজের বিষয়ে কঠোর সতর্কতা এসেছে: নেশাদার দ্রব্য পান করা, পিতা-মাতার অবাধ্য হওয়া এবং দান করে খোটা দেওয়া। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, এ ধরনের লোক জান্নাতে যাবে না—হাদিসের ভাষা অত্যন্ত সতর্কতামূলক। এর অর্থ বুঝতে আল্লাহর রহমত, তাওবা এবং অন্যান্য শরঈ বিষয় আলাদা আলোচনার বিষয়; তবে এই হাদিসের সরাসরি শিক্ষা হলো, এসব কাজ খুব ভয়াবহ। মদ মানুষের বিবেক নষ্ট করে, পিতা-মাতার অবাধ্যতা সম্পর্ক ভেঙে দেয়, আর খোটা দান সদকার সৌন্দর্য নষ্ট করে। তাই মুমিনের উচিত এসব কাজ থেকে দূরে থাকা এবং ভুল হলে দ্রুত তাওবার পথে ফেরা। তাই এই তিনটি বিষয়ে পরিবারে নিয়মিত নসিহত, আত্মসমালোচনা এবং সংশোধনের পরিবেশ থাকা দরকার।"},"teachings":["মদে আসক্তি ভয়াবহ গোনাহের দিকে নিয়ে যেতে পারে।","পিতা-মাতার অবাধ্যতা থেকে সতর্ক থাকতে হবে।","দান করে খোটা দেওয়া দানের সৌন্দর্য নষ্ট করে।","হাদিসটি তিনটি গুরুতর আচরণ থেকে বাঁচার শিক্ষা দেয়।"],"related_hadiths":[{"id":"5975","book_id":"1","label":"Sahih Bukhari"},{"id":"3371","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ পান করলে ৪০ দিনের অসন্তুষ্টির সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপানের পর আল্লাহর অসন্তুষ্টির কথা এসেছে, যা মাদক থেকে দূরে থাকার কঠোর সতর্কবার্তা।"},"heading":{"title":"মদ পান করলে ৪০ দিন আল্লাহর অসন্তুষ্টি: হাদিসের শিক্ষা","description":"এই হাদিসে মদপানের পরিণতি নিয়ে খুব কঠোর সতর্কতা এসেছে। বলা হয়েছে, যে ব্যক্তি মদ পান করবে, আল্লাহ তার উপর ৪০ দিন সন্তুষ্ট হবেন না। এখানে সংখ্যাটি হাদিসের সরাসরি ভাষায় এসেছে, তাই বিষয়টি হালকা করে দেখার সুযোগ নেই। মদ শুধু শরীরের ক্ষতি নয়; এটি বান্দার আল্লাহর সাথে সম্পর্ক, ইবাদতের মনোভাব এবং নৈতিক শক্তিকেও আঘাত করে। হাদিসটি আমাদের শেখায়, নেশা সাময়িক আনন্দের বিষয় নয়; এর আধ্যাত্মিক ক্ষতিও ভয়াবহ। তাই মুমিনের উচিত মদ থেকে দূরে থাকা, এমন সঙ্গ এড়িয়ে চলা যা তাকে মদের দিকে টানে, এবং ভুল হলে দেরি না করে তাওবার পথ ধরা। এ কারণে মদ থেকে বাঁচা শুধু ব্যক্তিগত স্বাস্থ্যরক্ষা নয়, আল্লাহর সন্তুষ্টি খোঁজারও অংশ।"},"teachings":["মদপান আল্লাহর অসন্তুষ্টির কারণ হতে পারে।","৪০ দিনের সতর্কতা হাদিসে সরাসরি এসেছে।","নেশা ঈমানি জীবনের জন্য ক্ষতিকর।","ভুল হলে তাওবার দিকে দ্রুত ফিরতে হবে।"],"related_hadiths":[{"id":"3371","book_id":"6","label":"Sunan Ibn Majah"},{"id":"33৮৮","book_id":"6","label":"Sunan Ibn Majah"},{"id":"557৮","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ পান করলে ৪০ দিনের অসন্তুষ্টির সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপানের পর আল্লাহর অসন্তুষ্টির কথা এসেছে, যা মাদক থেকে দূরে থাকার কঠোর সতর্কবার্তা।"},"heading":{"title":"মদ পান করলে ৪০ দিন আল্লাহর অসন্তুষ্টি: হাদিসের শিক্ষা","description":"এই হাদিসে মদপানের পরিণতি নিয়ে খুব কঠোর সতর্কতা এসেছে। বলা হয়েছে, যে ব্যক্তি মদ পান করবে, আল্লাহ তার উপর ৪০ দিন সন্তুষ্ট হবেন না। এখানে সংখ্যাটি হাদিসের সরাসরি ভাষায় এসেছে, তাই বিষয়টি হালকা করে দেখার সুযোগ নেই। মদ শুধু শরীরের ক্ষতি নয়; এটি বান্দার আল্লাহর সাথে সম্পর্ক, ইবাদতের মনোভাব এবং নৈতিক শক্তিকেও আঘাত করে। হাদিসটি আমাদের শেখায়, নেশা সাময়িক আনন্দের বিষয় নয়; এর আধ্যাত্মিক ক্ষতিও ভয়াবহ। তাই মুমিনের উচিত মদ থেকে দূরে থাকা, এমন সঙ্গ এড়িয়ে চলা যা তাকে মদের দিকে টানে, এবং ভুল হলে দেরি না করে তাওবার পথ ধরা। এ কারণে মদ থেকে বাঁচা শুধু ব্যক্তিগত স্বাস্থ্যরক্ষা নয়, আল্লাহর সন্তুষ্টি খোঁজারও অংশ।"},"teachings":["মদপান আল্লাহর অসন্তুষ্টির কারণ হতে পারে।","৪০ দিনের সতর্কতা হাদিসে সরাসরি এসেছে।","নেশা ঈমানি জীবনের জন্য ক্ষতিকর।","ভুল হলে তাওবার দিকে দ্রুত ফিরতে হবে।"],"related_hadiths":[{"id":"3371","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5578","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপানের শাস্তি ও সমাজে হারাম ঠেকানোর শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি মদপানকারীকে জুতা ও বেত দিয়ে ৪০ বার শাস্তি দিতেন; পরে উমর (রাঃ) ৮০ বেত্রাঘাত করেন।"},"heading":{"title":"মদপানের শাস্তি: শরীয়তী সতর্কতা ও সামাজিক শিক্ষা","description":"এই হাদিসে মদপানের শরীয়তী শাস্তির একটি ঘটনা এসেছে। আনাস (রাঃ) বর্ণনা করেছেন, রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) নেশাদার দ্রব্য পানকারীকে জুতা ও বেতের মাধ্যমে ৪০ বার মারতেন। পরে উমর (রাঃ)-এর সময়ে যখন নেশাদার দ্রব্য পানকারীদের সংখ্যা বেড়ে যায়, তিনি ৮০ বেত্রাঘাত করতেন বলে বর্ণনায় এসেছে। এই হাদিসের আলোচনা বিচার ও শাস্তির বিষয়, তাই তা ব্যক্তিগতভাবে প্রয়োগের বিষয় নয়; এটি দায়িত্বশীল বিচারব্যবস্থার সঙ্গে সম্পর্কিত। সরাসরি শিক্ষা হলো, ইসলাম মদপানকে ব্যক্তিগত পছন্দ হিসেবে দেখে না; বরং এটি ব্যক্তি, পরিবার ও সমাজের ক্ষতি ডেকে আনতে পারে। তাই মাদক থেকে দূরে থাকা জরুরি। তাই পরিবার, শিক্ষা ও সমাজে মাদকবিরোধী সচেতনতা গড়ে তোলা এই হাদিসের সাথে মানানসই শিক্ষা।"},"teachings":["মদপানকে শরীয়তে গুরুতর অপরাধ হিসেবে দেখা হয়েছে।","শাস্তির বিষয় দায়িত্বশীল বিচারব্যবস্থার সাথে সম্পর্কিত।","সমাজে মাদক ছড়ানো বড় ক্ষতির কারণ হতে পারে।","মাদক থেকে বাঁচা ব্যক্তি ও সমাজ উভয়ের জন্য দরকার।"],"related_hadiths":[{"id":"6773","book_id":"1","label":"Sahih Bukhari"},{"id":"33৮৮","book_id":"6","label":"Sunan Ibn Majah"},{"id":"36৮1","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপানের শাস্তি ও সমাজে হারাম ঠেকানোর শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি মদপানকারীকে জুতা ও বেত দিয়ে ৪০ বার শাস্তি দিতেন; পরে উমর (রাঃ) ৮০ বেত্রাঘাত করেন।"},"heading":{"title":"মদপানের শাস্তি: শরীয়তী সতর্কতা ও সামাজিক শিক্ষা","description":"এই হাদিসে মদপানের শরীয়তী শাস্তির একটি ঘটনা এসেছে। আনাস (রাঃ) বর্ণনা করেছেন, রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) নেশাদার দ্রব্য পানকারীকে জুতা ও বেতের মাধ্যমে ৪০ বার মারতেন। পরে উমর (রাঃ)-এর সময়ে যখন নেশাদার দ্রব্য পানকারীদের সংখ্যা বেড়ে যায়, তিনি ৮০ বেত্রাঘাত করতেন বলে বর্ণনায় এসেছে। এই হাদিসের আলোচনা বিচার ও শাস্তির বিষয়, তাই তা ব্যক্তিগতভাবে প্রয়োগের বিষয় নয়; এটি দায়িত্বশীল বিচারব্যবস্থার সঙ্গে সম্পর্কিত। সরাসরি শিক্ষা হলো, ইসলাম মদপানকে ব্যক্তিগত পছন্দ হিসেবে দেখে না; বরং এটি ব্যক্তি, পরিবার ও সমাজের ক্ষতি ডেকে আনতে পারে। তাই মাদক থেকে দূরে থাকা জরুরি। তাই পরিবার, শিক্ষা ও সমাজে মাদকবিরোধী সচেতনতা গড়ে তোলা এই হাদিসের সাথে মানানসই শিক্ষা।"},"teachings":["মদপানকে শরীয়তে গুরুতর অপরাধ হিসেবে দেখা হয়েছে।","শাস্তির বিষয় দায়িত্বশীল বিচারব্যবস্থার সাথে সম্পর্কিত।","সমাজে মাদক ছড়ানো বড় ক্ষতির কারণ হতে পারে।","মাদক থেকে বাঁচা ব্যক্তি ও সমাজ উভয়ের জন্য দরকার।"],"related_hadiths":[{"id":"6773","book_id":"1","label":"Sahih Bukhari"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3681","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যেনা, রেশম, মদ ও বাদ্যযন্ত্রকে হালাল ভাবার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি বলেছেন, কিছু লোক যেনা, রেশম, মদ ও বাদ্যযন্ত্রকে হালাল মনে করবে—এটি গুরুতর সতর্কতা।"},"heading":{"title":"হারামকে হালাল মনে করা: মদ ও বাদ্যযন্ত্র সম্পর্কে হাদিস","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ভবিষ্যতের একটি বিপদের কথা বলেছেন। তাঁর উম্মতের কিছু লোক যেনা, রেশম, নেশাদার দ্রব্য এবং গান-বাজনা-বাদ্যযন্ত্রকে হালাল মনে করবে। এখানে সবচেয়ে বড় সতর্কতা হলো—হারামকে শুধু করা নয়, বরং সেটিকে হালাল মনে করা। মানুষ কখনও নিজের পছন্দ, সমাজের চাপ বা আনন্দের নামে সীমা বদলাতে চায়। কিন্তু হাদিসটি জানায়, আল্লাহর বিধানকে নিজের ইচ্ছামতো বদলানো বড় ঝুঁকির বিষয়। মদ ও বাদ্যযন্ত্র নিয়ে এই হাদিসটি বাংলায় অনেক খোঁজা হয়, কারণ এটি সরাসরি চারটি বড় সামাজিক ফিতনার নাম উল্লেখ করে। মুমিনের কাজ হলো সত্যকে সত্য বলা এবং হারাম থেকে বাঁচা। তাই মুমিনের উচিত জনপ্রিয় সংস্কৃতি নয়, হাদিসের নির্দেশকে নিজের মাপকাঠি বানানো।"},"teachings":["হারামকে হালাল মনে করা গুরুতর সতর্কতার বিষয়।","মদ ও বাদ্যযন্ত্র হাদিসে একসাথে উল্লেখ হয়েছে।","সমাজের প্রচলন দিয়ে আল্লাহর বিধান বদলায় না।","নিজের পছন্দের ওপর দ্বীনের নির্দেশকে প্রাধান্য দিতে হবে।"],"related_hadiths":[{"id":"4৯24","book_id":"4","label":"Sunan Abu Dawud"},{"id":"33৮৮","book_id":"6","label":"Sunan Ibn Majah"},{"id":"৮0","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যেনা, রেশম, মদ ও বাদ্যযন্ত্রকে হালাল ভাবার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি বলেছেন, কিছু লোক যেনা, রেশম, মদ ও বাদ্যযন্ত্রকে হালাল মনে করবে—এটি গুরুতর সতর্কতা।"},"heading":{"title":"হারামকে হালাল মনে করা: মদ ও বাদ্যযন্ত্র সম্পর্কে হাদিস","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ভবিষ্যতের একটি বিপদের কথা বলেছেন। তাঁর উম্মতের কিছু লোক যেনা, রেশম, নেশাদার দ্রব্য এবং গান-বাজনা-বাদ্যযন্ত্রকে হালাল মনে করবে। এখানে সবচেয়ে বড় সতর্কতা হলো—হারামকে শুধু করা নয়, বরং সেটিকে হালাল মনে করা। মানুষ কখনও নিজের পছন্দ, সমাজের চাপ বা আনন্দের নামে সীমা বদলাতে চায়। কিন্তু হাদিসটি জানায়, আল্লাহর বিধানকে নিজের ইচ্ছামতো বদলানো বড় ঝুঁকির বিষয়। মদ ও বাদ্যযন্ত্র নিয়ে এই হাদিসটি বাংলায় অনেক খোঁজা হয়, কারণ এটি সরাসরি চারটি বড় সামাজিক ফিতনার নাম উল্লেখ করে। মুমিনের কাজ হলো সত্যকে সত্য বলা এবং হারাম থেকে বাঁচা। তাই মুমিনের উচিত জনপ্রিয় সংস্কৃতি নয়, হাদিসের নির্দেশকে নিজের মাপকাঠি বানানো।"},"teachings":["হারামকে হালাল মনে করা গুরুতর সতর্কতার বিষয়।","মদ ও বাদ্যযন্ত্র হাদিসে একসাথে উল্লেখ হয়েছে।","সমাজের প্রচলন দিয়ে আল্লাহর বিধান বদলায় না।","নিজের পছন্দের ওপর দ্বীনের নির্দেশকে প্রাধান্য দিতে হবে।"],"related_hadiths":[{"id":"4924","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"80","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, জুয়া ও বাদ্যযন্ত্র হারাম হওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ মদ, জুয়া ও বাদ্যযন্ত্র হারাম করেছেন—এ হাদিস হারাম আনন্দ থেকে বাঁচার শিক্ষা দেয়।"},"heading":{"title":"মদ, জুয়া ও বাদ্যযন্ত্র হারাম: হাদিসের সরল ব্যাখ্যা","description":"এই হাদিসে তিনটি বিষয় একসাথে এসেছে: মদ, জুয়া এবং বাদ্যযন্ত্র। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ তা‘আলা এগুলো হারাম করেছেন। মদ বিবেক নষ্ট করে, জুয়া মানুষকে লোভ ও ক্ষতির পথে নেয়, আর বাদ্যযন্ত্র সম্পর্কে এখানে নিষেধ এসেছে। হাদিসটি আমাদের শেখায়, আনন্দ বা লাভের নামে এমন কাজ করা ঠিক নয় যা আল্লাহ হারাম করেছেন। অনেক সময় মানুষ বলে, “শুধু বিনোদন” বা “শুধু খেলা”; কিন্তু মুমিনের কাছে হালাল-হারামের সীমা বেশি গুরুত্বপূর্ণ। এই হাদিস সামাজিক জীবন, অর্থ, অবসর এবং বিনোদনে আল্লাহভীতির শিক্ষা দেয়। তাই নিজের আয়, খেলা, আনন্দ ও অবসর—সব ক্ষেত্রেই আল্লাহর ভয় রাখার প্রয়োজন আছে। এতে বোঝা যায়, দ্বীন শুধু ইবাদতের জায়গায় নয়; মানুষের অভ্যাস, লেনদেন ও বিনোদনের ক্ষেত্রেও পথ দেখায়।"},"teachings":["মদ, জুয়া ও বাদ্যযন্ত্র থেকে সতর্ক থাকার নির্দেশ এসেছে।","বিনোদন হলেও হারামের সীমা মানতে হবে।","জুয়া লোভ ও ক্ষতির পথ খুলে দিতে পারে।","আল্লাহর বিধানকে আনন্দের অজুহাতে হালকা করা ঠিক নয়।"],"related_hadiths":[{"id":"55৯0","book_id":"1","label":"Sahih Bukhari"},{"id":"4৯24","book_id":"4","label":"Sunan Abu Dawud"},{"id":"33৮৮","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, জুয়া ও বাদ্যযন্ত্র হারাম হওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ মদ, জুয়া ও বাদ্যযন্ত্র হারাম করেছেন—এ হাদিস হারাম আনন্দ থেকে বাঁচার শিক্ষা দেয়।"},"heading":{"title":"মদ, জুয়া ও বাদ্যযন্ত্র হারাম: হাদিসের সরল ব্যাখ্যা","description":"এই হাদিসে তিনটি বিষয় একসাথে এসেছে: মদ, জুয়া এবং বাদ্যযন্ত্র। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ তা‘আলা এগুলো হারাম করেছেন। মদ বিবেক নষ্ট করে, জুয়া মানুষকে লোভ ও ক্ষতির পথে নেয়, আর বাদ্যযন্ত্র সম্পর্কে এখানে নিষেধ এসেছে। হাদিসটি আমাদের শেখায়, আনন্দ বা লাভের নামে এমন কাজ করা ঠিক নয় যা আল্লাহ হারাম করেছেন। অনেক সময় মানুষ বলে, “শুধু বিনোদন” বা “শুধু খেলা”; কিন্তু মুমিনের কাছে হালাল-হারামের সীমা বেশি গুরুত্বপূর্ণ। এই হাদিস সামাজিক জীবন, অর্থ, অবসর এবং বিনোদনে আল্লাহভীতির শিক্ষা দেয়। তাই নিজের আয়, খেলা, আনন্দ ও অবসর—সব ক্ষেত্রেই আল্লাহর ভয় রাখার প্রয়োজন আছে। এতে বোঝা যায়, দ্বীন শুধু ইবাদতের জায়গায় নয়; মানুষের অভ্যাস, লেনদেন ও বিনোদনের ক্ষেত্রেও পথ দেখায়।"},"teachings":["মদ, জুয়া ও বাদ্যযন্ত্র থেকে সতর্ক থাকার নির্দেশ এসেছে।","বিনোদন হলেও হারামের সীমা মানতে হবে।","জুয়া লোভ ও ক্ষতির পথ খুলে দিতে পারে।","আল্লাহর বিধানকে আনন্দের অজুহাতে হালকা করা ঠিক নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"4924","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গায়িকা নর্তকী, গান-বাজনা ও হারাম উপার্জন","description":"$book_name$ $hadith_number$ - $chapter_name$. গায়িকা-নর্তকী কেনাবেচা, গান-বাজনা শেখানো এবং এ পথের উপার্জন সম্পর্কে কঠোর নিষেধ এসেছে।"},"heading":{"title":"গায়িকা নর্তকী ও গান-বাজনার উপার্জন সম্পর্কে হাদিস","description":"এই হাদিসে গায়িকা নর্তকীদের কেনাবেচা, তাদের গান-বাজনা ও বাদ্যযন্ত্র শেখানো এবং তাদের উপার্জন সম্পর্কে নিষেধ এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাদের বিক্রি করো না, ক্রয় করো না, তাদের গান-বাজনা ও বাদ্যযন্ত্র শেখিও না, এবং তাদের উপার্জন হারাম। এখানে মূল শিক্ষা হলো, শুধু নিজের কাজ নয়, হারামের আয়োজন, প্রশিক্ষণ ও আয়ের পথ থেকেও বাঁচতে হবে। কোনো কাজ যদি মানুষকে অশ্লীলতা, নাচ-গান বা হারাম বিনোদনের দিকে নেয়, তবে সেটিকে পেশা বানানো নিরাপদ নয়। হাদিসটি উপার্জনকে হালাল রাখার এবং বিনোদনের নামে সীমা না ভাঙার শিক্ষা দেয়। তাই শিল্প, পেশা বা বিনোদনের নামে এমন পথ নেওয়া যাবে না যা হারামের দিকে টেনে নেয়।"},"teachings":["হারাম বিনোদনের আয়োজন থেকেও দূরে থাকা দরকার।","গান-বাজনা শেখানো ও এর আয় সম্পর্কে নিষেধ এসেছে।","উপার্জন হালাল রাখা ঈমানি জীবনের অংশ।","নিজে না করলেও হারামের সহায়তা থেকে সতর্ক থাকতে হবে।"],"related_hadiths":[{"id":"55৯0","book_id":"1","label":"Sahih Bukhari"},{"id":"4৯24","book_id":"4","label":"Sunan Abu Dawud"},{"id":"33৮৮","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গায়িকা নর্তকী, গান-বাজনা ও হারাম উপার্জন","description":"$book_name$ $hadith_number$ - $chapter_name$. গায়িকা-নর্তকী কেনাবেচা, গান-বাজনা শেখানো এবং এ পথের উপার্জন সম্পর্কে কঠোর নিষেধ এসেছে।"},"heading":{"title":"গায়িকা নর্তকী ও গান-বাজনার উপার্জন সম্পর্কে হাদিস","description":"এই হাদিসে গায়িকা নর্তকীদের কেনাবেচা, তাদের গান-বাজনা ও বাদ্যযন্ত্র শেখানো এবং তাদের উপার্জন সম্পর্কে নিষেধ এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাদের বিক্রি করো না, ক্রয় করো না, তাদের গান-বাজনা ও বাদ্যযন্ত্র শেখিও না, এবং তাদের উপার্জন হারাম। এখানে মূল শিক্ষা হলো, শুধু নিজের কাজ নয়, হারামের আয়োজন, প্রশিক্ষণ ও আয়ের পথ থেকেও বাঁচতে হবে। কোনো কাজ যদি মানুষকে অশ্লীলতা, নাচ-গান বা হারাম বিনোদনের দিকে নেয়, তবে সেটিকে পেশা বানানো নিরাপদ নয়। হাদিসটি উপার্জনকে হালাল রাখার এবং বিনোদনের নামে সীমা না ভাঙার শিক্ষা দেয়। তাই শিল্প, পেশা বা বিনোদনের নামে এমন পথ নেওয়া যাবে না যা হারামের দিকে টেনে নেয়।"},"teachings":["হারাম বিনোদনের আয়োজন থেকেও দূরে থাকা দরকার।","গান-বাজনা শেখানো ও এর আয় সম্পর্কে নিষেধ এসেছে।","উপার্জন হালাল রাখা ঈমানি জীবনের অংশ।","নিজে না করলেও হারামের সহায়তা থেকে সতর্ক থাকতে হবে।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"4924","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বাদ্যযন্ত্রের শব্দ থেকে বাঁচার চেষ্টা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইবনু উমর (রাঃ) বাদ্যযন্ত্রের শব্দ শুনে কানে আঙুল দিলেন এবং নবীজির একই আমলের কথা জানালেন।"},"heading":{"title":"বাদ্যযন্ত্রের শব্দ থেকে দূরে থাকা: ইবনু উমর (রাঃ)-এর বর্ণনা","description":"এই হাদিসে একটি বাস্তব ঘটনা এসেছে। ইবনু উমর (রাঃ) বাদ্যযন্ত্রের শব্দ শুনে দুই কানে দুই আঙুল ঢুকিয়ে রাস্তা থেকে সরে গেলেন। পরে নাফে‘কে জিজ্ঞেস করলেন, তিনি কিছু শুনতে পাচ্ছেন কি না। যখন নাফে‘ বললেন, না, তখন তিনি আঙুল বের করলেন এবং জানালেন যে তিনি একদা রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর সঙ্গে ছিলেন; নবীজি এমন শব্দ শুনে একই কাজ করেছিলেন। হাদিসের সঙ্গে দেওয়া ব্যাখ্যায়ও বলা হয়েছে, গান-বাজনা ও বাদ্যযন্ত্রের শব্দ যেন কানে না আসে, সে জন্য সম্ভবপর চেষ্টা করতে হবে। তাই শিক্ষা হলো, হারাম শব্দের পরিবেশ এলে সাধ্যের মধ্যে সরে যাওয়া বা বাঁচার চেষ্টা করা। এতে বোঝা যায়, গুনাহ থেকে বাঁচা শুধু মনে অপছন্দ করা নয়; অনেক সময় বাস্তব পদক্ষেপও দরকার।"},"teachings":["বাদ্যযন্ত্রের শব্দ থেকে বাঁচার চেষ্টা করা উচিত।","সাহাবিরা নবীজির আমল দেখে তা অনুসরণ করতেন।","হারাম পরিবেশ এলে সাধ্যের মধ্যে সরে যাওয়া ভালো।","শুধু শোনা নয়, শোনার পরিবেশ থেকেও সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"55৯0","book_id":"1","label":"Sahih Bukhari"},{"id":"33৮৮","book_id":"6","label":"Sunan Ibn Majah"},{"id":"৮0","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বাদ্যযন্ত্রের শব্দ থেকে বাঁচার চেষ্টা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইবনু উমর (রাঃ) বাদ্যযন্ত্রের শব্দ শুনে কানে আঙুল দিলেন এবং নবীজির একই আমলের কথা জানালেন।"},"heading":{"title":"বাদ্যযন্ত্রের শব্দ থেকে দূরে থাকা: ইবনু উমর (রাঃ)-এর বর্ণনা","description":"এই হাদিসে একটি বাস্তব ঘটনা এসেছে। ইবনু উমর (রাঃ) বাদ্যযন্ত্রের শব্দ শুনে দুই কানে দুই আঙুল ঢুকিয়ে রাস্তা থেকে সরে গেলেন। পরে নাফে‘কে জিজ্ঞেস করলেন, তিনি কিছু শুনতে পাচ্ছেন কি না। যখন নাফে‘ বললেন, না, তখন তিনি আঙুল বের করলেন এবং জানালেন যে তিনি একদা রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর সঙ্গে ছিলেন; নবীজি এমন শব্দ শুনে একই কাজ করেছিলেন। হাদিসের সঙ্গে দেওয়া ব্যাখ্যায়ও বলা হয়েছে, গান-বাজনা ও বাদ্যযন্ত্রের শব্দ যেন কানে না আসে, সে জন্য সম্ভবপর চেষ্টা করতে হবে। তাই শিক্ষা হলো, হারাম শব্দের পরিবেশ এলে সাধ্যের মধ্যে সরে যাওয়া বা বাঁচার চেষ্টা করা। এতে বোঝা যায়, গুনাহ থেকে বাঁচা শুধু মনে অপছন্দ করা নয়; অনেক সময় বাস্তব পদক্ষেপও দরকার।"},"teachings":["বাদ্যযন্ত্রের শব্দ থেকে বাঁচার চেষ্টা করা উচিত।","সাহাবিরা নবীজির আমল দেখে তা অনুসরণ করতেন।","হারাম পরিবেশ এলে সাধ্যের মধ্যে সরে যাওয়া ভালো।","শুধু শোনা নয়, শোনার পরিবেশ থেকেও সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"80","book_id":"1","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, গায়িকা ও বাদ্যযন্ত্রে মত্ততার গজব","description":"$book_name$ $hadith_number$ - $chapter_name$. মদ, গায়িকা নিয়ে নাচ-গান ও বাদ্যযন্ত্রে ডুবে থাকার কারণে তিন ধরনের ভয়াবহ বিপদের সতর্কতা।"},"heading":{"title":"মদ, নাচ-গান ও বাদ্যযন্ত্র: ভয়াবহ বিপদের হাদিস","description":"এই হাদিসটি মদ, গায়িকা এবং বাদ্যযন্ত্রের ফিতনা সম্পর্কে স্পষ্ট সতর্কতা দেয়। নবী করীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যখন তাঁর উম্মত নেশাদার দ্রব্য পান করবে, গায়িকাদের নিয়ে নাচ-গানে মত্ত হবে এবং বাদ্যযন্ত্র নিয়ে ব্যস্ত হবে, তখন তিনটি ভয়াবহ বিপদ নেমে আসবে। সেগুলো হলো—ভূমি ধসে যাওয়া, উপর থেকে বা কোনো জাতির পক্ষ থেকে যুলুম চাপিয়ে দেওয়া, এবং অনেকের আকার-আকৃতি বিকৃত করা। হাদিসের ভাষা কঠোর, তাই এর বার্তাও গভীর: হারাম আনন্দকে সাধারণ বানানো মুমিনের পথ নয়। মদ, নাচ-গান ও বাদ্যযন্ত্রের প্রতি আসক্তি থেকে নিজেকে এবং পরিবারকে সতর্ক রাখা দরকার। তাই এই হাদিস শুধু ভয় দেখায় না; এটি মানুষকে নিজের জীবনযাপন নতুন করে যাচাই করতেও ডাকে।"},"teachings":["মদপান ও হারাম বিনোদন বড় বিপদের কারণ হতে পারে।","গায়িকা ও নাচ-গানে মত্ততা থেকে সতর্ক করা হয়েছে।","বাদ্যযন্ত্রে ব্যস্ততা হাদিসে নিন্দিতভাবে এসেছে।","হারামকে আনন্দের নামে স্বাভাবিক বানানো উচিত নয়।"],"related_hadiths":[{"id":"55৯0","book_id":"1","label":"Sahih Bukhari"},{"id":"4৯24","book_id":"4","label":"Sunan Abu Dawud"},{"id":"33৮৮","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, গায়িকা ও বাদ্যযন্ত্রে মত্ততার গজব","description":"$book_name$ $hadith_number$ - $chapter_name$. মদ, গায়িকা নিয়ে নাচ-গান ও বাদ্যযন্ত্রে ডুবে থাকার কারণে তিন ধরনের ভয়াবহ বিপদের সতর্কতা।"},"heading":{"title":"মদ, নাচ-গান ও বাদ্যযন্ত্র: ভয়াবহ বিপদের হাদিস","description":"এই হাদিসটি মদ, গায়িকা এবং বাদ্যযন্ত্রের ফিতনা সম্পর্কে স্পষ্ট সতর্কতা দেয়। নবী করীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যখন তাঁর উম্মত নেশাদার দ্রব্য পান করবে, গায়িকাদের নিয়ে নাচ-গানে মত্ত হবে এবং বাদ্যযন্ত্র নিয়ে ব্যস্ত হবে, তখন তিনটি ভয়াবহ বিপদ নেমে আসবে। সেগুলো হলো—ভূমি ধসে যাওয়া, উপর থেকে বা কোনো জাতির পক্ষ থেকে যুলুম চাপিয়ে দেওয়া, এবং অনেকের আকার-আকৃতি বিকৃত করা। হাদিসের ভাষা কঠোর, তাই এর বার্তাও গভীর: হারাম আনন্দকে সাধারণ বানানো মুমিনের পথ নয়। মদ, নাচ-গান ও বাদ্যযন্ত্রের প্রতি আসক্তি থেকে নিজেকে এবং পরিবারকে সতর্ক রাখা দরকার। তাই এই হাদিস শুধু ভয় দেখায় না; এটি মানুষকে নিজের জীবনযাপন নতুন করে যাচাই করতেও ডাকে।"},"teachings":["মদপান ও হারাম বিনোদন বড় বিপদের কারণ হতে পারে।","গায়িকা ও নাচ-গানে মত্ততা থেকে সতর্ক করা হয়েছে।","বাদ্যযন্ত্রে ব্যস্ততা হাদিসে নিন্দিতভাবে এসেছে।","হারামকে আনন্দের নামে স্বাভাবিক বানানো উচিত নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"4924","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
     </row>

--- a/SINGLE HADITH CONTENT/BOOK WISE FINAL UPDATED CONTENT/BN/BN_UPODESH.xlsx
+++ b/SINGLE HADITH CONTENT/BOOK WISE FINAL UPDATED CONTENT/BN/BN_UPODESH.xlsx
@@ -60,8 +60,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -488,7 +492,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দ্বীন হচ্ছে উপদেশ ও কল্যাণ কামনা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীন হলো কল্যাণ কামনা—আল্লাহ, তাঁর কিতাব, রাসূল, মুসলিম নেতা ও সাধারণ মুসলমানের জন্য।"},"heading":{"title":"দ্বীন হচ্ছে উপদেশ: কল্যাণ কামনার সহজ শিক্ষা","description":"এই হাদিসের মূল বিষয় হলো কল্যাণ কামনা। নবী করীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, দ্বীন হচ্ছে উপদেশ। তিনি কথাটি তিনবার বলেছেন, যা বিষয়টির গুরুত্ব বোঝায়। সাহাবীরা জানতে চেয়েছেন, কার জন্য এই উপদেশ বা নসীহত? উত্তরে তিনি বলেছেন, আল্লাহর জন্য, তাঁর কিতাবের জন্য, তাঁর রাসূলের জন্য, মুসলিম নেতাদের জন্য এবং সাধারণ মুসলমানের জন্য। এখানে উপদেশ মানে শুধু কথা বলা নয়; বরং সত্য, ভালোবাসা ও কল্যাণের মন রাখা। আল্লাহর প্রতি সঠিক বিশ্বাস, কিতাবের মর্যাদা, রাসূলের আনুগত্য, নেতার ভালো চাওয়া এবং মুসলমানদের জন্য ভালো চাওয়া—এসবই দ্বীনের অংশ। তাই দ্বীন হচ্ছে উপদেশ হাদিসটি মুসলিম জীবনে আন্তরিকতার বড় শিক্ষা দেয়।"},"teachings":["দ্বীনের একটি বড় অংশ হলো সবার জন্য সত্যিকারের কল্যাণ কামনা করা।","আল্লাহ, কিতাব ও রাসূলের প্রতি দায়িত্বশীল মন রাখা জরুরি।","মুসলিম নেতা ও সাধারণ মুসলমানদের জন্য ভালো চাওয়া ঈমানি আচরণ।","উপদেশ দিতে হলে আন্তরিকতা ও কল্যাণের মন থাকা দরকার।"],"related_hadiths":[{"id":"55","book_id":"2","label":"Sahih Muslim"},{"id":"4200","book_id":"3","label":"Sunan an-Nasai"},{"id":"4966","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দ্বীন হচ্ছে উপদেশ ও কল্যাণ কামনা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীন হলো কল্যাণ কামনা—আল্লাহ, তাঁর কিতাব, রাসূল, মুসলিম নেতা ও সাধারণ মুসলমানের জন্য।"},"heading":{"title":"দ্বীন হচ্ছে উপদেশ: কল্যাণ কামনার সহজ শিক্ষা","description":"এই হাদিসের মূল বিষয় হলো কল্যাণ কামনা। নবী করীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, দ্বীন হচ্ছে উপদেশ। তিনি কথাটি তিনবার বলেছেন, যা বিষয়টির গুরুত্ব বোঝায়। সাহাবীরা জানতে চেয়েছেন, কার জন্য এই উপদেশ বা নসীহত? উত্তরে তিনি বলেছেন, আল্লাহর জন্য, তাঁর কিতাবের জন্য, তাঁর রাসূলের জন্য, মুসলিম নেতাদের জন্য এবং সাধারণ মুসলমানের জন্য। এখানে উপদেশ মানে শুধু কথা বলা নয়; বরং সত্য, ভালোবাসা ও কল্যাণের মন রাখা। আল্লাহর প্রতি সঠিক বিশ্বাস, কিতাবের মর্যাদা, রাসূলের আনুগত্য, নেতার ভালো চাওয়া এবং মুসলমানদের জন্য ভালো চাওয়া—এসবই দ্বীনের অংশ। তাই দ্বীন হচ্ছে উপদেশ হাদিসটি মুসলিম জীবনে আন্তরিকতার বড় শিক্ষা দেয়।"},"teachings":["দ্বীনের একটি বড় অংশ হলো সবার জন্য সত্যিকারের কল্যাণ কামনা করা।","আল্লাহ, কিতাব ও রাসূলের প্রতি দায়িত্বশীল মন রাখা জরুরি।","মুসলিম নেতা ও সাধারণ মুসলমানদের জন্য ভালো চাওয়া ঈমানি আচরণ।","উপদেশ দিতে হলে আন্তরিকতা ও কল্যাণের মন থাকা দরকার।"],"related_hadiths":[{"id":"55","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"4200","book_id":"3","slug":"nasai","label":"সুনান আন-নাসায়ী"},{"id":"4966","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E2" s="4" t="n"/>
@@ -511,7 +515,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কালিমার ওজন ও আল্লাহর নামের মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. নিরানব্বই দফতরের বিপরীতে কালিমার ছোট কাগজ ভারী হবে; আল্লাহর নামের মর্যাদা বোঝায়।"},"heading":{"title":"কালিমার ওজন: নিরানব্বই দফতর ও ছোট কাগজের হাদিস","description":"এই হাদিসে কিয়ামতের দিন এক ব্যক্তির হিসাবের কথা এসেছে। তার আমলনামা নিরানব্বইটি বড় দফতরে খোলা হবে, প্রতিটি দফতর দৃষ্টিসীমা পর্যন্ত বিস্তৃত। আল্লাহ তাকে জিজ্ঞেস করবেন, সে কি এগুলোর কিছু অস্বীকার করতে পারে বা ফেরেশতারা কি তার প্রতি যুলুম করেছে। সে বলবে, না। এরপর আল্লাহ বলবেন, তার একটি নেকী আছে এবং আজ তার প্রতি যুলুম করা হবে না। তারপর একটি ছোট কাগজ বের হবে, যাতে কালিমার সাক্ষ্য লেখা থাকবে। দফতর এক পাল্লায় আর কালিমার কাগজ অন্য পাল্লায় রাখা হলে কালিমার পাল্লা ভারী হবে। এই হাদিস কালিমার মর্যাদা, আল্লাহর ন্যায়বিচার এবং তাওহীদের গুরুত্ব শেখায়।"},"teachings":["কিয়ামতের হিসাব আল্লাহর ন্যায়বিচারের সঙ্গে হবে।","কালিমার সাক্ষ্য তাওহীদের বড় মর্যাদা বোঝায়।","ফেরেশতাদের লেখা আমলনামা অস্বীকার করা যাবে না।","আল্লাহর নামের মর্যাদা মানুষের হিসাবের চেয়ে বড়।"],"related_hadiths":[{"id":"2639","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"4300","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5559","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কালিমার ওজন ও আল্লাহর নামের মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. নিরানব্বই দফতরের বিপরীতে কালিমার ছোট কাগজ ভারী হবে; আল্লাহর নামের মর্যাদা বোঝায়।"},"heading":{"title":"কালিমার ওজন: নিরানব্বই দফতর ও ছোট কাগজের হাদিস","description":"এই হাদিসে কিয়ামতের দিন এক ব্যক্তির হিসাবের কথা এসেছে। তার আমলনামা নিরানব্বইটি বড় দফতরে খোলা হবে, প্রতিটি দফতর দৃষ্টিসীমা পর্যন্ত বিস্তৃত। আল্লাহ তাকে জিজ্ঞেস করবেন, সে কি এগুলোর কিছু অস্বীকার করতে পারে বা ফেরেশতারা কি তার প্রতি যুলুম করেছে। সে বলবে, না। এরপর আল্লাহ বলবেন, তার একটি নেকী আছে এবং আজ তার প্রতি যুলুম করা হবে না। তারপর একটি ছোট কাগজ বের হবে, যাতে কালিমার সাক্ষ্য লেখা থাকবে। দফতর এক পাল্লায় আর কালিমার কাগজ অন্য পাল্লায় রাখা হলে কালিমার পাল্লা ভারী হবে। এই হাদিস কালিমার মর্যাদা, আল্লাহর ন্যায়বিচার এবং তাওহীদের গুরুত্ব শেখায়।"},"teachings":["কিয়ামতের হিসাব আল্লাহর ন্যায়বিচারের সঙ্গে হবে।","কালিমার সাক্ষ্য তাওহীদের বড় মর্যাদা বোঝায়।","ফেরেশতাদের লেখা আমলনামা অস্বীকার করা যাবে না।","আল্লাহর নামের মর্যাদা মানুষের হিসাবের চেয়ে বড়।"],"related_hadiths":[{"id":"2639","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"4300","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"5559","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E3" s="4" t="n"/>
@@ -534,7 +538,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রাতের ভোগ-বিলাস ও হারাম বিনোদনের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য-পানীয় ও আনন্দ-প্রমোদের মধ্যে ডুবে থাকা কিছু লোকের ভয়াবহ রূপান্তর নিয়ে সতর্কতা।"},"heading":{"title":"ভোগ-বিলাস, মদ ও বিনোদনের ভয়াবহ পরিণতি সম্পর্কে হাদিস","description":"এই হাদিসে বলা হয়েছে, উম্মতের কিছু লোক নানা খাদ্য-পানীয় ও আনন্দ-প্রমোদের মধ্যে রাত কাটাবে। এরপর তাদের সকাল হবে শূকর ও বানরের আকৃতিতে রূপান্তরিত হয়ে। দেওয়া ব্যাখ্যায় বলা হয়েছে, এক শ্রেণীর অর্থশালী মানুষ নানা ধরনের মদ ও পানীয়ের ব্যবস্থা করে ভোগ-বিলাসে ডুবে থাকবে এবং নায়িকা, মদ ও বাদ্যযন্ত্রের মাধ্যমে রাত কাটাবে। হাদিসের মূল শিক্ষা হলো, সম্পদ ও বিনোদন যেন মানুষকে হালাল-হারামের সীমা ভুলিয়ে না দেয়। দুনিয়ার আরাম যদি আল্লাহর অবাধ্যতা, নেশা ও অশ্লীলতার পথে নেয়, তবে তা মুমিনের জন্য বিপদের কারণ। তাই আনন্দেও সংযম, লজ্জা ও আল্লাহভীতি থাকা দরকার। তাই দুনিয়ার আরামকে নিয়ন্ত্রণে রাখা এবং আখিরাতের জবাবদিহি মনে রাখা এই হাদিসের বড় শিক্ষা।"},"teachings":["ভোগ-বিলাসে ডুবে হারামকে স্বাভাবিক করা বিপজ্জনক।","মদ, নায়িকা ও বাদ্যযন্ত্রের পরিবেশ থেকে সতর্ক থাকা দরকার।","সম্পদ মানুষকে আল্লাহভীতি ভুলিয়ে দিলে তা ক্ষতির কারণ হতে পারে।","আনন্দ ও বিনোদনেও হালাল-হারামের সীমা মানতে হবে।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"4924","book_id":"4","label":"Sunan Abu Dawud"},{"id":"80","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রাতের ভোগ-বিলাস ও হারাম বিনোদনের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য-পানীয় ও আনন্দ-প্রমোদের মধ্যে ডুবে থাকা কিছু লোকের ভয়াবহ রূপান্তর নিয়ে সতর্কতা।"},"heading":{"title":"ভোগ-বিলাস, মদ ও বিনোদনের ভয়াবহ পরিণতি সম্পর্কে হাদিস","description":"এই হাদিসে বলা হয়েছে, উম্মতের কিছু লোক নানা খাদ্য-পানীয় ও আনন্দ-প্রমোদের মধ্যে রাত কাটাবে। এরপর তাদের সকাল হবে শূকর ও বানরের আকৃতিতে রূপান্তরিত হয়ে। দেওয়া ব্যাখ্যায় বলা হয়েছে, এক শ্রেণীর অর্থশালী মানুষ নানা ধরনের মদ ও পানীয়ের ব্যবস্থা করে ভোগ-বিলাসে ডুবে থাকবে এবং নায়িকা, মদ ও বাদ্যযন্ত্রের মাধ্যমে রাত কাটাবে। হাদিসের মূল শিক্ষা হলো, সম্পদ ও বিনোদন যেন মানুষকে হালাল-হারামের সীমা ভুলিয়ে না দেয়। দুনিয়ার আরাম যদি আল্লাহর অবাধ্যতা, নেশা ও অশ্লীলতার পথে নেয়, তবে তা মুমিনের জন্য বিপদের কারণ। তাই আনন্দেও সংযম, লজ্জা ও আল্লাহভীতি থাকা দরকার। তাই দুনিয়ার আরামকে নিয়ন্ত্রণে রাখা এবং আখিরাতের জবাবদিহি মনে রাখা এই হাদিসের বড় শিক্ষা।"},"teachings":["ভোগ-বিলাসে ডুবে হারামকে স্বাভাবিক করা বিপজ্জনক।","মদ, নায়িকা ও বাদ্যযন্ত্রের পরিবেশ থেকে সতর্ক থাকা দরকার।","সম্পদ মানুষকে আল্লাহভীতি ভুলিয়ে দিলে তা ক্ষতির কারণ হতে পারে।","আনন্দ ও বিনোদনেও হালাল-হারামের সীমা মানতে হবে।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E4" s="4" t="n"/>
@@ -557,7 +561,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ ও বাদ্যযন্ত্রের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. মদের নাম বদলে পান করা, গায়িকা ও বাদ্যযন্ত্রকে সম্মান করা—এসব কাজের ভয়াবহ পরিণতি এই হাদিসে সতর্ক করা হয়েছে।"},"heading":{"title":"মদ ও বাদ্যযন্ত্র সম্পর্কে হাদিস: নাম বদলালেও পাপ বদলায় না","description":"এই হাদিসের মূল শিক্ষা হলো, হারাম জিনিসের নাম বদলালে তা হালাল হয়ে যায় না। নবী করীম সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তাঁর উম্মতের কিছু মানুষ মদ পান করবে, কিন্তু সেটির অন্য নাম রাখবে। অর্থাৎ বাহ্যিক নাম পাল্টালেও কাজের আসল রূপ পাল্টাবে না। হাদিসে আরও এসেছে, কিছু নেতাকে গায়িকা ও বাদ্যযন্ত্র দিয়ে সম্মান করা হবে। এতে বোঝা যায়, নেতৃত্ব ও সমাজ যখন পাপকে বিনোদন বা মর্যাদার বিষয় বানায়, তখন তা বড় বিপদের কারণ হয়। মদ, গান-বাজনা, অশ্লীলতা ও খারাপ সংস্কৃতির দিকে ঝুঁকে পড়া এখানে কঠোরভাবে সতর্ক করা হয়েছে। তাই একজন মুসলিমের জন্য প্রয়োজন হলো, কাজের নাম নয়, কাজের আসল হুকুম ও ফল নিয়ে ভাবা।"},"teachings":["মদের নাম বদলালেও মদ্যপানের পাপ বদলায় না।","নেতা ও দায়িত্বশীলদের পাপাচার সমাজে বড় ক্ষতির কারণ হতে পারে।","গায়িকা ও বাদ্যযন্ত্রকে সম্মানের মাধ্যম বানানো থেকে সতর্ক থাকা উচিত।","হারামকে সুন্দর নামে চালু করার প্রবণতা ঈমানের জন্য ক্ষতিকর।"],"related_hadiths":[{"id":"2475","book_id":"1","label":"Sahih Bukhari"},{"id":"6772","book_id":"1","label":"Sahih Bukhari"},{"id":"1898","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ ও বাদ্যযন্ত্রের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. মদের নাম বদলে পান করা, গায়িকা ও বাদ্যযন্ত্রকে সম্মান করা—এসব কাজের ভয়াবহ পরিণতি এই হাদিসে সতর্ক করা হয়েছে।"},"heading":{"title":"মদ ও বাদ্যযন্ত্র সম্পর্কে হাদিস: নাম বদলালেও পাপ বদলায় না","description":"এই হাদিসের মূল শিক্ষা হলো, হারাম জিনিসের নাম বদলালে তা হালাল হয়ে যায় না। নবী করীম সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তাঁর উম্মতের কিছু মানুষ মদ পান করবে, কিন্তু সেটির অন্য নাম রাখবে। অর্থাৎ বাহ্যিক নাম পাল্টালেও কাজের আসল রূপ পাল্টাবে না। হাদিসে আরও এসেছে, কিছু নেতাকে গায়িকা ও বাদ্যযন্ত্র দিয়ে সম্মান করা হবে। এতে বোঝা যায়, নেতৃত্ব ও সমাজ যখন পাপকে বিনোদন বা মর্যাদার বিষয় বানায়, তখন তা বড় বিপদের কারণ হয়। মদ, গান-বাজনা, অশ্লীলতা ও খারাপ সংস্কৃতির দিকে ঝুঁকে পড়া এখানে কঠোরভাবে সতর্ক করা হয়েছে। তাই একজন মুসলিমের জন্য প্রয়োজন হলো, কাজের নাম নয়, কাজের আসল হুকুম ও ফল নিয়ে ভাবা।"},"teachings":["মদের নাম বদলালেও মদ্যপানের পাপ বদলায় না।","নেতা ও দায়িত্বশীলদের পাপাচার সমাজে বড় ক্ষতির কারণ হতে পারে।","গায়িকা ও বাদ্যযন্ত্রকে সম্মানের মাধ্যম বানানো থেকে সতর্ক থাকা উচিত।","হারামকে সুন্দর নামে চালু করার প্রবণতা ঈমানের জন্য ক্ষতিকর।"],"related_hadiths":[{"id":"2475","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6772","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1898","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E5" s="4" t="n"/>
@@ -580,7 +584,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পথভ্রষ্ট নেতা ও ঈমানের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ভ্রান্ত নেতা, ভুল আলেম, মূর্তিপূজা ও বিজাতিদের সাথে মিশে যাওয়ার ফিতনা থেকে উম্মতকে সতর্ক করা হয়েছে।"},"heading":{"title":"পথভ্রষ্ট নেতা ও আলেম সম্পর্কে হাদিস: ঈমান রক্ষার সতর্কতা","description":"এই হাদিসে নবী করীম সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম উম্মতের জন্য এক বড় ভয় প্রকাশ করেছেন। তিনি বলেছেন, তিনি বেশি ভয় করেন নেতা ও এক শ্রেণীর আলেম সমাজকে। কারণ মানুষ সাধারণত নেতা ও আলেমদের কথা দেখে ও শুনে পথ নেয়। তারা যদি ভুল পথে ডাকে, তাহলে অনেক মানুষ ক্ষতিগ্রস্ত হতে পারে। হাদিসে আরও বলা হয়েছে, উম্মতের কিছু লোক মূর্তিপূজা করবে এবং কিছু লোক মুশরিকদের সাথে মিশে যাবে। এখানে মূল শিক্ষা হলো, ঈমান, তাওহীদ ও ইসলামী পরিচয়কে হালকা করে দেখা যাবে না। কারও পদ, নাম বা বাহ্যিক সম্মান দেখে অন্ধভাবে অনুসরণ না করে সত্য-ভিত্তিক দীন মানতে হবে।"},"teachings":["ভ্রান্ত নেতা ও ভুল আলেম মানুষের দীনী জীবনে বড় ক্ষতির কারণ হতে পারে।","তাওহীদ রক্ষা করা একজন মুসলিমের মূল দায়িত্ব।","অন্ধ অনুসরণ নয়, সত্য ও সঠিক দীন বুঝে চলা দরকার।","মূর্তিপূজা ও শিরকের পথ থেকে দূরে থাকা জরুরি।"],"related_hadiths":[{"id":"5406","book_id":"14","label":"Mishkat al-Masabih"},{"id":"7084","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পথভ্রষ্ট নেতা ও ঈমানের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ভ্রান্ত নেতা, ভুল আলেম, মূর্তিপূজা ও বিজাতিদের সাথে মিশে যাওয়ার ফিতনা থেকে উম্মতকে সতর্ক করা হয়েছে।"},"heading":{"title":"পথভ্রষ্ট নেতা ও আলেম সম্পর্কে হাদিস: ঈমান রক্ষার সতর্কতা","description":"এই হাদিসে নবী করীম সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম উম্মতের জন্য এক বড় ভয় প্রকাশ করেছেন। তিনি বলেছেন, তিনি বেশি ভয় করেন নেতা ও এক শ্রেণীর আলেম সমাজকে। কারণ মানুষ সাধারণত নেতা ও আলেমদের কথা দেখে ও শুনে পথ নেয়। তারা যদি ভুল পথে ডাকে, তাহলে অনেক মানুষ ক্ষতিগ্রস্ত হতে পারে। হাদিসে আরও বলা হয়েছে, উম্মতের কিছু লোক মূর্তিপূজা করবে এবং কিছু লোক মুশরিকদের সাথে মিশে যাবে। এখানে মূল শিক্ষা হলো, ঈমান, তাওহীদ ও ইসলামী পরিচয়কে হালকা করে দেখা যাবে না। কারও পদ, নাম বা বাহ্যিক সম্মান দেখে অন্ধভাবে অনুসরণ না করে সত্য-ভিত্তিক দীন মানতে হবে।"},"teachings":["ভ্রান্ত নেতা ও ভুল আলেম মানুষের দীনী জীবনে বড় ক্ষতির কারণ হতে পারে।","তাওহীদ রক্ষা করা একজন মুসলিমের মূল দায়িত্ব।","অন্ধ অনুসরণ নয়, সত্য ও সঠিক দীন বুঝে চলা দরকার।","মূর্তিপূজা ও শিরকের পথ থেকে দূরে থাকা জরুরি।"],"related_hadiths":[{"id":"5406","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"7084","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -607,7 +611,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যিনার শরয়ী দণ্ডের বর্ণনা","description":"$book_name$ $hadith_number$ - $chapter_name$. অবিবাহিত ও বিবাহিত যিনাকারীর জন্য হাদিসে যে শরয়ী দণ্ডের কথা এসেছে, তা স্পষ্টভাবে বর্ণনা করা হয়েছে।"},"heading":{"title":"যিনার দণ্ড সম্পর্কে হাদিস: আল্লাহর বিধান গ্রহণের শিক্ষা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তোমরা আমার কাছ থেকে আল্লাহর বিধান গ্রহণ কর। কথাটি তিনি দুইবার বলেছেন, যা বিষয়টির গুরুত্ব বোঝায়। এরপর তিনি অবিবাহিত নারী-পুরুষের যিনার জন্য একশ বেত্রাঘাত ও এক বছরের নির্বাসনের কথা বলেছেন। আর বিবাহিত নারী-পুরুষের ক্ষেত্রে রজমের কথা এসেছে। এখানে মূল বিষয় হলো, যিনা ইসলামে খুব গুরুতর পাপ এবং সমাজের পবিত্রতা রক্ষার সাথে এর সম্পর্ক আছে। ইসলামী স্কলারদের মতে, এ ধরনের দণ্ড ব্যক্তিগতভাবে প্রয়োগের বিষয় নয়; বিচার, প্রমাণ ও বৈধ কর্তৃপক্ষের অধীনে শরয়ী বিচারব্যবস্থার বিষয়। হাদিসটি আমাদেরকে যিনা থেকে দূরে থাকতে, লজ্জা ও পবিত্রতা রক্ষা করতে এবং আল্লাহর বিধানকে গুরুত্ব দিতে শেখায়।"},"teachings":["যিনা ইসলামে গুরুতর পাপ হিসেবে বর্ণিত হয়েছে।","আল্লাহর বিধান রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর কাছ থেকে গ্রহণ করতে বলা হয়েছে।","পবিত্র জীবন ও লজ্জাশীলতা রক্ষা করা জরুরি।","শরয়ী দণ্ড বিচার ও কর্তৃপক্ষের অধীন বিষয়।"],"related_hadiths":[{"id":"3562","book_id":"14","label":"Mishkat al-Masabih"},{"id":"4353","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6772","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যিনার শরয়ী দণ্ডের বর্ণনা","description":"$book_name$ $hadith_number$ - $chapter_name$. অবিবাহিত ও বিবাহিত যিনাকারীর জন্য হাদিসে যে শরয়ী দণ্ডের কথা এসেছে, তা স্পষ্টভাবে বর্ণনা করা হয়েছে।"},"heading":{"title":"যিনার দণ্ড সম্পর্কে হাদিস: আল্লাহর বিধান গ্রহণের শিক্ষা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তোমরা আমার কাছ থেকে আল্লাহর বিধান গ্রহণ কর। কথাটি তিনি দুইবার বলেছেন, যা বিষয়টির গুরুত্ব বোঝায়। এরপর তিনি অবিবাহিত নারী-পুরুষের যিনার জন্য একশ বেত্রাঘাত ও এক বছরের নির্বাসনের কথা বলেছেন। আর বিবাহিত নারী-পুরুষের ক্ষেত্রে রজমের কথা এসেছে। এখানে মূল বিষয় হলো, যিনা ইসলামে খুব গুরুতর পাপ এবং সমাজের পবিত্রতা রক্ষার সাথে এর সম্পর্ক আছে। ইসলামী স্কলারদের মতে, এ ধরনের দণ্ড ব্যক্তিগতভাবে প্রয়োগের বিষয় নয়; বিচার, প্রমাণ ও বৈধ কর্তৃপক্ষের অধীনে শরয়ী বিচারব্যবস্থার বিষয়। হাদিসটি আমাদেরকে যিনা থেকে দূরে থাকতে, লজ্জা ও পবিত্রতা রক্ষা করতে এবং আল্লাহর বিধানকে গুরুত্ব দিতে শেখায়।"},"teachings":["যিনা ইসলামে গুরুতর পাপ হিসেবে বর্ণিত হয়েছে।","আল্লাহর বিধান রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর কাছ থেকে গ্রহণ করতে বলা হয়েছে।","পবিত্র জীবন ও লজ্জাশীলতা রক্ষা করা জরুরি।","শরয়ী দণ্ড বিচার ও কর্তৃপক্ষের অধীন বিষয়।"],"related_hadiths":[{"id":"3562","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"4353","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6772","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
@@ -630,7 +634,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর মানুষের কঠিন সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. বৃদ্ধ যিনাকারী, মিথ্যাবাদী শাসক ও অহঙ্কারী দরিদ্র ব্যক্তির জন্য কিয়ামতের কঠিন সতর্কতা এসেছে।"},"heading":{"title":"তিন শ্রেণীর মানুষের ব্যাপারে হাদিস: যিনা, মিথ্যা ও অহঙ্কারের ভয়াবহতা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তিন ধরনের মানুষের ব্যাপারে কঠিন সতর্কতা দিয়েছেন। তারা হলো বৃদ্ধ যিনাকারী, মিথ্যাবাদী শাসক এবং অহঙ্কারী দরিদ্র ব্যক্তি। হাদিসে বলা হয়েছে, কিয়ামতের দিন আল্লাহ তাদের সাথে কথা বলবেন না, তাদের পবিত্র করবেন না; অন্য বর্ণনায় আছে, তাদের দিকে তাকাবেন না এবং তাদের জন্য যন্ত্রণাদায়ক শাস্তি রয়েছে। এখানে তিনটি পাপ খুব স্পষ্ট: যিনা, মিথ্যা এবং অহঙ্কার। বয়স, পদ বা অবস্থা কোনো মানুষকে গুনাহ থেকে নিরাপদ করে না। বিশেষ করে শাসকের মিথ্যা মানুষের উপর বড় প্রভাব ফেলে। আবার দরিদ্র হয়েও অহঙ্কার করা দেখায় যে অহঙ্কার শুধু সম্পদের কারণে নয়, মনের রোগ হিসেবেও থাকতে পারে।"},"teachings":["যিনা, মিথ্যা ও অহঙ্কার—তিনটি কাজই গুরুতর পাপ।","ক্ষমতাবান ব্যক্তির মিথ্যা সমাজে বড় ক্ষতি আনতে পারে।","দারিদ্র্য অহঙ্কার থেকে নিরাপত্তা দেয় না; মনকে বিনয়ী রাখতে হয়।","কিয়ামতের জবাবদিহির কথা মনে রাখা গুনাহ থেকে বাঁচতে সাহায্য করে।"],"related_hadiths":[{"id":"194","book_id":"2","label":"Sahih Muslim"},{"id":"2515","book_id":"1","label":"Sahih Bukhari"},{"id":"6772","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর মানুষের কঠিন সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. বৃদ্ধ যিনাকারী, মিথ্যাবাদী শাসক ও অহঙ্কারী দরিদ্র ব্যক্তির জন্য কিয়ামতের কঠিন সতর্কতা এসেছে।"},"heading":{"title":"তিন শ্রেণীর মানুষের ব্যাপারে হাদিস: যিনা, মিথ্যা ও অহঙ্কারের ভয়াবহতা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তিন ধরনের মানুষের ব্যাপারে কঠিন সতর্কতা দিয়েছেন। তারা হলো বৃদ্ধ যিনাকারী, মিথ্যাবাদী শাসক এবং অহঙ্কারী দরিদ্র ব্যক্তি। হাদিসে বলা হয়েছে, কিয়ামতের দিন আল্লাহ তাদের সাথে কথা বলবেন না, তাদের পবিত্র করবেন না; অন্য বর্ণনায় আছে, তাদের দিকে তাকাবেন না এবং তাদের জন্য যন্ত্রণাদায়ক শাস্তি রয়েছে। এখানে তিনটি পাপ খুব স্পষ্ট: যিনা, মিথ্যা এবং অহঙ্কার। বয়স, পদ বা অবস্থা কোনো মানুষকে গুনাহ থেকে নিরাপদ করে না। বিশেষ করে শাসকের মিথ্যা মানুষের উপর বড় প্রভাব ফেলে। আবার দরিদ্র হয়েও অহঙ্কার করা দেখায় যে অহঙ্কার শুধু সম্পদের কারণে নয়, মনের রোগ হিসেবেও থাকতে পারে।"},"teachings":["যিনা, মিথ্যা ও অহঙ্কার—তিনটি কাজই গুরুতর পাপ।","ক্ষমতাবান ব্যক্তির মিথ্যা সমাজে বড় ক্ষতি আনতে পারে।","দারিদ্র্য অহঙ্কার থেকে নিরাপত্তা দেয় না; মনকে বিনয়ী রাখতে হয়।","কিয়ামতের জবাবদিহির কথা মনে রাখা গুনাহ থেকে বাঁচতে সাহায্য করে।"],"related_hadiths":[{"id":"194","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2515","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6772","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুসলিমের রক্ত ও তিন ব্যতিক্রম","description":"$book_name$ $hadith_number$ - $chapter_name$. মুসলিমের রক্তের মর্যাদা এবং তিন ধরনের অপরাধে শরয়ী দণ্ডের বিষয় এই হাদিসে উল্লেখ করা হয়েছে।"},"heading":{"title":"মুসলিমের রক্তের মর্যাদা: তিন ব্যতিক্রম সম্পর্কে হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম মুসলিমের রক্তের মর্যাদা স্পষ্ট করেছেন। যে ব্যক্তি আল্লাহ ছাড়া কোনো মাবুদ নেই এবং মুহাম্মাদ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম আল্লাহর রাসূল—এই সাক্ষ্য দেয়, তার রক্ত হালাল নয়। তবে তিনটি অপরাধের কথা হাদিসে এসেছে: বিবাহের পর যিনা, আল্লাহ ও তাঁর রাসূলের বিরুদ্ধে যুদ্ধের অবস্থান, এবং কাউকে হত্যা করা। হাদিসে এদের জন্য শরয়ী দণ্ডের কথা বলা হয়েছে। ইসলামী স্কলারদের মতে, এসব দণ্ড ব্যক্তি বা দল নিজের ইচ্ছায় প্রয়োগ করতে পারে না; বিচার, প্রমাণ ও বৈধ কর্তৃপক্ষের মাধ্যমে হয়। এই হাদিস মানুষের জীবনকে সম্মান করতে শেখায় এবং একই সাথে গুরুতর অপরাধের ভয়াবহতা বুঝায়।"},"teachings":["একজন মুসলিমের জীবন ও রক্তের মর্যাদা অনেক বড়।","হত্যা, যিনা ও আল্লাহ-রাসূলের বিরুদ্ধে যুদ্ধ গুরুতর অপরাধ।","শরয়ী দণ্ড ব্যক্তিগত প্রতিশোধের বিষয় নয়; বিচারব্যবস্থার বিষয়।","জীবনের নিরাপত্তা ও ন্যায়বিচার ইসলামের গুরুত্বপূর্ণ শিক্ষা।"],"related_hadiths":[{"id":"6878","book_id":"1","label":"Sahih Bukhari"},{"id":"6879","book_id":"1","label":"Sahih Bukhari"},{"id":"3562","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুসলিমের রক্ত ও তিন ব্যতিক্রম","description":"$book_name$ $hadith_number$ - $chapter_name$. মুসলিমের রক্তের মর্যাদা এবং তিন ধরনের অপরাধে শরয়ী দণ্ডের বিষয় এই হাদিসে উল্লেখ করা হয়েছে।"},"heading":{"title":"মুসলিমের রক্তের মর্যাদা: তিন ব্যতিক্রম সম্পর্কে হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম মুসলিমের রক্তের মর্যাদা স্পষ্ট করেছেন। যে ব্যক্তি আল্লাহ ছাড়া কোনো মাবুদ নেই এবং মুহাম্মাদ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম আল্লাহর রাসূল—এই সাক্ষ্য দেয়, তার রক্ত হালাল নয়। তবে তিনটি অপরাধের কথা হাদিসে এসেছে: বিবাহের পর যিনা, আল্লাহ ও তাঁর রাসূলের বিরুদ্ধে যুদ্ধের অবস্থান, এবং কাউকে হত্যা করা। হাদিসে এদের জন্য শরয়ী দণ্ডের কথা বলা হয়েছে। ইসলামী স্কলারদের মতে, এসব দণ্ড ব্যক্তি বা দল নিজের ইচ্ছায় প্রয়োগ করতে পারে না; বিচার, প্রমাণ ও বৈধ কর্তৃপক্ষের মাধ্যমে হয়। এই হাদিস মানুষের জীবনকে সম্মান করতে শেখায় এবং একই সাথে গুরুতর অপরাধের ভয়াবহতা বুঝায়।"},"teachings":["একজন মুসলিমের জীবন ও রক্তের মর্যাদা অনেক বড়।","হত্যা, যিনা ও আল্লাহ-রাসূলের বিরুদ্ধে যুদ্ধ গুরুতর অপরাধ।","শরয়ী দণ্ড ব্যক্তিগত প্রতিশোধের বিষয় নয়; বিচারব্যবস্থার বিষয়।","জীবনের নিরাপত্তা ও ন্যায়বিচার ইসলামের গুরুত্বপূর্ণ শিক্ষা।"],"related_hadiths":[{"id":"6878","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6879","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3562","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E9" s="4" t="n"/>
@@ -676,7 +680,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | চোখ, কান ও অন্তরের যিনা","description":"$book_name$ $hadith_number$ - $chapter_name$. চোখ, কান, জিহ্বা, হাত, পা ও অন্তরের যিনার কথা বলে পবিত্রতা রক্ষার গভীর শিক্ষা দেওয়া হয়েছে।"},"heading":{"title":"চোখের যিনা সম্পর্কে হাদিস: দৃষ্টি, কথা ও অন্তরকে হেফাজত করুন","description":"এই হাদিসে যিনার পথগুলো খুব সহজ ভাষায় বুঝানো হয়েছে। নবী করীম সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, মানুষের চোখের যিনা হলো দেখা, কানের যিনা হলো শোনা, জিহ্বার যিনা হলো কথা বলা, হাতের যিনা হলো স্পর্শ করা, পায়ের যিনা হলো সেই পথে চলা, আর অন্তরের যিনা হলো আকাঙ্ক্ষা করা। শেষে বলা হয়েছে, লজ্জাস্থান তা সত্য বা মিথ্যা প্রমাণ করে। এর মানে পাপ একবারে শুরু হয় না; অনেক সময় দৃষ্টি, কথা, শোনা, স্পর্শ ও মনের ইচ্ছা থেকে তা ধীরে ধীরে বড় পাপে গড়ায়। তাই চোখের হেফাজত, কানের হেফাজত, কথার হেফাজত এবং অন্তরের পবিত্রতা—সবই জরুরি। এই হাদিস আমাদের ছোট ছোট পদক্ষেপকে গুরুত্ব দিতে শেখায়।"},"teachings":["যিনার দিকে নিয়ে যায় এমন দৃষ্টি, কথা ও স্পর্শ থেকে বাঁচতে হবে।","অন্তরের খারাপ আকাঙ্ক্ষাও মানুষকে ভুল পথে নিতে পারে।","পাপের শুরু ছোট মনে হলেও তার শেষ বড় হতে পারে।","চোখ, কান, জিহ্বা, হাত ও পা—সব অঙ্গের হেফাজত দরকার।"],"related_hadiths":[{"id":"6243","book_id":"1","label":"Sahih Bukhari"},{"id":"6772","book_id":"1","label":"Sahih Bukhari"},{"id":"3562","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | চোখ, কান ও অন্তরের যিনা","description":"$book_name$ $hadith_number$ - $chapter_name$. চোখ, কান, জিহ্বা, হাত, পা ও অন্তরের যিনার কথা বলে পবিত্রতা রক্ষার গভীর শিক্ষা দেওয়া হয়েছে।"},"heading":{"title":"চোখের যিনা সম্পর্কে হাদিস: দৃষ্টি, কথা ও অন্তরকে হেফাজত করুন","description":"এই হাদিসে যিনার পথগুলো খুব সহজ ভাষায় বুঝানো হয়েছে। নবী করীম সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, মানুষের চোখের যিনা হলো দেখা, কানের যিনা হলো শোনা, জিহ্বার যিনা হলো কথা বলা, হাতের যিনা হলো স্পর্শ করা, পায়ের যিনা হলো সেই পথে চলা, আর অন্তরের যিনা হলো আকাঙ্ক্ষা করা। শেষে বলা হয়েছে, লজ্জাস্থান তা সত্য বা মিথ্যা প্রমাণ করে। এর মানে পাপ একবারে শুরু হয় না; অনেক সময় দৃষ্টি, কথা, শোনা, স্পর্শ ও মনের ইচ্ছা থেকে তা ধীরে ধীরে বড় পাপে গড়ায়। তাই চোখের হেফাজত, কানের হেফাজত, কথার হেফাজত এবং অন্তরের পবিত্রতা—সবই জরুরি। এই হাদিস আমাদের ছোট ছোট পদক্ষেপকে গুরুত্ব দিতে শেখায়।"},"teachings":["যিনার দিকে নিয়ে যায় এমন দৃষ্টি, কথা ও স্পর্শ থেকে বাঁচতে হবে।","অন্তরের খারাপ আকাঙ্ক্ষাও মানুষকে ভুল পথে নিতে পারে।","পাপের শুরু ছোট মনে হলেও তার শেষ বড় হতে পারে।","চোখ, কান, জিহ্বা, হাত ও পা—সব অঙ্গের হেফাজত দরকার।"],"related_hadiths":[{"id":"6243","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6772","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3562","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E10" s="4" t="n"/>
@@ -699,7 +703,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অর্ধরাতের দোয়া ও ক্ষমার সুযোগ","description":"$book_name$ $hadith_number$ - $chapter_name$. অর্ধরাতে দোয়া, সাহায্য ও সংকটমুক্তির আহ্বান আসে; তবে অশ্লীলতায় লিপ্তদের জন্য কঠিন সতর্কতা আছে।"},"heading":{"title":"অর্ধরাতের দোয়া সম্পর্কে হাদিস: আল্লাহর কাছে ফিরে আসার সময়","description":"এই হাদিসে অর্ধরাতের দোয়া ও ক্ষমা চাওয়ার বড় সুযোগের কথা এসেছে। রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, অর্ধরাতে আকাশের দরজা খোলা হয়। তখন আহ্বান করা হয়—কেউ দোয়া করবে কি, তার দোয়া কবুল করা হবে? কেউ সাহায্য চাইবে কি, তাকে সাহায্য করা হবে? কেউ সংকটে আছে কি, তার সংকট দূর করা হবে? হাদিসে বলা হয়েছে, এ সময় কোনো মুসলমান দোয়া করলে আল্লাহ তার দোয়া কবুল করেন। তবে অশ্লীল কাজে লিপ্ত নারীর ব্যাপারে ব্যতিক্রমের কথা এসেছে। অন্য বর্ণনায় ক্ষমা চাওয়ার কথাও আছে। এই হাদিস আমাদের শেখায়, রাতের নীরব সময়ে আল্লাহর কাছে দোয়া, ইস্তেগফার ও নিজের ভুল থেকে ফিরে আসা খুব গুরুত্বপূর্ণ।"},"teachings":["অর্ধরাত দোয়া ও ইস্তেগফারের গুরুত্বপূর্ণ সময় হিসেবে বর্ণিত হয়েছে।","সংকটে পড়লে আল্লাহর কাছে সাহায্য চাইতে হবে।","অশ্লীল কাজে লিপ্ত থাকা দোয়া ও ক্ষমার পথে বাধা হতে পারে।","নিজের ভুল বুঝে আল্লাহর কাছে ফিরে আসা দরকার।"],"related_hadiths":[{"id":"1145","book_id":"1","label":"Sahih Bukhari"},{"id":"1656","book_id":"2","label":"Sahih Muslim"},{"id":"6845","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অর্ধরাতের দোয়া ও ক্ষমার সুযোগ","description":"$book_name$ $hadith_number$ - $chapter_name$. অর্ধরাতে দোয়া, সাহায্য ও সংকটমুক্তির আহ্বান আসে; তবে অশ্লীলতায় লিপ্তদের জন্য কঠিন সতর্কতা আছে।"},"heading":{"title":"অর্ধরাতের দোয়া সম্পর্কে হাদিস: আল্লাহর কাছে ফিরে আসার সময়","description":"এই হাদিসে অর্ধরাতের দোয়া ও ক্ষমা চাওয়ার বড় সুযোগের কথা এসেছে। রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, অর্ধরাতে আকাশের দরজা খোলা হয়। তখন আহ্বান করা হয়—কেউ দোয়া করবে কি, তার দোয়া কবুল করা হবে? কেউ সাহায্য চাইবে কি, তাকে সাহায্য করা হবে? কেউ সংকটে আছে কি, তার সংকট দূর করা হবে? হাদিসে বলা হয়েছে, এ সময় কোনো মুসলমান দোয়া করলে আল্লাহ তার দোয়া কবুল করেন। তবে অশ্লীল কাজে লিপ্ত নারীর ব্যাপারে ব্যতিক্রমের কথা এসেছে। অন্য বর্ণনায় ক্ষমা চাওয়ার কথাও আছে। এই হাদিস আমাদের শেখায়, রাতের নীরব সময়ে আল্লাহর কাছে দোয়া, ইস্তেগফার ও নিজের ভুল থেকে ফিরে আসা খুব গুরুত্বপূর্ণ।"},"teachings":["অর্ধরাত দোয়া ও ইস্তেগফারের গুরুত্বপূর্ণ সময় হিসেবে বর্ণিত হয়েছে।","সংকটে পড়লে আল্লাহর কাছে সাহায্য চাইতে হবে।","অশ্লীল কাজে লিপ্ত থাকা দোয়া ও ক্ষমার পথে বাধা হতে পারে।","নিজের ভুল বুঝে আল্লাহর কাছে ফিরে আসা দরকার।"],"related_hadiths":[{"id":"1145","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1656","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6845","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E11" s="4" t="n"/>
@@ -722,7 +726,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যিনা ও গোপন প্রবৃত্তির ভয়","description":"$book_name$ $hadith_number$ - $chapter_name$. যিনা ও গোপন প্রবৃত্তিকে উম্মতের জন্য ভয়ংকর ফিতনা হিসেবে সতর্ক করা হয়েছে।"},"heading":{"title":"যিনা ও গোপন প্রবৃত্তি সম্পর্কে হাদিস: অন্তরের পবিত্রতার শিক্ষা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তিনি উম্মতের জন্য যে বিষয়ে বেশি ভয় করেন তা হলো যিনা ও গোপন প্রবৃত্তি। এখানে যিনা শুধু প্রকাশ্য পাপ নয়, বরং তার পেছনের মনের টান, লুকানো কামনা ও গোপন ইচ্ছার দিকেও ইশারা আছে। মানুষ বাইরে ভালো দেখালেও অন্তরে খারাপ আকাঙ্ক্ষা লালন করতে পারে। তাই শুধু বাহ্যিক আচরণ নয়, অন্তরও ঠিক রাখা দরকার। এই হাদিস আমাদের শেখায়, পাপের আগের ধাপগুলোকে হালকা করে দেখা যাবে না। চোখ, কথা, একাকী আচরণ ও গোপন ইচ্ছার জায়গায় আল্লাহভীতি থাকা জরুরি। যিনা থেকে বাঁচতে হলে গোপন প্রবৃত্তিকেও নিয়ন্ত্রণ করতে হবে।"},"teachings":["যিনা উম্মতের জন্য বড় ফিতনা হিসেবে সতর্ক করা হয়েছে।","গোপন কামনা ও লুকানো প্রবৃত্তি পাপের দিকে নিয়ে যেতে পারে।","বাহ্যিক আচরণের সাথে অন্তরের পবিত্রতাও দরকার।","একাকী অবস্থাতেও আল্লাহভীতি বজায় রাখা জরুরি।"],"related_hadiths":[{"id":"6772","book_id":"1","label":"Sahih Bukhari"},{"id":"6243","book_id":"1","label":"Sahih Bukhari"},{"id":"86","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যিনা ও গোপন প্রবৃত্তির ভয়","description":"$book_name$ $hadith_number$ - $chapter_name$. যিনা ও গোপন প্রবৃত্তিকে উম্মতের জন্য ভয়ংকর ফিতনা হিসেবে সতর্ক করা হয়েছে।"},"heading":{"title":"যিনা ও গোপন প্রবৃত্তি সম্পর্কে হাদিস: অন্তরের পবিত্রতার শিক্ষা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তিনি উম্মতের জন্য যে বিষয়ে বেশি ভয় করেন তা হলো যিনা ও গোপন প্রবৃত্তি। এখানে যিনা শুধু প্রকাশ্য পাপ নয়, বরং তার পেছনের মনের টান, লুকানো কামনা ও গোপন ইচ্ছার দিকেও ইশারা আছে। মানুষ বাইরে ভালো দেখালেও অন্তরে খারাপ আকাঙ্ক্ষা লালন করতে পারে। তাই শুধু বাহ্যিক আচরণ নয়, অন্তরও ঠিক রাখা দরকার। এই হাদিস আমাদের শেখায়, পাপের আগের ধাপগুলোকে হালকা করে দেখা যাবে না। চোখ, কথা, একাকী আচরণ ও গোপন ইচ্ছার জায়গায় আল্লাহভীতি থাকা জরুরি। যিনা থেকে বাঁচতে হলে গোপন প্রবৃত্তিকেও নিয়ন্ত্রণ করতে হবে।"},"teachings":["যিনা উম্মতের জন্য বড় ফিতনা হিসেবে সতর্ক করা হয়েছে।","গোপন কামনা ও লুকানো প্রবৃত্তি পাপের দিকে নিয়ে যেতে পারে।","বাহ্যিক আচরণের সাথে অন্তরের পবিত্রতাও দরকার।","একাকী অবস্থাতেও আল্লাহভীতি বজায় রাখা জরুরি।"],"related_hadiths":[{"id":"6772","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6243","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"86","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E12" s="4" t="n"/>
@@ -745,7 +749,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ব্যভিচারীদের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. স্বপ্নে ব্যভিচারী নারী-পুরুষের দুর্গন্ধময় ও অপমানজনক অবস্থা দেখিয়ে যিনা থেকে সতর্ক করা হয়েছে।"},"heading":{"title":"ব্যভিচারীদের পরিণতি সম্পর্কে হাদিস: যিনা থেকে সতর্ক থাকার শিক্ষা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তাঁর দেখা এক ঘটনার বর্ণনা দিয়েছেন। তিনি বলেন, ঘুমের মধ্যে দুইজন লোক এসে তাঁর বাহু ধরে নিয়ে গেল। এরপর তিনি এমন কিছু লোক দেখলেন, যারা খুব ফুলে আছে এবং তাদের গন্ধ ছিল অত্যন্ত খারাপ, যেন ভাগাড়ের গন্ধ। তিনি জানতে চাইলে বলা হলো, এরা ব্যভিচারী নারী-পুরুষ। এই বর্ণনা যিনার ভয়াবহ পরিণতি বুঝায়। হাদিসের ভাষা কঠিন, কারণ পাপটিও গুরুতর। এখানে উদ্দেশ্য হলো মানুষকে অশ্লীলতা, অবৈধ সম্পর্ক ও লজ্জাহীনতা থেকে দূরে রাখা। একজন মুসলিমের জন্য দেহ, মন, দৃষ্টি ও সম্পর্ককে পবিত্র রাখা জরুরি।"},"teachings":["যিনা মানুষের দুনিয়া ও আখেরাতের জন্য বড় ক্ষতির কারণ হতে পারে।","অবৈধ সম্পর্ক ও অশ্লীলতা থেকে দূরে থাকা জরুরি।","পাপের পরিণতি মনে রাখা আত্মসংযমে সাহায্য করে।","নারী-পুরুষ উভয়ের জন্য পবিত্রতা রক্ষা গুরুত্বপূর্ণ।"],"related_hadiths":[{"id":"7047","book_id":"1","label":"Sahih Bukhari"},{"id":"6772","book_id":"1","label":"Sahih Bukhari"},{"id":"3562","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ব্যভিচারীদের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. স্বপ্নে ব্যভিচারী নারী-পুরুষের দুর্গন্ধময় ও অপমানজনক অবস্থা দেখিয়ে যিনা থেকে সতর্ক করা হয়েছে।"},"heading":{"title":"ব্যভিচারীদের পরিণতি সম্পর্কে হাদিস: যিনা থেকে সতর্ক থাকার শিক্ষা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তাঁর দেখা এক ঘটনার বর্ণনা দিয়েছেন। তিনি বলেন, ঘুমের মধ্যে দুইজন লোক এসে তাঁর বাহু ধরে নিয়ে গেল। এরপর তিনি এমন কিছু লোক দেখলেন, যারা খুব ফুলে আছে এবং তাদের গন্ধ ছিল অত্যন্ত খারাপ, যেন ভাগাড়ের গন্ধ। তিনি জানতে চাইলে বলা হলো, এরা ব্যভিচারী নারী-পুরুষ। এই বর্ণনা যিনার ভয়াবহ পরিণতি বুঝায়। হাদিসের ভাষা কঠিন, কারণ পাপটিও গুরুতর। এখানে উদ্দেশ্য হলো মানুষকে অশ্লীলতা, অবৈধ সম্পর্ক ও লজ্জাহীনতা থেকে দূরে রাখা। একজন মুসলিমের জন্য দেহ, মন, দৃষ্টি ও সম্পর্ককে পবিত্র রাখা জরুরি।"},"teachings":["যিনা মানুষের দুনিয়া ও আখেরাতের জন্য বড় ক্ষতির কারণ হতে পারে।","অবৈধ সম্পর্ক ও অশ্লীলতা থেকে দূরে থাকা জরুরি।","পাপের পরিণতি মনে রাখা আত্মসংযমে সাহায্য করে।","নারী-পুরুষ উভয়ের জন্য পবিত্রতা রক্ষা গুরুত্বপূর্ণ।"],"related_hadiths":[{"id":"7047","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6772","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3562","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E13" s="4" t="n"/>
@@ -768,7 +772,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দোভাষী ছাড়া রবের সাথে কথা","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে প্রত্যেকে দোভাষী ছাড়া রবের সঙ্গে কথা বলবে; সামনে জাহান্নাম দেখে দান দ্বারা বাঁচতে বলা হয়েছে।"},"heading":{"title":"দোভাষী ছাড়া রবের সাথে কথা ও জাহান্নাম থেকে বাঁচার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তোমাদের প্রত্যেকের সঙ্গে তার রব কথা বলবেন। তার ও রবের মাঝে কোনো দোভাষী থাকবে না এবং এমন কোনো পর্দাও থাকবে না যা তাকে আড়াল করে। সে ডানে তাকিয়ে নিজের আগে পাঠানো আমল ছাড়া কিছু দেখবে না, বামে তাকিয়েও নিজের আমল দেখবে। সামনে তাকালে জাহান্নাম দেখবে। এরপর নবীজি বলেছেন, খেজুরের অর্ধেক অংশ দিয়েও জাহান্নাম থেকে বাঁচার চেষ্টা করো। এই হাদিস কিয়ামতের জবাবদিহি, আমলের গুরুত্ব এবং ছোট দানের মূল্য শেখায়। সামান্য ভালো কাজকেও ছোট মনে করা ঠিক নয়, কারণ আখেরাতে মানুষ নিজের পাঠানো কাজই সামনে পাবে।"},"teachings":["কিয়ামতে প্রত্যেকে নিজের রবের সামনে জবাবদিহি করবে।","মানুষ নিজের পাঠানো আমলই সামনে দেখতে পাবে।","সামান্য দানও জাহান্নাম থেকে বাঁচার চেষ্টা হতে পারে।","আখেরাতের জন্য ভালো কাজ আগে পাঠানো দরকার।"],"related_hadiths":[{"id":"6539","book_id":"1","label":"Sahih Bukhari"},{"id":"1016","book_id":"2","label":"Sahih Muslim"},{"id":"5550","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দোভাষী ছাড়া রবের সাথে কথা","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে প্রত্যেকে দোভাষী ছাড়া রবের সঙ্গে কথা বলবে; সামনে জাহান্নাম দেখে দান দ্বারা বাঁচতে বলা হয়েছে।"},"heading":{"title":"দোভাষী ছাড়া রবের সাথে কথা ও জাহান্নাম থেকে বাঁচার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তোমাদের প্রত্যেকের সঙ্গে তার রব কথা বলবেন। তার ও রবের মাঝে কোনো দোভাষী থাকবে না এবং এমন কোনো পর্দাও থাকবে না যা তাকে আড়াল করে। সে ডানে তাকিয়ে নিজের আগে পাঠানো আমল ছাড়া কিছু দেখবে না, বামে তাকিয়েও নিজের আমল দেখবে। সামনে তাকালে জাহান্নাম দেখবে। এরপর নবীজি বলেছেন, খেজুরের অর্ধেক অংশ দিয়েও জাহান্নাম থেকে বাঁচার চেষ্টা করো। এই হাদিস কিয়ামতের জবাবদিহি, আমলের গুরুত্ব এবং ছোট দানের মূল্য শেখায়। সামান্য ভালো কাজকেও ছোট মনে করা ঠিক নয়, কারণ আখেরাতে মানুষ নিজের পাঠানো কাজই সামনে পাবে।"},"teachings":["কিয়ামতে প্রত্যেকে নিজের রবের সামনে জবাবদিহি করবে।","মানুষ নিজের পাঠানো আমলই সামনে দেখতে পাবে।","সামান্য দানও জাহান্নাম থেকে বাঁচার চেষ্টা হতে পারে।","আখেরাতের জন্য ভালো কাজ আগে পাঠানো দরকার।"],"related_hadiths":[{"id":"6539","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1016","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"5550","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E14" s="4" t="n"/>
@@ -791,7 +795,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মায়েয ও গামেদী নারীর খাঁটি তওবা","description":"$book_name$ $hadith_number$ - $chapter_name$. মায়েয ও গামেদী নারীর ঘটনায় পাপের স্বীকারোক্তি, তওবা, বিচার ও শিশুর হকের শিক্ষা এসেছে।"},"heading":{"title":"মায়েয ও গামেদী নারীর তওবা: যিনা, বিচার ও আল্লাহর ক্ষমার শিক্ষা","description":"এই দীর্ঘ হাদিসে মায়েয ইবনে মালেক রাদিয়াল্লাহু আনহু এবং গামেদী গোত্রের এক নারীর ঘটনা এসেছে। মায়েয বারবার রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর কাছে এসে নিজেকে পবিত্র করার কথা বলেন। নবীজি প্রথমে তাকে ফিরে গিয়ে আল্লাহর কাছে ক্ষমা চাইতে ও তওবা করতে বলেন। পরে বিষয়টি যাচাই করা হয়—তিনি পাগল কি না, মদ পান করেছেন কি না, সত্যিই যিনা করেছেন কি না। এরপর রজমের নির্দেশ দেওয়া হয়। গামেদী নারীও তওবার জন্য আসেন। তিনি গর্ভবতী ছিলেন, তাই সন্তান জন্ম ও দুধপানের বিষয় বিবেচনা করা হয়। হাদিসে তওবার মর্যাদা, বিচারপূর্ব যাচাই, শিশুর হক এবং পাপীকে গালি না দেওয়ার শিক্ষা আছে। ইসলামী স্কলারদের মতে, এসব দণ্ড ব্যক্তিগতভাবে প্রয়োগের বিষয় নয়; বৈধ বিচারব্যবস্থার বিষয়।"},"teachings":["খাঁটি তওবা আল্লাহর কাছে বড় মর্যাদার বিষয়।","গুরুতর অভিযোগে যাচাই ছাড়া সিদ্ধান্ত নেওয়া যায় না।","শিশুর হক ও দুধপানের দায়িত্ব বিবেচনা করা হয়েছে।","তওবাকারী মানুষকে গালি দেওয়া উচিত নয়।"],"related_hadiths":[{"id":"3558","book_id":"14","label":"Mishkat al-Masabih"},{"id":"4353","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6824","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মায়েয ও গামেদী নারীর খাঁটি তওবা","description":"$book_name$ $hadith_number$ - $chapter_name$. মায়েয ও গামেদী নারীর ঘটনায় পাপের স্বীকারোক্তি, তওবা, বিচার ও শিশুর হকের শিক্ষা এসেছে।"},"heading":{"title":"মায়েয ও গামেদী নারীর তওবা: যিনা, বিচার ও আল্লাহর ক্ষমার শিক্ষা","description":"এই দীর্ঘ হাদিসে মায়েয ইবনে মালেক রাদিয়াল্লাহু আনহু এবং গামেদী গোত্রের এক নারীর ঘটনা এসেছে। মায়েয বারবার রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর কাছে এসে নিজেকে পবিত্র করার কথা বলেন। নবীজি প্রথমে তাকে ফিরে গিয়ে আল্লাহর কাছে ক্ষমা চাইতে ও তওবা করতে বলেন। পরে বিষয়টি যাচাই করা হয়—তিনি পাগল কি না, মদ পান করেছেন কি না, সত্যিই যিনা করেছেন কি না। এরপর রজমের নির্দেশ দেওয়া হয়। গামেদী নারীও তওবার জন্য আসেন। তিনি গর্ভবতী ছিলেন, তাই সন্তান জন্ম ও দুধপানের বিষয় বিবেচনা করা হয়। হাদিসে তওবার মর্যাদা, বিচারপূর্ব যাচাই, শিশুর হক এবং পাপীকে গালি না দেওয়ার শিক্ষা আছে। ইসলামী স্কলারদের মতে, এসব দণ্ড ব্যক্তিগতভাবে প্রয়োগের বিষয় নয়; বৈধ বিচারব্যবস্থার বিষয়।"},"teachings":["খাঁটি তওবা আল্লাহর কাছে বড় মর্যাদার বিষয়।","গুরুতর অভিযোগে যাচাই ছাড়া সিদ্ধান্ত নেওয়া যায় না।","শিশুর হক ও দুধপানের দায়িত্ব বিবেচনা করা হয়েছে।","তওবাকারী মানুষকে গালি দেওয়া উচিত নয়।"],"related_hadiths":[{"id":"3558","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"4353","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6824","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E15" s="4" t="n"/>
@@ -814,7 +818,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | স্বপ্নে পাপের পরিণতি ও জান্নাতের দৃশ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. মিথ্যা, কুরআন অবহেলা, যিনা ও সুদের পরিণতি এবং মুমিন-শহীদের মর্যাদা স্বপ্নে দেখানো হয়েছে।"},"heading":{"title":"নবীজির স্বপ্নের হাদিস: মিথ্যা, যিনা, সুদ ও কুরআন অবহেলার পরিণতি","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর এক দীর্ঘ স্বপ্নের বর্ণনা আছে। তিনি ফজরের পর সাহাবিদের কাছে স্বপ্ন জানতে চাইতেন এবং আল্লাহর ইচ্ছায় তার ব্যাখ্যা করতেন। এক রাতে তিনি দুইজন ফেরেশতার সাথে বিভিন্ন দৃশ্য দেখেন। এক ব্যক্তির গাল চেরা হচ্ছিল, কারণ সে মিথ্যা বলত এবং তা ছড়িয়ে পড়ত। আরেকজনের মাথা পাথর দিয়ে ভাঙা হচ্ছিল, কারণ সে কুরআন শিখেও রাতে তা থেকে গাফেল ছিল এবং দিনে আমল করত না। তন্দুরের মতো স্থানে উলঙ্গ নারী-পুরুষ ছিল; তারা যিনাকারী। রক্তের নদীতে থাকা ব্যক্তি সুদখোর। পরে তিনি ইবরাহীম আলাইহিস সালাম, শিশুদের, জান্নাতের ঘর এবং শহীদদের ঘর দেখেন। হাদিসটি পাপের পরিণতি ও সৎ জীবনের আশা—দুই দিকই শেখায়।"},"teachings":["মিথ্যা ছড়ানো বড় পাপ এবং এর পরিণতি ভয়াবহ হতে পারে।","কুরআন শিখে অবহেলা করা ও আমল না করা বিপদের কারণ।","যিনা ও সুদ থেকে দূরে থাকার শক্ত সতর্কতা এসেছে।","মুমিন ও শহীদদের জন্য সম্মানের দৃশ্য বর্ণিত হয়েছে।"],"related_hadiths":[{"id":"6096","book_id":"1","label":"Sahih Bukhari"},{"id":"6772","book_id":"1","label":"Sahih Bukhari"},{"id":"2086","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | স্বপ্নে পাপের পরিণতি ও জান্নাতের দৃশ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. মিথ্যা, কুরআন অবহেলা, যিনা ও সুদের পরিণতি এবং মুমিন-শহীদের মর্যাদা স্বপ্নে দেখানো হয়েছে।"},"heading":{"title":"নবীজির স্বপ্নের হাদিস: মিথ্যা, যিনা, সুদ ও কুরআন অবহেলার পরিণতি","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর এক দীর্ঘ স্বপ্নের বর্ণনা আছে। তিনি ফজরের পর সাহাবিদের কাছে স্বপ্ন জানতে চাইতেন এবং আল্লাহর ইচ্ছায় তার ব্যাখ্যা করতেন। এক রাতে তিনি দুইজন ফেরেশতার সাথে বিভিন্ন দৃশ্য দেখেন। এক ব্যক্তির গাল চেরা হচ্ছিল, কারণ সে মিথ্যা বলত এবং তা ছড়িয়ে পড়ত। আরেকজনের মাথা পাথর দিয়ে ভাঙা হচ্ছিল, কারণ সে কুরআন শিখেও রাতে তা থেকে গাফেল ছিল এবং দিনে আমল করত না। তন্দুরের মতো স্থানে উলঙ্গ নারী-পুরুষ ছিল; তারা যিনাকারী। রক্তের নদীতে থাকা ব্যক্তি সুদখোর। পরে তিনি ইবরাহীম আলাইহিস সালাম, শিশুদের, জান্নাতের ঘর এবং শহীদদের ঘর দেখেন। হাদিসটি পাপের পরিণতি ও সৎ জীবনের আশা—দুই দিকই শেখায়।"},"teachings":["মিথ্যা ছড়ানো বড় পাপ এবং এর পরিণতি ভয়াবহ হতে পারে।","কুরআন শিখে অবহেলা করা ও আমল না করা বিপদের কারণ।","যিনা ও সুদ থেকে দূরে থাকার শক্ত সতর্কতা এসেছে।","মুমিন ও শহীদদের জন্য সম্মানের দৃশ্য বর্ণিত হয়েছে।"],"related_hadiths":[{"id":"6096","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6772","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2086","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E16" s="4" t="n"/>
@@ -837,7 +841,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে কুকুর ও ছবি রাখার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. যে ঘরে কুকুর ও ছবি থাকে, সে ঘরে রহমতের ফেরেশতা প্রবেশ না করার সতর্কতা এসেছে।"},"heading":{"title":"ঘরে কুকুর ও ছবি সম্পর্কে হাদিস: ফেরেশতা প্রবেশ না করার সতর্কতা","description":"এই হাদিসে নবী সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যে ঘরে কুকুর ও ছবি থাকে, সে ঘরে ফেরেশতা প্রবেশ করে না। এখানে মূল শিক্ষা হলো ঘরের পরিবেশকে এমন রাখা, যা আল্লাহর রহমত ও বরকতের সাথে মানানসই। হাদিসের ভাষায় কুকুর ও ছবি—দুটি বিষয় আলাদা করে উল্লেখ হয়েছে। তাই ঘরের সাজসজ্জা, দেয়াল, পর্দা বা ব্যবহারের জিনিসে ছবি রাখার বিষয়টি মুসলিম জীবনে সতর্কতার দাবি রাখে। তবে হাদিসের বাইরে গিয়ে সব ধরনের প্রয়োজনীয় ব্যবহার নিয়ে বড় দাবি করা ঠিক নয়। ইসলামী স্কলারদের মতে, প্রাণীর ছবি ও অপ্রয়োজনীয় ছবি রাখার বিষয়ে বিশেষ সতর্কতা আছে। এই হাদিস পরিবারকে ঘরের দীনী পরিবেশ নিয়ে ভাবতে শেখায়।"},"teachings":["ঘরের পরিবেশকে রহমত ও বরকতের উপযোগী রাখা উচিত।","কুকুর ও ছবি রাখার বিষয়ে হাদিসে সতর্কতা এসেছে।","অপ্রয়োজনীয় ছবি দিয়ে ঘর সাজানো থেকে বাঁচা উচিত।","পরিবারে দীনী সচেতনতা গড়ে তোলা দরকার।"],"related_hadiths":[{"id":"5961","book_id":"1","label":"Sahih Bukhari"},{"id":"5959","book_id":"1","label":"Sahih Bukhari"},{"id":"5952","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে কুকুর ও ছবি রাখার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. যে ঘরে কুকুর ও ছবি থাকে, সে ঘরে রহমতের ফেরেশতা প্রবেশ না করার সতর্কতা এসেছে।"},"heading":{"title":"ঘরে কুকুর ও ছবি সম্পর্কে হাদিস: ফেরেশতা প্রবেশ না করার সতর্কতা","description":"এই হাদিসে নবী সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যে ঘরে কুকুর ও ছবি থাকে, সে ঘরে ফেরেশতা প্রবেশ করে না। এখানে মূল শিক্ষা হলো ঘরের পরিবেশকে এমন রাখা, যা আল্লাহর রহমত ও বরকতের সাথে মানানসই। হাদিসের ভাষায় কুকুর ও ছবি—দুটি বিষয় আলাদা করে উল্লেখ হয়েছে। তাই ঘরের সাজসজ্জা, দেয়াল, পর্দা বা ব্যবহারের জিনিসে ছবি রাখার বিষয়টি মুসলিম জীবনে সতর্কতার দাবি রাখে। তবে হাদিসের বাইরে গিয়ে সব ধরনের প্রয়োজনীয় ব্যবহার নিয়ে বড় দাবি করা ঠিক নয়। ইসলামী স্কলারদের মতে, প্রাণীর ছবি ও অপ্রয়োজনীয় ছবি রাখার বিষয়ে বিশেষ সতর্কতা আছে। এই হাদিস পরিবারকে ঘরের দীনী পরিবেশ নিয়ে ভাবতে শেখায়।"},"teachings":["ঘরের পরিবেশকে রহমত ও বরকতের উপযোগী রাখা উচিত।","কুকুর ও ছবি রাখার বিষয়ে হাদিসে সতর্কতা এসেছে।","অপ্রয়োজনীয় ছবি দিয়ে ঘর সাজানো থেকে বাঁচা উচিত।","পরিবারে দীনী সচেতনতা গড়ে তোলা দরকার।"],"related_hadiths":[{"id":"5961","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5959","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5952","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E17" s="4" t="n"/>
@@ -860,7 +864,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবি অঙ্কনকারীর কঠিন শাস্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবি-মূর্তি অঙ্কনকারীদের জন্য কিয়ামতের কঠিন শাস্তির সতর্কতা এই হাদিসে এসেছে।"},"heading":{"title":"ছবি অঙ্কনকারীর শাস্তি সম্পর্কে হাদিস: ছবি-মূর্তি থেকে সতর্কতা","description":"এই হাদিসে আবদুল্লাহ ইবনে মাসউদ রাদিয়াল্লাহু আনহু বলেন, তিনি নবী সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-কে বলতে শুনেছেন যে, আল্লাহর কাছে ছবি-মূর্তি অঙ্কনকারীদের কঠিন শাস্তি হবে। হাদিসের মূল কথা খুব স্পষ্ট: ছবি-মূর্তি তৈরি বা অঙ্কনের বিষয়টি হালকা করে দেখার সুযোগ নেই। এখানে বিশেষ করে প্রাণীর ছবি ও মূর্তি তৈরির ব্যাপারে সতর্কতা বোঝা যায়, কারণ অন্য হাদিসগুলোতেও ছবির ঘর, ছবিযুক্ত পর্দা এবং ছবি নির্মাতাদের শাস্তির কথা এসেছে। একজন মুসলিমের জন্য উচিত হলো ঘর, পোশাক, সাজসজ্জা ও কাজকর্মে এমন বিষয় এড়িয়ে চলা, যা এই সতর্কতার মধ্যে পড়ে।"},"teachings":["ছবি-মূর্তি অঙ্কনকারীদের জন্য কঠিন সতর্কতা এসেছে।","ধর্মীয় বিষয়ে হালকা মনোভাব রাখা ঠিক নয়।","ঘর ও ব্যবহারের জিনিসে ছবি নিয়ে সতর্ক হওয়া দরকার।","যে কাজ আল্লাহর অসন্তুষ্টির কারণ হতে পারে, তা থেকে দূরে থাকা উচিত।"],"related_hadiths":[{"id":"5951","book_id":"1","label":"Sahih Bukhari"},{"id":"5954","book_id":"1","label":"Sahih Bukhari"},{"id":"5961","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবি অঙ্কনকারীর কঠিন শাস্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবি-মূর্তি অঙ্কনকারীদের জন্য কিয়ামতের কঠিন শাস্তির সতর্কতা এই হাদিসে এসেছে।"},"heading":{"title":"ছবি অঙ্কনকারীর শাস্তি সম্পর্কে হাদিস: ছবি-মূর্তি থেকে সতর্কতা","description":"এই হাদিসে আবদুল্লাহ ইবনে মাসউদ রাদিয়াল্লাহু আনহু বলেন, তিনি নবী সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-কে বলতে শুনেছেন যে, আল্লাহর কাছে ছবি-মূর্তি অঙ্কনকারীদের কঠিন শাস্তি হবে। হাদিসের মূল কথা খুব স্পষ্ট: ছবি-মূর্তি তৈরি বা অঙ্কনের বিষয়টি হালকা করে দেখার সুযোগ নেই। এখানে বিশেষ করে প্রাণীর ছবি ও মূর্তি তৈরির ব্যাপারে সতর্কতা বোঝা যায়, কারণ অন্য হাদিসগুলোতেও ছবির ঘর, ছবিযুক্ত পর্দা এবং ছবি নির্মাতাদের শাস্তির কথা এসেছে। একজন মুসলিমের জন্য উচিত হলো ঘর, পোশাক, সাজসজ্জা ও কাজকর্মে এমন বিষয় এড়িয়ে চলা, যা এই সতর্কতার মধ্যে পড়ে।"},"teachings":["ছবি-মূর্তি অঙ্কনকারীদের জন্য কঠিন সতর্কতা এসেছে।","ধর্মীয় বিষয়ে হালকা মনোভাব রাখা ঠিক নয়।","ঘর ও ব্যবহারের জিনিসে ছবি নিয়ে সতর্ক হওয়া দরকার।","যে কাজ আল্লাহর অসন্তুষ্টির কারণ হতে পারে, তা থেকে দূরে থাকা উচিত।"],"related_hadiths":[{"id":"5951","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5954","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5961","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E18" s="4" t="n"/>
@@ -883,7 +887,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবি-মূর্তি নির্মাতাদের জবাবদিহি","description":"$book_name$ $hadith_number$ - $chapter_name$. যারা ছবি-মূর্তি তৈরি করে, কিয়ামতে তাদের বলা হবে—যা বানিয়েছ তাতে প্রাণ দাও।"},"heading":{"title":"ছবি-মূর্তি তৈরি সম্পর্কে হাদিস: যা বানানো হয় তাতে প্রাণ দিতে বলা হবে","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যারা এসব ছবি-মূর্তি তৈরি করে, কিয়ামতের দিন তাদের শাস্তি দেওয়া হবে। তাদের বলা হবে, তোমরা যা বানিয়েছ তাতে প্রাণ দাও। এই কথাটি মানুষের সীমাবদ্ধতা মনে করিয়ে দেয়। মানুষ আঁকতে বা বানাতে পারে, কিন্তু প্রাণ দিতে পারে না। তাই প্রাণীর ছবি-মূর্তি বানানোকে হাদিসে কঠিনভাবে সতর্ক করা হয়েছে। এখানে মূল শিক্ষা হলো সৃষ্টির মালিক আল্লাহ, আর মানুষ যেন এমন কাজকে খেলা বা গর্বের বিষয় না বানায় যা আল্লাহর অসন্তুষ্টির কারণ হতে পারে। মুসলিম জীবনে সাজসজ্জা, শিল্পকর্ম ও ঘরের জিনিস বেছে নেওয়ার সময় এই হাদিসের শিক্ষা মনে রাখা দরকার।"},"teachings":["সৃষ্টির ক্ষমতা একমাত্র আল্লাহর; মানুষ প্রাণ দিতে পারে না।","ছবি-মূর্তি তৈরি সম্পর্কে কিয়ামতের জবাবদিহি আছে।","শিল্প বা সাজসজ্জা বাছাইয়ে দীনী সতর্কতা দরকার।","আল্লাহর অসন্তুষ্টির আশঙ্কা আছে এমন কাজ থেকে দূরে থাকা উচিত।"],"related_hadiths":[{"id":"5950","book_id":"1","label":"Sahih Bukhari"},{"id":"5954","book_id":"1","label":"Sahih Bukhari"},{"id":"5961","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবি-মূর্তি নির্মাতাদের জবাবদিহি","description":"$book_name$ $hadith_number$ - $chapter_name$. যারা ছবি-মূর্তি তৈরি করে, কিয়ামতে তাদের বলা হবে—যা বানিয়েছ তাতে প্রাণ দাও।"},"heading":{"title":"ছবি-মূর্তি তৈরি সম্পর্কে হাদিস: যা বানানো হয় তাতে প্রাণ দিতে বলা হবে","description":"এই হাদিসে রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যারা এসব ছবি-মূর্তি তৈরি করে, কিয়ামতের দিন তাদের শাস্তি দেওয়া হবে। তাদের বলা হবে, তোমরা যা বানিয়েছ তাতে প্রাণ দাও। এই কথাটি মানুষের সীমাবদ্ধতা মনে করিয়ে দেয়। মানুষ আঁকতে বা বানাতে পারে, কিন্তু প্রাণ দিতে পারে না। তাই প্রাণীর ছবি-মূর্তি বানানোকে হাদিসে কঠিনভাবে সতর্ক করা হয়েছে। এখানে মূল শিক্ষা হলো সৃষ্টির মালিক আল্লাহ, আর মানুষ যেন এমন কাজকে খেলা বা গর্বের বিষয় না বানায় যা আল্লাহর অসন্তুষ্টির কারণ হতে পারে। মুসলিম জীবনে সাজসজ্জা, শিল্পকর্ম ও ঘরের জিনিস বেছে নেওয়ার সময় এই হাদিসের শিক্ষা মনে রাখা দরকার।"},"teachings":["সৃষ্টির ক্ষমতা একমাত্র আল্লাহর; মানুষ প্রাণ দিতে পারে না।","ছবি-মূর্তি তৈরি সম্পর্কে কিয়ামতের জবাবদিহি আছে।","শিল্প বা সাজসজ্জা বাছাইয়ে দীনী সতর্কতা দরকার।","আল্লাহর অসন্তুষ্টির আশঙ্কা আছে এমন কাজ থেকে দূরে থাকা উচিত।"],"related_hadiths":[{"id":"5950","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5954","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5961","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E19" s="4" t="n"/>
@@ -906,7 +910,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | একটি ছবি তৈরিরও কঠিন জবাবদিহি","description":"$book_name$ $hadith_number$ - $chapter_name$. একটি ছবি-মূর্তি তৈরি করলেও কিয়ামতে শাস্তি ও প্রাণ দেওয়ার অক্ষমতার সতর্কতা এসেছে।"},"heading":{"title":"একটি ছবি-মূর্তি তৈরির শাস্তি: প্রাণ দিতে বলা হবে কিন্তু পারবে না","description":"এই হাদিসে বলা হয়েছে, যে ব্যক্তি একটি ছবি-মূর্তিও তৈরি করবে, তাকে শাস্তি দেওয়া হবে এবং তাতে প্রাণ দিতে বলা হবে; কিন্তু সে তা করতে পারবে না। হাদিসের ভাষা দেখায়, বিষয়টি সংখ্যার কারণে ছোট হয়ে যায় না। একটি ছবিও যদি নিষিদ্ধ ছবির মধ্যে পড়ে, তবে তা নিয়ে সতর্কতা আছে। এখানে মূল শিক্ষা হলো, মানুষ যেন সৃষ্টির কাজকে নিজের ক্ষমতার বিষয় মনে না করে। ছবি-মূর্তি তৈরি, ঘরে রাখা বা সাজসজ্জায় ব্যবহার করার আগে একজন মুসলিমকে ভাবতে হবে—এটি কি হাদিসের সতর্কতার মধ্যে পড়ে কি না। এই হাদিস অপ্রয়োজনীয় প্রাণীর ছবি ও মূর্তি থেকে দূরে থাকার শক্ত শিক্ষা দেয়।"},"teachings":["একটি ছবিও হাদিসের সতর্কতার বিষয় হতে পারে।","মানুষ ছবি বানাতে পারে, কিন্তু প্রাণ দিতে পারে না।","অপ্রয়োজনীয় প্রাণীর ছবি-মূর্তি থেকে দূরে থাকা উচিত।","ছোট মনে হওয়া কাজও কিয়ামতে জবাবদিহির কারণ হতে পারে।"],"related_hadiths":[{"id":"5950","book_id":"1","label":"Sahih Bukhari"},{"id":"5951","book_id":"1","label":"Sahih Bukhari"},{"id":"5961","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | একটি ছবি তৈরিরও কঠিন জবাবদিহি","description":"$book_name$ $hadith_number$ - $chapter_name$. একটি ছবি-মূর্তি তৈরি করলেও কিয়ামতে শাস্তি ও প্রাণ দেওয়ার অক্ষমতার সতর্কতা এসেছে।"},"heading":{"title":"একটি ছবি-মূর্তি তৈরির শাস্তি: প্রাণ দিতে বলা হবে কিন্তু পারবে না","description":"এই হাদিসে বলা হয়েছে, যে ব্যক্তি একটি ছবি-মূর্তিও তৈরি করবে, তাকে শাস্তি দেওয়া হবে এবং তাতে প্রাণ দিতে বলা হবে; কিন্তু সে তা করতে পারবে না। হাদিসের ভাষা দেখায়, বিষয়টি সংখ্যার কারণে ছোট হয়ে যায় না। একটি ছবিও যদি নিষিদ্ধ ছবির মধ্যে পড়ে, তবে তা নিয়ে সতর্কতা আছে। এখানে মূল শিক্ষা হলো, মানুষ যেন সৃষ্টির কাজকে নিজের ক্ষমতার বিষয় মনে না করে। ছবি-মূর্তি তৈরি, ঘরে রাখা বা সাজসজ্জায় ব্যবহার করার আগে একজন মুসলিমকে ভাবতে হবে—এটি কি হাদিসের সতর্কতার মধ্যে পড়ে কি না। এই হাদিস অপ্রয়োজনীয় প্রাণীর ছবি ও মূর্তি থেকে দূরে থাকার শক্ত শিক্ষা দেয়।"},"teachings":["একটি ছবিও হাদিসের সতর্কতার বিষয় হতে পারে।","মানুষ ছবি বানাতে পারে, কিন্তু প্রাণ দিতে পারে না।","অপ্রয়োজনীয় প্রাণীর ছবি-মূর্তি থেকে দূরে থাকা উচিত।","ছোট মনে হওয়া কাজও কিয়ামতে জবাবদিহির কারণ হতে পারে।"],"related_hadiths":[{"id":"5950","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5951","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5961","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E20" s="4" t="n"/>
@@ -929,7 +933,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে ছবিযুক্ত বস্তু রাখার বিধান","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি ঘরে ছবিযুক্ত কিছু দেখলে তা ভেঙে বা সরিয়ে দিতেন—এতে ঘর পবিত্র রাখার শিক্ষা আছে।"},"heading":{"title":"ঘরে ছবিযুক্ত বস্তু সম্পর্কে হাদিস: নবীজির আমলের শিক্ষা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা থেকে এসেছে, রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তাঁর ঘরে ছবিযুক্ত কোনো কিছু দেখলে তা ছিঁড়ে বা ভেঙে ফেলতেন। এটি শুধু কথা নয়, নবীজির বাস্তব আমল। এর মাধ্যমে বোঝা যায়, ঘরের ভেতর ছবিযুক্ত বস্তু রাখা নিয়ে তিনি খুব সতর্ক ছিলেন। ঘর একজন মুসলিমের শান্তি, ইবাদত ও পরিবারের জায়গা। তাই সেখানে এমন জিনিস রাখা ঠিক নয়, যা দীনী পরিবেশকে নষ্ট করে বা হাদিসের সতর্কতার মধ্যে পড়ে। এই হাদিস আমাদের শেখায়, ঘরের সাজসজ্জা শুধু সৌন্দর্যের জন্য নয়; তা ঈমান, সালাত ও আল্লাহর স্মরণের অনুকূল হওয়া দরকার।"},"teachings":["নবীজি ছবিযুক্ত বস্তু ঘরে রেখে দিতেন না।","ঘরের পরিবেশকে দীনীভাবে পরিষ্কার রাখা দরকার।","সাজসজ্জার জিনিস বাছাইয়ে সতর্ক হতে হবে।","কথার সাথে আমলের মিল রাখা নবীজির শিক্ষা।"],"related_hadiths":[{"id":"5955","book_id":"1","label":"Sahih Bukhari"},{"id":"5959","book_id":"1","label":"Sahih Bukhari"},{"id":"5961","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে ছবিযুক্ত বস্তু রাখার বিধান","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি ঘরে ছবিযুক্ত কিছু দেখলে তা ভেঙে বা সরিয়ে দিতেন—এতে ঘর পবিত্র রাখার শিক্ষা আছে।"},"heading":{"title":"ঘরে ছবিযুক্ত বস্তু সম্পর্কে হাদিস: নবীজির আমলের শিক্ষা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা থেকে এসেছে, রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তাঁর ঘরে ছবিযুক্ত কোনো কিছু দেখলে তা ছিঁড়ে বা ভেঙে ফেলতেন। এটি শুধু কথা নয়, নবীজির বাস্তব আমল। এর মাধ্যমে বোঝা যায়, ঘরের ভেতর ছবিযুক্ত বস্তু রাখা নিয়ে তিনি খুব সতর্ক ছিলেন। ঘর একজন মুসলিমের শান্তি, ইবাদত ও পরিবারের জায়গা। তাই সেখানে এমন জিনিস রাখা ঠিক নয়, যা দীনী পরিবেশকে নষ্ট করে বা হাদিসের সতর্কতার মধ্যে পড়ে। এই হাদিস আমাদের শেখায়, ঘরের সাজসজ্জা শুধু সৌন্দর্যের জন্য নয়; তা ঈমান, সালাত ও আল্লাহর স্মরণের অনুকূল হওয়া দরকার।"},"teachings":["নবীজি ছবিযুক্ত বস্তু ঘরে রেখে দিতেন না।","ঘরের পরিবেশকে দীনীভাবে পরিষ্কার রাখা দরকার।","সাজসজ্জার জিনিস বাছাইয়ে সতর্ক হতে হবে।","কথার সাথে আমলের মিল রাখা নবীজির শিক্ষা।"],"related_hadiths":[{"id":"5955","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5959","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5961","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E21" s="4" t="n"/>
@@ -952,7 +956,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত পর্দা ও কঠিন সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত পর্দা ছিঁড়ে ফেলা এবং ছবি-মূর্তি অঙ্কনকারীদের শাস্তির কথা এই হাদিসে এসেছে।"},"heading":{"title":"ছবিযুক্ত পর্দা সম্পর্কে হাদিস: ঘরের সাজসজ্জায় দীনী সতর্কতা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা বলেন, রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম সফর থেকে এসে ছবিযুক্ত পর্দা দেখেন। তিনি তা ছিঁড়ে টুকরা করে দেন এবং বলেন, যারা ছবি-মূর্তি অঙ্কন করে, কিয়ামতের দিন তাদের কঠিন শাস্তি হবে। হাদিসটি দেখায়, ছবিযুক্ত পর্দা বা ঘরের সাজসজ্জা শুধু সাধারণ বস্তু নয়; তা ইবাদত, ঘরের পরিবেশ ও দীনী সতর্কতার সাথে জড়িত হতে পারে। এখানে ছবি-মূর্তি অঙ্কনের শাস্তির কথাও যুক্ত হয়েছে। তাই মুসলিম পরিবারে দেয়াল, পর্দা, কাপড় বা সাজসজ্জায় প্রাণীর ছবি ব্যবহারে সতর্ক থাকা উচিত। এই হাদিস আমাদের শেখায়, ঘরের সৌন্দর্যের চেয়ে আল্লাহর সন্তুষ্টি বেশি গুরুত্বপূর্ণ।"},"teachings":["ছবিযুক্ত পর্দা ঘরে রাখার বিষয়ে হাদিসে সতর্কতা আছে।","নবীজি অপছন্দনীয় বস্তু সরিয়ে দিতেন।","ছবি-মূর্তি অঙ্কনকারীদের জন্য কিয়ামতের শাস্তির সতর্কতা এসেছে।","ঘরের সাজসজ্জায় আল্লাহর সন্তুষ্টিকে অগ্রাধিকার দিতে হবে।"],"related_hadiths":[{"id":"5952","book_id":"1","label":"Sahih Bukhari"},{"id":"5955","book_id":"1","label":"Sahih Bukhari"},{"id":"5959","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত পর্দা ও কঠিন সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত পর্দা ছিঁড়ে ফেলা এবং ছবি-মূর্তি অঙ্কনকারীদের শাস্তির কথা এই হাদিসে এসেছে।"},"heading":{"title":"ছবিযুক্ত পর্দা সম্পর্কে হাদিস: ঘরের সাজসজ্জায় দীনী সতর্কতা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা বলেন, রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম সফর থেকে এসে ছবিযুক্ত পর্দা দেখেন। তিনি তা ছিঁড়ে টুকরা করে দেন এবং বলেন, যারা ছবি-মূর্তি অঙ্কন করে, কিয়ামতের দিন তাদের কঠিন শাস্তি হবে। হাদিসটি দেখায়, ছবিযুক্ত পর্দা বা ঘরের সাজসজ্জা শুধু সাধারণ বস্তু নয়; তা ইবাদত, ঘরের পরিবেশ ও দীনী সতর্কতার সাথে জড়িত হতে পারে। এখানে ছবি-মূর্তি অঙ্কনের শাস্তির কথাও যুক্ত হয়েছে। তাই মুসলিম পরিবারে দেয়াল, পর্দা, কাপড় বা সাজসজ্জায় প্রাণীর ছবি ব্যবহারে সতর্ক থাকা উচিত। এই হাদিস আমাদের শেখায়, ঘরের সৌন্দর্যের চেয়ে আল্লাহর সন্তুষ্টি বেশি গুরুত্বপূর্ণ।"},"teachings":["ছবিযুক্ত পর্দা ঘরে রাখার বিষয়ে হাদিসে সতর্কতা আছে।","নবীজি অপছন্দনীয় বস্তু সরিয়ে দিতেন।","ছবি-মূর্তি অঙ্কনকারীদের জন্য কিয়ামতের শাস্তির সতর্কতা এসেছে।","ঘরের সাজসজ্জায় আল্লাহর সন্তুষ্টিকে অগ্রাধিকার দিতে হবে।"],"related_hadiths":[{"id":"5952","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5955","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5959","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E22" s="4" t="n"/>
@@ -975,7 +979,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত পর্দা সরানোর নির্দেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. সফর থেকে ফিরে নবীজি ছবিযুক্ত পর্দা সরাতে বললেন; ঘরকে ছবি থেকে পরিষ্কার রাখার শিক্ষা আছে।"},"heading":{"title":"ছবিযুক্ত পর্দা সরানো সম্পর্কে হাদিস: ঘরকে দীনীভাবে সাজানোর শিক্ষা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা বলেন, রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম এক সফর থেকে ফিরে দেখলেন, তিনি ছবিযুক্ত একটি পর্দা ঝুলিয়েছেন। তখন নবীজি তাকে সেটি সরিয়ে ফেলতে বললেন, আর তিনি তা সরিয়ে দিলেন। এই হাদিসের শিক্ষা খুব সরল: ঘরের ভেতরে ছবিযুক্ত পর্দা বা এমন সাজসজ্জা রাখা থেকে সতর্ক থাকতে হবে। নবীজি বিষয়টি দেখেই নির্দেশ দিয়েছেন, আর আয়েশা রাদিয়াল্লাহু আনহা তা মেনে নিয়েছেন। এতে আনুগত্যের সুন্দর শিক্ষা আছে। মুসলিম ঘর শুধু থাকার জায়গা নয়; সেখানে সালাত, দোয়া ও আল্লাহর স্মরণ হয়। তাই ঘরের জিনিস বাছাইয়ে দীনী সচেতনতা থাকা দরকার।"},"teachings":["নবীজির নির্দেশ শুনে দ্রুত মানা সাহাবাদের সুন্দর গুণ।","ছবিযুক্ত পর্দা সরানোর শিক্ষা এই হাদিসে এসেছে।","ঘরের সাজসজ্জায় দীনী সতর্কতা রাখা উচিত।","মুসলিম ঘরকে ইবাদতের উপযোগী রাখা দরকার।"],"related_hadiths":[{"id":"5952","book_id":"1","label":"Sahih Bukhari"},{"id":"5954","book_id":"1","label":"Sahih Bukhari"},{"id":"5959","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত পর্দা সরানোর নির্দেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. সফর থেকে ফিরে নবীজি ছবিযুক্ত পর্দা সরাতে বললেন; ঘরকে ছবি থেকে পরিষ্কার রাখার শিক্ষা আছে।"},"heading":{"title":"ছবিযুক্ত পর্দা সরানো সম্পর্কে হাদিস: ঘরকে দীনীভাবে সাজানোর শিক্ষা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা বলেন, রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম এক সফর থেকে ফিরে দেখলেন, তিনি ছবিযুক্ত একটি পর্দা ঝুলিয়েছেন। তখন নবীজি তাকে সেটি সরিয়ে ফেলতে বললেন, আর তিনি তা সরিয়ে দিলেন। এই হাদিসের শিক্ষা খুব সরল: ঘরের ভেতরে ছবিযুক্ত পর্দা বা এমন সাজসজ্জা রাখা থেকে সতর্ক থাকতে হবে। নবীজি বিষয়টি দেখেই নির্দেশ দিয়েছেন, আর আয়েশা রাদিয়াল্লাহু আনহা তা মেনে নিয়েছেন। এতে আনুগত্যের সুন্দর শিক্ষা আছে। মুসলিম ঘর শুধু থাকার জায়গা নয়; সেখানে সালাত, দোয়া ও আল্লাহর স্মরণ হয়। তাই ঘরের জিনিস বাছাইয়ে দীনী সচেতনতা থাকা দরকার।"},"teachings":["নবীজির নির্দেশ শুনে দ্রুত মানা সাহাবাদের সুন্দর গুণ।","ছবিযুক্ত পর্দা সরানোর শিক্ষা এই হাদিসে এসেছে।","ঘরের সাজসজ্জায় দীনী সতর্কতা রাখা উচিত।","মুসলিম ঘরকে ইবাদতের উপযোগী রাখা দরকার।"],"related_hadiths":[{"id":"5952","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5954","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5959","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E23" s="4" t="n"/>
@@ -998,7 +1002,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সালাতে মনোযোগ নষ্ট করে ছবিযুক্ত চাদর","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত চাদর সালাতে সামনে আসায় নবীজি তা সরাতে বলেন; সালাতে মনোযোগ রক্ষার শিক্ষা আছে।"},"heading":{"title":"সালাতে ছবিযুক্ত চাদর সম্পর্কে হাদিস: মনোযোগ রক্ষার সহজ শিক্ষা","description":"এই হাদিসে আনাস ইবনে মালেক রাদিয়াল্লাহু আনহু বলেন, আয়েশা রাদিয়াল্লাহু আনহার একটি চাদর ছিল, যা দিয়ে ঘরের এক পাশে পর্দা করা হয়েছিল। রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বললেন, এটি আমার সামনে থেকে সরাও; এর ছবিগুলো আমার সালাতে সামনে আসে। এখানে ছবির বিষয়ে সতর্কতার সাথে সালাতের মনোযোগের কথাও এসেছে। সালাত হলো আল্লাহর সামনে দাঁড়ানো। সেখানে এমন কিছু সামনে রাখা উচিত নয়, যা চোখে পড়ে মনকে ব্যস্ত করে। এই হাদিস আমাদের ঘর ও সালাতের জায়গা সাজানোর সময় ভাবতে শেখায়। দেয়াল, পর্দা, কাপড় বা সামনে থাকা জিনিস যেন ইবাদতে বাধা না হয়।"},"teachings":["সালাতে মনোযোগ নষ্ট করে এমন জিনিস সামনে রাখা উচিত নয়।","ছবিযুক্ত কাপড় বা পর্দা ইবাদতে বাধা হতে পারে।","নবীজি সালাতের একাগ্রতাকে গুরুত্ব দিয়েছেন।","ঘরের সালাতের জায়গা সরল ও মনোযোগবান্ধব হওয়া ভালো।"],"related_hadiths":[{"id":"374","book_id":"1","label":"Sahih Bukhari"},{"id":"5955","book_id":"1","label":"Sahih Bukhari"},{"id":"5961","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সালাতে মনোযোগ নষ্ট করে ছবিযুক্ত চাদর","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত চাদর সালাতে সামনে আসায় নবীজি তা সরাতে বলেন; সালাতে মনোযোগ রক্ষার শিক্ষা আছে।"},"heading":{"title":"সালাতে ছবিযুক্ত চাদর সম্পর্কে হাদিস: মনোযোগ রক্ষার সহজ শিক্ষা","description":"এই হাদিসে আনাস ইবনে মালেক রাদিয়াল্লাহু আনহু বলেন, আয়েশা রাদিয়াল্লাহু আনহার একটি চাদর ছিল, যা দিয়ে ঘরের এক পাশে পর্দা করা হয়েছিল। রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বললেন, এটি আমার সামনে থেকে সরাও; এর ছবিগুলো আমার সালাতে সামনে আসে। এখানে ছবির বিষয়ে সতর্কতার সাথে সালাতের মনোযোগের কথাও এসেছে। সালাত হলো আল্লাহর সামনে দাঁড়ানো। সেখানে এমন কিছু সামনে রাখা উচিত নয়, যা চোখে পড়ে মনকে ব্যস্ত করে। এই হাদিস আমাদের ঘর ও সালাতের জায়গা সাজানোর সময় ভাবতে শেখায়। দেয়াল, পর্দা, কাপড় বা সামনে থাকা জিনিস যেন ইবাদতে বাধা না হয়।"},"teachings":["সালাতে মনোযোগ নষ্ট করে এমন জিনিস সামনে রাখা উচিত নয়।","ছবিযুক্ত কাপড় বা পর্দা ইবাদতে বাধা হতে পারে।","নবীজি সালাতের একাগ্রতাকে গুরুত্ব দিয়েছেন।","ঘরের সালাতের জায়গা সরল ও মনোযোগবান্ধব হওয়া ভালো।"],"related_hadiths":[{"id":"374","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5955","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5961","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E24" s="4" t="n"/>
@@ -1021,7 +1025,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতের আলামত ও বস্তু কথা বলা","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতের আগে হিংস্র পশু, চাবুক, জুতার ফিতা ও উরুর কথা বলার আলামত হাদিসে এসেছে।"},"heading":{"title":"কিয়ামতের আলামত: পশু ও জিনিসপত্র কথা বলার হাদিস","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) শপথ করে বলেছেন, কিয়ামত কায়েম হবে না যতক্ষণ না কিছু বিস্ময়কর আলামত দেখা যায়। হিংস্র পশু মানুষের সঙ্গে কথা বলবে, মানুষের চাবুকের মাথা তার সঙ্গে কথা বলবে, জুতার ফিতা কথা বলবে এবং তার উরু তাকে জানাবে, তার অনুপস্থিতিতে তার স্ত্রী কী করেছে। হাদিসের ভাষা যেমন আছে, তেমনভাবেই গ্রহণ করা উচিত। এখানে কিয়ামতের আলামত, আল্লাহর ক্ষমতা এবং মানুষের অজানা বিষয় প্রকাশের কথা এসেছে। ব্যাখ্যায় নিজের থেকে সময়, পদ্ধতি বা আধুনিক কোনো জিনিসের সঙ্গে নিশ্চিত মিলিয়ে দেওয়া ঠিক নয়। মূল শিক্ষা হলো, কিয়ামত সত্য এবং আল্লাহ যেভাবে চান সেভাবে অদ্ভুত ঘটনাও ঘটতে পারে।"},"teachings":["কিয়ামতের আগে কিছু আশ্চর্য আলামত ঘটবে।","আল্লাহ চাইলে পশু ও জিনিসপত্রকেও কথা বলাতে পারেন।","হাদিসের আলামত নিজের ধারণা দিয়ে নির্দিষ্ট করা ঠিক নয়।","কিয়ামতের বিশ্বাস মানুষকে সতর্ক জীবন শেখায়।"],"related_hadiths":[{"id":"2181","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"5225","book_id":"14","label":"Mishkat al-Masabih"},{"id":"2969","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতের আলামত ও বস্তু কথা বলা","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতের আগে হিংস্র পশু, চাবুক, জুতার ফিতা ও উরুর কথা বলার আলামত হাদিসে এসেছে।"},"heading":{"title":"কিয়ামতের আলামত: পশু ও জিনিসপত্র কথা বলার হাদিস","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) শপথ করে বলেছেন, কিয়ামত কায়েম হবে না যতক্ষণ না কিছু বিস্ময়কর আলামত দেখা যায়। হিংস্র পশু মানুষের সঙ্গে কথা বলবে, মানুষের চাবুকের মাথা তার সঙ্গে কথা বলবে, জুতার ফিতা কথা বলবে এবং তার উরু তাকে জানাবে, তার অনুপস্থিতিতে তার স্ত্রী কী করেছে। হাদিসের ভাষা যেমন আছে, তেমনভাবেই গ্রহণ করা উচিত। এখানে কিয়ামতের আলামত, আল্লাহর ক্ষমতা এবং মানুষের অজানা বিষয় প্রকাশের কথা এসেছে। ব্যাখ্যায় নিজের থেকে সময়, পদ্ধতি বা আধুনিক কোনো জিনিসের সঙ্গে নিশ্চিত মিলিয়ে দেওয়া ঠিক নয়। মূল শিক্ষা হলো, কিয়ামত সত্য এবং আল্লাহ যেভাবে চান সেভাবে অদ্ভুত ঘটনাও ঘটতে পারে।"},"teachings":["কিয়ামতের আগে কিছু আশ্চর্য আলামত ঘটবে।","আল্লাহ চাইলে পশু ও জিনিসপত্রকেও কথা বলাতে পারেন।","হাদিসের আলামত নিজের ধারণা দিয়ে নির্দিষ্ট করা ঠিক নয়।","কিয়ামতের বিশ্বাস মানুষকে সতর্ক জীবন শেখায়।"],"related_hadiths":[{"id":"2181","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"5225","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"2969","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E25" s="4" t="n"/>
@@ -1044,7 +1048,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত বালিশ ও ফেরেশতার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত বালিশ দেখে নবীজি ঘরে প্রবেশ করলেন না; ছবি নির্মাতা ও ঘরে ছবির বিষয়ে সতর্কতা দিলেন।"},"heading":{"title":"ছবিযুক্ত বালিশ সম্পর্কে হাদিস: ঘরে ছবি থাকলে ফেরেশতা প্রবেশ না করার সতর্কতা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা একটি ছোট বালিশ কিনেছিলেন, তাতে ছবি ছিল। রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তা দেখে ঘরে প্রবেশ না করে দরজায় দাঁড়িয়ে থাকেন। আয়েশা রাদিয়াল্লাহু আনহা তাঁর মুখে অপছন্দের চিহ্ন দেখে তওবা করেন এবং নিজের ভুল জানতে চান। নবীজি বলেন, যারা এসব ছবি তৈরি করে, কিয়ামতের দিন তাদের শাস্তি দেওয়া হবে এবং বলা হবে, যাদের তৈরি করেছ তাদের জীবিত কর। এরপর তিনি বলেন, যে ঘরে ছবি থাকে, সে ঘরে ফেরেশতা প্রবেশ করে না। হাদিসটি ঘরের ছবি, ছবি নির্মাতা এবং দীনী পরিবেশ—তিনটি বিষয় একসাথে শেখায়। মুসলিম পরিবারের জন্য এটি ঘরকে অপ্রয়োজনীয় ছবি থেকে পরিষ্কার রাখার শক্ত শিক্ষা।"},"teachings":["ছবিযুক্ত বালিশ দেখেও নবীজি অপছন্দ প্রকাশ করেছেন।","ছবি নির্মাতাদের জন্য কিয়ামতের জবাবদিহির কথা এসেছে।","যে ঘরে ছবি থাকে, সেখানে ফেরেশতা প্রবেশ না করার সতর্কতা আছে।","ভুল বুঝতে পারলে দ্রুত তওবা করা মুমিনের গুণ।"],"related_hadiths":[{"id":"5949","book_id":"1","label":"Sahih Bukhari"},{"id":"5950","book_id":"1","label":"Sahih Bukhari"},{"id":"5959","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত বালিশ ও ফেরেশতার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত বালিশ দেখে নবীজি ঘরে প্রবেশ করলেন না; ছবি নির্মাতা ও ঘরে ছবির বিষয়ে সতর্কতা দিলেন।"},"heading":{"title":"ছবিযুক্ত বালিশ সম্পর্কে হাদিস: ঘরে ছবি থাকলে ফেরেশতা প্রবেশ না করার সতর্কতা","description":"এই হাদিসে আয়েশা রাদিয়াল্লাহু আনহা একটি ছোট বালিশ কিনেছিলেন, তাতে ছবি ছিল। রাসূল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তা দেখে ঘরে প্রবেশ না করে দরজায় দাঁড়িয়ে থাকেন। আয়েশা রাদিয়াল্লাহু আনহা তাঁর মুখে অপছন্দের চিহ্ন দেখে তওবা করেন এবং নিজের ভুল জানতে চান। নবীজি বলেন, যারা এসব ছবি তৈরি করে, কিয়ামতের দিন তাদের শাস্তি দেওয়া হবে এবং বলা হবে, যাদের তৈরি করেছ তাদের জীবিত কর। এরপর তিনি বলেন, যে ঘরে ছবি থাকে, সে ঘরে ফেরেশতা প্রবেশ করে না। হাদিসটি ঘরের ছবি, ছবি নির্মাতা এবং দীনী পরিবেশ—তিনটি বিষয় একসাথে শেখায়। মুসলিম পরিবারের জন্য এটি ঘরকে অপ্রয়োজনীয় ছবি থেকে পরিষ্কার রাখার শক্ত শিক্ষা।"},"teachings":["ছবিযুক্ত বালিশ দেখেও নবীজি অপছন্দ প্রকাশ করেছেন।","ছবি নির্মাতাদের জন্য কিয়ামতের জবাবদিহির কথা এসেছে।","যে ঘরে ছবি থাকে, সেখানে ফেরেশতা প্রবেশ না করার সতর্কতা আছে।","ভুল বুঝতে পারলে দ্রুত তওবা করা মুমিনের গুণ।"],"related_hadiths":[{"id":"5949","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5950","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5959","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E26" s="4" t="n"/>
@@ -1067,7 +1071,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে ছবি টাঙ্গানোর সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত পর্দা, সৃষ্টির সাদৃশ্য বানানো ও ঘরে ফেরেশতা প্রবেশ না করার বিষয়ে স্পষ্ট সতর্কতা।"},"heading":{"title":"ঘরে ছবি টাঙ্গানো: সৃষ্টির সাদৃশ্য বানানো নিয়ে হাদিসের শিক্ষা","description":"এই হাদিসে মূল বিষয় হলো ঘরে ছবি টাঙ্গানো এবং প্রাণীর ছবি ব্যবহার। আয়েশা (রাঃ) ঘরের সামনে একটি পাতলা ছবিযুক্ত কাপড় ঝুলিয়েছিলেন। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তা দেখে অসন্তুষ্ট হন, কাপড়টি ছিঁড়ে ফেলেন এবং বলেন, যারা আল্লাহর সৃষ্টির সাদৃশ্য তৈরি করে, কিয়ামতের দিন তাদের কঠিন শাস্তির কথা বলা হয়েছে। হাদিসে আরও এসেছে, ছবির মালিকদের বলা হবে, যা তৈরি করেছ তা জীবিত কর। এখানে ঘরে ছবি থাকলে ফেরেশতা প্রবেশ না করার কথাও এসেছে। তবে আয়েশা (রাঃ) কাপড়টি কেটে বালিশ বানিয়েছিলেন, আর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে সেটিতে হেলান দিতে দেখা গেছে। তাই ছবিওয়ালা পর্দা টাঙ্গানো ও সম্মানের স্থানে রাখা থেকে সতর্ক থাকা এই হাদিসের মূল শিক্ষা।"},"teachings":["ঘরে প্রাণীর ছবি টাঙ্গানো থেকে সতর্ক থাকা উচিত।","আল্লাহর সৃষ্টির সাদৃশ্য বানানো গুরুতর সতর্কতার বিষয়।","ছবিযুক্ত জিনিস সম্মানের জায়গায় না রেখে ব্যবহার বদলানো হাদিসে এসেছে।","ঘরের পরিবেশ এমন রাখা দরকার, যাতে রহমতের ফেরেশতা আসার বাধা না থাকে।"],"related_hadiths":[{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"5958","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে ছবি টাঙ্গানোর সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ছবিযুক্ত পর্দা, সৃষ্টির সাদৃশ্য বানানো ও ঘরে ফেরেশতা প্রবেশ না করার বিষয়ে স্পষ্ট সতর্কতা।"},"heading":{"title":"ঘরে ছবি টাঙ্গানো: সৃষ্টির সাদৃশ্য বানানো নিয়ে হাদিসের শিক্ষা","description":"এই হাদিসে মূল বিষয় হলো ঘরে ছবি টাঙ্গানো এবং প্রাণীর ছবি ব্যবহার। আয়েশা (রাঃ) ঘরের সামনে একটি পাতলা ছবিযুক্ত কাপড় ঝুলিয়েছিলেন। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তা দেখে অসন্তুষ্ট হন, কাপড়টি ছিঁড়ে ফেলেন এবং বলেন, যারা আল্লাহর সৃষ্টির সাদৃশ্য তৈরি করে, কিয়ামতের দিন তাদের কঠিন শাস্তির কথা বলা হয়েছে। হাদিসে আরও এসেছে, ছবির মালিকদের বলা হবে, যা তৈরি করেছ তা জীবিত কর। এখানে ঘরে ছবি থাকলে ফেরেশতা প্রবেশ না করার কথাও এসেছে। তবে আয়েশা (রাঃ) কাপড়টি কেটে বালিশ বানিয়েছিলেন, আর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে সেটিতে হেলান দিতে দেখা গেছে। তাই ছবিওয়ালা পর্দা টাঙ্গানো ও সম্মানের স্থানে রাখা থেকে সতর্ক থাকা এই হাদিসের মূল শিক্ষা।"},"teachings":["ঘরে প্রাণীর ছবি টাঙ্গানো থেকে সতর্ক থাকা উচিত।","আল্লাহর সৃষ্টির সাদৃশ্য বানানো গুরুতর সতর্কতার বিষয়।","ছবিযুক্ত জিনিস সম্মানের জায়গায় না রেখে ব্যবহার বদলানো হাদিসে এসেছে।","ঘরের পরিবেশ এমন রাখা দরকার, যাতে রহমতের ফেরেশতা আসার বাধা না থাকে।"],"related_hadiths":[{"id":"3225","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5958","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4002","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E27" s="4" t="n"/>
@@ -1090,7 +1094,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুকুর ও ছবি থাকা ঘরের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ঘরে কুকুর বা ছবি থাকলে ফেরেশতা প্রবেশ করেন না—এ শিক্ষা ঘরকে পবিত্র রাখার কথা স্মরণ করায়।"},"heading":{"title":"কুকুর বা ছবি থাকা ঘরে ফেরেশতা প্রবেশ না করার শিক্ষা","description":"এই হাদিসে ঘরের ভেতরে কুকুর ও ছবি থাকার বিষয়ে স্পষ্ট সতর্কতা এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) চিন্তিত ছিলেন, কারণ জিব্রীল (আঃ) সাক্ষাতের ওয়াদা করেও আসেননি। পরে জানা গেল, তাঁর খাটের নিচে একটি কুকুর ছানা ছিল। সেটি বের করা হলো এবং জায়গায় পানি ছিটানো হলো। পরে জিব্রীল (আঃ) এসে বললেন, আমরা এমন ঘরে প্রবেশ করি না, যেখানে কুকুর বা ছবি থাকে। এরপর কুকুর বিষয়ে নির্দেশের কথাও এসেছে, তবে ছোট বাগানের হেফাযতে রাখা কুকুর ছেড়ে দেওয়া হয়েছে বলে বর্ণনায় আছে। তাই এই হাদিসে ঘরের ভেতরের পরিবেশ, অপ্রয়োজনীয় কুকুর রাখা এবং ছবি রাখার বিষয়ে সতর্কতা প্রধান শিক্ষা। এতে অযথা কঠোরতা নয়, বরং হাদিসে যে সীমা এসেছে, সেটি বোঝা জরুরি।"},"teachings":["ঘরের ভেতরে অপ্রয়োজনীয় কুকুর রাখা থেকে সতর্ক থাকতে হবে।","ঘরে ছবি থাকলে ফেরেশতা প্রবেশ না করার কথা হাদিসে এসেছে।","সমস্যার কারণ জানা গেলে তা সরিয়ে ঘর পরিষ্কার রাখা উচিত।","হাদিসে বাগান হেফাযতের কুকুরের আলাদা উল্লেখ আছে—এক বিষয়কে অন্য বিষয়ের সঙ্গে মেলানো ঠিক নয়।"],"related_hadiths":[{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"},{"id":"5958","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুকুর ও ছবি থাকা ঘরের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ঘরে কুকুর বা ছবি থাকলে ফেরেশতা প্রবেশ করেন না—এ শিক্ষা ঘরকে পবিত্র রাখার কথা স্মরণ করায়।"},"heading":{"title":"কুকুর বা ছবি থাকা ঘরে ফেরেশতা প্রবেশ না করার শিক্ষা","description":"এই হাদিসে ঘরের ভেতরে কুকুর ও ছবি থাকার বিষয়ে স্পষ্ট সতর্কতা এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) চিন্তিত ছিলেন, কারণ জিব্রীল (আঃ) সাক্ষাতের ওয়াদা করেও আসেননি। পরে জানা গেল, তাঁর খাটের নিচে একটি কুকুর ছানা ছিল। সেটি বের করা হলো এবং জায়গায় পানি ছিটানো হলো। পরে জিব্রীল (আঃ) এসে বললেন, আমরা এমন ঘরে প্রবেশ করি না, যেখানে কুকুর বা ছবি থাকে। এরপর কুকুর বিষয়ে নির্দেশের কথাও এসেছে, তবে ছোট বাগানের হেফাযতে রাখা কুকুর ছেড়ে দেওয়া হয়েছে বলে বর্ণনায় আছে। তাই এই হাদিসে ঘরের ভেতরের পরিবেশ, অপ্রয়োজনীয় কুকুর রাখা এবং ছবি রাখার বিষয়ে সতর্কতা প্রধান শিক্ষা। এতে অযথা কঠোরতা নয়, বরং হাদিসে যে সীমা এসেছে, সেটি বোঝা জরুরি।"},"teachings":["ঘরের ভেতরে অপ্রয়োজনীয় কুকুর রাখা থেকে সতর্ক থাকতে হবে।","ঘরে ছবি থাকলে ফেরেশতা প্রবেশ না করার কথা হাদিসে এসেছে।","সমস্যার কারণ জানা গেলে তা সরিয়ে ঘর পরিষ্কার রাখা উচিত।","হাদিসে বাগান হেফাযতের কুকুরের আলাদা উল্লেখ আছে—এক বিষয়কে অন্য বিষয়ের সঙ্গে মেলানো ঠিক নয়।"],"related_hadiths":[{"id":"3225","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4002","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5958","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E28" s="4" t="n"/>
@@ -1113,7 +1117,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দেওয়ালে পর্দা লাগানো নিয়ে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. বিয়ের ঘর সাজাতে দেওয়াল ঢেকে পর্দা লাগানো দেখে আবু আইয়ুবের অপছন্দের শিক্ষা।"},"heading":{"title":"দেওয়ালে পর্দা লাগানো: বিয়ের ঘর সাজানোর সীমা নিয়ে শিক্ষা","description":"এই বর্ণনার মূল বিষয় হলো বিয়ের ঘর সাজাতে বাড়াবাড়ি এবং দেওয়ালে পর্দা লাগানো। বর্ণনাকারী বলেন, তাঁর বিয়ের সময় লোকজনকে দাওয়াত দেওয়া হয়েছিল। একজন ঘরটি সবুজ কাপড়, বিছানা ও বালিশ দিয়ে সাজান। আবু আইয়ুব (রাঃ) এসে দেখেন ঘরের দেওয়াল সবুজ কাপড় দিয়ে ঢাকা। তিনি প্রশ্ন করেন, তোমরা কি দেওয়ালে পর্দা লাগাও? এতে তাঁর অপছন্দ স্পষ্ট হয়। বর্ণনায় দেখা যায়, তিনি খাবার খেতে ও ঘরে প্রবেশ করতে অস্বীকার করে বেরিয়ে যান। এখানে ছবির প্রসঙ্গ নেই, বরং দেওয়াল ঢেকে সাজানোর বিষয় আছে। তাই ব্যাখ্যায় এই ঘটনার সীমার মধ্যেই থাকা দরকার। শিক্ষা হলো, বিয়ে বা ওয়ালীমার আয়োজনেও সরলতা রাখা, অপচয় ও বাড়তি সাজসজ্জা থেকে বেঁচে থাকা এবং সাহাবীদের সংবেদনশীলতা বোঝা।"},"teachings":["বিয়ের ঘর সাজাতে বাড়াবাড়ি করা থেকে সতর্ক থাকা উচিত।","দেওয়াল ঢেকে পর্দা লাগানো সাহাবীর কাছে অপছন্দনীয় ছিল।","দাওয়াতের আয়োজনেও সরলতা ও সংযম রাখা ভালো।","কোনো কাজ অপছন্দনীয় মনে হলে নম্রভাবে সতর্ক করা একটি শিক্ষা।"],"related_hadiths":[{"id":"5958","book_id":"1","label":"Sahih Bukhari"},{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দেওয়ালে পর্দা লাগানো নিয়ে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. বিয়ের ঘর সাজাতে দেওয়াল ঢেকে পর্দা লাগানো দেখে আবু আইয়ুবের অপছন্দের শিক্ষা।"},"heading":{"title":"দেওয়ালে পর্দা লাগানো: বিয়ের ঘর সাজানোর সীমা নিয়ে শিক্ষা","description":"এই বর্ণনার মূল বিষয় হলো বিয়ের ঘর সাজাতে বাড়াবাড়ি এবং দেওয়ালে পর্দা লাগানো। বর্ণনাকারী বলেন, তাঁর বিয়ের সময় লোকজনকে দাওয়াত দেওয়া হয়েছিল। একজন ঘরটি সবুজ কাপড়, বিছানা ও বালিশ দিয়ে সাজান। আবু আইয়ুব (রাঃ) এসে দেখেন ঘরের দেওয়াল সবুজ কাপড় দিয়ে ঢাকা। তিনি প্রশ্ন করেন, তোমরা কি দেওয়ালে পর্দা লাগাও? এতে তাঁর অপছন্দ স্পষ্ট হয়। বর্ণনায় দেখা যায়, তিনি খাবার খেতে ও ঘরে প্রবেশ করতে অস্বীকার করে বেরিয়ে যান। এখানে ছবির প্রসঙ্গ নেই, বরং দেওয়াল ঢেকে সাজানোর বিষয় আছে। তাই ব্যাখ্যায় এই ঘটনার সীমার মধ্যেই থাকা দরকার। শিক্ষা হলো, বিয়ে বা ওয়ালীমার আয়োজনেও সরলতা রাখা, অপচয় ও বাড়তি সাজসজ্জা থেকে বেঁচে থাকা এবং সাহাবীদের সংবেদনশীলতা বোঝা।"},"teachings":["বিয়ের ঘর সাজাতে বাড়াবাড়ি করা থেকে সতর্ক থাকা উচিত।","দেওয়াল ঢেকে পর্দা লাগানো সাহাবীর কাছে অপছন্দনীয় ছিল।","দাওয়াতের আয়োজনেও সরলতা ও সংযম রাখা ভালো।","কোনো কাজ অপছন্দনীয় মনে হলে নম্রভাবে সতর্ক করা একটি শিক্ষা।"],"related_hadiths":[{"id":"5958","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3225","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4002","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E29" s="4" t="n"/>
@@ -1136,7 +1140,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত স্থানে প্রবেশ নিয়ে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ওমর (রাঃ) গীর্জায় ছবি থাকার কারণে সেখানে প্রবেশ না করার কথা জানান।"},"heading":{"title":"ছবিযুক্ত স্থানে প্রবেশ: ওমর (রাঃ)-এর সতর্ক অবস্থান","description":"এই বর্ণনায় ছবিযুক্ত স্থানে প্রবেশের বিষয়ে ওমর (রাঃ)-এর অবস্থান এসেছে। সিরিয়ায় এক সম্মানিত খ্রিস্টান ব্যক্তি তাঁর জন্য খাবার তৈরি করেন এবং ওমর (রাঃ) ও তাঁর সাথীদের বাড়িতে এসে তাকে সম্মানিত করতে অনুরোধ করেন। ওমর (রাঃ) তাকে বলেন, তোমাদের গীর্জায় ছবি থাকার কারণে আমরা সেখানে প্রবেশ করি না। এখানে বর্ণনাটি গীর্জা, দাওয়াত এবং ছবি—এই তিনটি বিষয়ের সঙ্গে যুক্ত। হাদিসের আলোচনায় মূল কথা হলো, সম্মানিত দাওয়াত হলেও ছবিযুক্ত স্থানের বিষয়ে সতর্কতা রাখা। তবে এই বর্ণনা থেকে বাড়তি কোনো ঘটনা বা আলাদা বিধান বানিয়ে বলা ঠিক নয়। সহজ শিক্ষা হলো, যেখানে দ্বীনের দিক থেকে আপত্তির বিষয় থাকে, সেখানে সামাজিক সম্মান বা দাওয়াতের চাপেও একজন মুমিন সতর্ক থাকতে পারে।"},"teachings":["ছবিযুক্ত স্থানে প্রবেশের বিষয়ে সতর্কতা রাখা সাহাবীদের আমলে দেখা যায়।","সম্মানিত দাওয়াত হলেও দ্বীনের সীমা মনে রাখা দরকার।","ওমর (রাঃ) স্পষ্টভাবে কারণ জানিয়ে নিজের অবস্থান বলেছেন।","সামাজিক সম্পর্ক রাখতে গিয়ে শরিয়তের সতর্কতা ভুলে যাওয়া উচিত নয়।"],"related_hadiths":[{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"5958","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছবিযুক্ত স্থানে প্রবেশ নিয়ে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ওমর (রাঃ) গীর্জায় ছবি থাকার কারণে সেখানে প্রবেশ না করার কথা জানান।"},"heading":{"title":"ছবিযুক্ত স্থানে প্রবেশ: ওমর (রাঃ)-এর সতর্ক অবস্থান","description":"এই বর্ণনায় ছবিযুক্ত স্থানে প্রবেশের বিষয়ে ওমর (রাঃ)-এর অবস্থান এসেছে। সিরিয়ায় এক সম্মানিত খ্রিস্টান ব্যক্তি তাঁর জন্য খাবার তৈরি করেন এবং ওমর (রাঃ) ও তাঁর সাথীদের বাড়িতে এসে তাকে সম্মানিত করতে অনুরোধ করেন। ওমর (রাঃ) তাকে বলেন, তোমাদের গীর্জায় ছবি থাকার কারণে আমরা সেখানে প্রবেশ করি না। এখানে বর্ণনাটি গীর্জা, দাওয়াত এবং ছবি—এই তিনটি বিষয়ের সঙ্গে যুক্ত। হাদিসের আলোচনায় মূল কথা হলো, সম্মানিত দাওয়াত হলেও ছবিযুক্ত স্থানের বিষয়ে সতর্কতা রাখা। তবে এই বর্ণনা থেকে বাড়তি কোনো ঘটনা বা আলাদা বিধান বানিয়ে বলা ঠিক নয়। সহজ শিক্ষা হলো, যেখানে দ্বীনের দিক থেকে আপত্তির বিষয় থাকে, সেখানে সামাজিক সম্মান বা দাওয়াতের চাপেও একজন মুমিন সতর্ক থাকতে পারে।"},"teachings":["ছবিযুক্ত স্থানে প্রবেশের বিষয়ে সতর্কতা রাখা সাহাবীদের আমলে দেখা যায়।","সম্মানিত দাওয়াত হলেও দ্বীনের সীমা মনে রাখা দরকার।","ওমর (রাঃ) স্পষ্টভাবে কারণ জানিয়ে নিজের অবস্থান বলেছেন।","সামাজিক সম্পর্ক রাখতে গিয়ে শরিয়তের সতর্কতা ভুলে যাওয়া উচিত নয়।"],"related_hadiths":[{"id":"3225","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5958","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4002","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E30" s="4" t="n"/>
@@ -1159,7 +1163,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে ছবি থাকলে প্রবেশ না করা","description":"$book_name$ $hadith_number$ - $chapter_name$. ঘরে ছবি থাকায় প্রবেশে অস্বীকৃতি এবং ছবি ভেঙে ফেলার পর প্রবেশ করার শিক্ষা।"},"heading":{"title":"ঘরে ছবি থাকলে প্রবেশ না করা: সাহাবীর আমলের শিক্ষা","description":"এই বর্ণনার মূল শিক্ষা হলো ঘরে ছবি থাকার বিষয়ে সতর্কতা। এক ব্যক্তি খাবার তৈরি করে দাওয়াত দিলেন। দাওয়াত গ্রহণের আগে জিজ্ঞেস করা হলো, ঘরে কি ছবি আছে? যখন বলা হলো, হ্যাঁ, তখন তিনি ঘরে প্রবেশ করতে অস্বীকার করলেন। পরে ছবি ভেঙে ফেলা হলে তিনি প্রবেশ করলেন। এখানে বিষয়টি খুব সরাসরি: দাওয়াত, ঘরের ছবি এবং ছবির কারণে প্রবেশ না করা। তাই ব্যাখ্যায় এটিকে অন্য ঘটনার সঙ্গে মিশিয়ে ফেলা ঠিক নয়। এই বর্ণনা আমাদের মনে করায়, খাবার বা দাওয়াতের আকর্ষণ থাকলেও ঘরের পরিবেশ ও দ্বীনি সতর্কতা গুরুত্বপূর্ণ। ছবি সরানো হলে প্রবেশ করার বিষয়টি দেখায়, আপত্তির কারণ দূর হলে সম্পর্ক বা দাওয়াত গ্রহণে বাধা থাকে না।"},"teachings":["দাওয়াতের ঘরে ছবি থাকলে সতর্কতা রাখা উচিত।","আপত্তির কারণ দূর হলে দাওয়াত গ্রহণ করা যায়—বর্ণনায় এমন আমল এসেছে।","ছবি সম্পর্কে সাহাবীদের সংবেদনশীলতা ছিল।","দ্বীনি সতর্কতা সামাজিক সৌজন্যের সঙ্গে মিলিয়ে রাখা দরকার।"],"related_hadiths":[{"id":"3225","book_id":"1","label":"Sahih Bukhari"},{"id":"5958","book_id":"1","label":"Sahih Bukhari"},{"id":"4002","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘরে ছবি থাকলে প্রবেশ না করা","description":"$book_name$ $hadith_number$ - $chapter_name$. ঘরে ছবি থাকায় প্রবেশে অস্বীকৃতি এবং ছবি ভেঙে ফেলার পর প্রবেশ করার শিক্ষা।"},"heading":{"title":"ঘরে ছবি থাকলে প্রবেশ না করা: সাহাবীর আমলের শিক্ষা","description":"এই বর্ণনার মূল শিক্ষা হলো ঘরে ছবি থাকার বিষয়ে সতর্কতা। এক ব্যক্তি খাবার তৈরি করে দাওয়াত দিলেন। দাওয়াত গ্রহণের আগে জিজ্ঞেস করা হলো, ঘরে কি ছবি আছে? যখন বলা হলো, হ্যাঁ, তখন তিনি ঘরে প্রবেশ করতে অস্বীকার করলেন। পরে ছবি ভেঙে ফেলা হলে তিনি প্রবেশ করলেন। এখানে বিষয়টি খুব সরাসরি: দাওয়াত, ঘরের ছবি এবং ছবির কারণে প্রবেশ না করা। তাই ব্যাখ্যায় এটিকে অন্য ঘটনার সঙ্গে মিশিয়ে ফেলা ঠিক নয়। এই বর্ণনা আমাদের মনে করায়, খাবার বা দাওয়াতের আকর্ষণ থাকলেও ঘরের পরিবেশ ও দ্বীনি সতর্কতা গুরুত্বপূর্ণ। ছবি সরানো হলে প্রবেশ করার বিষয়টি দেখায়, আপত্তির কারণ দূর হলে সম্পর্ক বা দাওয়াত গ্রহণে বাধা থাকে না।"},"teachings":["দাওয়াতের ঘরে ছবি থাকলে সতর্কতা রাখা উচিত।","আপত্তির কারণ দূর হলে দাওয়াত গ্রহণ করা যায়—বর্ণনায় এমন আমল এসেছে।","ছবি সম্পর্কে সাহাবীদের সংবেদনশীলতা ছিল।","দ্বীনি সতর্কতা সামাজিক সৌজন্যের সঙ্গে মিলিয়ে রাখা দরকার।"],"related_hadiths":[{"id":"3225","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5958","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4002","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E31" s="4" t="n"/>
@@ -1182,7 +1186,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ওয়ালীমায় বাদ্যযন্ত্র থেকে বাঁচা","description":"$book_name$ $hadith_number$ - $chapter_name$. তবলা ও বাদ্যযন্ত্র থাকা ওয়ালীমাতে না যাওয়ার সংক্ষিপ্ত কিন্তু স্পষ্ট সতর্কতা।"},"heading":{"title":"ওয়ালীমায় বাদ্যযন্ত্র: দাওয়াত গ্রহণে সতর্কতার শিক্ষা","description":"এই বর্ণনার মূল বিষয় হলো ওয়ালীমা বা বিয়ের দাওয়াতে তবলা ও বাদ্যযন্ত্র থাকা। ইমাম আওযাঈ (রহ.) বলেন, আমরা এমন ওয়ালীমাতে যাই না, যেখানে তবলা ও বাদ্যযন্ত্র থাকে। বর্ণনাটি খুব সংক্ষিপ্ত, তাই এর ব্যাখ্যাও সীমিত রাখা দরকার। এখানে খাবার, বিয়ে বা দাওয়াতকে খারাপ বলা হয়নি; বরং নির্দিষ্টভাবে তবলা ও বাদ্যযন্ত্র থাকা ওয়ালীমার কথা বলা হয়েছে। তাই শিক্ষা হলো, আনন্দের আয়োজন হলেও এমন উপাদান থেকে দূরে থাকা, যা দ্বীনি দৃষ্টিতে আপত্তিকর হতে পারে। ওয়ালীমা ইসলামী জীবনের একটি সামাজিক আয়োজন, কিন্তু সেই আয়োজন যেন সীমার বাইরে না যায়। এই হাদিসভিত্তিক সার্চে মানুষ সাধারণত “ওয়ালিমায় গান বাজনা”, “বাদ্যযন্ত্র হাদিস” এবং “বিয়েতে তবলা” জাতীয় শব্দ খোঁজে।"},"teachings":["ওয়ালীমার দাওয়াতে বাদ্যযন্ত্র থাকলে সতর্ক থাকা দরকার।","বিয়ের আনন্দও শরিয়তের সীমার ভেতরে রাখা উচিত।","দাওয়াত গ্রহণের আগে পরিবেশ সম্পর্কে জানা উপকারী হতে পারে।","সংক্ষিপ্ত বর্ণনা থেকে অতিরিক্ত দাবি করা ঠিক নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"949","book_id":"1","label":"Sahih Bukhari"},{"id":"952","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ওয়ালীমায় বাদ্যযন্ত্র থেকে বাঁচা","description":"$book_name$ $hadith_number$ - $chapter_name$. তবলা ও বাদ্যযন্ত্র থাকা ওয়ালীমাতে না যাওয়ার সংক্ষিপ্ত কিন্তু স্পষ্ট সতর্কতা।"},"heading":{"title":"ওয়ালীমায় বাদ্যযন্ত্র: দাওয়াত গ্রহণে সতর্কতার শিক্ষা","description":"এই বর্ণনার মূল বিষয় হলো ওয়ালীমা বা বিয়ের দাওয়াতে তবলা ও বাদ্যযন্ত্র থাকা। ইমাম আওযাঈ (রহ.) বলেন, আমরা এমন ওয়ালীমাতে যাই না, যেখানে তবলা ও বাদ্যযন্ত্র থাকে। বর্ণনাটি খুব সংক্ষিপ্ত, তাই এর ব্যাখ্যাও সীমিত রাখা দরকার। এখানে খাবার, বিয়ে বা দাওয়াতকে খারাপ বলা হয়নি; বরং নির্দিষ্টভাবে তবলা ও বাদ্যযন্ত্র থাকা ওয়ালীমার কথা বলা হয়েছে। তাই শিক্ষা হলো, আনন্দের আয়োজন হলেও এমন উপাদান থেকে দূরে থাকা, যা দ্বীনি দৃষ্টিতে আপত্তিকর হতে পারে। ওয়ালীমা ইসলামী জীবনের একটি সামাজিক আয়োজন, কিন্তু সেই আয়োজন যেন সীমার বাইরে না যায়। এই হাদিসভিত্তিক সার্চে মানুষ সাধারণত “ওয়ালিমায় গান বাজনা”, “বাদ্যযন্ত্র হাদিস” এবং “বিয়েতে তবলা” জাতীয় শব্দ খোঁজে।"},"teachings":["ওয়ালীমার দাওয়াতে বাদ্যযন্ত্র থাকলে সতর্ক থাকা দরকার।","বিয়ের আনন্দও শরিয়তের সীমার ভেতরে রাখা উচিত।","দাওয়াত গ্রহণের আগে পরিবেশ সম্পর্কে জানা উপকারী হতে পারে।","সংক্ষিপ্ত বর্ণনা থেকে অতিরিক্ত দাবি করা ঠিক নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"949","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"952","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E32" s="4" t="n"/>
@@ -1205,7 +1209,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুদ নেওয়া-দেওয়ার ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সুদ গ্রহণকারী, প্রদানকারী, লেখক ও সাক্ষীদের একই সতর্কতার আওতায় আনার শিক্ষা।"},"heading":{"title":"সুদ নেওয়া ও দেওয়া: রিবা থেকে বাঁচার কঠোর সতর্কতা","description":"এই হাদিসের মূল বিষয় হলো সুদ বা রিবা। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সুদ গ্রহণকারী, সুদ প্রদানকারী, সুদের লেখক এবং সুদের দুই সাক্ষীর প্রতি অভিশাপ করেছেন। এরপর বলেছেন, অভিশাপে তারা সবাই সমান। এখানে শুধু সুদ খাওয়ার কথাই নেই; বরং যারা লেনদেনটি চালাতে সাহায্য করে, লেখে বা সাক্ষী থাকে, তাদের কথাও এসেছে। তাই ইসলামে সুদ থেকে বাঁচা মানে শুধু নিজের লাভের সুদ না নেওয়া নয়, বরং সুদের কাজে অংশ না নেওয়ার সতর্কতাও আছে। তবে হাদিসে যে চারটি ভূমিকা এসেছে, ব্যাখ্যায় সেটিতেই থাকা দরকার। বর্তমান জীবনে এই শিক্ষা আর্থিক লেনদেনের সময় সতর্কতা, হালাল উপার্জন এবং সন্দেহজনক চুক্তি এড়িয়ে চলার কথা মনে করায়।"},"teachings":["সুদ গ্রহণ ও প্রদান—দুটিই গুরুতর সতর্কতার বিষয়।","সুদের লেখক ও সাক্ষীর ভূমিকাও হাদিসে উল্লেখ হয়েছে।","আর্থিক চুক্তিতে হালাল-হারামের দিক দেখা জরুরি।","সুদের কাজে সহায়তা করা থেকেও সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"2085","book_id":"1","label":"Sahih Bukhari"},{"id":"2086","book_id":"1","label":"Sahih Bukhari"},{"id":"2087","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুদ নেওয়া-দেওয়ার ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সুদ গ্রহণকারী, প্রদানকারী, লেখক ও সাক্ষীদের একই সতর্কতার আওতায় আনার শিক্ষা।"},"heading":{"title":"সুদ নেওয়া ও দেওয়া: রিবা থেকে বাঁচার কঠোর সতর্কতা","description":"এই হাদিসের মূল বিষয় হলো সুদ বা রিবা। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সুদ গ্রহণকারী, সুদ প্রদানকারী, সুদের লেখক এবং সুদের দুই সাক্ষীর প্রতি অভিশাপ করেছেন। এরপর বলেছেন, অভিশাপে তারা সবাই সমান। এখানে শুধু সুদ খাওয়ার কথাই নেই; বরং যারা লেনদেনটি চালাতে সাহায্য করে, লেখে বা সাক্ষী থাকে, তাদের কথাও এসেছে। তাই ইসলামে সুদ থেকে বাঁচা মানে শুধু নিজের লাভের সুদ না নেওয়া নয়, বরং সুদের কাজে অংশ না নেওয়ার সতর্কতাও আছে। তবে হাদিসে যে চারটি ভূমিকা এসেছে, ব্যাখ্যায় সেটিতেই থাকা দরকার। বর্তমান জীবনে এই শিক্ষা আর্থিক লেনদেনের সময় সতর্কতা, হালাল উপার্জন এবং সন্দেহজনক চুক্তি এড়িয়ে চলার কথা মনে করায়।"},"teachings":["সুদ গ্রহণ ও প্রদান—দুটিই গুরুতর সতর্কতার বিষয়।","সুদের লেখক ও সাক্ষীর ভূমিকাও হাদিসে উল্লেখ হয়েছে।","আর্থিক চুক্তিতে হালাল-হারামের দিক দেখা জরুরি।","সুদের কাজে সহায়তা করা থেকেও সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"2085","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2086","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2087","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E33" s="4" t="n"/>
@@ -1228,7 +1232,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জেনে সুদ গ্রহণের ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. জেনে শুনে সামান্য সুদ গ্রহণকেও ভয়ংকর পাপ হিসেবে সতর্ক করা হয়েছে।"},"heading":{"title":"জেনে শুনে সুদ গ্রহণ: এক দিরহাম রিবার কঠিন সতর্কতা","description":"এই হাদিসে জেনে শুনে সুদ গ্রহণের ভয়াবহতা বলা হয়েছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কোনো ব্যক্তি জেনে শুনে এক দিরহাম বা একটি মুদ্রা সুদ গ্রহণ করলে তা ছত্রিশবার যেনা করার চেয়ে কঠিন হবে। এখানে মূল শব্দ হলো “জেনে শুনে”। অর্থাৎ মানুষ যখন বুঝে যে এটি সুদ, তবু গ্রহণ করে, তখন বিষয়টি খুব কঠিন সতর্কতার মধ্যে পড়ে। এই হাদিসের ব্যাখ্যায় অতিরিক্ত আর্থিক তত্ত্ব যোগ করার দরকার নেই; মূল শিক্ষা হলো, ছোট অঙ্কের সুদকেও হালকা মনে না করা। অনেক সময় মানুষ বলে “এ তো সামান্য”, কিন্তু হাদিসে সামান্য এক দিরহামের কথাই এসেছে। তাই রিবা, ব্যাংক সুদ বা ব্যক্তিগত ঋণের বাড়তি সুবিধা—যাই হোক, আগে যাচাই করা এবং আল্লাহকে ভয় করা জরুরি।"},"teachings":["জেনে শুনে সামান্য সুদ গ্রহণও হালকা বিষয় নয়।","হারাম লেনদেনে অঙ্ক ছোট হলেও সতর্কতা কমে না।","সুদকে সাধারণ লাভ মনে করে নেওয়া বিপজ্জনক হতে পারে।","লেনদেনের আগে তা সুদ কিনা বোঝার চেষ্টা করা দরকার।"],"related_hadiths":[{"id":"2085","book_id":"1","label":"Sahih Bukhari"},{"id":"2086","book_id":"1","label":"Sahih Bukhari"},{"id":"2087","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জেনে সুদ গ্রহণের ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. জেনে শুনে সামান্য সুদ গ্রহণকেও ভয়ংকর পাপ হিসেবে সতর্ক করা হয়েছে।"},"heading":{"title":"জেনে শুনে সুদ গ্রহণ: এক দিরহাম রিবার কঠিন সতর্কতা","description":"এই হাদিসে জেনে শুনে সুদ গ্রহণের ভয়াবহতা বলা হয়েছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কোনো ব্যক্তি জেনে শুনে এক দিরহাম বা একটি মুদ্রা সুদ গ্রহণ করলে তা ছত্রিশবার যেনা করার চেয়ে কঠিন হবে। এখানে মূল শব্দ হলো “জেনে শুনে”। অর্থাৎ মানুষ যখন বুঝে যে এটি সুদ, তবু গ্রহণ করে, তখন বিষয়টি খুব কঠিন সতর্কতার মধ্যে পড়ে। এই হাদিসের ব্যাখ্যায় অতিরিক্ত আর্থিক তত্ত্ব যোগ করার দরকার নেই; মূল শিক্ষা হলো, ছোট অঙ্কের সুদকেও হালকা মনে না করা। অনেক সময় মানুষ বলে “এ তো সামান্য”, কিন্তু হাদিসে সামান্য এক দিরহামের কথাই এসেছে। তাই রিবা, ব্যাংক সুদ বা ব্যক্তিগত ঋণের বাড়তি সুবিধা—যাই হোক, আগে যাচাই করা এবং আল্লাহকে ভয় করা জরুরি।"},"teachings":["জেনে শুনে সামান্য সুদ গ্রহণও হালকা বিষয় নয়।","হারাম লেনদেনে অঙ্ক ছোট হলেও সতর্কতা কমে না।","সুদকে সাধারণ লাভ মনে করে নেওয়া বিপজ্জনক হতে পারে।","লেনদেনের আগে তা সুদ কিনা বোঝার চেষ্টা করা দরকার।"],"related_hadiths":[{"id":"2085","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2086","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2087","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E34" s="4" t="n"/>
@@ -1251,7 +1255,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুখ বন্ধ ও শরীরের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে মুখ বন্ধ রাখা হবে এবং উরু ও কাঁধকে প্রথমে জিজ্ঞেস করা হবে—হাদিসটি জবাবদিহি শেখায়।"},"heading":{"title":"মুখ বন্ধ হলে উরু ও কাঁধের সাক্ষ্য: কিয়ামতের শিক্ষা","description":"এই হাদিসে নবী কারীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কিয়ামতের দিন মানুষকে এমন অবস্থায় ডাকা হবে, যখন তাদের মুখ বন্ধ থাকবে। তখন সর্বপ্রথম মানুষের উরু এবং কাঁধকে জিজ্ঞেস করা হবে। হাদিসের বক্তব্য সংক্ষিপ্ত, কিন্তু এর শিক্ষা স্পষ্ট। মানুষ দুনিয়ায় অনেক কিছু মুখে অস্বীকার করতে পারে, কিন্তু আখেরাতে আল্লাহর সামনে সত্য প্রকাশ পাবে। শরীরের অঙ্গ-প্রত্যঙ্গও সাক্ষ্য দিতে পারে—এটা কিয়ামতের জবাবদিহির বড় সতর্কতা। এই হাদিস আমাদের শেখায়, কাজ করার আগে ভাবতে হবে, একদিন সেই কাজের হিসাব দিতে হবে। মুখ বন্ধ থাকলেও আমল লুকিয়ে থাকবে না।"},"teachings":["কিয়ামতে মুখ বন্ধ থাকলেও সত্য প্রকাশ পাবে।","উরু ও কাঁধের সাক্ষ্যের কথা হাদিসে এসেছে।","মানুষের কাজ আল্লাহর কাছে লুকানো নয়।","দুনিয়ার আমল নিয়ে আখেরাতে জবাবদিহি আছে।"],"related_hadiths":[{"id":"2969","book_id":"2","label":"Sahih Muslim"},{"id":"5554","book_id":"14","label":"Mishkat al-Masabih"},{"id":"2181","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুখ বন্ধ ও শরীরের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে মুখ বন্ধ রাখা হবে এবং উরু ও কাঁধকে প্রথমে জিজ্ঞেস করা হবে—হাদিসটি জবাবদিহি শেখায়।"},"heading":{"title":"মুখ বন্ধ হলে উরু ও কাঁধের সাক্ষ্য: কিয়ামতের শিক্ষা","description":"এই হাদিসে নবী কারীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কিয়ামতের দিন মানুষকে এমন অবস্থায় ডাকা হবে, যখন তাদের মুখ বন্ধ থাকবে। তখন সর্বপ্রথম মানুষের উরু এবং কাঁধকে জিজ্ঞেস করা হবে। হাদিসের বক্তব্য সংক্ষিপ্ত, কিন্তু এর শিক্ষা স্পষ্ট। মানুষ দুনিয়ায় অনেক কিছু মুখে অস্বীকার করতে পারে, কিন্তু আখেরাতে আল্লাহর সামনে সত্য প্রকাশ পাবে। শরীরের অঙ্গ-প্রত্যঙ্গও সাক্ষ্য দিতে পারে—এটা কিয়ামতের জবাবদিহির বড় সতর্কতা। এই হাদিস আমাদের শেখায়, কাজ করার আগে ভাবতে হবে, একদিন সেই কাজের হিসাব দিতে হবে। মুখ বন্ধ থাকলেও আমল লুকিয়ে থাকবে না।"},"teachings":["কিয়ামতে মুখ বন্ধ থাকলেও সত্য প্রকাশ পাবে।","উরু ও কাঁধের সাক্ষ্যের কথা হাদিসে এসেছে।","মানুষের কাজ আল্লাহর কাছে লুকানো নয়।","দুনিয়ার আমল নিয়ে আখেরাতে জবাবদিহি আছে।"],"related_hadiths":[{"id":"2969","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"5554","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"2181","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E35" s="4" t="n"/>
@@ -1274,7 +1278,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুদের পাপের স্তর","description":"$book_name$ $hadith_number$ - $chapter_name$. সুদের পাপের বহু স্তর আছে—এই হাদিস রিবা থেকে দূরে থাকার শক্ত সতর্কতা দেয়।"},"heading":{"title":"সুদের পাপের স্তর: রিবা থেকে দূরে থাকার শিক্ষা","description":"এই হাদিসে সুদের পাপকে খুব কঠিন ভাষায় সতর্ক করা হয়েছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, সুদের পাপের ৭০টি স্তর রয়েছে; তার মধ্যে সবচেয়ে সাধারণ স্তরও নিজের মাতাকে বিবাহ করার মতো ভয়াবহ উদাহরণ দিয়ে বোঝানো হয়েছে। এই ভাষা আমাদের জানায়, রিবা শুধু অর্থনৈতিক ভুল নয়; এটি বড় নৈতিক ও দ্বীনি বিপদের বিষয়। তবে ব্যাখ্যায় হাদিসের শব্দের বাইরে গিয়ে নির্দিষ্ট লোকের ব্যাপারে রায় দেওয়া উচিত নয়। মূল শিক্ষা হলো, সুদকে ছোট, আধুনিক বা সাধারণ সুবিধা মনে না করা। মুসলিমের আয়, ঋণ, ব্যবসা ও চুক্তি যতটা সম্ভব পরিষ্কার ও হালাল পথে রাখা প্রয়োজন। এই হাদিস “সুদের পাপ”, “রিবার স্তর” এবং “সুদ হারাম” বিষয়ে মানুষের খোঁজার সঙ্গে সরাসরি যুক্ত।"},"teachings":["সুদকে সাধারণ আর্থিক লাভ মনে করা ঠিক নয়।","রিবার পাপের স্তর সম্পর্কে হাদিসে কঠিন সতর্কতা এসেছে।","লেনদেনে সন্দেহ হলে জ্ঞানীদের কাছে জেনে নেওয়া ভালো।","হালাল উপার্জন রক্ষায় সুদ থেকে দূরে থাকা জরুরি।"],"related_hadiths":[{"id":"2085","book_id":"1","label":"Sahih Bukhari"},{"id":"2086","book_id":"1","label":"Sahih Bukhari"},{"id":"2087","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুদের পাপের স্তর","description":"$book_name$ $hadith_number$ - $chapter_name$. সুদের পাপের বহু স্তর আছে—এই হাদিস রিবা থেকে দূরে থাকার শক্ত সতর্কতা দেয়।"},"heading":{"title":"সুদের পাপের স্তর: রিবা থেকে দূরে থাকার শিক্ষা","description":"এই হাদিসে সুদের পাপকে খুব কঠিন ভাষায় সতর্ক করা হয়েছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, সুদের পাপের ৭০টি স্তর রয়েছে; তার মধ্যে সবচেয়ে সাধারণ স্তরও নিজের মাতাকে বিবাহ করার মতো ভয়াবহ উদাহরণ দিয়ে বোঝানো হয়েছে। এই ভাষা আমাদের জানায়, রিবা শুধু অর্থনৈতিক ভুল নয়; এটি বড় নৈতিক ও দ্বীনি বিপদের বিষয়। তবে ব্যাখ্যায় হাদিসের শব্দের বাইরে গিয়ে নির্দিষ্ট লোকের ব্যাপারে রায় দেওয়া উচিত নয়। মূল শিক্ষা হলো, সুদকে ছোট, আধুনিক বা সাধারণ সুবিধা মনে না করা। মুসলিমের আয়, ঋণ, ব্যবসা ও চুক্তি যতটা সম্ভব পরিষ্কার ও হালাল পথে রাখা প্রয়োজন। এই হাদিস “সুদের পাপ”, “রিবার স্তর” এবং “সুদ হারাম” বিষয়ে মানুষের খোঁজার সঙ্গে সরাসরি যুক্ত।"},"teachings":["সুদকে সাধারণ আর্থিক লাভ মনে করা ঠিক নয়।","রিবার পাপের স্তর সম্পর্কে হাদিসে কঠিন সতর্কতা এসেছে।","লেনদেনে সন্দেহ হলে জ্ঞানীদের কাছে জেনে নেওয়া ভালো।","হালাল উপার্জন রক্ষায় সুদ থেকে দূরে থাকা জরুরি।"],"related_hadiths":[{"id":"2085","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2086","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2087","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E36" s="4" t="n"/>
@@ -1297,7 +1301,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুদের শেষ পরিণাম কমে যাওয়া","description":"$book_name$ $hadith_number$ - $chapter_name$. সুদ বাহ্যিকভাবে বাড়তি মনে হলেও এর পরিণাম সংকোচন—এ শিক্ষা রিবা থেকে সতর্ক করে।"},"heading":{"title":"সুদ বাড়তি মনে হলেও পরিণাম কমে যায়: রিবার শিক্ষা","description":"এই হাদিসে সুদের পরিণাম নিয়ে সংক্ষিপ্ত কিন্তু গভীর সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, সুদ এমন বস্তু যার পরিণাম সংকুচিত হওয়া, যদিও তা বৃদ্ধি মনে হয়। অর্থাৎ বাহ্যিকভাবে সুদে টাকা বাড়ছে বলে দেখা যেতে পারে, কিন্তু হাদিসে তার শেষ ফল কমে যাওয়া বলা হয়েছে। এখানে “তাৎক্ষণিক লাভ” আর “শেষ পরিণাম”—এই দুইটি দিক বোঝা জরুরি। অনেক মানুষ সুদকে সহজ আয় বা নিশ্চিন্ত লাভ মনে করে। কিন্তু হাদিস শেখায়, মুমিন শুধু চোখের সামনে থাকা বাড়তি অঙ্ক দেখে সিদ্ধান্ত নেয় না; বরং আল্লাহর নির্দেশ ও শেষ ফলের কথাও ভাবে। তাই আয়-রোজগার, ঋণ, বিনিয়োগ ও চুক্তিতে রিবার সন্দেহ থাকলে সতর্ক হওয়া দরকার।"},"teachings":["সুদ বাহ্যিকভাবে বাড়তি মনে হলেও হাদিসে তার পরিণাম ভালো বলা হয়নি।","তাৎক্ষণিক লাভ দেখে হারাম লেনদেনে জড়ানো উচিত নয়।","আর্থিক সিদ্ধান্তে আখিরাতের চিন্তা রাখা দরকার।","হালাল পথে কম আয়ও বরকতের কারণ হতে পারে—এমন আশা করা যায়।"],"related_hadiths":[{"id":"2085","book_id":"1","label":"Sahih Bukhari"},{"id":"2086","book_id":"1","label":"Sahih Bukhari"},{"id":"2087","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুদের শেষ পরিণাম কমে যাওয়া","description":"$book_name$ $hadith_number$ - $chapter_name$. সুদ বাহ্যিকভাবে বাড়তি মনে হলেও এর পরিণাম সংকোচন—এ শিক্ষা রিবা থেকে সতর্ক করে।"},"heading":{"title":"সুদ বাড়তি মনে হলেও পরিণাম কমে যায়: রিবার শিক্ষা","description":"এই হাদিসে সুদের পরিণাম নিয়ে সংক্ষিপ্ত কিন্তু গভীর সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, সুদ এমন বস্তু যার পরিণাম সংকুচিত হওয়া, যদিও তা বৃদ্ধি মনে হয়। অর্থাৎ বাহ্যিকভাবে সুদে টাকা বাড়ছে বলে দেখা যেতে পারে, কিন্তু হাদিসে তার শেষ ফল কমে যাওয়া বলা হয়েছে। এখানে “তাৎক্ষণিক লাভ” আর “শেষ পরিণাম”—এই দুইটি দিক বোঝা জরুরি। অনেক মানুষ সুদকে সহজ আয় বা নিশ্চিন্ত লাভ মনে করে। কিন্তু হাদিস শেখায়, মুমিন শুধু চোখের সামনে থাকা বাড়তি অঙ্ক দেখে সিদ্ধান্ত নেয় না; বরং আল্লাহর নির্দেশ ও শেষ ফলের কথাও ভাবে। তাই আয়-রোজগার, ঋণ, বিনিয়োগ ও চুক্তিতে রিবার সন্দেহ থাকলে সতর্ক হওয়া দরকার।"},"teachings":["সুদ বাহ্যিকভাবে বাড়তি মনে হলেও হাদিসে তার পরিণাম ভালো বলা হয়নি।","তাৎক্ষণিক লাভ দেখে হারাম লেনদেনে জড়ানো উচিত নয়।","আর্থিক সিদ্ধান্তে আখিরাতের চিন্তা রাখা দরকার।","হালাল পথে কম আয়ও বরকতের কারণ হতে পারে—এমন আশা করা যায়।"],"related_hadiths":[{"id":"2085","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2086","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2087","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E37" s="4" t="n"/>
@@ -1320,7 +1324,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘুষ দেওয়া-নেওয়ার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ঘুষ গ্রহণকারী ও প্রদানকারীর ওপর অভিশাপের হাদিস ন্যায় ও সততার শিক্ষা দেয়।"},"heading":{"title":"ঘুষ দেওয়া ও নেওয়া: ন্যায়বিচার নষ্ট করার বড় সতর্কতা","description":"এই হাদিসের মূল বিষয় হলো ঘুষ। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ঘুষ গ্রহণকারী ও ঘুষ প্রদানকারীর উপর অভিশাপ করেছেন। বর্ণনাটি ছোট হলেও শিক্ষা খুব স্পষ্ট। ঘুষ শুধু টাকা নেওয়ার বিষয় নয়; এটি সাধারণত কোনো কাজকে অন্যায় পথে এগিয়ে নেওয়া, কারও অধিকার নষ্ট করা বা দায়িত্বশীল ব্যক্তিকে প্রভাবিত করার সঙ্গে জড়িত। তবে এই হাদিসে বিশেষভাবে দুই পক্ষের কথা এসেছে—যে দেয় এবং যে নেয়। তাই ব্যাখ্যায় এই সীমাই ধরে রাখা ভালো। বাস্তব জীবনে চাকরি, অফিস, বিচার, সেবা বা অনুমতির কাজে ঘুষের চাপ দেখা যেতে পারে। একজন মুমিনের দায়িত্ব হলো নিজের সামর্থ্য অনুযায়ী ঘুষ থেকে বাঁচা, ন্যায় পথে কাজ করা এবং হারাম উপার্জনকে হালকা মনে না করা।"},"teachings":["ঘুষ দেওয়া ও নেওয়া—দুই পক্ষই হাদিসে কঠোর সতর্কতার মধ্যে এসেছে।","অন্যায় সুবিধার জন্য অর্থ দেওয়া থেকে দূরে থাকা দরকার।","দায়িত্বশীল পদে থাকলে অবৈধ সুবিধা নেওয়া আরও বিপজ্জনক।","সততা ও ন্যায়ের পথে কাজ করা মুমিনের দায়িত্ব।"],"related_hadiths":[{"id":"3580","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3118","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘুষ দেওয়া-নেওয়ার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ঘুষ গ্রহণকারী ও প্রদানকারীর ওপর অভিশাপের হাদিস ন্যায় ও সততার শিক্ষা দেয়।"},"heading":{"title":"ঘুষ দেওয়া ও নেওয়া: ন্যায়বিচার নষ্ট করার বড় সতর্কতা","description":"এই হাদিসের মূল বিষয় হলো ঘুষ। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ঘুষ গ্রহণকারী ও ঘুষ প্রদানকারীর উপর অভিশাপ করেছেন। বর্ণনাটি ছোট হলেও শিক্ষা খুব স্পষ্ট। ঘুষ শুধু টাকা নেওয়ার বিষয় নয়; এটি সাধারণত কোনো কাজকে অন্যায় পথে এগিয়ে নেওয়া, কারও অধিকার নষ্ট করা বা দায়িত্বশীল ব্যক্তিকে প্রভাবিত করার সঙ্গে জড়িত। তবে এই হাদিসে বিশেষভাবে দুই পক্ষের কথা এসেছে—যে দেয় এবং যে নেয়। তাই ব্যাখ্যায় এই সীমাই ধরে রাখা ভালো। বাস্তব জীবনে চাকরি, অফিস, বিচার, সেবা বা অনুমতির কাজে ঘুষের চাপ দেখা যেতে পারে। একজন মুমিনের দায়িত্ব হলো নিজের সামর্থ্য অনুযায়ী ঘুষ থেকে বাঁচা, ন্যায় পথে কাজ করা এবং হারাম উপার্জনকে হালকা মনে না করা।"},"teachings":["ঘুষ দেওয়া ও নেওয়া—দুই পক্ষই হাদিসে কঠোর সতর্কতার মধ্যে এসেছে।","অন্যায় সুবিধার জন্য অর্থ দেওয়া থেকে দূরে থাকা দরকার।","দায়িত্বশীল পদে থাকলে অবৈধ সুবিধা নেওয়া আরও বিপজ্জনক।","সততা ও ন্যায়ের পথে কাজ করা মুমিনের দায়িত্ব।"],"related_hadiths":[{"id":"3580","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3118","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -1347,7 +1351,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুপারিশের বিনিময়ে উপহার","description":"$book_name$ $hadith_number$ - $chapter_name$. সুপারিশের প্রতিদানে উপহার গ্রহণকে রিবার বড় দরজার সঙ্গে তুলনা করা হয়েছে।"},"heading":{"title":"সুপারিশের বিনিময়ে উপহার: হাদিসের সতর্ক শিক্ষা","description":"এই হাদিসে সুপারিশের বিনিময়ে উপহার গ্রহণের বিষয়ে সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কেউ যদি কারো জন্য সুপারিশ করে, তারপর সেই সুপারিশের প্রতিদান হিসেবে তাকে উপহার দেওয়া হয় এবং সে তা গ্রহণ করে, তাহলে সে সূদের দরজাসমূহের একটি বড় দরজায় উপস্থিত হলো। এখানে সাধারণ উপহার নয়, বরং সুপারিশের বদলে পাওয়া উপহারের কথা বলা হয়েছে। তাই ব্যাখ্যায় সব উপহারকে একভাবে বলা ঠিক নয়। বিষয়টি মূলত স্বার্থের বিনিময়ে প্রভাব ব্যবহার করা। কেউ চাকরি, কাজ, সুবিধা বা সিদ্ধান্তে সাহায্য করল, এরপর তার বিনিময়ে উপহার নিল—এমন অবস্থায় এই হাদিস সতর্ক করে। শিক্ষা হলো, ভালো কাজ বা ন্যায়সঙ্গত সুপারিশকে অর্থ বা উপহার নেওয়ার মাধ্যম বানানো ঠিক নয়।"},"teachings":["সুপারিশের বদলে উপহার গ্রহণ করা থেকে সতর্ক থাকতে হবে।","সাধারণ হাদিয়া ও স্বার্থের বিনিময়ের উপহার এক নয়।","প্রভাব বা পরিচয় ব্যবহার করে সুবিধা নেওয়া বিপজ্জনক হতে পারে।","মানুষের সাহায্য করলে তা আল্লাহর সন্তুষ্টির জন্য করা উচিত।"],"related_hadiths":[{"id":"3541","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3580","book_id":"4","label":"Sunan Abu Dawud"},{"id":"4632","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুপারিশের বিনিময়ে উপহার","description":"$book_name$ $hadith_number$ - $chapter_name$. সুপারিশের প্রতিদানে উপহার গ্রহণকে রিবার বড় দরজার সঙ্গে তুলনা করা হয়েছে।"},"heading":{"title":"সুপারিশের বিনিময়ে উপহার: হাদিসের সতর্ক শিক্ষা","description":"এই হাদিসে সুপারিশের বিনিময়ে উপহার গ্রহণের বিষয়ে সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কেউ যদি কারো জন্য সুপারিশ করে, তারপর সেই সুপারিশের প্রতিদান হিসেবে তাকে উপহার দেওয়া হয় এবং সে তা গ্রহণ করে, তাহলে সে সূদের দরজাসমূহের একটি বড় দরজায় উপস্থিত হলো। এখানে সাধারণ উপহার নয়, বরং সুপারিশের বদলে পাওয়া উপহারের কথা বলা হয়েছে। তাই ব্যাখ্যায় সব উপহারকে একভাবে বলা ঠিক নয়। বিষয়টি মূলত স্বার্থের বিনিময়ে প্রভাব ব্যবহার করা। কেউ চাকরি, কাজ, সুবিধা বা সিদ্ধান্তে সাহায্য করল, এরপর তার বিনিময়ে উপহার নিল—এমন অবস্থায় এই হাদিস সতর্ক করে। শিক্ষা হলো, ভালো কাজ বা ন্যায়সঙ্গত সুপারিশকে অর্থ বা উপহার নেওয়ার মাধ্যম বানানো ঠিক নয়।"},"teachings":["সুপারিশের বদলে উপহার গ্রহণ করা থেকে সতর্ক থাকতে হবে।","সাধারণ হাদিয়া ও স্বার্থের বিনিময়ের উপহার এক নয়।","প্রভাব বা পরিচয় ব্যবহার করে সুবিধা নেওয়া বিপজ্জনক হতে পারে।","মানুষের সাহায্য করলে তা আল্লাহর সন্তুষ্টির জন্য করা উচিত।"],"related_hadiths":[{"id":"3541","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3580","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"4632","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E39" s="4" t="n"/>
@@ -1370,7 +1374,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দায়িত্বে অতিরিক্ত গ্রহণ খিয়ানাত","description":"$book_name$ $hadith_number$ - $chapter_name$. ভাতা নির্ধারিত কাজের দায়িত্বে অতিরিক্ত কিছু গ্রহণকে খিয়ানাত বলা হয়েছে।"},"heading":{"title":"দায়িত্বে অতিরিক্ত গ্রহণ: খিয়ানাত থেকে বাঁচার শিক্ষা","description":"এই হাদিসে সরকারি বা দায়িত্বপ্রাপ্ত কাজের সততা নিয়ে শিক্ষা আছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যাকে ভাতা দিয়ে কোনো কাজের দায়িত্ব দেওয়া হয়েছে, সে যদি সেই ভাতা ছাড়া অন্য কিছু গ্রহণ করে, তাহলে তা খিয়ানাত। এখানে মূল বিষয় হলো দায়িত্ব, নির্ধারিত ভাতা এবং অতিরিক্ত গ্রহণ। অর্থাৎ কেউ কোনো কাজের জন্য নিয়োগ পেয়েছে এবং তার পাওনা ঠিক করা আছে; এরপর কাজের কারণে বাড়তি কিছু নেওয়া আমানতের বিপরীত। এই হাদিসকে ঘুষ, অফিসের অবৈধ সুবিধা, কমিশন বা দায়িত্বের নামে উপহার নেওয়ার সঙ্গে মানুষ খোঁজে। তবে ব্যাখ্যায় মনে রাখতে হবে, হাদিসে নির্দিষ্টভাবে ভাতা দেওয়া দায়িত্বের অতিরিক্ত গ্রহণের কথা বলা হয়েছে। তাই মুসলিম কর্মী, কর্মকর্তা বা দায়িত্বশীল ব্যক্তি নিজের পাওনা ও অন্যের সম্পদের সীমা পরিষ্কার রাখবে।"},"teachings":["নির্ধারিত ভাতা পেলে দায়িত্বের কারণে বাড়তি কিছু নেওয়া থেকে বাঁচতে হবে।","কাজের আমানত রক্ষা করা একজন দায়িত্বশীল ব্যক্তির কর্তব্য।","অবৈধ সুবিধা খিয়ানাতের পথে নিয়ে যেতে পারে।","পাওনা ও উপহার—দুইয়ের সীমা পরিষ্কার রাখা দরকার।"],"related_hadiths":[{"id":"4632","book_id":"2","label":"Sahih Muslim"},{"id":"3541","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3118","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দায়িত্বে অতিরিক্ত গ্রহণ খিয়ানাত","description":"$book_name$ $hadith_number$ - $chapter_name$. ভাতা নির্ধারিত কাজের দায়িত্বে অতিরিক্ত কিছু গ্রহণকে খিয়ানাত বলা হয়েছে।"},"heading":{"title":"দায়িত্বে অতিরিক্ত গ্রহণ: খিয়ানাত থেকে বাঁচার শিক্ষা","description":"এই হাদিসে সরকারি বা দায়িত্বপ্রাপ্ত কাজের সততা নিয়ে শিক্ষা আছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যাকে ভাতা দিয়ে কোনো কাজের দায়িত্ব দেওয়া হয়েছে, সে যদি সেই ভাতা ছাড়া অন্য কিছু গ্রহণ করে, তাহলে তা খিয়ানাত। এখানে মূল বিষয় হলো দায়িত্ব, নির্ধারিত ভাতা এবং অতিরিক্ত গ্রহণ। অর্থাৎ কেউ কোনো কাজের জন্য নিয়োগ পেয়েছে এবং তার পাওনা ঠিক করা আছে; এরপর কাজের কারণে বাড়তি কিছু নেওয়া আমানতের বিপরীত। এই হাদিসকে ঘুষ, অফিসের অবৈধ সুবিধা, কমিশন বা দায়িত্বের নামে উপহার নেওয়ার সঙ্গে মানুষ খোঁজে। তবে ব্যাখ্যায় মনে রাখতে হবে, হাদিসে নির্দিষ্টভাবে ভাতা দেওয়া দায়িত্বের অতিরিক্ত গ্রহণের কথা বলা হয়েছে। তাই মুসলিম কর্মী, কর্মকর্তা বা দায়িত্বশীল ব্যক্তি নিজের পাওনা ও অন্যের সম্পদের সীমা পরিষ্কার রাখবে।"},"teachings":["নির্ধারিত ভাতা পেলে দায়িত্বের কারণে বাড়তি কিছু নেওয়া থেকে বাঁচতে হবে।","কাজের আমানত রক্ষা করা একজন দায়িত্বশীল ব্যক্তির কর্তব্য।","অবৈধ সুবিধা খিয়ানাতের পথে নিয়ে যেতে পারে।","পাওনা ও উপহার—দুইয়ের সীমা পরিষ্কার রাখা দরকার।"],"related_hadiths":[{"id":"4632","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"3541","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3118","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E40" s="4" t="n"/>
@@ -1393,7 +1397,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অন্যায়ভাবে সম্পদ ভক্ষণ","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর সম্পদ অন্যায়ভাবে ভক্ষণকারীদের জন্য কিয়ামতের দিনের কঠিন সতর্কতা।"},"heading":{"title":"অন্যায়ভাবে সম্পদ ভক্ষণ: হারাম আয় থেকে বাঁচার শিক্ষা","description":"এই হাদিসে অন্যায়ভাবে সম্পদ ভক্ষণ করার ভয়াবহতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কিছু লোক আল্লাহর সম্পদ অন্যায়ভাবে ভক্ষণ করে; কিয়ামতের দিন তাদের জন্য জাহান্নাম রয়েছে। এখানে “আল্লাহর সম্পদ” এবং “অন্যায়ভাবে ভক্ষণ”—এই দুইটি কথা খুব গুরুত্বপূর্ণ। এটি ব্যক্তিগত লোভ, দায়িত্বের অপব্যবহার, আমানতের খিয়ানাত বা জনসম্পদ নষ্ট করার বিষয়ে সতর্কতা হিসেবে বোঝা যায়। তবে হাদিসে যেটুকু বলা হয়েছে, তার বাইরে নির্দিষ্ট কোনো ব্যক্তি বা প্রতিষ্ঠানের ওপর রায় দেওয়া ঠিক নয়। মূল শিক্ষা হলো, যে সম্পদ নিজের অধিকার নয়, তা গ্রহণ করা বা ব্যবহার করা ভয়ংকর পরিণামের কারণ হতে পারে। মুসলিমের জন্য হালাল আয়, আমানত রক্ষা এবং অন্যের অধিকার থেকে দূরে থাকা বড় দায়িত্ব।"},"teachings":["অন্যায়ভাবে সম্পদ নেওয়া আখিরাতের জন্য বিপজ্জনক।","আমানত ও জনসম্পদের বিষয়ে খুব সতর্ক থাকা দরকার।","নিজের অধিকার নয় এমন সম্পদ থেকে দূরে থাকতে হবে।","হারাম আয় সাময়িক লাভ মনে হলেও পরিণাম কঠিন হতে পারে।"],"related_hadiths":[{"id":"3118","book_id":"1","label":"Sahih Bukhari"},{"id":"4632","book_id":"2","label":"Sahih Muslim"},{"id":"3580","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অন্যায়ভাবে সম্পদ ভক্ষণ","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর সম্পদ অন্যায়ভাবে ভক্ষণকারীদের জন্য কিয়ামতের দিনের কঠিন সতর্কতা।"},"heading":{"title":"অন্যায়ভাবে সম্পদ ভক্ষণ: হারাম আয় থেকে বাঁচার শিক্ষা","description":"এই হাদিসে অন্যায়ভাবে সম্পদ ভক্ষণ করার ভয়াবহতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কিছু লোক আল্লাহর সম্পদ অন্যায়ভাবে ভক্ষণ করে; কিয়ামতের দিন তাদের জন্য জাহান্নাম রয়েছে। এখানে “আল্লাহর সম্পদ” এবং “অন্যায়ভাবে ভক্ষণ”—এই দুইটি কথা খুব গুরুত্বপূর্ণ। এটি ব্যক্তিগত লোভ, দায়িত্বের অপব্যবহার, আমানতের খিয়ানাত বা জনসম্পদ নষ্ট করার বিষয়ে সতর্কতা হিসেবে বোঝা যায়। তবে হাদিসে যেটুকু বলা হয়েছে, তার বাইরে নির্দিষ্ট কোনো ব্যক্তি বা প্রতিষ্ঠানের ওপর রায় দেওয়া ঠিক নয়। মূল শিক্ষা হলো, যে সম্পদ নিজের অধিকার নয়, তা গ্রহণ করা বা ব্যবহার করা ভয়ংকর পরিণামের কারণ হতে পারে। মুসলিমের জন্য হালাল আয়, আমানত রক্ষা এবং অন্যের অধিকার থেকে দূরে থাকা বড় দায়িত্ব।"},"teachings":["অন্যায়ভাবে সম্পদ নেওয়া আখিরাতের জন্য বিপজ্জনক।","আমানত ও জনসম্পদের বিষয়ে খুব সতর্ক থাকা দরকার।","নিজের অধিকার নয় এমন সম্পদ থেকে দূরে থাকতে হবে।","হারাম আয় সাময়িক লাভ মনে হলেও পরিণাম কঠিন হতে পারে।"],"related_hadiths":[{"id":"3118","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4632","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"3580","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E41" s="4" t="n"/>
@@ -1416,7 +1420,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বড় গোনাহের সতর্ক তালিকা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, দারিদ্র্যের ভয়ে সন্তান হত্যা ও প্রতিবেশীর স্ত্রীর সঙ্গে ব্যভিচারের ভয়াবহতা।"},"heading":{"title":"আল্লাহর কাছে বড় গোনাহ: শিরক, সন্তান হত্যা ও প্রতিবেশীর অধিকার","description":"এই হাদিসে আল্লাহর কাছে বড় গোনাহ সম্পর্কে প্রশ্ন করা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) প্রথমে বলেন, আল্লাহর সমকক্ষ সাব্যস্ত করা, অথচ তিনি মানুষকে সৃষ্টি করেছেন। এরপর বলা হয়, নিজের সন্তানকে এ ভয়ে হত্যা করা যে সে তোমার সঙ্গে খাবে। তারপর বলা হয়, প্রতিবেশীর স্ত্রীর সঙ্গে ব্যভিচারে লিপ্ত হওয়া। শেষে কুরআনের আয়াত নাযিলের কথা এসেছে, যেখানে আল্লাহর সঙ্গে অন্য উপাস্যকে না ডাকা, অন্যায়ভাবে হত্যা না করা এবং ব্যভিচার না করার গুণ বলা হয়েছে। এই হাদিসে তিনটি বিষয় আলাদা: শিরক, দারিদ্র্যের ভয়ে সন্তান হত্যা এবং প্রতিবেশীর স্ত্রীর সঙ্গে ব্যভিচার। তাই ব্যাখ্যায় এগুলোকে মিশিয়ে ফেলা ঠিক নয়। শিক্ষা হলো, ঈমান, জীবন ও প্রতিবেশীর সম্মান—এই তিনটি বিষয়কে অত্যন্ত গুরুত্ব দেওয়া।"},"teachings":["আল্লাহর সঙ্গে কাউকে সমকক্ষ করা সবচেয়ে বড় সতর্কতার বিষয়।","দারিদ্র্যের ভয়ে সন্তান হত্যা বড় গোনাহ হিসেবে উল্লেখ হয়েছে।","প্রতিবেশীর অধিকার ও সম্মান রক্ষা করা জরুরি।","ব্যভিচার ও অন্যায় হত্যা থেকে দূরে থাকা মুমিনের গুণ।"],"related_hadiths":[{"id":"5976","book_id":"1","label":"Sahih Bukhari"},{"id":"2766","book_id":"1","label":"Sahih Bukhari"},{"id":"6857","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বড় গোনাহের সতর্ক তালিকা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, দারিদ্র্যের ভয়ে সন্তান হত্যা ও প্রতিবেশীর স্ত্রীর সঙ্গে ব্যভিচারের ভয়াবহতা।"},"heading":{"title":"আল্লাহর কাছে বড় গোনাহ: শিরক, সন্তান হত্যা ও প্রতিবেশীর অধিকার","description":"এই হাদিসে আল্লাহর কাছে বড় গোনাহ সম্পর্কে প্রশ্ন করা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) প্রথমে বলেন, আল্লাহর সমকক্ষ সাব্যস্ত করা, অথচ তিনি মানুষকে সৃষ্টি করেছেন। এরপর বলা হয়, নিজের সন্তানকে এ ভয়ে হত্যা করা যে সে তোমার সঙ্গে খাবে। তারপর বলা হয়, প্রতিবেশীর স্ত্রীর সঙ্গে ব্যভিচারে লিপ্ত হওয়া। শেষে কুরআনের আয়াত নাযিলের কথা এসেছে, যেখানে আল্লাহর সঙ্গে অন্য উপাস্যকে না ডাকা, অন্যায়ভাবে হত্যা না করা এবং ব্যভিচার না করার গুণ বলা হয়েছে। এই হাদিসে তিনটি বিষয় আলাদা: শিরক, দারিদ্র্যের ভয়ে সন্তান হত্যা এবং প্রতিবেশীর স্ত্রীর সঙ্গে ব্যভিচার। তাই ব্যাখ্যায় এগুলোকে মিশিয়ে ফেলা ঠিক নয়। শিক্ষা হলো, ঈমান, জীবন ও প্রতিবেশীর সম্মান—এই তিনটি বিষয়কে অত্যন্ত গুরুত্ব দেওয়া।"},"teachings":["আল্লাহর সঙ্গে কাউকে সমকক্ষ করা সবচেয়ে বড় সতর্কতার বিষয়।","দারিদ্র্যের ভয়ে সন্তান হত্যা বড় গোনাহ হিসেবে উল্লেখ হয়েছে।","প্রতিবেশীর অধিকার ও সম্মান রক্ষা করা জরুরি।","ব্যভিচার ও অন্যায় হত্যা থেকে দূরে থাকা মুমিনের গুণ।"],"related_hadiths":[{"id":"5976","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2766","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6857","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E42" s="4" t="n"/>
@@ -1439,7 +1443,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবীরা গোনাহের পরিচয়","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, মানুষ হত্যা ও মিথ্যা শপথ বা সাক্ষ্যের সতর্কতা।"},"heading":{"title":"কবীরা গোনাহ: শিরক, পিতা-মাতার অবাধ্যতা ও মিথ্যার ভয়াবহতা","description":"এই হাদিসে কবীরা গোনাহের কয়েকটি বড় দিক বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কবীরা গোনাহ হলো আল্লাহর সঙ্গে শরীক করা, পিতা-মাতার অবাধ্য হওয়া, মানুষ হত্যা করা এবং মিথ্যা শপথ করা। বর্ণনায় আরও এসেছে, আনাস (রাঃ)-এর বর্ণনায় মিথ্যা শপথের বদলে মিথ্যা সাক্ষ্য শব্দ এসেছে। এখানে দুটি বর্ণনার শব্দ আলাদা হওয়ায় ব্যাখ্যায় সতর্ক থাকা দরকার। শিরক ঈমানের মূলকে নষ্ট করে। পিতা-মাতার অবাধ্যতা পারিবারিক দায়িত্ব নষ্ট করে। মানুষ হত্যা জীবনের নিরাপত্তা ভাঙে। আর মিথ্যা শপথ বা মিথ্যা সাক্ষ্য মানুষের অধিকার ও বিচারকে ক্ষতিগ্রস্ত করে। তাই এই হাদিস ব্যক্তিগত ইবাদত, পরিবার, সমাজ ও ন্যায়বিচার—সব ক্ষেত্রেই সতর্কতার ডাক দেয়।"},"teachings":["শিরক কবীরা গোনাহের মধ্যে প্রথমে উল্লেখ হয়েছে।","পিতা-মাতার অবাধ্যতা বড় পাপ হিসেবে এসেছে।","অন্যায়ভাবে মানুষ হত্যা গুরুতর গোনাহ।","মিথ্যা শপথ ও মিথ্যা সাক্ষ্য অধিকার নষ্ট করতে পারে।"],"related_hadiths":[{"id":"5976","book_id":"1","label":"Sahih Bukhari"},{"id":"6871","book_id":"1","label":"Sahih Bukhari"},{"id":"2766","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবীরা গোনাহের পরিচয়","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, মানুষ হত্যা ও মিথ্যা শপথ বা সাক্ষ্যের সতর্কতা।"},"heading":{"title":"কবীরা গোনাহ: শিরক, পিতা-মাতার অবাধ্যতা ও মিথ্যার ভয়াবহতা","description":"এই হাদিসে কবীরা গোনাহের কয়েকটি বড় দিক বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কবীরা গোনাহ হলো আল্লাহর সঙ্গে শরীক করা, পিতা-মাতার অবাধ্য হওয়া, মানুষ হত্যা করা এবং মিথ্যা শপথ করা। বর্ণনায় আরও এসেছে, আনাস (রাঃ)-এর বর্ণনায় মিথ্যা শপথের বদলে মিথ্যা সাক্ষ্য শব্দ এসেছে। এখানে দুটি বর্ণনার শব্দ আলাদা হওয়ায় ব্যাখ্যায় সতর্ক থাকা দরকার। শিরক ঈমানের মূলকে নষ্ট করে। পিতা-মাতার অবাধ্যতা পারিবারিক দায়িত্ব নষ্ট করে। মানুষ হত্যা জীবনের নিরাপত্তা ভাঙে। আর মিথ্যা শপথ বা মিথ্যা সাক্ষ্য মানুষের অধিকার ও বিচারকে ক্ষতিগ্রস্ত করে। তাই এই হাদিস ব্যক্তিগত ইবাদত, পরিবার, সমাজ ও ন্যায়বিচার—সব ক্ষেত্রেই সতর্কতার ডাক দেয়।"},"teachings":["শিরক কবীরা গোনাহের মধ্যে প্রথমে উল্লেখ হয়েছে।","পিতা-মাতার অবাধ্যতা বড় পাপ হিসেবে এসেছে।","অন্যায়ভাবে মানুষ হত্যা গুরুতর গোনাহ।","মিথ্যা শপথ ও মিথ্যা সাক্ষ্য অধিকার নষ্ট করতে পারে।"],"related_hadiths":[{"id":"5976","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6871","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2766","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E43" s="4" t="n"/>
@@ -1462,7 +1466,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সাত ধ্বংসকারী গোনাহ","description":"$book_name$ $hadith_number$ - $chapter_name$. সাতটি ধ্বংসকারী গোনাহ থেকে দূরে থাকার নববী নির্দেশ।"},"heading":{"title":"সাতটি ধ্বংসকারী গোনাহ: মুমিনের জন্য সতর্ক তালিকা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সাতটি ধ্বংসকারী বিষয় থেকে দূরে থাকতে বলেছেন। সাহাবীগণ জিজ্ঞেস করলে তিনি একে একে বলেন: আল্লাহর সঙ্গে শরীক করা, জাদু করা, অন্যায়ভাবে মানুষ হত্যা করা, সুদ খাওয়া, ইয়াতীমের মাল অন্যায়ভাবে খাওয়া, জিহাদের ময়দান থেকে পালিয়ে যাওয়া এবং সরল নির্দোষ মুমিন নারীদের নামে ব্যভিচারের অপবাদ দেওয়া। এই হাদিসের শক্তি হলো এর স্পষ্ট তালিকা। প্রতিটি গোনাহ আলাদা আলাদা ক্ষতি করে—ঈমান, জীবন, সম্পদ, সমাজ, দুর্বল মানুষের অধিকার এবং মানুষের সম্মান নষ্ট করে। ব্যাখ্যায় তালিকার বাইরে নতুন গোনাহ যোগ না করাই ভালো। মূল শিক্ষা হলো, মুমিন নিজের ঈমান, আচরণ, লেনদেন, কথা এবং দায়িত্বের জায়গায় সতর্ক থাকবে।"},"teachings":["শিরক সাত ধ্বংসকারী গোনাহের প্রথমে এসেছে।","সুদ ও ইয়াতীমের মাল খাওয়া অর্থনৈতিক পাপের বড় সতর্কতা।","মানুষ হত্যা ও অপবাদ মানুষের জীবন ও সম্মান নষ্ট করে।","জিহাদের ময়দান থেকে পালানোর বিষয়টি নির্দিষ্ট অবস্থার সঙ্গে যুক্ত—এটি সাধারণ ভয়ের সঙ্গে মেলানো ঠিক নয়।"],"related_hadiths":[{"id":"2766","book_id":"1","label":"Sahih Bukhari"},{"id":"6857","book_id":"1","label":"Sahih Bukhari"},{"id":"5976","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সাত ধ্বংসকারী গোনাহ","description":"$book_name$ $hadith_number$ - $chapter_name$. সাতটি ধ্বংসকারী গোনাহ থেকে দূরে থাকার নববী নির্দেশ।"},"heading":{"title":"সাতটি ধ্বংসকারী গোনাহ: মুমিনের জন্য সতর্ক তালিকা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সাতটি ধ্বংসকারী বিষয় থেকে দূরে থাকতে বলেছেন। সাহাবীগণ জিজ্ঞেস করলে তিনি একে একে বলেন: আল্লাহর সঙ্গে শরীক করা, জাদু করা, অন্যায়ভাবে মানুষ হত্যা করা, সুদ খাওয়া, ইয়াতীমের মাল অন্যায়ভাবে খাওয়া, জিহাদের ময়দান থেকে পালিয়ে যাওয়া এবং সরল নির্দোষ মুমিন নারীদের নামে ব্যভিচারের অপবাদ দেওয়া। এই হাদিসের শক্তি হলো এর স্পষ্ট তালিকা। প্রতিটি গোনাহ আলাদা আলাদা ক্ষতি করে—ঈমান, জীবন, সম্পদ, সমাজ, দুর্বল মানুষের অধিকার এবং মানুষের সম্মান নষ্ট করে। ব্যাখ্যায় তালিকার বাইরে নতুন গোনাহ যোগ না করাই ভালো। মূল শিক্ষা হলো, মুমিন নিজের ঈমান, আচরণ, লেনদেন, কথা এবং দায়িত্বের জায়গায় সতর্ক থাকবে।"},"teachings":["শিরক সাত ধ্বংসকারী গোনাহের প্রথমে এসেছে।","সুদ ও ইয়াতীমের মাল খাওয়া অর্থনৈতিক পাপের বড় সতর্কতা।","মানুষ হত্যা ও অপবাদ মানুষের জীবন ও সম্মান নষ্ট করে।","জিহাদের ময়দান থেকে পালানোর বিষয়টি নির্দিষ্ট অবস্থার সঙ্গে যুক্ত—এটি সাধারণ ভয়ের সঙ্গে মেলানো ঠিক নয়।"],"related_hadiths":[{"id":"2766","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6857","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5976","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E44" s="4" t="n"/>
@@ -1485,7 +1489,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দশটি নববী উপদেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতা, সালাত, মাদক, গোনাহ ও পরিবারের দায়িত্ব নিয়ে দশটি উপদেশ।"},"heading":{"title":"দশটি নববী উপদেশ: ঈমান, সালাত ও পরিবারের দায়িত্ব","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মু‘আয (রাঃ)-কে দশটি বিষয়ে উপদেশ দিয়েছেন। প্রথমে এসেছে, আল্লাহর সঙ্গে কাউকে শরীক না করা, যদিও হত্যা বা আগুনে জ্বালানোর ভয় থাকে। এরপর পিতা-মাতার অবাধ্য না হওয়া, ইচ্ছাকৃত ফরয সালাত ত্যাগ না করা, মাদক না পান করা, গোনাহ থেকে দূরে থাকা, জিহাদের ময়দান থেকে না পালানো, মহামারী এলাকায় থাকলে পালিয়ে না যাওয়া, সামর্থ্য অনুযায়ী পরিবারে ব্যয় করা, পরিবারের শাসন-শিক্ষা পুরো তুলে না নেওয়া এবং তাদেরকে আল্লাহর ভয় শেখানো। এই হাদিসে ব্যক্তিগত ঈমান, ইবাদত, চরিত্র, সামাজিক দায়িত্ব ও পরিবার—সব একসঙ্গে এসেছে। তাই ব্যাখ্যায় একটি দিককে পুরো হাদিস বানিয়ে ফেলা ঠিক নয়। এটি মুসলিম জীবনের ভারসাম্যপূর্ণ উপদেশ।"},"teachings":["শিরক থেকে দূরে থাকা সব অবস্থায় বড় দায়িত্ব।","ফরয সালাত ইচ্ছাকৃতভাবে ত্যাগ করা নিয়ে কঠিন সতর্কতা এসেছে।","মাদককে অশ্লীলতার মূল বলা হয়েছে।","পরিবারের খরচ, শিক্ষা ও আল্লাহভীতি শেখানো দায়িত্বের অংশ।"],"related_hadiths":[{"id":"5976","book_id":"1","label":"Sahih Bukhari"},{"id":"2766","book_id":"1","label":"Sahih Bukhari"},{"id":"6857","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দশটি নববী উপদেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতা, সালাত, মাদক, গোনাহ ও পরিবারের দায়িত্ব নিয়ে দশটি উপদেশ।"},"heading":{"title":"দশটি নববী উপদেশ: ঈমান, সালাত ও পরিবারের দায়িত্ব","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মু‘আয (রাঃ)-কে দশটি বিষয়ে উপদেশ দিয়েছেন। প্রথমে এসেছে, আল্লাহর সঙ্গে কাউকে শরীক না করা, যদিও হত্যা বা আগুনে জ্বালানোর ভয় থাকে। এরপর পিতা-মাতার অবাধ্য না হওয়া, ইচ্ছাকৃত ফরয সালাত ত্যাগ না করা, মাদক না পান করা, গোনাহ থেকে দূরে থাকা, জিহাদের ময়দান থেকে না পালানো, মহামারী এলাকায় থাকলে পালিয়ে না যাওয়া, সামর্থ্য অনুযায়ী পরিবারে ব্যয় করা, পরিবারের শাসন-শিক্ষা পুরো তুলে না নেওয়া এবং তাদেরকে আল্লাহর ভয় শেখানো। এই হাদিসে ব্যক্তিগত ঈমান, ইবাদত, চরিত্র, সামাজিক দায়িত্ব ও পরিবার—সব একসঙ্গে এসেছে। তাই ব্যাখ্যায় একটি দিককে পুরো হাদিস বানিয়ে ফেলা ঠিক নয়। এটি মুসলিম জীবনের ভারসাম্যপূর্ণ উপদেশ।"},"teachings":["শিরক থেকে দূরে থাকা সব অবস্থায় বড় দায়িত্ব।","ফরয সালাত ইচ্ছাকৃতভাবে ত্যাগ করা নিয়ে কঠিন সতর্কতা এসেছে।","মাদককে অশ্লীলতার মূল বলা হয়েছে।","পরিবারের খরচ, শিক্ষা ও আল্লাহভীতি শেখানো দায়িত্বের অংশ।"],"related_hadiths":[{"id":"5976","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2766","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6857","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E45" s="4" t="n"/>
@@ -1508,7 +1512,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বাম উরুর হাড় কথা বলবে","description":"$book_name$ $hadith_number$ - $chapter_name$. মুখ বন্ধ থাকার দিনে মানুষের বাম উরুর হাড় প্রথম কথা বলবে—এতে আমলের জবাবদিহির শিক্ষা আছে।"},"heading":{"title":"কিয়ামতে বাম উরুর হাড় কথা বলবে—হাদিসের সতর্কতা","description":"এই হাদিসে বলা হয়েছে, কিয়ামতের দিন মানুষের মুখ বন্ধ থাকবে। তখন মানুষের বাম উরুর হাড় সর্বপ্রথম কথা বলবে। হাদিসটি ছোট, কিন্তু কিয়ামতের সাক্ষ্য সম্পর্কে খুব গুরুত্বপূর্ণ শিক্ষা দেয়। দুনিয়ায় মানুষ মুখ দিয়ে কথা বলে, যুক্তি দেয়, অস্বীকার করে বা নিজেকে বাঁচাতে চায়। কিন্তু আখেরাতে আল্লাহ চাইলে শরীরের অংশও কথা বলবে। তখন কাজের সত্যতা প্রকাশ হবে। এই হাদিস আমাদের মনে করায়, গোপনে করা কাজও আল্লাহর জ্ঞানের বাইরে নয়। তাই আমল ঠিক রাখা, অন্যায় থেকে বাঁচা এবং কিয়ামতের হিসাব মনে রাখা একজন মুসলিমের জন্য প্রয়োজনীয়।"},"teachings":["কিয়ামতে মুখ বন্ধ থাকলেও অঙ্গ কথা বলবে।","বাম উরুর হাড়ের সাক্ষ্যের কথা হাদিসে এসেছে।","গোপন কাজও আল্লাহর কাছে প্রকাশ্য।","কিয়ামতের হিসাব মনে রেখে জীবন চালানো দরকার।"],"related_hadiths":[{"id":"2969","book_id":"2","label":"Sahih Muslim"},{"id":"5554","book_id":"14","label":"Mishkat al-Masabih"},{"id":"5555","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বাম উরুর হাড় কথা বলবে","description":"$book_name$ $hadith_number$ - $chapter_name$. মুখ বন্ধ থাকার দিনে মানুষের বাম উরুর হাড় প্রথম কথা বলবে—এতে আমলের জবাবদিহির শিক্ষা আছে।"},"heading":{"title":"কিয়ামতে বাম উরুর হাড় কথা বলবে—হাদিসের সতর্কতা","description":"এই হাদিসে বলা হয়েছে, কিয়ামতের দিন মানুষের মুখ বন্ধ থাকবে। তখন মানুষের বাম উরুর হাড় সর্বপ্রথম কথা বলবে। হাদিসটি ছোট, কিন্তু কিয়ামতের সাক্ষ্য সম্পর্কে খুব গুরুত্বপূর্ণ শিক্ষা দেয়। দুনিয়ায় মানুষ মুখ দিয়ে কথা বলে, যুক্তি দেয়, অস্বীকার করে বা নিজেকে বাঁচাতে চায়। কিন্তু আখেরাতে আল্লাহ চাইলে শরীরের অংশও কথা বলবে। তখন কাজের সত্যতা প্রকাশ হবে। এই হাদিস আমাদের মনে করায়, গোপনে করা কাজও আল্লাহর জ্ঞানের বাইরে নয়। তাই আমল ঠিক রাখা, অন্যায় থেকে বাঁচা এবং কিয়ামতের হিসাব মনে রাখা একজন মুসলিমের জন্য প্রয়োজনীয়।"},"teachings":["কিয়ামতে মুখ বন্ধ থাকলেও অঙ্গ কথা বলবে।","বাম উরুর হাড়ের সাক্ষ্যের কথা হাদিসে এসেছে।","গোপন কাজও আল্লাহর কাছে প্রকাশ্য।","কিয়ামতের হিসাব মনে রেখে জীবন চালানো দরকার।"],"related_hadiths":[{"id":"2969","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"5554","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"5555","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E46" s="4" t="n"/>
@@ -1531,7 +1535,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিরক থেকে বাঁচার গুরুত্ব","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরকসহ মৃত্যু ও শিরকমুক্ত ঈমানের পরিণাম নিয়ে সংক্ষিপ্ত কিন্তু গভীর শিক্ষা।"},"heading":{"title":"শিরক থেকে বাঁচা: জান্নাত ও জাহান্নাম বিষয়ে হাদিসের শিক্ষা","description":"এই হাদিসের মূল বিষয় হলো শিরক ও তাওহীদ। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি আল্লাহর সঙ্গে বিন্দুমাত্র শরীক করে মারা যাবে, সে জাহান্নামে যাবে। আর যে ব্যক্তি আল্লাহর সঙ্গে বিন্দুমাত্র শরীক না করে মারা যাবে, সে জান্নাতে যাবে। হাদিসটি খুব সংক্ষিপ্ত, কিন্তু ঈমানের মূল কথা স্পষ্ট করে। এখানে “মারা যাবে” কথাটি গুরুত্বপূর্ণ; অর্থাৎ মানুষের শেষ অবস্থা ও ঈমানের অবস্থা বড় বিষয়। তাই ব্যাখ্যায় কারও নির্দিষ্ট পরিণাম নিয়ে কথা বলা উচিত নয়; বরং নিজের শিরকমুক্ত ঈমান রক্ষা করার শিক্ষা নেওয়া উচিত। তাওহীদ মানে আল্লাহকে একমাত্র রব, ইলাহ ও উপাস্য হিসেবে মানা। মুমিনের দোয়া হওয়া উচিত, আল্লাহ যেন তাকে শিরক থেকে বাঁচিয়ে রাখেন এবং শুদ্ধ ঈমানের ওপর মৃত্যু দেন।"},"teachings":["শিরক ঈমানের সবচেয়ে বড় বিপদ।","তাওহীদের ওপর মৃত্যু জান্নাত লাভের কারণ হিসেবে হাদিসে এসেছে।","নিজের ঈমান শিরকমুক্ত রাখার চেষ্টা করা জরুরি।","অন্যের পরিণাম নিয়ে রায় না দিয়ে নিজের সংশোধনে মন দেওয়া উচিত।"],"related_hadiths":[{"id":"5976","book_id":"1","label":"Sahih Bukhari"},{"id":"2766","book_id":"1","label":"Sahih Bukhari"},{"id":"6857","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিরক থেকে বাঁচার গুরুত্ব","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরকসহ মৃত্যু ও শিরকমুক্ত ঈমানের পরিণাম নিয়ে সংক্ষিপ্ত কিন্তু গভীর শিক্ষা।"},"heading":{"title":"শিরক থেকে বাঁচা: জান্নাত ও জাহান্নাম বিষয়ে হাদিসের শিক্ষা","description":"এই হাদিসের মূল বিষয় হলো শিরক ও তাওহীদ। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি আল্লাহর সঙ্গে বিন্দুমাত্র শরীক করে মারা যাবে, সে জাহান্নামে যাবে। আর যে ব্যক্তি আল্লাহর সঙ্গে বিন্দুমাত্র শরীক না করে মারা যাবে, সে জান্নাতে যাবে। হাদিসটি খুব সংক্ষিপ্ত, কিন্তু ঈমানের মূল কথা স্পষ্ট করে। এখানে “মারা যাবে” কথাটি গুরুত্বপূর্ণ; অর্থাৎ মানুষের শেষ অবস্থা ও ঈমানের অবস্থা বড় বিষয়। তাই ব্যাখ্যায় কারও নির্দিষ্ট পরিণাম নিয়ে কথা বলা উচিত নয়; বরং নিজের শিরকমুক্ত ঈমান রক্ষা করার শিক্ষা নেওয়া উচিত। তাওহীদ মানে আল্লাহকে একমাত্র রব, ইলাহ ও উপাস্য হিসেবে মানা। মুমিনের দোয়া হওয়া উচিত, আল্লাহ যেন তাকে শিরক থেকে বাঁচিয়ে রাখেন এবং শুদ্ধ ঈমানের ওপর মৃত্যু দেন।"},"teachings":["শিরক ঈমানের সবচেয়ে বড় বিপদ।","তাওহীদের ওপর মৃত্যু জান্নাত লাভের কারণ হিসেবে হাদিসে এসেছে।","নিজের ঈমান শিরকমুক্ত রাখার চেষ্টা করা জরুরি।","অন্যের পরিণাম নিয়ে রায় না দিয়ে নিজের সংশোধনে মন দেওয়া উচিত।"],"related_hadiths":[{"id":"5976","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2766","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6857","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E47" s="4" t="n"/>
@@ -1554,7 +1558,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইস্তিগফার ও আল্লাহর ক্ষমার আশা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহকে ডাকলে, ক্ষমার আশা রাখলে ও শির্ক থেকে বাঁচলে বান্দা আল্লাহর ক্ষমা লাভের বড় আশা রাখতে পারে।"},"heading":{"title":"ইস্তিগফার হাদিস: গুনাহের পরও আল্লাহর ক্ষমার আশা","description":"এই হাদিসে আল্লাহর রহমত ও ইস্তিগফারের বড় শিক্ষা আছে। বান্দা যতদিন আল্লাহকে ডাকবে এবং তাঁর কাছে ক্ষমার আশা রাখবে, আল্লাহ তাকে ক্ষমা করার কথা বলেছেন। এখানে মূল কথা হলো—গুনাহ হয়ে গেলে হতাশ হয়ে বসে থাকা নয়; বরং আল্লাহর কাছে ফিরে আসা। হাদিসে আরও বলা হয়েছে, গুনাহ আকাশ পর্যন্ত পৌঁছালেও যদি বান্দা ক্ষমা চায়, আল্লাহ ক্ষমা করবেন। তবে শেষ অংশটি খুব গুরুত্বপূর্ণ: বান্দা যদি পৃথিবী পরিমাণ গুনাহ নিয়েও আসে, কিন্তু আল্লাহর সাথে কাউকে শরীক না করে, আল্লাহ পৃথিবী পরিমাণ ক্ষমা নিয়ে আসবেন। তাই তাওবা, দোয়া, গুনাহ মাফের দোয়া এবং শির্ক থেকে বেঁচে থাকা—এই হাদিসের মূল শিক্ষা।"},"teachings":["গুনাহ হয়ে গেলে আল্লাহর কাছে ক্ষমা চাইতে হবে।","আল্লাহকে ডাকা ও তাঁর ক্ষমার আশা রাখা মুমিনের কাজ।","শির্ক থেকে বেঁচে থাকা ক্ষমা লাভের বড় কারণ।","নিজের গুনাহ দেখে হতাশ না হয়ে তাওবার পথে ফিরতে হবে।"],"related_hadiths":[{"id":"7507","book_id":"1","label":"Sahih Bukhari"},{"id":"6306","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইস্তিগফার ও আল্লাহর ক্ষমার আশা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহকে ডাকলে, ক্ষমার আশা রাখলে ও শির্ক থেকে বাঁচলে বান্দা আল্লাহর ক্ষমা লাভের বড় আশা রাখতে পারে।"},"heading":{"title":"ইস্তিগফার হাদিস: গুনাহের পরও আল্লাহর ক্ষমার আশা","description":"এই হাদিসে আল্লাহর রহমত ও ইস্তিগফারের বড় শিক্ষা আছে। বান্দা যতদিন আল্লাহকে ডাকবে এবং তাঁর কাছে ক্ষমার আশা রাখবে, আল্লাহ তাকে ক্ষমা করার কথা বলেছেন। এখানে মূল কথা হলো—গুনাহ হয়ে গেলে হতাশ হয়ে বসে থাকা নয়; বরং আল্লাহর কাছে ফিরে আসা। হাদিসে আরও বলা হয়েছে, গুনাহ আকাশ পর্যন্ত পৌঁছালেও যদি বান্দা ক্ষমা চায়, আল্লাহ ক্ষমা করবেন। তবে শেষ অংশটি খুব গুরুত্বপূর্ণ: বান্দা যদি পৃথিবী পরিমাণ গুনাহ নিয়েও আসে, কিন্তু আল্লাহর সাথে কাউকে শরীক না করে, আল্লাহ পৃথিবী পরিমাণ ক্ষমা নিয়ে আসবেন। তাই তাওবা, দোয়া, গুনাহ মাফের দোয়া এবং শির্ক থেকে বেঁচে থাকা—এই হাদিসের মূল শিক্ষা।"},"teachings":["গুনাহ হয়ে গেলে আল্লাহর কাছে ক্ষমা চাইতে হবে।","আল্লাহকে ডাকা ও তাঁর ক্ষমার আশা রাখা মুমিনের কাজ।","শির্ক থেকে বেঁচে থাকা ক্ষমা লাভের বড় কারণ।","নিজের গুনাহ দেখে হতাশ না হয়ে তাওবার পথে ফিরতে হবে।"],"related_hadiths":[{"id":"7507","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6306","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E48" s="4" t="n"/>
@@ -1658,7 +1662,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গণকের কাছে যাওয়ার ভয়াবহ ক্ষতি","description":"$book_name$ $hadith_number$ - $chapter_name$. গণক বা জ্যোতিষীর কাছে গিয়ে প্রশ্ন করলে চল্লিশ দিন সালাত কবুল না হওয়ার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"গণকের কাছে যাওয়ার হাদিস: সালাত কবুল না হওয়ার সতর্কতা","description":"এই হাদিসে গণক বা জ্যোতিষীর কাছে যাওয়ার বিষয়ে কঠোর সতর্কতা দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি কোনো গণক বা জ্যোতির্বিদের কাছে যায় এবং তাকে কোনো কথা জিজ্ঞেস করে, চল্লিশ দিন তার সালাত কবুল করা হবে না। এখানে শুধু বিশ্বাস করার কথা নয়; জিজ্ঞেস করার কথাও এসেছে। কারণ ভবিষ্যৎ, ভাগ্য বা গায়েব জানার চেষ্টা মানুষকে ভুল নির্ভরতার দিকে নিয়ে যায়। একজন মুমিন জানে, গায়েবের জ্ঞান আল্লাহর। তাই বিপদ, হারানো জিনিস, ভবিষ্যৎ বা ভাগ্য জানার জন্য গণকের কাছে যাওয়া ঈমানের জন্য ক্ষতিকর। এই হাদিস মানুষকে আল্লাহর উপর ভরসা করতে শেখায়।"},"teachings":["গণক বা জ্যোতিষীর কাছে প্রশ্ন করা থেকে বাঁচতে হবে।","গায়েব জানার দাবিদারদের কাছে যাওয়া ঈমানের জন্য ক্ষতিকর।","সালাতের মর্যাদা রক্ষায় বিশ্বাসের ভুল দরজা বন্ধ করতে হবে।","ভাগ্য ও অদৃশ্য বিষয়ের ব্যাপারে আল্লাহর উপর ভরসা করতে হবে।"],"related_hadiths":[{"id":"4594","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গণকের কাছে যাওয়ার ভয়াবহ ক্ষতি","description":"$book_name$ $hadith_number$ - $chapter_name$. গণক বা জ্যোতিষীর কাছে গিয়ে প্রশ্ন করলে চল্লিশ দিন সালাত কবুল না হওয়ার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"গণকের কাছে যাওয়ার হাদিস: সালাত কবুল না হওয়ার সতর্কতা","description":"এই হাদিসে গণক বা জ্যোতিষীর কাছে যাওয়ার বিষয়ে কঠোর সতর্কতা দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি কোনো গণক বা জ্যোতির্বিদের কাছে যায় এবং তাকে কোনো কথা জিজ্ঞেস করে, চল্লিশ দিন তার সালাত কবুল করা হবে না। এখানে শুধু বিশ্বাস করার কথা নয়; জিজ্ঞেস করার কথাও এসেছে। কারণ ভবিষ্যৎ, ভাগ্য বা গায়েব জানার চেষ্টা মানুষকে ভুল নির্ভরতার দিকে নিয়ে যায়। একজন মুমিন জানে, গায়েবের জ্ঞান আল্লাহর। তাই বিপদ, হারানো জিনিস, ভবিষ্যৎ বা ভাগ্য জানার জন্য গণকের কাছে যাওয়া ঈমানের জন্য ক্ষতিকর। এই হাদিস মানুষকে আল্লাহর উপর ভরসা করতে শেখায়।"},"teachings":["গণক বা জ্যোতিষীর কাছে প্রশ্ন করা থেকে বাঁচতে হবে।","গায়েব জানার দাবিদারদের কাছে যাওয়া ঈমানের জন্য ক্ষতিকর।","সালাতের মর্যাদা রক্ষায় বিশ্বাসের ভুল দরজা বন্ধ করতে হবে।","ভাগ্য ও অদৃশ্য বিষয়ের ব্যাপারে আল্লাহর উপর ভরসা করতে হবে।"],"related_hadiths":[{"id":"4594","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -1685,7 +1689,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যাতুল আনওয়াত ও শির্ক থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মুশরিকদের মতো বরকতের জন্য বিশেষ গাছ চাওয়াকে নবীজি পূর্ববর্তীদের ভুল রীতির সাথে তুলনা করেছেন।"},"heading":{"title":"যাতুল আনওয়াত হাদিস: বরকত লাভে ভুল পথ থেকে সাবধান","description":"এই হাদিসে হুনাইনের পথে একটি ঘটনার কথা এসেছে। কিছু নতুন মুসলিম মুশরিকদের একটি গাছ দেখে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম-কে বললেন, তাদের যেমন নির্দিষ্ট গাছ আছে, আমাদের জন্যও তেমন একটি গাছ নির্ধারণ করে দিন। নবীজি এ কথাকে খুব গুরুতরভাবে নিলেন এবং বললেন, এটি পূর্ববর্তী লোকদের রীতির মতো। তিনি বনী ইসরাঈলের সেই কথাও স্মরণ করালেন, যখন তারা মূসা আলাইহিস সালামকে মুশরিকদের মতো মা‘বূদ বানিয়ে দিতে বলেছিল। এখানে মূল শিক্ষা হলো—বরকত, সাহায্য ও কল্যাণের আশা আল্লাহর বিধান ছাড়া কোনো বস্তু বা স্থানের সাথে জুড়ে দেওয়া বিপজ্জনক। মুসলিমকে অন্যদের ভুল রীতি নকল করা থেকে বাঁচতে হবে।"},"teachings":["বরকত পাওয়ার নামে মুশরিকদের রীতি অনুসরণ করা যাবে না।","নতুন মুসলিম হলেও তাওহীদের বিষয়ে সতর্ক থাকা জরুরি।","কল্যাণের আশা আল্লাহর অনুমোদিত পথেই রাখতে হবে।","পূর্ববর্তী জাতির ভুল থেকে শিক্ষা নেওয়া দরকার।"],"related_hadiths":[{"id":"3456","book_id":"1","label":"Sahih Bukhari"},{"id":"2669","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যাতুল আনওয়াত ও শির্ক থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মুশরিকদের মতো বরকতের জন্য বিশেষ গাছ চাওয়াকে নবীজি পূর্ববর্তীদের ভুল রীতির সাথে তুলনা করেছেন।"},"heading":{"title":"যাতুল আনওয়াত হাদিস: বরকত লাভে ভুল পথ থেকে সাবধান","description":"এই হাদিসে হুনাইনের পথে একটি ঘটনার কথা এসেছে। কিছু নতুন মুসলিম মুশরিকদের একটি গাছ দেখে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম-কে বললেন, তাদের যেমন নির্দিষ্ট গাছ আছে, আমাদের জন্যও তেমন একটি গাছ নির্ধারণ করে দিন। নবীজি এ কথাকে খুব গুরুতরভাবে নিলেন এবং বললেন, এটি পূর্ববর্তী লোকদের রীতির মতো। তিনি বনী ইসরাঈলের সেই কথাও স্মরণ করালেন, যখন তারা মূসা আলাইহিস সালামকে মুশরিকদের মতো মা‘বূদ বানিয়ে দিতে বলেছিল। এখানে মূল শিক্ষা হলো—বরকত, সাহায্য ও কল্যাণের আশা আল্লাহর বিধান ছাড়া কোনো বস্তু বা স্থানের সাথে জুড়ে দেওয়া বিপজ্জনক। মুসলিমকে অন্যদের ভুল রীতি নকল করা থেকে বাঁচতে হবে।"},"teachings":["বরকত পাওয়ার নামে মুশরিকদের রীতি অনুসরণ করা যাবে না।","নতুন মুসলিম হলেও তাওহীদের বিষয়ে সতর্ক থাকা জরুরি।","কল্যাণের আশা আল্লাহর অনুমোদিত পথেই রাখতে হবে।","পূর্ববর্তী জাতির ভুল থেকে শিক্ষা নেওয়া দরকার।"],"related_hadiths":[{"id":"3456","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2669","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E53" s="4" t="n"/>
@@ -1708,7 +1712,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মানত পূরণ ও নাফরমানী থেকে বাঁচা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর আনুগত্যের মানত পূরণ করতে হবে, আর নাফরমানীর মানত পূরণ করা যাবে না—এটাই মূল শিক্ষা।"},"heading":{"title":"মানত সম্পর্কে হাদিস: আনুগত্যের মানত পূরণ, পাপের মানত নয়","description":"এই হাদিসে মানত সম্পর্কে সহজ ও পরিষ্কার নীতি দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি আল্লাহর আনুগত্যের কাজে মানত করে, সে যেন তা পূরণ করে। আর যে ব্যক্তি আল্লাহর নাফরমানীমূলক কাজে মানত করে, সে যেন আল্লাহর নাফরমানী না করে। অর্থাৎ মানত হলেই সব পূরণ করতে হবে—এমন নয়। যদি মানতটি ভালো কাজ, ইবাদত বা আল্লাহর আনুগত্যের মধ্যে পড়ে, তবে তা পূরণ করতে হবে। কিন্তু যদি তা পাপ, অন্যায় বা আল্লাহর অবাধ্যতার দিকে নিয়ে যায়, তাহলে তা করা যাবে না। এই হাদিস মানতের বিষয়ে আবেগ নয়, শরীয়তের সীমা মানতে শেখায়।"},"teachings":["আল্লাহর আনুগত্যের মানত পূরণ করতে হবে।","পাপ বা নাফরমানীর মানত পূরণ করা যাবে না।","মানতের আগে কাজটি বৈধ কি না তা বুঝে নেওয়া দরকার।","ইবাদতের ক্ষেত্রেও আল্লাহর সীমা মানা জরুরি।"],"related_hadiths":[{"id":"6608","book_id":"1","label":"Sahih Bukhari"},{"id":"3426","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মানত পূরণ ও নাফরমানী থেকে বাঁচা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর আনুগত্যের মানত পূরণ করতে হবে, আর নাফরমানীর মানত পূরণ করা যাবে না—এটাই মূল শিক্ষা।"},"heading":{"title":"মানত সম্পর্কে হাদিস: আনুগত্যের মানত পূরণ, পাপের মানত নয়","description":"এই হাদিসে মানত সম্পর্কে সহজ ও পরিষ্কার নীতি দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি আল্লাহর আনুগত্যের কাজে মানত করে, সে যেন তা পূরণ করে। আর যে ব্যক্তি আল্লাহর নাফরমানীমূলক কাজে মানত করে, সে যেন আল্লাহর নাফরমানী না করে। অর্থাৎ মানত হলেই সব পূরণ করতে হবে—এমন নয়। যদি মানতটি ভালো কাজ, ইবাদত বা আল্লাহর আনুগত্যের মধ্যে পড়ে, তবে তা পূরণ করতে হবে। কিন্তু যদি তা পাপ, অন্যায় বা আল্লাহর অবাধ্যতার দিকে নিয়ে যায়, তাহলে তা করা যাবে না। এই হাদিস মানতের বিষয়ে আবেগ নয়, শরীয়তের সীমা মানতে শেখায়।"},"teachings":["আল্লাহর আনুগত্যের মানত পূরণ করতে হবে।","পাপ বা নাফরমানীর মানত পূরণ করা যাবে না।","মানতের আগে কাজটি বৈধ কি না তা বুঝে নেওয়া দরকার।","ইবাদতের ক্ষেত্রেও আল্লাহর সীমা মানা জরুরি।"],"related_hadiths":[{"id":"6608","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3426","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E54" s="4" t="n"/>
@@ -1731,7 +1735,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নতুন স্থানে পড়ার নিরাপদ দোয়া","description":"$book_name$ $hadith_number$ - $chapter_name$. কোনো স্থানে নামলে আল্লাহর পূর্ণ কালামের আশ্রয় চাওয়ার দোয়া শেখানো হয়েছে।"},"heading":{"title":"নতুন স্থানে নামার দোয়া: আল্লাহর কালামের আশ্রয়","description":"এই হাদিসে সফর, বাড়ি, পথ বা কোনো নতুন স্থানে নামার সময় একটি দোয়া শেখানো হয়েছে। দোয়াটি হলো: أَعُوْذُ بِكَلِمَاتِ اللهِ التَّامَّاتِ مِنْ شَرِّ مَا خَلَقَ — অর্থাৎ, আমি আল্লাহর পূর্ণ কালামের নিকট তাঁর সৃষ্টির সব অনিষ্ট থেকে আশ্রয় চাই। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি কোনো বাড়ি বা স্থানে নেমে এই দোয়া পড়বে, সে ঐ স্থান ত্যাগ না করা পর্যন্ত কোনো কিছু তার ক্ষতি করতে পারবে না। এখানে মূল শিক্ষা হলো নিরাপত্তার জন্য তাবিজ বা কুসংস্কার নয়, আল্লাহর কাছে আশ্রয় চাওয়া। মুসলিমের ভরসা হবে আল্লাহর কালাম, দোয়া ও তাওয়াক্কুলের উপর।"},"teachings":["নতুন স্থানে নামলে আল্লাহর কাছে আশ্রয় চাইতে হবে।","সৃষ্টির অনিষ্ট থেকে বাঁচার জন্য দোয়া বড় উপায়।","নিরাপত্তার ভরসা তাবিজ নয়, আল্লাহর উপর রাখতে হবে।","দোয়া মুখস্থ করে জীবনে ব্যবহার করা দরকার।"],"related_hadiths":[{"id":"2708","book_id":"2","label":"Sahih Muslim"},{"id":"2310","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নতুন স্থানে পড়ার নিরাপদ দোয়া","description":"$book_name$ $hadith_number$ - $chapter_name$. কোনো স্থানে নামলে আল্লাহর পূর্ণ কালামের আশ্রয় চাওয়ার দোয়া শেখানো হয়েছে।"},"heading":{"title":"নতুন স্থানে নামার দোয়া: আল্লাহর কালামের আশ্রয়","description":"এই হাদিসে সফর, বাড়ি, পথ বা কোনো নতুন স্থানে নামার সময় একটি দোয়া শেখানো হয়েছে। দোয়াটি হলো: أَعُوْذُ بِكَلِمَاتِ اللهِ التَّامَّاتِ مِنْ شَرِّ مَا خَلَقَ — অর্থাৎ, আমি আল্লাহর পূর্ণ কালামের নিকট তাঁর সৃষ্টির সব অনিষ্ট থেকে আশ্রয় চাই। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি কোনো বাড়ি বা স্থানে নেমে এই দোয়া পড়বে, সে ঐ স্থান ত্যাগ না করা পর্যন্ত কোনো কিছু তার ক্ষতি করতে পারবে না। এখানে মূল শিক্ষা হলো নিরাপত্তার জন্য তাবিজ বা কুসংস্কার নয়, আল্লাহর কাছে আশ্রয় চাওয়া। মুসলিমের ভরসা হবে আল্লাহর কালাম, দোয়া ও তাওয়াক্কুলের উপর।"},"teachings":["নতুন স্থানে নামলে আল্লাহর কাছে আশ্রয় চাইতে হবে।","সৃষ্টির অনিষ্ট থেকে বাঁচার জন্য দোয়া বড় উপায়।","নিরাপত্তার ভরসা তাবিজ নয়, আল্লাহর উপর রাখতে হবে।","দোয়া মুখস্থ করে জীবনে ব্যবহার করা দরকার।"],"related_hadiths":[{"id":"2708","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2310","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E55" s="4" t="n"/>
@@ -1754,7 +1758,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গুনাহের সময় ঈমানের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. যেনা, মদ, চুরি, ছিনতাই ও খিয়ানতের সময় ঈমানের দুর্বলতার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"গুনাহের সময় ঈমানের সতর্কতা: যেনা, মদ, চুরি ও খিয়ানত","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়সাল্লাম) কয়েকটি বড় গুনাহ সম্পর্কে কঠোর সতর্কতা দিয়েছেন। তিনি বলেছেন, যেনাকার যখন যেনা করে তখন মুমিন অবস্থায় তা করে না। মদখোর যখন মদ পান করে, চোর যখন চুরি করে, প্রকাশ্যে ডাকাতি বা ছিনতাইকারী যখন তা করে, এবং কেউ যখন গানীমত বা কোনো মালে খিয়ানত করে—তখন সে মুমিন অবস্থায় থাকে না। শেষে নবীজি বলেছেন, সাবধান হও, সাবধান হও। হাদিসের ভাষা খুব সতর্কতামূলক। এখানে গুনাহকে হালকা করে দেখার সুযোগ নেই। ঈমানের দাবি হলো মানুষ যেন বড় গুনাহ থেকে দূরে থাকে এবং যদি ভুল হয়, আল্লাহর দিকে ফিরে আসে।"},"teachings":["যেনা, মদ, চুরি, ছিনতাই ও খিয়ানত বড় সতর্কতার বিষয়।","গুনাহের সময় ঈমানের দাবি দুর্বল হয়ে যায়—এ কথা হাদিসে এসেছে।","অন্যের মাল বা গানীমতে খিয়ানত করা ভয়ংকর কাজ।","নবীজির সাবধানবাণী গুনাহ থেকে দূরে থাকতে শেখায়।"],"related_hadiths":[{"id":"2475","book_id":"1","label":"Sahih Bukhari"},{"id":"57","book_id":"2","label":"Sahih Muslim"},{"id":"53","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গুনাহের সময় ঈমানের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. যেনা, মদ, চুরি, ছিনতাই ও খিয়ানতের সময় ঈমানের দুর্বলতার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"গুনাহের সময় ঈমানের সতর্কতা: যেনা, মদ, চুরি ও খিয়ানত","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়সাল্লাম) কয়েকটি বড় গুনাহ সম্পর্কে কঠোর সতর্কতা দিয়েছেন। তিনি বলেছেন, যেনাকার যখন যেনা করে তখন মুমিন অবস্থায় তা করে না। মদখোর যখন মদ পান করে, চোর যখন চুরি করে, প্রকাশ্যে ডাকাতি বা ছিনতাইকারী যখন তা করে, এবং কেউ যখন গানীমত বা কোনো মালে খিয়ানত করে—তখন সে মুমিন অবস্থায় থাকে না। শেষে নবীজি বলেছেন, সাবধান হও, সাবধান হও। হাদিসের ভাষা খুব সতর্কতামূলক। এখানে গুনাহকে হালকা করে দেখার সুযোগ নেই। ঈমানের দাবি হলো মানুষ যেন বড় গুনাহ থেকে দূরে থাকে এবং যদি ভুল হয়, আল্লাহর দিকে ফিরে আসে।"},"teachings":["যেনা, মদ, চুরি, ছিনতাই ও খিয়ানত বড় সতর্কতার বিষয়।","গুনাহের সময় ঈমানের দাবি দুর্বল হয়ে যায়—এ কথা হাদিসে এসেছে।","অন্যের মাল বা গানীমতে খিয়ানত করা ভয়ংকর কাজ।","নবীজির সাবধানবাণী গুনাহ থেকে দূরে থাকতে শেখায়।"],"related_hadiths":[{"id":"2475","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"57","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"53","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E56" s="4" t="n"/>
@@ -1777,7 +1781,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মূর্তিপূজার সূচনা থেকে শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. নেককারদের স্মৃতিতে মূর্তি স্থাপন পরে ইবাদতের পথে নিয়ে যায়—এ বর্ণনায় সেই বিপদের শুরু দেখানো হয়েছে।"},"heading":{"title":"মূর্তিপূজার সূচনা: নেককারদের নামে মূর্তি স্থাপনের বিপদ","description":"এই বর্ণনায় নূহ আলাইহিস সালাম-এর সম্প্রদায়ের কিছু নেককার মানুষের নাম নিয়ে বলা হয়েছে। তারা মারা গেলে শয়তান তাদের সম্প্রদায়কে কুমন্ত্রণা দিল—যেখানে তারা বসতেন, সেখানে তাদের মূর্তি স্থাপন করো এবং তাদের নামেই মূর্তির নাম রাখো। শুরুতে এগুলোর পূজা হয়নি। কিন্তু যারা এগুলো স্থাপন করেছিল তারা মারা গেল, এরপর মূল ঘটনা ও জ্ঞান হারিয়ে গেল। তখন সেই মূর্তিগুলোর ইবাদত শুরু হলো। এই বর্ণনার শিক্ষা খুব গভীর: নেককার মানুষকে ভালোবাসা এক বিষয়, আর তাদের নামে এমন স্মৃতিচিহ্ন বানানো আরেক বিষয়, যা পরে ইবাদতের রূপ নিতে পারে। শির্কের পথ অনেক সময় ধীরে ধীরে খুলে যায়।"},"teachings":["নেককারদের ভালোবাসা যেন ইবাদতের সীমা না ছাড়ায়।","মূর্তি বা প্রতিমা স্থাপন পরে বড় ফিতনার কারণ হতে পারে।","শয়তান ধীরে ধীরে মানুষকে শির্কের দিকে টানে।","ইতিহাস ভুলে গেলে ভুল কাজকে ধর্ম মনে করার ঝুঁকি থাকে।"],"related_hadiths":[{"id":"4920","book_id":"1","label":"Sahih Bukhari"},{"id":"4921","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মূর্তিপূজার সূচনা থেকে শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. নেককারদের স্মৃতিতে মূর্তি স্থাপন পরে ইবাদতের পথে নিয়ে যায়—এ বর্ণনায় সেই বিপদের শুরু দেখানো হয়েছে।"},"heading":{"title":"মূর্তিপূজার সূচনা: নেককারদের নামে মূর্তি স্থাপনের বিপদ","description":"এই বর্ণনায় নূহ আলাইহিস সালাম-এর সম্প্রদায়ের কিছু নেককার মানুষের নাম নিয়ে বলা হয়েছে। তারা মারা গেলে শয়তান তাদের সম্প্রদায়কে কুমন্ত্রণা দিল—যেখানে তারা বসতেন, সেখানে তাদের মূর্তি স্থাপন করো এবং তাদের নামেই মূর্তির নাম রাখো। শুরুতে এগুলোর পূজা হয়নি। কিন্তু যারা এগুলো স্থাপন করেছিল তারা মারা গেল, এরপর মূল ঘটনা ও জ্ঞান হারিয়ে গেল। তখন সেই মূর্তিগুলোর ইবাদত শুরু হলো। এই বর্ণনার শিক্ষা খুব গভীর: নেককার মানুষকে ভালোবাসা এক বিষয়, আর তাদের নামে এমন স্মৃতিচিহ্ন বানানো আরেক বিষয়, যা পরে ইবাদতের রূপ নিতে পারে। শির্কের পথ অনেক সময় ধীরে ধীরে খুলে যায়।"},"teachings":["নেককারদের ভালোবাসা যেন ইবাদতের সীমা না ছাড়ায়।","মূর্তি বা প্রতিমা স্থাপন পরে বড় ফিতনার কারণ হতে পারে।","শয়তান ধীরে ধীরে মানুষকে শির্কের দিকে টানে।","ইতিহাস ভুলে গেলে ভুল কাজকে ধর্ম মনে করার ঝুঁকি থাকে।"],"related_hadiths":[{"id":"4920","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4921","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E57" s="4" t="n"/>
@@ -1800,7 +1804,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবরকে মসজিদ বানানো থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীদের কবরকে মসজিদ বানানো নিয়ে ইহুদী-খৃষ্টানদের কাজের প্রতি কঠোর সতর্কতা এসেছে।"},"heading":{"title":"কবরকে মসজিদ বানানো: শেষ অসুখের গুরুত্বপূর্ণ সতর্কতা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম জীবনের শেষ অসুখে একটি গুরুত্বপূর্ণ কথা বলেছেন। তিনি বলেছেন, ইহুদী-খৃষ্টানদের উপর আল্লাহর অভিশাপ; তারা তাদের নবীদের কবরকে মসজিদ বানিয়ে নিয়েছিল। হাদিসের সময়টিও গুরুত্বপূর্ণ, কারণ শেষ অসুখে বলা কথা সাধারণত বিশেষ গুরুত্ব বহন করে। এখানে মূল শিক্ষা হলো কবরকে ইবাদতের জায়গা বানানো থেকে বাঁচা। নবীদের প্রতি সম্মান থাকবে, কিন্তু সেই সম্মান যেন কবরকে কেন্দ্র করে ইবাদতের রূপ না নেয়। কবরকে মসজিদ বানানো মানুষের বিশ্বাসকে তাওহীদ থেকে সরিয়ে দিতে পারে। তাই ইবাদত হবে শুধু আল্লাহর জন্য, আল্লাহর শেখানো পদ্ধতিতে।"},"teachings":["কবরকে মসজিদ বানানো থেকে সতর্ক থাকতে হবে।","নবী ও নেককারদের সম্মান ইবাদতের সীমা ছাড়াতে পারে না।","শেষ জীবনে নবীজির বলা সতর্কতাকে গুরুত্ব দিতে হবে।","ইবাদতের জায়গা ও কবরের সীমা আলাদা রাখা দরকার।"],"related_hadiths":[{"id":"713","book_id":"14","label":"Mishkat al-Masabih"},{"id":"435","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবরকে মসজিদ বানানো থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীদের কবরকে মসজিদ বানানো নিয়ে ইহুদী-খৃষ্টানদের কাজের প্রতি কঠোর সতর্কতা এসেছে।"},"heading":{"title":"কবরকে মসজিদ বানানো: শেষ অসুখের গুরুত্বপূর্ণ সতর্কতা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম জীবনের শেষ অসুখে একটি গুরুত্বপূর্ণ কথা বলেছেন। তিনি বলেছেন, ইহুদী-খৃষ্টানদের উপর আল্লাহর অভিশাপ; তারা তাদের নবীদের কবরকে মসজিদ বানিয়ে নিয়েছিল। হাদিসের সময়টিও গুরুত্বপূর্ণ, কারণ শেষ অসুখে বলা কথা সাধারণত বিশেষ গুরুত্ব বহন করে। এখানে মূল শিক্ষা হলো কবরকে ইবাদতের জায়গা বানানো থেকে বাঁচা। নবীদের প্রতি সম্মান থাকবে, কিন্তু সেই সম্মান যেন কবরকে কেন্দ্র করে ইবাদতের রূপ না নেয়। কবরকে মসজিদ বানানো মানুষের বিশ্বাসকে তাওহীদ থেকে সরিয়ে দিতে পারে। তাই ইবাদত হবে শুধু আল্লাহর জন্য, আল্লাহর শেখানো পদ্ধতিতে।"},"teachings":["কবরকে মসজিদ বানানো থেকে সতর্ক থাকতে হবে।","নবী ও নেককারদের সম্মান ইবাদতের সীমা ছাড়াতে পারে না।","শেষ জীবনে নবীজির বলা সতর্কতাকে গুরুত্ব দিতে হবে।","ইবাদতের জায়গা ও কবরের সীমা আলাদা রাখা দরকার।"],"related_hadiths":[{"id":"713","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"435","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E58" s="4" t="n"/>
@@ -1823,7 +1827,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবরকে মসজিদ না বানানোর নির্দেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. পূর্ববর্তী লোকেরা নবী ও নেককারদের কবরকে মসজিদ বানিয়েছিল; মুসলিমদের তা থেকে নিষেধ করা হয়েছে।"},"heading":{"title":"কবরকে মসজিদ বানিও না: তাওহীদ রক্ষার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম খুব সরাসরি নিষেধ করেছেন। তিনি বলেন, পূর্ববর্তী লোকেরা তাদের নবী ও নেককার লোকদের কবরকে মসজিদ বানিয়েছিল। তারপর তিনি মুসলিমদের বলেন, তোমরা কবরকে মসজিদ বানিও না; আমি তোমাদেরকে তা থেকে নিষেধ করছি। এখানে কোনো অস্পষ্টতা নেই। কবরের প্রতি সম্মান থাকবে, মৃতের জন্য দোয়া থাকবে; কিন্তু কবরকে সালাত, সিজদা বা ইবাদতের কেন্দ্র বানানো যাবে না। কারণ এতে মানুষের মন ধীরে ধীরে কবরবাসীর দিকে ঝুঁকতে পারে। তাওহীদ রক্ষার জন্য ইবাদতের স্থান, দিক ও উদ্দেশ্য সবই আল্লাহর বিধান অনুযায়ী হওয়া দরকার।"},"teachings":["কবরকে ইবাদতের জায়গা বানানো যাবে না।","নেককারদের কবরের ব্যাপারেও সীমা মানতে হবে।","নবীজির সরাসরি নিষেধকে গুরুত্ব দিতে হবে।","তাওহীদ রক্ষায় ইবাদত শুধু আল্লাহর জন্য রাখতে হবে।"],"related_hadiths":[{"id":"712","book_id":"14","label":"Mishkat al-Masabih"},{"id":"436","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবরকে মসজিদ না বানানোর নির্দেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. পূর্ববর্তী লোকেরা নবী ও নেককারদের কবরকে মসজিদ বানিয়েছিল; মুসলিমদের তা থেকে নিষেধ করা হয়েছে।"},"heading":{"title":"কবরকে মসজিদ বানিও না: তাওহীদ রক্ষার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম খুব সরাসরি নিষেধ করেছেন। তিনি বলেন, পূর্ববর্তী লোকেরা তাদের নবী ও নেককার লোকদের কবরকে মসজিদ বানিয়েছিল। তারপর তিনি মুসলিমদের বলেন, তোমরা কবরকে মসজিদ বানিও না; আমি তোমাদেরকে তা থেকে নিষেধ করছি। এখানে কোনো অস্পষ্টতা নেই। কবরের প্রতি সম্মান থাকবে, মৃতের জন্য দোয়া থাকবে; কিন্তু কবরকে সালাত, সিজদা বা ইবাদতের কেন্দ্র বানানো যাবে না। কারণ এতে মানুষের মন ধীরে ধীরে কবরবাসীর দিকে ঝুঁকতে পারে। তাওহীদ রক্ষার জন্য ইবাদতের স্থান, দিক ও উদ্দেশ্য সবই আল্লাহর বিধান অনুযায়ী হওয়া দরকার।"},"teachings":["কবরকে ইবাদতের জায়গা বানানো যাবে না।","নেককারদের কবরের ব্যাপারেও সীমা মানতে হবে।","নবীজির সরাসরি নিষেধকে গুরুত্ব দিতে হবে।","তাওহীদ রক্ষায় ইবাদত শুধু আল্লাহর জন্য রাখতে হবে।"],"related_hadiths":[{"id":"712","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"436","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E59" s="4" t="n"/>
@@ -1846,7 +1850,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মক্কা বিজয়ে মূর্তি অপসারণের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. কা‘বার চারপাশের মূর্তি সরিয়ে সত্যের আগমন ও মিথ্যার বিলুপ্তির ঘোষণা দেওয়া হয়েছিল।"},"heading":{"title":"মক্কা বিজয়ের হাদিস: সত্য এসেছে, মিথ্যা বিলুপ্ত হয়েছে","description":"এই হাদিসে মক্কা বিজয়ের দিনের একটি দৃশ্য এসেছে। রাসূলুল্লাহ সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম যখন মক্কায় প্রবেশ করলেন, তখন কা‘বা ঘরের চারপাশে তিনশ ষাটটি মূর্তি ছিল। তিনি হাতে থাকা ছড়ি দিয়ে সেগুলোকে ঠোকা দিচ্ছিলেন এবং বলছিলেন, সত্য এসেছে আর মিথ্যা বিলুপ্ত হয়েছে; মিথ্যা তো বিলুপ্ত হওয়ারই। এই ঘটনা তাওহীদের বিজয় ও শির্কের অপসারণের বড় শিক্ষা দেয়। কা‘বা আল্লাহর ঘর, সেখানে মূর্তি থাকার কোনো স্থান নেই। হাদিসের মূল বার্তা হলো—সত্য প্রতিষ্ঠিত হলে মিথ্যা টেকে না। মুসলিমের হৃদয়েও তাওহীদের জায়গায় কোনো মূর্তি, শির্ক বা ভুল ভরসা রাখা যায় না।"},"teachings":["আল্লাহর ঘর থেকে মূর্তি অপসারণ তাওহীদের দাবি।","সত্য প্রতিষ্ঠার সাথে মিথ্যা দূর হয়।","শির্কের চিহ্নকে সম্মান নয়, বর্জন করতে হবে।","ইবাদতের স্থানকে শুদ্ধ রাখা জরুরি।"],"related_hadiths":[{"id":"4920","book_id":"1","label":"Sahih Bukhari"},{"id":"712","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মক্কা বিজয়ে মূর্তি অপসারণের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. কা‘বার চারপাশের মূর্তি সরিয়ে সত্যের আগমন ও মিথ্যার বিলুপ্তির ঘোষণা দেওয়া হয়েছিল।"},"heading":{"title":"মক্কা বিজয়ের হাদিস: সত্য এসেছে, মিথ্যা বিলুপ্ত হয়েছে","description":"এই হাদিসে মক্কা বিজয়ের দিনের একটি দৃশ্য এসেছে। রাসূলুল্লাহ সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম যখন মক্কায় প্রবেশ করলেন, তখন কা‘বা ঘরের চারপাশে তিনশ ষাটটি মূর্তি ছিল। তিনি হাতে থাকা ছড়ি দিয়ে সেগুলোকে ঠোকা দিচ্ছিলেন এবং বলছিলেন, সত্য এসেছে আর মিথ্যা বিলুপ্ত হয়েছে; মিথ্যা তো বিলুপ্ত হওয়ারই। এই ঘটনা তাওহীদের বিজয় ও শির্কের অপসারণের বড় শিক্ষা দেয়। কা‘বা আল্লাহর ঘর, সেখানে মূর্তি থাকার কোনো স্থান নেই। হাদিসের মূল বার্তা হলো—সত্য প্রতিষ্ঠিত হলে মিথ্যা টেকে না। মুসলিমের হৃদয়েও তাওহীদের জায়গায় কোনো মূর্তি, শির্ক বা ভুল ভরসা রাখা যায় না।"},"teachings":["আল্লাহর ঘর থেকে মূর্তি অপসারণ তাওহীদের দাবি।","সত্য প্রতিষ্ঠার সাথে মিথ্যা দূর হয়।","শির্কের চিহ্নকে সম্মান নয়, বর্জন করতে হবে।","ইবাদতের স্থানকে শুদ্ধ রাখা জরুরি।"],"related_hadiths":[{"id":"4920","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"712","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E60" s="4" t="n"/>
@@ -1869,7 +1873,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নবীজির কবর নিয়ে শির্ক থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি নিজের কবরকে ইবাদতের বস্তু না বানানোর দোয়া করেছেন এবং কবরকে মসজিদ বানানো থেকে সতর্ক করেছেন।"},"heading":{"title":"আমার কবরকে মূর্তি বানিও না: কবর বিষয়ে তাওহীদের শিক্ষা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম দোয়া করেছেন: হে আল্লাহ! তুমি আমার কবরকে এমন মূর্তিতে পরিণত করো না যার ইবাদত করা হবে। এরপর তিনি বলেন, যারা তাদের নবীদের কবরকে মসজিদ বানিয়েছে, আল্লাহ তাদের উপর রাগান্বিত হয়েছেন। এখানে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম নিজের কবর সম্পর্কেও মানুষকে সতর্ক করে দিয়েছেন। তাই নবীজির প্রতি ভালোবাসা কখনোই তাঁর কবরকে ইবাদতের কেন্দ্র বানানোর অনুমতি দেয় না। ভালোবাসা হবে অনুসরণে, দোয়া ও দরূদে, কিন্তু ইবাদত হবে শুধু আল্লাহর জন্য। কবরকে মূর্তি বা মসজিদের মতো বানানো তাওহীদের জন্য ভয়াবহ ঝুঁকি।"},"teachings":["নবীজির কবরকেও ইবাদতের বস্তু বানানো যাবে না।","কবরকে মসজিদ বানানো আল্লাহর রাগের কারণ হিসেবে এসেছে।","রাসূলের ভালোবাসা তাঁর অনুসরণে প্রকাশ পায়।","ইবাদত শুধু আল্লাহর জন্য সংরক্ষিত রাখতে হবে।"],"related_hadiths":[{"id":"712","book_id":"14","label":"Mishkat al-Masabih"},{"id":"713","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নবীজির কবর নিয়ে শির্ক থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি নিজের কবরকে ইবাদতের বস্তু না বানানোর দোয়া করেছেন এবং কবরকে মসজিদ বানানো থেকে সতর্ক করেছেন।"},"heading":{"title":"আমার কবরকে মূর্তি বানিও না: কবর বিষয়ে তাওহীদের শিক্ষা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম দোয়া করেছেন: হে আল্লাহ! তুমি আমার কবরকে এমন মূর্তিতে পরিণত করো না যার ইবাদত করা হবে। এরপর তিনি বলেন, যারা তাদের নবীদের কবরকে মসজিদ বানিয়েছে, আল্লাহ তাদের উপর রাগান্বিত হয়েছেন। এখানে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম নিজের কবর সম্পর্কেও মানুষকে সতর্ক করে দিয়েছেন। তাই নবীজির প্রতি ভালোবাসা কখনোই তাঁর কবরকে ইবাদতের কেন্দ্র বানানোর অনুমতি দেয় না। ভালোবাসা হবে অনুসরণে, দোয়া ও দরূদে, কিন্তু ইবাদত হবে শুধু আল্লাহর জন্য। কবরকে মূর্তি বা মসজিদের মতো বানানো তাওহীদের জন্য ভয়াবহ ঝুঁকি।"},"teachings":["নবীজির কবরকেও ইবাদতের বস্তু বানানো যাবে না।","কবরকে মসজিদ বানানো আল্লাহর রাগের কারণ হিসেবে এসেছে।","রাসূলের ভালোবাসা তাঁর অনুসরণে প্রকাশ পায়।","ইবাদত শুধু আল্লাহর জন্য সংরক্ষিত রাখতে হবে।"],"related_hadiths":[{"id":"712","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"713","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E61" s="4" t="n"/>
@@ -1892,7 +1896,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যাদুর প্রতি বিশ্বাসের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপায়ী, আত্মীয়তা ছিন্নকারী ও যাদুতে বিশ্বাসকারীর বিষয়ে কঠোর সতর্কতা এসেছে।"},"heading":{"title":"যাদুর প্রতি বিশ্বাস: জান্নাত থেকে বঞ্চনার কঠোর সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের ব্যাপারে কঠোর সতর্কতা এসেছে: সর্বদা মদপানকারী, আত্মীয়তার বন্ধন ছিন্নকারী এবং যাদুর প্রতি বিশ্বাসকারী। এখানে যাদুর প্রতি বিশ্বাসকে এমন গুরুতর বিষয়ের সাথে উল্লেখ করা হয়েছে, যেগুলো মানুষের দ্বীন ও চরিত্রের বড় ক্ষতি করে। যাদুর প্রতি বিশ্বাস বলতে এমন নির্ভরতা বোঝায়, যেখানে মানুষ যাদুকে বাস্তব কল্যাণ-অকল্যাণের স্বাধীন ক্ষমতার মতো মনে করে বা যাদুকরের পথে ভরসা রাখে। এই হাদিস আমাদের মনে করিয়ে দেয়, ঈমানের জায়গায় যাদু, কুসংস্কার বা অন্ধ বিশ্বাস ঢুকতে দেওয়া যাবে না। আল্লাহর উপর ভরসা, আত্মীয়তার সম্পর্ক রক্ষা এবং হারাম কাজ থেকে বাঁচা—এসবই মুমিনের পথ।"},"teachings":["যাদুর প্রতি বিশ্বাসকে হাদিসে কঠোরভাবে নিন্দা করা হয়েছে।","মদপান ও আত্মীয়তা ছিন্ন করার মতো কাজ থেকেও সতর্ক থাকতে হবে।","যাদুকর বা যাদুর উপর ভরসা রাখা ঈমানের জন্য ক্ষতিকর।","মুমিনের ভরসা আল্লাহর উপর, অন্ধ বিশ্বাসের উপর নয়।"],"related_hadiths":[{"id":"2766","book_id":"1","label":"Sahih Bukhari"},{"id":"52","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যাদুর প্রতি বিশ্বাসের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপায়ী, আত্মীয়তা ছিন্নকারী ও যাদুতে বিশ্বাসকারীর বিষয়ে কঠোর সতর্কতা এসেছে।"},"heading":{"title":"যাদুর প্রতি বিশ্বাস: জান্নাত থেকে বঞ্চনার কঠোর সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের ব্যাপারে কঠোর সতর্কতা এসেছে: সর্বদা মদপানকারী, আত্মীয়তার বন্ধন ছিন্নকারী এবং যাদুর প্রতি বিশ্বাসকারী। এখানে যাদুর প্রতি বিশ্বাসকে এমন গুরুতর বিষয়ের সাথে উল্লেখ করা হয়েছে, যেগুলো মানুষের দ্বীন ও চরিত্রের বড় ক্ষতি করে। যাদুর প্রতি বিশ্বাস বলতে এমন নির্ভরতা বোঝায়, যেখানে মানুষ যাদুকে বাস্তব কল্যাণ-অকল্যাণের স্বাধীন ক্ষমতার মতো মনে করে বা যাদুকরের পথে ভরসা রাখে। এই হাদিস আমাদের মনে করিয়ে দেয়, ঈমানের জায়গায় যাদু, কুসংস্কার বা অন্ধ বিশ্বাস ঢুকতে দেওয়া যাবে না। আল্লাহর উপর ভরসা, আত্মীয়তার সম্পর্ক রক্ষা এবং হারাম কাজ থেকে বাঁচা—এসবই মুমিনের পথ।"},"teachings":["যাদুর প্রতি বিশ্বাসকে হাদিসে কঠোরভাবে নিন্দা করা হয়েছে।","মদপান ও আত্মীয়তা ছিন্ন করার মতো কাজ থেকেও সতর্ক থাকতে হবে।","যাদুকর বা যাদুর উপর ভরসা রাখা ঈমানের জন্য ক্ষতিকর।","মুমিনের ভরসা আল্লাহর উপর, অন্ধ বিশ্বাসের উপর নয়।"],"related_hadiths":[{"id":"2766","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E62" s="4" t="n"/>
@@ -1915,7 +1919,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অশুভ লক্ষণ গ্রহণ শির্কী কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. কুলক্ষণ বা অশুভ ধারণাকে কাজের ভিত্তি বানানো শির্কী কাজ—এ কথা তিনবার বলা হয়েছে।"},"heading":{"title":"অশুভ লক্ষণ শির্ক: কুলক্ষণ বিশ্বাসের বিরুদ্ধে হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, অশুভ বা কুলক্ষণ ফল গ্রহণ করা শির্কী কাজ। তিনি কথাটি তিনবার বলেছেন। কোনো কথা তিনবার বলা হলে তার গুরুত্ব আরও পরিষ্কার হয়। কুলক্ষণ মানে কোনো পাখি, শব্দ, দিন, দিক, ব্যক্তি বা ঘটনার কারণে নিজের কাজে অশুভ ফল হবে—এমন বিশ্বাস করা। এই ধরনের ধারণা মানুষের সিদ্ধান্তকে আল্লাহর উপর ভরসা থেকে সরিয়ে দেয়। মুমিন কাজ করবে বৈধ কারণ, পরামর্শ ও দোয়ার মাধ্যমে; অশুভ ধারণার কারণে কাজ ছেড়ে দেবে না। এই হাদিস তাওহীদকে পরিষ্কার রাখার শিক্ষা দেয়। ভয়, অনুমান ও কুসংস্কার নয়—আল্লাহর উপর ভরসাই মুমিনের ভিত্তি।"},"teachings":["অশুভ লক্ষণকে সত্য ধরে নেওয়া শির্কী কাজ।","কুলক্ষণে বিশ্বাস মানুষের তাওয়াক্কুল দুর্বল করে।","নবীজি বিষয়টি তিনবার বলে গুরুত্ব বুঝিয়েছেন।","কাজের সিদ্ধান্ত কুসংস্কার নয়, আল্লাহর ভরসায় নিতে হবে।"],"related_hadiths":[{"id":"4578","book_id":"14","label":"Mishkat al-Masabih"},{"id":"4382","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অশুভ লক্ষণ গ্রহণ শির্কী কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. কুলক্ষণ বা অশুভ ধারণাকে কাজের ভিত্তি বানানো শির্কী কাজ—এ কথা তিনবার বলা হয়েছে।"},"heading":{"title":"অশুভ লক্ষণ শির্ক: কুলক্ষণ বিশ্বাসের বিরুদ্ধে হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, অশুভ বা কুলক্ষণ ফল গ্রহণ করা শির্কী কাজ। তিনি কথাটি তিনবার বলেছেন। কোনো কথা তিনবার বলা হলে তার গুরুত্ব আরও পরিষ্কার হয়। কুলক্ষণ মানে কোনো পাখি, শব্দ, দিন, দিক, ব্যক্তি বা ঘটনার কারণে নিজের কাজে অশুভ ফল হবে—এমন বিশ্বাস করা। এই ধরনের ধারণা মানুষের সিদ্ধান্তকে আল্লাহর উপর ভরসা থেকে সরিয়ে দেয়। মুমিন কাজ করবে বৈধ কারণ, পরামর্শ ও দোয়ার মাধ্যমে; অশুভ ধারণার কারণে কাজ ছেড়ে দেবে না। এই হাদিস তাওহীদকে পরিষ্কার রাখার শিক্ষা দেয়। ভয়, অনুমান ও কুসংস্কার নয়—আল্লাহর উপর ভরসাই মুমিনের ভিত্তি।"},"teachings":["অশুভ লক্ষণকে সত্য ধরে নেওয়া শির্কী কাজ।","কুলক্ষণে বিশ্বাস মানুষের তাওয়াক্কুল দুর্বল করে।","নবীজি বিষয়টি তিনবার বলে গুরুত্ব বুঝিয়েছেন।","কাজের সিদ্ধান্ত কুসংস্কার নয়, আল্লাহর ভরসায় নিতে হবে।"],"related_hadiths":[{"id":"4578","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"4382","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E63" s="4" t="n"/>
@@ -1938,7 +1942,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিকের তিন আলামত","description":"$book_name$ $hadith_number$ - $chapter_name$. কথা বললে মিথ্যা, ওয়াদা করলে ভঙ্গ এবং আমানত রাখলে খিয়ানত—মুনাফিকের তিন আলামত এখানে এসেছে।"},"heading":{"title":"মুনাফিকের তিন আলামত: মিথ্যা, ওয়াদা ভঙ্গ ও খিয়ানত","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মুনাফিকের তিনটি আলামত বলেছেন। প্রথমত, সে কথা বললে মিথ্যা বলে। দ্বিতীয়ত, ওয়াদা করলে তা ভঙ্গ করে। তৃতীয়ত, তার কাছে আমানত রাখা হলে সে খিয়ানত করে। এই হাদিস খুব পরিচিত, কিন্তু এর শিক্ষা প্রতিদিনের জীবনে দরকার। মুনাফিকের আলামত হাদিস আমাদের কথা, প্রতিশ্রুতি ও আমানতের ব্যাপারে সতর্ক করে। মানুষকে বিশ্বাসযোগ্য হতে হলে সত্য বলা, ওয়াদা রাখা এবং আমানত রক্ষা করা জরুরি। এখানে শুধু বড় লেনদেন নয়; কথা, দায়িত্ব, গোপন তথ্য বা মানুষের হক—সব ক্ষেত্রেই সততা দরকার।"},"teachings":["মিথ্যা বলা মুনাফিকের আলামতের মধ্যে এসেছে।","ওয়াদা করে তা ভেঙে ফেলা খারাপ আচরণ।","আমানত রাখলে খিয়ানত করা মুনাফিকী স্বভাবের লক্ষণ।","সত্যবাদিতা ও আমানতদারি মুসলিম চরিত্রের জরুরি অংশ।"],"related_hadiths":[{"id":"33","book_id":"1","label":"Sahih Bukhari"},{"id":"59","book_id":"2","label":"Sahih Muslim"},{"id":"2631","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিকের তিন আলামত","description":"$book_name$ $hadith_number$ - $chapter_name$. কথা বললে মিথ্যা, ওয়াদা করলে ভঙ্গ এবং আমানত রাখলে খিয়ানত—মুনাফিকের তিন আলামত এখানে এসেছে।"},"heading":{"title":"মুনাফিকের তিন আলামত: মিথ্যা, ওয়াদা ভঙ্গ ও খিয়ানত","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মুনাফিকের তিনটি আলামত বলেছেন। প্রথমত, সে কথা বললে মিথ্যা বলে। দ্বিতীয়ত, ওয়াদা করলে তা ভঙ্গ করে। তৃতীয়ত, তার কাছে আমানত রাখা হলে সে খিয়ানত করে। এই হাদিস খুব পরিচিত, কিন্তু এর শিক্ষা প্রতিদিনের জীবনে দরকার। মুনাফিকের আলামত হাদিস আমাদের কথা, প্রতিশ্রুতি ও আমানতের ব্যাপারে সতর্ক করে। মানুষকে বিশ্বাসযোগ্য হতে হলে সত্য বলা, ওয়াদা রাখা এবং আমানত রক্ষা করা জরুরি। এখানে শুধু বড় লেনদেন নয়; কথা, দায়িত্ব, গোপন তথ্য বা মানুষের হক—সব ক্ষেত্রেই সততা দরকার।"},"teachings":["মিথ্যা বলা মুনাফিকের আলামতের মধ্যে এসেছে।","ওয়াদা করে তা ভেঙে ফেলা খারাপ আচরণ।","আমানত রাখলে খিয়ানত করা মুনাফিকী স্বভাবের লক্ষণ।","সত্যবাদিতা ও আমানতদারি মুসলিম চরিত্রের জরুরি অংশ।"],"related_hadiths":[{"id":"33","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"59","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2631","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E64" s="4" t="n"/>
@@ -1961,7 +1965,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুলক্ষণ দূর করার দোয়া ও তাওহীদ","description":"$book_name$ $hadith_number$ - $chapter_name$. অশুভ ধারণা কাজ থেকে ফিরিয়ে দিলে তা শির্ক; এর কাফ্ফারা হিসেবে তাওহীদের দোয়া শেখানো হয়েছে।"},"heading":{"title":"কুলক্ষণ দূর করার দোয়া: অশুভ ধারণা থেকে তাওহীদের পথে","description":"এই হাদিসে কুলক্ষণ বা অশুভ ধারণার বাস্তব ক্ষতি বোঝানো হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, কুলক্ষণ যে ব্যক্তিকে তার প্রয়োজন, দায়িত্ব বা কর্তব্য থেকে ফিরিয়ে রাখে, সে শির্ক করল। অর্থাৎ মনে অশুভ ধারণা আসা এক বিষয়, কিন্তু সেই ধারণার কারণে বৈধ কাজ ছেড়ে দেওয়া বড় ভুল। সাহাবীগণ এর কাফ্ফারা জানতে চাইলে নবীজি একটি দোয়া শিখিয়েছেন: اللَّهُمَّ لاَ خَيْرَ إِلاَّ خَيْرُكَ وَلاَ طَيْرَ إِلاَّ طَيْرُكَ وَلاَ إِلَهَ غَيْرُكَ। অর্থ হলো, হে আল্লাহ! তোমার মঙ্গল ছাড়া কোনো মঙ্গল নেই। তোমার অশুভ ছাড়া কোনো অশুভ নেই এবং তুমি ছাড়া কোনো মা‘বূদ নেই। এই দোয়া কুসংস্কার ভেঙে তাওহীদ মজবুত করে।"},"teachings":["অশুভ ধারণার কারণে দায়িত্ব ছেড়ে দেওয়া শির্কের পথে নিয়ে যায়।","কুলক্ষণ দূর করতে নবীজি তাওহীদের দোয়া শিখিয়েছেন।","মঙ্গল ও অমঙ্গলের নিয়ন্ত্রণ আল্লাহর হাতে।","মন দুর্বল হলে দোয়ার মাধ্যমে আল্লাহর দিকে ফিরতে হবে।"],"related_hadiths":[{"id":"4584","book_id":"14","label":"Mishkat al-Masabih"},{"id":"4578","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুলক্ষণ দূর করার দোয়া ও তাওহীদ","description":"$book_name$ $hadith_number$ - $chapter_name$. অশুভ ধারণা কাজ থেকে ফিরিয়ে দিলে তা শির্ক; এর কাফ্ফারা হিসেবে তাওহীদের দোয়া শেখানো হয়েছে।"},"heading":{"title":"কুলক্ষণ দূর করার দোয়া: অশুভ ধারণা থেকে তাওহীদের পথে","description":"এই হাদিসে কুলক্ষণ বা অশুভ ধারণার বাস্তব ক্ষতি বোঝানো হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, কুলক্ষণ যে ব্যক্তিকে তার প্রয়োজন, দায়িত্ব বা কর্তব্য থেকে ফিরিয়ে রাখে, সে শির্ক করল। অর্থাৎ মনে অশুভ ধারণা আসা এক বিষয়, কিন্তু সেই ধারণার কারণে বৈধ কাজ ছেড়ে দেওয়া বড় ভুল। সাহাবীগণ এর কাফ্ফারা জানতে চাইলে নবীজি একটি দোয়া শিখিয়েছেন: اللَّهُمَّ لاَ خَيْرَ إِلاَّ خَيْرُكَ وَلاَ طَيْرَ إِلاَّ طَيْرُكَ وَلاَ إِلَهَ غَيْرُكَ। অর্থ হলো, হে আল্লাহ! তোমার মঙ্গল ছাড়া কোনো মঙ্গল নেই। তোমার অশুভ ছাড়া কোনো অশুভ নেই এবং তুমি ছাড়া কোনো মা‘বূদ নেই। এই দোয়া কুসংস্কার ভেঙে তাওহীদ মজবুত করে।"},"teachings":["অশুভ ধারণার কারণে দায়িত্ব ছেড়ে দেওয়া শির্কের পথে নিয়ে যায়।","কুলক্ষণ দূর করতে নবীজি তাওহীদের দোয়া শিখিয়েছেন।","মঙ্গল ও অমঙ্গলের নিয়ন্ত্রণ আল্লাহর হাতে।","মন দুর্বল হলে দোয়ার মাধ্যমে আল্লাহর দিকে ফিরতে হবে।"],"related_hadiths":[{"id":"4584","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"4578","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E65" s="4" t="n"/>
@@ -1984,7 +1988,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিরক থেকে আমল রক্ষার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর সন্তুষ্টির জন্য আমল করা জরুরি; আমলে শিরক থাকলে তা প্রত্যাখ্যাত হওয়ার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"শিরক থেকে আমল রক্ষা: আল্লাহর জন্য খাঁটি ইবাদত","description":"এই হাদিসের মূল শিক্ষা হলো, ইবাদত ও সৎকাজ শুধু আল্লাহর জন্য হতে হবে। এখানে আল্লাহ তা‘আলা নিজেই বলেছেন, তিনি অংশীদারদের অংশীদারিত্ব থেকে সম্পূর্ণ মুক্ত। অর্থাৎ কেউ যদি কোনো আমল করে, কিন্তু সেই আমলে আল্লাহর সাথে অন্য কাউকে শরীক করে, তাহলে সেই আমল আল্লাহর কাছে গ্রহণযোগ্য থাকে না। শিরক শুধু প্রকাশ্য মূর্তি বা বস্তু পূজার মধ্যেই সীমাবদ্ধ নয়; আমলের উদ্দেশ্যে অন্য কারও সন্তুষ্টি, মর্যাদা বা প্রশংসা ঢুকে গেলে সেটিও ভয়ংকর বিষয়। এই হাদিস আমাদের নিয়ত ঠিক করার কথা স্মরণ করায়। তাই নামাজ, দান, শিক্ষা, দাওয়াত বা যে কোনো ভালো কাজের আগে নিজের অন্তরকে জিজ্ঞেস করা দরকার—আমি এটা কার জন্য করছি?"},"teachings":["আমল আল্লাহর জন্য খাঁটি না হলে তা গ্রহণযোগ্যতার ঝুঁকিতে পড়ে।","ইবাদতে আল্লাহর সাথে কাউকে শরীক করা বড় সতর্কতার বিষয়।","প্রতিটি ভালো কাজের আগে নিয়ত যাচাই করা দরকার।","মানুষের প্রশংসা নয়, আল্লাহর সন্তুষ্টিই আমলের মূল লক্ষ্য হওয়া উচিত।"],"related_hadiths":[{"id":"158","book_id":"2","label":"Sahih Muslim"},{"id":"1","book_id":"1","label":"Sahih Bukhari"},{"id":"7365","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিরক থেকে আমল রক্ষার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর সন্তুষ্টির জন্য আমল করা জরুরি; আমলে শিরক থাকলে তা প্রত্যাখ্যাত হওয়ার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"শিরক থেকে আমল রক্ষা: আল্লাহর জন্য খাঁটি ইবাদত","description":"এই হাদিসের মূল শিক্ষা হলো, ইবাদত ও সৎকাজ শুধু আল্লাহর জন্য হতে হবে। এখানে আল্লাহ তা‘আলা নিজেই বলেছেন, তিনি অংশীদারদের অংশীদারিত্ব থেকে সম্পূর্ণ মুক্ত। অর্থাৎ কেউ যদি কোনো আমল করে, কিন্তু সেই আমলে আল্লাহর সাথে অন্য কাউকে শরীক করে, তাহলে সেই আমল আল্লাহর কাছে গ্রহণযোগ্য থাকে না। শিরক শুধু প্রকাশ্য মূর্তি বা বস্তু পূজার মধ্যেই সীমাবদ্ধ নয়; আমলের উদ্দেশ্যে অন্য কারও সন্তুষ্টি, মর্যাদা বা প্রশংসা ঢুকে গেলে সেটিও ভয়ংকর বিষয়। এই হাদিস আমাদের নিয়ত ঠিক করার কথা স্মরণ করায়। তাই নামাজ, দান, শিক্ষা, দাওয়াত বা যে কোনো ভালো কাজের আগে নিজের অন্তরকে জিজ্ঞেস করা দরকার—আমি এটা কার জন্য করছি?"},"teachings":["আমল আল্লাহর জন্য খাঁটি না হলে তা গ্রহণযোগ্যতার ঝুঁকিতে পড়ে।","ইবাদতে আল্লাহর সাথে কাউকে শরীক করা বড় সতর্কতার বিষয়।","প্রতিটি ভালো কাজের আগে নিয়ত যাচাই করা দরকার।","মানুষের প্রশংসা নয়, আল্লাহর সন্তুষ্টিই আমলের মূল লক্ষ্য হওয়া উচিত।"],"related_hadiths":[{"id":"158","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7365","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E66" s="4" t="n"/>
@@ -2007,7 +2011,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গোপন শিরক ও লোক দেখানো নামাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. লোক দেখানোর উদ্দেশ্যে ইবাদত করা গোপন শিরকের অন্তর্ভুক্ত; নামাজেও নিয়ত খাঁটি রাখা জরুরি।"},"heading":{"title":"গোপন শিরক: লোক দেখানো ইবাদত থেকে সতর্কতা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) দাজ্জাল নিয়ে আলোচনার সময় আরও ভয়ঙ্কর একটি বিষয়ের কথা বলেছেন—গোপন শিরক। হাদিসে এর উদাহরণ দেওয়া হয়েছে, একজন মানুষ নামাজে দাঁড়ায় এবং মনে মনে ভাবে, কেউ তাকে দেখছে; তাই সে নামাজকে মানুষের চোখে সুন্দর করে তুলতে চায়। এখানে মূল বিষয় হলো রিয়া বা লোক দেখানো আমল। নামাজের বাহ্যিক রূপ সুন্দর হলেও যদি উদ্দেশ্য মানুষের প্রশংসা হয়, তাহলে তা অন্তরের জন্য ক্ষতিকর। এই হাদিস আমাদের শেখায়, ইবাদতের সময় মানুষের চোখ নয়, আল্লাহর সন্তুষ্টিকে সামনে রাখতে হবে। নিজের আমল নিয়ে অহংকার বা সুনাম পাওয়ার আশা থেকে সতর্ক থাকা মুমিনের দরকারি কাজ।"},"teachings":["লোক দেখানোর জন্য নামাজ পড়া গোপন শিরকের একটি উদাহরণ।","ইবাদতের সৌন্দর্য মানুষের প্রশংসার জন্য নয়, আল্লাহর সন্তুষ্টির জন্য হওয়া উচিত।","নামাজে দাঁড়ানোর সময় অন্তরের নিয়ত ঠিক রাখা দরকার।","সুনাম, নেতৃত্ব বা দুনিয়ার স্বার্থ ইবাদতের উদ্দেশ্য হওয়া উচিত নয়।"],"related_hadiths":[{"id":"7365","book_id":"2","label":"Sahih Muslim"},{"id":"1","book_id":"1","label":"Sahih Bukhari"},{"id":"158","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গোপন শিরক ও লোক দেখানো নামাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. লোক দেখানোর উদ্দেশ্যে ইবাদত করা গোপন শিরকের অন্তর্ভুক্ত; নামাজেও নিয়ত খাঁটি রাখা জরুরি।"},"heading":{"title":"গোপন শিরক: লোক দেখানো ইবাদত থেকে সতর্কতা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) দাজ্জাল নিয়ে আলোচনার সময় আরও ভয়ঙ্কর একটি বিষয়ের কথা বলেছেন—গোপন শিরক। হাদিসে এর উদাহরণ দেওয়া হয়েছে, একজন মানুষ নামাজে দাঁড়ায় এবং মনে মনে ভাবে, কেউ তাকে দেখছে; তাই সে নামাজকে মানুষের চোখে সুন্দর করে তুলতে চায়। এখানে মূল বিষয় হলো রিয়া বা লোক দেখানো আমল। নামাজের বাহ্যিক রূপ সুন্দর হলেও যদি উদ্দেশ্য মানুষের প্রশংসা হয়, তাহলে তা অন্তরের জন্য ক্ষতিকর। এই হাদিস আমাদের শেখায়, ইবাদতের সময় মানুষের চোখ নয়, আল্লাহর সন্তুষ্টিকে সামনে রাখতে হবে। নিজের আমল নিয়ে অহংকার বা সুনাম পাওয়ার আশা থেকে সতর্ক থাকা মুমিনের দরকারি কাজ।"},"teachings":["লোক দেখানোর জন্য নামাজ পড়া গোপন শিরকের একটি উদাহরণ।","ইবাদতের সৌন্দর্য মানুষের প্রশংসার জন্য নয়, আল্লাহর সন্তুষ্টির জন্য হওয়া উচিত।","নামাজে দাঁড়ানোর সময় অন্তরের নিয়ত ঠিক রাখা দরকার।","সুনাম, নেতৃত্ব বা দুনিয়ার স্বার্থ ইবাদতের উদ্দেশ্য হওয়া উচিত নয়।"],"related_hadiths":[{"id":"7365","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"158","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E67" s="4" t="n"/>
@@ -2030,7 +2034,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দ্বীনে নতুন কাজের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীনের অংশ নয় এমন নতুন বিষয় ইবাদত হিসেবে চালু করলে তা প্রত্যাখ্যাত—হাদিসটি সুন্নাহ মেনে চলার শিক্ষা দেয়।"},"heading":{"title":"বিদআত থেকে বাঁচার হাদিস: দ্বীনে নতুন কিছু যোগ করার সতর্কতা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব স্পষ্টভাবে বলেছেন, যে ব্যক্তি দ্বীনের মধ্যে এমন কিছু নতুনভাবে চালু করে, যা দ্বীনের অংশ নয়, তা প্রত্যাখ্যাত। এখানে মূল শিক্ষা হলো, ইবাদতের ক্ষেত্রে নিজের পছন্দ, আবেগ বা প্রচলনকে দলিল বানানো যাবে না। ইসলাম আল্লাহর দেওয়া দ্বীন, আর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তা মানুষের কাছে পৌঁছে দিয়েছেন। তাই যে কাজকে ইবাদত বলা হবে, সেটির ভিত্তি কুরআন ও সুন্নাহতে থাকতে হবে। এই হাদিস মানুষকে বাড়াবাড়ি থেকে ফিরিয়ে আনে। দ্বীনের নামে নতুন আমল তৈরি করা দেখতে ভালো লাগলেও, হাদিসের ভাষায় তা গ্রহণযোগ্য নয়। তাই আমলের আগে জানা দরকার—এটি রাসূলের শেখানো পথে আছে কি না।"},"teachings":["দ্বীনের অংশ নয় এমন নতুন কাজ ইবাদত হিসেবে চালু করা গ্রহণযোগ্য নয়।","ইবাদতের মানদণ্ড ব্যক্তিগত পছন্দ নয়, কুরআন ও সুন্নাহ।","সুন্নাহ অনুসরণ করলে দ্বীনের সঠিক পথ পরিষ্কার থাকে।","ভালো মনে হলেই কোনো কাজ দ্বীনের আমল হয়ে যায় না।"],"related_hadiths":[{"id":"4385","book_id":"2","label":"Sahih Muslim"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দ্বীনে নতুন কাজের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীনের অংশ নয় এমন নতুন বিষয় ইবাদত হিসেবে চালু করলে তা প্রত্যাখ্যাত—হাদিসটি সুন্নাহ মেনে চলার শিক্ষা দেয়।"},"heading":{"title":"বিদআত থেকে বাঁচার হাদিস: দ্বীনে নতুন কিছু যোগ করার সতর্কতা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব স্পষ্টভাবে বলেছেন, যে ব্যক্তি দ্বীনের মধ্যে এমন কিছু নতুনভাবে চালু করে, যা দ্বীনের অংশ নয়, তা প্রত্যাখ্যাত। এখানে মূল শিক্ষা হলো, ইবাদতের ক্ষেত্রে নিজের পছন্দ, আবেগ বা প্রচলনকে দলিল বানানো যাবে না। ইসলাম আল্লাহর দেওয়া দ্বীন, আর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তা মানুষের কাছে পৌঁছে দিয়েছেন। তাই যে কাজকে ইবাদত বলা হবে, সেটির ভিত্তি কুরআন ও সুন্নাহতে থাকতে হবে। এই হাদিস মানুষকে বাড়াবাড়ি থেকে ফিরিয়ে আনে। দ্বীনের নামে নতুন আমল তৈরি করা দেখতে ভালো লাগলেও, হাদিসের ভাষায় তা গ্রহণযোগ্য নয়। তাই আমলের আগে জানা দরকার—এটি রাসূলের শেখানো পথে আছে কি না।"},"teachings":["দ্বীনের অংশ নয় এমন নতুন কাজ ইবাদত হিসেবে চালু করা গ্রহণযোগ্য নয়।","ইবাদতের মানদণ্ড ব্যক্তিগত পছন্দ নয়, কুরআন ও সুন্নাহ।","সুন্নাহ অনুসরণ করলে দ্বীনের সঠিক পথ পরিষ্কার থাকে।","ভালো মনে হলেই কোনো কাজ দ্বীনের আমল হয়ে যায় না।"],"related_hadiths":[{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E68" s="4" t="n"/>
@@ -2053,7 +2057,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নির্দেশনাহীন আমলের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের নির্দেশনা ছাড়া ইবাদত করলে তা পরিত্যাজ্য; তাই আমলকে সুন্নাহর সাথে মিলিয়ে করা জরুরি।"},"heading":{"title":"সুন্নাহ ছাড়া আমল নয়: নির্দেশনাহীন কাজের সতর্কতা","description":"এই হাদিসে বলা হয়েছে, যে ব্যক্তি এমন আমল করে যার ওপর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কোনো নির্দেশনা নেই, তা পরিত্যাজ্য। এখানে আমলের শুদ্ধতার গুরুত্বপূর্ণ নিয়ম বোঝানো হয়েছে। শুধু ভালো উদ্দেশ্য থাকলেই ইবাদত সঠিক হয়ে যায় না; ইবাদতের পদ্ধতিও রাসূলের শেখানো মতো হতে হবে। কেউ যদি নামাজ, রোজা, দোয়া, যিকির বা অন্য কোনো ইবাদতে নিজের মতো নিয়ম বানায়, তাহলে তা হাদিসের সতর্কতার মধ্যে পড়ে। এই শিক্ষা মানুষকে সুন্নাহর দিকে ফিরিয়ে নেয়। দ্বীনের কাজে নিরাপদ পথ হলো—যা প্রমাণিত, তা করা; যা প্রমাণিত নয়, তা ইবাদত হিসেবে না ধরা। এতে আমল পরিষ্কার থাকে এবং দ্বীনের নামে বাড়তি চাপ তৈরি হয় না।"},"teachings":["রাসূলের নির্দেশনা ছাড়া কোনো কাজ ইবাদত হিসেবে গ্রহণযোগ্য নয়।","ভালো নিয়তের পাশাপাশি সঠিক পদ্ধতিও জরুরি।","সুন্নাহর সাথে মিলিয়ে আমল করা নিরাপদ পথ।","নিজের বানানো নিয়মকে দ্বীনের অংশ বলা ঠিক নয়।"],"related_hadiths":[{"id":"2697","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নির্দেশনাহীন আমলের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের নির্দেশনা ছাড়া ইবাদত করলে তা পরিত্যাজ্য; তাই আমলকে সুন্নাহর সাথে মিলিয়ে করা জরুরি।"},"heading":{"title":"সুন্নাহ ছাড়া আমল নয়: নির্দেশনাহীন কাজের সতর্কতা","description":"এই হাদিসে বলা হয়েছে, যে ব্যক্তি এমন আমল করে যার ওপর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কোনো নির্দেশনা নেই, তা পরিত্যাজ্য। এখানে আমলের শুদ্ধতার গুরুত্বপূর্ণ নিয়ম বোঝানো হয়েছে। শুধু ভালো উদ্দেশ্য থাকলেই ইবাদত সঠিক হয়ে যায় না; ইবাদতের পদ্ধতিও রাসূলের শেখানো মতো হতে হবে। কেউ যদি নামাজ, রোজা, দোয়া, যিকির বা অন্য কোনো ইবাদতে নিজের মতো নিয়ম বানায়, তাহলে তা হাদিসের সতর্কতার মধ্যে পড়ে। এই শিক্ষা মানুষকে সুন্নাহর দিকে ফিরিয়ে নেয়। দ্বীনের কাজে নিরাপদ পথ হলো—যা প্রমাণিত, তা করা; যা প্রমাণিত নয়, তা ইবাদত হিসেবে না ধরা। এতে আমল পরিষ্কার থাকে এবং দ্বীনের নামে বাড়তি চাপ তৈরি হয় না।"},"teachings":["রাসূলের নির্দেশনা ছাড়া কোনো কাজ ইবাদত হিসেবে গ্রহণযোগ্য নয়।","ভালো নিয়তের পাশাপাশি সঠিক পদ্ধতিও জরুরি।","সুন্নাহর সাথে মিলিয়ে আমল করা নিরাপদ পথ।","নিজের বানানো নিয়মকে দ্বীনের অংশ বলা ঠিক নয়।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E69" s="4" t="n"/>
@@ -2076,7 +2080,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিতাবুল্লাহ ও নবীর হেদায়াত","description":"$book_name$ $hadith_number$ - $chapter_name$. শ্রেষ্ঠ বাণী আল্লাহর কিতাব, শ্রেষ্ঠ হেদায়াত রাসূলের হেদায়াত; বিদআত থেকে সতর্ক থাকার শিক্ষা।"},"heading":{"title":"শ্রেষ্ঠ হেদায়াত: আল্লাহর কিতাব ও রাসূলের সুন্নাহ","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) হামদ ও ছালাতের পর কয়েকটি বড় মূলনীতি বলেছেন। শ্রেষ্ঠ বাণী হলো আল্লাহর কিতাব, আর শ্রেষ্ঠ হেদায়াত হলো মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর হেদায়াত। এর মানে, মুসলিমের পথচলার প্রধান আলো কুরআন ও সুন্নাহ। এরপর তিনি বলেছেন, দ্বীনের মধ্যে নতুন সৃষ্টি নিকৃষ্ট কাজ এবং প্রত্যেক নতুন সৃষ্টি ভ্রষ্টতা। এই হাদিস আমাদের শেখায়, দ্বীনকে সুন্দর করার নামে নতুন নিয়ম বানানো নয়; বরং আল্লাহর কিতাব ও নবীর পথ আঁকড়ে ধরা দরকার। ইবাদত, বিশ্বাস ও জীবনযাপনে সুন্নাহকে গুরুত্ব দিলে মানুষ বিভ্রান্তি থেকে দূরে থাকার সুযোগ পায়।"},"teachings":["আল্লাহর কিতাব মুসলিমের জন্য শ্রেষ্ঠ বাণী।","রাসূলুল্লাহর হেদায়াতই অনুসরণের জন্য শ্রেষ্ঠ পথ।","দ্বীনের মধ্যে নতুন সৃষ্টি থেকে সতর্ক থাকা দরকার।","কুরআন ও সুন্নাহকে জীবনের মূল দিশা বানানো উচিত।"],"related_hadiths":[{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"},{"id":"2697","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিতাবুল্লাহ ও নবীর হেদায়াত","description":"$book_name$ $hadith_number$ - $chapter_name$. শ্রেষ্ঠ বাণী আল্লাহর কিতাব, শ্রেষ্ঠ হেদায়াত রাসূলের হেদায়াত; বিদআত থেকে সতর্ক থাকার শিক্ষা।"},"heading":{"title":"শ্রেষ্ঠ হেদায়াত: আল্লাহর কিতাব ও রাসূলের সুন্নাহ","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) হামদ ও ছালাতের পর কয়েকটি বড় মূলনীতি বলেছেন। শ্রেষ্ঠ বাণী হলো আল্লাহর কিতাব, আর শ্রেষ্ঠ হেদায়াত হলো মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর হেদায়াত। এর মানে, মুসলিমের পথচলার প্রধান আলো কুরআন ও সুন্নাহ। এরপর তিনি বলেছেন, দ্বীনের মধ্যে নতুন সৃষ্টি নিকৃষ্ট কাজ এবং প্রত্যেক নতুন সৃষ্টি ভ্রষ্টতা। এই হাদিস আমাদের শেখায়, দ্বীনকে সুন্দর করার নামে নতুন নিয়ম বানানো নয়; বরং আল্লাহর কিতাব ও নবীর পথ আঁকড়ে ধরা দরকার। ইবাদত, বিশ্বাস ও জীবনযাপনে সুন্নাহকে গুরুত্ব দিলে মানুষ বিভ্রান্তি থেকে দূরে থাকার সুযোগ পায়।"},"teachings":["আল্লাহর কিতাব মুসলিমের জন্য শ্রেষ্ঠ বাণী।","রাসূলুল্লাহর হেদায়াতই অনুসরণের জন্য শ্রেষ্ঠ পথ।","দ্বীনের মধ্যে নতুন সৃষ্টি থেকে সতর্ক থাকা দরকার।","কুরআন ও সুন্নাহকে জীবনের মূল দিশা বানানো উচিত।"],"related_hadiths":[{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E70" s="4" t="n"/>
@@ -2099,7 +2103,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জাহেলী রীতি ও অন্যায় রক্তপাত","description":"$book_name$ $hadith_number$ - $chapter_name$. হারামে অন্যায়, ইসলামে জাহেলী রীতি চাওয়া ও অন্যায় রক্তপাত—এসব থেকে কঠোরভাবে সতর্ক করা হয়েছে।"},"heading":{"title":"জাহেলী রীতি থেকে দূরে থাকা: ইসলামের পরিষ্কার সতর্কতা","description":"এই হাদিসে তিন ধরনের মানুষকে আল্লাহর কাছে সবচেয়ে বেশি ঘৃণিত বলা হয়েছে। প্রথমত, যে হারাম এলাকায় নিষিদ্ধ কাজ করে। দ্বিতীয়ত, যে ইসলামের মধ্যে জাহেলী যুগের রীতি চালু করতে চায়। তৃতীয়ত, যে অন্যায়ভাবে কারো রক্ত চাইতে থাকে শুধু রক্তপাতের উদ্দেশ্যে। এখানে মূল শিক্ষা হলো, ইসলাম মানুষকে পবিত্রতা, ন্যায় ও সুস্থ রীতি শেখায়। জাহেলিয়াত মানে এমন রীতি, যা ইসলামি নীতির বিপরীত। তাই মুসলিম সমাজে অন্যায় রসম, হিংসা, রক্তপাত বা পুরনো অন্ধ অভ্যাসকে ফিরিয়ে আনার চেষ্টা বিপজ্জনক। এই হাদিস আমাদের মনে করিয়ে দেয়, দ্বীনের নামে বা সমাজের নামে কোনো কাজ করা হলেও তা যদি ইসলামের ন্যায়নীতির বিরুদ্ধে যায়, তবে তা বর্জনীয়।"},"teachings":["হারাম এলাকায় নিষিদ্ধ কাজ করা কঠোর সতর্কতার বিষয়।","ইসলামের মধ্যে জাহেলী রীতি ফিরিয়ে আনার চেষ্টা নিন্দনীয়।","অন্যায়ভাবে কারো রক্তপাত চাওয়া বড় অন্যায়।","মুসলিমের কাজ হলো ন্যায়, পবিত্রতা ও ইসলামী রীতি মেনে চলা।"],"related_hadiths":[{"id":"6882","book_id":"1","label":"Sahih Bukhari"},{"id":"2697","book_id":"1","label":"Sahih Bukhari"},{"id":"4385","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জাহেলী রীতি ও অন্যায় রক্তপাত","description":"$book_name$ $hadith_number$ - $chapter_name$. হারামে অন্যায়, ইসলামে জাহেলী রীতি চাওয়া ও অন্যায় রক্তপাত—এসব থেকে কঠোরভাবে সতর্ক করা হয়েছে।"},"heading":{"title":"জাহেলী রীতি থেকে দূরে থাকা: ইসলামের পরিষ্কার সতর্কতা","description":"এই হাদিসে তিন ধরনের মানুষকে আল্লাহর কাছে সবচেয়ে বেশি ঘৃণিত বলা হয়েছে। প্রথমত, যে হারাম এলাকায় নিষিদ্ধ কাজ করে। দ্বিতীয়ত, যে ইসলামের মধ্যে জাহেলী যুগের রীতি চালু করতে চায়। তৃতীয়ত, যে অন্যায়ভাবে কারো রক্ত চাইতে থাকে শুধু রক্তপাতের উদ্দেশ্যে। এখানে মূল শিক্ষা হলো, ইসলাম মানুষকে পবিত্রতা, ন্যায় ও সুস্থ রীতি শেখায়। জাহেলিয়াত মানে এমন রীতি, যা ইসলামি নীতির বিপরীত। তাই মুসলিম সমাজে অন্যায় রসম, হিংসা, রক্তপাত বা পুরনো অন্ধ অভ্যাসকে ফিরিয়ে আনার চেষ্টা বিপজ্জনক। এই হাদিস আমাদের মনে করিয়ে দেয়, দ্বীনের নামে বা সমাজের নামে কোনো কাজ করা হলেও তা যদি ইসলামের ন্যায়নীতির বিরুদ্ধে যায়, তবে তা বর্জনীয়।"},"teachings":["হারাম এলাকায় নিষিদ্ধ কাজ করা কঠোর সতর্কতার বিষয়।","ইসলামের মধ্যে জাহেলী রীতি ফিরিয়ে আনার চেষ্টা নিন্দনীয়।","অন্যায়ভাবে কারো রক্তপাত চাওয়া বড় অন্যায়।","মুসলিমের কাজ হলো ন্যায়, পবিত্রতা ও ইসলামী রীতি মেনে চলা।"],"related_hadiths":[{"id":"6882","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E71" s="4" t="n"/>
@@ -2122,7 +2126,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রাসূলের আনুগত্য ও জান্নাতের পথ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের আনুগত্য জান্নাতের পথে নিয়ে যায়; অবাধ্যতা মানুষকে নিজের জন্য ক্ষতির দিকে ঠেলে দেয়।"},"heading":{"title":"রাসূলের আনুগত্য: জান্নাতের পথে চলার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের সবাই জান্নাতে প্রবেশ করবে, কেবল যে অসম্মত সে ছাড়া। সাহাবীগণ জানতে চাইলেন, কে অসম্মত? তিনি বললেন, যে তাঁর আনুগত্য করবে, সে জান্নাতে প্রবেশ করবে; আর যে তাঁর অবাধ্যতা করবে, সে যেন নিজেই অসম্মত হলো। এই কথায় রাসূলের আনুগত্যের গুরুত্ব পরিষ্কার। মুসলিম পরিচয় শুধু মুখের দাবি নয়; জীবনে নবীর নির্দেশ মানার চেষ্টা থাকতে হবে। সুন্নাহ মেনে চলা, তাঁর নিষেধ থেকে দূরে থাকা এবং তাঁর দেখানো পথে ইবাদত করা—এসবই আনুগত্যের অংশ। হাদিসটি কাউকে হতাশ করার জন্য নয়, বরং মানুষকে রাসূলের পথে ফিরিয়ে আনার জন্য শক্তিশালী স্মরণিকা।"},"teachings":["রাসূলের আনুগত্য জান্নাতের পথ অনুসরণের কারণ।","অবাধ্যতা মানুষকে নিজেই ক্ষতির পথে নিতে পারে।","মুসলিম জীবনে সুন্নাহ মানার চেষ্টা জরুরি।","নবীর নির্দেশকে ভালোবাসা ও মান্য করা ঈমানের দাবি।"],"related_hadiths":[{"id":"7281","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রাসূলের আনুগত্য ও জান্নাতের পথ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের আনুগত্য জান্নাতের পথে নিয়ে যায়; অবাধ্যতা মানুষকে নিজের জন্য ক্ষতির দিকে ঠেলে দেয়।"},"heading":{"title":"রাসূলের আনুগত্য: জান্নাতের পথে চলার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের সবাই জান্নাতে প্রবেশ করবে, কেবল যে অসম্মত সে ছাড়া। সাহাবীগণ জানতে চাইলেন, কে অসম্মত? তিনি বললেন, যে তাঁর আনুগত্য করবে, সে জান্নাতে প্রবেশ করবে; আর যে তাঁর অবাধ্যতা করবে, সে যেন নিজেই অসম্মত হলো। এই কথায় রাসূলের আনুগত্যের গুরুত্ব পরিষ্কার। মুসলিম পরিচয় শুধু মুখের দাবি নয়; জীবনে নবীর নির্দেশ মানার চেষ্টা থাকতে হবে। সুন্নাহ মেনে চলা, তাঁর নিষেধ থেকে দূরে থাকা এবং তাঁর দেখানো পথে ইবাদত করা—এসবই আনুগত্যের অংশ। হাদিসটি কাউকে হতাশ করার জন্য নয়, বরং মানুষকে রাসূলের পথে ফিরিয়ে আনার জন্য শক্তিশালী স্মরণিকা।"},"teachings":["রাসূলের আনুগত্য জান্নাতের পথ অনুসরণের কারণ।","অবাধ্যতা মানুষকে নিজেই ক্ষতির পথে নিতে পারে।","মুসলিম জীবনে সুন্নাহ মানার চেষ্টা জরুরি।","নবীর নির্দেশকে ভালোবাসা ও মান্য করা ঈমানের দাবি।"],"related_hadiths":[{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E72" s="4" t="n"/>
@@ -2145,7 +2149,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জান্নাতের আহ্বান ও নবীর অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. জান্নাতের দাওয়াতে সাড়া দেওয়া মানে মুহাম্মাদকে মানা; তাঁর আনুগত্য আল্লাহর আনুগত্যের সাথে যুক্ত।"},"heading":{"title":"জান্নাতের আহ্বান: মুহাম্মাদের আনুগত্যই আল্লাহর আনুগত্য","description":"এই হাদিসে ফেরেশতাদের কথার মাধ্যমে একটি সুন্দর উদাহরণ এসেছে। এক ব্যক্তি ঘর বানালেন, ভোজের আয়োজন করলেন এবং একজন আহ্বায়ক পাঠালেন। যে আহ্বানে সাড়া দিল, সে ঘরে ঢুকল এবং খাবার পেল; যে সাড়া দিল না, সে ঢুকতেও পারল না, খেতেও পারল না। এরপর ব্যাখ্যা করা হলো—ঘরটি জান্নাত, আহ্বায়ক হলেন মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)। তাই যে মুহাম্মাদের আনুগত্য করল, সে আল্লাহর আনুগত্য করল; আর যে তাঁর অবাধ্য হলো, সে আল্লাহর অবাধ্য হলো। এই হাদিস আমাদের শেখায়, জান্নাতের পথ কল্পনা বা নিজের বানানো নিয়মে নয়; নবীর আহ্বানে সাড়া দেওয়ার মধ্যেই সঠিক পথ।"},"teachings":["মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর আহ্বানে সাড়া দেওয়া আল্লাহর আনুগত্যের অংশ।","জান্নাতের পথে নবীর নির্দেশনা অপরিহার্য।","নবীর অবাধ্যতা আল্লাহর অবাধ্যতার সাথে যুক্ত।","সঠিক পথ বুঝতে রাসূলের দাওয়াতকে গ্রহণ করা দরকার।"],"related_hadiths":[{"id":"7280","book_id":"1","label":"Sahih Bukhari"},{"id":"1988","book_id":"2","label":"Sahih Muslim"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জান্নাতের আহ্বান ও নবীর অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. জান্নাতের দাওয়াতে সাড়া দেওয়া মানে মুহাম্মাদকে মানা; তাঁর আনুগত্য আল্লাহর আনুগত্যের সাথে যুক্ত।"},"heading":{"title":"জান্নাতের আহ্বান: মুহাম্মাদের আনুগত্যই আল্লাহর আনুগত্য","description":"এই হাদিসে ফেরেশতাদের কথার মাধ্যমে একটি সুন্দর উদাহরণ এসেছে। এক ব্যক্তি ঘর বানালেন, ভোজের আয়োজন করলেন এবং একজন আহ্বায়ক পাঠালেন। যে আহ্বানে সাড়া দিল, সে ঘরে ঢুকল এবং খাবার পেল; যে সাড়া দিল না, সে ঢুকতেও পারল না, খেতেও পারল না। এরপর ব্যাখ্যা করা হলো—ঘরটি জান্নাত, আহ্বায়ক হলেন মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)। তাই যে মুহাম্মাদের আনুগত্য করল, সে আল্লাহর আনুগত্য করল; আর যে তাঁর অবাধ্য হলো, সে আল্লাহর অবাধ্য হলো। এই হাদিস আমাদের শেখায়, জান্নাতের পথ কল্পনা বা নিজের বানানো নিয়মে নয়; নবীর আহ্বানে সাড়া দেওয়ার মধ্যেই সঠিক পথ।"},"teachings":["মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর আহ্বানে সাড়া দেওয়া আল্লাহর আনুগত্যের অংশ।","জান্নাতের পথে নবীর নির্দেশনা অপরিহার্য।","নবীর অবাধ্যতা আল্লাহর অবাধ্যতার সাথে যুক্ত।","সঠিক পথ বুঝতে রাসূলের দাওয়াতকে গ্রহণ করা দরকার।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1988","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E73" s="4" t="n"/>
@@ -2168,7 +2172,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইবাদতে মধ্যপন্থা ও সুন্নাহ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের সুন্নাহ হলো ইবাদত, বিশ্রাম, সিয়াম ও বিবাহে ভারসাম্যপূর্ণ পথ; বাড়াবাড়ি নয়।"},"heading":{"title":"ইবাদতে মধ্যপন্থা: রাসূলের সুন্নাহ থেকে মুখ ফিরানো নয়","description":"এই হাদিসে তিনজন ব্যক্তি রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর ইবাদত সম্পর্কে জানতে এসে নিজেদের জন্য কঠোর সিদ্ধান্ত নেয়। একজন বলল, সে সারারাত নামাজ পড়বে; আরেকজন বলল, সবসময় রোজা রাখবে; তৃতীয়জন বলল, কখনো বিয়ে করবে না। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাদের ভুল ঠিক করে দিলেন। তিনি বললেন, তিনি আল্লাহকে বেশি ভয় করেন এবং বেশি পরহেযগার, তবু তিনি রোজা রাখেন আবার ছাড়েন, নামাজ পড়েন আবার ঘুমান, এবং বিবাহ করেছেন। তাই সুন্নাহ মানে অস্বাভাবিক কঠোরতা নয়; বরং আল্লাহর ইবাদত ও মানুষের স্বাভাবিক জীবনের মধ্যে সঠিক ভারসাম্য। এই হাদিস ইবাদতে বাড়াবাড়ি থেকে বাঁচতে শেখায়।"},"teachings":["ইবাদতে অতিরিক্ত বাড়াবাড়ি রাসূলের সুন্নাহ নয়।","রোজা, নামাজ, ঘুম ও বিবাহ—সবকিছুর মধ্যে ভারসাম্য দরকার।","রাসূলুল্লাহর জীবনই আল্লাহভীতির সঠিক নমুনা।","সুন্নাহ থেকে মুখ ফিরিয়ে নিজের বানানো পথ নেওয়া বিপজ্জনক।"],"related_hadiths":[{"id":"3294","book_id":"2","label":"Sahih Muslim"},{"id":"1961","book_id":"1","label":"Sahih Bukhari"},{"id":"1981","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইবাদতে মধ্যপন্থা ও সুন্নাহ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের সুন্নাহ হলো ইবাদত, বিশ্রাম, সিয়াম ও বিবাহে ভারসাম্যপূর্ণ পথ; বাড়াবাড়ি নয়।"},"heading":{"title":"ইবাদতে মধ্যপন্থা: রাসূলের সুন্নাহ থেকে মুখ ফিরানো নয়","description":"এই হাদিসে তিনজন ব্যক্তি রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর ইবাদত সম্পর্কে জানতে এসে নিজেদের জন্য কঠোর সিদ্ধান্ত নেয়। একজন বলল, সে সারারাত নামাজ পড়বে; আরেকজন বলল, সবসময় রোজা রাখবে; তৃতীয়জন বলল, কখনো বিয়ে করবে না। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাদের ভুল ঠিক করে দিলেন। তিনি বললেন, তিনি আল্লাহকে বেশি ভয় করেন এবং বেশি পরহেযগার, তবু তিনি রোজা রাখেন আবার ছাড়েন, নামাজ পড়েন আবার ঘুমান, এবং বিবাহ করেছেন। তাই সুন্নাহ মানে অস্বাভাবিক কঠোরতা নয়; বরং আল্লাহর ইবাদত ও মানুষের স্বাভাবিক জীবনের মধ্যে সঠিক ভারসাম্য। এই হাদিস ইবাদতে বাড়াবাড়ি থেকে বাঁচতে শেখায়।"},"teachings":["ইবাদতে অতিরিক্ত বাড়াবাড়ি রাসূলের সুন্নাহ নয়।","রোজা, নামাজ, ঘুম ও বিবাহ—সবকিছুর মধ্যে ভারসাম্য দরকার।","রাসূলুল্লাহর জীবনই আল্লাহভীতির সঠিক নমুনা।","সুন্নাহ থেকে মুখ ফিরিয়ে নিজের বানানো পথ নেওয়া বিপজ্জনক।"],"related_hadiths":[{"id":"3294","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1961","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1981","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E74" s="4" t="n"/>
@@ -2191,7 +2195,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানতদারি ও অঙ্গীকারের মূল্য","description":"$book_name$ $hadith_number$ - $chapter_name$. যার আমানতদারি নেই তার ঈমান নেই, আর যার অঙ্গীকারের মূল্য নেই তার দ্বীন নেই—এ কঠোর শিক্ষা এসেছে।"},"heading":{"title":"আমানতদারি ও অঙ্গীকার পূরণ: পূর্ণ ঈমানের বড় লক্ষণ","description":"এই হাদিসে আনাস (রাঃ) বলেন, রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব কমই এমন উপদেশ দিয়েছেন, যাতে তিনি বলেননি: যার আমানতদারি নেই তার ঈমান নেই এবং যার অঙ্গীকারের মূল্য নেই তার দ্বীন নেই। এই কথা মুসলিম জীবনে আমানত ও অঙ্গীকারের গুরুত্ব খুব স্পষ্ট করে। আমানত শুধু টাকা বা মাল নয়; দায়িত্ব, কথা, গোপন বিষয় এবং মানুষের অধিকারও আমানতের মধ্যে পড়তে পারে—ইসলামী স্কলারদের মতে। তবে হাদিসের সরাসরি শিক্ষা হলো, আমানত রক্ষা ও অঙ্গীকার পূরণ ছাড়া মানুষের ঈমানি চরিত্র পূর্ণ হয় না। তাই কথা দিলে তা রক্ষা করা এবং দায়িত্ব পেলে তা ঠিকমতো পালন করা জরুরি।"},"teachings":["আমানতদারি ঈমানি চরিত্রের গুরুত্বপূর্ণ অংশ।","অঙ্গীকারের মূল্য না দিলে দ্বীনি আচরণ ক্ষতিগ্রস্ত হয়।","উপদেশে আমানত ও ওয়াদার কথা বারবার স্মরণ করানো হয়েছে।","বিশ্বাসযোগ্য হওয়া মুসলিম জীবনের বড় গুণ।"],"related_hadiths":[{"id":"35","book_id":"14","label":"Mishkat al-Masabih"},{"id":"55","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানতদারি ও অঙ্গীকারের মূল্য","description":"$book_name$ $hadith_number$ - $chapter_name$. যার আমানতদারি নেই তার ঈমান নেই, আর যার অঙ্গীকারের মূল্য নেই তার দ্বীন নেই—এ কঠোর শিক্ষা এসেছে।"},"heading":{"title":"আমানতদারি ও অঙ্গীকার পূরণ: পূর্ণ ঈমানের বড় লক্ষণ","description":"এই হাদিসে আনাস (রাঃ) বলেন, রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব কমই এমন উপদেশ দিয়েছেন, যাতে তিনি বলেননি: যার আমানতদারি নেই তার ঈমান নেই এবং যার অঙ্গীকারের মূল্য নেই তার দ্বীন নেই। এই কথা মুসলিম জীবনে আমানত ও অঙ্গীকারের গুরুত্ব খুব স্পষ্ট করে। আমানত শুধু টাকা বা মাল নয়; দায়িত্ব, কথা, গোপন বিষয় এবং মানুষের অধিকারও আমানতের মধ্যে পড়তে পারে—ইসলামী স্কলারদের মতে। তবে হাদিসের সরাসরি শিক্ষা হলো, আমানত রক্ষা ও অঙ্গীকার পূরণ ছাড়া মানুষের ঈমানি চরিত্র পূর্ণ হয় না। তাই কথা দিলে তা রক্ষা করা এবং দায়িত্ব পেলে তা ঠিকমতো পালন করা জরুরি।"},"teachings":["আমানতদারি ঈমানি চরিত্রের গুরুত্বপূর্ণ অংশ।","অঙ্গীকারের মূল্য না দিলে দ্বীনি আচরণ ক্ষতিগ্রস্ত হয়।","উপদেশে আমানত ও ওয়াদার কথা বারবার স্মরণ করানো হয়েছে।","বিশ্বাসযোগ্য হওয়া মুসলিম জীবনের বড় গুণ।"],"related_hadiths":[{"id":"35","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"55","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -2218,7 +2222,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সৎপথে আহ্বান ও গোনাহের দায়","description":"$book_name$ $hadith_number$ - $chapter_name$. সৎপথে ডাকার সওয়াব আছে, আর পথভ্রষ্টতার দিকে ডাকলে অনুসারীদের মতো গোনাহের দায় আসে।"},"heading":{"title":"সৎপথে আহ্বান: দাওয়াতের সওয়াব ও দায়িত্ব","description":"এই হাদিসে দাওয়াতের বড় দায়িত্ব বোঝানো হয়েছে। যে ব্যক্তি কাউকে সৎ পথের দিকে আহ্বান করে, তার জন্য অনুসারীদের মতো সওয়াব থাকে; অথচ অনুসারীদের সওয়াব কমে না। আবার যে পথভ্রষ্টতার দিকে আহ্বান করে, তার ওপর অনুসারীদের মতো গোনাহ থাকে; অথচ তাদের গোনাহও কমে না। তাই কথা, লেখা, শিক্ষা, পোস্ট, পরামর্শ—সবকিছুতেই সতর্ক থাকা দরকার। মানুষকে ভালো কাজে ডাকা শুধু সুন্দর কাজ নয়, এটি দায়িত্বও। একইভাবে ভুল পথ, বিদআত, পাপ বা বিভ্রান্তি ছড়ানো হালকা বিষয় নয়। এই হাদিস আমাদের শেখায়, প্রভাবশালী কথা বলার আগে ভাবতে হবে—এটি মানুষকে আল্লাহর পথে ডাকছে, নাকি ভুল পথে ঠেলে দিচ্ছে?"},"teachings":["সৎপথে আহ্বান করলে অনুসারীদের মতো সওয়াবের অংশ পাওয়া যায়।","ভুল পথে ডাকলে অনুসারীদের মতো গোনাহের দায় আসতে পারে।","দাওয়াত, লেখা ও পরামর্শে সতর্ক থাকা জরুরি।","সওয়াব বা গোনাহ কারও থেকে কমে না; প্রত্যেকের নিজ নিজ হিসাব থাকে।"],"related_hadiths":[{"id":"2697","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সৎপথে আহ্বান ও গোনাহের দায়","description":"$book_name$ $hadith_number$ - $chapter_name$. সৎপথে ডাকার সওয়াব আছে, আর পথভ্রষ্টতার দিকে ডাকলে অনুসারীদের মতো গোনাহের দায় আসে।"},"heading":{"title":"সৎপথে আহ্বান: দাওয়াতের সওয়াব ও দায়িত্ব","description":"এই হাদিসে দাওয়াতের বড় দায়িত্ব বোঝানো হয়েছে। যে ব্যক্তি কাউকে সৎ পথের দিকে আহ্বান করে, তার জন্য অনুসারীদের মতো সওয়াব থাকে; অথচ অনুসারীদের সওয়াব কমে না। আবার যে পথভ্রষ্টতার দিকে আহ্বান করে, তার ওপর অনুসারীদের মতো গোনাহ থাকে; অথচ তাদের গোনাহও কমে না। তাই কথা, লেখা, শিক্ষা, পোস্ট, পরামর্শ—সবকিছুতেই সতর্ক থাকা দরকার। মানুষকে ভালো কাজে ডাকা শুধু সুন্দর কাজ নয়, এটি দায়িত্বও। একইভাবে ভুল পথ, বিদআত, পাপ বা বিভ্রান্তি ছড়ানো হালকা বিষয় নয়। এই হাদিস আমাদের শেখায়, প্রভাবশালী কথা বলার আগে ভাবতে হবে—এটি মানুষকে আল্লাহর পথে ডাকছে, নাকি ভুল পথে ঠেলে দিচ্ছে?"},"teachings":["সৎপথে আহ্বান করলে অনুসারীদের মতো সওয়াবের অংশ পাওয়া যায়।","ভুল পথে ডাকলে অনুসারীদের মতো গোনাহের দায় আসতে পারে।","দাওয়াত, লেখা ও পরামর্শে সতর্ক থাকা জরুরি।","সওয়াব বা গোনাহ কারও থেকে কমে না; প্রত্যেকের নিজ নিজ হিসাব থাকে।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E76" s="4" t="n"/>
@@ -2241,7 +2245,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অপরিচিতদের জন্য সুসংবাদ","description":"$book_name$ $hadith_number$ - $chapter_name$. ইসলাম অপরিচিতভাবে শুরু হয়েছে এবং আবার অপরিচিত হবে; সুন্নাহ ঠিক রাখাদের জন্য সুসংবাদ।"},"heading":{"title":"ইসলাম অপরিচিত হবে: সুন্নাহ আঁকড়ে থাকা মানুষের মর্যাদা","description":"এই হাদিসে বলা হয়েছে, ইসলাম মুষ্টিমেয় লোকদের মাধ্যমে শুরু হয়েছে এবং একসময় আবার সেইরকম অপরিচিত অবস্থায় ফিরে আসবে। এরপর সুসংবাদ দেওয়া হয়েছে ‘গুরাবা’ বা সেই মুষ্টিমেয় লোকদের জন্য। তিরমিযীর বর্ণনায় এসেছে, তারা হলো এমন মানুষ, যারা রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর পরে মানুষ সুন্নাহর যে বিষয়গুলো নষ্ট করেছে, সেগুলো সংশোধনের চেষ্টা করে। এখানে শিক্ষা হলো, সত্য পথ অনেক সময় সংখ্যায় কম মানুষের কাছে থাকে। মানুষের ভিড়, প্রচলন বা জনপ্রিয়তা সবসময় সঠিকতার প্রমাণ নয়। মুসলিমের কাজ হলো কুরআন ও সুন্নাহর আলোকে নিজেকে ঠিক রাখা এবং ভদ্রভাবে মানুষকে সঠিক পথে ডাকতে থাকা।"},"teachings":["ইসলাম শুরুতে অপরিচিত ছিল এবং আবার অপরিচিত অবস্থায় ফিরবে।","সুন্নাহ ঠিক রাখার চেষ্টা করা প্রশংসনীয় কাজ।","সংখ্যা বেশি হলেই কোনো পথ সঠিক হয়ে যায় না।","সত্যের পথে থাকলে ধৈর্য ও বিনয় দরকার।"],"related_hadiths":[{"id":"267","book_id":"2","label":"Sahih Muslim"},{"id":"268","book_id":"2","label":"Sahih Muslim"},{"id":"2630","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অপরিচিতদের জন্য সুসংবাদ","description":"$book_name$ $hadith_number$ - $chapter_name$. ইসলাম অপরিচিতভাবে শুরু হয়েছে এবং আবার অপরিচিত হবে; সুন্নাহ ঠিক রাখাদের জন্য সুসংবাদ।"},"heading":{"title":"ইসলাম অপরিচিত হবে: সুন্নাহ আঁকড়ে থাকা মানুষের মর্যাদা","description":"এই হাদিসে বলা হয়েছে, ইসলাম মুষ্টিমেয় লোকদের মাধ্যমে শুরু হয়েছে এবং একসময় আবার সেইরকম অপরিচিত অবস্থায় ফিরে আসবে। এরপর সুসংবাদ দেওয়া হয়েছে ‘গুরাবা’ বা সেই মুষ্টিমেয় লোকদের জন্য। তিরমিযীর বর্ণনায় এসেছে, তারা হলো এমন মানুষ, যারা রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর পরে মানুষ সুন্নাহর যে বিষয়গুলো নষ্ট করেছে, সেগুলো সংশোধনের চেষ্টা করে। এখানে শিক্ষা হলো, সত্য পথ অনেক সময় সংখ্যায় কম মানুষের কাছে থাকে। মানুষের ভিড়, প্রচলন বা জনপ্রিয়তা সবসময় সঠিকতার প্রমাণ নয়। মুসলিমের কাজ হলো কুরআন ও সুন্নাহর আলোকে নিজেকে ঠিক রাখা এবং ভদ্রভাবে মানুষকে সঠিক পথে ডাকতে থাকা।"},"teachings":["ইসলাম শুরুতে অপরিচিত ছিল এবং আবার অপরিচিত অবস্থায় ফিরবে।","সুন্নাহ ঠিক রাখার চেষ্টা করা প্রশংসনীয় কাজ।","সংখ্যা বেশি হলেই কোনো পথ সঠিক হয়ে যায় না।","সত্যের পথে থাকলে ধৈর্য ও বিনয় দরকার।"],"related_hadiths":[{"id":"267","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"268","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2630","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E77" s="4" t="n"/>
@@ -2264,7 +2268,7 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মতভেদে সুন্নাহ আঁকড়ে ধরা","description":"$book_name$ $hadith_number$ - $chapter_name$. মতভেদ দেখা দিলে রাসূলের সুন্নাহ ও খুলাফায়ে রাশেদীনের পথ শক্তভাবে ধরার উপদেশ দেওয়া হয়েছে।"},"heading":{"title":"মতভেদের সময়ে করণীয়: সুন্নাহকে মাড়ির দাঁত দিয়ে আঁকড়ে ধরা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর একটি গভীর উপদেশ এসেছে। তিনি তাকওয়া অবলম্বন, আমীরের কথা শোনা ও মানার কথা বলেছেন, যদিও তিনি হাবশী গোলাম হন। এরপর জানিয়েছেন, তাঁর পরে যারা বেঁচে থাকবে তারা অনেক মতভেদ দেখবে। সেই সময়ে করণীয় হলো রাসূলের সুন্নাহ এবং সুপথপ্রাপ্ত খুলাফায়ে রাশেদীনের সুন্নাহ শক্তভাবে ধরে রাখা। তিনি আরও সতর্ক করেছেন, দ্বীনের নতুন সৃষ্টি থেকে দূরে থাকতে; কারণ প্রত্যেক নতুন সৃষ্টি বিদআত, আর প্রত্যেক বিদআত পথভ্রষ্টতা। এই হাদিস মুসলিমকে আবেগ নয়, প্রমাণিত সুন্নাহর দিকে ফিরিয়ে দেয়। মতভেদে বিভ্রান্ত না হয়ে তাকওয়া, আনুগত্য ও সুন্নাহ—এই তিনটি বিষয় ধরে রাখা দরকার।"},"teachings":["মতভেদের সময় রাসূলের সুন্নাহ শক্তভাবে আঁকড়ে ধরতে হবে।","খুলাফায়ে রাশেদীনের পথও অনুসরণের গুরুত্বপূর্ণ দিশা।","দ্বীনের নতুন সৃষ্টি থেকে সতর্ক থাকা দরকার।","তাকওয়া ও বৈধ নেতৃত্বের আনুগত্য মুসলিম জীবনে গুরুত্বপূর্ণ।"],"related_hadiths":[{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"},{"id":"2697","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মতভেদে সুন্নাহ আঁকড়ে ধরা","description":"$book_name$ $hadith_number$ - $chapter_name$. মতভেদ দেখা দিলে রাসূলের সুন্নাহ ও খুলাফায়ে রাশেদীনের পথ শক্তভাবে ধরার উপদেশ দেওয়া হয়েছে।"},"heading":{"title":"মতভেদের সময়ে করণীয়: সুন্নাহকে মাড়ির দাঁত দিয়ে আঁকড়ে ধরা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর একটি গভীর উপদেশ এসেছে। তিনি তাকওয়া অবলম্বন, আমীরের কথা শোনা ও মানার কথা বলেছেন, যদিও তিনি হাবশী গোলাম হন। এরপর জানিয়েছেন, তাঁর পরে যারা বেঁচে থাকবে তারা অনেক মতভেদ দেখবে। সেই সময়ে করণীয় হলো রাসূলের সুন্নাহ এবং সুপথপ্রাপ্ত খুলাফায়ে রাশেদীনের সুন্নাহ শক্তভাবে ধরে রাখা। তিনি আরও সতর্ক করেছেন, দ্বীনের নতুন সৃষ্টি থেকে দূরে থাকতে; কারণ প্রত্যেক নতুন সৃষ্টি বিদআত, আর প্রত্যেক বিদআত পথভ্রষ্টতা। এই হাদিস মুসলিমকে আবেগ নয়, প্রমাণিত সুন্নাহর দিকে ফিরিয়ে দেয়। মতভেদে বিভ্রান্ত না হয়ে তাকওয়া, আনুগত্য ও সুন্নাহ—এই তিনটি বিষয় ধরে রাখা দরকার।"},"teachings":["মতভেদের সময় রাসূলের সুন্নাহ শক্তভাবে আঁকড়ে ধরতে হবে।","খুলাফায়ে রাশেদীনের পথও অনুসরণের গুরুত্বপূর্ণ দিশা।","দ্বীনের নতুন সৃষ্টি থেকে সতর্ক থাকা দরকার।","তাকওয়া ও বৈধ নেতৃত্বের আনুগত্য মুসলিম জীবনে গুরুত্বপূর্ণ।"],"related_hadiths":[{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E78" s="4" t="n"/>
@@ -2287,7 +2291,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পরিচ্ছন্ন দ্বীন ও নবীর অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের আনা উজ্জ্বল দ্বীন যথেষ্ট; মূসা জীবিত থাকলেও তাঁকে মুহাম্মাদের অনুসরণ করতে হতো।"},"heading":{"title":"পরিচ্ছন্ন দ্বীন: রাসূলের অনুসরণই মুসলিমের নিরাপদ পথ","description":"এই হাদিসে ওমর (রাঃ) ইহুদীদের কিছু পুরনো ধর্মীয় কাহিনী লিখে রাখার অনুমতি চাইলে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাঁকে সতর্ক করেন। তিনি বলেন, তোমরা কি দিকভ্রান্ত হয়েছ, যেমন ইহুদী-নাছারারা দিকভ্রান্ত হয়েছে? এরপর তিনি জানান, তিনি উজ্জ্বল ও পরিচ্ছন্ন দ্বীন নিয়ে এসেছেন। এমনকি মূসা (আলাইহিস সালাম) যদি তখন জীবিত থাকতেন, তাঁর পক্ষেও মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ ছাড়া পথ থাকত না। এখানে শিক্ষা হলো, মুসলিমের জন্য রাসূলের আনা দ্বীন পূর্ণ ও পরিষ্কার। তাই দ্বীনের দিশা নেওয়ার ক্ষেত্রে অপ্রয়োজনীয়ভাবে অন্য ধর্মীয় কাহিনীর প্রতি আকর্ষণ রাখা ঠিক নয়। মুসলিমের মূল ভরসা কুরআন ও সুন্নাহ।"},"teachings":["রাসূলুল্লাহর আনা দ্বীন উজ্জ্বল ও পরিচ্ছন্ন।","দ্বীনের দিশা নিতে কুরআন ও সুন্নাহ যথেষ্ট পথনির্দেশ।","আগের জাতির দিকভ্রান্ত পথ অনুসরণ থেকে সতর্ক থাকতে হবে।","মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ সব মুসলিমের জন্য মূল পথ।"],"related_hadiths":[{"id":"7280","book_id":"1","label":"Sahih Bukhari"},{"id":"7281","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পরিচ্ছন্ন দ্বীন ও নবীর অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের আনা উজ্জ্বল দ্বীন যথেষ্ট; মূসা জীবিত থাকলেও তাঁকে মুহাম্মাদের অনুসরণ করতে হতো।"},"heading":{"title":"পরিচ্ছন্ন দ্বীন: রাসূলের অনুসরণই মুসলিমের নিরাপদ পথ","description":"এই হাদিসে ওমর (রাঃ) ইহুদীদের কিছু পুরনো ধর্মীয় কাহিনী লিখে রাখার অনুমতি চাইলে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাঁকে সতর্ক করেন। তিনি বলেন, তোমরা কি দিকভ্রান্ত হয়েছ, যেমন ইহুদী-নাছারারা দিকভ্রান্ত হয়েছে? এরপর তিনি জানান, তিনি উজ্জ্বল ও পরিচ্ছন্ন দ্বীন নিয়ে এসেছেন। এমনকি মূসা (আলাইহিস সালাম) যদি তখন জীবিত থাকতেন, তাঁর পক্ষেও মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ ছাড়া পথ থাকত না। এখানে শিক্ষা হলো, মুসলিমের জন্য রাসূলের আনা দ্বীন পূর্ণ ও পরিষ্কার। তাই দ্বীনের দিশা নেওয়ার ক্ষেত্রে অপ্রয়োজনীয়ভাবে অন্য ধর্মীয় কাহিনীর প্রতি আকর্ষণ রাখা ঠিক নয়। মুসলিমের মূল ভরসা কুরআন ও সুন্নাহ।"},"teachings":["রাসূলুল্লাহর আনা দ্বীন উজ্জ্বল ও পরিচ্ছন্ন।","দ্বীনের দিশা নিতে কুরআন ও সুন্নাহ যথেষ্ট পথনির্দেশ।","আগের জাতির দিকভ্রান্ত পথ অনুসরণ থেকে সতর্ক থাকতে হবে।","মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ সব মুসলিমের জন্য মূল পথ।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E79" s="4" t="n"/>
@@ -2310,7 +2314,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুরআন ও সুন্নাহ আঁকড়ে ধরা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর কিতাব ও রাসূলের সুন্নাহ শক্তভাবে ধরলে সঠিক পথে থাকার দিশা পাওয়া যায়।"},"heading":{"title":"কুরআন ও সুন্নাহ: পথভ্রষ্টতা থেকে বাঁচার মূল দিশা","description":"এই বর্ণনায় রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) দুইটি বিষয় আঁকড়ে ধরার কথা বলেছেন—আল্লাহর কিতাব এবং তাঁর রাসূলের সুন্নাত। যতদিন মুসলিমরা এই দুইটি শক্তভাবে ধরে রাখবে, তারা পথভ্রষ্ট হবে না—এটাই হাদিসের মূল শিক্ষা। কুরআন মুসলিমের বিশ্বাস, ইবাদত ও জীবনযাপনের মূল আলো। আর সুন্নাহ দেখায়, কুরআনের নির্দেশ বাস্তবে কীভাবে পালন করতে হয়। তাই শুধু কুরআনের নাম নেওয়া যথেষ্ট নয়, আবার সুন্নাহকে অবহেলা করাও ঠিক নয়। দুইটিকে একসাথে সম্মান ও অনুসরণ করতে হবে। এই হাদিস আমাদের আমলের মানদণ্ড পরিষ্কার করে—যে কথা, কাজ বা রীতি কুরআন ও সুন্নাহর সাথে মেলে, সেটিই নিরাপদ।"},"teachings":["আল্লাহর কিতাব মুসলিমের প্রধান পথনির্দেশ।","রাসূলের সুন্নাহ কুরআন অনুযায়ী চলার বাস্তব পথ দেখায়।","কুরআন ও সুন্নাহ একসাথে আঁকড়ে ধরা দরকার।","দ্বীনের কাজে সঠিক মানদণ্ড হলো কিতাব ও সুন্নাহ।"],"related_hadiths":[{"id":"7280","book_id":"1","label":"Sahih Bukhari"},{"id":"7281","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুরআন ও সুন্নাহ আঁকড়ে ধরা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর কিতাব ও রাসূলের সুন্নাহ শক্তভাবে ধরলে সঠিক পথে থাকার দিশা পাওয়া যায়।"},"heading":{"title":"কুরআন ও সুন্নাহ: পথভ্রষ্টতা থেকে বাঁচার মূল দিশা","description":"এই বর্ণনায় রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) দুইটি বিষয় আঁকড়ে ধরার কথা বলেছেন—আল্লাহর কিতাব এবং তাঁর রাসূলের সুন্নাত। যতদিন মুসলিমরা এই দুইটি শক্তভাবে ধরে রাখবে, তারা পথভ্রষ্ট হবে না—এটাই হাদিসের মূল শিক্ষা। কুরআন মুসলিমের বিশ্বাস, ইবাদত ও জীবনযাপনের মূল আলো। আর সুন্নাহ দেখায়, কুরআনের নির্দেশ বাস্তবে কীভাবে পালন করতে হয়। তাই শুধু কুরআনের নাম নেওয়া যথেষ্ট নয়, আবার সুন্নাহকে অবহেলা করাও ঠিক নয়। দুইটিকে একসাথে সম্মান ও অনুসরণ করতে হবে। এই হাদিস আমাদের আমলের মানদণ্ড পরিষ্কার করে—যে কথা, কাজ বা রীতি কুরআন ও সুন্নাহর সাথে মেলে, সেটিই নিরাপদ।"},"teachings":["আল্লাহর কিতাব মুসলিমের প্রধান পথনির্দেশ।","রাসূলের সুন্নাহ কুরআন অনুযায়ী চলার বাস্তব পথ দেখায়।","কুরআন ও সুন্নাহ একসাথে আঁকড়ে ধরা দরকার।","দ্বীনের কাজে সঠিক মানদণ্ড হলো কিতাব ও সুন্নাহ।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E80" s="4" t="n"/>
@@ -2333,7 +2337,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিদআত করলে সুন্নাহ হারানোর আশঙ্কা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীনে বিদআত চালু হলে সুন্নাহ হারানোর ভয় আছে; তাই প্রমাণিত আমলকে গুরুত্ব দেওয়া জরুরি।"},"heading":{"title":"বিদআত ও সুন্নাহ: নতুন আমলে পুরনো সুন্নাহ হারানোর ভয়","description":"এই বর্ণনায় বলা হয়েছে, কোনো সম্প্রদায় যখন তাদের দ্বীনের মধ্যে বিদআত সৃষ্টি করে, তখন আল্লাহ তাদের মধ্য থেকে সেই পরিমাণ সুন্নাত উঠিয়ে নেন; এরপর তা কিয়ামত পর্যন্ত আর ফিরে আসে না। এই কথার মূল শিক্ষা হলো, বিদআত শুধু একটি বাড়তি কাজ নয়; এটি সুন্নাহর জায়গা দখল করে নিতে পারে। মানুষ যখন নতুন বানানো আমলে ব্যস্ত হয়ে যায়, তখন রাসূলের শেখানো সহজ ও প্রমাণিত আমল অবহেলিত হয়। তাই দ্বীনের নামে নতুন রীতি যোগ করাকে হালকা করে দেখা ঠিক নয়। মুসলিমের জন্য নিরাপদ পথ হলো, প্রমাণিত সুন্নাহ শিখে সেটির ওপর আমল করা। যত বেশি সুন্নাহ জীবিত থাকবে, তত বেশি দ্বীনের আসল সৌন্দর্য মানুষের জীবনে থাকবে।"},"teachings":["বিদআত চালু হলে সুন্নাহ অবহেলিত হওয়ার ভয় থাকে।","দ্বীনের নতুন রীতি সুন্নাহর জায়গা দখল করতে পারে।","প্রমাণিত আমলকে অগ্রাধিকার দেওয়া জরুরি।","সুন্নাহ জীবিত রাখা মুসলিম সমাজের বড় দায়িত্ব।"],"related_hadiths":[{"id":"2697","book_id":"1","label":"Sahih Bukhari"},{"id":"4385","book_id":"2","label":"Sahih Muslim"},{"id":"42","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিদআত করলে সুন্নাহ হারানোর আশঙ্কা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীনে বিদআত চালু হলে সুন্নাহ হারানোর ভয় আছে; তাই প্রমাণিত আমলকে গুরুত্ব দেওয়া জরুরি।"},"heading":{"title":"বিদআত ও সুন্নাহ: নতুন আমলে পুরনো সুন্নাহ হারানোর ভয়","description":"এই বর্ণনায় বলা হয়েছে, কোনো সম্প্রদায় যখন তাদের দ্বীনের মধ্যে বিদআত সৃষ্টি করে, তখন আল্লাহ তাদের মধ্য থেকে সেই পরিমাণ সুন্নাত উঠিয়ে নেন; এরপর তা কিয়ামত পর্যন্ত আর ফিরে আসে না। এই কথার মূল শিক্ষা হলো, বিদআত শুধু একটি বাড়তি কাজ নয়; এটি সুন্নাহর জায়গা দখল করে নিতে পারে। মানুষ যখন নতুন বানানো আমলে ব্যস্ত হয়ে যায়, তখন রাসূলের শেখানো সহজ ও প্রমাণিত আমল অবহেলিত হয়। তাই দ্বীনের নামে নতুন রীতি যোগ করাকে হালকা করে দেখা ঠিক নয়। মুসলিমের জন্য নিরাপদ পথ হলো, প্রমাণিত সুন্নাহ শিখে সেটির ওপর আমল করা। যত বেশি সুন্নাহ জীবিত থাকবে, তত বেশি দ্বীনের আসল সৌন্দর্য মানুষের জীবনে থাকবে।"},"teachings":["বিদআত চালু হলে সুন্নাহ অবহেলিত হওয়ার ভয় থাকে।","দ্বীনের নতুন রীতি সুন্নাহর জায়গা দখল করতে পারে।","প্রমাণিত আমলকে অগ্রাধিকার দেওয়া জরুরি।","সুন্নাহ জীবিত রাখা মুসলিম সমাজের বড় দায়িত্ব।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E81" s="4" t="n"/>
@@ -2356,7 +2360,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মূসার অনুসরণ নয়, মুহাম্মাদের অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. নবুঅতের পর মুহাম্মাদকে ছেড়ে অন্য পথ অনুসরণ করলে সরল পথ থেকে বিচ্যুতির সতর্কতা এসেছে।"},"heading":{"title":"মুহাম্মাদের অনুসরণ: সরল পথে থাকার মূল শর্ত","description":"এই বর্ণনায় রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কসম করে বলেছেন, যদি মূসা (আলাইহিস সালাম) মানুষের সামনে উপস্থিত হতেন এবং মানুষ তাঁকে অনুসরণ করে মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে ছেড়ে দিত, তাহলে তারা সরল পথ থেকে বিচ্যুত হতো। তিনি আরও বলেন, মূসা যদি জীবিত থাকতেন এবং তাঁর নবুঅতকাল পেতেন, তাহলে তিনিও তাঁকে অনুসরণ করতেন। এখানে মূল শিক্ষা হলো, শেষ নবী হিসেবে মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ মুসলিমের জন্য অপরিহার্য। অন্য নবীদের প্রতি ঈমান রাখা জরুরি, কিন্তু শরীআতের অনুসরণ হবে শেষ রাসূলের পথে। তাই দ্বীনের বিষয়ে নিরাপদ পথ হলো তাঁর সুন্নাহকে মানা এবং তাঁর নির্দেশকে অগ্রাধিকার দেওয়া।"},"teachings":["শেষ নবীর শরীআত অনুসরণ করা মুসলিমের দায়িত্ব।","মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে ছেড়ে অন্য পথ নেওয়া বিচ্যুতির কারণ।","আগের নবীদের প্রতি ঈমান থাকবে, কিন্তু অনুসরণ হবে শেষ রাসূলের শরীআতের।","সরল পথে থাকতে নবীর সুন্নাহকে অগ্রাধিকার দিতে হবে।"],"related_hadiths":[{"id":"7280","book_id":"1","label":"Sahih Bukhari"},{"id":"7281","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মূসার অনুসরণ নয়, মুহাম্মাদের অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. নবুঅতের পর মুহাম্মাদকে ছেড়ে অন্য পথ অনুসরণ করলে সরল পথ থেকে বিচ্যুতির সতর্কতা এসেছে।"},"heading":{"title":"মুহাম্মাদের অনুসরণ: সরল পথে থাকার মূল শর্ত","description":"এই বর্ণনায় রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কসম করে বলেছেন, যদি মূসা (আলাইহিস সালাম) মানুষের সামনে উপস্থিত হতেন এবং মানুষ তাঁকে অনুসরণ করে মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে ছেড়ে দিত, তাহলে তারা সরল পথ থেকে বিচ্যুত হতো। তিনি আরও বলেন, মূসা যদি জীবিত থাকতেন এবং তাঁর নবুঅতকাল পেতেন, তাহলে তিনিও তাঁকে অনুসরণ করতেন। এখানে মূল শিক্ষা হলো, শেষ নবী হিসেবে মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ মুসলিমের জন্য অপরিহার্য। অন্য নবীদের প্রতি ঈমান রাখা জরুরি, কিন্তু শরীআতের অনুসরণ হবে শেষ রাসূলের পথে। তাই দ্বীনের বিষয়ে নিরাপদ পথ হলো তাঁর সুন্নাহকে মানা এবং তাঁর নির্দেশকে অগ্রাধিকার দেওয়া।"},"teachings":["শেষ নবীর শরীআত অনুসরণ করা মুসলিমের দায়িত্ব।","মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে ছেড়ে অন্য পথ নেওয়া বিচ্যুতির কারণ।","আগের নবীদের প্রতি ঈমান থাকবে, কিন্তু অনুসরণ হবে শেষ রাসূলের শরীআতের।","সরল পথে থাকতে নবীর সুন্নাহকে অগ্রাধিকার দিতে হবে।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E82" s="4" t="n"/>
@@ -2379,7 +2383,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদীনার সম্মান ও প্রতিশ্রুতি রক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদীনার সম্মান, বিদআত থেকে বিরত থাকা ও মুসলমানের প্রতিশ্রুতি রক্ষার কঠোর শিক্ষা এসেছে।"},"heading":{"title":"মদীনার মর্যাদা: বিদআত, আশ্রয় ও প্রতিশ্রুতি ভঙ্গের সতর্কতা","description":"এই দীর্ঘ হাদিসে আলী (রাঃ) একটি লিখিত কাগজের কথা বলেন, যাতে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কয়েকটি গুরুত্বপূর্ণ নির্দেশ ছিল। এর মধ্যে আছে, মদীনা আইর থেকে সওর পর্যন্ত সম্মানার্হ এলাকা। সেখানে কেউ বিদআত সৃষ্টি করলে বা বিদআত সৃষ্টিকারীকে আশ্রয় দিলে তার ওপর কঠোর লা‘নতের কথা এসেছে। আরও বলা হয়েছে, মুসলমানদের প্রতিশ্রুতি এক; তাদের ক্ষুদ্র ব্যক্তিও সেই প্রতিশ্রুতির চেষ্টা করতে পারে। যে মুসলমানের প্রতিশ্রুতি ভঙ্গ করে, তার ব্যাপারেও কঠোর সতর্কতা এসেছে। এই হাদিস মদীনার মর্যাদা, দ্বীনে নতুন কাজের ভয়াবহতা এবং সামাজিক অঙ্গীকার রক্ষার গুরুত্ব একসাথে শেখায়। মুসলিমের কথা, আশ্রয় ও প্রতিশ্রুতি হালকা বিষয় নয়।"},"teachings":["মদীনা সম্মানার্হ এলাকা; সেখানে অন্যায় ও বিদআত থেকে সতর্ক থাকা দরকার।","বিদআতকারীকে আশ্রয় দেওয়া কঠোর সতর্কতার বিষয়।","মুসলমানের প্রতিশ্রুতি রক্ষা করা গুরুত্বপূর্ণ দায়িত্ব।","অন্যায়ভাবে সম্পর্ক বা আনুগত্য বদল করাও নিন্দনীয়।"],"related_hadiths":[{"id":"2697","book_id":"1","label":"Sahih Bukhari"},{"id":"4385","book_id":"2","label":"Sahih Muslim"},{"id":"6882","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদীনার সম্মান ও প্রতিশ্রুতি রক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদীনার সম্মান, বিদআত থেকে বিরত থাকা ও মুসলমানের প্রতিশ্রুতি রক্ষার কঠোর শিক্ষা এসেছে।"},"heading":{"title":"মদীনার মর্যাদা: বিদআত, আশ্রয় ও প্রতিশ্রুতি ভঙ্গের সতর্কতা","description":"এই দীর্ঘ হাদিসে আলী (রাঃ) একটি লিখিত কাগজের কথা বলেন, যাতে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কয়েকটি গুরুত্বপূর্ণ নির্দেশ ছিল। এর মধ্যে আছে, মদীনা আইর থেকে সওর পর্যন্ত সম্মানার্হ এলাকা। সেখানে কেউ বিদআত সৃষ্টি করলে বা বিদআত সৃষ্টিকারীকে আশ্রয় দিলে তার ওপর কঠোর লা‘নতের কথা এসেছে। আরও বলা হয়েছে, মুসলমানদের প্রতিশ্রুতি এক; তাদের ক্ষুদ্র ব্যক্তিও সেই প্রতিশ্রুতির চেষ্টা করতে পারে। যে মুসলমানের প্রতিশ্রুতি ভঙ্গ করে, তার ব্যাপারেও কঠোর সতর্কতা এসেছে। এই হাদিস মদীনার মর্যাদা, দ্বীনে নতুন কাজের ভয়াবহতা এবং সামাজিক অঙ্গীকার রক্ষার গুরুত্ব একসাথে শেখায়। মুসলিমের কথা, আশ্রয় ও প্রতিশ্রুতি হালকা বিষয় নয়।"},"teachings":["মদীনা সম্মানার্হ এলাকা; সেখানে অন্যায় ও বিদআত থেকে সতর্ক থাকা দরকার।","বিদআতকারীকে আশ্রয় দেওয়া কঠোর সতর্কতার বিষয়।","মুসলমানের প্রতিশ্রুতি রক্ষা করা গুরুত্বপূর্ণ দায়িত্ব।","অন্যায়ভাবে সম্পর্ক বা আনুগত্য বদল করাও নিন্দনীয়।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6882","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E83" s="4" t="n"/>
@@ -2402,7 +2406,7 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিতাব ও নবীর সুন্নাহর দিশা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর কিতাব ও নবীর সুন্নাহ শক্তভাবে ধরলে পথভ্রষ্টতা থেকে বাঁচার দিশা পাওয়া যায়।"},"heading":{"title":"কিতাব ও নবীর সুন্নাহ: পথভ্রষ্টতা থেকে বাঁচার দিশা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তিনি উম্মতের মাঝে এমন জিনিস রেখে যাচ্ছেন, যা শক্তভাবে ধরলে তারা পথভ্রষ্ট হবে না—আল্লাহর কিতাব এবং তাঁর নবীর সুন্নাত। এখানে মুসলিম জীবনের মূল ভিত্তি স্পষ্ট করা হয়েছে। কুরআন নির্দেশ দেয়, আর সুন্নাহ সেই নির্দেশের বাস্তব রূপ শেখায়। কেউ যদি শুধু নিজের মত, সমাজের প্রচলন বা আবেগকে ধর্মের মানদণ্ড বানায়, তাহলে ভুলের আশঙ্কা থাকে। কিন্তু কিতাব ও সুন্নাহকে মানদণ্ড বানালে পথ পরিষ্কার হয়। এই হাদিস আমাদের শেখায়, মতভেদ, সন্দেহ বা নতুন রীতির ভিড়ে নিরাপদ আশ্রয় হলো আল্লাহর কিতাব ও নবীর প্রমাণিত সুন্নাহ।"},"teachings":["আল্লাহর কিতাব ও নবীর সুন্নাহ মুসলিমের মূল পথনির্দেশ।","পথভ্রষ্টতা থেকে বাঁচতে কিতাব ও সুন্নাহ আঁকড়ে ধরতে হবে।","দ্বীনের মানদণ্ড সমাজের প্রচলন নয়, প্রমাণিত দলিল।","সুন্নাহ ছাড়া কুরআনের বাস্তব আমল বোঝা অসম্পূর্ণ হয়ে যায়।"],"related_hadiths":[{"id":"7280","book_id":"1","label":"Sahih Bukhari"},{"id":"7281","book_id":"1","label":"Sahih Bukhari"},{"id":"2676","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিতাব ও নবীর সুন্নাহর দিশা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর কিতাব ও নবীর সুন্নাহ শক্তভাবে ধরলে পথভ্রষ্টতা থেকে বাঁচার দিশা পাওয়া যায়।"},"heading":{"title":"কিতাব ও নবীর সুন্নাহ: পথভ্রষ্টতা থেকে বাঁচার দিশা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তিনি উম্মতের মাঝে এমন জিনিস রেখে যাচ্ছেন, যা শক্তভাবে ধরলে তারা পথভ্রষ্ট হবে না—আল্লাহর কিতাব এবং তাঁর নবীর সুন্নাত। এখানে মুসলিম জীবনের মূল ভিত্তি স্পষ্ট করা হয়েছে। কুরআন নির্দেশ দেয়, আর সুন্নাহ সেই নির্দেশের বাস্তব রূপ শেখায়। কেউ যদি শুধু নিজের মত, সমাজের প্রচলন বা আবেগকে ধর্মের মানদণ্ড বানায়, তাহলে ভুলের আশঙ্কা থাকে। কিন্তু কিতাব ও সুন্নাহকে মানদণ্ড বানালে পথ পরিষ্কার হয়। এই হাদিস আমাদের শেখায়, মতভেদ, সন্দেহ বা নতুন রীতির ভিড়ে নিরাপদ আশ্রয় হলো আল্লাহর কিতাব ও নবীর প্রমাণিত সুন্নাহ।"},"teachings":["আল্লাহর কিতাব ও নবীর সুন্নাহ মুসলিমের মূল পথনির্দেশ।","পথভ্রষ্টতা থেকে বাঁচতে কিতাব ও সুন্নাহ আঁকড়ে ধরতে হবে।","দ্বীনের মানদণ্ড সমাজের প্রচলন নয়, প্রমাণিত দলিল।","সুন্নাহ ছাড়া কুরআনের বাস্তব আমল বোঝা অসম্পূর্ণ হয়ে যায়।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E84" s="4" t="n"/>
@@ -2425,7 +2429,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মধ্যম পথে সুন্নাহর আমল","description":"$book_name$ $hadith_number$ - $chapter_name$. বিদআতে বেশি চেষ্টা করার চেয়ে সুন্নাহর ওপর মধ্যমভাবে আমল করাই উত্তম—এটি বড় শিক্ষা।"},"heading":{"title":"সুন্নাহর ওপর মধ্যম আমল: বিদআতে পরিশ্রমের চেয়ে উত্তম","description":"এই বর্ণনায় বলা হয়েছে, শরীআতে নতুন কাজ নিয়ে বেশি পরিশ্রম করার চেয়ে মধ্যম পন্থায় সুন্নাহর ওপর আমল করা অনেক উত্তম। এখানে খুব দরকারি ভারসাম্যের শিক্ষা আছে। অনেক সময় মানুষ নতুন নতুন আমল, বিশেষ নিয়ম বা নিজের বানানো পদ্ধতিতে বেশি উৎসাহী হয়। কিন্তু যদি তা সুন্নাহভিত্তিক না হয়, তাহলে সেই পরিশ্রম নিরাপদ নয়। অন্যদিকে, সুন্নাহর প্রমাণিত আমল ছোট মনে হলেও সেটিই উত্তম পথ। দ্বীনে সফলতা বেশি জটিলতা বানানোর মধ্যে নয়; বরং রাসূলের শেখানো পথে স্থির থাকার মধ্যে। তাই কম হলেও নিয়মিত, খাঁটি এবং সুন্নাহসম্মত আমল করা উচিত। এই শিক্ষা মানুষকে সহজ, পরিষ্কার ও প্রমাণিত দ্বীনের পথে ফিরিয়ে আনে।"},"teachings":["বিদআতে বেশি পরিশ্রম করার চেয়ে সুন্নাহর ওপর কম আমলও উত্তম।","দ্বীনের কাজে প্রমাণিত পথকে অগ্রাধিকার দিতে হবে।","ইবাদতে জটিলতা নয়, সুন্নাহভিত্তিক সরলতা দরকার।","মধ্যম পন্থা মুসলিমকে বাড়াবাড়ি থেকে বাঁচায়।"],"related_hadiths":[{"id":"2697","book_id":"1","label":"Sahih Bukhari"},{"id":"4385","book_id":"2","label":"Sahih Muslim"},{"id":"5063","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মধ্যম পথে সুন্নাহর আমল","description":"$book_name$ $hadith_number$ - $chapter_name$. বিদআতে বেশি চেষ্টা করার চেয়ে সুন্নাহর ওপর মধ্যমভাবে আমল করাই উত্তম—এটি বড় শিক্ষা।"},"heading":{"title":"সুন্নাহর ওপর মধ্যম আমল: বিদআতে পরিশ্রমের চেয়ে উত্তম","description":"এই বর্ণনায় বলা হয়েছে, শরীআতে নতুন কাজ নিয়ে বেশি পরিশ্রম করার চেয়ে মধ্যম পন্থায় সুন্নাহর ওপর আমল করা অনেক উত্তম। এখানে খুব দরকারি ভারসাম্যের শিক্ষা আছে। অনেক সময় মানুষ নতুন নতুন আমল, বিশেষ নিয়ম বা নিজের বানানো পদ্ধতিতে বেশি উৎসাহী হয়। কিন্তু যদি তা সুন্নাহভিত্তিক না হয়, তাহলে সেই পরিশ্রম নিরাপদ নয়। অন্যদিকে, সুন্নাহর প্রমাণিত আমল ছোট মনে হলেও সেটিই উত্তম পথ। দ্বীনে সফলতা বেশি জটিলতা বানানোর মধ্যে নয়; বরং রাসূলের শেখানো পথে স্থির থাকার মধ্যে। তাই কম হলেও নিয়মিত, খাঁটি এবং সুন্নাহসম্মত আমল করা উচিত। এই শিক্ষা মানুষকে সহজ, পরিষ্কার ও প্রমাণিত দ্বীনের পথে ফিরিয়ে আনে।"},"teachings":["বিদআতে বেশি পরিশ্রম করার চেয়ে সুন্নাহর ওপর কম আমলও উত্তম।","দ্বীনের কাজে প্রমাণিত পথকে অগ্রাধিকার দিতে হবে।","ইবাদতে জটিলতা নয়, সুন্নাহভিত্তিক সরলতা দরকার।","মধ্যম পন্থা মুসলিমকে বাড়াবাড়ি থেকে বাঁচায়।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"5063","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E85" s="4" t="n"/>
@@ -2448,7 +2452,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত ফেরত ও খিয়ানত না করা","description":"$book_name$ $hadith_number$ - $chapter_name$. যে আমানত রেখেছে তাকে তা বুঝিয়ে দাও, আর কেউ খিয়ানত করলেও তার সঙ্গে খিয়ানত করো না।"},"heading":{"title":"আমানত ফেরত দাও, খিয়ানতের জবাবে খিয়ানত করো না","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব সহজ কিন্তু গভীর একটি নিয়ম শিখিয়েছেন। যে ব্যক্তি তোমার কাছে আমানত রেখেছে, তাকে সময়মতো আমানত বুঝিয়ে দাও। আর যে তোমার সঙ্গে খিয়ানত করে, তার সঙ্গে তুমি খিয়ানত করো না। এখানে আমানতদারি ও নৈতিকতার বড় শিক্ষা আছে। কেউ অন্যায় করলেই তার মতো অন্যায় করা মুসলিমের আচরণ নয়। আমানত ফেরত দেওয়া মানুষের হক। আর খিয়ানতের জবাবে খিয়ানত না করা চরিত্রের শক্তি দেখায়। এই হাদিস ব্যবসা, সম্পর্ক, দায়িত্ব, টাকা-পয়সা, কথা বা কোনো জিনিসের হেফাজত—সব জায়গায় কাজে লাগে। মুসলিমের পরিচয় হলো সে নিজের দায়িত্ব ঠিক রাখে।"},"teachings":["যে আমানত রাখে, তাকে আমানত ফেরত দেওয়া জরুরি।","অন্য কেউ খিয়ানত করলেও নিজে খিয়ানত করা ঠিক নয়।","আমানতদারি মানুষের হক রক্ষার শিক্ষা দেয়।","ভালো চরিত্র অন্যের খারাপ আচরণের ওপর নির্ভর করে না।"],"related_hadiths":[{"id":"3535","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1264","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"2934","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত ফেরত ও খিয়ানত না করা","description":"$book_name$ $hadith_number$ - $chapter_name$. যে আমানত রেখেছে তাকে তা বুঝিয়ে দাও, আর কেউ খিয়ানত করলেও তার সঙ্গে খিয়ানত করো না।"},"heading":{"title":"আমানত ফেরত দাও, খিয়ানতের জবাবে খিয়ানত করো না","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব সহজ কিন্তু গভীর একটি নিয়ম শিখিয়েছেন। যে ব্যক্তি তোমার কাছে আমানত রেখেছে, তাকে সময়মতো আমানত বুঝিয়ে দাও। আর যে তোমার সঙ্গে খিয়ানত করে, তার সঙ্গে তুমি খিয়ানত করো না। এখানে আমানতদারি ও নৈতিকতার বড় শিক্ষা আছে। কেউ অন্যায় করলেই তার মতো অন্যায় করা মুসলিমের আচরণ নয়। আমানত ফেরত দেওয়া মানুষের হক। আর খিয়ানতের জবাবে খিয়ানত না করা চরিত্রের শক্তি দেখায়। এই হাদিস ব্যবসা, সম্পর্ক, দায়িত্ব, টাকা-পয়সা, কথা বা কোনো জিনিসের হেফাজত—সব জায়গায় কাজে লাগে। মুসলিমের পরিচয় হলো সে নিজের দায়িত্ব ঠিক রাখে।"},"teachings":["যে আমানত রাখে, তাকে আমানত ফেরত দেওয়া জরুরি।","অন্য কেউ খিয়ানত করলেও নিজে খিয়ানত করা ঠিক নয়।","আমানতদারি মানুষের হক রক্ষার শিক্ষা দেয়।","ভালো চরিত্র অন্যের খারাপ আচরণের ওপর নির্ভর করে না।"],"related_hadiths":[{"id":"3535","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"1264","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"2934","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E86" s="4" t="n"/>
@@ -2471,7 +2475,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হাজরে আসওয়াদ ও সুন্নাহ অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. হাজরে আসওয়াদ নিজে উপকার-অপকার করতে পারে না; নবীকে করতে দেখে উমর তা চুম্বন করেন।"},"heading":{"title":"হাজরে আসওয়াদ চুম্বন: বিশ্বাস নয়, সুন্নাহ অনুসরণের শিক্ষা","description":"এই হাদিসে ওমর (রাঃ) হাজরে আসওয়াদের কাছে এসে তা চুম্বন করেন এবং বলেন, তিনি জানেন এটি একটি পাথর মাত্র; এটি কারও কল্যাণ বা অকল্যাণ করতে পারে না। এরপর তিনি বলেন, নবী (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে এটি চুম্বন করতে না দেখলে তিনি চুম্বন করতেন না। এই কথায় তাওহীদ ও সুন্নাহ অনুসরণের সুন্দর শিক্ষা আছে। হাজরে আসওয়াদকে সম্মান করা হয় রাসূলের আমল অনুসরণ করে, পাথরকে উপকার-অপকারের মালিক মনে করে নয়। তাই মুসলিমের বিশ্বাস পরিষ্কার হওয়া দরকার—উপকার ও ক্ষতির ক্ষমতা আল্লাহর হাতে। আর ইবাদতের কাজ করা হবে নবীর দেখানো পদ্ধতিতে। আবেগ, কুসংস্কার বা অতিরিক্ত বিশ্বাস এখানে গ্রহণযোগ্য নয়।"},"teachings":["হাজরে আসওয়াদ নিজে উপকার বা অপকার করার ক্ষমতা রাখে না।","উমর (রাঃ) এটি চুম্বন করেছেন নবীর অনুসরণে।","তাওহীদ হলো কল্যাণ-অকল্যাণের মালিক আল্লাহকে মানা।","ইবাদতের কাজে আবেগ নয়, রাসূলের সুন্নাহ অনুসরণ করা দরকার।"],"related_hadiths":[{"id":"2957","book_id":"2","label":"Sahih Muslim"},{"id":"2958","book_id":"2","label":"Sahih Muslim"},{"id":"2959","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হাজরে আসওয়াদ ও সুন্নাহ অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. হাজরে আসওয়াদ নিজে উপকার-অপকার করতে পারে না; নবীকে করতে দেখে উমর তা চুম্বন করেন।"},"heading":{"title":"হাজরে আসওয়াদ চুম্বন: বিশ্বাস নয়, সুন্নাহ অনুসরণের শিক্ষা","description":"এই হাদিসে ওমর (রাঃ) হাজরে আসওয়াদের কাছে এসে তা চুম্বন করেন এবং বলেন, তিনি জানেন এটি একটি পাথর মাত্র; এটি কারও কল্যাণ বা অকল্যাণ করতে পারে না। এরপর তিনি বলেন, নবী (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে এটি চুম্বন করতে না দেখলে তিনি চুম্বন করতেন না। এই কথায় তাওহীদ ও সুন্নাহ অনুসরণের সুন্দর শিক্ষা আছে। হাজরে আসওয়াদকে সম্মান করা হয় রাসূলের আমল অনুসরণ করে, পাথরকে উপকার-অপকারের মালিক মনে করে নয়। তাই মুসলিমের বিশ্বাস পরিষ্কার হওয়া দরকার—উপকার ও ক্ষতির ক্ষমতা আল্লাহর হাতে। আর ইবাদতের কাজ করা হবে নবীর দেখানো পদ্ধতিতে। আবেগ, কুসংস্কার বা অতিরিক্ত বিশ্বাস এখানে গ্রহণযোগ্য নয়।"},"teachings":["হাজরে আসওয়াদ নিজে উপকার বা অপকার করার ক্ষমতা রাখে না।","উমর (রাঃ) এটি চুম্বন করেছেন নবীর অনুসরণে।","তাওহীদ হলো কল্যাণ-অকল্যাণের মালিক আল্লাহকে মানা।","ইবাদতের কাজে আবেগ নয়, রাসূলের সুন্নাহ অনুসরণ করা দরকার।"],"related_hadiths":[{"id":"2957","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2958","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2959","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E87" s="4" t="n"/>
@@ -2737,7 +2741,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অন্যায়ভাবে জমি দখলের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. অর্ধহাত জমি অন্যায়ভাবে দখল করলে কিয়ামতে সাত জমিনের বোঝা তার কাঁধে দেওয়া হবে।"},"heading":{"title":"অন্যায়ভাবে জমি দখল: সাত জমিনের কঠিন সতর্কতা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি অত্যাচার করে অর্ধহাত জমি দখল করে, কিয়ামতের দিন অনুরূপ সাতটি জমিন তার কাঁধে ঝুলিয়ে দেওয়া হবে। এখানে জমি দখল সম্পর্কে খুব কঠোর সতর্কতা এসেছে। অল্প জমি হলেও অন্যায়ভাবে নেওয়া হালকা বিষয় নয়। মানুষের সম্পদ, জমি ও অধিকার রক্ষা করা ইসলামী ন্যায়ের অংশ। এই হাদিস জমির সীমানা, মালিকানা এবং অন্যের হক নিয়ে ভয় দেখায়। অর্ধহাত জমির কথাও এসেছে, তাই ছোট অন্যায়কে ছোট ভেবে নেওয়া ঠিক নয়। কিয়ামতের জবাবদিহি মনে রাখলে অন্যের সম্পদ দখল থেকে মানুষ বাঁচতে পারে।"},"teachings":["অন্যায়ভাবে অল্প জমি দখল করাও ভয়ংকর অপরাধ।","মানুষের জমি ও সম্পদের হক রক্ষা করা দরকার।","কিয়ামতে জমি দখলের কঠিন জবাবদিহি হবে।","ছোট অন্যায়কে হালকা মনে করা উচিত নয়।"],"related_hadiths":[{"id":"2452","book_id":"1","label":"Sahih Bukhari"},{"id":"1610","book_id":"2","label":"Sahih Muslim"},{"id":"2938","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অন্যায়ভাবে জমি দখলের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. অর্ধহাত জমি অন্যায়ভাবে দখল করলে কিয়ামতে সাত জমিনের বোঝা তার কাঁধে দেওয়া হবে।"},"heading":{"title":"অন্যায়ভাবে জমি দখল: সাত জমিনের কঠিন সতর্কতা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি অত্যাচার করে অর্ধহাত জমি দখল করে, কিয়ামতের দিন অনুরূপ সাতটি জমিন তার কাঁধে ঝুলিয়ে দেওয়া হবে। এখানে জমি দখল সম্পর্কে খুব কঠোর সতর্কতা এসেছে। অল্প জমি হলেও অন্যায়ভাবে নেওয়া হালকা বিষয় নয়। মানুষের সম্পদ, জমি ও অধিকার রক্ষা করা ইসলামী ন্যায়ের অংশ। এই হাদিস জমির সীমানা, মালিকানা এবং অন্যের হক নিয়ে ভয় দেখায়। অর্ধহাত জমির কথাও এসেছে, তাই ছোট অন্যায়কে ছোট ভেবে নেওয়া ঠিক নয়। কিয়ামতের জবাবদিহি মনে রাখলে অন্যের সম্পদ দখল থেকে মানুষ বাঁচতে পারে।"},"teachings":["অন্যায়ভাবে অল্প জমি দখল করাও ভয়ংকর অপরাধ।","মানুষের জমি ও সম্পদের হক রক্ষা করা দরকার।","কিয়ামতে জমি দখলের কঠিন জবাবদিহি হবে।","ছোট অন্যায়কে হালকা মনে করা উচিত নয়।"],"related_hadiths":[{"id":"2452","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1610","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2938","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E97" s="4" t="n"/>
@@ -3030,7 +3034,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সালাত যাকাত ও মুসলমানের কল্যাণ","description":"$book_name$ $hadith_number$ - $chapter_name$. সালাত কায়েম, যাকাত আদায় ও সকল মুসলমানের কল্যাণ কামনার উপর বায়আতের শিক্ষা এই হাদিসে এসেছে।"},"heading":{"title":"সালাত যাকাত ও সকল মুসলমানের কল্যাণ কামনার বায়আত","description":"এই হাদিসে জারীর ইবনু আবদুল্লাহ (রাঃ) বলেন, তিনি রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর সাথে বায়আত করেছেন তিনটি বিষয়ের উপর: সালাত প্রতিষ্ঠা করা, যাকাত প্রদান করা এবং সকল মুসলমানের কল্যাণ কামনা করা। এখানে সালাত, যাকাত ও নসীহত একসঙ্গে এসেছে। এতে বোঝা যায়, ইবাদত শুধু ব্যক্তিগত কাজ নয়; মুসলমানদের জন্য ভালো চাওয়াও দ্বীনের অংশ। সালাত মানুষকে আল্লাহর সঙ্গে যুক্ত করে, যাকাত সম্পদের দায়িত্ব শেখায়, আর মুসলমানের কল্যাণ কামনা সমাজকে সুন্দর করে। এই বায়আত হাদিস আমাদের শেখায়, একজন মুসলিম নিজের ইবাদত ঠিক রাখার পাশাপাশি অন্য মুসলমানের ক্ষতি নয়, বরং কল্যাণ চায়।"},"teachings":["সালাত প্রতিষ্ঠা করা মুসলিম জীবনের গুরুত্বপূর্ণ দায়িত্ব।","যাকাত আদায় সম্পদের হক বুঝে দেওয়ার শিক্ষা দেয়।","সকল মুসলমানের কল্যাণ কামনা দ্বীনের সুন্দর আচরণ।","বায়আত মানে দায়িত্ব মেনে চলার অঙ্গীকার।"],"related_hadiths":[{"id":"57","book_id":"1","label":"Sahih Bukhari"},{"id":"56","book_id":"2","label":"Sahih Muslim"},{"id":"4967","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সালাত যাকাত ও মুসলমানের কল্যাণ","description":"$book_name$ $hadith_number$ - $chapter_name$. সালাত কায়েম, যাকাত আদায় ও সকল মুসলমানের কল্যাণ কামনার উপর বায়আতের শিক্ষা এই হাদিসে এসেছে।"},"heading":{"title":"সালাত যাকাত ও সকল মুসলমানের কল্যাণ কামনার বায়আত","description":"এই হাদিসে জারীর ইবনু আবদুল্লাহ (রাঃ) বলেন, তিনি রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর সাথে বায়আত করেছেন তিনটি বিষয়ের উপর: সালাত প্রতিষ্ঠা করা, যাকাত প্রদান করা এবং সকল মুসলমানের কল্যাণ কামনা করা। এখানে সালাত, যাকাত ও নসীহত একসঙ্গে এসেছে। এতে বোঝা যায়, ইবাদত শুধু ব্যক্তিগত কাজ নয়; মুসলমানদের জন্য ভালো চাওয়াও দ্বীনের অংশ। সালাত মানুষকে আল্লাহর সঙ্গে যুক্ত করে, যাকাত সম্পদের দায়িত্ব শেখায়, আর মুসলমানের কল্যাণ কামনা সমাজকে সুন্দর করে। এই বায়আত হাদিস আমাদের শেখায়, একজন মুসলিম নিজের ইবাদত ঠিক রাখার পাশাপাশি অন্য মুসলমানের ক্ষতি নয়, বরং কল্যাণ চায়।"},"teachings":["সালাত প্রতিষ্ঠা করা মুসলিম জীবনের গুরুত্বপূর্ণ দায়িত্ব।","যাকাত আদায় সম্পদের হক বুঝে দেওয়ার শিক্ষা দেয়।","সকল মুসলমানের কল্যাণ কামনা দ্বীনের সুন্দর আচরণ।","বায়আত মানে দায়িত্ব মেনে চলার অঙ্গীকার।"],"related_hadiths":[{"id":"57","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"56","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"4967","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E108" s="4" t="n"/>
@@ -3053,7 +3057,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অনধিকার জমি নেওয়ার শাস্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. অনধিকারে কারও জমি নিলে কিয়ামতের দিন তাকে সাত তবক জমিন পর্যন্ত ধসিয়ে দেওয়ার সতর্কতা এসেছে।"},"heading":{"title":"অনধিকার জমি নেওয়ার পরিণতি ও হক রক্ষার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি অনধিকারে কারও কিছু জমি নেয়, কিয়ামতের দিন তাকে সাত তবক জমিন পর্যন্ত ধসিয়ে দেওয়া হবে। এই হাদিস জমি দখল, অন্যের হক নেওয়া এবং যুলুমের বিরুদ্ধে কঠোর সতর্কতা দেয়। জমি ছোট হোক বা বড়—অধিকার ছাড়া নেওয়া বৈধ নয়। মানুষের সম্পদে হাত দেওয়ার আগে মনে রাখতে হবে, আখেরাতে এর হিসাব আছে। এই হাদিস আমাদের জমির সীমানা, দলিল, মালিকানা ও ন্যায্য অধিকার বিষয়ে সতর্ক করে। অন্যের হক বাঁচিয়ে চলা শুধু সামাজিক নিয়ম নয়; এটি আখেরাতের জবাবদিহির সঙ্গেও জড়িত।"},"teachings":["অনধিকারে জমি নেওয়া যুলুমের মধ্যে পড়ে।","কিয়ামতে জমি দখলের কঠিন পরিণতির কথা এসেছে।","অন্যের সম্পদ ও জমির অধিকার মানা জরুরি।","ন্যায্য হক ছাড়া কিছু নেওয়া থেকে বিরত থাকা দরকার।"],"related_hadiths":[{"id":"2454","book_id":"1","label":"Sahih Bukhari"},{"id":"2958","book_id":"14","label":"Mishkat al-Masabih"},{"id":"1610","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অনধিকার জমি নেওয়ার শাস্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. অনধিকারে কারও জমি নিলে কিয়ামতের দিন তাকে সাত তবক জমিন পর্যন্ত ধসিয়ে দেওয়ার সতর্কতা এসেছে।"},"heading":{"title":"অনধিকার জমি নেওয়ার পরিণতি ও হক রক্ষার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি অনধিকারে কারও কিছু জমি নেয়, কিয়ামতের দিন তাকে সাত তবক জমিন পর্যন্ত ধসিয়ে দেওয়া হবে। এই হাদিস জমি দখল, অন্যের হক নেওয়া এবং যুলুমের বিরুদ্ধে কঠোর সতর্কতা দেয়। জমি ছোট হোক বা বড়—অধিকার ছাড়া নেওয়া বৈধ নয়। মানুষের সম্পদে হাত দেওয়ার আগে মনে রাখতে হবে, আখেরাতে এর হিসাব আছে। এই হাদিস আমাদের জমির সীমানা, দলিল, মালিকানা ও ন্যায্য অধিকার বিষয়ে সতর্ক করে। অন্যের হক বাঁচিয়ে চলা শুধু সামাজিক নিয়ম নয়; এটি আখেরাতের জবাবদিহির সঙ্গেও জড়িত।"},"teachings":["অনধিকারে জমি নেওয়া যুলুমের মধ্যে পড়ে।","কিয়ামতে জমি দখলের কঠিন পরিণতির কথা এসেছে।","অন্যের সম্পদ ও জমির অধিকার মানা জরুরি।","ন্যায্য হক ছাড়া কিছু নেওয়া থেকে বিরত থাকা দরকার।"],"related_hadiths":[{"id":"2454","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2958","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"1610","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E109" s="4" t="n"/>
@@ -3103,7 +3107,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নম্রতা ও কোমলতার কল্যাণ","description":"$book_name$ $hadith_number$ - $chapter_name$. কোমলতা থেকে বঞ্চিত হলে মানুষ অনেক কল্যাণ হারায়; এই হাদিসে সুন্দর আচরণ ও নরম ব্যবহারের গুরুত্ব বোঝানো হয়েছে।"},"heading":{"title":"নম্রতা ও কোমলতা: কল্যাণ পাওয়ার বড় শিক্ষা","description":"এই হাদিসের মূল কথা খুব সরল: কোমলতা ও নম্রতা মানুষের জীবনে কল্যাণের দরজা খুলে দেয়। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যাকে কোমলতা থেকে বঞ্চিত করা হয়, তাকে কল্যাণ থেকেও বঞ্চিত করা হয়। এখানে নম্রতা মানে দুর্বলতা নয়; বরং কথা, আচরণ ও ব্যবহারকে নরম রাখা। পরিবারে, কাজে বা মানুষের সঙ্গে মেলামেশায় রুক্ষ কথা অনেক সময় সম্পর্ক নষ্ট করে। আর কোমল ব্যবহার মানুষকে কাছে আনে। তাই এই হাদিস আমাদের শেখায়, ভালো মুসলিম চরিত্র গড়তে নরম ভাষা, ধৈর্য আর সুন্দর আচরণ জরুরি। হাদিসে কল্যাণের কথা এসেছে, তাই আমরা বলতে পারি—নম্রতা মানুষকে ভালো গুণের দিকে নিয়ে যায়। তাই নিজের ভাষা ও আচরণে কোমলতা আছে কি না, তা নিয়মিত খেয়াল করা এই হাদিসের খুব বাস্তব প্রয়োগ।"},"teachings":["কথা ও আচরণে কোমলতা রাখা কল্যাণের কারণ।","রুক্ষ স্বভাব মানুষকে ভালো দিক থেকে দূরে নিতে পারে।","নম্র ব্যবহার পরিবার ও সমাজে সম্পর্ক সুন্দর করে।","কোমলতা দুর্বলতা নয়; এটি ভালো চরিত্রের অংশ।"],"related_hadiths":[{"id":"5068","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নম্রতা ও কোমলতার কল্যাণ","description":"$book_name$ $hadith_number$ - $chapter_name$. কোমলতা থেকে বঞ্চিত হলে মানুষ অনেক কল্যাণ হারায়; এই হাদিসে সুন্দর আচরণ ও নরম ব্যবহারের গুরুত্ব বোঝানো হয়েছে।"},"heading":{"title":"নম্রতা ও কোমলতা: কল্যাণ পাওয়ার বড় শিক্ষা","description":"এই হাদিসের মূল কথা খুব সরল: কোমলতা ও নম্রতা মানুষের জীবনে কল্যাণের দরজা খুলে দেয়। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যাকে কোমলতা থেকে বঞ্চিত করা হয়, তাকে কল্যাণ থেকেও বঞ্চিত করা হয়। এখানে নম্রতা মানে দুর্বলতা নয়; বরং কথা, আচরণ ও ব্যবহারকে নরম রাখা। পরিবারে, কাজে বা মানুষের সঙ্গে মেলামেশায় রুক্ষ কথা অনেক সময় সম্পর্ক নষ্ট করে। আর কোমল ব্যবহার মানুষকে কাছে আনে। তাই এই হাদিস আমাদের শেখায়, ভালো মুসলিম চরিত্র গড়তে নরম ভাষা, ধৈর্য আর সুন্দর আচরণ জরুরি। হাদিসে কল্যাণের কথা এসেছে, তাই আমরা বলতে পারি—নম্রতা মানুষকে ভালো গুণের দিকে নিয়ে যায়। তাই নিজের ভাষা ও আচরণে কোমলতা আছে কি না, তা নিয়মিত খেয়াল করা এই হাদিসের খুব বাস্তব প্রয়োগ।"},"teachings":["কথা ও আচরণে কোমলতা রাখা কল্যাণের কারণ।","রুক্ষ স্বভাব মানুষকে ভালো দিক থেকে দূরে নিতে পারে।","নম্র ব্যবহার পরিবার ও সমাজে সম্পর্ক সুন্দর করে।","কোমলতা দুর্বলতা নয়; এটি ভালো চরিত্রের অংশ।"],"related_hadiths":[{"id":"5068","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -3130,7 +3134,7 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জমি দখল হারাম ও কিয়ামতের দায়","description":"$book_name$ $hadith_number$ - $chapter_name$. অন্যায়ভাবে সামান্য জমি দখলও কিয়ামতে কঠিন দায়ের কারণ হবে; তাই জমি ও হকের ব্যাপারে সতর্ক থাকার শিক্ষা।"},"heading":{"title":"জমি দখল হারাম: অন্যের হক নিলে কিয়ামতে দায় আছে","description":"এই হাদিসের মূল শিক্ষা হলো, অন্যের জমি দখল করা শুধু সামাজিক অন্যায় নয়, আখিরাতের বড় দায়ও। এখানে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কেউ অন্যায়ভাবে কারো এক বিগত জমি দখল করলে তাকে কিয়ামতের দিন সেই জমির কারণে কঠিন অবস্থার মুখোমুখি হতে হবে। তাই জমি দখল হারাম—এই বিষয়টি খুব পরিষ্কারভাবে বোঝা যায়। অনেক সময় মানুষ জমির সীমানা, দলিল, উত্তরাধিকার বা ক্ষমতার জোরে সামান্য অংশকে ছোট ব্যাপার মনে করে। কিন্তু হাদিসটি শেখায়, অন্যের হক সামান্য হলেও তা হালকা নয়। মুসলিমের জন্য জরুরি হলো জমি, সম্পদ ও অধিকার নিয়ে ইনসাফ করা এবং কাউকে যুলুম না করা।"},"teachings":["অন্যের জমির সামান্য অংশও অন্যায়ভাবে নেওয়া বড় দায়ের কারণ।","জমি ও সম্পদের ব্যাপারে যুলুম থেকে বেঁচে থাকা জরুরি।","মানুষের হক নষ্ট করলে কিয়ামতের দিন জবাবদিহি করতে হবে।","সীমানা, দলিল ও মালিকানার বিষয়ে সততা রাখা ঈমানি আচরণের অংশ।"],"related_hadiths":[{"id":"2453","book_id":"1","label":"Sahih Bukhari"},{"id":"4028","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জমি দখল হারাম ও কিয়ামতের দায়","description":"$book_name$ $hadith_number$ - $chapter_name$. অন্যায়ভাবে সামান্য জমি দখলও কিয়ামতে কঠিন দায়ের কারণ হবে; তাই জমি ও হকের ব্যাপারে সতর্ক থাকার শিক্ষা।"},"heading":{"title":"জমি দখল হারাম: অন্যের হক নিলে কিয়ামতে দায় আছে","description":"এই হাদিসের মূল শিক্ষা হলো, অন্যের জমি দখল করা শুধু সামাজিক অন্যায় নয়, আখিরাতের বড় দায়ও। এখানে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কেউ অন্যায়ভাবে কারো এক বিগত জমি দখল করলে তাকে কিয়ামতের দিন সেই জমির কারণে কঠিন অবস্থার মুখোমুখি হতে হবে। তাই জমি দখল হারাম—এই বিষয়টি খুব পরিষ্কারভাবে বোঝা যায়। অনেক সময় মানুষ জমির সীমানা, দলিল, উত্তরাধিকার বা ক্ষমতার জোরে সামান্য অংশকে ছোট ব্যাপার মনে করে। কিন্তু হাদিসটি শেখায়, অন্যের হক সামান্য হলেও তা হালকা নয়। মুসলিমের জন্য জরুরি হলো জমি, সম্পদ ও অধিকার নিয়ে ইনসাফ করা এবং কাউকে যুলুম না করা।"},"teachings":["অন্যের জমির সামান্য অংশও অন্যায়ভাবে নেওয়া বড় দায়ের কারণ।","জমি ও সম্পদের ব্যাপারে যুলুম থেকে বেঁচে থাকা জরুরি।","মানুষের হক নষ্ট করলে কিয়ামতের দিন জবাবদিহি করতে হবে।","সীমানা, দলিল ও মালিকানার বিষয়ে সততা রাখা ঈমানি আচরণের অংশ।"],"related_hadiths":[{"id":"2453","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4028","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -3157,7 +3161,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পবিত্র অন্তর ও সত্যভাষীর মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. উত্তম মানুষের পরিচয় হলো সত্য কথা বলা ও অন্তরকে পাপ, যুলুম, খিয়ানত ও হিংসা থেকে পরিষ্কার রাখা।"},"heading":{"title":"পবিত্র অন্তর ও সত্যভাষী: উত্তম মানুষের সহজ পরিচয়","description":"এই হাদিসে মানুষের উত্তম হওয়ার একটি সহজ কিন্তু গভীর মানদণ্ড বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে জিজ্ঞেস করা হলে তিনি বলেন, নিষ্কলুষ অন্তঃকরণ ও সত্যভাষী মানুষ উত্তম। এখানে পবিত্র অন্তর বলতে শুধু নরম মন বোঝানো হয়নি। হাদিসের ভাষায় এমন অন্তর, যেখানে পাপ নেই, যুলুম নেই, খিয়ানত নেই এবং হিংসা-বিদ্বেষ নেই। তাই পবিত্র অন্তর হাদিস আমাদের নিজের ভেতর দেখার শিক্ষা দেয়। আমরা মুখে সত্য বলি কি না, মানুষের প্রতি হিংসা রাখি কি না, কারো হক নষ্ট করি কি না—এসব বিষয় নিজের জীবনেই যাচাই করতে হবে। সত্যভাষী হওয়া এবং অন্তর পরিষ্কার রাখা একসঙ্গে চলা উচিত।"},"teachings":["উত্তম মানুষের বড় গুণ হলো সত্য কথা বলা।","অন্তরকে পাপ, যুলুম ও খিয়ানত থেকে পরিষ্কার রাখা দরকার।","হিংসা-বিদ্বেষ থেকে মুক্ত থাকা পবিত্র অন্তরের লক্ষণ।","বাহ্যিক ভালো আচরণের সঙ্গে ভেতরের সততাও জরুরি।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"593","book_id":"8","label":"Riyadus Salihin"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পবিত্র অন্তর ও সত্যভাষীর মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. উত্তম মানুষের পরিচয় হলো সত্য কথা বলা ও অন্তরকে পাপ, যুলুম, খিয়ানত ও হিংসা থেকে পরিষ্কার রাখা।"},"heading":{"title":"পবিত্র অন্তর ও সত্যভাষী: উত্তম মানুষের সহজ পরিচয়","description":"এই হাদিসে মানুষের উত্তম হওয়ার একটি সহজ কিন্তু গভীর মানদণ্ড বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে জিজ্ঞেস করা হলে তিনি বলেন, নিষ্কলুষ অন্তঃকরণ ও সত্যভাষী মানুষ উত্তম। এখানে পবিত্র অন্তর বলতে শুধু নরম মন বোঝানো হয়নি। হাদিসের ভাষায় এমন অন্তর, যেখানে পাপ নেই, যুলুম নেই, খিয়ানত নেই এবং হিংসা-বিদ্বেষ নেই। তাই পবিত্র অন্তর হাদিস আমাদের নিজের ভেতর দেখার শিক্ষা দেয়। আমরা মুখে সত্য বলি কি না, মানুষের প্রতি হিংসা রাখি কি না, কারো হক নষ্ট করি কি না—এসব বিষয় নিজের জীবনেই যাচাই করতে হবে। সত্যভাষী হওয়া এবং অন্তর পরিষ্কার রাখা একসঙ্গে চলা উচিত।"},"teachings":["উত্তম মানুষের বড় গুণ হলো সত্য কথা বলা।","অন্তরকে পাপ, যুলুম ও খিয়ানত থেকে পরিষ্কার রাখা দরকার।","হিংসা-বিদ্বেষ থেকে মুক্ত থাকা পবিত্র অন্তরের লক্ষণ।","বাহ্যিক ভালো আচরণের সঙ্গে ভেতরের সততাও জরুরি।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"593","book_id":"8","slug":"riyadus-salihin","label":"রিয়াদুস সালেহীন"}]}</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -3184,7 +3188,7 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিশুদের প্রতি স্নেহ-মমতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুদের চুম্বন ও আদর নিয়ে এই হাদিস দেখায়, অন্তরে স্নেহ-মমতা থাকা আল্লাহর বড় দান।"},"heading":{"title":"শিশুদের প্রতি স্নেহ-মমতা: আদর, দয়া ও কোমল হৃদয়ের হাদিস","description":"এই হাদিসের মূল বিষয় শিশুদের প্রতি স্নেহ-মমতা। এক বেদুঈন সাহাবীদের শিশুদের চুমু দিতে দেখে বলল, তারা শিশুদের চুম্বন করে না। তখন রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বললেন, আল্লাহ যদি তার অন্তর থেকে রহমত তুলে নেন, তবে তিনি তা বাধা দিতে পারবেন কি? এই কথায় বোঝা যায়, শিশুকে আদর করা দুর্বলতা নয়; বরং অন্তরের দয়া ও কোমলতার লক্ষণ। শিশুদের প্রতি স্নেহ, চুম্বন ও ভালোবাসা দেখানো ইসলামী আদবের সঙ্গে মিলে যায়। প্রধান কীওয়ার্ড হলো শিশুদের প্রতি স্নেহ-মমতা, আর সম্পর্কিত কীওয়ার্ড হলো শিশুকে আদর করা, সন্তানকে চুমু দেওয়া, দয়ার হাদিস, কোমল হৃদয়। হাদিসটি আমাদের শেখায়, ঘরের ছোটদের সঙ্গে রুক্ষ আচরণ নয়, ভালোবাসা ও মমতা থাকা উচিত।"},"teachings":["শিশুকে আদর করা ও ভালোবাসা দেখানো সুন্দর আচরণ।","অন্তরে রহমত থাকা আল্লাহর দান—এটি হারিয়ে যাওয়া ভয়ংকর ক্ষতি।","শিশুদের সঙ্গে কঠোরতার বদলে কোমল আচরণ করা উচিত।"],"related_hadiths":[{"id":"5997","book_id":"1","label":"Sahih Bukhari"},{"id":"6013","book_id":"1","label":"Sahih Bukhari"},{"id":"6008","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিশুদের প্রতি স্নেহ-মমতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুদের চুম্বন ও আদর নিয়ে এই হাদিস দেখায়, অন্তরে স্নেহ-মমতা থাকা আল্লাহর বড় দান।"},"heading":{"title":"শিশুদের প্রতি স্নেহ-মমতা: আদর, দয়া ও কোমল হৃদয়ের হাদিস","description":"এই হাদিসের মূল বিষয় শিশুদের প্রতি স্নেহ-মমতা। এক বেদুঈন সাহাবীদের শিশুদের চুমু দিতে দেখে বলল, তারা শিশুদের চুম্বন করে না। তখন রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বললেন, আল্লাহ যদি তার অন্তর থেকে রহমত তুলে নেন, তবে তিনি তা বাধা দিতে পারবেন কি? এই কথায় বোঝা যায়, শিশুকে আদর করা দুর্বলতা নয়; বরং অন্তরের দয়া ও কোমলতার লক্ষণ। শিশুদের প্রতি স্নেহ, চুম্বন ও ভালোবাসা দেখানো ইসলামী আদবের সঙ্গে মিলে যায়। প্রধান কীওয়ার্ড হলো শিশুদের প্রতি স্নেহ-মমতা, আর সম্পর্কিত কীওয়ার্ড হলো শিশুকে আদর করা, সন্তানকে চুমু দেওয়া, দয়ার হাদিস, কোমল হৃদয়। হাদিসটি আমাদের শেখায়, ঘরের ছোটদের সঙ্গে রুক্ষ আচরণ নয়, ভালোবাসা ও মমতা থাকা উচিত।"},"teachings":["শিশুকে আদর করা ও ভালোবাসা দেখানো সুন্দর আচরণ।","অন্তরে রহমত থাকা আল্লাহর দান—এটি হারিয়ে যাওয়া ভয়ংকর ক্ষতি।","শিশুদের সঙ্গে কঠোরতার বদলে কোমল আচরণ করা উচিত।"],"related_hadiths":[{"id":"5997","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6013","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6008","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E114" s="4" t="n"/>
@@ -3207,7 +3211,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দুই কন্যা লালন-পালনের ফজিলত","description":"$book_name$ $hadith_number$ - $chapter_name$. দুই কন্যাকে পূর্ণ বয়স্কা হওয়া পর্যন্ত লালন করলে কিয়ামতে নবীর নৈকট্যের আশা জাগে।"},"heading":{"title":"দুই কন্যার লালন-পালন: নবীর নৈকট্য লাভের আশাব্যঞ্জক হাদিস","description":"এই হাদিসের মূল বিষয় দুই কন্যার লালন-পালন। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি দুই কন্যাকে পূর্ণ বয়স্কা হওয়া পর্যন্ত লালন-পালন করবে, কিয়ামতের দিন সে তাঁর সঙ্গে এভাবে আসবে। এরপর তিনি নিজের আঙ্গুল একত্র করে দেখিয়েছেন। হাদিসটি কন্যা সন্তানের মর্যাদা ও তাদের দায়িত্বশীলভাবে বড় করার গুরুত্ব তুলে ধরে। এখানে প্রধান কীওয়ার্ড হলো দুই কন্যা লালন-পালনের হাদিস। সম্পর্কিত কীওয়ার্ড: কন্যা সন্তানের ফজিলত, মেয়েদের লালন-পালন, কন্যার মর্যাদা, ইসলামে সন্তান প্রতিপালন। হাদিসের শিক্ষা হলো, কন্যাদের যত্ন, নিরাপত্তা, খাবার, শিক্ষা ও বড় হওয়া পর্যন্ত অভিভাবকত্ব একটি মূল্যবান দায়িত্ব। তবে ব্যাখ্যায় আমরা শুধু হাদিসে থাকা কথাটুকুই ধরে বলি—এই কাজ কিয়ামতের দিনে রাসূলের নৈকট্যের কারণ হতে পারে।"},"teachings":["দুই কন্যাকে বড় হওয়া পর্যন্ত দায়িত্ব নিয়ে লালন-পালন করা প্রশংসনীয়।","কন্যা সন্তানকে অবহেলা নয়, যত্ন ও ভালো আচরণ দেওয়া দরকার।","কন্যাদের দায়িত্ব পালন কিয়ামতের দিনে নবীর নৈকট্যের কারণ হতে পারে।"],"related_hadiths":[{"id":"5995","book_id":"1","label":"Sahih Bukhari"},{"id":"5304","book_id":"1","label":"Sahih Bukhari"},{"id":"6005","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দুই কন্যা লালন-পালনের ফজিলত","description":"$book_name$ $hadith_number$ - $chapter_name$. দুই কন্যাকে পূর্ণ বয়স্কা হওয়া পর্যন্ত লালন করলে কিয়ামতে নবীর নৈকট্যের আশা জাগে।"},"heading":{"title":"দুই কন্যার লালন-পালন: নবীর নৈকট্য লাভের আশাব্যঞ্জক হাদিস","description":"এই হাদিসের মূল বিষয় দুই কন্যার লালন-পালন। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি দুই কন্যাকে পূর্ণ বয়স্কা হওয়া পর্যন্ত লালন-পালন করবে, কিয়ামতের দিন সে তাঁর সঙ্গে এভাবে আসবে। এরপর তিনি নিজের আঙ্গুল একত্র করে দেখিয়েছেন। হাদিসটি কন্যা সন্তানের মর্যাদা ও তাদের দায়িত্বশীলভাবে বড় করার গুরুত্ব তুলে ধরে। এখানে প্রধান কীওয়ার্ড হলো দুই কন্যা লালন-পালনের হাদিস। সম্পর্কিত কীওয়ার্ড: কন্যা সন্তানের ফজিলত, মেয়েদের লালন-পালন, কন্যার মর্যাদা, ইসলামে সন্তান প্রতিপালন। হাদিসের শিক্ষা হলো, কন্যাদের যত্ন, নিরাপত্তা, খাবার, শিক্ষা ও বড় হওয়া পর্যন্ত অভিভাবকত্ব একটি মূল্যবান দায়িত্ব। তবে ব্যাখ্যায় আমরা শুধু হাদিসে থাকা কথাটুকুই ধরে বলি—এই কাজ কিয়ামতের দিনে রাসূলের নৈকট্যের কারণ হতে পারে।"},"teachings":["দুই কন্যাকে বড় হওয়া পর্যন্ত দায়িত্ব নিয়ে লালন-পালন করা প্রশংসনীয়।","কন্যা সন্তানকে অবহেলা নয়, যত্ন ও ভালো আচরণ দেওয়া দরকার।","কন্যাদের দায়িত্ব পালন কিয়ামতের দিনে নবীর নৈকট্যের কারণ হতে পারে।"],"related_hadiths":[{"id":"5995","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5304","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6005","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E115" s="4" t="n"/>
@@ -3230,7 +3234,7 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিধবা ও মিসকীনকে সাহায্য","description":"$book_name$ $hadith_number$ - $chapter_name$. বিধবা ও মিসকীনের সহযোগিতা বড় নেকির কাজ; হাদিসে এর মর্যাদা জিহাদ, কিয়াম ও সিয়ামের সঙ্গে তুলনা করা হয়েছে।"},"heading":{"title":"বিধবা ও মিসকীনকে সাহায্য: অসহায়ের পাশে দাঁড়ানোর বড় ফজিলত","description":"এই হাদিসের মূল বিষয় বিধবা ও মিসকীনকে সাহায্য করা। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, বিধবা ও মিসকীনের সহযোগী আল্লাহর পথে জিহাদকারীর ন্যায়, এমন তাহাজ্জুদগুজার ব্যক্তির ন্যায় যে অলস হয় না, এবং এমন সিয়াম পালনকারীর ন্যায় যে ইফতার করে না। এই বর্ণনা অসহায় মানুষের পাশে দাঁড়ানোর মর্যাদা বুঝিয়ে দেয়। এখানে প্রধান কীওয়ার্ড হলো বিধবা ও মিসকীনকে সাহায্য। সম্পর্কিত কীওয়ার্ড: অসহায়কে সাহায্য, দান-সদকা, বিধবার ভরণ-পোষণ, মিসকীনের হক, মানবসেবা হাদিস। হাদিসের আলোকে বোঝা যায়, সামাজিক দায়িত্ব শুধু কথায় নয়; বাস্তবে সাহায্য, খোঁজখবর ও ভরণ-পোষণের চেষ্টায় প্রকাশ পায়। তবে সাহায্য যেন সম্মান রেখে করা হয়, কারণ হাদিসটি সহযোগিতার মর্যাদা বলেছে, কাউকে ছোট করার অনুমতি দেয়নি।"},"teachings":["বিধবা ও মিসকীনের সহযোগিতা অত্যন্ত মর্যাদাপূর্ণ কাজ।","অসহায় মানুষের পাশে দাঁড়ানো ইবাদতের মতো বড় নেকির কারণ হতে পারে।","সহযোগিতা করতে গিয়ে মানুষের সম্মান রক্ষা করা জরুরি।"],"related_hadiths":[{"id":"6005","book_id":"1","label":"Sahih Bukhari"},{"id":"1432","book_id":"1","label":"Sahih Bukhari"},{"id":"6011","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিধবা ও মিসকীনকে সাহায্য","description":"$book_name$ $hadith_number$ - $chapter_name$. বিধবা ও মিসকীনের সহযোগিতা বড় নেকির কাজ; হাদিসে এর মর্যাদা জিহাদ, কিয়াম ও সিয়ামের সঙ্গে তুলনা করা হয়েছে।"},"heading":{"title":"বিধবা ও মিসকীনকে সাহায্য: অসহায়ের পাশে দাঁড়ানোর বড় ফজিলত","description":"এই হাদিসের মূল বিষয় বিধবা ও মিসকীনকে সাহায্য করা। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, বিধবা ও মিসকীনের সহযোগী আল্লাহর পথে জিহাদকারীর ন্যায়, এমন তাহাজ্জুদগুজার ব্যক্তির ন্যায় যে অলস হয় না, এবং এমন সিয়াম পালনকারীর ন্যায় যে ইফতার করে না। এই বর্ণনা অসহায় মানুষের পাশে দাঁড়ানোর মর্যাদা বুঝিয়ে দেয়। এখানে প্রধান কীওয়ার্ড হলো বিধবা ও মিসকীনকে সাহায্য। সম্পর্কিত কীওয়ার্ড: অসহায়কে সাহায্য, দান-সদকা, বিধবার ভরণ-পোষণ, মিসকীনের হক, মানবসেবা হাদিস। হাদিসের আলোকে বোঝা যায়, সামাজিক দায়িত্ব শুধু কথায় নয়; বাস্তবে সাহায্য, খোঁজখবর ও ভরণ-পোষণের চেষ্টায় প্রকাশ পায়। তবে সাহায্য যেন সম্মান রেখে করা হয়, কারণ হাদিসটি সহযোগিতার মর্যাদা বলেছে, কাউকে ছোট করার অনুমতি দেয়নি।"},"teachings":["বিধবা ও মিসকীনের সহযোগিতা অত্যন্ত মর্যাদাপূর্ণ কাজ।","অসহায় মানুষের পাশে দাঁড়ানো ইবাদতের মতো বড় নেকির কারণ হতে পারে।","সহযোগিতা করতে গিয়ে মানুষের সম্মান রক্ষা করা জরুরি।"],"related_hadiths":[{"id":"6005","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6011","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E116" s="4" t="n"/>
@@ -3253,7 +3257,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইয়াতীম পালনকারীর মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইয়াতীম পালনকারীর জান্নাতে নবীর নৈকট্যের কথা এসেছে; এটি অসহায় শিশুর যত্নের বড় শিক্ষা।"},"heading":{"title":"ইয়াতীম পালনকারীর মর্যাদা: জান্নাতে নবীর নৈকট্যের হাদিস","description":"এই হাদিসের মূল বিষয় ইয়াতীম পালন। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তিনি ও ইয়াতীম পালনকারী জান্নাতে এভাবে থাকবেন। তারপর তিনি তর্জনী ও মধ্যমা আঙ্গুলের মাঝে সামান্য ফাঁক রেখে ইশারা করেছেন। হাদিসটি ইয়াতীম শিশুর প্রতি দায়িত্ব, দয়া ও যত্নের বড় মর্যাদা বুঝায়। এখানে প্রধান কীওয়ার্ড হলো ইয়াতীম পালনকারীর মর্যাদা। সম্পর্কিত কীওয়ার্ড: ইয়াতীমের হক, এতিমের যত্ন, ইয়াতীমকে সাহায্য, জান্নাতে নবীর সান্নিধ্য, অসহায় শিশুর লালন-পালন। হাদিসটি আমাদের মনে করায়, যে শিশুর সহায় দরকার, তাকে আশ্রয় ও যত্ন দেওয়া শুধু সামাজিক কাজ নয়; এটি বড় নেকির দরজা। তবে ইয়াতীমের সম্পদ বা অধিকার নিয়ে অতিরিক্ত আলোচনা এই হাদিসে নেই, তাই এখানে মূল শিক্ষা শুধু পালন ও যত্নের মর্যাদায় সীমিত রাখা হয়েছে।"},"teachings":["ইয়াতীম শিশুর দায়িত্ব নেওয়া জান্নাতে নবীর নৈকট্যের কারণ হতে পারে।","অসহায় শিশুর প্রতি দয়া, যত্ন ও নিরাপত্তা দেওয়া গুরুত্বপূর্ণ।","ইয়াতীম পালন শুধু দান নয়; এটি দীর্ঘমেয়াদি দায়িত্ব ও মমতার কাজ।"],"related_hadiths":[{"id":"6006","book_id":"1","label":"Sahih Bukhari"},{"id":"1432","book_id":"1","label":"Sahih Bukhari"},{"id":"6008","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইয়াতীম পালনকারীর মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইয়াতীম পালনকারীর জান্নাতে নবীর নৈকট্যের কথা এসেছে; এটি অসহায় শিশুর যত্নের বড় শিক্ষা।"},"heading":{"title":"ইয়াতীম পালনকারীর মর্যাদা: জান্নাতে নবীর নৈকট্যের হাদিস","description":"এই হাদিসের মূল বিষয় ইয়াতীম পালন। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তিনি ও ইয়াতীম পালনকারী জান্নাতে এভাবে থাকবেন। তারপর তিনি তর্জনী ও মধ্যমা আঙ্গুলের মাঝে সামান্য ফাঁক রেখে ইশারা করেছেন। হাদিসটি ইয়াতীম শিশুর প্রতি দায়িত্ব, দয়া ও যত্নের বড় মর্যাদা বুঝায়। এখানে প্রধান কীওয়ার্ড হলো ইয়াতীম পালনকারীর মর্যাদা। সম্পর্কিত কীওয়ার্ড: ইয়াতীমের হক, এতিমের যত্ন, ইয়াতীমকে সাহায্য, জান্নাতে নবীর সান্নিধ্য, অসহায় শিশুর লালন-পালন। হাদিসটি আমাদের মনে করায়, যে শিশুর সহায় দরকার, তাকে আশ্রয় ও যত্ন দেওয়া শুধু সামাজিক কাজ নয়; এটি বড় নেকির দরজা। তবে ইয়াতীমের সম্পদ বা অধিকার নিয়ে অতিরিক্ত আলোচনা এই হাদিসে নেই, তাই এখানে মূল শিক্ষা শুধু পালন ও যত্নের মর্যাদায় সীমিত রাখা হয়েছে।"},"teachings":["ইয়াতীম শিশুর দায়িত্ব নেওয়া জান্নাতে নবীর নৈকট্যের কারণ হতে পারে।","অসহায় শিশুর প্রতি দয়া, যত্ন ও নিরাপত্তা দেওয়া গুরুত্বপূর্ণ।","ইয়াতীম পালন শুধু দান নয়; এটি দীর্ঘমেয়াদি দায়িত্ব ও মমতার কাজ।"],"related_hadiths":[{"id":"6006","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6008","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E117" s="4" t="n"/>
@@ -3276,7 +3280,7 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত, সত্যবাদিতা ও ভালো চরিত্র","description":"$book_name$ $hadith_number$ - $chapter_name$. আমানত রক্ষা, সত্য কথা, ভালো চরিত্র ও খাদ্যে সতর্কতা—এই চার গুণ মানুষের জীবনকে সঠিক পথে রাখে।"},"heading":{"title":"আমানত রক্ষা ও সত্য কথা: জীবনের চারটি মূল্যবান গুণ","description":"এই হাদিসে চারটি গুণের কথা এসেছে, যা একজন মুমিনের জীবনকে সুন্দর করে। আমানত রক্ষা করা, সত্য কথা বলা, উত্তম চরিত্র রাখা এবং খানা-পিনাতে সতর্ক থাকা—এসব বিষয় শুধু ইবাদতের বাইরে আলাদা কিছু নয়; বরং দৈনন্দিন জীবনের বড় পরীক্ষা। আমানত রক্ষা মানে কারো দেওয়া দায়িত্ব, সম্পদ বা বিশ্বাস নষ্ট না করা। সত্য কথা বলা মানে সুবিধা-অসুবিধা দেখে কথা বদলে না ফেলা। উত্তম চরিত্র মানে মানুষের সঙ্গে সুন্দর আচরণ করা। আর খানা-পিনাতে সতর্কতা মানে খাবার ও উপার্জনের উৎস নিয়ে সাবধান থাকা। হাদিসটি দুনিয়ার ক্ষতি নিয়ে হতাশ না হয়ে চরিত্র ও সততার দিকে মন দিতে শেখায়।"},"teachings":["আমানত রক্ষা করা মুমিনের গুরুত্বপূর্ণ গুণ।","সত্য কথা বলা চরিত্রের ভিত্তি মজবুত করে।","খানা-পিনার বিষয়ে সতর্কতা জীবনকে হালাল পথে রাখে।","ভালো চরিত্র মানুষের সঙ্গে আচরণে প্রকাশ পায়।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"2059","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত, সত্যবাদিতা ও ভালো চরিত্র","description":"$book_name$ $hadith_number$ - $chapter_name$. আমানত রক্ষা, সত্য কথা, ভালো চরিত্র ও খাদ্যে সতর্কতা—এই চার গুণ মানুষের জীবনকে সঠিক পথে রাখে।"},"heading":{"title":"আমানত রক্ষা ও সত্য কথা: জীবনের চারটি মূল্যবান গুণ","description":"এই হাদিসে চারটি গুণের কথা এসেছে, যা একজন মুমিনের জীবনকে সুন্দর করে। আমানত রক্ষা করা, সত্য কথা বলা, উত্তম চরিত্র রাখা এবং খানা-পিনাতে সতর্ক থাকা—এসব বিষয় শুধু ইবাদতের বাইরে আলাদা কিছু নয়; বরং দৈনন্দিন জীবনের বড় পরীক্ষা। আমানত রক্ষা মানে কারো দেওয়া দায়িত্ব, সম্পদ বা বিশ্বাস নষ্ট না করা। সত্য কথা বলা মানে সুবিধা-অসুবিধা দেখে কথা বদলে না ফেলা। উত্তম চরিত্র মানে মানুষের সঙ্গে সুন্দর আচরণ করা। আর খানা-পিনাতে সতর্কতা মানে খাবার ও উপার্জনের উৎস নিয়ে সাবধান থাকা। হাদিসটি দুনিয়ার ক্ষতি নিয়ে হতাশ না হয়ে চরিত্র ও সততার দিকে মন দিতে শেখায়।"},"teachings":["আমানত রক্ষা করা মুমিনের গুরুত্বপূর্ণ গুণ।","সত্য কথা বলা চরিত্রের ভিত্তি মজবুত করে।","খানা-পিনার বিষয়ে সতর্কতা জীবনকে হালাল পথে রাখে।","ভালো চরিত্র মানুষের সঙ্গে আচরণে প্রকাশ পায়।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -3303,7 +3307,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুমিন মুমিনের সহায়ক","description":"$book_name$ $hadith_number$ - $chapter_name$. মুমিনকে গৃহের মতো বলা হয়েছে, যার এক অংশ অন্য অংশকে মজবুত রাখে—এটি সহযোগিতার শিক্ষা দেয়।"},"heading":{"title":"মুমিন মুমিনের সহায়ক: একে অন্যকে শক্ত রাখার হাদিস","description":"এই হাদিসের মূল বিষয় মুমিন মুমিনের সহায়ক। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, একজন মুমিন অপর মুমিনের জন্য গৃহের মতো, যার এক অংশ অন্য অংশকে দৃঢ় রাখে। এরপর তিনি দুই হাতের আঙ্গুল একটির মধ্যে আরেকটি প্রবেশ করিয়ে দেখিয়েছেন। এই দৃশ্যমান ইশারা সহযোগিতার অর্থ সহজ করে দেয়। একজন মুসলিম একা সব দায়িত্ব সামলাতে পারে না; অন্য ভাইয়ের সহায়তা, সাহস ও পাশে থাকা দরকার হতে পারে। প্রধান কীওয়ার্ড হলো মুমিন মুমিনের সহায়ক, আর সম্পর্কিত কীওয়ার্ড: মুসলিম ভ্রাতৃত্ব, সহযোগিতার হাদিস, একে অন্যকে সাহায্য, মুমিনের সম্পর্ক। হাদিসটি দলাদলি নয়, বরং ভালো কাজে একে অন্যকে শক্ত করার শিক্ষা দেয়। এখানে নির্দিষ্ট কোনো রাজনৈতিক বা সামাজিক দাবি করা হয়নি; শুধু হাদিসের সরাসরি সহযোগিতার বার্তা তুলে ধরা হয়েছে।"},"teachings":["মুমিনদের একে অন্যের সহায়ক হওয়া উচিত।","ভালো কাজে সহযোগিতা মুসলিম সমাজকে শক্ত রাখে।","সম্পর্ক শুধু কথায় নয়; প্রয়োজনের সময় পাশে দাঁড়ালে তা সত্য হয়।"],"related_hadiths":[{"id":"6011","book_id":"1","label":"Sahih Bukhari"},{"id":"2443","book_id":"1","label":"Sahih Bukhari"},{"id":"1432","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুমিন মুমিনের সহায়ক","description":"$book_name$ $hadith_number$ - $chapter_name$. মুমিনকে গৃহের মতো বলা হয়েছে, যার এক অংশ অন্য অংশকে মজবুত রাখে—এটি সহযোগিতার শিক্ষা দেয়।"},"heading":{"title":"মুমিন মুমিনের সহায়ক: একে অন্যকে শক্ত রাখার হাদিস","description":"এই হাদিসের মূল বিষয় মুমিন মুমিনের সহায়ক। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, একজন মুমিন অপর মুমিনের জন্য গৃহের মতো, যার এক অংশ অন্য অংশকে দৃঢ় রাখে। এরপর তিনি দুই হাতের আঙ্গুল একটির মধ্যে আরেকটি প্রবেশ করিয়ে দেখিয়েছেন। এই দৃশ্যমান ইশারা সহযোগিতার অর্থ সহজ করে দেয়। একজন মুসলিম একা সব দায়িত্ব সামলাতে পারে না; অন্য ভাইয়ের সহায়তা, সাহস ও পাশে থাকা দরকার হতে পারে। প্রধান কীওয়ার্ড হলো মুমিন মুমিনের সহায়ক, আর সম্পর্কিত কীওয়ার্ড: মুসলিম ভ্রাতৃত্ব, সহযোগিতার হাদিস, একে অন্যকে সাহায্য, মুমিনের সম্পর্ক। হাদিসটি দলাদলি নয়, বরং ভালো কাজে একে অন্যকে শক্ত করার শিক্ষা দেয়। এখানে নির্দিষ্ট কোনো রাজনৈতিক বা সামাজিক দাবি করা হয়নি; শুধু হাদিসের সরাসরি সহযোগিতার বার্তা তুলে ধরা হয়েছে।"},"teachings":["মুমিনদের একে অন্যের সহায়ক হওয়া উচিত।","ভালো কাজে সহযোগিতা মুসলিম সমাজকে শক্ত রাখে।","সম্পর্ক শুধু কথায় নয়; প্রয়োজনের সময় পাশে দাঁড়ালে তা সত্য হয়।"],"related_hadiths":[{"id":"6011","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2443","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E119" s="4" t="n"/>
@@ -3326,7 +3330,7 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অভাবীর জন্য সুপারিশ","description":"$book_name$ $hadith_number$ - $chapter_name$. অভাবী বা প্রয়োজনমন্দের জন্য সুপারিশ করলে নেকি হতে পারে; চূড়ান্ত ফায়সালা আল্লাহর ইচ্ছায় হয়।"},"heading":{"title":"অভাবীর জন্য সুপারিশ: সাহায্যের দরজা খুলে দেওয়ার হাদিস","description":"এই হাদিসের মূল বিষয় অভাবীর জন্য সুপারিশ। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর কাছে কোনো ভিক্ষুক বা প্রয়োজনমন্দ এলে তিনি সাহাবীদের বলতেন, তোমরা সুপারিশ কর, এতে তোমাদের নেকি দেওয়া হবে। আর আল্লাহ তাঁর রাসূলের মুখ দিয়ে যে ফয়সালা চান তা জারি করবেন। হাদিসটি দেখায়, সরাসরি সাহায্য করতে না পারলেও ভালো সুপারিশ, পরিচয় করিয়ে দেওয়া বা প্রয়োজনের কথা পৌঁছে দেওয়া নেকির কাজ হতে পারে। প্রধান কীওয়ার্ড হলো অভাবীর জন্য সুপারিশ। সম্পর্কিত কীওয়ার্ড: দরিদ্রকে সাহায্য, নেক সুপারিশ, প্রয়োজনমন্দের সহায়তা, ইসলামে সুপারিশ। হাদিসে একই সঙ্গে ভারসাম্যও আছে—সুপারিশ করা মানুষের কাজ, কিন্তু ফল আল্লাহর ইচ্ছা অনুযায়ী হয়। তাই সাহায্যের চেষ্টা করতে হবে, তবে ফল নিয়ে অহংকার বা চাপ সৃষ্টি করা ঠিক নয়।"},"teachings":["অভাবী মানুষের প্রয়োজনে ভালো সুপারিশ করা নেকির কারণ হতে পারে।","সরাসরি দিতে না পারলেও সাহায্যের দরজা খুলে দেওয়া যায়।","মানুষ চেষ্টা করবে, আর চূড়ান্ত ফল আল্লাহর ইচ্ছার উপর ছেড়ে দেবে।"],"related_hadiths":[{"id":"6006","book_id":"1","label":"Sahih Bukhari"},{"id":"6005","book_id":"1","label":"Sahih Bukhari"},{"id":"6019","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অভাবীর জন্য সুপারিশ","description":"$book_name$ $hadith_number$ - $chapter_name$. অভাবী বা প্রয়োজনমন্দের জন্য সুপারিশ করলে নেকি হতে পারে; চূড়ান্ত ফায়সালা আল্লাহর ইচ্ছায় হয়।"},"heading":{"title":"অভাবীর জন্য সুপারিশ: সাহায্যের দরজা খুলে দেওয়ার হাদিস","description":"এই হাদিসের মূল বিষয় অভাবীর জন্য সুপারিশ। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর কাছে কোনো ভিক্ষুক বা প্রয়োজনমন্দ এলে তিনি সাহাবীদের বলতেন, তোমরা সুপারিশ কর, এতে তোমাদের নেকি দেওয়া হবে। আর আল্লাহ তাঁর রাসূলের মুখ দিয়ে যে ফয়সালা চান তা জারি করবেন। হাদিসটি দেখায়, সরাসরি সাহায্য করতে না পারলেও ভালো সুপারিশ, পরিচয় করিয়ে দেওয়া বা প্রয়োজনের কথা পৌঁছে দেওয়া নেকির কাজ হতে পারে। প্রধান কীওয়ার্ড হলো অভাবীর জন্য সুপারিশ। সম্পর্কিত কীওয়ার্ড: দরিদ্রকে সাহায্য, নেক সুপারিশ, প্রয়োজনমন্দের সহায়তা, ইসলামে সুপারিশ। হাদিসে একই সঙ্গে ভারসাম্যও আছে—সুপারিশ করা মানুষের কাজ, কিন্তু ফল আল্লাহর ইচ্ছা অনুযায়ী হয়। তাই সাহায্যের চেষ্টা করতে হবে, তবে ফল নিয়ে অহংকার বা চাপ সৃষ্টি করা ঠিক নয়।"},"teachings":["অভাবী মানুষের প্রয়োজনে ভালো সুপারিশ করা নেকির কারণ হতে পারে।","সরাসরি দিতে না পারলেও সাহায্যের দরজা খুলে দেওয়া যায়।","মানুষ চেষ্টা করবে, আর চূড়ান্ত ফল আল্লাহর ইচ্ছার উপর ছেড়ে দেবে।"],"related_hadiths":[{"id":"6006","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6005","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6019","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E120" s="4" t="n"/>
@@ -3349,7 +3353,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যালিম ও মাযলুমকে সাহায্য","description":"$book_name$ $hadith_number$ - $chapter_name$. অত্যাচারিতকে সাহায্য করা যেমন জরুরি, তেমনি অত্যাচারীকে যুলুম থেকে থামানোও তার প্রতি সাহায্য।"},"heading":{"title":"যালিম ও মাযলুমকে সাহায্য: যুলুম থামানোই প্রকৃত সহায়তা","description":"এই হাদিসের মূল বিষয় যুলুম থেকে বিরত রাখা। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তোমার ভাইকে সাহায্য কর, সে অত্যাচারী হোক বা অত্যাচারিত হোক। সাহাবী প্রশ্ন করলেন, অত্যাচারিতকে সাহায্য করা বোঝা যায়, কিন্তু অত্যাচারীকে কীভাবে সাহায্য করা হবে? তিনি বললেন, তাকে যুলুম করা থেকে বিরত রাখাই তার সাহায্য। এখানে প্রধান কীওয়ার্ড হলো যালিম ও মাযলুমকে সাহায্য। সম্পর্কিত কীওয়ার্ড: যুলুম থেকে বিরত রাখা, অত্যাচারিতের পাশে দাঁড়ানো, অন্যায় বন্ধ করা, মুসলিম ভাইকে সাহায্য। হাদিসটি খুব ভারসাম্যপূর্ণ শিক্ষা দেয়। নিজের লোক বলে অন্যায়ের পক্ষে দাঁড়ানো সাহায্য নয়। প্রকৃত সাহায্য হলো অন্যায়কারীকে থামানো এবং অত্যাচারিতকে রক্ষা করা। হাদিসের বাইরে কোনো শাস্তি বা আইনগত ধাপ এখানে যোগ করা হয়নি; শুধু নৈতিক দায়িত্বের কথা বলা হয়েছে।"},"teachings":["অত্যাচারিত মানুষের পাশে দাঁড়ানো জরুরি।","অত্যাচারীকে যুলুম থেকে থামানোও তার প্রতি সত্যিকারের সাহায্য।","নিজের ভাই হলেও অন্যায়ের পক্ষে দাঁড়ানো ঠিক নয়।"],"related_hadiths":[{"id":"1432","book_id":"1","label":"Sahih Bukhari"},{"id":"6011","book_id":"1","label":"Sahih Bukhari"},{"id":"6013","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যালিম ও মাযলুমকে সাহায্য","description":"$book_name$ $hadith_number$ - $chapter_name$. অত্যাচারিতকে সাহায্য করা যেমন জরুরি, তেমনি অত্যাচারীকে যুলুম থেকে থামানোও তার প্রতি সাহায্য।"},"heading":{"title":"যালিম ও মাযলুমকে সাহায্য: যুলুম থামানোই প্রকৃত সহায়তা","description":"এই হাদিসের মূল বিষয় যুলুম থেকে বিরত রাখা। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তোমার ভাইকে সাহায্য কর, সে অত্যাচারী হোক বা অত্যাচারিত হোক। সাহাবী প্রশ্ন করলেন, অত্যাচারিতকে সাহায্য করা বোঝা যায়, কিন্তু অত্যাচারীকে কীভাবে সাহায্য করা হবে? তিনি বললেন, তাকে যুলুম করা থেকে বিরত রাখাই তার সাহায্য। এখানে প্রধান কীওয়ার্ড হলো যালিম ও মাযলুমকে সাহায্য। সম্পর্কিত কীওয়ার্ড: যুলুম থেকে বিরত রাখা, অত্যাচারিতের পাশে দাঁড়ানো, অন্যায় বন্ধ করা, মুসলিম ভাইকে সাহায্য। হাদিসটি খুব ভারসাম্যপূর্ণ শিক্ষা দেয়। নিজের লোক বলে অন্যায়ের পক্ষে দাঁড়ানো সাহায্য নয়। প্রকৃত সাহায্য হলো অন্যায়কারীকে থামানো এবং অত্যাচারিতকে রক্ষা করা। হাদিসের বাইরে কোনো শাস্তি বা আইনগত ধাপ এখানে যোগ করা হয়নি; শুধু নৈতিক দায়িত্বের কথা বলা হয়েছে।"},"teachings":["অত্যাচারিত মানুষের পাশে দাঁড়ানো জরুরি।","অত্যাচারীকে যুলুম থেকে থামানোও তার প্রতি সত্যিকারের সাহায্য।","নিজের ভাই হলেও অন্যায়ের পক্ষে দাঁড়ানো ঠিক নয়।"],"related_hadiths":[{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6011","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6013","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E121" s="4" t="n"/>
@@ -3372,7 +3376,7 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুসলিম ভাইয়ের হক ও সাহায্য","description":"$book_name$ $hadith_number$ - $chapter_name$. মুসলিম ভাইয়ের উপর যুলুম না করা, প্রয়োজন পূরণ, কষ্ট দূর করা ও দোষ ঢাকার শিক্ষা একসাথে এসেছে।"},"heading":{"title":"মুসলিম ভাইয়ের হক: সাহায্য, কষ্ট দূর করা ও দোষ ঢাকার শিক্ষা","description":"এই হাদিসের মূল বিষয় মুসলিম ভাইয়ের হক। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, এক মুসলমান অপর মুসলমানের ভাই। সে তার উপর যুলুম করবে না এবং তাকে ধ্বংসের দিকে ঠেলে দেবে না। যে তার মুসলিম ভাইয়ের প্রয়োজনে সাহায্য করবে, আল্লাহ তার প্রয়োজনের সাহায্য করবেন। যে মুসলমানের দুঃখ-কষ্ট দূর করবে, আল্লাহ কিয়ামতের দিনের বিপদ থেকে তাকে মুক্তির কারণ দেবেন। আর যে মুসলমানের দোষ ঢেকে রাখবে, আল্লাহ তার দোষ ঢেকে রাখবেন। প্রধান কীওয়ার্ড হলো মুসলিম ভাইয়ের হক। সম্পর্কিত কীওয়ার্ড: মুসলিমকে সাহায্য, কষ্ট দূর করার হাদিস, দোষ ঢেকে রাখা, মুসলিম ভ্রাতৃত্ব, যুলুম না করা। হাদিসটি সম্পর্ককে বাস্তব কাজে নামিয়ে আনে—অন্যায় না করা, অসহায় না ফেলে রাখা, প্রয়োজনে পাশে থাকা এবং অকারণে দোষ ছড়িয়ে না দেওয়া।"},"teachings":["মুসলিম ভাইয়ের উপর যুলুম করা যাবে না এবং তাকে বিপদে ফেলে রাখা ঠিক নয়।","ভাইয়ের প্রয়োজন পূরণে সাহায্য করা আল্লাহর সাহায্য লাভের কারণ হতে পারে।","মুসলমানের দুঃখ-কষ্ট দূর করা ও দোষ ঢেকে রাখা বড় নেকির কাজ।"],"related_hadiths":[{"id":"2443","book_id":"1","label":"Sahih Bukhari"},{"id":"1432","book_id":"1","label":"Sahih Bukhari"},{"id":"6013","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুসলিম ভাইয়ের হক ও সাহায্য","description":"$book_name$ $hadith_number$ - $chapter_name$. মুসলিম ভাইয়ের উপর যুলুম না করা, প্রয়োজন পূরণ, কষ্ট দূর করা ও দোষ ঢাকার শিক্ষা একসাথে এসেছে।"},"heading":{"title":"মুসলিম ভাইয়ের হক: সাহায্য, কষ্ট দূর করা ও দোষ ঢাকার শিক্ষা","description":"এই হাদিসের মূল বিষয় মুসলিম ভাইয়ের হক। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, এক মুসলমান অপর মুসলমানের ভাই। সে তার উপর যুলুম করবে না এবং তাকে ধ্বংসের দিকে ঠেলে দেবে না। যে তার মুসলিম ভাইয়ের প্রয়োজনে সাহায্য করবে, আল্লাহ তার প্রয়োজনের সাহায্য করবেন। যে মুসলমানের দুঃখ-কষ্ট দূর করবে, আল্লাহ কিয়ামতের দিনের বিপদ থেকে তাকে মুক্তির কারণ দেবেন। আর যে মুসলমানের দোষ ঢেকে রাখবে, আল্লাহ তার দোষ ঢেকে রাখবেন। প্রধান কীওয়ার্ড হলো মুসলিম ভাইয়ের হক। সম্পর্কিত কীওয়ার্ড: মুসলিমকে সাহায্য, কষ্ট দূর করার হাদিস, দোষ ঢেকে রাখা, মুসলিম ভ্রাতৃত্ব, যুলুম না করা। হাদিসটি সম্পর্ককে বাস্তব কাজে নামিয়ে আনে—অন্যায় না করা, অসহায় না ফেলে রাখা, প্রয়োজনে পাশে থাকা এবং অকারণে দোষ ছড়িয়ে না দেওয়া।"},"teachings":["মুসলিম ভাইয়ের উপর যুলুম করা যাবে না এবং তাকে বিপদে ফেলে রাখা ঠিক নয়।","ভাইয়ের প্রয়োজন পূরণে সাহায্য করা আল্লাহর সাহায্য লাভের কারণ হতে পারে।","মুসলমানের দুঃখ-কষ্ট দূর করা ও দোষ ঢেকে রাখা বড় নেকির কাজ।"],"related_hadiths":[{"id":"2443","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6013","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E122" s="4" t="n"/>
@@ -3395,7 +3399,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গনীমতের মাল আত্মসাৎ থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. গনীমতের মাল সময়মতো জমা না দিয়ে পরে অজুহাত দেখানো গ্রহণযোগ্য নয়; আত্মসাৎ ছোট হলেও দায় থেকে যায়।"},"heading":{"title":"গনীমতের মাল আত্মসাৎ: অজুহাত নয়, সময়মতো আমানত জমা দিন","description":"এই হাদিসে গনীমতের মাল বণ্টনের নিয়ম ও আমানতদারির গুরুত্ব দেখা যায়। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) গনীমতের মাল এলে বেলাল (রাঃ)-কে ঘোষণা দিতে বলতেন। লোকেরা যার কাছে যা থাকত তা নিয়ে আসত। তারপর খুমুস বের করে বাকি মাল বণ্টন করা হতো। কিন্তু এক ব্যক্তি সব শেষ হওয়ার পর পশমের লাগাম নিয়ে এসে বলল, এটি গনীমতের মাল। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাকে জিজ্ঞেস করলেন, ঘোষণা শুনেও কেন আগে আনেনি। তার অজুহাত গ্রহণ করা হয়নি। হাদিসটি শেখায়, গনীমতের মাল আত্মসাৎ বা দেরিতে গোপন রাখা খুবই গুরুতর বিষয়। আমানত সময়মতো আদায় করা জরুরি।"},"teachings":["গনীমতের মাল ব্যক্তিগতভাবে রেখে দেওয়া ঠিক নয়।","ঘোষণা শোনার পর আমানত দেরি না করে জমা দিতে হয়।","ছোট জিনিস হলেও আত্মসাৎ হালকা বিষয় নয়।","অজুহাত দিয়ে দায়িত্ব এড়ানো নিরাপদ পথ নয়।"],"related_hadiths":[{"id":"3073","book_id":"1","label":"Sahih Bukhari"},{"id":"3074","book_id":"1","label":"Sahih Bukhari"},{"id":"210","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গনীমতের মাল আত্মসাৎ থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. গনীমতের মাল সময়মতো জমা না দিয়ে পরে অজুহাত দেখানো গ্রহণযোগ্য নয়; আত্মসাৎ ছোট হলেও দায় থেকে যায়।"},"heading":{"title":"গনীমতের মাল আত্মসাৎ: অজুহাত নয়, সময়মতো আমানত জমা দিন","description":"এই হাদিসে গনীমতের মাল বণ্টনের নিয়ম ও আমানতদারির গুরুত্ব দেখা যায়। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) গনীমতের মাল এলে বেলাল (রাঃ)-কে ঘোষণা দিতে বলতেন। লোকেরা যার কাছে যা থাকত তা নিয়ে আসত। তারপর খুমুস বের করে বাকি মাল বণ্টন করা হতো। কিন্তু এক ব্যক্তি সব শেষ হওয়ার পর পশমের লাগাম নিয়ে এসে বলল, এটি গনীমতের মাল। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাকে জিজ্ঞেস করলেন, ঘোষণা শুনেও কেন আগে আনেনি। তার অজুহাত গ্রহণ করা হয়নি। হাদিসটি শেখায়, গনীমতের মাল আত্মসাৎ বা দেরিতে গোপন রাখা খুবই গুরুতর বিষয়। আমানত সময়মতো আদায় করা জরুরি।"},"teachings":["গনীমতের মাল ব্যক্তিগতভাবে রেখে দেওয়া ঠিক নয়।","ঘোষণা শোনার পর আমানত দেরি না করে জমা দিতে হয়।","ছোট জিনিস হলেও আত্মসাৎ হালকা বিষয় নয়।","অজুহাত দিয়ে দায়িত্ব এড়ানো নিরাপদ পথ নয়।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E123" s="4" t="n"/>
@@ -3418,7 +3422,7 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সম্পদে সততা ও বরকতের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. সম্পদ আকর্ষণীয় হলেও ন্যায্যভাবে অর্জন করলে তাতে বরকত হয়; অন্যায় তসরূপ আখিরাতের ক্ষতির কারণ।"},"heading":{"title":"হালাল সম্পদে বরকত: আল্লাহর সম্পদে অন্যায় তসরূপ নয়","description":"এই হাদিসে সম্পদের আকর্ষণ ও তার পরীক্ষার কথা বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, পার্থিব সম্পদ শ্যামল ও সুমিষ্ট, অর্থাৎ মানুষকে টানে। কিন্তু সম্পদ তখনই কল্যাণের কারণ হয়, যখন তা ন্যায়ভাবে পাওয়া যায়। হালাল সম্পদে বরকত—এই শিক্ষা এখানেই স্পষ্ট। আবার যারা আল্লাহ ও তাঁর রাসূলের সম্পদে নিজের ইচ্ছামতো তসরূপ করে, তাদের জন্য কিয়ামতের দিন কঠিন পরিণামের কথা এসেছে। তাই সম্পদ বেশি হওয়াই মূল কথা নয়; বরং তা কীভাবে পাওয়া হলো এবং কীভাবে ব্যবহার করা হলো, সেটাই বড় বিষয়। বিশেষ করে দায়িত্বে থাকা মাল, গনীমত বা জনস্বার্থের সম্পদে সততা রাখা খুব জরুরি।"},"teachings":["সম্পদ আকর্ষণীয় হলেও তা পরীক্ষা হতে পারে।","ন্যায়ভাবে পাওয়া সম্পদে বরকতের কথা এসেছে।","আল্লাহ ও রাসূলের সম্পদে অন্যায় তসরূপ গুরুতর অপরাধ।","সম্পদের উৎস ও ব্যবহার—দুই দিকেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"3118","book_id":"1","label":"Sahih Bukhari"},{"id":"3073","book_id":"1","label":"Sahih Bukhari"},{"id":"210","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সম্পদে সততা ও বরকতের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. সম্পদ আকর্ষণীয় হলেও ন্যায্যভাবে অর্জন করলে তাতে বরকত হয়; অন্যায় তসরূপ আখিরাতের ক্ষতির কারণ।"},"heading":{"title":"হালাল সম্পদে বরকত: আল্লাহর সম্পদে অন্যায় তসরূপ নয়","description":"এই হাদিসে সম্পদের আকর্ষণ ও তার পরীক্ষার কথা বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, পার্থিব সম্পদ শ্যামল ও সুমিষ্ট, অর্থাৎ মানুষকে টানে। কিন্তু সম্পদ তখনই কল্যাণের কারণ হয়, যখন তা ন্যায়ভাবে পাওয়া যায়। হালাল সম্পদে বরকত—এই শিক্ষা এখানেই স্পষ্ট। আবার যারা আল্লাহ ও তাঁর রাসূলের সম্পদে নিজের ইচ্ছামতো তসরূপ করে, তাদের জন্য কিয়ামতের দিন কঠিন পরিণামের কথা এসেছে। তাই সম্পদ বেশি হওয়াই মূল কথা নয়; বরং তা কীভাবে পাওয়া হলো এবং কীভাবে ব্যবহার করা হলো, সেটাই বড় বিষয়। বিশেষ করে দায়িত্বে থাকা মাল, গনীমত বা জনস্বার্থের সম্পদে সততা রাখা খুব জরুরি।"},"teachings":["সম্পদ আকর্ষণীয় হলেও তা পরীক্ষা হতে পারে।","ন্যায়ভাবে পাওয়া সম্পদে বরকতের কথা এসেছে।","আল্লাহ ও রাসূলের সম্পদে অন্যায় তসরূপ গুরুতর অপরাধ।","সম্পদের উৎস ও ব্যবহার—দুই দিকেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"3118","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E124" s="4" t="n"/>
@@ -3441,7 +3445,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | খিয়ানত ও কিয়ামতের জবাবদিহি","description":"$book_name$ $hadith_number$ - $chapter_name$. খিয়ানত করা বস্তু কিয়ামতে মানুষের কাঁধে প্রকাশ পাবে; নবী আগেই সতর্ক করেছেন, তাই আমানত রক্ষা জরুরি।"},"heading":{"title":"খিয়ানত থেকে বাঁচুন: কিয়ামতে গোপন আত্মসাৎ প্রকাশ পাবে","description":"এই হাদিসে খিয়ানতের ভয়াবহতা খুব পরিষ্কারভাবে এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খিয়ানতের বিষয়টি বড় করে তুলে ধরেছেন এবং কিয়ামতের দিনের কয়েকটি দৃশ্য বলেছেন। কেউ উট, কেউ ঘোড়া, কেউ ছাগল, কেউ মানুষ, কেউ কাপড়, কেউ সোনা-চাঁদির মতো সম্পদ কাঁধে নিয়ে আসবে—অর্থাৎ যে জিনিসে খিয়ানত করেছে, সেটিই তার দায় হয়ে প্রকাশ পাবে। তখন সে সাহায্য চাইবে, কিন্তু রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলবেন, তিনি আগেই আল্লাহর বিধান জানিয়ে দিয়েছেন। এই হাদিস আত্মসাৎ ও খিয়ানত থেকে কঠোরভাবে সতর্ক করে। আমানত লুকিয়ে রাখা, দায়িত্বের সম্পদ নেওয়া বা অন্যের মাল নিজের করে নেওয়া কখনো নিরাপদ নয়।"},"teachings":["খিয়ানত করা বস্তু কিয়ামতে দায় হিসেবে প্রকাশ পাবে।","আগে সতর্ক করা হলে পরে অজুহাতের সুযোগ কমে যায়।","অন্যের মাল, প্রাণী, কাপড় বা সম্পদ আত্মসাৎ করা গুরুতর বিষয়।","আমানত রক্ষা করা আখিরাতের জবাবদিহির সঙ্গে জড়িত।"],"related_hadiths":[{"id":"3073","book_id":"1","label":"Sahih Bukhari"},{"id":"3074","book_id":"1","label":"Sahih Bukhari"},{"id":"1201","book_id":"10","label":"Luluwal Marjan"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | খিয়ানত ও কিয়ামতের জবাবদিহি","description":"$book_name$ $hadith_number$ - $chapter_name$. খিয়ানত করা বস্তু কিয়ামতে মানুষের কাঁধে প্রকাশ পাবে; নবী আগেই সতর্ক করেছেন, তাই আমানত রক্ষা জরুরি।"},"heading":{"title":"খিয়ানত থেকে বাঁচুন: কিয়ামতে গোপন আত্মসাৎ প্রকাশ পাবে","description":"এই হাদিসে খিয়ানতের ভয়াবহতা খুব পরিষ্কারভাবে এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খিয়ানতের বিষয়টি বড় করে তুলে ধরেছেন এবং কিয়ামতের দিনের কয়েকটি দৃশ্য বলেছেন। কেউ উট, কেউ ঘোড়া, কেউ ছাগল, কেউ মানুষ, কেউ কাপড়, কেউ সোনা-চাঁদির মতো সম্পদ কাঁধে নিয়ে আসবে—অর্থাৎ যে জিনিসে খিয়ানত করেছে, সেটিই তার দায় হয়ে প্রকাশ পাবে। তখন সে সাহায্য চাইবে, কিন্তু রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলবেন, তিনি আগেই আল্লাহর বিধান জানিয়ে দিয়েছেন। এই হাদিস আত্মসাৎ ও খিয়ানত থেকে কঠোরভাবে সতর্ক করে। আমানত লুকিয়ে রাখা, দায়িত্বের সম্পদ নেওয়া বা অন্যের মাল নিজের করে নেওয়া কখনো নিরাপদ নয়।"},"teachings":["খিয়ানত করা বস্তু কিয়ামতে দায় হিসেবে প্রকাশ পাবে।","আগে সতর্ক করা হলে পরে অজুহাতের সুযোগ কমে যায়।","অন্যের মাল, প্রাণী, কাপড় বা সম্পদ আত্মসাৎ করা গুরুতর বিষয়।","আমানত রক্ষা করা আখিরাতের জবাবদিহির সঙ্গে জড়িত।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1201","book_id":"10","slug":"luluwal-marjan","label":"লুলুওয়াল মারজান"}]}</t>
         </is>
       </c>
       <c r="E125" s="4" t="n"/>
@@ -3464,7 +3468,7 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সামান্য আত্মসাতের বড় পরিণাম","description":"$book_name$ $hadith_number$ - $chapter_name$. গনীমত বণ্টনের আগে নেওয়া ছোট চাদরও আগুনের কারণ বলা হয়েছে; আত্মসাৎ ছোট মনে করা উচিত নয়।"},"heading":{"title":"সামান্য আত্মসাৎও ভয়াবহ: গনীমতের মাল নিয়ে সতর্ক হোন","description":"এই হাদিসে মিদআম নামে এক ব্যক্তির ঘটনা এসেছে। তিনি মারা গেলে সাহাবীগণ তার জন্য জান্নাতের কথা বলেছিলেন। কিন্তু রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) জানালেন, খায়বারের গনীমত বণ্টনের আগে নেওয়া একটি চাদর তার জন্য আগুনের কারণ হচ্ছে। এটি শুনে একজন লোক জুতার ফিতা বা দু’টি ফিতা নিয়ে এলো। তখনও রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সেটির ব্যাপারে আগুনের কথা বললেন। এই হাদিসের মূল শিক্ষা হলো, আত্মসাৎ ছোট মনে করা যাবে না। গনীমতের মাল হোক বা অন্য কোনো আমানত—বণ্টন বা অনুমতি ছাড়া নেওয়া বড় দায়। বাহ্যিকভাবে ভালো অবস্থায় মৃত্যু হলেও মানুষের গোপন কাজের হিসাব আল্লাহর কাছে থাকবে।"},"teachings":["গনীমত বণ্টনের আগে কিছু নেওয়া আত্মসাতের মধ্যে পড়ে।","সামান্য বস্তু হলেও আত্মসাৎকে ছোট মনে করা ঠিক নয়।","মানুষের বাহ্যিক ধারণা সব সময় আসল অবস্থা জানায় না।","অমানত ও গনীমতের মাল ফেরত দিতে দেরি করা বিপজ্জনক।"],"related_hadiths":[{"id":"3073","book_id":"1","label":"Sahih Bukhari"},{"id":"3074","book_id":"1","label":"Sahih Bukhari"},{"id":"3118","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সামান্য আত্মসাতের বড় পরিণাম","description":"$book_name$ $hadith_number$ - $chapter_name$. গনীমত বণ্টনের আগে নেওয়া ছোট চাদরও আগুনের কারণ বলা হয়েছে; আত্মসাৎ ছোট মনে করা উচিত নয়।"},"heading":{"title":"সামান্য আত্মসাৎও ভয়াবহ: গনীমতের মাল নিয়ে সতর্ক হোন","description":"এই হাদিসে মিদআম নামে এক ব্যক্তির ঘটনা এসেছে। তিনি মারা গেলে সাহাবীগণ তার জন্য জান্নাতের কথা বলেছিলেন। কিন্তু রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) জানালেন, খায়বারের গনীমত বণ্টনের আগে নেওয়া একটি চাদর তার জন্য আগুনের কারণ হচ্ছে। এটি শুনে একজন লোক জুতার ফিতা বা দু’টি ফিতা নিয়ে এলো। তখনও রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সেটির ব্যাপারে আগুনের কথা বললেন। এই হাদিসের মূল শিক্ষা হলো, আত্মসাৎ ছোট মনে করা যাবে না। গনীমতের মাল হোক বা অন্য কোনো আমানত—বণ্টন বা অনুমতি ছাড়া নেওয়া বড় দায়। বাহ্যিকভাবে ভালো অবস্থায় মৃত্যু হলেও মানুষের গোপন কাজের হিসাব আল্লাহর কাছে থাকবে।"},"teachings":["গনীমত বণ্টনের আগে কিছু নেওয়া আত্মসাতের মধ্যে পড়ে।","সামান্য বস্তু হলেও আত্মসাৎকে ছোট মনে করা ঠিক নয়।","মানুষের বাহ্যিক ধারণা সব সময় আসল অবস্থা জানায় না।","অমানত ও গনীমতের মাল ফেরত দিতে দেরি করা বিপজ্জনক।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3118","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E126" s="4" t="n"/>
@@ -3487,7 +3491,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দায়িত্বের মাল আত্মসাৎ থেকে ভয়","description":"$book_name$ $hadith_number$ - $chapter_name$. দায়িত্বে থাকা ব্যক্তির চাদর আত্মসাৎ তার পরিণামকে ভয়াবহ করেছে; আমানতের মাল গোপন করা বড় অপরাধ।"},"heading":{"title":"দায়িত্বের মাল আত্মসাৎ: কারকারার ঘটনা থেকে সতর্ক শিক্ষা","description":"এই হাদিসে এমন এক ব্যক্তির কথা এসেছে, যে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর গনীমতের মালের দায়িত্বে ছিল। তার নাম ছিল কারকারা। সে মারা গেলে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাকে জাহান্নামী বলে জানান। পরে সাহাবীগণ গিয়ে দেখলেন, সে একটি চাদর আত্মসাৎ করেছিল। হাদিসটি দায়িত্বের মাল আত্মসাৎ সম্পর্কে কঠিন সতর্কতা দেয়। কেউ যদি কোনো সম্পদের পাহারাদার, দায়িত্বশীল বা ব্যবস্থাপক হয়, তাহলে তার দায়িত্ব আরও বড়। কারণ সে নিজের জন্য নয়, আমানতের জন্য কাজ করছে। একটি চাদরকে ছোট মনে করা হলেও হাদিসে তার পরিণাম কঠিনভাবে এসেছে। তাই সরকারি, সামাজিক, পারিবারিক বা যে কোনো দায়িত্বের মাল নিজের করে নেওয়া থেকে বেঁচে থাকা দরকার।"},"teachings":["দায়িত্বে থাকা মাল নিজের জন্য নেওয়া খিয়ানত।","আত্মসাৎ করা বস্তু ছোট হলেও এর দায় বড় হতে পারে।","দায়িত্বশীল ব্যক্তির আমানতদারি আরও বেশি জরুরি।","গোপনভাবে নেওয়া জিনিস আল্লাহর কাছে গোপন থাকে না।"],"related_hadiths":[{"id":"210","book_id":"2","label":"Sahih Muslim"},{"id":"3073","book_id":"1","label":"Sahih Bukhari"},{"id":"3118","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দায়িত্বের মাল আত্মসাৎ থেকে ভয়","description":"$book_name$ $hadith_number$ - $chapter_name$. দায়িত্বে থাকা ব্যক্তির চাদর আত্মসাৎ তার পরিণামকে ভয়াবহ করেছে; আমানতের মাল গোপন করা বড় অপরাধ।"},"heading":{"title":"দায়িত্বের মাল আত্মসাৎ: কারকারার ঘটনা থেকে সতর্ক শিক্ষা","description":"এই হাদিসে এমন এক ব্যক্তির কথা এসেছে, যে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর গনীমতের মালের দায়িত্বে ছিল। তার নাম ছিল কারকারা। সে মারা গেলে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাকে জাহান্নামী বলে জানান। পরে সাহাবীগণ গিয়ে দেখলেন, সে একটি চাদর আত্মসাৎ করেছিল। হাদিসটি দায়িত্বের মাল আত্মসাৎ সম্পর্কে কঠিন সতর্কতা দেয়। কেউ যদি কোনো সম্পদের পাহারাদার, দায়িত্বশীল বা ব্যবস্থাপক হয়, তাহলে তার দায়িত্ব আরও বড়। কারণ সে নিজের জন্য নয়, আমানতের জন্য কাজ করছে। একটি চাদরকে ছোট মনে করা হলেও হাদিসে তার পরিণাম কঠিনভাবে এসেছে। তাই সরকারি, সামাজিক, পারিবারিক বা যে কোনো দায়িত্বের মাল নিজের করে নেওয়া থেকে বেঁচে থাকা দরকার।"},"teachings":["দায়িত্বে থাকা মাল নিজের জন্য নেওয়া খিয়ানত।","আত্মসাৎ করা বস্তু ছোট হলেও এর দায় বড় হতে পারে।","দায়িত্বশীল ব্যক্তির আমানতদারি আরও বেশি জরুরি।","গোপনভাবে নেওয়া জিনিস আল্লাহর কাছে গোপন থাকে না।"],"related_hadiths":[{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3118","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E127" s="4" t="n"/>
@@ -3510,7 +3514,7 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আত্মসাৎ শহীদের মর্যাদায় বাধা","description":"$book_name$ $hadith_number$ - $chapter_name$. বাহ্যিকভাবে শহীদ বলা হলেও চাদর আত্মসাৎকারীর পরিণাম কঠিন হয়েছে; গোপন খিয়ানত থেকে সতর্ক থাকতে হবে।"},"heading":{"title":"আত্মসাৎ ও শহীদের দাবি: গোপন খিয়ানত আখিরাতে প্রকাশ পায়","description":"এই হাদিসে খায়বারের দিনের একটি ঘটনা এসেছে। সাহাবীগণ কয়েকজনকে শহীদ বলছিলেন। এমন একজনের ব্যাপারে তারা শহীদ বললে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বললেন, কখনো নয়; তিনি তাকে জাহান্নামে দেখেছেন, কারণ সে একটি চাদর আত্মসাৎ করেছিল। এই বক্তব্য খুব গভীর শিক্ষা দেয়। মানুষের চোখে কেউ বাহ্যিকভাবে ভালো বা সম্মানিত মনে হতে পারে, কিন্তু গোপন খিয়ানত থাকলে তার হিসাব আল্লাহর কাছে থাকবে। আত্মসাৎ শহীদের মর্যাদার দাবিকেও বিপদে ফেলতে পারে—হাদিসের ভাষায় বিষয়টি এভাবেই এসেছে। তাই গনীমতের মাল, দায়িত্বের মাল বা কোনো আমানত গোপনে নেওয়া থেকে কঠোরভাবে বাঁচা দরকার।"},"teachings":["মানুষের বাহ্যিক প্রশংসা আখিরাতের হিসাব বদলায় না।","একটি চাদর আত্মসাৎ করাও ভয়াবহ পরিণামের কারণ হয়েছে।","গোপন খিয়ানত মানুষের মর্যাদাকে ক্ষতিগ্রস্ত করতে পারে।","আল্লাহর কাছে আমানতের হিসাব খুবই গুরুতর।"],"related_hadiths":[{"id":"3073","book_id":"1","label":"Sahih Bukhari"},{"id":"3074","book_id":"1","label":"Sahih Bukhari"},{"id":"210","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আত্মসাৎ শহীদের মর্যাদায় বাধা","description":"$book_name$ $hadith_number$ - $chapter_name$. বাহ্যিকভাবে শহীদ বলা হলেও চাদর আত্মসাৎকারীর পরিণাম কঠিন হয়েছে; গোপন খিয়ানত থেকে সতর্ক থাকতে হবে।"},"heading":{"title":"আত্মসাৎ ও শহীদের দাবি: গোপন খিয়ানত আখিরাতে প্রকাশ পায়","description":"এই হাদিসে খায়বারের দিনের একটি ঘটনা এসেছে। সাহাবীগণ কয়েকজনকে শহীদ বলছিলেন। এমন একজনের ব্যাপারে তারা শহীদ বললে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বললেন, কখনো নয়; তিনি তাকে জাহান্নামে দেখেছেন, কারণ সে একটি চাদর আত্মসাৎ করেছিল। এই বক্তব্য খুব গভীর শিক্ষা দেয়। মানুষের চোখে কেউ বাহ্যিকভাবে ভালো বা সম্মানিত মনে হতে পারে, কিন্তু গোপন খিয়ানত থাকলে তার হিসাব আল্লাহর কাছে থাকবে। আত্মসাৎ শহীদের মর্যাদার দাবিকেও বিপদে ফেলতে পারে—হাদিসের ভাষায় বিষয়টি এভাবেই এসেছে। তাই গনীমতের মাল, দায়িত্বের মাল বা কোনো আমানত গোপনে নেওয়া থেকে কঠোরভাবে বাঁচা দরকার।"},"teachings":["মানুষের বাহ্যিক প্রশংসা আখিরাতের হিসাব বদলায় না।","একটি চাদর আত্মসাৎ করাও ভয়াবহ পরিণামের কারণ হয়েছে।","গোপন খিয়ানত মানুষের মর্যাদাকে ক্ষতিগ্রস্ত করতে পারে।","আল্লাহর কাছে আমানতের হিসাব খুবই গুরুতর।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E128" s="4" t="n"/>
@@ -3533,7 +3537,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আল্লাহর সন্তুষ্টি ও অসন্তুষ্টির কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ তিন কাজে সন্তুষ্ট হন এবং তিন কাজে অসন্তুষ্ট হন—ইবাদত, ঐক্য, উপদেশ ও অপচয়ের শিক্ষা এখানে আছে।"},"heading":{"title":"আল্লাহর সন্তুষ্টির তিন কাজ ও অসন্তুষ্টির তিন কাজ","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ তিনটি কাজে সন্তুষ্ট হন এবং তিনটি কাজে অসন্তুষ্ট হন। সন্তুষ্টির কাজ হলো আল্লাহর ইবাদত করা ও তাঁর সঙ্গে শরীক না করা, আল্লাহর বিধানকে শক্তভাবে আঁকড়ে ধরা ও বিচ্ছিন্ন না হওয়া, এবং যাকে আল্লাহ কাজের নেতা করেন তার জন্য পরস্পরে কল্যাণ কামনা করা। আর আল্লাহ অসন্তুষ্ট হন অপ্রয়োজনীয় কথা, সম্পদ নষ্ট করা এবং অনর্থক বেশি প্রশ্ন করার কারণে। এই হাদিসে তাওহীদ, ঐক্য, নসীহত, সম্পদ রক্ষা ও কথা নিয়ন্ত্রণের শিক্ষা এসেছে। মুসলিম জীবনে শুধু ইবাদত নয়, কথা, সম্পদ ও সামাজিক আচরণও গুরুত্বপূর্ণ। আল্লাহর সন্তুষ্টির কাজ খুঁজে জীবন সাজানোই এই হাদিসের সহজ বার্তা।"},"teachings":["আল্লাহর ইবাদত করা এবং শিরক থেকে দূরে থাকা বড় দায়িত্ব।","আল্লাহর বিধান আঁকড়ে ধরা ও বিচ্ছিন্নতা এড়ানো দরকার।","অপ্রয়োজনীয় কথা ও সম্পদ নষ্ট করা থেকে বাঁচতে হবে।","নেতার জন্য কল্যাণ কামনা করা ভালো সামাজিক আচরণ।"],"related_hadiths":[{"id":"1715","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আল্লাহর সন্তুষ্টি ও অসন্তুষ্টির কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ তিন কাজে সন্তুষ্ট হন এবং তিন কাজে অসন্তুষ্ট হন—ইবাদত, ঐক্য, উপদেশ ও অপচয়ের শিক্ষা এখানে আছে।"},"heading":{"title":"আল্লাহর সন্তুষ্টির তিন কাজ ও অসন্তুষ্টির তিন কাজ","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ তিনটি কাজে সন্তুষ্ট হন এবং তিনটি কাজে অসন্তুষ্ট হন। সন্তুষ্টির কাজ হলো আল্লাহর ইবাদত করা ও তাঁর সঙ্গে শরীক না করা, আল্লাহর বিধানকে শক্তভাবে আঁকড়ে ধরা ও বিচ্ছিন্ন না হওয়া, এবং যাকে আল্লাহ কাজের নেতা করেন তার জন্য পরস্পরে কল্যাণ কামনা করা। আর আল্লাহ অসন্তুষ্ট হন অপ্রয়োজনীয় কথা, সম্পদ নষ্ট করা এবং অনর্থক বেশি প্রশ্ন করার কারণে। এই হাদিসে তাওহীদ, ঐক্য, নসীহত, সম্পদ রক্ষা ও কথা নিয়ন্ত্রণের শিক্ষা এসেছে। মুসলিম জীবনে শুধু ইবাদত নয়, কথা, সম্পদ ও সামাজিক আচরণও গুরুত্বপূর্ণ। আল্লাহর সন্তুষ্টির কাজ খুঁজে জীবন সাজানোই এই হাদিসের সহজ বার্তা।"},"teachings":["আল্লাহর ইবাদত করা এবং শিরক থেকে দূরে থাকা বড় দায়িত্ব।","আল্লাহর বিধান আঁকড়ে ধরা ও বিচ্ছিন্নতা এড়ানো দরকার।","অপ্রয়োজনীয় কথা ও সম্পদ নষ্ট করা থেকে বাঁচতে হবে।","নেতার জন্য কল্যাণ কামনা করা ভালো সামাজিক আচরণ।"],"related_hadiths":[{"id":"1715","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -3560,7 +3564,7 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অন্যায় সম্পদ দখলের ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর সম্পদ অন্যায়ভাবে দখল বা ব্যবহার করলে কিয়ামতের দিন জাহান্নামের কঠিন সতর্কতা এসেছে।"},"heading":{"title":"অন্যায় সম্পদ দখল: আল্লাহর মালে অন্যায় ব্যবহার থেকে বাঁচুন","description":"এই হাদিসে অন্যায়ভাবে সম্পদ দখল করার পরিণাম খুব স্পষ্টভাবে বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যারা আল্লাহর সম্পদে অন্যায়ভাবে তসরূপ করে, কিয়ামতের দিন তাদের জন্য জাহান্নাম রয়েছে। এখানে মূল বিষয় হলো, সম্পদকে নিজের ইচ্ছামতো ব্যবহার করা যাবে না, যদি সেটি নিজের হক না হয়। অন্যায় সম্পদ দখল শুধু চুরি বা প্রকাশ্য ছিনিয়ে নেওয়ার মধ্যে সীমিত নয়; দায়িত্বের মাল, গনীমতের মাল বা মানুষের হক—সব ক্ষেত্রেই সতর্কতা দরকার। হাদিসটি আমাদের শেখায়, সম্পদের ব্যাপারে আল্লাহর ভয় রাখা দরকার। যা ন্যায্য নয়, তা থেকে দূরে থাকা নিরাপদ পথ।"},"teachings":["অন্যায়ভাবে সম্পদ দখল করা আখিরাতের বড় ক্ষতির কারণ।","আল্লাহর মাল বা দায়িত্বের মাল নিজের ইচ্ছায় ব্যবহার করা ঠিক নয়।","সম্পদের ব্যাপারে হক-না-হক বিচার করা জরুরি।","কিয়ামতের জবাবদিহি মনে রাখলে আত্মসাৎ থেকে বাঁচা সহজ হয়।"],"related_hadiths":[{"id":"3073","book_id":"1","label":"Sahih Bukhari"},{"id":"3074","book_id":"1","label":"Sahih Bukhari"},{"id":"210","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অন্যায় সম্পদ দখলের ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর সম্পদ অন্যায়ভাবে দখল বা ব্যবহার করলে কিয়ামতের দিন জাহান্নামের কঠিন সতর্কতা এসেছে।"},"heading":{"title":"অন্যায় সম্পদ দখল: আল্লাহর মালে অন্যায় ব্যবহার থেকে বাঁচুন","description":"এই হাদিসে অন্যায়ভাবে সম্পদ দখল করার পরিণাম খুব স্পষ্টভাবে বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যারা আল্লাহর সম্পদে অন্যায়ভাবে তসরূপ করে, কিয়ামতের দিন তাদের জন্য জাহান্নাম রয়েছে। এখানে মূল বিষয় হলো, সম্পদকে নিজের ইচ্ছামতো ব্যবহার করা যাবে না, যদি সেটি নিজের হক না হয়। অন্যায় সম্পদ দখল শুধু চুরি বা প্রকাশ্য ছিনিয়ে নেওয়ার মধ্যে সীমিত নয়; দায়িত্বের মাল, গনীমতের মাল বা মানুষের হক—সব ক্ষেত্রেই সতর্কতা দরকার। হাদিসটি আমাদের শেখায়, সম্পদের ব্যাপারে আল্লাহর ভয় রাখা দরকার। যা ন্যায্য নয়, তা থেকে দূরে থাকা নিরাপদ পথ।"},"teachings":["অন্যায়ভাবে সম্পদ দখল করা আখিরাতের বড় ক্ষতির কারণ।","আল্লাহর মাল বা দায়িত্বের মাল নিজের ইচ্ছায় ব্যবহার করা ঠিক নয়।","সম্পদের ব্যাপারে হক-না-হক বিচার করা জরুরি।","কিয়ামতের জবাবদিহি মনে রাখলে আত্মসাৎ থেকে বাঁচা সহজ হয়।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E130" s="4" t="n"/>
@@ -3583,7 +3587,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল রিজিক ও দোয়া কবুলের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য, পানীয়, পোশাক ও জীবিকা হারাম হলে দোয়া কবুলের পথে বাধা তৈরি হয়; পবিত্র রিজিক জরুরি।"},"heading":{"title":"হালাল রিজিক ও দোয়া কবুল: খাদ্য-পোশাকে পবিত্রতা কেন জরুরি","description":"এই হাদিসে হালাল রিজিকের গুরুত্ব খুব সুন্দরভাবে বোঝানো হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ পবিত্র এবং তিনি পবিত্র ছাড়া গ্রহণ করেন না। এরপর এমন এক ব্যক্তির কথা এসেছে, যে সফরে ক্লান্ত, ধুলামলিন, দু’হাত তুলে কাতরভাবে দোয়া করছে। বাহ্যিকভাবে দোয়ার অনেক কারণ আছে। কিন্তু তার খাদ্য হারাম, পানীয় হারাম, পোশাক হারাম এবং জীবিকা হারাম। তাই বলা হয়েছে, তার দোয়া কীভাবে কবুল হবে? হালাল রিজিক হাদিস আমাদের শেখায়, দোয়া শুধু মুখের শব্দ নয়; জীবনের উপার্জন, খাবার ও পোশাকের সঙ্গেও এর সম্পর্ক আছে। তাই ইবাদতের সঙ্গে হালাল উপার্জনকে গুরুত্ব দেওয়া দরকার।"},"teachings":["আল্লাহ পবিত্র, তাই পবিত্র বস্তু গ্রহণ করেন।","হারাম খাদ্য, পানীয় ও পোশাক দোয়া কবুলের পথে বাধা হতে পারে।","দোয়ার সঙ্গে জীবিকার পবিত্রতার সম্পর্ক আছে।","হালাল উপার্জন ইবাদতের জীবনে গুরুত্বপূর্ণ অংশ।"],"related_hadiths":[{"id":"2059","book_id":"1","label":"Sahih Bukhari"},{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"1205","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল রিজিক ও দোয়া কবুলের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য, পানীয়, পোশাক ও জীবিকা হারাম হলে দোয়া কবুলের পথে বাধা তৈরি হয়; পবিত্র রিজিক জরুরি।"},"heading":{"title":"হালাল রিজিক ও দোয়া কবুল: খাদ্য-পোশাকে পবিত্রতা কেন জরুরি","description":"এই হাদিসে হালাল রিজিকের গুরুত্ব খুব সুন্দরভাবে বোঝানো হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ পবিত্র এবং তিনি পবিত্র ছাড়া গ্রহণ করেন না। এরপর এমন এক ব্যক্তির কথা এসেছে, যে সফরে ক্লান্ত, ধুলামলিন, দু’হাত তুলে কাতরভাবে দোয়া করছে। বাহ্যিকভাবে দোয়ার অনেক কারণ আছে। কিন্তু তার খাদ্য হারাম, পানীয় হারাম, পোশাক হারাম এবং জীবিকা হারাম। তাই বলা হয়েছে, তার দোয়া কীভাবে কবুল হবে? হালাল রিজিক হাদিস আমাদের শেখায়, দোয়া শুধু মুখের শব্দ নয়; জীবনের উপার্জন, খাবার ও পোশাকের সঙ্গেও এর সম্পর্ক আছে। তাই ইবাদতের সঙ্গে হালাল উপার্জনকে গুরুত্ব দেওয়া দরকার।"},"teachings":["আল্লাহ পবিত্র, তাই পবিত্র বস্তু গ্রহণ করেন।","হারাম খাদ্য, পানীয় ও পোশাক দোয়া কবুলের পথে বাধা হতে পারে।","দোয়ার সঙ্গে জীবিকার পবিত্রতার সম্পর্ক আছে।","হালাল উপার্জন ইবাদতের জীবনে গুরুত্বপূর্ণ অংশ।"],"related_hadiths":[{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1205","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E131" s="4" t="n"/>
@@ -3606,7 +3610,7 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল-হারাম উপার্জনে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. এমন সময় আসবে যখন মানুষ উপার্জনের হালাল-হারাম নিয়ে পরোয়া করবে না; তাই আয়ের উৎস যাচাই জরুরি।"},"heading":{"title":"হালাল-হারাম উপার্জন: আয়ের উৎস নিয়ে উদাসীন হবেন না","description":"এই হাদিসে ভবিষ্যৎ সময়ের একটি বড় বিপদের কথা বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, মানুষের উপর এমন সময় আসবে, যখন মানুষ হালাল-হারাম উপার্জন বিবেচনা করবে না। অর্থাৎ টাকা আসছে কি না—এটাই যদি প্রধান চিন্তা হয়ে যায়, তাহলে মানুষ উৎস ভুলে যেতে পারে। হালাল হারাম উপার্জন বিষয়টি তাই শুধু ফিকহের আলোচনা নয়; এটি ব্যক্তিগত জীবনের প্রতিদিনের পরীক্ষা। ব্যবসা, চাকরি, লেনদেন, কমিশন, বেতন—সব ক্ষেত্রেই মুসলিমের দেখা দরকার, এই আয় বৈধ পথে হচ্ছে কি না। হাদিসটি আমাদের আগে থেকেই সতর্ক করে, যাতে সমাজের ভুল পথে ভেসে না যাই এবং নিজের রিজিকের বিষয়ে আল্লাহকে ভয় করি।"},"teachings":["উপার্জনের উৎস হালাল কি না তা দেখা জরুরি।","সমাজে উদাসীনতা বাড়লেও মুমিনকে সতর্ক থাকতে হবে।","শুধু টাকা পাওয়া নয়, বৈধ পথে পাওয়া গুরুত্বপূর্ণ।","হালাল-হারাম বিচার না করা বড় নৈতিক ক্ষতির কারণ হতে পারে।"],"related_hadiths":[{"id":"2236","book_id":"2","label":"Sahih Muslim"},{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"1205","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল-হারাম উপার্জনে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. এমন সময় আসবে যখন মানুষ উপার্জনের হালাল-হারাম নিয়ে পরোয়া করবে না; তাই আয়ের উৎস যাচাই জরুরি।"},"heading":{"title":"হালাল-হারাম উপার্জন: আয়ের উৎস নিয়ে উদাসীন হবেন না","description":"এই হাদিসে ভবিষ্যৎ সময়ের একটি বড় বিপদের কথা বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, মানুষের উপর এমন সময় আসবে, যখন মানুষ হালাল-হারাম উপার্জন বিবেচনা করবে না। অর্থাৎ টাকা আসছে কি না—এটাই যদি প্রধান চিন্তা হয়ে যায়, তাহলে মানুষ উৎস ভুলে যেতে পারে। হালাল হারাম উপার্জন বিষয়টি তাই শুধু ফিকহের আলোচনা নয়; এটি ব্যক্তিগত জীবনের প্রতিদিনের পরীক্ষা। ব্যবসা, চাকরি, লেনদেন, কমিশন, বেতন—সব ক্ষেত্রেই মুসলিমের দেখা দরকার, এই আয় বৈধ পথে হচ্ছে কি না। হাদিসটি আমাদের আগে থেকেই সতর্ক করে, যাতে সমাজের ভুল পথে ভেসে না যাই এবং নিজের রিজিকের বিষয়ে আল্লাহকে ভয় করি।"},"teachings":["উপার্জনের উৎস হালাল কি না তা দেখা জরুরি।","সমাজে উদাসীনতা বাড়লেও মুমিনকে সতর্ক থাকতে হবে।","শুধু টাকা পাওয়া নয়, বৈধ পথে পাওয়া গুরুত্বপূর্ণ।","হালাল-হারাম বিচার না করা বড় নৈতিক ক্ষতির কারণ হতে পারে।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1205","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E132" s="4" t="n"/>
@@ -3629,7 +3633,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম খাদ্যের ভয়াবহ পরিণাম","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম খাদ্যে লালিত শরীরের পরিণাম কঠিন বলা হয়েছে; তাই খাবার ও উপার্জনে হালাল পথ জরুরি।"},"heading":{"title":"হারাম খাদ্য থেকে বাঁচুন: শরীর ও রিজিকের পবিত্রতা","description":"এই হাদিসে খুব সংক্ষিপ্ত ভাষায় বড় একটি সতর্কতা এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, হারাম খাদ্য দ্বারা পরিপুষ্ট শরীর জান্নাতে যাবে না। তাই হারাম খাদ্য হাদিস আমাদের শুধু খাবারের নাম নয়, খাবারের উৎস নিয়েও ভাবতে শেখায়। যে খাবার আমরা খাই, সেটি কীভাবে কেনা হলো, আয়টি বৈধ ছিল কি না, অন্যের হক মিশে আছে কি না—এসব বিষয় গুরুত্বপূর্ণ। শরীর খাবার দিয়ে গড়ে ওঠে, আর মুমিনের জীবন ইবাদত ও আনুগত্যের জন্য। তাই হারাম খাদ্যকে হালকা মনে করা ঠিক নয়। এই হাদিসের শিক্ষা হলো, নিজের ও পরিবারের খাবারের ব্যাপারে সতর্ক থাকা এবং হালাল রিজিকের চেষ্টা করা।"},"teachings":["হারাম খাদ্যে শরীর গড়ে ওঠা ভয়াবহ সতর্কতার বিষয়।","খাবারের সঙ্গে উপার্জনের উৎসও দেখা দরকার।","পরিবারের খাবার হালাল কি না তা অভিভাবকের দায়িত্বের অংশ।","হালাল রিজিকের চেষ্টা করা ঈমানি জীবনের গুরুত্বপূর্ণ কাজ।"],"related_hadiths":[{"id":"2236","book_id":"2","label":"Sahih Muslim"},{"id":"2059","book_id":"1","label":"Sahih Bukhari"},{"id":"52","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম খাদ্যের ভয়াবহ পরিণাম","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম খাদ্যে লালিত শরীরের পরিণাম কঠিন বলা হয়েছে; তাই খাবার ও উপার্জনে হালাল পথ জরুরি।"},"heading":{"title":"হারাম খাদ্য থেকে বাঁচুন: শরীর ও রিজিকের পবিত্রতা","description":"এই হাদিসে খুব সংক্ষিপ্ত ভাষায় বড় একটি সতর্কতা এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, হারাম খাদ্য দ্বারা পরিপুষ্ট শরীর জান্নাতে যাবে না। তাই হারাম খাদ্য হাদিস আমাদের শুধু খাবারের নাম নয়, খাবারের উৎস নিয়েও ভাবতে শেখায়। যে খাবার আমরা খাই, সেটি কীভাবে কেনা হলো, আয়টি বৈধ ছিল কি না, অন্যের হক মিশে আছে কি না—এসব বিষয় গুরুত্বপূর্ণ। শরীর খাবার দিয়ে গড়ে ওঠে, আর মুমিনের জীবন ইবাদত ও আনুগত্যের জন্য। তাই হারাম খাদ্যকে হালকা মনে করা ঠিক নয়। এই হাদিসের শিক্ষা হলো, নিজের ও পরিবারের খাবারের ব্যাপারে সতর্ক থাকা এবং হালাল রিজিকের চেষ্টা করা।"},"teachings":["হারাম খাদ্যে শরীর গড়ে ওঠা ভয়াবহ সতর্কতার বিষয়।","খাবারের সঙ্গে উপার্জনের উৎসও দেখা দরকার।","পরিবারের খাবার হালাল কি না তা অভিভাবকের দায়িত্বের অংশ।","হালাল রিজিকের চেষ্টা করা ঈমানি জীবনের গুরুত্বপূর্ণ কাজ।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E133" s="4" t="n"/>
@@ -3652,7 +3656,7 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল-হারাম ও সন্দেহজনক বিষয়","description":"$book_name$ $hadith_number$ - $chapter_name$. হালাল-হারাম স্পষ্ট; সন্দেহজনক বিষয় থেকে বাঁচলে দ্বীন ও মর্যাদা রক্ষা হয়, আর অন্তর ঠিক থাকলে শরীর ঠিক থাকে।"},"heading":{"title":"হালাল হারাম স্পষ্ট: সন্দেহজনক বিষয় থেকে বাঁচার শিক্ষা","description":"এই হাদিস ইসলামী জীবনের একটি মৌলিক নীতি শেখায়। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, হালাল স্পষ্ট এবং হারামও স্পষ্ট। মাঝখানে কিছু সন্দেহজনক বিষয় আছে, যা অনেক মানুষ জানে না। যে ব্যক্তি সন্দেহজনক বিষয় থেকে বেঁচে থাকে, সে তার দ্বীন ও মর্যাদা রক্ষা করে। আর যে সন্দেহজনক বিষয়ে পড়ে, সে হারামের কাছাকাছি চলে যায়। রাখালের উদাহরণ দিয়ে বোঝানো হয়েছে, নিষিদ্ধ সীমার ধারে থাকলে ভিতরে ঢুকে পড়ার ভয় থাকে। শেষে অন্তরের কথা বলা হয়েছে: অন্তর ঠিক থাকলে শরীর ঠিক থাকে, নষ্ট হলে শরীরও নষ্ট হয়। তাই সন্দেহজনক বিষয় হাদিস আমাদের সতর্ক, পরিষ্কার ও অন্তর-সচেতন জীবন শেখায়।"},"teachings":["হালাল ও হারামের স্পষ্ট সীমা মানা জরুরি।","সন্দেহজনক বিষয় থেকে দূরে থাকলে দ্বীন ও মর্যাদা রক্ষা হয়।","হারামের কাছাকাছি ঘোরাফেরা করা ঝুঁকিপূর্ণ।","অন্তর ভালো থাকলে আচরণও ভালো হওয়ার পথ তৈরি হয়।"],"related_hadiths":[{"id":"2236","book_id":"2","label":"Sahih Muslim"},{"id":"2059","book_id":"1","label":"Sahih Bukhari"},{"id":"593","book_id":"8","label":"Riyadus Salihin"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল-হারাম ও সন্দেহজনক বিষয়","description":"$book_name$ $hadith_number$ - $chapter_name$. হালাল-হারাম স্পষ্ট; সন্দেহজনক বিষয় থেকে বাঁচলে দ্বীন ও মর্যাদা রক্ষা হয়, আর অন্তর ঠিক থাকলে শরীর ঠিক থাকে।"},"heading":{"title":"হালাল হারাম স্পষ্ট: সন্দেহজনক বিষয় থেকে বাঁচার শিক্ষা","description":"এই হাদিস ইসলামী জীবনের একটি মৌলিক নীতি শেখায়। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, হালাল স্পষ্ট এবং হারামও স্পষ্ট। মাঝখানে কিছু সন্দেহজনক বিষয় আছে, যা অনেক মানুষ জানে না। যে ব্যক্তি সন্দেহজনক বিষয় থেকে বেঁচে থাকে, সে তার দ্বীন ও মর্যাদা রক্ষা করে। আর যে সন্দেহজনক বিষয়ে পড়ে, সে হারামের কাছাকাছি চলে যায়। রাখালের উদাহরণ দিয়ে বোঝানো হয়েছে, নিষিদ্ধ সীমার ধারে থাকলে ভিতরে ঢুকে পড়ার ভয় থাকে। শেষে অন্তরের কথা বলা হয়েছে: অন্তর ঠিক থাকলে শরীর ঠিক থাকে, নষ্ট হলে শরীরও নষ্ট হয়। তাই সন্দেহজনক বিষয় হাদিস আমাদের সতর্ক, পরিষ্কার ও অন্তর-সচেতন জীবন শেখায়।"},"teachings":["হালাল ও হারামের স্পষ্ট সীমা মানা জরুরি।","সন্দেহজনক বিষয় থেকে দূরে থাকলে দ্বীন ও মর্যাদা রক্ষা হয়।","হারামের কাছাকাছি ঘোরাফেরা করা ঝুঁকিপূর্ণ।","অন্তর ভালো থাকলে আচরণও ভালো হওয়ার পথ তৈরি হয়।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"593","book_id":"8","slug":"riyadus-salihin","label":"রিয়াদুস সালেহীন"}]}</t>
         </is>
       </c>
       <c r="E134" s="4" t="n"/>
@@ -3675,7 +3679,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম রিজিক দোয়ার পথে বাধা","description":"$book_name$ $hadith_number$ - $chapter_name$. সফরে ক্লান্ত অবস্থায় দোয়া করলেও খাদ্য, পানীয়, পোশাক ও জীবিকা হারাম হলে দোয়া কবুলের প্রশ্ন ওঠে।"},"heading":{"title":"হারাম রিজিক দোয়ার পথে বাধা: হালাল জীবিকা কেন দরকার","description":"এই হাদিসে দোয়ার একটি গুরুত্বপূর্ণ দিক তুলে ধরা হয়েছে। একজন মানুষ দূর-দূরান্তে সফর করছে, চুল এলোমেলো, শরীরে ধুলা-বালি, দুই হাত আসমানের দিকে তুলে কাতরভাবে বলছে, হে প্রভু! হে প্রভু! বাহ্যিকভাবে এটি দোয়ার বিনয়ী অবস্থা। কিন্তু হাদিসে বলা হলো, তার খাদ্য হারাম, পানীয় হারাম, পোশাক হারাম এবং জীবিকা হারাম; তাহলে তার দোয়া কীভাবে কবুল হবে? তাই হারাম রিজিক দোয়ার পথে বড় বাধা হতে পারে। এই শিক্ষা আমাদের দৈনন্দিন জীবনে খুব দরকার। আমরা শুধু দোয়া বাড়াব না, বরং খাবার, পোশাক ও আয়ের উৎসও পবিত্র রাখার চেষ্টা করব। হালাল জীবিকা ইবাদতের সৌন্দর্য বাড়ায়।"},"teachings":["দোয়ার সঙ্গে হালাল জীবিকার সম্পর্ক আছে।","বাহ্যিক বিনয় থাকলেও হারাম রিজিক বড় বাধা হতে পারে।","খাদ্য, পানীয়, পোশাক ও আয়—সব ক্ষেত্রেই সতর্কতা দরকার।","আল্লাহ পবিত্র, তাই পবিত্র উপায় পছন্দনীয়।"],"related_hadiths":[{"id":"2059","book_id":"1","label":"Sahih Bukhari"},{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"1205","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম রিজিক দোয়ার পথে বাধা","description":"$book_name$ $hadith_number$ - $chapter_name$. সফরে ক্লান্ত অবস্থায় দোয়া করলেও খাদ্য, পানীয়, পোশাক ও জীবিকা হারাম হলে দোয়া কবুলের প্রশ্ন ওঠে।"},"heading":{"title":"হারাম রিজিক দোয়ার পথে বাধা: হালাল জীবিকা কেন দরকার","description":"এই হাদিসে দোয়ার একটি গুরুত্বপূর্ণ দিক তুলে ধরা হয়েছে। একজন মানুষ দূর-দূরান্তে সফর করছে, চুল এলোমেলো, শরীরে ধুলা-বালি, দুই হাত আসমানের দিকে তুলে কাতরভাবে বলছে, হে প্রভু! হে প্রভু! বাহ্যিকভাবে এটি দোয়ার বিনয়ী অবস্থা। কিন্তু হাদিসে বলা হলো, তার খাদ্য হারাম, পানীয় হারাম, পোশাক হারাম এবং জীবিকা হারাম; তাহলে তার দোয়া কীভাবে কবুল হবে? তাই হারাম রিজিক দোয়ার পথে বড় বাধা হতে পারে। এই শিক্ষা আমাদের দৈনন্দিন জীবনে খুব দরকার। আমরা শুধু দোয়া বাড়াব না, বরং খাবার, পোশাক ও আয়ের উৎসও পবিত্র রাখার চেষ্টা করব। হালাল জীবিকা ইবাদতের সৌন্দর্য বাড়ায়।"},"teachings":["দোয়ার সঙ্গে হালাল জীবিকার সম্পর্ক আছে।","বাহ্যিক বিনয় থাকলেও হারাম রিজিক বড় বাধা হতে পারে।","খাদ্য, পানীয়, পোশাক ও আয়—সব ক্ষেত্রেই সতর্কতা দরকার।","আল্লাহ পবিত্র, তাই পবিত্র উপায় পছন্দনীয়।"],"related_hadiths":[{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1205","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E135" s="4" t="n"/>
@@ -3698,7 +3702,7 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল-হারাম আয়ের যুগসতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. এমন যুগ আসবে যখন মানুষ সম্পদ কীভাবে পেল তা দেখবে না; মুসলিমের জন্য হালাল উৎস যাচাই অপরিহার্য।"},"heading":{"title":"হালাল-হারাম আয়ের সতর্কতা: সম্পদ পেলেই যথেষ্ট নয়","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) এমন এক সময়ের কথা বলেছেন, যখন মানুষ পরোয়া করবে না—সে কী উপায়ে মাল পেল, হারাম পথে নাকি হালাল পথে। এর মানে হলো, আয়ের পরিমাণকে মানুষ অনেক সময় আয়ের বৈধতার চেয়ে বড় করে দেখে। কিন্তু মুমিনের জন্য শুধু সম্পদ পাওয়া লক্ষ্য নয়। হালাল হারাম আয় যাচাই করা ঈমানি দায়িত্বের অংশ। ব্যবসায় প্রতারণা, অন্যের হক, অবৈধ চুক্তি, সন্দেহজনক লেনদেন—এসব বিষয় থেকে সতর্ক থাকা দরকার। হাদিসটি আমাদের সমাজের চাপের মাঝেও আল্লাহর ভয় ধরে রাখতে শেখায়। টাকা আসছে কি না—এ প্রশ্নের সঙ্গে আরেকটি প্রশ্ন দরকার: এই টাকা হালালভাবে আসছে কি না?"},"teachings":["সম্পদ পাওয়ার উপায় বৈধ কি না তা যাচাই করতে হবে।","সময়ের খারাপ প্রবণতার সঙ্গে ভেসে যাওয়া উচিত নয়।","হালাল আয় মুমিনের নৈতিক পরিচয়ের অংশ।","হারাম আয়ের ব্যাপারে উদাসীনতা বড় ক্ষতির কারণ হতে পারে।"],"related_hadiths":[{"id":"2236","book_id":"2","label":"Sahih Muslim"},{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"1205","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল-হারাম আয়ের যুগসতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. এমন যুগ আসবে যখন মানুষ সম্পদ কীভাবে পেল তা দেখবে না; মুসলিমের জন্য হালাল উৎস যাচাই অপরিহার্য।"},"heading":{"title":"হালাল-হারাম আয়ের সতর্কতা: সম্পদ পেলেই যথেষ্ট নয়","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) এমন এক সময়ের কথা বলেছেন, যখন মানুষ পরোয়া করবে না—সে কী উপায়ে মাল পেল, হারাম পথে নাকি হালাল পথে। এর মানে হলো, আয়ের পরিমাণকে মানুষ অনেক সময় আয়ের বৈধতার চেয়ে বড় করে দেখে। কিন্তু মুমিনের জন্য শুধু সম্পদ পাওয়া লক্ষ্য নয়। হালাল হারাম আয় যাচাই করা ঈমানি দায়িত্বের অংশ। ব্যবসায় প্রতারণা, অন্যের হক, অবৈধ চুক্তি, সন্দেহজনক লেনদেন—এসব বিষয় থেকে সতর্ক থাকা দরকার। হাদিসটি আমাদের সমাজের চাপের মাঝেও আল্লাহর ভয় ধরে রাখতে শেখায়। টাকা আসছে কি না—এ প্রশ্নের সঙ্গে আরেকটি প্রশ্ন দরকার: এই টাকা হালালভাবে আসছে কি না?"},"teachings":["সম্পদ পাওয়ার উপায় বৈধ কি না তা যাচাই করতে হবে।","সময়ের খারাপ প্রবণতার সঙ্গে ভেসে যাওয়া উচিত নয়।","হালাল আয় মুমিনের নৈতিক পরিচয়ের অংশ।","হারাম আয়ের ব্যাপারে উদাসীনতা বড় ক্ষতির কারণ হতে পারে।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1205","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E136" s="4" t="n"/>
@@ -3721,7 +3725,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক বিষয় ও অন্তরের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহজনক বিষয় ছাড়লে দ্বীন ও সম্মান নিরাপদ থাকে; অন্তর ভালো থাকলে জীবনও সঠিক পথে থাকে।"},"heading":{"title":"সন্দেহজনক বিষয় থেকে বাঁচুন: হালাল-হারামের নিরাপদ পথ","description":"এই হাদিসে হালাল, হারাম এবং সন্দেহজনক বিষয়ের সম্পর্ক পরিষ্কার করা হয়েছে। হালাল সুস্পষ্ট, হারামও সুস্পষ্ট। কিন্তু কিছু বিষয় আছে, যেগুলো সম্পর্কে অনেকেই সিদ্ধান্ত নিতে পারে না। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি সন্দেহের বস্তুকে পরিহার করে, তার দ্বীন ও সম্মান পরিষ্কার থাকে। আর যে সন্দেহজনক কাজে জড়ায়, সে হারামে পড়ে যেতে পারে। রাখালের উদাহরণটি খুব সহজ: নিষিদ্ধ এলাকার ধারে পশু চরালে ভেতরে ঢুকে পড়ার ভয় থাকে। তাই নিরাপদ পথ হলো হারামের কাছাকাছি না যাওয়া। হাদিসের শেষে অন্তরের গুরুত্ব এসেছে। অন্তর ভালো থাকলে জীবন ভালো দিকে যায়, আর অন্তর নষ্ট হলে কাজও নষ্ট হতে থাকে।"},"teachings":["সন্দেহজনক বিষয় এড়িয়ে চলা নিরাপদ পথ।","হারামের সীমানার কাছাকাছি গেলে পড়ে যাওয়ার ভয় থাকে।","দ্বীন ও সম্মান রক্ষায় সতর্কতা দরকার।","অন্তর ঠিক রাখা আচরণ ঠিক রাখার বড় মাধ্যম।"],"related_hadiths":[{"id":"2236","book_id":"2","label":"Sahih Muslim"},{"id":"2059","book_id":"1","label":"Sahih Bukhari"},{"id":"593","book_id":"8","label":"Riyadus Salihin"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক বিষয় ও অন্তরের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহজনক বিষয় ছাড়লে দ্বীন ও সম্মান নিরাপদ থাকে; অন্তর ভালো থাকলে জীবনও সঠিক পথে থাকে।"},"heading":{"title":"সন্দেহজনক বিষয় থেকে বাঁচুন: হালাল-হারামের নিরাপদ পথ","description":"এই হাদিসে হালাল, হারাম এবং সন্দেহজনক বিষয়ের সম্পর্ক পরিষ্কার করা হয়েছে। হালাল সুস্পষ্ট, হারামও সুস্পষ্ট। কিন্তু কিছু বিষয় আছে, যেগুলো সম্পর্কে অনেকেই সিদ্ধান্ত নিতে পারে না। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি সন্দেহের বস্তুকে পরিহার করে, তার দ্বীন ও সম্মান পরিষ্কার থাকে। আর যে সন্দেহজনক কাজে জড়ায়, সে হারামে পড়ে যেতে পারে। রাখালের উদাহরণটি খুব সহজ: নিষিদ্ধ এলাকার ধারে পশু চরালে ভেতরে ঢুকে পড়ার ভয় থাকে। তাই নিরাপদ পথ হলো হারামের কাছাকাছি না যাওয়া। হাদিসের শেষে অন্তরের গুরুত্ব এসেছে। অন্তর ভালো থাকলে জীবন ভালো দিকে যায়, আর অন্তর নষ্ট হলে কাজও নষ্ট হতে থাকে।"},"teachings":["সন্দেহজনক বিষয় এড়িয়ে চলা নিরাপদ পথ।","হারামের সীমানার কাছাকাছি গেলে পড়ে যাওয়ার ভয় থাকে।","দ্বীন ও সম্মান রক্ষায় সতর্কতা দরকার।","অন্তর ঠিক রাখা আচরণ ঠিক রাখার বড় মাধ্যম।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"593","book_id":"8","slug":"riyadus-salihin","label":"রিয়াদুস সালেহীন"}]}</t>
         </is>
       </c>
       <c r="E137" s="4" t="n"/>
@@ -3744,7 +3748,7 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘৃণিত উপার্জন থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. কুকুর বিক্রয়, ব্যভিচারের বিনিময় ও সিঙ্গা লাগানোর মূল্যকে ঘৃণিত বলা হয়েছে; উপার্জনে সতর্কতা দরকার।"},"heading":{"title":"ঘৃণিত উপার্জন: কুকুর বিক্রয় ও অনৈতিক আয়ের সতর্কতা","description":"এই হাদিসে কয়েক ধরনের উপার্জনকে ঘৃণিত বলা হয়েছে। কুকুর বিক্রয়ের মূল্য, ব্যভিচারের বিনিময় এবং সিঙ্গা লাগানোর মূল্য—এই তিনটি বিষয় হাদিসে এসেছে। এখানে মূল শিক্ষা হলো, উপার্জনের সব পথ সমান নয়। টাকা পাওয়া গেলেই তা ভালো উপার্জন হয়ে যায় না। ঘৃণিত উপার্জন হাদিস আমাদের আয়ের উৎস নিয়ে সতর্ক করে। বিশেষ করে ব্যভিচারের বিনিময়ের মতো অনৈতিক আয়ের কথা স্পষ্টভাবে এসেছে। কুকুর বিক্রয়ের মূল্য ও সিঙ্গা লাগানোর মূল্য সম্পর্কেও হাদিসে সতর্ক ভাষা ব্যবহৃত হয়েছে। তাই মুসলিমের জন্য উপার্জনের ক্ষেত্রে শুধু লাভ নয়, শরিয়তের দৃষ্টিতে তা পরিষ্কার কি না—এটাও দেখা দরকার।"},"teachings":["সব ধরনের আয় গ্রহণযোগ্য নয়।","অনৈতিক কাজের বিনিময় ঘৃণিত উপার্জনের মধ্যে পড়ে।","উপার্জনের উৎস নিয়ে সতর্ক থাকা দরকার।","লাভের আগে হালাল-হারাম বিচার করা জরুরি।"],"related_hadiths":[{"id":"2237","book_id":"1","label":"Sahih Bukhari"},{"id":"2282","book_id":"1","label":"Sahih Bukhari"},{"id":"5962","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘৃণিত উপার্জন থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. কুকুর বিক্রয়, ব্যভিচারের বিনিময় ও সিঙ্গা লাগানোর মূল্যকে ঘৃণিত বলা হয়েছে; উপার্জনে সতর্কতা দরকার।"},"heading":{"title":"ঘৃণিত উপার্জন: কুকুর বিক্রয় ও অনৈতিক আয়ের সতর্কতা","description":"এই হাদিসে কয়েক ধরনের উপার্জনকে ঘৃণিত বলা হয়েছে। কুকুর বিক্রয়ের মূল্য, ব্যভিচারের বিনিময় এবং সিঙ্গা লাগানোর মূল্য—এই তিনটি বিষয় হাদিসে এসেছে। এখানে মূল শিক্ষা হলো, উপার্জনের সব পথ সমান নয়। টাকা পাওয়া গেলেই তা ভালো উপার্জন হয়ে যায় না। ঘৃণিত উপার্জন হাদিস আমাদের আয়ের উৎস নিয়ে সতর্ক করে। বিশেষ করে ব্যভিচারের বিনিময়ের মতো অনৈতিক আয়ের কথা স্পষ্টভাবে এসেছে। কুকুর বিক্রয়ের মূল্য ও সিঙ্গা লাগানোর মূল্য সম্পর্কেও হাদিসে সতর্ক ভাষা ব্যবহৃত হয়েছে। তাই মুসলিমের জন্য উপার্জনের ক্ষেত্রে শুধু লাভ নয়, শরিয়তের দৃষ্টিতে তা পরিষ্কার কি না—এটাও দেখা দরকার।"},"teachings":["সব ধরনের আয় গ্রহণযোগ্য নয়।","অনৈতিক কাজের বিনিময় ঘৃণিত উপার্জনের মধ্যে পড়ে।","উপার্জনের উৎস নিয়ে সতর্ক থাকা দরকার।","লাভের আগে হালাল-হারাম বিচার করা জরুরি।"],"related_hadiths":[{"id":"2237","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2282","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5962","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E138" s="4" t="n"/>
@@ -3767,7 +3771,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নিষিদ্ধ আয়ের তিনটি পথ","description":"$book_name$ $hadith_number$ - $chapter_name$. কুকুরের মূল্য, যিনাকারীনীর উপার্জন ও গণকের উপার্জন খেতে নিষেধ করা হয়েছে; রিজিকে পবিত্রতা জরুরি।"},"heading":{"title":"নিষিদ্ধ আয় থেকে বাঁচুন: কুকুরের মূল্য, যিনা ও গণকের উপার্জন","description":"এই হাদিসে তিনটি উপার্জন খেতে নিষেধ করা হয়েছে: কুকুরের মূল্য, যিনাকারীনীর উপার্জন এবং গণকের উপার্জন। হাদিসটি খুব পরিষ্কারভাবে শেখায়, আয়ের উৎস ভালো না হলে সেই আয় গ্রহণ করা উচিত নয়। নিষিদ্ধ আয় শুধু ব্যক্তির পকেটে আসে না; তা খাবার, পরিবার ও জীবনের ওপরও প্রভাব ফেলে। বিশেষ করে যিনা-ভিত্তিক উপার্জন ও গণকের উপার্জন মানুষের নৈতিকতা ও বিশ্বাসের সঙ্গে জড়িত। কুকুরের মূল্য সম্পর্কেও স্পষ্ট নিষেধ এসেছে। তাই মুসলিমের জন্য উপার্জনের ক্ষেত্রে সতর্ক থাকা জরুরি। কোন কাজ থেকে আয় হচ্ছে, তা আল্লাহর নাফরমানির সঙ্গে যুক্ত কি না—এই প্রশ্ন নিজের কাছে রাখা দরকার।"},"teachings":["কুকুরের মূল্য খেতে নিষেধ করা হয়েছে।","যিনাকারীনীর উপার্জন গ্রহণযোগ্য নয়।","গণকের উপার্জন থেকে বাঁচতে বলা হয়েছে।","রিজিক পবিত্র রাখতে আয়ের উৎস যাচাই করা দরকার।"],"related_hadiths":[{"id":"5962","book_id":"1","label":"Sahih Bukhari"},{"id":"5761","book_id":"1","label":"Sahih Bukhari"},{"id":"2236","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নিষিদ্ধ আয়ের তিনটি পথ","description":"$book_name$ $hadith_number$ - $chapter_name$. কুকুরের মূল্য, যিনাকারীনীর উপার্জন ও গণকের উপার্জন খেতে নিষেধ করা হয়েছে; রিজিকে পবিত্রতা জরুরি।"},"heading":{"title":"নিষিদ্ধ আয় থেকে বাঁচুন: কুকুরের মূল্য, যিনা ও গণকের উপার্জন","description":"এই হাদিসে তিনটি উপার্জন খেতে নিষেধ করা হয়েছে: কুকুরের মূল্য, যিনাকারীনীর উপার্জন এবং গণকের উপার্জন। হাদিসটি খুব পরিষ্কারভাবে শেখায়, আয়ের উৎস ভালো না হলে সেই আয় গ্রহণ করা উচিত নয়। নিষিদ্ধ আয় শুধু ব্যক্তির পকেটে আসে না; তা খাবার, পরিবার ও জীবনের ওপরও প্রভাব ফেলে। বিশেষ করে যিনা-ভিত্তিক উপার্জন ও গণকের উপার্জন মানুষের নৈতিকতা ও বিশ্বাসের সঙ্গে জড়িত। কুকুরের মূল্য সম্পর্কেও স্পষ্ট নিষেধ এসেছে। তাই মুসলিমের জন্য উপার্জনের ক্ষেত্রে সতর্ক থাকা জরুরি। কোন কাজ থেকে আয় হচ্ছে, তা আল্লাহর নাফরমানির সঙ্গে যুক্ত কি না—এই প্রশ্ন নিজের কাছে রাখা দরকার।"},"teachings":["কুকুরের মূল্য খেতে নিষেধ করা হয়েছে।","যিনাকারীনীর উপার্জন গ্রহণযোগ্য নয়।","গণকের উপার্জন থেকে বাঁচতে বলা হয়েছে।","রিজিক পবিত্র রাখতে আয়ের উৎস যাচাই করা দরকার।"],"related_hadiths":[{"id":"5962","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5761","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E139" s="4" t="n"/>
@@ -3790,7 +3794,7 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আব্দুল ক্বায়েস প্রতিনিধিদলের ঈমান শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আব্দুল ক্বায়েস প্রতিনিধিদলকে ঈমান, সালাত, যাকাত, রমযানের সিয়াম ও খুমুসের শিক্ষা দেওয়া হয়।"},"heading":{"title":"আব্দুল ক্বায়েস প্রতিনিধিদল ও ঈমানের মূল আমল","description":"এই হাদিসে আব্দুল ক্বায়েস গোত্রের প্রতিনিধিদলের ঘটনা এসেছে। তারা রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কাছে এসে এমন পরিষ্কার নির্দেশ চাইলো, যা তারা নিজেদের লোকদের জানাতে পারে এবং যার মাধ্যমে জান্নাতে প্রবেশের আশা রাখতে পারে। নবীজি তাদেরকে চারটি বিষয়ে নির্দেশ দেন: এক আল্লাহর উপর ঈমান, সালাত কায়েম, যাকাত আদায়, রমযানের সিয়াম এবং গানীমতের এক পঞ্চমাংশ জমা দেওয়া। তিনি কিছু পাত্র থেকেও নিষেধ করেন, যেগুলো শরাব তৈরির সঙ্গে যুক্ত ছিল। এই হাদিসে ঈমানের মূল আমল, শিক্ষা গ্রহণ ও অন্যদের কাছে দ্বীনের কথা পৌঁছে দেওয়ার গুরুত্ব আছে। সাহাবীরা শুধু শুনতে আসেননি; তারা আমল করতে ও অন্যদের জানাতে চেয়েছেন।"},"teachings":["দ্বীনের পরিষ্কার শিক্ষা জানা ও মানা দরকার।","ঈমানের সঙ্গে সালাত, যাকাত ও রমযানের সিয়াম জড়িত।","যা শেখা হয়, তা নিজের লোকদের জানানো ভালো কাজ।","নিষিদ্ধ জিনিসের উপায় থেকেও সতর্ক থাকতে হয়।"],"related_hadiths":[{"id":"53","book_id":"1","label":"Sahih Bukhari"},{"id":"17","book_id":"2","label":"Sahih Muslim"},{"id":"17","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আব্দুল ক্বায়েস প্রতিনিধিদলের ঈমান শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আব্দুল ক্বায়েস প্রতিনিধিদলকে ঈমান, সালাত, যাকাত, রমযানের সিয়াম ও খুমুসের শিক্ষা দেওয়া হয়।"},"heading":{"title":"আব্দুল ক্বায়েস প্রতিনিধিদল ও ঈমানের মূল আমল","description":"এই হাদিসে আব্দুল ক্বায়েস গোত্রের প্রতিনিধিদলের ঘটনা এসেছে। তারা রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কাছে এসে এমন পরিষ্কার নির্দেশ চাইলো, যা তারা নিজেদের লোকদের জানাতে পারে এবং যার মাধ্যমে জান্নাতে প্রবেশের আশা রাখতে পারে। নবীজি তাদেরকে চারটি বিষয়ে নির্দেশ দেন: এক আল্লাহর উপর ঈমান, সালাত কায়েম, যাকাত আদায়, রমযানের সিয়াম এবং গানীমতের এক পঞ্চমাংশ জমা দেওয়া। তিনি কিছু পাত্র থেকেও নিষেধ করেন, যেগুলো শরাব তৈরির সঙ্গে যুক্ত ছিল। এই হাদিসে ঈমানের মূল আমল, শিক্ষা গ্রহণ ও অন্যদের কাছে দ্বীনের কথা পৌঁছে দেওয়ার গুরুত্ব আছে। সাহাবীরা শুধু শুনতে আসেননি; তারা আমল করতে ও অন্যদের জানাতে চেয়েছেন।"},"teachings":["দ্বীনের পরিষ্কার শিক্ষা জানা ও মানা দরকার।","ঈমানের সঙ্গে সালাত, যাকাত ও রমযানের সিয়াম জড়িত।","যা শেখা হয়, তা নিজের লোকদের জানানো ভালো কাজ।","নিষিদ্ধ জিনিসের উপায় থেকেও সতর্ক থাকতে হয়।"],"related_hadiths":[{"id":"53","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"17","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"17","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E140" s="4" t="n"/>
@@ -3813,7 +3817,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম উপার্জন ও অভিশপ্ত কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. রক্ত, কুকুর ও ব্যভিচারের আয় নিষিদ্ধ; সুদ, উল্কি ও ছবি অঙ্কনের ব্যাপারেও কঠিন সতর্কতা এসেছে।"},"heading":{"title":"হারাম উপার্জন ও নিষিদ্ধ কাজ: রক্ত, সুদ, উল্কি ও ছবি নিয়ে সতর্কতা","description":"এই হাদিসে কয়েকটি বিষয় একসঙ্গে এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) রক্ত বিক্রয়ের মূল্য, কুকুর বিক্রয়ের মূল্য এবং ব্যভিচারের বিনিময় থেকে নিষেধ করেছেন। এরপর সুদ গ্রহীতা ও সুদদাতার প্রতি লা’নতের কথা এসেছে। আরও বলা হয়েছে, যে উল্কি করে এবং যে উল্কি করায়, তাদের ওপরও লা’নত করা হয়েছে। ছবি অঙ্কনকারীর প্রতিও লা’নতের কথা এসেছে। তাই হারাম উপার্জন হাদিস আমাদের আয়ের উৎস এবং কিছু কাজের ব্যাপারে গভীর সতর্ক করে। এখানে অযথা বাড়তি ব্যাখ্যা না করে মূল বার্তাই স্পষ্ট: মুসলিমকে এমন আয় ও কাজ থেকে দূরে থাকতে হবে, যেগুলোর ব্যাপারে নবী (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কঠিন নিষেধ দিয়েছেন।"},"teachings":["রক্ত, কুকুর ও ব্যভিচারের বিনিময় থেকে নিষেধ করা হয়েছে।","সুদ গ্রহণ ও সুদ দেওয়া—দুটির ব্যাপারেই কঠিন সতর্কতা এসেছে।","উল্কি করা ও করানো থেকে বাঁচতে বলা হয়েছে।","নিষিদ্ধ আয়ের সঙ্গে নিষিদ্ধ কাজ থেকেও দূরে থাকা দরকার।"],"related_hadiths":[{"id":"2237","book_id":"1","label":"Sahih Bukhari"},{"id":"2282","book_id":"1","label":"Sahih Bukhari"},{"id":"2236","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম উপার্জন ও অভিশপ্ত কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. রক্ত, কুকুর ও ব্যভিচারের আয় নিষিদ্ধ; সুদ, উল্কি ও ছবি অঙ্কনের ব্যাপারেও কঠিন সতর্কতা এসেছে।"},"heading":{"title":"হারাম উপার্জন ও নিষিদ্ধ কাজ: রক্ত, সুদ, উল্কি ও ছবি নিয়ে সতর্কতা","description":"এই হাদিসে কয়েকটি বিষয় একসঙ্গে এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) রক্ত বিক্রয়ের মূল্য, কুকুর বিক্রয়ের মূল্য এবং ব্যভিচারের বিনিময় থেকে নিষেধ করেছেন। এরপর সুদ গ্রহীতা ও সুদদাতার প্রতি লা’নতের কথা এসেছে। আরও বলা হয়েছে, যে উল্কি করে এবং যে উল্কি করায়, তাদের ওপরও লা’নত করা হয়েছে। ছবি অঙ্কনকারীর প্রতিও লা’নতের কথা এসেছে। তাই হারাম উপার্জন হাদিস আমাদের আয়ের উৎস এবং কিছু কাজের ব্যাপারে গভীর সতর্ক করে। এখানে অযথা বাড়তি ব্যাখ্যা না করে মূল বার্তাই স্পষ্ট: মুসলিমকে এমন আয় ও কাজ থেকে দূরে থাকতে হবে, যেগুলোর ব্যাপারে নবী (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কঠিন নিষেধ দিয়েছেন।"},"teachings":["রক্ত, কুকুর ও ব্যভিচারের বিনিময় থেকে নিষেধ করা হয়েছে।","সুদ গ্রহণ ও সুদ দেওয়া—দুটির ব্যাপারেই কঠিন সতর্কতা এসেছে।","উল্কি করা ও করানো থেকে বাঁচতে বলা হয়েছে।","নিষিদ্ধ আয়ের সঙ্গে নিষিদ্ধ কাজ থেকেও দূরে থাকা দরকার।"],"related_hadiths":[{"id":"2237","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2282","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E141" s="4" t="n"/>
@@ -3836,7 +3840,7 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম উপার্জনের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম মালে গড়া দেহের ভয়াবহ পরিণতি জানুন এবং হালাল রুজির পথে চলার শিক্ষা নিন।"},"heading":{"title":"হালাল রুজি ও হারাম উপার্জন: মুমিনের জীবনে সতর্কতার শিক্ষা","description":"এই হাদিসে হারাম উপার্জন সম্পর্কে খুব স্পষ্ট সতর্কতা এসেছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে দেহের গোশত হারাম মালে গঠিত, তা জান্নাতে প্রবেশ করতে পারবে না। কথাটি আমাদের খাবার, আয়, ব্যবসা ও লেনদেন নিয়ে ভাবতে শেখায়। শুধু টাকা হাতে এলেই তা ভালো হয়ে যায় না; টাকা কোথা থেকে এল, সেটাও বড় বিষয়। হালাল রুজি মুমিনের জীবনকে নিরাপদ পথে রাখে। আর হারাম মাল শরীরকে পুষ্ট করলেও তা আখিরাতের জন্য ভয়ংকর ক্ষতির কারণ হতে পারে। তাই এই হাদিসের মূল শিক্ষা হলো, আয়-রোজগারে সাবধান থাকা, সন্দেহজনক পথ এড়িয়ে চলা এবং নিজের পরিবারকে হালাল খাবার খাওয়ানোর চেষ্টা করা।"},"teachings":["হারাম উপার্জনে গড়া দেহের জন্য হাদিসে কঠিন সতর্কতা এসেছে।","খাবার ও আয় হালাল কি না, তা মুমিনের জন্য গুরুত্বপূর্ণ বিষয়।","পরিবারকে হালাল রুজি খাওয়ানো ঈমানি দায়িত্বের অংশ।","মাল বেশি হওয়া নয়, মাল হালাল হওয়াই আসল নিরাপত্তার পথ।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"1599","book_id":"2","label":"Sahih Muslim"},{"id":"2760","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম উপার্জনের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম মালে গড়া দেহের ভয়াবহ পরিণতি জানুন এবং হালাল রুজির পথে চলার শিক্ষা নিন।"},"heading":{"title":"হালাল রুজি ও হারাম উপার্জন: মুমিনের জীবনে সতর্কতার শিক্ষা","description":"এই হাদিসে হারাম উপার্জন সম্পর্কে খুব স্পষ্ট সতর্কতা এসেছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে দেহের গোশত হারাম মালে গঠিত, তা জান্নাতে প্রবেশ করতে পারবে না। কথাটি আমাদের খাবার, আয়, ব্যবসা ও লেনদেন নিয়ে ভাবতে শেখায়। শুধু টাকা হাতে এলেই তা ভালো হয়ে যায় না; টাকা কোথা থেকে এল, সেটাও বড় বিষয়। হালাল রুজি মুমিনের জীবনকে নিরাপদ পথে রাখে। আর হারাম মাল শরীরকে পুষ্ট করলেও তা আখিরাতের জন্য ভয়ংকর ক্ষতির কারণ হতে পারে। তাই এই হাদিসের মূল শিক্ষা হলো, আয়-রোজগারে সাবধান থাকা, সন্দেহজনক পথ এড়িয়ে চলা এবং নিজের পরিবারকে হালাল খাবার খাওয়ানোর চেষ্টা করা।"},"teachings":["হারাম উপার্জনে গড়া দেহের জন্য হাদিসে কঠিন সতর্কতা এসেছে।","খাবার ও আয় হালাল কি না, তা মুমিনের জন্য গুরুত্বপূর্ণ বিষয়।","পরিবারকে হালাল রুজি খাওয়ানো ঈমানি দায়িত্বের অংশ।","মাল বেশি হওয়া নয়, মাল হালাল হওয়াই আসল নিরাপত্তার পথ।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1599","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2760","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E142" s="4" t="n"/>
@@ -3859,7 +3863,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক কাজ ছেড়ে নিশ্চিত পথে চলা","description":"$book_name$ $hadith_number$ - $chapter_name$. মনে খটকা লাগা কাজ ছেড়ে পরিষ্কার ও শান্তির পথে চলার সুন্দর নববী শিক্ষা জানুন।"},"heading":{"title":"সন্দেহজনক কাজ থেকে বাঁচার হাদিস: সত্যে শান্তি, মিথ্যায় খটকা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম একটি সহজ কিন্তু গভীর নিয়ম শিখিয়েছেন। যে কাজে মনে খটকা লাগে, সে কাজ ছেড়ে এমন কাজ বেছে নিতে বলা হয়েছে যাতে খটকা নেই। মানুষের অন্তর অনেক সময় ভুল ও ঠিকের মাঝে অস্বস্তি টের পায়। হাদিসটি বলে, সত্য ও শুদ্ধ জিনিস সাধারণত অন্তরে প্রশান্তি আনে, আর মিথ্যা ও অশুদ্ধ জিনিস দ্বিধা তৈরি করে। তাই সন্দেহজনক কাজ এড়িয়ে চলা শুধু ইবাদতের বিষয় নয়; এটি চরিত্র, কথা, ব্যবসা ও সম্পর্কের ক্ষেত্রেও দরকারি। এই শিক্ষা মানুষকে নিরাপদ, পরিষ্কার এবং সৎ পথে চলতে সাহায্য করে।"},"teachings":["যে কাজে মনে খটকা লাগে, তা ছেড়ে দেওয়া ভালো।","সত্য অন্তরে প্রশান্তি আনে, মিথ্যা দ্বিধা সৃষ্টি করে।","সন্দেহজনক কাজ থেকে দূরে থাকা দ্বীন রক্ষার পথ।","কথা ও কাজে পরিষ্কার অবস্থান নেওয়া মুমিনের গুণ।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"1599","book_id":"2","label":"Sahih Muslim"},{"id":"2553","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক কাজ ছেড়ে নিশ্চিত পথে চলা","description":"$book_name$ $hadith_number$ - $chapter_name$. মনে খটকা লাগা কাজ ছেড়ে পরিষ্কার ও শান্তির পথে চলার সুন্দর নববী শিক্ষা জানুন।"},"heading":{"title":"সন্দেহজনক কাজ থেকে বাঁচার হাদিস: সত্যে শান্তি, মিথ্যায় খটকা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম একটি সহজ কিন্তু গভীর নিয়ম শিখিয়েছেন। যে কাজে মনে খটকা লাগে, সে কাজ ছেড়ে এমন কাজ বেছে নিতে বলা হয়েছে যাতে খটকা নেই। মানুষের অন্তর অনেক সময় ভুল ও ঠিকের মাঝে অস্বস্তি টের পায়। হাদিসটি বলে, সত্য ও শুদ্ধ জিনিস সাধারণত অন্তরে প্রশান্তি আনে, আর মিথ্যা ও অশুদ্ধ জিনিস দ্বিধা তৈরি করে। তাই সন্দেহজনক কাজ এড়িয়ে চলা শুধু ইবাদতের বিষয় নয়; এটি চরিত্র, কথা, ব্যবসা ও সম্পর্কের ক্ষেত্রেও দরকারি। এই শিক্ষা মানুষকে নিরাপদ, পরিষ্কার এবং সৎ পথে চলতে সাহায্য করে।"},"teachings":["যে কাজে মনে খটকা লাগে, তা ছেড়ে দেওয়া ভালো।","সত্য অন্তরে প্রশান্তি আনে, মিথ্যা দ্বিধা সৃষ্টি করে।","সন্দেহজনক কাজ থেকে দূরে থাকা দ্বীন রক্ষার পথ।","কথা ও কাজে পরিষ্কার অবস্থান নেওয়া মুমিনের গুণ।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1599","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2553","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E143" s="4" t="n"/>
@@ -3882,7 +3886,7 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গায়িকা কেনাবেচা ও হারাম মূল্য","description":"$book_name$ $hadith_number$ - $chapter_name$. গায়িকা ক্রয়-বিক্রয়, গান শেখানো ও তার মূল্য সম্পর্কে হাদিসের সতর্ক বার্তা জানুন।"},"heading":{"title":"গায়িকা ক্রয়-বিক্রয় ও হারাম উপার্জন নিয়ে হাদিসের শিক্ষা","description":"এই হাদিসে গায়িকা ক্রয়-বিক্রয়, তাদের গান শেখানো এবং এ ধরনের কাজে পাওয়া মূল্য সম্পর্কে কঠোরভাবে নিষেধ এসেছে। হাদিসের ভাষায় তাদের মূল্য হারাম বলা হয়েছে। এখানে মূল শিক্ষা হলো, বিনোদনের নামে এমন কাজে জড়ানো থেকে বাঁচা যা মানুষকে আল্লাহর পথ থেকে দূরে নিতে পারে। অনুবাদে কুরআনের একটি আয়াতের কথাও এসেছে, যেখানে রং-তামাশার গাথা কেনার কথা বলা হয়েছে। তাই এই হাদিস শুধু গান-বাজনা নিয়ে নয়; বরং এমন আয়ের পথ নিয়েও সতর্ক করে, যা দ্বীন ও চরিত্রের ক্ষতি করতে পারে। একজন মুমিনের উচিত নিজের আয় ও বিনোদন—দুটো ক্ষেত্রেই আল্লাহভীতি রাখা।"},"teachings":["গায়িকা ক্রয়-বিক্রয় ও গান শেখানোর বিষয়ে হাদিসে নিষেধ এসেছে।","এ ধরনের কাজের মূল্যকে হাদিসে হারাম বলা হয়েছে।","বিনোদন যেন দ্বীন থেকে দূরে নেওয়ার কারণ না হয়।","আয়ের উৎস হালাল কি না, তা যাচাই করা জরুরি।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"4020","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গায়িকা কেনাবেচা ও হারাম মূল্য","description":"$book_name$ $hadith_number$ - $chapter_name$. গায়িকা ক্রয়-বিক্রয়, গান শেখানো ও তার মূল্য সম্পর্কে হাদিসের সতর্ক বার্তা জানুন।"},"heading":{"title":"গায়িকা ক্রয়-বিক্রয় ও হারাম উপার্জন নিয়ে হাদিসের শিক্ষা","description":"এই হাদিসে গায়িকা ক্রয়-বিক্রয়, তাদের গান শেখানো এবং এ ধরনের কাজে পাওয়া মূল্য সম্পর্কে কঠোরভাবে নিষেধ এসেছে। হাদিসের ভাষায় তাদের মূল্য হারাম বলা হয়েছে। এখানে মূল শিক্ষা হলো, বিনোদনের নামে এমন কাজে জড়ানো থেকে বাঁচা যা মানুষকে আল্লাহর পথ থেকে দূরে নিতে পারে। অনুবাদে কুরআনের একটি আয়াতের কথাও এসেছে, যেখানে রং-তামাশার গাথা কেনার কথা বলা হয়েছে। তাই এই হাদিস শুধু গান-বাজনা নিয়ে নয়; বরং এমন আয়ের পথ নিয়েও সতর্ক করে, যা দ্বীন ও চরিত্রের ক্ষতি করতে পারে। একজন মুমিনের উচিত নিজের আয় ও বিনোদন—দুটো ক্ষেত্রেই আল্লাহভীতি রাখা।"},"teachings":["গায়িকা ক্রয়-বিক্রয় ও গান শেখানোর বিষয়ে হাদিসে নিষেধ এসেছে।","এ ধরনের কাজের মূল্যকে হাদিসে হারাম বলা হয়েছে।","বিনোদন যেন দ্বীন থেকে দূরে নেওয়ার কারণ না হয়।","আয়ের উৎস হালাল কি না, তা যাচাই করা জরুরি।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4020","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
@@ -3909,7 +3913,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম খাদ্য থেকে আবু বকরের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহজনক ও হারাম উৎসের খাদ্য থেকে বাঁচতে আবু বকর রাঃ-এর সতর্কতার ঘটনা জানুন।"},"heading":{"title":"হারাম খাদ্য এড়ানোর বাস্তব শিক্ষা: আবু বকর রাঃ-এর ঘটনা","description":"এই বর্ণনায় আবু বকর ছিদ্দীক রাদিয়াল্লাহু আনহুর অত্যন্ত সতর্ক মনোভাব দেখা যায়। তাঁর গোলাম যে খাবার এনেছিল, তিনি প্রথমে তা থেকে কিছু খেয়েছিলেন। পরে যখন জানা গেল খাবারটি এমন আয়ের সাথে যুক্ত, যেখানে জাহেলী যুগের গণকী ও ধোঁকার কথা আছে, তখন তিনি মুখে হাত ঢুকিয়ে সব বের করে দিলেন। এই ঘটনা আমাদের শেখায়, হারাম খাদ্য বা সন্দেহজনক উৎসের খাবার নিয়ে সাহাবীগণ কতটা সাবধান ছিলেন। হালাল রুজি শুধু আয় করার বিষয় নয়; তা খাওয়া, গ্রহণ করা এবং পরিবারের জীবনে ঢোকানোর ক্ষেত্রেও সতর্কতা দরকার।"},"teachings":["খাবারের উৎস জানার বিষয়টি গুরুত্বের সাথে দেখা দরকার।","ধোঁকা ও গণকীর মাধ্যমে পাওয়া আয় থেকে বাঁচা উচিত।","ভুলে কিছু গ্রহণ করলে জানার পর তা থেকে সরে আসা ভালো।","আবু বকর রাঃ-এর ঘটনা হারাম খাদ্য এড়ানোর শক্ত শিক্ষা দেয়।"],"related_hadiths":[{"id":"2237","book_id":"1","label":"Sahih Bukhari"},{"id":"1567","book_id":"2","label":"Sahih Muslim"},{"id":"2764","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম খাদ্য থেকে আবু বকরের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহজনক ও হারাম উৎসের খাদ্য থেকে বাঁচতে আবু বকর রাঃ-এর সতর্কতার ঘটনা জানুন।"},"heading":{"title":"হারাম খাদ্য এড়ানোর বাস্তব শিক্ষা: আবু বকর রাঃ-এর ঘটনা","description":"এই বর্ণনায় আবু বকর ছিদ্দীক রাদিয়াল্লাহু আনহুর অত্যন্ত সতর্ক মনোভাব দেখা যায়। তাঁর গোলাম যে খাবার এনেছিল, তিনি প্রথমে তা থেকে কিছু খেয়েছিলেন। পরে যখন জানা গেল খাবারটি এমন আয়ের সাথে যুক্ত, যেখানে জাহেলী যুগের গণকী ও ধোঁকার কথা আছে, তখন তিনি মুখে হাত ঢুকিয়ে সব বের করে দিলেন। এই ঘটনা আমাদের শেখায়, হারাম খাদ্য বা সন্দেহজনক উৎসের খাবার নিয়ে সাহাবীগণ কতটা সাবধান ছিলেন। হালাল রুজি শুধু আয় করার বিষয় নয়; তা খাওয়া, গ্রহণ করা এবং পরিবারের জীবনে ঢোকানোর ক্ষেত্রেও সতর্কতা দরকার।"},"teachings":["খাবারের উৎস জানার বিষয়টি গুরুত্বের সাথে দেখা দরকার।","ধোঁকা ও গণকীর মাধ্যমে পাওয়া আয় থেকে বাঁচা উচিত।","ভুলে কিছু গ্রহণ করলে জানার পর তা থেকে সরে আসা ভালো।","আবু বকর রাঃ-এর ঘটনা হারাম খাদ্য এড়ানোর শক্ত শিক্ষা দেয়।"],"related_hadiths":[{"id":"2237","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1567","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2764","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E145" s="4" t="n"/>
@@ -3932,7 +3936,7 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম দ্বারা প্রতিপালিত দেহের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম দ্বারা প্রতিপালিত দেহ সম্পর্কে নবীজির সতর্ক বাণী ও হালাল জীবনের শিক্ষা পড়ুন।"},"heading":{"title":"হারাম রুজি থেকে বাঁচার হাদিস: দেহ, খাদ্য ও আখিরাতের ভাবনা","description":"এই হাদিসে খুব সংক্ষিপ্ত ভাষায় বড় সতর্কতা দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে দেহ হারাম দ্বারা প্রতিপালিত, তা জান্নাতে প্রবেশ করবে না। এর মানে, মানুষের শরীর কী দিয়ে বড় হচ্ছে—এটি দ্বীনের দৃষ্টিতে গুরুত্বপূর্ণ। হারাম আয়, হারাম খাবার এবং অন্যায় পথে পাওয়া সম্পদ শুধু দুনিয়ার বিষয় নয়; এর আখিরাতের দিকও আছে। হালাল রুজি কম হলেও তা নিরাপদ। আর হারাম রুজি বেশি হলেও তা ক্ষতির কারণ হতে পারে। তাই এই হাদিস মুমিনকে নিজের উপার্জন, খাওয়া-দাওয়া ও পরিবারের খরচের উৎস নিয়ে সচেতন করে।"},"teachings":["হারাম দ্বারা প্রতিপালিত দেহ সম্পর্কে হাদিসে কঠিন সতর্কতা এসেছে।","রুজির উৎস হালাল হওয়া মুমিনের জীবনে বড় বিষয়।","কম হালাল আয়ও হারাম বেশি আয়ের চেয়ে নিরাপদ।","নিজের ও পরিবারের খাবারের উৎস যাচাই করা দরকার।"],"related_hadiths":[{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"1599","book_id":"2","label":"Sahih Muslim"},{"id":"2760","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম দ্বারা প্রতিপালিত দেহের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম দ্বারা প্রতিপালিত দেহ সম্পর্কে নবীজির সতর্ক বাণী ও হালাল জীবনের শিক্ষা পড়ুন।"},"heading":{"title":"হারাম রুজি থেকে বাঁচার হাদিস: দেহ, খাদ্য ও আখিরাতের ভাবনা","description":"এই হাদিসে খুব সংক্ষিপ্ত ভাষায় বড় সতর্কতা দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে দেহ হারাম দ্বারা প্রতিপালিত, তা জান্নাতে প্রবেশ করবে না। এর মানে, মানুষের শরীর কী দিয়ে বড় হচ্ছে—এটি দ্বীনের দৃষ্টিতে গুরুত্বপূর্ণ। হারাম আয়, হারাম খাবার এবং অন্যায় পথে পাওয়া সম্পদ শুধু দুনিয়ার বিষয় নয়; এর আখিরাতের দিকও আছে। হালাল রুজি কম হলেও তা নিরাপদ। আর হারাম রুজি বেশি হলেও তা ক্ষতির কারণ হতে পারে। তাই এই হাদিস মুমিনকে নিজের উপার্জন, খাওয়া-দাওয়া ও পরিবারের খরচের উৎস নিয়ে সচেতন করে।"},"teachings":["হারাম দ্বারা প্রতিপালিত দেহ সম্পর্কে হাদিসে কঠিন সতর্কতা এসেছে।","রুজির উৎস হালাল হওয়া মুমিনের জীবনে বড় বিষয়।","কম হালাল আয়ও হারাম বেশি আয়ের চেয়ে নিরাপদ।","নিজের ও পরিবারের খাবারের উৎস যাচাই করা দরকার।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1599","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2760","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E146" s="4" t="n"/>
@@ -3955,7 +3959,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক খেজুর না খাওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. সদকার খেজুর হতে পারে—এই আশঙ্কায় নবীজির সতর্কতা থেকে সন্দেহ এড়ানোর শিক্ষা জানুন।"},"heading":{"title":"সদকার সন্দেহে খেজুর না খাওয়া: নবীজির সতর্কতার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম রাস্তায় পড়ে থাকা একটি খেজুরের পাশ দিয়ে যান। তিনি বলেন, যদি সদকার খেজুর হওয়ার সন্দেহ না থাকত, তবে তিনি তা খেতেন। এই ছোট ঘটনাতেই বড় শিক্ষা আছে। এখানে খেজুরটি সামান্য জিনিস, কিন্তু নবীজি সন্দেহের জায়গায় সতর্কতা দেখিয়েছেন। কারণ সদকা তাঁর জন্য খাওয়া বৈধ ছিল না। হাদিসটি আমাদের শেখায়, সামান্য জিনিস হলেও হালাল-হারামের সীমা মানা দরকার। যখন কোনো বিষয়ে সন্দেহ থাকে, তখন সাবধান থাকা মুমিনের চরিত্রকে সুন্দর করে। এটি লোভ কমায় এবং অন্তরে আল্লাহভীতি বাড়ায়।"},"teachings":["সন্দেহের জায়গায় সাবধান থাকা নবীজির শিক্ষা।","সামান্য জিনিস হলেও হালাল-হারাম দেখা দরকার।","নিজের জন্য যা বৈধ নয়, তা থেকে দূরে থাকা উচিত।","খাবার গ্রহণেও আল্লাহভীতি থাকা মুমিনের গুণ।"],"related_hadiths":[{"id":"2055","book_id":"1","label":"Sahih Bukhari"},{"id":"1071","book_id":"2","label":"Sahih Muslim"},{"id":"1652","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক খেজুর না খাওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. সদকার খেজুর হতে পারে—এই আশঙ্কায় নবীজির সতর্কতা থেকে সন্দেহ এড়ানোর শিক্ষা জানুন।"},"heading":{"title":"সদকার সন্দেহে খেজুর না খাওয়া: নবীজির সতর্কতার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম রাস্তায় পড়ে থাকা একটি খেজুরের পাশ দিয়ে যান। তিনি বলেন, যদি সদকার খেজুর হওয়ার সন্দেহ না থাকত, তবে তিনি তা খেতেন। এই ছোট ঘটনাতেই বড় শিক্ষা আছে। এখানে খেজুরটি সামান্য জিনিস, কিন্তু নবীজি সন্দেহের জায়গায় সতর্কতা দেখিয়েছেন। কারণ সদকা তাঁর জন্য খাওয়া বৈধ ছিল না। হাদিসটি আমাদের শেখায়, সামান্য জিনিস হলেও হালাল-হারামের সীমা মানা দরকার। যখন কোনো বিষয়ে সন্দেহ থাকে, তখন সাবধান থাকা মুমিনের চরিত্রকে সুন্দর করে। এটি লোভ কমায় এবং অন্তরে আল্লাহভীতি বাড়ায়।"},"teachings":["সন্দেহের জায়গায় সাবধান থাকা নবীজির শিক্ষা।","সামান্য জিনিস হলেও হালাল-হারাম দেখা দরকার।","নিজের জন্য যা বৈধ নয়, তা থেকে দূরে থাকা উচিত।","খাবার গ্রহণেও আল্লাহভীতি থাকা মুমিনের গুণ।"],"related_hadiths":[{"id":"2055","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1071","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1652","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E147" s="4" t="n"/>
@@ -3978,7 +3982,7 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যাকাতের খেজুর ও নবী পরিবারের বিধান","description":"$book_name$ $hadith_number$ - $chapter_name$. হাসান রাঃ-এর যাকাতের খেজুর ঘটনায় নবী পরিবারের জন্য সদকা না খাওয়ার শিক্ষা জানুন।"},"heading":{"title":"যাকাতের খেজুর নিয়ে হাদিস: নবী পরিবারের জন্য সদকার বিধান","description":"এই হাদিসে হাসান ইবনে আলী রাদিয়াল্লাহু আনহু যাকাতের একটি খেজুর মুখে দেন। নবী করীম সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম সঙ্গে সঙ্গে তাঁকে তা ফেলে দিতে বলেন এবং জানান, তাঁরা যাকাত খান না। এখানে শিক্ষা খুব পরিষ্কার। শিশুর ক্ষেত্রেও নবীজি হালাল-হারামের সীমা শেখাতে দেরি করেননি। তবে ভাষা ছিল কোমল ও শাসনের মতো। যাকাত একটি নির্দিষ্ট ইবাদত এবং এর খাতও নির্দিষ্ট। যাদের জন্য তা গ্রহণের বিধান নেই, তাদের তা খাওয়া উচিত নয়। এই হাদিস আমাদের শেখায়, ছোট বয়স থেকেই সন্তানকে বৈধ-অবৈধের শিক্ষা দেওয়া দরকার।"},"teachings":["যাকাতের মাল যার জন্য বৈধ নয়, তার তা খাওয়া উচিত নয়।","শিশুকেও হালাল-হারামের শিক্ষা দেওয়া দরকার।","নবীজি পরিবারকে দ্বীনের বিধান মানতে শিখিয়েছেন।","খাবার মুখে দেওয়ার আগেও উৎস জানা গুরুত্বপূর্ণ।"],"related_hadiths":[{"id":"2363","book_id":"2","label":"Sahih Muslim"},{"id":"2055","book_id":"1","label":"Sahih Bukhari"},{"id":"1071","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যাকাতের খেজুর ও নবী পরিবারের বিধান","description":"$book_name$ $hadith_number$ - $chapter_name$. হাসান রাঃ-এর যাকাতের খেজুর ঘটনায় নবী পরিবারের জন্য সদকা না খাওয়ার শিক্ষা জানুন।"},"heading":{"title":"যাকাতের খেজুর নিয়ে হাদিস: নবী পরিবারের জন্য সদকার বিধান","description":"এই হাদিসে হাসান ইবনে আলী রাদিয়াল্লাহু আনহু যাকাতের একটি খেজুর মুখে দেন। নবী করীম সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম সঙ্গে সঙ্গে তাঁকে তা ফেলে দিতে বলেন এবং জানান, তাঁরা যাকাত খান না। এখানে শিক্ষা খুব পরিষ্কার। শিশুর ক্ষেত্রেও নবীজি হালাল-হারামের সীমা শেখাতে দেরি করেননি। তবে ভাষা ছিল কোমল ও শাসনের মতো। যাকাত একটি নির্দিষ্ট ইবাদত এবং এর খাতও নির্দিষ্ট। যাদের জন্য তা গ্রহণের বিধান নেই, তাদের তা খাওয়া উচিত নয়। এই হাদিস আমাদের শেখায়, ছোট বয়স থেকেই সন্তানকে বৈধ-অবৈধের শিক্ষা দেওয়া দরকার।"},"teachings":["যাকাতের মাল যার জন্য বৈধ নয়, তার তা খাওয়া উচিত নয়।","শিশুকেও হালাল-হারামের শিক্ষা দেওয়া দরকার।","নবীজি পরিবারকে দ্বীনের বিধান মানতে শিখিয়েছেন।","খাবার মুখে দেওয়ার আগেও উৎস জানা গুরুত্বপূর্ণ।"],"related_hadiths":[{"id":"2363","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2055","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1071","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E148" s="4" t="n"/>
@@ -4001,7 +4005,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিককে নেতা বলা থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মুনাফিক বা মিথ্যুক ব্যক্তিকে নেতা হিসেবে সম্মান করার বিষয়ে নবীজির সতর্ক বাণী জানুন।"},"heading":{"title":"মুনাফিককে নেতা বলা: সত্য, নেতৃত্ব ও ঈমানি সতর্কতার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম মুনাফিক ব্যক্তিকে নেতা বা সাইয়িদ বলতে নিষেধ করেছেন। অনুবাদে এসেছে, যদি নেতা মুনাফিক হয়, তাহলে এতে প্রতিপালককে অসন্তুষ্ট করার কথা বলা হয়েছে। অন্য বর্ণনায় মিথ্যুক মুনাফিককে নেতা বলা নিয়েও কঠিন সতর্কতা এসেছে। হাদিসটি নেতৃত্বের ভাষা ও সম্মান দেওয়ার বিষয়ে আমাদের সতর্ক করে। সম্মান এমন কাউকে দেওয়া উচিত নয়, যার ভেতরে মুনাফিকি, মিথ্যা বা দ্বীনের বিরুদ্ধে আচরণ আছে। এর মানে সাধারণ আচরণে অশোভন হওয়া নয়; বরং নৈতিক সম্মান ও নেতৃত্বের আসন কাকে দেওয়া হচ্ছে, সে বিষয়ে সতর্ক থাকা।"},"teachings":["মুনাফিক ব্যক্তিকে নেতৃত্বের সম্মান দেওয়ার বিষয়ে সতর্কতা এসেছে।","মিথ্যুক ও দ্বিমুখী চরিত্রের মানুষকে অকারণে বড় করা উচিত নয়।","নেতৃত্বের সম্মান নৈতিকতার সাথে জড়িত।","কথার মাধ্যমে কাকে মর্যাদা দিচ্ছি, তা ভাবা দরকার।"],"related_hadiths":[{"id":"33","book_id":"1","label":"Sahih Bukhari"},{"id":"59","book_id":"2","label":"Sahih Muslim"},{"id":"4873","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিককে নেতা বলা থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মুনাফিক বা মিথ্যুক ব্যক্তিকে নেতা হিসেবে সম্মান করার বিষয়ে নবীজির সতর্ক বাণী জানুন।"},"heading":{"title":"মুনাফিককে নেতা বলা: সত্য, নেতৃত্ব ও ঈমানি সতর্কতার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম মুনাফিক ব্যক্তিকে নেতা বা সাইয়িদ বলতে নিষেধ করেছেন। অনুবাদে এসেছে, যদি নেতা মুনাফিক হয়, তাহলে এতে প্রতিপালককে অসন্তুষ্ট করার কথা বলা হয়েছে। অন্য বর্ণনায় মিথ্যুক মুনাফিককে নেতা বলা নিয়েও কঠিন সতর্কতা এসেছে। হাদিসটি নেতৃত্বের ভাষা ও সম্মান দেওয়ার বিষয়ে আমাদের সতর্ক করে। সম্মান এমন কাউকে দেওয়া উচিত নয়, যার ভেতরে মুনাফিকি, মিথ্যা বা দ্বীনের বিরুদ্ধে আচরণ আছে। এর মানে সাধারণ আচরণে অশোভন হওয়া নয়; বরং নৈতিক সম্মান ও নেতৃত্বের আসন কাকে দেওয়া হচ্ছে, সে বিষয়ে সতর্ক থাকা।"},"teachings":["মুনাফিক ব্যক্তিকে নেতৃত্বের সম্মান দেওয়ার বিষয়ে সতর্কতা এসেছে।","মিথ্যুক ও দ্বিমুখী চরিত্রের মানুষকে অকারণে বড় করা উচিত নয়।","নেতৃত্বের সম্মান নৈতিকতার সাথে জড়িত।","কথার মাধ্যমে কাকে মর্যাদা দিচ্ছি, তা ভাবা দরকার।"],"related_hadiths":[{"id":"33","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"59","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"4873","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E149" s="4" t="n"/>
@@ -4024,7 +4028,7 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তর্ক, মিথ্যা ও সুন্দর চরিত্রের ফজিলত","description":"$book_name$ $hadith_number$ - $chapter_name$. হক হলেও তর্ক ছাড়া, মজা করেও মিথ্যা না বলা এবং চরিত্র সুন্দর করার বড় শিক্ষা জানুন।"},"heading":{"title":"সুন্দর চরিত্রের হাদিস: তর্ক ছাড়া, মিথ্যা ছাড়া, ভালো আচরণ","description":"এই হাদিসে তিনটি বড় আচরণ শেখানো হয়েছে। প্রথমত, কেউ হক হলেও তর্ক পরিহার করলে তার জন্য জান্নাতে ঘরের কথা এসেছে। দ্বিতীয়ত, মজা করেও মিথ্যা ছেড়ে দেওয়ার কথা বলা হয়েছে। তৃতীয়ত, চরিত্র সুন্দর করার ফজিলত এসেছে। হাদিসটি আমাদের দৈনন্দিন কথা ও আচরণকে ঠিক করার সহজ পথ দেখায়। অনেক সময় মানুষ সত্য কথা বলেও তর্কে জড়িয়ে পড়ে, আবার হাসানোর জন্য মিথ্যা বলে ফেলে। এই হাদিস শেখায়, সত্যের সাথে নম্রতা, কথার সাথে সততা এবং মানুষের সাথে ভালো ব্যবহার—সবই মুমিনের চরিত্রের অংশ। সুন্দর চরিত্র শুধু বাহ্যিক ভদ্রতা নয়; এটি কথা, রাগ, তর্ক ও আচরণে প্রকাশ পায়।"},"teachings":["হক হলেও অপ্রয়োজনীয় তর্ক ছেড়ে দেওয়া উত্তম কাজ।","মজা করেও মিথ্যা বলা থেকে বাঁচতে হবে।","সুন্দর চরিত্র জান্নাতের বড় ফজিলতের কারণ।","সত্য কথা বলার সঙ্গে নম্র আচরণও দরকার।"],"related_hadiths":[{"id":"4800","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"2004","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তর্ক, মিথ্যা ও সুন্দর চরিত্রের ফজিলত","description":"$book_name$ $hadith_number$ - $chapter_name$. হক হলেও তর্ক ছাড়া, মজা করেও মিথ্যা না বলা এবং চরিত্র সুন্দর করার বড় শিক্ষা জানুন।"},"heading":{"title":"সুন্দর চরিত্রের হাদিস: তর্ক ছাড়া, মিথ্যা ছাড়া, ভালো আচরণ","description":"এই হাদিসে তিনটি বড় আচরণ শেখানো হয়েছে। প্রথমত, কেউ হক হলেও তর্ক পরিহার করলে তার জন্য জান্নাতে ঘরের কথা এসেছে। দ্বিতীয়ত, মজা করেও মিথ্যা ছেড়ে দেওয়ার কথা বলা হয়েছে। তৃতীয়ত, চরিত্র সুন্দর করার ফজিলত এসেছে। হাদিসটি আমাদের দৈনন্দিন কথা ও আচরণকে ঠিক করার সহজ পথ দেখায়। অনেক সময় মানুষ সত্য কথা বলেও তর্কে জড়িয়ে পড়ে, আবার হাসানোর জন্য মিথ্যা বলে ফেলে। এই হাদিস শেখায়, সত্যের সাথে নম্রতা, কথার সাথে সততা এবং মানুষের সাথে ভালো ব্যবহার—সবই মুমিনের চরিত্রের অংশ। সুন্দর চরিত্র শুধু বাহ্যিক ভদ্রতা নয়; এটি কথা, রাগ, তর্ক ও আচরণে প্রকাশ পায়।"},"teachings":["হক হলেও অপ্রয়োজনীয় তর্ক ছেড়ে দেওয়া উত্তম কাজ।","মজা করেও মিথ্যা বলা থেকে বাঁচতে হবে।","সুন্দর চরিত্র জান্নাতের বড় ফজিলতের কারণ।","সত্য কথা বলার সঙ্গে নম্র আচরণও দরকার।"],"related_hadiths":[{"id":"4800","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2004","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E150" s="4" t="n"/>
@@ -4047,7 +4051,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বায়আত ও বড় গুনাহ থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, চুরি, যেনা, সন্তান হত্যা, অপবাদ ও অবাধ্যতা থেকে দূরে থাকার বায়আতের শিক্ষা এসেছে।"},"heading":{"title":"বায়আতের শর্ত ও বড় গুনাহ থেকে বাঁচার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সাহাবীদের কাছ থেকে বায়আত নেন। তিনি বলেন, তারা যেন আল্লাহর সঙ্গে কাউকে শরীক না করে, চুরি না করে, যেনা না করে, সন্তান হত্যা না করে, কারও প্রতি অপবাদ না দেয় এবং শরীআতসম্মত বিষয়ে অবাধ্যতা না করে। এরপর তিনি জানান, যে এসব অঙ্গীকার পূর্ণ করবে, তার পুরস্কার আল্লাহর কাছে। কেউ যদি কোনো অপরাধ করে এবং দুনিয়াতে শাস্তি পায়, তা তার জন্য কাফফারা হতে পারে। আর আল্লাহ যদি তা ঢেকে রাখেন, তাহলে বিষয়টি আল্লাহর ইচ্ছার উপর। এই হাদিসে বায়আত, তাওহীদ, নৈতিকতা, অপরাধ থেকে বাঁচা এবং আল্লাহর বিচার—সব মিলিয়ে দায়িত্বশীল জীবনের শিক্ষা আছে।"},"teachings":["শিরক, চুরি, যেনা, অপবাদ ও অন্যায় থেকে দূরে থাকা জরুরি।","শরীআতসম্মত বিষয়ে অবাধ্যতা করা ঠিক নয়।","অঙ্গীকার পূরণ করলে প্রতিদান আল্লাহর কাছে।","গুনাহের বিচার আল্লাহর ইচ্ছা ও ন্যায়ের সঙ্গে জড়িত।"],"related_hadiths":[{"id":"18","book_id":"1","label":"Sahih Bukhari"},{"id":"1709","book_id":"2","label":"Sahih Muslim"},{"id":"18","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বায়আত ও বড় গুনাহ থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, চুরি, যেনা, সন্তান হত্যা, অপবাদ ও অবাধ্যতা থেকে দূরে থাকার বায়আতের শিক্ষা এসেছে।"},"heading":{"title":"বায়আতের শর্ত ও বড় গুনাহ থেকে বাঁচার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সাহাবীদের কাছ থেকে বায়আত নেন। তিনি বলেন, তারা যেন আল্লাহর সঙ্গে কাউকে শরীক না করে, চুরি না করে, যেনা না করে, সন্তান হত্যা না করে, কারও প্রতি অপবাদ না দেয় এবং শরীআতসম্মত বিষয়ে অবাধ্যতা না করে। এরপর তিনি জানান, যে এসব অঙ্গীকার পূর্ণ করবে, তার পুরস্কার আল্লাহর কাছে। কেউ যদি কোনো অপরাধ করে এবং দুনিয়াতে শাস্তি পায়, তা তার জন্য কাফফারা হতে পারে। আর আল্লাহ যদি তা ঢেকে রাখেন, তাহলে বিষয়টি আল্লাহর ইচ্ছার উপর। এই হাদিসে বায়আত, তাওহীদ, নৈতিকতা, অপরাধ থেকে বাঁচা এবং আল্লাহর বিচার—সব মিলিয়ে দায়িত্বশীল জীবনের শিক্ষা আছে।"},"teachings":["শিরক, চুরি, যেনা, অপবাদ ও অন্যায় থেকে দূরে থাকা জরুরি।","শরীআতসম্মত বিষয়ে অবাধ্যতা করা ঠিক নয়।","অঙ্গীকার পূরণ করলে প্রতিদান আল্লাহর কাছে।","গুনাহের বিচার আল্লাহর ইচ্ছা ও ন্যায়ের সঙ্গে জড়িত।"],"related_hadiths":[{"id":"18","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1709","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"18","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E151" s="4" t="n"/>
@@ -4070,7 +4074,7 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আল্লাহর ভালোবাসার পথে আমানত ও সত্য","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ ও রাসূলের ভালোবাসা পেতে আমানত, সত্য কথা ও প্রতিবেশীর ভালো আচরণের শিক্ষা জানুন।"},"heading":{"title":"আমানত রক্ষা, সত্য কথা ও প্রতিবেশীর হক: ভালোবাসার হাদিস","description":"এই হাদিসে সাহাবীরা নবীজির ওযূর পানির প্রতি ভালোবাসা দেখিয়েছিলেন। তাঁরা বললেন, এটি আল্লাহ ও তাঁর রাসূলের ভালোবাসার কারণে করেছেন। তখন রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম তাঁদের সামনে ভালোবাসার বাস্তব পথ জানালেন। তিনি বললেন, আমানত রাখা হলে তা ফিরিয়ে দাও, কথা বললে সত্য বল, আর প্রতিবেশীর সাথে ভালো আচরণ কর। এতে বোঝা যায়, ভালোবাসা শুধু আবেগে সীমাবদ্ধ নয়; তা কাজে প্রকাশ পায়। একজন মুমিন আল্লাহ ও রাসূলকে ভালোবাসতে চাইলে তার লেনদেন সৎ হবে, কথায় মিথ্যা থাকবে না এবং পাশের মানুষের সাথে আচরণ সুন্দর হবে।"},"teachings":["আমানত রাখা হলে তা যথাযথভাবে ফিরিয়ে দেওয়া দরকার।","কথা বলার সময় সত্য বলা ভালোবাসার বাস্তব প্রকাশ।","প্রতিবেশীর সাথে ভালো আচরণ মুমিনের দায়িত্ব।","আল্লাহ ও রাসূলের ভালোবাসা কাজে প্রমাণ করতে হয়।"],"related_hadiths":[{"id":"33","book_id":"1","label":"Sahih Bukhari"},{"id":"6016","book_id":"1","label":"Sahih Bukhari"},{"id":"46","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আল্লাহর ভালোবাসার পথে আমানত ও সত্য","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ ও রাসূলের ভালোবাসা পেতে আমানত, সত্য কথা ও প্রতিবেশীর ভালো আচরণের শিক্ষা জানুন।"},"heading":{"title":"আমানত রক্ষা, সত্য কথা ও প্রতিবেশীর হক: ভালোবাসার হাদিস","description":"এই হাদিসে সাহাবীরা নবীজির ওযূর পানির প্রতি ভালোবাসা দেখিয়েছিলেন। তাঁরা বললেন, এটি আল্লাহ ও তাঁর রাসূলের ভালোবাসার কারণে করেছেন। তখন রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম তাঁদের সামনে ভালোবাসার বাস্তব পথ জানালেন। তিনি বললেন, আমানত রাখা হলে তা ফিরিয়ে দাও, কথা বললে সত্য বল, আর প্রতিবেশীর সাথে ভালো আচরণ কর। এতে বোঝা যায়, ভালোবাসা শুধু আবেগে সীমাবদ্ধ নয়; তা কাজে প্রকাশ পায়। একজন মুমিন আল্লাহ ও রাসূলকে ভালোবাসতে চাইলে তার লেনদেন সৎ হবে, কথায় মিথ্যা থাকবে না এবং পাশের মানুষের সাথে আচরণ সুন্দর হবে।"},"teachings":["আমানত রাখা হলে তা যথাযথভাবে ফিরিয়ে দেওয়া দরকার।","কথা বলার সময় সত্য বলা ভালোবাসার বাস্তব প্রকাশ।","প্রতিবেশীর সাথে ভালো আচরণ মুমিনের দায়িত্ব।","আল্লাহ ও রাসূলের ভালোবাসা কাজে প্রমাণ করতে হয়।"],"related_hadiths":[{"id":"33","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6016","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"46","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E152" s="4" t="n"/>
@@ -4093,7 +4097,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত, সত্য, চরিত্র ও বৈধ রুজি","description":"$book_name$ $hadith_number$ - $chapter_name$. চারটি গুণ—আমানত, সত্য কথা, সুন্দর চরিত্র ও বৈধ রুজি—নিয়ে নবীজির গভীর শিক্ষা জানুন।"},"heading":{"title":"চারটি গুণের হাদিস: আমানত, সত্যবাদিতা, সুন্দর চরিত্র ও বৈধ রুজি","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম চারটি জিনিসের কথা বলেছেন। এগুলো মানুষের জীবনে থাকলে দুনিয়ার অনেক কিছু হারালেও তার বড় ক্ষতি নেই—এমন শিক্ষা এসেছে। চারটি গুণ হলো আমানত রক্ষা করা, সত্য কথা বলা, সুন্দর চরিত্র রাখা এবং বৈধ রুজি গ্রহণ করা। এই চারটি বিষয় ব্যক্তিগত জীবন, পরিবার, ব্যবসা ও সমাজ—সব জায়গায় দরকার। আমানত মানুষকে বিশ্বাসযোগ্য করে, সত্য কথা তাকে পরিষ্কার রাখে, সুন্দর চরিত্র তাকে প্রিয় করে, আর বৈধ রুজি তার জীবনকে পবিত্র পথে রাখে। হাদিসটি খুব সহজ ভাষায় সফল মুসলিম জীবনের একটি নীতিমালা দেয়।"},"teachings":["আমানত রক্ষা মানুষকে বিশ্বাসযোগ্য করে।","সত্য কথা বলা মুমিনের বড় গুণ।","সুন্দর চরিত্র মানুষের সাথে সম্পর্ক ভালো রাখে।","বৈধ রুজি গ্রহণ করা জীবনের নিরাপদ পথ।"],"related_hadiths":[{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"52","book_id":"1","label":"Sahih Bukhari"},{"id":"2004","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত, সত্য, চরিত্র ও বৈধ রুজি","description":"$book_name$ $hadith_number$ - $chapter_name$. চারটি গুণ—আমানত, সত্য কথা, সুন্দর চরিত্র ও বৈধ রুজি—নিয়ে নবীজির গভীর শিক্ষা জানুন।"},"heading":{"title":"চারটি গুণের হাদিস: আমানত, সত্যবাদিতা, সুন্দর চরিত্র ও বৈধ রুজি","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম চারটি জিনিসের কথা বলেছেন। এগুলো মানুষের জীবনে থাকলে দুনিয়ার অনেক কিছু হারালেও তার বড় ক্ষতি নেই—এমন শিক্ষা এসেছে। চারটি গুণ হলো আমানত রক্ষা করা, সত্য কথা বলা, সুন্দর চরিত্র রাখা এবং বৈধ রুজি গ্রহণ করা। এই চারটি বিষয় ব্যক্তিগত জীবন, পরিবার, ব্যবসা ও সমাজ—সব জায়গায় দরকার। আমানত মানুষকে বিশ্বাসযোগ্য করে, সত্য কথা তাকে পরিষ্কার রাখে, সুন্দর চরিত্র তাকে প্রিয় করে, আর বৈধ রুজি তার জীবনকে পবিত্র পথে রাখে। হাদিসটি খুব সহজ ভাষায় সফল মুসলিম জীবনের একটি নীতিমালা দেয়।"},"teachings":["আমানত রক্ষা মানুষকে বিশ্বাসযোগ্য করে।","সত্য কথা বলা মুমিনের বড় গুণ।","সুন্দর চরিত্র মানুষের সাথে সম্পর্ক ভালো রাখে।","বৈধ রুজি গ্রহণ করা জীবনের নিরাপদ পথ।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2004","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E153" s="4" t="n"/>
@@ -4116,7 +4120,7 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহ ছাড়ুন, সত্যে শান্তি খুঁজুন","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহযুক্ত কথা ও কাজ ছেড়ে সত্যের শান্তি এবং মিথ্যার অশান্তি বুঝে চলার শিক্ষা নিন।"},"heading":{"title":"সত্যে প্রশান্তি, মিথ্যায় অশান্তি: সন্দেহ ছাড়ার হাদিস","description":"এই হাদিসে বলা হয়েছে, সন্দেহযুক্ত কথা ও কাজ ছেড়ে এমন দিকে ফিরে যেতে, যেখানে সন্দেহ নেই। এরপর বলা হয়েছে, সত্য প্রশান্তির নাম এবং মিথ্যা সন্দেহ ও অশান্তির নাম। এখানে সত্যবাদিতা শুধু মুখের কথা নয়; কাজের ক্ষেত্রেও সত্যের পথ বেছে নেওয়ার কথা আছে। যখন কোনো কথা, লেনদেন বা কাজ অন্তরে অস্বস্তি আনে, তখন তা নিয়ে থেমে ভাবা দরকার। মুমিনের জীবন এমন হওয়া উচিত, যেখানে কথা ও কাজে স্বচ্ছতা থাকে। মিথ্যা কিছু সময় সুবিধা দিলেও অন্তরে অস্থিরতা আনে। তাই এই হাদিস মানুষকে সহজ, সৎ ও শান্ত পথের দিকে ডাকছে।"},"teachings":["সন্দেহযুক্ত কথা ও কাজ ছেড়ে দেওয়া উচিত।","সত্য অন্তরে প্রশান্তি আনে।","মিথ্যা সন্দেহ ও অশান্তির কারণ হয়।","কথা ও কাজ—দুটোতেই সততা দরকার।"],"related_hadiths":[{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"2607","book_id":"2","label":"Sahih Muslim"},{"id":"52","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহ ছাড়ুন, সত্যে শান্তি খুঁজুন","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহযুক্ত কথা ও কাজ ছেড়ে সত্যের শান্তি এবং মিথ্যার অশান্তি বুঝে চলার শিক্ষা নিন।"},"heading":{"title":"সত্যে প্রশান্তি, মিথ্যায় অশান্তি: সন্দেহ ছাড়ার হাদিস","description":"এই হাদিসে বলা হয়েছে, সন্দেহযুক্ত কথা ও কাজ ছেড়ে এমন দিকে ফিরে যেতে, যেখানে সন্দেহ নেই। এরপর বলা হয়েছে, সত্য প্রশান্তির নাম এবং মিথ্যা সন্দেহ ও অশান্তির নাম। এখানে সত্যবাদিতা শুধু মুখের কথা নয়; কাজের ক্ষেত্রেও সত্যের পথ বেছে নেওয়ার কথা আছে। যখন কোনো কথা, লেনদেন বা কাজ অন্তরে অস্বস্তি আনে, তখন তা নিয়ে থেমে ভাবা দরকার। মুমিনের জীবন এমন হওয়া উচিত, যেখানে কথা ও কাজে স্বচ্ছতা থাকে। মিথ্যা কিছু সময় সুবিধা দিলেও অন্তরে অস্থিরতা আনে। তাই এই হাদিস মানুষকে সহজ, সৎ ও শান্ত পথের দিকে ডাকছে।"},"teachings":["সন্দেহযুক্ত কথা ও কাজ ছেড়ে দেওয়া উচিত।","সত্য অন্তরে প্রশান্তি আনে।","মিথ্যা সন্দেহ ও অশান্তির কারণ হয়।","কথা ও কাজ—দুটোতেই সততা দরকার।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2607","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E154" s="4" t="n"/>
@@ -4139,7 +4143,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হিংসামুক্ত অন্তর ও সত্য ভাষার মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. উত্তম মানুষের পরিচয়ে সত্য ভাষা, পরহেযগার অন্তর ও হিংসা থেকে মুক্ত থাকার শিক্ষা জানুন।"},"heading":{"title":"হিংসামুক্ত অন্তর ও সত্য ভাষা: উত্তম মানুষের পরিচয়","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লামকে জিজ্ঞেস করা হলো, সবচেয়ে ভাল মানুষ কে? উত্তরে তিনি বললেন, যে ব্যক্তি হিংসা-বিদ্বেষ মুক্ত অন্তরের অধিকারী এবং সত্য কথার অধিকারী। সাহাবীগণ সত্য ভাষা বুঝলেন, কিন্তু হিংসা-বিদ্বেষ মুক্ত অন্তরের ব্যাখ্যা জানতে চাইলেন। তখন তিনি বললেন, সে ব্যক্তি স্বচ্ছ ও পরহেযগার; যার মধ্যে পাপ, সীমালংঘন, খিয়ানত ও হিংসা নেই। এই হাদিস আমাদের বাহ্যিক ভালো কাজের পাশাপাশি অন্তরের পরিচ্ছন্নতার দিকে ডাকে। শুধু মুখে সত্য বললেই শেষ নয়; অন্তর থেকেও হিংসা, খিয়ানত ও অন্যায় দূর করার চেষ্টা করতে হয়।"},"teachings":["সত্য ভাষা উত্তম মানুষের গুণ।","হিংসা-বিদ্বেষ মুক্ত অন্তর মুমিনের বড় সৌন্দর্য।","খিয়ানত ও সীমালংঘন থেকে দূরে থাকা দরকার।","ভালো মানুষ হতে অন্তর ও ভাষা—দুটোই ঠিক রাখা জরুরি।"],"related_hadiths":[{"id":"4216","book_id":"6","label":"Sunan Ibn Majah"},{"id":"91","book_id":"2","label":"Sahih Muslim"},{"id":"6094","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হিংসামুক্ত অন্তর ও সত্য ভাষার মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. উত্তম মানুষের পরিচয়ে সত্য ভাষা, পরহেযগার অন্তর ও হিংসা থেকে মুক্ত থাকার শিক্ষা জানুন।"},"heading":{"title":"হিংসামুক্ত অন্তর ও সত্য ভাষা: উত্তম মানুষের পরিচয়","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লামকে জিজ্ঞেস করা হলো, সবচেয়ে ভাল মানুষ কে? উত্তরে তিনি বললেন, যে ব্যক্তি হিংসা-বিদ্বেষ মুক্ত অন্তরের অধিকারী এবং সত্য কথার অধিকারী। সাহাবীগণ সত্য ভাষা বুঝলেন, কিন্তু হিংসা-বিদ্বেষ মুক্ত অন্তরের ব্যাখ্যা জানতে চাইলেন। তখন তিনি বললেন, সে ব্যক্তি স্বচ্ছ ও পরহেযগার; যার মধ্যে পাপ, সীমালংঘন, খিয়ানত ও হিংসা নেই। এই হাদিস আমাদের বাহ্যিক ভালো কাজের পাশাপাশি অন্তরের পরিচ্ছন্নতার দিকে ডাকে। শুধু মুখে সত্য বললেই শেষ নয়; অন্তর থেকেও হিংসা, খিয়ানত ও অন্যায় দূর করার চেষ্টা করতে হয়।"},"teachings":["সত্য ভাষা উত্তম মানুষের গুণ।","হিংসা-বিদ্বেষ মুক্ত অন্তর মুমিনের বড় সৌন্দর্য।","খিয়ানত ও সীমালংঘন থেকে দূরে থাকা দরকার।","ভালো মানুষ হতে অন্তর ও ভাষা—দুটোই ঠিক রাখা জরুরি।"],"related_hadiths":[{"id":"4216","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"91","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E155" s="4" t="n"/>
@@ -4162,7 +4166,7 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সত্য নেকীর পথে, মিথ্যা পাপের পথে","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য গ্রহণ ও মিথ্যা থেকে বাঁচার মাধ্যমে নেকী ও পাপের পথ বুঝে চলার শিক্ষা জানুন।"},"heading":{"title":"সত্য নেকীর সাথে, মিথ্যা পাপের সাথে: নবীজির সরল শিক্ষা","description":"এই হাদিসে সত্য ও মিথ্যার পথ খুব পরিষ্কার করে বলা হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, সত্য গ্রহণ কর; কারণ সত্য নেকীর সাথে রয়েছে। আর মিথ্যা থেকে বেঁচে থাক; কারণ মিথ্যা পাপের সাথে রয়েছে। এখানে সত্যকে শুধু ভালো অভ্যাস বলা হয়নি; বরং তা নেকীর পথে নিয়ে যায় বলা হয়েছে। আবার মিথ্যাকে ছোট ভুল হিসেবে দেখা হয়নি; তা পাপের সাথে যুক্ত বলা হয়েছে। তাই একজন মুমিনের কথা, প্রতিশ্রুতি, লেনদেন ও সম্পর্ক—সব জায়গায় সত্য দরকার। মিথ্যা সাময়িক সুবিধা দিলেও মানুষকে খারাপ পথে টেনে নিতে পারে।"},"teachings":["সত্য নেকীর পথে নিয়ে যায়।","মিথ্যা পাপের সাথে যুক্ত।","কথা ও লেনদেনে সত্যবাদিতা রাখা জরুরি।","মিথ্যাকে ছোট ভুল ভেবে অবহেলা করা উচিত নয়।"],"related_hadiths":[{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"2607","book_id":"2","label":"Sahih Muslim"},{"id":"2518","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সত্য নেকীর পথে, মিথ্যা পাপের পথে","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য গ্রহণ ও মিথ্যা থেকে বাঁচার মাধ্যমে নেকী ও পাপের পথ বুঝে চলার শিক্ষা জানুন।"},"heading":{"title":"সত্য নেকীর সাথে, মিথ্যা পাপের সাথে: নবীজির সরল শিক্ষা","description":"এই হাদিসে সত্য ও মিথ্যার পথ খুব পরিষ্কার করে বলা হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, সত্য গ্রহণ কর; কারণ সত্য নেকীর সাথে রয়েছে। আর মিথ্যা থেকে বেঁচে থাক; কারণ মিথ্যা পাপের সাথে রয়েছে। এখানে সত্যকে শুধু ভালো অভ্যাস বলা হয়নি; বরং তা নেকীর পথে নিয়ে যায় বলা হয়েছে। আবার মিথ্যাকে ছোট ভুল হিসেবে দেখা হয়নি; তা পাপের সাথে যুক্ত বলা হয়েছে। তাই একজন মুমিনের কথা, প্রতিশ্রুতি, লেনদেন ও সম্পর্ক—সব জায়গায় সত্য দরকার। মিথ্যা সাময়িক সুবিধা দিলেও মানুষকে খারাপ পথে টেনে নিতে পারে।"},"teachings":["সত্য নেকীর পথে নিয়ে যায়।","মিথ্যা পাপের সাথে যুক্ত।","কথা ও লেনদেনে সত্যবাদিতা রাখা জরুরি।","মিথ্যাকে ছোট ভুল ভেবে অবহেলা করা উচিত নয়।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2607","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2518","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E156" s="4" t="n"/>
@@ -4185,7 +4189,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মিথ্যা ঈমানকে ক্ষতিগ্রস্ত করে","description":"$book_name$ $hadith_number$ - $chapter_name$. মিথ্যা থেকে বেঁচে থাকার গুরুত্ব এবং ঈমানের সাথে সত্যবাদিতার সম্পর্ক বুঝে নিন।"},"heading":{"title":"মিথ্যা থেকে বাঁচার হাদিস: ঈমানের জন্য সততার প্রয়োজন","description":"এই বর্ণনায় মিথ্যা থেকে বেঁচে থাকার কঠিন সতর্কতা এসেছে। বলা হয়েছে, মিথ্যা ঈমানকে ক্ষতিগ্রস্ত করে। কথাটি ছোট হলেও খুব গভীর। অনেক সময় মানুষ মিথ্যাকে হালকা ভাবে নেয়—মজা করে, সুবিধার জন্য, লজ্জা ঢাকতে বা সম্পর্ক বাঁচাতে। কিন্তু হাদিসের শিক্ষা হলো, মিথ্যা মানুষের ভেতরের ঈমানি শক্তিকে দুর্বল করে। সত্য বলা সব সময় সহজ না-ও হতে পারে, কিন্তু মিথ্যার পথে অভ্যাস তৈরি হলে তা চরিত্রকে নষ্ট করে। তাই মুমিনের জন্য সত্যবাদিতা শুধু সামাজিক ভালো গুণ নয়; এটি ঈমান রক্ষার সাথে জড়িত একটি বড় বিষয়।"},"teachings":["মিথ্যা ঈমানের ক্ষতির কারণ হতে পারে।","মিথ্যাকে ছোট বা হালকা বিষয় ভাবা উচিত নয়।","সত্যবাদিতা ঈমানি চরিত্রের অংশ।","সুবিধার জন্য মিথ্যা বলা থেকে বাঁচতে হবে।"],"related_hadiths":[{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"2607","book_id":"2","label":"Sahih Muslim"},{"id":"4990","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মিথ্যা ঈমানকে ক্ষতিগ্রস্ত করে","description":"$book_name$ $hadith_number$ - $chapter_name$. মিথ্যা থেকে বেঁচে থাকার গুরুত্ব এবং ঈমানের সাথে সত্যবাদিতার সম্পর্ক বুঝে নিন।"},"heading":{"title":"মিথ্যা থেকে বাঁচার হাদিস: ঈমানের জন্য সততার প্রয়োজন","description":"এই বর্ণনায় মিথ্যা থেকে বেঁচে থাকার কঠিন সতর্কতা এসেছে। বলা হয়েছে, মিথ্যা ঈমানকে ক্ষতিগ্রস্ত করে। কথাটি ছোট হলেও খুব গভীর। অনেক সময় মানুষ মিথ্যাকে হালকা ভাবে নেয়—মজা করে, সুবিধার জন্য, লজ্জা ঢাকতে বা সম্পর্ক বাঁচাতে। কিন্তু হাদিসের শিক্ষা হলো, মিথ্যা মানুষের ভেতরের ঈমানি শক্তিকে দুর্বল করে। সত্য বলা সব সময় সহজ না-ও হতে পারে, কিন্তু মিথ্যার পথে অভ্যাস তৈরি হলে তা চরিত্রকে নষ্ট করে। তাই মুমিনের জন্য সত্যবাদিতা শুধু সামাজিক ভালো গুণ নয়; এটি ঈমান রক্ষার সাথে জড়িত একটি বড় বিষয়।"},"teachings":["মিথ্যা ঈমানের ক্ষতির কারণ হতে পারে।","মিথ্যাকে ছোট বা হালকা বিষয় ভাবা উচিত নয়।","সত্যবাদিতা ঈমানি চরিত্রের অংশ।","সুবিধার জন্য মিথ্যা বলা থেকে বাঁচতে হবে।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2607","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"4990","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E157" s="4" t="n"/>
@@ -4208,7 +4212,7 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিশুকে মিথ্যা প্রতিশ্রুতি না দেওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুকে “আসো নাও” বলে কিছু না দিলে সেটিও মিথ্যা—এই নববী শিক্ষা জানুন।"},"heading":{"title":"শিশুকে মিথ্যা কথা নয়: ছোট প্রতিশ্রুতিতেও সত্যের শিক্ষা","description":"এই হাদিসে শিশুদের সাথে সত্যবাদিতার শিক্ষা এসেছে। কেউ যদি বাচ্চাকে বলে, “আসো নাও”, কিন্তু পরে তাকে কিছু না দেয়, তাহলে সেটিকে মিথ্যা বলা হয়েছে। এতে বোঝা যায়, শিশুর সাথে কথাবার্তাও দ্বীনের বাইরে নয়। অনেক সময় বড়রা শিশুকে শান্ত করার জন্য বা কাছে ডাকার জন্য এমন কথা বলে যা পরে রাখে না। হাদিসটি শেখায়, শিশুকে ছোট মনে করে তার সাথে মিথ্যা বলা ঠিক নয়। কারণ শিশু বড়দের কথায় বিশ্বাস করতে শেখে। যদি বড়রা কথা না রাখে, তাহলে শিশুর মনেও মিথ্যার স্বাভাবিক ধারণা তৈরি হতে পারে। তাই সন্তানের সামনে সত্য কথা ও কথা রাখার অভ্যাস জরুরি।"},"teachings":["শিশুকে মিথ্যা প্রতিশ্রুতি দেওয়া থেকে বাঁচতে হবে।","ছোট কথাতেও সত্যবাদিতা দরকার।","বড়দের আচরণ শিশুদের শেখার মাধ্যম।","কথা দিলে তা রাখার চেষ্টা করা উচিত।"],"related_hadiths":[{"id":"4991","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6094","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিশুকে মিথ্যা প্রতিশ্রুতি না দেওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুকে “আসো নাও” বলে কিছু না দিলে সেটিও মিথ্যা—এই নববী শিক্ষা জানুন।"},"heading":{"title":"শিশুকে মিথ্যা কথা নয়: ছোট প্রতিশ্রুতিতেও সত্যের শিক্ষা","description":"এই হাদিসে শিশুদের সাথে সত্যবাদিতার শিক্ষা এসেছে। কেউ যদি বাচ্চাকে বলে, “আসো নাও”, কিন্তু পরে তাকে কিছু না দেয়, তাহলে সেটিকে মিথ্যা বলা হয়েছে। এতে বোঝা যায়, শিশুর সাথে কথাবার্তাও দ্বীনের বাইরে নয়। অনেক সময় বড়রা শিশুকে শান্ত করার জন্য বা কাছে ডাকার জন্য এমন কথা বলে যা পরে রাখে না। হাদিসটি শেখায়, শিশুকে ছোট মনে করে তার সাথে মিথ্যা বলা ঠিক নয়। কারণ শিশু বড়দের কথায় বিশ্বাস করতে শেখে। যদি বড়রা কথা না রাখে, তাহলে শিশুর মনেও মিথ্যার স্বাভাবিক ধারণা তৈরি হতে পারে। তাই সন্তানের সামনে সত্য কথা ও কথা রাখার অভ্যাস জরুরি।"},"teachings":["শিশুকে মিথ্যা প্রতিশ্রুতি দেওয়া থেকে বাঁচতে হবে।","ছোট কথাতেও সত্যবাদিতা দরকার।","বড়দের আচরণ শিশুদের শেখার মাধ্যম।","কথা দিলে তা রাখার চেষ্টা করা উচিত।"],"related_hadiths":[{"id":"4991","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -4235,7 +4239,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্তানকে দেওয়া কথাও রাখতে হবে","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুকে কিছু দেওয়ার কথা বলে না দিলে মিথ্যা লেখা হয়—এই শিক্ষামূলক হাদিস পড়ুন।"},"heading":{"title":"সন্তানকে দেওয়া প্রতিশ্রুতি: খেজুরের ঘটনায় সত্যবাদিতার শিক্ষা","description":"এই হাদিসে একটি ঘরোয়া ঘটনা এসেছে। আবদুল্লাহ ইবনে আমির রাদিয়াল্লাহু আনহুকে তাঁর মা ডাকলেন এবং বললেন, আসো, তোমাকে কিছু দেব। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম তখন তাঁদের ঘরে ছিলেন। তিনি জিজ্ঞেস করলেন, তুমি তাকে কী দিতে চাও? মা বললেন, খেজুর দেব। তখন নবীজি জানালেন, যদি কিছু না দাও, তবে তা মিথ্যা হিসেবে লেখা হবে। এই হাদিস আমাদের শেখায়, সন্তানকে দেওয়া ছোট প্রতিশ্রুতিও হালকা নয়। মা-বাবা যদি কথা রাখে, শিশু সত্য ও আস্থার পরিবেশে বড় হয়। আর কথা না রাখলে শিশুর মনেও মিথ্যা সহজ হয়ে যেতে পারে।"},"teachings":["সন্তানকে দেওয়া কথাও গুরুত্বের সাথে রাখা দরকার।","শিশুকে ডাকার জন্য মিথ্যা বলা উচিত নয়।","ছোট প্রতিশ্রুতিও মিথ্যা বা সত্যের অংশ হতে পারে।","মা-বাবার সত্যবাদিতা সন্তানের চরিত্র গঠনে সাহায্য করে।"],"related_hadiths":[{"id":"4991","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"4990","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্তানকে দেওয়া কথাও রাখতে হবে","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুকে কিছু দেওয়ার কথা বলে না দিলে মিথ্যা লেখা হয়—এই শিক্ষামূলক হাদিস পড়ুন।"},"heading":{"title":"সন্তানকে দেওয়া প্রতিশ্রুতি: খেজুরের ঘটনায় সত্যবাদিতার শিক্ষা","description":"এই হাদিসে একটি ঘরোয়া ঘটনা এসেছে। আবদুল্লাহ ইবনে আমির রাদিয়াল্লাহু আনহুকে তাঁর মা ডাকলেন এবং বললেন, আসো, তোমাকে কিছু দেব। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম তখন তাঁদের ঘরে ছিলেন। তিনি জিজ্ঞেস করলেন, তুমি তাকে কী দিতে চাও? মা বললেন, খেজুর দেব। তখন নবীজি জানালেন, যদি কিছু না দাও, তবে তা মিথ্যা হিসেবে লেখা হবে। এই হাদিস আমাদের শেখায়, সন্তানকে দেওয়া ছোট প্রতিশ্রুতিও হালকা নয়। মা-বাবা যদি কথা রাখে, শিশু সত্য ও আস্থার পরিবেশে বড় হয়। আর কথা না রাখলে শিশুর মনেও মিথ্যা সহজ হয়ে যেতে পারে।"},"teachings":["সন্তানকে দেওয়া কথাও গুরুত্বের সাথে রাখা দরকার।","শিশুকে ডাকার জন্য মিথ্যা বলা উচিত নয়।","ছোট প্রতিশ্রুতিও মিথ্যা বা সত্যের অংশ হতে পারে।","মা-বাবার সত্যবাদিতা সন্তানের চরিত্র গঠনে সাহায্য করে।"],"related_hadiths":[{"id":"4991","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4990","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E159" s="4" t="n"/>
@@ -4258,7 +4262,7 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হাসানোর জন্য মিথ্যা বলার ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মানুষকে হাসানোর জন্য মিথ্যা বলা নিয়ে নবীজির কঠিন সতর্ক বাণী জানুন।"},"heading":{"title":"হাসানোর জন্য মিথ্যা বলা: মজার কথাতেও সত্যের গুরুত্ব","description":"এই হাদিসে সেই ব্যক্তির জন্য কঠিন সতর্কতা এসেছে, যে মানুষকে হাসানোর জন্য মিথ্যা কথা বলে। নবীজি বলেছেন, তার জন্য ধ্বংস, তার জন্য ধ্বংস। কথাটি আমাদের দৈনন্দিন জীবনের একটি সাধারণ ভুল ধরিয়ে দেয়। অনেক সময় আড্ডা, গল্প, বক্তৃতা বা অনলাইনে মানুষ হাসানোর জন্য বানানো কথা বলে। কেউ ভাবতে পারে, এটি তো শুধু মজা। কিন্তু হাদিস দেখাচ্ছে, মজার নামেও মিথ্যা হালকা নয়। সত্যবাদিতা শুধু গুরুতর আলোচনায় দরকার নয়; হাসি-ঠাট্টাতেও দরকার। মুমিনের কথা এমন হওয়া উচিত, যাতে মানুষ আনন্দ পেলেও মিথ্যা বা ধোঁকার ওপর দাঁড়িয়ে না থাকে।"},"teachings":["মানুষকে হাসানোর জন্য মিথ্যা বলা থেকে বাঁচতে হবে।","মজা করেও মিথ্যা বলা হালকা বিষয় নয়।","আড্ডা ও গল্পেও সত্যবাদিতা দরকার।","কথার মাধ্যমে মানুষকে আনন্দ দিতে হলে মিথ্যা ছাড়াই দেওয়া উচিত।"],"related_hadiths":[{"id":"4990","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"4800","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হাসানোর জন্য মিথ্যা বলার ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মানুষকে হাসানোর জন্য মিথ্যা বলা নিয়ে নবীজির কঠিন সতর্ক বাণী জানুন।"},"heading":{"title":"হাসানোর জন্য মিথ্যা বলা: মজার কথাতেও সত্যের গুরুত্ব","description":"এই হাদিসে সেই ব্যক্তির জন্য কঠিন সতর্কতা এসেছে, যে মানুষকে হাসানোর জন্য মিথ্যা কথা বলে। নবীজি বলেছেন, তার জন্য ধ্বংস, তার জন্য ধ্বংস। কথাটি আমাদের দৈনন্দিন জীবনের একটি সাধারণ ভুল ধরিয়ে দেয়। অনেক সময় আড্ডা, গল্প, বক্তৃতা বা অনলাইনে মানুষ হাসানোর জন্য বানানো কথা বলে। কেউ ভাবতে পারে, এটি তো শুধু মজা। কিন্তু হাদিস দেখাচ্ছে, মজার নামেও মিথ্যা হালকা নয়। সত্যবাদিতা শুধু গুরুতর আলোচনায় দরকার নয়; হাসি-ঠাট্টাতেও দরকার। মুমিনের কথা এমন হওয়া উচিত, যাতে মানুষ আনন্দ পেলেও মিথ্যা বা ধোঁকার ওপর দাঁড়িয়ে না থাকে।"},"teachings":["মানুষকে হাসানোর জন্য মিথ্যা বলা থেকে বাঁচতে হবে।","মজা করেও মিথ্যা বলা হালকা বিষয় নয়।","আড্ডা ও গল্পেও সত্যবাদিতা দরকার।","কথার মাধ্যমে মানুষকে আনন্দ দিতে হলে মিথ্যা ছাড়াই দেওয়া উচিত।"],"related_hadiths":[{"id":"4990","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4800","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E160" s="4" t="n"/>
@@ -4281,7 +4285,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর কঠিন পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. বৃদ্ধ ব্যভিচারী, মিথ্যুক শাসক ও অহংকারী গরীব সম্পর্কে কিয়ামতের কঠিন সতর্কতা জানুন।"},"heading":{"title":"মিথ্যুক শাসকসহ তিন শ্রেণীর মানুষের কঠিন সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের কথা এসেছে, যাদের ব্যাপারে কিয়ামতের দিন কঠিন সতর্কতা দেওয়া হয়েছে। তারা হলো বৃদ্ধ ব্যভিচারকারী, মিথ্যুক শাসক এবং অহংকারী গরীব। হাদিসে বলা হয়েছে, আল্লাহ তাদের সাথে কথা বলবেন না, তাদের পবিত্র করবেন না, দয়ার দৃষ্টিতে তাকাবেন না এবং তাদের জন্য কষ্টদায়ক শাস্তি রয়েছে। এখানে বিশেষভাবে মিথ্যুক শাসকের কথা আমাদের দায়িত্ব ও ক্ষমতার জায়গায় সত্যের গুরুত্ব বুঝায়। যার হাতে নেতৃত্ব বা ক্ষমতা আছে, তার মিথ্যা শুধু নিজের ক্ষতি করে না; অন্যদেরও ক্ষতিগ্রস্ত করতে পারে। আর অহংকার ও পাপ যেকোন অবস্থায় ভয়ংকর বিষয়।"},"teachings":["মিথ্যুক শাসকের বিষয়ে হাদিসে কঠিন সতর্কতা এসেছে।","ক্ষমতা থাকলে সত্যবাদিতা আরও বেশি জরুরি।","অহংকার ও পাপ মানুষকে কঠিন পরিণতির দিকে নিতে পারে।","বয়স, পদ বা দারিদ্র্য কোনো পাপকে হালকা করে না।"],"related_hadiths":[{"id":"107","book_id":"2","label":"Sahih Muslim"},{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"91","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর কঠিন পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. বৃদ্ধ ব্যভিচারী, মিথ্যুক শাসক ও অহংকারী গরীব সম্পর্কে কিয়ামতের কঠিন সতর্কতা জানুন।"},"heading":{"title":"মিথ্যুক শাসকসহ তিন শ্রেণীর মানুষের কঠিন সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের কথা এসেছে, যাদের ব্যাপারে কিয়ামতের দিন কঠিন সতর্কতা দেওয়া হয়েছে। তারা হলো বৃদ্ধ ব্যভিচারকারী, মিথ্যুক শাসক এবং অহংকারী গরীব। হাদিসে বলা হয়েছে, আল্লাহ তাদের সাথে কথা বলবেন না, তাদের পবিত্র করবেন না, দয়ার দৃষ্টিতে তাকাবেন না এবং তাদের জন্য কষ্টদায়ক শাস্তি রয়েছে। এখানে বিশেষভাবে মিথ্যুক শাসকের কথা আমাদের দায়িত্ব ও ক্ষমতার জায়গায় সত্যের গুরুত্ব বুঝায়। যার হাতে নেতৃত্ব বা ক্ষমতা আছে, তার মিথ্যা শুধু নিজের ক্ষতি করে না; অন্যদেরও ক্ষতিগ্রস্ত করতে পারে। আর অহংকার ও পাপ যেকোন অবস্থায় ভয়ংকর বিষয়।"},"teachings":["মিথ্যুক শাসকের বিষয়ে হাদিসে কঠিন সতর্কতা এসেছে।","ক্ষমতা থাকলে সত্যবাদিতা আরও বেশি জরুরি।","অহংকার ও পাপ মানুষকে কঠিন পরিণতির দিকে নিতে পারে।","বয়স, পদ বা দারিদ্র্য কোনো পাপকে হালকা করে না।"],"related_hadiths":[{"id":"107","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"91","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E161" s="4" t="n"/>
@@ -4304,7 +4308,7 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শেষ যামানার মিথ্যাবাদী দাজ্জালদের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শেষ যামানায় মিথ্যাবাদীরা নতুন কথা ছড়াবে; তাদের থেকে দূরে থেকে পথভ্রষ্টতা থেকে বাঁচতে বলা হয়েছে।"},"heading":{"title":"শেষ যামানার মিথ্যাবাদী দাজ্জাল থেকে বাঁচার সতর্কতা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) শেষ যামানার কিছু মিথ্যাবাদী দাজ্জালের কথা বলেছেন। তারা এমন সব কথা নিয়ে আসবে, যা মানুষ আগে শোনেনি এবং তাদের বাপ-দাদারাও শোনেনি। নবীজি স্পষ্টভাবে সাবধান করেছেন: তোমরা তাদের থেকে বেঁচে থাকো এবং তাদেরকে তোমাদের থেকে দূরে রাখো। কারণ তারা মানুষকে পথভ্রষ্ট করতে পারে এবং ফিতনায় ফেলতে পারে। এই হাদিসে মিথ্যা কথা, অদ্ভুত দাবি ও বিভ্রান্তির বিরুদ্ধে সতর্ক থাকার শিক্ষা আছে। নতুন কথা শুনলেই গ্রহণ করা ঠিক নয়। দ্বীনের বিষয়ে সত্য-মিথ্যা যাচাই, নিরাপদ থাকা এবং বিভ্রান্ত লোকদের প্রভাব থেকে দূরে থাকা খুব দরকার।"},"teachings":["শেষ যামানায় মিথ্যাবাদী লোকদের ব্যাপারে সতর্ক থাকতে হবে।","অচেনা ও ভিত্তিহীন কথা শুনে সহজে গ্রহণ করা উচিত নয়।","ভ্রান্ত কথা মানুষকে ফিতনায় ফেলতে পারে।","দ্বীনের বিষয়ে নিরাপদ থাকতে সত্য যাচাই করা দরকার।"],"related_hadiths":[{"id":"7","book_id":"2","label":"Sahih Muslim"},{"id":"154","book_id":"14","label":"Mishkat al-Masabih"},{"id":"4333","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শেষ যামানার মিথ্যাবাদী দাজ্জালদের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শেষ যামানায় মিথ্যাবাদীরা নতুন কথা ছড়াবে; তাদের থেকে দূরে থেকে পথভ্রষ্টতা থেকে বাঁচতে বলা হয়েছে।"},"heading":{"title":"শেষ যামানার মিথ্যাবাদী দাজ্জাল থেকে বাঁচার সতর্কতা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) শেষ যামানার কিছু মিথ্যাবাদী দাজ্জালের কথা বলেছেন। তারা এমন সব কথা নিয়ে আসবে, যা মানুষ আগে শোনেনি এবং তাদের বাপ-দাদারাও শোনেনি। নবীজি স্পষ্টভাবে সাবধান করেছেন: তোমরা তাদের থেকে বেঁচে থাকো এবং তাদেরকে তোমাদের থেকে দূরে রাখো। কারণ তারা মানুষকে পথভ্রষ্ট করতে পারে এবং ফিতনায় ফেলতে পারে। এই হাদিসে মিথ্যা কথা, অদ্ভুত দাবি ও বিভ্রান্তির বিরুদ্ধে সতর্ক থাকার শিক্ষা আছে। নতুন কথা শুনলেই গ্রহণ করা ঠিক নয়। দ্বীনের বিষয়ে সত্য-মিথ্যা যাচাই, নিরাপদ থাকা এবং বিভ্রান্ত লোকদের প্রভাব থেকে দূরে থাকা খুব দরকার।"},"teachings":["শেষ যামানায় মিথ্যাবাদী লোকদের ব্যাপারে সতর্ক থাকতে হবে।","অচেনা ও ভিত্তিহীন কথা শুনে সহজে গ্রহণ করা উচিত নয়।","ভ্রান্ত কথা মানুষকে ফিতনায় ফেলতে পারে।","দ্বীনের বিষয়ে নিরাপদ থাকতে সত্য যাচাই করা দরকার।"],"related_hadiths":[{"id":"7","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"154","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"4333","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E162" s="4" t="n"/>
@@ -4327,7 +4331,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দুই মুখের মানুষের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. দুনিয়ায় দ্বিমুখী আচরণকারীর কিয়ামতের ভয়াবহ পরিণতি সম্পর্কে হাদিসের শিক্ষা জানুন।"},"heading":{"title":"দ্বিমুখী চরিত্রের হাদিস: এক মুখে এক কথা, আরেক মুখে আরেক কথা নয়","description":"এই হাদিসে বলা হয়েছে, যার দুনিয়াতে দু’টি মুখ হবে, কিয়ামতের মাঠে তার মুখে আগুনের দু’টি জিহ্বা হবে। অর্থাৎ যে মানুষ একদলের সামনে এক কথা বলে, অন্য দলের সামনে উল্টো কথা বলে এবং মিথ্যা, চোগলখুরী বা পরনিন্দার মাধ্যমে সম্পর্ক নষ্ট করে—তার বিষয়ে কঠিন সতর্কতা এসেছে। দ্বিমুখী চরিত্র মানুষের আস্থা নষ্ট করে। এতে বন্ধু, পরিবার ও সমাজে ঝগড়া বাড়ে। মুমিনের কথা সোজা হওয়া উচিত। সে কারও সামনে এমন কথা বলবে না, যা অন্যের সামনে গিয়ে বদলে ফেলে। এই হাদিস আমাদের সত্যবাদী, পরিষ্কার এবং ভরসাযোগ্য হতে শেখায়।"},"teachings":["দ্বিমুখী আচরণের বিষয়ে হাদিসে কঠিন সতর্কতা এসেছে।","একজনের সামনে এক কথা, অন্যজনের সামনে আরেক কথা বলা ক্ষতিকর।","চোগলখুরী ও পরনিন্দা সম্পর্ক নষ্ট করে।","মুমিনের কথা পরিষ্কার ও বিশ্বাসযোগ্য হওয়া দরকার।"],"related_hadiths":[{"id":"4873","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6056","book_id":"1","label":"Sahih Bukhari"},{"id":"2606","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দুই মুখের মানুষের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. দুনিয়ায় দ্বিমুখী আচরণকারীর কিয়ামতের ভয়াবহ পরিণতি সম্পর্কে হাদিসের শিক্ষা জানুন।"},"heading":{"title":"দ্বিমুখী চরিত্রের হাদিস: এক মুখে এক কথা, আরেক মুখে আরেক কথা নয়","description":"এই হাদিসে বলা হয়েছে, যার দুনিয়াতে দু’টি মুখ হবে, কিয়ামতের মাঠে তার মুখে আগুনের দু’টি জিহ্বা হবে। অর্থাৎ যে মানুষ একদলের সামনে এক কথা বলে, অন্য দলের সামনে উল্টো কথা বলে এবং মিথ্যা, চোগলখুরী বা পরনিন্দার মাধ্যমে সম্পর্ক নষ্ট করে—তার বিষয়ে কঠিন সতর্কতা এসেছে। দ্বিমুখী চরিত্র মানুষের আস্থা নষ্ট করে। এতে বন্ধু, পরিবার ও সমাজে ঝগড়া বাড়ে। মুমিনের কথা সোজা হওয়া উচিত। সে কারও সামনে এমন কথা বলবে না, যা অন্যের সামনে গিয়ে বদলে ফেলে। এই হাদিস আমাদের সত্যবাদী, পরিষ্কার এবং ভরসাযোগ্য হতে শেখায়।"},"teachings":["দ্বিমুখী আচরণের বিষয়ে হাদিসে কঠিন সতর্কতা এসেছে।","একজনের সামনে এক কথা, অন্যজনের সামনে আরেক কথা বলা ক্ষতিকর।","চোগলখুরী ও পরনিন্দা সম্পর্ক নষ্ট করে।","মুমিনের কথা পরিষ্কার ও বিশ্বাসযোগ্য হওয়া দরকার।"],"related_hadiths":[{"id":"4873","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6056","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2606","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E163" s="4" t="n"/>
@@ -4350,7 +4354,7 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবীরা গুনাহ থেকে বাঁচার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, হত্যা ও মিথ্যা কসম বা সাক্ষ্যের ভয়াবহতা বুঝুন।"},"heading":{"title":"কবীরা গুনাহ: শিরক, অবাধ্যতা, হত্যা ও মিথ্যার ভয়াবহ শিক্ষা","description":"এই হাদিসে বড় বড় কবীরা গুনাহের কয়েকটি স্পষ্ট উদাহরণ বলা হয়েছে। মূল বিষয় হলো, মানুষের ঈমান, পরিবার, জীবন ও কথার সততা—সবকিছু আল্লাহর কাছে গুরুত্বপূর্ণ। আল্লাহর সাথে কাউকে শরীক করা সবচেয়ে বড় অন্যায় হিসেবে এসেছে। এরপর পিতা-মাতার অবাধ্যতা বলা হয়েছে, যা পরিবার ও দায়িত্ববোধের সাথে জড়িত। কাউকে হত্যা করা মানুষের জীবনের অধিকার নষ্ট করে। আর মিথ্যা কসম বা মিথ্যা সাক্ষ্য মানুষের বিশ্বাস, বিচার ও সম্পর্ককে ক্ষতিগ্রস্ত করে। তাই এই হাদিস আমাদের শেখায়, বড় গুনাহ থেকে দূরে থাকতে হলে ঈমানকে শুদ্ধ রাখা, বাবা-মায়ের হক মানা, মানুষের জীবনকে সম্মান করা এবং কথায় সত্যবাদী থাকা জরুরি।"},"teachings":["আল্লাহর সাথে কাউকে শরীক করা বড় কবীরা গুনাহের অন্তর্ভুক্ত।","পিতা-মাতার অবাধ্যতা থেকে সতর্ক থাকা দরকার।","অন্যায়ভাবে কাউকে হত্যা করা ভয়াবহ গুনাহ।","মিথ্যা কসম ও মিথ্যা সাক্ষ্য মানুষের হক নষ্ট করতে পারে।"],"related_hadiths":[{"id":"161","book_id":"2","label":"Sahih Muslim"},{"id":"162","book_id":"2","label":"Sahih Muslim"},{"id":"6871","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবীরা গুনাহ থেকে বাঁচার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, হত্যা ও মিথ্যা কসম বা সাক্ষ্যের ভয়াবহতা বুঝুন।"},"heading":{"title":"কবীরা গুনাহ: শিরক, অবাধ্যতা, হত্যা ও মিথ্যার ভয়াবহ শিক্ষা","description":"এই হাদিসে বড় বড় কবীরা গুনাহের কয়েকটি স্পষ্ট উদাহরণ বলা হয়েছে। মূল বিষয় হলো, মানুষের ঈমান, পরিবার, জীবন ও কথার সততা—সবকিছু আল্লাহর কাছে গুরুত্বপূর্ণ। আল্লাহর সাথে কাউকে শরীক করা সবচেয়ে বড় অন্যায় হিসেবে এসেছে। এরপর পিতা-মাতার অবাধ্যতা বলা হয়েছে, যা পরিবার ও দায়িত্ববোধের সাথে জড়িত। কাউকে হত্যা করা মানুষের জীবনের অধিকার নষ্ট করে। আর মিথ্যা কসম বা মিথ্যা সাক্ষ্য মানুষের বিশ্বাস, বিচার ও সম্পর্ককে ক্ষতিগ্রস্ত করে। তাই এই হাদিস আমাদের শেখায়, বড় গুনাহ থেকে দূরে থাকতে হলে ঈমানকে শুদ্ধ রাখা, বাবা-মায়ের হক মানা, মানুষের জীবনকে সম্মান করা এবং কথায় সত্যবাদী থাকা জরুরি।"},"teachings":["আল্লাহর সাথে কাউকে শরীক করা বড় কবীরা গুনাহের অন্তর্ভুক্ত।","পিতা-মাতার অবাধ্যতা থেকে সতর্ক থাকা দরকার।","অন্যায়ভাবে কাউকে হত্যা করা ভয়াবহ গুনাহ।","মিথ্যা কসম ও মিথ্যা সাক্ষ্য মানুষের হক নষ্ট করতে পারে।"],"related_hadiths":[{"id":"161","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"162","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6871","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E164" s="4" t="n"/>
@@ -4373,7 +4377,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিকের তিন আলামত","description":"$book_name$ $hadith_number$ - $chapter_name$. মিথ্যা বলা, ওয়াদা ভঙ্গ ও আমানতে খিয়ানত—মুনাফিকের তিন আলামত সম্পর্কে সহজ শিক্ষা।"},"heading":{"title":"মুনাফিকের আলামত: মিথ্যা, ওয়াদা ভঙ্গ ও আমানতে খিয়ানত","description":"এই হাদিসে মুনাফিকের আলামত তিনটি বলা হয়েছে। যখন সে কথা বলে, মিথ্যা বলে; ওয়াদা করলে তা ভঙ্গ করে; আর আমানত রাখা হলে খিয়ানত করে। এখানে ইসলাম মানুষের বাহ্যিক ইবাদতের পাশাপাশি চরিত্রকেও গুরুত্ব দিয়েছে। মুসলিমের পরিচয় শুধু সালাত বা সিয়ামের মধ্যে সীমিত নয়; কথার সত্যতা, প্রতিশ্রুতি রক্ষা এবং আমানতের দায়িত্বও তার জীবনের অংশ। মুসলিমের বর্ণনায় এসেছে, কেউ সালাত আদায় করলেও, সিয়াম পালন করলেও এবং নিজেকে মুসলিম মনে করলেও এই খারাপ গুণগুলো খুব বিপজ্জনক। তাই এই হাদিস আমাদের নিজের কথা, প্রতিশ্রুতি ও দায়িত্ব নিয়ে নিয়মিত ভাবতে শেখায়।"},"teachings":["মিথ্যা বলা মুনাফিকী স্বভাবের একটি বড় আলামত।","ওয়াদা করলে তা রক্ষা করা মুসলিম চরিত্রের অংশ।","অমানত রাখা হলে তা সঠিকভাবে ফিরিয়ে দেওয়া দরকার।","ইবাদতের পাশাপাশি চরিত্র ঠিক রাখা জরুরি।"],"related_hadiths":[{"id":"114","book_id":"2","label":"Sahih Muslim"},{"id":"116","book_id":"2","label":"Sahih Muslim"},{"id":"2631","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিকের তিন আলামত","description":"$book_name$ $hadith_number$ - $chapter_name$. মিথ্যা বলা, ওয়াদা ভঙ্গ ও আমানতে খিয়ানত—মুনাফিকের তিন আলামত সম্পর্কে সহজ শিক্ষা।"},"heading":{"title":"মুনাফিকের আলামত: মিথ্যা, ওয়াদা ভঙ্গ ও আমানতে খিয়ানত","description":"এই হাদিসে মুনাফিকের আলামত তিনটি বলা হয়েছে। যখন সে কথা বলে, মিথ্যা বলে; ওয়াদা করলে তা ভঙ্গ করে; আর আমানত রাখা হলে খিয়ানত করে। এখানে ইসলাম মানুষের বাহ্যিক ইবাদতের পাশাপাশি চরিত্রকেও গুরুত্ব দিয়েছে। মুসলিমের পরিচয় শুধু সালাত বা সিয়ামের মধ্যে সীমিত নয়; কথার সত্যতা, প্রতিশ্রুতি রক্ষা এবং আমানতের দায়িত্বও তার জীবনের অংশ। মুসলিমের বর্ণনায় এসেছে, কেউ সালাত আদায় করলেও, সিয়াম পালন করলেও এবং নিজেকে মুসলিম মনে করলেও এই খারাপ গুণগুলো খুব বিপজ্জনক। তাই এই হাদিস আমাদের নিজের কথা, প্রতিশ্রুতি ও দায়িত্ব নিয়ে নিয়মিত ভাবতে শেখায়।"},"teachings":["মিথ্যা বলা মুনাফিকী স্বভাবের একটি বড় আলামত।","ওয়াদা করলে তা রক্ষা করা মুসলিম চরিত্রের অংশ।","অমানত রাখা হলে তা সঠিকভাবে ফিরিয়ে দেওয়া দরকার।","ইবাদতের পাশাপাশি চরিত্র ঠিক রাখা জরুরি।"],"related_hadiths":[{"id":"114","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"116","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2631","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E165" s="4" t="n"/>
@@ -4396,7 +4400,7 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিকীর চার স্বভাব","description":"$book_name$ $hadith_number$ - $chapter_name$. খিয়ানত, মিথ্যা, ওয়াদা ভঙ্গ ও ঝগড়ায় অশ্লীলতা—মুনাফিকী স্বভাব থেকে বাঁচার শিক্ষা।"},"heading":{"title":"মুনাফিকীর চার স্বভাব: নিজের চরিত্র যাচাই করার হাদিস","description":"এই হাদিসে চারটি স্বভাবের কথা এসেছে, যা মানুষের চরিত্রকে খুব ক্ষতিগ্রস্ত করে। আমানত রাখা হলে খিয়ানত করা, কথা বললে মিথ্যা বলা, ওয়াদা করলে ভঙ্গ করা এবং ঝগড়ার সময় অশ্লীল ভাষা ব্যবহার করা—এগুলোকে মুনাফিকী স্বভাব বলা হয়েছে। হাদিসে আরও বলা হয়েছে, যার মধ্যে এসবের একটি থাকবে, সে তা না ছাড়লে তার মধ্যে মুনাফিকীর একটি স্বভাব থাকবে। এখানে মূল শিক্ষা হলো আত্মপরীক্ষা। আমরা অনেক সময় নিজেদের ভালো মনে করি, কিন্তু কথা, প্রতিশ্রুতি, আমানত ও রাগের সময় ভাষা—এসব জায়গায় ভুল করি। তাই এই হাদিস মানুষকে নিজের আচরণ ঠিক করতে নরম কিন্তু শক্ত সতর্কতা দেয়।"},"teachings":["আমানতে খিয়ানত করা মুনাফিকী স্বভাবের অন্তর্ভুক্ত।","মিথ্যা কথা মানুষের ঈমানী চরিত্রকে দুর্বল করে।","চুক্তি বা ওয়াদা ভঙ্গ করা গুরুতর খারাপ অভ্যাস।","ঝগড়ার সময় অশ্লীল ভাষা থেকে দূরে থাকা দরকার।"],"related_hadiths":[{"id":"34","book_id":"1","label":"Sahih Bukhari"},{"id":"113","book_id":"2","label":"Sahih Muslim"},{"id":"2632","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিকীর চার স্বভাব","description":"$book_name$ $hadith_number$ - $chapter_name$. খিয়ানত, মিথ্যা, ওয়াদা ভঙ্গ ও ঝগড়ায় অশ্লীলতা—মুনাফিকী স্বভাব থেকে বাঁচার শিক্ষা।"},"heading":{"title":"মুনাফিকীর চার স্বভাব: নিজের চরিত্র যাচাই করার হাদিস","description":"এই হাদিসে চারটি স্বভাবের কথা এসেছে, যা মানুষের চরিত্রকে খুব ক্ষতিগ্রস্ত করে। আমানত রাখা হলে খিয়ানত করা, কথা বললে মিথ্যা বলা, ওয়াদা করলে ভঙ্গ করা এবং ঝগড়ার সময় অশ্লীল ভাষা ব্যবহার করা—এগুলোকে মুনাফিকী স্বভাব বলা হয়েছে। হাদিসে আরও বলা হয়েছে, যার মধ্যে এসবের একটি থাকবে, সে তা না ছাড়লে তার মধ্যে মুনাফিকীর একটি স্বভাব থাকবে। এখানে মূল শিক্ষা হলো আত্মপরীক্ষা। আমরা অনেক সময় নিজেদের ভালো মনে করি, কিন্তু কথা, প্রতিশ্রুতি, আমানত ও রাগের সময় ভাষা—এসব জায়গায় ভুল করি। তাই এই হাদিস মানুষকে নিজের আচরণ ঠিক করতে নরম কিন্তু শক্ত সতর্কতা দেয়।"},"teachings":["আমানতে খিয়ানত করা মুনাফিকী স্বভাবের অন্তর্ভুক্ত।","মিথ্যা কথা মানুষের ঈমানী চরিত্রকে দুর্বল করে।","চুক্তি বা ওয়াদা ভঙ্গ করা গুরুতর খারাপ অভ্যাস।","ঝগড়ার সময় অশ্লীল ভাষা থেকে দূরে থাকা দরকার।"],"related_hadiths":[{"id":"34","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"113","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2632","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E166" s="4" t="n"/>
@@ -4419,7 +4423,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জিহ্বা সংযমের গুরুত্ব","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূল صلى الله عليه وسلم জিহ্বার দিকে ইঙ্গিত করে কথার বিপদ থেকে সতর্ক করেছেন—এ হাদিসের সহজ শিক্ষা।"},"heading":{"title":"জিহ্বা সংযম: কথার কারণে বিপদে পড়া থেকে বাঁচার শিক্ষা","description":"এই হাদিসে একজন সাহাবী রাসূলুল্লাহ صلى الله عليه وسلم-কে জিজ্ঞেস করেন, তাঁর জন্য সবচেয়ে বেশি ভয়ের বিষয় কী। রাসূল صلى الله عليه وسلم নিজের জিহ্বা ধরলেন এবং বললেন, এটি। হাদিসটি খুব ছোট, কিন্তু শিক্ষা গভীর। মানুষ অনেক সময় হাতে বা কাজে যত ভুল করে, কথার মাধ্যমেও তত বড় ক্ষতি করে বসে। মিথ্যা, কষ্টদায়ক কথা, অশ্লীল ভাষা, গীবত বা অন্যের ক্ষতি করা কথা—এসবের দরজা খুলে যায় জিহ্বা নিয়ন্ত্রণ না করলে। তবে এই হাদিসে শুধু জিহ্বার ভয় বলা হয়েছে; অতিরিক্ত বিস্তারিত বিধান এখানে নেই। মূল বার্তা হলো, কথা বলার আগে ভাবা, অপ্রয়োজনীয় কথা কমানো এবং নিজের ভাষাকে আল্লাহর ভয় দিয়ে নিয়ন্ত্রণ করা।"},"teachings":["জিহ্বা মানুষের জন্য বড় পরীক্ষার কারণ হতে পারে।","কথা বলার আগে চিন্তা করা নিরাপদ অভ্যাস।","ভাষা নিয়ন্ত্রণ করা মুসলিম চরিত্রের গুরুত্বপূর্ণ অংশ।","অপ্রয়োজনীয় ও ক্ষতিকর কথা থেকে দূরে থাকা দরকার।"],"related_hadiths":[{"id":"2410","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3972","book_id":"6","label":"Sunan Ibn Majah"},{"id":"6474","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জিহ্বা সংযমের গুরুত্ব","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূল صلى الله عليه وسلم জিহ্বার দিকে ইঙ্গিত করে কথার বিপদ থেকে সতর্ক করেছেন—এ হাদিসের সহজ শিক্ষা।"},"heading":{"title":"জিহ্বা সংযম: কথার কারণে বিপদে পড়া থেকে বাঁচার শিক্ষা","description":"এই হাদিসে একজন সাহাবী রাসূলুল্লাহ صلى الله عليه وسلم-কে জিজ্ঞেস করেন, তাঁর জন্য সবচেয়ে বেশি ভয়ের বিষয় কী। রাসূল صلى الله عليه وسلم নিজের জিহ্বা ধরলেন এবং বললেন, এটি। হাদিসটি খুব ছোট, কিন্তু শিক্ষা গভীর। মানুষ অনেক সময় হাতে বা কাজে যত ভুল করে, কথার মাধ্যমেও তত বড় ক্ষতি করে বসে। মিথ্যা, কষ্টদায়ক কথা, অশ্লীল ভাষা, গীবত বা অন্যের ক্ষতি করা কথা—এসবের দরজা খুলে যায় জিহ্বা নিয়ন্ত্রণ না করলে। তবে এই হাদিসে শুধু জিহ্বার ভয় বলা হয়েছে; অতিরিক্ত বিস্তারিত বিধান এখানে নেই। মূল বার্তা হলো, কথা বলার আগে ভাবা, অপ্রয়োজনীয় কথা কমানো এবং নিজের ভাষাকে আল্লাহর ভয় দিয়ে নিয়ন্ত্রণ করা।"},"teachings":["জিহ্বা মানুষের জন্য বড় পরীক্ষার কারণ হতে পারে।","কথা বলার আগে চিন্তা করা নিরাপদ অভ্যাস।","ভাষা নিয়ন্ত্রণ করা মুসলিম চরিত্রের গুরুত্বপূর্ণ অংশ।","অপ্রয়োজনীয় ও ক্ষতিকর কথা থেকে দূরে থাকা দরকার।"],"related_hadiths":[{"id":"2410","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3972","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"6474","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E167" s="4" t="n"/>
@@ -4442,7 +4446,7 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছয়টি অঙ্গীকার ও জান্নাতের আশা","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য কথা, ওয়াদা পূরণ, আমানত আদায়, লজ্জাস্থান, দৃষ্টি ও হাত হেফাজতের শিক্ষা।"},"heading":{"title":"ছয়টি অঙ্গীকার: সত্যবাদিতা, আমানত ও চরিত্র রক্ষার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم ছয়টি বিষয়ের জামানত চাইছেন। এগুলো হলো কথা বললে সত্য বলা, ওয়াদা করলে তা পূর্ণ করা, আমানত রাখা হলে তা আদায় করা, লজ্জাস্থান হেফাজত করা, দৃষ্টি নিচু রাখা এবং হাতকে অন্যায় কাজ থেকে বিরত রাখা। এখানে সততা, আমানতদারি ও শালীনতা একসাথে এসেছে। একজন মুসলিম শুধু মুখে ভালো কথা বললেই যথেষ্ট নয়; তার কথা, চুক্তি, দৃষ্টি, শরীর ও হাত—সবকিছুতে দায়িত্ববোধ থাকা দরকার। হাদিসে জান্নাতের যামিনের কথা এসেছে, তাই বিষয়গুলোকে হালকা করে দেখা উচিত নয়। তবে এর শিক্ষা হলো চেষ্টা, নিয়ন্ত্রণ এবং নিজের নফসকে ভালো পথে রাখা।"},"teachings":["কথা বললে সত্য বলা মুসলিম চরিত্রের ভিত্তি।","ওয়াদা ও আমানত রক্ষা করা বড় দায়িত্ব।","দৃষ্টি ও লজ্জাস্থান হেফাজত করা শালীনতার অংশ।","হাতকে অন্যায় কাজ থেকে বিরত রাখা দরকার।"],"related_hadiths":[{"id":"6474","book_id":"1","label":"Sahih Bukhari"},{"id":"6136","book_id":"1","label":"Sahih Bukhari"},{"id":"2410","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছয়টি অঙ্গীকার ও জান্নাতের আশা","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য কথা, ওয়াদা পূরণ, আমানত আদায়, লজ্জাস্থান, দৃষ্টি ও হাত হেফাজতের শিক্ষা।"},"heading":{"title":"ছয়টি অঙ্গীকার: সত্যবাদিতা, আমানত ও চরিত্র রক্ষার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم ছয়টি বিষয়ের জামানত চাইছেন। এগুলো হলো কথা বললে সত্য বলা, ওয়াদা করলে তা পূর্ণ করা, আমানত রাখা হলে তা আদায় করা, লজ্জাস্থান হেফাজত করা, দৃষ্টি নিচু রাখা এবং হাতকে অন্যায় কাজ থেকে বিরত রাখা। এখানে সততা, আমানতদারি ও শালীনতা একসাথে এসেছে। একজন মুসলিম শুধু মুখে ভালো কথা বললেই যথেষ্ট নয়; তার কথা, চুক্তি, দৃষ্টি, শরীর ও হাত—সবকিছুতে দায়িত্ববোধ থাকা দরকার। হাদিসে জান্নাতের যামিনের কথা এসেছে, তাই বিষয়গুলোকে হালকা করে দেখা উচিত নয়। তবে এর শিক্ষা হলো চেষ্টা, নিয়ন্ত্রণ এবং নিজের নফসকে ভালো পথে রাখা।"},"teachings":["কথা বললে সত্য বলা মুসলিম চরিত্রের ভিত্তি।","ওয়াদা ও আমানত রক্ষা করা বড় দায়িত্ব।","দৃষ্টি ও লজ্জাস্থান হেফাজত করা শালীনতার অংশ।","হাতকে অন্যায় কাজ থেকে বিরত রাখা দরকার।"],"related_hadiths":[{"id":"6474","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6136","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2410","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E168" s="4" t="n"/>
@@ -4465,7 +4469,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সত্যবাদিতার পথ ও মিথ্যার ক্ষতি","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য মানুষকে পুণ্যের পথে নেয়, আর মিথ্যা পাপের দিকে ঠেলে দেয়—এ হাদিসের শিক্ষা।"},"heading":{"title":"সত্যবাদিতা: জান্নাতের পথে চলার সুন্দর শিক্ষা","description":"এই হাদিসে সত্য ও মিথ্যার ফল খুব পরিষ্কারভাবে বলা হয়েছে। সত্য পুণ্যময় কাজ, আর পুণ্য জান্নাতের পথ দেখায়। যে ব্যক্তি সত্যের উপর দৃঢ় থাকে, তাকে আল্লাহর কাছে সত্যনিষ্ঠ হিসেবে লেখা হয়। অন্যদিকে মিথ্যা পাপকাজ, আর পাপ জাহান্নামের পথ দেখায়। যে মিথ্যায় অভ্যস্ত হয়ে পড়ে, তাকে আল্লাহর কাছে মিথ্যুক হিসেবে লেখা হয়। এখানে মূল শিক্ষা হলো অভ্যাসের প্রভাব। একবার সত্য বলা ভালো, কিন্তু নিয়মিত সত্য বলা মানুষকে সত্যনিষ্ঠ করে। একইভাবে মিথ্যাকে ছোট মনে করলে তা অভ্যাসে পরিণত হতে পারে। তাই দৈনন্দিন কথা, লেনদেন, পরিবার ও সমাজে সত্যবাদিতা ধরে রাখা ঈমানী চরিত্রের বড় অংশ।"},"teachings":["সত্য কথা পুণ্যের পথে নিয়ে যায়।","নিয়মিত সত্য বলার অভ্যাস মানুষকে সত্যনিষ্ঠ করে।","মিথ্যা পাপের দিকে নিয়ে যেতে পারে।","মিথ্যায় অভ্যস্ত হওয়া থেকে শুরুতেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"6094","book_id":"1","label":"Sahih Bukhari"},{"id":"2607","book_id":"2","label":"Sahih Muslim"},{"id":"1971","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সত্যবাদিতার পথ ও মিথ্যার ক্ষতি","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য মানুষকে পুণ্যের পথে নেয়, আর মিথ্যা পাপের দিকে ঠেলে দেয়—এ হাদিসের শিক্ষা।"},"heading":{"title":"সত্যবাদিতা: জান্নাতের পথে চলার সুন্দর শিক্ষা","description":"এই হাদিসে সত্য ও মিথ্যার ফল খুব পরিষ্কারভাবে বলা হয়েছে। সত্য পুণ্যময় কাজ, আর পুণ্য জান্নাতের পথ দেখায়। যে ব্যক্তি সত্যের উপর দৃঢ় থাকে, তাকে আল্লাহর কাছে সত্যনিষ্ঠ হিসেবে লেখা হয়। অন্যদিকে মিথ্যা পাপকাজ, আর পাপ জাহান্নামের পথ দেখায়। যে মিথ্যায় অভ্যস্ত হয়ে পড়ে, তাকে আল্লাহর কাছে মিথ্যুক হিসেবে লেখা হয়। এখানে মূল শিক্ষা হলো অভ্যাসের প্রভাব। একবার সত্য বলা ভালো, কিন্তু নিয়মিত সত্য বলা মানুষকে সত্যনিষ্ঠ করে। একইভাবে মিথ্যাকে ছোট মনে করলে তা অভ্যাসে পরিণত হতে পারে। তাই দৈনন্দিন কথা, লেনদেন, পরিবার ও সমাজে সত্যবাদিতা ধরে রাখা ঈমানী চরিত্রের বড় অংশ।"},"teachings":["সত্য কথা পুণ্যের পথে নিয়ে যায়।","নিয়মিত সত্য বলার অভ্যাস মানুষকে সত্যনিষ্ঠ করে।","মিথ্যা পাপের দিকে নিয়ে যেতে পারে।","মিথ্যায় অভ্যস্ত হওয়া থেকে শুরুতেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2607","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1971","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E169" s="4" t="n"/>
@@ -4488,7 +4492,7 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুখ ও লজ্জাস্থান হেফাজত","description":"$book_name$ $hadith_number$ - $chapter_name$. জিহ্বা ও লজ্জাস্থান হেফাজতের অঙ্গীকার জান্নাতের আশার বড় কারণ—হাদিসের শিক্ষা।"},"heading":{"title":"মুখ ও লজ্জাস্থান হেফাজত: জান্নাতের আশার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم দুইটি গুরুত্বপূর্ণ অঙ্গের দায়িত্ব নেওয়ার কথা বলেছেন। এক হলো দুই চোয়ালের মাঝের বস্তু, অর্থাৎ জিহ্বা; আর অন্যটি দুই পায়ের মাঝের বস্তু, অর্থাৎ লজ্জাস্থান। যে এগুলোর যিম্মাদার হবে, রাসূল صلى الله عليه وسلم তার জন্য জান্নাতের যিম্মাদার হওয়ার কথা বলেছেন। এখানে মানুষের চরিত্রের দুই বড় দরজা বোঝানো হয়েছে—কথা ও কামনা। জিহ্বা দিয়ে মিথ্যা, গালি, কষ্টদায়ক কথা বা অন্যায় কথা হতে পারে। লজ্জাস্থান নিয়ন্ত্রণ না করলে অবৈধ সম্পর্কের দিকে মানুষ ঝুঁকে যেতে পারে। তাই এই হাদিস মুসলিমকে নিজের ভাষা ও শালীনতা নিয়ে সতর্ক থাকতে শেখায়।"},"teachings":["জিহ্বা হেফাজত করা জান্নাতের আশার একটি বড় কারণ।","লজ্জাস্থান হেফাজত করা চরিত্র রক্ষার অংশ।","কথা ও কামনা—দুই ক্ষেত্রেই আত্মনিয়ন্ত্রণ দরকার।","নিজের অঙ্গের দায়িত্ব নেওয়া ঈমানী শৃঙ্খলার অংশ।"],"related_hadiths":[{"id":"6474","book_id":"1","label":"Sahih Bukhari"},{"id":"2410","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3972","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুখ ও লজ্জাস্থান হেফাজত","description":"$book_name$ $hadith_number$ - $chapter_name$. জিহ্বা ও লজ্জাস্থান হেফাজতের অঙ্গীকার জান্নাতের আশার বড় কারণ—হাদিসের শিক্ষা।"},"heading":{"title":"মুখ ও লজ্জাস্থান হেফাজত: জান্নাতের আশার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم দুইটি গুরুত্বপূর্ণ অঙ্গের দায়িত্ব নেওয়ার কথা বলেছেন। এক হলো দুই চোয়ালের মাঝের বস্তু, অর্থাৎ জিহ্বা; আর অন্যটি দুই পায়ের মাঝের বস্তু, অর্থাৎ লজ্জাস্থান। যে এগুলোর যিম্মাদার হবে, রাসূল صلى الله عليه وسلم তার জন্য জান্নাতের যিম্মাদার হওয়ার কথা বলেছেন। এখানে মানুষের চরিত্রের দুই বড় দরজা বোঝানো হয়েছে—কথা ও কামনা। জিহ্বা দিয়ে মিথ্যা, গালি, কষ্টদায়ক কথা বা অন্যায় কথা হতে পারে। লজ্জাস্থান নিয়ন্ত্রণ না করলে অবৈধ সম্পর্কের দিকে মানুষ ঝুঁকে যেতে পারে। তাই এই হাদিস মুসলিমকে নিজের ভাষা ও শালীনতা নিয়ে সতর্ক থাকতে শেখায়।"},"teachings":["জিহ্বা হেফাজত করা জান্নাতের আশার একটি বড় কারণ।","লজ্জাস্থান হেফাজত করা চরিত্র রক্ষার অংশ।","কথা ও কামনা—দুই ক্ষেত্রেই আত্মনিয়ন্ত্রণ দরকার।","নিজের অঙ্গের দায়িত্ব নেওয়া ঈমানী শৃঙ্খলার অংশ।"],"related_hadiths":[{"id":"6474","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2410","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3972","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E170" s="4" t="n"/>
@@ -4511,7 +4515,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রক্ষাকারী ও ধ্বংসকারী কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. তাকওয়া, হক কথা ও মধ্যম পথ রক্ষা করে; প্রবৃত্তি, কৃপণতা ও অহংকার ধ্বংসের কারণ।"},"heading":{"title":"রক্ষাকারী তিন কাজ ও ধ্বংসকারী তিন কাজ: তাকওয়ার হাদিস","description":"এই হাদিসে মানুষের জন্য তিনটি রক্ষাকারী কাজ এবং তিনটি ধ্বংসকারী কাজ বলা হয়েছে। রক্ষাকারী কাজ হলো প্রকাশ্যে ও গোপনে আল্লাহকে ভয় করা, সন্তুষ্টি ও অসন্তুষ্টি—উভয় অবস্থায় হক কথা বলা এবং সচ্ছলতা ও অসচ্ছলতায় মধ্যম পথ রাখা। অর্থাৎ ভালো চরিত্র শুধু মানুষের সামনে নয়, একান্ত অবস্থাতেও দরকার। আবার সত্য কথা শুধু সুবিধার সময়ে নয়, রাগ বা অসন্তুষ্টির সময়েও জরুরি। ধ্বংসকারী কাজ হলো প্রবৃত্তির অনুসরণ, কৃপণতাকে মেনে নেওয়া এবং নিজের প্রতি অহংকার করা। হাদিসে আত্ম-অহংকারকে সবচেয়ে কঠিন বলা হয়েছে। তাই এই শিক্ষা আমাদের ভারসাম্য, সত্য এবং বিনয়ী জীবনের দিকে ডাকে।"},"teachings":["প্রকাশ্যে ও গোপনে আল্লাহকে ভয় করা রক্ষাকারী কাজ।","সন্তুষ্টি ও অসন্তুষ্টি—দুই অবস্থাতেই হক কথা বলা দরকার।","সচ্ছলতা ও অসচ্ছলতায় মধ্যম পথ রাখা ভালো অভ্যাস।","প্রবৃত্তি, কৃপণতা ও অহংকার ধ্বংসের কারণ হতে পারে।"],"related_hadiths":[{"id":"168","book_id":"2","label":"Sahih Muslim"},{"id":"1987","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"7200","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রক্ষাকারী ও ধ্বংসকারী কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. তাকওয়া, হক কথা ও মধ্যম পথ রক্ষা করে; প্রবৃত্তি, কৃপণতা ও অহংকার ধ্বংসের কারণ।"},"heading":{"title":"রক্ষাকারী তিন কাজ ও ধ্বংসকারী তিন কাজ: তাকওয়ার হাদিস","description":"এই হাদিসে মানুষের জন্য তিনটি রক্ষাকারী কাজ এবং তিনটি ধ্বংসকারী কাজ বলা হয়েছে। রক্ষাকারী কাজ হলো প্রকাশ্যে ও গোপনে আল্লাহকে ভয় করা, সন্তুষ্টি ও অসন্তুষ্টি—উভয় অবস্থায় হক কথা বলা এবং সচ্ছলতা ও অসচ্ছলতায় মধ্যম পথ রাখা। অর্থাৎ ভালো চরিত্র শুধু মানুষের সামনে নয়, একান্ত অবস্থাতেও দরকার। আবার সত্য কথা শুধু সুবিধার সময়ে নয়, রাগ বা অসন্তুষ্টির সময়েও জরুরি। ধ্বংসকারী কাজ হলো প্রবৃত্তির অনুসরণ, কৃপণতাকে মেনে নেওয়া এবং নিজের প্রতি অহংকার করা। হাদিসে আত্ম-অহংকারকে সবচেয়ে কঠিন বলা হয়েছে। তাই এই শিক্ষা আমাদের ভারসাম্য, সত্য এবং বিনয়ী জীবনের দিকে ডাকে।"},"teachings":["প্রকাশ্যে ও গোপনে আল্লাহকে ভয় করা রক্ষাকারী কাজ।","সন্তুষ্টি ও অসন্তুষ্টি—দুই অবস্থাতেই হক কথা বলা দরকার।","সচ্ছলতা ও অসচ্ছলতায় মধ্যম পথ রাখা ভালো অভ্যাস।","প্রবৃত্তি, কৃপণতা ও অহংকার ধ্বংসের কারণ হতে পারে।"],"related_hadiths":[{"id":"168","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1987","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"7200","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E171" s="4" t="n"/>
@@ -4534,7 +4538,7 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে মুমিনের গুনাহ ঢেকে মাফ","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতের দিন মুমিনের গুনাহ স্বীকারের পর আল্লাহ দুনিয়ায় ঢেকে রাখা গুনাহ মাফ করে দেবেন।"},"heading":{"title":"কিয়ামতের দিন মুমিনের গুনাহ ঢেকে মাফ করার হাদিস","description":"এই হাদিসে কিয়ামতের দিনের একটি গভীর দৃশ্য এসেছে। আল্লাহ মুমিন বান্দাকে নিজের নিকটবর্তী করবেন, তাকে ঢেকে রাখবেন এবং একে একে তার গুনাহ সম্পর্কে জিজ্ঞেস করবেন। বান্দা স্বীকার করবে যে সে গুনাহগুলো জানে। তখন সে মনে করবে, এসব কারণে সে ধ্বংস হয়ে যাবে। কিন্তু আল্লাহ বলবেন, দুনিয়াতে আমি তোমার এই গুনাহগুলো ঢেকে রেখেছিলাম, আজ আমি তা মাফ করে দিচ্ছি। তারপর তাকে নেকীর আমলনামা দেওয়া হবে। আর কাফের ও মুনাফিকদের ব্যাপারে সবার সামনে ঘোষণা হবে যে তারা রবের বিরুদ্ধে মিথ্যা বলত। এই হাদিস আল্লাহর ক্ষমা, গুনাহ ঢেকে রাখা এবং কিয়ামতের হিসাবের কথা মনে করায়।"},"teachings":["মুমিন বান্দা কিয়ামতে নিজের গুনাহ স্বীকার করবে।","আল্লাহ দুনিয়ায় গুনাহ ঢেকে রেখেছেন—এটি বড় দয়া।","ক্ষমা আল্লাহর পক্ষ থেকে আসে, তাই তাঁর দিকে ফিরতে হয়।","মিথ্যাচার ও মুনাফিকী কিয়ামতে প্রকাশ পাবে।"],"related_hadiths":[{"id":"2441","book_id":"1","label":"Sahih Bukhari"},{"id":"2768","book_id":"2","label":"Sahih Muslim"},{"id":"5551","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে মুমিনের গুনাহ ঢেকে মাফ","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতের দিন মুমিনের গুনাহ স্বীকারের পর আল্লাহ দুনিয়ায় ঢেকে রাখা গুনাহ মাফ করে দেবেন।"},"heading":{"title":"কিয়ামতের দিন মুমিনের গুনাহ ঢেকে মাফ করার হাদিস","description":"এই হাদিসে কিয়ামতের দিনের একটি গভীর দৃশ্য এসেছে। আল্লাহ মুমিন বান্দাকে নিজের নিকটবর্তী করবেন, তাকে ঢেকে রাখবেন এবং একে একে তার গুনাহ সম্পর্কে জিজ্ঞেস করবেন। বান্দা স্বীকার করবে যে সে গুনাহগুলো জানে। তখন সে মনে করবে, এসব কারণে সে ধ্বংস হয়ে যাবে। কিন্তু আল্লাহ বলবেন, দুনিয়াতে আমি তোমার এই গুনাহগুলো ঢেকে রেখেছিলাম, আজ আমি তা মাফ করে দিচ্ছি। তারপর তাকে নেকীর আমলনামা দেওয়া হবে। আর কাফের ও মুনাফিকদের ব্যাপারে সবার সামনে ঘোষণা হবে যে তারা রবের বিরুদ্ধে মিথ্যা বলত। এই হাদিস আল্লাহর ক্ষমা, গুনাহ ঢেকে রাখা এবং কিয়ামতের হিসাবের কথা মনে করায়।"},"teachings":["মুমিন বান্দা কিয়ামতে নিজের গুনাহ স্বীকার করবে।","আল্লাহ দুনিয়ায় গুনাহ ঢেকে রেখেছেন—এটি বড় দয়া।","ক্ষমা আল্লাহর পক্ষ থেকে আসে, তাই তাঁর দিকে ফিরতে হয়।","মিথ্যাচার ও মুনাফিকী কিয়ামতে প্রকাশ পাবে।"],"related_hadiths":[{"id":"2441","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2768","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"5551","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E172" s="4" t="n"/>
@@ -4557,7 +4561,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সব নেশাদার দ্রব্য মদ","description":"$book_name$ $hadith_number$ - $chapter_name$. সব নেশাদার দ্রব্য মদ এবং সব মদ হারাম—তওবা ছাড়া আসক্তির ভয়াবহ সতর্কতা।"},"heading":{"title":"সব নেশাদার দ্রব্য মদ: খামর হারামের স্পষ্ট হাদিস","description":"এই হাদিসে খুব স্পষ্টভাবে বলা হয়েছে, সব নেশাদার দ্রব্য মদ এবং সব ধরনের মদ হারাম। অর্থাৎ শুধু নির্দিষ্ট কোনো পানীয় নয়, যে বস্তু নেশা তৈরি করে তা এই সতর্কতার মধ্যে পড়ে। হাদিসে আরও বলা হয়েছে, যে ব্যক্তি দুনিয়ায় মদ পান করে এবং তওবা ছাড়া আসক্ত অবস্থায় মারা যায়, সে পরকালে সুস্বাদু পানীয় পান করতে পাবে না। এখানে মূল শিক্ষা হলো নেশা থেকে দূরে থাকা এবং ভুল হলে তওবার দিকে ফিরে আসা। হাদিসে আসক্তির কথা এসেছে, তাই নিয়মিত নেশাকে সাধারণ অভ্যাস মনে করা বিপজ্জনক। একজন মুসলিমের জন্য বিবেক, ইবাদত ও চরিত্র রক্ষায় নেশাদার দ্রব্য থেকে বাঁচা প্রয়োজন।"},"teachings":["সব নেশাদার দ্রব্যকে মদের অন্তর্ভুক্ত বলা হয়েছে।","সব ধরনের মদ হারাম—এ শিক্ষা স্পষ্ট।","আসক্ত অবস্থায় তওবা ছাড়া মৃত্যু ভয়াবহ সতর্কতার বিষয়।","ভুল হলে তওবার দিকে দ্রুত ফিরে আসা দরকার।"],"related_hadiths":[{"id":"5112","book_id":"2","label":"Sahih Muslim"},{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3450","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সব নেশাদার দ্রব্য মদ","description":"$book_name$ $hadith_number$ - $chapter_name$. সব নেশাদার দ্রব্য মদ এবং সব মদ হারাম—তওবা ছাড়া আসক্তির ভয়াবহ সতর্কতা।"},"heading":{"title":"সব নেশাদার দ্রব্য মদ: খামর হারামের স্পষ্ট হাদিস","description":"এই হাদিসে খুব স্পষ্টভাবে বলা হয়েছে, সব নেশাদার দ্রব্য মদ এবং সব ধরনের মদ হারাম। অর্থাৎ শুধু নির্দিষ্ট কোনো পানীয় নয়, যে বস্তু নেশা তৈরি করে তা এই সতর্কতার মধ্যে পড়ে। হাদিসে আরও বলা হয়েছে, যে ব্যক্তি দুনিয়ায় মদ পান করে এবং তওবা ছাড়া আসক্ত অবস্থায় মারা যায়, সে পরকালে সুস্বাদু পানীয় পান করতে পাবে না। এখানে মূল শিক্ষা হলো নেশা থেকে দূরে থাকা এবং ভুল হলে তওবার দিকে ফিরে আসা। হাদিসে আসক্তির কথা এসেছে, তাই নিয়মিত নেশাকে সাধারণ অভ্যাস মনে করা বিপজ্জনক। একজন মুসলিমের জন্য বিবেক, ইবাদত ও চরিত্র রক্ষায় নেশাদার দ্রব্য থেকে বাঁচা প্রয়োজন।"},"teachings":["সব নেশাদার দ্রব্যকে মদের অন্তর্ভুক্ত বলা হয়েছে।","সব ধরনের মদ হারাম—এ শিক্ষা স্পষ্ট।","আসক্ত অবস্থায় তওবা ছাড়া মৃত্যু ভয়াবহ সতর্কতার বিষয়।","ভুল হলে তওবার দিকে দ্রুত ফিরে আসা দরকার।"],"related_hadiths":[{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3450","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E173" s="4" t="n"/>
@@ -4580,7 +4584,7 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ত্বিনাতে খাবালের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নেশাদার দ্রব্য পানকারীর জন্য ত্বিনাতে খাবাল—জাহান্নামীদের রক্ত-পুঁজের কঠিন সতর্কতা।"},"heading":{"title":"ত্বিনাতে খাবাল: নেশাদার দ্রব্য পানকারীর কঠিন সতর্কতা","description":"এই হাদিসে নেশাদার দ্রব্য পানকারীদের জন্য খুব কঠিন সতর্কতা এসেছে। রাসূলুল্লাহ صلى الله عليه وسلم বলেছেন, আল্লাহর ওয়াদা রয়েছে যে নেশাদার দ্রব্য পানকারীকে তিনি ত্বিনাতে খাবাল পান করাবেন। সাহাবীগণ জিজ্ঞেস করলে রাসূল صلى الله عليه وسلم ব্যাখ্যা করেন, এটি জাহান্নামীদের শরীর থেকে গলে পড়া রক্ত-পুঁজ মিশ্রিত অত্যন্ত গরম তরল পদার্থ। হাদিসের ভাষা ভয় জাগায়, কারণ নেশা মানুষের বিবেক, ইবাদত ও চরিত্রকে ক্ষতি করতে পারে। এখানে অতিরিক্ত কোনো গল্প যোগ করার দরকার নেই; মূল শিক্ষা যথেষ্ট পরিষ্কার। মদ ও মাদক থেকে দূরে থাকা, আসক্তি হলে তওবা করা এবং সাহায্য নিয়ে ফিরে আসা—এটাই একজন মুসলিমের নিরাপদ পথ।"},"teachings":["নেশাদার দ্রব্য পানকারীর জন্য কঠিন সতর্কতা এসেছে।","ত্বিনাতে খাবালকে জাহান্নামীদের রক্ত-পুঁজের তরল বলা হয়েছে।","নেশাকে সাধারণ ভুল মনে করে হালকা করা উচিত নয়।","ভুল হলে তওবা ও নেশা ছাড়ার চেষ্টা জরুরি।"],"related_hadiths":[{"id":"5112","book_id":"2","label":"Sahih Muslim"},{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3377","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ত্বিনাতে খাবালের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নেশাদার দ্রব্য পানকারীর জন্য ত্বিনাতে খাবাল—জাহান্নামীদের রক্ত-পুঁজের কঠিন সতর্কতা।"},"heading":{"title":"ত্বিনাতে খাবাল: নেশাদার দ্রব্য পানকারীর কঠিন সতর্কতা","description":"এই হাদিসে নেশাদার দ্রব্য পানকারীদের জন্য খুব কঠিন সতর্কতা এসেছে। রাসূলুল্লাহ صلى الله عليه وسلم বলেছেন, আল্লাহর ওয়াদা রয়েছে যে নেশাদার দ্রব্য পানকারীকে তিনি ত্বিনাতে খাবাল পান করাবেন। সাহাবীগণ জিজ্ঞেস করলে রাসূল صلى الله عليه وسلم ব্যাখ্যা করেন, এটি জাহান্নামীদের শরীর থেকে গলে পড়া রক্ত-পুঁজ মিশ্রিত অত্যন্ত গরম তরল পদার্থ। হাদিসের ভাষা ভয় জাগায়, কারণ নেশা মানুষের বিবেক, ইবাদত ও চরিত্রকে ক্ষতি করতে পারে। এখানে অতিরিক্ত কোনো গল্প যোগ করার দরকার নেই; মূল শিক্ষা যথেষ্ট পরিষ্কার। মদ ও মাদক থেকে দূরে থাকা, আসক্তি হলে তওবা করা এবং সাহায্য নিয়ে ফিরে আসা—এটাই একজন মুসলিমের নিরাপদ পথ।"},"teachings":["নেশাদার দ্রব্য পানকারীর জন্য কঠিন সতর্কতা এসেছে।","ত্বিনাতে খাবালকে জাহান্নামীদের রক্ত-পুঁজের তরল বলা হয়েছে।","নেশাকে সাধারণ ভুল মনে করে হালকা করা উচিত নয়।","ভুল হলে তওবা ও নেশা ছাড়ার চেষ্টা জরুরি।"],"related_hadiths":[{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3377","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E174" s="4" t="n"/>
@@ -4603,7 +4607,7 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদাসক্তির ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নিয়মিত নেশাদার দ্রব্য পানকারীকে মূর্তিপূজকের মতো গুরুতর অপরাধী বলা হয়েছে।"},"heading":{"title":"মদাসক্তি: নিয়মিত নেশা করার ভয়াবহ সতর্কতা","description":"এই হাদিসে নিয়মিত নেশাদার দ্রব্য পানকারীকে মূর্তিপূজকের ন্যায় অপরাধী বলা হয়েছে। এখানে মূল শিক্ষা হলো মদাসক্তি বা নেশার অভ্যাসকে খুব গুরুতরভাবে দেখা। হাদিসে একবার ভুল করা ও নিয়মিত আসক্তির মধ্যে ভাষাগতভাবে পার্থক্য আছে, কারণ ‘সর্বদা পানকারী’ শব্দটি অভ্যাস ও আসক্তির দিকে ইঙ্গিত করে। তবে কোনো মানুষকে ব্যক্তিগতভাবে বিচার করার চেয়ে নিজের অবস্থার দিকে তাকানো বেশি দরকার। মদ বা নেশা মানুষকে আল্লাহর আনুগত্য থেকে দূরে নিতে পারে এবং চরিত্র নষ্ট করতে পারে। তাই যে কেউ এই অভ্যাসে জড়িয়ে পড়লে তাকে তওবা, দোয়া ও বাস্তব পদক্ষেপের মাধ্যমে ফিরে আসার চেষ্টা করা উচিত।"},"teachings":["নিয়মিত নেশা করা গুরুতর অপরাধ হিসেবে এসেছে।","নেশার অভ্যাসকে হালকা করে দেখা ঠিক নয়।","মদাসক্তি আল্লাহর আনুগত্য থেকে দূরে নিতে পারে।","তওবা ও নেশা ছাড়ার চেষ্টা জরুরি।"],"related_hadiths":[{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3377","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5112","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদাসক্তির ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নিয়মিত নেশাদার দ্রব্য পানকারীকে মূর্তিপূজকের মতো গুরুতর অপরাধী বলা হয়েছে।"},"heading":{"title":"মদাসক্তি: নিয়মিত নেশা করার ভয়াবহ সতর্কতা","description":"এই হাদিসে নিয়মিত নেশাদার দ্রব্য পানকারীকে মূর্তিপূজকের ন্যায় অপরাধী বলা হয়েছে। এখানে মূল শিক্ষা হলো মদাসক্তি বা নেশার অভ্যাসকে খুব গুরুতরভাবে দেখা। হাদিসে একবার ভুল করা ও নিয়মিত আসক্তির মধ্যে ভাষাগতভাবে পার্থক্য আছে, কারণ ‘সর্বদা পানকারী’ শব্দটি অভ্যাস ও আসক্তির দিকে ইঙ্গিত করে। তবে কোনো মানুষকে ব্যক্তিগতভাবে বিচার করার চেয়ে নিজের অবস্থার দিকে তাকানো বেশি দরকার। মদ বা নেশা মানুষকে আল্লাহর আনুগত্য থেকে দূরে নিতে পারে এবং চরিত্র নষ্ট করতে পারে। তাই যে কেউ এই অভ্যাসে জড়িয়ে পড়লে তাকে তওবা, দোয়া ও বাস্তব পদক্ষেপের মাধ্যমে ফিরে আসার চেষ্টা করা উচিত।"},"teachings":["নিয়মিত নেশা করা গুরুতর অপরাধ হিসেবে এসেছে।","নেশার অভ্যাসকে হালকা করে দেখা ঠিক নয়।","মদাসক্তি আল্লাহর আনুগত্য থেকে দূরে নিতে পারে।","তওবা ও নেশা ছাড়ার চেষ্টা জরুরি।"],"related_hadiths":[{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3377","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E175" s="4" t="n"/>
@@ -4626,7 +4630,7 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপানকারীর জান্নাত সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সর্বদা নেশাদার দ্রব্য পানকারীর জন্য জান্নাত বিষয়ে কঠিন সতর্কতা—নিজেকে সংশোধনের ডাক।"},"heading":{"title":"সর্বদা নেশাদার দ্রব্য পানকারী: জান্নাত বিষয়ে কঠিন সতর্কতা","description":"এই হাদিসে বলা হয়েছে, সর্বদা নেশাদার দ্রব্য পানকারী জান্নাতে যাবে না। হাদিসের ভাষা খুব কঠিন, তাই একে হালকা করে দেখা উচিত নয়। এখানে মূল বিষয় হলো মদাসক্তি ও নিয়মিত নেশা। নেশা মানুষের বিবেক ঢেকে দেয়, আমল দুর্বল করে এবং অনেক অন্যায়ের দরজা খুলে দিতে পারে। তবে হাদিস থেকে অতিরিক্ত সিদ্ধান্ত বানানো ঠিক নয়; যে কথা এসেছে, সেটুকুই মানতে হবে। মুসলিমের কাজ হলো ভয় পাওয়া, নিজেকে ফিরিয়ে আনা এবং তওবার পথ ধরা। যদি কারও জীবনে এই অভ্যাস থাকে, তাহলে গোপনে বা প্রকাশ্যে আল্লাহর কাছে ক্ষমা চেয়ে নেশা ছাড়ার বাস্তব চেষ্টা করা জরুরি।"},"teachings":["নিয়মিত নেশাদার দ্রব্য পানকারীর জন্য কঠিন সতর্কতা এসেছে।","নেশাকে সাধারণ সামাজিক অভ্যাস মনে করা ভুল।","নেশা ছাড়ার জন্য তওবা ও চেষ্টা দরকার।","হাদিসের ভাষা যতটুকু, ব্যাখ্যাও ততটুকুতে রাখা উচিত।"],"related_hadiths":[{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"5112","book_id":"2","label":"Sahih Muslim"},{"id":"3377","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপানকারীর জান্নাত সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সর্বদা নেশাদার দ্রব্য পানকারীর জন্য জান্নাত বিষয়ে কঠিন সতর্কতা—নিজেকে সংশোধনের ডাক।"},"heading":{"title":"সর্বদা নেশাদার দ্রব্য পানকারী: জান্নাত বিষয়ে কঠিন সতর্কতা","description":"এই হাদিসে বলা হয়েছে, সর্বদা নেশাদার দ্রব্য পানকারী জান্নাতে যাবে না। হাদিসের ভাষা খুব কঠিন, তাই একে হালকা করে দেখা উচিত নয়। এখানে মূল বিষয় হলো মদাসক্তি ও নিয়মিত নেশা। নেশা মানুষের বিবেক ঢেকে দেয়, আমল দুর্বল করে এবং অনেক অন্যায়ের দরজা খুলে দিতে পারে। তবে হাদিস থেকে অতিরিক্ত সিদ্ধান্ত বানানো ঠিক নয়; যে কথা এসেছে, সেটুকুই মানতে হবে। মুসলিমের কাজ হলো ভয় পাওয়া, নিজেকে ফিরিয়ে আনা এবং তওবার পথ ধরা। যদি কারও জীবনে এই অভ্যাস থাকে, তাহলে গোপনে বা প্রকাশ্যে আল্লাহর কাছে ক্ষমা চেয়ে নেশা ছাড়ার বাস্তব চেষ্টা করা জরুরি।"},"teachings":["নিয়মিত নেশাদার দ্রব্য পানকারীর জন্য কঠিন সতর্কতা এসেছে।","নেশাকে সাধারণ সামাজিক অভ্যাস মনে করা ভুল।","নেশা ছাড়ার জন্য তওবা ও চেষ্টা দরকার।","হাদিসের ভাষা যতটুকু, ব্যাখ্যাও ততটুকুতে রাখা উচিত।"],"related_hadiths":[{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"3377","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E176" s="4" t="n"/>
@@ -4649,7 +4653,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অবাধ্যতা, জুয়া, খোঁটা ও মদাসক্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. পিতা-মাতার অবাধ্যতা, জুয়া-লটারী, খোঁটা দেওয়া ও মদাসক্তির কঠিন সতর্কতা।"},"heading":{"title":"অবাধ্য সন্তান, জুয়া, খোঁটা ও মদপান: চারটি গুরুতর সতর্কতা","description":"এই হাদিসে চার শ্রেণীর মানুষের ব্যাপারে জান্নাত বিষয়ে কঠিন সতর্কতা এসেছে। তারা হলো পিতা-মাতার অবাধ্য সন্তান, জুয়া ও লটারীতে অংশগ্রহণকারী, খোঁটাদানকারী এবং সর্বদা মদপানকারী। এখানে একসাথে কয়েকটি সামাজিক ও ব্যক্তিগত অপরাধ এসেছে। পিতা-মাতার অবাধ্যতা পরিবারকে আঘাত করে। জুয়া ও লটারী মানুষের সম্পদ ও মনকে অন্য পথে নেয়। খোঁটা দেওয়া দান বা উপকারের সৌন্দর্য নষ্ট করে। আর মদাসক্তি বিবেক ও চরিত্রকে ক্ষতি করে। হাদিসটি আমাদের শেখায়, শুধু ব্যক্তিগত ইবাদত নয়; পারিবারিক দায়িত্ব, অর্থনৈতিক সততা, মানুষের সম্মান এবং নেশা থেকে দূরে থাকা—সবই মুসলিম জীবনের অংশ।"},"teachings":["পিতা-মাতার অবাধ্যতা গুরুতর সতর্কতার বিষয়।","জুয়া ও লটারী থেকে দূরে থাকা দরকার।","উপকার করে খোঁটা দেওয়া খারাপ অভ্যাস।","সর্বদা মদপান করা ভয়াবহ পরিণতির কারণ হতে পারে।"],"related_hadiths":[{"id":"161","book_id":"2","label":"Sahih Muslim"},{"id":"6871","book_id":"1","label":"Sahih Bukhari"},{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অবাধ্যতা, জুয়া, খোঁটা ও মদাসক্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. পিতা-মাতার অবাধ্যতা, জুয়া-লটারী, খোঁটা দেওয়া ও মদাসক্তির কঠিন সতর্কতা।"},"heading":{"title":"অবাধ্য সন্তান, জুয়া, খোঁটা ও মদপান: চারটি গুরুতর সতর্কতা","description":"এই হাদিসে চার শ্রেণীর মানুষের ব্যাপারে জান্নাত বিষয়ে কঠিন সতর্কতা এসেছে। তারা হলো পিতা-মাতার অবাধ্য সন্তান, জুয়া ও লটারীতে অংশগ্রহণকারী, খোঁটাদানকারী এবং সর্বদা মদপানকারী। এখানে একসাথে কয়েকটি সামাজিক ও ব্যক্তিগত অপরাধ এসেছে। পিতা-মাতার অবাধ্যতা পরিবারকে আঘাত করে। জুয়া ও লটারী মানুষের সম্পদ ও মনকে অন্য পথে নেয়। খোঁটা দেওয়া দান বা উপকারের সৌন্দর্য নষ্ট করে। আর মদাসক্তি বিবেক ও চরিত্রকে ক্ষতি করে। হাদিসটি আমাদের শেখায়, শুধু ব্যক্তিগত ইবাদত নয়; পারিবারিক দায়িত্ব, অর্থনৈতিক সততা, মানুষের সম্মান এবং নেশা থেকে দূরে থাকা—সবই মুসলিম জীবনের অংশ।"},"teachings":["পিতা-মাতার অবাধ্যতা গুরুতর সতর্কতার বিষয়।","জুয়া ও লটারী থেকে দূরে থাকা দরকার।","উপকার করে খোঁটা দেওয়া খারাপ অভ্যাস।","সর্বদা মদপান করা ভয়াবহ পরিণতির কারণ হতে পারে।"],"related_hadiths":[{"id":"161","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6871","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E177" s="4" t="n"/>
@@ -4672,7 +4676,7 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর কঠিন সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. পরিবারে বেহায়াপনা, পুরুষের বেশধারী নারী ও নিয়মিত নেশাকারীর ব্যাপারে সতর্কতা।"},"heading":{"title":"তিন শ্রেণীর মানুষ: পরিবার, পোশাক-আচরণ ও নেশা বিষয়ে সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের ব্যাপারে কঠিন সতর্কতা এসেছে। প্রথমত, যে ব্যক্তি তার পরিবারে বেহায়াপনার সুযোগ দেয়। দ্বিতীয়ত, পুরুষের বেশধারী নারী। তৃতীয়ত, নিয়মিত নেশাদার দ্রব্য পানকারী। এখানে পরিবার, পরিচয় ও নেশার বিষয় একসাথে এসেছে। পরিবারে অশালীনতার সুযোগ দেওয়া মানে নিজের দায়িত্বকে অবহেলা করা। পোশাক ও আচরণে সীমা রক্ষা করাও ইসলামী শালীনতার অংশ। আর নিয়মিত নেশা মানুষের বিবেক ও আমলকে ক্ষতি করে। হাদিসের ভাষা কঠোর, তাই এটি নিজের সংশোধনের জন্য নেওয়া উচিত। অন্যকে অপমান করার জন্য নয়; বরং নিজের পরিবার, চরিত্র ও অভ্যাস ঠিক করার জন্য।"},"teachings":["পরিবারে বেহায়াপনার সুযোগ দেওয়া গুরুতর সতর্কতার বিষয়।","পোশাক ও আচরণে শালীনতা রক্ষা করা দরকার।","নিয়মিত নেশাদার দ্রব্য পান করা ভয়াবহ অভ্যাস।","হাদিসের শিক্ষা নিজের সংশোধনের জন্য গ্রহণ করা উচিত।"],"related_hadiths":[{"id":"168","book_id":"2","label":"Sahih Muslim"},{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"6136","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর কঠিন সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. পরিবারে বেহায়াপনা, পুরুষের বেশধারী নারী ও নিয়মিত নেশাকারীর ব্যাপারে সতর্কতা।"},"heading":{"title":"তিন শ্রেণীর মানুষ: পরিবার, পোশাক-আচরণ ও নেশা বিষয়ে সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের ব্যাপারে কঠিন সতর্কতা এসেছে। প্রথমত, যে ব্যক্তি তার পরিবারে বেহায়াপনার সুযোগ দেয়। দ্বিতীয়ত, পুরুষের বেশধারী নারী। তৃতীয়ত, নিয়মিত নেশাদার দ্রব্য পানকারী। এখানে পরিবার, পরিচয় ও নেশার বিষয় একসাথে এসেছে। পরিবারে অশালীনতার সুযোগ দেওয়া মানে নিজের দায়িত্বকে অবহেলা করা। পোশাক ও আচরণে সীমা রক্ষা করাও ইসলামী শালীনতার অংশ। আর নিয়মিত নেশা মানুষের বিবেক ও আমলকে ক্ষতি করে। হাদিসের ভাষা কঠোর, তাই এটি নিজের সংশোধনের জন্য নেওয়া উচিত। অন্যকে অপমান করার জন্য নয়; বরং নিজের পরিবার, চরিত্র ও অভ্যাস ঠিক করার জন্য।"},"teachings":["পরিবারে বেহায়াপনার সুযোগ দেওয়া গুরুতর সতর্কতার বিষয়।","পোশাক ও আচরণে শালীনতা রক্ষা করা দরকার।","নিয়মিত নেশাদার দ্রব্য পান করা ভয়াবহ অভ্যাস।","হাদিসের শিক্ষা নিজের সংশোধনের জন্য গ্রহণ করা উচিত।"],"related_hadiths":[{"id":"168","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"6136","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E178" s="4" t="n"/>
@@ -4695,7 +4699,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপান, অবাধ্যতা ও দায়ূস","description":"$book_name$ $hadith_number$ - $chapter_name$. মদাসক্ত, পিতা-মাতার অবাধ্য সন্তান ও পরিবারে বেপর্দার সুযোগদাতার সতর্কতা।"},"heading":{"title":"মদাসক্ত, অবাধ্য সন্তান ও দায়ূস: তিন শ্রেণীর কঠিন সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর লোকের প্রতি আল্লাহ জান্নাত হারাম করেছেন বলে সতর্ক করা হয়েছে। তারা হলো সর্বদা মদপানকারী, পিতা-মাতার অবাধ্য সন্তান এবং পরিবারে বেপর্দা বা খারাপ কাজের সুযোগ দানকারী দায়ূস। এখানে তিনটি বিষয়ে জোর আছে—নিজের নেশার অভ্যাস, পিতা-মাতার হক এবং পরিবারের নৈতিক দায়িত্ব। মদাসক্তি ব্যক্তিকে ভেতর থেকে দুর্বল করে। পিতা-মাতার অবাধ্যতা কৃতজ্ঞতা ও দায়িত্বের বিপরীত। আর পরিবারে খারাপ কাজকে মেনে নেওয়া দায়িত্বহীনতা। হাদিসটি মানুষকে ভয় দেখিয়ে ভেঙে দিতে নয়; বরং জাগিয়ে দিতে এসেছে, যেন সে তওবা করে, সম্পর্ক ঠিক করে এবং পরিবারকে সঠিক পথে রাখতে চেষ্টা করে।"},"teachings":["সর্বদা মদপানকারী সম্পর্কে কঠিন সতর্কতা এসেছে।","পিতা-মাতার অবাধ্যতা বড় অপরাধের মধ্যে পড়ে।","পরিবারে খারাপ কাজ মেনে নেওয়া দায়িত্বহীনতা।","তওবা ও সংশোধনের পথে ফিরে আসা দরকার।"],"related_hadiths":[{"id":"161","book_id":"2","label":"Sahih Muslim"},{"id":"6871","book_id":"1","label":"Sahih Bukhari"},{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপান, অবাধ্যতা ও দায়ূস","description":"$book_name$ $hadith_number$ - $chapter_name$. মদাসক্ত, পিতা-মাতার অবাধ্য সন্তান ও পরিবারে বেপর্দার সুযোগদাতার সতর্কতা।"},"heading":{"title":"মদাসক্ত, অবাধ্য সন্তান ও দায়ূস: তিন শ্রেণীর কঠিন সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর লোকের প্রতি আল্লাহ জান্নাত হারাম করেছেন বলে সতর্ক করা হয়েছে। তারা হলো সর্বদা মদপানকারী, পিতা-মাতার অবাধ্য সন্তান এবং পরিবারে বেপর্দা বা খারাপ কাজের সুযোগ দানকারী দায়ূস। এখানে তিনটি বিষয়ে জোর আছে—নিজের নেশার অভ্যাস, পিতা-মাতার হক এবং পরিবারের নৈতিক দায়িত্ব। মদাসক্তি ব্যক্তিকে ভেতর থেকে দুর্বল করে। পিতা-মাতার অবাধ্যতা কৃতজ্ঞতা ও দায়িত্বের বিপরীত। আর পরিবারে খারাপ কাজকে মেনে নেওয়া দায়িত্বহীনতা। হাদিসটি মানুষকে ভয় দেখিয়ে ভেঙে দিতে নয়; বরং জাগিয়ে দিতে এসেছে, যেন সে তওবা করে, সম্পর্ক ঠিক করে এবং পরিবারকে সঠিক পথে রাখতে চেষ্টা করে।"},"teachings":["সর্বদা মদপানকারী সম্পর্কে কঠিন সতর্কতা এসেছে।","পিতা-মাতার অবাধ্যতা বড় অপরাধের মধ্যে পড়ে।","পরিবারে খারাপ কাজ মেনে নেওয়া দায়িত্বহীনতা।","তওবা ও সংশোধনের পথে ফিরে আসা দরকার।"],"related_hadiths":[{"id":"161","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6871","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E179" s="4" t="n"/>
@@ -4718,7 +4722,7 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, সম্পর্কচ্ছেদ ও যাদু","description":"$book_name$ $hadith_number$ - $chapter_name$. মদাসক্তি, আত্মীয়তার সম্পর্ক ছিন্ন করা ও যাদু বিশ্বাসের ব্যাপারে কঠিন সতর্কতা।"},"heading":{"title":"মদাসক্তি, আত্মীয়তা ছিন্ন ও যাদু বিশ্বাস: তিনটি বড় সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর লোকের ব্যাপারে বলা হয়েছে, তারা জান্নাতে যাবে না। প্রথম শ্রেণী হলো সর্বদা নেশাদার দ্রব্য পানকারী। দ্বিতীয় হলো আত্মীয়তার সম্পর্ক বিচ্ছিন্নকারী। তৃতীয় হলো যাদুকে বিশ্বাসকারী। এখানে তিনটি ভিন্ন ক্ষতির দিক দেখা যায়। নেশা নিজের বিবেক ও আমলকে ক্ষতি করে। আত্মীয়তার সম্পর্ক ছিন্ন করা পরিবার ও সমাজের বন্ধন নষ্ট করে। আর যাদুকে বিশ্বাস করা ঈমানী চিন্তা ও আল্লাহর ওপর ভরসাকে দুর্বল করতে পারে। হাদিসটি আমাদের নিজের জীবনকে তিন দিক থেকে দেখতে শেখায়—অভ্যাস, সম্পর্ক এবং বিশ্বাস। ভুল থাকলে তা স্বীকার করে ফিরে আসাই নিরাপদ পথ।"},"teachings":["সর্বদা নেশাদার দ্রব্য পান করা ভয়াবহ সতর্কতার বিষয়।","আত্মীয়তার সম্পর্ক ছিন্ন করা থেকে দূরে থাকতে হবে।","যাদুকে বিশ্বাস করা ঈমানের জন্য বিপজ্জনক।","অভ্যাস, সম্পর্ক ও বিশ্বাস—তিন দিকেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"1862","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"5112","book_id":"2","label":"Sahih Muslim"},{"id":"6136","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, সম্পর্কচ্ছেদ ও যাদু","description":"$book_name$ $hadith_number$ - $chapter_name$. মদাসক্তি, আত্মীয়তার সম্পর্ক ছিন্ন করা ও যাদু বিশ্বাসের ব্যাপারে কঠিন সতর্কতা।"},"heading":{"title":"মদাসক্তি, আত্মীয়তা ছিন্ন ও যাদু বিশ্বাস: তিনটি বড় সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর লোকের ব্যাপারে বলা হয়েছে, তারা জান্নাতে যাবে না। প্রথম শ্রেণী হলো সর্বদা নেশাদার দ্রব্য পানকারী। দ্বিতীয় হলো আত্মীয়তার সম্পর্ক বিচ্ছিন্নকারী। তৃতীয় হলো যাদুকে বিশ্বাসকারী। এখানে তিনটি ভিন্ন ক্ষতির দিক দেখা যায়। নেশা নিজের বিবেক ও আমলকে ক্ষতি করে। আত্মীয়তার সম্পর্ক ছিন্ন করা পরিবার ও সমাজের বন্ধন নষ্ট করে। আর যাদুকে বিশ্বাস করা ঈমানী চিন্তা ও আল্লাহর ওপর ভরসাকে দুর্বল করতে পারে। হাদিসটি আমাদের নিজের জীবনকে তিন দিক থেকে দেখতে শেখায়—অভ্যাস, সম্পর্ক এবং বিশ্বাস। ভুল থাকলে তা স্বীকার করে ফিরে আসাই নিরাপদ পথ।"},"teachings":["সর্বদা নেশাদার দ্রব্য পান করা ভয়াবহ সতর্কতার বিষয়।","আত্মীয়তার সম্পর্ক ছিন্ন করা থেকে দূরে থাকতে হবে।","যাদুকে বিশ্বাস করা ঈমানের জন্য বিপজ্জনক।","অভ্যাস, সম্পর্ক ও বিশ্বাস—তিন দিকেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6136","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E180" s="4" t="n"/>
@@ -4741,7 +4745,7 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে অঙ্গ-প্রত্যঙ্গের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে মুখ বন্ধ করে অঙ্গ-প্রত্যঙ্গকে কথা বলানো হবে; মানুষ নিজের কাজের সাক্ষ্য নিজ থেকেই পাবে।"},"heading":{"title":"কিয়ামতের দিন অঙ্গ-প্রত্যঙ্গের সাক্ষ্য দেওয়ার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কিয়ামতের দিনের এক কথোপকথনের কথা বলেছেন। বান্দা বলবে, সে নিজের বিরুদ্ধে শুধু নিজের পক্ষ থেকে সাক্ষ্য গ্রহণ করবে। তখন আল্লাহ বলবেন, আজ তুমি নিজেই তোমার সাক্ষী হিসেবে যথেষ্ট, আর কিরামান-কাতিবীনও সাক্ষী। এরপর তার মুখে মোহর লাগিয়ে দেওয়া হবে এবং অঙ্গ-প্রত্যঙ্গকে বলা হবে, তারা যেন তার কাজের কথা বলে। তখন অঙ্গ-প্রত্যঙ্গ তার কাজ প্রকাশ করবে। পরে মুখ খুলে দেওয়া হলে সে নিজের অঙ্গগুলোকে দোষ দেবে, অথচ তাদের জন্যই সে আগে নিজের রবের সঙ্গে বিতর্ক করছিল। এই হাদিস আমাদের মনে করায়, কিয়ামতের সাক্ষ্য খুব স্পষ্ট হবে এবং মানুষের কাজ লুকানো থাকবে না।"},"teachings":["কিয়ামতে মানুষের নিজের অঙ্গ-প্রত্যঙ্গ তার কাজের সাক্ষ্য দেবে।","কিরামান-কাতিবীন মানুষের কাজ লিখে রাখেন।","মুখের কথা দিয়ে সবকিছু অস্বীকার করা সম্ভব হবে না।","দুনিয়ার কাজের জন্য আখেরাতে জবাবদিহি আছে।"],"related_hadiths":[{"id":"2969","book_id":"2","label":"Sahih Muslim"},{"id":"5554","book_id":"14","label":"Mishkat al-Masabih"},{"id":"2429","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে অঙ্গ-প্রত্যঙ্গের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে মুখ বন্ধ করে অঙ্গ-প্রত্যঙ্গকে কথা বলানো হবে; মানুষ নিজের কাজের সাক্ষ্য নিজ থেকেই পাবে।"},"heading":{"title":"কিয়ামতের দিন অঙ্গ-প্রত্যঙ্গের সাক্ষ্য দেওয়ার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কিয়ামতের দিনের এক কথোপকথনের কথা বলেছেন। বান্দা বলবে, সে নিজের বিরুদ্ধে শুধু নিজের পক্ষ থেকে সাক্ষ্য গ্রহণ করবে। তখন আল্লাহ বলবেন, আজ তুমি নিজেই তোমার সাক্ষী হিসেবে যথেষ্ট, আর কিরামান-কাতিবীনও সাক্ষী। এরপর তার মুখে মোহর লাগিয়ে দেওয়া হবে এবং অঙ্গ-প্রত্যঙ্গকে বলা হবে, তারা যেন তার কাজের কথা বলে। তখন অঙ্গ-প্রত্যঙ্গ তার কাজ প্রকাশ করবে। পরে মুখ খুলে দেওয়া হলে সে নিজের অঙ্গগুলোকে দোষ দেবে, অথচ তাদের জন্যই সে আগে নিজের রবের সঙ্গে বিতর্ক করছিল। এই হাদিস আমাদের মনে করায়, কিয়ামতের সাক্ষ্য খুব স্পষ্ট হবে এবং মানুষের কাজ লুকানো থাকবে না।"},"teachings":["কিয়ামতে মানুষের নিজের অঙ্গ-প্রত্যঙ্গ তার কাজের সাক্ষ্য দেবে।","কিরামান-কাতিবীন মানুষের কাজ লিখে রাখেন।","মুখের কথা দিয়ে সবকিছু অস্বীকার করা সম্ভব হবে না।","দুনিয়ার কাজের জন্য আখেরাতে জবাবদিহি আছে।"],"related_hadiths":[{"id":"2969","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"5554","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"2429","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E181" s="4" t="n"/>
@@ -4764,7 +4768,7 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শাসকদের যুগ ও পাপকে হালাল মনে করার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইসলামের শুরু, খেলাফত, কঠোর শাসন এবং পাপকে হালাল মনে করার ভয়াবহ পরিণতি সম্পর্কে সতর্ক শিক্ষা।"},"heading":{"title":"অত্যাচারী শাসক ও পাপকে হালাল মনে করার হাদিস","description":"এই হাদিসের মূল বিষয় শাসনব্যবস্থা, ফিতনা এবং পাপকে হালাল মনে করার ভয়াবহতা। এখানে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ইসলামের শুরুতে নবুয়ত ও রহমতের কথা বলেছেন। এরপর খেলাফত ও রহমতের যুগের কথা এসেছে। তারপর এমন রাজত্ব ও কঠোর শাসনের কথা বলা হয়েছে, যেখানে যুলুম, উচ্ছৃঙ্খলতা এবং জমিনে বিপর্যয় দেখা দেবে। হাদিসে বিশেষভাবে বলা হয়েছে, কিছু অত্যাচারী শাসক রেশম, অবৈধ সম্পর্ক ও মদকে হালাল মনে করবে। তাদের দুনিয়াবী রিযিক ও সাহায্য পাওয়া যেতে পারে, কিন্তু সেটি তাদের কাজের সঠিকতা প্রমাণ করে না। তাই মুমিনের জন্য শিক্ষা হলো—ক্ষমতা, ধন বা বাহ্যিক সফলতা দেখে পাপকে ছোট মনে করা যাবে না। তাই নেতৃত্বের অবস্থানে থাকা মানুষদের জন্য এটি আরও বড় সতর্কতা, আর সাধারণ মানুষের জন্যও সত্য ও পাপের পার্থক্য বুঝে চলার শিক্ষা।"},"teachings":["ক্ষমতা ও দুনিয়াবী সাফল্য পাপকে বৈধ করে না।","রহমতপূর্ণ নেতৃত্ব মানুষের জন্য কল্যাণের পথ খুলে দেয়।","যুলুম, মদ ও অশ্লীলতাকে হালাল মনে করা বড় সতর্কতার বিষয়।","দুনিয়ার সাহায্য পেলেও আল্লাহর সামনে জবাবদিহি থেকে কেউ মুক্ত নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"80","book_id":"1","label":"Sahih Bukhari"},{"id":"81","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শাসকদের যুগ ও পাপকে হালাল মনে করার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইসলামের শুরু, খেলাফত, কঠোর শাসন এবং পাপকে হালাল মনে করার ভয়াবহ পরিণতি সম্পর্কে সতর্ক শিক্ষা।"},"heading":{"title":"অত্যাচারী শাসক ও পাপকে হালাল মনে করার হাদিস","description":"এই হাদিসের মূল বিষয় শাসনব্যবস্থা, ফিতনা এবং পাপকে হালাল মনে করার ভয়াবহতা। এখানে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ইসলামের শুরুতে নবুয়ত ও রহমতের কথা বলেছেন। এরপর খেলাফত ও রহমতের যুগের কথা এসেছে। তারপর এমন রাজত্ব ও কঠোর শাসনের কথা বলা হয়েছে, যেখানে যুলুম, উচ্ছৃঙ্খলতা এবং জমিনে বিপর্যয় দেখা দেবে। হাদিসে বিশেষভাবে বলা হয়েছে, কিছু অত্যাচারী শাসক রেশম, অবৈধ সম্পর্ক ও মদকে হালাল মনে করবে। তাদের দুনিয়াবী রিযিক ও সাহায্য পাওয়া যেতে পারে, কিন্তু সেটি তাদের কাজের সঠিকতা প্রমাণ করে না। তাই মুমিনের জন্য শিক্ষা হলো—ক্ষমতা, ধন বা বাহ্যিক সফলতা দেখে পাপকে ছোট মনে করা যাবে না। তাই নেতৃত্বের অবস্থানে থাকা মানুষদের জন্য এটি আরও বড় সতর্কতা, আর সাধারণ মানুষের জন্যও সত্য ও পাপের পার্থক্য বুঝে চলার শিক্ষা।"},"teachings":["ক্ষমতা ও দুনিয়াবী সাফল্য পাপকে বৈধ করে না।","রহমতপূর্ণ নেতৃত্ব মানুষের জন্য কল্যাণের পথ খুলে দেয়।","যুলুম, মদ ও অশ্লীলতাকে হালাল মনে করা বড় সতর্কতার বিষয়।","দুনিয়ার সাহায্য পেলেও আল্লাহর সামনে জবাবদিহি থেকে কেউ মুক্ত নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"81","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E182" s="4" t="n"/>
@@ -4787,7 +4791,7 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতের আলামত ও ইলম কমে যাওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইলম কমে যাওয়া, মূর্খতা, ব্যভিচার, মদপান ও নারী-পুরুষের সংখ্যার পরিবর্তন—কিয়ামতের কিছু আলামত।"},"heading":{"title":"কিয়ামতের আলামত: ইলম কমে যাওয়া ও মদপান বৃদ্ধি","description":"এই হাদিসে কিয়ামতের আলামত নিয়ে কয়েকটি স্পষ্ট সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, বিদ্যা উঠে যাবে বা কমে যাবে, মূর্খতা বেড়ে যাবে, ব্যভিচার বেশি হবে এবং মদপান বৃদ্ধি পাবে। আরও বলা হয়েছে, পুরুষের সংখ্যা কমে যাবে এবং নারীর সংখ্যা বেশি হবে, এমনকি একজন পুরুষ বহু নারীর দায়িত্বে থাকবে। হাদিসটি আমাদের বোঝায় যে সমাজে দ্বীনি জ্ঞান কমে গেলে ভুল কাজ সহজে ছড়িয়ে পড়ে। তাই কিয়ামতের আলামত হাদিস পড়ার উদ্দেশ্য শুধু ভবিষ্যৎ জানা নয়; বরং নিজের জীবনে ইলম, লজ্জাশীলতা, সংযম এবং হারাম থেকে বাঁচার চেষ্টা বাড়ানো। এই বার্তাটি সরল কিন্তু গভীর। তাই পাঠকের উচিত হাদিসটি পড়ে ভয় পাওয়ার পাশাপাশি নিজের ঘর, শিক্ষা ও চরিত্রের দিকে বাস্তবভাবে নজর দেওয়া।"},"teachings":["দ্বীনি ইলম কমে যাওয়া সমাজের জন্য বড় সতর্কতা।","মূর্খতা বাড়লে হারাম কাজের পথ সহজ হয়।","মদপান ও ব্যভিচার বৃদ্ধি কিয়ামতের আলামতের মধ্যে এসেছে।","হাদিসটি জ্ঞান ও নৈতিকতার গুরুত্ব মনে করিয়ে দেয়।"],"related_hadiths":[{"id":"80","book_id":"1","label":"Sahih Bukhari"},{"id":"81","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতের আলামত ও ইলম কমে যাওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইলম কমে যাওয়া, মূর্খতা, ব্যভিচার, মদপান ও নারী-পুরুষের সংখ্যার পরিবর্তন—কিয়ামতের কিছু আলামত।"},"heading":{"title":"কিয়ামতের আলামত: ইলম কমে যাওয়া ও মদপান বৃদ্ধি","description":"এই হাদিসে কিয়ামতের আলামত নিয়ে কয়েকটি স্পষ্ট সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, বিদ্যা উঠে যাবে বা কমে যাবে, মূর্খতা বেড়ে যাবে, ব্যভিচার বেশি হবে এবং মদপান বৃদ্ধি পাবে। আরও বলা হয়েছে, পুরুষের সংখ্যা কমে যাবে এবং নারীর সংখ্যা বেশি হবে, এমনকি একজন পুরুষ বহু নারীর দায়িত্বে থাকবে। হাদিসটি আমাদের বোঝায় যে সমাজে দ্বীনি জ্ঞান কমে গেলে ভুল কাজ সহজে ছড়িয়ে পড়ে। তাই কিয়ামতের আলামত হাদিস পড়ার উদ্দেশ্য শুধু ভবিষ্যৎ জানা নয়; বরং নিজের জীবনে ইলম, লজ্জাশীলতা, সংযম এবং হারাম থেকে বাঁচার চেষ্টা বাড়ানো। এই বার্তাটি সরল কিন্তু গভীর। তাই পাঠকের উচিত হাদিসটি পড়ে ভয় পাওয়ার পাশাপাশি নিজের ঘর, শিক্ষা ও চরিত্রের দিকে বাস্তবভাবে নজর দেওয়া।"},"teachings":["দ্বীনি ইলম কমে যাওয়া সমাজের জন্য বড় সতর্কতা।","মূর্খতা বাড়লে হারাম কাজের পথ সহজ হয়।","মদপান ও ব্যভিচার বৃদ্ধি কিয়ামতের আলামতের মধ্যে এসেছে।","হাদিসটি জ্ঞান ও নৈতিকতার গুরুত্ব মনে করিয়ে দেয়।"],"related_hadiths":[{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"81","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E183" s="4" t="n"/>
@@ -4810,7 +4814,7 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, গায়িকা ও বাদ্যযন্ত্রের ভয়াবহ সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপান, গায়িকা নিয়ে নাচ-গান ও বাদ্যযন্ত্রে মত্ততার কারণে বড় বিপদের বিষয়ে হাদিসের সতর্কতা।"},"heading":{"title":"মদ ও বাদ্যযন্ত্র সম্পর্কে ভয়াবহ সতর্কবার্তার হাদিস","description":"এই হাদিসের মূল বিষয় মদ, গায়িকা নিয়ে নাচ-গান এবং বাদ্যযন্ত্রে ব্যস্ত থাকা। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের মধ্যে এমন সময় আসবে যখন মানুষ নেশাদার দ্রব্য পান করবে, গায়িকাদের নিয়ে নাচ-গানে মত্ত হবে এবং বাদ্যযন্ত্র নিয়ে ব্যস্ত হবে। তখন তিন ধরনের ভয়াবহ বিপদের কথা বলা হয়েছে: ভূমি ধসে যাওয়া, উপর থেকে বা কোনো জাতির পক্ষ থেকে যুলুম চাপিয়ে দেওয়া, এবং অনেকের আকার-আকৃতি বিকৃত হওয়া। এখানে শিক্ষা হলো, আনন্দের নামে হারামকে সাধারণ বানানো নিরাপদ পথ নয়। হাদিসটি মানুষকে মদ, নাচ-গান এবং বাদ্যযন্ত্রের ফিতনা থেকে সাবধান হতে বলছে। তাই সতর্কতা শুরু হতে পারে নিজের পছন্দ, বন্ধু-বান্ধব এবং অবসর কাটানোর ধরন ঠিক করার মাধ্যমে।"},"teachings":["মদপানকে হাদিসে বড় বিপদের কারণ হিসেবে উল্লেখ করা হয়েছে।","গায়িকা ও নাচ-গানে মত্ত হওয়া থেকে সতর্ক করা হয়েছে।","বাদ্যযন্ত্রের প্রতি আসক্তি হাদিসে নিন্দিতভাবে এসেছে।","সমাজে হারাম কাজ ছড়ালে বিপদের আশঙ্কা বাড়ে।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"4924","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, গায়িকা ও বাদ্যযন্ত্রের ভয়াবহ সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপান, গায়িকা নিয়ে নাচ-গান ও বাদ্যযন্ত্রে মত্ততার কারণে বড় বিপদের বিষয়ে হাদিসের সতর্কতা।"},"heading":{"title":"মদ ও বাদ্যযন্ত্র সম্পর্কে ভয়াবহ সতর্কবার্তার হাদিস","description":"এই হাদিসের মূল বিষয় মদ, গায়িকা নিয়ে নাচ-গান এবং বাদ্যযন্ত্রে ব্যস্ত থাকা। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের মধ্যে এমন সময় আসবে যখন মানুষ নেশাদার দ্রব্য পান করবে, গায়িকাদের নিয়ে নাচ-গানে মত্ত হবে এবং বাদ্যযন্ত্র নিয়ে ব্যস্ত হবে। তখন তিন ধরনের ভয়াবহ বিপদের কথা বলা হয়েছে: ভূমি ধসে যাওয়া, উপর থেকে বা কোনো জাতির পক্ষ থেকে যুলুম চাপিয়ে দেওয়া, এবং অনেকের আকার-আকৃতি বিকৃত হওয়া। এখানে শিক্ষা হলো, আনন্দের নামে হারামকে সাধারণ বানানো নিরাপদ পথ নয়। হাদিসটি মানুষকে মদ, নাচ-গান এবং বাদ্যযন্ত্রের ফিতনা থেকে সাবধান হতে বলছে। তাই সতর্কতা শুরু হতে পারে নিজের পছন্দ, বন্ধু-বান্ধব এবং অবসর কাটানোর ধরন ঠিক করার মাধ্যমে।"},"teachings":["মদপানকে হাদিসে বড় বিপদের কারণ হিসেবে উল্লেখ করা হয়েছে।","গায়িকা ও নাচ-গানে মত্ত হওয়া থেকে সতর্ক করা হয়েছে।","বাদ্যযন্ত্রের প্রতি আসক্তি হাদিসে নিন্দিতভাবে এসেছে।","সমাজে হারাম কাজ ছড়ালে বিপদের আশঙ্কা বাড়ে।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E184" s="4" t="n"/>
@@ -4833,7 +4837,7 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | খাদ্য-পানীয় ও আমোদ-প্রমোদের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য-পানীয় ও বিনোদনে ডুবে থাকা কিছু লোকের ভয়াবহ রূপান্তর সম্পর্কে সতর্ক করা হয়েছে।"},"heading":{"title":"ভোগ-বিলাস ও আমোদ-প্রমোদের পরিণতি নিয়ে হাদিস","description":"এই হাদিসে ভোগ-বিলাস, খাদ্য-পানীয় এবং আমোদ-প্রমোদের বিষয়ে কঠোর সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের কিছু লোক রাত কাটাবে নানা ধরনের খাবার, পানীয় ও বিনোদনে ডুবে থেকে। এরপর তাদের সকাল হবে বানর ও শূকরের আকৃতিতে রূপান্তরিত হয়ে। হাদিসটি আনন্দ বা খাবারকে আলাদা করে নিষিদ্ধ বলছে না; বরং এমন জীবনধারার দিকে সতর্ক করছে যেখানে মানুষ আল্লাহভীতি ভুলে ভোগ, নেশা এবং অসংযত বিনোদনে ডুবে যায়। মূল শিক্ষা হলো, আনন্দ যেন ঈমান, লজ্জা ও হারাম-হালালের সীমা নষ্ট না করে। দুনিয়ার মজা সাময়িক, কিন্তু জবাবদিহি খুব বাস্তব। পরিবার ও সমাজে এমন পরিবেশ তৈরি করা দরকার, যেখানে আনন্দ থাকবে কিন্তু হারামের সীমা অতিক্রম করা হবে না।"},"teachings":["ভোগ-বিলাসে ডুবে আল্লাহভীতি ভুলে যাওয়া বিপজ্জনক।","বিনোদন যদি হারামের পথে নেয়, তা থেকে সতর্ক থাকা দরকার।","হাদিসে কিছু লোকের ভয়াবহ পরিণতির কথা এসেছে।","খাবার-পানীয় ও আনন্দের ক্ষেত্রেও সীমা মানা জরুরি।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"4924","book_id":"4","label":"Sunan Abu Dawud"},{"id":"80","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | খাদ্য-পানীয় ও আমোদ-প্রমোদের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য-পানীয় ও বিনোদনে ডুবে থাকা কিছু লোকের ভয়াবহ রূপান্তর সম্পর্কে সতর্ক করা হয়েছে।"},"heading":{"title":"ভোগ-বিলাস ও আমোদ-প্রমোদের পরিণতি নিয়ে হাদিস","description":"এই হাদিসে ভোগ-বিলাস, খাদ্য-পানীয় এবং আমোদ-প্রমোদের বিষয়ে কঠোর সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের কিছু লোক রাত কাটাবে নানা ধরনের খাবার, পানীয় ও বিনোদনে ডুবে থেকে। এরপর তাদের সকাল হবে বানর ও শূকরের আকৃতিতে রূপান্তরিত হয়ে। হাদিসটি আনন্দ বা খাবারকে আলাদা করে নিষিদ্ধ বলছে না; বরং এমন জীবনধারার দিকে সতর্ক করছে যেখানে মানুষ আল্লাহভীতি ভুলে ভোগ, নেশা এবং অসংযত বিনোদনে ডুবে যায়। মূল শিক্ষা হলো, আনন্দ যেন ঈমান, লজ্জা ও হারাম-হালালের সীমা নষ্ট না করে। দুনিয়ার মজা সাময়িক, কিন্তু জবাবদিহি খুব বাস্তব। পরিবার ও সমাজে এমন পরিবেশ তৈরি করা দরকার, যেখানে আনন্দ থাকবে কিন্তু হারামের সীমা অতিক্রম করা হবে না।"},"teachings":["ভোগ-বিলাসে ডুবে আল্লাহভীতি ভুলে যাওয়া বিপজ্জনক।","বিনোদন যদি হারামের পথে নেয়, তা থেকে সতর্ক থাকা দরকার।","হাদিসে কিছু লোকের ভয়াবহ পরিণতির কথা এসেছে।","খাবার-পানীয় ও আনন্দের ক্ষেত্রেও সীমা মানা জরুরি।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E185" s="4" t="n"/>
@@ -4856,7 +4860,7 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঈমান, সালাত, পরিবার ও গোনাহ থেকে বাঁচার দশ শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, ফরয সালাত ত্যাগ, মদপান, গোনাহ ও পরিবার বিষয়ে দশটি গুরুত্বপূর্ণ উপদেশ।"},"heading":{"title":"রাসূলের দশ উপদেশ: ঈমান, সালাত ও পরিবার জীবনের শিক্ষা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মু‘আয (রাঃ)-কে দশটি বিষয়ে উপদেশ দিয়েছেন। প্রথমে এসেছে আল্লাহর সাথে কাউকে শরীক না করা। এরপর পিতা-মাতার অবাধ্য না হওয়া, ইচ্ছা করে ফরয সালাত না ছাড়া, মদ পান না করা এবং গোনাহ থেকে বেঁচে থাকার কথা এসেছে। আরও আছে জিহাদ থেকে পলায়ন না করা, মহামারী দেখা দিলে যেখানে আছে সেখানে স্থির থাকা, সামর্থ্য অনুযায়ী পরিবারের জন্য ব্যয় করা, পরিবারকে আদব শেখানো এবং আল্লাহর ভয় মনে করিয়ে দেওয়া। হাদিসটি ব্যক্তিগত ঈমান, ইবাদত, পরিবার, শৃঙ্খলা ও দায়িত্ব—সব দিককে একসাথে মনে করিয়ে দেয়। এটি জীবনের জন্য সংক্ষিপ্ত কিন্তু শক্তিশালী দিকনির্দেশনা। ফলে এই দশ উপদেশ একজন মুসলিমকে ঘর, সমাজ ও ব্যক্তিগত ইবাদতে ভারসাম্য রাখতে সাহায্য করে।"},"teachings":["তাওহীদ হলো জীবনের সবচেয়ে মূল দায়িত্ব।","ইচ্ছা করে ফরয সালাত ত্যাগ করা বড় সতর্কতার বিষয়।","মদকে অশ্লীলতার মূল হিসেবে উল্লেখ করা হয়েছে।","পরিবারের ব্যয়, আদব ও আল্লাহভীতি শেখানো দায়িত্বের অংশ।"],"related_hadiths":[{"id":"527","book_id":"1","label":"Sahih Bukhari"},{"id":"5975","book_id":"1","label":"Sahih Bukhari"},{"id":"3371","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঈমান, সালাত, পরিবার ও গোনাহ থেকে বাঁচার দশ শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, ফরয সালাত ত্যাগ, মদপান, গোনাহ ও পরিবার বিষয়ে দশটি গুরুত্বপূর্ণ উপদেশ।"},"heading":{"title":"রাসূলের দশ উপদেশ: ঈমান, সালাত ও পরিবার জীবনের শিক্ষা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মু‘আয (রাঃ)-কে দশটি বিষয়ে উপদেশ দিয়েছেন। প্রথমে এসেছে আল্লাহর সাথে কাউকে শরীক না করা। এরপর পিতা-মাতার অবাধ্য না হওয়া, ইচ্ছা করে ফরয সালাত না ছাড়া, মদ পান না করা এবং গোনাহ থেকে বেঁচে থাকার কথা এসেছে। আরও আছে জিহাদ থেকে পলায়ন না করা, মহামারী দেখা দিলে যেখানে আছে সেখানে স্থির থাকা, সামর্থ্য অনুযায়ী পরিবারের জন্য ব্যয় করা, পরিবারকে আদব শেখানো এবং আল্লাহর ভয় মনে করিয়ে দেওয়া। হাদিসটি ব্যক্তিগত ঈমান, ইবাদত, পরিবার, শৃঙ্খলা ও দায়িত্ব—সব দিককে একসাথে মনে করিয়ে দেয়। এটি জীবনের জন্য সংক্ষিপ্ত কিন্তু শক্তিশালী দিকনির্দেশনা। ফলে এই দশ উপদেশ একজন মুসলিমকে ঘর, সমাজ ও ব্যক্তিগত ইবাদতে ভারসাম্য রাখতে সাহায্য করে।"},"teachings":["তাওহীদ হলো জীবনের সবচেয়ে মূল দায়িত্ব।","ইচ্ছা করে ফরয সালাত ত্যাগ করা বড় সতর্কতার বিষয়।","মদকে অশ্লীলতার মূল হিসেবে উল্লেখ করা হয়েছে।","পরিবারের ব্যয়, আদব ও আল্লাহভীতি শেখানো দায়িত্বের অংশ।"],"related_hadiths":[{"id":"527","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5975","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3371","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E186" s="4" t="n"/>
@@ -4879,7 +4883,7 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নেশাদার দ্রব্য সব অন্যায়ের চাবী","description":"$book_name$ $hadith_number$ - $chapter_name$. নেশাদার দ্রব্য থেকে দূরে থাকার উপদেশ এসেছে, কারণ তা বহু অন্যায়ের দরজা খুলে দিতে পারে।"},"heading":{"title":"নেশাদার দ্রব্য: সব অন্যায়ের চাবী সম্পর্কে হাদিস","description":"এই ছোট হাদিসটি খুব সহজ ভাষায় বড় শিক্ষা দেয়। আবূ দারদা (রাঃ) বলেন, তাঁর দোস্ত রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাঁকে অছিয়ত করেছেন—নেশাদার দ্রব্য পান করো না; নিশ্চয়ই তা সব ধরনের অন্যায়ের চাবী। এখানে মূল কথা হলো মদ বা নেশা মানুষকে শুধু একটি গোনাহে আটকে রাখে না; বরং তা বিবেক, লজ্জা এবং সংযম দুর্বল করে আরও অনেক ভুলের দিকে ঠেলে দিতে পারে। তাই ইসলাম শুধু শেষ ক্ষতি নয়, ক্ষতির দরজাও বন্ধ করতে শেখায়। এই হাদিস মাদক থেকে দূরে থাকা, সঙ্গ বাছাই করা এবং নিজের বিবেককে সুরক্ষিত রাখার পরিষ্কার বার্তা দেয়। বিশেষ করে তরুণদের জন্য এটি শক্ত বার্তা—নেশার শুরু ছোট মনে হলেও শেষটা খুব ক্ষতিকর হতে পারে।"},"teachings":["নেশাদার দ্রব্য থেকে দূরে থাকা নিরাপদ পথ।","মদকে বহু অন্যায়ের দরজা হিসেবে সতর্ক করা হয়েছে।","বিবেক নষ্ট হলে অন্য গোনাহে পড়ার ঝুঁকি বাড়ে।","ভালো উপদেশ মানা ঈমানি জীবনের অংশ।"],"related_hadiths":[{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3390","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3681","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নেশাদার দ্রব্য সব অন্যায়ের চাবী","description":"$book_name$ $hadith_number$ - $chapter_name$. নেশাদার দ্রব্য থেকে দূরে থাকার উপদেশ এসেছে, কারণ তা বহু অন্যায়ের দরজা খুলে দিতে পারে।"},"heading":{"title":"নেশাদার দ্রব্য: সব অন্যায়ের চাবী সম্পর্কে হাদিস","description":"এই ছোট হাদিসটি খুব সহজ ভাষায় বড় শিক্ষা দেয়। আবূ দারদা (রাঃ) বলেন, তাঁর দোস্ত রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাঁকে অছিয়ত করেছেন—নেশাদার দ্রব্য পান করো না; নিশ্চয়ই তা সব ধরনের অন্যায়ের চাবী। এখানে মূল কথা হলো মদ বা নেশা মানুষকে শুধু একটি গোনাহে আটকে রাখে না; বরং তা বিবেক, লজ্জা এবং সংযম দুর্বল করে আরও অনেক ভুলের দিকে ঠেলে দিতে পারে। তাই ইসলাম শুধু শেষ ক্ষতি নয়, ক্ষতির দরজাও বন্ধ করতে শেখায়। এই হাদিস মাদক থেকে দূরে থাকা, সঙ্গ বাছাই করা এবং নিজের বিবেককে সুরক্ষিত রাখার পরিষ্কার বার্তা দেয়। বিশেষ করে তরুণদের জন্য এটি শক্ত বার্তা—নেশার শুরু ছোট মনে হলেও শেষটা খুব ক্ষতিকর হতে পারে।"},"teachings":["নেশাদার দ্রব্য থেকে দূরে থাকা নিরাপদ পথ।","মদকে বহু অন্যায়ের দরজা হিসেবে সতর্ক করা হয়েছে।","বিবেক নষ্ট হলে অন্য গোনাহে পড়ার ঝুঁকি বাড়ে।","ভালো উপদেশ মানা ঈমানি জীবনের অংশ।"],"related_hadiths":[{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3390","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E187" s="4" t="n"/>
@@ -4902,7 +4906,7 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সব নেশাদার দ্রব্য হারাম হওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. হাদিসে স্পষ্ট বলা হয়েছে, যে কোনো নেশা উদ্রেককারী বস্তু হারাম; তাই মাদক থেকে দূরে থাকা জরুরি।"},"heading":{"title":"সব নেশাদার দ্রব্য হারাম: স্পষ্ট হাদিসের শিক্ষা","description":"এই হাদিসের মূল শিক্ষা খুব সরল: সব ধরনের নেশাদার দ্রব্য হারাম। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, “কুল্লু মুসকিরিন হারাম”—প্রতিটি নেশা উদ্রেককারী জিনিস হারাম। তাই বিষয়টি শুধু নির্দিষ্ট কোনো পানীয়ের মধ্যে সীমাবদ্ধ নয়। যে জিনিস মানুষের বিবেক ঢেকে দেয়, সিদ্ধান্ত নেওয়ার ক্ষমতা দুর্বল করে এবং তাকে ভুল কাজে ঠেলে দেয়, সেটি এই সতর্কতার মধ্যে পড়ে। হাদিসটি মুসলিমকে নাম বা ধরন নিয়ে চালাকি না করতে শেখায়। মদ, মাদক বা যে কোনো নেশা—মূল বিচার হলো তা নেশা সৃষ্টি করে কি না। ঈমানদার জীবনে বিবেক রক্ষা করা বড় দায়িত্ব। এ কারণে নেশা নিয়ে মজা, পরীক্ষা বা কৌতূহল দেখানোও মুমিনের জন্য ঝুঁকিপূর্ণ আচরণ হতে পারে।"},"teachings":["নেশা সৃষ্টি করে এমন জিনিস থেকে বাঁচতে হবে।","হারামকে নাম বদলে বৈধ ভাবা ঠিক নয়।","বিবেক ও সংযম রক্ষা করা ঈমানি জীবনের অংশ।","হাদিসটি মাদক বিষয়ে সংক্ষিপ্ত কিন্তু স্পষ্ট নির্দেশ দেয়।"],"related_hadiths":[{"id":"3390","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3393","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3681","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সব নেশাদার দ্রব্য হারাম হওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. হাদিসে স্পষ্ট বলা হয়েছে, যে কোনো নেশা উদ্রেককারী বস্তু হারাম; তাই মাদক থেকে দূরে থাকা জরুরি।"},"heading":{"title":"সব নেশাদার দ্রব্য হারাম: স্পষ্ট হাদিসের শিক্ষা","description":"এই হাদিসের মূল শিক্ষা খুব সরল: সব ধরনের নেশাদার দ্রব্য হারাম। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, “কুল্লু মুসকিরিন হারাম”—প্রতিটি নেশা উদ্রেককারী জিনিস হারাম। তাই বিষয়টি শুধু নির্দিষ্ট কোনো পানীয়ের মধ্যে সীমাবদ্ধ নয়। যে জিনিস মানুষের বিবেক ঢেকে দেয়, সিদ্ধান্ত নেওয়ার ক্ষমতা দুর্বল করে এবং তাকে ভুল কাজে ঠেলে দেয়, সেটি এই সতর্কতার মধ্যে পড়ে। হাদিসটি মুসলিমকে নাম বা ধরন নিয়ে চালাকি না করতে শেখায়। মদ, মাদক বা যে কোনো নেশা—মূল বিচার হলো তা নেশা সৃষ্টি করে কি না। ঈমানদার জীবনে বিবেক রক্ষা করা বড় দায়িত্ব। এ কারণে নেশা নিয়ে মজা, পরীক্ষা বা কৌতূহল দেখানোও মুমিনের জন্য ঝুঁকিপূর্ণ আচরণ হতে পারে।"},"teachings":["নেশা সৃষ্টি করে এমন জিনিস থেকে বাঁচতে হবে।","হারামকে নাম বদলে বৈধ ভাবা ঠিক নয়।","বিবেক ও সংযম রক্ষা করা ঈমানি জীবনের অংশ।","হাদিসটি মাদক বিষয়ে সংক্ষিপ্ত কিন্তু স্পষ্ট নির্দেশ দেয়।"],"related_hadiths":[{"id":"3390","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3393","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E188" s="4" t="n"/>
@@ -4925,7 +4929,7 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিবেক নষ্টকারী বস্তুই মদ—হারামের স্পষ্ট মানদণ্ড","description":"$book_name$ $hadith_number$ - $chapter_name$. যা বিবেকের ক্ষতি করে তা মদের অন্তর্ভুক্ত, আর সব ধরনের মদ হারাম—হাদিসের সরল শিক্ষা।"},"heading":{"title":"মদ কাকে বলে: বিবেক নষ্টকারী সব নেশার হুকুম","description":"এই হাদিসে মদের পরিচয় খুব সহজভাবে এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, প্রত্যেক নেশাদার বস্তুই মদ, আর প্রত্যেক মদই হারাম। অর্থাৎ মদ শুধু আঙুর, খেজুর বা নির্দিষ্ট কোনো নামে সীমাবদ্ধ নয়। যে জিনিস পান, খাওয়া বা গ্রহণ করলে মানুষের বিবেক ও বোঝার ক্ষমতা নষ্ট হয়, সেটি খামর বা মদের হুকুমের মধ্যে পড়ে। এই হাদিস নামের চেয়ে প্রভাবকে গুরুত্ব দেয়। তাই কোনো বস্তু আধুনিক নাম, নতুন প্যাকেট বা ভিন্ন রূপে এলেও যদি তা নেশা সৃষ্টি করে, তাহলে মুমিনের জন্য সতর্কতা একই থাকে। মূল কথা: বিবেক আল্লাহর বড় নেয়ামত, একে নেশার হাতে তুলে দেওয়া যাবে না। তাই পরিবারে ও সমাজে মাদককে সাধারণ বিষয় বানানো নয়, বরং পরিষ্কারভাবে ভুল বলা দরকার।"},"teachings":["নেশা সৃষ্টি করলে নাম বদলালেও হুকুম বদলায় না।","বিবেক নষ্টকারী বস্তু থেকে দূরে থাকা জরুরি।","সব ধরনের মদ হারাম—হাদিসে স্পষ্ট বলা হয়েছে।","মুমিনের জন্য হালাল-হারামের মানদণ্ড প্রভাবের ওপরও নির্ভর করে।"],"related_hadiths":[{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3393","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3681","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিবেক নষ্টকারী বস্তুই মদ—হারামের স্পষ্ট মানদণ্ড","description":"$book_name$ $hadith_number$ - $chapter_name$. যা বিবেকের ক্ষতি করে তা মদের অন্তর্ভুক্ত, আর সব ধরনের মদ হারাম—হাদিসের সরল শিক্ষা।"},"heading":{"title":"মদ কাকে বলে: বিবেক নষ্টকারী সব নেশার হুকুম","description":"এই হাদিসে মদের পরিচয় খুব সহজভাবে এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, প্রত্যেক নেশাদার বস্তুই মদ, আর প্রত্যেক মদই হারাম। অর্থাৎ মদ শুধু আঙুর, খেজুর বা নির্দিষ্ট কোনো নামে সীমাবদ্ধ নয়। যে জিনিস পান, খাওয়া বা গ্রহণ করলে মানুষের বিবেক ও বোঝার ক্ষমতা নষ্ট হয়, সেটি খামর বা মদের হুকুমের মধ্যে পড়ে। এই হাদিস নামের চেয়ে প্রভাবকে গুরুত্ব দেয়। তাই কোনো বস্তু আধুনিক নাম, নতুন প্যাকেট বা ভিন্ন রূপে এলেও যদি তা নেশা সৃষ্টি করে, তাহলে মুমিনের জন্য সতর্কতা একই থাকে। মূল কথা: বিবেক আল্লাহর বড় নেয়ামত, একে নেশার হাতে তুলে দেওয়া যাবে না। তাই পরিবারে ও সমাজে মাদককে সাধারণ বিষয় বানানো নয়, বরং পরিষ্কারভাবে ভুল বলা দরকার।"},"teachings":["নেশা সৃষ্টি করলে নাম বদলালেও হুকুম বদলায় না।","বিবেক নষ্টকারী বস্তু থেকে দূরে থাকা জরুরি।","সব ধরনের মদ হারাম—হাদিসে স্পষ্ট বলা হয়েছে।","মুমিনের জন্য হালাল-হারামের মানদণ্ড প্রভাবের ওপরও নির্ভর করে।"],"related_hadiths":[{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3393","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E189" s="4" t="n"/>
@@ -4948,7 +4952,7 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বেশি নেশা হলে কমও হারাম—সতর্কতার হাদিস","description":"$book_name$ $hadith_number$ - $chapter_name$. যে বস্তু বেশি খেলে নেশা হয়, তার অল্প পরিমাণও হারাম—হারাম থেকে দূরে থাকার পরিষ্কার শিক্ষা।"},"heading":{"title":"যার বেশি নেশা আনে, তার কমও হারাম: মাদক বিষয়ে হাদিস","description":"এই হাদিসে নেশাদার বস্তু সম্পর্কে একটি গুরুত্বপূর্ণ নীতি এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে বস্তু বেশি পরিমাণে গ্রহণ করলে বিবেকের ক্ষতি হয় বা নেশা আসে, তার কম পরিমাণও হারাম। এর মানে হলো, “অল্প খেলে ক্ষতি নেই”—এমন অজুহাত দিয়ে নেশার দরজা খোলা যাবে না। ইসলাম মানুষের বিবেক, আত্মসম্মান ও ইবাদতকে সুরক্ষিত রাখতে চায়। তাই যে জিনিস বেশি হলে মানুষকে মাতাল করে, সেটির সামান্য অংশও নিরাপদ খেলার বিষয় নয়। এই হাদিস মাদক, অ্যালকোহল ও নেশা নিয়ে আপস না করার শিক্ষা দেয়। ছোট ছাড় অনেক সময় বড় বিপদের শুরু হতে পারে। এই নীতি মানুষকে সন্দেহজনক নেশাদার জিনিস থেকেও দূরে থাকতে সাহায্য করে।"},"teachings":["অল্প নেশাদার দ্রব্যকেও হালকা মনে করা ঠিক নয়।","যার বেশি নেশা আনে, তার কমও হারাম।","হারামের দরজা শুরুতেই বন্ধ করা নিরাপদ।","বিবেক রক্ষা করা মুমিনের গুরুত্বপূর্ণ দায়িত্ব।"],"related_hadiths":[{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3390","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3681","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বেশি নেশা হলে কমও হারাম—সতর্কতার হাদিস","description":"$book_name$ $hadith_number$ - $chapter_name$. যে বস্তু বেশি খেলে নেশা হয়, তার অল্প পরিমাণও হারাম—হারাম থেকে দূরে থাকার পরিষ্কার শিক্ষা।"},"heading":{"title":"যার বেশি নেশা আনে, তার কমও হারাম: মাদক বিষয়ে হাদিস","description":"এই হাদিসে নেশাদার বস্তু সম্পর্কে একটি গুরুত্বপূর্ণ নীতি এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে বস্তু বেশি পরিমাণে গ্রহণ করলে বিবেকের ক্ষতি হয় বা নেশা আসে, তার কম পরিমাণও হারাম। এর মানে হলো, “অল্প খেলে ক্ষতি নেই”—এমন অজুহাত দিয়ে নেশার দরজা খোলা যাবে না। ইসলাম মানুষের বিবেক, আত্মসম্মান ও ইবাদতকে সুরক্ষিত রাখতে চায়। তাই যে জিনিস বেশি হলে মানুষকে মাতাল করে, সেটির সামান্য অংশও নিরাপদ খেলার বিষয় নয়। এই হাদিস মাদক, অ্যালকোহল ও নেশা নিয়ে আপস না করার শিক্ষা দেয়। ছোট ছাড় অনেক সময় বড় বিপদের শুরু হতে পারে। এই নীতি মানুষকে সন্দেহজনক নেশাদার জিনিস থেকেও দূরে থাকতে সাহায্য করে।"},"teachings":["অল্প নেশাদার দ্রব্যকেও হালকা মনে করা ঠিক নয়।","যার বেশি নেশা আনে, তার কমও হারাম।","হারামের দরজা শুরুতেই বন্ধ করা নিরাপদ।","বিবেক রক্ষা করা মুমিনের গুরুত্বপূর্ণ দায়িত্ব।"],"related_hadiths":[{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3390","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E190" s="4" t="n"/>
@@ -4971,7 +4975,7 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে রবকে দেখা ও আমলের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে রবকে দেখা, নেয়ামতের জবাবদিহি ও অঙ্গ-প্রত্যঙ্গের সাক্ষ্য—এই হাদিসে সতর্কতা এসেছে।"},"heading":{"title":"কিয়ামতের দিন রবকে দেখা ও অঙ্গের সাক্ষ্যের শিক্ষা","description":"এই হাদিসে সাহাবীরা জিজ্ঞেস করেছেন, কিয়ামতের দিন তারা কি তাদের রবকে দেখতে পাবে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সূর্য ও পূর্ণিমার চাঁদ দেখার উদাহরণ দিয়ে বলেছেন, রবকে দেখতে অসুবিধা হবে না। এরপর তিনি বান্দাদের জবাবদিহির কথা বলেন। আল্লাহ বান্দাকে নিজের দেওয়া মর্যাদা, নেতৃত্ব, পরিবার ও নিয়ামতের কথা স্মরণ করাবেন। কেউ আল্লাহর সাক্ষাতের কথা অস্বীকার করেছিল বলে তাকে কঠিন পরিণতির কথা বলা হবে। আর এক ব্যক্তি নিজের ভালো কাজের কথা বললেও তার মুখে মোহর লাগিয়ে অঙ্গ-প্রত্যঙ্গকে সাক্ষ্য দিতে বলা হবে। হাদিসে তাকে মুনাফিক বলা হয়েছে। এই হাদিস নেয়ামত, হিসাব, মুনাফিকী এবং সত্য সাক্ষ্যের কথা মনে করায়।"},"teachings":["কিয়ামতের দিন রবকে দেখার বিষয়টি হাদিসে এসেছে।","আল্লাহর দেওয়া নিয়ামতের জন্য জবাবদিহি থাকবে।","মুখে দাবি করলেই যথেষ্ট নয়, কাজের সাক্ষ্যও আসবে।","মুনাফিকী আচরণ আল্লাহর ক্রোধের কারণ হতে পারে।"],"related_hadiths":[{"id":"2968","book_id":"2","label":"Sahih Muslim"},{"id":"7440","book_id":"1","label":"Sahih Bukhari"},{"id":"5555","book_id":"14","label":"Mishkat al-Masabih"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে রবকে দেখা ও আমলের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে রবকে দেখা, নেয়ামতের জবাবদিহি ও অঙ্গ-প্রত্যঙ্গের সাক্ষ্য—এই হাদিসে সতর্কতা এসেছে।"},"heading":{"title":"কিয়ামতের দিন রবকে দেখা ও অঙ্গের সাক্ষ্যের শিক্ষা","description":"এই হাদিসে সাহাবীরা জিজ্ঞেস করেছেন, কিয়ামতের দিন তারা কি তাদের রবকে দেখতে পাবে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সূর্য ও পূর্ণিমার চাঁদ দেখার উদাহরণ দিয়ে বলেছেন, রবকে দেখতে অসুবিধা হবে না। এরপর তিনি বান্দাদের জবাবদিহির কথা বলেন। আল্লাহ বান্দাকে নিজের দেওয়া মর্যাদা, নেতৃত্ব, পরিবার ও নিয়ামতের কথা স্মরণ করাবেন। কেউ আল্লাহর সাক্ষাতের কথা অস্বীকার করেছিল বলে তাকে কঠিন পরিণতির কথা বলা হবে। আর এক ব্যক্তি নিজের ভালো কাজের কথা বললেও তার মুখে মোহর লাগিয়ে অঙ্গ-প্রত্যঙ্গকে সাক্ষ্য দিতে বলা হবে। হাদিসে তাকে মুনাফিক বলা হয়েছে। এই হাদিস নেয়ামত, হিসাব, মুনাফিকী এবং সত্য সাক্ষ্যের কথা মনে করায়।"},"teachings":["কিয়ামতের দিন রবকে দেখার বিষয়টি হাদিসে এসেছে।","আল্লাহর দেওয়া নিয়ামতের জন্য জবাবদিহি থাকবে।","মুখে দাবি করলেই যথেষ্ট নয়, কাজের সাক্ষ্যও আসবে।","মুনাফিকী আচরণ আল্লাহর ক্রোধের কারণ হতে পারে।"],"related_hadiths":[{"id":"2968","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"7440","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5555","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E191" s="4" t="n"/>
@@ -4994,7 +4998,7 @@
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, মৃতপ্রাণী ও শূকরের মূল্য হারাম","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ মদ, মৃতপ্রাণী ও শূকর এবং এগুলোর মূল্য হারাম করেছেন—হারাম আয় থেকে বাঁচার শিক্ষা।"},"heading":{"title":"হারাম আয়: মদ ও নিষিদ্ধ বস্তুর মূল্য সম্পর্কে হাদিস","description":"এই হাদিসে শুধু মদ পান নয়, মদের মূল্য বা এর অর্থনৈতিক লেনদেনের দিকেও সতর্ক করা হয়েছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ নেশাদার দ্রব্য এবং তার মূল্য হারাম করেছেন। একইভাবে মৃতপ্রাণী ও তার মূল্য, শূকর ও তার মূল্যও হারাম করা হয়েছে। এখানে গুরুত্বপূর্ণ শিক্ষা হলো—কোনো বস্তু হারাম হলে তার ব্যবসা, মূল্য এবং লাভও সতর্কতার বিষয় হয়। মানুষ অনেক সময় নিজে না খেয়ে বিক্রি করে লাভ নেওয়াকে হালকা মনে করতে পারে। কিন্তু এই হাদিস জানায়, হারাম জিনিস থেকে অর্থ উপার্জনও নিরাপদ নয়। রিযিক পবিত্র রাখা ঈমানি জীবনের বড় অংশ। তাই আয়ের উৎস যাচাই করা এবং সন্দেহজনক লাভ থেকে বাঁচা একজন মুসলিমের নিত্যদিনের দায়িত্ব।"},"teachings":["মদ শুধু পান নয়, তার মূল্যও হারাম বলা হয়েছে।","হারাম বস্তু থেকে আয় নেওয়া থেকে বাঁচতে হবে।","রিযিক পবিত্র রাখা মুসলিম জীবনের গুরুত্বপূর্ণ কাজ।","মৃতপ্রাণী ও শূকরের মূল্য সম্পর্কেও হাদিসে সতর্কতা এসেছে।"],"related_hadiths":[{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"3681","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, মৃতপ্রাণী ও শূকরের মূল্য হারাম","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ মদ, মৃতপ্রাণী ও শূকর এবং এগুলোর মূল্য হারাম করেছেন—হারাম আয় থেকে বাঁচার শিক্ষা।"},"heading":{"title":"হারাম আয়: মদ ও নিষিদ্ধ বস্তুর মূল্য সম্পর্কে হাদিস","description":"এই হাদিসে শুধু মদ পান নয়, মদের মূল্য বা এর অর্থনৈতিক লেনদেনের দিকেও সতর্ক করা হয়েছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ নেশাদার দ্রব্য এবং তার মূল্য হারাম করেছেন। একইভাবে মৃতপ্রাণী ও তার মূল্য, শূকর ও তার মূল্যও হারাম করা হয়েছে। এখানে গুরুত্বপূর্ণ শিক্ষা হলো—কোনো বস্তু হারাম হলে তার ব্যবসা, মূল্য এবং লাভও সতর্কতার বিষয় হয়। মানুষ অনেক সময় নিজে না খেয়ে বিক্রি করে লাভ নেওয়াকে হালকা মনে করতে পারে। কিন্তু এই হাদিস জানায়, হারাম জিনিস থেকে অর্থ উপার্জনও নিরাপদ নয়। রিযিক পবিত্র রাখা ঈমানি জীবনের বড় অংশ। তাই আয়ের উৎস যাচাই করা এবং সন্দেহজনক লাভ থেকে বাঁচা একজন মুসলিমের নিত্যদিনের দায়িত্ব।"},"teachings":["মদ শুধু পান নয়, তার মূল্যও হারাম বলা হয়েছে।","হারাম বস্তু থেকে আয় নেওয়া থেকে বাঁচতে হবে।","রিযিক পবিত্র রাখা মুসলিম জীবনের গুরুত্বপূর্ণ কাজ।","মৃতপ্রাণী ও শূকরের মূল্য সম্পর্কেও হাদিসে সতর্কতা এসেছে।"],"related_hadiths":[{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E192" s="4" t="n"/>
@@ -5017,7 +5021,7 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, মৃতপ্রাণী, শূকর ও মূর্তি বিক্রি হারাম","description":"$book_name$ $hadith_number$ - $chapter_name$. মক্কা বিজয়ের বছরে নবীজি মদ, মৃতপ্রাণী, শূকর ও মূর্তির ক্রয়-বিক্রয় হারাম হওয়ার কথা বলেছেন।"},"heading":{"title":"হারাম ব্যবসা: মদ ও মূর্তি ক্রয়-বিক্রয় সম্পর্কে হাদিস","description":"এই হাদিসে মক্কা বিজয়ের বছরে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর একটি ঘোষণা এসেছে। তিনি বলেছেন, আল্লাহ মদ, মৃতপ্রাণী, শূকর এবং মূর্তির ক্রয়-বিক্রয় হারাম করেছেন। এখানে শিক্ষা শুধু কিছু জিনিস খাওয়া বা ব্যবহার না করার মধ্যে সীমাবদ্ধ নয়; বরং সেগুলোকে ব্যবসার পণ্য বানানো থেকেও বারণ করা হয়েছে। ইসলামে রিযিকের পবিত্রতা খুব গুরুত্বপূর্ণ। লাভ বেশি হলেই কোনো ব্যবসা ভালো হয়ে যায় না। হালাল-হারামের সীমা মানতে হয়। এই হাদিস ব্যবসায়ী, ক্রেতা ও সমাজ—সবার জন্য সতর্কতা: এমন পণ্য থেকে দূরে থাকা দরকার, যাকে আল্লাহ হারাম করেছেন। তাই ব্যবসায় সততা মানে শুধু ওজন ঠিক রাখা নয়, পণ্যটিও হালাল হওয়া। বিশেষ করে যে পণ্য মানুষের ঈমান, বিবেক বা তাওহীদের ক্ষতি করে, তা থেকে আয় করা মুমিনের জন্য নিরাপদ পথ নয়।"},"teachings":["হারাম জিনিস ব্যবসার পণ্য বানানো যায় না।","মদ, মৃতপ্রাণী, শূকর ও মূর্তির ক্রয়-বিক্রয় নিষিদ্ধ বলা হয়েছে।","লাভের চেয়ে হালাল রিযিক বেশি গুরুত্বপূর্ণ।","ব্যবসায়ও আল্লাহর সীমা মানা জরুরি।"],"related_hadiths":[{"id":"3485","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5590","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, মৃতপ্রাণী, শূকর ও মূর্তি বিক্রি হারাম","description":"$book_name$ $hadith_number$ - $chapter_name$. মক্কা বিজয়ের বছরে নবীজি মদ, মৃতপ্রাণী, শূকর ও মূর্তির ক্রয়-বিক্রয় হারাম হওয়ার কথা বলেছেন।"},"heading":{"title":"হারাম ব্যবসা: মদ ও মূর্তি ক্রয়-বিক্রয় সম্পর্কে হাদিস","description":"এই হাদিসে মক্কা বিজয়ের বছরে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর একটি ঘোষণা এসেছে। তিনি বলেছেন, আল্লাহ মদ, মৃতপ্রাণী, শূকর এবং মূর্তির ক্রয়-বিক্রয় হারাম করেছেন। এখানে শিক্ষা শুধু কিছু জিনিস খাওয়া বা ব্যবহার না করার মধ্যে সীমাবদ্ধ নয়; বরং সেগুলোকে ব্যবসার পণ্য বানানো থেকেও বারণ করা হয়েছে। ইসলামে রিযিকের পবিত্রতা খুব গুরুত্বপূর্ণ। লাভ বেশি হলেই কোনো ব্যবসা ভালো হয়ে যায় না। হালাল-হারামের সীমা মানতে হয়। এই হাদিস ব্যবসায়ী, ক্রেতা ও সমাজ—সবার জন্য সতর্কতা: এমন পণ্য থেকে দূরে থাকা দরকার, যাকে আল্লাহ হারাম করেছেন। তাই ব্যবসায় সততা মানে শুধু ওজন ঠিক রাখা নয়, পণ্যটিও হালাল হওয়া। বিশেষ করে যে পণ্য মানুষের ঈমান, বিবেক বা তাওহীদের ক্ষতি করে, তা থেকে আয় করা মুমিনের জন্য নিরাপদ পথ নয়।"},"teachings":["হারাম জিনিস ব্যবসার পণ্য বানানো যায় না।","মদ, মৃতপ্রাণী, শূকর ও মূর্তির ক্রয়-বিক্রয় নিষিদ্ধ বলা হয়েছে।","লাভের চেয়ে হালাল রিযিক বেশি গুরুত্বপূর্ণ।","ব্যবসায়ও আল্লাহর সীমা মানা জরুরি।"],"related_hadiths":[{"id":"3485","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E193" s="4" t="n"/>
@@ -5040,7 +5044,7 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপান, পিতামাতার অবাধ্যতা ও খোটা দানের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদে আসক্তি, পিতা-মাতার অবাধ্যতা ও দান করে খোটা দেওয়ার ভয়াবহ পরিণতি সম্পর্কে সতর্কতা।"},"heading":{"title":"মদপানকারী, অবাধ্য সন্তান ও খোটা দানকারী সম্পর্কে হাদিস","description":"এই হাদিসে তিনটি কাজের বিষয়ে কঠোর সতর্কতা এসেছে: নেশাদার দ্রব্য পান করা, পিতা-মাতার অবাধ্য হওয়া এবং দান করে খোটা দেওয়া। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, এ ধরনের লোক জান্নাতে যাবে না—হাদিসের ভাষা অত্যন্ত সতর্কতামূলক। এর অর্থ বুঝতে আল্লাহর রহমত, তাওবা এবং অন্যান্য শরঈ বিষয় আলাদা আলোচনার বিষয়; তবে এই হাদিসের সরাসরি শিক্ষা হলো, এসব কাজ খুব ভয়াবহ। মদ মানুষের বিবেক নষ্ট করে, পিতা-মাতার অবাধ্যতা সম্পর্ক ভেঙে দেয়, আর খোটা দান সদকার সৌন্দর্য নষ্ট করে। তাই মুমিনের উচিত এসব কাজ থেকে দূরে থাকা এবং ভুল হলে দ্রুত তাওবার পথে ফেরা। তাই এই তিনটি বিষয়ে পরিবারে নিয়মিত নসিহত, আত্মসমালোচনা এবং সংশোধনের পরিবেশ থাকা দরকার।"},"teachings":["মদে আসক্তি ভয়াবহ গোনাহের দিকে নিয়ে যেতে পারে।","পিতা-মাতার অবাধ্যতা থেকে সতর্ক থাকতে হবে।","দান করে খোটা দেওয়া দানের সৌন্দর্য নষ্ট করে।","হাদিসটি তিনটি গুরুতর আচরণ থেকে বাঁচার শিক্ষা দেয়।"],"related_hadiths":[{"id":"5975","book_id":"1","label":"Sahih Bukhari"},{"id":"3371","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপান, পিতামাতার অবাধ্যতা ও খোটা দানের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদে আসক্তি, পিতা-মাতার অবাধ্যতা ও দান করে খোটা দেওয়ার ভয়াবহ পরিণতি সম্পর্কে সতর্কতা।"},"heading":{"title":"মদপানকারী, অবাধ্য সন্তান ও খোটা দানকারী সম্পর্কে হাদিস","description":"এই হাদিসে তিনটি কাজের বিষয়ে কঠোর সতর্কতা এসেছে: নেশাদার দ্রব্য পান করা, পিতা-মাতার অবাধ্য হওয়া এবং দান করে খোটা দেওয়া। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, এ ধরনের লোক জান্নাতে যাবে না—হাদিসের ভাষা অত্যন্ত সতর্কতামূলক। এর অর্থ বুঝতে আল্লাহর রহমত, তাওবা এবং অন্যান্য শরঈ বিষয় আলাদা আলোচনার বিষয়; তবে এই হাদিসের সরাসরি শিক্ষা হলো, এসব কাজ খুব ভয়াবহ। মদ মানুষের বিবেক নষ্ট করে, পিতা-মাতার অবাধ্যতা সম্পর্ক ভেঙে দেয়, আর খোটা দান সদকার সৌন্দর্য নষ্ট করে। তাই মুমিনের উচিত এসব কাজ থেকে দূরে থাকা এবং ভুল হলে দ্রুত তাওবার পথে ফেরা। তাই এই তিনটি বিষয়ে পরিবারে নিয়মিত নসিহত, আত্মসমালোচনা এবং সংশোধনের পরিবেশ থাকা দরকার।"},"teachings":["মদে আসক্তি ভয়াবহ গোনাহের দিকে নিয়ে যেতে পারে।","পিতা-মাতার অবাধ্যতা থেকে সতর্ক থাকতে হবে।","দান করে খোটা দেওয়া দানের সৌন্দর্য নষ্ট করে।","হাদিসটি তিনটি গুরুতর আচরণ থেকে বাঁচার শিক্ষা দেয়।"],"related_hadiths":[{"id":"5975","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3371","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E194" s="4" t="n"/>
@@ -5063,7 +5067,7 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ পান করলে ৪০ দিনের অসন্তুষ্টির সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপানের পর আল্লাহর অসন্তুষ্টির কথা এসেছে, যা মাদক থেকে দূরে থাকার কঠোর সতর্কবার্তা।"},"heading":{"title":"মদ পান করলে ৪০ দিন আল্লাহর অসন্তুষ্টি: হাদিসের শিক্ষা","description":"এই হাদিসে মদপানের পরিণতি নিয়ে খুব কঠোর সতর্কতা এসেছে। বলা হয়েছে, যে ব্যক্তি মদ পান করবে, আল্লাহ তার উপর ৪০ দিন সন্তুষ্ট হবেন না। এখানে সংখ্যাটি হাদিসের সরাসরি ভাষায় এসেছে, তাই বিষয়টি হালকা করে দেখার সুযোগ নেই। মদ শুধু শরীরের ক্ষতি নয়; এটি বান্দার আল্লাহর সাথে সম্পর্ক, ইবাদতের মনোভাব এবং নৈতিক শক্তিকেও আঘাত করে। হাদিসটি আমাদের শেখায়, নেশা সাময়িক আনন্দের বিষয় নয়; এর আধ্যাত্মিক ক্ষতিও ভয়াবহ। তাই মুমিনের উচিত মদ থেকে দূরে থাকা, এমন সঙ্গ এড়িয়ে চলা যা তাকে মদের দিকে টানে, এবং ভুল হলে দেরি না করে তাওবার পথ ধরা। এ কারণে মদ থেকে বাঁচা শুধু ব্যক্তিগত স্বাস্থ্যরক্ষা নয়, আল্লাহর সন্তুষ্টি খোঁজারও অংশ।"},"teachings":["মদপান আল্লাহর অসন্তুষ্টির কারণ হতে পারে।","৪০ দিনের সতর্কতা হাদিসে সরাসরি এসেছে।","নেশা ঈমানি জীবনের জন্য ক্ষতিকর।","ভুল হলে তাওবার দিকে দ্রুত ফিরতে হবে।"],"related_hadiths":[{"id":"3371","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5578","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ পান করলে ৪০ দিনের অসন্তুষ্টির সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপানের পর আল্লাহর অসন্তুষ্টির কথা এসেছে, যা মাদক থেকে দূরে থাকার কঠোর সতর্কবার্তা।"},"heading":{"title":"মদ পান করলে ৪০ দিন আল্লাহর অসন্তুষ্টি: হাদিসের শিক্ষা","description":"এই হাদিসে মদপানের পরিণতি নিয়ে খুব কঠোর সতর্কতা এসেছে। বলা হয়েছে, যে ব্যক্তি মদ পান করবে, আল্লাহ তার উপর ৪০ দিন সন্তুষ্ট হবেন না। এখানে সংখ্যাটি হাদিসের সরাসরি ভাষায় এসেছে, তাই বিষয়টি হালকা করে দেখার সুযোগ নেই। মদ শুধু শরীরের ক্ষতি নয়; এটি বান্দার আল্লাহর সাথে সম্পর্ক, ইবাদতের মনোভাব এবং নৈতিক শক্তিকেও আঘাত করে। হাদিসটি আমাদের শেখায়, নেশা সাময়িক আনন্দের বিষয় নয়; এর আধ্যাত্মিক ক্ষতিও ভয়াবহ। তাই মুমিনের উচিত মদ থেকে দূরে থাকা, এমন সঙ্গ এড়িয়ে চলা যা তাকে মদের দিকে টানে, এবং ভুল হলে দেরি না করে তাওবার পথ ধরা। এ কারণে মদ থেকে বাঁচা শুধু ব্যক্তিগত স্বাস্থ্যরক্ষা নয়, আল্লাহর সন্তুষ্টি খোঁজারও অংশ।"},"teachings":["মদপান আল্লাহর অসন্তুষ্টির কারণ হতে পারে।","৪০ দিনের সতর্কতা হাদিসে সরাসরি এসেছে।","নেশা ঈমানি জীবনের জন্য ক্ষতিকর।","ভুল হলে তাওবার দিকে দ্রুত ফিরতে হবে।"],"related_hadiths":[{"id":"3371","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"5578","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E195" s="4" t="n"/>
@@ -5086,7 +5090,7 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপানের শাস্তি ও সমাজে হারাম ঠেকানোর শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি মদপানকারীকে জুতা ও বেত দিয়ে ৪০ বার শাস্তি দিতেন; পরে উমর (রাঃ) ৮০ বেত্রাঘাত করেন।"},"heading":{"title":"মদপানের শাস্তি: শরীয়তী সতর্কতা ও সামাজিক শিক্ষা","description":"এই হাদিসে মদপানের শরীয়তী শাস্তির একটি ঘটনা এসেছে। আনাস (রাঃ) বর্ণনা করেছেন, রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) নেশাদার দ্রব্য পানকারীকে জুতা ও বেতের মাধ্যমে ৪০ বার মারতেন। পরে উমর (রাঃ)-এর সময়ে যখন নেশাদার দ্রব্য পানকারীদের সংখ্যা বেড়ে যায়, তিনি ৮০ বেত্রাঘাত করতেন বলে বর্ণনায় এসেছে। এই হাদিসের আলোচনা বিচার ও শাস্তির বিষয়, তাই তা ব্যক্তিগতভাবে প্রয়োগের বিষয় নয়; এটি দায়িত্বশীল বিচারব্যবস্থার সঙ্গে সম্পর্কিত। সরাসরি শিক্ষা হলো, ইসলাম মদপানকে ব্যক্তিগত পছন্দ হিসেবে দেখে না; বরং এটি ব্যক্তি, পরিবার ও সমাজের ক্ষতি ডেকে আনতে পারে। তাই মাদক থেকে দূরে থাকা জরুরি। তাই পরিবার, শিক্ষা ও সমাজে মাদকবিরোধী সচেতনতা গড়ে তোলা এই হাদিসের সাথে মানানসই শিক্ষা।"},"teachings":["মদপানকে শরীয়তে গুরুতর অপরাধ হিসেবে দেখা হয়েছে।","শাস্তির বিষয় দায়িত্বশীল বিচারব্যবস্থার সাথে সম্পর্কিত।","সমাজে মাদক ছড়ানো বড় ক্ষতির কারণ হতে পারে।","মাদক থেকে বাঁচা ব্যক্তি ও সমাজ উভয়ের জন্য দরকার।"],"related_hadiths":[{"id":"6773","book_id":"1","label":"Sahih Bukhari"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"3681","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপানের শাস্তি ও সমাজে হারাম ঠেকানোর শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি মদপানকারীকে জুতা ও বেত দিয়ে ৪০ বার শাস্তি দিতেন; পরে উমর (রাঃ) ৮০ বেত্রাঘাত করেন।"},"heading":{"title":"মদপানের শাস্তি: শরীয়তী সতর্কতা ও সামাজিক শিক্ষা","description":"এই হাদিসে মদপানের শরীয়তী শাস্তির একটি ঘটনা এসেছে। আনাস (রাঃ) বর্ণনা করেছেন, রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) নেশাদার দ্রব্য পানকারীকে জুতা ও বেতের মাধ্যমে ৪০ বার মারতেন। পরে উমর (রাঃ)-এর সময়ে যখন নেশাদার দ্রব্য পানকারীদের সংখ্যা বেড়ে যায়, তিনি ৮০ বেত্রাঘাত করতেন বলে বর্ণনায় এসেছে। এই হাদিসের আলোচনা বিচার ও শাস্তির বিষয়, তাই তা ব্যক্তিগতভাবে প্রয়োগের বিষয় নয়; এটি দায়িত্বশীল বিচারব্যবস্থার সঙ্গে সম্পর্কিত। সরাসরি শিক্ষা হলো, ইসলাম মদপানকে ব্যক্তিগত পছন্দ হিসেবে দেখে না; বরং এটি ব্যক্তি, পরিবার ও সমাজের ক্ষতি ডেকে আনতে পারে। তাই মাদক থেকে দূরে থাকা জরুরি। তাই পরিবার, শিক্ষা ও সমাজে মাদকবিরোধী সচেতনতা গড়ে তোলা এই হাদিসের সাথে মানানসই শিক্ষা।"},"teachings":["মদপানকে শরীয়তে গুরুতর অপরাধ হিসেবে দেখা হয়েছে।","শাস্তির বিষয় দায়িত্বশীল বিচারব্যবস্থার সাথে সম্পর্কিত।","সমাজে মাদক ছড়ানো বড় ক্ষতির কারণ হতে পারে।","মাদক থেকে বাঁচা ব্যক্তি ও সমাজ উভয়ের জন্য দরকার।"],"related_hadiths":[{"id":"6773","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E196" s="4" t="n"/>
@@ -5109,7 +5113,7 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যেনা, রেশম, মদ ও বাদ্যযন্ত্রকে হালাল ভাবার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি বলেছেন, কিছু লোক যেনা, রেশম, মদ ও বাদ্যযন্ত্রকে হালাল মনে করবে—এটি গুরুতর সতর্কতা।"},"heading":{"title":"হারামকে হালাল মনে করা: মদ ও বাদ্যযন্ত্র সম্পর্কে হাদিস","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ভবিষ্যতের একটি বিপদের কথা বলেছেন। তাঁর উম্মতের কিছু লোক যেনা, রেশম, নেশাদার দ্রব্য এবং গান-বাজনা-বাদ্যযন্ত্রকে হালাল মনে করবে। এখানে সবচেয়ে বড় সতর্কতা হলো—হারামকে শুধু করা নয়, বরং সেটিকে হালাল মনে করা। মানুষ কখনও নিজের পছন্দ, সমাজের চাপ বা আনন্দের নামে সীমা বদলাতে চায়। কিন্তু হাদিসটি জানায়, আল্লাহর বিধানকে নিজের ইচ্ছামতো বদলানো বড় ঝুঁকির বিষয়। মদ ও বাদ্যযন্ত্র নিয়ে এই হাদিসটি বাংলায় অনেক খোঁজা হয়, কারণ এটি সরাসরি চারটি বড় সামাজিক ফিতনার নাম উল্লেখ করে। মুমিনের কাজ হলো সত্যকে সত্য বলা এবং হারাম থেকে বাঁচা। তাই মুমিনের উচিত জনপ্রিয় সংস্কৃতি নয়, হাদিসের নির্দেশকে নিজের মাপকাঠি বানানো।"},"teachings":["হারামকে হালাল মনে করা গুরুতর সতর্কতার বিষয়।","মদ ও বাদ্যযন্ত্র হাদিসে একসাথে উল্লেখ হয়েছে।","সমাজের প্রচলন দিয়ে আল্লাহর বিধান বদলায় না।","নিজের পছন্দের ওপর দ্বীনের নির্দেশকে প্রাধান্য দিতে হবে।"],"related_hadiths":[{"id":"4924","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"80","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যেনা, রেশম, মদ ও বাদ্যযন্ত্রকে হালাল ভাবার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি বলেছেন, কিছু লোক যেনা, রেশম, মদ ও বাদ্যযন্ত্রকে হালাল মনে করবে—এটি গুরুতর সতর্কতা।"},"heading":{"title":"হারামকে হালাল মনে করা: মদ ও বাদ্যযন্ত্র সম্পর্কে হাদিস","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ভবিষ্যতের একটি বিপদের কথা বলেছেন। তাঁর উম্মতের কিছু লোক যেনা, রেশম, নেশাদার দ্রব্য এবং গান-বাজনা-বাদ্যযন্ত্রকে হালাল মনে করবে। এখানে সবচেয়ে বড় সতর্কতা হলো—হারামকে শুধু করা নয়, বরং সেটিকে হালাল মনে করা। মানুষ কখনও নিজের পছন্দ, সমাজের চাপ বা আনন্দের নামে সীমা বদলাতে চায়। কিন্তু হাদিসটি জানায়, আল্লাহর বিধানকে নিজের ইচ্ছামতো বদলানো বড় ঝুঁকির বিষয়। মদ ও বাদ্যযন্ত্র নিয়ে এই হাদিসটি বাংলায় অনেক খোঁজা হয়, কারণ এটি সরাসরি চারটি বড় সামাজিক ফিতনার নাম উল্লেখ করে। মুমিনের কাজ হলো সত্যকে সত্য বলা এবং হারাম থেকে বাঁচা। তাই মুমিনের উচিত জনপ্রিয় সংস্কৃতি নয়, হাদিসের নির্দেশকে নিজের মাপকাঠি বানানো।"},"teachings":["হারামকে হালাল মনে করা গুরুতর সতর্কতার বিষয়।","মদ ও বাদ্যযন্ত্র হাদিসে একসাথে উল্লেখ হয়েছে।","সমাজের প্রচলন দিয়ে আল্লাহর বিধান বদলায় না।","নিজের পছন্দের ওপর দ্বীনের নির্দেশকে প্রাধান্য দিতে হবে।"],"related_hadiths":[{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E197" s="4" t="n"/>
@@ -5132,7 +5136,7 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, জুয়া ও বাদ্যযন্ত্র হারাম হওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ মদ, জুয়া ও বাদ্যযন্ত্র হারাম করেছেন—এ হাদিস হারাম আনন্দ থেকে বাঁচার শিক্ষা দেয়।"},"heading":{"title":"মদ, জুয়া ও বাদ্যযন্ত্র হারাম: হাদিসের সরল ব্যাখ্যা","description":"এই হাদিসে তিনটি বিষয় একসাথে এসেছে: মদ, জুয়া এবং বাদ্যযন্ত্র। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ তা‘আলা এগুলো হারাম করেছেন। মদ বিবেক নষ্ট করে, জুয়া মানুষকে লোভ ও ক্ষতির পথে নেয়, আর বাদ্যযন্ত্র সম্পর্কে এখানে নিষেধ এসেছে। হাদিসটি আমাদের শেখায়, আনন্দ বা লাভের নামে এমন কাজ করা ঠিক নয় যা আল্লাহ হারাম করেছেন। অনেক সময় মানুষ বলে, “শুধু বিনোদন” বা “শুধু খেলা”; কিন্তু মুমিনের কাছে হালাল-হারামের সীমা বেশি গুরুত্বপূর্ণ। এই হাদিস সামাজিক জীবন, অর্থ, অবসর এবং বিনোদনে আল্লাহভীতির শিক্ষা দেয়। তাই নিজের আয়, খেলা, আনন্দ ও অবসর—সব ক্ষেত্রেই আল্লাহর ভয় রাখার প্রয়োজন আছে। এতে বোঝা যায়, দ্বীন শুধু ইবাদতের জায়গায় নয়; মানুষের অভ্যাস, লেনদেন ও বিনোদনের ক্ষেত্রেও পথ দেখায়।"},"teachings":["মদ, জুয়া ও বাদ্যযন্ত্র থেকে সতর্ক থাকার নির্দেশ এসেছে।","বিনোদন হলেও হারামের সীমা মানতে হবে।","জুয়া লোভ ও ক্ষতির পথ খুলে দিতে পারে।","আল্লাহর বিধানকে আনন্দের অজুহাতে হালকা করা ঠিক নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"4924","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, জুয়া ও বাদ্যযন্ত্র হারাম হওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ মদ, জুয়া ও বাদ্যযন্ত্র হারাম করেছেন—এ হাদিস হারাম আনন্দ থেকে বাঁচার শিক্ষা দেয়।"},"heading":{"title":"মদ, জুয়া ও বাদ্যযন্ত্র হারাম: হাদিসের সরল ব্যাখ্যা","description":"এই হাদিসে তিনটি বিষয় একসাথে এসেছে: মদ, জুয়া এবং বাদ্যযন্ত্র। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ তা‘আলা এগুলো হারাম করেছেন। মদ বিবেক নষ্ট করে, জুয়া মানুষকে লোভ ও ক্ষতির পথে নেয়, আর বাদ্যযন্ত্র সম্পর্কে এখানে নিষেধ এসেছে। হাদিসটি আমাদের শেখায়, আনন্দ বা লাভের নামে এমন কাজ করা ঠিক নয় যা আল্লাহ হারাম করেছেন। অনেক সময় মানুষ বলে, “শুধু বিনোদন” বা “শুধু খেলা”; কিন্তু মুমিনের কাছে হালাল-হারামের সীমা বেশি গুরুত্বপূর্ণ। এই হাদিস সামাজিক জীবন, অর্থ, অবসর এবং বিনোদনে আল্লাহভীতির শিক্ষা দেয়। তাই নিজের আয়, খেলা, আনন্দ ও অবসর—সব ক্ষেত্রেই আল্লাহর ভয় রাখার প্রয়োজন আছে। এতে বোঝা যায়, দ্বীন শুধু ইবাদতের জায়গায় নয়; মানুষের অভ্যাস, লেনদেন ও বিনোদনের ক্ষেত্রেও পথ দেখায়।"},"teachings":["মদ, জুয়া ও বাদ্যযন্ত্র থেকে সতর্ক থাকার নির্দেশ এসেছে।","বিনোদন হলেও হারামের সীমা মানতে হবে।","জুয়া লোভ ও ক্ষতির পথ খুলে দিতে পারে।","আল্লাহর বিধানকে আনন্দের অজুহাতে হালকা করা ঠিক নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E198" s="4" t="n"/>
@@ -5155,7 +5159,7 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গায়িকা নর্তকী, গান-বাজনা ও হারাম উপার্জন","description":"$book_name$ $hadith_number$ - $chapter_name$. গায়িকা-নর্তকী কেনাবেচা, গান-বাজনা শেখানো এবং এ পথের উপার্জন সম্পর্কে কঠোর নিষেধ এসেছে।"},"heading":{"title":"গায়িকা নর্তকী ও গান-বাজনার উপার্জন সম্পর্কে হাদিস","description":"এই হাদিসে গায়িকা নর্তকীদের কেনাবেচা, তাদের গান-বাজনা ও বাদ্যযন্ত্র শেখানো এবং তাদের উপার্জন সম্পর্কে নিষেধ এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাদের বিক্রি করো না, ক্রয় করো না, তাদের গান-বাজনা ও বাদ্যযন্ত্র শেখিও না, এবং তাদের উপার্জন হারাম। এখানে মূল শিক্ষা হলো, শুধু নিজের কাজ নয়, হারামের আয়োজন, প্রশিক্ষণ ও আয়ের পথ থেকেও বাঁচতে হবে। কোনো কাজ যদি মানুষকে অশ্লীলতা, নাচ-গান বা হারাম বিনোদনের দিকে নেয়, তবে সেটিকে পেশা বানানো নিরাপদ নয়। হাদিসটি উপার্জনকে হালাল রাখার এবং বিনোদনের নামে সীমা না ভাঙার শিক্ষা দেয়। তাই শিল্প, পেশা বা বিনোদনের নামে এমন পথ নেওয়া যাবে না যা হারামের দিকে টেনে নেয়।"},"teachings":["হারাম বিনোদনের আয়োজন থেকেও দূরে থাকা দরকার।","গান-বাজনা শেখানো ও এর আয় সম্পর্কে নিষেধ এসেছে।","উপার্জন হালাল রাখা ঈমানি জীবনের অংশ।","নিজে না করলেও হারামের সহায়তা থেকে সতর্ক থাকতে হবে।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"4924","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গায়িকা নর্তকী, গান-বাজনা ও হারাম উপার্জন","description":"$book_name$ $hadith_number$ - $chapter_name$. গায়িকা-নর্তকী কেনাবেচা, গান-বাজনা শেখানো এবং এ পথের উপার্জন সম্পর্কে কঠোর নিষেধ এসেছে।"},"heading":{"title":"গায়িকা নর্তকী ও গান-বাজনার উপার্জন সম্পর্কে হাদিস","description":"এই হাদিসে গায়িকা নর্তকীদের কেনাবেচা, তাদের গান-বাজনা ও বাদ্যযন্ত্র শেখানো এবং তাদের উপার্জন সম্পর্কে নিষেধ এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাদের বিক্রি করো না, ক্রয় করো না, তাদের গান-বাজনা ও বাদ্যযন্ত্র শেখিও না, এবং তাদের উপার্জন হারাম। এখানে মূল শিক্ষা হলো, শুধু নিজের কাজ নয়, হারামের আয়োজন, প্রশিক্ষণ ও আয়ের পথ থেকেও বাঁচতে হবে। কোনো কাজ যদি মানুষকে অশ্লীলতা, নাচ-গান বা হারাম বিনোদনের দিকে নেয়, তবে সেটিকে পেশা বানানো নিরাপদ নয়। হাদিসটি উপার্জনকে হালাল রাখার এবং বিনোদনের নামে সীমা না ভাঙার শিক্ষা দেয়। তাই শিল্প, পেশা বা বিনোদনের নামে এমন পথ নেওয়া যাবে না যা হারামের দিকে টেনে নেয়।"},"teachings":["হারাম বিনোদনের আয়োজন থেকেও দূরে থাকা দরকার।","গান-বাজনা শেখানো ও এর আয় সম্পর্কে নিষেধ এসেছে।","উপার্জন হালাল রাখা ঈমানি জীবনের অংশ।","নিজে না করলেও হারামের সহায়তা থেকে সতর্ক থাকতে হবে।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E199" s="4" t="n"/>
@@ -5178,7 +5182,7 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বাদ্যযন্ত্রের শব্দ থেকে বাঁচার চেষ্টা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইবনু উমর (রাঃ) বাদ্যযন্ত্রের শব্দ শুনে কানে আঙুল দিলেন এবং নবীজির একই আমলের কথা জানালেন।"},"heading":{"title":"বাদ্যযন্ত্রের শব্দ থেকে দূরে থাকা: ইবনু উমর (রাঃ)-এর বর্ণনা","description":"এই হাদিসে একটি বাস্তব ঘটনা এসেছে। ইবনু উমর (রাঃ) বাদ্যযন্ত্রের শব্দ শুনে দুই কানে দুই আঙুল ঢুকিয়ে রাস্তা থেকে সরে গেলেন। পরে নাফে‘কে জিজ্ঞেস করলেন, তিনি কিছু শুনতে পাচ্ছেন কি না। যখন নাফে‘ বললেন, না, তখন তিনি আঙুল বের করলেন এবং জানালেন যে তিনি একদা রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর সঙ্গে ছিলেন; নবীজি এমন শব্দ শুনে একই কাজ করেছিলেন। হাদিসের সঙ্গে দেওয়া ব্যাখ্যায়ও বলা হয়েছে, গান-বাজনা ও বাদ্যযন্ত্রের শব্দ যেন কানে না আসে, সে জন্য সম্ভবপর চেষ্টা করতে হবে। তাই শিক্ষা হলো, হারাম শব্দের পরিবেশ এলে সাধ্যের মধ্যে সরে যাওয়া বা বাঁচার চেষ্টা করা। এতে বোঝা যায়, গুনাহ থেকে বাঁচা শুধু মনে অপছন্দ করা নয়; অনেক সময় বাস্তব পদক্ষেপও দরকার।"},"teachings":["বাদ্যযন্ত্রের শব্দ থেকে বাঁচার চেষ্টা করা উচিত।","সাহাবিরা নবীজির আমল দেখে তা অনুসরণ করতেন।","হারাম পরিবেশ এলে সাধ্যের মধ্যে সরে যাওয়া ভালো।","শুধু শোনা নয়, শোনার পরিবেশ থেকেও সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"},{"id":"80","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বাদ্যযন্ত্রের শব্দ থেকে বাঁচার চেষ্টা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইবনু উমর (রাঃ) বাদ্যযন্ত্রের শব্দ শুনে কানে আঙুল দিলেন এবং নবীজির একই আমলের কথা জানালেন।"},"heading":{"title":"বাদ্যযন্ত্রের শব্দ থেকে দূরে থাকা: ইবনু উমর (রাঃ)-এর বর্ণনা","description":"এই হাদিসে একটি বাস্তব ঘটনা এসেছে। ইবনু উমর (রাঃ) বাদ্যযন্ত্রের শব্দ শুনে দুই কানে দুই আঙুল ঢুকিয়ে রাস্তা থেকে সরে গেলেন। পরে নাফে‘কে জিজ্ঞেস করলেন, তিনি কিছু শুনতে পাচ্ছেন কি না। যখন নাফে‘ বললেন, না, তখন তিনি আঙুল বের করলেন এবং জানালেন যে তিনি একদা রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর সঙ্গে ছিলেন; নবীজি এমন শব্দ শুনে একই কাজ করেছিলেন। হাদিসের সঙ্গে দেওয়া ব্যাখ্যায়ও বলা হয়েছে, গান-বাজনা ও বাদ্যযন্ত্রের শব্দ যেন কানে না আসে, সে জন্য সম্ভবপর চেষ্টা করতে হবে। তাই শিক্ষা হলো, হারাম শব্দের পরিবেশ এলে সাধ্যের মধ্যে সরে যাওয়া বা বাঁচার চেষ্টা করা। এতে বোঝা যায়, গুনাহ থেকে বাঁচা শুধু মনে অপছন্দ করা নয়; অনেক সময় বাস্তব পদক্ষেপও দরকার।"},"teachings":["বাদ্যযন্ত্রের শব্দ থেকে বাঁচার চেষ্টা করা উচিত।","সাহাবিরা নবীজির আমল দেখে তা অনুসরণ করতেন।","হারাম পরিবেশ এলে সাধ্যের মধ্যে সরে যাওয়া ভালো।","শুধু শোনা নয়, শোনার পরিবেশ থেকেও সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E200" s="4" t="n"/>
@@ -5201,7 +5205,7 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, গায়িকা ও বাদ্যযন্ত্রে মত্ততার গজব","description":"$book_name$ $hadith_number$ - $chapter_name$. মদ, গায়িকা নিয়ে নাচ-গান ও বাদ্যযন্ত্রে ডুবে থাকার কারণে তিন ধরনের ভয়াবহ বিপদের সতর্কতা।"},"heading":{"title":"মদ, নাচ-গান ও বাদ্যযন্ত্র: ভয়াবহ বিপদের হাদিস","description":"এই হাদিসটি মদ, গায়িকা এবং বাদ্যযন্ত্রের ফিতনা সম্পর্কে স্পষ্ট সতর্কতা দেয়। নবী করীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যখন তাঁর উম্মত নেশাদার দ্রব্য পান করবে, গায়িকাদের নিয়ে নাচ-গানে মত্ত হবে এবং বাদ্যযন্ত্র নিয়ে ব্যস্ত হবে, তখন তিনটি ভয়াবহ বিপদ নেমে আসবে। সেগুলো হলো—ভূমি ধসে যাওয়া, উপর থেকে বা কোনো জাতির পক্ষ থেকে যুলুম চাপিয়ে দেওয়া, এবং অনেকের আকার-আকৃতি বিকৃত করা। হাদিসের ভাষা কঠোর, তাই এর বার্তাও গভীর: হারাম আনন্দকে সাধারণ বানানো মুমিনের পথ নয়। মদ, নাচ-গান ও বাদ্যযন্ত্রের প্রতি আসক্তি থেকে নিজেকে এবং পরিবারকে সতর্ক রাখা দরকার। তাই এই হাদিস শুধু ভয় দেখায় না; এটি মানুষকে নিজের জীবনযাপন নতুন করে যাচাই করতেও ডাকে।"},"teachings":["মদপান ও হারাম বিনোদন বড় বিপদের কারণ হতে পারে।","গায়িকা ও নাচ-গানে মত্ততা থেকে সতর্ক করা হয়েছে।","বাদ্যযন্ত্রে ব্যস্ততা হাদিসে নিন্দিতভাবে এসেছে।","হারামকে আনন্দের নামে স্বাভাবিক বানানো উচিত নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","label":"Sahih Bukhari"},{"id":"4924","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3388","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, গায়িকা ও বাদ্যযন্ত্রে মত্ততার গজব","description":"$book_name$ $hadith_number$ - $chapter_name$. মদ, গায়িকা নিয়ে নাচ-গান ও বাদ্যযন্ত্রে ডুবে থাকার কারণে তিন ধরনের ভয়াবহ বিপদের সতর্কতা।"},"heading":{"title":"মদ, নাচ-গান ও বাদ্যযন্ত্র: ভয়াবহ বিপদের হাদিস","description":"এই হাদিসটি মদ, গায়িকা এবং বাদ্যযন্ত্রের ফিতনা সম্পর্কে স্পষ্ট সতর্কতা দেয়। নবী করীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যখন তাঁর উম্মত নেশাদার দ্রব্য পান করবে, গায়িকাদের নিয়ে নাচ-গানে মত্ত হবে এবং বাদ্যযন্ত্র নিয়ে ব্যস্ত হবে, তখন তিনটি ভয়াবহ বিপদ নেমে আসবে। সেগুলো হলো—ভূমি ধসে যাওয়া, উপর থেকে বা কোনো জাতির পক্ষ থেকে যুলুম চাপিয়ে দেওয়া, এবং অনেকের আকার-আকৃতি বিকৃত করা। হাদিসের ভাষা কঠোর, তাই এর বার্তাও গভীর: হারাম আনন্দকে সাধারণ বানানো মুমিনের পথ নয়। মদ, নাচ-গান ও বাদ্যযন্ত্রের প্রতি আসক্তি থেকে নিজেকে এবং পরিবারকে সতর্ক রাখা দরকার। তাই এই হাদিস শুধু ভয় দেখায় না; এটি মানুষকে নিজের জীবনযাপন নতুন করে যাচাই করতেও ডাকে।"},"teachings":["মদপান ও হারাম বিনোদন বড় বিপদের কারণ হতে পারে।","গায়িকা ও নাচ-গানে মত্ততা থেকে সতর্ক করা হয়েছে।","বাদ্যযন্ত্রে ব্যস্ততা হাদিসে নিন্দিতভাবে এসেছে।","হারামকে আনন্দের নামে স্বাভাবিক বানানো উচিত নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E201" s="4" t="n"/>

--- a/SINGLE HADITH CONTENT/BOOK WISE FINAL UPDATED CONTENT/BN/BN_UPODESH.xlsx
+++ b/SINGLE HADITH CONTENT/BOOK WISE FINAL UPDATED CONTENT/BN/BN_UPODESH.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1576,17 +1576,17 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>145</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তাবিজ ব্যবহারের ভয়াবহ সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. তাবিজ ও কড়ির উপর ভরসা মানুষকে আল্লাহর উপর নির্ভরতা থেকে সরিয়ে দেয়—এ হাদিসে সেই বিপদ সম্পর্কে সতর্কতা আছে।"},"heading":{"title":"তাবিজ ব্যবহার সম্পর্কে হাদিস: আল্লাহর উপর ভরসার শিক্ষা","description":"এই হাদিসে তাবিজ ব্যবহার ও কড়ি ঝুলানোর বিষয়ে স্পষ্ট সতর্কতা এসেছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি তাবিজ ব্যবহার করবে, আল্লাহ তাকে পূর্ণতা দেবেন না। আর যে কড়ি ব্যবহার করবে, আল্লাহ তাকে মঙ্গল দান করবেন না। সহজ কথায়, মানুষ যখন নিজের নিরাপত্তা বা কল্যাণের জন্য তাবিজ, কড়ি বা এমন কোনো ঝুলানো জিনিসের উপর ভরসা করে, তখন তার মন আল্লাহর উপর সরাসরি ভরসা থেকে দূরে যেতে পারে। এই হাদিসের মূল বিষয় হলো তাওহীদ ও তাওয়াক্কুল। সাহায্য, নিরাপত্তা ও মঙ্গল চাইতে হলে আল্লাহর কাছেই চাইতে হবে। তাবিজের উপর নির্ভরতা ঈমানের জন্য ঝুঁকিপূর্ণ।"},"teachings":["কল্যাণ ও নিরাপত্তার ভরসা আল্লাহর উপর রাখতে হবে।","তাবিজ ও কড়ির উপর নির্ভর করা থেকে বাঁচতে হবে।","বাহ্যিক জিনিসকে অদৃশ্য উপকারের মালিক মনে করা বিপজ্জনক।","তাওহীদ রক্ষার জন্য ছোট ভুলকেও গুরুত্ব দিতে হবে।"],"related_hadiths":[]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গণকের কাছে যাওয়ার ভয়াবহ ক্ষতি","description":"$book_name$ $hadith_number$ - $chapter_name$. গণক বা জ্যোতিষীর কাছে গিয়ে প্রশ্ন করলে চল্লিশ দিন সালাত কবুল না হওয়ার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"গণকের কাছে যাওয়ার হাদিস: সালাত কবুল না হওয়ার সতর্কতা","description":"এই হাদিসে গণক বা জ্যোতিষীর কাছে যাওয়ার বিষয়ে কঠোর সতর্কতা দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি কোনো গণক বা জ্যোতির্বিদের কাছে যায় এবং তাকে কোনো কথা জিজ্ঞেস করে, চল্লিশ দিন তার সালাত কবুল করা হবে না। এখানে শুধু বিশ্বাস করার কথা নয়; জিজ্ঞেস করার কথাও এসেছে। কারণ ভবিষ্যৎ, ভাগ্য বা গায়েব জানার চেষ্টা মানুষকে ভুল নির্ভরতার দিকে নিয়ে যায়। একজন মুমিন জানে, গায়েবের জ্ঞান আল্লাহর। তাই বিপদ, হারানো জিনিস, ভবিষ্যৎ বা ভাগ্য জানার জন্য গণকের কাছে যাওয়া ঈমানের জন্য ক্ষতিকর। এই হাদিস মানুষকে আল্লাহর উপর ভরসা করতে শেখায়।"},"teachings":["গণক বা জ্যোতিষীর কাছে প্রশ্ন করা থেকে বাঁচতে হবে।","গায়েব জানার দাবিদারদের কাছে যাওয়া ঈমানের জন্য ক্ষতিকর।","সালাতের মর্যাদা রক্ষায় বিশ্বাসের ভুল দরজা বন্ধ করতে হবে।","ভাগ্য ও অদৃশ্য বিষয়ের ব্যাপারে আল্লাহর উপর ভরসা করতে হবে।"],"related_hadiths":[{"id":"4594","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>related_hadiths[0]: unknown book label "মুসনাদ আহমাদ ১৬৭৭১"; related_hadiths[1]: unknown book label "সুনান আবূ দাঊদ ৩৮৮৩ (প্রাসঙ্গিক বর্ণনা)"</t>
+          <t>related_hadiths[1]: unknown book label "সুনান আবূ দাঊদ ৩৯০৪ (প্রাসঙ্গিক বর্ণনা)"</t>
         </is>
       </c>
     </row>
@@ -1603,19 +1603,15 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>147</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তাবিজ শির্ক হওয়ার স্পষ্ট সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. তাবিজ খুলে ফেলার পর বায়আত নেওয়া হয়েছিল—এ হাদিসে তাবিজকে শির্ক বলা হয়েছে।"},"heading":{"title":"তাবিজ শির্ক হাদিস: ঈমান রক্ষায় বড় সতর্কতা","description":"এই হাদিসে একটি ঘটনা বলা হয়েছে। একদল লোক রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম-এর কাছে এলে তিনি নয়জনের বায়আত নিলেন, কিন্তু একজনের বায়আত নিলেন না। কারণ তার সাথে একটি তাবিজ ছিল। পরে লোকটি হাত ঢুকিয়ে তাবিজ ছিঁড়ে ফেলল, এরপর রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম তার বায়আত নিলেন। তারপর তিনি বললেন, যে ব্যক্তি তাবিজ ব্যবহার করল, সে শির্ক করল। এখানে শিক্ষা খুব পরিষ্কার। তাবিজ শুধু একটি ঝুলানো বস্তু নয়; এর সাথে যদি অদৃশ্য উপকার বা সুরক্ষার বিশ্বাস জড়িয়ে যায়, তাহলে তা তাওহীদের বিপরীত পথে নিয়ে যায়। মুসলিমের ভরসা হবে আল্লাহর উপর, তাবিজের উপর নয়।"},"teachings":["তাবিজ ব্যবহারকে হাদিসে শির্ক বলা হয়েছে।","ভুল বুঝলে তা ছেড়ে দেওয়াই মুমিনের কাজ।","বায়আতের মতো বড় কাজে তাওহীদের শুদ্ধতা গুরুত্বপূর্ণ।","অদৃশ্য উপকারের আশা আল্লাহ ছাড়া অন্য কিছুর কাছে রাখা যাবে না।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "মুসনাদ আহমাদ ১৬৭৬৩"; related_hadiths[1]: unknown book label "সুনান আবূ দাঊদ ৩৮৮৩ (প্রাসঙ্গিক বর্ণনা)"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যাতুল আনওয়াত ও শির্ক থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মুশরিকদের মতো বরকতের জন্য বিশেষ গাছ চাওয়াকে নবীজি পূর্ববর্তীদের ভুল রীতির সাথে তুলনা করেছেন।"},"heading":{"title":"যাতুল আনওয়াত হাদিস: বরকত লাভে ভুল পথ থেকে সাবধান","description":"এই হাদিসে হুনাইনের পথে একটি ঘটনার কথা এসেছে। কিছু নতুন মুসলিম মুশরিকদের একটি গাছ দেখে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম-কে বললেন, তাদের যেমন নির্দিষ্ট গাছ আছে, আমাদের জন্যও তেমন একটি গাছ নির্ধারণ করে দিন। নবীজি এ কথাকে খুব গুরুতরভাবে নিলেন এবং বললেন, এটি পূর্ববর্তী লোকদের রীতির মতো। তিনি বনী ইসরাঈলের সেই কথাও স্মরণ করালেন, যখন তারা মূসা আলাইহিস সালামকে মুশরিকদের মতো মা‘বূদ বানিয়ে দিতে বলেছিল। এখানে মূল শিক্ষা হলো—বরকত, সাহায্য ও কল্যাণের আশা আল্লাহর বিধান ছাড়া কোনো বস্তু বা স্থানের সাথে জুড়ে দেওয়া বিপজ্জনক। মুসলিমকে অন্যদের ভুল রীতি নকল করা থেকে বাঁচতে হবে।"},"teachings":["বরকত পাওয়ার নামে মুশরিকদের রীতি অনুসরণ করা যাবে না।","নতুন মুসলিম হলেও তাওহীদের বিষয়ে সতর্ক থাকা জরুরি।","কল্যাণের আশা আল্লাহর অনুমোদিত পথেই রাখতে হবে।","পূর্ববর্তী জাতির ভুল থেকে শিক্ষা নেওয়া দরকার।"],"related_hadiths":[{"id":"3456","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2669","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n"/>
     </row>
     <row r="51" ht="46" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -1630,19 +1626,15 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>148</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তাবিজ ও নিষিদ্ধ কাজ থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. দাড়িতে গিট, তাবিজ জাতীয় বস্তু পরানো এবং হাড় বা গোবর দিয়ে ইসতেঞ্জা—এসব থেকে কঠোরভাবে সতর্ক করা হয়েছে।"},"heading":{"title":"তাবিজ ও ইসতেঞ্জার আদব: নিষিদ্ধ কাজ থেকে বাঁচার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম রুওয়াইফা রাদিয়াল্লাহু আনহুকে কিছু কথা মানুষের কাছে পৌঁছে দিতে বলেন। তিনি জানালেন, যে দাড়িতে গিট দেয়, তাবিজ জাতীয় বেল্ট বা সুতা পরায়, অথবা চতুষ্পদ জন্তুর গোবর বা হাড় দিয়ে ইসতেঞ্জা করে, তার সাথে মুহাম্মাদ সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম-এর সম্পর্ক নেই। এখানে কয়েকটি আলাদা বিষয় এসেছে। একদিকে তাবিজ জাতীয় জিনিস পরানোর সতর্কতা আছে, অন্যদিকে পবিত্রতার আদবও আছে। হাদিসের ভাষা কঠোর, তাই মুসলিমের উচিত এমন কাজকে হালকা না নেওয়া। শরীর, বিশ্বাস ও পবিত্রতা—সব ক্ষেত্রেই নবীজির শেখানো সীমা মানা ঈমানের দাবি।"},"teachings":["তাবিজ জাতীয় সুতা বা বেল্ট পরানো থেকে বাঁচতে হবে।","ইসতেঞ্জার ক্ষেত্রে শরীয়তের আদব মানা দরকার।","নবীজির নিষেধ করা কাজকে ছোট মনে করা উচিত নয়।","বিশ্বাস ও পবিত্রতা—দুই বিষয়েই সতর্ক থাকা জরুরি।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "সুনান আবূ দাঊদ ৩৮৮৩ (প্রাসঙ্গিক বর্ণনা)"; related_hadiths[1]: unknown book label "মুসনাদ আহমাদ ১৬৭৭১ (প্রাসঙ্গিক বর্ণনা)"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মানত পূরণ ও নাফরমানী থেকে বাঁচা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর আনুগত্যের মানত পূরণ করতে হবে, আর নাফরমানীর মানত পূরণ করা যাবে না—এটাই মূল শিক্ষা।"},"heading":{"title":"মানত সম্পর্কে হাদিস: আনুগত্যের মানত পূরণ, পাপের মানত নয়","description":"এই হাদিসে মানত সম্পর্কে সহজ ও পরিষ্কার নীতি দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি আল্লাহর আনুগত্যের কাজে মানত করে, সে যেন তা পূরণ করে। আর যে ব্যক্তি আল্লাহর নাফরমানীমূলক কাজে মানত করে, সে যেন আল্লাহর নাফরমানী না করে। অর্থাৎ মানত হলেই সব পূরণ করতে হবে—এমন নয়। যদি মানতটি ভালো কাজ, ইবাদত বা আল্লাহর আনুগত্যের মধ্যে পড়ে, তবে তা পূরণ করতে হবে। কিন্তু যদি তা পাপ, অন্যায় বা আল্লাহর অবাধ্যতার দিকে নিয়ে যায়, তাহলে তা করা যাবে না। এই হাদিস মানতের বিষয়ে আবেগ নয়, শরীয়তের সীমা মানতে শেখায়।"},"teachings":["আল্লাহর আনুগত্যের মানত পূরণ করতে হবে।","পাপ বা নাফরমানীর মানত পূরণ করা যাবে না।","মানতের আগে কাজটি বৈধ কি না তা বুঝে নেওয়া দরকার।","ইবাদতের ক্ষেত্রেও আল্লাহর সীমা মানা জরুরি।"],"related_hadiths":[{"id":"6608","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3426","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n"/>
     </row>
     <row r="52" ht="46" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
@@ -1657,19 +1649,15 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>149</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গণকের কাছে যাওয়ার ভয়াবহ ক্ষতি","description":"$book_name$ $hadith_number$ - $chapter_name$. গণক বা জ্যোতিষীর কাছে গিয়ে প্রশ্ন করলে চল্লিশ দিন সালাত কবুল না হওয়ার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"গণকের কাছে যাওয়ার হাদিস: সালাত কবুল না হওয়ার সতর্কতা","description":"এই হাদিসে গণক বা জ্যোতিষীর কাছে যাওয়ার বিষয়ে কঠোর সতর্কতা দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি কোনো গণক বা জ্যোতির্বিদের কাছে যায় এবং তাকে কোনো কথা জিজ্ঞেস করে, চল্লিশ দিন তার সালাত কবুল করা হবে না। এখানে শুধু বিশ্বাস করার কথা নয়; জিজ্ঞেস করার কথাও এসেছে। কারণ ভবিষ্যৎ, ভাগ্য বা গায়েব জানার চেষ্টা মানুষকে ভুল নির্ভরতার দিকে নিয়ে যায়। একজন মুমিন জানে, গায়েবের জ্ঞান আল্লাহর। তাই বিপদ, হারানো জিনিস, ভবিষ্যৎ বা ভাগ্য জানার জন্য গণকের কাছে যাওয়া ঈমানের জন্য ক্ষতিকর। এই হাদিস মানুষকে আল্লাহর উপর ভরসা করতে শেখায়।"},"teachings":["গণক বা জ্যোতিষীর কাছে প্রশ্ন করা থেকে বাঁচতে হবে।","গায়েব জানার দাবিদারদের কাছে যাওয়া ঈমানের জন্য ক্ষতিকর।","সালাতের মর্যাদা রক্ষায় বিশ্বাসের ভুল দরজা বন্ধ করতে হবে।","ভাগ্য ও অদৃশ্য বিষয়ের ব্যাপারে আল্লাহর উপর ভরসা করতে হবে।"],"related_hadiths":[{"id":"4594","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[1]: unknown book label "সুনান আবূ দাঊদ ৩৯০৪ (প্রাসঙ্গিক বর্ণনা)"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নতুন স্থানে পড়ার নিরাপদ দোয়া","description":"$book_name$ $hadith_number$ - $chapter_name$. কোনো স্থানে নামলে আল্লাহর পূর্ণ কালামের আশ্রয় চাওয়ার দোয়া শেখানো হয়েছে।"},"heading":{"title":"নতুন স্থানে নামার দোয়া: আল্লাহর কালামের আশ্রয়","description":"এই হাদিসে সফর, বাড়ি, পথ বা কোনো নতুন স্থানে নামার সময় একটি দোয়া শেখানো হয়েছে। দোয়াটি হলো: أَعُوْذُ بِكَلِمَاتِ اللهِ التَّامَّاتِ مِنْ شَرِّ مَا خَلَقَ — অর্থাৎ, আমি আল্লাহর পূর্ণ কালামের নিকট তাঁর সৃষ্টির সব অনিষ্ট থেকে আশ্রয় চাই। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি কোনো বাড়ি বা স্থানে নেমে এই দোয়া পড়বে, সে ঐ স্থান ত্যাগ না করা পর্যন্ত কোনো কিছু তার ক্ষতি করতে পারবে না। এখানে মূল শিক্ষা হলো নিরাপত্তার জন্য তাবিজ বা কুসংস্কার নয়, আল্লাহর কাছে আশ্রয় চাওয়া। মুসলিমের ভরসা হবে আল্লাহর কালাম, দোয়া ও তাওয়াক্কুলের উপর।"},"teachings":["নতুন স্থানে নামলে আল্লাহর কাছে আশ্রয় চাইতে হবে।","সৃষ্টির অনিষ্ট থেকে বাঁচার জন্য দোয়া বড় উপায়।","নিরাপত্তার ভরসা তাবিজ নয়, আল্লাহর উপর রাখতে হবে।","দোয়া মুখস্থ করে জীবনে ব্যবহার করা দরকার।"],"related_hadiths":[{"id":"2708","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2310","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="n"/>
     </row>
     <row r="53" ht="46" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -1684,12 +1672,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যাতুল আনওয়াত ও শির্ক থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মুশরিকদের মতো বরকতের জন্য বিশেষ গাছ চাওয়াকে নবীজি পূর্ববর্তীদের ভুল রীতির সাথে তুলনা করেছেন।"},"heading":{"title":"যাতুল আনওয়াত হাদিস: বরকত লাভে ভুল পথ থেকে সাবধান","description":"এই হাদিসে হুনাইনের পথে একটি ঘটনার কথা এসেছে। কিছু নতুন মুসলিম মুশরিকদের একটি গাছ দেখে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম-কে বললেন, তাদের যেমন নির্দিষ্ট গাছ আছে, আমাদের জন্যও তেমন একটি গাছ নির্ধারণ করে দিন। নবীজি এ কথাকে খুব গুরুতরভাবে নিলেন এবং বললেন, এটি পূর্ববর্তী লোকদের রীতির মতো। তিনি বনী ইসরাঈলের সেই কথাও স্মরণ করালেন, যখন তারা মূসা আলাইহিস সালামকে মুশরিকদের মতো মা‘বূদ বানিয়ে দিতে বলেছিল। এখানে মূল শিক্ষা হলো—বরকত, সাহায্য ও কল্যাণের আশা আল্লাহর বিধান ছাড়া কোনো বস্তু বা স্থানের সাথে জুড়ে দেওয়া বিপজ্জনক। মুসলিমকে অন্যদের ভুল রীতি নকল করা থেকে বাঁচতে হবে।"},"teachings":["বরকত পাওয়ার নামে মুশরিকদের রীতি অনুসরণ করা যাবে না।","নতুন মুসলিম হলেও তাওহীদের বিষয়ে সতর্ক থাকা জরুরি।","কল্যাণের আশা আল্লাহর অনুমোদিত পথেই রাখতে হবে।","পূর্ববর্তী জাতির ভুল থেকে শিক্ষা নেওয়া দরকার।"],"related_hadiths":[{"id":"3456","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2669","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গুনাহের সময় ঈমানের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. যেনা, মদ, চুরি, ছিনতাই ও খিয়ানতের সময় ঈমানের দুর্বলতার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"গুনাহের সময় ঈমানের সতর্কতা: যেনা, মদ, চুরি ও খিয়ানত","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়সাল্লাম) কয়েকটি বড় গুনাহ সম্পর্কে কঠোর সতর্কতা দিয়েছেন। তিনি বলেছেন, যেনাকার যখন যেনা করে তখন মুমিন অবস্থায় তা করে না। মদখোর যখন মদ পান করে, চোর যখন চুরি করে, প্রকাশ্যে ডাকাতি বা ছিনতাইকারী যখন তা করে, এবং কেউ যখন গানীমত বা কোনো মালে খিয়ানত করে—তখন সে মুমিন অবস্থায় থাকে না। শেষে নবীজি বলেছেন, সাবধান হও, সাবধান হও। হাদিসের ভাষা খুব সতর্কতামূলক। এখানে গুনাহকে হালকা করে দেখার সুযোগ নেই। ঈমানের দাবি হলো মানুষ যেন বড় গুনাহ থেকে দূরে থাকে এবং যদি ভুল হয়, আল্লাহর দিকে ফিরে আসে।"},"teachings":["যেনা, মদ, চুরি, ছিনতাই ও খিয়ানত বড় সতর্কতার বিষয়।","গুনাহের সময় ঈমানের দাবি দুর্বল হয়ে যায়—এ কথা হাদিসে এসেছে।","অন্যের মাল বা গানীমতে খিয়ানত করা ভয়ংকর কাজ।","নবীজির সাবধানবাণী গুনাহ থেকে দূরে থাকতে শেখায়।"],"related_hadiths":[{"id":"2475","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"57","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"53","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E53" s="4" t="n"/>
@@ -1707,12 +1695,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মানত পূরণ ও নাফরমানী থেকে বাঁচা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর আনুগত্যের মানত পূরণ করতে হবে, আর নাফরমানীর মানত পূরণ করা যাবে না—এটাই মূল শিক্ষা।"},"heading":{"title":"মানত সম্পর্কে হাদিস: আনুগত্যের মানত পূরণ, পাপের মানত নয়","description":"এই হাদিসে মানত সম্পর্কে সহজ ও পরিষ্কার নীতি দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি আল্লাহর আনুগত্যের কাজে মানত করে, সে যেন তা পূরণ করে। আর যে ব্যক্তি আল্লাহর নাফরমানীমূলক কাজে মানত করে, সে যেন আল্লাহর নাফরমানী না করে। অর্থাৎ মানত হলেই সব পূরণ করতে হবে—এমন নয়। যদি মানতটি ভালো কাজ, ইবাদত বা আল্লাহর আনুগত্যের মধ্যে পড়ে, তবে তা পূরণ করতে হবে। কিন্তু যদি তা পাপ, অন্যায় বা আল্লাহর অবাধ্যতার দিকে নিয়ে যায়, তাহলে তা করা যাবে না। এই হাদিস মানতের বিষয়ে আবেগ নয়, শরীয়তের সীমা মানতে শেখায়।"},"teachings":["আল্লাহর আনুগত্যের মানত পূরণ করতে হবে।","পাপ বা নাফরমানীর মানত পূরণ করা যাবে না।","মানতের আগে কাজটি বৈধ কি না তা বুঝে নেওয়া দরকার।","ইবাদতের ক্ষেত্রেও আল্লাহর সীমা মানা জরুরি।"],"related_hadiths":[{"id":"6608","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3426","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মূর্তিপূজার সূচনা থেকে শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. নেককারদের স্মৃতিতে মূর্তি স্থাপন পরে ইবাদতের পথে নিয়ে যায়—এ বর্ণনায় সেই বিপদের শুরু দেখানো হয়েছে।"},"heading":{"title":"মূর্তিপূজার সূচনা: নেককারদের নামে মূর্তি স্থাপনের বিপদ","description":"এই বর্ণনায় নূহ আলাইহিস সালাম-এর সম্প্রদায়ের কিছু নেককার মানুষের নাম নিয়ে বলা হয়েছে। তারা মারা গেলে শয়তান তাদের সম্প্রদায়কে কুমন্ত্রণা দিল—যেখানে তারা বসতেন, সেখানে তাদের মূর্তি স্থাপন করো এবং তাদের নামেই মূর্তির নাম রাখো। শুরুতে এগুলোর পূজা হয়নি। কিন্তু যারা এগুলো স্থাপন করেছিল তারা মারা গেল, এরপর মূল ঘটনা ও জ্ঞান হারিয়ে গেল। তখন সেই মূর্তিগুলোর ইবাদত শুরু হলো। এই বর্ণনার শিক্ষা খুব গভীর: নেককার মানুষকে ভালোবাসা এক বিষয়, আর তাদের নামে এমন স্মৃতিচিহ্ন বানানো আরেক বিষয়, যা পরে ইবাদতের রূপ নিতে পারে। শির্কের পথ অনেক সময় ধীরে ধীরে খুলে যায়।"},"teachings":["নেককারদের ভালোবাসা যেন ইবাদতের সীমা না ছাড়ায়।","মূর্তি বা প্রতিমা স্থাপন পরে বড় ফিতনার কারণ হতে পারে।","শয়তান ধীরে ধীরে মানুষকে শির্কের দিকে টানে।","ইতিহাস ভুলে গেলে ভুল কাজকে ধর্ম মনে করার ঝুঁকি থাকে।"],"related_hadiths":[{"id":"4920","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4921","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E54" s="4" t="n"/>
@@ -1730,12 +1718,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>151</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নতুন স্থানে পড়ার নিরাপদ দোয়া","description":"$book_name$ $hadith_number$ - $chapter_name$. কোনো স্থানে নামলে আল্লাহর পূর্ণ কালামের আশ্রয় চাওয়ার দোয়া শেখানো হয়েছে।"},"heading":{"title":"নতুন স্থানে নামার দোয়া: আল্লাহর কালামের আশ্রয়","description":"এই হাদিসে সফর, বাড়ি, পথ বা কোনো নতুন স্থানে নামার সময় একটি দোয়া শেখানো হয়েছে। দোয়াটি হলো: أَعُوْذُ بِكَلِمَاتِ اللهِ التَّامَّاتِ مِنْ شَرِّ مَا خَلَقَ — অর্থাৎ, আমি আল্লাহর পূর্ণ কালামের নিকট তাঁর সৃষ্টির সব অনিষ্ট থেকে আশ্রয় চাই। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি কোনো বাড়ি বা স্থানে নেমে এই দোয়া পড়বে, সে ঐ স্থান ত্যাগ না করা পর্যন্ত কোনো কিছু তার ক্ষতি করতে পারবে না। এখানে মূল শিক্ষা হলো নিরাপত্তার জন্য তাবিজ বা কুসংস্কার নয়, আল্লাহর কাছে আশ্রয় চাওয়া। মুসলিমের ভরসা হবে আল্লাহর কালাম, দোয়া ও তাওয়াক্কুলের উপর।"},"teachings":["নতুন স্থানে নামলে আল্লাহর কাছে আশ্রয় চাইতে হবে।","সৃষ্টির অনিষ্ট থেকে বাঁচার জন্য দোয়া বড় উপায়।","নিরাপত্তার ভরসা তাবিজ নয়, আল্লাহর উপর রাখতে হবে।","দোয়া মুখস্থ করে জীবনে ব্যবহার করা দরকার।"],"related_hadiths":[{"id":"2708","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2310","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবরকে মসজিদ বানানো থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীদের কবরকে মসজিদ বানানো নিয়ে ইহুদী-খৃষ্টানদের কাজের প্রতি কঠোর সতর্কতা এসেছে।"},"heading":{"title":"কবরকে মসজিদ বানানো: শেষ অসুখের গুরুত্বপূর্ণ সতর্কতা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম জীবনের শেষ অসুখে একটি গুরুত্বপূর্ণ কথা বলেছেন। তিনি বলেছেন, ইহুদী-খৃষ্টানদের উপর আল্লাহর অভিশাপ; তারা তাদের নবীদের কবরকে মসজিদ বানিয়ে নিয়েছিল। হাদিসের সময়টিও গুরুত্বপূর্ণ, কারণ শেষ অসুখে বলা কথা সাধারণত বিশেষ গুরুত্ব বহন করে। এখানে মূল শিক্ষা হলো কবরকে ইবাদতের জায়গা বানানো থেকে বাঁচা। নবীদের প্রতি সম্মান থাকবে, কিন্তু সেই সম্মান যেন কবরকে কেন্দ্র করে ইবাদতের রূপ না নেয়। কবরকে মসজিদ বানানো মানুষের বিশ্বাসকে তাওহীদ থেকে সরিয়ে দিতে পারে। তাই ইবাদত হবে শুধু আল্লাহর জন্য, আল্লাহর শেখানো পদ্ধতিতে।"},"teachings":["কবরকে মসজিদ বানানো থেকে সতর্ক থাকতে হবে।","নবী ও নেককারদের সম্মান ইবাদতের সীমা ছাড়াতে পারে না।","শেষ জীবনে নবীজির বলা সতর্কতাকে গুরুত্ব দিতে হবে।","ইবাদতের জায়গা ও কবরের সীমা আলাদা রাখা দরকার।"],"related_hadiths":[{"id":"713","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"435","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E55" s="4" t="n"/>
@@ -1753,12 +1741,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গুনাহের সময় ঈমানের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. যেনা, মদ, চুরি, ছিনতাই ও খিয়ানতের সময় ঈমানের দুর্বলতার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"গুনাহের সময় ঈমানের সতর্কতা: যেনা, মদ, চুরি ও খিয়ানত","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়সাল্লাম) কয়েকটি বড় গুনাহ সম্পর্কে কঠোর সতর্কতা দিয়েছেন। তিনি বলেছেন, যেনাকার যখন যেনা করে তখন মুমিন অবস্থায় তা করে না। মদখোর যখন মদ পান করে, চোর যখন চুরি করে, প্রকাশ্যে ডাকাতি বা ছিনতাইকারী যখন তা করে, এবং কেউ যখন গানীমত বা কোনো মালে খিয়ানত করে—তখন সে মুমিন অবস্থায় থাকে না। শেষে নবীজি বলেছেন, সাবধান হও, সাবধান হও। হাদিসের ভাষা খুব সতর্কতামূলক। এখানে গুনাহকে হালকা করে দেখার সুযোগ নেই। ঈমানের দাবি হলো মানুষ যেন বড় গুনাহ থেকে দূরে থাকে এবং যদি ভুল হয়, আল্লাহর দিকে ফিরে আসে।"},"teachings":["যেনা, মদ, চুরি, ছিনতাই ও খিয়ানত বড় সতর্কতার বিষয়।","গুনাহের সময় ঈমানের দাবি দুর্বল হয়ে যায়—এ কথা হাদিসে এসেছে।","অন্যের মাল বা গানীমতে খিয়ানত করা ভয়ংকর কাজ।","নবীজির সাবধানবাণী গুনাহ থেকে দূরে থাকতে শেখায়।"],"related_hadiths":[{"id":"2475","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"57","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"53","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবরকে মসজিদ না বানানোর নির্দেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. পূর্ববর্তী লোকেরা নবী ও নেককারদের কবরকে মসজিদ বানিয়েছিল; মুসলিমদের তা থেকে নিষেধ করা হয়েছে।"},"heading":{"title":"কবরকে মসজিদ বানিও না: তাওহীদ রক্ষার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম খুব সরাসরি নিষেধ করেছেন। তিনি বলেন, পূর্ববর্তী লোকেরা তাদের নবী ও নেককার লোকদের কবরকে মসজিদ বানিয়েছিল। তারপর তিনি মুসলিমদের বলেন, তোমরা কবরকে মসজিদ বানিও না; আমি তোমাদেরকে তা থেকে নিষেধ করছি। এখানে কোনো অস্পষ্টতা নেই। কবরের প্রতি সম্মান থাকবে, মৃতের জন্য দোয়া থাকবে; কিন্তু কবরকে সালাত, সিজদা বা ইবাদতের কেন্দ্র বানানো যাবে না। কারণ এতে মানুষের মন ধীরে ধীরে কবরবাসীর দিকে ঝুঁকতে পারে। তাওহীদ রক্ষার জন্য ইবাদতের স্থান, দিক ও উদ্দেশ্য সবই আল্লাহর বিধান অনুযায়ী হওয়া দরকার।"},"teachings":["কবরকে ইবাদতের জায়গা বানানো যাবে না।","নেককারদের কবরের ব্যাপারেও সীমা মানতে হবে।","নবীজির সরাসরি নিষেধকে গুরুত্ব দিতে হবে।","তাওহীদ রক্ষায় ইবাদত শুধু আল্লাহর জন্য রাখতে হবে।"],"related_hadiths":[{"id":"712","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"436","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E56" s="4" t="n"/>
@@ -1776,12 +1764,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>153</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মূর্তিপূজার সূচনা থেকে শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. নেককারদের স্মৃতিতে মূর্তি স্থাপন পরে ইবাদতের পথে নিয়ে যায়—এ বর্ণনায় সেই বিপদের শুরু দেখানো হয়েছে।"},"heading":{"title":"মূর্তিপূজার সূচনা: নেককারদের নামে মূর্তি স্থাপনের বিপদ","description":"এই বর্ণনায় নূহ আলাইহিস সালাম-এর সম্প্রদায়ের কিছু নেককার মানুষের নাম নিয়ে বলা হয়েছে। তারা মারা গেলে শয়তান তাদের সম্প্রদায়কে কুমন্ত্রণা দিল—যেখানে তারা বসতেন, সেখানে তাদের মূর্তি স্থাপন করো এবং তাদের নামেই মূর্তির নাম রাখো। শুরুতে এগুলোর পূজা হয়নি। কিন্তু যারা এগুলো স্থাপন করেছিল তারা মারা গেল, এরপর মূল ঘটনা ও জ্ঞান হারিয়ে গেল। তখন সেই মূর্তিগুলোর ইবাদত শুরু হলো। এই বর্ণনার শিক্ষা খুব গভীর: নেককার মানুষকে ভালোবাসা এক বিষয়, আর তাদের নামে এমন স্মৃতিচিহ্ন বানানো আরেক বিষয়, যা পরে ইবাদতের রূপ নিতে পারে। শির্কের পথ অনেক সময় ধীরে ধীরে খুলে যায়।"},"teachings":["নেককারদের ভালোবাসা যেন ইবাদতের সীমা না ছাড়ায়।","মূর্তি বা প্রতিমা স্থাপন পরে বড় ফিতনার কারণ হতে পারে।","শয়তান ধীরে ধীরে মানুষকে শির্কের দিকে টানে।","ইতিহাস ভুলে গেলে ভুল কাজকে ধর্ম মনে করার ঝুঁকি থাকে।"],"related_hadiths":[{"id":"4920","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4921","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মক্কা বিজয়ে মূর্তি অপসারণের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. কা‘বার চারপাশের মূর্তি সরিয়ে সত্যের আগমন ও মিথ্যার বিলুপ্তির ঘোষণা দেওয়া হয়েছিল।"},"heading":{"title":"মক্কা বিজয়ের হাদিস: সত্য এসেছে, মিথ্যা বিলুপ্ত হয়েছে","description":"এই হাদিসে মক্কা বিজয়ের দিনের একটি দৃশ্য এসেছে। রাসূলুল্লাহ সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম যখন মক্কায় প্রবেশ করলেন, তখন কা‘বা ঘরের চারপাশে তিনশ ষাটটি মূর্তি ছিল। তিনি হাতে থাকা ছড়ি দিয়ে সেগুলোকে ঠোকা দিচ্ছিলেন এবং বলছিলেন, সত্য এসেছে আর মিথ্যা বিলুপ্ত হয়েছে; মিথ্যা তো বিলুপ্ত হওয়ারই। এই ঘটনা তাওহীদের বিজয় ও শির্কের অপসারণের বড় শিক্ষা দেয়। কা‘বা আল্লাহর ঘর, সেখানে মূর্তি থাকার কোনো স্থান নেই। হাদিসের মূল বার্তা হলো—সত্য প্রতিষ্ঠিত হলে মিথ্যা টেকে না। মুসলিমের হৃদয়েও তাওহীদের জায়গায় কোনো মূর্তি, শির্ক বা ভুল ভরসা রাখা যায় না।"},"teachings":["আল্লাহর ঘর থেকে মূর্তি অপসারণ তাওহীদের দাবি।","সত্য প্রতিষ্ঠার সাথে মিথ্যা দূর হয়।","শির্কের চিহ্নকে সম্মান নয়, বর্জন করতে হবে।","ইবাদতের স্থানকে শুদ্ধ রাখা জরুরি।"],"related_hadiths":[{"id":"4920","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"712","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E57" s="4" t="n"/>
@@ -1799,12 +1787,12 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবরকে মসজিদ বানানো থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীদের কবরকে মসজিদ বানানো নিয়ে ইহুদী-খৃষ্টানদের কাজের প্রতি কঠোর সতর্কতা এসেছে।"},"heading":{"title":"কবরকে মসজিদ বানানো: শেষ অসুখের গুরুত্বপূর্ণ সতর্কতা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম জীবনের শেষ অসুখে একটি গুরুত্বপূর্ণ কথা বলেছেন। তিনি বলেছেন, ইহুদী-খৃষ্টানদের উপর আল্লাহর অভিশাপ; তারা তাদের নবীদের কবরকে মসজিদ বানিয়ে নিয়েছিল। হাদিসের সময়টিও গুরুত্বপূর্ণ, কারণ শেষ অসুখে বলা কথা সাধারণত বিশেষ গুরুত্ব বহন করে। এখানে মূল শিক্ষা হলো কবরকে ইবাদতের জায়গা বানানো থেকে বাঁচা। নবীদের প্রতি সম্মান থাকবে, কিন্তু সেই সম্মান যেন কবরকে কেন্দ্র করে ইবাদতের রূপ না নেয়। কবরকে মসজিদ বানানো মানুষের বিশ্বাসকে তাওহীদ থেকে সরিয়ে দিতে পারে। তাই ইবাদত হবে শুধু আল্লাহর জন্য, আল্লাহর শেখানো পদ্ধতিতে।"},"teachings":["কবরকে মসজিদ বানানো থেকে সতর্ক থাকতে হবে।","নবী ও নেককারদের সম্মান ইবাদতের সীমা ছাড়াতে পারে না।","শেষ জীবনে নবীজির বলা সতর্কতাকে গুরুত্ব দিতে হবে।","ইবাদতের জায়গা ও কবরের সীমা আলাদা রাখা দরকার।"],"related_hadiths":[{"id":"713","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"435","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নবীজির কবর নিয়ে শির্ক থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি নিজের কবরকে ইবাদতের বস্তু না বানানোর দোয়া করেছেন এবং কবরকে মসজিদ বানানো থেকে সতর্ক করেছেন।"},"heading":{"title":"আমার কবরকে মূর্তি বানিও না: কবর বিষয়ে তাওহীদের শিক্ষা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম দোয়া করেছেন: হে আল্লাহ! তুমি আমার কবরকে এমন মূর্তিতে পরিণত করো না যার ইবাদত করা হবে। এরপর তিনি বলেন, যারা তাদের নবীদের কবরকে মসজিদ বানিয়েছে, আল্লাহ তাদের উপর রাগান্বিত হয়েছেন। এখানে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম নিজের কবর সম্পর্কেও মানুষকে সতর্ক করে দিয়েছেন। তাই নবীজির প্রতি ভালোবাসা কখনোই তাঁর কবরকে ইবাদতের কেন্দ্র বানানোর অনুমতি দেয় না। ভালোবাসা হবে অনুসরণে, দোয়া ও দরূদে, কিন্তু ইবাদত হবে শুধু আল্লাহর জন্য। কবরকে মূর্তি বা মসজিদের মতো বানানো তাওহীদের জন্য ভয়াবহ ঝুঁকি।"},"teachings":["নবীজির কবরকেও ইবাদতের বস্তু বানানো যাবে না।","কবরকে মসজিদ বানানো আল্লাহর রাগের কারণ হিসেবে এসেছে।","রাসূলের ভালোবাসা তাঁর অনুসরণে প্রকাশ পায়।","ইবাদত শুধু আল্লাহর জন্য সংরক্ষিত রাখতে হবে।"],"related_hadiths":[{"id":"712","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"713","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E58" s="4" t="n"/>
@@ -1822,12 +1810,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>157</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবরকে মসজিদ না বানানোর নির্দেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. পূর্ববর্তী লোকেরা নবী ও নেককারদের কবরকে মসজিদ বানিয়েছিল; মুসলিমদের তা থেকে নিষেধ করা হয়েছে।"},"heading":{"title":"কবরকে মসজিদ বানিও না: তাওহীদ রক্ষার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম খুব সরাসরি নিষেধ করেছেন। তিনি বলেন, পূর্ববর্তী লোকেরা তাদের নবী ও নেককার লোকদের কবরকে মসজিদ বানিয়েছিল। তারপর তিনি মুসলিমদের বলেন, তোমরা কবরকে মসজিদ বানিও না; আমি তোমাদেরকে তা থেকে নিষেধ করছি। এখানে কোনো অস্পষ্টতা নেই। কবরের প্রতি সম্মান থাকবে, মৃতের জন্য দোয়া থাকবে; কিন্তু কবরকে সালাত, সিজদা বা ইবাদতের কেন্দ্র বানানো যাবে না। কারণ এতে মানুষের মন ধীরে ধীরে কবরবাসীর দিকে ঝুঁকতে পারে। তাওহীদ রক্ষার জন্য ইবাদতের স্থান, দিক ও উদ্দেশ্য সবই আল্লাহর বিধান অনুযায়ী হওয়া দরকার।"},"teachings":["কবরকে ইবাদতের জায়গা বানানো যাবে না।","নেককারদের কবরের ব্যাপারেও সীমা মানতে হবে।","নবীজির সরাসরি নিষেধকে গুরুত্ব দিতে হবে।","তাওহীদ রক্ষায় ইবাদত শুধু আল্লাহর জন্য রাখতে হবে।"],"related_hadiths":[{"id":"712","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"436","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যাদুর প্রতি বিশ্বাসের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপায়ী, আত্মীয়তা ছিন্নকারী ও যাদুতে বিশ্বাসকারীর বিষয়ে কঠোর সতর্কতা এসেছে।"},"heading":{"title":"যাদুর প্রতি বিশ্বাস: জান্নাত থেকে বঞ্চনার কঠোর সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের ব্যাপারে কঠোর সতর্কতা এসেছে: সর্বদা মদপানকারী, আত্মীয়তার বন্ধন ছিন্নকারী এবং যাদুর প্রতি বিশ্বাসকারী। এখানে যাদুর প্রতি বিশ্বাসকে এমন গুরুতর বিষয়ের সাথে উল্লেখ করা হয়েছে, যেগুলো মানুষের দ্বীন ও চরিত্রের বড় ক্ষতি করে। যাদুর প্রতি বিশ্বাস বলতে এমন নির্ভরতা বোঝায়, যেখানে মানুষ যাদুকে বাস্তব কল্যাণ-অকল্যাণের স্বাধীন ক্ষমতার মতো মনে করে বা যাদুকরের পথে ভরসা রাখে। এই হাদিস আমাদের মনে করিয়ে দেয়, ঈমানের জায়গায় যাদু, কুসংস্কার বা অন্ধ বিশ্বাস ঢুকতে দেওয়া যাবে না। আল্লাহর উপর ভরসা, আত্মীয়তার সম্পর্ক রক্ষা এবং হারাম কাজ থেকে বাঁচা—এসবই মুমিনের পথ।"},"teachings":["যাদুর প্রতি বিশ্বাসকে হাদিসে কঠোরভাবে নিন্দা করা হয়েছে।","মদপান ও আত্মীয়তা ছিন্ন করার মতো কাজ থেকেও সতর্ক থাকতে হবে।","যাদুকর বা যাদুর উপর ভরসা রাখা ঈমানের জন্য ক্ষতিকর।","মুমিনের ভরসা আল্লাহর উপর, অন্ধ বিশ্বাসের উপর নয়।"],"related_hadiths":[{"id":"2766","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E59" s="4" t="n"/>
@@ -1845,12 +1833,12 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মক্কা বিজয়ে মূর্তি অপসারণের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. কা‘বার চারপাশের মূর্তি সরিয়ে সত্যের আগমন ও মিথ্যার বিলুপ্তির ঘোষণা দেওয়া হয়েছিল।"},"heading":{"title":"মক্কা বিজয়ের হাদিস: সত্য এসেছে, মিথ্যা বিলুপ্ত হয়েছে","description":"এই হাদিসে মক্কা বিজয়ের দিনের একটি দৃশ্য এসেছে। রাসূলুল্লাহ সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম যখন মক্কায় প্রবেশ করলেন, তখন কা‘বা ঘরের চারপাশে তিনশ ষাটটি মূর্তি ছিল। তিনি হাতে থাকা ছড়ি দিয়ে সেগুলোকে ঠোকা দিচ্ছিলেন এবং বলছিলেন, সত্য এসেছে আর মিথ্যা বিলুপ্ত হয়েছে; মিথ্যা তো বিলুপ্ত হওয়ারই। এই ঘটনা তাওহীদের বিজয় ও শির্কের অপসারণের বড় শিক্ষা দেয়। কা‘বা আল্লাহর ঘর, সেখানে মূর্তি থাকার কোনো স্থান নেই। হাদিসের মূল বার্তা হলো—সত্য প্রতিষ্ঠিত হলে মিথ্যা টেকে না। মুসলিমের হৃদয়েও তাওহীদের জায়গায় কোনো মূর্তি, শির্ক বা ভুল ভরসা রাখা যায় না।"},"teachings":["আল্লাহর ঘর থেকে মূর্তি অপসারণ তাওহীদের দাবি।","সত্য প্রতিষ্ঠার সাথে মিথ্যা দূর হয়।","শির্কের চিহ্নকে সম্মান নয়, বর্জন করতে হবে।","ইবাদতের স্থানকে শুদ্ধ রাখা জরুরি।"],"related_hadiths":[{"id":"4920","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"712","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অশুভ লক্ষণ গ্রহণ শির্কী কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. কুলক্ষণ বা অশুভ ধারণাকে কাজের ভিত্তি বানানো শির্কী কাজ—এ কথা তিনবার বলা হয়েছে।"},"heading":{"title":"অশুভ লক্ষণ শির্ক: কুলক্ষণ বিশ্বাসের বিরুদ্ধে হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, অশুভ বা কুলক্ষণ ফল গ্রহণ করা শির্কী কাজ। তিনি কথাটি তিনবার বলেছেন। কোনো কথা তিনবার বলা হলে তার গুরুত্ব আরও পরিষ্কার হয়। কুলক্ষণ মানে কোনো পাখি, শব্দ, দিন, দিক, ব্যক্তি বা ঘটনার কারণে নিজের কাজে অশুভ ফল হবে—এমন বিশ্বাস করা। এই ধরনের ধারণা মানুষের সিদ্ধান্তকে আল্লাহর উপর ভরসা থেকে সরিয়ে দেয়। মুমিন কাজ করবে বৈধ কারণ, পরামর্শ ও দোয়ার মাধ্যমে; অশুভ ধারণার কারণে কাজ ছেড়ে দেবে না। এই হাদিস তাওহীদকে পরিষ্কার রাখার শিক্ষা দেয়। ভয়, অনুমান ও কুসংস্কার নয়—আল্লাহর উপর ভরসাই মুমিনের ভিত্তি।"},"teachings":["অশুভ লক্ষণকে সত্য ধরে নেওয়া শির্কী কাজ।","কুলক্ষণে বিশ্বাস মানুষের তাওয়াক্কুল দুর্বল করে।","নবীজি বিষয়টি তিনবার বলে গুরুত্ব বুঝিয়েছেন।","কাজের সিদ্ধান্ত কুসংস্কার নয়, আল্লাহর ভরসায় নিতে হবে।"],"related_hadiths":[{"id":"4578","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"4382","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E60" s="4" t="n"/>
@@ -1868,12 +1856,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নবীজির কবর নিয়ে শির্ক থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি নিজের কবরকে ইবাদতের বস্তু না বানানোর দোয়া করেছেন এবং কবরকে মসজিদ বানানো থেকে সতর্ক করেছেন।"},"heading":{"title":"আমার কবরকে মূর্তি বানিও না: কবর বিষয়ে তাওহীদের শিক্ষা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম দোয়া করেছেন: হে আল্লাহ! তুমি আমার কবরকে এমন মূর্তিতে পরিণত করো না যার ইবাদত করা হবে। এরপর তিনি বলেন, যারা তাদের নবীদের কবরকে মসজিদ বানিয়েছে, আল্লাহ তাদের উপর রাগান্বিত হয়েছেন। এখানে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম নিজের কবর সম্পর্কেও মানুষকে সতর্ক করে দিয়েছেন। তাই নবীজির প্রতি ভালোবাসা কখনোই তাঁর কবরকে ইবাদতের কেন্দ্র বানানোর অনুমতি দেয় না। ভালোবাসা হবে অনুসরণে, দোয়া ও দরূদে, কিন্তু ইবাদত হবে শুধু আল্লাহর জন্য। কবরকে মূর্তি বা মসজিদের মতো বানানো তাওহীদের জন্য ভয়াবহ ঝুঁকি।"},"teachings":["নবীজির কবরকেও ইবাদতের বস্তু বানানো যাবে না।","কবরকে মসজিদ বানানো আল্লাহর রাগের কারণ হিসেবে এসেছে।","রাসূলের ভালোবাসা তাঁর অনুসরণে প্রকাশ পায়।","ইবাদত শুধু আল্লাহর জন্য সংরক্ষিত রাখতে হবে।"],"related_hadiths":[{"id":"712","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"713","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিকের তিন আলামত","description":"$book_name$ $hadith_number$ - $chapter_name$. কথা বললে মিথ্যা, ওয়াদা করলে ভঙ্গ এবং আমানত রাখলে খিয়ানত—মুনাফিকের তিন আলামত এখানে এসেছে।"},"heading":{"title":"মুনাফিকের তিন আলামত: মিথ্যা, ওয়াদা ভঙ্গ ও খিয়ানত","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মুনাফিকের তিনটি আলামত বলেছেন। প্রথমত, সে কথা বললে মিথ্যা বলে। দ্বিতীয়ত, ওয়াদা করলে তা ভঙ্গ করে। তৃতীয়ত, তার কাছে আমানত রাখা হলে সে খিয়ানত করে। এই হাদিস খুব পরিচিত, কিন্তু এর শিক্ষা প্রতিদিনের জীবনে দরকার। মুনাফিকের আলামত হাদিস আমাদের কথা, প্রতিশ্রুতি ও আমানতের ব্যাপারে সতর্ক করে। মানুষকে বিশ্বাসযোগ্য হতে হলে সত্য বলা, ওয়াদা রাখা এবং আমানত রক্ষা করা জরুরি। এখানে শুধু বড় লেনদেন নয়; কথা, দায়িত্ব, গোপন তথ্য বা মানুষের হক—সব ক্ষেত্রেই সততা দরকার।"},"teachings":["মিথ্যা বলা মুনাফিকের আলামতের মধ্যে এসেছে।","ওয়াদা করে তা ভেঙে ফেলা খারাপ আচরণ।","আমানত রাখলে খিয়ানত করা মুনাফিকী স্বভাবের লক্ষণ।","সত্যবাদিতা ও আমানতদারি মুসলিম চরিত্রের জরুরি অংশ।"],"related_hadiths":[{"id":"33","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"59","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2631","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E61" s="4" t="n"/>
@@ -1891,12 +1879,12 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যাদুর প্রতি বিশ্বাসের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপায়ী, আত্মীয়তা ছিন্নকারী ও যাদুতে বিশ্বাসকারীর বিষয়ে কঠোর সতর্কতা এসেছে।"},"heading":{"title":"যাদুর প্রতি বিশ্বাস: জান্নাত থেকে বঞ্চনার কঠোর সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের ব্যাপারে কঠোর সতর্কতা এসেছে: সর্বদা মদপানকারী, আত্মীয়তার বন্ধন ছিন্নকারী এবং যাদুর প্রতি বিশ্বাসকারী। এখানে যাদুর প্রতি বিশ্বাসকে এমন গুরুতর বিষয়ের সাথে উল্লেখ করা হয়েছে, যেগুলো মানুষের দ্বীন ও চরিত্রের বড় ক্ষতি করে। যাদুর প্রতি বিশ্বাস বলতে এমন নির্ভরতা বোঝায়, যেখানে মানুষ যাদুকে বাস্তব কল্যাণ-অকল্যাণের স্বাধীন ক্ষমতার মতো মনে করে বা যাদুকরের পথে ভরসা রাখে। এই হাদিস আমাদের মনে করিয়ে দেয়, ঈমানের জায়গায় যাদু, কুসংস্কার বা অন্ধ বিশ্বাস ঢুকতে দেওয়া যাবে না। আল্লাহর উপর ভরসা, আত্মীয়তার সম্পর্ক রক্ষা এবং হারাম কাজ থেকে বাঁচা—এসবই মুমিনের পথ।"},"teachings":["যাদুর প্রতি বিশ্বাসকে হাদিসে কঠোরভাবে নিন্দা করা হয়েছে।","মদপান ও আত্মীয়তা ছিন্ন করার মতো কাজ থেকেও সতর্ক থাকতে হবে।","যাদুকর বা যাদুর উপর ভরসা রাখা ঈমানের জন্য ক্ষতিকর।","মুমিনের ভরসা আল্লাহর উপর, অন্ধ বিশ্বাসের উপর নয়।"],"related_hadiths":[{"id":"2766","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুলক্ষণ দূর করার দোয়া ও তাওহীদ","description":"$book_name$ $hadith_number$ - $chapter_name$. অশুভ ধারণা কাজ থেকে ফিরিয়ে দিলে তা শির্ক; এর কাফ্ফারা হিসেবে তাওহীদের দোয়া শেখানো হয়েছে।"},"heading":{"title":"কুলক্ষণ দূর করার দোয়া: অশুভ ধারণা থেকে তাওহীদের পথে","description":"এই হাদিসে কুলক্ষণ বা অশুভ ধারণার বাস্তব ক্ষতি বোঝানো হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, কুলক্ষণ যে ব্যক্তিকে তার প্রয়োজন, দায়িত্ব বা কর্তব্য থেকে ফিরিয়ে রাখে, সে শির্ক করল। অর্থাৎ মনে অশুভ ধারণা আসা এক বিষয়, কিন্তু সেই ধারণার কারণে বৈধ কাজ ছেড়ে দেওয়া বড় ভুল। সাহাবীগণ এর কাফ্ফারা জানতে চাইলে নবীজি একটি দোয়া শিখিয়েছেন: اللَّهُمَّ لاَ خَيْرَ إِلاَّ خَيْرُكَ وَلاَ طَيْرَ إِلاَّ طَيْرُكَ وَلاَ إِلَهَ غَيْرُكَ। অর্থ হলো, হে আল্লাহ! তোমার মঙ্গল ছাড়া কোনো মঙ্গল নেই। তোমার অশুভ ছাড়া কোনো অশুভ নেই এবং তুমি ছাড়া কোনো মা‘বূদ নেই। এই দোয়া কুসংস্কার ভেঙে তাওহীদ মজবুত করে।"},"teachings":["অশুভ ধারণার কারণে দায়িত্ব ছেড়ে দেওয়া শির্কের পথে নিয়ে যায়।","কুলক্ষণ দূর করতে নবীজি তাওহীদের দোয়া শিখিয়েছেন।","মঙ্গল ও অমঙ্গলের নিয়ন্ত্রণ আল্লাহর হাতে।","মন দুর্বল হলে দোয়ার মাধ্যমে আল্লাহর দিকে ফিরতে হবে।"],"related_hadiths":[{"id":"4584","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"4578","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E62" s="4" t="n"/>
@@ -1914,12 +1902,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>161</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অশুভ লক্ষণ গ্রহণ শির্কী কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. কুলক্ষণ বা অশুভ ধারণাকে কাজের ভিত্তি বানানো শির্কী কাজ—এ কথা তিনবার বলা হয়েছে।"},"heading":{"title":"অশুভ লক্ষণ শির্ক: কুলক্ষণ বিশ্বাসের বিরুদ্ধে হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, অশুভ বা কুলক্ষণ ফল গ্রহণ করা শির্কী কাজ। তিনি কথাটি তিনবার বলেছেন। কোনো কথা তিনবার বলা হলে তার গুরুত্ব আরও পরিষ্কার হয়। কুলক্ষণ মানে কোনো পাখি, শব্দ, দিন, দিক, ব্যক্তি বা ঘটনার কারণে নিজের কাজে অশুভ ফল হবে—এমন বিশ্বাস করা। এই ধরনের ধারণা মানুষের সিদ্ধান্তকে আল্লাহর উপর ভরসা থেকে সরিয়ে দেয়। মুমিন কাজ করবে বৈধ কারণ, পরামর্শ ও দোয়ার মাধ্যমে; অশুভ ধারণার কারণে কাজ ছেড়ে দেবে না। এই হাদিস তাওহীদকে পরিষ্কার রাখার শিক্ষা দেয়। ভয়, অনুমান ও কুসংস্কার নয়—আল্লাহর উপর ভরসাই মুমিনের ভিত্তি।"},"teachings":["অশুভ লক্ষণকে সত্য ধরে নেওয়া শির্কী কাজ।","কুলক্ষণে বিশ্বাস মানুষের তাওয়াক্কুল দুর্বল করে।","নবীজি বিষয়টি তিনবার বলে গুরুত্ব বুঝিয়েছেন।","কাজের সিদ্ধান্ত কুসংস্কার নয়, আল্লাহর ভরসায় নিতে হবে।"],"related_hadiths":[{"id":"4578","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"4382","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিরক থেকে আমল রক্ষার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর সন্তুষ্টির জন্য আমল করা জরুরি; আমলে শিরক থাকলে তা প্রত্যাখ্যাত হওয়ার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"শিরক থেকে আমল রক্ষা: আল্লাহর জন্য খাঁটি ইবাদত","description":"এই হাদিসের মূল শিক্ষা হলো, ইবাদত ও সৎকাজ শুধু আল্লাহর জন্য হতে হবে। এখানে আল্লাহ তা‘আলা নিজেই বলেছেন, তিনি অংশীদারদের অংশীদারিত্ব থেকে সম্পূর্ণ মুক্ত। অর্থাৎ কেউ যদি কোনো আমল করে, কিন্তু সেই আমলে আল্লাহর সাথে অন্য কাউকে শরীক করে, তাহলে সেই আমল আল্লাহর কাছে গ্রহণযোগ্য থাকে না। শিরক শুধু প্রকাশ্য মূর্তি বা বস্তু পূজার মধ্যেই সীমাবদ্ধ নয়; আমলের উদ্দেশ্যে অন্য কারও সন্তুষ্টি, মর্যাদা বা প্রশংসা ঢুকে গেলে সেটিও ভয়ংকর বিষয়। এই হাদিস আমাদের নিয়ত ঠিক করার কথা স্মরণ করায়। তাই নামাজ, দান, শিক্ষা, দাওয়াত বা যে কোনো ভালো কাজের আগে নিজের অন্তরকে জিজ্ঞেস করা দরকার—আমি এটা কার জন্য করছি?"},"teachings":["আমল আল্লাহর জন্য খাঁটি না হলে তা গ্রহণযোগ্যতার ঝুঁকিতে পড়ে।","ইবাদতে আল্লাহর সাথে কাউকে শরীক করা বড় সতর্কতার বিষয়।","প্রতিটি ভালো কাজের আগে নিয়ত যাচাই করা দরকার।","মানুষের প্রশংসা নয়, আল্লাহর সন্তুষ্টিই আমলের মূল লক্ষ্য হওয়া উচিত।"],"related_hadiths":[{"id":"158","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7365","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E63" s="4" t="n"/>
@@ -1937,12 +1925,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিকের তিন আলামত","description":"$book_name$ $hadith_number$ - $chapter_name$. কথা বললে মিথ্যা, ওয়াদা করলে ভঙ্গ এবং আমানত রাখলে খিয়ানত—মুনাফিকের তিন আলামত এখানে এসেছে।"},"heading":{"title":"মুনাফিকের তিন আলামত: মিথ্যা, ওয়াদা ভঙ্গ ও খিয়ানত","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মুনাফিকের তিনটি আলামত বলেছেন। প্রথমত, সে কথা বললে মিথ্যা বলে। দ্বিতীয়ত, ওয়াদা করলে তা ভঙ্গ করে। তৃতীয়ত, তার কাছে আমানত রাখা হলে সে খিয়ানত করে। এই হাদিস খুব পরিচিত, কিন্তু এর শিক্ষা প্রতিদিনের জীবনে দরকার। মুনাফিকের আলামত হাদিস আমাদের কথা, প্রতিশ্রুতি ও আমানতের ব্যাপারে সতর্ক করে। মানুষকে বিশ্বাসযোগ্য হতে হলে সত্য বলা, ওয়াদা রাখা এবং আমানত রক্ষা করা জরুরি। এখানে শুধু বড় লেনদেন নয়; কথা, দায়িত্ব, গোপন তথ্য বা মানুষের হক—সব ক্ষেত্রেই সততা দরকার।"},"teachings":["মিথ্যা বলা মুনাফিকের আলামতের মধ্যে এসেছে।","ওয়াদা করে তা ভেঙে ফেলা খারাপ আচরণ।","আমানত রাখলে খিয়ানত করা মুনাফিকী স্বভাবের লক্ষণ।","সত্যবাদিতা ও আমানতদারি মুসলিম চরিত্রের জরুরি অংশ।"],"related_hadiths":[{"id":"33","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"59","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2631","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গোপন শিরক ও লোক দেখানো নামাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. লোক দেখানোর উদ্দেশ্যে ইবাদত করা গোপন শিরকের অন্তর্ভুক্ত; নামাজেও নিয়ত খাঁটি রাখা জরুরি।"},"heading":{"title":"গোপন শিরক: লোক দেখানো ইবাদত থেকে সতর্কতা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) দাজ্জাল নিয়ে আলোচনার সময় আরও ভয়ঙ্কর একটি বিষয়ের কথা বলেছেন—গোপন শিরক। হাদিসে এর উদাহরণ দেওয়া হয়েছে, একজন মানুষ নামাজে দাঁড়ায় এবং মনে মনে ভাবে, কেউ তাকে দেখছে; তাই সে নামাজকে মানুষের চোখে সুন্দর করে তুলতে চায়। এখানে মূল বিষয় হলো রিয়া বা লোক দেখানো আমল। নামাজের বাহ্যিক রূপ সুন্দর হলেও যদি উদ্দেশ্য মানুষের প্রশংসা হয়, তাহলে তা অন্তরের জন্য ক্ষতিকর। এই হাদিস আমাদের শেখায়, ইবাদতের সময় মানুষের চোখ নয়, আল্লাহর সন্তুষ্টিকে সামনে রাখতে হবে। নিজের আমল নিয়ে অহংকার বা সুনাম পাওয়ার আশা থেকে সতর্ক থাকা মুমিনের দরকারি কাজ।"},"teachings":["লোক দেখানোর জন্য নামাজ পড়া গোপন শিরকের একটি উদাহরণ।","ইবাদতের সৌন্দর্য মানুষের প্রশংসার জন্য নয়, আল্লাহর সন্তুষ্টির জন্য হওয়া উচিত।","নামাজে দাঁড়ানোর সময় অন্তরের নিয়ত ঠিক রাখা দরকার।","সুনাম, নেতৃত্ব বা দুনিয়ার স্বার্থ ইবাদতের উদ্দেশ্য হওয়া উচিত নয়।"],"related_hadiths":[{"id":"7365","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"158","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E64" s="4" t="n"/>
@@ -1960,12 +1948,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>163</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুলক্ষণ দূর করার দোয়া ও তাওহীদ","description":"$book_name$ $hadith_number$ - $chapter_name$. অশুভ ধারণা কাজ থেকে ফিরিয়ে দিলে তা শির্ক; এর কাফ্ফারা হিসেবে তাওহীদের দোয়া শেখানো হয়েছে।"},"heading":{"title":"কুলক্ষণ দূর করার দোয়া: অশুভ ধারণা থেকে তাওহীদের পথে","description":"এই হাদিসে কুলক্ষণ বা অশুভ ধারণার বাস্তব ক্ষতি বোঝানো হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, কুলক্ষণ যে ব্যক্তিকে তার প্রয়োজন, দায়িত্ব বা কর্তব্য থেকে ফিরিয়ে রাখে, সে শির্ক করল। অর্থাৎ মনে অশুভ ধারণা আসা এক বিষয়, কিন্তু সেই ধারণার কারণে বৈধ কাজ ছেড়ে দেওয়া বড় ভুল। সাহাবীগণ এর কাফ্ফারা জানতে চাইলে নবীজি একটি দোয়া শিখিয়েছেন: اللَّهُمَّ لاَ خَيْرَ إِلاَّ خَيْرُكَ وَلاَ طَيْرَ إِلاَّ طَيْرُكَ وَلاَ إِلَهَ غَيْرُكَ। অর্থ হলো, হে আল্লাহ! তোমার মঙ্গল ছাড়া কোনো মঙ্গল নেই। তোমার অশুভ ছাড়া কোনো অশুভ নেই এবং তুমি ছাড়া কোনো মা‘বূদ নেই। এই দোয়া কুসংস্কার ভেঙে তাওহীদ মজবুত করে।"},"teachings":["অশুভ ধারণার কারণে দায়িত্ব ছেড়ে দেওয়া শির্কের পথে নিয়ে যায়।","কুলক্ষণ দূর করতে নবীজি তাওহীদের দোয়া শিখিয়েছেন।","মঙ্গল ও অমঙ্গলের নিয়ন্ত্রণ আল্লাহর হাতে।","মন দুর্বল হলে দোয়ার মাধ্যমে আল্লাহর দিকে ফিরতে হবে।"],"related_hadiths":[{"id":"4584","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"4578","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দ্বীনে নতুন কাজের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীনের অংশ নয় এমন নতুন বিষয় ইবাদত হিসেবে চালু করলে তা প্রত্যাখ্যাত—হাদিসটি সুন্নাহ মেনে চলার শিক্ষা দেয়।"},"heading":{"title":"বিদআত থেকে বাঁচার হাদিস: দ্বীনে নতুন কিছু যোগ করার সতর্কতা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব স্পষ্টভাবে বলেছেন, যে ব্যক্তি দ্বীনের মধ্যে এমন কিছু নতুনভাবে চালু করে, যা দ্বীনের অংশ নয়, তা প্রত্যাখ্যাত। এখানে মূল শিক্ষা হলো, ইবাদতের ক্ষেত্রে নিজের পছন্দ, আবেগ বা প্রচলনকে দলিল বানানো যাবে না। ইসলাম আল্লাহর দেওয়া দ্বীন, আর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তা মানুষের কাছে পৌঁছে দিয়েছেন। তাই যে কাজকে ইবাদত বলা হবে, সেটির ভিত্তি কুরআন ও সুন্নাহতে থাকতে হবে। এই হাদিস মানুষকে বাড়াবাড়ি থেকে ফিরিয়ে আনে। দ্বীনের নামে নতুন আমল তৈরি করা দেখতে ভালো লাগলেও, হাদিসের ভাষায় তা গ্রহণযোগ্য নয়। তাই আমলের আগে জানা দরকার—এটি রাসূলের শেখানো পথে আছে কি না।"},"teachings":["দ্বীনের অংশ নয় এমন নতুন কাজ ইবাদত হিসেবে চালু করা গ্রহণযোগ্য নয়।","ইবাদতের মানদণ্ড ব্যক্তিগত পছন্দ নয়, কুরআন ও সুন্নাহ।","সুন্নাহ অনুসরণ করলে দ্বীনের সঠিক পথ পরিষ্কার থাকে।","ভালো মনে হলেই কোনো কাজ দ্বীনের আমল হয়ে যায় না।"],"related_hadiths":[{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E65" s="4" t="n"/>
@@ -1983,12 +1971,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>164</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিরক থেকে আমল রক্ষার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর সন্তুষ্টির জন্য আমল করা জরুরি; আমলে শিরক থাকলে তা প্রত্যাখ্যাত হওয়ার কঠোর সতর্কতা এসেছে।"},"heading":{"title":"শিরক থেকে আমল রক্ষা: আল্লাহর জন্য খাঁটি ইবাদত","description":"এই হাদিসের মূল শিক্ষা হলো, ইবাদত ও সৎকাজ শুধু আল্লাহর জন্য হতে হবে। এখানে আল্লাহ তা‘আলা নিজেই বলেছেন, তিনি অংশীদারদের অংশীদারিত্ব থেকে সম্পূর্ণ মুক্ত। অর্থাৎ কেউ যদি কোনো আমল করে, কিন্তু সেই আমলে আল্লাহর সাথে অন্য কাউকে শরীক করে, তাহলে সেই আমল আল্লাহর কাছে গ্রহণযোগ্য থাকে না। শিরক শুধু প্রকাশ্য মূর্তি বা বস্তু পূজার মধ্যেই সীমাবদ্ধ নয়; আমলের উদ্দেশ্যে অন্য কারও সন্তুষ্টি, মর্যাদা বা প্রশংসা ঢুকে গেলে সেটিও ভয়ংকর বিষয়। এই হাদিস আমাদের নিয়ত ঠিক করার কথা স্মরণ করায়। তাই নামাজ, দান, শিক্ষা, দাওয়াত বা যে কোনো ভালো কাজের আগে নিজের অন্তরকে জিজ্ঞেস করা দরকার—আমি এটা কার জন্য করছি?"},"teachings":["আমল আল্লাহর জন্য খাঁটি না হলে তা গ্রহণযোগ্যতার ঝুঁকিতে পড়ে।","ইবাদতে আল্লাহর সাথে কাউকে শরীক করা বড় সতর্কতার বিষয়।","প্রতিটি ভালো কাজের আগে নিয়ত যাচাই করা দরকার।","মানুষের প্রশংসা নয়, আল্লাহর সন্তুষ্টিই আমলের মূল লক্ষ্য হওয়া উচিত।"],"related_hadiths":[{"id":"158","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7365","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নির্দেশনাহীন আমলের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের নির্দেশনা ছাড়া ইবাদত করলে তা পরিত্যাজ্য; তাই আমলকে সুন্নাহর সাথে মিলিয়ে করা জরুরি।"},"heading":{"title":"সুন্নাহ ছাড়া আমল নয়: নির্দেশনাহীন কাজের সতর্কতা","description":"এই হাদিসে বলা হয়েছে, যে ব্যক্তি এমন আমল করে যার ওপর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কোনো নির্দেশনা নেই, তা পরিত্যাজ্য। এখানে আমলের শুদ্ধতার গুরুত্বপূর্ণ নিয়ম বোঝানো হয়েছে। শুধু ভালো উদ্দেশ্য থাকলেই ইবাদত সঠিক হয়ে যায় না; ইবাদতের পদ্ধতিও রাসূলের শেখানো মতো হতে হবে। কেউ যদি নামাজ, রোজা, দোয়া, যিকির বা অন্য কোনো ইবাদতে নিজের মতো নিয়ম বানায়, তাহলে তা হাদিসের সতর্কতার মধ্যে পড়ে। এই শিক্ষা মানুষকে সুন্নাহর দিকে ফিরিয়ে নেয়। দ্বীনের কাজে নিরাপদ পথ হলো—যা প্রমাণিত, তা করা; যা প্রমাণিত নয়, তা ইবাদত হিসেবে না ধরা। এতে আমল পরিষ্কার থাকে এবং দ্বীনের নামে বাড়তি চাপ তৈরি হয় না।"},"teachings":["রাসূলের নির্দেশনা ছাড়া কোনো কাজ ইবাদত হিসেবে গ্রহণযোগ্য নয়।","ভালো নিয়তের পাশাপাশি সঠিক পদ্ধতিও জরুরি।","সুন্নাহর সাথে মিলিয়ে আমল করা নিরাপদ পথ।","নিজের বানানো নিয়মকে দ্বীনের অংশ বলা ঠিক নয়।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E66" s="4" t="n"/>
@@ -2006,12 +1994,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>165</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গোপন শিরক ও লোক দেখানো নামাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. লোক দেখানোর উদ্দেশ্যে ইবাদত করা গোপন শিরকের অন্তর্ভুক্ত; নামাজেও নিয়ত খাঁটি রাখা জরুরি।"},"heading":{"title":"গোপন শিরক: লোক দেখানো ইবাদত থেকে সতর্কতা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) দাজ্জাল নিয়ে আলোচনার সময় আরও ভয়ঙ্কর একটি বিষয়ের কথা বলেছেন—গোপন শিরক। হাদিসে এর উদাহরণ দেওয়া হয়েছে, একজন মানুষ নামাজে দাঁড়ায় এবং মনে মনে ভাবে, কেউ তাকে দেখছে; তাই সে নামাজকে মানুষের চোখে সুন্দর করে তুলতে চায়। এখানে মূল বিষয় হলো রিয়া বা লোক দেখানো আমল। নামাজের বাহ্যিক রূপ সুন্দর হলেও যদি উদ্দেশ্য মানুষের প্রশংসা হয়, তাহলে তা অন্তরের জন্য ক্ষতিকর। এই হাদিস আমাদের শেখায়, ইবাদতের সময় মানুষের চোখ নয়, আল্লাহর সন্তুষ্টিকে সামনে রাখতে হবে। নিজের আমল নিয়ে অহংকার বা সুনাম পাওয়ার আশা থেকে সতর্ক থাকা মুমিনের দরকারি কাজ।"},"teachings":["লোক দেখানোর জন্য নামাজ পড়া গোপন শিরকের একটি উদাহরণ।","ইবাদতের সৌন্দর্য মানুষের প্রশংসার জন্য নয়, আল্লাহর সন্তুষ্টির জন্য হওয়া উচিত।","নামাজে দাঁড়ানোর সময় অন্তরের নিয়ত ঠিক রাখা দরকার।","সুনাম, নেতৃত্ব বা দুনিয়ার স্বার্থ ইবাদতের উদ্দেশ্য হওয়া উচিত নয়।"],"related_hadiths":[{"id":"7365","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"158","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিতাবুল্লাহ ও নবীর হেদায়াত","description":"$book_name$ $hadith_number$ - $chapter_name$. শ্রেষ্ঠ বাণী আল্লাহর কিতাব, শ্রেষ্ঠ হেদায়াত রাসূলের হেদায়াত; বিদআত থেকে সতর্ক থাকার শিক্ষা।"},"heading":{"title":"শ্রেষ্ঠ হেদায়াত: আল্লাহর কিতাব ও রাসূলের সুন্নাহ","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) হামদ ও ছালাতের পর কয়েকটি বড় মূলনীতি বলেছেন। শ্রেষ্ঠ বাণী হলো আল্লাহর কিতাব, আর শ্রেষ্ঠ হেদায়াত হলো মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর হেদায়াত। এর মানে, মুসলিমের পথচলার প্রধান আলো কুরআন ও সুন্নাহ। এরপর তিনি বলেছেন, দ্বীনের মধ্যে নতুন সৃষ্টি নিকৃষ্ট কাজ এবং প্রত্যেক নতুন সৃষ্টি ভ্রষ্টতা। এই হাদিস আমাদের শেখায়, দ্বীনকে সুন্দর করার নামে নতুন নিয়ম বানানো নয়; বরং আল্লাহর কিতাব ও নবীর পথ আঁকড়ে ধরা দরকার। ইবাদত, বিশ্বাস ও জীবনযাপনে সুন্নাহকে গুরুত্ব দিলে মানুষ বিভ্রান্তি থেকে দূরে থাকার সুযোগ পায়।"},"teachings":["আল্লাহর কিতাব মুসলিমের জন্য শ্রেষ্ঠ বাণী।","রাসূলুল্লাহর হেদায়াতই অনুসরণের জন্য শ্রেষ্ঠ পথ।","দ্বীনের মধ্যে নতুন সৃষ্টি থেকে সতর্ক থাকা দরকার।","কুরআন ও সুন্নাহকে জীবনের মূল দিশা বানানো উচিত।"],"related_hadiths":[{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E67" s="4" t="n"/>
@@ -2029,12 +2017,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>166</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দ্বীনে নতুন কাজের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীনের অংশ নয় এমন নতুন বিষয় ইবাদত হিসেবে চালু করলে তা প্রত্যাখ্যাত—হাদিসটি সুন্নাহ মেনে চলার শিক্ষা দেয়।"},"heading":{"title":"বিদআত থেকে বাঁচার হাদিস: দ্বীনে নতুন কিছু যোগ করার সতর্কতা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব স্পষ্টভাবে বলেছেন, যে ব্যক্তি দ্বীনের মধ্যে এমন কিছু নতুনভাবে চালু করে, যা দ্বীনের অংশ নয়, তা প্রত্যাখ্যাত। এখানে মূল শিক্ষা হলো, ইবাদতের ক্ষেত্রে নিজের পছন্দ, আবেগ বা প্রচলনকে দলিল বানানো যাবে না। ইসলাম আল্লাহর দেওয়া দ্বীন, আর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তা মানুষের কাছে পৌঁছে দিয়েছেন। তাই যে কাজকে ইবাদত বলা হবে, সেটির ভিত্তি কুরআন ও সুন্নাহতে থাকতে হবে। এই হাদিস মানুষকে বাড়াবাড়ি থেকে ফিরিয়ে আনে। দ্বীনের নামে নতুন আমল তৈরি করা দেখতে ভালো লাগলেও, হাদিসের ভাষায় তা গ্রহণযোগ্য নয়। তাই আমলের আগে জানা দরকার—এটি রাসূলের শেখানো পথে আছে কি না।"},"teachings":["দ্বীনের অংশ নয় এমন নতুন কাজ ইবাদত হিসেবে চালু করা গ্রহণযোগ্য নয়।","ইবাদতের মানদণ্ড ব্যক্তিগত পছন্দ নয়, কুরআন ও সুন্নাহ।","সুন্নাহ অনুসরণ করলে দ্বীনের সঠিক পথ পরিষ্কার থাকে।","ভালো মনে হলেই কোনো কাজ দ্বীনের আমল হয়ে যায় না।"],"related_hadiths":[{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জাহেলী রীতি ও অন্যায় রক্তপাত","description":"$book_name$ $hadith_number$ - $chapter_name$. হারামে অন্যায়, ইসলামে জাহেলী রীতি চাওয়া ও অন্যায় রক্তপাত—এসব থেকে কঠোরভাবে সতর্ক করা হয়েছে।"},"heading":{"title":"জাহেলী রীতি থেকে দূরে থাকা: ইসলামের পরিষ্কার সতর্কতা","description":"এই হাদিসে তিন ধরনের মানুষকে আল্লাহর কাছে সবচেয়ে বেশি ঘৃণিত বলা হয়েছে। প্রথমত, যে হারাম এলাকায় নিষিদ্ধ কাজ করে। দ্বিতীয়ত, যে ইসলামের মধ্যে জাহেলী যুগের রীতি চালু করতে চায়। তৃতীয়ত, যে অন্যায়ভাবে কারো রক্ত চাইতে থাকে শুধু রক্তপাতের উদ্দেশ্যে। এখানে মূল শিক্ষা হলো, ইসলাম মানুষকে পবিত্রতা, ন্যায় ও সুস্থ রীতি শেখায়। জাহেলিয়াত মানে এমন রীতি, যা ইসলামি নীতির বিপরীত। তাই মুসলিম সমাজে অন্যায় রসম, হিংসা, রক্তপাত বা পুরনো অন্ধ অভ্যাসকে ফিরিয়ে আনার চেষ্টা বিপজ্জনক। এই হাদিস আমাদের মনে করিয়ে দেয়, দ্বীনের নামে বা সমাজের নামে কোনো কাজ করা হলেও তা যদি ইসলামের ন্যায়নীতির বিরুদ্ধে যায়, তবে তা বর্জনীয়।"},"teachings":["হারাম এলাকায় নিষিদ্ধ কাজ করা কঠোর সতর্কতার বিষয়।","ইসলামের মধ্যে জাহেলী রীতি ফিরিয়ে আনার চেষ্টা নিন্দনীয়।","অন্যায়ভাবে কারো রক্তপাত চাওয়া বড় অন্যায়।","মুসলিমের কাজ হলো ন্যায়, পবিত্রতা ও ইসলামী রীতি মেনে চলা।"],"related_hadiths":[{"id":"6882","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E68" s="4" t="n"/>
@@ -2052,12 +2040,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>167</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নির্দেশনাহীন আমলের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের নির্দেশনা ছাড়া ইবাদত করলে তা পরিত্যাজ্য; তাই আমলকে সুন্নাহর সাথে মিলিয়ে করা জরুরি।"},"heading":{"title":"সুন্নাহ ছাড়া আমল নয়: নির্দেশনাহীন কাজের সতর্কতা","description":"এই হাদিসে বলা হয়েছে, যে ব্যক্তি এমন আমল করে যার ওপর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কোনো নির্দেশনা নেই, তা পরিত্যাজ্য। এখানে আমলের শুদ্ধতার গুরুত্বপূর্ণ নিয়ম বোঝানো হয়েছে। শুধু ভালো উদ্দেশ্য থাকলেই ইবাদত সঠিক হয়ে যায় না; ইবাদতের পদ্ধতিও রাসূলের শেখানো মতো হতে হবে। কেউ যদি নামাজ, রোজা, দোয়া, যিকির বা অন্য কোনো ইবাদতে নিজের মতো নিয়ম বানায়, তাহলে তা হাদিসের সতর্কতার মধ্যে পড়ে। এই শিক্ষা মানুষকে সুন্নাহর দিকে ফিরিয়ে নেয়। দ্বীনের কাজে নিরাপদ পথ হলো—যা প্রমাণিত, তা করা; যা প্রমাণিত নয়, তা ইবাদত হিসেবে না ধরা। এতে আমল পরিষ্কার থাকে এবং দ্বীনের নামে বাড়তি চাপ তৈরি হয় না।"},"teachings":["রাসূলের নির্দেশনা ছাড়া কোনো কাজ ইবাদত হিসেবে গ্রহণযোগ্য নয়।","ভালো নিয়তের পাশাপাশি সঠিক পদ্ধতিও জরুরি।","সুন্নাহর সাথে মিলিয়ে আমল করা নিরাপদ পথ।","নিজের বানানো নিয়মকে দ্বীনের অংশ বলা ঠিক নয়।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রাসূলের আনুগত্য ও জান্নাতের পথ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের আনুগত্য জান্নাতের পথে নিয়ে যায়; অবাধ্যতা মানুষকে নিজের জন্য ক্ষতির দিকে ঠেলে দেয়।"},"heading":{"title":"রাসূলের আনুগত্য: জান্নাতের পথে চলার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের সবাই জান্নাতে প্রবেশ করবে, কেবল যে অসম্মত সে ছাড়া। সাহাবীগণ জানতে চাইলেন, কে অসম্মত? তিনি বললেন, যে তাঁর আনুগত্য করবে, সে জান্নাতে প্রবেশ করবে; আর যে তাঁর অবাধ্যতা করবে, সে যেন নিজেই অসম্মত হলো। এই কথায় রাসূলের আনুগত্যের গুরুত্ব পরিষ্কার। মুসলিম পরিচয় শুধু মুখের দাবি নয়; জীবনে নবীর নির্দেশ মানার চেষ্টা থাকতে হবে। সুন্নাহ মেনে চলা, তাঁর নিষেধ থেকে দূরে থাকা এবং তাঁর দেখানো পথে ইবাদত করা—এসবই আনুগত্যের অংশ। হাদিসটি কাউকে হতাশ করার জন্য নয়, বরং মানুষকে রাসূলের পথে ফিরিয়ে আনার জন্য শক্তিশালী স্মরণিকা।"},"teachings":["রাসূলের আনুগত্য জান্নাতের পথ অনুসরণের কারণ।","অবাধ্যতা মানুষকে নিজেই ক্ষতির পথে নিতে পারে।","মুসলিম জীবনে সুন্নাহ মানার চেষ্টা জরুরি।","নবীর নির্দেশকে ভালোবাসা ও মান্য করা ঈমানের দাবি।"],"related_hadiths":[{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E69" s="4" t="n"/>
@@ -2075,12 +2063,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>168</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিতাবুল্লাহ ও নবীর হেদায়াত","description":"$book_name$ $hadith_number$ - $chapter_name$. শ্রেষ্ঠ বাণী আল্লাহর কিতাব, শ্রেষ্ঠ হেদায়াত রাসূলের হেদায়াত; বিদআত থেকে সতর্ক থাকার শিক্ষা।"},"heading":{"title":"শ্রেষ্ঠ হেদায়াত: আল্লাহর কিতাব ও রাসূলের সুন্নাহ","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) হামদ ও ছালাতের পর কয়েকটি বড় মূলনীতি বলেছেন। শ্রেষ্ঠ বাণী হলো আল্লাহর কিতাব, আর শ্রেষ্ঠ হেদায়াত হলো মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর হেদায়াত। এর মানে, মুসলিমের পথচলার প্রধান আলো কুরআন ও সুন্নাহ। এরপর তিনি বলেছেন, দ্বীনের মধ্যে নতুন সৃষ্টি নিকৃষ্ট কাজ এবং প্রত্যেক নতুন সৃষ্টি ভ্রষ্টতা। এই হাদিস আমাদের শেখায়, দ্বীনকে সুন্দর করার নামে নতুন নিয়ম বানানো নয়; বরং আল্লাহর কিতাব ও নবীর পথ আঁকড়ে ধরা দরকার। ইবাদত, বিশ্বাস ও জীবনযাপনে সুন্নাহকে গুরুত্ব দিলে মানুষ বিভ্রান্তি থেকে দূরে থাকার সুযোগ পায়।"},"teachings":["আল্লাহর কিতাব মুসলিমের জন্য শ্রেষ্ঠ বাণী।","রাসূলুল্লাহর হেদায়াতই অনুসরণের জন্য শ্রেষ্ঠ পথ।","দ্বীনের মধ্যে নতুন সৃষ্টি থেকে সতর্ক থাকা দরকার।","কুরআন ও সুন্নাহকে জীবনের মূল দিশা বানানো উচিত।"],"related_hadiths":[{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জান্নাতের আহ্বান ও নবীর অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. জান্নাতের দাওয়াতে সাড়া দেওয়া মানে মুহাম্মাদকে মানা; তাঁর আনুগত্য আল্লাহর আনুগত্যের সাথে যুক্ত।"},"heading":{"title":"জান্নাতের আহ্বান: মুহাম্মাদের আনুগত্যই আল্লাহর আনুগত্য","description":"এই হাদিসে ফেরেশতাদের কথার মাধ্যমে একটি সুন্দর উদাহরণ এসেছে। এক ব্যক্তি ঘর বানালেন, ভোজের আয়োজন করলেন এবং একজন আহ্বায়ক পাঠালেন। যে আহ্বানে সাড়া দিল, সে ঘরে ঢুকল এবং খাবার পেল; যে সাড়া দিল না, সে ঢুকতেও পারল না, খেতেও পারল না। এরপর ব্যাখ্যা করা হলো—ঘরটি জান্নাত, আহ্বায়ক হলেন মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)। তাই যে মুহাম্মাদের আনুগত্য করল, সে আল্লাহর আনুগত্য করল; আর যে তাঁর অবাধ্য হলো, সে আল্লাহর অবাধ্য হলো। এই হাদিস আমাদের শেখায়, জান্নাতের পথ কল্পনা বা নিজের বানানো নিয়মে নয়; নবীর আহ্বানে সাড়া দেওয়ার মধ্যেই সঠিক পথ।"},"teachings":["মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর আহ্বানে সাড়া দেওয়া আল্লাহর আনুগত্যের অংশ।","জান্নাতের পথে নবীর নির্দেশনা অপরিহার্য।","নবীর অবাধ্যতা আল্লাহর অবাধ্যতার সাথে যুক্ত।","সঠিক পথ বুঝতে রাসূলের দাওয়াতকে গ্রহণ করা দরকার।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1988","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E70" s="4" t="n"/>
@@ -2098,12 +2086,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>169</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জাহেলী রীতি ও অন্যায় রক্তপাত","description":"$book_name$ $hadith_number$ - $chapter_name$. হারামে অন্যায়, ইসলামে জাহেলী রীতি চাওয়া ও অন্যায় রক্তপাত—এসব থেকে কঠোরভাবে সতর্ক করা হয়েছে।"},"heading":{"title":"জাহেলী রীতি থেকে দূরে থাকা: ইসলামের পরিষ্কার সতর্কতা","description":"এই হাদিসে তিন ধরনের মানুষকে আল্লাহর কাছে সবচেয়ে বেশি ঘৃণিত বলা হয়েছে। প্রথমত, যে হারাম এলাকায় নিষিদ্ধ কাজ করে। দ্বিতীয়ত, যে ইসলামের মধ্যে জাহেলী যুগের রীতি চালু করতে চায়। তৃতীয়ত, যে অন্যায়ভাবে কারো রক্ত চাইতে থাকে শুধু রক্তপাতের উদ্দেশ্যে। এখানে মূল শিক্ষা হলো, ইসলাম মানুষকে পবিত্রতা, ন্যায় ও সুস্থ রীতি শেখায়। জাহেলিয়াত মানে এমন রীতি, যা ইসলামি নীতির বিপরীত। তাই মুসলিম সমাজে অন্যায় রসম, হিংসা, রক্তপাত বা পুরনো অন্ধ অভ্যাসকে ফিরিয়ে আনার চেষ্টা বিপজ্জনক। এই হাদিস আমাদের মনে করিয়ে দেয়, দ্বীনের নামে বা সমাজের নামে কোনো কাজ করা হলেও তা যদি ইসলামের ন্যায়নীতির বিরুদ্ধে যায়, তবে তা বর্জনীয়।"},"teachings":["হারাম এলাকায় নিষিদ্ধ কাজ করা কঠোর সতর্কতার বিষয়।","ইসলামের মধ্যে জাহেলী রীতি ফিরিয়ে আনার চেষ্টা নিন্দনীয়।","অন্যায়ভাবে কারো রক্তপাত চাওয়া বড় অন্যায়।","মুসলিমের কাজ হলো ন্যায়, পবিত্রতা ও ইসলামী রীতি মেনে চলা।"],"related_hadiths":[{"id":"6882","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইবাদতে মধ্যপন্থা ও সুন্নাহ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের সুন্নাহ হলো ইবাদত, বিশ্রাম, সিয়াম ও বিবাহে ভারসাম্যপূর্ণ পথ; বাড়াবাড়ি নয়।"},"heading":{"title":"ইবাদতে মধ্যপন্থা: রাসূলের সুন্নাহ থেকে মুখ ফিরানো নয়","description":"এই হাদিসে তিনজন ব্যক্তি রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর ইবাদত সম্পর্কে জানতে এসে নিজেদের জন্য কঠোর সিদ্ধান্ত নেয়। একজন বলল, সে সারারাত নামাজ পড়বে; আরেকজন বলল, সবসময় রোজা রাখবে; তৃতীয়জন বলল, কখনো বিয়ে করবে না। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাদের ভুল ঠিক করে দিলেন। তিনি বললেন, তিনি আল্লাহকে বেশি ভয় করেন এবং বেশি পরহেযগার, তবু তিনি রোজা রাখেন আবার ছাড়েন, নামাজ পড়েন আবার ঘুমান, এবং বিবাহ করেছেন। তাই সুন্নাহ মানে অস্বাভাবিক কঠোরতা নয়; বরং আল্লাহর ইবাদত ও মানুষের স্বাভাবিক জীবনের মধ্যে সঠিক ভারসাম্য। এই হাদিস ইবাদতে বাড়াবাড়ি থেকে বাঁচতে শেখায়।"},"teachings":["ইবাদতে অতিরিক্ত বাড়াবাড়ি রাসূলের সুন্নাহ নয়।","রোজা, নামাজ, ঘুম ও বিবাহ—সবকিছুর মধ্যে ভারসাম্য দরকার।","রাসূলুল্লাহর জীবনই আল্লাহভীতির সঠিক নমুনা।","সুন্নাহ থেকে মুখ ফিরিয়ে নিজের বানানো পথ নেওয়া বিপজ্জনক।"],"related_hadiths":[{"id":"3294","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1961","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1981","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E71" s="4" t="n"/>
@@ -2121,15 +2109,19 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রাসূলের আনুগত্য ও জান্নাতের পথ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের আনুগত্য জান্নাতের পথে নিয়ে যায়; অবাধ্যতা মানুষকে নিজের জন্য ক্ষতির দিকে ঠেলে দেয়।"},"heading":{"title":"রাসূলের আনুগত্য: জান্নাতের পথে চলার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের সবাই জান্নাতে প্রবেশ করবে, কেবল যে অসম্মত সে ছাড়া। সাহাবীগণ জানতে চাইলেন, কে অসম্মত? তিনি বললেন, যে তাঁর আনুগত্য করবে, সে জান্নাতে প্রবেশ করবে; আর যে তাঁর অবাধ্যতা করবে, সে যেন নিজেই অসম্মত হলো। এই কথায় রাসূলের আনুগত্যের গুরুত্ব পরিষ্কার। মুসলিম পরিচয় শুধু মুখের দাবি নয়; জীবনে নবীর নির্দেশ মানার চেষ্টা থাকতে হবে। সুন্নাহ মেনে চলা, তাঁর নিষেধ থেকে দূরে থাকা এবং তাঁর দেখানো পথে ইবাদত করা—এসবই আনুগত্যের অংশ। হাদিসটি কাউকে হতাশ করার জন্য নয়, বরং মানুষকে রাসূলের পথে ফিরিয়ে আনার জন্য শক্তিশালী স্মরণিকা।"},"teachings":["রাসূলের আনুগত্য জান্নাতের পথ অনুসরণের কারণ।","অবাধ্যতা মানুষকে নিজেই ক্ষতির পথে নিতে পারে।","মুসলিম জীবনে সুন্নাহ মানার চেষ্টা জরুরি।","নবীর নির্দেশকে ভালোবাসা ও মান্য করা ঈমানের দাবি।"],"related_hadiths":[{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="n"/>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানতদারি ও অঙ্গীকারের মূল্য","description":"$book_name$ $hadith_number$ - $chapter_name$. যার আমানতদারি নেই তার ঈমান নেই, আর যার অঙ্গীকারের মূল্য নেই তার দ্বীন নেই—এ কঠোর শিক্ষা এসেছে।"},"heading":{"title":"আমানতদারি ও অঙ্গীকার পূরণ: পূর্ণ ঈমানের বড় লক্ষণ","description":"এই হাদিসে আনাস (রাঃ) বলেন, রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব কমই এমন উপদেশ দিয়েছেন, যাতে তিনি বলেননি: যার আমানতদারি নেই তার ঈমান নেই এবং যার অঙ্গীকারের মূল্য নেই তার দ্বীন নেই। এই কথা মুসলিম জীবনে আমানত ও অঙ্গীকারের গুরুত্ব খুব স্পষ্ট করে। আমানত শুধু টাকা বা মাল নয়; দায়িত্ব, কথা, গোপন বিষয় এবং মানুষের অধিকারও আমানতের মধ্যে পড়তে পারে—ইসলামী স্কলারদের মতে। তবে হাদিসের সরাসরি শিক্ষা হলো, আমানত রক্ষা ও অঙ্গীকার পূরণ ছাড়া মানুষের ঈমানি চরিত্র পূর্ণ হয় না। তাই কথা দিলে তা রক্ষা করা এবং দায়িত্ব পেলে তা ঠিকমতো পালন করা জরুরি।"},"teachings":["আমানতদারি ঈমানি চরিত্রের গুরুত্বপূর্ণ অংশ।","অঙ্গীকারের মূল্য না দিলে দ্বীনি আচরণ ক্ষতিগ্রস্ত হয়।","উপদেশে আমানত ও ওয়াদার কথা বারবার স্মরণ করানো হয়েছে।","বিশ্বাসযোগ্য হওয়া মুসলিম জীবনের বড় গুণ।"],"related_hadiths":[{"id":"35","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"55","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>related_hadiths[1]: unknown book label "মুসনাদে আহমাদ ১১৯৩৫"</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="46" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
@@ -2144,12 +2136,12 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>170</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জান্নাতের আহ্বান ও নবীর অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. জান্নাতের দাওয়াতে সাড়া দেওয়া মানে মুহাম্মাদকে মানা; তাঁর আনুগত্য আল্লাহর আনুগত্যের সাথে যুক্ত।"},"heading":{"title":"জান্নাতের আহ্বান: মুহাম্মাদের আনুগত্যই আল্লাহর আনুগত্য","description":"এই হাদিসে ফেরেশতাদের কথার মাধ্যমে একটি সুন্দর উদাহরণ এসেছে। এক ব্যক্তি ঘর বানালেন, ভোজের আয়োজন করলেন এবং একজন আহ্বায়ক পাঠালেন। যে আহ্বানে সাড়া দিল, সে ঘরে ঢুকল এবং খাবার পেল; যে সাড়া দিল না, সে ঢুকতেও পারল না, খেতেও পারল না। এরপর ব্যাখ্যা করা হলো—ঘরটি জান্নাত, আহ্বায়ক হলেন মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)। তাই যে মুহাম্মাদের আনুগত্য করল, সে আল্লাহর আনুগত্য করল; আর যে তাঁর অবাধ্য হলো, সে আল্লাহর অবাধ্য হলো। এই হাদিস আমাদের শেখায়, জান্নাতের পথ কল্পনা বা নিজের বানানো নিয়মে নয়; নবীর আহ্বানে সাড়া দেওয়ার মধ্যেই সঠিক পথ।"},"teachings":["মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর আহ্বানে সাড়া দেওয়া আল্লাহর আনুগত্যের অংশ।","জান্নাতের পথে নবীর নির্দেশনা অপরিহার্য।","নবীর অবাধ্যতা আল্লাহর অবাধ্যতার সাথে যুক্ত।","সঠিক পথ বুঝতে রাসূলের দাওয়াতকে গ্রহণ করা দরকার।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1988","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সৎপথে আহ্বান ও গোনাহের দায়","description":"$book_name$ $hadith_number$ - $chapter_name$. সৎপথে ডাকার সওয়াব আছে, আর পথভ্রষ্টতার দিকে ডাকলে অনুসারীদের মতো গোনাহের দায় আসে।"},"heading":{"title":"সৎপথে আহ্বান: দাওয়াতের সওয়াব ও দায়িত্ব","description":"এই হাদিসে দাওয়াতের বড় দায়িত্ব বোঝানো হয়েছে। যে ব্যক্তি কাউকে সৎ পথের দিকে আহ্বান করে, তার জন্য অনুসারীদের মতো সওয়াব থাকে; অথচ অনুসারীদের সওয়াব কমে না। আবার যে পথভ্রষ্টতার দিকে আহ্বান করে, তার ওপর অনুসারীদের মতো গোনাহ থাকে; অথচ তাদের গোনাহও কমে না। তাই কথা, লেখা, শিক্ষা, পোস্ট, পরামর্শ—সবকিছুতেই সতর্ক থাকা দরকার। মানুষকে ভালো কাজে ডাকা শুধু সুন্দর কাজ নয়, এটি দায়িত্বও। একইভাবে ভুল পথ, বিদআত, পাপ বা বিভ্রান্তি ছড়ানো হালকা বিষয় নয়। এই হাদিস আমাদের শেখায়, প্রভাবশালী কথা বলার আগে ভাবতে হবে—এটি মানুষকে আল্লাহর পথে ডাকছে, নাকি ভুল পথে ঠেলে দিচ্ছে?"},"teachings":["সৎপথে আহ্বান করলে অনুসারীদের মতো সওয়াবের অংশ পাওয়া যায়।","ভুল পথে ডাকলে অনুসারীদের মতো গোনাহের দায় আসতে পারে।","দাওয়াত, লেখা ও পরামর্শে সতর্ক থাকা জরুরি।","সওয়াব বা গোনাহ কারও থেকে কমে না; প্রত্যেকের নিজ নিজ হিসাব থাকে।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E73" s="4" t="n"/>
@@ -2167,12 +2159,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>171</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইবাদতে মধ্যপন্থা ও সুন্নাহ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের সুন্নাহ হলো ইবাদত, বিশ্রাম, সিয়াম ও বিবাহে ভারসাম্যপূর্ণ পথ; বাড়াবাড়ি নয়।"},"heading":{"title":"ইবাদতে মধ্যপন্থা: রাসূলের সুন্নাহ থেকে মুখ ফিরানো নয়","description":"এই হাদিসে তিনজন ব্যক্তি রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর ইবাদত সম্পর্কে জানতে এসে নিজেদের জন্য কঠোর সিদ্ধান্ত নেয়। একজন বলল, সে সারারাত নামাজ পড়বে; আরেকজন বলল, সবসময় রোজা রাখবে; তৃতীয়জন বলল, কখনো বিয়ে করবে না। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাদের ভুল ঠিক করে দিলেন। তিনি বললেন, তিনি আল্লাহকে বেশি ভয় করেন এবং বেশি পরহেযগার, তবু তিনি রোজা রাখেন আবার ছাড়েন, নামাজ পড়েন আবার ঘুমান, এবং বিবাহ করেছেন। তাই সুন্নাহ মানে অস্বাভাবিক কঠোরতা নয়; বরং আল্লাহর ইবাদত ও মানুষের স্বাভাবিক জীবনের মধ্যে সঠিক ভারসাম্য। এই হাদিস ইবাদতে বাড়াবাড়ি থেকে বাঁচতে শেখায়।"},"teachings":["ইবাদতে অতিরিক্ত বাড়াবাড়ি রাসূলের সুন্নাহ নয়।","রোজা, নামাজ, ঘুম ও বিবাহ—সবকিছুর মধ্যে ভারসাম্য দরকার।","রাসূলুল্লাহর জীবনই আল্লাহভীতির সঠিক নমুনা।","সুন্নাহ থেকে মুখ ফিরিয়ে নিজের বানানো পথ নেওয়া বিপজ্জনক।"],"related_hadiths":[{"id":"3294","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1961","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1981","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অপরিচিতদের জন্য সুসংবাদ","description":"$book_name$ $hadith_number$ - $chapter_name$. ইসলাম অপরিচিতভাবে শুরু হয়েছে এবং আবার অপরিচিত হবে; সুন্নাহ ঠিক রাখাদের জন্য সুসংবাদ।"},"heading":{"title":"ইসলাম অপরিচিত হবে: সুন্নাহ আঁকড়ে থাকা মানুষের মর্যাদা","description":"এই হাদিসে বলা হয়েছে, ইসলাম মুষ্টিমেয় লোকদের মাধ্যমে শুরু হয়েছে এবং একসময় আবার সেইরকম অপরিচিত অবস্থায় ফিরে আসবে। এরপর সুসংবাদ দেওয়া হয়েছে ‘গুরাবা’ বা সেই মুষ্টিমেয় লোকদের জন্য। তিরমিযীর বর্ণনায় এসেছে, তারা হলো এমন মানুষ, যারা রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর পরে মানুষ সুন্নাহর যে বিষয়গুলো নষ্ট করেছে, সেগুলো সংশোধনের চেষ্টা করে। এখানে শিক্ষা হলো, সত্য পথ অনেক সময় সংখ্যায় কম মানুষের কাছে থাকে। মানুষের ভিড়, প্রচলন বা জনপ্রিয়তা সবসময় সঠিকতার প্রমাণ নয়। মুসলিমের কাজ হলো কুরআন ও সুন্নাহর আলোকে নিজেকে ঠিক রাখা এবং ভদ্রভাবে মানুষকে সঠিক পথে ডাকতে থাকা।"},"teachings":["ইসলাম শুরুতে অপরিচিত ছিল এবং আবার অপরিচিত অবস্থায় ফিরবে।","সুন্নাহ ঠিক রাখার চেষ্টা করা প্রশংসনীয় কাজ।","সংখ্যা বেশি হলেই কোনো পথ সঠিক হয়ে যায় না।","সত্যের পথে থাকলে ধৈর্য ও বিনয় দরকার।"],"related_hadiths":[{"id":"267","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"268","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2630","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E74" s="4" t="n"/>
@@ -2190,19 +2182,15 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>172</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানতদারি ও অঙ্গীকারের মূল্য","description":"$book_name$ $hadith_number$ - $chapter_name$. যার আমানতদারি নেই তার ঈমান নেই, আর যার অঙ্গীকারের মূল্য নেই তার দ্বীন নেই—এ কঠোর শিক্ষা এসেছে।"},"heading":{"title":"আমানতদারি ও অঙ্গীকার পূরণ: পূর্ণ ঈমানের বড় লক্ষণ","description":"এই হাদিসে আনাস (রাঃ) বলেন, রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব কমই এমন উপদেশ দিয়েছেন, যাতে তিনি বলেননি: যার আমানতদারি নেই তার ঈমান নেই এবং যার অঙ্গীকারের মূল্য নেই তার দ্বীন নেই। এই কথা মুসলিম জীবনে আমানত ও অঙ্গীকারের গুরুত্ব খুব স্পষ্ট করে। আমানত শুধু টাকা বা মাল নয়; দায়িত্ব, কথা, গোপন বিষয় এবং মানুষের অধিকারও আমানতের মধ্যে পড়তে পারে—ইসলামী স্কলারদের মতে। তবে হাদিসের সরাসরি শিক্ষা হলো, আমানত রক্ষা ও অঙ্গীকার পূরণ ছাড়া মানুষের ঈমানি চরিত্র পূর্ণ হয় না। তাই কথা দিলে তা রক্ষা করা এবং দায়িত্ব পেলে তা ঠিকমতো পালন করা জরুরি।"},"teachings":["আমানতদারি ঈমানি চরিত্রের গুরুত্বপূর্ণ অংশ।","অঙ্গীকারের মূল্য না দিলে দ্বীনি আচরণ ক্ষতিগ্রস্ত হয়।","উপদেশে আমানত ও ওয়াদার কথা বারবার স্মরণ করানো হয়েছে।","বিশ্বাসযোগ্য হওয়া মুসলিম জীবনের বড় গুণ।"],"related_hadiths":[{"id":"35","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"55","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[1]: unknown book label "মুসনাদে আহমাদ ১১৯৩৫"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মতভেদে সুন্নাহ আঁকড়ে ধরা","description":"$book_name$ $hadith_number$ - $chapter_name$. মতভেদ দেখা দিলে রাসূলের সুন্নাহ ও খুলাফায়ে রাশেদীনের পথ শক্তভাবে ধরার উপদেশ দেওয়া হয়েছে।"},"heading":{"title":"মতভেদের সময়ে করণীয়: সুন্নাহকে মাড়ির দাঁত দিয়ে আঁকড়ে ধরা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর একটি গভীর উপদেশ এসেছে। তিনি তাকওয়া অবলম্বন, আমীরের কথা শোনা ও মানার কথা বলেছেন, যদিও তিনি হাবশী গোলাম হন। এরপর জানিয়েছেন, তাঁর পরে যারা বেঁচে থাকবে তারা অনেক মতভেদ দেখবে। সেই সময়ে করণীয় হলো রাসূলের সুন্নাহ এবং সুপথপ্রাপ্ত খুলাফায়ে রাশেদীনের সুন্নাহ শক্তভাবে ধরে রাখা। তিনি আরও সতর্ক করেছেন, দ্বীনের নতুন সৃষ্টি থেকে দূরে থাকতে; কারণ প্রত্যেক নতুন সৃষ্টি বিদআত, আর প্রত্যেক বিদআত পথভ্রষ্টতা। এই হাদিস মুসলিমকে আবেগ নয়, প্রমাণিত সুন্নাহর দিকে ফিরিয়ে দেয়। মতভেদে বিভ্রান্ত না হয়ে তাকওয়া, আনুগত্য ও সুন্নাহ—এই তিনটি বিষয় ধরে রাখা দরকার।"},"teachings":["মতভেদের সময় রাসূলের সুন্নাহ শক্তভাবে আঁকড়ে ধরতে হবে।","খুলাফায়ে রাশেদীনের পথও অনুসরণের গুরুত্বপূর্ণ দিশা।","দ্বীনের নতুন সৃষ্টি থেকে সতর্ক থাকা দরকার।","তাকওয়া ও বৈধ নেতৃত্বের আনুগত্য মুসলিম জীবনে গুরুত্বপূর্ণ।"],"related_hadiths":[{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="n"/>
     </row>
     <row r="76" ht="46" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
@@ -2217,12 +2205,12 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>173</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সৎপথে আহ্বান ও গোনাহের দায়","description":"$book_name$ $hadith_number$ - $chapter_name$. সৎপথে ডাকার সওয়াব আছে, আর পথভ্রষ্টতার দিকে ডাকলে অনুসারীদের মতো গোনাহের দায় আসে।"},"heading":{"title":"সৎপথে আহ্বান: দাওয়াতের সওয়াব ও দায়িত্ব","description":"এই হাদিসে দাওয়াতের বড় দায়িত্ব বোঝানো হয়েছে। যে ব্যক্তি কাউকে সৎ পথের দিকে আহ্বান করে, তার জন্য অনুসারীদের মতো সওয়াব থাকে; অথচ অনুসারীদের সওয়াব কমে না। আবার যে পথভ্রষ্টতার দিকে আহ্বান করে, তার ওপর অনুসারীদের মতো গোনাহ থাকে; অথচ তাদের গোনাহও কমে না। তাই কথা, লেখা, শিক্ষা, পোস্ট, পরামর্শ—সবকিছুতেই সতর্ক থাকা দরকার। মানুষকে ভালো কাজে ডাকা শুধু সুন্দর কাজ নয়, এটি দায়িত্বও। একইভাবে ভুল পথ, বিদআত, পাপ বা বিভ্রান্তি ছড়ানো হালকা বিষয় নয়। এই হাদিস আমাদের শেখায়, প্রভাবশালী কথা বলার আগে ভাবতে হবে—এটি মানুষকে আল্লাহর পথে ডাকছে, নাকি ভুল পথে ঠেলে দিচ্ছে?"},"teachings":["সৎপথে আহ্বান করলে অনুসারীদের মতো সওয়াবের অংশ পাওয়া যায়।","ভুল পথে ডাকলে অনুসারীদের মতো গোনাহের দায় আসতে পারে।","দাওয়াত, লেখা ও পরামর্শে সতর্ক থাকা জরুরি।","সওয়াব বা গোনাহ কারও থেকে কমে না; প্রত্যেকের নিজ নিজ হিসাব থাকে।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পরিচ্ছন্ন দ্বীন ও নবীর অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের আনা উজ্জ্বল দ্বীন যথেষ্ট; মূসা জীবিত থাকলেও তাঁকে মুহাম্মাদের অনুসরণ করতে হতো।"},"heading":{"title":"পরিচ্ছন্ন দ্বীন: রাসূলের অনুসরণই মুসলিমের নিরাপদ পথ","description":"এই হাদিসে ওমর (রাঃ) ইহুদীদের কিছু পুরনো ধর্মীয় কাহিনী লিখে রাখার অনুমতি চাইলে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাঁকে সতর্ক করেন। তিনি বলেন, তোমরা কি দিকভ্রান্ত হয়েছ, যেমন ইহুদী-নাছারারা দিকভ্রান্ত হয়েছে? এরপর তিনি জানান, তিনি উজ্জ্বল ও পরিচ্ছন্ন দ্বীন নিয়ে এসেছেন। এমনকি মূসা (আলাইহিস সালাম) যদি তখন জীবিত থাকতেন, তাঁর পক্ষেও মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ ছাড়া পথ থাকত না। এখানে শিক্ষা হলো, মুসলিমের জন্য রাসূলের আনা দ্বীন পূর্ণ ও পরিষ্কার। তাই দ্বীনের দিশা নেওয়ার ক্ষেত্রে অপ্রয়োজনীয়ভাবে অন্য ধর্মীয় কাহিনীর প্রতি আকর্ষণ রাখা ঠিক নয়। মুসলিমের মূল ভরসা কুরআন ও সুন্নাহ।"},"teachings":["রাসূলুল্লাহর আনা দ্বীন উজ্জ্বল ও পরিচ্ছন্ন।","দ্বীনের দিশা নিতে কুরআন ও সুন্নাহ যথেষ্ট পথনির্দেশ।","আগের জাতির দিকভ্রান্ত পথ অনুসরণ থেকে সতর্ক থাকতে হবে।","মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ সব মুসলিমের জন্য মূল পথ।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E76" s="4" t="n"/>
@@ -2240,12 +2228,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>174</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অপরিচিতদের জন্য সুসংবাদ","description":"$book_name$ $hadith_number$ - $chapter_name$. ইসলাম অপরিচিতভাবে শুরু হয়েছে এবং আবার অপরিচিত হবে; সুন্নাহ ঠিক রাখাদের জন্য সুসংবাদ।"},"heading":{"title":"ইসলাম অপরিচিত হবে: সুন্নাহ আঁকড়ে থাকা মানুষের মর্যাদা","description":"এই হাদিসে বলা হয়েছে, ইসলাম মুষ্টিমেয় লোকদের মাধ্যমে শুরু হয়েছে এবং একসময় আবার সেইরকম অপরিচিত অবস্থায় ফিরে আসবে। এরপর সুসংবাদ দেওয়া হয়েছে ‘গুরাবা’ বা সেই মুষ্টিমেয় লোকদের জন্য। তিরমিযীর বর্ণনায় এসেছে, তারা হলো এমন মানুষ, যারা রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর পরে মানুষ সুন্নাহর যে বিষয়গুলো নষ্ট করেছে, সেগুলো সংশোধনের চেষ্টা করে। এখানে শিক্ষা হলো, সত্য পথ অনেক সময় সংখ্যায় কম মানুষের কাছে থাকে। মানুষের ভিড়, প্রচলন বা জনপ্রিয়তা সবসময় সঠিকতার প্রমাণ নয়। মুসলিমের কাজ হলো কুরআন ও সুন্নাহর আলোকে নিজেকে ঠিক রাখা এবং ভদ্রভাবে মানুষকে সঠিক পথে ডাকতে থাকা।"},"teachings":["ইসলাম শুরুতে অপরিচিত ছিল এবং আবার অপরিচিত অবস্থায় ফিরবে।","সুন্নাহ ঠিক রাখার চেষ্টা করা প্রশংসনীয় কাজ।","সংখ্যা বেশি হলেই কোনো পথ সঠিক হয়ে যায় না।","সত্যের পথে থাকলে ধৈর্য ও বিনয় দরকার।"],"related_hadiths":[{"id":"267","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"268","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2630","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুরআন ও সুন্নাহ আঁকড়ে ধরা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর কিতাব ও রাসূলের সুন্নাহ শক্তভাবে ধরলে সঠিক পথে থাকার দিশা পাওয়া যায়।"},"heading":{"title":"কুরআন ও সুন্নাহ: পথভ্রষ্টতা থেকে বাঁচার মূল দিশা","description":"এই বর্ণনায় রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) দুইটি বিষয় আঁকড়ে ধরার কথা বলেছেন—আল্লাহর কিতাব এবং তাঁর রাসূলের সুন্নাত। যতদিন মুসলিমরা এই দুইটি শক্তভাবে ধরে রাখবে, তারা পথভ্রষ্ট হবে না—এটাই হাদিসের মূল শিক্ষা। কুরআন মুসলিমের বিশ্বাস, ইবাদত ও জীবনযাপনের মূল আলো। আর সুন্নাহ দেখায়, কুরআনের নির্দেশ বাস্তবে কীভাবে পালন করতে হয়। তাই শুধু কুরআনের নাম নেওয়া যথেষ্ট নয়, আবার সুন্নাহকে অবহেলা করাও ঠিক নয়। দুইটিকে একসাথে সম্মান ও অনুসরণ করতে হবে। এই হাদিস আমাদের আমলের মানদণ্ড পরিষ্কার করে—যে কথা, কাজ বা রীতি কুরআন ও সুন্নাহর সাথে মেলে, সেটিই নিরাপদ।"},"teachings":["আল্লাহর কিতাব মুসলিমের প্রধান পথনির্দেশ।","রাসূলের সুন্নাহ কুরআন অনুযায়ী চলার বাস্তব পথ দেখায়।","কুরআন ও সুন্নাহ একসাথে আঁকড়ে ধরা দরকার।","দ্বীনের কাজে সঠিক মানদণ্ড হলো কিতাব ও সুন্নাহ।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E77" s="4" t="n"/>
@@ -2263,12 +2251,12 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>175</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মতভেদে সুন্নাহ আঁকড়ে ধরা","description":"$book_name$ $hadith_number$ - $chapter_name$. মতভেদ দেখা দিলে রাসূলের সুন্নাহ ও খুলাফায়ে রাশেদীনের পথ শক্তভাবে ধরার উপদেশ দেওয়া হয়েছে।"},"heading":{"title":"মতভেদের সময়ে করণীয়: সুন্নাহকে মাড়ির দাঁত দিয়ে আঁকড়ে ধরা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর একটি গভীর উপদেশ এসেছে। তিনি তাকওয়া অবলম্বন, আমীরের কথা শোনা ও মানার কথা বলেছেন, যদিও তিনি হাবশী গোলাম হন। এরপর জানিয়েছেন, তাঁর পরে যারা বেঁচে থাকবে তারা অনেক মতভেদ দেখবে। সেই সময়ে করণীয় হলো রাসূলের সুন্নাহ এবং সুপথপ্রাপ্ত খুলাফায়ে রাশেদীনের সুন্নাহ শক্তভাবে ধরে রাখা। তিনি আরও সতর্ক করেছেন, দ্বীনের নতুন সৃষ্টি থেকে দূরে থাকতে; কারণ প্রত্যেক নতুন সৃষ্টি বিদআত, আর প্রত্যেক বিদআত পথভ্রষ্টতা। এই হাদিস মুসলিমকে আবেগ নয়, প্রমাণিত সুন্নাহর দিকে ফিরিয়ে দেয়। মতভেদে বিভ্রান্ত না হয়ে তাকওয়া, আনুগত্য ও সুন্নাহ—এই তিনটি বিষয় ধরে রাখা দরকার।"},"teachings":["মতভেদের সময় রাসূলের সুন্নাহ শক্তভাবে আঁকড়ে ধরতে হবে।","খুলাফায়ে রাশেদীনের পথও অনুসরণের গুরুত্বপূর্ণ দিশা।","দ্বীনের নতুন সৃষ্টি থেকে সতর্ক থাকা দরকার।","তাকওয়া ও বৈধ নেতৃত্বের আনুগত্য মুসলিম জীবনে গুরুত্বপূর্ণ।"],"related_hadiths":[{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিদআত করলে সুন্নাহ হারানোর আশঙ্কা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীনে বিদআত চালু হলে সুন্নাহ হারানোর ভয় আছে; তাই প্রমাণিত আমলকে গুরুত্ব দেওয়া জরুরি।"},"heading":{"title":"বিদআত ও সুন্নাহ: নতুন আমলে পুরনো সুন্নাহ হারানোর ভয়","description":"এই বর্ণনায় বলা হয়েছে, কোনো সম্প্রদায় যখন তাদের দ্বীনের মধ্যে বিদআত সৃষ্টি করে, তখন আল্লাহ তাদের মধ্য থেকে সেই পরিমাণ সুন্নাত উঠিয়ে নেন; এরপর তা কিয়ামত পর্যন্ত আর ফিরে আসে না। এই কথার মূল শিক্ষা হলো, বিদআত শুধু একটি বাড়তি কাজ নয়; এটি সুন্নাহর জায়গা দখল করে নিতে পারে। মানুষ যখন নতুন বানানো আমলে ব্যস্ত হয়ে যায়, তখন রাসূলের শেখানো সহজ ও প্রমাণিত আমল অবহেলিত হয়। তাই দ্বীনের নামে নতুন রীতি যোগ করাকে হালকা করে দেখা ঠিক নয়। মুসলিমের জন্য নিরাপদ পথ হলো, প্রমাণিত সুন্নাহ শিখে সেটির ওপর আমল করা। যত বেশি সুন্নাহ জীবিত থাকবে, তত বেশি দ্বীনের আসল সৌন্দর্য মানুষের জীবনে থাকবে।"},"teachings":["বিদআত চালু হলে সুন্নাহ অবহেলিত হওয়ার ভয় থাকে।","দ্বীনের নতুন রীতি সুন্নাহর জায়গা দখল করতে পারে।","প্রমাণিত আমলকে অগ্রাধিকার দেওয়া জরুরি।","সুন্নাহ জীবিত রাখা মুসলিম সমাজের বড় দায়িত্ব।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E78" s="4" t="n"/>
@@ -2286,12 +2274,12 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>176</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পরিচ্ছন্ন দ্বীন ও নবীর অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূলের আনা উজ্জ্বল দ্বীন যথেষ্ট; মূসা জীবিত থাকলেও তাঁকে মুহাম্মাদের অনুসরণ করতে হতো।"},"heading":{"title":"পরিচ্ছন্ন দ্বীন: রাসূলের অনুসরণই মুসলিমের নিরাপদ পথ","description":"এই হাদিসে ওমর (রাঃ) ইহুদীদের কিছু পুরনো ধর্মীয় কাহিনী লিখে রাখার অনুমতি চাইলে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাঁকে সতর্ক করেন। তিনি বলেন, তোমরা কি দিকভ্রান্ত হয়েছ, যেমন ইহুদী-নাছারারা দিকভ্রান্ত হয়েছে? এরপর তিনি জানান, তিনি উজ্জ্বল ও পরিচ্ছন্ন দ্বীন নিয়ে এসেছেন। এমনকি মূসা (আলাইহিস সালাম) যদি তখন জীবিত থাকতেন, তাঁর পক্ষেও মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ ছাড়া পথ থাকত না। এখানে শিক্ষা হলো, মুসলিমের জন্য রাসূলের আনা দ্বীন পূর্ণ ও পরিষ্কার। তাই দ্বীনের দিশা নেওয়ার ক্ষেত্রে অপ্রয়োজনীয়ভাবে অন্য ধর্মীয় কাহিনীর প্রতি আকর্ষণ রাখা ঠিক নয়। মুসলিমের মূল ভরসা কুরআন ও সুন্নাহ।"},"teachings":["রাসূলুল্লাহর আনা দ্বীন উজ্জ্বল ও পরিচ্ছন্ন।","দ্বীনের দিশা নিতে কুরআন ও সুন্নাহ যথেষ্ট পথনির্দেশ।","আগের জাতির দিকভ্রান্ত পথ অনুসরণ থেকে সতর্ক থাকতে হবে।","মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ সব মুসলিমের জন্য মূল পথ।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মূসার অনুসরণ নয়, মুহাম্মাদের অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. নবুঅতের পর মুহাম্মাদকে ছেড়ে অন্য পথ অনুসরণ করলে সরল পথ থেকে বিচ্যুতির সতর্কতা এসেছে।"},"heading":{"title":"মুহাম্মাদের অনুসরণ: সরল পথে থাকার মূল শর্ত","description":"এই বর্ণনায় রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কসম করে বলেছেন, যদি মূসা (আলাইহিস সালাম) মানুষের সামনে উপস্থিত হতেন এবং মানুষ তাঁকে অনুসরণ করে মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে ছেড়ে দিত, তাহলে তারা সরল পথ থেকে বিচ্যুত হতো। তিনি আরও বলেন, মূসা যদি জীবিত থাকতেন এবং তাঁর নবুঅতকাল পেতেন, তাহলে তিনিও তাঁকে অনুসরণ করতেন। এখানে মূল শিক্ষা হলো, শেষ নবী হিসেবে মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ মুসলিমের জন্য অপরিহার্য। অন্য নবীদের প্রতি ঈমান রাখা জরুরি, কিন্তু শরীআতের অনুসরণ হবে শেষ রাসূলের পথে। তাই দ্বীনের বিষয়ে নিরাপদ পথ হলো তাঁর সুন্নাহকে মানা এবং তাঁর নির্দেশকে অগ্রাধিকার দেওয়া।"},"teachings":["শেষ নবীর শরীআত অনুসরণ করা মুসলিমের দায়িত্ব।","মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে ছেড়ে অন্য পথ নেওয়া বিচ্যুতির কারণ।","আগের নবীদের প্রতি ঈমান থাকবে, কিন্তু অনুসরণ হবে শেষ রাসূলের শরীআতের।","সরল পথে থাকতে নবীর সুন্নাহকে অগ্রাধিকার দিতে হবে।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E79" s="4" t="n"/>
@@ -2309,12 +2297,12 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>177</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কুরআন ও সুন্নাহ আঁকড়ে ধরা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর কিতাব ও রাসূলের সুন্নাহ শক্তভাবে ধরলে সঠিক পথে থাকার দিশা পাওয়া যায়।"},"heading":{"title":"কুরআন ও সুন্নাহ: পথভ্রষ্টতা থেকে বাঁচার মূল দিশা","description":"এই বর্ণনায় রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) দুইটি বিষয় আঁকড়ে ধরার কথা বলেছেন—আল্লাহর কিতাব এবং তাঁর রাসূলের সুন্নাত। যতদিন মুসলিমরা এই দুইটি শক্তভাবে ধরে রাখবে, তারা পথভ্রষ্ট হবে না—এটাই হাদিসের মূল শিক্ষা। কুরআন মুসলিমের বিশ্বাস, ইবাদত ও জীবনযাপনের মূল আলো। আর সুন্নাহ দেখায়, কুরআনের নির্দেশ বাস্তবে কীভাবে পালন করতে হয়। তাই শুধু কুরআনের নাম নেওয়া যথেষ্ট নয়, আবার সুন্নাহকে অবহেলা করাও ঠিক নয়। দুইটিকে একসাথে সম্মান ও অনুসরণ করতে হবে। এই হাদিস আমাদের আমলের মানদণ্ড পরিষ্কার করে—যে কথা, কাজ বা রীতি কুরআন ও সুন্নাহর সাথে মেলে, সেটিই নিরাপদ।"},"teachings":["আল্লাহর কিতাব মুসলিমের প্রধান পথনির্দেশ।","রাসূলের সুন্নাহ কুরআন অনুযায়ী চলার বাস্তব পথ দেখায়।","কুরআন ও সুন্নাহ একসাথে আঁকড়ে ধরা দরকার।","দ্বীনের কাজে সঠিক মানদণ্ড হলো কিতাব ও সুন্নাহ।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদীনার সম্মান ও প্রতিশ্রুতি রক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদীনার সম্মান, বিদআত থেকে বিরত থাকা ও মুসলমানের প্রতিশ্রুতি রক্ষার কঠোর শিক্ষা এসেছে।"},"heading":{"title":"মদীনার মর্যাদা: বিদআত, আশ্রয় ও প্রতিশ্রুতি ভঙ্গের সতর্কতা","description":"এই দীর্ঘ হাদিসে আলী (রাঃ) একটি লিখিত কাগজের কথা বলেন, যাতে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কয়েকটি গুরুত্বপূর্ণ নির্দেশ ছিল। এর মধ্যে আছে, মদীনা আইর থেকে সওর পর্যন্ত সম্মানার্হ এলাকা। সেখানে কেউ বিদআত সৃষ্টি করলে বা বিদআত সৃষ্টিকারীকে আশ্রয় দিলে তার ওপর কঠোর লা‘নতের কথা এসেছে। আরও বলা হয়েছে, মুসলমানদের প্রতিশ্রুতি এক; তাদের ক্ষুদ্র ব্যক্তিও সেই প্রতিশ্রুতির চেষ্টা করতে পারে। যে মুসলমানের প্রতিশ্রুতি ভঙ্গ করে, তার ব্যাপারেও কঠোর সতর্কতা এসেছে। এই হাদিস মদীনার মর্যাদা, দ্বীনে নতুন কাজের ভয়াবহতা এবং সামাজিক অঙ্গীকার রক্ষার গুরুত্ব একসাথে শেখায়। মুসলিমের কথা, আশ্রয় ও প্রতিশ্রুতি হালকা বিষয় নয়।"},"teachings":["মদীনা সম্মানার্হ এলাকা; সেখানে অন্যায় ও বিদআত থেকে সতর্ক থাকা দরকার।","বিদআতকারীকে আশ্রয় দেওয়া কঠোর সতর্কতার বিষয়।","মুসলমানের প্রতিশ্রুতি রক্ষা করা গুরুত্বপূর্ণ দায়িত্ব।","অন্যায়ভাবে সম্পর্ক বা আনুগত্য বদল করাও নিন্দনীয়।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6882","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E80" s="4" t="n"/>
@@ -2332,12 +2320,12 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>178</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিদআত করলে সুন্নাহ হারানোর আশঙ্কা","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বীনে বিদআত চালু হলে সুন্নাহ হারানোর ভয় আছে; তাই প্রমাণিত আমলকে গুরুত্ব দেওয়া জরুরি।"},"heading":{"title":"বিদআত ও সুন্নাহ: নতুন আমলে পুরনো সুন্নাহ হারানোর ভয়","description":"এই বর্ণনায় বলা হয়েছে, কোনো সম্প্রদায় যখন তাদের দ্বীনের মধ্যে বিদআত সৃষ্টি করে, তখন আল্লাহ তাদের মধ্য থেকে সেই পরিমাণ সুন্নাত উঠিয়ে নেন; এরপর তা কিয়ামত পর্যন্ত আর ফিরে আসে না। এই কথার মূল শিক্ষা হলো, বিদআত শুধু একটি বাড়তি কাজ নয়; এটি সুন্নাহর জায়গা দখল করে নিতে পারে। মানুষ যখন নতুন বানানো আমলে ব্যস্ত হয়ে যায়, তখন রাসূলের শেখানো সহজ ও প্রমাণিত আমল অবহেলিত হয়। তাই দ্বীনের নামে নতুন রীতি যোগ করাকে হালকা করে দেখা ঠিক নয়। মুসলিমের জন্য নিরাপদ পথ হলো, প্রমাণিত সুন্নাহ শিখে সেটির ওপর আমল করা। যত বেশি সুন্নাহ জীবিত থাকবে, তত বেশি দ্বীনের আসল সৌন্দর্য মানুষের জীবনে থাকবে।"},"teachings":["বিদআত চালু হলে সুন্নাহ অবহেলিত হওয়ার ভয় থাকে।","দ্বীনের নতুন রীতি সুন্নাহর জায়গা দখল করতে পারে।","প্রমাণিত আমলকে অগ্রাধিকার দেওয়া জরুরি।","সুন্নাহ জীবিত রাখা মুসলিম সমাজের বড় দায়িত্ব।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"42","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিতাব ও নবীর সুন্নাহর দিশা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর কিতাব ও নবীর সুন্নাহ শক্তভাবে ধরলে পথভ্রষ্টতা থেকে বাঁচার দিশা পাওয়া যায়।"},"heading":{"title":"কিতাব ও নবীর সুন্নাহ: পথভ্রষ্টতা থেকে বাঁচার দিশা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তিনি উম্মতের মাঝে এমন জিনিস রেখে যাচ্ছেন, যা শক্তভাবে ধরলে তারা পথভ্রষ্ট হবে না—আল্লাহর কিতাব এবং তাঁর নবীর সুন্নাত। এখানে মুসলিম জীবনের মূল ভিত্তি স্পষ্ট করা হয়েছে। কুরআন নির্দেশ দেয়, আর সুন্নাহ সেই নির্দেশের বাস্তব রূপ শেখায়। কেউ যদি শুধু নিজের মত, সমাজের প্রচলন বা আবেগকে ধর্মের মানদণ্ড বানায়, তাহলে ভুলের আশঙ্কা থাকে। কিন্তু কিতাব ও সুন্নাহকে মানদণ্ড বানালে পথ পরিষ্কার হয়। এই হাদিস আমাদের শেখায়, মতভেদ, সন্দেহ বা নতুন রীতির ভিড়ে নিরাপদ আশ্রয় হলো আল্লাহর কিতাব ও নবীর প্রমাণিত সুন্নাহ।"},"teachings":["আল্লাহর কিতাব ও নবীর সুন্নাহ মুসলিমের মূল পথনির্দেশ।","পথভ্রষ্টতা থেকে বাঁচতে কিতাব ও সুন্নাহ আঁকড়ে ধরতে হবে।","দ্বীনের মানদণ্ড সমাজের প্রচলন নয়, প্রমাণিত দলিল।","সুন্নাহ ছাড়া কুরআনের বাস্তব আমল বোঝা অসম্পূর্ণ হয়ে যায়।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E81" s="4" t="n"/>
@@ -2355,12 +2343,12 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>179</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মূসার অনুসরণ নয়, মুহাম্মাদের অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. নবুঅতের পর মুহাম্মাদকে ছেড়ে অন্য পথ অনুসরণ করলে সরল পথ থেকে বিচ্যুতির সতর্কতা এসেছে।"},"heading":{"title":"মুহাম্মাদের অনুসরণ: সরল পথে থাকার মূল শর্ত","description":"এই বর্ণনায় রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কসম করে বলেছেন, যদি মূসা (আলাইহিস সালাম) মানুষের সামনে উপস্থিত হতেন এবং মানুষ তাঁকে অনুসরণ করে মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে ছেড়ে দিত, তাহলে তারা সরল পথ থেকে বিচ্যুত হতো। তিনি আরও বলেন, মূসা যদি জীবিত থাকতেন এবং তাঁর নবুঅতকাল পেতেন, তাহলে তিনিও তাঁকে অনুসরণ করতেন। এখানে মূল শিক্ষা হলো, শেষ নবী হিসেবে মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর অনুসরণ মুসলিমের জন্য অপরিহার্য। অন্য নবীদের প্রতি ঈমান রাখা জরুরি, কিন্তু শরীআতের অনুসরণ হবে শেষ রাসূলের পথে। তাই দ্বীনের বিষয়ে নিরাপদ পথ হলো তাঁর সুন্নাহকে মানা এবং তাঁর নির্দেশকে অগ্রাধিকার দেওয়া।"},"teachings":["শেষ নবীর শরীআত অনুসরণ করা মুসলিমের দায়িত্ব।","মুহাম্মাদ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে ছেড়ে অন্য পথ নেওয়া বিচ্যুতির কারণ।","আগের নবীদের প্রতি ঈমান থাকবে, কিন্তু অনুসরণ হবে শেষ রাসূলের শরীআতের।","সরল পথে থাকতে নবীর সুন্নাহকে অগ্রাধিকার দিতে হবে।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মধ্যম পথে সুন্নাহর আমল","description":"$book_name$ $hadith_number$ - $chapter_name$. বিদআতে বেশি চেষ্টা করার চেয়ে সুন্নাহর ওপর মধ্যমভাবে আমল করাই উত্তম—এটি বড় শিক্ষা।"},"heading":{"title":"সুন্নাহর ওপর মধ্যম আমল: বিদআতে পরিশ্রমের চেয়ে উত্তম","description":"এই বর্ণনায় বলা হয়েছে, শরীআতে নতুন কাজ নিয়ে বেশি পরিশ্রম করার চেয়ে মধ্যম পন্থায় সুন্নাহর ওপর আমল করা অনেক উত্তম। এখানে খুব দরকারি ভারসাম্যের শিক্ষা আছে। অনেক সময় মানুষ নতুন নতুন আমল, বিশেষ নিয়ম বা নিজের বানানো পদ্ধতিতে বেশি উৎসাহী হয়। কিন্তু যদি তা সুন্নাহভিত্তিক না হয়, তাহলে সেই পরিশ্রম নিরাপদ নয়। অন্যদিকে, সুন্নাহর প্রমাণিত আমল ছোট মনে হলেও সেটিই উত্তম পথ। দ্বীনে সফলতা বেশি জটিলতা বানানোর মধ্যে নয়; বরং রাসূলের শেখানো পথে স্থির থাকার মধ্যে। তাই কম হলেও নিয়মিত, খাঁটি এবং সুন্নাহসম্মত আমল করা উচিত। এই শিক্ষা মানুষকে সহজ, পরিষ্কার ও প্রমাণিত দ্বীনের পথে ফিরিয়ে আনে।"},"teachings":["বিদআতে বেশি পরিশ্রম করার চেয়ে সুন্নাহর ওপর কম আমলও উত্তম।","দ্বীনের কাজে প্রমাণিত পথকে অগ্রাধিকার দিতে হবে।","ইবাদতে জটিলতা নয়, সুন্নাহভিত্তিক সরলতা দরকার।","মধ্যম পন্থা মুসলিমকে বাড়াবাড়ি থেকে বাঁচায়।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"5063","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E82" s="4" t="n"/>
@@ -2378,12 +2366,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদীনার সম্মান ও প্রতিশ্রুতি রক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদীনার সম্মান, বিদআত থেকে বিরত থাকা ও মুসলমানের প্রতিশ্রুতি রক্ষার কঠোর শিক্ষা এসেছে।"},"heading":{"title":"মদীনার মর্যাদা: বিদআত, আশ্রয় ও প্রতিশ্রুতি ভঙ্গের সতর্কতা","description":"এই দীর্ঘ হাদিসে আলী (রাঃ) একটি লিখিত কাগজের কথা বলেন, যাতে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কয়েকটি গুরুত্বপূর্ণ নির্দেশ ছিল। এর মধ্যে আছে, মদীনা আইর থেকে সওর পর্যন্ত সম্মানার্হ এলাকা। সেখানে কেউ বিদআত সৃষ্টি করলে বা বিদআত সৃষ্টিকারীকে আশ্রয় দিলে তার ওপর কঠোর লা‘নতের কথা এসেছে। আরও বলা হয়েছে, মুসলমানদের প্রতিশ্রুতি এক; তাদের ক্ষুদ্র ব্যক্তিও সেই প্রতিশ্রুতির চেষ্টা করতে পারে। যে মুসলমানের প্রতিশ্রুতি ভঙ্গ করে, তার ব্যাপারেও কঠোর সতর্কতা এসেছে। এই হাদিস মদীনার মর্যাদা, দ্বীনে নতুন কাজের ভয়াবহতা এবং সামাজিক অঙ্গীকার রক্ষার গুরুত্ব একসাথে শেখায়। মুসলিমের কথা, আশ্রয় ও প্রতিশ্রুতি হালকা বিষয় নয়।"},"teachings":["মদীনা সম্মানার্হ এলাকা; সেখানে অন্যায় ও বিদআত থেকে সতর্ক থাকা দরকার।","বিদআতকারীকে আশ্রয় দেওয়া কঠোর সতর্কতার বিষয়।","মুসলমানের প্রতিশ্রুতি রক্ষা করা গুরুত্বপূর্ণ দায়িত্ব।","অন্যায়ভাবে সম্পর্ক বা আনুগত্য বদল করাও নিন্দনীয়।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6882","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত ফেরত ও খিয়ানত না করা","description":"$book_name$ $hadith_number$ - $chapter_name$. যে আমানত রেখেছে তাকে তা বুঝিয়ে দাও, আর কেউ খিয়ানত করলেও তার সঙ্গে খিয়ানত করো না।"},"heading":{"title":"আমানত ফেরত দাও, খিয়ানতের জবাবে খিয়ানত করো না","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব সহজ কিন্তু গভীর একটি নিয়ম শিখিয়েছেন। যে ব্যক্তি তোমার কাছে আমানত রেখেছে, তাকে সময়মতো আমানত বুঝিয়ে দাও। আর যে তোমার সঙ্গে খিয়ানত করে, তার সঙ্গে তুমি খিয়ানত করো না। এখানে আমানতদারি ও নৈতিকতার বড় শিক্ষা আছে। কেউ অন্যায় করলেই তার মতো অন্যায় করা মুসলিমের আচরণ নয়। আমানত ফেরত দেওয়া মানুষের হক। আর খিয়ানতের জবাবে খিয়ানত না করা চরিত্রের শক্তি দেখায়। এই হাদিস ব্যবসা, সম্পর্ক, দায়িত্ব, টাকা-পয়সা, কথা বা কোনো জিনিসের হেফাজত—সব জায়গায় কাজে লাগে। মুসলিমের পরিচয় হলো সে নিজের দায়িত্ব ঠিক রাখে।"},"teachings":["যে আমানত রাখে, তাকে আমানত ফেরত দেওয়া জরুরি।","অন্য কেউ খিয়ানত করলেও নিজে খিয়ানত করা ঠিক নয়।","আমানতদারি মানুষের হক রক্ষার শিক্ষা দেয়।","ভালো চরিত্র অন্যের খারাপ আচরণের ওপর নির্ভর করে না।"],"related_hadiths":[{"id":"3535","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"1264","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"2934","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E83" s="4" t="n"/>
@@ -2401,12 +2389,12 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>180</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিতাব ও নবীর সুন্নাহর দিশা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর কিতাব ও নবীর সুন্নাহ শক্তভাবে ধরলে পথভ্রষ্টতা থেকে বাঁচার দিশা পাওয়া যায়।"},"heading":{"title":"কিতাব ও নবীর সুন্নাহ: পথভ্রষ্টতা থেকে বাঁচার দিশা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তিনি উম্মতের মাঝে এমন জিনিস রেখে যাচ্ছেন, যা শক্তভাবে ধরলে তারা পথভ্রষ্ট হবে না—আল্লাহর কিতাব এবং তাঁর নবীর সুন্নাত। এখানে মুসলিম জীবনের মূল ভিত্তি স্পষ্ট করা হয়েছে। কুরআন নির্দেশ দেয়, আর সুন্নাহ সেই নির্দেশের বাস্তব রূপ শেখায়। কেউ যদি শুধু নিজের মত, সমাজের প্রচলন বা আবেগকে ধর্মের মানদণ্ড বানায়, তাহলে ভুলের আশঙ্কা থাকে। কিন্তু কিতাব ও সুন্নাহকে মানদণ্ড বানালে পথ পরিষ্কার হয়। এই হাদিস আমাদের শেখায়, মতভেদ, সন্দেহ বা নতুন রীতির ভিড়ে নিরাপদ আশ্রয় হলো আল্লাহর কিতাব ও নবীর প্রমাণিত সুন্নাহ।"},"teachings":["আল্লাহর কিতাব ও নবীর সুন্নাহ মুসলিমের মূল পথনির্দেশ।","পথভ্রষ্টতা থেকে বাঁচতে কিতাব ও সুন্নাহ আঁকড়ে ধরতে হবে।","দ্বীনের মানদণ্ড সমাজের প্রচলন নয়, প্রমাণিত দলিল।","সুন্নাহ ছাড়া কুরআনের বাস্তব আমল বোঝা অসম্পূর্ণ হয়ে যায়।"],"related_hadiths":[{"id":"7280","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"7281","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2676","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হাজরে আসওয়াদ ও সুন্নাহ অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. হাজরে আসওয়াদ নিজে উপকার-অপকার করতে পারে না; নবীকে করতে দেখে উমর তা চুম্বন করেন।"},"heading":{"title":"হাজরে আসওয়াদ চুম্বন: বিশ্বাস নয়, সুন্নাহ অনুসরণের শিক্ষা","description":"এই হাদিসে ওমর (রাঃ) হাজরে আসওয়াদের কাছে এসে তা চুম্বন করেন এবং বলেন, তিনি জানেন এটি একটি পাথর মাত্র; এটি কারও কল্যাণ বা অকল্যাণ করতে পারে না। এরপর তিনি বলেন, নবী (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে এটি চুম্বন করতে না দেখলে তিনি চুম্বন করতেন না। এই কথায় তাওহীদ ও সুন্নাহ অনুসরণের সুন্দর শিক্ষা আছে। হাজরে আসওয়াদকে সম্মান করা হয় রাসূলের আমল অনুসরণ করে, পাথরকে উপকার-অপকারের মালিক মনে করে নয়। তাই মুসলিমের বিশ্বাস পরিষ্কার হওয়া দরকার—উপকার ও ক্ষতির ক্ষমতা আল্লাহর হাতে। আর ইবাদতের কাজ করা হবে নবীর দেখানো পদ্ধতিতে। আবেগ, কুসংস্কার বা অতিরিক্ত বিশ্বাস এখানে গ্রহণযোগ্য নয়।"},"teachings":["হাজরে আসওয়াদ নিজে উপকার বা অপকার করার ক্ষমতা রাখে না।","উমর (রাঃ) এটি চুম্বন করেছেন নবীর অনুসরণে।","তাওহীদ হলো কল্যাণ-অকল্যাণের মালিক আল্লাহকে মানা।","ইবাদতের কাজে আবেগ নয়, রাসূলের সুন্নাহ অনুসরণ করা দরকার।"],"related_hadiths":[{"id":"2957","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2958","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2959","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E84" s="4" t="n"/>
@@ -2424,12 +2412,12 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মধ্যম পথে সুন্নাহর আমল","description":"$book_name$ $hadith_number$ - $chapter_name$. বিদআতে বেশি চেষ্টা করার চেয়ে সুন্নাহর ওপর মধ্যমভাবে আমল করাই উত্তম—এটি বড় শিক্ষা।"},"heading":{"title":"সুন্নাহর ওপর মধ্যম আমল: বিদআতে পরিশ্রমের চেয়ে উত্তম","description":"এই বর্ণনায় বলা হয়েছে, শরীআতে নতুন কাজ নিয়ে বেশি পরিশ্রম করার চেয়ে মধ্যম পন্থায় সুন্নাহর ওপর আমল করা অনেক উত্তম। এখানে খুব দরকারি ভারসাম্যের শিক্ষা আছে। অনেক সময় মানুষ নতুন নতুন আমল, বিশেষ নিয়ম বা নিজের বানানো পদ্ধতিতে বেশি উৎসাহী হয়। কিন্তু যদি তা সুন্নাহভিত্তিক না হয়, তাহলে সেই পরিশ্রম নিরাপদ নয়। অন্যদিকে, সুন্নাহর প্রমাণিত আমল ছোট মনে হলেও সেটিই উত্তম পথ। দ্বীনে সফলতা বেশি জটিলতা বানানোর মধ্যে নয়; বরং রাসূলের শেখানো পথে স্থির থাকার মধ্যে। তাই কম হলেও নিয়মিত, খাঁটি এবং সুন্নাহসম্মত আমল করা উচিত। এই শিক্ষা মানুষকে সহজ, পরিষ্কার ও প্রমাণিত দ্বীনের পথে ফিরিয়ে আনে।"},"teachings":["বিদআতে বেশি পরিশ্রম করার চেয়ে সুন্নাহর ওপর কম আমলও উত্তম।","দ্বীনের কাজে প্রমাণিত পথকে অগ্রাধিকার দিতে হবে।","ইবাদতে জটিলতা নয়, সুন্নাহভিত্তিক সরলতা দরকার।","মধ্যম পন্থা মুসলিমকে বাড়াবাড়ি থেকে বাঁচায়।"],"related_hadiths":[{"id":"2697","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4385","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"5063","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অন্যায়ভাবে জমি দখলের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. অর্ধহাত জমি অন্যায়ভাবে দখল করলে কিয়ামতে সাত জমিনের বোঝা তার কাঁধে দেওয়া হবে।"},"heading":{"title":"অন্যায়ভাবে জমি দখল: সাত জমিনের কঠিন সতর্কতা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি অত্যাচার করে অর্ধহাত জমি দখল করে, কিয়ামতের দিন অনুরূপ সাতটি জমিন তার কাঁধে ঝুলিয়ে দেওয়া হবে। এখানে জমি দখল সম্পর্কে খুব কঠোর সতর্কতা এসেছে। অল্প জমি হলেও অন্যায়ভাবে নেওয়া হালকা বিষয় নয়। মানুষের সম্পদ, জমি ও অধিকার রক্ষা করা ইসলামী ন্যায়ের অংশ। এই হাদিস জমির সীমানা, মালিকানা এবং অন্যের হক নিয়ে ভয় দেখায়। অর্ধহাত জমির কথাও এসেছে, তাই ছোট অন্যায়কে ছোট ভেবে নেওয়া ঠিক নয়। কিয়ামতের জবাবদিহি মনে রাখলে অন্যের সম্পদ দখল থেকে মানুষ বাঁচতে পারে।"},"teachings":["অন্যায়ভাবে অল্প জমি দখল করাও ভয়ংকর অপরাধ।","মানুষের জমি ও সম্পদের হক রক্ষা করা দরকার।","কিয়ামতে জমি দখলের কঠিন জবাবদিহি হবে।","ছোট অন্যায়কে হালকা মনে করা উচিত নয়।"],"related_hadiths":[{"id":"2452","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1610","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2938","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E85" s="4" t="n"/>
@@ -2447,12 +2435,12 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত ফেরত ও খিয়ানত না করা","description":"$book_name$ $hadith_number$ - $chapter_name$. যে আমানত রেখেছে তাকে তা বুঝিয়ে দাও, আর কেউ খিয়ানত করলেও তার সঙ্গে খিয়ানত করো না।"},"heading":{"title":"আমানত ফেরত দাও, খিয়ানতের জবাবে খিয়ানত করো না","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব সহজ কিন্তু গভীর একটি নিয়ম শিখিয়েছেন। যে ব্যক্তি তোমার কাছে আমানত রেখেছে, তাকে সময়মতো আমানত বুঝিয়ে দাও। আর যে তোমার সঙ্গে খিয়ানত করে, তার সঙ্গে তুমি খিয়ানত করো না। এখানে আমানতদারি ও নৈতিকতার বড় শিক্ষা আছে। কেউ অন্যায় করলেই তার মতো অন্যায় করা মুসলিমের আচরণ নয়। আমানত ফেরত দেওয়া মানুষের হক। আর খিয়ানতের জবাবে খিয়ানত না করা চরিত্রের শক্তি দেখায়। এই হাদিস ব্যবসা, সম্পর্ক, দায়িত্ব, টাকা-পয়সা, কথা বা কোনো জিনিসের হেফাজত—সব জায়গায় কাজে লাগে। মুসলিমের পরিচয় হলো সে নিজের দায়িত্ব ঠিক রাখে।"},"teachings":["যে আমানত রাখে, তাকে আমানত ফেরত দেওয়া জরুরি।","অন্য কেউ খিয়ানত করলেও নিজে খিয়ানত করা ঠিক নয়।","আমানতদারি মানুষের হক রক্ষার শিক্ষা দেয়।","ভালো চরিত্র অন্যের খারাপ আচরণের ওপর নির্ভর করে না।"],"related_hadiths":[{"id":"3535","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"1264","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"2934","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সালাত যাকাত ও মুসলমানের কল্যাণ","description":"$book_name$ $hadith_number$ - $chapter_name$. সালাত কায়েম, যাকাত আদায় ও সকল মুসলমানের কল্যাণ কামনার উপর বায়আতের শিক্ষা এই হাদিসে এসেছে।"},"heading":{"title":"সালাত যাকাত ও সকল মুসলমানের কল্যাণ কামনার বায়আত","description":"এই হাদিসে জারীর ইবনু আবদুল্লাহ (রাঃ) বলেন, তিনি রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর সাথে বায়আত করেছেন তিনটি বিষয়ের উপর: সালাত প্রতিষ্ঠা করা, যাকাত প্রদান করা এবং সকল মুসলমানের কল্যাণ কামনা করা। এখানে সালাত, যাকাত ও নসীহত একসঙ্গে এসেছে। এতে বোঝা যায়, ইবাদত শুধু ব্যক্তিগত কাজ নয়; মুসলমানদের জন্য ভালো চাওয়াও দ্বীনের অংশ। সালাত মানুষকে আল্লাহর সঙ্গে যুক্ত করে, যাকাত সম্পদের দায়িত্ব শেখায়, আর মুসলমানের কল্যাণ কামনা সমাজকে সুন্দর করে। এই বায়আত হাদিস আমাদের শেখায়, একজন মুসলিম নিজের ইবাদত ঠিক রাখার পাশাপাশি অন্য মুসলমানের ক্ষতি নয়, বরং কল্যাণ চায়।"},"teachings":["সালাত প্রতিষ্ঠা করা মুসলিম জীবনের গুরুত্বপূর্ণ দায়িত্ব।","যাকাত আদায় সম্পদের হক বুঝে দেওয়ার শিক্ষা দেয়।","সকল মুসলমানের কল্যাণ কামনা দ্বীনের সুন্দর আচরণ।","বায়আত মানে দায়িত্ব মেনে চলার অঙ্গীকার।"],"related_hadiths":[{"id":"57","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"56","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"4967","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E86" s="4" t="n"/>
@@ -2470,12 +2458,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হাজরে আসওয়াদ ও সুন্নাহ অনুসরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. হাজরে আসওয়াদ নিজে উপকার-অপকার করতে পারে না; নবীকে করতে দেখে উমর তা চুম্বন করেন।"},"heading":{"title":"হাজরে আসওয়াদ চুম্বন: বিশ্বাস নয়, সুন্নাহ অনুসরণের শিক্ষা","description":"এই হাদিসে ওমর (রাঃ) হাজরে আসওয়াদের কাছে এসে তা চুম্বন করেন এবং বলেন, তিনি জানেন এটি একটি পাথর মাত্র; এটি কারও কল্যাণ বা অকল্যাণ করতে পারে না। এরপর তিনি বলেন, নবী (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে এটি চুম্বন করতে না দেখলে তিনি চুম্বন করতেন না। এই কথায় তাওহীদ ও সুন্নাহ অনুসরণের সুন্দর শিক্ষা আছে। হাজরে আসওয়াদকে সম্মান করা হয় রাসূলের আমল অনুসরণ করে, পাথরকে উপকার-অপকারের মালিক মনে করে নয়। তাই মুসলিমের বিশ্বাস পরিষ্কার হওয়া দরকার—উপকার ও ক্ষতির ক্ষমতা আল্লাহর হাতে। আর ইবাদতের কাজ করা হবে নবীর দেখানো পদ্ধতিতে। আবেগ, কুসংস্কার বা অতিরিক্ত বিশ্বাস এখানে গ্রহণযোগ্য নয়।"},"teachings":["হাজরে আসওয়াদ নিজে উপকার বা অপকার করার ক্ষমতা রাখে না।","উমর (রাঃ) এটি চুম্বন করেছেন নবীর অনুসরণে।","তাওহীদ হলো কল্যাণ-অকল্যাণের মালিক আল্লাহকে মানা।","ইবাদতের কাজে আবেগ নয়, রাসূলের সুন্নাহ অনুসরণ করা দরকার।"],"related_hadiths":[{"id":"2957","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2958","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2959","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অনধিকার জমি নেওয়ার শাস্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. অনধিকারে কারও জমি নিলে কিয়ামতের দিন তাকে সাত তবক জমিন পর্যন্ত ধসিয়ে দেওয়ার সতর্কতা এসেছে।"},"heading":{"title":"অনধিকার জমি নেওয়ার পরিণতি ও হক রক্ষার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি অনধিকারে কারও কিছু জমি নেয়, কিয়ামতের দিন তাকে সাত তবক জমিন পর্যন্ত ধসিয়ে দেওয়া হবে। এই হাদিস জমি দখল, অন্যের হক নেওয়া এবং যুলুমের বিরুদ্ধে কঠোর সতর্কতা দেয়। জমি ছোট হোক বা বড়—অধিকার ছাড়া নেওয়া বৈধ নয়। মানুষের সম্পদে হাত দেওয়ার আগে মনে রাখতে হবে, আখেরাতে এর হিসাব আছে। এই হাদিস আমাদের জমির সীমানা, দলিল, মালিকানা ও ন্যায্য অধিকার বিষয়ে সতর্ক করে। অন্যের হক বাঁচিয়ে চলা শুধু সামাজিক নিয়ম নয়; এটি আখেরাতের জবাবদিহির সঙ্গেও জড়িত।"},"teachings":["অনধিকারে জমি নেওয়া যুলুমের মধ্যে পড়ে।","কিয়ামতে জমি দখলের কঠিন পরিণতির কথা এসেছে।","অন্যের সম্পদ ও জমির অধিকার মানা জরুরি।","ন্যায্য হক ছাড়া কিছু নেওয়া থেকে বিরত থাকা দরকার।"],"related_hadiths":[{"id":"2454","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2958","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"1610","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E87" s="4" t="n"/>
@@ -2493,17 +2481,17 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>201</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সুন্নাহ অনুসরণে সাহাবীদের ভালোবাসা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইবনু ওমর রাঃ রাসূল صلى الله عليه وسلم-কে যেখানে যেমন করতে দেখেছেন, সেখানেই তাই করেছেন; এটিই সুন্নাহ অনুসরণের শিক্ষা।"},"heading":{"title":"সুন্নাহ অনুসরণ: রাসূল صلى الله عليه وسلم-এর কাজকে ভালোবাসা দিয়ে মানা","description":"এই হাদিসে ইবনু ওমর রাঃ-এর একটি সহজ কিন্তু গভীর কাজ তুলে ধরা হয়েছে। তিনি সফরে ছিলেন। পথের একটি জায়গা দিয়ে যাওয়ার সময় তিনি মূল রাস্তা থেকে একটু সরে গেলেন। লোকেরা কারণ জানতে চাইলে তিনি বললেন, রাসূলুল্লাহ صلى الله عليه وسلم-কে তিনি এই স্থানে এমন করতে দেখেছেন, তাই তিনিও করলেন। এখানে সুন্নাহ অনুসরণ শুধু কথার বিষয় নয়; কাজের মধ্যেও তা দেখা যায়। ইবনু ওমর রাঃ কোনো নতুন ব্যাখ্যা দেননি, নিজের পছন্দকেও সামনে আনেননি। তিনি শুধু নবীজির কাজকে অনুসরণ করেছেন। তাই এই হাদিস আমাদের শেখায়, রাসূলের অনুসরণ মানে তাঁর পথকে ভালোবাসা, সম্মান করা এবং সুযোগ পেলে নিজের জীবনে তা ধরে রাখা।"},"teachings":["রাসূল صلى الله عليه وسلم-এর কাজকে ভালোবাসা দিয়ে অনুসরণ করা সাহাবীদের অভ্যাস ছিল।","ধর্মীয় আচরণে নিজের পছন্দের চেয়ে নবীজির দেখানো পথকে আগে রাখা উচিত।","সুন্নাহ অনুসরণ কখনও ছোট কাজেও প্রকাশ পেতে পারে।"],"related_hadiths":[]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নম্রতা ও কোমলতার কল্যাণ","description":"$book_name$ $hadith_number$ - $chapter_name$. কোমলতা থেকে বঞ্চিত হলে মানুষ অনেক কল্যাণ হারায়; এই হাদিসে সুন্দর আচরণ ও নরম ব্যবহারের গুরুত্ব বোঝানো হয়েছে।"},"heading":{"title":"নম্রতা ও কোমলতা: কল্যাণ পাওয়ার বড় শিক্ষা","description":"এই হাদিসের মূল কথা খুব সরল: কোমলতা ও নম্রতা মানুষের জীবনে কল্যাণের দরজা খুলে দেয়। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যাকে কোমলতা থেকে বঞ্চিত করা হয়, তাকে কল্যাণ থেকেও বঞ্চিত করা হয়। এখানে নম্রতা মানে দুর্বলতা নয়; বরং কথা, আচরণ ও ব্যবহারকে নরম রাখা। পরিবারে, কাজে বা মানুষের সঙ্গে মেলামেশায় রুক্ষ কথা অনেক সময় সম্পর্ক নষ্ট করে। আর কোমল ব্যবহার মানুষকে কাছে আনে। তাই এই হাদিস আমাদের শেখায়, ভালো মুসলিম চরিত্র গড়তে নরম ভাষা, ধৈর্য আর সুন্দর আচরণ জরুরি। হাদিসে কল্যাণের কথা এসেছে, তাই আমরা বলতে পারি—নম্রতা মানুষকে ভালো গুণের দিকে নিয়ে যায়। তাই নিজের ভাষা ও আচরণে কোমলতা আছে কি না, তা নিয়মিত খেয়াল করা এই হাদিসের খুব বাস্তব প্রয়োগ।"},"teachings":["কথা ও আচরণে কোমলতা রাখা কল্যাণের কারণ।","রুক্ষ স্বভাব মানুষকে ভালো দিক থেকে দূরে নিতে পারে।","নম্র ব্যবহার পরিবার ও সমাজে সম্পর্ক সুন্দর করে।","কোমলতা দুর্বলতা নয়; এটি ভালো চরিত্রের অংশ।"],"related_hadiths":[{"id":"5068","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৮২ (প্রাসঙ্গিক বর্ণনা)"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৯৬ (প্রাসঙ্গিক বর্ণনা)"</t>
+          <t>related_hadiths[0]: unknown book label "আদাবুল মুফরাদ ৪৬৫"</t>
         </is>
       </c>
     </row>
@@ -2520,17 +2508,17 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | প্রবৃত্তির অনুসরণ থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবী صلى الله عليه وسلم অবৈধ কামনা, অশ্লীলতার টান ও খেয়ালখুশির কারণে সুন্নাহ থেকে সরে যাওয়ার ভয় দেখিয়েছেন।"},"heading":{"title":"প্রবৃত্তির অনুসরণ থেকে বাঁচার হাদিস ও সুন্নাহর পথে থাকা","description":"এই হাদিসে নবী কারীম صلى الله عليه وسلم উম্মতের জন্য কয়েকটি বড় ভয় প্রকাশ করেছেন। তিনি বলেছেন, মানুষের পেট ও লজ্জাস্থানের সঙ্গে জড়িত অবৈধ টান, অশ্লীল কাজে জড়িয়ে পড়ার ইচ্ছা এবং খেয়ালখুশির অনুসরণ মানুষকে ভুল পথে নিতে পারে। বিশেষ করে সুন্নাহর বিষয়ে প্রবৃত্তির অনুসরণ করলে মানুষ সঠিক পথ থেকে সরে যেতে পারে। এখানে মূল শিক্ষা হলো, নিজের ইচ্ছাকে সব সময় সত্যের মাপকাঠি বানানো নিরাপদ নয়। অবৈধ উপার্জন, অশ্লীলতা এবং নিজের মনমতো ধর্ম মানার প্রবণতা—এসব থেকে সতর্ক থাকা দরকার। সুন্নাহর পথ তখনই নিরাপদ থাকে, যখন মানুষ নিজের কামনা নয়, রাসূল صلى الله عليه وسلم-এর নির্দেশিত পথকে গুরুত্ব দেয়।"},"teachings":["অবৈধ উপার্জনের টান মানুষকে বিপদে ফেলতে পারে।","অশ্লীল কাজের প্রবৃত্তি থেকে নিজেকে বাঁচানো দরকার।","সুন্নাহর বিষয়ে নিজের খেয়ালখুশির অনুসরণ করলে ভ্রান্তির আশঙ্কা থাকে।"],"related_hadiths":[]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জমি দখল হারাম ও কিয়ামতের দায়","description":"$book_name$ $hadith_number$ - $chapter_name$. অন্যায়ভাবে সামান্য জমি দখলও কিয়ামতে কঠিন দায়ের কারণ হবে; তাই জমি ও হকের ব্যাপারে সতর্ক থাকার শিক্ষা।"},"heading":{"title":"জমি দখল হারাম: অন্যের হক নিলে কিয়ামতে দায় আছে","description":"এই হাদিসের মূল শিক্ষা হলো, অন্যের জমি দখল করা শুধু সামাজিক অন্যায় নয়, আখিরাতের বড় দায়ও। এখানে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কেউ অন্যায়ভাবে কারো এক বিগত জমি দখল করলে তাকে কিয়ামতের দিন সেই জমির কারণে কঠিন অবস্থার মুখোমুখি হতে হবে। তাই জমি দখল হারাম—এই বিষয়টি খুব পরিষ্কারভাবে বোঝা যায়। অনেক সময় মানুষ জমির সীমানা, দলিল, উত্তরাধিকার বা ক্ষমতার জোরে সামান্য অংশকে ছোট ব্যাপার মনে করে। কিন্তু হাদিসটি শেখায়, অন্যের হক সামান্য হলেও তা হালকা নয়। মুসলিমের জন্য জরুরি হলো জমি, সম্পদ ও অধিকার নিয়ে ইনসাফ করা এবং কাউকে যুলুম না করা।"},"teachings":["অন্যের জমির সামান্য অংশও অন্যায়ভাবে নেওয়া বড় দায়ের কারণ।","জমি ও সম্পদের ব্যাপারে যুলুম থেকে বেঁচে থাকা জরুরি।","মানুষের হক নষ্ট করলে কিয়ামতের দিন জবাবদিহি করতে হবে।","সীমানা, দলিল ও মালিকানার বিষয়ে সততা রাখা ঈমানি আচরণের অংশ।"],"related_hadiths":[{"id":"2453","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4028","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৮১ (প্রাসঙ্গিক বর্ণনা)"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৯৬ (প্রাসঙ্গিক বর্ণনা)"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৯৭ (প্রাসঙ্গিক বর্ণনা)"</t>
+          <t>related_hadiths[2]: unknown book label "ঊপদেশ ১৯ (প্রাসঙ্গিক বর্ণনা)"</t>
         </is>
       </c>
     </row>
@@ -2547,17 +2535,17 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জান্নাতের পথ তাকওয়া ও উত্তম চরিত্র","description":"$book_name$ $hadith_number$ - $chapter_name$. তাকওয়া ও ভালো চরিত্র জান্নাতের বড় কারণ; আর মুখ ও লজ্জাস্থানের অপব্যবহার মানুষকে ক্ষতির পথে নেয়।"},"heading":{"title":"তাকওয়া ও উত্তম চরিত্র: জান্নাতের পথে সবচেয়ে বড় শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم-কে জিজ্ঞেস করা হলো, কোন জিনিস মানুষকে সবচেয়ে বেশি জান্নাতে প্রবেশ করাবে। তিনি বললেন, আল্লাহভীতি ও উত্তম চরিত্র। আবার জিজ্ঞেস করা হলো, কোন জিনিস মানুষকে সবচেয়ে বেশি জাহান্নামে প্রবেশ করাবে। তিনি বললেন, মুখ এবং লজ্জাস্থান। তাই এই হাদিসের মূল বিষয় হলো তাকওয়া, উত্তম চরিত্র, জিহ্বা নিয়ন্ত্রণ এবং লজ্জাস্থান হেফাজত। মানুষ মুখ দিয়ে সত্যও বলতে পারে, আবার মিথ্যা, গীবত, গালমন্দ বা ক্ষতিকর কথাও বলতে পারে। লজ্জাস্থানের ভুল ব্যবহারও বড় পাপের কারণ হতে পারে। তাই জান্নাতের পথ শুধু ইবাদতের কথায় সীমিত নয়; চরিত্র, কথা ও আচরণও এখানে বড় ভূমিকা রাখে।"},"teachings":["আল্লাহভীতি ও ভালো চরিত্র জান্নাতের পথে বড় সহায়।","মুখের ভুল ব্যবহার মানুষকে বড় ক্ষতির দিকে নিতে পারে।","লজ্জাস্থান হেফাজত করা ঈমানি জীবনের গুরুত্বপূর্ণ অংশ।"],"related_hadiths":[]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পবিত্র অন্তর ও সত্যভাষীর মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. উত্তম মানুষের পরিচয় হলো সত্য কথা বলা ও অন্তরকে পাপ, যুলুম, খিয়ানত ও হিংসা থেকে পরিষ্কার রাখা।"},"heading":{"title":"পবিত্র অন্তর ও সত্যভাষী: উত্তম মানুষের সহজ পরিচয়","description":"এই হাদিসে মানুষের উত্তম হওয়ার একটি সহজ কিন্তু গভীর মানদণ্ড বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে জিজ্ঞেস করা হলে তিনি বলেন, নিষ্কলুষ অন্তঃকরণ ও সত্যভাষী মানুষ উত্তম। এখানে পবিত্র অন্তর বলতে শুধু নরম মন বোঝানো হয়নি। হাদিসের ভাষায় এমন অন্তর, যেখানে পাপ নেই, যুলুম নেই, খিয়ানত নেই এবং হিংসা-বিদ্বেষ নেই। তাই পবিত্র অন্তর হাদিস আমাদের নিজের ভেতর দেখার শিক্ষা দেয়। আমরা মুখে সত্য বলি কি না, মানুষের প্রতি হিংসা রাখি কি না, কারো হক নষ্ট করি কি না—এসব বিষয় নিজের জীবনেই যাচাই করতে হবে। সত্যভাষী হওয়া এবং অন্তর পরিষ্কার রাখা একসঙ্গে চলা উচিত।"},"teachings":["উত্তম মানুষের বড় গুণ হলো সত্য কথা বলা।","অন্তরকে পাপ, যুলুম ও খিয়ানত থেকে পরিষ্কার রাখা দরকার।","হিংসা-বিদ্বেষ থেকে মুক্ত থাকা পবিত্র অন্তরের লক্ষণ।","বাহ্যিক ভালো আচরণের সঙ্গে ভেতরের সততাও জরুরি।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"593","book_id":"8","slug":"riyadus-salihin","label":"রিয়াদুস সালেহীন"}]}</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৮৪"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৮৭"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৯৬"</t>
+          <t>related_hadiths[0]: unknown book label "ঊপদেশ ১৮৮ (প্রাসঙ্গিক বর্ণনা)"</t>
         </is>
       </c>
     </row>
@@ -2574,19 +2562,15 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>224</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জিহ্বা ও লজ্জাস্থান হেফাজতের ফজিলত","description":"$book_name$ $hadith_number$ - $chapter_name$. যে ব্যক্তি জিহ্বা ও লজ্জাস্থান হেফাজতের দায়িত্ব নেয়, নবী صلى الله عليه وسلم তার জন্য জান্নাতের যিম্মাদার হওয়ার কথা বলেছেন।"},"heading":{"title":"জিহ্বা হেফাজত ও লজ্জাস্থান হেফাজত: জান্নাতের আশ্বাসের হাদিস","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم খুব সংক্ষিপ্ত ভাষায় বড় একটি শিক্ষা দিয়েছেন। তিনি বলেছেন, যে ব্যক্তি তার দুই চোয়ালের মাঝের বস্তু এবং দুই পায়ের মাঝের বস্তুর দায়িত্ব নেবে, তিনি তার জন্য জান্নাতের যিম্মাদার হবেন। দুই চোয়ালের মাঝের বস্তু বলতে জিহ্বা বোঝানো হয়েছে, আর দুই পায়ের মাঝের বস্তু বলতে লজ্জাস্থান বোঝানো হয়েছে। মানুষের অনেক পাপ মুখের কথার মাধ্যমে হয়। আবার লজ্জাস্থানের ভুল ব্যবহারও মানুষকে অশ্লীলতা ও অপমানের দিকে নিতে পারে। তাই জিহ্বা হেফাজত ও লজ্জাস্থান হেফাজত শুধু ব্যক্তিগত শুদ্ধতার বিষয় নয়; এটি দ্বীনদার জীবনের বড় পরীক্ষা। হাদিসটি আমাদের কথা ও চরিত্রকে নিয়ন্ত্রণে রাখার শিক্ষা দেয়।"},"teachings":["জিহ্বা হেফাজত করা জান্নাতের আশ্বাস লাভের একটি কারণ।","লজ্জাস্থান হেফাজত করা মুসলিম জীবনের গুরুত্বপূর্ণ দায়িত্ব।","মানুষের বড় ক্ষতি অনেক সময় কথা ও কামনার ভুল ব্যবহারে আসে।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৮৩"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৮৭"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৯৬"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিশুদের প্রতি স্নেহ-মমতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুদের চুম্বন ও আদর নিয়ে এই হাদিস দেখায়, অন্তরে স্নেহ-মমতা থাকা আল্লাহর বড় দান।"},"heading":{"title":"শিশুদের প্রতি স্নেহ-মমতা: আদর, দয়া ও কোমল হৃদয়ের হাদিস","description":"এই হাদিসের মূল বিষয় শিশুদের প্রতি স্নেহ-মমতা। এক বেদুঈন সাহাবীদের শিশুদের চুমু দিতে দেখে বলল, তারা শিশুদের চুম্বন করে না। তখন রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বললেন, আল্লাহ যদি তার অন্তর থেকে রহমত তুলে নেন, তবে তিনি তা বাধা দিতে পারবেন কি? এই কথায় বোঝা যায়, শিশুকে আদর করা দুর্বলতা নয়; বরং অন্তরের দয়া ও কোমলতার লক্ষণ। শিশুদের প্রতি স্নেহ, চুম্বন ও ভালোবাসা দেখানো ইসলামী আদবের সঙ্গে মিলে যায়। প্রধান কীওয়ার্ড হলো শিশুদের প্রতি স্নেহ-মমতা, আর সম্পর্কিত কীওয়ার্ড হলো শিশুকে আদর করা, সন্তানকে চুমু দেওয়া, দয়ার হাদিস, কোমল হৃদয়। হাদিসটি আমাদের শেখায়, ঘরের ছোটদের সঙ্গে রুক্ষ আচরণ নয়, ভালোবাসা ও মমতা থাকা উচিত।"},"teachings":["শিশুকে আদর করা ও ভালোবাসা দেখানো সুন্দর আচরণ।","অন্তরে রহমত থাকা আল্লাহর দান—এটি হারিয়ে যাওয়া ভয়ংকর ক্ষতি।","শিশুদের সঙ্গে কঠোরতার বদলে কোমল আচরণ করা উচিত।"],"related_hadiths":[{"id":"5997","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6013","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6008","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="n"/>
     </row>
     <row r="92" ht="46" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
@@ -2601,19 +2585,15 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>226</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দ্বিমুখী মানুষের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. দ্বিমুখী ব্যক্তি এক দলের কাছে এক রূপে, অন্য দলের কাছে অন্য রূপে যায়; কিয়ামতে সে মন্দ মানুষের অন্তর্ভুক্ত।"},"heading":{"title":"দ্বিমুখী মানুষ সম্পর্কে হাদিস: মুখের সততা কেন জরুরি","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم দ্বিমুখী মানুষের বিষয়ে কঠোর সতর্কতা দিয়েছেন। তিনি বলেছেন, কিয়ামতের দিন মন্দ লোকদের মধ্যে সেই ব্যক্তিকে পাওয়া যাবে, যে এক মুখ নিয়ে এক দলের কাছে যায় এবং আরেক মুখ নিয়ে অন্য দলের কাছে যায়। অর্থাৎ সে নিজের কথা ও অবস্থান বদলে মানুষকে বিভ্রান্ত করে। এই হাদিস মূলত জিহ্বার সততা, সরলতা এবং ভেতর-বাইরের মিল রাখার শিক্ষা দেয়। দ্বিমুখিতা মানুষের মধ্যে সন্দেহ, অশান্তি ও অবিশ্বাস তৈরি করতে পারে। একজন মুসলিমের কথা এমন হওয়া উচিত, যাতে প্রতারণা না থাকে। এখানে শিক্ষা হলো, মানুষের সামনে মিষ্টি কথা বললেও পিছনে ভিন্ন আচরণ করা নিরাপদ পথ নয়। সত্যবাদিতা ও সৎ চরিত্রই সম্মানের পথ।"},"teachings":["দ্বিমুখী আচরণ কিয়ামতের দিন মন্দ অবস্থার কারণ হতে পারে।","একজনের কাছে এক কথা, অন্যজনের কাছে অন্য কথা বলা থেকে বাঁচতে হবে।","মুখের সততা ও চরিত্রের সরলতা মুসলিম আচরণের অংশ।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৯৩"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৮৮"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৮৯"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দুই কন্যা লালন-পালনের ফজিলত","description":"$book_name$ $hadith_number$ - $chapter_name$. দুই কন্যাকে পূর্ণ বয়স্কা হওয়া পর্যন্ত লালন করলে কিয়ামতে নবীর নৈকট্যের আশা জাগে।"},"heading":{"title":"দুই কন্যার লালন-পালন: নবীর নৈকট্য লাভের আশাব্যঞ্জক হাদিস","description":"এই হাদিসের মূল বিষয় দুই কন্যার লালন-পালন। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি দুই কন্যাকে পূর্ণ বয়স্কা হওয়া পর্যন্ত লালন-পালন করবে, কিয়ামতের দিন সে তাঁর সঙ্গে এভাবে আসবে। এরপর তিনি নিজের আঙ্গুল একত্র করে দেখিয়েছেন। হাদিসটি কন্যা সন্তানের মর্যাদা ও তাদের দায়িত্বশীলভাবে বড় করার গুরুত্ব তুলে ধরে। এখানে প্রধান কীওয়ার্ড হলো দুই কন্যা লালন-পালনের হাদিস। সম্পর্কিত কীওয়ার্ড: কন্যা সন্তানের ফজিলত, মেয়েদের লালন-পালন, কন্যার মর্যাদা, ইসলামে সন্তান প্রতিপালন। হাদিসের শিক্ষা হলো, কন্যাদের যত্ন, নিরাপত্তা, খাবার, শিক্ষা ও বড় হওয়া পর্যন্ত অভিভাবকত্ব একটি মূল্যবান দায়িত্ব। তবে ব্যাখ্যায় আমরা শুধু হাদিসে থাকা কথাটুকুই ধরে বলি—এই কাজ কিয়ামতের দিনে রাসূলের নৈকট্যের কারণ হতে পারে।"},"teachings":["দুই কন্যাকে বড় হওয়া পর্যন্ত দায়িত্ব নিয়ে লালন-পালন করা প্রশংসনীয়।","কন্যা সন্তানকে অবহেলা নয়, যত্ন ও ভালো আচরণ দেওয়া দরকার।","কন্যাদের দায়িত্ব পালন কিয়ামতের দিনে নবীর নৈকট্যের কারণ হতে পারে।"],"related_hadiths":[{"id":"5995","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5304","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6005","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="n"/>
     </row>
     <row r="93" ht="46" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
@@ -2628,19 +2608,15 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>227</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অভিশাপকারী সম্পর্কে সতর্ক হাদিস","description":"$book_name$ $hadith_number$ - $chapter_name$. অভিশাপ করতে অভ্যস্ত মানুষ কিয়ামতের দিন সাক্ষী ও সুপারিশকারী হতে পারবে না—এ হাদিসে সেই সতর্কতা এসেছে।"},"heading":{"title":"অভিশাপকারী সম্পর্কে হাদিস: মুখের ভাষা সংযত রাখার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم বলেছেন, অভিশাপকারীরা কিয়ামতের মাঠে সাক্ষীও হবে না এবং সুপারিশকারীও হবে না। এখানে মুখের ভাষা নিয়ে বড় সতর্কতা আছে। অনেক সময় মানুষ রাগে, বিরক্তিতে বা অভ্যাসে অন্যকে অভিশাপ দিয়ে বসে। কিন্তু হাদিসটি জানায়, এমন ভাষা হালকা বিষয় নয়। একজন মুমিনের মুখ থেকে গালমন্দ, অভিশাপ ও কষ্টদায়ক কথা যেন সহজে বের না হয়। অভিশাপের বদলে সংযম, দোয়া এবং শান্ত আচরণ ভালো পথ। এই হাদিস আমাদের মনে করিয়ে দেয়, মুখের কথা শুধু মানুষের সম্পর্ক নষ্ট করে না; আখিরাতের অবস্থার সঙ্গেও এর সম্পর্ক আছে। তাই কথা বলার আগে থামা ও ভাবা দরকার।"},"teachings":["অভিশাপ করতে অভ্যস্ত হওয়া আখিরাতের জন্য ক্ষতিকর।","রাগের সময় মুখের ভাষা নিয়ন্ত্রণ করা দরকার।","মুমিনের ভাষা গালমন্দ ও অভিশাপ থেকে দূরে থাকা উচিত।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৯৪"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৮৭"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৮৪"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিধবা ও মিসকীনকে সাহায্য","description":"$book_name$ $hadith_number$ - $chapter_name$. বিধবা ও মিসকীনের সহযোগিতা বড় নেকির কাজ; হাদিসে এর মর্যাদা জিহাদ, কিয়াম ও সিয়ামের সঙ্গে তুলনা করা হয়েছে।"},"heading":{"title":"বিধবা ও মিসকীনকে সাহায্য: অসহায়ের পাশে দাঁড়ানোর বড় ফজিলত","description":"এই হাদিসের মূল বিষয় বিধবা ও মিসকীনকে সাহায্য করা। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, বিধবা ও মিসকীনের সহযোগী আল্লাহর পথে জিহাদকারীর ন্যায়, এমন তাহাজ্জুদগুজার ব্যক্তির ন্যায় যে অলস হয় না, এবং এমন সিয়াম পালনকারীর ন্যায় যে ইফতার করে না। এই বর্ণনা অসহায় মানুষের পাশে দাঁড়ানোর মর্যাদা বুঝিয়ে দেয়। এখানে প্রধান কীওয়ার্ড হলো বিধবা ও মিসকীনকে সাহায্য। সম্পর্কিত কীওয়ার্ড: অসহায়কে সাহায্য, দান-সদকা, বিধবার ভরণ-পোষণ, মিসকীনের হক, মানবসেবা হাদিস। হাদিসের আলোকে বোঝা যায়, সামাজিক দায়িত্ব শুধু কথায় নয়; বাস্তবে সাহায্য, খোঁজখবর ও ভরণ-পোষণের চেষ্টায় প্রকাশ পায়। তবে সাহায্য যেন সম্মান রেখে করা হয়, কারণ হাদিসটি সহযোগিতার মর্যাদা বলেছে, কাউকে ছোট করার অনুমতি দেয়নি।"},"teachings":["বিধবা ও মিসকীনের সহযোগিতা অত্যন্ত মর্যাদাপূর্ণ কাজ।","অসহায় মানুষের পাশে দাঁড়ানো ইবাদতের মতো বড় নেকির কারণ হতে পারে।","সহযোগিতা করতে গিয়ে মানুষের সম্মান রক্ষা করা জরুরি।"],"related_hadiths":[{"id":"6005","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6011","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="n"/>
     </row>
     <row r="94" ht="46" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
@@ -2655,19 +2631,15 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>228</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | একটি কথার ভালো-মন্দ প্রভাব","description":"$book_name$ $hadith_number$ - $chapter_name$. মানুষ অনেক সময় কথার গুরুত্ব বুঝে না; ভালো কথা মর্যাদা বাড়ায়, আর মন্দ কথা জাহান্নামের কারণ হতে পারে।"},"heading":{"title":"কথার প্রভাব সম্পর্কে হাদিস: জিহ্বা নিয়ন্ত্রণ কেন প্রয়োজন","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم কথার শক্তি বুঝিয়েছেন। একজন বান্দা এমন কথা বলে, যাতে আল্লাহর সন্তুষ্টি থাকে; সে হয়তো তার গুরুত্ব বুঝতে পারে না, তবু আল্লাহ তার মর্যাদা বাড়িয়ে দেন। আবার কেউ এমন কথা বলে, যাতে আল্লাহর অসন্তুষ্টি থাকে; সে হয়তো ক্ষতির গভীরতা বুঝে না, অথচ সেই কথাই তাকে জাহান্নামের দিকে নিয়ে যায়। তাই কথার প্রভাব খুব বড়। এই হাদিস আমাদের শেখায়, মুখের কথা ছোট মনে হলেও তার ফল ছোট নাও হতে পারে। জিহ্বা নিয়ন্ত্রণ, ভালো কথা বলা এবং মন্দ কথা থেকে বাঁচা—এসব মুসলিম জীবনের গুরুত্বপূর্ণ শিক্ষা। কথা বলার আগে ভাবা নিরাপদ পথ।"},"teachings":["আল্লাহর সন্তুষ্টির কথা বান্দার মর্যাদা বাড়ার কারণ হতে পারে।","মন্দ কথা মানুষকে বড় ক্ষতির দিকে নিয়ে যেতে পারে।","কথা বলার আগে তার ফল নিয়ে ভাবা উচিত।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৮৪"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৮৮"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৯৪"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইয়াতীম পালনকারীর মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইয়াতীম পালনকারীর জান্নাতে নবীর নৈকট্যের কথা এসেছে; এটি অসহায় শিশুর যত্নের বড় শিক্ষা।"},"heading":{"title":"ইয়াতীম পালনকারীর মর্যাদা: জান্নাতে নবীর নৈকট্যের হাদিস","description":"এই হাদিসের মূল বিষয় ইয়াতীম পালন। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তিনি ও ইয়াতীম পালনকারী জান্নাতে এভাবে থাকবেন। তারপর তিনি তর্জনী ও মধ্যমা আঙ্গুলের মাঝে সামান্য ফাঁক রেখে ইশারা করেছেন। হাদিসটি ইয়াতীম শিশুর প্রতি দায়িত্ব, দয়া ও যত্নের বড় মর্যাদা বুঝায়। এখানে প্রধান কীওয়ার্ড হলো ইয়াতীম পালনকারীর মর্যাদা। সম্পর্কিত কীওয়ার্ড: ইয়াতীমের হক, এতিমের যত্ন, ইয়াতীমকে সাহায্য, জান্নাতে নবীর সান্নিধ্য, অসহায় শিশুর লালন-পালন। হাদিসটি আমাদের মনে করায়, যে শিশুর সহায় দরকার, তাকে আশ্রয় ও যত্ন দেওয়া শুধু সামাজিক কাজ নয়; এটি বড় নেকির দরজা। তবে ইয়াতীমের সম্পদ বা অধিকার নিয়ে অতিরিক্ত আলোচনা এই হাদিসে নেই, তাই এখানে মূল শিক্ষা শুধু পালন ও যত্নের মর্যাদায় সীমিত রাখা হয়েছে।"},"teachings":["ইয়াতীম শিশুর দায়িত্ব নেওয়া জান্নাতে নবীর নৈকট্যের কারণ হতে পারে।","অসহায় শিশুর প্রতি দয়া, যত্ন ও নিরাপত্তা দেওয়া গুরুত্বপূর্ণ।","ইয়াতীম পালন শুধু দান নয়; এটি দীর্ঘমেয়াদি দায়িত্ব ও মমতার কাজ।"],"related_hadiths":[{"id":"6006","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6008","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="n"/>
     </row>
     <row r="95" ht="46" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
@@ -2682,17 +2654,17 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সত্যবাদিতা জান্নাতের পথে নেয়","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য পুণ্যের পথ দেখায়, পুণ্য জান্নাতের দিকে নেয়; আর মিথ্যা পাপের পথে নিয়ে যায়—এটাই হাদিসের শিক্ষা।"},"heading":{"title":"সত্যবাদিতা সম্পর্কে হাদিস: সত্যের পথ জান্নাতের দিকে নিয়ে যায়","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم সত্য ও মিথ্যার ফল খুব পরিষ্কারভাবে বলেছেন। সত্যবাদিতা পুণ্যময় কাজ, আর পুণ্য জান্নাতের পথ দেখায়। যে মানুষ সত্যের উপর স্থির থাকার চেষ্টা করে, তাকে আল্লাহর কাছে সত্যনিষ্ঠ হিসেবে লেখা হয়। অন্যদিকে মিথ্যা পাপের পথ, আর পাপ জাহান্নামের দিকে নিয়ে যায়। যে ব্যক্তি বারবার মিথ্যা বলে এবং মিথ্যায় অভ্যস্ত হয়, তাকে আল্লাহর কাছে মিথ্যুক হিসেবে লেখা হয়। তাই সত্যবাদিতা শুধু ভালো অভ্যাস নয়; এটি ঈমানি চরিত্রের বড় অংশ। কথা বলার আগে ভেবে বলা, সত্যকে ধরে রাখা এবং মিথ্যা থেকে দূরে থাকা—এই হাদিসের মূল শিক্ষা।"},"teachings":["সত্য কথা পুণ্যের পথে নিয়ে যায়।","বারবার সত্য বলার চেষ্টা মানুষকে সত্যনিষ্ঠ হতে সাহায্য করে।","মিথ্যায় অভ্যস্ত হওয়া পাপের দিকে নিয়ে যেতে পারে।"],"related_hadiths":[]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত, সত্যবাদিতা ও ভালো চরিত্র","description":"$book_name$ $hadith_number$ - $chapter_name$. আমানত রক্ষা, সত্য কথা, ভালো চরিত্র ও খাদ্যে সতর্কতা—এই চার গুণ মানুষের জীবনকে সঠিক পথে রাখে।"},"heading":{"title":"আমানত রক্ষা ও সত্য কথা: জীবনের চারটি মূল্যবান গুণ","description":"এই হাদিসে চারটি গুণের কথা এসেছে, যা একজন মুমিনের জীবনকে সুন্দর করে। আমানত রক্ষা করা, সত্য কথা বলা, উত্তম চরিত্র রাখা এবং খানা-পিনাতে সতর্ক থাকা—এসব বিষয় শুধু ইবাদতের বাইরে আলাদা কিছু নয়; বরং দৈনন্দিন জীবনের বড় পরীক্ষা। আমানত রক্ষা মানে কারো দেওয়া দায়িত্ব, সম্পদ বা বিশ্বাস নষ্ট না করা। সত্য কথা বলা মানে সুবিধা-অসুবিধা দেখে কথা বদলে না ফেলা। উত্তম চরিত্র মানে মানুষের সঙ্গে সুন্দর আচরণ করা। আর খানা-পিনাতে সতর্কতা মানে খাবার ও উপার্জনের উৎস নিয়ে সাবধান থাকা। হাদিসটি দুনিয়ার ক্ষতি নিয়ে হতাশ না হয়ে চরিত্র ও সততার দিকে মন দিতে শেখায়।"},"teachings":["আমানত রক্ষা করা মুমিনের গুরুত্বপূর্ণ গুণ।","সত্য কথা বলা চরিত্রের ভিত্তি মজবুত করে।","খানা-পিনার বিষয়ে সতর্কতা জীবনকে হালাল পথে রাখে।","ভালো চরিত্র মানুষের সঙ্গে আচরণে প্রকাশ পায়।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৮৭"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৮৫"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৯৬"</t>
+          <t>related_hadiths[0]: unknown book label "ঊপদেশ ১৮৮ (প্রাসঙ্গিক বর্ণনা)"</t>
         </is>
       </c>
     </row>
@@ -2709,19 +2681,15 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>231</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | চোগলখোরির ভয়াবহ সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূল صلى الله عليه وسلم বলেছেন, চোগলখোর জান্নাতে প্রবেশ করবে না; তাই মানুষের কথা লাগানো থেকে সতর্ক থাকা দরকার।"},"heading":{"title":"চোগলখোরি সম্পর্কে হাদিস: মানুষের কথা লাগানোর ভয়াবহতা","description":"এই হাদিসটি খুব ছোট, কিন্তু এর সতর্কতা বড়। রাসূলুল্লাহ صلى الله عليه وسلم বলেছেন, চোগলখোর জান্নাতে প্রবেশ করবে না। চোগলখোরি হলো মানুষের কথা এক পক্ষ থেকে আরেক পক্ষের কাছে এমনভাবে নেওয়া, যাতে সম্পর্ক নষ্ট হয় বা ঝগড়া বাড়ে। যদিও হাদিসের বাক্য সংক্ষিপ্ত, তবু এর বার্তা স্পষ্ট: মানুষের মাঝে আগুন লাগানো কোনো হালকা পাপ নয়। জিহ্বার ভুল ব্যবহার অনেক সময় পরিবার, বন্ধু বা সমাজে অশান্তি তৈরি করে। একজন মুসলিমের কাজ হলো মিল রাখা, ঝগড়া না বাড়ানো এবং কারও কথা অন্যের কাছে ক্ষতির উদ্দেশ্যে না নেওয়া। তাই চোগলখোরি থেকে বাঁচা জিহ্বা হেফাজতের গুরুত্বপূর্ণ অংশ।"},"teachings":["চোগলখোরির বিষয়ে হাদিসে কঠোর সতর্কতা এসেছে।","মানুষের কথা লাগানো সম্পর্ক নষ্ট করতে পারে।","জিহ্বা হেফাজত করার মধ্যে চোগলখোরি থেকে দূরে থাকাও আছে।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৮৫"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৯০"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৯৩"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুমিন মুমিনের সহায়ক","description":"$book_name$ $hadith_number$ - $chapter_name$. মুমিনকে গৃহের মতো বলা হয়েছে, যার এক অংশ অন্য অংশকে মজবুত রাখে—এটি সহযোগিতার শিক্ষা দেয়।"},"heading":{"title":"মুমিন মুমিনের সহায়ক: একে অন্যকে শক্ত রাখার হাদিস","description":"এই হাদিসের মূল বিষয় মুমিন মুমিনের সহায়ক। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, একজন মুমিন অপর মুমিনের জন্য গৃহের মতো, যার এক অংশ অন্য অংশকে দৃঢ় রাখে। এরপর তিনি দুই হাতের আঙ্গুল একটির মধ্যে আরেকটি প্রবেশ করিয়ে দেখিয়েছেন। এই দৃশ্যমান ইশারা সহযোগিতার অর্থ সহজ করে দেয়। একজন মুসলিম একা সব দায়িত্ব সামলাতে পারে না; অন্য ভাইয়ের সহায়তা, সাহস ও পাশে থাকা দরকার হতে পারে। প্রধান কীওয়ার্ড হলো মুমিন মুমিনের সহায়ক, আর সম্পর্কিত কীওয়ার্ড: মুসলিম ভ্রাতৃত্ব, সহযোগিতার হাদিস, একে অন্যকে সাহায্য, মুমিনের সম্পর্ক। হাদিসটি দলাদলি নয়, বরং ভালো কাজে একে অন্যকে শক্ত করার শিক্ষা দেয়। এখানে নির্দিষ্ট কোনো রাজনৈতিক বা সামাজিক দাবি করা হয়নি; শুধু হাদিসের সরাসরি সহযোগিতার বার্তা তুলে ধরা হয়েছে।"},"teachings":["মুমিনদের একে অন্যের সহায়ক হওয়া উচিত।","ভালো কাজে সহযোগিতা মুসলিম সমাজকে শক্ত রাখে।","সম্পর্ক শুধু কথায় নয়; প্রয়োজনের সময় পাশে দাঁড়ালে তা সত্য হয়।"],"related_hadiths":[{"id":"6011","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2443","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="n"/>
     </row>
     <row r="97" ht="46" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
@@ -2736,12 +2704,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>232</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অন্যায়ভাবে জমি দখলের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. অর্ধহাত জমি অন্যায়ভাবে দখল করলে কিয়ামতে সাত জমিনের বোঝা তার কাঁধে দেওয়া হবে।"},"heading":{"title":"অন্যায়ভাবে জমি দখল: সাত জমিনের কঠিন সতর্কতা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি অত্যাচার করে অর্ধহাত জমি দখল করে, কিয়ামতের দিন অনুরূপ সাতটি জমিন তার কাঁধে ঝুলিয়ে দেওয়া হবে। এখানে জমি দখল সম্পর্কে খুব কঠোর সতর্কতা এসেছে। অল্প জমি হলেও অন্যায়ভাবে নেওয়া হালকা বিষয় নয়। মানুষের সম্পদ, জমি ও অধিকার রক্ষা করা ইসলামী ন্যায়ের অংশ। এই হাদিস জমির সীমানা, মালিকানা এবং অন্যের হক নিয়ে ভয় দেখায়। অর্ধহাত জমির কথাও এসেছে, তাই ছোট অন্যায়কে ছোট ভেবে নেওয়া ঠিক নয়। কিয়ামতের জবাবদিহি মনে রাখলে অন্যের সম্পদ দখল থেকে মানুষ বাঁচতে পারে।"},"teachings":["অন্যায়ভাবে অল্প জমি দখল করাও ভয়ংকর অপরাধ।","মানুষের জমি ও সম্পদের হক রক্ষা করা দরকার।","কিয়ামতে জমি দখলের কঠিন জবাবদিহি হবে।","ছোট অন্যায়কে হালকা মনে করা উচিত নয়।"],"related_hadiths":[{"id":"2452","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1610","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2938","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অভাবীর জন্য সুপারিশ","description":"$book_name$ $hadith_number$ - $chapter_name$. অভাবী বা প্রয়োজনমন্দের জন্য সুপারিশ করলে নেকি হতে পারে; চূড়ান্ত ফায়সালা আল্লাহর ইচ্ছায় হয়।"},"heading":{"title":"অভাবীর জন্য সুপারিশ: সাহায্যের দরজা খুলে দেওয়ার হাদিস","description":"এই হাদিসের মূল বিষয় অভাবীর জন্য সুপারিশ। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর কাছে কোনো ভিক্ষুক বা প্রয়োজনমন্দ এলে তিনি সাহাবীদের বলতেন, তোমরা সুপারিশ কর, এতে তোমাদের নেকি দেওয়া হবে। আর আল্লাহ তাঁর রাসূলের মুখ দিয়ে যে ফয়সালা চান তা জারি করবেন। হাদিসটি দেখায়, সরাসরি সাহায্য করতে না পারলেও ভালো সুপারিশ, পরিচয় করিয়ে দেওয়া বা প্রয়োজনের কথা পৌঁছে দেওয়া নেকির কাজ হতে পারে। প্রধান কীওয়ার্ড হলো অভাবীর জন্য সুপারিশ। সম্পর্কিত কীওয়ার্ড: দরিদ্রকে সাহায্য, নেক সুপারিশ, প্রয়োজনমন্দের সহায়তা, ইসলামে সুপারিশ। হাদিসে একই সঙ্গে ভারসাম্যও আছে—সুপারিশ করা মানুষের কাজ, কিন্তু ফল আল্লাহর ইচ্ছা অনুযায়ী হয়। তাই সাহায্যের চেষ্টা করতে হবে, তবে ফল নিয়ে অহংকার বা চাপ সৃষ্টি করা ঠিক নয়।"},"teachings":["অভাবী মানুষের প্রয়োজনে ভালো সুপারিশ করা নেকির কারণ হতে পারে।","সরাসরি দিতে না পারলেও সাহায্যের দরজা খুলে দেওয়া যায়।","মানুষ চেষ্টা করবে, আর চূড়ান্ত ফল আল্লাহর ইচ্ছার উপর ছেড়ে দেবে।"],"related_hadiths":[{"id":"6006","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6005","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6019","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E97" s="4" t="n"/>
@@ -2759,19 +2727,15 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>233</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গীবত কী? নবী صلى الله عليه وسلم-এর সহজ ব্যাখ্যা","description":"$book_name$ $hadith_number$ - $chapter_name$. ভাইয়ের অপছন্দের কথা তার অনুপস্থিতিতে বলা গীবত; আর মিথ্যা হলে তা অপবাদ—নবী صلى الله عليه وسلم এভাবে বুঝিয়েছেন।"},"heading":{"title":"গীবত কী: ভাইয়ের অপছন্দের কথা বলা সম্পর্কে হাদিস","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم গীবতের সংজ্ঞা খুব সহজভাবে বুঝিয়েছেন। সাহাবীরা জিজ্ঞেস করলেন, গীবত কী? তিনি বললেন, তোমার ভাই সম্পর্কে এমন কথা বলা, যা সে অপছন্দ করে। এরপর প্রশ্ন করা হলো, যদি কথাটি সত্যিই তার মধ্যে থাকে? নবী صلى الله عليه وسلم বললেন, যদি তা থাকে, তবু তুমি তার গীবত করলে। আর যদি তা না থাকে, তাহলে তুমি তার ওপর মিথ্যা অপবাদ দিলে। এই হাদিস আমাদের শেখায়, সত্য কথা হলেও কারও অপছন্দের বিষয় নিয়ে তার পিছনে কথা বলা নিরাপদ নয়। গীবত ও অপবাদ দুটিই জিহ্বার বড় ভুল। তাই অন্যের দোষ নিয়ে কথা বলার আগে নিজেকে থামানো দরকার।"},"teachings":["কারও অপছন্দের কথা তার পিছনে বলা গীবত।","দোষ সত্য হলেও পিছনে বলা গীবত হতে পারে।","যে দোষ নেই তা বললে মিথ্যা অপবাদ হয়।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৮৯"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৯৫"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৯৯"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যালিম ও মাযলুমকে সাহায্য","description":"$book_name$ $hadith_number$ - $chapter_name$. অত্যাচারিতকে সাহায্য করা যেমন জরুরি, তেমনি অত্যাচারীকে যুলুম থেকে থামানোও তার প্রতি সাহায্য।"},"heading":{"title":"যালিম ও মাযলুমকে সাহায্য: যুলুম থামানোই প্রকৃত সহায়তা","description":"এই হাদিসের মূল বিষয় যুলুম থেকে বিরত রাখা। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তোমার ভাইকে সাহায্য কর, সে অত্যাচারী হোক বা অত্যাচারিত হোক। সাহাবী প্রশ্ন করলেন, অত্যাচারিতকে সাহায্য করা বোঝা যায়, কিন্তু অত্যাচারীকে কীভাবে সাহায্য করা হবে? তিনি বললেন, তাকে যুলুম করা থেকে বিরত রাখাই তার সাহায্য। এখানে প্রধান কীওয়ার্ড হলো যালিম ও মাযলুমকে সাহায্য। সম্পর্কিত কীওয়ার্ড: যুলুম থেকে বিরত রাখা, অত্যাচারিতের পাশে দাঁড়ানো, অন্যায় বন্ধ করা, মুসলিম ভাইকে সাহায্য। হাদিসটি খুব ভারসাম্যপূর্ণ শিক্ষা দেয়। নিজের লোক বলে অন্যায়ের পক্ষে দাঁড়ানো সাহায্য নয়। প্রকৃত সাহায্য হলো অন্যায়কারীকে থামানো এবং অত্যাচারিতকে রক্ষা করা। হাদিসের বাইরে কোনো শাস্তি বা আইনগত ধাপ এখানে যোগ করা হয়নি; শুধু নৈতিক দায়িত্বের কথা বলা হয়েছে।"},"teachings":["অত্যাচারিত মানুষের পাশে দাঁড়ানো জরুরি।","অত্যাচারীকে যুলুম থেকে থামানোও তার প্রতি সত্যিকারের সাহায্য।","নিজের ভাই হলেও অন্যায়ের পক্ষে দাঁড়ানো ঠিক নয়।"],"related_hadiths":[{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6011","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6013","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="n"/>
     </row>
     <row r="99" ht="46" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
@@ -2786,19 +2750,15 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>234</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যার অনিষ্টে মানুষ দূরে থাকে","description":"$book_name$ $hadith_number$ - $chapter_name$. যার অনিষ্ট বা অশ্লীলতার ভয়ে মানুষ তাকে এড়িয়ে চলে, কিয়ামতে সে আল্লাহর কাছে মন্দ মর্যাদার লোক হবে।"},"heading":{"title":"অশ্লীল আচরণ সম্পর্কে হাদিস: মানুষকে কষ্ট দেওয়া কেন ভয়ংকর","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم এমন ব্যক্তির কথা বলেছেন, যার অনিষ্টের ভয়ে মানুষ তাকে ছেড়ে দেয়। অন্য বর্ণনায় এসেছে, যার অশ্লীলতার ভয়ে মানুষ তাকে পরিত্যাগ করে। এমন ব্যক্তি কিয়ামতের দিন আল্লাহর কাছে মন্দ মর্যাদার বলে সাব্যস্ত হবে। হাদিসটি আমাদের নিজের আচরণ নিয়ে ভাবতে শেখায়। মানুষ যদি কারও খারাপ কথা, কষ্টদায়ক ব্যবহার বা অশ্লীল আচরণের ভয়ে তাকে এড়িয়ে চলে, তাহলে এটি বড় সতর্ক সংকেত। একজন মুসলিমের আচরণ এমন হওয়া উচিত, যাতে মানুষ নিরাপদ বোধ করে। ভয় দেখিয়ে, কষ্ট দিয়ে বা অশ্লীল ভাষায় মানুষকে দূরে ঠেলে দেওয়া ঈমানি চরিত্রের সঙ্গে মানায় না।"},"teachings":["মানুষের অনিষ্ট থেকে অন্যরা দূরে থাকলে সেটি বড় সতর্কতা।","অশ্লীল আচরণ কিয়ামতে মন্দ মর্যাদার কারণ হতে পারে।","মুসলিমের আচরণে মানুষ নিরাপদ বোধ করা উচিত।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৯৪"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ২০০"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৯৮"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুসলিম ভাইয়ের হক ও সাহায্য","description":"$book_name$ $hadith_number$ - $chapter_name$. মুসলিম ভাইয়ের উপর যুলুম না করা, প্রয়োজন পূরণ, কষ্ট দূর করা ও দোষ ঢাকার শিক্ষা একসাথে এসেছে।"},"heading":{"title":"মুসলিম ভাইয়ের হক: সাহায্য, কষ্ট দূর করা ও দোষ ঢাকার শিক্ষা","description":"এই হাদিসের মূল বিষয় মুসলিম ভাইয়ের হক। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, এক মুসলমান অপর মুসলমানের ভাই। সে তার উপর যুলুম করবে না এবং তাকে ধ্বংসের দিকে ঠেলে দেবে না। যে তার মুসলিম ভাইয়ের প্রয়োজনে সাহায্য করবে, আল্লাহ তার প্রয়োজনের সাহায্য করবেন। যে মুসলমানের দুঃখ-কষ্ট দূর করবে, আল্লাহ কিয়ামতের দিনের বিপদ থেকে তাকে মুক্তির কারণ দেবেন। আর যে মুসলমানের দোষ ঢেকে রাখবে, আল্লাহ তার দোষ ঢেকে রাখবেন। প্রধান কীওয়ার্ড হলো মুসলিম ভাইয়ের হক। সম্পর্কিত কীওয়ার্ড: মুসলিমকে সাহায্য, কষ্ট দূর করার হাদিস, দোষ ঢেকে রাখা, মুসলিম ভ্রাতৃত্ব, যুলুম না করা। হাদিসটি সম্পর্ককে বাস্তব কাজে নামিয়ে আনে—অন্যায় না করা, অসহায় না ফেলে রাখা, প্রয়োজনে পাশে থাকা এবং অকারণে দোষ ছড়িয়ে না দেওয়া।"},"teachings":["মুসলিম ভাইয়ের উপর যুলুম করা যাবে না এবং তাকে বিপদে ফেলে রাখা ঠিক নয়।","ভাইয়ের প্রয়োজন পূরণে সাহায্য করা আল্লাহর সাহায্য লাভের কারণ হতে পারে।","মুসলমানের দুঃখ-কষ্ট দূর করা ও দোষ ঢেকে রাখা বড় নেকির কাজ।"],"related_hadiths":[{"id":"2443","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6013","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="n"/>
     </row>
     <row r="100" ht="46" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
@@ -2813,19 +2773,15 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নাজাতের উপায়: জিহ্বা নিয়ন্ত্রণ","description":"$book_name$ $hadith_number$ - $chapter_name$. নাজাতের উপায় জানতে চাইলে নবী صلى الله عليه وسلم জিহ্বা নিয়ন্ত্রণ, ঘরে থাকা ও নিজের পাপের জন্য কান্নার শিক্ষা দেন।"},"heading":{"title":"নাজাতের উপায় সম্পর্কে হাদিস: জিহ্বা আয়ত্তে রাখা","description":"এই হাদিসে একজন সাহাবী রাসূলুল্লাহ صلى الله عليه وسلم-কে জিজ্ঞেস করেন, নাজাতের উপায় কী? নবী صلى الله عليه وسلم তিনটি নির্দেশ দেন: নিজের জিহ্বা আয়ত্তে রাখো, নিজের ঘরে থাকো, এবং নিজের পাপের জন্য কাঁদো। এই কথাগুলো খুব সহজ, কিন্তু জীবনের জন্য বড় দিকনির্দেশনা। জিহ্বা আয়ত্তে রাখা মানে এমন কথা থেকে বাঁচা, যা পাপ, ঝগড়া বা কষ্টের কারণ হয়। নিজের ঘরে থাকা বলতে এখানে অনর্থক মেলামেশা ও ক্ষতির পরিবেশ থেকে নিজেকে দূরে রাখার শিক্ষা বোঝা যায়। আর পাপের জন্য কান্না মানে নিজের ভুল বুঝে আল্লাহর কাছে ফিরে যাওয়া। হাদিসটি আত্মসমালোচনা, সংযম ও তাওবার পথ দেখায়।"},"teachings":["নাজাতের পথে জিহ্বা নিয়ন্ত্রণ গুরুত্বপূর্ণ।","ক্ষতির পরিবেশ থেকে দূরে থাকা ভালো সিদ্ধান্ত হতে পারে।","নিজের পাপের জন্য অনুতপ্ত হওয়া আল্লাহর দিকে ফেরার পথ।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৮৪"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৮৭"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৮৮"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গনীমতের মাল আত্মসাৎ থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. গনীমতের মাল সময়মতো জমা না দিয়ে পরে অজুহাত দেখানো গ্রহণযোগ্য নয়; আত্মসাৎ ছোট হলেও দায় থেকে যায়।"},"heading":{"title":"গনীমতের মাল আত্মসাৎ: অজুহাত নয়, সময়মতো আমানত জমা দিন","description":"এই হাদিসে গনীমতের মাল বণ্টনের নিয়ম ও আমানতদারির গুরুত্ব দেখা যায়। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) গনীমতের মাল এলে বেলাল (রাঃ)-কে ঘোষণা দিতে বলতেন। লোকেরা যার কাছে যা থাকত তা নিয়ে আসত। তারপর খুমুস বের করে বাকি মাল বণ্টন করা হতো। কিন্তু এক ব্যক্তি সব শেষ হওয়ার পর পশমের লাগাম নিয়ে এসে বলল, এটি গনীমতের মাল। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাকে জিজ্ঞেস করলেন, ঘোষণা শুনেও কেন আগে আনেনি। তার অজুহাত গ্রহণ করা হয়নি। হাদিসটি শেখায়, গনীমতের মাল আত্মসাৎ বা দেরিতে গোপন রাখা খুবই গুরুতর বিষয়। আমানত সময়মতো আদায় করা জরুরি।"},"teachings":["গনীমতের মাল ব্যক্তিগতভাবে রেখে দেওয়া ঠিক নয়।","ঘোষণা শোনার পর আমানত দেরি না করে জমা দিতে হয়।","ছোট জিনিস হলেও আত্মসাৎ হালকা বিষয় নয়।","অজুহাত দিয়ে দায়িত্ব এড়ানো নিরাপদ পথ নয়।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="n"/>
     </row>
     <row r="101" ht="46" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
@@ -2840,19 +2796,15 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দ্বিমুখী ব্যক্তির আখিরাতের শাস্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. দুনিয়ায় দ্বিমুখী ব্যক্তি কিয়ামতের দিন আগুনের দুই জিহ্বা নিয়ে উঠবে—এ হাদিসে কঠোর সতর্কতা এসেছে।"},"heading":{"title":"দ্বিমুখী ব্যক্তির শাস্তি: আগুনের দুই জিহ্বা সম্পর্কে হাদিস","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم বলেছেন, যে ব্যক্তি দুনিয়াতে দ্বিমুখী, কিয়ামতের দিন তার জন্য আগুনের দুটি জিহ্বা হবে। দ্বিমুখী আচরণ হলো এক জায়গায় এক কথা বলা, আর অন্য জায়গায় ভিন্ন কথা বলা; এতে মানুষ বিভ্রান্ত হয় এবং সম্পর্ক নষ্ট হয়। হাদিসটি জিহ্বার সততা নিয়ে কঠোর শিক্ষা দেয়। মানুষের মুখ যদি সত্যের বদলে কৌশল, ধোঁকা ও সম্পর্ক নষ্টের উপায় হয়ে যায়, তাহলে সেটি আখিরাতের জন্য বড় ক্ষতির কারণ হতে পারে। একজন মুমিনের কথা পরিষ্কার ও ন্যায়ের পক্ষে হওয়া দরকার। ভেতরে এক, বাইরে আরেক—এমন চরিত্র থেকে বাঁচাই এই হাদিসের মূল শিক্ষা।"},"teachings":["দ্বিমুখী আচরণের জন্য কিয়ামতে কঠোর সতর্কতা এসেছে।","এক জায়গায় এক কথা, অন্য জায়গায় অন্য কথা বলা থেকে বাঁচতে হবে।","জিহ্বার সততা মুমিনের চরিত্রের গুরুত্বপূর্ণ অংশ।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৮৫"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৮৯"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৮৮"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সম্পদে সততা ও বরকতের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. সম্পদ আকর্ষণীয় হলেও ন্যায্যভাবে অর্জন করলে তাতে বরকত হয়; অন্যায় তসরূপ আখিরাতের ক্ষতির কারণ।"},"heading":{"title":"হালাল সম্পদে বরকত: আল্লাহর সম্পদে অন্যায় তসরূপ নয়","description":"এই হাদিসে সম্পদের আকর্ষণ ও তার পরীক্ষার কথা বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, পার্থিব সম্পদ শ্যামল ও সুমিষ্ট, অর্থাৎ মানুষকে টানে। কিন্তু সম্পদ তখনই কল্যাণের কারণ হয়, যখন তা ন্যায়ভাবে পাওয়া যায়। হালাল সম্পদে বরকত—এই শিক্ষা এখানেই স্পষ্ট। আবার যারা আল্লাহ ও তাঁর রাসূলের সম্পদে নিজের ইচ্ছামতো তসরূপ করে, তাদের জন্য কিয়ামতের দিন কঠিন পরিণামের কথা এসেছে। তাই সম্পদ বেশি হওয়াই মূল কথা নয়; বরং তা কীভাবে পাওয়া হলো এবং কীভাবে ব্যবহার করা হলো, সেটাই বড় বিষয়। বিশেষ করে দায়িত্বে থাকা মাল, গনীমত বা জনস্বার্থের সম্পদে সততা রাখা খুব জরুরি।"},"teachings":["সম্পদ আকর্ষণীয় হলেও তা পরীক্ষা হতে পারে।","ন্যায়ভাবে পাওয়া সম্পদে বরকতের কথা এসেছে।","আল্লাহ ও রাসূলের সম্পদে অন্যায় তসরূপ গুরুতর অপরাধ।","সম্পদের উৎস ও ব্যবহার—দুই দিকেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"3118","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="n"/>
     </row>
     <row r="102" ht="46" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
@@ -2867,19 +2819,15 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুমিনের ভাষা গালমন্দমুক্ত","description":"$book_name$ $hadith_number$ - $chapter_name$. মুমিন ভর্ৎসনাকারী, অভিশাপকারী, অশ্লীল গালমন্দকারী বা নির্লজ্জ হয় না—এটাই হাদিসের শিক্ষা।"},"heading":{"title":"মুমিনের ভাষা কেমন হবে: গালমন্দ ও অশ্লীলতা থেকে দূরে থাকা","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم মুমিনের মুখের ভাষা ও চরিত্র কেমন হওয়া উচিত তা স্পষ্ট করেছেন। তিনি বলেছেন, মুমিন ব্যক্তি ভর্ৎসনাকারী, অভিশাপকারী, অশ্লীল গালমন্দকারী ও নির্লজ্জ হতে পারে না। অর্থাৎ ঈমান শুধু ভেতরের বিশ্বাস নয়; মুখের ভাষা ও আচরণেও তার ছাপ থাকা দরকার। কেউ যদি কথায় কথায় মানুষকে খোঁচা দেয়, অভিশাপ করে, অশ্লীল কথা বলে বা লজ্জাহীন ভাষা ব্যবহার করে, তাহলে সে নিজের চরিত্র নিয়ে ভাবতে পারে। এই হাদিস আমাদের শেখায়, ভালো ভাষা মুমিনের পরিচয়ের অংশ। রাগ হলেও শব্দ বেছে বলা, গালমন্দ থেকে দূরে থাকা এবং শালীনতা রাখা—এসব ঈমানি আচরণ।"},"teachings":["মুমিনের ভাষা গালমন্দ ও অশ্লীলতা থেকে দূরে থাকা উচিত।","অভিশাপ ও ভর্ৎসনা মুমিনের সুন্দর চরিত্রের সঙ্গে মানায় না।","শালীন কথা বলা ঈমানি আচরণের একটি অংশ।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৮৬"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৯১"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ২০০"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | খিয়ানত ও কিয়ামতের জবাবদিহি","description":"$book_name$ $hadith_number$ - $chapter_name$. খিয়ানত করা বস্তু কিয়ামতে মানুষের কাঁধে প্রকাশ পাবে; নবী আগেই সতর্ক করেছেন, তাই আমানত রক্ষা জরুরি।"},"heading":{"title":"খিয়ানত থেকে বাঁচুন: কিয়ামতে গোপন আত্মসাৎ প্রকাশ পাবে","description":"এই হাদিসে খিয়ানতের ভয়াবহতা খুব পরিষ্কারভাবে এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খিয়ানতের বিষয়টি বড় করে তুলে ধরেছেন এবং কিয়ামতের দিনের কয়েকটি দৃশ্য বলেছেন। কেউ উট, কেউ ঘোড়া, কেউ ছাগল, কেউ মানুষ, কেউ কাপড়, কেউ সোনা-চাঁদির মতো সম্পদ কাঁধে নিয়ে আসবে—অর্থাৎ যে জিনিসে খিয়ানত করেছে, সেটিই তার দায় হয়ে প্রকাশ পাবে। তখন সে সাহায্য চাইবে, কিন্তু রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলবেন, তিনি আগেই আল্লাহর বিধান জানিয়ে দিয়েছেন। এই হাদিস আত্মসাৎ ও খিয়ানত থেকে কঠোরভাবে সতর্ক করে। আমানত লুকিয়ে রাখা, দায়িত্বের সম্পদ নেওয়া বা অন্যের মাল নিজের করে নেওয়া কখনো নিরাপদ নয়।"},"teachings":["খিয়ানত করা বস্তু কিয়ামতে দায় হিসেবে প্রকাশ পাবে।","আগে সতর্ক করা হলে পরে অজুহাতের সুযোগ কমে যায়।","অন্যের মাল, প্রাণী, কাপড় বা সম্পদ আত্মসাৎ করা গুরুতর বিষয়।","আমানত রক্ষা করা আখিরাতের জবাবদিহির সঙ্গে জড়িত।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1201","book_id":"10","slug":"luluwal-marjan","label":"লুলুওয়াল মারজান"}]}</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="n"/>
     </row>
     <row r="103" ht="46" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
@@ -2894,19 +2842,15 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সামান্য কথাও গীবত হতে পারে","description":"$book_name$ $hadith_number$ - $chapter_name$. কারও শারীরিক দিক নিয়ে অপছন্দের কথা বলা হালকা নয়; নবী صلى الله عليه وسلم এমন কথার ক্ষতি কঠোরভাবে বুঝিয়েছেন।"},"heading":{"title":"গীবতের ক্ষতি: ছোট করে বলা কথাও বড় হতে পারে","description":"এই হাদিসে আয়েশা রাঃ ছাফিয়্যা রাঃ সম্পর্কে এমন কথা বলেন, যার অর্থ ছিল তিনি বেঁটে। রাসূলুল্লাহ صلى الله عليه وسلم তখন বলেন, যদি এই কথাটি সমুদ্রের সঙ্গে মিশিয়ে দেওয়া হয়, তবে তা সমুদ্রের রং বদলে দেবে। এখানে বড় শিক্ষা হলো, মানুষের শারীরিক দিক বা অপছন্দের বিষয় নিয়ে কথা বলা হালকা নয়। অনেক সময় আমরা ছোট মন্তব্যকে হাসি-ঠাট্টা মনে করি, কিন্তু তা গীবত বা কষ্টের কারণ হতে পারে। হাদিসটি আমাদের জিহ্বা নিয়ন্ত্রণের শিক্ষা দেয়। বিশেষ করে কারও শরীর, চেহারা বা দুর্বলতা নিয়ে কথা বলার আগে থামা দরকার। মুমিনের কথা এমন হওয়া উচিত, যাতে অন্যের সম্মান নষ্ট না হয়।"},"teachings":["কারও শারীরিক দিক নিয়ে অপছন্দের কথা বলা বিপজ্জনক হতে পারে।","ছোট মনে হওয়া কথাও বড় ক্ষতির কারণ হতে পারে।","অন্যের সম্মান রক্ষায় জিহ্বা নিয়ন্ত্রণ জরুরি।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৯০"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৯৯"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৮৭"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সামান্য আত্মসাতের বড় পরিণাম","description":"$book_name$ $hadith_number$ - $chapter_name$. গনীমত বণ্টনের আগে নেওয়া ছোট চাদরও আগুনের কারণ বলা হয়েছে; আত্মসাৎ ছোট মনে করা উচিত নয়।"},"heading":{"title":"সামান্য আত্মসাৎও ভয়াবহ: গনীমতের মাল নিয়ে সতর্ক হোন","description":"এই হাদিসে মিদআম নামে এক ব্যক্তির ঘটনা এসেছে। তিনি মারা গেলে সাহাবীগণ তার জন্য জান্নাতের কথা বলেছিলেন। কিন্তু রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) জানালেন, খায়বারের গনীমত বণ্টনের আগে নেওয়া একটি চাদর তার জন্য আগুনের কারণ হচ্ছে। এটি শুনে একজন লোক জুতার ফিতা বা দু’টি ফিতা নিয়ে এলো। তখনও রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সেটির ব্যাপারে আগুনের কথা বললেন। এই হাদিসের মূল শিক্ষা হলো, আত্মসাৎ ছোট মনে করা যাবে না। গনীমতের মাল হোক বা অন্য কোনো আমানত—বণ্টন বা অনুমতি ছাড়া নেওয়া বড় দায়। বাহ্যিকভাবে ভালো অবস্থায় মৃত্যু হলেও মানুষের গোপন কাজের হিসাব আল্লাহর কাছে থাকবে।"},"teachings":["গনীমত বণ্টনের আগে কিছু নেওয়া আত্মসাতের মধ্যে পড়ে।","সামান্য বস্তু হলেও আত্মসাৎকে ছোট মনে করা ঠিক নয়।","মানুষের বাহ্যিক ধারণা সব সময় আসল অবস্থা জানায় না।","অমানত ও গনীমতের মাল ফেরত দিতে দেরি করা বিপজ্জনক।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3118","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="n"/>
     </row>
     <row r="104" ht="46" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
@@ -2921,19 +2865,15 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছয়টি আমল ও জান্নাতের আশ্বাস","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য বলা, ওয়াদা রাখা, আমানত আদায়, লজ্জাস্থান হেফাজত, দৃষ্টি নিচু রাখা ও হাত বিরত রাখার শিক্ষা এসেছে।"},"heading":{"title":"ছয়টি আমল সম্পর্কে হাদিস: জান্নাতের আশ্বাস লাভের পথ","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم ছয়টি বিষয়ের জামানত চাইতে বলেছেন এবং এর বিনিময়ে জান্নাতের যামিন হওয়ার কথা বলেছেন। ছয়টি বিষয় হলো: কথা বললে সত্য বলা, ওয়াদা করলে তা পূর্ণ করা, আমানত রাখা হলে তা আদায় করা, লজ্জাস্থান হেফাজত করা, দৃষ্টি অবনত রাখা এবং হাতকে অন্যায় কাজ থেকে বিরত রাখা। এখানে ইসলামের সুন্দর চরিত্রের বড় ছবি দেখা যায়। শুধু মুখের কথা নয়, ওয়াদা, আমানত, চোখ, হাত এবং ব্যক্তিগত পবিত্রতা—সবই একজন মুসলিমের দায়িত্ব। এই হাদিস আমাদের শেখায়, ভালো মুসলিম হতে হলে জীবনের নানা দিক ঠিক রাখতে হয়। সত্যবাদিতা, আমানতদারি ও সংযম একসঙ্গে দরকার।"},"teachings":["কথা বললে সত্য বলা মুসলিম চরিত্রের অংশ।","ওয়াদা পূরণ ও আমানত আদায় করা গুরুত্বপূর্ণ দায়িত্ব।","দৃষ্টি, হাত ও লজ্জাস্থানকে অন্যায় থেকে বাঁচাতে হবে।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৮৪"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৮৮"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৮৩"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দায়িত্বের মাল আত্মসাৎ থেকে ভয়","description":"$book_name$ $hadith_number$ - $chapter_name$. দায়িত্বে থাকা ব্যক্তির চাদর আত্মসাৎ তার পরিণামকে ভয়াবহ করেছে; আমানতের মাল গোপন করা বড় অপরাধ।"},"heading":{"title":"দায়িত্বের মাল আত্মসাৎ: কারকারার ঘটনা থেকে সতর্ক শিক্ষা","description":"এই হাদিসে এমন এক ব্যক্তির কথা এসেছে, যে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর গনীমতের মালের দায়িত্বে ছিল। তার নাম ছিল কারকারা। সে মারা গেলে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাকে জাহান্নামী বলে জানান। পরে সাহাবীগণ গিয়ে দেখলেন, সে একটি চাদর আত্মসাৎ করেছিল। হাদিসটি দায়িত্বের মাল আত্মসাৎ সম্পর্কে কঠিন সতর্কতা দেয়। কেউ যদি কোনো সম্পদের পাহারাদার, দায়িত্বশীল বা ব্যবস্থাপক হয়, তাহলে তার দায়িত্ব আরও বড়। কারণ সে নিজের জন্য নয়, আমানতের জন্য কাজ করছে। একটি চাদরকে ছোট মনে করা হলেও হাদিসে তার পরিণাম কঠিনভাবে এসেছে। তাই সরকারি, সামাজিক, পারিবারিক বা যে কোনো দায়িত্বের মাল নিজের করে নেওয়া থেকে বেঁচে থাকা দরকার।"},"teachings":["দায়িত্বে থাকা মাল নিজের জন্য নেওয়া খিয়ানত।","আত্মসাৎ করা বস্তু ছোট হলেও এর দায় বড় হতে পারে।","দায়িত্বশীল ব্যক্তির আমানতদারি আরও বেশি জরুরি।","গোপনভাবে নেওয়া জিনিস আল্লাহর কাছে গোপন থাকে না।"],"related_hadiths":[{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3118","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="n"/>
     </row>
     <row r="105" ht="46" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
@@ -2948,19 +2888,15 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহ, হিংসা ও গোয়েন্দাগিরি থেকে বাঁচা","description":"$book_name$ $hadith_number$ - $chapter_name$. মন্দ ধারণা, দোষ খোঁজা, গোয়েন্দাগিরি, ধোঁকাবাজি, হিংসা ও শত্রুতা ছেড়ে ভাই ভাই হয়ে থাকার শিক্ষা।"},"heading":{"title":"মুসলিম ভ্রাতৃত্বের হাদিস: সন্দেহ ও গোয়েন্দাগিরি থেকে বাঁচা","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم একসঙ্গে অনেক সামাজিক রোগ থেকে সতর্ক করেছেন। তিনি বলেছেন, মন্দ ধারণা থেকে বেঁচে থাক, কারণ ধারণা বড় ধরনের মিথ্যা। কারও দোষ খুঁজতে চেষ্টা করো না, গোয়েন্দাগিরি করো না, ক্রয়-বিক্রয়ে ধোঁকাবাজি করো না, একে অন্যের প্রতি হিংসা রেখো না, শত্রুতা করো না এবং একে অন্যের পিছনে লেগো না। বরং আল্লাহর বান্দা হিসেবে ভাই ভাই হয়ে থাকো। এই হাদিস মুসলিম ভ্রাতৃত্বের ভিত্তি শেখায়। সম্পর্ক নষ্ট হয় সন্দেহ, দোষ খোঁজা, হিংসা ও ঘৃণা থেকে। তাই একজন মুসলিমের কাজ হলো সম্পর্ক রক্ষা করা, অন্যের ক্ষতি না করা এবং ভাইয়ের মতো আচরণ করা।"},"teachings":["মন্দ ধারণা থেকে বাঁচতে বলা হয়েছে।","দোষ খোঁজা ও গোয়েন্দাগিরি সম্পর্ক নষ্ট করে।","মুসলিমদের মধ্যে ভাই ভাই সম্পর্ক বজায় রাখা দরকার।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৯৮"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৯১"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ২০০"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আত্মসাৎ শহীদের মর্যাদায় বাধা","description":"$book_name$ $hadith_number$ - $chapter_name$. বাহ্যিকভাবে শহীদ বলা হলেও চাদর আত্মসাৎকারীর পরিণাম কঠিন হয়েছে; গোপন খিয়ানত থেকে সতর্ক থাকতে হবে।"},"heading":{"title":"আত্মসাৎ ও শহীদের দাবি: গোপন খিয়ানত আখিরাতে প্রকাশ পায়","description":"এই হাদিসে খায়বারের দিনের একটি ঘটনা এসেছে। সাহাবীগণ কয়েকজনকে শহীদ বলছিলেন। এমন একজনের ব্যাপারে তারা শহীদ বললে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বললেন, কখনো নয়; তিনি তাকে জাহান্নামে দেখেছেন, কারণ সে একটি চাদর আত্মসাৎ করেছিল। এই বক্তব্য খুব গভীর শিক্ষা দেয়। মানুষের চোখে কেউ বাহ্যিকভাবে ভালো বা সম্মানিত মনে হতে পারে, কিন্তু গোপন খিয়ানত থাকলে তার হিসাব আল্লাহর কাছে থাকবে। আত্মসাৎ শহীদের মর্যাদার দাবিকেও বিপদে ফেলতে পারে—হাদিসের ভাষায় বিষয়টি এভাবেই এসেছে। তাই গনীমতের মাল, দায়িত্বের মাল বা কোনো আমানত গোপনে নেওয়া থেকে কঠোরভাবে বাঁচা দরকার।"},"teachings":["মানুষের বাহ্যিক প্রশংসা আখিরাতের হিসাব বদলায় না।","একটি চাদর আত্মসাৎ করাও ভয়াবহ পরিণামের কারণ হয়েছে।","গোপন খিয়ানত মানুষের মর্যাদাকে ক্ষতিগ্রস্ত করতে পারে।","আল্লাহর কাছে আমানতের হিসাব খুবই গুরুতর।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="n"/>
     </row>
     <row r="106" ht="46" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
@@ -2975,17 +2911,17 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুসলিমের দোষ খোঁজা থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মুসলমানকে কষ্ট দেওয়া, ভর্ৎসনা করা ও তার দোষ খোঁজা থেকে নবী صلى الله عليه وسلم কঠোরভাবে সতর্ক করেছেন।"},"heading":{"title":"মুসলিমের দোষ খোঁজা সম্পর্কে হাদিস: সম্মান রক্ষা করার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم মিম্বরে উঠে উচ্চ স্বরে সতর্ক করেছেন। তিনি বলেছেন, যারা মুখে ইসলাম গ্রহণ করেছে কিন্তু ঈমান অন্তরে গভীর হয়নি, তারা যেন মুসলমানদের কষ্ট না দেয়, ভর্ৎসনা না করে এবং তাদের দোষ-ত্রুটি অনুসন্ধান না করে। যে তার মুসলিম ভাইয়ের দোষ খুঁজে বেড়ায়, আল্লাহ তার দোষ খুঁজবেন; আর আল্লাহ যার দোষ ধরবেন, তাকে অপদস্থ করবেন। এই হাদিস আমাদের অন্যের সম্মান রক্ষা করতে শেখায়। কারও ভুল খুঁজে বেড়ানো, তাকে হেয় করা বা কষ্ট দেওয়া ঈমানি আচরণ নয়। নিজের জিহ্বা ও আচরণকে সংযত রাখা, মুসলিম ভাইয়ের মান রক্ষা করা—এটাই মূল শিক্ষা।"},"teachings":["মুসলমানকে কষ্ট দেওয়া থেকে বাঁচতে হবে।","অন্যের দোষ খুঁজে বেড়ানো কঠোরভাবে নিষেধ করা হয়েছে।","মুসলিম ভাইয়ের সম্মান রক্ষা করা ঈমানি দায়িত্ব।"],"related_hadiths":[]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আল্লাহর সন্তুষ্টি ও অসন্তুষ্টির কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ তিন কাজে সন্তুষ্ট হন এবং তিন কাজে অসন্তুষ্ট হন—ইবাদত, ঐক্য, উপদেশ ও অপচয়ের শিক্ষা এখানে আছে।"},"heading":{"title":"আল্লাহর সন্তুষ্টির তিন কাজ ও অসন্তুষ্টির তিন কাজ","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ তিনটি কাজে সন্তুষ্ট হন এবং তিনটি কাজে অসন্তুষ্ট হন। সন্তুষ্টির কাজ হলো আল্লাহর ইবাদত করা ও তাঁর সঙ্গে শরীক না করা, আল্লাহর বিধানকে শক্তভাবে আঁকড়ে ধরা ও বিচ্ছিন্ন না হওয়া, এবং যাকে আল্লাহ কাজের নেতা করেন তার জন্য পরস্পরে কল্যাণ কামনা করা। আর আল্লাহ অসন্তুষ্ট হন অপ্রয়োজনীয় কথা, সম্পদ নষ্ট করা এবং অনর্থক বেশি প্রশ্ন করার কারণে। এই হাদিসে তাওহীদ, ঐক্য, নসীহত, সম্পদ রক্ষা ও কথা নিয়ন্ত্রণের শিক্ষা এসেছে। মুসলিম জীবনে শুধু ইবাদত নয়, কথা, সম্পদ ও সামাজিক আচরণও গুরুত্বপূর্ণ। আল্লাহর সন্তুষ্টির কাজ খুঁজে জীবন সাজানোই এই হাদিসের সহজ বার্তা।"},"teachings":["আল্লাহর ইবাদত করা এবং শিরক থেকে দূরে থাকা বড় দায়িত্ব।","আল্লাহর বিধান আঁকড়ে ধরা ও বিচ্ছিন্নতা এড়ানো দরকার।","অপ্রয়োজনীয় কথা ও সম্পদ নষ্ট করা থেকে বাঁচতে হবে।","নেতার জন্য কল্যাণ কামনা করা ভালো সামাজিক আচরণ।"],"related_hadiths":[{"id":"1715","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৯৭"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৯০"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৯৯"</t>
+          <t>related_hadiths[1]: unknown book label "মুসনাদে আহমাদ ৮৭৮৫"; related_hadiths[2]: unknown book label "সহীহ ইবনু হিব্বান ৩৩৮৮"</t>
         </is>
       </c>
     </row>
@@ -3002,19 +2938,15 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মানুষের সম্মানহানি ও কঠোর সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মি‘রাজে নবী صلى الله عليه وسلم এমন লোক দেখেছেন, যারা মানুষের সম্মান নষ্ট করত; তাদের কঠিন অবস্থার কথা বলা হয়েছে।"},"heading":{"title":"মানুষের সম্মানহানি সম্পর্কে হাদিস: গীবত ও অপমান থেকে সতর্কতা","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم মি‘রাজের সময় দেখা একটি ঘটনার কথা বলেছেন। তিনি কিছু লোককে দেখলেন, যাদের নখ ছিল তামার। তারা সেই নখ দিয়ে নিজেদের মুখমণ্ডল ও বুক আঁচড়াচ্ছিল। তিনি জিবরাঈল আঃ-কে জিজ্ঞেস করলে তিনি বললেন, এরা সেই লোক, যারা মানুষের গোশত খেত এবং মানুষের ইজ্জত-আব্রুতে আঘাত করত। হাদিসের ভাষা খুব কঠোর এবং সতর্ক করার মতো। এখানে মানুষের সম্মানহানি, গীবত ও অপমানের ভয়াবহতা বোঝানো হয়েছে। অন্যের সম্মান নষ্ট করা শুধু সামাজিক ভুল নয়; এর আখিরাতের ভয়ও আছে। তাই মানুষের দোষ ছড়ানো, অপমান করা এবং সম্মান নিয়ে খেলা থেকে দূরে থাকা দরকার।"},"teachings":["মানুষের সম্মান নষ্ট করা ভয়াবহ পাপের কারণ হতে পারে।","গীবত ও অপমানের বিষয়ে হাদিসে কঠোর সতর্কতা এসেছে।","অন্যের ইজ্জত রক্ষা করা মুসলিম চরিত্রের অংশ।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৯০"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৯৫"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৯৮"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অন্যায় সম্পদ দখলের ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর সম্পদ অন্যায়ভাবে দখল বা ব্যবহার করলে কিয়ামতের দিন জাহান্নামের কঠিন সতর্কতা এসেছে।"},"heading":{"title":"অন্যায় সম্পদ দখল: আল্লাহর মালে অন্যায় ব্যবহার থেকে বাঁচুন","description":"এই হাদিসে অন্যায়ভাবে সম্পদ দখল করার পরিণাম খুব স্পষ্টভাবে বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যারা আল্লাহর সম্পদে অন্যায়ভাবে তসরূপ করে, কিয়ামতের দিন তাদের জন্য জাহান্নাম রয়েছে। এখানে মূল বিষয় হলো, সম্পদকে নিজের ইচ্ছামতো ব্যবহার করা যাবে না, যদি সেটি নিজের হক না হয়। অন্যায় সম্পদ দখল শুধু চুরি বা প্রকাশ্য ছিনিয়ে নেওয়ার মধ্যে সীমিত নয়; দায়িত্বের মাল, গনীমতের মাল বা মানুষের হক—সব ক্ষেত্রেই সতর্কতা দরকার। হাদিসটি আমাদের শেখায়, সম্পদের ব্যাপারে আল্লাহর ভয় রাখা দরকার। যা ন্যায্য নয়, তা থেকে দূরে থাকা নিরাপদ পথ।"},"teachings":["অন্যায়ভাবে সম্পদ দখল করা আখিরাতের বড় ক্ষতির কারণ।","আল্লাহর মাল বা দায়িত্বের মাল নিজের ইচ্ছায় ব্যবহার করা ঠিক নয়।","সম্পদের ব্যাপারে হক-না-হক বিচার করা জরুরি।","কিয়ামতের জবাবদিহি মনে রাখলে আত্মসাৎ থেকে বাঁচা সহজ হয়।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="n"/>
     </row>
     <row r="108" ht="46" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
@@ -3029,12 +2961,12 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সালাত যাকাত ও মুসলমানের কল্যাণ","description":"$book_name$ $hadith_number$ - $chapter_name$. সালাত কায়েম, যাকাত আদায় ও সকল মুসলমানের কল্যাণ কামনার উপর বায়আতের শিক্ষা এই হাদিসে এসেছে।"},"heading":{"title":"সালাত যাকাত ও সকল মুসলমানের কল্যাণ কামনার বায়আত","description":"এই হাদিসে জারীর ইবনু আবদুল্লাহ (রাঃ) বলেন, তিনি রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর সাথে বায়আত করেছেন তিনটি বিষয়ের উপর: সালাত প্রতিষ্ঠা করা, যাকাত প্রদান করা এবং সকল মুসলমানের কল্যাণ কামনা করা। এখানে সালাত, যাকাত ও নসীহত একসঙ্গে এসেছে। এতে বোঝা যায়, ইবাদত শুধু ব্যক্তিগত কাজ নয়; মুসলমানদের জন্য ভালো চাওয়াও দ্বীনের অংশ। সালাত মানুষকে আল্লাহর সঙ্গে যুক্ত করে, যাকাত সম্পদের দায়িত্ব শেখায়, আর মুসলমানের কল্যাণ কামনা সমাজকে সুন্দর করে। এই বায়আত হাদিস আমাদের শেখায়, একজন মুসলিম নিজের ইবাদত ঠিক রাখার পাশাপাশি অন্য মুসলমানের ক্ষতি নয়, বরং কল্যাণ চায়।"},"teachings":["সালাত প্রতিষ্ঠা করা মুসলিম জীবনের গুরুত্বপূর্ণ দায়িত্ব।","যাকাত আদায় সম্পদের হক বুঝে দেওয়ার শিক্ষা দেয়।","সকল মুসলমানের কল্যাণ কামনা দ্বীনের সুন্দর আচরণ।","বায়আত মানে দায়িত্ব মেনে চলার অঙ্গীকার।"],"related_hadiths":[{"id":"57","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"56","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"4967","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল রিজিক ও দোয়া কবুলের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য, পানীয়, পোশাক ও জীবিকা হারাম হলে দোয়া কবুলের পথে বাধা তৈরি হয়; পবিত্র রিজিক জরুরি।"},"heading":{"title":"হালাল রিজিক ও দোয়া কবুল: খাদ্য-পোশাকে পবিত্রতা কেন জরুরি","description":"এই হাদিসে হালাল রিজিকের গুরুত্ব খুব সুন্দরভাবে বোঝানো হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ পবিত্র এবং তিনি পবিত্র ছাড়া গ্রহণ করেন না। এরপর এমন এক ব্যক্তির কথা এসেছে, যে সফরে ক্লান্ত, ধুলামলিন, দু’হাত তুলে কাতরভাবে দোয়া করছে। বাহ্যিকভাবে দোয়ার অনেক কারণ আছে। কিন্তু তার খাদ্য হারাম, পানীয় হারাম, পোশাক হারাম এবং জীবিকা হারাম। তাই বলা হয়েছে, তার দোয়া কীভাবে কবুল হবে? হালাল রিজিক হাদিস আমাদের শেখায়, দোয়া শুধু মুখের শব্দ নয়; জীবনের উপার্জন, খাবার ও পোশাকের সঙ্গেও এর সম্পর্ক আছে। তাই ইবাদতের সঙ্গে হালাল উপার্জনকে গুরুত্ব দেওয়া দরকার।"},"teachings":["আল্লাহ পবিত্র, তাই পবিত্র বস্তু গ্রহণ করেন।","হারাম খাদ্য, পানীয় ও পোশাক দোয়া কবুলের পথে বাধা হতে পারে।","দোয়ার সঙ্গে জীবিকার পবিত্রতার সম্পর্ক আছে।","হালাল উপার্জন ইবাদতের জীবনে গুরুত্বপূর্ণ অংশ।"],"related_hadiths":[{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1205","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E108" s="4" t="n"/>
@@ -3052,12 +2984,12 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অনধিকার জমি নেওয়ার শাস্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. অনধিকারে কারও জমি নিলে কিয়ামতের দিন তাকে সাত তবক জমিন পর্যন্ত ধসিয়ে দেওয়ার সতর্কতা এসেছে।"},"heading":{"title":"অনধিকার জমি নেওয়ার পরিণতি ও হক রক্ষার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি অনধিকারে কারও কিছু জমি নেয়, কিয়ামতের দিন তাকে সাত তবক জমিন পর্যন্ত ধসিয়ে দেওয়া হবে। এই হাদিস জমি দখল, অন্যের হক নেওয়া এবং যুলুমের বিরুদ্ধে কঠোর সতর্কতা দেয়। জমি ছোট হোক বা বড়—অধিকার ছাড়া নেওয়া বৈধ নয়। মানুষের সম্পদে হাত দেওয়ার আগে মনে রাখতে হবে, আখেরাতে এর হিসাব আছে। এই হাদিস আমাদের জমির সীমানা, দলিল, মালিকানা ও ন্যায্য অধিকার বিষয়ে সতর্ক করে। অন্যের হক বাঁচিয়ে চলা শুধু সামাজিক নিয়ম নয়; এটি আখেরাতের জবাবদিহির সঙ্গেও জড়িত।"},"teachings":["অনধিকারে জমি নেওয়া যুলুমের মধ্যে পড়ে।","কিয়ামতে জমি দখলের কঠিন পরিণতির কথা এসেছে।","অন্যের সম্পদ ও জমির অধিকার মানা জরুরি।","ন্যায্য হক ছাড়া কিছু নেওয়া থেকে বিরত থাকা দরকার।"],"related_hadiths":[{"id":"2454","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2958","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"1610","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল-হারাম উপার্জনে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. এমন সময় আসবে যখন মানুষ উপার্জনের হালাল-হারাম নিয়ে পরোয়া করবে না; তাই আয়ের উৎস যাচাই জরুরি।"},"heading":{"title":"হালাল-হারাম উপার্জন: আয়ের উৎস নিয়ে উদাসীন হবেন না","description":"এই হাদিসে ভবিষ্যৎ সময়ের একটি বড় বিপদের কথা বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, মানুষের উপর এমন সময় আসবে, যখন মানুষ হালাল-হারাম উপার্জন বিবেচনা করবে না। অর্থাৎ টাকা আসছে কি না—এটাই যদি প্রধান চিন্তা হয়ে যায়, তাহলে মানুষ উৎস ভুলে যেতে পারে। হালাল হারাম উপার্জন বিষয়টি তাই শুধু ফিকহের আলোচনা নয়; এটি ব্যক্তিগত জীবনের প্রতিদিনের পরীক্ষা। ব্যবসা, চাকরি, লেনদেন, কমিশন, বেতন—সব ক্ষেত্রেই মুসলিমের দেখা দরকার, এই আয় বৈধ পথে হচ্ছে কি না। হাদিসটি আমাদের আগে থেকেই সতর্ক করে, যাতে সমাজের ভুল পথে ভেসে না যাই এবং নিজের রিজিকের বিষয়ে আল্লাহকে ভয় করি।"},"teachings":["উপার্জনের উৎস হালাল কি না তা দেখা জরুরি।","সমাজে উদাসীনতা বাড়লেও মুমিনকে সতর্ক থাকতে হবে।","শুধু টাকা পাওয়া নয়, বৈধ পথে পাওয়া গুরুত্বপূর্ণ।","হালাল-হারাম বিচার না করা বড় নৈতিক ক্ষতির কারণ হতে পারে।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1205","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E109" s="4" t="n"/>
@@ -3075,19 +3007,15 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কোমলতার সৌন্দর্য ও ফজিলত","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ কোমল এবং কোমলতা ভালোবাসেন; কোমলতা কোনো বিষয়ে থাকলে তা সুন্দর হয়, আর না থাকলে দোষ দেখা দেয়।"},"heading":{"title":"কোমলতা সম্পর্কে হাদিস: কঠোরতা ছেড়ে সুন্দর আচরণের শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم বলেছেন, আল্লাহ কোমল, তিনি কোমলতাকে ভালোবাসেন। তিনি কোমলতার প্রতি এমন অনুগ্রহ করেন, যা কঠোরতা বা অন্য আচরণের প্রতি করেন না। মুসলিমের অপর বর্ণনায় নবী صلى الله عليه وسلم আয়েশা রাঃ-কে বলেন, কোমলতা নিজের জন্য গ্রহণ করো এবং কঠোরতা ও নির্লজ্জতা থেকে বাঁচো। কারণ কোনো বিষয়ে কোমলতা থাকলে তা সুন্দর হয়; আর কোমলতা তুলে নেওয়া হলে তা দোষণীয় হয়ে পড়ে। এই হাদিস আমাদের আচরণে নরম হওয়া শেখায়। কোমলতা মানে দুর্বলতা নয়; বরং কথা, ব্যবহার ও আচরণে সৌন্দর্য রাখা। পরিবার, সমাজ ও মানুষের সঙ্গে চলাফেরায় কোমল ভাষা এবং শান্ত মন ভালো প্রভাব ফেলে।"},"teachings":["আল্লাহ কোমলতাকে ভালোবাসেন।","কোমলতা কোনো বিষয়ে থাকলে তা সুন্দর হয়।","কঠোরতা ও নির্লজ্জতা থেকে নিজেকে বাঁচানো উচিত।"],"related_hadiths":[]}</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ হাদিস ১৯৪"; related_hadiths[1]: unknown book label "ঊপদেশ হাদিস ১৯১"; related_hadiths[2]: unknown book label "ঊপদেশ হাদিস ১৯৭"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম খাদ্যের ভয়াবহ পরিণাম","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম খাদ্যে লালিত শরীরের পরিণাম কঠিন বলা হয়েছে; তাই খাবার ও উপার্জনে হালাল পথ জরুরি।"},"heading":{"title":"হারাম খাদ্য থেকে বাঁচুন: শরীর ও রিজিকের পবিত্রতা","description":"এই হাদিসে খুব সংক্ষিপ্ত ভাষায় বড় একটি সতর্কতা এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, হারাম খাদ্য দ্বারা পরিপুষ্ট শরীর জান্নাতে যাবে না। তাই হারাম খাদ্য হাদিস আমাদের শুধু খাবারের নাম নয়, খাবারের উৎস নিয়েও ভাবতে শেখায়। যে খাবার আমরা খাই, সেটি কীভাবে কেনা হলো, আয়টি বৈধ ছিল কি না, অন্যের হক মিশে আছে কি না—এসব বিষয় গুরুত্বপূর্ণ। শরীর খাবার দিয়ে গড়ে ওঠে, আর মুমিনের জীবন ইবাদত ও আনুগত্যের জন্য। তাই হারাম খাদ্যকে হালকা মনে করা ঠিক নয়। এই হাদিসের শিক্ষা হলো, নিজের ও পরিবারের খাবারের ব্যাপারে সতর্ক থাকা এবং হালাল রিজিকের চেষ্টা করা।"},"teachings":["হারাম খাদ্যে শরীর গড়ে ওঠা ভয়াবহ সতর্কতার বিষয়।","খাবারের সঙ্গে উপার্জনের উৎসও দেখা দরকার।","পরিবারের খাবার হালাল কি না তা অভিভাবকের দায়িত্বের অংশ।","হালাল রিজিকের চেষ্টা করা ঈমানি জীবনের গুরুত্বপূর্ণ কাজ।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="n"/>
     </row>
     <row r="111" ht="46" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
@@ -3102,19 +3030,15 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নম্রতা ও কোমলতার কল্যাণ","description":"$book_name$ $hadith_number$ - $chapter_name$. কোমলতা থেকে বঞ্চিত হলে মানুষ অনেক কল্যাণ হারায়; এই হাদিসে সুন্দর আচরণ ও নরম ব্যবহারের গুরুত্ব বোঝানো হয়েছে।"},"heading":{"title":"নম্রতা ও কোমলতা: কল্যাণ পাওয়ার বড় শিক্ষা","description":"এই হাদিসের মূল কথা খুব সরল: কোমলতা ও নম্রতা মানুষের জীবনে কল্যাণের দরজা খুলে দেয়। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যাকে কোমলতা থেকে বঞ্চিত করা হয়, তাকে কল্যাণ থেকেও বঞ্চিত করা হয়। এখানে নম্রতা মানে দুর্বলতা নয়; বরং কথা, আচরণ ও ব্যবহারকে নরম রাখা। পরিবারে, কাজে বা মানুষের সঙ্গে মেলামেশায় রুক্ষ কথা অনেক সময় সম্পর্ক নষ্ট করে। আর কোমল ব্যবহার মানুষকে কাছে আনে। তাই এই হাদিস আমাদের শেখায়, ভালো মুসলিম চরিত্র গড়তে নরম ভাষা, ধৈর্য আর সুন্দর আচরণ জরুরি। হাদিসে কল্যাণের কথা এসেছে, তাই আমরা বলতে পারি—নম্রতা মানুষকে ভালো গুণের দিকে নিয়ে যায়। তাই নিজের ভাষা ও আচরণে কোমলতা আছে কি না, তা নিয়মিত খেয়াল করা এই হাদিসের খুব বাস্তব প্রয়োগ।"},"teachings":["কথা ও আচরণে কোমলতা রাখা কল্যাণের কারণ।","রুক্ষ স্বভাব মানুষকে ভালো দিক থেকে দূরে নিতে পারে।","নম্র ব্যবহার পরিবার ও সমাজে সম্পর্ক সুন্দর করে।","কোমলতা দুর্বলতা নয়; এটি ভালো চরিত্রের অংশ।"],"related_hadiths":[{"id":"5068","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "আদাবুল মুফরাদ ৪৬৫"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল-হারাম ও সন্দেহজনক বিষয়","description":"$book_name$ $hadith_number$ - $chapter_name$. হালাল-হারাম স্পষ্ট; সন্দেহজনক বিষয় থেকে বাঁচলে দ্বীন ও মর্যাদা রক্ষা হয়, আর অন্তর ঠিক থাকলে শরীর ঠিক থাকে।"},"heading":{"title":"হালাল হারাম স্পষ্ট: সন্দেহজনক বিষয় থেকে বাঁচার শিক্ষা","description":"এই হাদিস ইসলামী জীবনের একটি মৌলিক নীতি শেখায়। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, হালাল স্পষ্ট এবং হারামও স্পষ্ট। মাঝখানে কিছু সন্দেহজনক বিষয় আছে, যা অনেক মানুষ জানে না। যে ব্যক্তি সন্দেহজনক বিষয় থেকে বেঁচে থাকে, সে তার দ্বীন ও মর্যাদা রক্ষা করে। আর যে সন্দেহজনক বিষয়ে পড়ে, সে হারামের কাছাকাছি চলে যায়। রাখালের উদাহরণ দিয়ে বোঝানো হয়েছে, নিষিদ্ধ সীমার ধারে থাকলে ভিতরে ঢুকে পড়ার ভয় থাকে। শেষে অন্তরের কথা বলা হয়েছে: অন্তর ঠিক থাকলে শরীর ঠিক থাকে, নষ্ট হলে শরীরও নষ্ট হয়। তাই সন্দেহজনক বিষয় হাদিস আমাদের সতর্ক, পরিষ্কার ও অন্তর-সচেতন জীবন শেখায়।"},"teachings":["হালাল ও হারামের স্পষ্ট সীমা মানা জরুরি।","সন্দেহজনক বিষয় থেকে দূরে থাকলে দ্বীন ও মর্যাদা রক্ষা হয়।","হারামের কাছাকাছি ঘোরাফেরা করা ঝুঁকিপূর্ণ।","অন্তর ভালো থাকলে আচরণও ভালো হওয়ার পথ তৈরি হয়।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"593","book_id":"8","slug":"riyadus-salihin","label":"রিয়াদুস সালেহীন"}]}</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="n"/>
     </row>
     <row r="112" ht="46" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
@@ -3129,19 +3053,15 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জমি দখল হারাম ও কিয়ামতের দায়","description":"$book_name$ $hadith_number$ - $chapter_name$. অন্যায়ভাবে সামান্য জমি দখলও কিয়ামতে কঠিন দায়ের কারণ হবে; তাই জমি ও হকের ব্যাপারে সতর্ক থাকার শিক্ষা।"},"heading":{"title":"জমি দখল হারাম: অন্যের হক নিলে কিয়ামতে দায় আছে","description":"এই হাদিসের মূল শিক্ষা হলো, অন্যের জমি দখল করা শুধু সামাজিক অন্যায় নয়, আখিরাতের বড় দায়ও। এখানে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, কেউ অন্যায়ভাবে কারো এক বিগত জমি দখল করলে তাকে কিয়ামতের দিন সেই জমির কারণে কঠিন অবস্থার মুখোমুখি হতে হবে। তাই জমি দখল হারাম—এই বিষয়টি খুব পরিষ্কারভাবে বোঝা যায়। অনেক সময় মানুষ জমির সীমানা, দলিল, উত্তরাধিকার বা ক্ষমতার জোরে সামান্য অংশকে ছোট ব্যাপার মনে করে। কিন্তু হাদিসটি শেখায়, অন্যের হক সামান্য হলেও তা হালকা নয়। মুসলিমের জন্য জরুরি হলো জমি, সম্পদ ও অধিকার নিয়ে ইনসাফ করা এবং কাউকে যুলুম না করা।"},"teachings":["অন্যের জমির সামান্য অংশও অন্যায়ভাবে নেওয়া বড় দায়ের কারণ।","জমি ও সম্পদের ব্যাপারে যুলুম থেকে বেঁচে থাকা জরুরি।","মানুষের হক নষ্ট করলে কিয়ামতের দিন জবাবদিহি করতে হবে।","সীমানা, দলিল ও মালিকানার বিষয়ে সততা রাখা ঈমানি আচরণের অংশ।"],"related_hadiths":[{"id":"2453","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4028","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
-        </is>
-      </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[2]: unknown book label "ঊপদেশ ১৯ (প্রাসঙ্গিক বর্ণনা)"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম রিজিক দোয়ার পথে বাধা","description":"$book_name$ $hadith_number$ - $chapter_name$. সফরে ক্লান্ত অবস্থায় দোয়া করলেও খাদ্য, পানীয়, পোশাক ও জীবিকা হারাম হলে দোয়া কবুলের প্রশ্ন ওঠে।"},"heading":{"title":"হারাম রিজিক দোয়ার পথে বাধা: হালাল জীবিকা কেন দরকার","description":"এই হাদিসে দোয়ার একটি গুরুত্বপূর্ণ দিক তুলে ধরা হয়েছে। একজন মানুষ দূর-দূরান্তে সফর করছে, চুল এলোমেলো, শরীরে ধুলা-বালি, দুই হাত আসমানের দিকে তুলে কাতরভাবে বলছে, হে প্রভু! হে প্রভু! বাহ্যিকভাবে এটি দোয়ার বিনয়ী অবস্থা। কিন্তু হাদিসে বলা হলো, তার খাদ্য হারাম, পানীয় হারাম, পোশাক হারাম এবং জীবিকা হারাম; তাহলে তার দোয়া কীভাবে কবুল হবে? তাই হারাম রিজিক দোয়ার পথে বড় বাধা হতে পারে। এই শিক্ষা আমাদের দৈনন্দিন জীবনে খুব দরকার। আমরা শুধু দোয়া বাড়াব না, বরং খাবার, পোশাক ও আয়ের উৎসও পবিত্র রাখার চেষ্টা করব। হালাল জীবিকা ইবাদতের সৌন্দর্য বাড়ায়।"},"teachings":["দোয়ার সঙ্গে হালাল জীবিকার সম্পর্ক আছে।","বাহ্যিক বিনয় থাকলেও হারাম রিজিক বড় বাধা হতে পারে।","খাদ্য, পানীয়, পোশাক ও আয়—সব ক্ষেত্রেই সতর্কতা দরকার।","আল্লাহ পবিত্র, তাই পবিত্র উপায় পছন্দনীয়।"],"related_hadiths":[{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1205","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="n"/>
     </row>
     <row r="113" ht="46" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
@@ -3156,19 +3076,15 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | পবিত্র অন্তর ও সত্যভাষীর মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. উত্তম মানুষের পরিচয় হলো সত্য কথা বলা ও অন্তরকে পাপ, যুলুম, খিয়ানত ও হিংসা থেকে পরিষ্কার রাখা।"},"heading":{"title":"পবিত্র অন্তর ও সত্যভাষী: উত্তম মানুষের সহজ পরিচয়","description":"এই হাদিসে মানুষের উত্তম হওয়ার একটি সহজ কিন্তু গভীর মানদণ্ড বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে জিজ্ঞেস করা হলে তিনি বলেন, নিষ্কলুষ অন্তঃকরণ ও সত্যভাষী মানুষ উত্তম। এখানে পবিত্র অন্তর বলতে শুধু নরম মন বোঝানো হয়নি। হাদিসের ভাষায় এমন অন্তর, যেখানে পাপ নেই, যুলুম নেই, খিয়ানত নেই এবং হিংসা-বিদ্বেষ নেই। তাই পবিত্র অন্তর হাদিস আমাদের নিজের ভেতর দেখার শিক্ষা দেয়। আমরা মুখে সত্য বলি কি না, মানুষের প্রতি হিংসা রাখি কি না, কারো হক নষ্ট করি কি না—এসব বিষয় নিজের জীবনেই যাচাই করতে হবে। সত্যভাষী হওয়া এবং অন্তর পরিষ্কার রাখা একসঙ্গে চলা উচিত।"},"teachings":["উত্তম মানুষের বড় গুণ হলো সত্য কথা বলা।","অন্তরকে পাপ, যুলুম ও খিয়ানত থেকে পরিষ্কার রাখা দরকার।","হিংসা-বিদ্বেষ থেকে মুক্ত থাকা পবিত্র অন্তরের লক্ষণ।","বাহ্যিক ভালো আচরণের সঙ্গে ভেতরের সততাও জরুরি।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"593","book_id":"8","slug":"riyadus-salihin","label":"রিয়াদুস সালেহীন"}]}</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ ১৮৮ (প্রাসঙ্গিক বর্ণনা)"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল-হারাম আয়ের যুগসতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. এমন যুগ আসবে যখন মানুষ সম্পদ কীভাবে পেল তা দেখবে না; মুসলিমের জন্য হালাল উৎস যাচাই অপরিহার্য।"},"heading":{"title":"হালাল-হারাম আয়ের সতর্কতা: সম্পদ পেলেই যথেষ্ট নয়","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) এমন এক সময়ের কথা বলেছেন, যখন মানুষ পরোয়া করবে না—সে কী উপায়ে মাল পেল, হারাম পথে নাকি হালাল পথে। এর মানে হলো, আয়ের পরিমাণকে মানুষ অনেক সময় আয়ের বৈধতার চেয়ে বড় করে দেখে। কিন্তু মুমিনের জন্য শুধু সম্পদ পাওয়া লক্ষ্য নয়। হালাল হারাম আয় যাচাই করা ঈমানি দায়িত্বের অংশ। ব্যবসায় প্রতারণা, অন্যের হক, অবৈধ চুক্তি, সন্দেহজনক লেনদেন—এসব বিষয় থেকে সতর্ক থাকা দরকার। হাদিসটি আমাদের সমাজের চাপের মাঝেও আল্লাহর ভয় ধরে রাখতে শেখায়। টাকা আসছে কি না—এ প্রশ্নের সঙ্গে আরেকটি প্রশ্ন দরকার: এই টাকা হালালভাবে আসছে কি না?"},"teachings":["সম্পদ পাওয়ার উপায় বৈধ কি না তা যাচাই করতে হবে।","সময়ের খারাপ প্রবণতার সঙ্গে ভেসে যাওয়া উচিত নয়।","হালাল আয় মুমিনের নৈতিক পরিচয়ের অংশ।","হারাম আয়ের ব্যাপারে উদাসীনতা বড় ক্ষতির কারণ হতে পারে।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1205","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="n"/>
     </row>
     <row r="114" ht="46" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
@@ -3183,12 +3099,12 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিশুদের প্রতি স্নেহ-মমতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুদের চুম্বন ও আদর নিয়ে এই হাদিস দেখায়, অন্তরে স্নেহ-মমতা থাকা আল্লাহর বড় দান।"},"heading":{"title":"শিশুদের প্রতি স্নেহ-মমতা: আদর, দয়া ও কোমল হৃদয়ের হাদিস","description":"এই হাদিসের মূল বিষয় শিশুদের প্রতি স্নেহ-মমতা। এক বেদুঈন সাহাবীদের শিশুদের চুমু দিতে দেখে বলল, তারা শিশুদের চুম্বন করে না। তখন রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বললেন, আল্লাহ যদি তার অন্তর থেকে রহমত তুলে নেন, তবে তিনি তা বাধা দিতে পারবেন কি? এই কথায় বোঝা যায়, শিশুকে আদর করা দুর্বলতা নয়; বরং অন্তরের দয়া ও কোমলতার লক্ষণ। শিশুদের প্রতি স্নেহ, চুম্বন ও ভালোবাসা দেখানো ইসলামী আদবের সঙ্গে মিলে যায়। প্রধান কীওয়ার্ড হলো শিশুদের প্রতি স্নেহ-মমতা, আর সম্পর্কিত কীওয়ার্ড হলো শিশুকে আদর করা, সন্তানকে চুমু দেওয়া, দয়ার হাদিস, কোমল হৃদয়। হাদিসটি আমাদের শেখায়, ঘরের ছোটদের সঙ্গে রুক্ষ আচরণ নয়, ভালোবাসা ও মমতা থাকা উচিত।"},"teachings":["শিশুকে আদর করা ও ভালোবাসা দেখানো সুন্দর আচরণ।","অন্তরে রহমত থাকা আল্লাহর দান—এটি হারিয়ে যাওয়া ভয়ংকর ক্ষতি।","শিশুদের সঙ্গে কঠোরতার বদলে কোমল আচরণ করা উচিত।"],"related_hadiths":[{"id":"5997","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6013","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6008","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক বিষয় ও অন্তরের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহজনক বিষয় ছাড়লে দ্বীন ও সম্মান নিরাপদ থাকে; অন্তর ভালো থাকলে জীবনও সঠিক পথে থাকে।"},"heading":{"title":"সন্দেহজনক বিষয় থেকে বাঁচুন: হালাল-হারামের নিরাপদ পথ","description":"এই হাদিসে হালাল, হারাম এবং সন্দেহজনক বিষয়ের সম্পর্ক পরিষ্কার করা হয়েছে। হালাল সুস্পষ্ট, হারামও সুস্পষ্ট। কিন্তু কিছু বিষয় আছে, যেগুলো সম্পর্কে অনেকেই সিদ্ধান্ত নিতে পারে না। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি সন্দেহের বস্তুকে পরিহার করে, তার দ্বীন ও সম্মান পরিষ্কার থাকে। আর যে সন্দেহজনক কাজে জড়ায়, সে হারামে পড়ে যেতে পারে। রাখালের উদাহরণটি খুব সহজ: নিষিদ্ধ এলাকার ধারে পশু চরালে ভেতরে ঢুকে পড়ার ভয় থাকে। তাই নিরাপদ পথ হলো হারামের কাছাকাছি না যাওয়া। হাদিসের শেষে অন্তরের গুরুত্ব এসেছে। অন্তর ভালো থাকলে জীবন ভালো দিকে যায়, আর অন্তর নষ্ট হলে কাজও নষ্ট হতে থাকে।"},"teachings":["সন্দেহজনক বিষয় এড়িয়ে চলা নিরাপদ পথ।","হারামের সীমানার কাছাকাছি গেলে পড়ে যাওয়ার ভয় থাকে।","দ্বীন ও সম্মান রক্ষায় সতর্কতা দরকার।","অন্তর ঠিক রাখা আচরণ ঠিক রাখার বড় মাধ্যম।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"593","book_id":"8","slug":"riyadus-salihin","label":"রিয়াদুস সালেহীন"}]}</t>
         </is>
       </c>
       <c r="E114" s="4" t="n"/>
@@ -3206,12 +3122,12 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দুই কন্যা লালন-পালনের ফজিলত","description":"$book_name$ $hadith_number$ - $chapter_name$. দুই কন্যাকে পূর্ণ বয়স্কা হওয়া পর্যন্ত লালন করলে কিয়ামতে নবীর নৈকট্যের আশা জাগে।"},"heading":{"title":"দুই কন্যার লালন-পালন: নবীর নৈকট্য লাভের আশাব্যঞ্জক হাদিস","description":"এই হাদিসের মূল বিষয় দুই কন্যার লালন-পালন। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যে ব্যক্তি দুই কন্যাকে পূর্ণ বয়স্কা হওয়া পর্যন্ত লালন-পালন করবে, কিয়ামতের দিন সে তাঁর সঙ্গে এভাবে আসবে। এরপর তিনি নিজের আঙ্গুল একত্র করে দেখিয়েছেন। হাদিসটি কন্যা সন্তানের মর্যাদা ও তাদের দায়িত্বশীলভাবে বড় করার গুরুত্ব তুলে ধরে। এখানে প্রধান কীওয়ার্ড হলো দুই কন্যা লালন-পালনের হাদিস। সম্পর্কিত কীওয়ার্ড: কন্যা সন্তানের ফজিলত, মেয়েদের লালন-পালন, কন্যার মর্যাদা, ইসলামে সন্তান প্রতিপালন। হাদিসের শিক্ষা হলো, কন্যাদের যত্ন, নিরাপত্তা, খাবার, শিক্ষা ও বড় হওয়া পর্যন্ত অভিভাবকত্ব একটি মূল্যবান দায়িত্ব। তবে ব্যাখ্যায় আমরা শুধু হাদিসে থাকা কথাটুকুই ধরে বলি—এই কাজ কিয়ামতের দিনে রাসূলের নৈকট্যের কারণ হতে পারে।"},"teachings":["দুই কন্যাকে বড় হওয়া পর্যন্ত দায়িত্ব নিয়ে লালন-পালন করা প্রশংসনীয়।","কন্যা সন্তানকে অবহেলা নয়, যত্ন ও ভালো আচরণ দেওয়া দরকার।","কন্যাদের দায়িত্ব পালন কিয়ামতের দিনে নবীর নৈকট্যের কারণ হতে পারে।"],"related_hadiths":[{"id":"5995","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5304","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6005","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘৃণিত উপার্জন থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. কুকুর বিক্রয়, ব্যভিচারের বিনিময় ও সিঙ্গা লাগানোর মূল্যকে ঘৃণিত বলা হয়েছে; উপার্জনে সতর্কতা দরকার।"},"heading":{"title":"ঘৃণিত উপার্জন: কুকুর বিক্রয় ও অনৈতিক আয়ের সতর্কতা","description":"এই হাদিসে কয়েক ধরনের উপার্জনকে ঘৃণিত বলা হয়েছে। কুকুর বিক্রয়ের মূল্য, ব্যভিচারের বিনিময় এবং সিঙ্গা লাগানোর মূল্য—এই তিনটি বিষয় হাদিসে এসেছে। এখানে মূল শিক্ষা হলো, উপার্জনের সব পথ সমান নয়। টাকা পাওয়া গেলেই তা ভালো উপার্জন হয়ে যায় না। ঘৃণিত উপার্জন হাদিস আমাদের আয়ের উৎস নিয়ে সতর্ক করে। বিশেষ করে ব্যভিচারের বিনিময়ের মতো অনৈতিক আয়ের কথা স্পষ্টভাবে এসেছে। কুকুর বিক্রয়ের মূল্য ও সিঙ্গা লাগানোর মূল্য সম্পর্কেও হাদিসে সতর্ক ভাষা ব্যবহৃত হয়েছে। তাই মুসলিমের জন্য উপার্জনের ক্ষেত্রে শুধু লাভ নয়, শরিয়তের দৃষ্টিতে তা পরিষ্কার কি না—এটাও দেখা দরকার।"},"teachings":["সব ধরনের আয় গ্রহণযোগ্য নয়।","অনৈতিক কাজের বিনিময় ঘৃণিত উপার্জনের মধ্যে পড়ে।","উপার্জনের উৎস নিয়ে সতর্ক থাকা দরকার।","লাভের আগে হালাল-হারাম বিচার করা জরুরি।"],"related_hadiths":[{"id":"2237","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2282","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5962","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E115" s="4" t="n"/>
@@ -3229,12 +3145,12 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিধবা ও মিসকীনকে সাহায্য","description":"$book_name$ $hadith_number$ - $chapter_name$. বিধবা ও মিসকীনের সহযোগিতা বড় নেকির কাজ; হাদিসে এর মর্যাদা জিহাদ, কিয়াম ও সিয়ামের সঙ্গে তুলনা করা হয়েছে।"},"heading":{"title":"বিধবা ও মিসকীনকে সাহায্য: অসহায়ের পাশে দাঁড়ানোর বড় ফজিলত","description":"এই হাদিসের মূল বিষয় বিধবা ও মিসকীনকে সাহায্য করা। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, বিধবা ও মিসকীনের সহযোগী আল্লাহর পথে জিহাদকারীর ন্যায়, এমন তাহাজ্জুদগুজার ব্যক্তির ন্যায় যে অলস হয় না, এবং এমন সিয়াম পালনকারীর ন্যায় যে ইফতার করে না। এই বর্ণনা অসহায় মানুষের পাশে দাঁড়ানোর মর্যাদা বুঝিয়ে দেয়। এখানে প্রধান কীওয়ার্ড হলো বিধবা ও মিসকীনকে সাহায্য। সম্পর্কিত কীওয়ার্ড: অসহায়কে সাহায্য, দান-সদকা, বিধবার ভরণ-পোষণ, মিসকীনের হক, মানবসেবা হাদিস। হাদিসের আলোকে বোঝা যায়, সামাজিক দায়িত্ব শুধু কথায় নয়; বাস্তবে সাহায্য, খোঁজখবর ও ভরণ-পোষণের চেষ্টায় প্রকাশ পায়। তবে সাহায্য যেন সম্মান রেখে করা হয়, কারণ হাদিসটি সহযোগিতার মর্যাদা বলেছে, কাউকে ছোট করার অনুমতি দেয়নি।"},"teachings":["বিধবা ও মিসকীনের সহযোগিতা অত্যন্ত মর্যাদাপূর্ণ কাজ।","অসহায় মানুষের পাশে দাঁড়ানো ইবাদতের মতো বড় নেকির কারণ হতে পারে।","সহযোগিতা করতে গিয়ে মানুষের সম্মান রক্ষা করা জরুরি।"],"related_hadiths":[{"id":"6005","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6011","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নিষিদ্ধ আয়ের তিনটি পথ","description":"$book_name$ $hadith_number$ - $chapter_name$. কুকুরের মূল্য, যিনাকারীনীর উপার্জন ও গণকের উপার্জন খেতে নিষেধ করা হয়েছে; রিজিকে পবিত্রতা জরুরি।"},"heading":{"title":"নিষিদ্ধ আয় থেকে বাঁচুন: কুকুরের মূল্য, যিনা ও গণকের উপার্জন","description":"এই হাদিসে তিনটি উপার্জন খেতে নিষেধ করা হয়েছে: কুকুরের মূল্য, যিনাকারীনীর উপার্জন এবং গণকের উপার্জন। হাদিসটি খুব পরিষ্কারভাবে শেখায়, আয়ের উৎস ভালো না হলে সেই আয় গ্রহণ করা উচিত নয়। নিষিদ্ধ আয় শুধু ব্যক্তির পকেটে আসে না; তা খাবার, পরিবার ও জীবনের ওপরও প্রভাব ফেলে। বিশেষ করে যিনা-ভিত্তিক উপার্জন ও গণকের উপার্জন মানুষের নৈতিকতা ও বিশ্বাসের সঙ্গে জড়িত। কুকুরের মূল্য সম্পর্কেও স্পষ্ট নিষেধ এসেছে। তাই মুসলিমের জন্য উপার্জনের ক্ষেত্রে সতর্ক থাকা জরুরি। কোন কাজ থেকে আয় হচ্ছে, তা আল্লাহর নাফরমানির সঙ্গে যুক্ত কি না—এই প্রশ্ন নিজের কাছে রাখা দরকার।"},"teachings":["কুকুরের মূল্য খেতে নিষেধ করা হয়েছে।","যিনাকারীনীর উপার্জন গ্রহণযোগ্য নয়।","গণকের উপার্জন থেকে বাঁচতে বলা হয়েছে।","রিজিক পবিত্র রাখতে আয়ের উৎস যাচাই করা দরকার।"],"related_hadiths":[{"id":"5962","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5761","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E116" s="4" t="n"/>
@@ -3252,12 +3168,12 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইয়াতীম পালনকারীর মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইয়াতীম পালনকারীর জান্নাতে নবীর নৈকট্যের কথা এসেছে; এটি অসহায় শিশুর যত্নের বড় শিক্ষা।"},"heading":{"title":"ইয়াতীম পালনকারীর মর্যাদা: জান্নাতে নবীর নৈকট্যের হাদিস","description":"এই হাদিসের মূল বিষয় ইয়াতীম পালন। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তিনি ও ইয়াতীম পালনকারী জান্নাতে এভাবে থাকবেন। তারপর তিনি তর্জনী ও মধ্যমা আঙ্গুলের মাঝে সামান্য ফাঁক রেখে ইশারা করেছেন। হাদিসটি ইয়াতীম শিশুর প্রতি দায়িত্ব, দয়া ও যত্নের বড় মর্যাদা বুঝায়। এখানে প্রধান কীওয়ার্ড হলো ইয়াতীম পালনকারীর মর্যাদা। সম্পর্কিত কীওয়ার্ড: ইয়াতীমের হক, এতিমের যত্ন, ইয়াতীমকে সাহায্য, জান্নাতে নবীর সান্নিধ্য, অসহায় শিশুর লালন-পালন। হাদিসটি আমাদের মনে করায়, যে শিশুর সহায় দরকার, তাকে আশ্রয় ও যত্ন দেওয়া শুধু সামাজিক কাজ নয়; এটি বড় নেকির দরজা। তবে ইয়াতীমের সম্পদ বা অধিকার নিয়ে অতিরিক্ত আলোচনা এই হাদিসে নেই, তাই এখানে মূল শিক্ষা শুধু পালন ও যত্নের মর্যাদায় সীমিত রাখা হয়েছে।"},"teachings":["ইয়াতীম শিশুর দায়িত্ব নেওয়া জান্নাতে নবীর নৈকট্যের কারণ হতে পারে।","অসহায় শিশুর প্রতি দয়া, যত্ন ও নিরাপত্তা দেওয়া গুরুত্বপূর্ণ।","ইয়াতীম পালন শুধু দান নয়; এটি দীর্ঘমেয়াদি দায়িত্ব ও মমতার কাজ।"],"related_hadiths":[{"id":"6006","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6008","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আব্দুল ক্বায়েস প্রতিনিধিদলের ঈমান শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আব্দুল ক্বায়েস প্রতিনিধিদলকে ঈমান, সালাত, যাকাত, রমযানের সিয়াম ও খুমুসের শিক্ষা দেওয়া হয়।"},"heading":{"title":"আব্দুল ক্বায়েস প্রতিনিধিদল ও ঈমানের মূল আমল","description":"এই হাদিসে আব্দুল ক্বায়েস গোত্রের প্রতিনিধিদলের ঘটনা এসেছে। তারা রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কাছে এসে এমন পরিষ্কার নির্দেশ চাইলো, যা তারা নিজেদের লোকদের জানাতে পারে এবং যার মাধ্যমে জান্নাতে প্রবেশের আশা রাখতে পারে। নবীজি তাদেরকে চারটি বিষয়ে নির্দেশ দেন: এক আল্লাহর উপর ঈমান, সালাত কায়েম, যাকাত আদায়, রমযানের সিয়াম এবং গানীমতের এক পঞ্চমাংশ জমা দেওয়া। তিনি কিছু পাত্র থেকেও নিষেধ করেন, যেগুলো শরাব তৈরির সঙ্গে যুক্ত ছিল। এই হাদিসে ঈমানের মূল আমল, শিক্ষা গ্রহণ ও অন্যদের কাছে দ্বীনের কথা পৌঁছে দেওয়ার গুরুত্ব আছে। সাহাবীরা শুধু শুনতে আসেননি; তারা আমল করতে ও অন্যদের জানাতে চেয়েছেন।"},"teachings":["দ্বীনের পরিষ্কার শিক্ষা জানা ও মানা দরকার।","ঈমানের সঙ্গে সালাত, যাকাত ও রমযানের সিয়াম জড়িত।","যা শেখা হয়, তা নিজের লোকদের জানানো ভালো কাজ।","নিষিদ্ধ জিনিসের উপায় থেকেও সতর্ক থাকতে হয়।"],"related_hadiths":[{"id":"53","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"17","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"17","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E117" s="4" t="n"/>
@@ -3275,19 +3191,15 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত, সত্যবাদিতা ও ভালো চরিত্র","description":"$book_name$ $hadith_number$ - $chapter_name$. আমানত রক্ষা, সত্য কথা, ভালো চরিত্র ও খাদ্যে সতর্কতা—এই চার গুণ মানুষের জীবনকে সঠিক পথে রাখে।"},"heading":{"title":"আমানত রক্ষা ও সত্য কথা: জীবনের চারটি মূল্যবান গুণ","description":"এই হাদিসে চারটি গুণের কথা এসেছে, যা একজন মুমিনের জীবনকে সুন্দর করে। আমানত রক্ষা করা, সত্য কথা বলা, উত্তম চরিত্র রাখা এবং খানা-পিনাতে সতর্ক থাকা—এসব বিষয় শুধু ইবাদতের বাইরে আলাদা কিছু নয়; বরং দৈনন্দিন জীবনের বড় পরীক্ষা। আমানত রক্ষা মানে কারো দেওয়া দায়িত্ব, সম্পদ বা বিশ্বাস নষ্ট না করা। সত্য কথা বলা মানে সুবিধা-অসুবিধা দেখে কথা বদলে না ফেলা। উত্তম চরিত্র মানে মানুষের সঙ্গে সুন্দর আচরণ করা। আর খানা-পিনাতে সতর্কতা মানে খাবার ও উপার্জনের উৎস নিয়ে সাবধান থাকা। হাদিসটি দুনিয়ার ক্ষতি নিয়ে হতাশ না হয়ে চরিত্র ও সততার দিকে মন দিতে শেখায়।"},"teachings":["আমানত রক্ষা করা মুমিনের গুরুত্বপূর্ণ গুণ।","সত্য কথা বলা চরিত্রের ভিত্তি মজবুত করে।","খানা-পিনার বিষয়ে সতর্কতা জীবনকে হালাল পথে রাখে।","ভালো চরিত্র মানুষের সঙ্গে আচরণে প্রকাশ পায়।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[0]: unknown book label "ঊপদেশ ১৮৮ (প্রাসঙ্গিক বর্ণনা)"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম উপার্জন ও অভিশপ্ত কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. রক্ত, কুকুর ও ব্যভিচারের আয় নিষিদ্ধ; সুদ, উল্কি ও ছবি অঙ্কনের ব্যাপারেও কঠিন সতর্কতা এসেছে।"},"heading":{"title":"হারাম উপার্জন ও নিষিদ্ধ কাজ: রক্ত, সুদ, উল্কি ও ছবি নিয়ে সতর্কতা","description":"এই হাদিসে কয়েকটি বিষয় একসঙ্গে এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) রক্ত বিক্রয়ের মূল্য, কুকুর বিক্রয়ের মূল্য এবং ব্যভিচারের বিনিময় থেকে নিষেধ করেছেন। এরপর সুদ গ্রহীতা ও সুদদাতার প্রতি লা’নতের কথা এসেছে। আরও বলা হয়েছে, যে উল্কি করে এবং যে উল্কি করায়, তাদের ওপরও লা’নত করা হয়েছে। ছবি অঙ্কনকারীর প্রতিও লা’নতের কথা এসেছে। তাই হারাম উপার্জন হাদিস আমাদের আয়ের উৎস এবং কিছু কাজের ব্যাপারে গভীর সতর্ক করে। এখানে অযথা বাড়তি ব্যাখ্যা না করে মূল বার্তাই স্পষ্ট: মুসলিমকে এমন আয় ও কাজ থেকে দূরে থাকতে হবে, যেগুলোর ব্যাপারে নবী (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কঠিন নিষেধ দিয়েছেন।"},"teachings":["রক্ত, কুকুর ও ব্যভিচারের বিনিময় থেকে নিষেধ করা হয়েছে।","সুদ গ্রহণ ও সুদ দেওয়া—দুটির ব্যাপারেই কঠিন সতর্কতা এসেছে।","উল্কি করা ও করানো থেকে বাঁচতে বলা হয়েছে।","নিষিদ্ধ আয়ের সঙ্গে নিষিদ্ধ কাজ থেকেও দূরে থাকা দরকার।"],"related_hadiths":[{"id":"2237","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2282","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="n"/>
     </row>
     <row r="119" ht="46" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
@@ -3302,12 +3214,12 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুমিন মুমিনের সহায়ক","description":"$book_name$ $hadith_number$ - $chapter_name$. মুমিনকে গৃহের মতো বলা হয়েছে, যার এক অংশ অন্য অংশকে মজবুত রাখে—এটি সহযোগিতার শিক্ষা দেয়।"},"heading":{"title":"মুমিন মুমিনের সহায়ক: একে অন্যকে শক্ত রাখার হাদিস","description":"এই হাদিসের মূল বিষয় মুমিন মুমিনের সহায়ক। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, একজন মুমিন অপর মুমিনের জন্য গৃহের মতো, যার এক অংশ অন্য অংশকে দৃঢ় রাখে। এরপর তিনি দুই হাতের আঙ্গুল একটির মধ্যে আরেকটি প্রবেশ করিয়ে দেখিয়েছেন। এই দৃশ্যমান ইশারা সহযোগিতার অর্থ সহজ করে দেয়। একজন মুসলিম একা সব দায়িত্ব সামলাতে পারে না; অন্য ভাইয়ের সহায়তা, সাহস ও পাশে থাকা দরকার হতে পারে। প্রধান কীওয়ার্ড হলো মুমিন মুমিনের সহায়ক, আর সম্পর্কিত কীওয়ার্ড: মুসলিম ভ্রাতৃত্ব, সহযোগিতার হাদিস, একে অন্যকে সাহায্য, মুমিনের সম্পর্ক। হাদিসটি দলাদলি নয়, বরং ভালো কাজে একে অন্যকে শক্ত করার শিক্ষা দেয়। এখানে নির্দিষ্ট কোনো রাজনৈতিক বা সামাজিক দাবি করা হয়নি; শুধু হাদিসের সরাসরি সহযোগিতার বার্তা তুলে ধরা হয়েছে।"},"teachings":["মুমিনদের একে অন্যের সহায়ক হওয়া উচিত।","ভালো কাজে সহযোগিতা মুসলিম সমাজকে শক্ত রাখে।","সম্পর্ক শুধু কথায় নয়; প্রয়োজনের সময় পাশে দাঁড়ালে তা সত্য হয়।"],"related_hadiths":[{"id":"6011","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2443","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম উপার্জনের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম মালে গড়া দেহের ভয়াবহ পরিণতি জানুন এবং হালাল রুজির পথে চলার শিক্ষা নিন।"},"heading":{"title":"হালাল রুজি ও হারাম উপার্জন: মুমিনের জীবনে সতর্কতার শিক্ষা","description":"এই হাদিসে হারাম উপার্জন সম্পর্কে খুব স্পষ্ট সতর্কতা এসেছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে দেহের গোশত হারাম মালে গঠিত, তা জান্নাতে প্রবেশ করতে পারবে না। কথাটি আমাদের খাবার, আয়, ব্যবসা ও লেনদেন নিয়ে ভাবতে শেখায়। শুধু টাকা হাতে এলেই তা ভালো হয়ে যায় না; টাকা কোথা থেকে এল, সেটাও বড় বিষয়। হালাল রুজি মুমিনের জীবনকে নিরাপদ পথে রাখে। আর হারাম মাল শরীরকে পুষ্ট করলেও তা আখিরাতের জন্য ভয়ংকর ক্ষতির কারণ হতে পারে। তাই এই হাদিসের মূল শিক্ষা হলো, আয়-রোজগারে সাবধান থাকা, সন্দেহজনক পথ এড়িয়ে চলা এবং নিজের পরিবারকে হালাল খাবার খাওয়ানোর চেষ্টা করা।"},"teachings":["হারাম উপার্জনে গড়া দেহের জন্য হাদিসে কঠিন সতর্কতা এসেছে।","খাবার ও আয় হালাল কি না, তা মুমিনের জন্য গুরুত্বপূর্ণ বিষয়।","পরিবারকে হালাল রুজি খাওয়ানো ঈমানি দায়িত্বের অংশ।","মাল বেশি হওয়া নয়, মাল হালাল হওয়াই আসল নিরাপত্তার পথ।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1599","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2760","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E119" s="4" t="n"/>
@@ -3325,12 +3237,12 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অভাবীর জন্য সুপারিশ","description":"$book_name$ $hadith_number$ - $chapter_name$. অভাবী বা প্রয়োজনমন্দের জন্য সুপারিশ করলে নেকি হতে পারে; চূড়ান্ত ফায়সালা আল্লাহর ইচ্ছায় হয়।"},"heading":{"title":"অভাবীর জন্য সুপারিশ: সাহায্যের দরজা খুলে দেওয়ার হাদিস","description":"এই হাদিসের মূল বিষয় অভাবীর জন্য সুপারিশ। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম-এর কাছে কোনো ভিক্ষুক বা প্রয়োজনমন্দ এলে তিনি সাহাবীদের বলতেন, তোমরা সুপারিশ কর, এতে তোমাদের নেকি দেওয়া হবে। আর আল্লাহ তাঁর রাসূলের মুখ দিয়ে যে ফয়সালা চান তা জারি করবেন। হাদিসটি দেখায়, সরাসরি সাহায্য করতে না পারলেও ভালো সুপারিশ, পরিচয় করিয়ে দেওয়া বা প্রয়োজনের কথা পৌঁছে দেওয়া নেকির কাজ হতে পারে। প্রধান কীওয়ার্ড হলো অভাবীর জন্য সুপারিশ। সম্পর্কিত কীওয়ার্ড: দরিদ্রকে সাহায্য, নেক সুপারিশ, প্রয়োজনমন্দের সহায়তা, ইসলামে সুপারিশ। হাদিসে একই সঙ্গে ভারসাম্যও আছে—সুপারিশ করা মানুষের কাজ, কিন্তু ফল আল্লাহর ইচ্ছা অনুযায়ী হয়। তাই সাহায্যের চেষ্টা করতে হবে, তবে ফল নিয়ে অহংকার বা চাপ সৃষ্টি করা ঠিক নয়।"},"teachings":["অভাবী মানুষের প্রয়োজনে ভালো সুপারিশ করা নেকির কারণ হতে পারে।","সরাসরি দিতে না পারলেও সাহায্যের দরজা খুলে দেওয়া যায়।","মানুষ চেষ্টা করবে, আর চূড়ান্ত ফল আল্লাহর ইচ্ছার উপর ছেড়ে দেবে।"],"related_hadiths":[{"id":"6006","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6005","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6019","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক কাজ ছেড়ে নিশ্চিত পথে চলা","description":"$book_name$ $hadith_number$ - $chapter_name$. মনে খটকা লাগা কাজ ছেড়ে পরিষ্কার ও শান্তির পথে চলার সুন্দর নববী শিক্ষা জানুন।"},"heading":{"title":"সন্দেহজনক কাজ থেকে বাঁচার হাদিস: সত্যে শান্তি, মিথ্যায় খটকা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম একটি সহজ কিন্তু গভীর নিয়ম শিখিয়েছেন। যে কাজে মনে খটকা লাগে, সে কাজ ছেড়ে এমন কাজ বেছে নিতে বলা হয়েছে যাতে খটকা নেই। মানুষের অন্তর অনেক সময় ভুল ও ঠিকের মাঝে অস্বস্তি টের পায়। হাদিসটি বলে, সত্য ও শুদ্ধ জিনিস সাধারণত অন্তরে প্রশান্তি আনে, আর মিথ্যা ও অশুদ্ধ জিনিস দ্বিধা তৈরি করে। তাই সন্দেহজনক কাজ এড়িয়ে চলা শুধু ইবাদতের বিষয় নয়; এটি চরিত্র, কথা, ব্যবসা ও সম্পর্কের ক্ষেত্রেও দরকারি। এই শিক্ষা মানুষকে নিরাপদ, পরিষ্কার এবং সৎ পথে চলতে সাহায্য করে।"},"teachings":["যে কাজে মনে খটকা লাগে, তা ছেড়ে দেওয়া ভালো।","সত্য অন্তরে প্রশান্তি আনে, মিথ্যা দ্বিধা সৃষ্টি করে।","সন্দেহজনক কাজ থেকে দূরে থাকা দ্বীন রক্ষার পথ।","কথা ও কাজে পরিষ্কার অবস্থান নেওয়া মুমিনের গুণ।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1599","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2553","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E120" s="4" t="n"/>
@@ -3348,15 +3260,19 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যালিম ও মাযলুমকে সাহায্য","description":"$book_name$ $hadith_number$ - $chapter_name$. অত্যাচারিতকে সাহায্য করা যেমন জরুরি, তেমনি অত্যাচারীকে যুলুম থেকে থামানোও তার প্রতি সাহায্য।"},"heading":{"title":"যালিম ও মাযলুমকে সাহায্য: যুলুম থামানোই প্রকৃত সহায়তা","description":"এই হাদিসের মূল বিষয় যুলুম থেকে বিরত রাখা। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তোমার ভাইকে সাহায্য কর, সে অত্যাচারী হোক বা অত্যাচারিত হোক। সাহাবী প্রশ্ন করলেন, অত্যাচারিতকে সাহায্য করা বোঝা যায়, কিন্তু অত্যাচারীকে কীভাবে সাহায্য করা হবে? তিনি বললেন, তাকে যুলুম করা থেকে বিরত রাখাই তার সাহায্য। এখানে প্রধান কীওয়ার্ড হলো যালিম ও মাযলুমকে সাহায্য। সম্পর্কিত কীওয়ার্ড: যুলুম থেকে বিরত রাখা, অত্যাচারিতের পাশে দাঁড়ানো, অন্যায় বন্ধ করা, মুসলিম ভাইকে সাহায্য। হাদিসটি খুব ভারসাম্যপূর্ণ শিক্ষা দেয়। নিজের লোক বলে অন্যায়ের পক্ষে দাঁড়ানো সাহায্য নয়। প্রকৃত সাহায্য হলো অন্যায়কারীকে থামানো এবং অত্যাচারিতকে রক্ষা করা। হাদিসের বাইরে কোনো শাস্তি বা আইনগত ধাপ এখানে যোগ করা হয়নি; শুধু নৈতিক দায়িত্বের কথা বলা হয়েছে।"},"teachings":["অত্যাচারিত মানুষের পাশে দাঁড়ানো জরুরি।","অত্যাচারীকে যুলুম থেকে থামানোও তার প্রতি সত্যিকারের সাহায্য।","নিজের ভাই হলেও অন্যায়ের পক্ষে দাঁড়ানো ঠিক নয়।"],"related_hadiths":[{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6011","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6013","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="n"/>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গায়িকা কেনাবেচা ও হারাম মূল্য","description":"$book_name$ $hadith_number$ - $chapter_name$. গায়িকা ক্রয়-বিক্রয়, গান শেখানো ও তার মূল্য সম্পর্কে হাদিসের সতর্ক বার্তা জানুন।"},"heading":{"title":"গায়িকা ক্রয়-বিক্রয় ও হারাম উপার্জন নিয়ে হাদিসের শিক্ষা","description":"এই হাদিসে গায়িকা ক্রয়-বিক্রয়, তাদের গান শেখানো এবং এ ধরনের কাজে পাওয়া মূল্য সম্পর্কে কঠোরভাবে নিষেধ এসেছে। হাদিসের ভাষায় তাদের মূল্য হারাম বলা হয়েছে। এখানে মূল শিক্ষা হলো, বিনোদনের নামে এমন কাজে জড়ানো থেকে বাঁচা যা মানুষকে আল্লাহর পথ থেকে দূরে নিতে পারে। অনুবাদে কুরআনের একটি আয়াতের কথাও এসেছে, যেখানে রং-তামাশার গাথা কেনার কথা বলা হয়েছে। তাই এই হাদিস শুধু গান-বাজনা নিয়ে নয়; বরং এমন আয়ের পথ নিয়েও সতর্ক করে, যা দ্বীন ও চরিত্রের ক্ষতি করতে পারে। একজন মুমিনের উচিত নিজের আয় ও বিনোদন—দুটো ক্ষেত্রেই আল্লাহভীতি রাখা।"},"teachings":["গায়িকা ক্রয়-বিক্রয় ও গান শেখানোর বিষয়ে হাদিসে নিষেধ এসেছে।","এ ধরনের কাজের মূল্যকে হাদিসে হারাম বলা হয়েছে।","বিনোদন যেন দ্বীন থেকে দূরে নেওয়ার কারণ না হয়।","আয়ের উৎস হালাল কি না, তা যাচাই করা জরুরি।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4020","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>related_hadiths[2]: unknown book label "ঊপদেশ ১০১ (প্রাসঙ্গিক বর্ণনা)"</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="46" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
@@ -3371,12 +3287,12 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুসলিম ভাইয়ের হক ও সাহায্য","description":"$book_name$ $hadith_number$ - $chapter_name$. মুসলিম ভাইয়ের উপর যুলুম না করা, প্রয়োজন পূরণ, কষ্ট দূর করা ও দোষ ঢাকার শিক্ষা একসাথে এসেছে।"},"heading":{"title":"মুসলিম ভাইয়ের হক: সাহায্য, কষ্ট দূর করা ও দোষ ঢাকার শিক্ষা","description":"এই হাদিসের মূল বিষয় মুসলিম ভাইয়ের হক। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, এক মুসলমান অপর মুসলমানের ভাই। সে তার উপর যুলুম করবে না এবং তাকে ধ্বংসের দিকে ঠেলে দেবে না। যে তার মুসলিম ভাইয়ের প্রয়োজনে সাহায্য করবে, আল্লাহ তার প্রয়োজনের সাহায্য করবেন। যে মুসলমানের দুঃখ-কষ্ট দূর করবে, আল্লাহ কিয়ামতের দিনের বিপদ থেকে তাকে মুক্তির কারণ দেবেন। আর যে মুসলমানের দোষ ঢেকে রাখবে, আল্লাহ তার দোষ ঢেকে রাখবেন। প্রধান কীওয়ার্ড হলো মুসলিম ভাইয়ের হক। সম্পর্কিত কীওয়ার্ড: মুসলিমকে সাহায্য, কষ্ট দূর করার হাদিস, দোষ ঢেকে রাখা, মুসলিম ভ্রাতৃত্ব, যুলুম না করা। হাদিসটি সম্পর্ককে বাস্তব কাজে নামিয়ে আনে—অন্যায় না করা, অসহায় না ফেলে রাখা, প্রয়োজনে পাশে থাকা এবং অকারণে দোষ ছড়িয়ে না দেওয়া।"},"teachings":["মুসলিম ভাইয়ের উপর যুলুম করা যাবে না এবং তাকে বিপদে ফেলে রাখা ঠিক নয়।","ভাইয়ের প্রয়োজন পূরণে সাহায্য করা আল্লাহর সাহায্য লাভের কারণ হতে পারে।","মুসলমানের দুঃখ-কষ্ট দূর করা ও দোষ ঢেকে রাখা বড় নেকির কাজ।"],"related_hadiths":[{"id":"2443","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1432","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6013","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম খাদ্য থেকে আবু বকরের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহজনক ও হারাম উৎসের খাদ্য থেকে বাঁচতে আবু বকর রাঃ-এর সতর্কতার ঘটনা জানুন।"},"heading":{"title":"হারাম খাদ্য এড়ানোর বাস্তব শিক্ষা: আবু বকর রাঃ-এর ঘটনা","description":"এই বর্ণনায় আবু বকর ছিদ্দীক রাদিয়াল্লাহু আনহুর অত্যন্ত সতর্ক মনোভাব দেখা যায়। তাঁর গোলাম যে খাবার এনেছিল, তিনি প্রথমে তা থেকে কিছু খেয়েছিলেন। পরে যখন জানা গেল খাবারটি এমন আয়ের সাথে যুক্ত, যেখানে জাহেলী যুগের গণকী ও ধোঁকার কথা আছে, তখন তিনি মুখে হাত ঢুকিয়ে সব বের করে দিলেন। এই ঘটনা আমাদের শেখায়, হারাম খাদ্য বা সন্দেহজনক উৎসের খাবার নিয়ে সাহাবীগণ কতটা সাবধান ছিলেন। হালাল রুজি শুধু আয় করার বিষয় নয়; তা খাওয়া, গ্রহণ করা এবং পরিবারের জীবনে ঢোকানোর ক্ষেত্রেও সতর্কতা দরকার।"},"teachings":["খাবারের উৎস জানার বিষয়টি গুরুত্বের সাথে দেখা দরকার।","ধোঁকা ও গণকীর মাধ্যমে পাওয়া আয় থেকে বাঁচা উচিত।","ভুলে কিছু গ্রহণ করলে জানার পর তা থেকে সরে আসা ভালো।","আবু বকর রাঃ-এর ঘটনা হারাম খাদ্য এড়ানোর শক্ত শিক্ষা দেয়।"],"related_hadiths":[{"id":"2237","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1567","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2764","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E122" s="4" t="n"/>
@@ -3394,12 +3310,12 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গনীমতের মাল আত্মসাৎ থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. গনীমতের মাল সময়মতো জমা না দিয়ে পরে অজুহাত দেখানো গ্রহণযোগ্য নয়; আত্মসাৎ ছোট হলেও দায় থেকে যায়।"},"heading":{"title":"গনীমতের মাল আত্মসাৎ: অজুহাত নয়, সময়মতো আমানত জমা দিন","description":"এই হাদিসে গনীমতের মাল বণ্টনের নিয়ম ও আমানতদারির গুরুত্ব দেখা যায়। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) গনীমতের মাল এলে বেলাল (রাঃ)-কে ঘোষণা দিতে বলতেন। লোকেরা যার কাছে যা থাকত তা নিয়ে আসত। তারপর খুমুস বের করে বাকি মাল বণ্টন করা হতো। কিন্তু এক ব্যক্তি সব শেষ হওয়ার পর পশমের লাগাম নিয়ে এসে বলল, এটি গনীমতের মাল। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাকে জিজ্ঞেস করলেন, ঘোষণা শুনেও কেন আগে আনেনি। তার অজুহাত গ্রহণ করা হয়নি। হাদিসটি শেখায়, গনীমতের মাল আত্মসাৎ বা দেরিতে গোপন রাখা খুবই গুরুতর বিষয়। আমানত সময়মতো আদায় করা জরুরি।"},"teachings":["গনীমতের মাল ব্যক্তিগতভাবে রেখে দেওয়া ঠিক নয়।","ঘোষণা শোনার পর আমানত দেরি না করে জমা দিতে হয়।","ছোট জিনিস হলেও আত্মসাৎ হালকা বিষয় নয়।","অজুহাত দিয়ে দায়িত্ব এড়ানো নিরাপদ পথ নয়।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম দ্বারা প্রতিপালিত দেহের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম দ্বারা প্রতিপালিত দেহ সম্পর্কে নবীজির সতর্ক বাণী ও হালাল জীবনের শিক্ষা পড়ুন।"},"heading":{"title":"হারাম রুজি থেকে বাঁচার হাদিস: দেহ, খাদ্য ও আখিরাতের ভাবনা","description":"এই হাদিসে খুব সংক্ষিপ্ত ভাষায় বড় সতর্কতা দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে দেহ হারাম দ্বারা প্রতিপালিত, তা জান্নাতে প্রবেশ করবে না। এর মানে, মানুষের শরীর কী দিয়ে বড় হচ্ছে—এটি দ্বীনের দৃষ্টিতে গুরুত্বপূর্ণ। হারাম আয়, হারাম খাবার এবং অন্যায় পথে পাওয়া সম্পদ শুধু দুনিয়ার বিষয় নয়; এর আখিরাতের দিকও আছে। হালাল রুজি কম হলেও তা নিরাপদ। আর হারাম রুজি বেশি হলেও তা ক্ষতির কারণ হতে পারে। তাই এই হাদিস মুমিনকে নিজের উপার্জন, খাওয়া-দাওয়া ও পরিবারের খরচের উৎস নিয়ে সচেতন করে।"},"teachings":["হারাম দ্বারা প্রতিপালিত দেহ সম্পর্কে হাদিসে কঠিন সতর্কতা এসেছে।","রুজির উৎস হালাল হওয়া মুমিনের জীবনে বড় বিষয়।","কম হালাল আয়ও হারাম বেশি আয়ের চেয়ে নিরাপদ।","নিজের ও পরিবারের খাবারের উৎস যাচাই করা দরকার।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1599","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2760","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E123" s="4" t="n"/>
@@ -3417,12 +3333,12 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সম্পদে সততা ও বরকতের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. সম্পদ আকর্ষণীয় হলেও ন্যায্যভাবে অর্জন করলে তাতে বরকত হয়; অন্যায় তসরূপ আখিরাতের ক্ষতির কারণ।"},"heading":{"title":"হালাল সম্পদে বরকত: আল্লাহর সম্পদে অন্যায় তসরূপ নয়","description":"এই হাদিসে সম্পদের আকর্ষণ ও তার পরীক্ষার কথা বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, পার্থিব সম্পদ শ্যামল ও সুমিষ্ট, অর্থাৎ মানুষকে টানে। কিন্তু সম্পদ তখনই কল্যাণের কারণ হয়, যখন তা ন্যায়ভাবে পাওয়া যায়। হালাল সম্পদে বরকত—এই শিক্ষা এখানেই স্পষ্ট। আবার যারা আল্লাহ ও তাঁর রাসূলের সম্পদে নিজের ইচ্ছামতো তসরূপ করে, তাদের জন্য কিয়ামতের দিন কঠিন পরিণামের কথা এসেছে। তাই সম্পদ বেশি হওয়াই মূল কথা নয়; বরং তা কীভাবে পাওয়া হলো এবং কীভাবে ব্যবহার করা হলো, সেটাই বড় বিষয়। বিশেষ করে দায়িত্বে থাকা মাল, গনীমত বা জনস্বার্থের সম্পদে সততা রাখা খুব জরুরি।"},"teachings":["সম্পদ আকর্ষণীয় হলেও তা পরীক্ষা হতে পারে।","ন্যায়ভাবে পাওয়া সম্পদে বরকতের কথা এসেছে।","আল্লাহ ও রাসূলের সম্পদে অন্যায় তসরূপ গুরুতর অপরাধ।","সম্পদের উৎস ও ব্যবহার—দুই দিকেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"3118","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক খেজুর না খাওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. সদকার খেজুর হতে পারে—এই আশঙ্কায় নবীজির সতর্কতা থেকে সন্দেহ এড়ানোর শিক্ষা জানুন।"},"heading":{"title":"সদকার সন্দেহে খেজুর না খাওয়া: নবীজির সতর্কতার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম রাস্তায় পড়ে থাকা একটি খেজুরের পাশ দিয়ে যান। তিনি বলেন, যদি সদকার খেজুর হওয়ার সন্দেহ না থাকত, তবে তিনি তা খেতেন। এই ছোট ঘটনাতেই বড় শিক্ষা আছে। এখানে খেজুরটি সামান্য জিনিস, কিন্তু নবীজি সন্দেহের জায়গায় সতর্কতা দেখিয়েছেন। কারণ সদকা তাঁর জন্য খাওয়া বৈধ ছিল না। হাদিসটি আমাদের শেখায়, সামান্য জিনিস হলেও হালাল-হারামের সীমা মানা দরকার। যখন কোনো বিষয়ে সন্দেহ থাকে, তখন সাবধান থাকা মুমিনের চরিত্রকে সুন্দর করে। এটি লোভ কমায় এবং অন্তরে আল্লাহভীতি বাড়ায়।"},"teachings":["সন্দেহের জায়গায় সাবধান থাকা নবীজির শিক্ষা।","সামান্য জিনিস হলেও হালাল-হারাম দেখা দরকার।","নিজের জন্য যা বৈধ নয়, তা থেকে দূরে থাকা উচিত।","খাবার গ্রহণেও আল্লাহভীতি থাকা মুমিনের গুণ।"],"related_hadiths":[{"id":"2055","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1071","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1652","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E124" s="4" t="n"/>
@@ -3440,12 +3356,12 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | খিয়ানত ও কিয়ামতের জবাবদিহি","description":"$book_name$ $hadith_number$ - $chapter_name$. খিয়ানত করা বস্তু কিয়ামতে মানুষের কাঁধে প্রকাশ পাবে; নবী আগেই সতর্ক করেছেন, তাই আমানত রক্ষা জরুরি।"},"heading":{"title":"খিয়ানত থেকে বাঁচুন: কিয়ামতে গোপন আত্মসাৎ প্রকাশ পাবে","description":"এই হাদিসে খিয়ানতের ভয়াবহতা খুব পরিষ্কারভাবে এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খিয়ানতের বিষয়টি বড় করে তুলে ধরেছেন এবং কিয়ামতের দিনের কয়েকটি দৃশ্য বলেছেন। কেউ উট, কেউ ঘোড়া, কেউ ছাগল, কেউ মানুষ, কেউ কাপড়, কেউ সোনা-চাঁদির মতো সম্পদ কাঁধে নিয়ে আসবে—অর্থাৎ যে জিনিসে খিয়ানত করেছে, সেটিই তার দায় হয়ে প্রকাশ পাবে। তখন সে সাহায্য চাইবে, কিন্তু রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলবেন, তিনি আগেই আল্লাহর বিধান জানিয়ে দিয়েছেন। এই হাদিস আত্মসাৎ ও খিয়ানত থেকে কঠোরভাবে সতর্ক করে। আমানত লুকিয়ে রাখা, দায়িত্বের সম্পদ নেওয়া বা অন্যের মাল নিজের করে নেওয়া কখনো নিরাপদ নয়।"},"teachings":["খিয়ানত করা বস্তু কিয়ামতে দায় হিসেবে প্রকাশ পাবে।","আগে সতর্ক করা হলে পরে অজুহাতের সুযোগ কমে যায়।","অন্যের মাল, প্রাণী, কাপড় বা সম্পদ আত্মসাৎ করা গুরুতর বিষয়।","আমানত রক্ষা করা আখিরাতের জবাবদিহির সঙ্গে জড়িত।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1201","book_id":"10","slug":"luluwal-marjan","label":"লুলুওয়াল মারজান"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যাকাতের খেজুর ও নবী পরিবারের বিধান","description":"$book_name$ $hadith_number$ - $chapter_name$. হাসান রাঃ-এর যাকাতের খেজুর ঘটনায় নবী পরিবারের জন্য সদকা না খাওয়ার শিক্ষা জানুন।"},"heading":{"title":"যাকাতের খেজুর নিয়ে হাদিস: নবী পরিবারের জন্য সদকার বিধান","description":"এই হাদিসে হাসান ইবনে আলী রাদিয়াল্লাহু আনহু যাকাতের একটি খেজুর মুখে দেন। নবী করীম সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম সঙ্গে সঙ্গে তাঁকে তা ফেলে দিতে বলেন এবং জানান, তাঁরা যাকাত খান না। এখানে শিক্ষা খুব পরিষ্কার। শিশুর ক্ষেত্রেও নবীজি হালাল-হারামের সীমা শেখাতে দেরি করেননি। তবে ভাষা ছিল কোমল ও শাসনের মতো। যাকাত একটি নির্দিষ্ট ইবাদত এবং এর খাতও নির্দিষ্ট। যাদের জন্য তা গ্রহণের বিধান নেই, তাদের তা খাওয়া উচিত নয়। এই হাদিস আমাদের শেখায়, ছোট বয়স থেকেই সন্তানকে বৈধ-অবৈধের শিক্ষা দেওয়া দরকার।"},"teachings":["যাকাতের মাল যার জন্য বৈধ নয়, তার তা খাওয়া উচিত নয়।","শিশুকেও হালাল-হারামের শিক্ষা দেওয়া দরকার।","নবীজি পরিবারকে দ্বীনের বিধান মানতে শিখিয়েছেন।","খাবার মুখে দেওয়ার আগেও উৎস জানা গুরুত্বপূর্ণ।"],"related_hadiths":[{"id":"2363","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2055","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1071","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E125" s="4" t="n"/>
@@ -3463,12 +3379,12 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সামান্য আত্মসাতের বড় পরিণাম","description":"$book_name$ $hadith_number$ - $chapter_name$. গনীমত বণ্টনের আগে নেওয়া ছোট চাদরও আগুনের কারণ বলা হয়েছে; আত্মসাৎ ছোট মনে করা উচিত নয়।"},"heading":{"title":"সামান্য আত্মসাৎও ভয়াবহ: গনীমতের মাল নিয়ে সতর্ক হোন","description":"এই হাদিসে মিদআম নামে এক ব্যক্তির ঘটনা এসেছে। তিনি মারা গেলে সাহাবীগণ তার জন্য জান্নাতের কথা বলেছিলেন। কিন্তু রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) জানালেন, খায়বারের গনীমত বণ্টনের আগে নেওয়া একটি চাদর তার জন্য আগুনের কারণ হচ্ছে। এটি শুনে একজন লোক জুতার ফিতা বা দু’টি ফিতা নিয়ে এলো। তখনও রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সেটির ব্যাপারে আগুনের কথা বললেন। এই হাদিসের মূল শিক্ষা হলো, আত্মসাৎ ছোট মনে করা যাবে না। গনীমতের মাল হোক বা অন্য কোনো আমানত—বণ্টন বা অনুমতি ছাড়া নেওয়া বড় দায়। বাহ্যিকভাবে ভালো অবস্থায় মৃত্যু হলেও মানুষের গোপন কাজের হিসাব আল্লাহর কাছে থাকবে।"},"teachings":["গনীমত বণ্টনের আগে কিছু নেওয়া আত্মসাতের মধ্যে পড়ে।","সামান্য বস্তু হলেও আত্মসাৎকে ছোট মনে করা ঠিক নয়।","মানুষের বাহ্যিক ধারণা সব সময় আসল অবস্থা জানায় না।","অমানত ও গনীমতের মাল ফেরত দিতে দেরি করা বিপজ্জনক।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3118","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিককে নেতা বলা থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মুনাফিক বা মিথ্যুক ব্যক্তিকে নেতা হিসেবে সম্মান করার বিষয়ে নবীজির সতর্ক বাণী জানুন।"},"heading":{"title":"মুনাফিককে নেতা বলা: সত্য, নেতৃত্ব ও ঈমানি সতর্কতার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম মুনাফিক ব্যক্তিকে নেতা বা সাইয়িদ বলতে নিষেধ করেছেন। অনুবাদে এসেছে, যদি নেতা মুনাফিক হয়, তাহলে এতে প্রতিপালককে অসন্তুষ্ট করার কথা বলা হয়েছে। অন্য বর্ণনায় মিথ্যুক মুনাফিককে নেতা বলা নিয়েও কঠিন সতর্কতা এসেছে। হাদিসটি নেতৃত্বের ভাষা ও সম্মান দেওয়ার বিষয়ে আমাদের সতর্ক করে। সম্মান এমন কাউকে দেওয়া উচিত নয়, যার ভেতরে মুনাফিকি, মিথ্যা বা দ্বীনের বিরুদ্ধে আচরণ আছে। এর মানে সাধারণ আচরণে অশোভন হওয়া নয়; বরং নৈতিক সম্মান ও নেতৃত্বের আসন কাকে দেওয়া হচ্ছে, সে বিষয়ে সতর্ক থাকা।"},"teachings":["মুনাফিক ব্যক্তিকে নেতৃত্বের সম্মান দেওয়ার বিষয়ে সতর্কতা এসেছে।","মিথ্যুক ও দ্বিমুখী চরিত্রের মানুষকে অকারণে বড় করা উচিত নয়।","নেতৃত্বের সম্মান নৈতিকতার সাথে জড়িত।","কথার মাধ্যমে কাকে মর্যাদা দিচ্ছি, তা ভাবা দরকার।"],"related_hadiths":[{"id":"33","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"59","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"4873","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E126" s="4" t="n"/>
@@ -3486,12 +3402,12 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দায়িত্বের মাল আত্মসাৎ থেকে ভয়","description":"$book_name$ $hadith_number$ - $chapter_name$. দায়িত্বে থাকা ব্যক্তির চাদর আত্মসাৎ তার পরিণামকে ভয়াবহ করেছে; আমানতের মাল গোপন করা বড় অপরাধ।"},"heading":{"title":"দায়িত্বের মাল আত্মসাৎ: কারকারার ঘটনা থেকে সতর্ক শিক্ষা","description":"এই হাদিসে এমন এক ব্যক্তির কথা এসেছে, যে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর গনীমতের মালের দায়িত্বে ছিল। তার নাম ছিল কারকারা। সে মারা গেলে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাকে জাহান্নামী বলে জানান। পরে সাহাবীগণ গিয়ে দেখলেন, সে একটি চাদর আত্মসাৎ করেছিল। হাদিসটি দায়িত্বের মাল আত্মসাৎ সম্পর্কে কঠিন সতর্কতা দেয়। কেউ যদি কোনো সম্পদের পাহারাদার, দায়িত্বশীল বা ব্যবস্থাপক হয়, তাহলে তার দায়িত্ব আরও বড়। কারণ সে নিজের জন্য নয়, আমানতের জন্য কাজ করছে। একটি চাদরকে ছোট মনে করা হলেও হাদিসে তার পরিণাম কঠিনভাবে এসেছে। তাই সরকারি, সামাজিক, পারিবারিক বা যে কোনো দায়িত্বের মাল নিজের করে নেওয়া থেকে বেঁচে থাকা দরকার।"},"teachings":["দায়িত্বে থাকা মাল নিজের জন্য নেওয়া খিয়ানত।","আত্মসাৎ করা বস্তু ছোট হলেও এর দায় বড় হতে পারে।","দায়িত্বশীল ব্যক্তির আমানতদারি আরও বেশি জরুরি।","গোপনভাবে নেওয়া জিনিস আল্লাহর কাছে গোপন থাকে না।"],"related_hadiths":[{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3118","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তর্ক, মিথ্যা ও সুন্দর চরিত্রের ফজিলত","description":"$book_name$ $hadith_number$ - $chapter_name$. হক হলেও তর্ক ছাড়া, মজা করেও মিথ্যা না বলা এবং চরিত্র সুন্দর করার বড় শিক্ষা জানুন।"},"heading":{"title":"সুন্দর চরিত্রের হাদিস: তর্ক ছাড়া, মিথ্যা ছাড়া, ভালো আচরণ","description":"এই হাদিসে তিনটি বড় আচরণ শেখানো হয়েছে। প্রথমত, কেউ হক হলেও তর্ক পরিহার করলে তার জন্য জান্নাতে ঘরের কথা এসেছে। দ্বিতীয়ত, মজা করেও মিথ্যা ছেড়ে দেওয়ার কথা বলা হয়েছে। তৃতীয়ত, চরিত্র সুন্দর করার ফজিলত এসেছে। হাদিসটি আমাদের দৈনন্দিন কথা ও আচরণকে ঠিক করার সহজ পথ দেখায়। অনেক সময় মানুষ সত্য কথা বলেও তর্কে জড়িয়ে পড়ে, আবার হাসানোর জন্য মিথ্যা বলে ফেলে। এই হাদিস শেখায়, সত্যের সাথে নম্রতা, কথার সাথে সততা এবং মানুষের সাথে ভালো ব্যবহার—সবই মুমিনের চরিত্রের অংশ। সুন্দর চরিত্র শুধু বাহ্যিক ভদ্রতা নয়; এটি কথা, রাগ, তর্ক ও আচরণে প্রকাশ পায়।"},"teachings":["হক হলেও অপ্রয়োজনীয় তর্ক ছেড়ে দেওয়া উত্তম কাজ।","মজা করেও মিথ্যা বলা থেকে বাঁচতে হবে।","সুন্দর চরিত্র জান্নাতের বড় ফজিলতের কারণ।","সত্য কথা বলার সঙ্গে নম্র আচরণও দরকার।"],"related_hadiths":[{"id":"4800","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2004","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E127" s="4" t="n"/>
@@ -3509,12 +3425,12 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আত্মসাৎ শহীদের মর্যাদায় বাধা","description":"$book_name$ $hadith_number$ - $chapter_name$. বাহ্যিকভাবে শহীদ বলা হলেও চাদর আত্মসাৎকারীর পরিণাম কঠিন হয়েছে; গোপন খিয়ানত থেকে সতর্ক থাকতে হবে।"},"heading":{"title":"আত্মসাৎ ও শহীদের দাবি: গোপন খিয়ানত আখিরাতে প্রকাশ পায়","description":"এই হাদিসে খায়বারের দিনের একটি ঘটনা এসেছে। সাহাবীগণ কয়েকজনকে শহীদ বলছিলেন। এমন একজনের ব্যাপারে তারা শহীদ বললে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বললেন, কখনো নয়; তিনি তাকে জাহান্নামে দেখেছেন, কারণ সে একটি চাদর আত্মসাৎ করেছিল। এই বক্তব্য খুব গভীর শিক্ষা দেয়। মানুষের চোখে কেউ বাহ্যিকভাবে ভালো বা সম্মানিত মনে হতে পারে, কিন্তু গোপন খিয়ানত থাকলে তার হিসাব আল্লাহর কাছে থাকবে। আত্মসাৎ শহীদের মর্যাদার দাবিকেও বিপদে ফেলতে পারে—হাদিসের ভাষায় বিষয়টি এভাবেই এসেছে। তাই গনীমতের মাল, দায়িত্বের মাল বা কোনো আমানত গোপনে নেওয়া থেকে কঠোরভাবে বাঁচা দরকার।"},"teachings":["মানুষের বাহ্যিক প্রশংসা আখিরাতের হিসাব বদলায় না।","একটি চাদর আত্মসাৎ করাও ভয়াবহ পরিণামের কারণ হয়েছে।","গোপন খিয়ানত মানুষের মর্যাদাকে ক্ষতিগ্রস্ত করতে পারে।","আল্লাহর কাছে আমানতের হিসাব খুবই গুরুতর।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বায়আত ও বড় গুনাহ থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, চুরি, যেনা, সন্তান হত্যা, অপবাদ ও অবাধ্যতা থেকে দূরে থাকার বায়আতের শিক্ষা এসেছে।"},"heading":{"title":"বায়আতের শর্ত ও বড় গুনাহ থেকে বাঁচার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সাহাবীদের কাছ থেকে বায়আত নেন। তিনি বলেন, তারা যেন আল্লাহর সঙ্গে কাউকে শরীক না করে, চুরি না করে, যেনা না করে, সন্তান হত্যা না করে, কারও প্রতি অপবাদ না দেয় এবং শরীআতসম্মত বিষয়ে অবাধ্যতা না করে। এরপর তিনি জানান, যে এসব অঙ্গীকার পূর্ণ করবে, তার পুরস্কার আল্লাহর কাছে। কেউ যদি কোনো অপরাধ করে এবং দুনিয়াতে শাস্তি পায়, তা তার জন্য কাফফারা হতে পারে। আর আল্লাহ যদি তা ঢেকে রাখেন, তাহলে বিষয়টি আল্লাহর ইচ্ছার উপর। এই হাদিসে বায়আত, তাওহীদ, নৈতিকতা, অপরাধ থেকে বাঁচা এবং আল্লাহর বিচার—সব মিলিয়ে দায়িত্বশীল জীবনের শিক্ষা আছে।"},"teachings":["শিরক, চুরি, যেনা, অপবাদ ও অন্যায় থেকে দূরে থাকা জরুরি।","শরীআতসম্মত বিষয়ে অবাধ্যতা করা ঠিক নয়।","অঙ্গীকার পূরণ করলে প্রতিদান আল্লাহর কাছে।","গুনাহের বিচার আল্লাহর ইচ্ছা ও ন্যায়ের সঙ্গে জড়িত।"],"related_hadiths":[{"id":"18","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1709","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"18","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E128" s="4" t="n"/>
@@ -3532,19 +3448,15 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আল্লাহর সন্তুষ্টি ও অসন্তুষ্টির কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ তিন কাজে সন্তুষ্ট হন এবং তিন কাজে অসন্তুষ্ট হন—ইবাদত, ঐক্য, উপদেশ ও অপচয়ের শিক্ষা এখানে আছে।"},"heading":{"title":"আল্লাহর সন্তুষ্টির তিন কাজ ও অসন্তুষ্টির তিন কাজ","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ তিনটি কাজে সন্তুষ্ট হন এবং তিনটি কাজে অসন্তুষ্ট হন। সন্তুষ্টির কাজ হলো আল্লাহর ইবাদত করা ও তাঁর সঙ্গে শরীক না করা, আল্লাহর বিধানকে শক্তভাবে আঁকড়ে ধরা ও বিচ্ছিন্ন না হওয়া, এবং যাকে আল্লাহ কাজের নেতা করেন তার জন্য পরস্পরে কল্যাণ কামনা করা। আর আল্লাহ অসন্তুষ্ট হন অপ্রয়োজনীয় কথা, সম্পদ নষ্ট করা এবং অনর্থক বেশি প্রশ্ন করার কারণে। এই হাদিসে তাওহীদ, ঐক্য, নসীহত, সম্পদ রক্ষা ও কথা নিয়ন্ত্রণের শিক্ষা এসেছে। মুসলিম জীবনে শুধু ইবাদত নয়, কথা, সম্পদ ও সামাজিক আচরণও গুরুত্বপূর্ণ। আল্লাহর সন্তুষ্টির কাজ খুঁজে জীবন সাজানোই এই হাদিসের সহজ বার্তা।"},"teachings":["আল্লাহর ইবাদত করা এবং শিরক থেকে দূরে থাকা বড় দায়িত্ব।","আল্লাহর বিধান আঁকড়ে ধরা ও বিচ্ছিন্নতা এড়ানো দরকার।","অপ্রয়োজনীয় কথা ও সম্পদ নষ্ট করা থেকে বাঁচতে হবে।","নেতার জন্য কল্যাণ কামনা করা ভালো সামাজিক আচরণ।"],"related_hadiths":[{"id":"1715","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[1]: unknown book label "মুসনাদে আহমাদ ৮৭৮৫"; related_hadiths[2]: unknown book label "সহীহ ইবনু হিব্বান ৩৩৮৮"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আল্লাহর ভালোবাসার পথে আমানত ও সত্য","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ ও রাসূলের ভালোবাসা পেতে আমানত, সত্য কথা ও প্রতিবেশীর ভালো আচরণের শিক্ষা জানুন।"},"heading":{"title":"আমানত রক্ষা, সত্য কথা ও প্রতিবেশীর হক: ভালোবাসার হাদিস","description":"এই হাদিসে সাহাবীরা নবীজির ওযূর পানির প্রতি ভালোবাসা দেখিয়েছিলেন। তাঁরা বললেন, এটি আল্লাহ ও তাঁর রাসূলের ভালোবাসার কারণে করেছেন। তখন রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম তাঁদের সামনে ভালোবাসার বাস্তব পথ জানালেন। তিনি বললেন, আমানত রাখা হলে তা ফিরিয়ে দাও, কথা বললে সত্য বল, আর প্রতিবেশীর সাথে ভালো আচরণ কর। এতে বোঝা যায়, ভালোবাসা শুধু আবেগে সীমাবদ্ধ নয়; তা কাজে প্রকাশ পায়। একজন মুমিন আল্লাহ ও রাসূলকে ভালোবাসতে চাইলে তার লেনদেন সৎ হবে, কথায় মিথ্যা থাকবে না এবং পাশের মানুষের সাথে আচরণ সুন্দর হবে।"},"teachings":["আমানত রাখা হলে তা যথাযথভাবে ফিরিয়ে দেওয়া দরকার।","কথা বলার সময় সত্য বলা ভালোবাসার বাস্তব প্রকাশ।","প্রতিবেশীর সাথে ভালো আচরণ মুমিনের দায়িত্ব।","আল্লাহ ও রাসূলের ভালোবাসা কাজে প্রমাণ করতে হয়।"],"related_hadiths":[{"id":"33","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6016","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"46","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="n"/>
     </row>
     <row r="130" ht="46" customHeight="1">
       <c r="A130" s="4" t="inlineStr">
@@ -3559,12 +3471,12 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অন্যায় সম্পদ দখলের ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর সম্পদ অন্যায়ভাবে দখল বা ব্যবহার করলে কিয়ামতের দিন জাহান্নামের কঠিন সতর্কতা এসেছে।"},"heading":{"title":"অন্যায় সম্পদ দখল: আল্লাহর মালে অন্যায় ব্যবহার থেকে বাঁচুন","description":"এই হাদিসে অন্যায়ভাবে সম্পদ দখল করার পরিণাম খুব স্পষ্টভাবে বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যারা আল্লাহর সম্পদে অন্যায়ভাবে তসরূপ করে, কিয়ামতের দিন তাদের জন্য জাহান্নাম রয়েছে। এখানে মূল বিষয় হলো, সম্পদকে নিজের ইচ্ছামতো ব্যবহার করা যাবে না, যদি সেটি নিজের হক না হয়। অন্যায় সম্পদ দখল শুধু চুরি বা প্রকাশ্য ছিনিয়ে নেওয়ার মধ্যে সীমিত নয়; দায়িত্বের মাল, গনীমতের মাল বা মানুষের হক—সব ক্ষেত্রেই সতর্কতা দরকার। হাদিসটি আমাদের শেখায়, সম্পদের ব্যাপারে আল্লাহর ভয় রাখা দরকার। যা ন্যায্য নয়, তা থেকে দূরে থাকা নিরাপদ পথ।"},"teachings":["অন্যায়ভাবে সম্পদ দখল করা আখিরাতের বড় ক্ষতির কারণ।","আল্লাহর মাল বা দায়িত্বের মাল নিজের ইচ্ছায় ব্যবহার করা ঠিক নয়।","সম্পদের ব্যাপারে হক-না-হক বিচার করা জরুরি।","কিয়ামতের জবাবদিহি মনে রাখলে আত্মসাৎ থেকে বাঁচা সহজ হয়।"],"related_hadiths":[{"id":"3073","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3074","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"210","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত, সত্য, চরিত্র ও বৈধ রুজি","description":"$book_name$ $hadith_number$ - $chapter_name$. চারটি গুণ—আমানত, সত্য কথা, সুন্দর চরিত্র ও বৈধ রুজি—নিয়ে নবীজির গভীর শিক্ষা জানুন।"},"heading":{"title":"চারটি গুণের হাদিস: আমানত, সত্যবাদিতা, সুন্দর চরিত্র ও বৈধ রুজি","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম চারটি জিনিসের কথা বলেছেন। এগুলো মানুষের জীবনে থাকলে দুনিয়ার অনেক কিছু হারালেও তার বড় ক্ষতি নেই—এমন শিক্ষা এসেছে। চারটি গুণ হলো আমানত রক্ষা করা, সত্য কথা বলা, সুন্দর চরিত্র রাখা এবং বৈধ রুজি গ্রহণ করা। এই চারটি বিষয় ব্যক্তিগত জীবন, পরিবার, ব্যবসা ও সমাজ—সব জায়গায় দরকার। আমানত মানুষকে বিশ্বাসযোগ্য করে, সত্য কথা তাকে পরিষ্কার রাখে, সুন্দর চরিত্র তাকে প্রিয় করে, আর বৈধ রুজি তার জীবনকে পবিত্র পথে রাখে। হাদিসটি খুব সহজ ভাষায় সফল মুসলিম জীবনের একটি নীতিমালা দেয়।"},"teachings":["আমানত রক্ষা মানুষকে বিশ্বাসযোগ্য করে।","সত্য কথা বলা মুমিনের বড় গুণ।","সুন্দর চরিত্র মানুষের সাথে সম্পর্ক ভালো রাখে।","বৈধ রুজি গ্রহণ করা জীবনের নিরাপদ পথ।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2004","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E130" s="4" t="n"/>
@@ -3582,12 +3494,12 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল রিজিক ও দোয়া কবুলের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য, পানীয়, পোশাক ও জীবিকা হারাম হলে দোয়া কবুলের পথে বাধা তৈরি হয়; পবিত্র রিজিক জরুরি।"},"heading":{"title":"হালাল রিজিক ও দোয়া কবুল: খাদ্য-পোশাকে পবিত্রতা কেন জরুরি","description":"এই হাদিসে হালাল রিজিকের গুরুত্ব খুব সুন্দরভাবে বোঝানো হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ পবিত্র এবং তিনি পবিত্র ছাড়া গ্রহণ করেন না। এরপর এমন এক ব্যক্তির কথা এসেছে, যে সফরে ক্লান্ত, ধুলামলিন, দু’হাত তুলে কাতরভাবে দোয়া করছে। বাহ্যিকভাবে দোয়ার অনেক কারণ আছে। কিন্তু তার খাদ্য হারাম, পানীয় হারাম, পোশাক হারাম এবং জীবিকা হারাম। তাই বলা হয়েছে, তার দোয়া কীভাবে কবুল হবে? হালাল রিজিক হাদিস আমাদের শেখায়, দোয়া শুধু মুখের শব্দ নয়; জীবনের উপার্জন, খাবার ও পোশাকের সঙ্গেও এর সম্পর্ক আছে। তাই ইবাদতের সঙ্গে হালাল উপার্জনকে গুরুত্ব দেওয়া দরকার।"},"teachings":["আল্লাহ পবিত্র, তাই পবিত্র বস্তু গ্রহণ করেন।","হারাম খাদ্য, পানীয় ও পোশাক দোয়া কবুলের পথে বাধা হতে পারে।","দোয়ার সঙ্গে জীবিকার পবিত্রতার সম্পর্ক আছে।","হালাল উপার্জন ইবাদতের জীবনে গুরুত্বপূর্ণ অংশ।"],"related_hadiths":[{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1205","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহ ছাড়ুন, সত্যে শান্তি খুঁজুন","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহযুক্ত কথা ও কাজ ছেড়ে সত্যের শান্তি এবং মিথ্যার অশান্তি বুঝে চলার শিক্ষা নিন।"},"heading":{"title":"সত্যে প্রশান্তি, মিথ্যায় অশান্তি: সন্দেহ ছাড়ার হাদিস","description":"এই হাদিসে বলা হয়েছে, সন্দেহযুক্ত কথা ও কাজ ছেড়ে এমন দিকে ফিরে যেতে, যেখানে সন্দেহ নেই। এরপর বলা হয়েছে, সত্য প্রশান্তির নাম এবং মিথ্যা সন্দেহ ও অশান্তির নাম। এখানে সত্যবাদিতা শুধু মুখের কথা নয়; কাজের ক্ষেত্রেও সত্যের পথ বেছে নেওয়ার কথা আছে। যখন কোনো কথা, লেনদেন বা কাজ অন্তরে অস্বস্তি আনে, তখন তা নিয়ে থেমে ভাবা দরকার। মুমিনের জীবন এমন হওয়া উচিত, যেখানে কথা ও কাজে স্বচ্ছতা থাকে। মিথ্যা কিছু সময় সুবিধা দিলেও অন্তরে অস্থিরতা আনে। তাই এই হাদিস মানুষকে সহজ, সৎ ও শান্ত পথের দিকে ডাকছে।"},"teachings":["সন্দেহযুক্ত কথা ও কাজ ছেড়ে দেওয়া উচিত।","সত্য অন্তরে প্রশান্তি আনে।","মিথ্যা সন্দেহ ও অশান্তির কারণ হয়।","কথা ও কাজ—দুটোতেই সততা দরকার।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2607","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E131" s="4" t="n"/>
@@ -3605,12 +3517,12 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল-হারাম উপার্জনে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. এমন সময় আসবে যখন মানুষ উপার্জনের হালাল-হারাম নিয়ে পরোয়া করবে না; তাই আয়ের উৎস যাচাই জরুরি।"},"heading":{"title":"হালাল-হারাম উপার্জন: আয়ের উৎস নিয়ে উদাসীন হবেন না","description":"এই হাদিসে ভবিষ্যৎ সময়ের একটি বড় বিপদের কথা বলা হয়েছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, মানুষের উপর এমন সময় আসবে, যখন মানুষ হালাল-হারাম উপার্জন বিবেচনা করবে না। অর্থাৎ টাকা আসছে কি না—এটাই যদি প্রধান চিন্তা হয়ে যায়, তাহলে মানুষ উৎস ভুলে যেতে পারে। হালাল হারাম উপার্জন বিষয়টি তাই শুধু ফিকহের আলোচনা নয়; এটি ব্যক্তিগত জীবনের প্রতিদিনের পরীক্ষা। ব্যবসা, চাকরি, লেনদেন, কমিশন, বেতন—সব ক্ষেত্রেই মুসলিমের দেখা দরকার, এই আয় বৈধ পথে হচ্ছে কি না। হাদিসটি আমাদের আগে থেকেই সতর্ক করে, যাতে সমাজের ভুল পথে ভেসে না যাই এবং নিজের রিজিকের বিষয়ে আল্লাহকে ভয় করি।"},"teachings":["উপার্জনের উৎস হালাল কি না তা দেখা জরুরি।","সমাজে উদাসীনতা বাড়লেও মুমিনকে সতর্ক থাকতে হবে।","শুধু টাকা পাওয়া নয়, বৈধ পথে পাওয়া গুরুত্বপূর্ণ।","হালাল-হারাম বিচার না করা বড় নৈতিক ক্ষতির কারণ হতে পারে।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1205","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হিংসামুক্ত অন্তর ও সত্য ভাষার মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. উত্তম মানুষের পরিচয়ে সত্য ভাষা, পরহেযগার অন্তর ও হিংসা থেকে মুক্ত থাকার শিক্ষা জানুন।"},"heading":{"title":"হিংসামুক্ত অন্তর ও সত্য ভাষা: উত্তম মানুষের পরিচয়","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লামকে জিজ্ঞেস করা হলো, সবচেয়ে ভাল মানুষ কে? উত্তরে তিনি বললেন, যে ব্যক্তি হিংসা-বিদ্বেষ মুক্ত অন্তরের অধিকারী এবং সত্য কথার অধিকারী। সাহাবীগণ সত্য ভাষা বুঝলেন, কিন্তু হিংসা-বিদ্বেষ মুক্ত অন্তরের ব্যাখ্যা জানতে চাইলেন। তখন তিনি বললেন, সে ব্যক্তি স্বচ্ছ ও পরহেযগার; যার মধ্যে পাপ, সীমালংঘন, খিয়ানত ও হিংসা নেই। এই হাদিস আমাদের বাহ্যিক ভালো কাজের পাশাপাশি অন্তরের পরিচ্ছন্নতার দিকে ডাকে। শুধু মুখে সত্য বললেই শেষ নয়; অন্তর থেকেও হিংসা, খিয়ানত ও অন্যায় দূর করার চেষ্টা করতে হয়।"},"teachings":["সত্য ভাষা উত্তম মানুষের গুণ।","হিংসা-বিদ্বেষ মুক্ত অন্তর মুমিনের বড় সৌন্দর্য।","খিয়ানত ও সীমালংঘন থেকে দূরে থাকা দরকার।","ভালো মানুষ হতে অন্তর ও ভাষা—দুটোই ঠিক রাখা জরুরি।"],"related_hadiths":[{"id":"4216","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"91","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E132" s="4" t="n"/>
@@ -3628,12 +3540,12 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম খাদ্যের ভয়াবহ পরিণাম","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম খাদ্যে লালিত শরীরের পরিণাম কঠিন বলা হয়েছে; তাই খাবার ও উপার্জনে হালাল পথ জরুরি।"},"heading":{"title":"হারাম খাদ্য থেকে বাঁচুন: শরীর ও রিজিকের পবিত্রতা","description":"এই হাদিসে খুব সংক্ষিপ্ত ভাষায় বড় একটি সতর্কতা এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, হারাম খাদ্য দ্বারা পরিপুষ্ট শরীর জান্নাতে যাবে না। তাই হারাম খাদ্য হাদিস আমাদের শুধু খাবারের নাম নয়, খাবারের উৎস নিয়েও ভাবতে শেখায়। যে খাবার আমরা খাই, সেটি কীভাবে কেনা হলো, আয়টি বৈধ ছিল কি না, অন্যের হক মিশে আছে কি না—এসব বিষয় গুরুত্বপূর্ণ। শরীর খাবার দিয়ে গড়ে ওঠে, আর মুমিনের জীবন ইবাদত ও আনুগত্যের জন্য। তাই হারাম খাদ্যকে হালকা মনে করা ঠিক নয়। এই হাদিসের শিক্ষা হলো, নিজের ও পরিবারের খাবারের ব্যাপারে সতর্ক থাকা এবং হালাল রিজিকের চেষ্টা করা।"},"teachings":["হারাম খাদ্যে শরীর গড়ে ওঠা ভয়াবহ সতর্কতার বিষয়।","খাবারের সঙ্গে উপার্জনের উৎসও দেখা দরকার।","পরিবারের খাবার হালাল কি না তা অভিভাবকের দায়িত্বের অংশ।","হালাল রিজিকের চেষ্টা করা ঈমানি জীবনের গুরুত্বপূর্ণ কাজ।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সত্য নেকীর পথে, মিথ্যা পাপের পথে","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য গ্রহণ ও মিথ্যা থেকে বাঁচার মাধ্যমে নেকী ও পাপের পথ বুঝে চলার শিক্ষা জানুন।"},"heading":{"title":"সত্য নেকীর সাথে, মিথ্যা পাপের সাথে: নবীজির সরল শিক্ষা","description":"এই হাদিসে সত্য ও মিথ্যার পথ খুব পরিষ্কার করে বলা হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, সত্য গ্রহণ কর; কারণ সত্য নেকীর সাথে রয়েছে। আর মিথ্যা থেকে বেঁচে থাক; কারণ মিথ্যা পাপের সাথে রয়েছে। এখানে সত্যকে শুধু ভালো অভ্যাস বলা হয়নি; বরং তা নেকীর পথে নিয়ে যায় বলা হয়েছে। আবার মিথ্যাকে ছোট ভুল হিসেবে দেখা হয়নি; তা পাপের সাথে যুক্ত বলা হয়েছে। তাই একজন মুমিনের কথা, প্রতিশ্রুতি, লেনদেন ও সম্পর্ক—সব জায়গায় সত্য দরকার। মিথ্যা সাময়িক সুবিধা দিলেও মানুষকে খারাপ পথে টেনে নিতে পারে।"},"teachings":["সত্য নেকীর পথে নিয়ে যায়।","মিথ্যা পাপের সাথে যুক্ত।","কথা ও লেনদেনে সত্যবাদিতা রাখা জরুরি।","মিথ্যাকে ছোট ভুল ভেবে অবহেলা করা উচিত নয়।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2607","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2518","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E133" s="4" t="n"/>
@@ -3651,12 +3563,12 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল-হারাম ও সন্দেহজনক বিষয়","description":"$book_name$ $hadith_number$ - $chapter_name$. হালাল-হারাম স্পষ্ট; সন্দেহজনক বিষয় থেকে বাঁচলে দ্বীন ও মর্যাদা রক্ষা হয়, আর অন্তর ঠিক থাকলে শরীর ঠিক থাকে।"},"heading":{"title":"হালাল হারাম স্পষ্ট: সন্দেহজনক বিষয় থেকে বাঁচার শিক্ষা","description":"এই হাদিস ইসলামী জীবনের একটি মৌলিক নীতি শেখায়। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, হালাল স্পষ্ট এবং হারামও স্পষ্ট। মাঝখানে কিছু সন্দেহজনক বিষয় আছে, যা অনেক মানুষ জানে না। যে ব্যক্তি সন্দেহজনক বিষয় থেকে বেঁচে থাকে, সে তার দ্বীন ও মর্যাদা রক্ষা করে। আর যে সন্দেহজনক বিষয়ে পড়ে, সে হারামের কাছাকাছি চলে যায়। রাখালের উদাহরণ দিয়ে বোঝানো হয়েছে, নিষিদ্ধ সীমার ধারে থাকলে ভিতরে ঢুকে পড়ার ভয় থাকে। শেষে অন্তরের কথা বলা হয়েছে: অন্তর ঠিক থাকলে শরীর ঠিক থাকে, নষ্ট হলে শরীরও নষ্ট হয়। তাই সন্দেহজনক বিষয় হাদিস আমাদের সতর্ক, পরিষ্কার ও অন্তর-সচেতন জীবন শেখায়।"},"teachings":["হালাল ও হারামের স্পষ্ট সীমা মানা জরুরি।","সন্দেহজনক বিষয় থেকে দূরে থাকলে দ্বীন ও মর্যাদা রক্ষা হয়।","হারামের কাছাকাছি ঘোরাফেরা করা ঝুঁকিপূর্ণ।","অন্তর ভালো থাকলে আচরণও ভালো হওয়ার পথ তৈরি হয়।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"593","book_id":"8","slug":"riyadus-salihin","label":"রিয়াদুস সালেহীন"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মিথ্যা ঈমানকে ক্ষতিগ্রস্ত করে","description":"$book_name$ $hadith_number$ - $chapter_name$. মিথ্যা থেকে বেঁচে থাকার গুরুত্ব এবং ঈমানের সাথে সত্যবাদিতার সম্পর্ক বুঝে নিন।"},"heading":{"title":"মিথ্যা থেকে বাঁচার হাদিস: ঈমানের জন্য সততার প্রয়োজন","description":"এই বর্ণনায় মিথ্যা থেকে বেঁচে থাকার কঠিন সতর্কতা এসেছে। বলা হয়েছে, মিথ্যা ঈমানকে ক্ষতিগ্রস্ত করে। কথাটি ছোট হলেও খুব গভীর। অনেক সময় মানুষ মিথ্যাকে হালকা ভাবে নেয়—মজা করে, সুবিধার জন্য, লজ্জা ঢাকতে বা সম্পর্ক বাঁচাতে। কিন্তু হাদিসের শিক্ষা হলো, মিথ্যা মানুষের ভেতরের ঈমানি শক্তিকে দুর্বল করে। সত্য বলা সব সময় সহজ না-ও হতে পারে, কিন্তু মিথ্যার পথে অভ্যাস তৈরি হলে তা চরিত্রকে নষ্ট করে। তাই মুমিনের জন্য সত্যবাদিতা শুধু সামাজিক ভালো গুণ নয়; এটি ঈমান রক্ষার সাথে জড়িত একটি বড় বিষয়।"},"teachings":["মিথ্যা ঈমানের ক্ষতির কারণ হতে পারে।","মিথ্যাকে ছোট বা হালকা বিষয় ভাবা উচিত নয়।","সত্যবাদিতা ঈমানি চরিত্রের অংশ।","সুবিধার জন্য মিথ্যা বলা থেকে বাঁচতে হবে।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2607","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"4990","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E134" s="4" t="n"/>
@@ -3674,15 +3586,19 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম রিজিক দোয়ার পথে বাধা","description":"$book_name$ $hadith_number$ - $chapter_name$. সফরে ক্লান্ত অবস্থায় দোয়া করলেও খাদ্য, পানীয়, পোশাক ও জীবিকা হারাম হলে দোয়া কবুলের প্রশ্ন ওঠে।"},"heading":{"title":"হারাম রিজিক দোয়ার পথে বাধা: হালাল জীবিকা কেন দরকার","description":"এই হাদিসে দোয়ার একটি গুরুত্বপূর্ণ দিক তুলে ধরা হয়েছে। একজন মানুষ দূর-দূরান্তে সফর করছে, চুল এলোমেলো, শরীরে ধুলা-বালি, দুই হাত আসমানের দিকে তুলে কাতরভাবে বলছে, হে প্রভু! হে প্রভু! বাহ্যিকভাবে এটি দোয়ার বিনয়ী অবস্থা। কিন্তু হাদিসে বলা হলো, তার খাদ্য হারাম, পানীয় হারাম, পোশাক হারাম এবং জীবিকা হারাম; তাহলে তার দোয়া কীভাবে কবুল হবে? তাই হারাম রিজিক দোয়ার পথে বড় বাধা হতে পারে। এই শিক্ষা আমাদের দৈনন্দিন জীবনে খুব দরকার। আমরা শুধু দোয়া বাড়াব না, বরং খাবার, পোশাক ও আয়ের উৎসও পবিত্র রাখার চেষ্টা করব। হালাল জীবিকা ইবাদতের সৌন্দর্য বাড়ায়।"},"teachings":["দোয়ার সঙ্গে হালাল জীবিকার সম্পর্ক আছে।","বাহ্যিক বিনয় থাকলেও হারাম রিজিক বড় বাধা হতে পারে।","খাদ্য, পানীয়, পোশাক ও আয়—সব ক্ষেত্রেই সতর্কতা দরকার।","আল্লাহ পবিত্র, তাই পবিত্র উপায় পছন্দনীয়।"],"related_hadiths":[{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1205","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="n"/>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিশুকে মিথ্যা প্রতিশ্রুতি না দেওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুকে “আসো নাও” বলে কিছু না দিলে সেটিও মিথ্যা—এই নববী শিক্ষা জানুন।"},"heading":{"title":"শিশুকে মিথ্যা কথা নয়: ছোট প্রতিশ্রুতিতেও সত্যের শিক্ষা","description":"এই হাদিসে শিশুদের সাথে সত্যবাদিতার শিক্ষা এসেছে। কেউ যদি বাচ্চাকে বলে, “আসো নাও”, কিন্তু পরে তাকে কিছু না দেয়, তাহলে সেটিকে মিথ্যা বলা হয়েছে। এতে বোঝা যায়, শিশুর সাথে কথাবার্তাও দ্বীনের বাইরে নয়। অনেক সময় বড়রা শিশুকে শান্ত করার জন্য বা কাছে ডাকার জন্য এমন কথা বলে যা পরে রাখে না। হাদিসটি শেখায়, শিশুকে ছোট মনে করে তার সাথে মিথ্যা বলা ঠিক নয়। কারণ শিশু বড়দের কথায় বিশ্বাস করতে শেখে। যদি বড়রা কথা না রাখে, তাহলে শিশুর মনেও মিথ্যার স্বাভাবিক ধারণা তৈরি হতে পারে। তাই সন্তানের সামনে সত্য কথা ও কথা রাখার অভ্যাস জরুরি।"},"teachings":["শিশুকে মিথ্যা প্রতিশ্রুতি দেওয়া থেকে বাঁচতে হবে।","ছোট কথাতেও সত্যবাদিতা দরকার।","বড়দের আচরণ শিশুদের শেখার মাধ্যম।","কথা দিলে তা রাখার চেষ্টা করা উচিত।"],"related_hadiths":[{"id":"4991","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>related_hadiths[1]: unknown book label "সূরা আস-সফ ৬১:২-৩ (প্রাসঙ্গিক আয়াত)"</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="46" customHeight="1">
       <c r="A136" s="4" t="inlineStr">
@@ -3697,12 +3613,12 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হালাল-হারাম আয়ের যুগসতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. এমন যুগ আসবে যখন মানুষ সম্পদ কীভাবে পেল তা দেখবে না; মুসলিমের জন্য হালাল উৎস যাচাই অপরিহার্য।"},"heading":{"title":"হালাল-হারাম আয়ের সতর্কতা: সম্পদ পেলেই যথেষ্ট নয়","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) এমন এক সময়ের কথা বলেছেন, যখন মানুষ পরোয়া করবে না—সে কী উপায়ে মাল পেল, হারাম পথে নাকি হালাল পথে। এর মানে হলো, আয়ের পরিমাণকে মানুষ অনেক সময় আয়ের বৈধতার চেয়ে বড় করে দেখে। কিন্তু মুমিনের জন্য শুধু সম্পদ পাওয়া লক্ষ্য নয়। হালাল হারাম আয় যাচাই করা ঈমানি দায়িত্বের অংশ। ব্যবসায় প্রতারণা, অন্যের হক, অবৈধ চুক্তি, সন্দেহজনক লেনদেন—এসব বিষয় থেকে সতর্ক থাকা দরকার। হাদিসটি আমাদের সমাজের চাপের মাঝেও আল্লাহর ভয় ধরে রাখতে শেখায়। টাকা আসছে কি না—এ প্রশ্নের সঙ্গে আরেকটি প্রশ্ন দরকার: এই টাকা হালালভাবে আসছে কি না?"},"teachings":["সম্পদ পাওয়ার উপায় বৈধ কি না তা যাচাই করতে হবে।","সময়ের খারাপ প্রবণতার সঙ্গে ভেসে যাওয়া উচিত নয়।","হালাল আয় মুমিনের নৈতিক পরিচয়ের অংশ।","হারাম আয়ের ব্যাপারে উদাসীনতা বড় ক্ষতির কারণ হতে পারে।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1205","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্তানকে দেওয়া কথাও রাখতে হবে","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুকে কিছু দেওয়ার কথা বলে না দিলে মিথ্যা লেখা হয়—এই শিক্ষামূলক হাদিস পড়ুন।"},"heading":{"title":"সন্তানকে দেওয়া প্রতিশ্রুতি: খেজুরের ঘটনায় সত্যবাদিতার শিক্ষা","description":"এই হাদিসে একটি ঘরোয়া ঘটনা এসেছে। আবদুল্লাহ ইবনে আমির রাদিয়াল্লাহু আনহুকে তাঁর মা ডাকলেন এবং বললেন, আসো, তোমাকে কিছু দেব। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম তখন তাঁদের ঘরে ছিলেন। তিনি জিজ্ঞেস করলেন, তুমি তাকে কী দিতে চাও? মা বললেন, খেজুর দেব। তখন নবীজি জানালেন, যদি কিছু না দাও, তবে তা মিথ্যা হিসেবে লেখা হবে। এই হাদিস আমাদের শেখায়, সন্তানকে দেওয়া ছোট প্রতিশ্রুতিও হালকা নয়। মা-বাবা যদি কথা রাখে, শিশু সত্য ও আস্থার পরিবেশে বড় হয়। আর কথা না রাখলে শিশুর মনেও মিথ্যা সহজ হয়ে যেতে পারে।"},"teachings":["সন্তানকে দেওয়া কথাও গুরুত্বের সাথে রাখা দরকার।","শিশুকে ডাকার জন্য মিথ্যা বলা উচিত নয়।","ছোট প্রতিশ্রুতিও মিথ্যা বা সত্যের অংশ হতে পারে।","মা-বাবার সত্যবাদিতা সন্তানের চরিত্র গঠনে সাহায্য করে।"],"related_hadiths":[{"id":"4991","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4990","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E136" s="4" t="n"/>
@@ -3720,12 +3636,12 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক বিষয় ও অন্তরের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহজনক বিষয় ছাড়লে দ্বীন ও সম্মান নিরাপদ থাকে; অন্তর ভালো থাকলে জীবনও সঠিক পথে থাকে।"},"heading":{"title":"সন্দেহজনক বিষয় থেকে বাঁচুন: হালাল-হারামের নিরাপদ পথ","description":"এই হাদিসে হালাল, হারাম এবং সন্দেহজনক বিষয়ের সম্পর্ক পরিষ্কার করা হয়েছে। হালাল সুস্পষ্ট, হারামও সুস্পষ্ট। কিন্তু কিছু বিষয় আছে, যেগুলো সম্পর্কে অনেকেই সিদ্ধান্ত নিতে পারে না। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে ব্যক্তি সন্দেহের বস্তুকে পরিহার করে, তার দ্বীন ও সম্মান পরিষ্কার থাকে। আর যে সন্দেহজনক কাজে জড়ায়, সে হারামে পড়ে যেতে পারে। রাখালের উদাহরণটি খুব সহজ: নিষিদ্ধ এলাকার ধারে পশু চরালে ভেতরে ঢুকে পড়ার ভয় থাকে। তাই নিরাপদ পথ হলো হারামের কাছাকাছি না যাওয়া। হাদিসের শেষে অন্তরের গুরুত্ব এসেছে। অন্তর ভালো থাকলে জীবন ভালো দিকে যায়, আর অন্তর নষ্ট হলে কাজও নষ্ট হতে থাকে।"},"teachings":["সন্দেহজনক বিষয় এড়িয়ে চলা নিরাপদ পথ।","হারামের সীমানার কাছাকাছি গেলে পড়ে যাওয়ার ভয় থাকে।","দ্বীন ও সম্মান রক্ষায় সতর্কতা দরকার।","অন্তর ঠিক রাখা আচরণ ঠিক রাখার বড় মাধ্যম।"],"related_hadiths":[{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2059","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"593","book_id":"8","slug":"riyadus-salihin","label":"রিয়াদুস সালেহীন"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হাসানোর জন্য মিথ্যা বলার ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মানুষকে হাসানোর জন্য মিথ্যা বলা নিয়ে নবীজির কঠিন সতর্ক বাণী জানুন।"},"heading":{"title":"হাসানোর জন্য মিথ্যা বলা: মজার কথাতেও সত্যের গুরুত্ব","description":"এই হাদিসে সেই ব্যক্তির জন্য কঠিন সতর্কতা এসেছে, যে মানুষকে হাসানোর জন্য মিথ্যা কথা বলে। নবীজি বলেছেন, তার জন্য ধ্বংস, তার জন্য ধ্বংস। কথাটি আমাদের দৈনন্দিন জীবনের একটি সাধারণ ভুল ধরিয়ে দেয়। অনেক সময় আড্ডা, গল্প, বক্তৃতা বা অনলাইনে মানুষ হাসানোর জন্য বানানো কথা বলে। কেউ ভাবতে পারে, এটি তো শুধু মজা। কিন্তু হাদিস দেখাচ্ছে, মজার নামেও মিথ্যা হালকা নয়। সত্যবাদিতা শুধু গুরুতর আলোচনায় দরকার নয়; হাসি-ঠাট্টাতেও দরকার। মুমিনের কথা এমন হওয়া উচিত, যাতে মানুষ আনন্দ পেলেও মিথ্যা বা ধোঁকার ওপর দাঁড়িয়ে না থাকে।"},"teachings":["মানুষকে হাসানোর জন্য মিথ্যা বলা থেকে বাঁচতে হবে।","মজা করেও মিথ্যা বলা হালকা বিষয় নয়।","আড্ডা ও গল্পেও সত্যবাদিতা দরকার।","কথার মাধ্যমে মানুষকে আনন্দ দিতে হলে মিথ্যা ছাড়াই দেওয়া উচিত।"],"related_hadiths":[{"id":"4990","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4800","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E137" s="4" t="n"/>
@@ -3743,12 +3659,12 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঘৃণিত উপার্জন থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. কুকুর বিক্রয়, ব্যভিচারের বিনিময় ও সিঙ্গা লাগানোর মূল্যকে ঘৃণিত বলা হয়েছে; উপার্জনে সতর্কতা দরকার।"},"heading":{"title":"ঘৃণিত উপার্জন: কুকুর বিক্রয় ও অনৈতিক আয়ের সতর্কতা","description":"এই হাদিসে কয়েক ধরনের উপার্জনকে ঘৃণিত বলা হয়েছে। কুকুর বিক্রয়ের মূল্য, ব্যভিচারের বিনিময় এবং সিঙ্গা লাগানোর মূল্য—এই তিনটি বিষয় হাদিসে এসেছে। এখানে মূল শিক্ষা হলো, উপার্জনের সব পথ সমান নয়। টাকা পাওয়া গেলেই তা ভালো উপার্জন হয়ে যায় না। ঘৃণিত উপার্জন হাদিস আমাদের আয়ের উৎস নিয়ে সতর্ক করে। বিশেষ করে ব্যভিচারের বিনিময়ের মতো অনৈতিক আয়ের কথা স্পষ্টভাবে এসেছে। কুকুর বিক্রয়ের মূল্য ও সিঙ্গা লাগানোর মূল্য সম্পর্কেও হাদিসে সতর্ক ভাষা ব্যবহৃত হয়েছে। তাই মুসলিমের জন্য উপার্জনের ক্ষেত্রে শুধু লাভ নয়, শরিয়তের দৃষ্টিতে তা পরিষ্কার কি না—এটাও দেখা দরকার।"},"teachings":["সব ধরনের আয় গ্রহণযোগ্য নয়।","অনৈতিক কাজের বিনিময় ঘৃণিত উপার্জনের মধ্যে পড়ে।","উপার্জনের উৎস নিয়ে সতর্ক থাকা দরকার।","লাভের আগে হালাল-হারাম বিচার করা জরুরি।"],"related_hadiths":[{"id":"2237","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2282","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5962","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর কঠিন পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. বৃদ্ধ ব্যভিচারী, মিথ্যুক শাসক ও অহংকারী গরীব সম্পর্কে কিয়ামতের কঠিন সতর্কতা জানুন।"},"heading":{"title":"মিথ্যুক শাসকসহ তিন শ্রেণীর মানুষের কঠিন সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের কথা এসেছে, যাদের ব্যাপারে কিয়ামতের দিন কঠিন সতর্কতা দেওয়া হয়েছে। তারা হলো বৃদ্ধ ব্যভিচারকারী, মিথ্যুক শাসক এবং অহংকারী গরীব। হাদিসে বলা হয়েছে, আল্লাহ তাদের সাথে কথা বলবেন না, তাদের পবিত্র করবেন না, দয়ার দৃষ্টিতে তাকাবেন না এবং তাদের জন্য কষ্টদায়ক শাস্তি রয়েছে। এখানে বিশেষভাবে মিথ্যুক শাসকের কথা আমাদের দায়িত্ব ও ক্ষমতার জায়গায় সত্যের গুরুত্ব বুঝায়। যার হাতে নেতৃত্ব বা ক্ষমতা আছে, তার মিথ্যা শুধু নিজের ক্ষতি করে না; অন্যদেরও ক্ষতিগ্রস্ত করতে পারে। আর অহংকার ও পাপ যেকোন অবস্থায় ভয়ংকর বিষয়।"},"teachings":["মিথ্যুক শাসকের বিষয়ে হাদিসে কঠিন সতর্কতা এসেছে।","ক্ষমতা থাকলে সত্যবাদিতা আরও বেশি জরুরি।","অহংকার ও পাপ মানুষকে কঠিন পরিণতির দিকে নিতে পারে।","বয়স, পদ বা দারিদ্র্য কোনো পাপকে হালকা করে না।"],"related_hadiths":[{"id":"107","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"91","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E138" s="4" t="n"/>
@@ -3766,12 +3682,12 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নিষিদ্ধ আয়ের তিনটি পথ","description":"$book_name$ $hadith_number$ - $chapter_name$. কুকুরের মূল্য, যিনাকারীনীর উপার্জন ও গণকের উপার্জন খেতে নিষেধ করা হয়েছে; রিজিকে পবিত্রতা জরুরি।"},"heading":{"title":"নিষিদ্ধ আয় থেকে বাঁচুন: কুকুরের মূল্য, যিনা ও গণকের উপার্জন","description":"এই হাদিসে তিনটি উপার্জন খেতে নিষেধ করা হয়েছে: কুকুরের মূল্য, যিনাকারীনীর উপার্জন এবং গণকের উপার্জন। হাদিসটি খুব পরিষ্কারভাবে শেখায়, আয়ের উৎস ভালো না হলে সেই আয় গ্রহণ করা উচিত নয়। নিষিদ্ধ আয় শুধু ব্যক্তির পকেটে আসে না; তা খাবার, পরিবার ও জীবনের ওপরও প্রভাব ফেলে। বিশেষ করে যিনা-ভিত্তিক উপার্জন ও গণকের উপার্জন মানুষের নৈতিকতা ও বিশ্বাসের সঙ্গে জড়িত। কুকুরের মূল্য সম্পর্কেও স্পষ্ট নিষেধ এসেছে। তাই মুসলিমের জন্য উপার্জনের ক্ষেত্রে সতর্ক থাকা জরুরি। কোন কাজ থেকে আয় হচ্ছে, তা আল্লাহর নাফরমানির সঙ্গে যুক্ত কি না—এই প্রশ্ন নিজের কাছে রাখা দরকার।"},"teachings":["কুকুরের মূল্য খেতে নিষেধ করা হয়েছে।","যিনাকারীনীর উপার্জন গ্রহণযোগ্য নয়।","গণকের উপার্জন থেকে বাঁচতে বলা হয়েছে।","রিজিক পবিত্র রাখতে আয়ের উৎস যাচাই করা দরকার।"],"related_hadiths":[{"id":"5962","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5761","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শেষ যামানার মিথ্যাবাদী দাজ্জালদের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শেষ যামানায় মিথ্যাবাদীরা নতুন কথা ছড়াবে; তাদের থেকে দূরে থেকে পথভ্রষ্টতা থেকে বাঁচতে বলা হয়েছে।"},"heading":{"title":"শেষ যামানার মিথ্যাবাদী দাজ্জাল থেকে বাঁচার সতর্কতা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) শেষ যামানার কিছু মিথ্যাবাদী দাজ্জালের কথা বলেছেন। তারা এমন সব কথা নিয়ে আসবে, যা মানুষ আগে শোনেনি এবং তাদের বাপ-দাদারাও শোনেনি। নবীজি স্পষ্টভাবে সাবধান করেছেন: তোমরা তাদের থেকে বেঁচে থাকো এবং তাদেরকে তোমাদের থেকে দূরে রাখো। কারণ তারা মানুষকে পথভ্রষ্ট করতে পারে এবং ফিতনায় ফেলতে পারে। এই হাদিসে মিথ্যা কথা, অদ্ভুত দাবি ও বিভ্রান্তির বিরুদ্ধে সতর্ক থাকার শিক্ষা আছে। নতুন কথা শুনলেই গ্রহণ করা ঠিক নয়। দ্বীনের বিষয়ে সত্য-মিথ্যা যাচাই, নিরাপদ থাকা এবং বিভ্রান্ত লোকদের প্রভাব থেকে দূরে থাকা খুব দরকার।"},"teachings":["শেষ যামানায় মিথ্যাবাদী লোকদের ব্যাপারে সতর্ক থাকতে হবে।","অচেনা ও ভিত্তিহীন কথা শুনে সহজে গ্রহণ করা উচিত নয়।","ভ্রান্ত কথা মানুষকে ফিতনায় ফেলতে পারে।","দ্বীনের বিষয়ে নিরাপদ থাকতে সত্য যাচাই করা দরকার।"],"related_hadiths":[{"id":"7","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"154","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"4333","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E139" s="4" t="n"/>
@@ -3789,12 +3705,12 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আব্দুল ক্বায়েস প্রতিনিধিদলের ঈমান শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আব্দুল ক্বায়েস প্রতিনিধিদলকে ঈমান, সালাত, যাকাত, রমযানের সিয়াম ও খুমুসের শিক্ষা দেওয়া হয়।"},"heading":{"title":"আব্দুল ক্বায়েস প্রতিনিধিদল ও ঈমানের মূল আমল","description":"এই হাদিসে আব্দুল ক্বায়েস গোত্রের প্রতিনিধিদলের ঘটনা এসেছে। তারা রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কাছে এসে এমন পরিষ্কার নির্দেশ চাইলো, যা তারা নিজেদের লোকদের জানাতে পারে এবং যার মাধ্যমে জান্নাতে প্রবেশের আশা রাখতে পারে। নবীজি তাদেরকে চারটি বিষয়ে নির্দেশ দেন: এক আল্লাহর উপর ঈমান, সালাত কায়েম, যাকাত আদায়, রমযানের সিয়াম এবং গানীমতের এক পঞ্চমাংশ জমা দেওয়া। তিনি কিছু পাত্র থেকেও নিষেধ করেন, যেগুলো শরাব তৈরির সঙ্গে যুক্ত ছিল। এই হাদিসে ঈমানের মূল আমল, শিক্ষা গ্রহণ ও অন্যদের কাছে দ্বীনের কথা পৌঁছে দেওয়ার গুরুত্ব আছে। সাহাবীরা শুধু শুনতে আসেননি; তারা আমল করতে ও অন্যদের জানাতে চেয়েছেন।"},"teachings":["দ্বীনের পরিষ্কার শিক্ষা জানা ও মানা দরকার।","ঈমানের সঙ্গে সালাত, যাকাত ও রমযানের সিয়াম জড়িত।","যা শেখা হয়, তা নিজের লোকদের জানানো ভালো কাজ।","নিষিদ্ধ জিনিসের উপায় থেকেও সতর্ক থাকতে হয়।"],"related_hadiths":[{"id":"53","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"17","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"17","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দুই মুখের মানুষের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. দুনিয়ায় দ্বিমুখী আচরণকারীর কিয়ামতের ভয়াবহ পরিণতি সম্পর্কে হাদিসের শিক্ষা জানুন।"},"heading":{"title":"দ্বিমুখী চরিত্রের হাদিস: এক মুখে এক কথা, আরেক মুখে আরেক কথা নয়","description":"এই হাদিসে বলা হয়েছে, যার দুনিয়াতে দু’টি মুখ হবে, কিয়ামতের মাঠে তার মুখে আগুনের দু’টি জিহ্বা হবে। অর্থাৎ যে মানুষ একদলের সামনে এক কথা বলে, অন্য দলের সামনে উল্টো কথা বলে এবং মিথ্যা, চোগলখুরী বা পরনিন্দার মাধ্যমে সম্পর্ক নষ্ট করে—তার বিষয়ে কঠিন সতর্কতা এসেছে। দ্বিমুখী চরিত্র মানুষের আস্থা নষ্ট করে। এতে বন্ধু, পরিবার ও সমাজে ঝগড়া বাড়ে। মুমিনের কথা সোজা হওয়া উচিত। সে কারও সামনে এমন কথা বলবে না, যা অন্যের সামনে গিয়ে বদলে ফেলে। এই হাদিস আমাদের সত্যবাদী, পরিষ্কার এবং ভরসাযোগ্য হতে শেখায়।"},"teachings":["দ্বিমুখী আচরণের বিষয়ে হাদিসে কঠিন সতর্কতা এসেছে।","একজনের সামনে এক কথা, অন্যজনের সামনে আরেক কথা বলা ক্ষতিকর।","চোগলখুরী ও পরনিন্দা সম্পর্ক নষ্ট করে।","মুমিনের কথা পরিষ্কার ও বিশ্বাসযোগ্য হওয়া দরকার।"],"related_hadiths":[{"id":"4873","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6056","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2606","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E140" s="4" t="n"/>
@@ -3812,12 +3728,12 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম উপার্জন ও অভিশপ্ত কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. রক্ত, কুকুর ও ব্যভিচারের আয় নিষিদ্ধ; সুদ, উল্কি ও ছবি অঙ্কনের ব্যাপারেও কঠিন সতর্কতা এসেছে।"},"heading":{"title":"হারাম উপার্জন ও নিষিদ্ধ কাজ: রক্ত, সুদ, উল্কি ও ছবি নিয়ে সতর্কতা","description":"এই হাদিসে কয়েকটি বিষয় একসঙ্গে এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) রক্ত বিক্রয়ের মূল্য, কুকুর বিক্রয়ের মূল্য এবং ব্যভিচারের বিনিময় থেকে নিষেধ করেছেন। এরপর সুদ গ্রহীতা ও সুদদাতার প্রতি লা’নতের কথা এসেছে। আরও বলা হয়েছে, যে উল্কি করে এবং যে উল্কি করায়, তাদের ওপরও লা’নত করা হয়েছে। ছবি অঙ্কনকারীর প্রতিও লা’নতের কথা এসেছে। তাই হারাম উপার্জন হাদিস আমাদের আয়ের উৎস এবং কিছু কাজের ব্যাপারে গভীর সতর্ক করে। এখানে অযথা বাড়তি ব্যাখ্যা না করে মূল বার্তাই স্পষ্ট: মুসলিমকে এমন আয় ও কাজ থেকে দূরে থাকতে হবে, যেগুলোর ব্যাপারে নবী (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কঠিন নিষেধ দিয়েছেন।"},"teachings":["রক্ত, কুকুর ও ব্যভিচারের বিনিময় থেকে নিষেধ করা হয়েছে।","সুদ গ্রহণ ও সুদ দেওয়া—দুটির ব্যাপারেই কঠিন সতর্কতা এসেছে।","উল্কি করা ও করানো থেকে বাঁচতে বলা হয়েছে।","নিষিদ্ধ আয়ের সঙ্গে নিষিদ্ধ কাজ থেকেও দূরে থাকা দরকার।"],"related_hadiths":[{"id":"2237","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2282","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2236","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবীরা গুনাহ থেকে বাঁচার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, হত্যা ও মিথ্যা কসম বা সাক্ষ্যের ভয়াবহতা বুঝুন।"},"heading":{"title":"কবীরা গুনাহ: শিরক, অবাধ্যতা, হত্যা ও মিথ্যার ভয়াবহ শিক্ষা","description":"এই হাদিসে বড় বড় কবীরা গুনাহের কয়েকটি স্পষ্ট উদাহরণ বলা হয়েছে। মূল বিষয় হলো, মানুষের ঈমান, পরিবার, জীবন ও কথার সততা—সবকিছু আল্লাহর কাছে গুরুত্বপূর্ণ। আল্লাহর সাথে কাউকে শরীক করা সবচেয়ে বড় অন্যায় হিসেবে এসেছে। এরপর পিতা-মাতার অবাধ্যতা বলা হয়েছে, যা পরিবার ও দায়িত্ববোধের সাথে জড়িত। কাউকে হত্যা করা মানুষের জীবনের অধিকার নষ্ট করে। আর মিথ্যা কসম বা মিথ্যা সাক্ষ্য মানুষের বিশ্বাস, বিচার ও সম্পর্ককে ক্ষতিগ্রস্ত করে। তাই এই হাদিস আমাদের শেখায়, বড় গুনাহ থেকে দূরে থাকতে হলে ঈমানকে শুদ্ধ রাখা, বাবা-মায়ের হক মানা, মানুষের জীবনকে সম্মান করা এবং কথায় সত্যবাদী থাকা জরুরি।"},"teachings":["আল্লাহর সাথে কাউকে শরীক করা বড় কবীরা গুনাহের অন্তর্ভুক্ত।","পিতা-মাতার অবাধ্যতা থেকে সতর্ক থাকা দরকার।","অন্যায়ভাবে কাউকে হত্যা করা ভয়াবহ গুনাহ।","মিথ্যা কসম ও মিথ্যা সাক্ষ্য মানুষের হক নষ্ট করতে পারে।"],"related_hadiths":[{"id":"161","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"162","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6871","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E141" s="4" t="n"/>
@@ -3835,12 +3751,12 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম উপার্জনের ভয়াবহ পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম মালে গড়া দেহের ভয়াবহ পরিণতি জানুন এবং হালাল রুজির পথে চলার শিক্ষা নিন।"},"heading":{"title":"হালাল রুজি ও হারাম উপার্জন: মুমিনের জীবনে সতর্কতার শিক্ষা","description":"এই হাদিসে হারাম উপার্জন সম্পর্কে খুব স্পষ্ট সতর্কতা এসেছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে দেহের গোশত হারাম মালে গঠিত, তা জান্নাতে প্রবেশ করতে পারবে না। কথাটি আমাদের খাবার, আয়, ব্যবসা ও লেনদেন নিয়ে ভাবতে শেখায়। শুধু টাকা হাতে এলেই তা ভালো হয়ে যায় না; টাকা কোথা থেকে এল, সেটাও বড় বিষয়। হালাল রুজি মুমিনের জীবনকে নিরাপদ পথে রাখে। আর হারাম মাল শরীরকে পুষ্ট করলেও তা আখিরাতের জন্য ভয়ংকর ক্ষতির কারণ হতে পারে। তাই এই হাদিসের মূল শিক্ষা হলো, আয়-রোজগারে সাবধান থাকা, সন্দেহজনক পথ এড়িয়ে চলা এবং নিজের পরিবারকে হালাল খাবার খাওয়ানোর চেষ্টা করা।"},"teachings":["হারাম উপার্জনে গড়া দেহের জন্য হাদিসে কঠিন সতর্কতা এসেছে।","খাবার ও আয় হালাল কি না, তা মুমিনের জন্য গুরুত্বপূর্ণ বিষয়।","পরিবারকে হালাল রুজি খাওয়ানো ঈমানি দায়িত্বের অংশ।","মাল বেশি হওয়া নয়, মাল হালাল হওয়াই আসল নিরাপত্তার পথ।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1599","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2760","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিকের তিন আলামত","description":"$book_name$ $hadith_number$ - $chapter_name$. মিথ্যা বলা, ওয়াদা ভঙ্গ ও আমানতে খিয়ানত—মুনাফিকের তিন আলামত সম্পর্কে সহজ শিক্ষা।"},"heading":{"title":"মুনাফিকের আলামত: মিথ্যা, ওয়াদা ভঙ্গ ও আমানতে খিয়ানত","description":"এই হাদিসে মুনাফিকের আলামত তিনটি বলা হয়েছে। যখন সে কথা বলে, মিথ্যা বলে; ওয়াদা করলে তা ভঙ্গ করে; আর আমানত রাখা হলে খিয়ানত করে। এখানে ইসলাম মানুষের বাহ্যিক ইবাদতের পাশাপাশি চরিত্রকেও গুরুত্ব দিয়েছে। মুসলিমের পরিচয় শুধু সালাত বা সিয়ামের মধ্যে সীমিত নয়; কথার সত্যতা, প্রতিশ্রুতি রক্ষা এবং আমানতের দায়িত্বও তার জীবনের অংশ। মুসলিমের বর্ণনায় এসেছে, কেউ সালাত আদায় করলেও, সিয়াম পালন করলেও এবং নিজেকে মুসলিম মনে করলেও এই খারাপ গুণগুলো খুব বিপজ্জনক। তাই এই হাদিস আমাদের নিজের কথা, প্রতিশ্রুতি ও দায়িত্ব নিয়ে নিয়মিত ভাবতে শেখায়।"},"teachings":["মিথ্যা বলা মুনাফিকী স্বভাবের একটি বড় আলামত।","ওয়াদা করলে তা রক্ষা করা মুসলিম চরিত্রের অংশ।","অমানত রাখা হলে তা সঠিকভাবে ফিরিয়ে দেওয়া দরকার।","ইবাদতের পাশাপাশি চরিত্র ঠিক রাখা জরুরি।"],"related_hadiths":[{"id":"114","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"116","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2631","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E142" s="4" t="n"/>
@@ -3858,12 +3774,12 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক কাজ ছেড়ে নিশ্চিত পথে চলা","description":"$book_name$ $hadith_number$ - $chapter_name$. মনে খটকা লাগা কাজ ছেড়ে পরিষ্কার ও শান্তির পথে চলার সুন্দর নববী শিক্ষা জানুন।"},"heading":{"title":"সন্দেহজনক কাজ থেকে বাঁচার হাদিস: সত্যে শান্তি, মিথ্যায় খটকা","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম একটি সহজ কিন্তু গভীর নিয়ম শিখিয়েছেন। যে কাজে মনে খটকা লাগে, সে কাজ ছেড়ে এমন কাজ বেছে নিতে বলা হয়েছে যাতে খটকা নেই। মানুষের অন্তর অনেক সময় ভুল ও ঠিকের মাঝে অস্বস্তি টের পায়। হাদিসটি বলে, সত্য ও শুদ্ধ জিনিস সাধারণত অন্তরে প্রশান্তি আনে, আর মিথ্যা ও অশুদ্ধ জিনিস দ্বিধা তৈরি করে। তাই সন্দেহজনক কাজ এড়িয়ে চলা শুধু ইবাদতের বিষয় নয়; এটি চরিত্র, কথা, ব্যবসা ও সম্পর্কের ক্ষেত্রেও দরকারি। এই শিক্ষা মানুষকে নিরাপদ, পরিষ্কার এবং সৎ পথে চলতে সাহায্য করে।"},"teachings":["যে কাজে মনে খটকা লাগে, তা ছেড়ে দেওয়া ভালো।","সত্য অন্তরে প্রশান্তি আনে, মিথ্যা দ্বিধা সৃষ্টি করে।","সন্দেহজনক কাজ থেকে দূরে থাকা দ্বীন রক্ষার পথ।","কথা ও কাজে পরিষ্কার অবস্থান নেওয়া মুমিনের গুণ।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1599","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2553","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিকীর চার স্বভাব","description":"$book_name$ $hadith_number$ - $chapter_name$. খিয়ানত, মিথ্যা, ওয়াদা ভঙ্গ ও ঝগড়ায় অশ্লীলতা—মুনাফিকী স্বভাব থেকে বাঁচার শিক্ষা।"},"heading":{"title":"মুনাফিকীর চার স্বভাব: নিজের চরিত্র যাচাই করার হাদিস","description":"এই হাদিসে চারটি স্বভাবের কথা এসেছে, যা মানুষের চরিত্রকে খুব ক্ষতিগ্রস্ত করে। আমানত রাখা হলে খিয়ানত করা, কথা বললে মিথ্যা বলা, ওয়াদা করলে ভঙ্গ করা এবং ঝগড়ার সময় অশ্লীল ভাষা ব্যবহার করা—এগুলোকে মুনাফিকী স্বভাব বলা হয়েছে। হাদিসে আরও বলা হয়েছে, যার মধ্যে এসবের একটি থাকবে, সে তা না ছাড়লে তার মধ্যে মুনাফিকীর একটি স্বভাব থাকবে। এখানে মূল শিক্ষা হলো আত্মপরীক্ষা। আমরা অনেক সময় নিজেদের ভালো মনে করি, কিন্তু কথা, প্রতিশ্রুতি, আমানত ও রাগের সময় ভাষা—এসব জায়গায় ভুল করি। তাই এই হাদিস মানুষকে নিজের আচরণ ঠিক করতে নরম কিন্তু শক্ত সতর্কতা দেয়।"},"teachings":["আমানতে খিয়ানত করা মুনাফিকী স্বভাবের অন্তর্ভুক্ত।","মিথ্যা কথা মানুষের ঈমানী চরিত্রকে দুর্বল করে।","চুক্তি বা ওয়াদা ভঙ্গ করা গুরুতর খারাপ অভ্যাস।","ঝগড়ার সময় অশ্লীল ভাষা থেকে দূরে থাকা দরকার।"],"related_hadiths":[{"id":"34","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"113","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2632","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E143" s="4" t="n"/>
@@ -3881,19 +3797,15 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গায়িকা কেনাবেচা ও হারাম মূল্য","description":"$book_name$ $hadith_number$ - $chapter_name$. গায়িকা ক্রয়-বিক্রয়, গান শেখানো ও তার মূল্য সম্পর্কে হাদিসের সতর্ক বার্তা জানুন।"},"heading":{"title":"গায়িকা ক্রয়-বিক্রয় ও হারাম উপার্জন নিয়ে হাদিসের শিক্ষা","description":"এই হাদিসে গায়িকা ক্রয়-বিক্রয়, তাদের গান শেখানো এবং এ ধরনের কাজে পাওয়া মূল্য সম্পর্কে কঠোরভাবে নিষেধ এসেছে। হাদিসের ভাষায় তাদের মূল্য হারাম বলা হয়েছে। এখানে মূল শিক্ষা হলো, বিনোদনের নামে এমন কাজে জড়ানো থেকে বাঁচা যা মানুষকে আল্লাহর পথ থেকে দূরে নিতে পারে। অনুবাদে কুরআনের একটি আয়াতের কথাও এসেছে, যেখানে রং-তামাশার গাথা কেনার কথা বলা হয়েছে। তাই এই হাদিস শুধু গান-বাজনা নিয়ে নয়; বরং এমন আয়ের পথ নিয়েও সতর্ক করে, যা দ্বীন ও চরিত্রের ক্ষতি করতে পারে। একজন মুমিনের উচিত নিজের আয় ও বিনোদন—দুটো ক্ষেত্রেই আল্লাহভীতি রাখা।"},"teachings":["গায়িকা ক্রয়-বিক্রয় ও গান শেখানোর বিষয়ে হাদিসে নিষেধ এসেছে।","এ ধরনের কাজের মূল্যকে হাদিসে হারাম বলা হয়েছে।","বিনোদন যেন দ্বীন থেকে দূরে নেওয়ার কারণ না হয়।","আয়ের উৎস হালাল কি না, তা যাচাই করা জরুরি।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4020","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[2]: unknown book label "ঊপদেশ ১০১ (প্রাসঙ্গিক বর্ণনা)"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জিহ্বা সংযমের গুরুত্ব","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূল صلى الله عليه وسلم জিহ্বার দিকে ইঙ্গিত করে কথার বিপদ থেকে সতর্ক করেছেন—এ হাদিসের সহজ শিক্ষা।"},"heading":{"title":"জিহ্বা সংযম: কথার কারণে বিপদে পড়া থেকে বাঁচার শিক্ষা","description":"এই হাদিসে একজন সাহাবী রাসূলুল্লাহ صلى الله عليه وسلم-কে জিজ্ঞেস করেন, তাঁর জন্য সবচেয়ে বেশি ভয়ের বিষয় কী। রাসূল صلى الله عليه وسلم নিজের জিহ্বা ধরলেন এবং বললেন, এটি। হাদিসটি খুব ছোট, কিন্তু শিক্ষা গভীর। মানুষ অনেক সময় হাতে বা কাজে যত ভুল করে, কথার মাধ্যমেও তত বড় ক্ষতি করে বসে। মিথ্যা, কষ্টদায়ক কথা, অশ্লীল ভাষা, গীবত বা অন্যের ক্ষতি করা কথা—এসবের দরজা খুলে যায় জিহ্বা নিয়ন্ত্রণ না করলে। তবে এই হাদিসে শুধু জিহ্বার ভয় বলা হয়েছে; অতিরিক্ত বিস্তারিত বিধান এখানে নেই। মূল বার্তা হলো, কথা বলার আগে ভাবা, অপ্রয়োজনীয় কথা কমানো এবং নিজের ভাষাকে আল্লাহর ভয় দিয়ে নিয়ন্ত্রণ করা।"},"teachings":["জিহ্বা মানুষের জন্য বড় পরীক্ষার কারণ হতে পারে।","কথা বলার আগে চিন্তা করা নিরাপদ অভ্যাস।","ভাষা নিয়ন্ত্রণ করা মুসলিম চরিত্রের গুরুত্বপূর্ণ অংশ।","অপ্রয়োজনীয় ও ক্ষতিকর কথা থেকে দূরে থাকা দরকার।"],"related_hadiths":[{"id":"2410","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3972","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"6474","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="n"/>
     </row>
     <row r="145" ht="46" customHeight="1">
       <c r="A145" s="4" t="inlineStr">
@@ -3908,12 +3820,12 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম খাদ্য থেকে আবু বকরের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহজনক ও হারাম উৎসের খাদ্য থেকে বাঁচতে আবু বকর রাঃ-এর সতর্কতার ঘটনা জানুন।"},"heading":{"title":"হারাম খাদ্য এড়ানোর বাস্তব শিক্ষা: আবু বকর রাঃ-এর ঘটনা","description":"এই বর্ণনায় আবু বকর ছিদ্দীক রাদিয়াল্লাহু আনহুর অত্যন্ত সতর্ক মনোভাব দেখা যায়। তাঁর গোলাম যে খাবার এনেছিল, তিনি প্রথমে তা থেকে কিছু খেয়েছিলেন। পরে যখন জানা গেল খাবারটি এমন আয়ের সাথে যুক্ত, যেখানে জাহেলী যুগের গণকী ও ধোঁকার কথা আছে, তখন তিনি মুখে হাত ঢুকিয়ে সব বের করে দিলেন। এই ঘটনা আমাদের শেখায়, হারাম খাদ্য বা সন্দেহজনক উৎসের খাবার নিয়ে সাহাবীগণ কতটা সাবধান ছিলেন। হালাল রুজি শুধু আয় করার বিষয় নয়; তা খাওয়া, গ্রহণ করা এবং পরিবারের জীবনে ঢোকানোর ক্ষেত্রেও সতর্কতা দরকার।"},"teachings":["খাবারের উৎস জানার বিষয়টি গুরুত্বের সাথে দেখা দরকার।","ধোঁকা ও গণকীর মাধ্যমে পাওয়া আয় থেকে বাঁচা উচিত।","ভুলে কিছু গ্রহণ করলে জানার পর তা থেকে সরে আসা ভালো।","আবু বকর রাঃ-এর ঘটনা হারাম খাদ্য এড়ানোর শক্ত শিক্ষা দেয়।"],"related_hadiths":[{"id":"2237","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1567","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2764","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছয়টি অঙ্গীকার ও জান্নাতের আশা","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য কথা, ওয়াদা পূরণ, আমানত আদায়, লজ্জাস্থান, দৃষ্টি ও হাত হেফাজতের শিক্ষা।"},"heading":{"title":"ছয়টি অঙ্গীকার: সত্যবাদিতা, আমানত ও চরিত্র রক্ষার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم ছয়টি বিষয়ের জামানত চাইছেন। এগুলো হলো কথা বললে সত্য বলা, ওয়াদা করলে তা পূর্ণ করা, আমানত রাখা হলে তা আদায় করা, লজ্জাস্থান হেফাজত করা, দৃষ্টি নিচু রাখা এবং হাতকে অন্যায় কাজ থেকে বিরত রাখা। এখানে সততা, আমানতদারি ও শালীনতা একসাথে এসেছে। একজন মুসলিম শুধু মুখে ভালো কথা বললেই যথেষ্ট নয়; তার কথা, চুক্তি, দৃষ্টি, শরীর ও হাত—সবকিছুতে দায়িত্ববোধ থাকা দরকার। হাদিসে জান্নাতের যামিনের কথা এসেছে, তাই বিষয়গুলোকে হালকা করে দেখা উচিত নয়। তবে এর শিক্ষা হলো চেষ্টা, নিয়ন্ত্রণ এবং নিজের নফসকে ভালো পথে রাখা।"},"teachings":["কথা বললে সত্য বলা মুসলিম চরিত্রের ভিত্তি।","ওয়াদা ও আমানত রক্ষা করা বড় দায়িত্ব।","দৃষ্টি ও লজ্জাস্থান হেফাজত করা শালীনতার অংশ।","হাতকে অন্যায় কাজ থেকে বিরত রাখা দরকার।"],"related_hadiths":[{"id":"6474","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6136","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2410","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E145" s="4" t="n"/>
@@ -3931,12 +3843,12 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হারাম দ্বারা প্রতিপালিত দেহের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. হারাম দ্বারা প্রতিপালিত দেহ সম্পর্কে নবীজির সতর্ক বাণী ও হালাল জীবনের শিক্ষা পড়ুন।"},"heading":{"title":"হারাম রুজি থেকে বাঁচার হাদিস: দেহ, খাদ্য ও আখিরাতের ভাবনা","description":"এই হাদিসে খুব সংক্ষিপ্ত ভাষায় বড় সতর্কতা দেওয়া হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, যে দেহ হারাম দ্বারা প্রতিপালিত, তা জান্নাতে প্রবেশ করবে না। এর মানে, মানুষের শরীর কী দিয়ে বড় হচ্ছে—এটি দ্বীনের দৃষ্টিতে গুরুত্বপূর্ণ। হারাম আয়, হারাম খাবার এবং অন্যায় পথে পাওয়া সম্পদ শুধু দুনিয়ার বিষয় নয়; এর আখিরাতের দিকও আছে। হালাল রুজি কম হলেও তা নিরাপদ। আর হারাম রুজি বেশি হলেও তা ক্ষতির কারণ হতে পারে। তাই এই হাদিস মুমিনকে নিজের উপার্জন, খাওয়া-দাওয়া ও পরিবারের খরচের উৎস নিয়ে সচেতন করে।"},"teachings":["হারাম দ্বারা প্রতিপালিত দেহ সম্পর্কে হাদিসে কঠিন সতর্কতা এসেছে।","রুজির উৎস হালাল হওয়া মুমিনের জীবনে বড় বিষয়।","কম হালাল আয়ও হারাম বেশি আয়ের চেয়ে নিরাপদ।","নিজের ও পরিবারের খাবারের উৎস যাচাই করা দরকার।"],"related_hadiths":[{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1599","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2760","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সত্যবাদিতার পথ ও মিথ্যার ক্ষতি","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য মানুষকে পুণ্যের পথে নেয়, আর মিথ্যা পাপের দিকে ঠেলে দেয়—এ হাদিসের শিক্ষা।"},"heading":{"title":"সত্যবাদিতা: জান্নাতের পথে চলার সুন্দর শিক্ষা","description":"এই হাদিসে সত্য ও মিথ্যার ফল খুব পরিষ্কারভাবে বলা হয়েছে। সত্য পুণ্যময় কাজ, আর পুণ্য জান্নাতের পথ দেখায়। যে ব্যক্তি সত্যের উপর দৃঢ় থাকে, তাকে আল্লাহর কাছে সত্যনিষ্ঠ হিসেবে লেখা হয়। অন্যদিকে মিথ্যা পাপকাজ, আর পাপ জাহান্নামের পথ দেখায়। যে মিথ্যায় অভ্যস্ত হয়ে পড়ে, তাকে আল্লাহর কাছে মিথ্যুক হিসেবে লেখা হয়। এখানে মূল শিক্ষা হলো অভ্যাসের প্রভাব। একবার সত্য বলা ভালো, কিন্তু নিয়মিত সত্য বলা মানুষকে সত্যনিষ্ঠ করে। একইভাবে মিথ্যাকে ছোট মনে করলে তা অভ্যাসে পরিণত হতে পারে। তাই দৈনন্দিন কথা, লেনদেন, পরিবার ও সমাজে সত্যবাদিতা ধরে রাখা ঈমানী চরিত্রের বড় অংশ।"},"teachings":["সত্য কথা পুণ্যের পথে নিয়ে যায়।","নিয়মিত সত্য বলার অভ্যাস মানুষকে সত্যনিষ্ঠ করে।","মিথ্যা পাপের দিকে নিয়ে যেতে পারে।","মিথ্যায় অভ্যস্ত হওয়া থেকে শুরুতেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2607","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1971","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E146" s="4" t="n"/>
@@ -3954,12 +3866,12 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহজনক খেজুর না খাওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. সদকার খেজুর হতে পারে—এই আশঙ্কায় নবীজির সতর্কতা থেকে সন্দেহ এড়ানোর শিক্ষা জানুন।"},"heading":{"title":"সদকার সন্দেহে খেজুর না খাওয়া: নবীজির সতর্কতার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম রাস্তায় পড়ে থাকা একটি খেজুরের পাশ দিয়ে যান। তিনি বলেন, যদি সদকার খেজুর হওয়ার সন্দেহ না থাকত, তবে তিনি তা খেতেন। এই ছোট ঘটনাতেই বড় শিক্ষা আছে। এখানে খেজুরটি সামান্য জিনিস, কিন্তু নবীজি সন্দেহের জায়গায় সতর্কতা দেখিয়েছেন। কারণ সদকা তাঁর জন্য খাওয়া বৈধ ছিল না। হাদিসটি আমাদের শেখায়, সামান্য জিনিস হলেও হালাল-হারামের সীমা মানা দরকার। যখন কোনো বিষয়ে সন্দেহ থাকে, তখন সাবধান থাকা মুমিনের চরিত্রকে সুন্দর করে। এটি লোভ কমায় এবং অন্তরে আল্লাহভীতি বাড়ায়।"},"teachings":["সন্দেহের জায়গায় সাবধান থাকা নবীজির শিক্ষা।","সামান্য জিনিস হলেও হালাল-হারাম দেখা দরকার।","নিজের জন্য যা বৈধ নয়, তা থেকে দূরে থাকা উচিত।","খাবার গ্রহণেও আল্লাহভীতি থাকা মুমিনের গুণ।"],"related_hadiths":[{"id":"2055","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1071","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1652","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুখ ও লজ্জাস্থান হেফাজত","description":"$book_name$ $hadith_number$ - $chapter_name$. জিহ্বা ও লজ্জাস্থান হেফাজতের অঙ্গীকার জান্নাতের আশার বড় কারণ—হাদিসের শিক্ষা।"},"heading":{"title":"মুখ ও লজ্জাস্থান হেফাজত: জান্নাতের আশার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم দুইটি গুরুত্বপূর্ণ অঙ্গের দায়িত্ব নেওয়ার কথা বলেছেন। এক হলো দুই চোয়ালের মাঝের বস্তু, অর্থাৎ জিহ্বা; আর অন্যটি দুই পায়ের মাঝের বস্তু, অর্থাৎ লজ্জাস্থান। যে এগুলোর যিম্মাদার হবে, রাসূল صلى الله عليه وسلم তার জন্য জান্নাতের যিম্মাদার হওয়ার কথা বলেছেন। এখানে মানুষের চরিত্রের দুই বড় দরজা বোঝানো হয়েছে—কথা ও কামনা। জিহ্বা দিয়ে মিথ্যা, গালি, কষ্টদায়ক কথা বা অন্যায় কথা হতে পারে। লজ্জাস্থান নিয়ন্ত্রণ না করলে অবৈধ সম্পর্কের দিকে মানুষ ঝুঁকে যেতে পারে। তাই এই হাদিস মুসলিমকে নিজের ভাষা ও শালীনতা নিয়ে সতর্ক থাকতে শেখায়।"},"teachings":["জিহ্বা হেফাজত করা জান্নাতের আশার একটি বড় কারণ।","লজ্জাস্থান হেফাজত করা চরিত্র রক্ষার অংশ।","কথা ও কামনা—দুই ক্ষেত্রেই আত্মনিয়ন্ত্রণ দরকার।","নিজের অঙ্গের দায়িত্ব নেওয়া ঈমানী শৃঙ্খলার অংশ।"],"related_hadiths":[{"id":"6474","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2410","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3972","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E147" s="4" t="n"/>
@@ -3977,12 +3889,12 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যাকাতের খেজুর ও নবী পরিবারের বিধান","description":"$book_name$ $hadith_number$ - $chapter_name$. হাসান রাঃ-এর যাকাতের খেজুর ঘটনায় নবী পরিবারের জন্য সদকা না খাওয়ার শিক্ষা জানুন।"},"heading":{"title":"যাকাতের খেজুর নিয়ে হাদিস: নবী পরিবারের জন্য সদকার বিধান","description":"এই হাদিসে হাসান ইবনে আলী রাদিয়াল্লাহু আনহু যাকাতের একটি খেজুর মুখে দেন। নবী করীম সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম সঙ্গে সঙ্গে তাঁকে তা ফেলে দিতে বলেন এবং জানান, তাঁরা যাকাত খান না। এখানে শিক্ষা খুব পরিষ্কার। শিশুর ক্ষেত্রেও নবীজি হালাল-হারামের সীমা শেখাতে দেরি করেননি। তবে ভাষা ছিল কোমল ও শাসনের মতো। যাকাত একটি নির্দিষ্ট ইবাদত এবং এর খাতও নির্দিষ্ট। যাদের জন্য তা গ্রহণের বিধান নেই, তাদের তা খাওয়া উচিত নয়। এই হাদিস আমাদের শেখায়, ছোট বয়স থেকেই সন্তানকে বৈধ-অবৈধের শিক্ষা দেওয়া দরকার।"},"teachings":["যাকাতের মাল যার জন্য বৈধ নয়, তার তা খাওয়া উচিত নয়।","শিশুকেও হালাল-হারামের শিক্ষা দেওয়া দরকার।","নবীজি পরিবারকে দ্বীনের বিধান মানতে শিখিয়েছেন।","খাবার মুখে দেওয়ার আগেও উৎস জানা গুরুত্বপূর্ণ।"],"related_hadiths":[{"id":"2363","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2055","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1071","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রক্ষাকারী ও ধ্বংসকারী কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. তাকওয়া, হক কথা ও মধ্যম পথ রক্ষা করে; প্রবৃত্তি, কৃপণতা ও অহংকার ধ্বংসের কারণ।"},"heading":{"title":"রক্ষাকারী তিন কাজ ও ধ্বংসকারী তিন কাজ: তাকওয়ার হাদিস","description":"এই হাদিসে মানুষের জন্য তিনটি রক্ষাকারী কাজ এবং তিনটি ধ্বংসকারী কাজ বলা হয়েছে। রক্ষাকারী কাজ হলো প্রকাশ্যে ও গোপনে আল্লাহকে ভয় করা, সন্তুষ্টি ও অসন্তুষ্টি—উভয় অবস্থায় হক কথা বলা এবং সচ্ছলতা ও অসচ্ছলতায় মধ্যম পথ রাখা। অর্থাৎ ভালো চরিত্র শুধু মানুষের সামনে নয়, একান্ত অবস্থাতেও দরকার। আবার সত্য কথা শুধু সুবিধার সময়ে নয়, রাগ বা অসন্তুষ্টির সময়েও জরুরি। ধ্বংসকারী কাজ হলো প্রবৃত্তির অনুসরণ, কৃপণতাকে মেনে নেওয়া এবং নিজের প্রতি অহংকার করা। হাদিসে আত্ম-অহংকারকে সবচেয়ে কঠিন বলা হয়েছে। তাই এই শিক্ষা আমাদের ভারসাম্য, সত্য এবং বিনয়ী জীবনের দিকে ডাকে।"},"teachings":["প্রকাশ্যে ও গোপনে আল্লাহকে ভয় করা রক্ষাকারী কাজ।","সন্তুষ্টি ও অসন্তুষ্টি—দুই অবস্থাতেই হক কথা বলা দরকার।","সচ্ছলতা ও অসচ্ছলতায় মধ্যম পথ রাখা ভালো অভ্যাস।","প্রবৃত্তি, কৃপণতা ও অহংকার ধ্বংসের কারণ হতে পারে।"],"related_hadiths":[{"id":"168","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1987","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"7200","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E148" s="4" t="n"/>
@@ -4000,12 +3912,12 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিককে নেতা বলা থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মুনাফিক বা মিথ্যুক ব্যক্তিকে নেতা হিসেবে সম্মান করার বিষয়ে নবীজির সতর্ক বাণী জানুন।"},"heading":{"title":"মুনাফিককে নেতা বলা: সত্য, নেতৃত্ব ও ঈমানি সতর্কতার হাদিস","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম মুনাফিক ব্যক্তিকে নেতা বা সাইয়িদ বলতে নিষেধ করেছেন। অনুবাদে এসেছে, যদি নেতা মুনাফিক হয়, তাহলে এতে প্রতিপালককে অসন্তুষ্ট করার কথা বলা হয়েছে। অন্য বর্ণনায় মিথ্যুক মুনাফিককে নেতা বলা নিয়েও কঠিন সতর্কতা এসেছে। হাদিসটি নেতৃত্বের ভাষা ও সম্মান দেওয়ার বিষয়ে আমাদের সতর্ক করে। সম্মান এমন কাউকে দেওয়া উচিত নয়, যার ভেতরে মুনাফিকি, মিথ্যা বা দ্বীনের বিরুদ্ধে আচরণ আছে। এর মানে সাধারণ আচরণে অশোভন হওয়া নয়; বরং নৈতিক সম্মান ও নেতৃত্বের আসন কাকে দেওয়া হচ্ছে, সে বিষয়ে সতর্ক থাকা।"},"teachings":["মুনাফিক ব্যক্তিকে নেতৃত্বের সম্মান দেওয়ার বিষয়ে সতর্কতা এসেছে।","মিথ্যুক ও দ্বিমুখী চরিত্রের মানুষকে অকারণে বড় করা উচিত নয়।","নেতৃত্বের সম্মান নৈতিকতার সাথে জড়িত।","কথার মাধ্যমে কাকে মর্যাদা দিচ্ছি, তা ভাবা দরকার।"],"related_hadiths":[{"id":"33","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"59","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"4873","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে মুমিনের গুনাহ ঢেকে মাফ","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতের দিন মুমিনের গুনাহ স্বীকারের পর আল্লাহ দুনিয়ায় ঢেকে রাখা গুনাহ মাফ করে দেবেন।"},"heading":{"title":"কিয়ামতের দিন মুমিনের গুনাহ ঢেকে মাফ করার হাদিস","description":"এই হাদিসে কিয়ামতের দিনের একটি গভীর দৃশ্য এসেছে। আল্লাহ মুমিন বান্দাকে নিজের নিকটবর্তী করবেন, তাকে ঢেকে রাখবেন এবং একে একে তার গুনাহ সম্পর্কে জিজ্ঞেস করবেন। বান্দা স্বীকার করবে যে সে গুনাহগুলো জানে। তখন সে মনে করবে, এসব কারণে সে ধ্বংস হয়ে যাবে। কিন্তু আল্লাহ বলবেন, দুনিয়াতে আমি তোমার এই গুনাহগুলো ঢেকে রেখেছিলাম, আজ আমি তা মাফ করে দিচ্ছি। তারপর তাকে নেকীর আমলনামা দেওয়া হবে। আর কাফের ও মুনাফিকদের ব্যাপারে সবার সামনে ঘোষণা হবে যে তারা রবের বিরুদ্ধে মিথ্যা বলত। এই হাদিস আল্লাহর ক্ষমা, গুনাহ ঢেকে রাখা এবং কিয়ামতের হিসাবের কথা মনে করায়।"},"teachings":["মুমিন বান্দা কিয়ামতে নিজের গুনাহ স্বীকার করবে।","আল্লাহ দুনিয়ায় গুনাহ ঢেকে রেখেছেন—এটি বড় দয়া।","ক্ষমা আল্লাহর পক্ষ থেকে আসে, তাই তাঁর দিকে ফিরতে হয়।","মিথ্যাচার ও মুনাফিকী কিয়ামতে প্রকাশ পাবে।"],"related_hadiths":[{"id":"2441","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2768","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"5551","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E149" s="4" t="n"/>
@@ -4023,12 +3935,12 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তর্ক, মিথ্যা ও সুন্দর চরিত্রের ফজিলত","description":"$book_name$ $hadith_number$ - $chapter_name$. হক হলেও তর্ক ছাড়া, মজা করেও মিথ্যা না বলা এবং চরিত্র সুন্দর করার বড় শিক্ষা জানুন।"},"heading":{"title":"সুন্দর চরিত্রের হাদিস: তর্ক ছাড়া, মিথ্যা ছাড়া, ভালো আচরণ","description":"এই হাদিসে তিনটি বড় আচরণ শেখানো হয়েছে। প্রথমত, কেউ হক হলেও তর্ক পরিহার করলে তার জন্য জান্নাতে ঘরের কথা এসেছে। দ্বিতীয়ত, মজা করেও মিথ্যা ছেড়ে দেওয়ার কথা বলা হয়েছে। তৃতীয়ত, চরিত্র সুন্দর করার ফজিলত এসেছে। হাদিসটি আমাদের দৈনন্দিন কথা ও আচরণকে ঠিক করার সহজ পথ দেখায়। অনেক সময় মানুষ সত্য কথা বলেও তর্কে জড়িয়ে পড়ে, আবার হাসানোর জন্য মিথ্যা বলে ফেলে। এই হাদিস শেখায়, সত্যের সাথে নম্রতা, কথার সাথে সততা এবং মানুষের সাথে ভালো ব্যবহার—সবই মুমিনের চরিত্রের অংশ। সুন্দর চরিত্র শুধু বাহ্যিক ভদ্রতা নয়; এটি কথা, রাগ, তর্ক ও আচরণে প্রকাশ পায়।"},"teachings":["হক হলেও অপ্রয়োজনীয় তর্ক ছেড়ে দেওয়া উত্তম কাজ।","মজা করেও মিথ্যা বলা থেকে বাঁচতে হবে।","সুন্দর চরিত্র জান্নাতের বড় ফজিলতের কারণ।","সত্য কথা বলার সঙ্গে নম্র আচরণও দরকার।"],"related_hadiths":[{"id":"4800","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2004","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সব নেশাদার দ্রব্য মদ","description":"$book_name$ $hadith_number$ - $chapter_name$. সব নেশাদার দ্রব্য মদ এবং সব মদ হারাম—তওবা ছাড়া আসক্তির ভয়াবহ সতর্কতা।"},"heading":{"title":"সব নেশাদার দ্রব্য মদ: খামর হারামের স্পষ্ট হাদিস","description":"এই হাদিসে খুব স্পষ্টভাবে বলা হয়েছে, সব নেশাদার দ্রব্য মদ এবং সব ধরনের মদ হারাম। অর্থাৎ শুধু নির্দিষ্ট কোনো পানীয় নয়, যে বস্তু নেশা তৈরি করে তা এই সতর্কতার মধ্যে পড়ে। হাদিসে আরও বলা হয়েছে, যে ব্যক্তি দুনিয়ায় মদ পান করে এবং তওবা ছাড়া আসক্ত অবস্থায় মারা যায়, সে পরকালে সুস্বাদু পানীয় পান করতে পাবে না। এখানে মূল শিক্ষা হলো নেশা থেকে দূরে থাকা এবং ভুল হলে তওবার দিকে ফিরে আসা। হাদিসে আসক্তির কথা এসেছে, তাই নিয়মিত নেশাকে সাধারণ অভ্যাস মনে করা বিপজ্জনক। একজন মুসলিমের জন্য বিবেক, ইবাদত ও চরিত্র রক্ষায় নেশাদার দ্রব্য থেকে বাঁচা প্রয়োজন।"},"teachings":["সব নেশাদার দ্রব্যকে মদের অন্তর্ভুক্ত বলা হয়েছে।","সব ধরনের মদ হারাম—এ শিক্ষা স্পষ্ট।","আসক্ত অবস্থায় তওবা ছাড়া মৃত্যু ভয়াবহ সতর্কতার বিষয়।","ভুল হলে তওবার দিকে দ্রুত ফিরে আসা দরকার।"],"related_hadiths":[{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3450","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E150" s="4" t="n"/>
@@ -4046,12 +3958,12 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বায়আত ও বড় গুনাহ থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, চুরি, যেনা, সন্তান হত্যা, অপবাদ ও অবাধ্যতা থেকে দূরে থাকার বায়আতের শিক্ষা এসেছে।"},"heading":{"title":"বায়আতের শর্ত ও বড় গুনাহ থেকে বাঁচার শিক্ষা","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সাহাবীদের কাছ থেকে বায়আত নেন। তিনি বলেন, তারা যেন আল্লাহর সঙ্গে কাউকে শরীক না করে, চুরি না করে, যেনা না করে, সন্তান হত্যা না করে, কারও প্রতি অপবাদ না দেয় এবং শরীআতসম্মত বিষয়ে অবাধ্যতা না করে। এরপর তিনি জানান, যে এসব অঙ্গীকার পূর্ণ করবে, তার পুরস্কার আল্লাহর কাছে। কেউ যদি কোনো অপরাধ করে এবং দুনিয়াতে শাস্তি পায়, তা তার জন্য কাফফারা হতে পারে। আর আল্লাহ যদি তা ঢেকে রাখেন, তাহলে বিষয়টি আল্লাহর ইচ্ছার উপর। এই হাদিসে বায়আত, তাওহীদ, নৈতিকতা, অপরাধ থেকে বাঁচা এবং আল্লাহর বিচার—সব মিলিয়ে দায়িত্বশীল জীবনের শিক্ষা আছে।"},"teachings":["শিরক, চুরি, যেনা, অপবাদ ও অন্যায় থেকে দূরে থাকা জরুরি।","শরীআতসম্মত বিষয়ে অবাধ্যতা করা ঠিক নয়।","অঙ্গীকার পূরণ করলে প্রতিদান আল্লাহর কাছে।","গুনাহের বিচার আল্লাহর ইচ্ছা ও ন্যায়ের সঙ্গে জড়িত।"],"related_hadiths":[{"id":"18","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1709","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"18","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ত্বিনাতে খাবালের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নেশাদার দ্রব্য পানকারীর জন্য ত্বিনাতে খাবাল—জাহান্নামীদের রক্ত-পুঁজের কঠিন সতর্কতা।"},"heading":{"title":"ত্বিনাতে খাবাল: নেশাদার দ্রব্য পানকারীর কঠিন সতর্কতা","description":"এই হাদিসে নেশাদার দ্রব্য পানকারীদের জন্য খুব কঠিন সতর্কতা এসেছে। রাসূলুল্লাহ صلى الله عليه وسلم বলেছেন, আল্লাহর ওয়াদা রয়েছে যে নেশাদার দ্রব্য পানকারীকে তিনি ত্বিনাতে খাবাল পান করাবেন। সাহাবীগণ জিজ্ঞেস করলে রাসূল صلى الله عليه وسلم ব্যাখ্যা করেন, এটি জাহান্নামীদের শরীর থেকে গলে পড়া রক্ত-পুঁজ মিশ্রিত অত্যন্ত গরম তরল পদার্থ। হাদিসের ভাষা ভয় জাগায়, কারণ নেশা মানুষের বিবেক, ইবাদত ও চরিত্রকে ক্ষতি করতে পারে। এখানে অতিরিক্ত কোনো গল্প যোগ করার দরকার নেই; মূল শিক্ষা যথেষ্ট পরিষ্কার। মদ ও মাদক থেকে দূরে থাকা, আসক্তি হলে তওবা করা এবং সাহায্য নিয়ে ফিরে আসা—এটাই একজন মুসলিমের নিরাপদ পথ।"},"teachings":["নেশাদার দ্রব্য পানকারীর জন্য কঠিন সতর্কতা এসেছে।","ত্বিনাতে খাবালকে জাহান্নামীদের রক্ত-পুঁজের তরল বলা হয়েছে।","নেশাকে সাধারণ ভুল মনে করে হালকা করা উচিত নয়।","ভুল হলে তওবা ও নেশা ছাড়ার চেষ্টা জরুরি।"],"related_hadiths":[{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3377","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E151" s="4" t="n"/>
@@ -4069,12 +3981,12 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আল্লাহর ভালোবাসার পথে আমানত ও সত্য","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ ও রাসূলের ভালোবাসা পেতে আমানত, সত্য কথা ও প্রতিবেশীর ভালো আচরণের শিক্ষা জানুন।"},"heading":{"title":"আমানত রক্ষা, সত্য কথা ও প্রতিবেশীর হক: ভালোবাসার হাদিস","description":"এই হাদিসে সাহাবীরা নবীজির ওযূর পানির প্রতি ভালোবাসা দেখিয়েছিলেন। তাঁরা বললেন, এটি আল্লাহ ও তাঁর রাসূলের ভালোবাসার কারণে করেছেন। তখন রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম তাঁদের সামনে ভালোবাসার বাস্তব পথ জানালেন। তিনি বললেন, আমানত রাখা হলে তা ফিরিয়ে দাও, কথা বললে সত্য বল, আর প্রতিবেশীর সাথে ভালো আচরণ কর। এতে বোঝা যায়, ভালোবাসা শুধু আবেগে সীমাবদ্ধ নয়; তা কাজে প্রকাশ পায়। একজন মুমিন আল্লাহ ও রাসূলকে ভালোবাসতে চাইলে তার লেনদেন সৎ হবে, কথায় মিথ্যা থাকবে না এবং পাশের মানুষের সাথে আচরণ সুন্দর হবে।"},"teachings":["আমানত রাখা হলে তা যথাযথভাবে ফিরিয়ে দেওয়া দরকার।","কথা বলার সময় সত্য বলা ভালোবাসার বাস্তব প্রকাশ।","প্রতিবেশীর সাথে ভালো আচরণ মুমিনের দায়িত্ব।","আল্লাহ ও রাসূলের ভালোবাসা কাজে প্রমাণ করতে হয়।"],"related_hadiths":[{"id":"33","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6016","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"46","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদাসক্তির ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নিয়মিত নেশাদার দ্রব্য পানকারীকে মূর্তিপূজকের মতো গুরুতর অপরাধী বলা হয়েছে।"},"heading":{"title":"মদাসক্তি: নিয়মিত নেশা করার ভয়াবহ সতর্কতা","description":"এই হাদিসে নিয়মিত নেশাদার দ্রব্য পানকারীকে মূর্তিপূজকের ন্যায় অপরাধী বলা হয়েছে। এখানে মূল শিক্ষা হলো মদাসক্তি বা নেশার অভ্যাসকে খুব গুরুতরভাবে দেখা। হাদিসে একবার ভুল করা ও নিয়মিত আসক্তির মধ্যে ভাষাগতভাবে পার্থক্য আছে, কারণ ‘সর্বদা পানকারী’ শব্দটি অভ্যাস ও আসক্তির দিকে ইঙ্গিত করে। তবে কোনো মানুষকে ব্যক্তিগতভাবে বিচার করার চেয়ে নিজের অবস্থার দিকে তাকানো বেশি দরকার। মদ বা নেশা মানুষকে আল্লাহর আনুগত্য থেকে দূরে নিতে পারে এবং চরিত্র নষ্ট করতে পারে। তাই যে কেউ এই অভ্যাসে জড়িয়ে পড়লে তাকে তওবা, দোয়া ও বাস্তব পদক্ষেপের মাধ্যমে ফিরে আসার চেষ্টা করা উচিত।"},"teachings":["নিয়মিত নেশা করা গুরুতর অপরাধ হিসেবে এসেছে।","নেশার অভ্যাসকে হালকা করে দেখা ঠিক নয়।","মদাসক্তি আল্লাহর আনুগত্য থেকে দূরে নিতে পারে।","তওবা ও নেশা ছাড়ার চেষ্টা জরুরি।"],"related_hadiths":[{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3377","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
         </is>
       </c>
       <c r="E152" s="4" t="n"/>
@@ -4092,12 +4004,12 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | আমানত, সত্য, চরিত্র ও বৈধ রুজি","description":"$book_name$ $hadith_number$ - $chapter_name$. চারটি গুণ—আমানত, সত্য কথা, সুন্দর চরিত্র ও বৈধ রুজি—নিয়ে নবীজির গভীর শিক্ষা জানুন।"},"heading":{"title":"চারটি গুণের হাদিস: আমানত, সত্যবাদিতা, সুন্দর চরিত্র ও বৈধ রুজি","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম চারটি জিনিসের কথা বলেছেন। এগুলো মানুষের জীবনে থাকলে দুনিয়ার অনেক কিছু হারালেও তার বড় ক্ষতি নেই—এমন শিক্ষা এসেছে। চারটি গুণ হলো আমানত রক্ষা করা, সত্য কথা বলা, সুন্দর চরিত্র রাখা এবং বৈধ রুজি গ্রহণ করা। এই চারটি বিষয় ব্যক্তিগত জীবন, পরিবার, ব্যবসা ও সমাজ—সব জায়গায় দরকার। আমানত মানুষকে বিশ্বাসযোগ্য করে, সত্য কথা তাকে পরিষ্কার রাখে, সুন্দর চরিত্র তাকে প্রিয় করে, আর বৈধ রুজি তার জীবনকে পবিত্র পথে রাখে। হাদিসটি খুব সহজ ভাষায় সফল মুসলিম জীবনের একটি নীতিমালা দেয়।"},"teachings":["আমানত রক্ষা মানুষকে বিশ্বাসযোগ্য করে।","সত্য কথা বলা মুমিনের বড় গুণ।","সুন্দর চরিত্র মানুষের সাথে সম্পর্ক ভালো রাখে।","বৈধ রুজি গ্রহণ করা জীবনের নিরাপদ পথ।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2004","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপানকারীর জান্নাত সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সর্বদা নেশাদার দ্রব্য পানকারীর জন্য জান্নাত বিষয়ে কঠিন সতর্কতা—নিজেকে সংশোধনের ডাক।"},"heading":{"title":"সর্বদা নেশাদার দ্রব্য পানকারী: জান্নাত বিষয়ে কঠিন সতর্কতা","description":"এই হাদিসে বলা হয়েছে, সর্বদা নেশাদার দ্রব্য পানকারী জান্নাতে যাবে না। হাদিসের ভাষা খুব কঠিন, তাই একে হালকা করে দেখা উচিত নয়। এখানে মূল বিষয় হলো মদাসক্তি ও নিয়মিত নেশা। নেশা মানুষের বিবেক ঢেকে দেয়, আমল দুর্বল করে এবং অনেক অন্যায়ের দরজা খুলে দিতে পারে। তবে হাদিস থেকে অতিরিক্ত সিদ্ধান্ত বানানো ঠিক নয়; যে কথা এসেছে, সেটুকুই মানতে হবে। মুসলিমের কাজ হলো ভয় পাওয়া, নিজেকে ফিরিয়ে আনা এবং তওবার পথ ধরা। যদি কারও জীবনে এই অভ্যাস থাকে, তাহলে গোপনে বা প্রকাশ্যে আল্লাহর কাছে ক্ষমা চেয়ে নেশা ছাড়ার বাস্তব চেষ্টা করা জরুরি।"},"teachings":["নিয়মিত নেশাদার দ্রব্য পানকারীর জন্য কঠিন সতর্কতা এসেছে।","নেশাকে সাধারণ সামাজিক অভ্যাস মনে করা ভুল।","নেশা ছাড়ার জন্য তওবা ও চেষ্টা দরকার।","হাদিসের ভাষা যতটুকু, ব্যাখ্যাও ততটুকুতে রাখা উচিত।"],"related_hadiths":[{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"3377","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E153" s="4" t="n"/>
@@ -4115,12 +4027,12 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্দেহ ছাড়ুন, সত্যে শান্তি খুঁজুন","description":"$book_name$ $hadith_number$ - $chapter_name$. সন্দেহযুক্ত কথা ও কাজ ছেড়ে সত্যের শান্তি এবং মিথ্যার অশান্তি বুঝে চলার শিক্ষা নিন।"},"heading":{"title":"সত্যে প্রশান্তি, মিথ্যায় অশান্তি: সন্দেহ ছাড়ার হাদিস","description":"এই হাদিসে বলা হয়েছে, সন্দেহযুক্ত কথা ও কাজ ছেড়ে এমন দিকে ফিরে যেতে, যেখানে সন্দেহ নেই। এরপর বলা হয়েছে, সত্য প্রশান্তির নাম এবং মিথ্যা সন্দেহ ও অশান্তির নাম। এখানে সত্যবাদিতা শুধু মুখের কথা নয়; কাজের ক্ষেত্রেও সত্যের পথ বেছে নেওয়ার কথা আছে। যখন কোনো কথা, লেনদেন বা কাজ অন্তরে অস্বস্তি আনে, তখন তা নিয়ে থেমে ভাবা দরকার। মুমিনের জীবন এমন হওয়া উচিত, যেখানে কথা ও কাজে স্বচ্ছতা থাকে। মিথ্যা কিছু সময় সুবিধা দিলেও অন্তরে অস্থিরতা আনে। তাই এই হাদিস মানুষকে সহজ, সৎ ও শান্ত পথের দিকে ডাকছে।"},"teachings":["সন্দেহযুক্ত কথা ও কাজ ছেড়ে দেওয়া উচিত।","সত্য অন্তরে প্রশান্তি আনে।","মিথ্যা সন্দেহ ও অশান্তির কারণ হয়।","কথা ও কাজ—দুটোতেই সততা দরকার।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2607","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"52","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অবাধ্যতা, জুয়া, খোঁটা ও মদাসক্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. পিতা-মাতার অবাধ্যতা, জুয়া-লটারী, খোঁটা দেওয়া ও মদাসক্তির কঠিন সতর্কতা।"},"heading":{"title":"অবাধ্য সন্তান, জুয়া, খোঁটা ও মদপান: চারটি গুরুতর সতর্কতা","description":"এই হাদিসে চার শ্রেণীর মানুষের ব্যাপারে জান্নাত বিষয়ে কঠিন সতর্কতা এসেছে। তারা হলো পিতা-মাতার অবাধ্য সন্তান, জুয়া ও লটারীতে অংশগ্রহণকারী, খোঁটাদানকারী এবং সর্বদা মদপানকারী। এখানে একসাথে কয়েকটি সামাজিক ও ব্যক্তিগত অপরাধ এসেছে। পিতা-মাতার অবাধ্যতা পরিবারকে আঘাত করে। জুয়া ও লটারী মানুষের সম্পদ ও মনকে অন্য পথে নেয়। খোঁটা দেওয়া দান বা উপকারের সৌন্দর্য নষ্ট করে। আর মদাসক্তি বিবেক ও চরিত্রকে ক্ষতি করে। হাদিসটি আমাদের শেখায়, শুধু ব্যক্তিগত ইবাদত নয়; পারিবারিক দায়িত্ব, অর্থনৈতিক সততা, মানুষের সম্মান এবং নেশা থেকে দূরে থাকা—সবই মুসলিম জীবনের অংশ।"},"teachings":["পিতা-মাতার অবাধ্যতা গুরুতর সতর্কতার বিষয়।","জুয়া ও লটারী থেকে দূরে থাকা দরকার।","উপকার করে খোঁটা দেওয়া খারাপ অভ্যাস।","সর্বদা মদপান করা ভয়াবহ পরিণতির কারণ হতে পারে।"],"related_hadiths":[{"id":"161","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6871","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E154" s="4" t="n"/>
@@ -4138,12 +4050,12 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হিংসামুক্ত অন্তর ও সত্য ভাষার মর্যাদা","description":"$book_name$ $hadith_number$ - $chapter_name$. উত্তম মানুষের পরিচয়ে সত্য ভাষা, পরহেযগার অন্তর ও হিংসা থেকে মুক্ত থাকার শিক্ষা জানুন।"},"heading":{"title":"হিংসামুক্ত অন্তর ও সত্য ভাষা: উত্তম মানুষের পরিচয়","description":"এই হাদিসে রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লামকে জিজ্ঞেস করা হলো, সবচেয়ে ভাল মানুষ কে? উত্তরে তিনি বললেন, যে ব্যক্তি হিংসা-বিদ্বেষ মুক্ত অন্তরের অধিকারী এবং সত্য কথার অধিকারী। সাহাবীগণ সত্য ভাষা বুঝলেন, কিন্তু হিংসা-বিদ্বেষ মুক্ত অন্তরের ব্যাখ্যা জানতে চাইলেন। তখন তিনি বললেন, সে ব্যক্তি স্বচ্ছ ও পরহেযগার; যার মধ্যে পাপ, সীমালংঘন, খিয়ানত ও হিংসা নেই। এই হাদিস আমাদের বাহ্যিক ভালো কাজের পাশাপাশি অন্তরের পরিচ্ছন্নতার দিকে ডাকে। শুধু মুখে সত্য বললেই শেষ নয়; অন্তর থেকেও হিংসা, খিয়ানত ও অন্যায় দূর করার চেষ্টা করতে হয়।"},"teachings":["সত্য ভাষা উত্তম মানুষের গুণ।","হিংসা-বিদ্বেষ মুক্ত অন্তর মুমিনের বড় সৌন্দর্য।","খিয়ানত ও সীমালংঘন থেকে দূরে থাকা দরকার।","ভালো মানুষ হতে অন্তর ও ভাষা—দুটোই ঠিক রাখা জরুরি।"],"related_hadiths":[{"id":"4216","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"91","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর কঠিন সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. পরিবারে বেহায়াপনা, পুরুষের বেশধারী নারী ও নিয়মিত নেশাকারীর ব্যাপারে সতর্কতা।"},"heading":{"title":"তিন শ্রেণীর মানুষ: পরিবার, পোশাক-আচরণ ও নেশা বিষয়ে সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের ব্যাপারে কঠিন সতর্কতা এসেছে। প্রথমত, যে ব্যক্তি তার পরিবারে বেহায়াপনার সুযোগ দেয়। দ্বিতীয়ত, পুরুষের বেশধারী নারী। তৃতীয়ত, নিয়মিত নেশাদার দ্রব্য পানকারী। এখানে পরিবার, পরিচয় ও নেশার বিষয় একসাথে এসেছে। পরিবারে অশালীনতার সুযোগ দেওয়া মানে নিজের দায়িত্বকে অবহেলা করা। পোশাক ও আচরণে সীমা রক্ষা করাও ইসলামী শালীনতার অংশ। আর নিয়মিত নেশা মানুষের বিবেক ও আমলকে ক্ষতি করে। হাদিসের ভাষা কঠোর, তাই এটি নিজের সংশোধনের জন্য নেওয়া উচিত। অন্যকে অপমান করার জন্য নয়; বরং নিজের পরিবার, চরিত্র ও অভ্যাস ঠিক করার জন্য।"},"teachings":["পরিবারে বেহায়াপনার সুযোগ দেওয়া গুরুতর সতর্কতার বিষয়।","পোশাক ও আচরণে শালীনতা রক্ষা করা দরকার।","নিয়মিত নেশাদার দ্রব্য পান করা ভয়াবহ অভ্যাস।","হাদিসের শিক্ষা নিজের সংশোধনের জন্য গ্রহণ করা উচিত।"],"related_hadiths":[{"id":"168","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"6136","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E155" s="4" t="n"/>
@@ -4161,12 +4073,12 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সত্য নেকীর পথে, মিথ্যা পাপের পথে","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য গ্রহণ ও মিথ্যা থেকে বাঁচার মাধ্যমে নেকী ও পাপের পথ বুঝে চলার শিক্ষা জানুন।"},"heading":{"title":"সত্য নেকীর সাথে, মিথ্যা পাপের সাথে: নবীজির সরল শিক্ষা","description":"এই হাদিসে সত্য ও মিথ্যার পথ খুব পরিষ্কার করে বলা হয়েছে। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন, সত্য গ্রহণ কর; কারণ সত্য নেকীর সাথে রয়েছে। আর মিথ্যা থেকে বেঁচে থাক; কারণ মিথ্যা পাপের সাথে রয়েছে। এখানে সত্যকে শুধু ভালো অভ্যাস বলা হয়নি; বরং তা নেকীর পথে নিয়ে যায় বলা হয়েছে। আবার মিথ্যাকে ছোট ভুল হিসেবে দেখা হয়নি; তা পাপের সাথে যুক্ত বলা হয়েছে। তাই একজন মুমিনের কথা, প্রতিশ্রুতি, লেনদেন ও সম্পর্ক—সব জায়গায় সত্য দরকার। মিথ্যা সাময়িক সুবিধা দিলেও মানুষকে খারাপ পথে টেনে নিতে পারে।"},"teachings":["সত্য নেকীর পথে নিয়ে যায়।","মিথ্যা পাপের সাথে যুক্ত।","কথা ও লেনদেনে সত্যবাদিতা রাখা জরুরি।","মিথ্যাকে ছোট ভুল ভেবে অবহেলা করা উচিত নয়।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2607","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2518","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপান, অবাধ্যতা ও দায়ূস","description":"$book_name$ $hadith_number$ - $chapter_name$. মদাসক্ত, পিতা-মাতার অবাধ্য সন্তান ও পরিবারে বেপর্দার সুযোগদাতার সতর্কতা।"},"heading":{"title":"মদাসক্ত, অবাধ্য সন্তান ও দায়ূস: তিন শ্রেণীর কঠিন সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর লোকের প্রতি আল্লাহ জান্নাত হারাম করেছেন বলে সতর্ক করা হয়েছে। তারা হলো সর্বদা মদপানকারী, পিতা-মাতার অবাধ্য সন্তান এবং পরিবারে বেপর্দা বা খারাপ কাজের সুযোগ দানকারী দায়ূস। এখানে তিনটি বিষয়ে জোর আছে—নিজের নেশার অভ্যাস, পিতা-মাতার হক এবং পরিবারের নৈতিক দায়িত্ব। মদাসক্তি ব্যক্তিকে ভেতর থেকে দুর্বল করে। পিতা-মাতার অবাধ্যতা কৃতজ্ঞতা ও দায়িত্বের বিপরীত। আর পরিবারে খারাপ কাজকে মেনে নেওয়া দায়িত্বহীনতা। হাদিসটি মানুষকে ভয় দেখিয়ে ভেঙে দিতে নয়; বরং জাগিয়ে দিতে এসেছে, যেন সে তওবা করে, সম্পর্ক ঠিক করে এবং পরিবারকে সঠিক পথে রাখতে চেষ্টা করে।"},"teachings":["সর্বদা মদপানকারী সম্পর্কে কঠিন সতর্কতা এসেছে।","পিতা-মাতার অবাধ্যতা বড় অপরাধের মধ্যে পড়ে।","পরিবারে খারাপ কাজ মেনে নেওয়া দায়িত্বহীনতা।","তওবা ও সংশোধনের পথে ফিরে আসা দরকার।"],"related_hadiths":[{"id":"161","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6871","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
         </is>
       </c>
       <c r="E156" s="4" t="n"/>
@@ -4184,12 +4096,12 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মিথ্যা ঈমানকে ক্ষতিগ্রস্ত করে","description":"$book_name$ $hadith_number$ - $chapter_name$. মিথ্যা থেকে বেঁচে থাকার গুরুত্ব এবং ঈমানের সাথে সত্যবাদিতার সম্পর্ক বুঝে নিন।"},"heading":{"title":"মিথ্যা থেকে বাঁচার হাদিস: ঈমানের জন্য সততার প্রয়োজন","description":"এই বর্ণনায় মিথ্যা থেকে বেঁচে থাকার কঠিন সতর্কতা এসেছে। বলা হয়েছে, মিথ্যা ঈমানকে ক্ষতিগ্রস্ত করে। কথাটি ছোট হলেও খুব গভীর। অনেক সময় মানুষ মিথ্যাকে হালকা ভাবে নেয়—মজা করে, সুবিধার জন্য, লজ্জা ঢাকতে বা সম্পর্ক বাঁচাতে। কিন্তু হাদিসের শিক্ষা হলো, মিথ্যা মানুষের ভেতরের ঈমানি শক্তিকে দুর্বল করে। সত্য বলা সব সময় সহজ না-ও হতে পারে, কিন্তু মিথ্যার পথে অভ্যাস তৈরি হলে তা চরিত্রকে নষ্ট করে। তাই মুমিনের জন্য সত্যবাদিতা শুধু সামাজিক ভালো গুণ নয়; এটি ঈমান রক্ষার সাথে জড়িত একটি বড় বিষয়।"},"teachings":["মিথ্যা ঈমানের ক্ষতির কারণ হতে পারে।","মিথ্যাকে ছোট বা হালকা বিষয় ভাবা উচিত নয়।","সত্যবাদিতা ঈমানি চরিত্রের অংশ।","সুবিধার জন্য মিথ্যা বলা থেকে বাঁচতে হবে।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2607","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"4990","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, সম্পর্কচ্ছেদ ও যাদু","description":"$book_name$ $hadith_number$ - $chapter_name$. মদাসক্তি, আত্মীয়তার সম্পর্ক ছিন্ন করা ও যাদু বিশ্বাসের ব্যাপারে কঠিন সতর্কতা।"},"heading":{"title":"মদাসক্তি, আত্মীয়তা ছিন্ন ও যাদু বিশ্বাস: তিনটি বড় সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর লোকের ব্যাপারে বলা হয়েছে, তারা জান্নাতে যাবে না। প্রথম শ্রেণী হলো সর্বদা নেশাদার দ্রব্য পানকারী। দ্বিতীয় হলো আত্মীয়তার সম্পর্ক বিচ্ছিন্নকারী। তৃতীয় হলো যাদুকে বিশ্বাসকারী। এখানে তিনটি ভিন্ন ক্ষতির দিক দেখা যায়। নেশা নিজের বিবেক ও আমলকে ক্ষতি করে। আত্মীয়তার সম্পর্ক ছিন্ন করা পরিবার ও সমাজের বন্ধন নষ্ট করে। আর যাদুকে বিশ্বাস করা ঈমানী চিন্তা ও আল্লাহর ওপর ভরসাকে দুর্বল করতে পারে। হাদিসটি আমাদের নিজের জীবনকে তিন দিক থেকে দেখতে শেখায়—অভ্যাস, সম্পর্ক এবং বিশ্বাস। ভুল থাকলে তা স্বীকার করে ফিরে আসাই নিরাপদ পথ।"},"teachings":["সর্বদা নেশাদার দ্রব্য পান করা ভয়াবহ সতর্কতার বিষয়।","আত্মীয়তার সম্পর্ক ছিন্ন করা থেকে দূরে থাকতে হবে।","যাদুকে বিশ্বাস করা ঈমানের জন্য বিপজ্জনক।","অভ্যাস, সম্পর্ক ও বিশ্বাস—তিন দিকেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6136","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E157" s="4" t="n"/>
@@ -4207,19 +4119,15 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শিশুকে মিথ্যা প্রতিশ্রুতি না দেওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুকে “আসো নাও” বলে কিছু না দিলে সেটিও মিথ্যা—এই নববী শিক্ষা জানুন।"},"heading":{"title":"শিশুকে মিথ্যা কথা নয়: ছোট প্রতিশ্রুতিতেও সত্যের শিক্ষা","description":"এই হাদিসে শিশুদের সাথে সত্যবাদিতার শিক্ষা এসেছে। কেউ যদি বাচ্চাকে বলে, “আসো নাও”, কিন্তু পরে তাকে কিছু না দেয়, তাহলে সেটিকে মিথ্যা বলা হয়েছে। এতে বোঝা যায়, শিশুর সাথে কথাবার্তাও দ্বীনের বাইরে নয়। অনেক সময় বড়রা শিশুকে শান্ত করার জন্য বা কাছে ডাকার জন্য এমন কথা বলে যা পরে রাখে না। হাদিসটি শেখায়, শিশুকে ছোট মনে করে তার সাথে মিথ্যা বলা ঠিক নয়। কারণ শিশু বড়দের কথায় বিশ্বাস করতে শেখে। যদি বড়রা কথা না রাখে, তাহলে শিশুর মনেও মিথ্যার স্বাভাবিক ধারণা তৈরি হতে পারে। তাই সন্তানের সামনে সত্য কথা ও কথা রাখার অভ্যাস জরুরি।"},"teachings":["শিশুকে মিথ্যা প্রতিশ্রুতি দেওয়া থেকে বাঁচতে হবে।","ছোট কথাতেও সত্যবাদিতা দরকার।","বড়দের আচরণ শিশুদের শেখার মাধ্যম।","কথা দিলে তা রাখার চেষ্টা করা উচিত।"],"related_hadiths":[{"id":"4991","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
-        </is>
-      </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>related_hadiths[1]: unknown book label "সূরা আস-সফ ৬১:২-৩ (প্রাসঙ্গিক আয়াত)"</t>
-        </is>
-      </c>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে অঙ্গ-প্রত্যঙ্গের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে মুখ বন্ধ করে অঙ্গ-প্রত্যঙ্গকে কথা বলানো হবে; মানুষ নিজের কাজের সাক্ষ্য নিজ থেকেই পাবে।"},"heading":{"title":"কিয়ামতের দিন অঙ্গ-প্রত্যঙ্গের সাক্ষ্য দেওয়ার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কিয়ামতের দিনের এক কথোপকথনের কথা বলেছেন। বান্দা বলবে, সে নিজের বিরুদ্ধে শুধু নিজের পক্ষ থেকে সাক্ষ্য গ্রহণ করবে। তখন আল্লাহ বলবেন, আজ তুমি নিজেই তোমার সাক্ষী হিসেবে যথেষ্ট, আর কিরামান-কাতিবীনও সাক্ষী। এরপর তার মুখে মোহর লাগিয়ে দেওয়া হবে এবং অঙ্গ-প্রত্যঙ্গকে বলা হবে, তারা যেন তার কাজের কথা বলে। তখন অঙ্গ-প্রত্যঙ্গ তার কাজ প্রকাশ করবে। পরে মুখ খুলে দেওয়া হলে সে নিজের অঙ্গগুলোকে দোষ দেবে, অথচ তাদের জন্যই সে আগে নিজের রবের সঙ্গে বিতর্ক করছিল। এই হাদিস আমাদের মনে করায়, কিয়ামতের সাক্ষ্য খুব স্পষ্ট হবে এবং মানুষের কাজ লুকানো থাকবে না।"},"teachings":["কিয়ামতে মানুষের নিজের অঙ্গ-প্রত্যঙ্গ তার কাজের সাক্ষ্য দেবে।","কিরামান-কাতিবীন মানুষের কাজ লিখে রাখেন।","মুখের কথা দিয়ে সবকিছু অস্বীকার করা সম্ভব হবে না।","দুনিয়ার কাজের জন্য আখেরাতে জবাবদিহি আছে।"],"related_hadiths":[{"id":"2969","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"5554","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"2429","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="n"/>
     </row>
     <row r="159" ht="46" customHeight="1">
       <c r="A159" s="4" t="inlineStr">
@@ -4234,12 +4142,12 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সন্তানকে দেওয়া কথাও রাখতে হবে","description":"$book_name$ $hadith_number$ - $chapter_name$. শিশুকে কিছু দেওয়ার কথা বলে না দিলে মিথ্যা লেখা হয়—এই শিক্ষামূলক হাদিস পড়ুন।"},"heading":{"title":"সন্তানকে দেওয়া প্রতিশ্রুতি: খেজুরের ঘটনায় সত্যবাদিতার শিক্ষা","description":"এই হাদিসে একটি ঘরোয়া ঘটনা এসেছে। আবদুল্লাহ ইবনে আমির রাদিয়াল্লাহু আনহুকে তাঁর মা ডাকলেন এবং বললেন, আসো, তোমাকে কিছু দেব। রাসূল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম তখন তাঁদের ঘরে ছিলেন। তিনি জিজ্ঞেস করলেন, তুমি তাকে কী দিতে চাও? মা বললেন, খেজুর দেব। তখন নবীজি জানালেন, যদি কিছু না দাও, তবে তা মিথ্যা হিসেবে লেখা হবে। এই হাদিস আমাদের শেখায়, সন্তানকে দেওয়া ছোট প্রতিশ্রুতিও হালকা নয়। মা-বাবা যদি কথা রাখে, শিশু সত্য ও আস্থার পরিবেশে বড় হয়। আর কথা না রাখলে শিশুর মনেও মিথ্যা সহজ হয়ে যেতে পারে।"},"teachings":["সন্তানকে দেওয়া কথাও গুরুত্বের সাথে রাখা দরকার।","শিশুকে ডাকার জন্য মিথ্যা বলা উচিত নয়।","ছোট প্রতিশ্রুতিও মিথ্যা বা সত্যের অংশ হতে পারে।","মা-বাবার সত্যবাদিতা সন্তানের চরিত্র গঠনে সাহায্য করে।"],"related_hadiths":[{"id":"4991","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4990","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শাসকদের যুগ ও পাপকে হালাল মনে করার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইসলামের শুরু, খেলাফত, কঠোর শাসন এবং পাপকে হালাল মনে করার ভয়াবহ পরিণতি সম্পর্কে সতর্ক শিক্ষা।"},"heading":{"title":"অত্যাচারী শাসক ও পাপকে হালাল মনে করার হাদিস","description":"এই হাদিসের মূল বিষয় শাসনব্যবস্থা, ফিতনা এবং পাপকে হালাল মনে করার ভয়াবহতা। এখানে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ইসলামের শুরুতে নবুয়ত ও রহমতের কথা বলেছেন। এরপর খেলাফত ও রহমতের যুগের কথা এসেছে। তারপর এমন রাজত্ব ও কঠোর শাসনের কথা বলা হয়েছে, যেখানে যুলুম, উচ্ছৃঙ্খলতা এবং জমিনে বিপর্যয় দেখা দেবে। হাদিসে বিশেষভাবে বলা হয়েছে, কিছু অত্যাচারী শাসক রেশম, অবৈধ সম্পর্ক ও মদকে হালাল মনে করবে। তাদের দুনিয়াবী রিযিক ও সাহায্য পাওয়া যেতে পারে, কিন্তু সেটি তাদের কাজের সঠিকতা প্রমাণ করে না। তাই মুমিনের জন্য শিক্ষা হলো—ক্ষমতা, ধন বা বাহ্যিক সফলতা দেখে পাপকে ছোট মনে করা যাবে না। তাই নেতৃত্বের অবস্থানে থাকা মানুষদের জন্য এটি আরও বড় সতর্কতা, আর সাধারণ মানুষের জন্যও সত্য ও পাপের পার্থক্য বুঝে চলার শিক্ষা।"},"teachings":["ক্ষমতা ও দুনিয়াবী সাফল্য পাপকে বৈধ করে না।","রহমতপূর্ণ নেতৃত্ব মানুষের জন্য কল্যাণের পথ খুলে দেয়।","যুলুম, মদ ও অশ্লীলতাকে হালাল মনে করা বড় সতর্কতার বিষয়।","দুনিয়ার সাহায্য পেলেও আল্লাহর সামনে জবাবদিহি থেকে কেউ মুক্ত নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"81","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E159" s="4" t="n"/>
@@ -4257,12 +4165,12 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | হাসানোর জন্য মিথ্যা বলার ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মানুষকে হাসানোর জন্য মিথ্যা বলা নিয়ে নবীজির কঠিন সতর্ক বাণী জানুন।"},"heading":{"title":"হাসানোর জন্য মিথ্যা বলা: মজার কথাতেও সত্যের গুরুত্ব","description":"এই হাদিসে সেই ব্যক্তির জন্য কঠিন সতর্কতা এসেছে, যে মানুষকে হাসানোর জন্য মিথ্যা কথা বলে। নবীজি বলেছেন, তার জন্য ধ্বংস, তার জন্য ধ্বংস। কথাটি আমাদের দৈনন্দিন জীবনের একটি সাধারণ ভুল ধরিয়ে দেয়। অনেক সময় আড্ডা, গল্প, বক্তৃতা বা অনলাইনে মানুষ হাসানোর জন্য বানানো কথা বলে। কেউ ভাবতে পারে, এটি তো শুধু মজা। কিন্তু হাদিস দেখাচ্ছে, মজার নামেও মিথ্যা হালকা নয়। সত্যবাদিতা শুধু গুরুতর আলোচনায় দরকার নয়; হাসি-ঠাট্টাতেও দরকার। মুমিনের কথা এমন হওয়া উচিত, যাতে মানুষ আনন্দ পেলেও মিথ্যা বা ধোঁকার ওপর দাঁড়িয়ে না থাকে।"},"teachings":["মানুষকে হাসানোর জন্য মিথ্যা বলা থেকে বাঁচতে হবে।","মজা করেও মিথ্যা বলা হালকা বিষয় নয়।","আড্ডা ও গল্পেও সত্যবাদিতা দরকার।","কথার মাধ্যমে মানুষকে আনন্দ দিতে হলে মিথ্যা ছাড়াই দেওয়া উচিত।"],"related_hadiths":[{"id":"4990","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4800","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতের আলামত ও ইলম কমে যাওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইলম কমে যাওয়া, মূর্খতা, ব্যভিচার, মদপান ও নারী-পুরুষের সংখ্যার পরিবর্তন—কিয়ামতের কিছু আলামত।"},"heading":{"title":"কিয়ামতের আলামত: ইলম কমে যাওয়া ও মদপান বৃদ্ধি","description":"এই হাদিসে কিয়ামতের আলামত নিয়ে কয়েকটি স্পষ্ট সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, বিদ্যা উঠে যাবে বা কমে যাবে, মূর্খতা বেড়ে যাবে, ব্যভিচার বেশি হবে এবং মদপান বৃদ্ধি পাবে। আরও বলা হয়েছে, পুরুষের সংখ্যা কমে যাবে এবং নারীর সংখ্যা বেশি হবে, এমনকি একজন পুরুষ বহু নারীর দায়িত্বে থাকবে। হাদিসটি আমাদের বোঝায় যে সমাজে দ্বীনি জ্ঞান কমে গেলে ভুল কাজ সহজে ছড়িয়ে পড়ে। তাই কিয়ামতের আলামত হাদিস পড়ার উদ্দেশ্য শুধু ভবিষ্যৎ জানা নয়; বরং নিজের জীবনে ইলম, লজ্জাশীলতা, সংযম এবং হারাম থেকে বাঁচার চেষ্টা বাড়ানো। এই বার্তাটি সরল কিন্তু গভীর। তাই পাঠকের উচিত হাদিসটি পড়ে ভয় পাওয়ার পাশাপাশি নিজের ঘর, শিক্ষা ও চরিত্রের দিকে বাস্তবভাবে নজর দেওয়া।"},"teachings":["দ্বীনি ইলম কমে যাওয়া সমাজের জন্য বড় সতর্কতা।","মূর্খতা বাড়লে হারাম কাজের পথ সহজ হয়।","মদপান ও ব্যভিচার বৃদ্ধি কিয়ামতের আলামতের মধ্যে এসেছে।","হাদিসটি জ্ঞান ও নৈতিকতার গুরুত্ব মনে করিয়ে দেয়।"],"related_hadiths":[{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"81","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E160" s="4" t="n"/>
@@ -4280,12 +4188,12 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর কঠিন পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. বৃদ্ধ ব্যভিচারী, মিথ্যুক শাসক ও অহংকারী গরীব সম্পর্কে কিয়ামতের কঠিন সতর্কতা জানুন।"},"heading":{"title":"মিথ্যুক শাসকসহ তিন শ্রেণীর মানুষের কঠিন সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের কথা এসেছে, যাদের ব্যাপারে কিয়ামতের দিন কঠিন সতর্কতা দেওয়া হয়েছে। তারা হলো বৃদ্ধ ব্যভিচারকারী, মিথ্যুক শাসক এবং অহংকারী গরীব। হাদিসে বলা হয়েছে, আল্লাহ তাদের সাথে কথা বলবেন না, তাদের পবিত্র করবেন না, দয়ার দৃষ্টিতে তাকাবেন না এবং তাদের জন্য কষ্টদায়ক শাস্তি রয়েছে। এখানে বিশেষভাবে মিথ্যুক শাসকের কথা আমাদের দায়িত্ব ও ক্ষমতার জায়গায় সত্যের গুরুত্ব বুঝায়। যার হাতে নেতৃত্ব বা ক্ষমতা আছে, তার মিথ্যা শুধু নিজের ক্ষতি করে না; অন্যদেরও ক্ষতিগ্রস্ত করতে পারে। আর অহংকার ও পাপ যেকোন অবস্থায় ভয়ংকর বিষয়।"},"teachings":["মিথ্যুক শাসকের বিষয়ে হাদিসে কঠিন সতর্কতা এসেছে।","ক্ষমতা থাকলে সত্যবাদিতা আরও বেশি জরুরি।","অহংকার ও পাপ মানুষকে কঠিন পরিণতির দিকে নিতে পারে।","বয়স, পদ বা দারিদ্র্য কোনো পাপকে হালকা করে না।"],"related_hadiths":[{"id":"107","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"91","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, গায়িকা ও বাদ্যযন্ত্রের ভয়াবহ সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপান, গায়িকা নিয়ে নাচ-গান ও বাদ্যযন্ত্রে মত্ততার কারণে বড় বিপদের বিষয়ে হাদিসের সতর্কতা।"},"heading":{"title":"মদ ও বাদ্যযন্ত্র সম্পর্কে ভয়াবহ সতর্কবার্তার হাদিস","description":"এই হাদিসের মূল বিষয় মদ, গায়িকা নিয়ে নাচ-গান এবং বাদ্যযন্ত্রে ব্যস্ত থাকা। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের মধ্যে এমন সময় আসবে যখন মানুষ নেশাদার দ্রব্য পান করবে, গায়িকাদের নিয়ে নাচ-গানে মত্ত হবে এবং বাদ্যযন্ত্র নিয়ে ব্যস্ত হবে। তখন তিন ধরনের ভয়াবহ বিপদের কথা বলা হয়েছে: ভূমি ধসে যাওয়া, উপর থেকে বা কোনো জাতির পক্ষ থেকে যুলুম চাপিয়ে দেওয়া, এবং অনেকের আকার-আকৃতি বিকৃত হওয়া। এখানে শিক্ষা হলো, আনন্দের নামে হারামকে সাধারণ বানানো নিরাপদ পথ নয়। হাদিসটি মানুষকে মদ, নাচ-গান এবং বাদ্যযন্ত্রের ফিতনা থেকে সাবধান হতে বলছে। তাই সতর্কতা শুরু হতে পারে নিজের পছন্দ, বন্ধু-বান্ধব এবং অবসর কাটানোর ধরন ঠিক করার মাধ্যমে।"},"teachings":["মদপানকে হাদিসে বড় বিপদের কারণ হিসেবে উল্লেখ করা হয়েছে।","গায়িকা ও নাচ-গানে মত্ত হওয়া থেকে সতর্ক করা হয়েছে।","বাদ্যযন্ত্রের প্রতি আসক্তি হাদিসে নিন্দিতভাবে এসেছে।","সমাজে হারাম কাজ ছড়ালে বিপদের আশঙ্কা বাড়ে।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E161" s="4" t="n"/>
@@ -4303,12 +4211,12 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শেষ যামানার মিথ্যাবাদী দাজ্জালদের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. শেষ যামানায় মিথ্যাবাদীরা নতুন কথা ছড়াবে; তাদের থেকে দূরে থেকে পথভ্রষ্টতা থেকে বাঁচতে বলা হয়েছে।"},"heading":{"title":"শেষ যামানার মিথ্যাবাদী দাজ্জাল থেকে বাঁচার সতর্কতা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) শেষ যামানার কিছু মিথ্যাবাদী দাজ্জালের কথা বলেছেন। তারা এমন সব কথা নিয়ে আসবে, যা মানুষ আগে শোনেনি এবং তাদের বাপ-দাদারাও শোনেনি। নবীজি স্পষ্টভাবে সাবধান করেছেন: তোমরা তাদের থেকে বেঁচে থাকো এবং তাদেরকে তোমাদের থেকে দূরে রাখো। কারণ তারা মানুষকে পথভ্রষ্ট করতে পারে এবং ফিতনায় ফেলতে পারে। এই হাদিসে মিথ্যা কথা, অদ্ভুত দাবি ও বিভ্রান্তির বিরুদ্ধে সতর্ক থাকার শিক্ষা আছে। নতুন কথা শুনলেই গ্রহণ করা ঠিক নয়। দ্বীনের বিষয়ে সত্য-মিথ্যা যাচাই, নিরাপদ থাকা এবং বিভ্রান্ত লোকদের প্রভাব থেকে দূরে থাকা খুব দরকার।"},"teachings":["শেষ যামানায় মিথ্যাবাদী লোকদের ব্যাপারে সতর্ক থাকতে হবে।","অচেনা ও ভিত্তিহীন কথা শুনে সহজে গ্রহণ করা উচিত নয়।","ভ্রান্ত কথা মানুষকে ফিতনায় ফেলতে পারে।","দ্বীনের বিষয়ে নিরাপদ থাকতে সত্য যাচাই করা দরকার।"],"related_hadiths":[{"id":"7","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"154","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"4333","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | খাদ্য-পানীয় ও আমোদ-প্রমোদের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য-পানীয় ও বিনোদনে ডুবে থাকা কিছু লোকের ভয়াবহ রূপান্তর সম্পর্কে সতর্ক করা হয়েছে।"},"heading":{"title":"ভোগ-বিলাস ও আমোদ-প্রমোদের পরিণতি নিয়ে হাদিস","description":"এই হাদিসে ভোগ-বিলাস, খাদ্য-পানীয় এবং আমোদ-প্রমোদের বিষয়ে কঠোর সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের কিছু লোক রাত কাটাবে নানা ধরনের খাবার, পানীয় ও বিনোদনে ডুবে থেকে। এরপর তাদের সকাল হবে বানর ও শূকরের আকৃতিতে রূপান্তরিত হয়ে। হাদিসটি আনন্দ বা খাবারকে আলাদা করে নিষিদ্ধ বলছে না; বরং এমন জীবনধারার দিকে সতর্ক করছে যেখানে মানুষ আল্লাহভীতি ভুলে ভোগ, নেশা এবং অসংযত বিনোদনে ডুবে যায়। মূল শিক্ষা হলো, আনন্দ যেন ঈমান, লজ্জা ও হারাম-হালালের সীমা নষ্ট না করে। দুনিয়ার মজা সাময়িক, কিন্তু জবাবদিহি খুব বাস্তব। পরিবার ও সমাজে এমন পরিবেশ তৈরি করা দরকার, যেখানে আনন্দ থাকবে কিন্তু হারামের সীমা অতিক্রম করা হবে না।"},"teachings":["ভোগ-বিলাসে ডুবে আল্লাহভীতি ভুলে যাওয়া বিপজ্জনক।","বিনোদন যদি হারামের পথে নেয়, তা থেকে সতর্ক থাকা দরকার।","হাদিসে কিছু লোকের ভয়াবহ পরিণতির কথা এসেছে।","খাবার-পানীয় ও আনন্দের ক্ষেত্রেও সীমা মানা জরুরি।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E162" s="4" t="n"/>
@@ -4326,12 +4234,12 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | দুই মুখের মানুষের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. দুনিয়ায় দ্বিমুখী আচরণকারীর কিয়ামতের ভয়াবহ পরিণতি সম্পর্কে হাদিসের শিক্ষা জানুন।"},"heading":{"title":"দ্বিমুখী চরিত্রের হাদিস: এক মুখে এক কথা, আরেক মুখে আরেক কথা নয়","description":"এই হাদিসে বলা হয়েছে, যার দুনিয়াতে দু’টি মুখ হবে, কিয়ামতের মাঠে তার মুখে আগুনের দু’টি জিহ্বা হবে। অর্থাৎ যে মানুষ একদলের সামনে এক কথা বলে, অন্য দলের সামনে উল্টো কথা বলে এবং মিথ্যা, চোগলখুরী বা পরনিন্দার মাধ্যমে সম্পর্ক নষ্ট করে—তার বিষয়ে কঠিন সতর্কতা এসেছে। দ্বিমুখী চরিত্র মানুষের আস্থা নষ্ট করে। এতে বন্ধু, পরিবার ও সমাজে ঝগড়া বাড়ে। মুমিনের কথা সোজা হওয়া উচিত। সে কারও সামনে এমন কথা বলবে না, যা অন্যের সামনে গিয়ে বদলে ফেলে। এই হাদিস আমাদের সত্যবাদী, পরিষ্কার এবং ভরসাযোগ্য হতে শেখায়।"},"teachings":["দ্বিমুখী আচরণের বিষয়ে হাদিসে কঠিন সতর্কতা এসেছে।","একজনের সামনে এক কথা, অন্যজনের সামনে আরেক কথা বলা ক্ষতিকর।","চোগলখুরী ও পরনিন্দা সম্পর্ক নষ্ট করে।","মুমিনের কথা পরিষ্কার ও বিশ্বাসযোগ্য হওয়া দরকার।"],"related_hadiths":[{"id":"4873","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"6056","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2606","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঈমান, সালাত, পরিবার ও গোনাহ থেকে বাঁচার দশ শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, ফরয সালাত ত্যাগ, মদপান, গোনাহ ও পরিবার বিষয়ে দশটি গুরুত্বপূর্ণ উপদেশ।"},"heading":{"title":"রাসূলের দশ উপদেশ: ঈমান, সালাত ও পরিবার জীবনের শিক্ষা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মু‘আয (রাঃ)-কে দশটি বিষয়ে উপদেশ দিয়েছেন। প্রথমে এসেছে আল্লাহর সাথে কাউকে শরীক না করা। এরপর পিতা-মাতার অবাধ্য না হওয়া, ইচ্ছা করে ফরয সালাত না ছাড়া, মদ পান না করা এবং গোনাহ থেকে বেঁচে থাকার কথা এসেছে। আরও আছে জিহাদ থেকে পলায়ন না করা, মহামারী দেখা দিলে যেখানে আছে সেখানে স্থির থাকা, সামর্থ্য অনুযায়ী পরিবারের জন্য ব্যয় করা, পরিবারকে আদব শেখানো এবং আল্লাহর ভয় মনে করিয়ে দেওয়া। হাদিসটি ব্যক্তিগত ঈমান, ইবাদত, পরিবার, শৃঙ্খলা ও দায়িত্ব—সব দিককে একসাথে মনে করিয়ে দেয়। এটি জীবনের জন্য সংক্ষিপ্ত কিন্তু শক্তিশালী দিকনির্দেশনা। ফলে এই দশ উপদেশ একজন মুসলিমকে ঘর, সমাজ ও ব্যক্তিগত ইবাদতে ভারসাম্য রাখতে সাহায্য করে।"},"teachings":["তাওহীদ হলো জীবনের সবচেয়ে মূল দায়িত্ব।","ইচ্ছা করে ফরয সালাত ত্যাগ করা বড় সতর্কতার বিষয়।","মদকে অশ্লীলতার মূল হিসেবে উল্লেখ করা হয়েছে।","পরিবারের ব্যয়, আদব ও আল্লাহভীতি শেখানো দায়িত্বের অংশ।"],"related_hadiths":[{"id":"527","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5975","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3371","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E163" s="4" t="n"/>
@@ -4349,12 +4257,12 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কবীরা গুনাহ থেকে বাঁচার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, হত্যা ও মিথ্যা কসম বা সাক্ষ্যের ভয়াবহতা বুঝুন।"},"heading":{"title":"কবীরা গুনাহ: শিরক, অবাধ্যতা, হত্যা ও মিথ্যার ভয়াবহ শিক্ষা","description":"এই হাদিসে বড় বড় কবীরা গুনাহের কয়েকটি স্পষ্ট উদাহরণ বলা হয়েছে। মূল বিষয় হলো, মানুষের ঈমান, পরিবার, জীবন ও কথার সততা—সবকিছু আল্লাহর কাছে গুরুত্বপূর্ণ। আল্লাহর সাথে কাউকে শরীক করা সবচেয়ে বড় অন্যায় হিসেবে এসেছে। এরপর পিতা-মাতার অবাধ্যতা বলা হয়েছে, যা পরিবার ও দায়িত্ববোধের সাথে জড়িত। কাউকে হত্যা করা মানুষের জীবনের অধিকার নষ্ট করে। আর মিথ্যা কসম বা মিথ্যা সাক্ষ্য মানুষের বিশ্বাস, বিচার ও সম্পর্ককে ক্ষতিগ্রস্ত করে। তাই এই হাদিস আমাদের শেখায়, বড় গুনাহ থেকে দূরে থাকতে হলে ঈমানকে শুদ্ধ রাখা, বাবা-মায়ের হক মানা, মানুষের জীবনকে সম্মান করা এবং কথায় সত্যবাদী থাকা জরুরি।"},"teachings":["আল্লাহর সাথে কাউকে শরীক করা বড় কবীরা গুনাহের অন্তর্ভুক্ত।","পিতা-মাতার অবাধ্যতা থেকে সতর্ক থাকা দরকার।","অন্যায়ভাবে কাউকে হত্যা করা ভয়াবহ গুনাহ।","মিথ্যা কসম ও মিথ্যা সাক্ষ্য মানুষের হক নষ্ট করতে পারে।"],"related_hadiths":[{"id":"161","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"162","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6871","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নেশাদার দ্রব্য সব অন্যায়ের চাবী","description":"$book_name$ $hadith_number$ - $chapter_name$. নেশাদার দ্রব্য থেকে দূরে থাকার উপদেশ এসেছে, কারণ তা বহু অন্যায়ের দরজা খুলে দিতে পারে।"},"heading":{"title":"নেশাদার দ্রব্য: সব অন্যায়ের চাবী সম্পর্কে হাদিস","description":"এই ছোট হাদিসটি খুব সহজ ভাষায় বড় শিক্ষা দেয়। আবূ দারদা (রাঃ) বলেন, তাঁর দোস্ত রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাঁকে অছিয়ত করেছেন—নেশাদার দ্রব্য পান করো না; নিশ্চয়ই তা সব ধরনের অন্যায়ের চাবী। এখানে মূল কথা হলো মদ বা নেশা মানুষকে শুধু একটি গোনাহে আটকে রাখে না; বরং তা বিবেক, লজ্জা এবং সংযম দুর্বল করে আরও অনেক ভুলের দিকে ঠেলে দিতে পারে। তাই ইসলাম শুধু শেষ ক্ষতি নয়, ক্ষতির দরজাও বন্ধ করতে শেখায়। এই হাদিস মাদক থেকে দূরে থাকা, সঙ্গ বাছাই করা এবং নিজের বিবেককে সুরক্ষিত রাখার পরিষ্কার বার্তা দেয়। বিশেষ করে তরুণদের জন্য এটি শক্ত বার্তা—নেশার শুরু ছোট মনে হলেও শেষটা খুব ক্ষতিকর হতে পারে।"},"teachings":["নেশাদার দ্রব্য থেকে দূরে থাকা নিরাপদ পথ।","মদকে বহু অন্যায়ের দরজা হিসেবে সতর্ক করা হয়েছে।","বিবেক নষ্ট হলে অন্য গোনাহে পড়ার ঝুঁকি বাড়ে।","ভালো উপদেশ মানা ঈমানি জীবনের অংশ।"],"related_hadiths":[{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3390","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E164" s="4" t="n"/>
@@ -4372,12 +4280,12 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিকের তিন আলামত","description":"$book_name$ $hadith_number$ - $chapter_name$. মিথ্যা বলা, ওয়াদা ভঙ্গ ও আমানতে খিয়ানত—মুনাফিকের তিন আলামত সম্পর্কে সহজ শিক্ষা।"},"heading":{"title":"মুনাফিকের আলামত: মিথ্যা, ওয়াদা ভঙ্গ ও আমানতে খিয়ানত","description":"এই হাদিসে মুনাফিকের আলামত তিনটি বলা হয়েছে। যখন সে কথা বলে, মিথ্যা বলে; ওয়াদা করলে তা ভঙ্গ করে; আর আমানত রাখা হলে খিয়ানত করে। এখানে ইসলাম মানুষের বাহ্যিক ইবাদতের পাশাপাশি চরিত্রকেও গুরুত্ব দিয়েছে। মুসলিমের পরিচয় শুধু সালাত বা সিয়ামের মধ্যে সীমিত নয়; কথার সত্যতা, প্রতিশ্রুতি রক্ষা এবং আমানতের দায়িত্বও তার জীবনের অংশ। মুসলিমের বর্ণনায় এসেছে, কেউ সালাত আদায় করলেও, সিয়াম পালন করলেও এবং নিজেকে মুসলিম মনে করলেও এই খারাপ গুণগুলো খুব বিপজ্জনক। তাই এই হাদিস আমাদের নিজের কথা, প্রতিশ্রুতি ও দায়িত্ব নিয়ে নিয়মিত ভাবতে শেখায়।"},"teachings":["মিথ্যা বলা মুনাফিকী স্বভাবের একটি বড় আলামত।","ওয়াদা করলে তা রক্ষা করা মুসলিম চরিত্রের অংশ।","অমানত রাখা হলে তা সঠিকভাবে ফিরিয়ে দেওয়া দরকার।","ইবাদতের পাশাপাশি চরিত্র ঠিক রাখা জরুরি।"],"related_hadiths":[{"id":"114","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"116","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2631","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সব নেশাদার দ্রব্য হারাম হওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. হাদিসে স্পষ্ট বলা হয়েছে, যে কোনো নেশা উদ্রেককারী বস্তু হারাম; তাই মাদক থেকে দূরে থাকা জরুরি।"},"heading":{"title":"সব নেশাদার দ্রব্য হারাম: স্পষ্ট হাদিসের শিক্ষা","description":"এই হাদিসের মূল শিক্ষা খুব সরল: সব ধরনের নেশাদার দ্রব্য হারাম। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, “কুল্লু মুসকিরিন হারাম”—প্রতিটি নেশা উদ্রেককারী জিনিস হারাম। তাই বিষয়টি শুধু নির্দিষ্ট কোনো পানীয়ের মধ্যে সীমাবদ্ধ নয়। যে জিনিস মানুষের বিবেক ঢেকে দেয়, সিদ্ধান্ত নেওয়ার ক্ষমতা দুর্বল করে এবং তাকে ভুল কাজে ঠেলে দেয়, সেটি এই সতর্কতার মধ্যে পড়ে। হাদিসটি মুসলিমকে নাম বা ধরন নিয়ে চালাকি না করতে শেখায়। মদ, মাদক বা যে কোনো নেশা—মূল বিচার হলো তা নেশা সৃষ্টি করে কি না। ঈমানদার জীবনে বিবেক রক্ষা করা বড় দায়িত্ব। এ কারণে নেশা নিয়ে মজা, পরীক্ষা বা কৌতূহল দেখানোও মুমিনের জন্য ঝুঁকিপূর্ণ আচরণ হতে পারে।"},"teachings":["নেশা সৃষ্টি করে এমন জিনিস থেকে বাঁচতে হবে।","হারামকে নাম বদলে বৈধ ভাবা ঠিক নয়।","বিবেক ও সংযম রক্ষা করা ঈমানি জীবনের অংশ।","হাদিসটি মাদক বিষয়ে সংক্ষিপ্ত কিন্তু স্পষ্ট নির্দেশ দেয়।"],"related_hadiths":[{"id":"3390","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3393","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E165" s="4" t="n"/>
@@ -4395,12 +4303,12 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুনাফিকীর চার স্বভাব","description":"$book_name$ $hadith_number$ - $chapter_name$. খিয়ানত, মিথ্যা, ওয়াদা ভঙ্গ ও ঝগড়ায় অশ্লীলতা—মুনাফিকী স্বভাব থেকে বাঁচার শিক্ষা।"},"heading":{"title":"মুনাফিকীর চার স্বভাব: নিজের চরিত্র যাচাই করার হাদিস","description":"এই হাদিসে চারটি স্বভাবের কথা এসেছে, যা মানুষের চরিত্রকে খুব ক্ষতিগ্রস্ত করে। আমানত রাখা হলে খিয়ানত করা, কথা বললে মিথ্যা বলা, ওয়াদা করলে ভঙ্গ করা এবং ঝগড়ার সময় অশ্লীল ভাষা ব্যবহার করা—এগুলোকে মুনাফিকী স্বভাব বলা হয়েছে। হাদিসে আরও বলা হয়েছে, যার মধ্যে এসবের একটি থাকবে, সে তা না ছাড়লে তার মধ্যে মুনাফিকীর একটি স্বভাব থাকবে। এখানে মূল শিক্ষা হলো আত্মপরীক্ষা। আমরা অনেক সময় নিজেদের ভালো মনে করি, কিন্তু কথা, প্রতিশ্রুতি, আমানত ও রাগের সময় ভাষা—এসব জায়গায় ভুল করি। তাই এই হাদিস মানুষকে নিজের আচরণ ঠিক করতে নরম কিন্তু শক্ত সতর্কতা দেয়।"},"teachings":["আমানতে খিয়ানত করা মুনাফিকী স্বভাবের অন্তর্ভুক্ত।","মিথ্যা কথা মানুষের ঈমানী চরিত্রকে দুর্বল করে।","চুক্তি বা ওয়াদা ভঙ্গ করা গুরুতর খারাপ অভ্যাস।","ঝগড়ার সময় অশ্লীল ভাষা থেকে দূরে থাকা দরকার।"],"related_hadiths":[{"id":"34","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"113","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"2632","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিবেক নষ্টকারী বস্তুই মদ—হারামের স্পষ্ট মানদণ্ড","description":"$book_name$ $hadith_number$ - $chapter_name$. যা বিবেকের ক্ষতি করে তা মদের অন্তর্ভুক্ত, আর সব ধরনের মদ হারাম—হাদিসের সরল শিক্ষা।"},"heading":{"title":"মদ কাকে বলে: বিবেক নষ্টকারী সব নেশার হুকুম","description":"এই হাদিসে মদের পরিচয় খুব সহজভাবে এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, প্রত্যেক নেশাদার বস্তুই মদ, আর প্রত্যেক মদই হারাম। অর্থাৎ মদ শুধু আঙুর, খেজুর বা নির্দিষ্ট কোনো নামে সীমাবদ্ধ নয়। যে জিনিস পান, খাওয়া বা গ্রহণ করলে মানুষের বিবেক ও বোঝার ক্ষমতা নষ্ট হয়, সেটি খামর বা মদের হুকুমের মধ্যে পড়ে। এই হাদিস নামের চেয়ে প্রভাবকে গুরুত্ব দেয়। তাই কোনো বস্তু আধুনিক নাম, নতুন প্যাকেট বা ভিন্ন রূপে এলেও যদি তা নেশা সৃষ্টি করে, তাহলে মুমিনের জন্য সতর্কতা একই থাকে। মূল কথা: বিবেক আল্লাহর বড় নেয়ামত, একে নেশার হাতে তুলে দেওয়া যাবে না। তাই পরিবারে ও সমাজে মাদককে সাধারণ বিষয় বানানো নয়, বরং পরিষ্কারভাবে ভুল বলা দরকার।"},"teachings":["নেশা সৃষ্টি করলে নাম বদলালেও হুকুম বদলায় না।","বিবেক নষ্টকারী বস্তু থেকে দূরে থাকা জরুরি।","সব ধরনের মদ হারাম—হাদিসে স্পষ্ট বলা হয়েছে।","মুমিনের জন্য হালাল-হারামের মানদণ্ড প্রভাবের ওপরও নির্ভর করে।"],"related_hadiths":[{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3393","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E166" s="4" t="n"/>
@@ -4418,12 +4326,12 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | জিহ্বা সংযমের গুরুত্ব","description":"$book_name$ $hadith_number$ - $chapter_name$. রাসূল صلى الله عليه وسلم জিহ্বার দিকে ইঙ্গিত করে কথার বিপদ থেকে সতর্ক করেছেন—এ হাদিসের সহজ শিক্ষা।"},"heading":{"title":"জিহ্বা সংযম: কথার কারণে বিপদে পড়া থেকে বাঁচার শিক্ষা","description":"এই হাদিসে একজন সাহাবী রাসূলুল্লাহ صلى الله عليه وسلم-কে জিজ্ঞেস করেন, তাঁর জন্য সবচেয়ে বেশি ভয়ের বিষয় কী। রাসূল صلى الله عليه وسلم নিজের জিহ্বা ধরলেন এবং বললেন, এটি। হাদিসটি খুব ছোট, কিন্তু শিক্ষা গভীর। মানুষ অনেক সময় হাতে বা কাজে যত ভুল করে, কথার মাধ্যমেও তত বড় ক্ষতি করে বসে। মিথ্যা, কষ্টদায়ক কথা, অশ্লীল ভাষা, গীবত বা অন্যের ক্ষতি করা কথা—এসবের দরজা খুলে যায় জিহ্বা নিয়ন্ত্রণ না করলে। তবে এই হাদিসে শুধু জিহ্বার ভয় বলা হয়েছে; অতিরিক্ত বিস্তারিত বিধান এখানে নেই। মূল বার্তা হলো, কথা বলার আগে ভাবা, অপ্রয়োজনীয় কথা কমানো এবং নিজের ভাষাকে আল্লাহর ভয় দিয়ে নিয়ন্ত্রণ করা।"},"teachings":["জিহ্বা মানুষের জন্য বড় পরীক্ষার কারণ হতে পারে।","কথা বলার আগে চিন্তা করা নিরাপদ অভ্যাস।","ভাষা নিয়ন্ত্রণ করা মুসলিম চরিত্রের গুরুত্বপূর্ণ অংশ।","অপ্রয়োজনীয় ও ক্ষতিকর কথা থেকে দূরে থাকা দরকার।"],"related_hadiths":[{"id":"2410","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3972","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"6474","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বেশি নেশা হলে কমও হারাম—সতর্কতার হাদিস","description":"$book_name$ $hadith_number$ - $chapter_name$. যে বস্তু বেশি খেলে নেশা হয়, তার অল্প পরিমাণও হারাম—হারাম থেকে দূরে থাকার পরিষ্কার শিক্ষা।"},"heading":{"title":"যার বেশি নেশা আনে, তার কমও হারাম: মাদক বিষয়ে হাদিস","description":"এই হাদিসে নেশাদার বস্তু সম্পর্কে একটি গুরুত্বপূর্ণ নীতি এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে বস্তু বেশি পরিমাণে গ্রহণ করলে বিবেকের ক্ষতি হয় বা নেশা আসে, তার কম পরিমাণও হারাম। এর মানে হলো, “অল্প খেলে ক্ষতি নেই”—এমন অজুহাত দিয়ে নেশার দরজা খোলা যাবে না। ইসলাম মানুষের বিবেক, আত্মসম্মান ও ইবাদতকে সুরক্ষিত রাখতে চায়। তাই যে জিনিস বেশি হলে মানুষকে মাতাল করে, সেটির সামান্য অংশও নিরাপদ খেলার বিষয় নয়। এই হাদিস মাদক, অ্যালকোহল ও নেশা নিয়ে আপস না করার শিক্ষা দেয়। ছোট ছাড় অনেক সময় বড় বিপদের শুরু হতে পারে। এই নীতি মানুষকে সন্দেহজনক নেশাদার জিনিস থেকেও দূরে থাকতে সাহায্য করে।"},"teachings":["অল্প নেশাদার দ্রব্যকেও হালকা মনে করা ঠিক নয়।","যার বেশি নেশা আনে, তার কমও হারাম।","হারামের দরজা শুরুতেই বন্ধ করা নিরাপদ।","বিবেক রক্ষা করা মুমিনের গুরুত্বপূর্ণ দায়িত্ব।"],"related_hadiths":[{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3390","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E167" s="4" t="n"/>
@@ -4441,12 +4349,12 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছয়টি অঙ্গীকার ও জান্নাতের আশা","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য কথা, ওয়াদা পূরণ, আমানত আদায়, লজ্জাস্থান, দৃষ্টি ও হাত হেফাজতের শিক্ষা।"},"heading":{"title":"ছয়টি অঙ্গীকার: সত্যবাদিতা, আমানত ও চরিত্র রক্ষার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم ছয়টি বিষয়ের জামানত চাইছেন। এগুলো হলো কথা বললে সত্য বলা, ওয়াদা করলে তা পূর্ণ করা, আমানত রাখা হলে তা আদায় করা, লজ্জাস্থান হেফাজত করা, দৃষ্টি নিচু রাখা এবং হাতকে অন্যায় কাজ থেকে বিরত রাখা। এখানে সততা, আমানতদারি ও শালীনতা একসাথে এসেছে। একজন মুসলিম শুধু মুখে ভালো কথা বললেই যথেষ্ট নয়; তার কথা, চুক্তি, দৃষ্টি, শরীর ও হাত—সবকিছুতে দায়িত্ববোধ থাকা দরকার। হাদিসে জান্নাতের যামিনের কথা এসেছে, তাই বিষয়গুলোকে হালকা করে দেখা উচিত নয়। তবে এর শিক্ষা হলো চেষ্টা, নিয়ন্ত্রণ এবং নিজের নফসকে ভালো পথে রাখা।"},"teachings":["কথা বললে সত্য বলা মুসলিম চরিত্রের ভিত্তি।","ওয়াদা ও আমানত রক্ষা করা বড় দায়িত্ব।","দৃষ্টি ও লজ্জাস্থান হেফাজত করা শালীনতার অংশ।","হাতকে অন্যায় কাজ থেকে বিরত রাখা দরকার।"],"related_hadiths":[{"id":"6474","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"6136","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2410","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে রবকে দেখা ও আমলের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে রবকে দেখা, নেয়ামতের জবাবদিহি ও অঙ্গ-প্রত্যঙ্গের সাক্ষ্য—এই হাদিসে সতর্কতা এসেছে।"},"heading":{"title":"কিয়ামতের দিন রবকে দেখা ও অঙ্গের সাক্ষ্যের শিক্ষা","description":"এই হাদিসে সাহাবীরা জিজ্ঞেস করেছেন, কিয়ামতের দিন তারা কি তাদের রবকে দেখতে পাবে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সূর্য ও পূর্ণিমার চাঁদ দেখার উদাহরণ দিয়ে বলেছেন, রবকে দেখতে অসুবিধা হবে না। এরপর তিনি বান্দাদের জবাবদিহির কথা বলেন। আল্লাহ বান্দাকে নিজের দেওয়া মর্যাদা, নেতৃত্ব, পরিবার ও নিয়ামতের কথা স্মরণ করাবেন। কেউ আল্লাহর সাক্ষাতের কথা অস্বীকার করেছিল বলে তাকে কঠিন পরিণতির কথা বলা হবে। আর এক ব্যক্তি নিজের ভালো কাজের কথা বললেও তার মুখে মোহর লাগিয়ে অঙ্গ-প্রত্যঙ্গকে সাক্ষ্য দিতে বলা হবে। হাদিসে তাকে মুনাফিক বলা হয়েছে। এই হাদিস নেয়ামত, হিসাব, মুনাফিকী এবং সত্য সাক্ষ্যের কথা মনে করায়।"},"teachings":["কিয়ামতের দিন রবকে দেখার বিষয়টি হাদিসে এসেছে।","আল্লাহর দেওয়া নিয়ামতের জন্য জবাবদিহি থাকবে।","মুখে দাবি করলেই যথেষ্ট নয়, কাজের সাক্ষ্যও আসবে।","মুনাফিকী আচরণ আল্লাহর ক্রোধের কারণ হতে পারে।"],"related_hadiths":[{"id":"2968","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"7440","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5555","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
         </is>
       </c>
       <c r="E168" s="4" t="n"/>
@@ -4464,12 +4372,12 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সত্যবাদিতার পথ ও মিথ্যার ক্ষতি","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য মানুষকে পুণ্যের পথে নেয়, আর মিথ্যা পাপের দিকে ঠেলে দেয়—এ হাদিসের শিক্ষা।"},"heading":{"title":"সত্যবাদিতা: জান্নাতের পথে চলার সুন্দর শিক্ষা","description":"এই হাদিসে সত্য ও মিথ্যার ফল খুব পরিষ্কারভাবে বলা হয়েছে। সত্য পুণ্যময় কাজ, আর পুণ্য জান্নাতের পথ দেখায়। যে ব্যক্তি সত্যের উপর দৃঢ় থাকে, তাকে আল্লাহর কাছে সত্যনিষ্ঠ হিসেবে লেখা হয়। অন্যদিকে মিথ্যা পাপকাজ, আর পাপ জাহান্নামের পথ দেখায়। যে মিথ্যায় অভ্যস্ত হয়ে পড়ে, তাকে আল্লাহর কাছে মিথ্যুক হিসেবে লেখা হয়। এখানে মূল শিক্ষা হলো অভ্যাসের প্রভাব। একবার সত্য বলা ভালো, কিন্তু নিয়মিত সত্য বলা মানুষকে সত্যনিষ্ঠ করে। একইভাবে মিথ্যাকে ছোট মনে করলে তা অভ্যাসে পরিণত হতে পারে। তাই দৈনন্দিন কথা, লেনদেন, পরিবার ও সমাজে সত্যবাদিতা ধরে রাখা ঈমানী চরিত্রের বড় অংশ।"},"teachings":["সত্য কথা পুণ্যের পথে নিয়ে যায়।","নিয়মিত সত্য বলার অভ্যাস মানুষকে সত্যনিষ্ঠ করে।","মিথ্যা পাপের দিকে নিয়ে যেতে পারে।","মিথ্যায় অভ্যস্ত হওয়া থেকে শুরুতেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"6094","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2607","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1971","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, মৃতপ্রাণী ও শূকরের মূল্য হারাম","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ মদ, মৃতপ্রাণী ও শূকর এবং এগুলোর মূল্য হারাম করেছেন—হারাম আয় থেকে বাঁচার শিক্ষা।"},"heading":{"title":"হারাম আয়: মদ ও নিষিদ্ধ বস্তুর মূল্য সম্পর্কে হাদিস","description":"এই হাদিসে শুধু মদ পান নয়, মদের মূল্য বা এর অর্থনৈতিক লেনদেনের দিকেও সতর্ক করা হয়েছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ নেশাদার দ্রব্য এবং তার মূল্য হারাম করেছেন। একইভাবে মৃতপ্রাণী ও তার মূল্য, শূকর ও তার মূল্যও হারাম করা হয়েছে। এখানে গুরুত্বপূর্ণ শিক্ষা হলো—কোনো বস্তু হারাম হলে তার ব্যবসা, মূল্য এবং লাভও সতর্কতার বিষয় হয়। মানুষ অনেক সময় নিজে না খেয়ে বিক্রি করে লাভ নেওয়াকে হালকা মনে করতে পারে। কিন্তু এই হাদিস জানায়, হারাম জিনিস থেকে অর্থ উপার্জনও নিরাপদ নয়। রিযিক পবিত্র রাখা ঈমানি জীবনের বড় অংশ। তাই আয়ের উৎস যাচাই করা এবং সন্দেহজনক লাভ থেকে বাঁচা একজন মুসলিমের নিত্যদিনের দায়িত্ব।"},"teachings":["মদ শুধু পান নয়, তার মূল্যও হারাম বলা হয়েছে।","হারাম বস্তু থেকে আয় নেওয়া থেকে বাঁচতে হবে।","রিযিক পবিত্র রাখা মুসলিম জীবনের গুরুত্বপূর্ণ কাজ।","মৃতপ্রাণী ও শূকরের মূল্য সম্পর্কেও হাদিসে সতর্কতা এসেছে।"],"related_hadiths":[{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E169" s="4" t="n"/>
@@ -4487,12 +4395,12 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুখ ও লজ্জাস্থান হেফাজত","description":"$book_name$ $hadith_number$ - $chapter_name$. জিহ্বা ও লজ্জাস্থান হেফাজতের অঙ্গীকার জান্নাতের আশার বড় কারণ—হাদিসের শিক্ষা।"},"heading":{"title":"মুখ ও লজ্জাস্থান হেফাজত: জান্নাতের আশার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ صلى الله عليه وسلم দুইটি গুরুত্বপূর্ণ অঙ্গের দায়িত্ব নেওয়ার কথা বলেছেন। এক হলো দুই চোয়ালের মাঝের বস্তু, অর্থাৎ জিহ্বা; আর অন্যটি দুই পায়ের মাঝের বস্তু, অর্থাৎ লজ্জাস্থান। যে এগুলোর যিম্মাদার হবে, রাসূল صلى الله عليه وسلم তার জন্য জান্নাতের যিম্মাদার হওয়ার কথা বলেছেন। এখানে মানুষের চরিত্রের দুই বড় দরজা বোঝানো হয়েছে—কথা ও কামনা। জিহ্বা দিয়ে মিথ্যা, গালি, কষ্টদায়ক কথা বা অন্যায় কথা হতে পারে। লজ্জাস্থান নিয়ন্ত্রণ না করলে অবৈধ সম্পর্কের দিকে মানুষ ঝুঁকে যেতে পারে। তাই এই হাদিস মুসলিমকে নিজের ভাষা ও শালীনতা নিয়ে সতর্ক থাকতে শেখায়।"},"teachings":["জিহ্বা হেফাজত করা জান্নাতের আশার একটি বড় কারণ।","লজ্জাস্থান হেফাজত করা চরিত্র রক্ষার অংশ।","কথা ও কামনা—দুই ক্ষেত্রেই আত্মনিয়ন্ত্রণ দরকার।","নিজের অঙ্গের দায়িত্ব নেওয়া ঈমানী শৃঙ্খলার অংশ।"],"related_hadiths":[{"id":"6474","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2410","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3972","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, মৃতপ্রাণী, শূকর ও মূর্তি বিক্রি হারাম","description":"$book_name$ $hadith_number$ - $chapter_name$. মক্কা বিজয়ের বছরে নবীজি মদ, মৃতপ্রাণী, শূকর ও মূর্তির ক্রয়-বিক্রয় হারাম হওয়ার কথা বলেছেন।"},"heading":{"title":"হারাম ব্যবসা: মদ ও মূর্তি ক্রয়-বিক্রয় সম্পর্কে হাদিস","description":"এই হাদিসে মক্কা বিজয়ের বছরে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর একটি ঘোষণা এসেছে। তিনি বলেছেন, আল্লাহ মদ, মৃতপ্রাণী, শূকর এবং মূর্তির ক্রয়-বিক্রয় হারাম করেছেন। এখানে শিক্ষা শুধু কিছু জিনিস খাওয়া বা ব্যবহার না করার মধ্যে সীমাবদ্ধ নয়; বরং সেগুলোকে ব্যবসার পণ্য বানানো থেকেও বারণ করা হয়েছে। ইসলামে রিযিকের পবিত্রতা খুব গুরুত্বপূর্ণ। লাভ বেশি হলেই কোনো ব্যবসা ভালো হয়ে যায় না। হালাল-হারামের সীমা মানতে হয়। এই হাদিস ব্যবসায়ী, ক্রেতা ও সমাজ—সবার জন্য সতর্কতা: এমন পণ্য থেকে দূরে থাকা দরকার, যাকে আল্লাহ হারাম করেছেন। তাই ব্যবসায় সততা মানে শুধু ওজন ঠিক রাখা নয়, পণ্যটিও হালাল হওয়া। বিশেষ করে যে পণ্য মানুষের ঈমান, বিবেক বা তাওহীদের ক্ষতি করে, তা থেকে আয় করা মুমিনের জন্য নিরাপদ পথ নয়।"},"teachings":["হারাম জিনিস ব্যবসার পণ্য বানানো যায় না।","মদ, মৃতপ্রাণী, শূকর ও মূর্তির ক্রয়-বিক্রয় নিষিদ্ধ বলা হয়েছে।","লাভের চেয়ে হালাল রিযিক বেশি গুরুত্বপূর্ণ।","ব্যবসায়ও আল্লাহর সীমা মানা জরুরি।"],"related_hadiths":[{"id":"3485","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E170" s="4" t="n"/>
@@ -4510,12 +4418,12 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | রক্ষাকারী ও ধ্বংসকারী কাজ","description":"$book_name$ $hadith_number$ - $chapter_name$. তাকওয়া, হক কথা ও মধ্যম পথ রক্ষা করে; প্রবৃত্তি, কৃপণতা ও অহংকার ধ্বংসের কারণ।"},"heading":{"title":"রক্ষাকারী তিন কাজ ও ধ্বংসকারী তিন কাজ: তাকওয়ার হাদিস","description":"এই হাদিসে মানুষের জন্য তিনটি রক্ষাকারী কাজ এবং তিনটি ধ্বংসকারী কাজ বলা হয়েছে। রক্ষাকারী কাজ হলো প্রকাশ্যে ও গোপনে আল্লাহকে ভয় করা, সন্তুষ্টি ও অসন্তুষ্টি—উভয় অবস্থায় হক কথা বলা এবং সচ্ছলতা ও অসচ্ছলতায় মধ্যম পথ রাখা। অর্থাৎ ভালো চরিত্র শুধু মানুষের সামনে নয়, একান্ত অবস্থাতেও দরকার। আবার সত্য কথা শুধু সুবিধার সময়ে নয়, রাগ বা অসন্তুষ্টির সময়েও জরুরি। ধ্বংসকারী কাজ হলো প্রবৃত্তির অনুসরণ, কৃপণতাকে মেনে নেওয়া এবং নিজের প্রতি অহংকার করা। হাদিসে আত্ম-অহংকারকে সবচেয়ে কঠিন বলা হয়েছে। তাই এই শিক্ষা আমাদের ভারসাম্য, সত্য এবং বিনয়ী জীবনের দিকে ডাকে।"},"teachings":["প্রকাশ্যে ও গোপনে আল্লাহকে ভয় করা রক্ষাকারী কাজ।","সন্তুষ্টি ও অসন্তুষ্টি—দুই অবস্থাতেই হক কথা বলা দরকার।","সচ্ছলতা ও অসচ্ছলতায় মধ্যম পথ রাখা ভালো অভ্যাস।","প্রবৃত্তি, কৃপণতা ও অহংকার ধ্বংসের কারণ হতে পারে।"],"related_hadiths":[{"id":"168","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1987","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"7200","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপান, পিতামাতার অবাধ্যতা ও খোটা দানের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদে আসক্তি, পিতা-মাতার অবাধ্যতা ও দান করে খোটা দেওয়ার ভয়াবহ পরিণতি সম্পর্কে সতর্কতা।"},"heading":{"title":"মদপানকারী, অবাধ্য সন্তান ও খোটা দানকারী সম্পর্কে হাদিস","description":"এই হাদিসে তিনটি কাজের বিষয়ে কঠোর সতর্কতা এসেছে: নেশাদার দ্রব্য পান করা, পিতা-মাতার অবাধ্য হওয়া এবং দান করে খোটা দেওয়া। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, এ ধরনের লোক জান্নাতে যাবে না—হাদিসের ভাষা অত্যন্ত সতর্কতামূলক। এর অর্থ বুঝতে আল্লাহর রহমত, তাওবা এবং অন্যান্য শরঈ বিষয় আলাদা আলোচনার বিষয়; তবে এই হাদিসের সরাসরি শিক্ষা হলো, এসব কাজ খুব ভয়াবহ। মদ মানুষের বিবেক নষ্ট করে, পিতা-মাতার অবাধ্যতা সম্পর্ক ভেঙে দেয়, আর খোটা দান সদকার সৌন্দর্য নষ্ট করে। তাই মুমিনের উচিত এসব কাজ থেকে দূরে থাকা এবং ভুল হলে দ্রুত তাওবার পথে ফেরা। তাই এই তিনটি বিষয়ে পরিবারে নিয়মিত নসিহত, আত্মসমালোচনা এবং সংশোধনের পরিবেশ থাকা দরকার।"},"teachings":["মদে আসক্তি ভয়াবহ গোনাহের দিকে নিয়ে যেতে পারে।","পিতা-মাতার অবাধ্যতা থেকে সতর্ক থাকতে হবে।","দান করে খোটা দেওয়া দানের সৌন্দর্য নষ্ট করে।","হাদিসটি তিনটি গুরুতর আচরণ থেকে বাঁচার শিক্ষা দেয়।"],"related_hadiths":[{"id":"5975","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3371","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E171" s="4" t="n"/>
@@ -4533,12 +4441,12 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে মুমিনের গুনাহ ঢেকে মাফ","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতের দিন মুমিনের গুনাহ স্বীকারের পর আল্লাহ দুনিয়ায় ঢেকে রাখা গুনাহ মাফ করে দেবেন।"},"heading":{"title":"কিয়ামতের দিন মুমিনের গুনাহ ঢেকে মাফ করার হাদিস","description":"এই হাদিসে কিয়ামতের দিনের একটি গভীর দৃশ্য এসেছে। আল্লাহ মুমিন বান্দাকে নিজের নিকটবর্তী করবেন, তাকে ঢেকে রাখবেন এবং একে একে তার গুনাহ সম্পর্কে জিজ্ঞেস করবেন। বান্দা স্বীকার করবে যে সে গুনাহগুলো জানে। তখন সে মনে করবে, এসব কারণে সে ধ্বংস হয়ে যাবে। কিন্তু আল্লাহ বলবেন, দুনিয়াতে আমি তোমার এই গুনাহগুলো ঢেকে রেখেছিলাম, আজ আমি তা মাফ করে দিচ্ছি। তারপর তাকে নেকীর আমলনামা দেওয়া হবে। আর কাফের ও মুনাফিকদের ব্যাপারে সবার সামনে ঘোষণা হবে যে তারা রবের বিরুদ্ধে মিথ্যা বলত। এই হাদিস আল্লাহর ক্ষমা, গুনাহ ঢেকে রাখা এবং কিয়ামতের হিসাবের কথা মনে করায়।"},"teachings":["মুমিন বান্দা কিয়ামতে নিজের গুনাহ স্বীকার করবে।","আল্লাহ দুনিয়ায় গুনাহ ঢেকে রেখেছেন—এটি বড় দয়া।","ক্ষমা আল্লাহর পক্ষ থেকে আসে, তাই তাঁর দিকে ফিরতে হয়।","মিথ্যাচার ও মুনাফিকী কিয়ামতে প্রকাশ পাবে।"],"related_hadiths":[{"id":"2441","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"2768","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"5551","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ পান করলে ৪০ দিনের অসন্তুষ্টির সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপানের পর আল্লাহর অসন্তুষ্টির কথা এসেছে, যা মাদক থেকে দূরে থাকার কঠোর সতর্কবার্তা।"},"heading":{"title":"মদ পান করলে ৪০ দিন আল্লাহর অসন্তুষ্টি: হাদিসের শিক্ষা","description":"এই হাদিসে মদপানের পরিণতি নিয়ে খুব কঠোর সতর্কতা এসেছে। বলা হয়েছে, যে ব্যক্তি মদ পান করবে, আল্লাহ তার উপর ৪০ দিন সন্তুষ্ট হবেন না। এখানে সংখ্যাটি হাদিসের সরাসরি ভাষায় এসেছে, তাই বিষয়টি হালকা করে দেখার সুযোগ নেই। মদ শুধু শরীরের ক্ষতি নয়; এটি বান্দার আল্লাহর সাথে সম্পর্ক, ইবাদতের মনোভাব এবং নৈতিক শক্তিকেও আঘাত করে। হাদিসটি আমাদের শেখায়, নেশা সাময়িক আনন্দের বিষয় নয়; এর আধ্যাত্মিক ক্ষতিও ভয়াবহ। তাই মুমিনের উচিত মদ থেকে দূরে থাকা, এমন সঙ্গ এড়িয়ে চলা যা তাকে মদের দিকে টানে, এবং ভুল হলে দেরি না করে তাওবার পথ ধরা। এ কারণে মদ থেকে বাঁচা শুধু ব্যক্তিগত স্বাস্থ্যরক্ষা নয়, আল্লাহর সন্তুষ্টি খোঁজারও অংশ।"},"teachings":["মদপান আল্লাহর অসন্তুষ্টির কারণ হতে পারে।","৪০ দিনের সতর্কতা হাদিসে সরাসরি এসেছে।","নেশা ঈমানি জীবনের জন্য ক্ষতিকর।","ভুল হলে তাওবার দিকে দ্রুত ফিরতে হবে।"],"related_hadiths":[{"id":"3371","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"5578","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E172" s="4" t="n"/>
@@ -4556,12 +4464,12 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সব নেশাদার দ্রব্য মদ","description":"$book_name$ $hadith_number$ - $chapter_name$. সব নেশাদার দ্রব্য মদ এবং সব মদ হারাম—তওবা ছাড়া আসক্তির ভয়াবহ সতর্কতা।"},"heading":{"title":"সব নেশাদার দ্রব্য মদ: খামর হারামের স্পষ্ট হাদিস","description":"এই হাদিসে খুব স্পষ্টভাবে বলা হয়েছে, সব নেশাদার দ্রব্য মদ এবং সব ধরনের মদ হারাম। অর্থাৎ শুধু নির্দিষ্ট কোনো পানীয় নয়, যে বস্তু নেশা তৈরি করে তা এই সতর্কতার মধ্যে পড়ে। হাদিসে আরও বলা হয়েছে, যে ব্যক্তি দুনিয়ায় মদ পান করে এবং তওবা ছাড়া আসক্ত অবস্থায় মারা যায়, সে পরকালে সুস্বাদু পানীয় পান করতে পাবে না। এখানে মূল শিক্ষা হলো নেশা থেকে দূরে থাকা এবং ভুল হলে তওবার দিকে ফিরে আসা। হাদিসে আসক্তির কথা এসেছে, তাই নিয়মিত নেশাকে সাধারণ অভ্যাস মনে করা বিপজ্জনক। একজন মুসলিমের জন্য বিবেক, ইবাদত ও চরিত্র রক্ষায় নেশাদার দ্রব্য থেকে বাঁচা প্রয়োজন।"},"teachings":["সব নেশাদার দ্রব্যকে মদের অন্তর্ভুক্ত বলা হয়েছে।","সব ধরনের মদ হারাম—এ শিক্ষা স্পষ্ট।","আসক্ত অবস্থায় তওবা ছাড়া মৃত্যু ভয়াবহ সতর্কতার বিষয়।","ভুল হলে তওবার দিকে দ্রুত ফিরে আসা দরকার।"],"related_hadiths":[{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3450","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপানের শাস্তি ও সমাজে হারাম ঠেকানোর শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি মদপানকারীকে জুতা ও বেত দিয়ে ৪০ বার শাস্তি দিতেন; পরে উমর (রাঃ) ৮০ বেত্রাঘাত করেন।"},"heading":{"title":"মদপানের শাস্তি: শরীয়তী সতর্কতা ও সামাজিক শিক্ষা","description":"এই হাদিসে মদপানের শরীয়তী শাস্তির একটি ঘটনা এসেছে। আনাস (রাঃ) বর্ণনা করেছেন, রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) নেশাদার দ্রব্য পানকারীকে জুতা ও বেতের মাধ্যমে ৪০ বার মারতেন। পরে উমর (রাঃ)-এর সময়ে যখন নেশাদার দ্রব্য পানকারীদের সংখ্যা বেড়ে যায়, তিনি ৮০ বেত্রাঘাত করতেন বলে বর্ণনায় এসেছে। এই হাদিসের আলোচনা বিচার ও শাস্তির বিষয়, তাই তা ব্যক্তিগতভাবে প্রয়োগের বিষয় নয়; এটি দায়িত্বশীল বিচারব্যবস্থার সঙ্গে সম্পর্কিত। সরাসরি শিক্ষা হলো, ইসলাম মদপানকে ব্যক্তিগত পছন্দ হিসেবে দেখে না; বরং এটি ব্যক্তি, পরিবার ও সমাজের ক্ষতি ডেকে আনতে পারে। তাই মাদক থেকে দূরে থাকা জরুরি। তাই পরিবার, শিক্ষা ও সমাজে মাদকবিরোধী সচেতনতা গড়ে তোলা এই হাদিসের সাথে মানানসই শিক্ষা।"},"teachings":["মদপানকে শরীয়তে গুরুতর অপরাধ হিসেবে দেখা হয়েছে।","শাস্তির বিষয় দায়িত্বশীল বিচারব্যবস্থার সাথে সম্পর্কিত।","সমাজে মাদক ছড়ানো বড় ক্ষতির কারণ হতে পারে।","মাদক থেকে বাঁচা ব্যক্তি ও সমাজ উভয়ের জন্য দরকার।"],"related_hadiths":[{"id":"6773","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
         </is>
       </c>
       <c r="E173" s="4" t="n"/>
@@ -4579,12 +4487,12 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ত্বিনাতে খাবালের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নেশাদার দ্রব্য পানকারীর জন্য ত্বিনাতে খাবাল—জাহান্নামীদের রক্ত-পুঁজের কঠিন সতর্কতা।"},"heading":{"title":"ত্বিনাতে খাবাল: নেশাদার দ্রব্য পানকারীর কঠিন সতর্কতা","description":"এই হাদিসে নেশাদার দ্রব্য পানকারীদের জন্য খুব কঠিন সতর্কতা এসেছে। রাসূলুল্লাহ صلى الله عليه وسلم বলেছেন, আল্লাহর ওয়াদা রয়েছে যে নেশাদার দ্রব্য পানকারীকে তিনি ত্বিনাতে খাবাল পান করাবেন। সাহাবীগণ জিজ্ঞেস করলে রাসূল صلى الله عليه وسلم ব্যাখ্যা করেন, এটি জাহান্নামীদের শরীর থেকে গলে পড়া রক্ত-পুঁজ মিশ্রিত অত্যন্ত গরম তরল পদার্থ। হাদিসের ভাষা ভয় জাগায়, কারণ নেশা মানুষের বিবেক, ইবাদত ও চরিত্রকে ক্ষতি করতে পারে। এখানে অতিরিক্ত কোনো গল্প যোগ করার দরকার নেই; মূল শিক্ষা যথেষ্ট পরিষ্কার। মদ ও মাদক থেকে দূরে থাকা, আসক্তি হলে তওবা করা এবং সাহায্য নিয়ে ফিরে আসা—এটাই একজন মুসলিমের নিরাপদ পথ।"},"teachings":["নেশাদার দ্রব্য পানকারীর জন্য কঠিন সতর্কতা এসেছে।","ত্বিনাতে খাবালকে জাহান্নামীদের রক্ত-পুঁজের তরল বলা হয়েছে।","নেশাকে সাধারণ ভুল মনে করে হালকা করা উচিত নয়।","ভুল হলে তওবা ও নেশা ছাড়ার চেষ্টা জরুরি।"],"related_hadiths":[{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3377","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যেনা, রেশম, মদ ও বাদ্যযন্ত্রকে হালাল ভাবার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি বলেছেন, কিছু লোক যেনা, রেশম, মদ ও বাদ্যযন্ত্রকে হালাল মনে করবে—এটি গুরুতর সতর্কতা।"},"heading":{"title":"হারামকে হালাল মনে করা: মদ ও বাদ্যযন্ত্র সম্পর্কে হাদিস","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ভবিষ্যতের একটি বিপদের কথা বলেছেন। তাঁর উম্মতের কিছু লোক যেনা, রেশম, নেশাদার দ্রব্য এবং গান-বাজনা-বাদ্যযন্ত্রকে হালাল মনে করবে। এখানে সবচেয়ে বড় সতর্কতা হলো—হারামকে শুধু করা নয়, বরং সেটিকে হালাল মনে করা। মানুষ কখনও নিজের পছন্দ, সমাজের চাপ বা আনন্দের নামে সীমা বদলাতে চায়। কিন্তু হাদিসটি জানায়, আল্লাহর বিধানকে নিজের ইচ্ছামতো বদলানো বড় ঝুঁকির বিষয়। মদ ও বাদ্যযন্ত্র নিয়ে এই হাদিসটি বাংলায় অনেক খোঁজা হয়, কারণ এটি সরাসরি চারটি বড় সামাজিক ফিতনার নাম উল্লেখ করে। মুমিনের কাজ হলো সত্যকে সত্য বলা এবং হারাম থেকে বাঁচা। তাই মুমিনের উচিত জনপ্রিয় সংস্কৃতি নয়, হাদিসের নির্দেশকে নিজের মাপকাঠি বানানো।"},"teachings":["হারামকে হালাল মনে করা গুরুতর সতর্কতার বিষয়।","মদ ও বাদ্যযন্ত্র হাদিসে একসাথে উল্লেখ হয়েছে।","সমাজের প্রচলন দিয়ে আল্লাহর বিধান বদলায় না।","নিজের পছন্দের ওপর দ্বীনের নির্দেশকে প্রাধান্য দিতে হবে।"],"related_hadiths":[{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E174" s="4" t="n"/>
@@ -4602,12 +4510,12 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদাসক্তির ভয়াবহতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নিয়মিত নেশাদার দ্রব্য পানকারীকে মূর্তিপূজকের মতো গুরুতর অপরাধী বলা হয়েছে।"},"heading":{"title":"মদাসক্তি: নিয়মিত নেশা করার ভয়াবহ সতর্কতা","description":"এই হাদিসে নিয়মিত নেশাদার দ্রব্য পানকারীকে মূর্তিপূজকের ন্যায় অপরাধী বলা হয়েছে। এখানে মূল শিক্ষা হলো মদাসক্তি বা নেশার অভ্যাসকে খুব গুরুতরভাবে দেখা। হাদিসে একবার ভুল করা ও নিয়মিত আসক্তির মধ্যে ভাষাগতভাবে পার্থক্য আছে, কারণ ‘সর্বদা পানকারী’ শব্দটি অভ্যাস ও আসক্তির দিকে ইঙ্গিত করে। তবে কোনো মানুষকে ব্যক্তিগতভাবে বিচার করার চেয়ে নিজের অবস্থার দিকে তাকানো বেশি দরকার। মদ বা নেশা মানুষকে আল্লাহর আনুগত্য থেকে দূরে নিতে পারে এবং চরিত্র নষ্ট করতে পারে। তাই যে কেউ এই অভ্যাসে জড়িয়ে পড়লে তাকে তওবা, দোয়া ও বাস্তব পদক্ষেপের মাধ্যমে ফিরে আসার চেষ্টা করা উচিত।"},"teachings":["নিয়মিত নেশা করা গুরুতর অপরাধ হিসেবে এসেছে।","নেশার অভ্যাসকে হালকা করে দেখা ঠিক নয়।","মদাসক্তি আল্লাহর আনুগত্য থেকে দূরে নিতে পারে।","তওবা ও নেশা ছাড়ার চেষ্টা জরুরি।"],"related_hadiths":[{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"3377","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, জুয়া ও বাদ্যযন্ত্র হারাম হওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ মদ, জুয়া ও বাদ্যযন্ত্র হারাম করেছেন—এ হাদিস হারাম আনন্দ থেকে বাঁচার শিক্ষা দেয়।"},"heading":{"title":"মদ, জুয়া ও বাদ্যযন্ত্র হারাম: হাদিসের সরল ব্যাখ্যা","description":"এই হাদিসে তিনটি বিষয় একসাথে এসেছে: মদ, জুয়া এবং বাদ্যযন্ত্র। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ তা‘আলা এগুলো হারাম করেছেন। মদ বিবেক নষ্ট করে, জুয়া মানুষকে লোভ ও ক্ষতির পথে নেয়, আর বাদ্যযন্ত্র সম্পর্কে এখানে নিষেধ এসেছে। হাদিসটি আমাদের শেখায়, আনন্দ বা লাভের নামে এমন কাজ করা ঠিক নয় যা আল্লাহ হারাম করেছেন। অনেক সময় মানুষ বলে, “শুধু বিনোদন” বা “শুধু খেলা”; কিন্তু মুমিনের কাছে হালাল-হারামের সীমা বেশি গুরুত্বপূর্ণ। এই হাদিস সামাজিক জীবন, অর্থ, অবসর এবং বিনোদনে আল্লাহভীতির শিক্ষা দেয়। তাই নিজের আয়, খেলা, আনন্দ ও অবসর—সব ক্ষেত্রেই আল্লাহর ভয় রাখার প্রয়োজন আছে। এতে বোঝা যায়, দ্বীন শুধু ইবাদতের জায়গায় নয়; মানুষের অভ্যাস, লেনদেন ও বিনোদনের ক্ষেত্রেও পথ দেখায়।"},"teachings":["মদ, জুয়া ও বাদ্যযন্ত্র থেকে সতর্ক থাকার নির্দেশ এসেছে।","বিনোদন হলেও হারামের সীমা মানতে হবে।","জুয়া লোভ ও ক্ষতির পথ খুলে দিতে পারে।","আল্লাহর বিধানকে আনন্দের অজুহাতে হালকা করা ঠিক নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E175" s="4" t="n"/>
@@ -4625,12 +4533,12 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপানকারীর জান্নাত সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সর্বদা নেশাদার দ্রব্য পানকারীর জন্য জান্নাত বিষয়ে কঠিন সতর্কতা—নিজেকে সংশোধনের ডাক।"},"heading":{"title":"সর্বদা নেশাদার দ্রব্য পানকারী: জান্নাত বিষয়ে কঠিন সতর্কতা","description":"এই হাদিসে বলা হয়েছে, সর্বদা নেশাদার দ্রব্য পানকারী জান্নাতে যাবে না। হাদিসের ভাষা খুব কঠিন, তাই একে হালকা করে দেখা উচিত নয়। এখানে মূল বিষয় হলো মদাসক্তি ও নিয়মিত নেশা। নেশা মানুষের বিবেক ঢেকে দেয়, আমল দুর্বল করে এবং অনেক অন্যায়ের দরজা খুলে দিতে পারে। তবে হাদিস থেকে অতিরিক্ত সিদ্ধান্ত বানানো ঠিক নয়; যে কথা এসেছে, সেটুকুই মানতে হবে। মুসলিমের কাজ হলো ভয় পাওয়া, নিজেকে ফিরিয়ে আনা এবং তওবার পথ ধরা। যদি কারও জীবনে এই অভ্যাস থাকে, তাহলে গোপনে বা প্রকাশ্যে আল্লাহর কাছে ক্ষমা চেয়ে নেশা ছাড়ার বাস্তব চেষ্টা করা জরুরি।"},"teachings":["নিয়মিত নেশাদার দ্রব্য পানকারীর জন্য কঠিন সতর্কতা এসেছে।","নেশাকে সাধারণ সামাজিক অভ্যাস মনে করা ভুল।","নেশা ছাড়ার জন্য তওবা ও চেষ্টা দরকার।","হাদিসের ভাষা যতটুকু, ব্যাখ্যাও ততটুকুতে রাখা উচিত।"],"related_hadiths":[{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"3377","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গায়িকা নর্তকী, গান-বাজনা ও হারাম উপার্জন","description":"$book_name$ $hadith_number$ - $chapter_name$. গায়িকা-নর্তকী কেনাবেচা, গান-বাজনা শেখানো এবং এ পথের উপার্জন সম্পর্কে কঠোর নিষেধ এসেছে।"},"heading":{"title":"গায়িকা নর্তকী ও গান-বাজনার উপার্জন সম্পর্কে হাদিস","description":"এই হাদিসে গায়িকা নর্তকীদের কেনাবেচা, তাদের গান-বাজনা ও বাদ্যযন্ত্র শেখানো এবং তাদের উপার্জন সম্পর্কে নিষেধ এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাদের বিক্রি করো না, ক্রয় করো না, তাদের গান-বাজনা ও বাদ্যযন্ত্র শেখিও না, এবং তাদের উপার্জন হারাম। এখানে মূল শিক্ষা হলো, শুধু নিজের কাজ নয়, হারামের আয়োজন, প্রশিক্ষণ ও আয়ের পথ থেকেও বাঁচতে হবে। কোনো কাজ যদি মানুষকে অশ্লীলতা, নাচ-গান বা হারাম বিনোদনের দিকে নেয়, তবে সেটিকে পেশা বানানো নিরাপদ নয়। হাদিসটি উপার্জনকে হালাল রাখার এবং বিনোদনের নামে সীমা না ভাঙার শিক্ষা দেয়। তাই শিল্প, পেশা বা বিনোদনের নামে এমন পথ নেওয়া যাবে না যা হারামের দিকে টেনে নেয়।"},"teachings":["হারাম বিনোদনের আয়োজন থেকেও দূরে থাকা দরকার।","গান-বাজনা শেখানো ও এর আয় সম্পর্কে নিষেধ এসেছে।","উপার্জন হালাল রাখা ঈমানি জীবনের অংশ।","নিজে না করলেও হারামের সহায়তা থেকে সতর্ক থাকতে হবে।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E176" s="4" t="n"/>
@@ -4648,12 +4556,12 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | অবাধ্যতা, জুয়া, খোঁটা ও মদাসক্তি","description":"$book_name$ $hadith_number$ - $chapter_name$. পিতা-মাতার অবাধ্যতা, জুয়া-লটারী, খোঁটা দেওয়া ও মদাসক্তির কঠিন সতর্কতা।"},"heading":{"title":"অবাধ্য সন্তান, জুয়া, খোঁটা ও মদপান: চারটি গুরুতর সতর্কতা","description":"এই হাদিসে চার শ্রেণীর মানুষের ব্যাপারে জান্নাত বিষয়ে কঠিন সতর্কতা এসেছে। তারা হলো পিতা-মাতার অবাধ্য সন্তান, জুয়া ও লটারীতে অংশগ্রহণকারী, খোঁটাদানকারী এবং সর্বদা মদপানকারী। এখানে একসাথে কয়েকটি সামাজিক ও ব্যক্তিগত অপরাধ এসেছে। পিতা-মাতার অবাধ্যতা পরিবারকে আঘাত করে। জুয়া ও লটারী মানুষের সম্পদ ও মনকে অন্য পথে নেয়। খোঁটা দেওয়া দান বা উপকারের সৌন্দর্য নষ্ট করে। আর মদাসক্তি বিবেক ও চরিত্রকে ক্ষতি করে। হাদিসটি আমাদের শেখায়, শুধু ব্যক্তিগত ইবাদত নয়; পারিবারিক দায়িত্ব, অর্থনৈতিক সততা, মানুষের সম্মান এবং নেশা থেকে দূরে থাকা—সবই মুসলিম জীবনের অংশ।"},"teachings":["পিতা-মাতার অবাধ্যতা গুরুতর সতর্কতার বিষয়।","জুয়া ও লটারী থেকে দূরে থাকা দরকার।","উপকার করে খোঁটা দেওয়া খারাপ অভ্যাস।","সর্বদা মদপান করা ভয়াবহ পরিণতির কারণ হতে পারে।"],"related_hadiths":[{"id":"161","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6871","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বাদ্যযন্ত্রের শব্দ থেকে বাঁচার চেষ্টা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইবনু উমর (রাঃ) বাদ্যযন্ত্রের শব্দ শুনে কানে আঙুল দিলেন এবং নবীজির একই আমলের কথা জানালেন।"},"heading":{"title":"বাদ্যযন্ত্রের শব্দ থেকে দূরে থাকা: ইবনু উমর (রাঃ)-এর বর্ণনা","description":"এই হাদিসে একটি বাস্তব ঘটনা এসেছে। ইবনু উমর (রাঃ) বাদ্যযন্ত্রের শব্দ শুনে দুই কানে দুই আঙুল ঢুকিয়ে রাস্তা থেকে সরে গেলেন। পরে নাফে‘কে জিজ্ঞেস করলেন, তিনি কিছু শুনতে পাচ্ছেন কি না। যখন নাফে‘ বললেন, না, তখন তিনি আঙুল বের করলেন এবং জানালেন যে তিনি একদা রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর সঙ্গে ছিলেন; নবীজি এমন শব্দ শুনে একই কাজ করেছিলেন। হাদিসের সঙ্গে দেওয়া ব্যাখ্যায়ও বলা হয়েছে, গান-বাজনা ও বাদ্যযন্ত্রের শব্দ যেন কানে না আসে, সে জন্য সম্ভবপর চেষ্টা করতে হবে। তাই শিক্ষা হলো, হারাম শব্দের পরিবেশ এলে সাধ্যের মধ্যে সরে যাওয়া বা বাঁচার চেষ্টা করা। এতে বোঝা যায়, গুনাহ থেকে বাঁচা শুধু মনে অপছন্দ করা নয়; অনেক সময় বাস্তব পদক্ষেপও দরকার।"},"teachings":["বাদ্যযন্ত্রের শব্দ থেকে বাঁচার চেষ্টা করা উচিত।","সাহাবিরা নবীজির আমল দেখে তা অনুসরণ করতেন।","হারাম পরিবেশ এলে সাধ্যের মধ্যে সরে যাওয়া ভালো।","শুধু শোনা নয়, শোনার পরিবেশ থেকেও সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
         </is>
       </c>
       <c r="E177" s="4" t="n"/>
@@ -4671,544 +4579,15 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | তিন শ্রেণীর কঠিন সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. পরিবারে বেহায়াপনা, পুরুষের বেশধারী নারী ও নিয়মিত নেশাকারীর ব্যাপারে সতর্কতা।"},"heading":{"title":"তিন শ্রেণীর মানুষ: পরিবার, পোশাক-আচরণ ও নেশা বিষয়ে সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর মানুষের ব্যাপারে কঠিন সতর্কতা এসেছে। প্রথমত, যে ব্যক্তি তার পরিবারে বেহায়াপনার সুযোগ দেয়। দ্বিতীয়ত, পুরুষের বেশধারী নারী। তৃতীয়ত, নিয়মিত নেশাদার দ্রব্য পানকারী। এখানে পরিবার, পরিচয় ও নেশার বিষয় একসাথে এসেছে। পরিবারে অশালীনতার সুযোগ দেওয়া মানে নিজের দায়িত্বকে অবহেলা করা। পোশাক ও আচরণে সীমা রক্ষা করাও ইসলামী শালীনতার অংশ। আর নিয়মিত নেশা মানুষের বিবেক ও আমলকে ক্ষতি করে। হাদিসের ভাষা কঠোর, তাই এটি নিজের সংশোধনের জন্য নেওয়া উচিত। অন্যকে অপমান করার জন্য নয়; বরং নিজের পরিবার, চরিত্র ও অভ্যাস ঠিক করার জন্য।"},"teachings":["পরিবারে বেহায়াপনার সুযোগ দেওয়া গুরুতর সতর্কতার বিষয়।","পোশাক ও আচরণে শালীনতা রক্ষা করা দরকার।","নিয়মিত নেশাদার দ্রব্য পান করা ভয়াবহ অভ্যাস।","হাদিসের শিক্ষা নিজের সংশোধনের জন্য গ্রহণ করা উচিত।"],"related_hadiths":[{"id":"168","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"6136","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, গায়িকা ও বাদ্যযন্ত্রে মত্ততার গজব","description":"$book_name$ $hadith_number$ - $chapter_name$. মদ, গায়িকা নিয়ে নাচ-গান ও বাদ্যযন্ত্রে ডুবে থাকার কারণে তিন ধরনের ভয়াবহ বিপদের সতর্কতা।"},"heading":{"title":"মদ, নাচ-গান ও বাদ্যযন্ত্র: ভয়াবহ বিপদের হাদিস","description":"এই হাদিসটি মদ, গায়িকা এবং বাদ্যযন্ত্রের ফিতনা সম্পর্কে স্পষ্ট সতর্কতা দেয়। নবী করীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যখন তাঁর উম্মত নেশাদার দ্রব্য পান করবে, গায়িকাদের নিয়ে নাচ-গানে মত্ত হবে এবং বাদ্যযন্ত্র নিয়ে ব্যস্ত হবে, তখন তিনটি ভয়াবহ বিপদ নেমে আসবে। সেগুলো হলো—ভূমি ধসে যাওয়া, উপর থেকে বা কোনো জাতির পক্ষ থেকে যুলুম চাপিয়ে দেওয়া, এবং অনেকের আকার-আকৃতি বিকৃত করা। হাদিসের ভাষা কঠোর, তাই এর বার্তাও গভীর: হারাম আনন্দকে সাধারণ বানানো মুমিনের পথ নয়। মদ, নাচ-গান ও বাদ্যযন্ত্রের প্রতি আসক্তি থেকে নিজেকে এবং পরিবারকে সতর্ক রাখা দরকার। তাই এই হাদিস শুধু ভয় দেখায় না; এটি মানুষকে নিজের জীবনযাপন নতুন করে যাচাই করতেও ডাকে।"},"teachings":["মদপান ও হারাম বিনোদন বড় বিপদের কারণ হতে পারে।","গায়িকা ও নাচ-গানে মত্ততা থেকে সতর্ক করা হয়েছে।","বাদ্যযন্ত্রে ব্যস্ততা হাদিসে নিন্দিতভাবে এসেছে।","হারামকে আনন্দের নামে স্বাভাবিক বানানো উচিত নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
         </is>
       </c>
       <c r="E178" s="4" t="n"/>
-    </row>
-    <row r="179" ht="46" customHeight="1">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপান, অবাধ্যতা ও দায়ূস","description":"$book_name$ $hadith_number$ - $chapter_name$. মদাসক্ত, পিতা-মাতার অবাধ্য সন্তান ও পরিবারে বেপর্দার সুযোগদাতার সতর্কতা।"},"heading":{"title":"মদাসক্ত, অবাধ্য সন্তান ও দায়ূস: তিন শ্রেণীর কঠিন সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর লোকের প্রতি আল্লাহ জান্নাত হারাম করেছেন বলে সতর্ক করা হয়েছে। তারা হলো সর্বদা মদপানকারী, পিতা-মাতার অবাধ্য সন্তান এবং পরিবারে বেপর্দা বা খারাপ কাজের সুযোগ দানকারী দায়ূস। এখানে তিনটি বিষয়ে জোর আছে—নিজের নেশার অভ্যাস, পিতা-মাতার হক এবং পরিবারের নৈতিক দায়িত্ব। মদাসক্তি ব্যক্তিকে ভেতর থেকে দুর্বল করে। পিতা-মাতার অবাধ্যতা কৃতজ্ঞতা ও দায়িত্বের বিপরীত। আর পরিবারে খারাপ কাজকে মেনে নেওয়া দায়িত্বহীনতা। হাদিসটি মানুষকে ভয় দেখিয়ে ভেঙে দিতে নয়; বরং জাগিয়ে দিতে এসেছে, যেন সে তওবা করে, সম্পর্ক ঠিক করে এবং পরিবারকে সঠিক পথে রাখতে চেষ্টা করে।"},"teachings":["সর্বদা মদপানকারী সম্পর্কে কঠিন সতর্কতা এসেছে।","পিতা-মাতার অবাধ্যতা বড় অপরাধের মধ্যে পড়ে।","পরিবারে খারাপ কাজ মেনে নেওয়া দায়িত্বহীনতা।","তওবা ও সংশোধনের পথে ফিরে আসা দরকার।"],"related_hadiths":[{"id":"161","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6871","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="n"/>
-    </row>
-    <row r="180" ht="46" customHeight="1">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, সম্পর্কচ্ছেদ ও যাদু","description":"$book_name$ $hadith_number$ - $chapter_name$. মদাসক্তি, আত্মীয়তার সম্পর্ক ছিন্ন করা ও যাদু বিশ্বাসের ব্যাপারে কঠিন সতর্কতা।"},"heading":{"title":"মদাসক্তি, আত্মীয়তা ছিন্ন ও যাদু বিশ্বাস: তিনটি বড় সতর্কতা","description":"এই হাদিসে তিন শ্রেণীর লোকের ব্যাপারে বলা হয়েছে, তারা জান্নাতে যাবে না। প্রথম শ্রেণী হলো সর্বদা নেশাদার দ্রব্য পানকারী। দ্বিতীয় হলো আত্মীয়তার সম্পর্ক বিচ্ছিন্নকারী। তৃতীয় হলো যাদুকে বিশ্বাসকারী। এখানে তিনটি ভিন্ন ক্ষতির দিক দেখা যায়। নেশা নিজের বিবেক ও আমলকে ক্ষতি করে। আত্মীয়তার সম্পর্ক ছিন্ন করা পরিবার ও সমাজের বন্ধন নষ্ট করে। আর যাদুকে বিশ্বাস করা ঈমানী চিন্তা ও আল্লাহর ওপর ভরসাকে দুর্বল করতে পারে। হাদিসটি আমাদের নিজের জীবনকে তিন দিক থেকে দেখতে শেখায়—অভ্যাস, সম্পর্ক এবং বিশ্বাস। ভুল থাকলে তা স্বীকার করে ফিরে আসাই নিরাপদ পথ।"},"teachings":["সর্বদা নেশাদার দ্রব্য পান করা ভয়াবহ সতর্কতার বিষয়।","আত্মীয়তার সম্পর্ক ছিন্ন করা থেকে দূরে থাকতে হবে।","যাদুকে বিশ্বাস করা ঈমানের জন্য বিপজ্জনক।","অভ্যাস, সম্পর্ক ও বিশ্বাস—তিন দিকেই সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"1862","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"},{"id":"5112","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"6136","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="n"/>
-    </row>
-    <row r="181" ht="46" customHeight="1">
-      <c r="A181" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে অঙ্গ-প্রত্যঙ্গের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে মুখ বন্ধ করে অঙ্গ-প্রত্যঙ্গকে কথা বলানো হবে; মানুষ নিজের কাজের সাক্ষ্য নিজ থেকেই পাবে।"},"heading":{"title":"কিয়ামতের দিন অঙ্গ-প্রত্যঙ্গের সাক্ষ্য দেওয়ার হাদিস","description":"এই হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) কিয়ামতের দিনের এক কথোপকথনের কথা বলেছেন। বান্দা বলবে, সে নিজের বিরুদ্ধে শুধু নিজের পক্ষ থেকে সাক্ষ্য গ্রহণ করবে। তখন আল্লাহ বলবেন, আজ তুমি নিজেই তোমার সাক্ষী হিসেবে যথেষ্ট, আর কিরামান-কাতিবীনও সাক্ষী। এরপর তার মুখে মোহর লাগিয়ে দেওয়া হবে এবং অঙ্গ-প্রত্যঙ্গকে বলা হবে, তারা যেন তার কাজের কথা বলে। তখন অঙ্গ-প্রত্যঙ্গ তার কাজ প্রকাশ করবে। পরে মুখ খুলে দেওয়া হলে সে নিজের অঙ্গগুলোকে দোষ দেবে, অথচ তাদের জন্যই সে আগে নিজের রবের সঙ্গে বিতর্ক করছিল। এই হাদিস আমাদের মনে করায়, কিয়ামতের সাক্ষ্য খুব স্পষ্ট হবে এবং মানুষের কাজ লুকানো থাকবে না।"},"teachings":["কিয়ামতে মানুষের নিজের অঙ্গ-প্রত্যঙ্গ তার কাজের সাক্ষ্য দেবে।","কিরামান-কাতিবীন মানুষের কাজ লিখে রাখেন।","মুখের কথা দিয়ে সবকিছু অস্বীকার করা সম্ভব হবে না।","দুনিয়ার কাজের জন্য আখেরাতে জবাবদিহি আছে।"],"related_hadiths":[{"id":"2969","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"5554","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"},{"id":"2429","book_id":"5","slug":"tirmidhi","label":"জামে আত-তিরমিজি"}]}</t>
-        </is>
-      </c>
-      <c r="E181" s="4" t="n"/>
-    </row>
-    <row r="182" ht="46" customHeight="1">
-      <c r="A182" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B182" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="D182" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | শাসকদের যুগ ও পাপকে হালাল মনে করার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইসলামের শুরু, খেলাফত, কঠোর শাসন এবং পাপকে হালাল মনে করার ভয়াবহ পরিণতি সম্পর্কে সতর্ক শিক্ষা।"},"heading":{"title":"অত্যাচারী শাসক ও পাপকে হালাল মনে করার হাদিস","description":"এই হাদিসের মূল বিষয় শাসনব্যবস্থা, ফিতনা এবং পাপকে হালাল মনে করার ভয়াবহতা। এখানে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ইসলামের শুরুতে নবুয়ত ও রহমতের কথা বলেছেন। এরপর খেলাফত ও রহমতের যুগের কথা এসেছে। তারপর এমন রাজত্ব ও কঠোর শাসনের কথা বলা হয়েছে, যেখানে যুলুম, উচ্ছৃঙ্খলতা এবং জমিনে বিপর্যয় দেখা দেবে। হাদিসে বিশেষভাবে বলা হয়েছে, কিছু অত্যাচারী শাসক রেশম, অবৈধ সম্পর্ক ও মদকে হালাল মনে করবে। তাদের দুনিয়াবী রিযিক ও সাহায্য পাওয়া যেতে পারে, কিন্তু সেটি তাদের কাজের সঠিকতা প্রমাণ করে না। তাই মুমিনের জন্য শিক্ষা হলো—ক্ষমতা, ধন বা বাহ্যিক সফলতা দেখে পাপকে ছোট মনে করা যাবে না। তাই নেতৃত্বের অবস্থানে থাকা মানুষদের জন্য এটি আরও বড় সতর্কতা, আর সাধারণ মানুষের জন্যও সত্য ও পাপের পার্থক্য বুঝে চলার শিক্ষা।"},"teachings":["ক্ষমতা ও দুনিয়াবী সাফল্য পাপকে বৈধ করে না।","রহমতপূর্ণ নেতৃত্ব মানুষের জন্য কল্যাণের পথ খুলে দেয়।","যুলুম, মদ ও অশ্লীলতাকে হালাল মনে করা বড় সতর্কতার বিষয়।","দুনিয়ার সাহায্য পেলেও আল্লাহর সামনে জবাবদিহি থেকে কেউ মুক্ত নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"81","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="n"/>
-    </row>
-    <row r="183" ht="46" customHeight="1">
-      <c r="A183" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B183" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C183" s="4" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="D183" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতের আলামত ও ইলম কমে যাওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইলম কমে যাওয়া, মূর্খতা, ব্যভিচার, মদপান ও নারী-পুরুষের সংখ্যার পরিবর্তন—কিয়ামতের কিছু আলামত।"},"heading":{"title":"কিয়ামতের আলামত: ইলম কমে যাওয়া ও মদপান বৃদ্ধি","description":"এই হাদিসে কিয়ামতের আলামত নিয়ে কয়েকটি স্পষ্ট সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, বিদ্যা উঠে যাবে বা কমে যাবে, মূর্খতা বেড়ে যাবে, ব্যভিচার বেশি হবে এবং মদপান বৃদ্ধি পাবে। আরও বলা হয়েছে, পুরুষের সংখ্যা কমে যাবে এবং নারীর সংখ্যা বেশি হবে, এমনকি একজন পুরুষ বহু নারীর দায়িত্বে থাকবে। হাদিসটি আমাদের বোঝায় যে সমাজে দ্বীনি জ্ঞান কমে গেলে ভুল কাজ সহজে ছড়িয়ে পড়ে। তাই কিয়ামতের আলামত হাদিস পড়ার উদ্দেশ্য শুধু ভবিষ্যৎ জানা নয়; বরং নিজের জীবনে ইলম, লজ্জাশীলতা, সংযম এবং হারাম থেকে বাঁচার চেষ্টা বাড়ানো। এই বার্তাটি সরল কিন্তু গভীর। তাই পাঠকের উচিত হাদিসটি পড়ে ভয় পাওয়ার পাশাপাশি নিজের ঘর, শিক্ষা ও চরিত্রের দিকে বাস্তবভাবে নজর দেওয়া।"},"teachings":["দ্বীনি ইলম কমে যাওয়া সমাজের জন্য বড় সতর্কতা।","মূর্খতা বাড়লে হারাম কাজের পথ সহজ হয়।","মদপান ও ব্যভিচার বৃদ্ধি কিয়ামতের আলামতের মধ্যে এসেছে।","হাদিসটি জ্ঞান ও নৈতিকতার গুরুত্ব মনে করিয়ে দেয়।"],"related_hadiths":[{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"81","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
-        </is>
-      </c>
-      <c r="E183" s="4" t="n"/>
-    </row>
-    <row r="184" ht="46" customHeight="1">
-      <c r="A184" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B184" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="D184" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, গায়িকা ও বাদ্যযন্ত্রের ভয়াবহ সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপান, গায়িকা নিয়ে নাচ-গান ও বাদ্যযন্ত্রে মত্ততার কারণে বড় বিপদের বিষয়ে হাদিসের সতর্কতা।"},"heading":{"title":"মদ ও বাদ্যযন্ত্র সম্পর্কে ভয়াবহ সতর্কবার্তার হাদিস","description":"এই হাদিসের মূল বিষয় মদ, গায়িকা নিয়ে নাচ-গান এবং বাদ্যযন্ত্রে ব্যস্ত থাকা। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের মধ্যে এমন সময় আসবে যখন মানুষ নেশাদার দ্রব্য পান করবে, গায়িকাদের নিয়ে নাচ-গানে মত্ত হবে এবং বাদ্যযন্ত্র নিয়ে ব্যস্ত হবে। তখন তিন ধরনের ভয়াবহ বিপদের কথা বলা হয়েছে: ভূমি ধসে যাওয়া, উপর থেকে বা কোনো জাতির পক্ষ থেকে যুলুম চাপিয়ে দেওয়া, এবং অনেকের আকার-আকৃতি বিকৃত হওয়া। এখানে শিক্ষা হলো, আনন্দের নামে হারামকে সাধারণ বানানো নিরাপদ পথ নয়। হাদিসটি মানুষকে মদ, নাচ-গান এবং বাদ্যযন্ত্রের ফিতনা থেকে সাবধান হতে বলছে। তাই সতর্কতা শুরু হতে পারে নিজের পছন্দ, বন্ধু-বান্ধব এবং অবসর কাটানোর ধরন ঠিক করার মাধ্যমে।"},"teachings":["মদপানকে হাদিসে বড় বিপদের কারণ হিসেবে উল্লেখ করা হয়েছে।","গায়িকা ও নাচ-গানে মত্ত হওয়া থেকে সতর্ক করা হয়েছে।","বাদ্যযন্ত্রের প্রতি আসক্তি হাদিসে নিন্দিতভাবে এসেছে।","সমাজে হারাম কাজ ছড়ালে বিপদের আশঙ্কা বাড়ে।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="n"/>
-    </row>
-    <row r="185" ht="46" customHeight="1">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="D185" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | খাদ্য-পানীয় ও আমোদ-প্রমোদের পরিণতি","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদ্য-পানীয় ও বিনোদনে ডুবে থাকা কিছু লোকের ভয়াবহ রূপান্তর সম্পর্কে সতর্ক করা হয়েছে।"},"heading":{"title":"ভোগ-বিলাস ও আমোদ-প্রমোদের পরিণতি নিয়ে হাদিস","description":"এই হাদিসে ভোগ-বিলাস, খাদ্য-পানীয় এবং আমোদ-প্রমোদের বিষয়ে কঠোর সতর্কতা এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাঁর উম্মতের কিছু লোক রাত কাটাবে নানা ধরনের খাবার, পানীয় ও বিনোদনে ডুবে থেকে। এরপর তাদের সকাল হবে বানর ও শূকরের আকৃতিতে রূপান্তরিত হয়ে। হাদিসটি আনন্দ বা খাবারকে আলাদা করে নিষিদ্ধ বলছে না; বরং এমন জীবনধারার দিকে সতর্ক করছে যেখানে মানুষ আল্লাহভীতি ভুলে ভোগ, নেশা এবং অসংযত বিনোদনে ডুবে যায়। মূল শিক্ষা হলো, আনন্দ যেন ঈমান, লজ্জা ও হারাম-হালালের সীমা নষ্ট না করে। দুনিয়ার মজা সাময়িক, কিন্তু জবাবদিহি খুব বাস্তব। পরিবার ও সমাজে এমন পরিবেশ তৈরি করা দরকার, যেখানে আনন্দ থাকবে কিন্তু হারামের সীমা অতিক্রম করা হবে না।"},"teachings":["ভোগ-বিলাসে ডুবে আল্লাহভীতি ভুলে যাওয়া বিপজ্জনক।","বিনোদন যদি হারামের পথে নেয়, তা থেকে সতর্ক থাকা দরকার।","হাদিসে কিছু লোকের ভয়াবহ পরিণতির কথা এসেছে।","খাবার-পানীয় ও আনন্দের ক্ষেত্রেও সীমা মানা জরুরি।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
-        </is>
-      </c>
-      <c r="E185" s="4" t="n"/>
-    </row>
-    <row r="186" ht="46" customHeight="1">
-      <c r="A186" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B186" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C186" s="4" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="D186" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | ঈমান, সালাত, পরিবার ও গোনাহ থেকে বাঁচার দশ শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. শিরক, পিতা-মাতার অবাধ্যতা, ফরয সালাত ত্যাগ, মদপান, গোনাহ ও পরিবার বিষয়ে দশটি গুরুত্বপূর্ণ উপদেশ।"},"heading":{"title":"রাসূলের দশ উপদেশ: ঈমান, সালাত ও পরিবার জীবনের শিক্ষা","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মু‘আয (রাঃ)-কে দশটি বিষয়ে উপদেশ দিয়েছেন। প্রথমে এসেছে আল্লাহর সাথে কাউকে শরীক না করা। এরপর পিতা-মাতার অবাধ্য না হওয়া, ইচ্ছা করে ফরয সালাত না ছাড়া, মদ পান না করা এবং গোনাহ থেকে বেঁচে থাকার কথা এসেছে। আরও আছে জিহাদ থেকে পলায়ন না করা, মহামারী দেখা দিলে যেখানে আছে সেখানে স্থির থাকা, সামর্থ্য অনুযায়ী পরিবারের জন্য ব্যয় করা, পরিবারকে আদব শেখানো এবং আল্লাহর ভয় মনে করিয়ে দেওয়া। হাদিসটি ব্যক্তিগত ঈমান, ইবাদত, পরিবার, শৃঙ্খলা ও দায়িত্ব—সব দিককে একসাথে মনে করিয়ে দেয়। এটি জীবনের জন্য সংক্ষিপ্ত কিন্তু শক্তিশালী দিকনির্দেশনা। ফলে এই দশ উপদেশ একজন মুসলিমকে ঘর, সমাজ ও ব্যক্তিগত ইবাদতে ভারসাম্য রাখতে সাহায্য করে।"},"teachings":["তাওহীদ হলো জীবনের সবচেয়ে মূল দায়িত্ব।","ইচ্ছা করে ফরয সালাত ত্যাগ করা বড় সতর্কতার বিষয়।","মদকে অশ্লীলতার মূল হিসেবে উল্লেখ করা হয়েছে।","পরিবারের ব্যয়, আদব ও আল্লাহভীতি শেখানো দায়িত্বের অংশ।"],"related_hadiths":[{"id":"527","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5975","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3371","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="n"/>
-    </row>
-    <row r="187" ht="46" customHeight="1">
-      <c r="A187" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B187" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C187" s="4" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D187" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | নেশাদার দ্রব্য সব অন্যায়ের চাবী","description":"$book_name$ $hadith_number$ - $chapter_name$. নেশাদার দ্রব্য থেকে দূরে থাকার উপদেশ এসেছে, কারণ তা বহু অন্যায়ের দরজা খুলে দিতে পারে।"},"heading":{"title":"নেশাদার দ্রব্য: সব অন্যায়ের চাবী সম্পর্কে হাদিস","description":"এই ছোট হাদিসটি খুব সহজ ভাষায় বড় শিক্ষা দেয়। আবূ দারদা (রাঃ) বলেন, তাঁর দোস্ত রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাঁকে অছিয়ত করেছেন—নেশাদার দ্রব্য পান করো না; নিশ্চয়ই তা সব ধরনের অন্যায়ের চাবী। এখানে মূল কথা হলো মদ বা নেশা মানুষকে শুধু একটি গোনাহে আটকে রাখে না; বরং তা বিবেক, লজ্জা এবং সংযম দুর্বল করে আরও অনেক ভুলের দিকে ঠেলে দিতে পারে। তাই ইসলাম শুধু শেষ ক্ষতি নয়, ক্ষতির দরজাও বন্ধ করতে শেখায়। এই হাদিস মাদক থেকে দূরে থাকা, সঙ্গ বাছাই করা এবং নিজের বিবেককে সুরক্ষিত রাখার পরিষ্কার বার্তা দেয়। বিশেষ করে তরুণদের জন্য এটি শক্ত বার্তা—নেশার শুরু ছোট মনে হলেও শেষটা খুব ক্ষতিকর হতে পারে।"},"teachings":["নেশাদার দ্রব্য থেকে দূরে থাকা নিরাপদ পথ।","মদকে বহু অন্যায়ের দরজা হিসেবে সতর্ক করা হয়েছে।","বিবেক নষ্ট হলে অন্য গোনাহে পড়ার ঝুঁকি বাড়ে।","ভালো উপদেশ মানা ঈমানি জীবনের অংশ।"],"related_hadiths":[{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3390","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
-        </is>
-      </c>
-      <c r="E187" s="4" t="n"/>
-    </row>
-    <row r="188" ht="46" customHeight="1">
-      <c r="A188" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="D188" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | সব নেশাদার দ্রব্য হারাম হওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. হাদিসে স্পষ্ট বলা হয়েছে, যে কোনো নেশা উদ্রেককারী বস্তু হারাম; তাই মাদক থেকে দূরে থাকা জরুরি।"},"heading":{"title":"সব নেশাদার দ্রব্য হারাম: স্পষ্ট হাদিসের শিক্ষা","description":"এই হাদিসের মূল শিক্ষা খুব সরল: সব ধরনের নেশাদার দ্রব্য হারাম। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, “কুল্লু মুসকিরিন হারাম”—প্রতিটি নেশা উদ্রেককারী জিনিস হারাম। তাই বিষয়টি শুধু নির্দিষ্ট কোনো পানীয়ের মধ্যে সীমাবদ্ধ নয়। যে জিনিস মানুষের বিবেক ঢেকে দেয়, সিদ্ধান্ত নেওয়ার ক্ষমতা দুর্বল করে এবং তাকে ভুল কাজে ঠেলে দেয়, সেটি এই সতর্কতার মধ্যে পড়ে। হাদিসটি মুসলিমকে নাম বা ধরন নিয়ে চালাকি না করতে শেখায়। মদ, মাদক বা যে কোনো নেশা—মূল বিচার হলো তা নেশা সৃষ্টি করে কি না। ঈমানদার জীবনে বিবেক রক্ষা করা বড় দায়িত্ব। এ কারণে নেশা নিয়ে মজা, পরীক্ষা বা কৌতূহল দেখানোও মুমিনের জন্য ঝুঁকিপূর্ণ আচরণ হতে পারে।"},"teachings":["নেশা সৃষ্টি করে এমন জিনিস থেকে বাঁচতে হবে।","হারামকে নাম বদলে বৈধ ভাবা ঠিক নয়।","বিবেক ও সংযম রক্ষা করা ঈমানি জীবনের অংশ।","হাদিসটি মাদক বিষয়ে সংক্ষিপ্ত কিন্তু স্পষ্ট নির্দেশ দেয়।"],"related_hadiths":[{"id":"3390","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3393","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
-        </is>
-      </c>
-      <c r="E188" s="4" t="n"/>
-    </row>
-    <row r="189" ht="46" customHeight="1">
-      <c r="A189" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="D189" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বিবেক নষ্টকারী বস্তুই মদ—হারামের স্পষ্ট মানদণ্ড","description":"$book_name$ $hadith_number$ - $chapter_name$. যা বিবেকের ক্ষতি করে তা মদের অন্তর্ভুক্ত, আর সব ধরনের মদ হারাম—হাদিসের সরল শিক্ষা।"},"heading":{"title":"মদ কাকে বলে: বিবেক নষ্টকারী সব নেশার হুকুম","description":"এই হাদিসে মদের পরিচয় খুব সহজভাবে এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, প্রত্যেক নেশাদার বস্তুই মদ, আর প্রত্যেক মদই হারাম। অর্থাৎ মদ শুধু আঙুর, খেজুর বা নির্দিষ্ট কোনো নামে সীমাবদ্ধ নয়। যে জিনিস পান, খাওয়া বা গ্রহণ করলে মানুষের বিবেক ও বোঝার ক্ষমতা নষ্ট হয়, সেটি খামর বা মদের হুকুমের মধ্যে পড়ে। এই হাদিস নামের চেয়ে প্রভাবকে গুরুত্ব দেয়। তাই কোনো বস্তু আধুনিক নাম, নতুন প্যাকেট বা ভিন্ন রূপে এলেও যদি তা নেশা সৃষ্টি করে, তাহলে মুমিনের জন্য সতর্কতা একই থাকে। মূল কথা: বিবেক আল্লাহর বড় নেয়ামত, একে নেশার হাতে তুলে দেওয়া যাবে না। তাই পরিবারে ও সমাজে মাদককে সাধারণ বিষয় বানানো নয়, বরং পরিষ্কারভাবে ভুল বলা দরকার।"},"teachings":["নেশা সৃষ্টি করলে নাম বদলালেও হুকুম বদলায় না।","বিবেক নষ্টকারী বস্তু থেকে দূরে থাকা জরুরি।","সব ধরনের মদ হারাম—হাদিসে স্পষ্ট বলা হয়েছে।","মুমিনের জন্য হালাল-হারামের মানদণ্ড প্রভাবের ওপরও নির্ভর করে।"],"related_hadiths":[{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3393","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
-        </is>
-      </c>
-      <c r="E189" s="4" t="n"/>
-    </row>
-    <row r="190" ht="46" customHeight="1">
-      <c r="A190" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B190" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C190" s="4" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="D190" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বেশি নেশা হলে কমও হারাম—সতর্কতার হাদিস","description":"$book_name$ $hadith_number$ - $chapter_name$. যে বস্তু বেশি খেলে নেশা হয়, তার অল্প পরিমাণও হারাম—হারাম থেকে দূরে থাকার পরিষ্কার শিক্ষা।"},"heading":{"title":"যার বেশি নেশা আনে, তার কমও হারাম: মাদক বিষয়ে হাদিস","description":"এই হাদিসে নেশাদার বস্তু সম্পর্কে একটি গুরুত্বপূর্ণ নীতি এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যে বস্তু বেশি পরিমাণে গ্রহণ করলে বিবেকের ক্ষতি হয় বা নেশা আসে, তার কম পরিমাণও হারাম। এর মানে হলো, “অল্প খেলে ক্ষতি নেই”—এমন অজুহাত দিয়ে নেশার দরজা খোলা যাবে না। ইসলাম মানুষের বিবেক, আত্মসম্মান ও ইবাদতকে সুরক্ষিত রাখতে চায়। তাই যে জিনিস বেশি হলে মানুষকে মাতাল করে, সেটির সামান্য অংশও নিরাপদ খেলার বিষয় নয়। এই হাদিস মাদক, অ্যালকোহল ও নেশা নিয়ে আপস না করার শিক্ষা দেয়। ছোট ছাড় অনেক সময় বড় বিপদের শুরু হতে পারে। এই নীতি মানুষকে সন্দেহজনক নেশাদার জিনিস থেকেও দূরে থাকতে সাহায্য করে।"},"teachings":["অল্প নেশাদার দ্রব্যকেও হালকা মনে করা ঠিক নয়।","যার বেশি নেশা আনে, তার কমও হারাম।","হারামের দরজা শুরুতেই বন্ধ করা নিরাপদ।","বিবেক রক্ষা করা মুমিনের গুরুত্বপূর্ণ দায়িত্ব।"],"related_hadiths":[{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3390","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
-        </is>
-      </c>
-      <c r="E190" s="4" t="n"/>
-    </row>
-    <row r="191" ht="46" customHeight="1">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D191" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | কিয়ামতে রবকে দেখা ও আমলের সাক্ষ্য","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতে রবকে দেখা, নেয়ামতের জবাবদিহি ও অঙ্গ-প্রত্যঙ্গের সাক্ষ্য—এই হাদিসে সতর্কতা এসেছে।"},"heading":{"title":"কিয়ামতের দিন রবকে দেখা ও অঙ্গের সাক্ষ্যের শিক্ষা","description":"এই হাদিসে সাহাবীরা জিজ্ঞেস করেছেন, কিয়ামতের দিন তারা কি তাদের রবকে দেখতে পাবে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) সূর্য ও পূর্ণিমার চাঁদ দেখার উদাহরণ দিয়ে বলেছেন, রবকে দেখতে অসুবিধা হবে না। এরপর তিনি বান্দাদের জবাবদিহির কথা বলেন। আল্লাহ বান্দাকে নিজের দেওয়া মর্যাদা, নেতৃত্ব, পরিবার ও নিয়ামতের কথা স্মরণ করাবেন। কেউ আল্লাহর সাক্ষাতের কথা অস্বীকার করেছিল বলে তাকে কঠিন পরিণতির কথা বলা হবে। আর এক ব্যক্তি নিজের ভালো কাজের কথা বললেও তার মুখে মোহর লাগিয়ে অঙ্গ-প্রত্যঙ্গকে সাক্ষ্য দিতে বলা হবে। হাদিসে তাকে মুনাফিক বলা হয়েছে। এই হাদিস নেয়ামত, হিসাব, মুনাফিকী এবং সত্য সাক্ষ্যের কথা মনে করায়।"},"teachings":["কিয়ামতের দিন রবকে দেখার বিষয়টি হাদিসে এসেছে।","আল্লাহর দেওয়া নিয়ামতের জন্য জবাবদিহি থাকবে।","মুখে দাবি করলেই যথেষ্ট নয়, কাজের সাক্ষ্যও আসবে।","মুনাফিকী আচরণ আল্লাহর ক্রোধের কারণ হতে পারে।"],"related_hadiths":[{"id":"2968","book_id":"2","slug":"muslim","label":"সহীহ মুসলিম"},{"id":"7440","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"5555","book_id":"14","slug":"mishkatul-masabih","label":"মিশকাতুল মাসাবীহ"}]}</t>
-        </is>
-      </c>
-      <c r="E191" s="4" t="n"/>
-    </row>
-    <row r="192" ht="46" customHeight="1">
-      <c r="A192" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="D192" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, মৃতপ্রাণী ও শূকরের মূল্য হারাম","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ মদ, মৃতপ্রাণী ও শূকর এবং এগুলোর মূল্য হারাম করেছেন—হারাম আয় থেকে বাঁচার শিক্ষা।"},"heading":{"title":"হারাম আয়: মদ ও নিষিদ্ধ বস্তুর মূল্য সম্পর্কে হাদিস","description":"এই হাদিসে শুধু মদ পান নয়, মদের মূল্য বা এর অর্থনৈতিক লেনদেনের দিকেও সতর্ক করা হয়েছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ নেশাদার দ্রব্য এবং তার মূল্য হারাম করেছেন। একইভাবে মৃতপ্রাণী ও তার মূল্য, শূকর ও তার মূল্যও হারাম করা হয়েছে। এখানে গুরুত্বপূর্ণ শিক্ষা হলো—কোনো বস্তু হারাম হলে তার ব্যবসা, মূল্য এবং লাভও সতর্কতার বিষয় হয়। মানুষ অনেক সময় নিজে না খেয়ে বিক্রি করে লাভ নেওয়াকে হালকা মনে করতে পারে। কিন্তু এই হাদিস জানায়, হারাম জিনিস থেকে অর্থ উপার্জনও নিরাপদ নয়। রিযিক পবিত্র রাখা ঈমানি জীবনের বড় অংশ। তাই আয়ের উৎস যাচাই করা এবং সন্দেহজনক লাভ থেকে বাঁচা একজন মুসলিমের নিত্যদিনের দায়িত্ব।"},"teachings":["মদ শুধু পান নয়, তার মূল্যও হারাম বলা হয়েছে।","হারাম বস্তু থেকে আয় নেওয়া থেকে বাঁচতে হবে।","রিযিক পবিত্র রাখা মুসলিম জীবনের গুরুত্বপূর্ণ কাজ।","মৃতপ্রাণী ও শূকরের মূল্য সম্পর্কেও হাদিসে সতর্কতা এসেছে।"],"related_hadiths":[{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
-        </is>
-      </c>
-      <c r="E192" s="4" t="n"/>
-    </row>
-    <row r="193" ht="46" customHeight="1">
-      <c r="A193" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B193" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="D193" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, মৃতপ্রাণী, শূকর ও মূর্তি বিক্রি হারাম","description":"$book_name$ $hadith_number$ - $chapter_name$. মক্কা বিজয়ের বছরে নবীজি মদ, মৃতপ্রাণী, শূকর ও মূর্তির ক্রয়-বিক্রয় হারাম হওয়ার কথা বলেছেন।"},"heading":{"title":"হারাম ব্যবসা: মদ ও মূর্তি ক্রয়-বিক্রয় সম্পর্কে হাদিস","description":"এই হাদিসে মক্কা বিজয়ের বছরে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর একটি ঘোষণা এসেছে। তিনি বলেছেন, আল্লাহ মদ, মৃতপ্রাণী, শূকর এবং মূর্তির ক্রয়-বিক্রয় হারাম করেছেন। এখানে শিক্ষা শুধু কিছু জিনিস খাওয়া বা ব্যবহার না করার মধ্যে সীমাবদ্ধ নয়; বরং সেগুলোকে ব্যবসার পণ্য বানানো থেকেও বারণ করা হয়েছে। ইসলামে রিযিকের পবিত্রতা খুব গুরুত্বপূর্ণ। লাভ বেশি হলেই কোনো ব্যবসা ভালো হয়ে যায় না। হালাল-হারামের সীমা মানতে হয়। এই হাদিস ব্যবসায়ী, ক্রেতা ও সমাজ—সবার জন্য সতর্কতা: এমন পণ্য থেকে দূরে থাকা দরকার, যাকে আল্লাহ হারাম করেছেন। তাই ব্যবসায় সততা মানে শুধু ওজন ঠিক রাখা নয়, পণ্যটিও হালাল হওয়া। বিশেষ করে যে পণ্য মানুষের ঈমান, বিবেক বা তাওহীদের ক্ষতি করে, তা থেকে আয় করা মুমিনের জন্য নিরাপদ পথ নয়।"},"teachings":["হারাম জিনিস ব্যবসার পণ্য বানানো যায় না।","মদ, মৃতপ্রাণী, শূকর ও মূর্তির ক্রয়-বিক্রয় নিষিদ্ধ বলা হয়েছে।","লাভের চেয়ে হালাল রিযিক বেশি গুরুত্বপূর্ণ।","ব্যবসায়ও আল্লাহর সীমা মানা জরুরি।"],"related_hadiths":[{"id":"3485","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
-        </is>
-      </c>
-      <c r="E193" s="4" t="n"/>
-    </row>
-    <row r="194" ht="46" customHeight="1">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="D194" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপান, পিতামাতার অবাধ্যতা ও খোটা দানের সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদে আসক্তি, পিতা-মাতার অবাধ্যতা ও দান করে খোটা দেওয়ার ভয়াবহ পরিণতি সম্পর্কে সতর্কতা।"},"heading":{"title":"মদপানকারী, অবাধ্য সন্তান ও খোটা দানকারী সম্পর্কে হাদিস","description":"এই হাদিসে তিনটি কাজের বিষয়ে কঠোর সতর্কতা এসেছে: নেশাদার দ্রব্য পান করা, পিতা-মাতার অবাধ্য হওয়া এবং দান করে খোটা দেওয়া। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, এ ধরনের লোক জান্নাতে যাবে না—হাদিসের ভাষা অত্যন্ত সতর্কতামূলক। এর অর্থ বুঝতে আল্লাহর রহমত, তাওবা এবং অন্যান্য শরঈ বিষয় আলাদা আলোচনার বিষয়; তবে এই হাদিসের সরাসরি শিক্ষা হলো, এসব কাজ খুব ভয়াবহ। মদ মানুষের বিবেক নষ্ট করে, পিতা-মাতার অবাধ্যতা সম্পর্ক ভেঙে দেয়, আর খোটা দান সদকার সৌন্দর্য নষ্ট করে। তাই মুমিনের উচিত এসব কাজ থেকে দূরে থাকা এবং ভুল হলে দ্রুত তাওবার পথে ফেরা। তাই এই তিনটি বিষয়ে পরিবারে নিয়মিত নসিহত, আত্মসমালোচনা এবং সংশোধনের পরিবেশ থাকা দরকার।"},"teachings":["মদে আসক্তি ভয়াবহ গোনাহের দিকে নিয়ে যেতে পারে।","পিতা-মাতার অবাধ্যতা থেকে সতর্ক থাকতে হবে।","দান করে খোটা দেওয়া দানের সৌন্দর্য নষ্ট করে।","হাদিসটি তিনটি গুরুতর আচরণ থেকে বাঁচার শিক্ষা দেয়।"],"related_hadiths":[{"id":"5975","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3371","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
-        </is>
-      </c>
-      <c r="E194" s="4" t="n"/>
-    </row>
-    <row r="195" ht="46" customHeight="1">
-      <c r="A195" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="D195" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ পান করলে ৪০ দিনের অসন্তুষ্টির সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মদপানের পর আল্লাহর অসন্তুষ্টির কথা এসেছে, যা মাদক থেকে দূরে থাকার কঠোর সতর্কবার্তা।"},"heading":{"title":"মদ পান করলে ৪০ দিন আল্লাহর অসন্তুষ্টি: হাদিসের শিক্ষা","description":"এই হাদিসে মদপানের পরিণতি নিয়ে খুব কঠোর সতর্কতা এসেছে। বলা হয়েছে, যে ব্যক্তি মদ পান করবে, আল্লাহ তার উপর ৪০ দিন সন্তুষ্ট হবেন না। এখানে সংখ্যাটি হাদিসের সরাসরি ভাষায় এসেছে, তাই বিষয়টি হালকা করে দেখার সুযোগ নেই। মদ শুধু শরীরের ক্ষতি নয়; এটি বান্দার আল্লাহর সাথে সম্পর্ক, ইবাদতের মনোভাব এবং নৈতিক শক্তিকেও আঘাত করে। হাদিসটি আমাদের শেখায়, নেশা সাময়িক আনন্দের বিষয় নয়; এর আধ্যাত্মিক ক্ষতিও ভয়াবহ। তাই মুমিনের উচিত মদ থেকে দূরে থাকা, এমন সঙ্গ এড়িয়ে চলা যা তাকে মদের দিকে টানে, এবং ভুল হলে দেরি না করে তাওবার পথ ধরা। এ কারণে মদ থেকে বাঁচা শুধু ব্যক্তিগত স্বাস্থ্যরক্ষা নয়, আল্লাহর সন্তুষ্টি খোঁজারও অংশ।"},"teachings":["মদপান আল্লাহর অসন্তুষ্টির কারণ হতে পারে।","৪০ দিনের সতর্কতা হাদিসে সরাসরি এসেছে।","নেশা ঈমানি জীবনের জন্য ক্ষতিকর।","ভুল হলে তাওবার দিকে দ্রুত ফিরতে হবে।"],"related_hadiths":[{"id":"3371","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"5578","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
-        </is>
-      </c>
-      <c r="E195" s="4" t="n"/>
-    </row>
-    <row r="196" ht="46" customHeight="1">
-      <c r="A196" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="D196" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদপানের শাস্তি ও সমাজে হারাম ঠেকানোর শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি মদপানকারীকে জুতা ও বেত দিয়ে ৪০ বার শাস্তি দিতেন; পরে উমর (রাঃ) ৮০ বেত্রাঘাত করেন।"},"heading":{"title":"মদপানের শাস্তি: শরীয়তী সতর্কতা ও সামাজিক শিক্ষা","description":"এই হাদিসে মদপানের শরীয়তী শাস্তির একটি ঘটনা এসেছে। আনাস (রাঃ) বর্ণনা করেছেন, রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) নেশাদার দ্রব্য পানকারীকে জুতা ও বেতের মাধ্যমে ৪০ বার মারতেন। পরে উমর (রাঃ)-এর সময়ে যখন নেশাদার দ্রব্য পানকারীদের সংখ্যা বেড়ে যায়, তিনি ৮০ বেত্রাঘাত করতেন বলে বর্ণনায় এসেছে। এই হাদিসের আলোচনা বিচার ও শাস্তির বিষয়, তাই তা ব্যক্তিগতভাবে প্রয়োগের বিষয় নয়; এটি দায়িত্বশীল বিচারব্যবস্থার সঙ্গে সম্পর্কিত। সরাসরি শিক্ষা হলো, ইসলাম মদপানকে ব্যক্তিগত পছন্দ হিসেবে দেখে না; বরং এটি ব্যক্তি, পরিবার ও সমাজের ক্ষতি ডেকে আনতে পারে। তাই মাদক থেকে দূরে থাকা জরুরি। তাই পরিবার, শিক্ষা ও সমাজে মাদকবিরোধী সচেতনতা গড়ে তোলা এই হাদিসের সাথে মানানসই শিক্ষা।"},"teachings":["মদপানকে শরীয়তে গুরুতর অপরাধ হিসেবে দেখা হয়েছে।","শাস্তির বিষয় দায়িত্বশীল বিচারব্যবস্থার সাথে সম্পর্কিত।","সমাজে মাদক ছড়ানো বড় ক্ষতির কারণ হতে পারে।","মাদক থেকে বাঁচা ব্যক্তি ও সমাজ উভয়ের জন্য দরকার।"],"related_hadiths":[{"id":"6773","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"3681","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"}]}</t>
-        </is>
-      </c>
-      <c r="E196" s="4" t="n"/>
-    </row>
-    <row r="197" ht="46" customHeight="1">
-      <c r="A197" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C197" s="4" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="D197" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | যেনা, রেশম, মদ ও বাদ্যযন্ত্রকে হালাল ভাবার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. নবীজি বলেছেন, কিছু লোক যেনা, রেশম, মদ ও বাদ্যযন্ত্রকে হালাল মনে করবে—এটি গুরুতর সতর্কতা।"},"heading":{"title":"হারামকে হালাল মনে করা: মদ ও বাদ্যযন্ত্র সম্পর্কে হাদিস","description":"এই হাদিসে রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ভবিষ্যতের একটি বিপদের কথা বলেছেন। তাঁর উম্মতের কিছু লোক যেনা, রেশম, নেশাদার দ্রব্য এবং গান-বাজনা-বাদ্যযন্ত্রকে হালাল মনে করবে। এখানে সবচেয়ে বড় সতর্কতা হলো—হারামকে শুধু করা নয়, বরং সেটিকে হালাল মনে করা। মানুষ কখনও নিজের পছন্দ, সমাজের চাপ বা আনন্দের নামে সীমা বদলাতে চায়। কিন্তু হাদিসটি জানায়, আল্লাহর বিধানকে নিজের ইচ্ছামতো বদলানো বড় ঝুঁকির বিষয়। মদ ও বাদ্যযন্ত্র নিয়ে এই হাদিসটি বাংলায় অনেক খোঁজা হয়, কারণ এটি সরাসরি চারটি বড় সামাজিক ফিতনার নাম উল্লেখ করে। মুমিনের কাজ হলো সত্যকে সত্য বলা এবং হারাম থেকে বাঁচা। তাই মুমিনের উচিত জনপ্রিয় সংস্কৃতি নয়, হাদিসের নির্দেশকে নিজের মাপকাঠি বানানো।"},"teachings":["হারামকে হালাল মনে করা গুরুতর সতর্কতার বিষয়।","মদ ও বাদ্যযন্ত্র হাদিসে একসাথে উল্লেখ হয়েছে।","সমাজের প্রচলন দিয়ে আল্লাহর বিধান বদলায় না।","নিজের পছন্দের ওপর দ্বীনের নির্দেশকে প্রাধান্য দিতে হবে।"],"related_hadiths":[{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
-        </is>
-      </c>
-      <c r="E197" s="4" t="n"/>
-    </row>
-    <row r="198" ht="46" customHeight="1">
-      <c r="A198" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B198" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C198" s="4" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="D198" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, জুয়া ও বাদ্যযন্ত্র হারাম হওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহ মদ, জুয়া ও বাদ্যযন্ত্র হারাম করেছেন—এ হাদিস হারাম আনন্দ থেকে বাঁচার শিক্ষা দেয়।"},"heading":{"title":"মদ, জুয়া ও বাদ্যযন্ত্র হারাম: হাদিসের সরল ব্যাখ্যা","description":"এই হাদিসে তিনটি বিষয় একসাথে এসেছে: মদ, জুয়া এবং বাদ্যযন্ত্র। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, আল্লাহ তা‘আলা এগুলো হারাম করেছেন। মদ বিবেক নষ্ট করে, জুয়া মানুষকে লোভ ও ক্ষতির পথে নেয়, আর বাদ্যযন্ত্র সম্পর্কে এখানে নিষেধ এসেছে। হাদিসটি আমাদের শেখায়, আনন্দ বা লাভের নামে এমন কাজ করা ঠিক নয় যা আল্লাহ হারাম করেছেন। অনেক সময় মানুষ বলে, “শুধু বিনোদন” বা “শুধু খেলা”; কিন্তু মুমিনের কাছে হালাল-হারামের সীমা বেশি গুরুত্বপূর্ণ। এই হাদিস সামাজিক জীবন, অর্থ, অবসর এবং বিনোদনে আল্লাহভীতির শিক্ষা দেয়। তাই নিজের আয়, খেলা, আনন্দ ও অবসর—সব ক্ষেত্রেই আল্লাহর ভয় রাখার প্রয়োজন আছে। এতে বোঝা যায়, দ্বীন শুধু ইবাদতের জায়গায় নয়; মানুষের অভ্যাস, লেনদেন ও বিনোদনের ক্ষেত্রেও পথ দেখায়।"},"teachings":["মদ, জুয়া ও বাদ্যযন্ত্র থেকে সতর্ক থাকার নির্দেশ এসেছে।","বিনোদন হলেও হারামের সীমা মানতে হবে।","জুয়া লোভ ও ক্ষতির পথ খুলে দিতে পারে।","আল্লাহর বিধানকে আনন্দের অজুহাতে হালকা করা ঠিক নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
-        </is>
-      </c>
-      <c r="E198" s="4" t="n"/>
-    </row>
-    <row r="199" ht="46" customHeight="1">
-      <c r="A199" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C199" s="4" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | গায়িকা নর্তকী, গান-বাজনা ও হারাম উপার্জন","description":"$book_name$ $hadith_number$ - $chapter_name$. গায়িকা-নর্তকী কেনাবেচা, গান-বাজনা শেখানো এবং এ পথের উপার্জন সম্পর্কে কঠোর নিষেধ এসেছে।"},"heading":{"title":"গায়িকা নর্তকী ও গান-বাজনার উপার্জন সম্পর্কে হাদিস","description":"এই হাদিসে গায়িকা নর্তকীদের কেনাবেচা, তাদের গান-বাজনা ও বাদ্যযন্ত্র শেখানো এবং তাদের উপার্জন সম্পর্কে নিষেধ এসেছে। রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তাদের বিক্রি করো না, ক্রয় করো না, তাদের গান-বাজনা ও বাদ্যযন্ত্র শেখিও না, এবং তাদের উপার্জন হারাম। এখানে মূল শিক্ষা হলো, শুধু নিজের কাজ নয়, হারামের আয়োজন, প্রশিক্ষণ ও আয়ের পথ থেকেও বাঁচতে হবে। কোনো কাজ যদি মানুষকে অশ্লীলতা, নাচ-গান বা হারাম বিনোদনের দিকে নেয়, তবে সেটিকে পেশা বানানো নিরাপদ নয়। হাদিসটি উপার্জনকে হালাল রাখার এবং বিনোদনের নামে সীমা না ভাঙার শিক্ষা দেয়। তাই শিল্প, পেশা বা বিনোদনের নামে এমন পথ নেওয়া যাবে না যা হারামের দিকে টেনে নেয়।"},"teachings":["হারাম বিনোদনের আয়োজন থেকেও দূরে থাকা দরকার।","গান-বাজনা শেখানো ও এর আয় সম্পর্কে নিষেধ এসেছে।","উপার্জন হালাল রাখা ঈমানি জীবনের অংশ।","নিজে না করলেও হারামের সহায়তা থেকে সতর্ক থাকতে হবে।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
-        </is>
-      </c>
-      <c r="E199" s="4" t="n"/>
-    </row>
-    <row r="200" ht="46" customHeight="1">
-      <c r="A200" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B200" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C200" s="4" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="D200" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | বাদ্যযন্ত্রের শব্দ থেকে বাঁচার চেষ্টা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইবনু উমর (রাঃ) বাদ্যযন্ত্রের শব্দ শুনে কানে আঙুল দিলেন এবং নবীজির একই আমলের কথা জানালেন।"},"heading":{"title":"বাদ্যযন্ত্রের শব্দ থেকে দূরে থাকা: ইবনু উমর (রাঃ)-এর বর্ণনা","description":"এই হাদিসে একটি বাস্তব ঘটনা এসেছে। ইবনু উমর (রাঃ) বাদ্যযন্ত্রের শব্দ শুনে দুই কানে দুই আঙুল ঢুকিয়ে রাস্তা থেকে সরে গেলেন। পরে নাফে‘কে জিজ্ঞেস করলেন, তিনি কিছু শুনতে পাচ্ছেন কি না। যখন নাফে‘ বললেন, না, তখন তিনি আঙুল বের করলেন এবং জানালেন যে তিনি একদা রাসূল (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর সঙ্গে ছিলেন; নবীজি এমন শব্দ শুনে একই কাজ করেছিলেন। হাদিসের সঙ্গে দেওয়া ব্যাখ্যায়ও বলা হয়েছে, গান-বাজনা ও বাদ্যযন্ত্রের শব্দ যেন কানে না আসে, সে জন্য সম্ভবপর চেষ্টা করতে হবে। তাই শিক্ষা হলো, হারাম শব্দের পরিবেশ এলে সাধ্যের মধ্যে সরে যাওয়া বা বাঁচার চেষ্টা করা। এতে বোঝা যায়, গুনাহ থেকে বাঁচা শুধু মনে অপছন্দ করা নয়; অনেক সময় বাস্তব পদক্ষেপও দরকার।"},"teachings":["বাদ্যযন্ত্রের শব্দ থেকে বাঁচার চেষ্টা করা উচিত।","সাহাবিরা নবীজির আমল দেখে তা অনুসরণ করতেন।","হারাম পরিবেশ এলে সাধ্যের মধ্যে সরে যাওয়া ভালো।","শুধু শোনা নয়, শোনার পরিবেশ থেকেও সতর্ক থাকা দরকার।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"},{"id":"80","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"}]}</t>
-        </is>
-      </c>
-      <c r="E200" s="4" t="n"/>
-    </row>
-    <row r="201" ht="46" customHeight="1">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B201" s="4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C201" s="4" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="D201" s="4" t="inlineStr">
-        <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | মদ, গায়িকা ও বাদ্যযন্ত্রে মত্ততার গজব","description":"$book_name$ $hadith_number$ - $chapter_name$. মদ, গায়িকা নিয়ে নাচ-গান ও বাদ্যযন্ত্রে ডুবে থাকার কারণে তিন ধরনের ভয়াবহ বিপদের সতর্কতা।"},"heading":{"title":"মদ, নাচ-গান ও বাদ্যযন্ত্র: ভয়াবহ বিপদের হাদিস","description":"এই হাদিসটি মদ, গায়িকা এবং বাদ্যযন্ত্রের ফিতনা সম্পর্কে স্পষ্ট সতর্কতা দেয়। নবী করীম (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, যখন তাঁর উম্মত নেশাদার দ্রব্য পান করবে, গায়িকাদের নিয়ে নাচ-গানে মত্ত হবে এবং বাদ্যযন্ত্র নিয়ে ব্যস্ত হবে, তখন তিনটি ভয়াবহ বিপদ নেমে আসবে। সেগুলো হলো—ভূমি ধসে যাওয়া, উপর থেকে বা কোনো জাতির পক্ষ থেকে যুলুম চাপিয়ে দেওয়া, এবং অনেকের আকার-আকৃতি বিকৃত করা। হাদিসের ভাষা কঠোর, তাই এর বার্তাও গভীর: হারাম আনন্দকে সাধারণ বানানো মুমিনের পথ নয়। মদ, নাচ-গান ও বাদ্যযন্ত্রের প্রতি আসক্তি থেকে নিজেকে এবং পরিবারকে সতর্ক রাখা দরকার। তাই এই হাদিস শুধু ভয় দেখায় না; এটি মানুষকে নিজের জীবনযাপন নতুন করে যাচাই করতেও ডাকে।"},"teachings":["মদপান ও হারাম বিনোদন বড় বিপদের কারণ হতে পারে।","গায়িকা ও নাচ-গানে মত্ততা থেকে সতর্ক করা হয়েছে।","বাদ্যযন্ত্রে ব্যস্ততা হাদিসে নিন্দিতভাবে এসেছে।","হারামকে আনন্দের নামে স্বাভাবিক বানানো উচিত নয়।"],"related_hadiths":[{"id":"5590","book_id":"1","slug":"bukhari","label":"সহীহ বুখারী"},{"id":"4924","book_id":"4","slug":"dawud","label":"সুনান আবু দাউদ"},{"id":"3388","book_id":"6","slug":"majah","label":"সুনান ইবনে মাজাহ"}]}</t>
-        </is>
-      </c>
-      <c r="E201" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
